--- a/BAJAJ_GROUP_Technical_Metrics.xlsx
+++ b/BAJAJ_GROUP_Technical_Metrics.xlsx
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="264" uniqueCount="73">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="288" uniqueCount="78">
   <si>
     <t>Symbol</t>
   </si>
@@ -163,12 +163,12 @@
     <t>No</t>
   </si>
   <si>
+    <t>DOWN</t>
+  </si>
+  <si>
     <t>UP</t>
   </si>
   <si>
-    <t>DOWN</t>
-  </si>
-  <si>
     <t>▶  SIGNAL EVENTS (vs Previous Run)</t>
   </si>
   <si>
@@ -190,16 +190,31 @@
     <t>RSI Momentum</t>
   </si>
   <si>
-    <t>51.8 → 48.9</t>
+    <t>54.4 → 48.4</t>
   </si>
   <si>
     <t>🔴 BEARISH</t>
   </si>
   <si>
-    <t>51.8</t>
-  </si>
-  <si>
-    <t>48.9</t>
+    <t>54.4</t>
+  </si>
+  <si>
+    <t>48.4</t>
+  </si>
+  <si>
+    <t>20 DMA &gt; 50 DMA</t>
+  </si>
+  <si>
+    <t>Yes → No</t>
+  </si>
+  <si>
+    <t>54.6 → 46.1</t>
+  </si>
+  <si>
+    <t>54.6</t>
+  </si>
+  <si>
+    <t>46.1</t>
   </si>
   <si>
     <t>▶  NUMERIC METRIC CHANGES (vs Previous Run)</t>
@@ -783,8 +798,8 @@
     <col min="13" max="13" width="10.7109375" customWidth="1"/>
     <col min="14" max="14" width="11.7109375" customWidth="1"/>
     <col min="15" max="15" width="10.7109375" customWidth="1"/>
-    <col min="16" max="16" width="9.7109375" customWidth="1"/>
-    <col min="17" max="19" width="10.7109375" customWidth="1"/>
+    <col min="16" max="17" width="9.7109375" customWidth="1"/>
+    <col min="18" max="19" width="10.7109375" customWidth="1"/>
     <col min="20" max="20" width="22.7109375" customWidth="1"/>
     <col min="21" max="21" width="9.7109375" customWidth="1"/>
     <col min="22" max="22" width="10.7109375" customWidth="1"/>
@@ -924,10 +939,10 @@
         <v>44</v>
       </c>
       <c r="C2">
-        <v>11678</v>
+        <v>11424</v>
       </c>
       <c r="D2">
-        <v>-0.76</v>
+        <v>-2.18</v>
       </c>
       <c r="E2">
         <v>12361</v>
@@ -936,46 +951,46 @@
         <v>8506.780000000001</v>
       </c>
       <c r="G2">
-        <v>-5.53</v>
+        <v>-7.58</v>
       </c>
       <c r="H2">
-        <v>37.28</v>
+        <v>34.29</v>
       </c>
       <c r="I2">
-        <v>-2.02</v>
+        <v>-3.19</v>
       </c>
       <c r="J2">
-        <v>0.15</v>
+        <v>-2.36</v>
       </c>
       <c r="K2">
-        <v>17.45</v>
+        <v>14.94</v>
       </c>
       <c r="L2">
-        <v>26.21</v>
+        <v>25.32</v>
       </c>
       <c r="M2">
-        <v>28.79</v>
+        <v>27.65</v>
       </c>
       <c r="N2">
         <v>85</v>
       </c>
       <c r="O2">
-        <v>79</v>
+        <v>81</v>
       </c>
       <c r="P2">
-        <v>11783.2</v>
+        <v>11708</v>
       </c>
       <c r="Q2">
-        <v>11845.1</v>
+        <v>11831.3</v>
       </c>
       <c r="R2">
-        <v>11346.93</v>
+        <v>11374.68</v>
       </c>
       <c r="S2">
-        <v>9993.25</v>
+        <v>10005.18</v>
       </c>
       <c r="T2">
-        <v>16.86</v>
+        <v>14.18</v>
       </c>
       <c r="U2" t="s">
         <v>45</v>
@@ -990,43 +1005,43 @@
         <v>3</v>
       </c>
       <c r="Y2">
-        <v>48.9</v>
+        <v>41.71</v>
       </c>
       <c r="Z2">
-        <v>113.69</v>
+        <v>72.33</v>
       </c>
       <c r="AA2">
-        <v>182.21</v>
+        <v>160.23</v>
       </c>
       <c r="AB2">
-        <v>-68.52</v>
+        <v>-87.90000000000001</v>
       </c>
       <c r="AC2">
         <v>0</v>
       </c>
       <c r="AD2">
-        <v>2.4</v>
+        <v>1.2</v>
       </c>
       <c r="AE2">
-        <v>215.57</v>
+        <v>221.1</v>
       </c>
       <c r="AF2">
-        <v>-2.16</v>
+        <v>6.11</v>
       </c>
       <c r="AG2">
-        <v>12219.14</v>
+        <v>12246.03</v>
       </c>
       <c r="AH2">
-        <v>11471.06</v>
+        <v>11416.57</v>
       </c>
       <c r="AI2">
-        <v>11623.52</v>
+        <v>12225.81</v>
       </c>
       <c r="AJ2" t="s">
         <v>47</v>
       </c>
       <c r="AK2">
-        <v>27.9</v>
+        <v>28.8</v>
       </c>
     </row>
     <row r="3" spans="1:37">
@@ -1037,58 +1052,58 @@
         <v>44</v>
       </c>
       <c r="C3">
-        <v>520.5</v>
+        <v>503.8</v>
       </c>
       <c r="D3">
-        <v>-0.75</v>
+        <v>-3.21</v>
       </c>
       <c r="E3">
         <v>670.25</v>
       </c>
       <c r="F3">
-        <v>222.01</v>
+        <v>223.92</v>
       </c>
       <c r="G3">
-        <v>-22.34</v>
+        <v>-24.83</v>
       </c>
       <c r="H3">
-        <v>134.45</v>
+        <v>124.99</v>
       </c>
       <c r="I3">
-        <v>0.57</v>
+        <v>-4.22</v>
       </c>
       <c r="J3">
-        <v>-1.36</v>
+        <v>0.64</v>
       </c>
       <c r="K3">
-        <v>-12.14</v>
+        <v>-16.1</v>
       </c>
       <c r="L3">
-        <v>134.44</v>
+        <v>126.93</v>
       </c>
       <c r="M3">
-        <v>16.95</v>
+        <v>16.01</v>
       </c>
       <c r="N3">
         <v>99</v>
       </c>
       <c r="O3">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="P3">
-        <v>521.3</v>
+        <v>516.86</v>
       </c>
       <c r="Q3">
-        <v>490.24</v>
+        <v>491.36</v>
       </c>
       <c r="R3">
-        <v>531.28</v>
+        <v>528.97</v>
       </c>
       <c r="S3">
-        <v>436.66</v>
+        <v>437.85</v>
       </c>
       <c r="T3">
-        <v>19.2</v>
+        <v>15.06</v>
       </c>
       <c r="U3" t="s">
         <v>46</v>
@@ -1103,43 +1118,43 @@
         <v>2</v>
       </c>
       <c r="Y3">
-        <v>54.35</v>
+        <v>48.39</v>
       </c>
       <c r="Z3">
-        <v>-0.65</v>
+        <v>-0.9</v>
       </c>
       <c r="AA3">
-        <v>-8.6</v>
+        <v>-7.06</v>
       </c>
       <c r="AB3">
-        <v>7.95</v>
+        <v>6.16</v>
       </c>
       <c r="AC3">
-        <v>93.27</v>
+        <v>84.86</v>
       </c>
       <c r="AD3">
-        <v>92.47</v>
+        <v>89.84999999999999</v>
       </c>
       <c r="AE3">
-        <v>20.62</v>
+        <v>21.5</v>
       </c>
       <c r="AF3">
-        <v>-9.779999999999999</v>
+        <v>-20</v>
       </c>
       <c r="AG3">
-        <v>539.3</v>
+        <v>540.59</v>
       </c>
       <c r="AH3">
-        <v>441.18</v>
+        <v>442.13</v>
       </c>
       <c r="AI3">
         <v>460.99</v>
       </c>
       <c r="AJ3" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="AK3">
-        <v>35.5</v>
+        <v>31.33</v>
       </c>
     </row>
     <row r="4" spans="1:37">
@@ -1150,10 +1165,10 @@
         <v>44</v>
       </c>
       <c r="C4">
-        <v>335.3</v>
+        <v>328.4</v>
       </c>
       <c r="D4">
-        <v>-0.73</v>
+        <v>-2.06</v>
       </c>
       <c r="E4">
         <v>604.85</v>
@@ -1162,49 +1177,49 @@
         <v>303.75</v>
       </c>
       <c r="G4">
-        <v>-44.56</v>
+        <v>-45.71</v>
       </c>
       <c r="H4">
-        <v>10.39</v>
+        <v>8.119999999999999</v>
       </c>
       <c r="I4">
-        <v>1.25</v>
+        <v>-4</v>
       </c>
       <c r="J4">
-        <v>-5.97</v>
+        <v>-9.380000000000001</v>
       </c>
       <c r="K4">
-        <v>4.63</v>
+        <v>1.67</v>
       </c>
       <c r="L4">
-        <v>-40.99</v>
+        <v>-43.94</v>
       </c>
       <c r="M4">
-        <v>-22.9</v>
+        <v>-24.24</v>
       </c>
       <c r="N4">
         <v>15</v>
       </c>
       <c r="O4">
-        <v>23</v>
+        <v>19</v>
       </c>
       <c r="P4">
-        <v>338.98</v>
+        <v>336.24</v>
       </c>
       <c r="Q4">
-        <v>339.96</v>
+        <v>338.26</v>
       </c>
       <c r="R4">
-        <v>339.9</v>
+        <v>339.94</v>
       </c>
       <c r="S4">
-        <v>378.51</v>
+        <v>377.71</v>
       </c>
       <c r="T4">
-        <v>-11.41</v>
+        <v>-13.05</v>
       </c>
       <c r="U4" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="V4" t="s">
         <v>46</v>
@@ -1213,46 +1228,46 @@
         <v>46</v>
       </c>
       <c r="X4">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Y4">
-        <v>46.52</v>
+        <v>41.76</v>
       </c>
       <c r="Z4">
-        <v>-2.26</v>
+        <v>-2.79</v>
       </c>
       <c r="AA4">
-        <v>-2.19</v>
+        <v>-2.31</v>
       </c>
       <c r="AB4">
-        <v>-0.07000000000000001</v>
+        <v>-0.49</v>
       </c>
       <c r="AC4">
-        <v>76.81</v>
+        <v>60.09</v>
       </c>
       <c r="AD4">
-        <v>79.2</v>
+        <v>72.18000000000001</v>
       </c>
       <c r="AE4">
-        <v>10.57</v>
+        <v>10.82</v>
       </c>
       <c r="AF4">
-        <v>-41.68</v>
+        <v>-24.2</v>
       </c>
       <c r="AG4">
-        <v>361.7</v>
+        <v>357.82</v>
       </c>
       <c r="AH4">
-        <v>318.21</v>
+        <v>318.69</v>
       </c>
       <c r="AI4">
         <v>357.31</v>
       </c>
       <c r="AJ4" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="AK4">
-        <v>24.13</v>
+        <v>21.21</v>
       </c>
     </row>
     <row r="5" spans="1:37">
@@ -1263,10 +1278,10 @@
         <v>44</v>
       </c>
       <c r="C5">
-        <v>1913.5</v>
+        <v>1855.5</v>
       </c>
       <c r="D5">
-        <v>-1.39</v>
+        <v>-3.03</v>
       </c>
       <c r="E5">
         <v>2176.6</v>
@@ -1275,46 +1290,46 @@
         <v>1631.8</v>
       </c>
       <c r="G5">
-        <v>-12.09</v>
+        <v>-14.75</v>
       </c>
       <c r="H5">
-        <v>17.26</v>
+        <v>13.71</v>
       </c>
       <c r="I5">
-        <v>-2.87</v>
+        <v>-4.29</v>
       </c>
       <c r="J5">
-        <v>-5.51</v>
+        <v>-7.61</v>
       </c>
       <c r="K5">
-        <v>9.33</v>
+        <v>3.82</v>
       </c>
       <c r="L5">
-        <v>-5.52</v>
+        <v>-8.960000000000001</v>
       </c>
       <c r="M5">
-        <v>2.51</v>
+        <v>2.01</v>
       </c>
       <c r="N5">
         <v>43</v>
       </c>
       <c r="O5">
-        <v>57</v>
+        <v>54</v>
       </c>
       <c r="P5">
-        <v>1931.54</v>
+        <v>1914.92</v>
       </c>
       <c r="Q5">
-        <v>1985.41</v>
+        <v>1977.93</v>
       </c>
       <c r="R5">
-        <v>1960.94</v>
+        <v>1960.64</v>
       </c>
       <c r="S5">
-        <v>1902.43</v>
+        <v>1901.28</v>
       </c>
       <c r="T5">
-        <v>0.58</v>
+        <v>-2.41</v>
       </c>
       <c r="U5" t="s">
         <v>45</v>
@@ -1326,46 +1341,46 @@
         <v>45</v>
       </c>
       <c r="X5">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="Y5">
-        <v>37.41</v>
+        <v>29.72</v>
       </c>
       <c r="Z5">
-        <v>-11.46</v>
+        <v>-18.86</v>
       </c>
       <c r="AA5">
-        <v>1.7</v>
+        <v>-2.41</v>
       </c>
       <c r="AB5">
-        <v>-13.16</v>
+        <v>-16.44</v>
       </c>
       <c r="AC5">
         <v>6.29</v>
       </c>
       <c r="AD5">
-        <v>4.19</v>
+        <v>6.29</v>
       </c>
       <c r="AE5">
-        <v>35.23</v>
+        <v>38.07</v>
       </c>
       <c r="AF5">
-        <v>18.72</v>
+        <v>-23.58</v>
       </c>
       <c r="AG5">
-        <v>2056.25</v>
+        <v>2068.79</v>
       </c>
       <c r="AH5">
-        <v>1914.57</v>
+        <v>1887.08</v>
       </c>
       <c r="AI5">
-        <v>2016.18</v>
+        <v>2007.27</v>
       </c>
       <c r="AJ5" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="AK5">
-        <v>48.65</v>
+        <v>53.28</v>
       </c>
     </row>
     <row r="6" spans="1:37">
@@ -1376,10 +1391,10 @@
         <v>44</v>
       </c>
       <c r="C6">
-        <v>11134</v>
+        <v>11100</v>
       </c>
       <c r="D6">
-        <v>1.29</v>
+        <v>-0.31</v>
       </c>
       <c r="E6">
         <v>13595.75</v>
@@ -1388,46 +1403,46 @@
         <v>8746</v>
       </c>
       <c r="G6">
-        <v>-18.11</v>
+        <v>-18.36</v>
       </c>
       <c r="H6">
-        <v>27.3</v>
+        <v>26.92</v>
       </c>
       <c r="I6">
-        <v>-0.25</v>
+        <v>1.31</v>
       </c>
       <c r="J6">
-        <v>-3.18</v>
+        <v>-3.27</v>
       </c>
       <c r="K6">
-        <v>8.24</v>
+        <v>6.08</v>
       </c>
       <c r="L6">
-        <v>-14.35</v>
+        <v>-14.55</v>
       </c>
       <c r="M6">
-        <v>22.86</v>
+        <v>22.63</v>
       </c>
       <c r="N6">
         <v>29</v>
       </c>
       <c r="O6">
-        <v>51</v>
+        <v>53</v>
       </c>
       <c r="P6">
-        <v>11041.2</v>
+        <v>11070</v>
       </c>
       <c r="Q6">
-        <v>11253.65</v>
+        <v>11234.9</v>
       </c>
       <c r="R6">
-        <v>11059.78</v>
+        <v>11065.4</v>
       </c>
       <c r="S6">
-        <v>10687.52</v>
+        <v>10684.35</v>
       </c>
       <c r="T6">
-        <v>4.18</v>
+        <v>3.89</v>
       </c>
       <c r="U6" t="s">
         <v>45</v>
@@ -1442,43 +1457,43 @@
         <v>3</v>
       </c>
       <c r="Y6">
-        <v>48.63</v>
+        <v>47.66</v>
       </c>
       <c r="Z6">
-        <v>-26.91</v>
+        <v>-29.32</v>
       </c>
       <c r="AA6">
-        <v>22.74</v>
+        <v>12.33</v>
       </c>
       <c r="AB6">
-        <v>-49.65</v>
+        <v>-41.65</v>
       </c>
       <c r="AC6">
-        <v>19.79</v>
+        <v>21.98</v>
       </c>
       <c r="AD6">
-        <v>15.12</v>
+        <v>18.61</v>
       </c>
       <c r="AE6">
-        <v>229.23</v>
+        <v>223.43</v>
       </c>
       <c r="AF6">
-        <v>12.13</v>
+        <v>23.5</v>
       </c>
       <c r="AG6">
-        <v>11624.41</v>
+        <v>11596.34</v>
       </c>
       <c r="AH6">
-        <v>10882.89</v>
+        <v>10873.46</v>
       </c>
       <c r="AI6">
         <v>10787.84</v>
       </c>
       <c r="AJ6" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="AK6">
-        <v>21.1</v>
+        <v>18.33</v>
       </c>
     </row>
     <row r="7" spans="1:37">
@@ -1489,10 +1504,10 @@
         <v>44</v>
       </c>
       <c r="C7">
-        <v>1034.5</v>
+        <v>1009.2</v>
       </c>
       <c r="D7">
-        <v>-0.86</v>
+        <v>-2.45</v>
       </c>
       <c r="E7">
         <v>1158.8</v>
@@ -1501,97 +1516,97 @@
         <v>801.55</v>
       </c>
       <c r="G7">
-        <v>-10.73</v>
+        <v>-12.91</v>
       </c>
       <c r="H7">
-        <v>29.06</v>
+        <v>25.91</v>
       </c>
       <c r="I7">
-        <v>-2.45</v>
+        <v>-4.79</v>
       </c>
       <c r="J7">
-        <v>-5.16</v>
+        <v>-7.16</v>
       </c>
       <c r="K7">
-        <v>9.779999999999999</v>
+        <v>5.16</v>
       </c>
       <c r="L7">
-        <v>9.08</v>
+        <v>4.26</v>
       </c>
       <c r="M7">
-        <v>7.22</v>
+        <v>6.77</v>
       </c>
       <c r="N7">
         <v>71</v>
       </c>
       <c r="O7">
-        <v>67</v>
+        <v>65</v>
       </c>
       <c r="P7">
-        <v>1046.28</v>
+        <v>1036.12</v>
       </c>
       <c r="Q7">
-        <v>1068.69</v>
+        <v>1064.69</v>
       </c>
       <c r="R7">
-        <v>1067.35</v>
+        <v>1066.95</v>
       </c>
       <c r="S7">
         <v>977.89</v>
       </c>
       <c r="T7">
-        <v>5.79</v>
+        <v>3.2</v>
       </c>
       <c r="U7" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="V7" t="s">
         <v>45</v>
       </c>
       <c r="W7" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="X7">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="Y7">
-        <v>38.17</v>
+        <v>31.65</v>
       </c>
       <c r="Z7">
-        <v>-8.550000000000001</v>
+        <v>-11.57</v>
       </c>
       <c r="AA7">
-        <v>-3.22</v>
+        <v>-4.89</v>
       </c>
       <c r="AB7">
-        <v>-5.33</v>
+        <v>-6.68</v>
       </c>
       <c r="AC7">
         <v>4.72</v>
       </c>
       <c r="AD7">
-        <v>10.58</v>
+        <v>6.66</v>
       </c>
       <c r="AE7">
-        <v>20.68</v>
+        <v>21.57</v>
       </c>
       <c r="AF7">
-        <v>18.32</v>
+        <v>22.75</v>
       </c>
       <c r="AG7">
-        <v>1108.54</v>
+        <v>1111.33</v>
       </c>
       <c r="AH7">
-        <v>1028.84</v>
+        <v>1018.04</v>
       </c>
       <c r="AI7">
-        <v>1087.09</v>
+        <v>1086.75</v>
       </c>
       <c r="AJ7" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="AK7">
-        <v>38.61</v>
+        <v>42.5</v>
       </c>
     </row>
     <row r="8" spans="1:37">
@@ -1602,10 +1617,10 @@
         <v>44</v>
       </c>
       <c r="C8">
-        <v>139.48</v>
+        <v>135.62</v>
       </c>
       <c r="D8">
-        <v>-2.17</v>
+        <v>-2.77</v>
       </c>
       <c r="E8">
         <v>148.95</v>
@@ -1614,46 +1629,46 @@
         <v>115.96</v>
       </c>
       <c r="G8">
-        <v>-6.36</v>
+        <v>-8.949999999999999</v>
       </c>
       <c r="H8">
-        <v>20.28</v>
+        <v>16.95</v>
       </c>
       <c r="I8">
-        <v>3.75</v>
+        <v>-0.93</v>
       </c>
       <c r="J8">
-        <v>2.86</v>
+        <v>1.1</v>
       </c>
       <c r="K8">
-        <v>2.85</v>
+        <v>0.1</v>
       </c>
       <c r="L8">
-        <v>5.97</v>
+        <v>0.42</v>
       </c>
       <c r="M8">
-        <v>0.36</v>
+        <v>-0.19</v>
       </c>
       <c r="N8">
         <v>57</v>
       </c>
       <c r="O8">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="P8">
-        <v>139.26</v>
+        <v>139</v>
       </c>
       <c r="Q8">
-        <v>136.56</v>
+        <v>136.64</v>
       </c>
       <c r="R8">
-        <v>138.13</v>
+        <v>138.19</v>
       </c>
       <c r="S8">
-        <v>133.8</v>
+        <v>133.81</v>
       </c>
       <c r="T8">
-        <v>4.24</v>
+        <v>1.35</v>
       </c>
       <c r="U8" t="s">
         <v>46</v>
@@ -1668,43 +1683,43 @@
         <v>2</v>
       </c>
       <c r="Y8">
-        <v>54.62</v>
+        <v>46.1</v>
       </c>
       <c r="Z8">
-        <v>0.31</v>
+        <v>0.1</v>
       </c>
       <c r="AA8">
-        <v>-0.37</v>
+        <v>-0.27</v>
       </c>
       <c r="AB8">
-        <v>0.67</v>
+        <v>0.38</v>
       </c>
       <c r="AC8">
-        <v>88.44</v>
+        <v>65.55</v>
       </c>
       <c r="AD8">
-        <v>96.15000000000001</v>
+        <v>84.66</v>
       </c>
       <c r="AE8">
-        <v>4.03</v>
+        <v>4.34</v>
       </c>
       <c r="AF8">
-        <v>-10.14</v>
+        <v>-36.4</v>
       </c>
       <c r="AG8">
-        <v>141.02</v>
+        <v>140.98</v>
       </c>
       <c r="AH8">
-        <v>132.1</v>
+        <v>132.29</v>
       </c>
       <c r="AI8">
         <v>131.91</v>
       </c>
       <c r="AJ8" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="AK8">
-        <v>32.61</v>
+        <v>31.02</v>
       </c>
     </row>
   </sheetData>
@@ -1845,7 +1860,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:F62"/>
+  <dimension ref="A1:F66"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="16.7109375" customWidth="1"/>
@@ -1885,7 +1900,7 @@
     </row>
     <row r="3" spans="1:6">
       <c r="A3" s="4" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="B3" s="4" t="s">
         <v>55</v>
@@ -1903,452 +1918,464 @@
         <v>59</v>
       </c>
     </row>
+    <row r="4" spans="1:6">
+      <c r="A4" s="4" t="s">
+        <v>39</v>
+      </c>
+      <c r="B4" s="4" t="s">
+        <v>60</v>
+      </c>
+      <c r="C4" s="4" t="s">
+        <v>61</v>
+      </c>
+      <c r="D4" s="4" t="s">
+        <v>57</v>
+      </c>
+      <c r="E4" s="4" t="s">
+        <v>45</v>
+      </c>
+      <c r="F4" s="4" t="s">
+        <v>46</v>
+      </c>
+    </row>
     <row r="5" spans="1:6">
-      <c r="A5" s="2" t="s">
+      <c r="A5" s="4" t="s">
+        <v>42</v>
+      </c>
+      <c r="B5" s="4" t="s">
+        <v>22</v>
+      </c>
+      <c r="C5" s="4" t="s">
+        <v>61</v>
+      </c>
+      <c r="D5" s="4" t="s">
+        <v>57</v>
+      </c>
+      <c r="E5" s="4" t="s">
+        <v>45</v>
+      </c>
+      <c r="F5" s="4" t="s">
+        <v>46</v>
+      </c>
+    </row>
+    <row r="6" spans="1:6">
+      <c r="A6" s="4" t="s">
+        <v>42</v>
+      </c>
+      <c r="B6" s="4" t="s">
         <v>60</v>
       </c>
-      <c r="B5" s="2"/>
-      <c r="C5" s="2"/>
-      <c r="D5" s="2"/>
-      <c r="E5" s="2"/>
-    </row>
-    <row r="6" spans="1:6">
-      <c r="A6" s="3" t="s">
+      <c r="C6" s="4" t="s">
+        <v>61</v>
+      </c>
+      <c r="D6" s="4" t="s">
+        <v>57</v>
+      </c>
+      <c r="E6" s="4" t="s">
+        <v>45</v>
+      </c>
+      <c r="F6" s="4" t="s">
+        <v>46</v>
+      </c>
+    </row>
+    <row r="7" spans="1:6">
+      <c r="A7" s="4" t="s">
+        <v>43</v>
+      </c>
+      <c r="B7" s="4" t="s">
+        <v>55</v>
+      </c>
+      <c r="C7" s="4" t="s">
+        <v>62</v>
+      </c>
+      <c r="D7" s="4" t="s">
+        <v>57</v>
+      </c>
+      <c r="E7" s="4" t="s">
+        <v>63</v>
+      </c>
+      <c r="F7" s="4" t="s">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="9" spans="1:6">
+      <c r="A9" s="2" t="s">
+        <v>65</v>
+      </c>
+      <c r="B9" s="2"/>
+      <c r="C9" s="2"/>
+      <c r="D9" s="2"/>
+      <c r="E9" s="2"/>
+    </row>
+    <row r="10" spans="1:6">
+      <c r="A10" s="3" t="s">
         <v>0</v>
       </c>
-      <c r="B6" s="3" t="s">
-        <v>61</v>
-      </c>
-      <c r="C6" s="3" t="s">
-        <v>62</v>
-      </c>
-      <c r="D6" s="3" t="s">
-        <v>63</v>
-      </c>
-      <c r="E6" s="3" t="s">
-        <v>64</v>
-      </c>
-    </row>
-    <row r="7" spans="1:6">
-      <c r="A7" s="5" t="s">
-        <v>37</v>
-      </c>
-      <c r="B7" s="5" t="s">
-        <v>9</v>
-      </c>
-      <c r="C7" s="6">
-        <v>0.58</v>
-      </c>
-      <c r="D7" s="6">
-        <v>0.15</v>
-      </c>
-      <c r="E7" s="7">
-        <v>-0.43</v>
-      </c>
-    </row>
-    <row r="8" spans="1:6">
-      <c r="A8" s="5" t="s">
-        <v>38</v>
-      </c>
-      <c r="B8" s="5" t="s">
-        <v>9</v>
-      </c>
-      <c r="C8" s="6">
-        <v>-2.56</v>
-      </c>
-      <c r="D8" s="6">
-        <v>-1.36</v>
-      </c>
-      <c r="E8" s="8">
-        <v>1.2</v>
-      </c>
-    </row>
-    <row r="9" spans="1:6">
-      <c r="A9" s="5" t="s">
-        <v>39</v>
-      </c>
-      <c r="B9" s="5" t="s">
-        <v>9</v>
-      </c>
-      <c r="C9" s="6">
-        <v>-7.2</v>
-      </c>
-      <c r="D9" s="6">
-        <v>-5.97</v>
-      </c>
-      <c r="E9" s="8">
-        <v>1.23</v>
-      </c>
-    </row>
-    <row r="10" spans="1:6">
-      <c r="A10" s="5" t="s">
-        <v>40</v>
-      </c>
-      <c r="B10" s="5" t="s">
-        <v>9</v>
-      </c>
-      <c r="C10" s="6">
-        <v>-3.96</v>
-      </c>
-      <c r="D10" s="6">
-        <v>-5.51</v>
-      </c>
-      <c r="E10" s="7">
-        <v>-1.55</v>
+      <c r="B10" s="3" t="s">
+        <v>66</v>
+      </c>
+      <c r="C10" s="3" t="s">
+        <v>67</v>
+      </c>
+      <c r="D10" s="3" t="s">
+        <v>68</v>
+      </c>
+      <c r="E10" s="3" t="s">
+        <v>69</v>
       </c>
     </row>
     <row r="11" spans="1:6">
       <c r="A11" s="5" t="s">
-        <v>41</v>
+        <v>37</v>
       </c>
       <c r="B11" s="5" t="s">
         <v>9</v>
       </c>
       <c r="C11" s="6">
-        <v>-5.07</v>
+        <v>0.15</v>
       </c>
       <c r="D11" s="6">
-        <v>-3.18</v>
-      </c>
-      <c r="E11" s="8">
-        <v>1.89</v>
+        <v>-2.36</v>
+      </c>
+      <c r="E11" s="7">
+        <v>-2.51</v>
       </c>
     </row>
     <row r="12" spans="1:6">
       <c r="A12" s="5" t="s">
-        <v>42</v>
+        <v>38</v>
       </c>
       <c r="B12" s="5" t="s">
         <v>9</v>
       </c>
       <c r="C12" s="6">
-        <v>-4.63</v>
+        <v>-1.36</v>
       </c>
       <c r="D12" s="6">
-        <v>-5.16</v>
-      </c>
-      <c r="E12" s="7">
-        <v>-0.53</v>
+        <v>0.64</v>
+      </c>
+      <c r="E12" s="8">
+        <v>2</v>
       </c>
     </row>
     <row r="13" spans="1:6">
       <c r="A13" s="5" t="s">
-        <v>43</v>
+        <v>39</v>
       </c>
       <c r="B13" s="5" t="s">
         <v>9</v>
       </c>
       <c r="C13" s="6">
-        <v>5.17</v>
+        <v>-5.97</v>
       </c>
       <c r="D13" s="6">
-        <v>2.86</v>
+        <v>-9.380000000000001</v>
       </c>
       <c r="E13" s="7">
-        <v>-2.31</v>
+        <v>-3.41</v>
       </c>
     </row>
     <row r="14" spans="1:6">
       <c r="A14" s="5" t="s">
-        <v>37</v>
+        <v>40</v>
       </c>
       <c r="B14" s="5" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="C14" s="6">
-        <v>-1.28</v>
+        <v>-5.51</v>
       </c>
       <c r="D14" s="6">
-        <v>-2.02</v>
+        <v>-7.61</v>
       </c>
       <c r="E14" s="7">
-        <v>-0.74</v>
+        <v>-2.1</v>
       </c>
     </row>
     <row r="15" spans="1:6">
       <c r="A15" s="5" t="s">
-        <v>38</v>
+        <v>41</v>
       </c>
       <c r="B15" s="5" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="C15" s="6">
-        <v>3.05</v>
+        <v>-3.18</v>
       </c>
       <c r="D15" s="6">
-        <v>0.57</v>
+        <v>-3.27</v>
       </c>
       <c r="E15" s="7">
-        <v>-2.48</v>
+        <v>-0.09</v>
       </c>
     </row>
     <row r="16" spans="1:6">
       <c r="A16" s="5" t="s">
-        <v>39</v>
+        <v>42</v>
       </c>
       <c r="B16" s="5" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="C16" s="6">
-        <v>1.06</v>
+        <v>-5.16</v>
       </c>
       <c r="D16" s="6">
-        <v>1.25</v>
-      </c>
-      <c r="E16" s="8">
-        <v>0.19</v>
+        <v>-7.16</v>
+      </c>
+      <c r="E16" s="7">
+        <v>-2</v>
       </c>
     </row>
     <row r="17" spans="1:5">
       <c r="A17" s="5" t="s">
-        <v>40</v>
+        <v>43</v>
       </c>
       <c r="B17" s="5" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="C17" s="6">
-        <v>-2.59</v>
+        <v>2.86</v>
       </c>
       <c r="D17" s="6">
-        <v>-2.87</v>
+        <v>1.1</v>
       </c>
       <c r="E17" s="7">
-        <v>-0.28</v>
+        <v>-1.76</v>
       </c>
     </row>
     <row r="18" spans="1:5">
       <c r="A18" s="5" t="s">
-        <v>41</v>
+        <v>37</v>
       </c>
       <c r="B18" s="5" t="s">
         <v>8</v>
       </c>
       <c r="C18" s="6">
-        <v>-1.55</v>
+        <v>-2.02</v>
       </c>
       <c r="D18" s="6">
-        <v>-0.25</v>
-      </c>
-      <c r="E18" s="8">
-        <v>1.3</v>
+        <v>-3.19</v>
+      </c>
+      <c r="E18" s="7">
+        <v>-1.17</v>
       </c>
     </row>
     <row r="19" spans="1:5">
       <c r="A19" s="5" t="s">
-        <v>42</v>
+        <v>38</v>
       </c>
       <c r="B19" s="5" t="s">
         <v>8</v>
       </c>
       <c r="C19" s="6">
-        <v>-0.52</v>
+        <v>0.57</v>
       </c>
       <c r="D19" s="6">
-        <v>-2.45</v>
+        <v>-4.22</v>
       </c>
       <c r="E19" s="7">
-        <v>-1.93</v>
+        <v>-4.79</v>
       </c>
     </row>
     <row r="20" spans="1:5">
       <c r="A20" s="5" t="s">
-        <v>43</v>
+        <v>39</v>
       </c>
       <c r="B20" s="5" t="s">
         <v>8</v>
       </c>
       <c r="C20" s="6">
-        <v>7.22</v>
+        <v>1.25</v>
       </c>
       <c r="D20" s="6">
-        <v>3.75</v>
+        <v>-4</v>
       </c>
       <c r="E20" s="7">
-        <v>-3.47</v>
+        <v>-5.25</v>
       </c>
     </row>
     <row r="21" spans="1:5">
       <c r="A21" s="5" t="s">
-        <v>37</v>
+        <v>40</v>
       </c>
       <c r="B21" s="5" t="s">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="C21" s="6">
-        <v>26.5</v>
+        <v>-2.87</v>
       </c>
       <c r="D21" s="6">
-        <v>26.21</v>
+        <v>-4.29</v>
       </c>
       <c r="E21" s="7">
-        <v>-0.29</v>
+        <v>-1.42</v>
       </c>
     </row>
     <row r="22" spans="1:5">
       <c r="A22" s="5" t="s">
-        <v>38</v>
+        <v>41</v>
       </c>
       <c r="B22" s="5" t="s">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="C22" s="6">
-        <v>133.93</v>
+        <v>-0.25</v>
       </c>
       <c r="D22" s="6">
-        <v>134.44</v>
+        <v>1.31</v>
       </c>
       <c r="E22" s="8">
-        <v>0.51</v>
+        <v>1.56</v>
       </c>
     </row>
     <row r="23" spans="1:5">
       <c r="A23" s="5" t="s">
-        <v>39</v>
+        <v>42</v>
       </c>
       <c r="B23" s="5" t="s">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="C23" s="6">
-        <v>-40.22</v>
+        <v>-2.45</v>
       </c>
       <c r="D23" s="6">
-        <v>-40.99</v>
+        <v>-4.79</v>
       </c>
       <c r="E23" s="7">
-        <v>-0.77</v>
+        <v>-2.34</v>
       </c>
     </row>
     <row r="24" spans="1:5">
       <c r="A24" s="5" t="s">
-        <v>40</v>
+        <v>43</v>
       </c>
       <c r="B24" s="5" t="s">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="C24" s="6">
-        <v>-3.38</v>
+        <v>3.75</v>
       </c>
       <c r="D24" s="6">
-        <v>-5.52</v>
+        <v>-0.93</v>
       </c>
       <c r="E24" s="7">
-        <v>-2.14</v>
+        <v>-4.68</v>
       </c>
     </row>
     <row r="25" spans="1:5">
       <c r="A25" s="5" t="s">
-        <v>41</v>
+        <v>37</v>
       </c>
       <c r="B25" s="5" t="s">
         <v>11</v>
       </c>
       <c r="C25" s="6">
-        <v>-13.5</v>
+        <v>26.21</v>
       </c>
       <c r="D25" s="6">
-        <v>-14.35</v>
+        <v>25.32</v>
       </c>
       <c r="E25" s="7">
-        <v>-0.85</v>
+        <v>-0.89</v>
       </c>
     </row>
     <row r="26" spans="1:5">
       <c r="A26" s="5" t="s">
-        <v>42</v>
+        <v>38</v>
       </c>
       <c r="B26" s="5" t="s">
         <v>11</v>
       </c>
       <c r="C26" s="6">
-        <v>10.51</v>
+        <v>134.44</v>
       </c>
       <c r="D26" s="6">
-        <v>9.08</v>
+        <v>126.93</v>
       </c>
       <c r="E26" s="7">
-        <v>-1.43</v>
+        <v>-7.51</v>
       </c>
     </row>
     <row r="27" spans="1:5">
       <c r="A27" s="5" t="s">
-        <v>43</v>
+        <v>39</v>
       </c>
       <c r="B27" s="5" t="s">
         <v>11</v>
       </c>
       <c r="C27" s="6">
-        <v>4.64</v>
+        <v>-40.99</v>
       </c>
       <c r="D27" s="6">
-        <v>5.97</v>
-      </c>
-      <c r="E27" s="8">
-        <v>1.33</v>
+        <v>-43.94</v>
+      </c>
+      <c r="E27" s="7">
+        <v>-2.95</v>
       </c>
     </row>
     <row r="28" spans="1:5">
       <c r="A28" s="5" t="s">
-        <v>37</v>
+        <v>40</v>
       </c>
       <c r="B28" s="5" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="C28" s="6">
-        <v>16.94</v>
+        <v>-5.52</v>
       </c>
       <c r="D28" s="6">
-        <v>17.45</v>
-      </c>
-      <c r="E28" s="8">
-        <v>0.51</v>
+        <v>-8.960000000000001</v>
+      </c>
+      <c r="E28" s="7">
+        <v>-3.44</v>
       </c>
     </row>
     <row r="29" spans="1:5">
       <c r="A29" s="5" t="s">
-        <v>38</v>
+        <v>41</v>
       </c>
       <c r="B29" s="5" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="C29" s="6">
-        <v>-11.36</v>
+        <v>-14.35</v>
       </c>
       <c r="D29" s="6">
-        <v>-12.14</v>
+        <v>-14.55</v>
       </c>
       <c r="E29" s="7">
-        <v>-0.78</v>
+        <v>-0.2</v>
       </c>
     </row>
     <row r="30" spans="1:5">
       <c r="A30" s="5" t="s">
-        <v>39</v>
+        <v>42</v>
       </c>
       <c r="B30" s="5" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="C30" s="6">
-        <v>8.619999999999999</v>
+        <v>9.08</v>
       </c>
       <c r="D30" s="6">
-        <v>4.63</v>
+        <v>4.26</v>
       </c>
       <c r="E30" s="7">
-        <v>-3.99</v>
+        <v>-4.82</v>
       </c>
     </row>
     <row r="31" spans="1:5">
       <c r="A31" s="5" t="s">
-        <v>40</v>
+        <v>43</v>
       </c>
       <c r="B31" s="5" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="C31" s="6">
-        <v>14.88</v>
+        <v>5.97</v>
       </c>
       <c r="D31" s="6">
-        <v>9.33</v>
+        <v>0.42</v>
       </c>
       <c r="E31" s="7">
         <v>-5.55</v>
@@ -2356,535 +2383,603 @@
     </row>
     <row r="32" spans="1:5">
       <c r="A32" s="5" t="s">
-        <v>41</v>
+        <v>37</v>
       </c>
       <c r="B32" s="5" t="s">
         <v>10</v>
       </c>
       <c r="C32" s="6">
-        <v>8.18</v>
+        <v>17.45</v>
       </c>
       <c r="D32" s="6">
-        <v>8.24</v>
-      </c>
-      <c r="E32" s="8">
-        <v>0.06</v>
+        <v>14.94</v>
+      </c>
+      <c r="E32" s="7">
+        <v>-2.51</v>
       </c>
     </row>
     <row r="33" spans="1:5">
       <c r="A33" s="5" t="s">
-        <v>42</v>
+        <v>38</v>
       </c>
       <c r="B33" s="5" t="s">
         <v>10</v>
       </c>
       <c r="C33" s="6">
-        <v>13.63</v>
+        <v>-12.14</v>
       </c>
       <c r="D33" s="6">
-        <v>9.779999999999999</v>
+        <v>-16.1</v>
       </c>
       <c r="E33" s="7">
-        <v>-3.85</v>
+        <v>-3.96</v>
       </c>
     </row>
     <row r="34" spans="1:5">
       <c r="A34" s="5" t="s">
-        <v>43</v>
+        <v>39</v>
       </c>
       <c r="B34" s="5" t="s">
         <v>10</v>
       </c>
       <c r="C34" s="6">
-        <v>6.22</v>
+        <v>4.63</v>
       </c>
       <c r="D34" s="6">
-        <v>2.85</v>
+        <v>1.67</v>
       </c>
       <c r="E34" s="7">
-        <v>-3.37</v>
+        <v>-2.96</v>
       </c>
     </row>
     <row r="35" spans="1:5">
       <c r="A35" s="5" t="s">
-        <v>37</v>
+        <v>40</v>
       </c>
       <c r="B35" s="5" t="s">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="C35" s="6">
-        <v>-4.8</v>
+        <v>9.33</v>
       </c>
       <c r="D35" s="6">
-        <v>-5.53</v>
+        <v>3.82</v>
       </c>
       <c r="E35" s="7">
-        <v>-0.73</v>
+        <v>-5.51</v>
       </c>
     </row>
     <row r="36" spans="1:5">
       <c r="A36" s="5" t="s">
-        <v>38</v>
+        <v>41</v>
       </c>
       <c r="B36" s="5" t="s">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="C36" s="6">
-        <v>-21.75</v>
+        <v>8.24</v>
       </c>
       <c r="D36" s="6">
-        <v>-22.34</v>
+        <v>6.08</v>
       </c>
       <c r="E36" s="7">
-        <v>-0.59</v>
+        <v>-2.16</v>
       </c>
     </row>
     <row r="37" spans="1:5">
       <c r="A37" s="5" t="s">
-        <v>39</v>
+        <v>42</v>
       </c>
       <c r="B37" s="5" t="s">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="C37" s="6">
-        <v>-44.16</v>
+        <v>9.779999999999999</v>
       </c>
       <c r="D37" s="6">
-        <v>-44.56</v>
+        <v>5.16</v>
       </c>
       <c r="E37" s="7">
-        <v>-0.4</v>
+        <v>-4.62</v>
       </c>
     </row>
     <row r="38" spans="1:5">
       <c r="A38" s="5" t="s">
-        <v>40</v>
+        <v>43</v>
       </c>
       <c r="B38" s="5" t="s">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="C38" s="6">
-        <v>-10.85</v>
+        <v>2.85</v>
       </c>
       <c r="D38" s="6">
-        <v>-12.09</v>
+        <v>0.1</v>
       </c>
       <c r="E38" s="7">
-        <v>-1.24</v>
+        <v>-2.75</v>
       </c>
     </row>
     <row r="39" spans="1:5">
       <c r="A39" s="5" t="s">
-        <v>41</v>
+        <v>37</v>
       </c>
       <c r="B39" s="5" t="s">
         <v>6</v>
       </c>
       <c r="C39" s="6">
-        <v>-19.15</v>
+        <v>-5.53</v>
       </c>
       <c r="D39" s="6">
-        <v>-18.11</v>
-      </c>
-      <c r="E39" s="8">
-        <v>1.04</v>
+        <v>-7.58</v>
+      </c>
+      <c r="E39" s="7">
+        <v>-2.05</v>
       </c>
     </row>
     <row r="40" spans="1:5">
       <c r="A40" s="5" t="s">
-        <v>42</v>
+        <v>38</v>
       </c>
       <c r="B40" s="5" t="s">
         <v>6</v>
       </c>
       <c r="C40" s="6">
-        <v>-9.949999999999999</v>
+        <v>-22.34</v>
       </c>
       <c r="D40" s="6">
-        <v>-10.73</v>
+        <v>-24.83</v>
       </c>
       <c r="E40" s="7">
-        <v>-0.78</v>
+        <v>-2.49</v>
       </c>
     </row>
     <row r="41" spans="1:5">
       <c r="A41" s="5" t="s">
-        <v>43</v>
+        <v>39</v>
       </c>
       <c r="B41" s="5" t="s">
         <v>6</v>
       </c>
       <c r="C41" s="6">
-        <v>-4.28</v>
+        <v>-44.56</v>
       </c>
       <c r="D41" s="6">
-        <v>-6.36</v>
+        <v>-45.71</v>
       </c>
       <c r="E41" s="7">
-        <v>-2.08</v>
+        <v>-1.15</v>
       </c>
     </row>
     <row r="42" spans="1:5">
       <c r="A42" s="5" t="s">
-        <v>37</v>
+        <v>40</v>
       </c>
       <c r="B42" s="5" t="s">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="C42" s="6">
-        <v>11768</v>
+        <v>-12.09</v>
       </c>
       <c r="D42" s="6">
-        <v>11678</v>
+        <v>-14.75</v>
       </c>
       <c r="E42" s="7">
-        <v>-90</v>
+        <v>-2.66</v>
       </c>
     </row>
     <row r="43" spans="1:5">
       <c r="A43" s="5" t="s">
-        <v>38</v>
+        <v>41</v>
       </c>
       <c r="B43" s="5" t="s">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="C43" s="6">
-        <v>524.45</v>
+        <v>-18.11</v>
       </c>
       <c r="D43" s="6">
-        <v>520.5</v>
+        <v>-18.36</v>
       </c>
       <c r="E43" s="7">
-        <v>-3.95</v>
+        <v>-0.25</v>
       </c>
     </row>
     <row r="44" spans="1:5">
       <c r="A44" s="5" t="s">
-        <v>39</v>
+        <v>42</v>
       </c>
       <c r="B44" s="5" t="s">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="C44" s="6">
-        <v>337.75</v>
+        <v>-10.73</v>
       </c>
       <c r="D44" s="6">
-        <v>335.3</v>
+        <v>-12.91</v>
       </c>
       <c r="E44" s="7">
-        <v>-2.45</v>
+        <v>-2.18</v>
       </c>
     </row>
     <row r="45" spans="1:5">
       <c r="A45" s="5" t="s">
-        <v>40</v>
+        <v>43</v>
       </c>
       <c r="B45" s="5" t="s">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="C45" s="6">
-        <v>1940.5</v>
+        <v>-6.36</v>
       </c>
       <c r="D45" s="6">
-        <v>1913.5</v>
+        <v>-8.949999999999999</v>
       </c>
       <c r="E45" s="7">
-        <v>-27</v>
+        <v>-2.59</v>
       </c>
     </row>
     <row r="46" spans="1:5">
       <c r="A46" s="5" t="s">
-        <v>41</v>
+        <v>37</v>
       </c>
       <c r="B46" s="5" t="s">
         <v>2</v>
       </c>
       <c r="C46" s="6">
-        <v>10992</v>
+        <v>11678</v>
       </c>
       <c r="D46" s="6">
-        <v>11134</v>
-      </c>
-      <c r="E46" s="8">
-        <v>142</v>
+        <v>11424</v>
+      </c>
+      <c r="E46" s="7">
+        <v>-254</v>
       </c>
     </row>
     <row r="47" spans="1:5">
       <c r="A47" s="5" t="s">
-        <v>42</v>
+        <v>38</v>
       </c>
       <c r="B47" s="5" t="s">
         <v>2</v>
       </c>
       <c r="C47" s="6">
-        <v>1043.5</v>
+        <v>520.5</v>
       </c>
       <c r="D47" s="6">
-        <v>1034.5</v>
+        <v>503.8</v>
       </c>
       <c r="E47" s="7">
-        <v>-9</v>
+        <v>-16.7</v>
       </c>
     </row>
     <row r="48" spans="1:5">
       <c r="A48" s="5" t="s">
-        <v>43</v>
+        <v>39</v>
       </c>
       <c r="B48" s="5" t="s">
         <v>2</v>
       </c>
       <c r="C48" s="6">
-        <v>142.57</v>
+        <v>335.3</v>
       </c>
       <c r="D48" s="6">
-        <v>139.48</v>
+        <v>328.4</v>
       </c>
       <c r="E48" s="7">
-        <v>-3.09</v>
+        <v>-6.9</v>
       </c>
     </row>
     <row r="49" spans="1:5">
       <c r="A49" s="5" t="s">
-        <v>37</v>
+        <v>40</v>
       </c>
       <c r="B49" s="5" t="s">
-        <v>24</v>
+        <v>2</v>
       </c>
       <c r="C49" s="6">
-        <v>51.84</v>
+        <v>1913.5</v>
       </c>
       <c r="D49" s="6">
-        <v>48.9</v>
+        <v>1855.5</v>
       </c>
       <c r="E49" s="7">
-        <v>-2.94</v>
+        <v>-58</v>
       </c>
     </row>
     <row r="50" spans="1:5">
       <c r="A50" s="5" t="s">
-        <v>38</v>
+        <v>41</v>
       </c>
       <c r="B50" s="5" t="s">
-        <v>24</v>
+        <v>2</v>
       </c>
       <c r="C50" s="6">
-        <v>55.87</v>
+        <v>11134</v>
       </c>
       <c r="D50" s="6">
-        <v>54.35</v>
+        <v>11100</v>
       </c>
       <c r="E50" s="7">
-        <v>-1.52</v>
+        <v>-34</v>
       </c>
     </row>
     <row r="51" spans="1:5">
       <c r="A51" s="5" t="s">
-        <v>39</v>
+        <v>42</v>
       </c>
       <c r="B51" s="5" t="s">
-        <v>24</v>
+        <v>2</v>
       </c>
       <c r="C51" s="6">
-        <v>48.33</v>
+        <v>1034.5</v>
       </c>
       <c r="D51" s="6">
-        <v>46.52</v>
+        <v>1009.2</v>
       </c>
       <c r="E51" s="7">
-        <v>-1.81</v>
+        <v>-25.3</v>
       </c>
     </row>
     <row r="52" spans="1:5">
       <c r="A52" s="5" t="s">
-        <v>40</v>
+        <v>43</v>
       </c>
       <c r="B52" s="5" t="s">
-        <v>24</v>
+        <v>2</v>
       </c>
       <c r="C52" s="6">
-        <v>42.13</v>
+        <v>139.48</v>
       </c>
       <c r="D52" s="6">
-        <v>37.41</v>
+        <v>135.62</v>
       </c>
       <c r="E52" s="7">
-        <v>-4.72</v>
+        <v>-3.86</v>
       </c>
     </row>
     <row r="53" spans="1:5">
       <c r="A53" s="5" t="s">
-        <v>41</v>
+        <v>37</v>
       </c>
       <c r="B53" s="5" t="s">
         <v>24</v>
       </c>
       <c r="C53" s="6">
-        <v>44.2</v>
+        <v>48.9</v>
       </c>
       <c r="D53" s="6">
-        <v>48.63</v>
-      </c>
-      <c r="E53" s="8">
-        <v>4.43</v>
+        <v>41.71</v>
+      </c>
+      <c r="E53" s="7">
+        <v>-7.19</v>
       </c>
     </row>
     <row r="54" spans="1:5">
       <c r="A54" s="5" t="s">
-        <v>42</v>
+        <v>38</v>
       </c>
       <c r="B54" s="5" t="s">
         <v>24</v>
       </c>
       <c r="C54" s="6">
-        <v>40.95</v>
+        <v>54.35</v>
       </c>
       <c r="D54" s="6">
-        <v>38.17</v>
+        <v>48.39</v>
       </c>
       <c r="E54" s="7">
-        <v>-2.78</v>
+        <v>-5.96</v>
       </c>
     </row>
     <row r="55" spans="1:5">
       <c r="A55" s="5" t="s">
-        <v>43</v>
+        <v>39</v>
       </c>
       <c r="B55" s="5" t="s">
         <v>24</v>
       </c>
       <c r="C55" s="6">
-        <v>63.33</v>
+        <v>46.52</v>
       </c>
       <c r="D55" s="6">
-        <v>54.62</v>
+        <v>41.76</v>
       </c>
       <c r="E55" s="7">
-        <v>-8.710000000000001</v>
+        <v>-4.76</v>
       </c>
     </row>
     <row r="56" spans="1:5">
       <c r="A56" s="5" t="s">
-        <v>37</v>
+        <v>40</v>
       </c>
       <c r="B56" s="5" t="s">
-        <v>31</v>
+        <v>24</v>
       </c>
       <c r="C56" s="6">
-        <v>-46.03</v>
+        <v>37.41</v>
       </c>
       <c r="D56" s="6">
-        <v>-2.16</v>
-      </c>
-      <c r="E56" s="8">
-        <v>43.87</v>
+        <v>29.72</v>
+      </c>
+      <c r="E56" s="7">
+        <v>-7.69</v>
       </c>
     </row>
     <row r="57" spans="1:5">
       <c r="A57" s="5" t="s">
-        <v>38</v>
+        <v>41</v>
       </c>
       <c r="B57" s="5" t="s">
-        <v>31</v>
+        <v>24</v>
       </c>
       <c r="C57" s="6">
-        <v>23.29</v>
+        <v>48.63</v>
       </c>
       <c r="D57" s="6">
-        <v>-9.779999999999999</v>
+        <v>47.66</v>
       </c>
       <c r="E57" s="7">
-        <v>-33.07</v>
+        <v>-0.97</v>
       </c>
     </row>
     <row r="58" spans="1:5">
       <c r="A58" s="5" t="s">
-        <v>39</v>
+        <v>42</v>
       </c>
       <c r="B58" s="5" t="s">
-        <v>31</v>
+        <v>24</v>
       </c>
       <c r="C58" s="6">
-        <v>-22.99</v>
+        <v>38.17</v>
       </c>
       <c r="D58" s="6">
-        <v>-41.68</v>
+        <v>31.65</v>
       </c>
       <c r="E58" s="7">
-        <v>-18.69</v>
+        <v>-6.52</v>
       </c>
     </row>
     <row r="59" spans="1:5">
       <c r="A59" s="5" t="s">
-        <v>40</v>
+        <v>43</v>
       </c>
       <c r="B59" s="5" t="s">
-        <v>31</v>
+        <v>24</v>
       </c>
       <c r="C59" s="6">
-        <v>2.17</v>
+        <v>54.62</v>
       </c>
       <c r="D59" s="6">
-        <v>18.72</v>
-      </c>
-      <c r="E59" s="8">
-        <v>16.55</v>
+        <v>46.1</v>
+      </c>
+      <c r="E59" s="7">
+        <v>-8.52</v>
       </c>
     </row>
     <row r="60" spans="1:5">
       <c r="A60" s="5" t="s">
-        <v>41</v>
+        <v>37</v>
       </c>
       <c r="B60" s="5" t="s">
         <v>31</v>
       </c>
       <c r="C60" s="6">
-        <v>-59.65</v>
+        <v>-2.16</v>
       </c>
       <c r="D60" s="6">
-        <v>12.13</v>
+        <v>6.11</v>
       </c>
       <c r="E60" s="8">
-        <v>71.78</v>
+        <v>8.27</v>
       </c>
     </row>
     <row r="61" spans="1:5">
       <c r="A61" s="5" t="s">
-        <v>42</v>
+        <v>38</v>
       </c>
       <c r="B61" s="5" t="s">
         <v>31</v>
       </c>
       <c r="C61" s="6">
-        <v>-17.38</v>
+        <v>-9.779999999999999</v>
       </c>
       <c r="D61" s="6">
-        <v>18.32</v>
-      </c>
-      <c r="E61" s="8">
-        <v>35.7</v>
+        <v>-20</v>
+      </c>
+      <c r="E61" s="7">
+        <v>-10.22</v>
       </c>
     </row>
     <row r="62" spans="1:5">
       <c r="A62" s="5" t="s">
-        <v>43</v>
+        <v>39</v>
       </c>
       <c r="B62" s="5" t="s">
         <v>31</v>
       </c>
       <c r="C62" s="6">
-        <v>115.85</v>
+        <v>-41.68</v>
       </c>
       <c r="D62" s="6">
+        <v>-24.2</v>
+      </c>
+      <c r="E62" s="8">
+        <v>17.48</v>
+      </c>
+    </row>
+    <row r="63" spans="1:5">
+      <c r="A63" s="5" t="s">
+        <v>40</v>
+      </c>
+      <c r="B63" s="5" t="s">
+        <v>31</v>
+      </c>
+      <c r="C63" s="6">
+        <v>18.72</v>
+      </c>
+      <c r="D63" s="6">
+        <v>-23.58</v>
+      </c>
+      <c r="E63" s="7">
+        <v>-42.3</v>
+      </c>
+    </row>
+    <row r="64" spans="1:5">
+      <c r="A64" s="5" t="s">
+        <v>41</v>
+      </c>
+      <c r="B64" s="5" t="s">
+        <v>31</v>
+      </c>
+      <c r="C64" s="6">
+        <v>12.13</v>
+      </c>
+      <c r="D64" s="6">
+        <v>23.5</v>
+      </c>
+      <c r="E64" s="8">
+        <v>11.37</v>
+      </c>
+    </row>
+    <row r="65" spans="1:5">
+      <c r="A65" s="5" t="s">
+        <v>42</v>
+      </c>
+      <c r="B65" s="5" t="s">
+        <v>31</v>
+      </c>
+      <c r="C65" s="6">
+        <v>18.32</v>
+      </c>
+      <c r="D65" s="6">
+        <v>22.75</v>
+      </c>
+      <c r="E65" s="8">
+        <v>4.43</v>
+      </c>
+    </row>
+    <row r="66" spans="1:5">
+      <c r="A66" s="5" t="s">
+        <v>43</v>
+      </c>
+      <c r="B66" s="5" t="s">
+        <v>31</v>
+      </c>
+      <c r="C66" s="6">
         <v>-10.14</v>
       </c>
-      <c r="E62" s="7">
-        <v>-125.99</v>
+      <c r="D66" s="6">
+        <v>-36.4</v>
+      </c>
+      <c r="E66" s="7">
+        <v>-26.26</v>
       </c>
     </row>
   </sheetData>
   <mergeCells count="2">
     <mergeCell ref="A1:F1"/>
-    <mergeCell ref="A5:E5"/>
+    <mergeCell ref="A9:E9"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -2908,28 +3003,28 @@
         <v>1</v>
       </c>
       <c r="B1" s="9" t="s">
-        <v>65</v>
+        <v>70</v>
       </c>
       <c r="C1" s="9" t="s">
-        <v>66</v>
+        <v>71</v>
       </c>
       <c r="D1" s="9" t="s">
-        <v>67</v>
+        <v>72</v>
       </c>
       <c r="E1" s="9" t="s">
-        <v>68</v>
+        <v>73</v>
       </c>
       <c r="F1" s="9" t="s">
-        <v>69</v>
+        <v>74</v>
       </c>
       <c r="G1" s="9" t="s">
-        <v>70</v>
+        <v>75</v>
       </c>
       <c r="H1" s="9" t="s">
-        <v>71</v>
+        <v>76</v>
       </c>
       <c r="I1" s="9" t="s">
-        <v>72</v>
+        <v>77</v>
       </c>
     </row>
     <row r="2" spans="1:9">
@@ -2937,28 +3032,28 @@
         <v>44</v>
       </c>
       <c r="B2" s="11">
-        <v>68.8</v>
+        <v>60.8</v>
       </c>
       <c r="C2" s="12">
         <v>7</v>
       </c>
       <c r="D2" s="11">
-        <v>46.9</v>
+        <v>41</v>
       </c>
       <c r="E2" s="11">
-        <v>90</v>
+        <v>70</v>
       </c>
       <c r="F2" s="11">
-        <v>-2.6</v>
+        <v>-4</v>
       </c>
       <c r="G2" s="11">
-        <v>5.7</v>
+        <v>2.2</v>
       </c>
       <c r="H2" s="11">
         <v>57</v>
       </c>
       <c r="I2" s="11">
-        <v>60</v>
+        <v>40</v>
       </c>
     </row>
   </sheetData>
@@ -3083,25 +3178,25 @@
     </row>
     <row r="2" spans="1:7">
       <c r="A2" s="14">
-        <v>0.2879</v>
+        <v>0.2765</v>
       </c>
       <c r="B2" s="14">
-        <v>0.2286</v>
+        <v>0.2263</v>
       </c>
       <c r="C2" s="14">
-        <v>0.1695</v>
+        <v>0.1601</v>
       </c>
       <c r="D2" s="14">
-        <v>0.0722</v>
+        <v>0.0677</v>
       </c>
       <c r="E2" s="14">
-        <v>0.0251</v>
+        <v>0.0201</v>
       </c>
       <c r="F2" s="14">
-        <v>0.0036</v>
+        <v>-0.0019</v>
       </c>
       <c r="G2" s="14">
-        <v>-0.229</v>
+        <v>-0.2424</v>
       </c>
     </row>
   </sheetData>

--- a/BAJAJ_GROUP_Technical_Metrics.xlsx
+++ b/BAJAJ_GROUP_Technical_Metrics.xlsx
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="288" uniqueCount="78">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="253" uniqueCount="64">
   <si>
     <t>Symbol</t>
   </si>
@@ -172,49 +172,7 @@
     <t>▶  SIGNAL EVENTS (vs Previous Run)</t>
   </si>
   <si>
-    <t>Signal</t>
-  </si>
-  <si>
-    <t>Change</t>
-  </si>
-  <si>
-    <t>Direction</t>
-  </si>
-  <si>
-    <t>Prev Value</t>
-  </si>
-  <si>
-    <t>Curr Value</t>
-  </si>
-  <si>
-    <t>RSI Momentum</t>
-  </si>
-  <si>
-    <t>54.4 → 48.4</t>
-  </si>
-  <si>
-    <t>🔴 BEARISH</t>
-  </si>
-  <si>
-    <t>54.4</t>
-  </si>
-  <si>
-    <t>48.4</t>
-  </si>
-  <si>
-    <t>20 DMA &gt; 50 DMA</t>
-  </si>
-  <si>
-    <t>Yes → No</t>
-  </si>
-  <si>
-    <t>54.6 → 46.1</t>
-  </si>
-  <si>
-    <t>54.6</t>
-  </si>
-  <si>
-    <t>46.1</t>
+    <t>No signal events detected since last run.</t>
   </si>
   <si>
     <t>▶  NUMERIC METRIC CHANGES (vs Previous Run)</t>
@@ -300,14 +258,14 @@
     </font>
     <font>
       <sz val="11"/>
-      <color rgb="FF9C0006"/>
+      <color rgb="FF006100"/>
       <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
     </font>
     <font>
       <sz val="11"/>
-      <color rgb="FF006100"/>
+      <color rgb="FF9C0006"/>
       <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
@@ -340,13 +298,13 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFFFC7CE"/>
+        <fgColor rgb="FFC6EFCE"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFC6EFCE"/>
+        <fgColor rgb="FFFFC7CE"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -416,15 +374,14 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="15">
+  <cellXfs count="14">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="2" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="3" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1"/>
     <xf numFmtId="165" fontId="4" fillId="5" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="165" fontId="5" fillId="6" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
@@ -939,10 +896,10 @@
         <v>44</v>
       </c>
       <c r="C2">
-        <v>11424</v>
+        <v>11593</v>
       </c>
       <c r="D2">
-        <v>-2.18</v>
+        <v>1.48</v>
       </c>
       <c r="E2">
         <v>12361</v>
@@ -951,46 +908,46 @@
         <v>8506.780000000001</v>
       </c>
       <c r="G2">
-        <v>-7.58</v>
+        <v>-6.21</v>
       </c>
       <c r="H2">
-        <v>34.29</v>
+        <v>36.28</v>
       </c>
       <c r="I2">
-        <v>-3.19</v>
+        <v>-2.42</v>
       </c>
       <c r="J2">
-        <v>-2.36</v>
+        <v>-0.91</v>
       </c>
       <c r="K2">
-        <v>14.94</v>
+        <v>15.45</v>
       </c>
       <c r="L2">
-        <v>25.32</v>
+        <v>29</v>
       </c>
       <c r="M2">
-        <v>27.65</v>
+        <v>27.79</v>
       </c>
       <c r="N2">
         <v>85</v>
       </c>
       <c r="O2">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="P2">
-        <v>11708</v>
+        <v>11650.6</v>
       </c>
       <c r="Q2">
-        <v>11831.3</v>
+        <v>11830.6</v>
       </c>
       <c r="R2">
-        <v>11374.68</v>
+        <v>11404.35</v>
       </c>
       <c r="S2">
-        <v>10005.18</v>
+        <v>10018.66</v>
       </c>
       <c r="T2">
-        <v>14.18</v>
+        <v>15.71</v>
       </c>
       <c r="U2" t="s">
         <v>45</v>
@@ -1005,43 +962,43 @@
         <v>3</v>
       </c>
       <c r="Y2">
-        <v>41.71</v>
+        <v>47.27</v>
       </c>
       <c r="Z2">
-        <v>72.33</v>
+        <v>52.59</v>
       </c>
       <c r="AA2">
-        <v>160.23</v>
+        <v>138.7</v>
       </c>
       <c r="AB2">
-        <v>-87.90000000000001</v>
+        <v>-86.12</v>
       </c>
       <c r="AC2">
-        <v>0</v>
+        <v>5.89</v>
       </c>
       <c r="AD2">
-        <v>1.2</v>
+        <v>1.96</v>
       </c>
       <c r="AE2">
-        <v>221.1</v>
+        <v>220.81</v>
       </c>
       <c r="AF2">
-        <v>6.11</v>
+        <v>37.09</v>
       </c>
       <c r="AG2">
-        <v>12246.03</v>
+        <v>12246.97</v>
       </c>
       <c r="AH2">
-        <v>11416.57</v>
+        <v>11414.23</v>
       </c>
       <c r="AI2">
-        <v>12225.81</v>
+        <v>12149.93</v>
       </c>
       <c r="AJ2" t="s">
         <v>47</v>
       </c>
       <c r="AK2">
-        <v>28.8</v>
+        <v>30.09</v>
       </c>
     </row>
     <row r="3" spans="1:37">
@@ -1052,10 +1009,10 @@
         <v>44</v>
       </c>
       <c r="C3">
-        <v>503.8</v>
+        <v>498.05</v>
       </c>
       <c r="D3">
-        <v>-3.21</v>
+        <v>-1.14</v>
       </c>
       <c r="E3">
         <v>670.25</v>
@@ -1064,46 +1021,46 @@
         <v>223.92</v>
       </c>
       <c r="G3">
-        <v>-24.83</v>
+        <v>-25.69</v>
       </c>
       <c r="H3">
-        <v>124.99</v>
+        <v>122.42</v>
       </c>
       <c r="I3">
-        <v>-4.22</v>
+        <v>-3.12</v>
       </c>
       <c r="J3">
-        <v>0.64</v>
+        <v>3.46</v>
       </c>
       <c r="K3">
-        <v>-16.1</v>
+        <v>-17.38</v>
       </c>
       <c r="L3">
-        <v>126.93</v>
+        <v>117.97</v>
       </c>
       <c r="M3">
-        <v>16.01</v>
+        <v>16.21</v>
       </c>
       <c r="N3">
         <v>99</v>
       </c>
       <c r="O3">
-        <v>94</v>
+        <v>92</v>
       </c>
       <c r="P3">
-        <v>516.86</v>
+        <v>513.65</v>
       </c>
       <c r="Q3">
-        <v>491.36</v>
+        <v>492.06</v>
       </c>
       <c r="R3">
-        <v>528.97</v>
+        <v>526.52</v>
       </c>
       <c r="S3">
-        <v>437.85</v>
+        <v>439.02</v>
       </c>
       <c r="T3">
-        <v>15.06</v>
+        <v>13.45</v>
       </c>
       <c r="U3" t="s">
         <v>46</v>
@@ -1118,34 +1075,34 @@
         <v>2</v>
       </c>
       <c r="Y3">
-        <v>48.39</v>
+        <v>46.5</v>
       </c>
       <c r="Z3">
-        <v>-0.9</v>
+        <v>-1.54</v>
       </c>
       <c r="AA3">
-        <v>-7.06</v>
+        <v>-5.96</v>
       </c>
       <c r="AB3">
-        <v>6.16</v>
+        <v>4.42</v>
       </c>
       <c r="AC3">
-        <v>84.86</v>
+        <v>72.98999999999999</v>
       </c>
       <c r="AD3">
-        <v>89.84999999999999</v>
+        <v>83.70999999999999</v>
       </c>
       <c r="AE3">
-        <v>21.5</v>
+        <v>20.98</v>
       </c>
       <c r="AF3">
-        <v>-20</v>
+        <v>-52.13</v>
       </c>
       <c r="AG3">
-        <v>540.59</v>
+        <v>541.25</v>
       </c>
       <c r="AH3">
-        <v>442.13</v>
+        <v>442.87</v>
       </c>
       <c r="AI3">
         <v>460.99</v>
@@ -1154,7 +1111,7 @@
         <v>48</v>
       </c>
       <c r="AK3">
-        <v>31.33</v>
+        <v>27.59</v>
       </c>
     </row>
     <row r="4" spans="1:37">
@@ -1165,10 +1122,10 @@
         <v>44</v>
       </c>
       <c r="C4">
-        <v>328.4</v>
+        <v>322.55</v>
       </c>
       <c r="D4">
-        <v>-2.06</v>
+        <v>-1.78</v>
       </c>
       <c r="E4">
         <v>604.85</v>
@@ -1177,46 +1134,46 @@
         <v>303.75</v>
       </c>
       <c r="G4">
-        <v>-45.71</v>
+        <v>-46.67</v>
       </c>
       <c r="H4">
-        <v>8.119999999999999</v>
+        <v>6.19</v>
       </c>
       <c r="I4">
-        <v>-4</v>
+        <v>-5.12</v>
       </c>
       <c r="J4">
-        <v>-9.380000000000001</v>
+        <v>-11</v>
       </c>
       <c r="K4">
-        <v>1.67</v>
+        <v>-1.6</v>
       </c>
       <c r="L4">
-        <v>-43.94</v>
+        <v>-44.94</v>
       </c>
       <c r="M4">
-        <v>-24.24</v>
+        <v>-24.78</v>
       </c>
       <c r="N4">
         <v>15</v>
       </c>
       <c r="O4">
-        <v>19</v>
+        <v>16</v>
       </c>
       <c r="P4">
-        <v>336.24</v>
+        <v>332.76</v>
       </c>
       <c r="Q4">
-        <v>338.26</v>
+        <v>336.61</v>
       </c>
       <c r="R4">
-        <v>339.94</v>
+        <v>339.78</v>
       </c>
       <c r="S4">
-        <v>377.71</v>
+        <v>376.9</v>
       </c>
       <c r="T4">
-        <v>-13.05</v>
+        <v>-14.42</v>
       </c>
       <c r="U4" t="s">
         <v>46</v>
@@ -1231,43 +1188,43 @@
         <v>0</v>
       </c>
       <c r="Y4">
-        <v>41.76</v>
+        <v>38.2</v>
       </c>
       <c r="Z4">
-        <v>-2.79</v>
+        <v>-3.65</v>
       </c>
       <c r="AA4">
-        <v>-2.31</v>
+        <v>-2.58</v>
       </c>
       <c r="AB4">
-        <v>-0.49</v>
+        <v>-1.07</v>
       </c>
       <c r="AC4">
-        <v>60.09</v>
+        <v>37.1</v>
       </c>
       <c r="AD4">
-        <v>72.18000000000001</v>
+        <v>58</v>
       </c>
       <c r="AE4">
-        <v>10.82</v>
+        <v>10.71</v>
       </c>
       <c r="AF4">
-        <v>-24.2</v>
+        <v>-40.98</v>
       </c>
       <c r="AG4">
-        <v>357.82</v>
+        <v>355.59</v>
       </c>
       <c r="AH4">
-        <v>318.69</v>
+        <v>317.63</v>
       </c>
       <c r="AI4">
-        <v>357.31</v>
+        <v>355.84</v>
       </c>
       <c r="AJ4" t="s">
         <v>47</v>
       </c>
       <c r="AK4">
-        <v>21.21</v>
+        <v>21.14</v>
       </c>
     </row>
     <row r="5" spans="1:37">
@@ -1278,10 +1235,10 @@
         <v>44</v>
       </c>
       <c r="C5">
-        <v>1855.5</v>
+        <v>1837</v>
       </c>
       <c r="D5">
-        <v>-3.03</v>
+        <v>-1</v>
       </c>
       <c r="E5">
         <v>2176.6</v>
@@ -1290,25 +1247,25 @@
         <v>1631.8</v>
       </c>
       <c r="G5">
-        <v>-14.75</v>
+        <v>-15.6</v>
       </c>
       <c r="H5">
-        <v>13.71</v>
+        <v>12.58</v>
       </c>
       <c r="I5">
-        <v>-4.29</v>
+        <v>-5.22</v>
       </c>
       <c r="J5">
-        <v>-7.61</v>
+        <v>-8.380000000000001</v>
       </c>
       <c r="K5">
-        <v>3.82</v>
+        <v>4.1</v>
       </c>
       <c r="L5">
-        <v>-8.960000000000001</v>
+        <v>-9.85</v>
       </c>
       <c r="M5">
-        <v>2.01</v>
+        <v>1.93</v>
       </c>
       <c r="N5">
         <v>43</v>
@@ -1317,19 +1274,19 @@
         <v>54</v>
       </c>
       <c r="P5">
-        <v>1914.92</v>
+        <v>1894.7</v>
       </c>
       <c r="Q5">
-        <v>1977.93</v>
+        <v>1969.22</v>
       </c>
       <c r="R5">
-        <v>1960.64</v>
+        <v>1959.67</v>
       </c>
       <c r="S5">
-        <v>1901.28</v>
+        <v>1899.95</v>
       </c>
       <c r="T5">
-        <v>-2.41</v>
+        <v>-3.31</v>
       </c>
       <c r="U5" t="s">
         <v>45</v>
@@ -1344,43 +1301,43 @@
         <v>2</v>
       </c>
       <c r="Y5">
-        <v>29.72</v>
+        <v>27.76</v>
       </c>
       <c r="Z5">
-        <v>-18.86</v>
+        <v>-25.91</v>
       </c>
       <c r="AA5">
-        <v>-2.41</v>
+        <v>-7.11</v>
       </c>
       <c r="AB5">
-        <v>-16.44</v>
+        <v>-18.8</v>
       </c>
       <c r="AC5">
-        <v>6.29</v>
+        <v>0</v>
       </c>
       <c r="AD5">
-        <v>6.29</v>
+        <v>4.19</v>
       </c>
       <c r="AE5">
-        <v>38.07</v>
+        <v>38.35</v>
       </c>
       <c r="AF5">
-        <v>-23.58</v>
+        <v>0.01</v>
       </c>
       <c r="AG5">
-        <v>2068.79</v>
+        <v>2078.24</v>
       </c>
       <c r="AH5">
-        <v>1887.08</v>
+        <v>1860.21</v>
       </c>
       <c r="AI5">
-        <v>2007.27</v>
+        <v>1968.89</v>
       </c>
       <c r="AJ5" t="s">
         <v>47</v>
       </c>
       <c r="AK5">
-        <v>53.28</v>
+        <v>57.68</v>
       </c>
     </row>
     <row r="6" spans="1:37">
@@ -1391,10 +1348,10 @@
         <v>44</v>
       </c>
       <c r="C6">
-        <v>11100</v>
+        <v>10930</v>
       </c>
       <c r="D6">
-        <v>-0.31</v>
+        <v>-1.53</v>
       </c>
       <c r="E6">
         <v>13595.75</v>
@@ -1403,46 +1360,46 @@
         <v>8746</v>
       </c>
       <c r="G6">
-        <v>-18.36</v>
+        <v>-19.61</v>
       </c>
       <c r="H6">
-        <v>26.92</v>
+        <v>24.97</v>
       </c>
       <c r="I6">
-        <v>1.31</v>
+        <v>-1.05</v>
       </c>
       <c r="J6">
-        <v>-3.27</v>
+        <v>-4.75</v>
       </c>
       <c r="K6">
-        <v>6.08</v>
+        <v>4.1</v>
       </c>
       <c r="L6">
-        <v>-14.55</v>
+        <v>-16.15</v>
       </c>
       <c r="M6">
-        <v>22.63</v>
+        <v>22.16</v>
       </c>
       <c r="N6">
         <v>29</v>
       </c>
       <c r="O6">
-        <v>53</v>
+        <v>51</v>
       </c>
       <c r="P6">
-        <v>11070</v>
+        <v>11046.8</v>
       </c>
       <c r="Q6">
-        <v>11234.9</v>
+        <v>11218.7</v>
       </c>
       <c r="R6">
-        <v>11065.4</v>
+        <v>11068.82</v>
       </c>
       <c r="S6">
-        <v>10684.35</v>
+        <v>10682.77</v>
       </c>
       <c r="T6">
-        <v>3.89</v>
+        <v>2.31</v>
       </c>
       <c r="U6" t="s">
         <v>45</v>
@@ -1457,34 +1414,34 @@
         <v>3</v>
       </c>
       <c r="Y6">
-        <v>47.66</v>
+        <v>43.01</v>
       </c>
       <c r="Z6">
-        <v>-29.32</v>
+        <v>-44.43</v>
       </c>
       <c r="AA6">
-        <v>12.33</v>
+        <v>0.98</v>
       </c>
       <c r="AB6">
-        <v>-41.65</v>
+        <v>-45.4</v>
       </c>
       <c r="AC6">
-        <v>21.98</v>
+        <v>19.81</v>
       </c>
       <c r="AD6">
-        <v>18.61</v>
+        <v>20.52</v>
       </c>
       <c r="AE6">
-        <v>223.43</v>
+        <v>219.97</v>
       </c>
       <c r="AF6">
-        <v>23.5</v>
+        <v>-45.91</v>
       </c>
       <c r="AG6">
-        <v>11596.34</v>
+        <v>11604.74</v>
       </c>
       <c r="AH6">
-        <v>10873.46</v>
+        <v>10832.66</v>
       </c>
       <c r="AI6">
         <v>10787.84</v>
@@ -1493,7 +1450,7 @@
         <v>48</v>
       </c>
       <c r="AK6">
-        <v>18.33</v>
+        <v>18.77</v>
       </c>
     </row>
     <row r="7" spans="1:37">
@@ -1504,10 +1461,10 @@
         <v>44</v>
       </c>
       <c r="C7">
-        <v>1009.2</v>
+        <v>1006.2</v>
       </c>
       <c r="D7">
-        <v>-2.45</v>
+        <v>-0.3</v>
       </c>
       <c r="E7">
         <v>1158.8</v>
@@ -1516,46 +1473,46 @@
         <v>801.55</v>
       </c>
       <c r="G7">
-        <v>-12.91</v>
+        <v>-13.17</v>
       </c>
       <c r="H7">
-        <v>25.91</v>
+        <v>25.53</v>
       </c>
       <c r="I7">
-        <v>-4.79</v>
+        <v>-4.54</v>
       </c>
       <c r="J7">
-        <v>-7.16</v>
+        <v>-7.63</v>
       </c>
       <c r="K7">
-        <v>5.16</v>
+        <v>4.99</v>
       </c>
       <c r="L7">
-        <v>4.26</v>
+        <v>3.71</v>
       </c>
       <c r="M7">
-        <v>6.77</v>
+        <v>6.71</v>
       </c>
       <c r="N7">
         <v>71</v>
       </c>
       <c r="O7">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="P7">
-        <v>1036.12</v>
+        <v>1026.54</v>
       </c>
       <c r="Q7">
-        <v>1064.69</v>
+        <v>1060.28</v>
       </c>
       <c r="R7">
-        <v>1066.95</v>
+        <v>1066.23</v>
       </c>
       <c r="S7">
-        <v>977.89</v>
+        <v>977.75</v>
       </c>
       <c r="T7">
-        <v>3.2</v>
+        <v>2.91</v>
       </c>
       <c r="U7" t="s">
         <v>46</v>
@@ -1570,43 +1527,43 @@
         <v>2</v>
       </c>
       <c r="Y7">
-        <v>31.65</v>
+        <v>30.97</v>
       </c>
       <c r="Z7">
-        <v>-11.57</v>
+        <v>-14.05</v>
       </c>
       <c r="AA7">
-        <v>-4.89</v>
+        <v>-6.72</v>
       </c>
       <c r="AB7">
-        <v>-6.68</v>
+        <v>-7.33</v>
       </c>
       <c r="AC7">
-        <v>4.72</v>
+        <v>0</v>
       </c>
       <c r="AD7">
-        <v>6.66</v>
+        <v>3.15</v>
       </c>
       <c r="AE7">
-        <v>21.57</v>
+        <v>20.96</v>
       </c>
       <c r="AF7">
-        <v>22.75</v>
+        <v>-12.55</v>
       </c>
       <c r="AG7">
-        <v>1111.33</v>
+        <v>1111.56</v>
       </c>
       <c r="AH7">
-        <v>1018.04</v>
+        <v>1009</v>
       </c>
       <c r="AI7">
-        <v>1086.75</v>
+        <v>1075.64</v>
       </c>
       <c r="AJ7" t="s">
         <v>47</v>
       </c>
       <c r="AK7">
-        <v>42.5</v>
+        <v>45.88</v>
       </c>
     </row>
     <row r="8" spans="1:37">
@@ -1617,10 +1574,10 @@
         <v>44</v>
       </c>
       <c r="C8">
-        <v>135.62</v>
+        <v>134.89</v>
       </c>
       <c r="D8">
-        <v>-2.77</v>
+        <v>-0.54</v>
       </c>
       <c r="E8">
         <v>148.95</v>
@@ -1629,46 +1586,46 @@
         <v>115.96</v>
       </c>
       <c r="G8">
-        <v>-8.949999999999999</v>
+        <v>-9.44</v>
       </c>
       <c r="H8">
-        <v>16.95</v>
+        <v>16.32</v>
       </c>
       <c r="I8">
-        <v>-0.93</v>
+        <v>-2.01</v>
       </c>
       <c r="J8">
-        <v>1.1</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="K8">
-        <v>0.1</v>
+        <v>0.46</v>
       </c>
       <c r="L8">
-        <v>0.42</v>
+        <v>-1.12</v>
       </c>
       <c r="M8">
-        <v>-0.19</v>
+        <v>-0.21</v>
       </c>
       <c r="N8">
         <v>57</v>
       </c>
       <c r="O8">
-        <v>62</v>
+        <v>60</v>
       </c>
       <c r="P8">
-        <v>139</v>
+        <v>138.45</v>
       </c>
       <c r="Q8">
-        <v>136.64</v>
+        <v>136.6</v>
       </c>
       <c r="R8">
-        <v>138.19</v>
+        <v>138.26</v>
       </c>
       <c r="S8">
         <v>133.81</v>
       </c>
       <c r="T8">
-        <v>1.35</v>
+        <v>0.8</v>
       </c>
       <c r="U8" t="s">
         <v>46</v>
@@ -1683,34 +1640,34 @@
         <v>2</v>
       </c>
       <c r="Y8">
-        <v>46.1</v>
+        <v>44.68</v>
       </c>
       <c r="Z8">
-        <v>0.1</v>
+        <v>-0.11</v>
       </c>
       <c r="AA8">
-        <v>-0.27</v>
+        <v>-0.24</v>
       </c>
       <c r="AB8">
-        <v>0.38</v>
+        <v>0.13</v>
       </c>
       <c r="AC8">
-        <v>65.55</v>
+        <v>40.78</v>
       </c>
       <c r="AD8">
-        <v>84.66</v>
+        <v>64.92</v>
       </c>
       <c r="AE8">
-        <v>4.34</v>
+        <v>4.48</v>
       </c>
       <c r="AF8">
-        <v>-36.4</v>
+        <v>62.21</v>
       </c>
       <c r="AG8">
-        <v>140.98</v>
+        <v>140.99</v>
       </c>
       <c r="AH8">
-        <v>132.29</v>
+        <v>132.2</v>
       </c>
       <c r="AI8">
         <v>131.91</v>
@@ -1719,7 +1676,7 @@
         <v>48</v>
       </c>
       <c r="AK8">
-        <v>31.02</v>
+        <v>28.75</v>
       </c>
     </row>
   </sheetData>
@@ -1860,7 +1817,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:F66"/>
+  <dimension ref="A1:F62"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="16.7109375" customWidth="1"/>
@@ -1880,1106 +1837,991 @@
     </row>
     <row r="2" spans="1:6">
       <c r="A2" s="3" t="s">
-        <v>0</v>
-      </c>
-      <c r="B2" s="3" t="s">
         <v>50</v>
       </c>
-      <c r="C2" s="3" t="s">
+    </row>
+    <row r="5" spans="1:6">
+      <c r="A5" s="2" t="s">
         <v>51</v>
       </c>
-      <c r="D2" s="3" t="s">
-        <v>52</v>
-      </c>
-      <c r="E2" s="3" t="s">
-        <v>53</v>
-      </c>
-      <c r="F2" s="3" t="s">
-        <v>54</v>
-      </c>
-    </row>
-    <row r="3" spans="1:6">
-      <c r="A3" s="4" t="s">
-        <v>38</v>
-      </c>
-      <c r="B3" s="4" t="s">
-        <v>55</v>
-      </c>
-      <c r="C3" s="4" t="s">
-        <v>56</v>
-      </c>
-      <c r="D3" s="4" t="s">
-        <v>57</v>
-      </c>
-      <c r="E3" s="4" t="s">
-        <v>58</v>
-      </c>
-      <c r="F3" s="4" t="s">
-        <v>59</v>
-      </c>
-    </row>
-    <row r="4" spans="1:6">
-      <c r="A4" s="4" t="s">
-        <v>39</v>
-      </c>
-      <c r="B4" s="4" t="s">
-        <v>60</v>
-      </c>
-      <c r="C4" s="4" t="s">
-        <v>61</v>
-      </c>
-      <c r="D4" s="4" t="s">
-        <v>57</v>
-      </c>
-      <c r="E4" s="4" t="s">
-        <v>45</v>
-      </c>
-      <c r="F4" s="4" t="s">
-        <v>46</v>
-      </c>
-    </row>
-    <row r="5" spans="1:6">
-      <c r="A5" s="4" t="s">
-        <v>42</v>
-      </c>
-      <c r="B5" s="4" t="s">
-        <v>22</v>
-      </c>
-      <c r="C5" s="4" t="s">
-        <v>61</v>
-      </c>
-      <c r="D5" s="4" t="s">
-        <v>57</v>
-      </c>
-      <c r="E5" s="4" t="s">
-        <v>45</v>
-      </c>
-      <c r="F5" s="4" t="s">
-        <v>46</v>
-      </c>
+      <c r="B5" s="2"/>
+      <c r="C5" s="2"/>
+      <c r="D5" s="2"/>
+      <c r="E5" s="2"/>
     </row>
     <row r="6" spans="1:6">
       <c r="A6" s="4" t="s">
-        <v>42</v>
+        <v>0</v>
       </c>
       <c r="B6" s="4" t="s">
-        <v>60</v>
+        <v>52</v>
       </c>
       <c r="C6" s="4" t="s">
-        <v>61</v>
+        <v>53</v>
       </c>
       <c r="D6" s="4" t="s">
-        <v>57</v>
+        <v>54</v>
       </c>
       <c r="E6" s="4" t="s">
-        <v>45</v>
-      </c>
-      <c r="F6" s="4" t="s">
-        <v>46</v>
+        <v>55</v>
       </c>
     </row>
     <row r="7" spans="1:6">
-      <c r="A7" s="4" t="s">
-        <v>43</v>
-      </c>
-      <c r="B7" s="4" t="s">
-        <v>55</v>
-      </c>
-      <c r="C7" s="4" t="s">
-        <v>62</v>
-      </c>
-      <c r="D7" s="4" t="s">
-        <v>57</v>
-      </c>
-      <c r="E7" s="4" t="s">
-        <v>63</v>
-      </c>
-      <c r="F7" s="4" t="s">
-        <v>64</v>
+      <c r="A7" s="3" t="s">
+        <v>37</v>
+      </c>
+      <c r="B7" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="C7" s="5">
+        <v>-2.36</v>
+      </c>
+      <c r="D7" s="5">
+        <v>-0.91</v>
+      </c>
+      <c r="E7" s="6">
+        <v>1.45</v>
+      </c>
+    </row>
+    <row r="8" spans="1:6">
+      <c r="A8" s="3" t="s">
+        <v>38</v>
+      </c>
+      <c r="B8" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="C8" s="5">
+        <v>0.64</v>
+      </c>
+      <c r="D8" s="5">
+        <v>3.46</v>
+      </c>
+      <c r="E8" s="6">
+        <v>2.82</v>
       </c>
     </row>
     <row r="9" spans="1:6">
-      <c r="A9" s="2" t="s">
-        <v>65</v>
-      </c>
-      <c r="B9" s="2"/>
-      <c r="C9" s="2"/>
-      <c r="D9" s="2"/>
-      <c r="E9" s="2"/>
+      <c r="A9" s="3" t="s">
+        <v>39</v>
+      </c>
+      <c r="B9" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="C9" s="5">
+        <v>-9.380000000000001</v>
+      </c>
+      <c r="D9" s="5">
+        <v>-11</v>
+      </c>
+      <c r="E9" s="7">
+        <v>-1.62</v>
+      </c>
     </row>
     <row r="10" spans="1:6">
       <c r="A10" s="3" t="s">
-        <v>0</v>
+        <v>40</v>
       </c>
       <c r="B10" s="3" t="s">
-        <v>66</v>
-      </c>
-      <c r="C10" s="3" t="s">
-        <v>67</v>
-      </c>
-      <c r="D10" s="3" t="s">
-        <v>68</v>
-      </c>
-      <c r="E10" s="3" t="s">
-        <v>69</v>
+        <v>9</v>
+      </c>
+      <c r="C10" s="5">
+        <v>-7.61</v>
+      </c>
+      <c r="D10" s="5">
+        <v>-8.380000000000001</v>
+      </c>
+      <c r="E10" s="7">
+        <v>-0.77</v>
       </c>
     </row>
     <row r="11" spans="1:6">
-      <c r="A11" s="5" t="s">
+      <c r="A11" s="3" t="s">
+        <v>41</v>
+      </c>
+      <c r="B11" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="C11" s="5">
+        <v>-3.27</v>
+      </c>
+      <c r="D11" s="5">
+        <v>-4.75</v>
+      </c>
+      <c r="E11" s="7">
+        <v>-1.48</v>
+      </c>
+    </row>
+    <row r="12" spans="1:6">
+      <c r="A12" s="3" t="s">
+        <v>42</v>
+      </c>
+      <c r="B12" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="C12" s="5">
+        <v>-7.16</v>
+      </c>
+      <c r="D12" s="5">
+        <v>-7.63</v>
+      </c>
+      <c r="E12" s="7">
+        <v>-0.47</v>
+      </c>
+    </row>
+    <row r="13" spans="1:6">
+      <c r="A13" s="3" t="s">
+        <v>43</v>
+      </c>
+      <c r="B13" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="C13" s="5">
+        <v>1.1</v>
+      </c>
+      <c r="D13" s="5">
+        <v>0.5600000000000001</v>
+      </c>
+      <c r="E13" s="7">
+        <v>-0.54</v>
+      </c>
+    </row>
+    <row r="14" spans="1:6">
+      <c r="A14" s="3" t="s">
         <v>37</v>
       </c>
-      <c r="B11" s="5" t="s">
-        <v>9</v>
-      </c>
-      <c r="C11" s="6">
-        <v>0.15</v>
-      </c>
-      <c r="D11" s="6">
+      <c r="B14" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="C14" s="5">
+        <v>-3.19</v>
+      </c>
+      <c r="D14" s="5">
+        <v>-2.42</v>
+      </c>
+      <c r="E14" s="6">
+        <v>0.77</v>
+      </c>
+    </row>
+    <row r="15" spans="1:6">
+      <c r="A15" s="3" t="s">
+        <v>38</v>
+      </c>
+      <c r="B15" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="C15" s="5">
+        <v>-4.22</v>
+      </c>
+      <c r="D15" s="5">
+        <v>-3.12</v>
+      </c>
+      <c r="E15" s="6">
+        <v>1.1</v>
+      </c>
+    </row>
+    <row r="16" spans="1:6">
+      <c r="A16" s="3" t="s">
+        <v>39</v>
+      </c>
+      <c r="B16" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="C16" s="5">
+        <v>-4</v>
+      </c>
+      <c r="D16" s="5">
+        <v>-5.12</v>
+      </c>
+      <c r="E16" s="7">
+        <v>-1.12</v>
+      </c>
+    </row>
+    <row r="17" spans="1:5">
+      <c r="A17" s="3" t="s">
+        <v>40</v>
+      </c>
+      <c r="B17" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="C17" s="5">
+        <v>-4.29</v>
+      </c>
+      <c r="D17" s="5">
+        <v>-5.22</v>
+      </c>
+      <c r="E17" s="7">
+        <v>-0.93</v>
+      </c>
+    </row>
+    <row r="18" spans="1:5">
+      <c r="A18" s="3" t="s">
+        <v>41</v>
+      </c>
+      <c r="B18" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="C18" s="5">
+        <v>1.31</v>
+      </c>
+      <c r="D18" s="5">
+        <v>-1.05</v>
+      </c>
+      <c r="E18" s="7">
         <v>-2.36</v>
       </c>
-      <c r="E11" s="7">
-        <v>-2.51</v>
-      </c>
-    </row>
-    <row r="12" spans="1:6">
-      <c r="A12" s="5" t="s">
+    </row>
+    <row r="19" spans="1:5">
+      <c r="A19" s="3" t="s">
+        <v>42</v>
+      </c>
+      <c r="B19" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="C19" s="5">
+        <v>-4.79</v>
+      </c>
+      <c r="D19" s="5">
+        <v>-4.54</v>
+      </c>
+      <c r="E19" s="6">
+        <v>0.25</v>
+      </c>
+    </row>
+    <row r="20" spans="1:5">
+      <c r="A20" s="3" t="s">
+        <v>43</v>
+      </c>
+      <c r="B20" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="C20" s="5">
+        <v>-0.93</v>
+      </c>
+      <c r="D20" s="5">
+        <v>-2.01</v>
+      </c>
+      <c r="E20" s="7">
+        <v>-1.08</v>
+      </c>
+    </row>
+    <row r="21" spans="1:5">
+      <c r="A21" s="3" t="s">
+        <v>37</v>
+      </c>
+      <c r="B21" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="C21" s="5">
+        <v>25.32</v>
+      </c>
+      <c r="D21" s="5">
+        <v>29</v>
+      </c>
+      <c r="E21" s="6">
+        <v>3.68</v>
+      </c>
+    </row>
+    <row r="22" spans="1:5">
+      <c r="A22" s="3" t="s">
         <v>38</v>
       </c>
-      <c r="B12" s="5" t="s">
-        <v>9</v>
-      </c>
-      <c r="C12" s="6">
-        <v>-1.36</v>
-      </c>
-      <c r="D12" s="6">
-        <v>0.64</v>
-      </c>
-      <c r="E12" s="8">
+      <c r="B22" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="C22" s="5">
+        <v>126.93</v>
+      </c>
+      <c r="D22" s="5">
+        <v>117.97</v>
+      </c>
+      <c r="E22" s="7">
+        <v>-8.960000000000001</v>
+      </c>
+    </row>
+    <row r="23" spans="1:5">
+      <c r="A23" s="3" t="s">
+        <v>39</v>
+      </c>
+      <c r="B23" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="C23" s="5">
+        <v>-43.94</v>
+      </c>
+      <c r="D23" s="5">
+        <v>-44.94</v>
+      </c>
+      <c r="E23" s="7">
+        <v>-1</v>
+      </c>
+    </row>
+    <row r="24" spans="1:5">
+      <c r="A24" s="3" t="s">
+        <v>40</v>
+      </c>
+      <c r="B24" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="C24" s="5">
+        <v>-8.960000000000001</v>
+      </c>
+      <c r="D24" s="5">
+        <v>-9.85</v>
+      </c>
+      <c r="E24" s="7">
+        <v>-0.89</v>
+      </c>
+    </row>
+    <row r="25" spans="1:5">
+      <c r="A25" s="3" t="s">
+        <v>41</v>
+      </c>
+      <c r="B25" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="C25" s="5">
+        <v>-14.55</v>
+      </c>
+      <c r="D25" s="5">
+        <v>-16.15</v>
+      </c>
+      <c r="E25" s="7">
+        <v>-1.6</v>
+      </c>
+    </row>
+    <row r="26" spans="1:5">
+      <c r="A26" s="3" t="s">
+        <v>42</v>
+      </c>
+      <c r="B26" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="C26" s="5">
+        <v>4.26</v>
+      </c>
+      <c r="D26" s="5">
+        <v>3.71</v>
+      </c>
+      <c r="E26" s="7">
+        <v>-0.55</v>
+      </c>
+    </row>
+    <row r="27" spans="1:5">
+      <c r="A27" s="3" t="s">
+        <v>43</v>
+      </c>
+      <c r="B27" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="C27" s="5">
+        <v>0.42</v>
+      </c>
+      <c r="D27" s="5">
+        <v>-1.12</v>
+      </c>
+      <c r="E27" s="7">
+        <v>-1.54</v>
+      </c>
+    </row>
+    <row r="28" spans="1:5">
+      <c r="A28" s="3" t="s">
+        <v>37</v>
+      </c>
+      <c r="B28" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="C28" s="5">
+        <v>14.94</v>
+      </c>
+      <c r="D28" s="5">
+        <v>15.45</v>
+      </c>
+      <c r="E28" s="6">
+        <v>0.51</v>
+      </c>
+    </row>
+    <row r="29" spans="1:5">
+      <c r="A29" s="3" t="s">
+        <v>38</v>
+      </c>
+      <c r="B29" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="C29" s="5">
+        <v>-16.1</v>
+      </c>
+      <c r="D29" s="5">
+        <v>-17.38</v>
+      </c>
+      <c r="E29" s="7">
+        <v>-1.28</v>
+      </c>
+    </row>
+    <row r="30" spans="1:5">
+      <c r="A30" s="3" t="s">
+        <v>39</v>
+      </c>
+      <c r="B30" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="C30" s="5">
+        <v>1.67</v>
+      </c>
+      <c r="D30" s="5">
+        <v>-1.6</v>
+      </c>
+      <c r="E30" s="7">
+        <v>-3.27</v>
+      </c>
+    </row>
+    <row r="31" spans="1:5">
+      <c r="A31" s="3" t="s">
+        <v>40</v>
+      </c>
+      <c r="B31" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="C31" s="5">
+        <v>3.82</v>
+      </c>
+      <c r="D31" s="5">
+        <v>4.1</v>
+      </c>
+      <c r="E31" s="6">
+        <v>0.28</v>
+      </c>
+    </row>
+    <row r="32" spans="1:5">
+      <c r="A32" s="3" t="s">
+        <v>41</v>
+      </c>
+      <c r="B32" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="C32" s="5">
+        <v>6.08</v>
+      </c>
+      <c r="D32" s="5">
+        <v>4.1</v>
+      </c>
+      <c r="E32" s="7">
+        <v>-1.98</v>
+      </c>
+    </row>
+    <row r="33" spans="1:5">
+      <c r="A33" s="3" t="s">
+        <v>42</v>
+      </c>
+      <c r="B33" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="C33" s="5">
+        <v>5.16</v>
+      </c>
+      <c r="D33" s="5">
+        <v>4.99</v>
+      </c>
+      <c r="E33" s="7">
+        <v>-0.17</v>
+      </c>
+    </row>
+    <row r="34" spans="1:5">
+      <c r="A34" s="3" t="s">
+        <v>43</v>
+      </c>
+      <c r="B34" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="C34" s="5">
+        <v>0.1</v>
+      </c>
+      <c r="D34" s="5">
+        <v>0.46</v>
+      </c>
+      <c r="E34" s="6">
+        <v>0.36</v>
+      </c>
+    </row>
+    <row r="35" spans="1:5">
+      <c r="A35" s="3" t="s">
+        <v>37</v>
+      </c>
+      <c r="B35" s="3" t="s">
+        <v>6</v>
+      </c>
+      <c r="C35" s="5">
+        <v>-7.58</v>
+      </c>
+      <c r="D35" s="5">
+        <v>-6.21</v>
+      </c>
+      <c r="E35" s="6">
+        <v>1.37</v>
+      </c>
+    </row>
+    <row r="36" spans="1:5">
+      <c r="A36" s="3" t="s">
+        <v>38</v>
+      </c>
+      <c r="B36" s="3" t="s">
+        <v>6</v>
+      </c>
+      <c r="C36" s="5">
+        <v>-24.83</v>
+      </c>
+      <c r="D36" s="5">
+        <v>-25.69</v>
+      </c>
+      <c r="E36" s="7">
+        <v>-0.86</v>
+      </c>
+    </row>
+    <row r="37" spans="1:5">
+      <c r="A37" s="3" t="s">
+        <v>39</v>
+      </c>
+      <c r="B37" s="3" t="s">
+        <v>6</v>
+      </c>
+      <c r="C37" s="5">
+        <v>-45.71</v>
+      </c>
+      <c r="D37" s="5">
+        <v>-46.67</v>
+      </c>
+      <c r="E37" s="7">
+        <v>-0.96</v>
+      </c>
+    </row>
+    <row r="38" spans="1:5">
+      <c r="A38" s="3" t="s">
+        <v>40</v>
+      </c>
+      <c r="B38" s="3" t="s">
+        <v>6</v>
+      </c>
+      <c r="C38" s="5">
+        <v>-14.75</v>
+      </c>
+      <c r="D38" s="5">
+        <v>-15.6</v>
+      </c>
+      <c r="E38" s="7">
+        <v>-0.85</v>
+      </c>
+    </row>
+    <row r="39" spans="1:5">
+      <c r="A39" s="3" t="s">
+        <v>41</v>
+      </c>
+      <c r="B39" s="3" t="s">
+        <v>6</v>
+      </c>
+      <c r="C39" s="5">
+        <v>-18.36</v>
+      </c>
+      <c r="D39" s="5">
+        <v>-19.61</v>
+      </c>
+      <c r="E39" s="7">
+        <v>-1.25</v>
+      </c>
+    </row>
+    <row r="40" spans="1:5">
+      <c r="A40" s="3" t="s">
+        <v>42</v>
+      </c>
+      <c r="B40" s="3" t="s">
+        <v>6</v>
+      </c>
+      <c r="C40" s="5">
+        <v>-12.91</v>
+      </c>
+      <c r="D40" s="5">
+        <v>-13.17</v>
+      </c>
+      <c r="E40" s="7">
+        <v>-0.26</v>
+      </c>
+    </row>
+    <row r="41" spans="1:5">
+      <c r="A41" s="3" t="s">
+        <v>43</v>
+      </c>
+      <c r="B41" s="3" t="s">
+        <v>6</v>
+      </c>
+      <c r="C41" s="5">
+        <v>-8.949999999999999</v>
+      </c>
+      <c r="D41" s="5">
+        <v>-9.44</v>
+      </c>
+      <c r="E41" s="7">
+        <v>-0.49</v>
+      </c>
+    </row>
+    <row r="42" spans="1:5">
+      <c r="A42" s="3" t="s">
+        <v>37</v>
+      </c>
+      <c r="B42" s="3" t="s">
         <v>2</v>
       </c>
-    </row>
-    <row r="13" spans="1:6">
-      <c r="A13" s="5" t="s">
+      <c r="C42" s="5">
+        <v>11424</v>
+      </c>
+      <c r="D42" s="5">
+        <v>11593</v>
+      </c>
+      <c r="E42" s="6">
+        <v>169</v>
+      </c>
+    </row>
+    <row r="43" spans="1:5">
+      <c r="A43" s="3" t="s">
+        <v>38</v>
+      </c>
+      <c r="B43" s="3" t="s">
+        <v>2</v>
+      </c>
+      <c r="C43" s="5">
+        <v>503.8</v>
+      </c>
+      <c r="D43" s="5">
+        <v>498.05</v>
+      </c>
+      <c r="E43" s="7">
+        <v>-5.75</v>
+      </c>
+    </row>
+    <row r="44" spans="1:5">
+      <c r="A44" s="3" t="s">
         <v>39</v>
       </c>
-      <c r="B13" s="5" t="s">
-        <v>9</v>
-      </c>
-      <c r="C13" s="6">
-        <v>-5.97</v>
-      </c>
-      <c r="D13" s="6">
-        <v>-9.380000000000001</v>
-      </c>
-      <c r="E13" s="7">
-        <v>-3.41</v>
-      </c>
-    </row>
-    <row r="14" spans="1:6">
-      <c r="A14" s="5" t="s">
+      <c r="B44" s="3" t="s">
+        <v>2</v>
+      </c>
+      <c r="C44" s="5">
+        <v>328.4</v>
+      </c>
+      <c r="D44" s="5">
+        <v>322.55</v>
+      </c>
+      <c r="E44" s="7">
+        <v>-5.85</v>
+      </c>
+    </row>
+    <row r="45" spans="1:5">
+      <c r="A45" s="3" t="s">
         <v>40</v>
       </c>
-      <c r="B14" s="5" t="s">
-        <v>9</v>
-      </c>
-      <c r="C14" s="6">
-        <v>-5.51</v>
-      </c>
-      <c r="D14" s="6">
-        <v>-7.61</v>
-      </c>
-      <c r="E14" s="7">
-        <v>-2.1</v>
-      </c>
-    </row>
-    <row r="15" spans="1:6">
-      <c r="A15" s="5" t="s">
+      <c r="B45" s="3" t="s">
+        <v>2</v>
+      </c>
+      <c r="C45" s="5">
+        <v>1855.5</v>
+      </c>
+      <c r="D45" s="5">
+        <v>1837</v>
+      </c>
+      <c r="E45" s="7">
+        <v>-18.5</v>
+      </c>
+    </row>
+    <row r="46" spans="1:5">
+      <c r="A46" s="3" t="s">
         <v>41</v>
       </c>
-      <c r="B15" s="5" t="s">
-        <v>9</v>
-      </c>
-      <c r="C15" s="6">
-        <v>-3.18</v>
-      </c>
-      <c r="D15" s="6">
-        <v>-3.27</v>
-      </c>
-      <c r="E15" s="7">
-        <v>-0.09</v>
-      </c>
-    </row>
-    <row r="16" spans="1:6">
-      <c r="A16" s="5" t="s">
+      <c r="B46" s="3" t="s">
+        <v>2</v>
+      </c>
+      <c r="C46" s="5">
+        <v>11100</v>
+      </c>
+      <c r="D46" s="5">
+        <v>10930</v>
+      </c>
+      <c r="E46" s="7">
+        <v>-170</v>
+      </c>
+    </row>
+    <row r="47" spans="1:5">
+      <c r="A47" s="3" t="s">
         <v>42</v>
       </c>
-      <c r="B16" s="5" t="s">
-        <v>9</v>
-      </c>
-      <c r="C16" s="6">
-        <v>-5.16</v>
-      </c>
-      <c r="D16" s="6">
-        <v>-7.16</v>
-      </c>
-      <c r="E16" s="7">
-        <v>-2</v>
-      </c>
-    </row>
-    <row r="17" spans="1:5">
-      <c r="A17" s="5" t="s">
+      <c r="B47" s="3" t="s">
+        <v>2</v>
+      </c>
+      <c r="C47" s="5">
+        <v>1009.2</v>
+      </c>
+      <c r="D47" s="5">
+        <v>1006.2</v>
+      </c>
+      <c r="E47" s="7">
+        <v>-3</v>
+      </c>
+    </row>
+    <row r="48" spans="1:5">
+      <c r="A48" s="3" t="s">
         <v>43</v>
       </c>
-      <c r="B17" s="5" t="s">
-        <v>9</v>
-      </c>
-      <c r="C17" s="6">
-        <v>2.86</v>
-      </c>
-      <c r="D17" s="6">
-        <v>1.1</v>
-      </c>
-      <c r="E17" s="7">
-        <v>-1.76</v>
-      </c>
-    </row>
-    <row r="18" spans="1:5">
-      <c r="A18" s="5" t="s">
+      <c r="B48" s="3" t="s">
+        <v>2</v>
+      </c>
+      <c r="C48" s="5">
+        <v>135.62</v>
+      </c>
+      <c r="D48" s="5">
+        <v>134.89</v>
+      </c>
+      <c r="E48" s="7">
+        <v>-0.73</v>
+      </c>
+    </row>
+    <row r="49" spans="1:5">
+      <c r="A49" s="3" t="s">
         <v>37</v>
       </c>
-      <c r="B18" s="5" t="s">
-        <v>8</v>
-      </c>
-      <c r="C18" s="6">
-        <v>-2.02</v>
-      </c>
-      <c r="D18" s="6">
-        <v>-3.19</v>
-      </c>
-      <c r="E18" s="7">
-        <v>-1.17</v>
-      </c>
-    </row>
-    <row r="19" spans="1:5">
-      <c r="A19" s="5" t="s">
+      <c r="B49" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="C49" s="5">
+        <v>41.71</v>
+      </c>
+      <c r="D49" s="5">
+        <v>47.27</v>
+      </c>
+      <c r="E49" s="6">
+        <v>5.56</v>
+      </c>
+    </row>
+    <row r="50" spans="1:5">
+      <c r="A50" s="3" t="s">
         <v>38</v>
       </c>
-      <c r="B19" s="5" t="s">
-        <v>8</v>
-      </c>
-      <c r="C19" s="6">
-        <v>0.57</v>
-      </c>
-      <c r="D19" s="6">
-        <v>-4.22</v>
-      </c>
-      <c r="E19" s="7">
-        <v>-4.79</v>
-      </c>
-    </row>
-    <row r="20" spans="1:5">
-      <c r="A20" s="5" t="s">
+      <c r="B50" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="C50" s="5">
+        <v>48.39</v>
+      </c>
+      <c r="D50" s="5">
+        <v>46.5</v>
+      </c>
+      <c r="E50" s="7">
+        <v>-1.89</v>
+      </c>
+    </row>
+    <row r="51" spans="1:5">
+      <c r="A51" s="3" t="s">
         <v>39</v>
       </c>
-      <c r="B20" s="5" t="s">
-        <v>8</v>
-      </c>
-      <c r="C20" s="6">
-        <v>1.25</v>
-      </c>
-      <c r="D20" s="6">
-        <v>-4</v>
-      </c>
-      <c r="E20" s="7">
-        <v>-5.25</v>
-      </c>
-    </row>
-    <row r="21" spans="1:5">
-      <c r="A21" s="5" t="s">
+      <c r="B51" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="C51" s="5">
+        <v>41.76</v>
+      </c>
+      <c r="D51" s="5">
+        <v>38.2</v>
+      </c>
+      <c r="E51" s="7">
+        <v>-3.56</v>
+      </c>
+    </row>
+    <row r="52" spans="1:5">
+      <c r="A52" s="3" t="s">
         <v>40</v>
       </c>
-      <c r="B21" s="5" t="s">
-        <v>8</v>
-      </c>
-      <c r="C21" s="6">
-        <v>-2.87</v>
-      </c>
-      <c r="D21" s="6">
-        <v>-4.29</v>
-      </c>
-      <c r="E21" s="7">
+      <c r="B52" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="C52" s="5">
+        <v>29.72</v>
+      </c>
+      <c r="D52" s="5">
+        <v>27.76</v>
+      </c>
+      <c r="E52" s="7">
+        <v>-1.96</v>
+      </c>
+    </row>
+    <row r="53" spans="1:5">
+      <c r="A53" s="3" t="s">
+        <v>41</v>
+      </c>
+      <c r="B53" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="C53" s="5">
+        <v>47.66</v>
+      </c>
+      <c r="D53" s="5">
+        <v>43.01</v>
+      </c>
+      <c r="E53" s="7">
+        <v>-4.65</v>
+      </c>
+    </row>
+    <row r="54" spans="1:5">
+      <c r="A54" s="3" t="s">
+        <v>42</v>
+      </c>
+      <c r="B54" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="C54" s="5">
+        <v>31.65</v>
+      </c>
+      <c r="D54" s="5">
+        <v>30.97</v>
+      </c>
+      <c r="E54" s="7">
+        <v>-0.68</v>
+      </c>
+    </row>
+    <row r="55" spans="1:5">
+      <c r="A55" s="3" t="s">
+        <v>43</v>
+      </c>
+      <c r="B55" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="C55" s="5">
+        <v>46.1</v>
+      </c>
+      <c r="D55" s="5">
+        <v>44.68</v>
+      </c>
+      <c r="E55" s="7">
         <v>-1.42</v>
       </c>
     </row>
-    <row r="22" spans="1:5">
-      <c r="A22" s="5" t="s">
+    <row r="56" spans="1:5">
+      <c r="A56" s="3" t="s">
+        <v>37</v>
+      </c>
+      <c r="B56" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="C56" s="5">
+        <v>6.11</v>
+      </c>
+      <c r="D56" s="5">
+        <v>37.09</v>
+      </c>
+      <c r="E56" s="6">
+        <v>30.98</v>
+      </c>
+    </row>
+    <row r="57" spans="1:5">
+      <c r="A57" s="3" t="s">
+        <v>38</v>
+      </c>
+      <c r="B57" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="C57" s="5">
+        <v>-20</v>
+      </c>
+      <c r="D57" s="5">
+        <v>-52.13</v>
+      </c>
+      <c r="E57" s="7">
+        <v>-32.13</v>
+      </c>
+    </row>
+    <row r="58" spans="1:5">
+      <c r="A58" s="3" t="s">
+        <v>39</v>
+      </c>
+      <c r="B58" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="C58" s="5">
+        <v>-24.2</v>
+      </c>
+      <c r="D58" s="5">
+        <v>-40.98</v>
+      </c>
+      <c r="E58" s="7">
+        <v>-16.78</v>
+      </c>
+    </row>
+    <row r="59" spans="1:5">
+      <c r="A59" s="3" t="s">
+        <v>40</v>
+      </c>
+      <c r="B59" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="C59" s="5">
+        <v>-23.58</v>
+      </c>
+      <c r="D59" s="5">
+        <v>0.01</v>
+      </c>
+      <c r="E59" s="6">
+        <v>23.59</v>
+      </c>
+    </row>
+    <row r="60" spans="1:5">
+      <c r="A60" s="3" t="s">
         <v>41</v>
       </c>
-      <c r="B22" s="5" t="s">
-        <v>8</v>
-      </c>
-      <c r="C22" s="6">
-        <v>-0.25</v>
-      </c>
-      <c r="D22" s="6">
-        <v>1.31</v>
-      </c>
-      <c r="E22" s="8">
-        <v>1.56</v>
-      </c>
-    </row>
-    <row r="23" spans="1:5">
-      <c r="A23" s="5" t="s">
+      <c r="B60" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="C60" s="5">
+        <v>23.5</v>
+      </c>
+      <c r="D60" s="5">
+        <v>-45.91</v>
+      </c>
+      <c r="E60" s="7">
+        <v>-69.41</v>
+      </c>
+    </row>
+    <row r="61" spans="1:5">
+      <c r="A61" s="3" t="s">
         <v>42</v>
       </c>
-      <c r="B23" s="5" t="s">
-        <v>8</v>
-      </c>
-      <c r="C23" s="6">
-        <v>-2.45</v>
-      </c>
-      <c r="D23" s="6">
-        <v>-4.79</v>
-      </c>
-      <c r="E23" s="7">
-        <v>-2.34</v>
-      </c>
-    </row>
-    <row r="24" spans="1:5">
-      <c r="A24" s="5" t="s">
+      <c r="B61" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="C61" s="5">
+        <v>22.75</v>
+      </c>
+      <c r="D61" s="5">
+        <v>-12.55</v>
+      </c>
+      <c r="E61" s="7">
+        <v>-35.3</v>
+      </c>
+    </row>
+    <row r="62" spans="1:5">
+      <c r="A62" s="3" t="s">
         <v>43</v>
       </c>
-      <c r="B24" s="5" t="s">
-        <v>8</v>
-      </c>
-      <c r="C24" s="6">
-        <v>3.75</v>
-      </c>
-      <c r="D24" s="6">
-        <v>-0.93</v>
-      </c>
-      <c r="E24" s="7">
-        <v>-4.68</v>
-      </c>
-    </row>
-    <row r="25" spans="1:5">
-      <c r="A25" s="5" t="s">
-        <v>37</v>
-      </c>
-      <c r="B25" s="5" t="s">
-        <v>11</v>
-      </c>
-      <c r="C25" s="6">
-        <v>26.21</v>
-      </c>
-      <c r="D25" s="6">
-        <v>25.32</v>
-      </c>
-      <c r="E25" s="7">
-        <v>-0.89</v>
-      </c>
-    </row>
-    <row r="26" spans="1:5">
-      <c r="A26" s="5" t="s">
-        <v>38</v>
-      </c>
-      <c r="B26" s="5" t="s">
-        <v>11</v>
-      </c>
-      <c r="C26" s="6">
-        <v>134.44</v>
-      </c>
-      <c r="D26" s="6">
-        <v>126.93</v>
-      </c>
-      <c r="E26" s="7">
-        <v>-7.51</v>
-      </c>
-    </row>
-    <row r="27" spans="1:5">
-      <c r="A27" s="5" t="s">
-        <v>39</v>
-      </c>
-      <c r="B27" s="5" t="s">
-        <v>11</v>
-      </c>
-      <c r="C27" s="6">
-        <v>-40.99</v>
-      </c>
-      <c r="D27" s="6">
-        <v>-43.94</v>
-      </c>
-      <c r="E27" s="7">
-        <v>-2.95</v>
-      </c>
-    </row>
-    <row r="28" spans="1:5">
-      <c r="A28" s="5" t="s">
-        <v>40</v>
-      </c>
-      <c r="B28" s="5" t="s">
-        <v>11</v>
-      </c>
-      <c r="C28" s="6">
-        <v>-5.52</v>
-      </c>
-      <c r="D28" s="6">
-        <v>-8.960000000000001</v>
-      </c>
-      <c r="E28" s="7">
-        <v>-3.44</v>
-      </c>
-    </row>
-    <row r="29" spans="1:5">
-      <c r="A29" s="5" t="s">
-        <v>41</v>
-      </c>
-      <c r="B29" s="5" t="s">
-        <v>11</v>
-      </c>
-      <c r="C29" s="6">
-        <v>-14.35</v>
-      </c>
-      <c r="D29" s="6">
-        <v>-14.55</v>
-      </c>
-      <c r="E29" s="7">
-        <v>-0.2</v>
-      </c>
-    </row>
-    <row r="30" spans="1:5">
-      <c r="A30" s="5" t="s">
-        <v>42</v>
-      </c>
-      <c r="B30" s="5" t="s">
-        <v>11</v>
-      </c>
-      <c r="C30" s="6">
-        <v>9.08</v>
-      </c>
-      <c r="D30" s="6">
-        <v>4.26</v>
-      </c>
-      <c r="E30" s="7">
-        <v>-4.82</v>
-      </c>
-    </row>
-    <row r="31" spans="1:5">
-      <c r="A31" s="5" t="s">
-        <v>43</v>
-      </c>
-      <c r="B31" s="5" t="s">
-        <v>11</v>
-      </c>
-      <c r="C31" s="6">
-        <v>5.97</v>
-      </c>
-      <c r="D31" s="6">
-        <v>0.42</v>
-      </c>
-      <c r="E31" s="7">
-        <v>-5.55</v>
-      </c>
-    </row>
-    <row r="32" spans="1:5">
-      <c r="A32" s="5" t="s">
-        <v>37</v>
-      </c>
-      <c r="B32" s="5" t="s">
-        <v>10</v>
-      </c>
-      <c r="C32" s="6">
-        <v>17.45</v>
-      </c>
-      <c r="D32" s="6">
-        <v>14.94</v>
-      </c>
-      <c r="E32" s="7">
-        <v>-2.51</v>
-      </c>
-    </row>
-    <row r="33" spans="1:5">
-      <c r="A33" s="5" t="s">
-        <v>38</v>
-      </c>
-      <c r="B33" s="5" t="s">
-        <v>10</v>
-      </c>
-      <c r="C33" s="6">
-        <v>-12.14</v>
-      </c>
-      <c r="D33" s="6">
-        <v>-16.1</v>
-      </c>
-      <c r="E33" s="7">
-        <v>-3.96</v>
-      </c>
-    </row>
-    <row r="34" spans="1:5">
-      <c r="A34" s="5" t="s">
-        <v>39</v>
-      </c>
-      <c r="B34" s="5" t="s">
-        <v>10</v>
-      </c>
-      <c r="C34" s="6">
-        <v>4.63</v>
-      </c>
-      <c r="D34" s="6">
-        <v>1.67</v>
-      </c>
-      <c r="E34" s="7">
-        <v>-2.96</v>
-      </c>
-    </row>
-    <row r="35" spans="1:5">
-      <c r="A35" s="5" t="s">
-        <v>40</v>
-      </c>
-      <c r="B35" s="5" t="s">
-        <v>10</v>
-      </c>
-      <c r="C35" s="6">
-        <v>9.33</v>
-      </c>
-      <c r="D35" s="6">
-        <v>3.82</v>
-      </c>
-      <c r="E35" s="7">
-        <v>-5.51</v>
-      </c>
-    </row>
-    <row r="36" spans="1:5">
-      <c r="A36" s="5" t="s">
-        <v>41</v>
-      </c>
-      <c r="B36" s="5" t="s">
-        <v>10</v>
-      </c>
-      <c r="C36" s="6">
-        <v>8.24</v>
-      </c>
-      <c r="D36" s="6">
-        <v>6.08</v>
-      </c>
-      <c r="E36" s="7">
-        <v>-2.16</v>
-      </c>
-    </row>
-    <row r="37" spans="1:5">
-      <c r="A37" s="5" t="s">
-        <v>42</v>
-      </c>
-      <c r="B37" s="5" t="s">
-        <v>10</v>
-      </c>
-      <c r="C37" s="6">
-        <v>9.779999999999999</v>
-      </c>
-      <c r="D37" s="6">
-        <v>5.16</v>
-      </c>
-      <c r="E37" s="7">
-        <v>-4.62</v>
-      </c>
-    </row>
-    <row r="38" spans="1:5">
-      <c r="A38" s="5" t="s">
-        <v>43</v>
-      </c>
-      <c r="B38" s="5" t="s">
-        <v>10</v>
-      </c>
-      <c r="C38" s="6">
-        <v>2.85</v>
-      </c>
-      <c r="D38" s="6">
-        <v>0.1</v>
-      </c>
-      <c r="E38" s="7">
-        <v>-2.75</v>
-      </c>
-    </row>
-    <row r="39" spans="1:5">
-      <c r="A39" s="5" t="s">
-        <v>37</v>
-      </c>
-      <c r="B39" s="5" t="s">
-        <v>6</v>
-      </c>
-      <c r="C39" s="6">
-        <v>-5.53</v>
-      </c>
-      <c r="D39" s="6">
-        <v>-7.58</v>
-      </c>
-      <c r="E39" s="7">
-        <v>-2.05</v>
-      </c>
-    </row>
-    <row r="40" spans="1:5">
-      <c r="A40" s="5" t="s">
-        <v>38</v>
-      </c>
-      <c r="B40" s="5" t="s">
-        <v>6</v>
-      </c>
-      <c r="C40" s="6">
-        <v>-22.34</v>
-      </c>
-      <c r="D40" s="6">
-        <v>-24.83</v>
-      </c>
-      <c r="E40" s="7">
-        <v>-2.49</v>
-      </c>
-    </row>
-    <row r="41" spans="1:5">
-      <c r="A41" s="5" t="s">
-        <v>39</v>
-      </c>
-      <c r="B41" s="5" t="s">
-        <v>6</v>
-      </c>
-      <c r="C41" s="6">
-        <v>-44.56</v>
-      </c>
-      <c r="D41" s="6">
-        <v>-45.71</v>
-      </c>
-      <c r="E41" s="7">
-        <v>-1.15</v>
-      </c>
-    </row>
-    <row r="42" spans="1:5">
-      <c r="A42" s="5" t="s">
-        <v>40</v>
-      </c>
-      <c r="B42" s="5" t="s">
-        <v>6</v>
-      </c>
-      <c r="C42" s="6">
-        <v>-12.09</v>
-      </c>
-      <c r="D42" s="6">
-        <v>-14.75</v>
-      </c>
-      <c r="E42" s="7">
-        <v>-2.66</v>
-      </c>
-    </row>
-    <row r="43" spans="1:5">
-      <c r="A43" s="5" t="s">
-        <v>41</v>
-      </c>
-      <c r="B43" s="5" t="s">
-        <v>6</v>
-      </c>
-      <c r="C43" s="6">
-        <v>-18.11</v>
-      </c>
-      <c r="D43" s="6">
-        <v>-18.36</v>
-      </c>
-      <c r="E43" s="7">
-        <v>-0.25</v>
-      </c>
-    </row>
-    <row r="44" spans="1:5">
-      <c r="A44" s="5" t="s">
-        <v>42</v>
-      </c>
-      <c r="B44" s="5" t="s">
-        <v>6</v>
-      </c>
-      <c r="C44" s="6">
-        <v>-10.73</v>
-      </c>
-      <c r="D44" s="6">
-        <v>-12.91</v>
-      </c>
-      <c r="E44" s="7">
-        <v>-2.18</v>
-      </c>
-    </row>
-    <row r="45" spans="1:5">
-      <c r="A45" s="5" t="s">
-        <v>43</v>
-      </c>
-      <c r="B45" s="5" t="s">
-        <v>6</v>
-      </c>
-      <c r="C45" s="6">
-        <v>-6.36</v>
-      </c>
-      <c r="D45" s="6">
-        <v>-8.949999999999999</v>
-      </c>
-      <c r="E45" s="7">
-        <v>-2.59</v>
-      </c>
-    </row>
-    <row r="46" spans="1:5">
-      <c r="A46" s="5" t="s">
-        <v>37</v>
-      </c>
-      <c r="B46" s="5" t="s">
-        <v>2</v>
-      </c>
-      <c r="C46" s="6">
-        <v>11678</v>
-      </c>
-      <c r="D46" s="6">
-        <v>11424</v>
-      </c>
-      <c r="E46" s="7">
-        <v>-254</v>
-      </c>
-    </row>
-    <row r="47" spans="1:5">
-      <c r="A47" s="5" t="s">
-        <v>38</v>
-      </c>
-      <c r="B47" s="5" t="s">
-        <v>2</v>
-      </c>
-      <c r="C47" s="6">
-        <v>520.5</v>
-      </c>
-      <c r="D47" s="6">
-        <v>503.8</v>
-      </c>
-      <c r="E47" s="7">
-        <v>-16.7</v>
-      </c>
-    </row>
-    <row r="48" spans="1:5">
-      <c r="A48" s="5" t="s">
-        <v>39</v>
-      </c>
-      <c r="B48" s="5" t="s">
-        <v>2</v>
-      </c>
-      <c r="C48" s="6">
-        <v>335.3</v>
-      </c>
-      <c r="D48" s="6">
-        <v>328.4</v>
-      </c>
-      <c r="E48" s="7">
-        <v>-6.9</v>
-      </c>
-    </row>
-    <row r="49" spans="1:5">
-      <c r="A49" s="5" t="s">
-        <v>40</v>
-      </c>
-      <c r="B49" s="5" t="s">
-        <v>2</v>
-      </c>
-      <c r="C49" s="6">
-        <v>1913.5</v>
-      </c>
-      <c r="D49" s="6">
-        <v>1855.5</v>
-      </c>
-      <c r="E49" s="7">
-        <v>-58</v>
-      </c>
-    </row>
-    <row r="50" spans="1:5">
-      <c r="A50" s="5" t="s">
-        <v>41</v>
-      </c>
-      <c r="B50" s="5" t="s">
-        <v>2</v>
-      </c>
-      <c r="C50" s="6">
-        <v>11134</v>
-      </c>
-      <c r="D50" s="6">
-        <v>11100</v>
-      </c>
-      <c r="E50" s="7">
-        <v>-34</v>
-      </c>
-    </row>
-    <row r="51" spans="1:5">
-      <c r="A51" s="5" t="s">
-        <v>42</v>
-      </c>
-      <c r="B51" s="5" t="s">
-        <v>2</v>
-      </c>
-      <c r="C51" s="6">
-        <v>1034.5</v>
-      </c>
-      <c r="D51" s="6">
-        <v>1009.2</v>
-      </c>
-      <c r="E51" s="7">
-        <v>-25.3</v>
-      </c>
-    </row>
-    <row r="52" spans="1:5">
-      <c r="A52" s="5" t="s">
-        <v>43</v>
-      </c>
-      <c r="B52" s="5" t="s">
-        <v>2</v>
-      </c>
-      <c r="C52" s="6">
-        <v>139.48</v>
-      </c>
-      <c r="D52" s="6">
-        <v>135.62</v>
-      </c>
-      <c r="E52" s="7">
-        <v>-3.86</v>
-      </c>
-    </row>
-    <row r="53" spans="1:5">
-      <c r="A53" s="5" t="s">
-        <v>37</v>
-      </c>
-      <c r="B53" s="5" t="s">
-        <v>24</v>
-      </c>
-      <c r="C53" s="6">
-        <v>48.9</v>
-      </c>
-      <c r="D53" s="6">
-        <v>41.71</v>
-      </c>
-      <c r="E53" s="7">
-        <v>-7.19</v>
-      </c>
-    </row>
-    <row r="54" spans="1:5">
-      <c r="A54" s="5" t="s">
-        <v>38</v>
-      </c>
-      <c r="B54" s="5" t="s">
-        <v>24</v>
-      </c>
-      <c r="C54" s="6">
-        <v>54.35</v>
-      </c>
-      <c r="D54" s="6">
-        <v>48.39</v>
-      </c>
-      <c r="E54" s="7">
-        <v>-5.96</v>
-      </c>
-    </row>
-    <row r="55" spans="1:5">
-      <c r="A55" s="5" t="s">
-        <v>39</v>
-      </c>
-      <c r="B55" s="5" t="s">
-        <v>24</v>
-      </c>
-      <c r="C55" s="6">
-        <v>46.52</v>
-      </c>
-      <c r="D55" s="6">
-        <v>41.76</v>
-      </c>
-      <c r="E55" s="7">
-        <v>-4.76</v>
-      </c>
-    </row>
-    <row r="56" spans="1:5">
-      <c r="A56" s="5" t="s">
-        <v>40</v>
-      </c>
-      <c r="B56" s="5" t="s">
-        <v>24</v>
-      </c>
-      <c r="C56" s="6">
-        <v>37.41</v>
-      </c>
-      <c r="D56" s="6">
-        <v>29.72</v>
-      </c>
-      <c r="E56" s="7">
-        <v>-7.69</v>
-      </c>
-    </row>
-    <row r="57" spans="1:5">
-      <c r="A57" s="5" t="s">
-        <v>41</v>
-      </c>
-      <c r="B57" s="5" t="s">
-        <v>24</v>
-      </c>
-      <c r="C57" s="6">
-        <v>48.63</v>
-      </c>
-      <c r="D57" s="6">
-        <v>47.66</v>
-      </c>
-      <c r="E57" s="7">
-        <v>-0.97</v>
-      </c>
-    </row>
-    <row r="58" spans="1:5">
-      <c r="A58" s="5" t="s">
-        <v>42</v>
-      </c>
-      <c r="B58" s="5" t="s">
-        <v>24</v>
-      </c>
-      <c r="C58" s="6">
-        <v>38.17</v>
-      </c>
-      <c r="D58" s="6">
-        <v>31.65</v>
-      </c>
-      <c r="E58" s="7">
-        <v>-6.52</v>
-      </c>
-    </row>
-    <row r="59" spans="1:5">
-      <c r="A59" s="5" t="s">
-        <v>43</v>
-      </c>
-      <c r="B59" s="5" t="s">
-        <v>24</v>
-      </c>
-      <c r="C59" s="6">
-        <v>54.62</v>
-      </c>
-      <c r="D59" s="6">
-        <v>46.1</v>
-      </c>
-      <c r="E59" s="7">
-        <v>-8.52</v>
-      </c>
-    </row>
-    <row r="60" spans="1:5">
-      <c r="A60" s="5" t="s">
-        <v>37</v>
-      </c>
-      <c r="B60" s="5" t="s">
+      <c r="B62" s="3" t="s">
         <v>31</v>
       </c>
-      <c r="C60" s="6">
-        <v>-2.16</v>
-      </c>
-      <c r="D60" s="6">
-        <v>6.11</v>
-      </c>
-      <c r="E60" s="8">
-        <v>8.27</v>
-      </c>
-    </row>
-    <row r="61" spans="1:5">
-      <c r="A61" s="5" t="s">
-        <v>38</v>
-      </c>
-      <c r="B61" s="5" t="s">
-        <v>31</v>
-      </c>
-      <c r="C61" s="6">
-        <v>-9.779999999999999</v>
-      </c>
-      <c r="D61" s="6">
-        <v>-20</v>
-      </c>
-      <c r="E61" s="7">
-        <v>-10.22</v>
-      </c>
-    </row>
-    <row r="62" spans="1:5">
-      <c r="A62" s="5" t="s">
-        <v>39</v>
-      </c>
-      <c r="B62" s="5" t="s">
-        <v>31</v>
-      </c>
-      <c r="C62" s="6">
-        <v>-41.68</v>
-      </c>
-      <c r="D62" s="6">
-        <v>-24.2</v>
-      </c>
-      <c r="E62" s="8">
-        <v>17.48</v>
-      </c>
-    </row>
-    <row r="63" spans="1:5">
-      <c r="A63" s="5" t="s">
-        <v>40</v>
-      </c>
-      <c r="B63" s="5" t="s">
-        <v>31</v>
-      </c>
-      <c r="C63" s="6">
-        <v>18.72</v>
-      </c>
-      <c r="D63" s="6">
-        <v>-23.58</v>
-      </c>
-      <c r="E63" s="7">
-        <v>-42.3</v>
-      </c>
-    </row>
-    <row r="64" spans="1:5">
-      <c r="A64" s="5" t="s">
-        <v>41</v>
-      </c>
-      <c r="B64" s="5" t="s">
-        <v>31</v>
-      </c>
-      <c r="C64" s="6">
-        <v>12.13</v>
-      </c>
-      <c r="D64" s="6">
-        <v>23.5</v>
-      </c>
-      <c r="E64" s="8">
-        <v>11.37</v>
-      </c>
-    </row>
-    <row r="65" spans="1:5">
-      <c r="A65" s="5" t="s">
-        <v>42</v>
-      </c>
-      <c r="B65" s="5" t="s">
-        <v>31</v>
-      </c>
-      <c r="C65" s="6">
-        <v>18.32</v>
-      </c>
-      <c r="D65" s="6">
-        <v>22.75</v>
-      </c>
-      <c r="E65" s="8">
-        <v>4.43</v>
-      </c>
-    </row>
-    <row r="66" spans="1:5">
-      <c r="A66" s="5" t="s">
-        <v>43</v>
-      </c>
-      <c r="B66" s="5" t="s">
-        <v>31</v>
-      </c>
-      <c r="C66" s="6">
-        <v>-10.14</v>
-      </c>
-      <c r="D66" s="6">
+      <c r="C62" s="5">
         <v>-36.4</v>
       </c>
-      <c r="E66" s="7">
-        <v>-26.26</v>
+      <c r="D62" s="5">
+        <v>62.21</v>
+      </c>
+      <c r="E62" s="6">
+        <v>98.61</v>
       </c>
     </row>
   </sheetData>
   <mergeCells count="2">
     <mergeCell ref="A1:F1"/>
-    <mergeCell ref="A9:E9"/>
+    <mergeCell ref="A5:E5"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -2999,60 +2841,60 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:9" ht="28" customHeight="1">
-      <c r="A1" s="9" t="s">
+      <c r="A1" s="8" t="s">
         <v>1</v>
       </c>
-      <c r="B1" s="9" t="s">
+      <c r="B1" s="8" t="s">
+        <v>56</v>
+      </c>
+      <c r="C1" s="8" t="s">
+        <v>57</v>
+      </c>
+      <c r="D1" s="8" t="s">
+        <v>58</v>
+      </c>
+      <c r="E1" s="8" t="s">
+        <v>59</v>
+      </c>
+      <c r="F1" s="8" t="s">
+        <v>60</v>
+      </c>
+      <c r="G1" s="8" t="s">
+        <v>61</v>
+      </c>
+      <c r="H1" s="8" t="s">
+        <v>62</v>
+      </c>
+      <c r="I1" s="8" t="s">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="2" spans="1:9">
+      <c r="A2" s="9" t="s">
+        <v>44</v>
+      </c>
+      <c r="B2" s="10">
+        <v>60.8</v>
+      </c>
+      <c r="C2" s="11">
+        <v>7</v>
+      </c>
+      <c r="D2" s="10">
+        <v>39.8</v>
+      </c>
+      <c r="E2" s="10">
         <v>70</v>
       </c>
-      <c r="C1" s="9" t="s">
-        <v>71</v>
-      </c>
-      <c r="D1" s="9" t="s">
-        <v>72</v>
-      </c>
-      <c r="E1" s="9" t="s">
-        <v>73</v>
-      </c>
-      <c r="F1" s="9" t="s">
-        <v>74</v>
-      </c>
-      <c r="G1" s="9" t="s">
-        <v>75</v>
-      </c>
-      <c r="H1" s="9" t="s">
-        <v>76</v>
-      </c>
-      <c r="I1" s="9" t="s">
-        <v>77</v>
-      </c>
-    </row>
-    <row r="2" spans="1:9">
-      <c r="A2" s="10" t="s">
-        <v>44</v>
-      </c>
-      <c r="B2" s="11">
-        <v>60.8</v>
-      </c>
-      <c r="C2" s="12">
-        <v>7</v>
-      </c>
-      <c r="D2" s="11">
-        <v>41</v>
-      </c>
-      <c r="E2" s="11">
-        <v>70</v>
-      </c>
-      <c r="F2" s="11">
-        <v>-4</v>
-      </c>
-      <c r="G2" s="11">
-        <v>2.2</v>
-      </c>
-      <c r="H2" s="11">
+      <c r="F2" s="10">
+        <v>-4.1</v>
+      </c>
+      <c r="G2" s="10">
+        <v>1.4</v>
+      </c>
+      <c r="H2" s="10">
         <v>57</v>
       </c>
-      <c r="I2" s="11">
+      <c r="I2" s="10">
         <v>40</v>
       </c>
     </row>
@@ -3154,49 +2996,49 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:7">
-      <c r="A1" s="13" t="s">
+      <c r="A1" s="12" t="s">
         <v>37</v>
       </c>
-      <c r="B1" s="13" t="s">
+      <c r="B1" s="12" t="s">
         <v>41</v>
       </c>
-      <c r="C1" s="13" t="s">
+      <c r="C1" s="12" t="s">
         <v>38</v>
       </c>
-      <c r="D1" s="13" t="s">
+      <c r="D1" s="12" t="s">
         <v>42</v>
       </c>
-      <c r="E1" s="13" t="s">
+      <c r="E1" s="12" t="s">
         <v>40</v>
       </c>
-      <c r="F1" s="13" t="s">
+      <c r="F1" s="12" t="s">
         <v>43</v>
       </c>
-      <c r="G1" s="13" t="s">
+      <c r="G1" s="12" t="s">
         <v>39</v>
       </c>
     </row>
     <row r="2" spans="1:7">
-      <c r="A2" s="14">
-        <v>0.2765</v>
-      </c>
-      <c r="B2" s="14">
-        <v>0.2263</v>
-      </c>
-      <c r="C2" s="14">
-        <v>0.1601</v>
-      </c>
-      <c r="D2" s="14">
-        <v>0.0677</v>
-      </c>
-      <c r="E2" s="14">
-        <v>0.0201</v>
-      </c>
-      <c r="F2" s="14">
-        <v>-0.0019</v>
-      </c>
-      <c r="G2" s="14">
-        <v>-0.2424</v>
+      <c r="A2" s="13">
+        <v>0.2779</v>
+      </c>
+      <c r="B2" s="13">
+        <v>0.2216</v>
+      </c>
+      <c r="C2" s="13">
+        <v>0.1621</v>
+      </c>
+      <c r="D2" s="13">
+        <v>0.06709999999999999</v>
+      </c>
+      <c r="E2" s="13">
+        <v>0.0193</v>
+      </c>
+      <c r="F2" s="13">
+        <v>-0.0021</v>
+      </c>
+      <c r="G2" s="13">
+        <v>-0.2478</v>
       </c>
     </row>
   </sheetData>

--- a/BAJAJ_GROUP_Technical_Metrics.xlsx
+++ b/BAJAJ_GROUP_Technical_Metrics.xlsx
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="253" uniqueCount="64">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="264" uniqueCount="73">
   <si>
     <t>Symbol</t>
   </si>
@@ -172,7 +172,34 @@
     <t>▶  SIGNAL EVENTS (vs Previous Run)</t>
   </si>
   <si>
-    <t>No signal events detected since last run.</t>
+    <t>Signal</t>
+  </si>
+  <si>
+    <t>Change</t>
+  </si>
+  <si>
+    <t>Direction</t>
+  </si>
+  <si>
+    <t>Prev Value</t>
+  </si>
+  <si>
+    <t>Curr Value</t>
+  </si>
+  <si>
+    <t>RSI Oversold Recovery</t>
+  </si>
+  <si>
+    <t>27.8 → 33.4</t>
+  </si>
+  <si>
+    <t>🟢 BULLISH</t>
+  </si>
+  <si>
+    <t>27.8</t>
+  </si>
+  <si>
+    <t>33.4</t>
   </si>
   <si>
     <t>▶  NUMERIC METRIC CHANGES (vs Previous Run)</t>
@@ -374,17 +401,18 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="14">
+  <cellXfs count="15">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="2" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="3" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
+    <xf numFmtId="0" fontId="4" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1"/>
+    <xf numFmtId="165" fontId="5" fillId="6" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="165" fontId="4" fillId="5" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="165" fontId="5" fillId="6" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="3" fillId="7" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
@@ -755,8 +783,8 @@
     <col min="13" max="13" width="10.7109375" customWidth="1"/>
     <col min="14" max="14" width="11.7109375" customWidth="1"/>
     <col min="15" max="15" width="10.7109375" customWidth="1"/>
-    <col min="16" max="17" width="9.7109375" customWidth="1"/>
-    <col min="18" max="19" width="10.7109375" customWidth="1"/>
+    <col min="16" max="16" width="9.7109375" customWidth="1"/>
+    <col min="17" max="19" width="10.7109375" customWidth="1"/>
     <col min="20" max="20" width="22.7109375" customWidth="1"/>
     <col min="21" max="21" width="9.7109375" customWidth="1"/>
     <col min="22" max="22" width="10.7109375" customWidth="1"/>
@@ -896,10 +924,10 @@
         <v>44</v>
       </c>
       <c r="C2">
-        <v>11593</v>
+        <v>11500</v>
       </c>
       <c r="D2">
-        <v>1.48</v>
+        <v>-0.8</v>
       </c>
       <c r="E2">
         <v>12361</v>
@@ -908,25 +936,25 @@
         <v>8506.780000000001</v>
       </c>
       <c r="G2">
-        <v>-6.21</v>
+        <v>-6.97</v>
       </c>
       <c r="H2">
-        <v>36.28</v>
+        <v>35.19</v>
       </c>
       <c r="I2">
-        <v>-2.42</v>
+        <v>-2.46</v>
       </c>
       <c r="J2">
-        <v>-0.91</v>
+        <v>-0.92</v>
       </c>
       <c r="K2">
-        <v>15.45</v>
+        <v>14.12</v>
       </c>
       <c r="L2">
-        <v>29</v>
+        <v>29.58</v>
       </c>
       <c r="M2">
-        <v>27.79</v>
+        <v>27.53</v>
       </c>
       <c r="N2">
         <v>85</v>
@@ -935,19 +963,19 @@
         <v>82</v>
       </c>
       <c r="P2">
-        <v>11650.6</v>
+        <v>11592.6</v>
       </c>
       <c r="Q2">
-        <v>11830.6</v>
+        <v>11823.35</v>
       </c>
       <c r="R2">
-        <v>11404.35</v>
+        <v>11431.07</v>
       </c>
       <c r="S2">
-        <v>10018.66</v>
+        <v>10031.42</v>
       </c>
       <c r="T2">
-        <v>15.71</v>
+        <v>14.64</v>
       </c>
       <c r="U2" t="s">
         <v>45</v>
@@ -962,34 +990,34 @@
         <v>3</v>
       </c>
       <c r="Y2">
-        <v>47.27</v>
+        <v>44.74</v>
       </c>
       <c r="Z2">
-        <v>52.59</v>
+        <v>29.1</v>
       </c>
       <c r="AA2">
-        <v>138.7</v>
+        <v>116.78</v>
       </c>
       <c r="AB2">
-        <v>-86.12</v>
+        <v>-87.68000000000001</v>
       </c>
       <c r="AC2">
-        <v>5.89</v>
+        <v>9.109999999999999</v>
       </c>
       <c r="AD2">
-        <v>1.96</v>
+        <v>5</v>
       </c>
       <c r="AE2">
-        <v>220.81</v>
+        <v>216.32</v>
       </c>
       <c r="AF2">
-        <v>37.09</v>
+        <v>-43.46</v>
       </c>
       <c r="AG2">
-        <v>12246.97</v>
+        <v>12257.97</v>
       </c>
       <c r="AH2">
-        <v>11414.23</v>
+        <v>11388.73</v>
       </c>
       <c r="AI2">
         <v>12149.93</v>
@@ -998,7 +1026,7 @@
         <v>47</v>
       </c>
       <c r="AK2">
-        <v>30.09</v>
+        <v>31.21</v>
       </c>
     </row>
     <row r="3" spans="1:37">
@@ -1009,58 +1037,58 @@
         <v>44</v>
       </c>
       <c r="C3">
-        <v>498.05</v>
+        <v>502.45</v>
       </c>
       <c r="D3">
-        <v>-1.14</v>
+        <v>0.88</v>
       </c>
       <c r="E3">
         <v>670.25</v>
       </c>
       <c r="F3">
-        <v>223.92</v>
+        <v>228.14</v>
       </c>
       <c r="G3">
-        <v>-25.69</v>
+        <v>-25.04</v>
       </c>
       <c r="H3">
-        <v>122.42</v>
+        <v>120.24</v>
       </c>
       <c r="I3">
-        <v>-3.12</v>
+        <v>-3.64</v>
       </c>
       <c r="J3">
-        <v>3.46</v>
+        <v>3.8</v>
       </c>
       <c r="K3">
-        <v>-17.38</v>
+        <v>-19.02</v>
       </c>
       <c r="L3">
-        <v>117.97</v>
+        <v>124.39</v>
       </c>
       <c r="M3">
-        <v>16.21</v>
+        <v>16.11</v>
       </c>
       <c r="N3">
         <v>99</v>
       </c>
       <c r="O3">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="P3">
-        <v>513.65</v>
+        <v>509.85</v>
       </c>
       <c r="Q3">
-        <v>492.06</v>
+        <v>492.15</v>
       </c>
       <c r="R3">
-        <v>526.52</v>
+        <v>524.29</v>
       </c>
       <c r="S3">
-        <v>439.02</v>
+        <v>440.19</v>
       </c>
       <c r="T3">
-        <v>13.45</v>
+        <v>14.14</v>
       </c>
       <c r="U3" t="s">
         <v>46</v>
@@ -1075,34 +1103,34 @@
         <v>2</v>
       </c>
       <c r="Y3">
-        <v>46.5</v>
+        <v>48.17</v>
       </c>
       <c r="Z3">
-        <v>-1.54</v>
+        <v>-1.68</v>
       </c>
       <c r="AA3">
-        <v>-5.96</v>
+        <v>-5.1</v>
       </c>
       <c r="AB3">
-        <v>4.42</v>
+        <v>3.42</v>
       </c>
       <c r="AC3">
-        <v>72.98999999999999</v>
+        <v>59.26</v>
       </c>
       <c r="AD3">
-        <v>83.70999999999999</v>
+        <v>72.37</v>
       </c>
       <c r="AE3">
-        <v>20.98</v>
+        <v>20.58</v>
       </c>
       <c r="AF3">
-        <v>-52.13</v>
+        <v>-68.7</v>
       </c>
       <c r="AG3">
-        <v>541.25</v>
+        <v>541.41</v>
       </c>
       <c r="AH3">
-        <v>442.87</v>
+        <v>442.89</v>
       </c>
       <c r="AI3">
         <v>460.99</v>
@@ -1111,7 +1139,7 @@
         <v>48</v>
       </c>
       <c r="AK3">
-        <v>27.59</v>
+        <v>24.56</v>
       </c>
     </row>
     <row r="4" spans="1:37">
@@ -1122,10 +1150,10 @@
         <v>44</v>
       </c>
       <c r="C4">
-        <v>322.55</v>
+        <v>325.3</v>
       </c>
       <c r="D4">
-        <v>-1.78</v>
+        <v>0.85</v>
       </c>
       <c r="E4">
         <v>604.85</v>
@@ -1134,46 +1162,46 @@
         <v>303.75</v>
       </c>
       <c r="G4">
-        <v>-46.67</v>
+        <v>-46.22</v>
       </c>
       <c r="H4">
-        <v>6.19</v>
+        <v>7.09</v>
       </c>
       <c r="I4">
-        <v>-5.12</v>
+        <v>-4.27</v>
       </c>
       <c r="J4">
-        <v>-11</v>
+        <v>-8.51</v>
       </c>
       <c r="K4">
-        <v>-1.6</v>
+        <v>-1.14</v>
       </c>
       <c r="L4">
-        <v>-44.94</v>
+        <v>-44.65</v>
       </c>
       <c r="M4">
-        <v>-24.78</v>
+        <v>-25.14</v>
       </c>
       <c r="N4">
         <v>15</v>
       </c>
       <c r="O4">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="P4">
-        <v>332.76</v>
+        <v>329.86</v>
       </c>
       <c r="Q4">
-        <v>336.61</v>
+        <v>335.19</v>
       </c>
       <c r="R4">
-        <v>339.78</v>
+        <v>339.87</v>
       </c>
       <c r="S4">
-        <v>376.9</v>
+        <v>376.12</v>
       </c>
       <c r="T4">
-        <v>-14.42</v>
+        <v>-13.51</v>
       </c>
       <c r="U4" t="s">
         <v>46</v>
@@ -1188,43 +1216,43 @@
         <v>0</v>
       </c>
       <c r="Y4">
-        <v>38.2</v>
+        <v>40.76</v>
       </c>
       <c r="Z4">
-        <v>-3.65</v>
+        <v>-4.06</v>
       </c>
       <c r="AA4">
-        <v>-2.58</v>
+        <v>-2.87</v>
       </c>
       <c r="AB4">
-        <v>-1.07</v>
+        <v>-1.18</v>
       </c>
       <c r="AC4">
-        <v>37.1</v>
+        <v>24.04</v>
       </c>
       <c r="AD4">
-        <v>58</v>
+        <v>40.41</v>
       </c>
       <c r="AE4">
-        <v>10.71</v>
+        <v>10.36</v>
       </c>
       <c r="AF4">
-        <v>-40.98</v>
+        <v>-66.45</v>
       </c>
       <c r="AG4">
-        <v>355.59</v>
+        <v>353.04</v>
       </c>
       <c r="AH4">
-        <v>317.63</v>
+        <v>317.35</v>
       </c>
       <c r="AI4">
-        <v>355.84</v>
+        <v>354.2</v>
       </c>
       <c r="AJ4" t="s">
         <v>47</v>
       </c>
       <c r="AK4">
-        <v>21.14</v>
+        <v>21.07</v>
       </c>
     </row>
     <row r="5" spans="1:37">
@@ -1235,10 +1263,10 @@
         <v>44</v>
       </c>
       <c r="C5">
-        <v>1837</v>
+        <v>1859.2</v>
       </c>
       <c r="D5">
-        <v>-1</v>
+        <v>1.21</v>
       </c>
       <c r="E5">
         <v>2176.6</v>
@@ -1247,46 +1275,46 @@
         <v>1631.8</v>
       </c>
       <c r="G5">
-        <v>-15.6</v>
+        <v>-14.58</v>
       </c>
       <c r="H5">
-        <v>12.58</v>
+        <v>13.94</v>
       </c>
       <c r="I5">
-        <v>-5.22</v>
+        <v>-3.52</v>
       </c>
       <c r="J5">
-        <v>-8.380000000000001</v>
+        <v>-7.56</v>
       </c>
       <c r="K5">
-        <v>4.1</v>
+        <v>4.94</v>
       </c>
       <c r="L5">
-        <v>-9.85</v>
+        <v>-10.68</v>
       </c>
       <c r="M5">
-        <v>1.93</v>
+        <v>2.04</v>
       </c>
       <c r="N5">
         <v>43</v>
       </c>
       <c r="O5">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="P5">
-        <v>1894.7</v>
+        <v>1881.14</v>
       </c>
       <c r="Q5">
-        <v>1969.22</v>
+        <v>1961.58</v>
       </c>
       <c r="R5">
-        <v>1959.67</v>
+        <v>1959.76</v>
       </c>
       <c r="S5">
-        <v>1899.95</v>
+        <v>1898.78</v>
       </c>
       <c r="T5">
-        <v>-3.31</v>
+        <v>-2.08</v>
       </c>
       <c r="U5" t="s">
         <v>45</v>
@@ -1301,43 +1329,43 @@
         <v>2</v>
       </c>
       <c r="Y5">
-        <v>27.76</v>
+        <v>33.43</v>
       </c>
       <c r="Z5">
-        <v>-25.91</v>
+        <v>-29.37</v>
       </c>
       <c r="AA5">
-        <v>-7.11</v>
+        <v>-11.56</v>
       </c>
       <c r="AB5">
-        <v>-18.8</v>
+        <v>-17.8</v>
       </c>
       <c r="AC5">
-        <v>0</v>
+        <v>6.34</v>
       </c>
       <c r="AD5">
-        <v>4.19</v>
+        <v>4.21</v>
       </c>
       <c r="AE5">
-        <v>38.35</v>
+        <v>37.82</v>
       </c>
       <c r="AF5">
-        <v>0.01</v>
+        <v>-22.51</v>
       </c>
       <c r="AG5">
-        <v>2078.24</v>
+        <v>2079.06</v>
       </c>
       <c r="AH5">
-        <v>1860.21</v>
+        <v>1844.11</v>
       </c>
       <c r="AI5">
-        <v>1968.89</v>
+        <v>1961</v>
       </c>
       <c r="AJ5" t="s">
         <v>47</v>
       </c>
       <c r="AK5">
-        <v>57.68</v>
+        <v>61.51</v>
       </c>
     </row>
     <row r="6" spans="1:37">
@@ -1348,10 +1376,10 @@
         <v>44</v>
       </c>
       <c r="C6">
-        <v>10930</v>
+        <v>11010</v>
       </c>
       <c r="D6">
-        <v>-1.53</v>
+        <v>0.73</v>
       </c>
       <c r="E6">
         <v>13595.75</v>
@@ -1360,46 +1388,46 @@
         <v>8746</v>
       </c>
       <c r="G6">
-        <v>-19.61</v>
+        <v>-19.02</v>
       </c>
       <c r="H6">
-        <v>24.97</v>
+        <v>25.89</v>
       </c>
       <c r="I6">
-        <v>-1.05</v>
+        <v>-0.61</v>
       </c>
       <c r="J6">
-        <v>-4.75</v>
+        <v>-2.17</v>
       </c>
       <c r="K6">
-        <v>4.1</v>
+        <v>3.13</v>
       </c>
       <c r="L6">
-        <v>-16.15</v>
+        <v>-16.25</v>
       </c>
       <c r="M6">
-        <v>22.16</v>
+        <v>21.89</v>
       </c>
       <c r="N6">
         <v>29</v>
       </c>
       <c r="O6">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="P6">
-        <v>11046.8</v>
+        <v>11033.2</v>
       </c>
       <c r="Q6">
-        <v>11218.7</v>
+        <v>11200.2</v>
       </c>
       <c r="R6">
-        <v>11068.82</v>
+        <v>11082.3</v>
       </c>
       <c r="S6">
-        <v>10682.77</v>
+        <v>10680.32</v>
       </c>
       <c r="T6">
-        <v>2.31</v>
+        <v>3.09</v>
       </c>
       <c r="U6" t="s">
         <v>45</v>
@@ -1414,34 +1442,34 @@
         <v>3</v>
       </c>
       <c r="Y6">
-        <v>43.01</v>
+        <v>45.69</v>
       </c>
       <c r="Z6">
-        <v>-44.43</v>
+        <v>-49.38</v>
       </c>
       <c r="AA6">
-        <v>0.98</v>
+        <v>-9.09</v>
       </c>
       <c r="AB6">
-        <v>-45.4</v>
+        <v>-40.28</v>
       </c>
       <c r="AC6">
-        <v>19.81</v>
+        <v>14.44</v>
       </c>
       <c r="AD6">
-        <v>20.52</v>
+        <v>18.74</v>
       </c>
       <c r="AE6">
-        <v>219.97</v>
+        <v>217.26</v>
       </c>
       <c r="AF6">
-        <v>-45.91</v>
+        <v>-28.52</v>
       </c>
       <c r="AG6">
-        <v>11604.74</v>
+        <v>11589.15</v>
       </c>
       <c r="AH6">
-        <v>10832.66</v>
+        <v>10811.25</v>
       </c>
       <c r="AI6">
         <v>10787.84</v>
@@ -1450,7 +1478,7 @@
         <v>48</v>
       </c>
       <c r="AK6">
-        <v>18.77</v>
+        <v>19.9</v>
       </c>
     </row>
     <row r="7" spans="1:37">
@@ -1461,10 +1489,10 @@
         <v>44</v>
       </c>
       <c r="C7">
-        <v>1006.2</v>
+        <v>1015</v>
       </c>
       <c r="D7">
-        <v>-0.3</v>
+        <v>0.87</v>
       </c>
       <c r="E7">
         <v>1158.8</v>
@@ -1473,46 +1501,46 @@
         <v>801.55</v>
       </c>
       <c r="G7">
-        <v>-13.17</v>
+        <v>-12.41</v>
       </c>
       <c r="H7">
-        <v>25.53</v>
+        <v>26.63</v>
       </c>
       <c r="I7">
-        <v>-4.54</v>
+        <v>-2.34</v>
       </c>
       <c r="J7">
-        <v>-7.63</v>
+        <v>-7.25</v>
       </c>
       <c r="K7">
-        <v>4.99</v>
+        <v>5.86</v>
       </c>
       <c r="L7">
-        <v>3.71</v>
+        <v>1.17</v>
       </c>
       <c r="M7">
-        <v>6.71</v>
+        <v>6.85</v>
       </c>
       <c r="N7">
         <v>71</v>
       </c>
       <c r="O7">
-        <v>64</v>
+        <v>62</v>
       </c>
       <c r="P7">
-        <v>1026.54</v>
+        <v>1021.68</v>
       </c>
       <c r="Q7">
-        <v>1060.28</v>
+        <v>1057.02</v>
       </c>
       <c r="R7">
-        <v>1066.23</v>
+        <v>1066.32</v>
       </c>
       <c r="S7">
-        <v>977.75</v>
+        <v>977.63</v>
       </c>
       <c r="T7">
-        <v>2.91</v>
+        <v>3.82</v>
       </c>
       <c r="U7" t="s">
         <v>46</v>
@@ -1527,34 +1555,34 @@
         <v>2</v>
       </c>
       <c r="Y7">
-        <v>30.97</v>
+        <v>35.33</v>
       </c>
       <c r="Z7">
-        <v>-14.05</v>
+        <v>-15.13</v>
       </c>
       <c r="AA7">
-        <v>-6.72</v>
+        <v>-8.4</v>
       </c>
       <c r="AB7">
-        <v>-7.33</v>
+        <v>-6.73</v>
       </c>
       <c r="AC7">
-        <v>0</v>
+        <v>7.53</v>
       </c>
       <c r="AD7">
-        <v>3.15</v>
+        <v>4.08</v>
       </c>
       <c r="AE7">
-        <v>20.96</v>
+        <v>21.01</v>
       </c>
       <c r="AF7">
-        <v>-12.55</v>
+        <v>-1.34</v>
       </c>
       <c r="AG7">
-        <v>1111.56</v>
+        <v>1111.18</v>
       </c>
       <c r="AH7">
-        <v>1009</v>
+        <v>1002.86</v>
       </c>
       <c r="AI7">
         <v>1075.64</v>
@@ -1563,7 +1591,7 @@
         <v>47</v>
       </c>
       <c r="AK7">
-        <v>45.88</v>
+        <v>45.65</v>
       </c>
     </row>
     <row r="8" spans="1:37">
@@ -1574,10 +1602,10 @@
         <v>44</v>
       </c>
       <c r="C8">
-        <v>134.89</v>
+        <v>134.2</v>
       </c>
       <c r="D8">
-        <v>-0.54</v>
+        <v>-0.51</v>
       </c>
       <c r="E8">
         <v>148.95</v>
@@ -1586,46 +1614,46 @@
         <v>115.96</v>
       </c>
       <c r="G8">
-        <v>-9.44</v>
+        <v>-9.9</v>
       </c>
       <c r="H8">
-        <v>16.32</v>
+        <v>15.73</v>
       </c>
       <c r="I8">
-        <v>-2.01</v>
+        <v>-3.93</v>
       </c>
       <c r="J8">
-        <v>0.5600000000000001</v>
+        <v>-1.1</v>
       </c>
       <c r="K8">
-        <v>0.46</v>
+        <v>-2.02</v>
       </c>
       <c r="L8">
-        <v>-1.12</v>
+        <v>-1.86</v>
       </c>
       <c r="M8">
-        <v>-0.21</v>
+        <v>-0.18</v>
       </c>
       <c r="N8">
         <v>57</v>
       </c>
       <c r="O8">
-        <v>60</v>
+        <v>57</v>
       </c>
       <c r="P8">
-        <v>138.45</v>
+        <v>137.35</v>
       </c>
       <c r="Q8">
-        <v>136.6</v>
+        <v>136.58</v>
       </c>
       <c r="R8">
-        <v>138.26</v>
+        <v>138.34</v>
       </c>
       <c r="S8">
         <v>133.81</v>
       </c>
       <c r="T8">
-        <v>0.8</v>
+        <v>0.29</v>
       </c>
       <c r="U8" t="s">
         <v>46</v>
@@ -1640,34 +1668,34 @@
         <v>2</v>
       </c>
       <c r="Y8">
-        <v>44.68</v>
+        <v>43.32</v>
       </c>
       <c r="Z8">
-        <v>-0.11</v>
+        <v>-0.34</v>
       </c>
       <c r="AA8">
-        <v>-0.24</v>
+        <v>-0.26</v>
       </c>
       <c r="AB8">
-        <v>0.13</v>
+        <v>-0.08</v>
       </c>
       <c r="AC8">
-        <v>40.78</v>
+        <v>25.77</v>
       </c>
       <c r="AD8">
-        <v>64.92</v>
+        <v>44.04</v>
       </c>
       <c r="AE8">
-        <v>4.48</v>
+        <v>4.41</v>
       </c>
       <c r="AF8">
-        <v>62.21</v>
+        <v>-70.84</v>
       </c>
       <c r="AG8">
-        <v>140.99</v>
+        <v>141.01</v>
       </c>
       <c r="AH8">
-        <v>132.2</v>
+        <v>132.15</v>
       </c>
       <c r="AI8">
         <v>131.91</v>
@@ -1676,7 +1704,7 @@
         <v>48</v>
       </c>
       <c r="AK8">
-        <v>28.75</v>
+        <v>26.34</v>
       </c>
     </row>
   </sheetData>
@@ -1837,12 +1865,47 @@
     </row>
     <row r="2" spans="1:6">
       <c r="A2" s="3" t="s">
+        <v>0</v>
+      </c>
+      <c r="B2" s="3" t="s">
         <v>50</v>
+      </c>
+      <c r="C2" s="3" t="s">
+        <v>51</v>
+      </c>
+      <c r="D2" s="3" t="s">
+        <v>52</v>
+      </c>
+      <c r="E2" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="F2" s="3" t="s">
+        <v>54</v>
+      </c>
+    </row>
+    <row r="3" spans="1:6">
+      <c r="A3" s="4" t="s">
+        <v>40</v>
+      </c>
+      <c r="B3" s="4" t="s">
+        <v>55</v>
+      </c>
+      <c r="C3" s="4" t="s">
+        <v>56</v>
+      </c>
+      <c r="D3" s="4" t="s">
+        <v>57</v>
+      </c>
+      <c r="E3" s="4" t="s">
+        <v>58</v>
+      </c>
+      <c r="F3" s="4" t="s">
+        <v>59</v>
       </c>
     </row>
     <row r="5" spans="1:6">
       <c r="A5" s="2" t="s">
-        <v>51</v>
+        <v>60</v>
       </c>
       <c r="B5" s="2"/>
       <c r="C5" s="2"/>
@@ -1850,972 +1913,972 @@
       <c r="E5" s="2"/>
     </row>
     <row r="6" spans="1:6">
-      <c r="A6" s="4" t="s">
+      <c r="A6" s="3" t="s">
         <v>0</v>
       </c>
-      <c r="B6" s="4" t="s">
-        <v>52</v>
-      </c>
-      <c r="C6" s="4" t="s">
-        <v>53</v>
-      </c>
-      <c r="D6" s="4" t="s">
-        <v>54</v>
-      </c>
-      <c r="E6" s="4" t="s">
-        <v>55</v>
+      <c r="B6" s="3" t="s">
+        <v>61</v>
+      </c>
+      <c r="C6" s="3" t="s">
+        <v>62</v>
+      </c>
+      <c r="D6" s="3" t="s">
+        <v>63</v>
+      </c>
+      <c r="E6" s="3" t="s">
+        <v>64</v>
       </c>
     </row>
     <row r="7" spans="1:6">
-      <c r="A7" s="3" t="s">
+      <c r="A7" s="5" t="s">
         <v>37</v>
       </c>
-      <c r="B7" s="3" t="s">
+      <c r="B7" s="5" t="s">
         <v>9</v>
       </c>
-      <c r="C7" s="5">
-        <v>-2.36</v>
-      </c>
-      <c r="D7" s="5">
+      <c r="C7" s="6">
         <v>-0.91</v>
       </c>
-      <c r="E7" s="6">
-        <v>1.45</v>
+      <c r="D7" s="6">
+        <v>-0.92</v>
+      </c>
+      <c r="E7" s="7">
+        <v>-0.01</v>
       </c>
     </row>
     <row r="8" spans="1:6">
-      <c r="A8" s="3" t="s">
+      <c r="A8" s="5" t="s">
         <v>38</v>
       </c>
-      <c r="B8" s="3" t="s">
+      <c r="B8" s="5" t="s">
         <v>9</v>
       </c>
-      <c r="C8" s="5">
-        <v>0.64</v>
-      </c>
-      <c r="D8" s="5">
+      <c r="C8" s="6">
         <v>3.46</v>
       </c>
-      <c r="E8" s="6">
-        <v>2.82</v>
+      <c r="D8" s="6">
+        <v>3.8</v>
+      </c>
+      <c r="E8" s="8">
+        <v>0.34</v>
       </c>
     </row>
     <row r="9" spans="1:6">
-      <c r="A9" s="3" t="s">
+      <c r="A9" s="5" t="s">
         <v>39</v>
       </c>
-      <c r="B9" s="3" t="s">
+      <c r="B9" s="5" t="s">
         <v>9</v>
       </c>
-      <c r="C9" s="5">
-        <v>-9.380000000000001</v>
-      </c>
-      <c r="D9" s="5">
+      <c r="C9" s="6">
         <v>-11</v>
       </c>
-      <c r="E9" s="7">
-        <v>-1.62</v>
+      <c r="D9" s="6">
+        <v>-8.51</v>
+      </c>
+      <c r="E9" s="8">
+        <v>2.49</v>
       </c>
     </row>
     <row r="10" spans="1:6">
-      <c r="A10" s="3" t="s">
+      <c r="A10" s="5" t="s">
         <v>40</v>
       </c>
-      <c r="B10" s="3" t="s">
+      <c r="B10" s="5" t="s">
         <v>9</v>
       </c>
-      <c r="C10" s="5">
-        <v>-7.61</v>
-      </c>
-      <c r="D10" s="5">
+      <c r="C10" s="6">
         <v>-8.380000000000001</v>
       </c>
-      <c r="E10" s="7">
-        <v>-0.77</v>
+      <c r="D10" s="6">
+        <v>-7.56</v>
+      </c>
+      <c r="E10" s="8">
+        <v>0.82</v>
       </c>
     </row>
     <row r="11" spans="1:6">
-      <c r="A11" s="3" t="s">
+      <c r="A11" s="5" t="s">
         <v>41</v>
       </c>
-      <c r="B11" s="3" t="s">
+      <c r="B11" s="5" t="s">
         <v>9</v>
       </c>
-      <c r="C11" s="5">
-        <v>-3.27</v>
-      </c>
-      <c r="D11" s="5">
+      <c r="C11" s="6">
         <v>-4.75</v>
       </c>
-      <c r="E11" s="7">
-        <v>-1.48</v>
+      <c r="D11" s="6">
+        <v>-2.17</v>
+      </c>
+      <c r="E11" s="8">
+        <v>2.58</v>
       </c>
     </row>
     <row r="12" spans="1:6">
-      <c r="A12" s="3" t="s">
+      <c r="A12" s="5" t="s">
         <v>42</v>
       </c>
-      <c r="B12" s="3" t="s">
+      <c r="B12" s="5" t="s">
         <v>9</v>
       </c>
-      <c r="C12" s="5">
-        <v>-7.16</v>
-      </c>
-      <c r="D12" s="5">
+      <c r="C12" s="6">
         <v>-7.63</v>
       </c>
-      <c r="E12" s="7">
-        <v>-0.47</v>
+      <c r="D12" s="6">
+        <v>-7.25</v>
+      </c>
+      <c r="E12" s="8">
+        <v>0.38</v>
       </c>
     </row>
     <row r="13" spans="1:6">
-      <c r="A13" s="3" t="s">
+      <c r="A13" s="5" t="s">
         <v>43</v>
       </c>
-      <c r="B13" s="3" t="s">
+      <c r="B13" s="5" t="s">
         <v>9</v>
       </c>
-      <c r="C13" s="5">
-        <v>1.1</v>
-      </c>
-      <c r="D13" s="5">
+      <c r="C13" s="6">
         <v>0.5600000000000001</v>
       </c>
+      <c r="D13" s="6">
+        <v>-1.1</v>
+      </c>
       <c r="E13" s="7">
-        <v>-0.54</v>
+        <v>-1.66</v>
       </c>
     </row>
     <row r="14" spans="1:6">
-      <c r="A14" s="3" t="s">
+      <c r="A14" s="5" t="s">
         <v>37</v>
       </c>
-      <c r="B14" s="3" t="s">
+      <c r="B14" s="5" t="s">
         <v>8</v>
       </c>
-      <c r="C14" s="5">
-        <v>-3.19</v>
-      </c>
-      <c r="D14" s="5">
+      <c r="C14" s="6">
         <v>-2.42</v>
       </c>
-      <c r="E14" s="6">
-        <v>0.77</v>
+      <c r="D14" s="6">
+        <v>-2.46</v>
+      </c>
+      <c r="E14" s="7">
+        <v>-0.04</v>
       </c>
     </row>
     <row r="15" spans="1:6">
-      <c r="A15" s="3" t="s">
+      <c r="A15" s="5" t="s">
         <v>38</v>
       </c>
-      <c r="B15" s="3" t="s">
+      <c r="B15" s="5" t="s">
         <v>8</v>
       </c>
-      <c r="C15" s="5">
-        <v>-4.22</v>
-      </c>
-      <c r="D15" s="5">
+      <c r="C15" s="6">
         <v>-3.12</v>
       </c>
-      <c r="E15" s="6">
-        <v>1.1</v>
+      <c r="D15" s="6">
+        <v>-3.64</v>
+      </c>
+      <c r="E15" s="7">
+        <v>-0.52</v>
       </c>
     </row>
     <row r="16" spans="1:6">
-      <c r="A16" s="3" t="s">
+      <c r="A16" s="5" t="s">
         <v>39</v>
       </c>
-      <c r="B16" s="3" t="s">
+      <c r="B16" s="5" t="s">
         <v>8</v>
       </c>
-      <c r="C16" s="5">
-        <v>-4</v>
-      </c>
-      <c r="D16" s="5">
+      <c r="C16" s="6">
         <v>-5.12</v>
       </c>
-      <c r="E16" s="7">
+      <c r="D16" s="6">
+        <v>-4.27</v>
+      </c>
+      <c r="E16" s="8">
+        <v>0.85</v>
+      </c>
+    </row>
+    <row r="17" spans="1:5">
+      <c r="A17" s="5" t="s">
+        <v>40</v>
+      </c>
+      <c r="B17" s="5" t="s">
+        <v>8</v>
+      </c>
+      <c r="C17" s="6">
+        <v>-5.22</v>
+      </c>
+      <c r="D17" s="6">
+        <v>-3.52</v>
+      </c>
+      <c r="E17" s="8">
+        <v>1.7</v>
+      </c>
+    </row>
+    <row r="18" spans="1:5">
+      <c r="A18" s="5" t="s">
+        <v>41</v>
+      </c>
+      <c r="B18" s="5" t="s">
+        <v>8</v>
+      </c>
+      <c r="C18" s="6">
+        <v>-1.05</v>
+      </c>
+      <c r="D18" s="6">
+        <v>-0.61</v>
+      </c>
+      <c r="E18" s="8">
+        <v>0.44</v>
+      </c>
+    </row>
+    <row r="19" spans="1:5">
+      <c r="A19" s="5" t="s">
+        <v>42</v>
+      </c>
+      <c r="B19" s="5" t="s">
+        <v>8</v>
+      </c>
+      <c r="C19" s="6">
+        <v>-4.54</v>
+      </c>
+      <c r="D19" s="6">
+        <v>-2.34</v>
+      </c>
+      <c r="E19" s="8">
+        <v>2.2</v>
+      </c>
+    </row>
+    <row r="20" spans="1:5">
+      <c r="A20" s="5" t="s">
+        <v>43</v>
+      </c>
+      <c r="B20" s="5" t="s">
+        <v>8</v>
+      </c>
+      <c r="C20" s="6">
+        <v>-2.01</v>
+      </c>
+      <c r="D20" s="6">
+        <v>-3.93</v>
+      </c>
+      <c r="E20" s="7">
+        <v>-1.92</v>
+      </c>
+    </row>
+    <row r="21" spans="1:5">
+      <c r="A21" s="5" t="s">
+        <v>37</v>
+      </c>
+      <c r="B21" s="5" t="s">
+        <v>11</v>
+      </c>
+      <c r="C21" s="6">
+        <v>29</v>
+      </c>
+      <c r="D21" s="6">
+        <v>29.58</v>
+      </c>
+      <c r="E21" s="8">
+        <v>0.58</v>
+      </c>
+    </row>
+    <row r="22" spans="1:5">
+      <c r="A22" s="5" t="s">
+        <v>38</v>
+      </c>
+      <c r="B22" s="5" t="s">
+        <v>11</v>
+      </c>
+      <c r="C22" s="6">
+        <v>117.97</v>
+      </c>
+      <c r="D22" s="6">
+        <v>124.39</v>
+      </c>
+      <c r="E22" s="8">
+        <v>6.42</v>
+      </c>
+    </row>
+    <row r="23" spans="1:5">
+      <c r="A23" s="5" t="s">
+        <v>39</v>
+      </c>
+      <c r="B23" s="5" t="s">
+        <v>11</v>
+      </c>
+      <c r="C23" s="6">
+        <v>-44.94</v>
+      </c>
+      <c r="D23" s="6">
+        <v>-44.65</v>
+      </c>
+      <c r="E23" s="8">
+        <v>0.29</v>
+      </c>
+    </row>
+    <row r="24" spans="1:5">
+      <c r="A24" s="5" t="s">
+        <v>40</v>
+      </c>
+      <c r="B24" s="5" t="s">
+        <v>11</v>
+      </c>
+      <c r="C24" s="6">
+        <v>-9.85</v>
+      </c>
+      <c r="D24" s="6">
+        <v>-10.68</v>
+      </c>
+      <c r="E24" s="7">
+        <v>-0.83</v>
+      </c>
+    </row>
+    <row r="25" spans="1:5">
+      <c r="A25" s="5" t="s">
+        <v>41</v>
+      </c>
+      <c r="B25" s="5" t="s">
+        <v>11</v>
+      </c>
+      <c r="C25" s="6">
+        <v>-16.15</v>
+      </c>
+      <c r="D25" s="6">
+        <v>-16.25</v>
+      </c>
+      <c r="E25" s="7">
+        <v>-0.1</v>
+      </c>
+    </row>
+    <row r="26" spans="1:5">
+      <c r="A26" s="5" t="s">
+        <v>42</v>
+      </c>
+      <c r="B26" s="5" t="s">
+        <v>11</v>
+      </c>
+      <c r="C26" s="6">
+        <v>3.71</v>
+      </c>
+      <c r="D26" s="6">
+        <v>1.17</v>
+      </c>
+      <c r="E26" s="7">
+        <v>-2.54</v>
+      </c>
+    </row>
+    <row r="27" spans="1:5">
+      <c r="A27" s="5" t="s">
+        <v>43</v>
+      </c>
+      <c r="B27" s="5" t="s">
+        <v>11</v>
+      </c>
+      <c r="C27" s="6">
         <v>-1.12</v>
       </c>
-    </row>
-    <row r="17" spans="1:5">
-      <c r="A17" s="3" t="s">
+      <c r="D27" s="6">
+        <v>-1.86</v>
+      </c>
+      <c r="E27" s="7">
+        <v>-0.74</v>
+      </c>
+    </row>
+    <row r="28" spans="1:5">
+      <c r="A28" s="5" t="s">
+        <v>37</v>
+      </c>
+      <c r="B28" s="5" t="s">
+        <v>10</v>
+      </c>
+      <c r="C28" s="6">
+        <v>15.45</v>
+      </c>
+      <c r="D28" s="6">
+        <v>14.12</v>
+      </c>
+      <c r="E28" s="7">
+        <v>-1.33</v>
+      </c>
+    </row>
+    <row r="29" spans="1:5">
+      <c r="A29" s="5" t="s">
+        <v>38</v>
+      </c>
+      <c r="B29" s="5" t="s">
+        <v>10</v>
+      </c>
+      <c r="C29" s="6">
+        <v>-17.38</v>
+      </c>
+      <c r="D29" s="6">
+        <v>-19.02</v>
+      </c>
+      <c r="E29" s="7">
+        <v>-1.64</v>
+      </c>
+    </row>
+    <row r="30" spans="1:5">
+      <c r="A30" s="5" t="s">
+        <v>39</v>
+      </c>
+      <c r="B30" s="5" t="s">
+        <v>10</v>
+      </c>
+      <c r="C30" s="6">
+        <v>-1.6</v>
+      </c>
+      <c r="D30" s="6">
+        <v>-1.14</v>
+      </c>
+      <c r="E30" s="8">
+        <v>0.46</v>
+      </c>
+    </row>
+    <row r="31" spans="1:5">
+      <c r="A31" s="5" t="s">
         <v>40</v>
       </c>
-      <c r="B17" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="C17" s="5">
-        <v>-4.29</v>
-      </c>
-      <c r="D17" s="5">
-        <v>-5.22</v>
-      </c>
-      <c r="E17" s="7">
-        <v>-0.93</v>
-      </c>
-    </row>
-    <row r="18" spans="1:5">
-      <c r="A18" s="3" t="s">
+      <c r="B31" s="5" t="s">
+        <v>10</v>
+      </c>
+      <c r="C31" s="6">
+        <v>4.1</v>
+      </c>
+      <c r="D31" s="6">
+        <v>4.94</v>
+      </c>
+      <c r="E31" s="8">
+        <v>0.84</v>
+      </c>
+    </row>
+    <row r="32" spans="1:5">
+      <c r="A32" s="5" t="s">
         <v>41</v>
       </c>
-      <c r="B18" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="C18" s="5">
-        <v>1.31</v>
-      </c>
-      <c r="D18" s="5">
-        <v>-1.05</v>
-      </c>
-      <c r="E18" s="7">
-        <v>-2.36</v>
-      </c>
-    </row>
-    <row r="19" spans="1:5">
-      <c r="A19" s="3" t="s">
+      <c r="B32" s="5" t="s">
+        <v>10</v>
+      </c>
+      <c r="C32" s="6">
+        <v>4.1</v>
+      </c>
+      <c r="D32" s="6">
+        <v>3.13</v>
+      </c>
+      <c r="E32" s="7">
+        <v>-0.97</v>
+      </c>
+    </row>
+    <row r="33" spans="1:5">
+      <c r="A33" s="5" t="s">
         <v>42</v>
       </c>
-      <c r="B19" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="C19" s="5">
-        <v>-4.79</v>
-      </c>
-      <c r="D19" s="5">
-        <v>-4.54</v>
-      </c>
-      <c r="E19" s="6">
-        <v>0.25</v>
-      </c>
-    </row>
-    <row r="20" spans="1:5">
-      <c r="A20" s="3" t="s">
+      <c r="B33" s="5" t="s">
+        <v>10</v>
+      </c>
+      <c r="C33" s="6">
+        <v>4.99</v>
+      </c>
+      <c r="D33" s="6">
+        <v>5.86</v>
+      </c>
+      <c r="E33" s="8">
+        <v>0.87</v>
+      </c>
+    </row>
+    <row r="34" spans="1:5">
+      <c r="A34" s="5" t="s">
         <v>43</v>
       </c>
-      <c r="B20" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="C20" s="5">
-        <v>-0.93</v>
-      </c>
-      <c r="D20" s="5">
-        <v>-2.01</v>
-      </c>
-      <c r="E20" s="7">
-        <v>-1.08</v>
-      </c>
-    </row>
-    <row r="21" spans="1:5">
-      <c r="A21" s="3" t="s">
+      <c r="B34" s="5" t="s">
+        <v>10</v>
+      </c>
+      <c r="C34" s="6">
+        <v>0.46</v>
+      </c>
+      <c r="D34" s="6">
+        <v>-2.02</v>
+      </c>
+      <c r="E34" s="7">
+        <v>-2.48</v>
+      </c>
+    </row>
+    <row r="35" spans="1:5">
+      <c r="A35" s="5" t="s">
         <v>37</v>
       </c>
-      <c r="B21" s="3" t="s">
-        <v>11</v>
-      </c>
-      <c r="C21" s="5">
-        <v>25.32</v>
-      </c>
-      <c r="D21" s="5">
-        <v>29</v>
-      </c>
-      <c r="E21" s="6">
-        <v>3.68</v>
-      </c>
-    </row>
-    <row r="22" spans="1:5">
-      <c r="A22" s="3" t="s">
+      <c r="B35" s="5" t="s">
+        <v>6</v>
+      </c>
+      <c r="C35" s="6">
+        <v>-6.21</v>
+      </c>
+      <c r="D35" s="6">
+        <v>-6.97</v>
+      </c>
+      <c r="E35" s="7">
+        <v>-0.76</v>
+      </c>
+    </row>
+    <row r="36" spans="1:5">
+      <c r="A36" s="5" t="s">
         <v>38</v>
       </c>
-      <c r="B22" s="3" t="s">
-        <v>11</v>
-      </c>
-      <c r="C22" s="5">
-        <v>126.93</v>
-      </c>
-      <c r="D22" s="5">
-        <v>117.97</v>
-      </c>
-      <c r="E22" s="7">
-        <v>-8.960000000000001</v>
-      </c>
-    </row>
-    <row r="23" spans="1:5">
-      <c r="A23" s="3" t="s">
+      <c r="B36" s="5" t="s">
+        <v>6</v>
+      </c>
+      <c r="C36" s="6">
+        <v>-25.69</v>
+      </c>
+      <c r="D36" s="6">
+        <v>-25.04</v>
+      </c>
+      <c r="E36" s="8">
+        <v>0.65</v>
+      </c>
+    </row>
+    <row r="37" spans="1:5">
+      <c r="A37" s="5" t="s">
         <v>39</v>
       </c>
-      <c r="B23" s="3" t="s">
-        <v>11</v>
-      </c>
-      <c r="C23" s="5">
-        <v>-43.94</v>
-      </c>
-      <c r="D23" s="5">
-        <v>-44.94</v>
-      </c>
-      <c r="E23" s="7">
-        <v>-1</v>
-      </c>
-    </row>
-    <row r="24" spans="1:5">
-      <c r="A24" s="3" t="s">
+      <c r="B37" s="5" t="s">
+        <v>6</v>
+      </c>
+      <c r="C37" s="6">
+        <v>-46.67</v>
+      </c>
+      <c r="D37" s="6">
+        <v>-46.22</v>
+      </c>
+      <c r="E37" s="8">
+        <v>0.45</v>
+      </c>
+    </row>
+    <row r="38" spans="1:5">
+      <c r="A38" s="5" t="s">
         <v>40</v>
       </c>
-      <c r="B24" s="3" t="s">
-        <v>11</v>
-      </c>
-      <c r="C24" s="5">
-        <v>-8.960000000000001</v>
-      </c>
-      <c r="D24" s="5">
-        <v>-9.85</v>
-      </c>
-      <c r="E24" s="7">
-        <v>-0.89</v>
-      </c>
-    </row>
-    <row r="25" spans="1:5">
-      <c r="A25" s="3" t="s">
+      <c r="B38" s="5" t="s">
+        <v>6</v>
+      </c>
+      <c r="C38" s="6">
+        <v>-15.6</v>
+      </c>
+      <c r="D38" s="6">
+        <v>-14.58</v>
+      </c>
+      <c r="E38" s="8">
+        <v>1.02</v>
+      </c>
+    </row>
+    <row r="39" spans="1:5">
+      <c r="A39" s="5" t="s">
         <v>41</v>
       </c>
-      <c r="B25" s="3" t="s">
-        <v>11</v>
-      </c>
-      <c r="C25" s="5">
-        <v>-14.55</v>
-      </c>
-      <c r="D25" s="5">
-        <v>-16.15</v>
-      </c>
-      <c r="E25" s="7">
-        <v>-1.6</v>
-      </c>
-    </row>
-    <row r="26" spans="1:5">
-      <c r="A26" s="3" t="s">
+      <c r="B39" s="5" t="s">
+        <v>6</v>
+      </c>
+      <c r="C39" s="6">
+        <v>-19.61</v>
+      </c>
+      <c r="D39" s="6">
+        <v>-19.02</v>
+      </c>
+      <c r="E39" s="8">
+        <v>0.59</v>
+      </c>
+    </row>
+    <row r="40" spans="1:5">
+      <c r="A40" s="5" t="s">
         <v>42</v>
       </c>
-      <c r="B26" s="3" t="s">
-        <v>11</v>
-      </c>
-      <c r="C26" s="5">
-        <v>4.26</v>
-      </c>
-      <c r="D26" s="5">
-        <v>3.71</v>
-      </c>
-      <c r="E26" s="7">
-        <v>-0.55</v>
-      </c>
-    </row>
-    <row r="27" spans="1:5">
-      <c r="A27" s="3" t="s">
+      <c r="B40" s="5" t="s">
+        <v>6</v>
+      </c>
+      <c r="C40" s="6">
+        <v>-13.17</v>
+      </c>
+      <c r="D40" s="6">
+        <v>-12.41</v>
+      </c>
+      <c r="E40" s="8">
+        <v>0.76</v>
+      </c>
+    </row>
+    <row r="41" spans="1:5">
+      <c r="A41" s="5" t="s">
         <v>43</v>
       </c>
-      <c r="B27" s="3" t="s">
-        <v>11</v>
-      </c>
-      <c r="C27" s="5">
-        <v>0.42</v>
-      </c>
-      <c r="D27" s="5">
-        <v>-1.12</v>
-      </c>
-      <c r="E27" s="7">
-        <v>-1.54</v>
-      </c>
-    </row>
-    <row r="28" spans="1:5">
-      <c r="A28" s="3" t="s">
+      <c r="B41" s="5" t="s">
+        <v>6</v>
+      </c>
+      <c r="C41" s="6">
+        <v>-9.44</v>
+      </c>
+      <c r="D41" s="6">
+        <v>-9.9</v>
+      </c>
+      <c r="E41" s="7">
+        <v>-0.46</v>
+      </c>
+    </row>
+    <row r="42" spans="1:5">
+      <c r="A42" s="5" t="s">
         <v>37</v>
       </c>
-      <c r="B28" s="3" t="s">
-        <v>10</v>
-      </c>
-      <c r="C28" s="5">
-        <v>14.94</v>
-      </c>
-      <c r="D28" s="5">
-        <v>15.45</v>
-      </c>
-      <c r="E28" s="6">
-        <v>0.51</v>
-      </c>
-    </row>
-    <row r="29" spans="1:5">
-      <c r="A29" s="3" t="s">
+      <c r="B42" s="5" t="s">
+        <v>2</v>
+      </c>
+      <c r="C42" s="6">
+        <v>11593</v>
+      </c>
+      <c r="D42" s="6">
+        <v>11500</v>
+      </c>
+      <c r="E42" s="7">
+        <v>-93</v>
+      </c>
+    </row>
+    <row r="43" spans="1:5">
+      <c r="A43" s="5" t="s">
         <v>38</v>
       </c>
-      <c r="B29" s="3" t="s">
-        <v>10</v>
-      </c>
-      <c r="C29" s="5">
-        <v>-16.1</v>
-      </c>
-      <c r="D29" s="5">
-        <v>-17.38</v>
-      </c>
-      <c r="E29" s="7">
-        <v>-1.28</v>
-      </c>
-    </row>
-    <row r="30" spans="1:5">
-      <c r="A30" s="3" t="s">
+      <c r="B43" s="5" t="s">
+        <v>2</v>
+      </c>
+      <c r="C43" s="6">
+        <v>498.05</v>
+      </c>
+      <c r="D43" s="6">
+        <v>502.45</v>
+      </c>
+      <c r="E43" s="8">
+        <v>4.4</v>
+      </c>
+    </row>
+    <row r="44" spans="1:5">
+      <c r="A44" s="5" t="s">
         <v>39</v>
       </c>
-      <c r="B30" s="3" t="s">
-        <v>10</v>
-      </c>
-      <c r="C30" s="5">
+      <c r="B44" s="5" t="s">
+        <v>2</v>
+      </c>
+      <c r="C44" s="6">
+        <v>322.55</v>
+      </c>
+      <c r="D44" s="6">
+        <v>325.3</v>
+      </c>
+      <c r="E44" s="8">
+        <v>2.75</v>
+      </c>
+    </row>
+    <row r="45" spans="1:5">
+      <c r="A45" s="5" t="s">
+        <v>40</v>
+      </c>
+      <c r="B45" s="5" t="s">
+        <v>2</v>
+      </c>
+      <c r="C45" s="6">
+        <v>1837</v>
+      </c>
+      <c r="D45" s="6">
+        <v>1859.2</v>
+      </c>
+      <c r="E45" s="8">
+        <v>22.2</v>
+      </c>
+    </row>
+    <row r="46" spans="1:5">
+      <c r="A46" s="5" t="s">
+        <v>41</v>
+      </c>
+      <c r="B46" s="5" t="s">
+        <v>2</v>
+      </c>
+      <c r="C46" s="6">
+        <v>10930</v>
+      </c>
+      <c r="D46" s="6">
+        <v>11010</v>
+      </c>
+      <c r="E46" s="8">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="47" spans="1:5">
+      <c r="A47" s="5" t="s">
+        <v>42</v>
+      </c>
+      <c r="B47" s="5" t="s">
+        <v>2</v>
+      </c>
+      <c r="C47" s="6">
+        <v>1006.2</v>
+      </c>
+      <c r="D47" s="6">
+        <v>1015</v>
+      </c>
+      <c r="E47" s="8">
+        <v>8.800000000000001</v>
+      </c>
+    </row>
+    <row r="48" spans="1:5">
+      <c r="A48" s="5" t="s">
+        <v>43</v>
+      </c>
+      <c r="B48" s="5" t="s">
+        <v>2</v>
+      </c>
+      <c r="C48" s="6">
+        <v>134.89</v>
+      </c>
+      <c r="D48" s="6">
+        <v>134.2</v>
+      </c>
+      <c r="E48" s="7">
+        <v>-0.6899999999999999</v>
+      </c>
+    </row>
+    <row r="49" spans="1:5">
+      <c r="A49" s="5" t="s">
+        <v>37</v>
+      </c>
+      <c r="B49" s="5" t="s">
+        <v>24</v>
+      </c>
+      <c r="C49" s="6">
+        <v>47.27</v>
+      </c>
+      <c r="D49" s="6">
+        <v>44.74</v>
+      </c>
+      <c r="E49" s="7">
+        <v>-2.53</v>
+      </c>
+    </row>
+    <row r="50" spans="1:5">
+      <c r="A50" s="5" t="s">
+        <v>38</v>
+      </c>
+      <c r="B50" s="5" t="s">
+        <v>24</v>
+      </c>
+      <c r="C50" s="6">
+        <v>46.5</v>
+      </c>
+      <c r="D50" s="6">
+        <v>48.17</v>
+      </c>
+      <c r="E50" s="8">
         <v>1.67</v>
       </c>
-      <c r="D30" s="5">
-        <v>-1.6</v>
-      </c>
-      <c r="E30" s="7">
-        <v>-3.27</v>
-      </c>
-    </row>
-    <row r="31" spans="1:5">
-      <c r="A31" s="3" t="s">
+    </row>
+    <row r="51" spans="1:5">
+      <c r="A51" s="5" t="s">
+        <v>39</v>
+      </c>
+      <c r="B51" s="5" t="s">
+        <v>24</v>
+      </c>
+      <c r="C51" s="6">
+        <v>38.2</v>
+      </c>
+      <c r="D51" s="6">
+        <v>40.76</v>
+      </c>
+      <c r="E51" s="8">
+        <v>2.56</v>
+      </c>
+    </row>
+    <row r="52" spans="1:5">
+      <c r="A52" s="5" t="s">
         <v>40</v>
       </c>
-      <c r="B31" s="3" t="s">
-        <v>10</v>
-      </c>
-      <c r="C31" s="5">
-        <v>3.82</v>
-      </c>
-      <c r="D31" s="5">
-        <v>4.1</v>
-      </c>
-      <c r="E31" s="6">
-        <v>0.28</v>
-      </c>
-    </row>
-    <row r="32" spans="1:5">
-      <c r="A32" s="3" t="s">
+      <c r="B52" s="5" t="s">
+        <v>24</v>
+      </c>
+      <c r="C52" s="6">
+        <v>27.76</v>
+      </c>
+      <c r="D52" s="6">
+        <v>33.43</v>
+      </c>
+      <c r="E52" s="8">
+        <v>5.67</v>
+      </c>
+    </row>
+    <row r="53" spans="1:5">
+      <c r="A53" s="5" t="s">
         <v>41</v>
       </c>
-      <c r="B32" s="3" t="s">
-        <v>10</v>
-      </c>
-      <c r="C32" s="5">
-        <v>6.08</v>
-      </c>
-      <c r="D32" s="5">
-        <v>4.1</v>
-      </c>
-      <c r="E32" s="7">
-        <v>-1.98</v>
-      </c>
-    </row>
-    <row r="33" spans="1:5">
-      <c r="A33" s="3" t="s">
+      <c r="B53" s="5" t="s">
+        <v>24</v>
+      </c>
+      <c r="C53" s="6">
+        <v>43.01</v>
+      </c>
+      <c r="D53" s="6">
+        <v>45.69</v>
+      </c>
+      <c r="E53" s="8">
+        <v>2.68</v>
+      </c>
+    </row>
+    <row r="54" spans="1:5">
+      <c r="A54" s="5" t="s">
         <v>42</v>
       </c>
-      <c r="B33" s="3" t="s">
-        <v>10</v>
-      </c>
-      <c r="C33" s="5">
-        <v>5.16</v>
-      </c>
-      <c r="D33" s="5">
-        <v>4.99</v>
-      </c>
-      <c r="E33" s="7">
-        <v>-0.17</v>
-      </c>
-    </row>
-    <row r="34" spans="1:5">
-      <c r="A34" s="3" t="s">
+      <c r="B54" s="5" t="s">
+        <v>24</v>
+      </c>
+      <c r="C54" s="6">
+        <v>30.97</v>
+      </c>
+      <c r="D54" s="6">
+        <v>35.33</v>
+      </c>
+      <c r="E54" s="8">
+        <v>4.36</v>
+      </c>
+    </row>
+    <row r="55" spans="1:5">
+      <c r="A55" s="5" t="s">
         <v>43</v>
       </c>
-      <c r="B34" s="3" t="s">
-        <v>10</v>
-      </c>
-      <c r="C34" s="5">
-        <v>0.1</v>
-      </c>
-      <c r="D34" s="5">
-        <v>0.46</v>
-      </c>
-      <c r="E34" s="6">
-        <v>0.36</v>
-      </c>
-    </row>
-    <row r="35" spans="1:5">
-      <c r="A35" s="3" t="s">
+      <c r="B55" s="5" t="s">
+        <v>24</v>
+      </c>
+      <c r="C55" s="6">
+        <v>44.68</v>
+      </c>
+      <c r="D55" s="6">
+        <v>43.32</v>
+      </c>
+      <c r="E55" s="7">
+        <v>-1.36</v>
+      </c>
+    </row>
+    <row r="56" spans="1:5">
+      <c r="A56" s="5" t="s">
         <v>37</v>
       </c>
-      <c r="B35" s="3" t="s">
-        <v>6</v>
-      </c>
-      <c r="C35" s="5">
-        <v>-7.58</v>
-      </c>
-      <c r="D35" s="5">
-        <v>-6.21</v>
-      </c>
-      <c r="E35" s="6">
-        <v>1.37</v>
-      </c>
-    </row>
-    <row r="36" spans="1:5">
-      <c r="A36" s="3" t="s">
+      <c r="B56" s="5" t="s">
+        <v>31</v>
+      </c>
+      <c r="C56" s="6">
+        <v>37.09</v>
+      </c>
+      <c r="D56" s="6">
+        <v>-43.46</v>
+      </c>
+      <c r="E56" s="7">
+        <v>-80.55</v>
+      </c>
+    </row>
+    <row r="57" spans="1:5">
+      <c r="A57" s="5" t="s">
         <v>38</v>
       </c>
-      <c r="B36" s="3" t="s">
-        <v>6</v>
-      </c>
-      <c r="C36" s="5">
-        <v>-24.83</v>
-      </c>
-      <c r="D36" s="5">
-        <v>-25.69</v>
-      </c>
-      <c r="E36" s="7">
-        <v>-0.86</v>
-      </c>
-    </row>
-    <row r="37" spans="1:5">
-      <c r="A37" s="3" t="s">
+      <c r="B57" s="5" t="s">
+        <v>31</v>
+      </c>
+      <c r="C57" s="6">
+        <v>-52.13</v>
+      </c>
+      <c r="D57" s="6">
+        <v>-68.7</v>
+      </c>
+      <c r="E57" s="7">
+        <v>-16.57</v>
+      </c>
+    </row>
+    <row r="58" spans="1:5">
+      <c r="A58" s="5" t="s">
         <v>39</v>
       </c>
-      <c r="B37" s="3" t="s">
-        <v>6</v>
-      </c>
-      <c r="C37" s="5">
-        <v>-45.71</v>
-      </c>
-      <c r="D37" s="5">
-        <v>-46.67</v>
-      </c>
-      <c r="E37" s="7">
-        <v>-0.96</v>
-      </c>
-    </row>
-    <row r="38" spans="1:5">
-      <c r="A38" s="3" t="s">
+      <c r="B58" s="5" t="s">
+        <v>31</v>
+      </c>
+      <c r="C58" s="6">
+        <v>-40.98</v>
+      </c>
+      <c r="D58" s="6">
+        <v>-66.45</v>
+      </c>
+      <c r="E58" s="7">
+        <v>-25.47</v>
+      </c>
+    </row>
+    <row r="59" spans="1:5">
+      <c r="A59" s="5" t="s">
         <v>40</v>
       </c>
-      <c r="B38" s="3" t="s">
-        <v>6</v>
-      </c>
-      <c r="C38" s="5">
-        <v>-14.75</v>
-      </c>
-      <c r="D38" s="5">
-        <v>-15.6</v>
-      </c>
-      <c r="E38" s="7">
-        <v>-0.85</v>
-      </c>
-    </row>
-    <row r="39" spans="1:5">
-      <c r="A39" s="3" t="s">
+      <c r="B59" s="5" t="s">
+        <v>31</v>
+      </c>
+      <c r="C59" s="6">
+        <v>0.01</v>
+      </c>
+      <c r="D59" s="6">
+        <v>-22.51</v>
+      </c>
+      <c r="E59" s="7">
+        <v>-22.52</v>
+      </c>
+    </row>
+    <row r="60" spans="1:5">
+      <c r="A60" s="5" t="s">
         <v>41</v>
       </c>
-      <c r="B39" s="3" t="s">
-        <v>6</v>
-      </c>
-      <c r="C39" s="5">
-        <v>-18.36</v>
-      </c>
-      <c r="D39" s="5">
-        <v>-19.61</v>
-      </c>
-      <c r="E39" s="7">
-        <v>-1.25</v>
-      </c>
-    </row>
-    <row r="40" spans="1:5">
-      <c r="A40" s="3" t="s">
+      <c r="B60" s="5" t="s">
+        <v>31</v>
+      </c>
+      <c r="C60" s="6">
+        <v>-45.91</v>
+      </c>
+      <c r="D60" s="6">
+        <v>-28.52</v>
+      </c>
+      <c r="E60" s="8">
+        <v>17.39</v>
+      </c>
+    </row>
+    <row r="61" spans="1:5">
+      <c r="A61" s="5" t="s">
         <v>42</v>
       </c>
-      <c r="B40" s="3" t="s">
-        <v>6</v>
-      </c>
-      <c r="C40" s="5">
-        <v>-12.91</v>
-      </c>
-      <c r="D40" s="5">
-        <v>-13.17</v>
-      </c>
-      <c r="E40" s="7">
-        <v>-0.26</v>
-      </c>
-    </row>
-    <row r="41" spans="1:5">
-      <c r="A41" s="3" t="s">
+      <c r="B61" s="5" t="s">
+        <v>31</v>
+      </c>
+      <c r="C61" s="6">
+        <v>-12.55</v>
+      </c>
+      <c r="D61" s="6">
+        <v>-1.34</v>
+      </c>
+      <c r="E61" s="8">
+        <v>11.21</v>
+      </c>
+    </row>
+    <row r="62" spans="1:5">
+      <c r="A62" s="5" t="s">
         <v>43</v>
       </c>
-      <c r="B41" s="3" t="s">
-        <v>6</v>
-      </c>
-      <c r="C41" s="5">
-        <v>-8.949999999999999</v>
-      </c>
-      <c r="D41" s="5">
-        <v>-9.44</v>
-      </c>
-      <c r="E41" s="7">
-        <v>-0.49</v>
-      </c>
-    </row>
-    <row r="42" spans="1:5">
-      <c r="A42" s="3" t="s">
-        <v>37</v>
-      </c>
-      <c r="B42" s="3" t="s">
-        <v>2</v>
-      </c>
-      <c r="C42" s="5">
-        <v>11424</v>
-      </c>
-      <c r="D42" s="5">
-        <v>11593</v>
-      </c>
-      <c r="E42" s="6">
-        <v>169</v>
-      </c>
-    </row>
-    <row r="43" spans="1:5">
-      <c r="A43" s="3" t="s">
-        <v>38</v>
-      </c>
-      <c r="B43" s="3" t="s">
-        <v>2</v>
-      </c>
-      <c r="C43" s="5">
-        <v>503.8</v>
-      </c>
-      <c r="D43" s="5">
-        <v>498.05</v>
-      </c>
-      <c r="E43" s="7">
-        <v>-5.75</v>
-      </c>
-    </row>
-    <row r="44" spans="1:5">
-      <c r="A44" s="3" t="s">
-        <v>39</v>
-      </c>
-      <c r="B44" s="3" t="s">
-        <v>2</v>
-      </c>
-      <c r="C44" s="5">
-        <v>328.4</v>
-      </c>
-      <c r="D44" s="5">
-        <v>322.55</v>
-      </c>
-      <c r="E44" s="7">
-        <v>-5.85</v>
-      </c>
-    </row>
-    <row r="45" spans="1:5">
-      <c r="A45" s="3" t="s">
-        <v>40</v>
-      </c>
-      <c r="B45" s="3" t="s">
-        <v>2</v>
-      </c>
-      <c r="C45" s="5">
-        <v>1855.5</v>
-      </c>
-      <c r="D45" s="5">
-        <v>1837</v>
-      </c>
-      <c r="E45" s="7">
-        <v>-18.5</v>
-      </c>
-    </row>
-    <row r="46" spans="1:5">
-      <c r="A46" s="3" t="s">
-        <v>41</v>
-      </c>
-      <c r="B46" s="3" t="s">
-        <v>2</v>
-      </c>
-      <c r="C46" s="5">
-        <v>11100</v>
-      </c>
-      <c r="D46" s="5">
-        <v>10930</v>
-      </c>
-      <c r="E46" s="7">
-        <v>-170</v>
-      </c>
-    </row>
-    <row r="47" spans="1:5">
-      <c r="A47" s="3" t="s">
-        <v>42</v>
-      </c>
-      <c r="B47" s="3" t="s">
-        <v>2</v>
-      </c>
-      <c r="C47" s="5">
-        <v>1009.2</v>
-      </c>
-      <c r="D47" s="5">
-        <v>1006.2</v>
-      </c>
-      <c r="E47" s="7">
-        <v>-3</v>
-      </c>
-    </row>
-    <row r="48" spans="1:5">
-      <c r="A48" s="3" t="s">
-        <v>43</v>
-      </c>
-      <c r="B48" s="3" t="s">
-        <v>2</v>
-      </c>
-      <c r="C48" s="5">
-        <v>135.62</v>
-      </c>
-      <c r="D48" s="5">
-        <v>134.89</v>
-      </c>
-      <c r="E48" s="7">
-        <v>-0.73</v>
-      </c>
-    </row>
-    <row r="49" spans="1:5">
-      <c r="A49" s="3" t="s">
-        <v>37</v>
-      </c>
-      <c r="B49" s="3" t="s">
-        <v>24</v>
-      </c>
-      <c r="C49" s="5">
-        <v>41.71</v>
-      </c>
-      <c r="D49" s="5">
-        <v>47.27</v>
-      </c>
-      <c r="E49" s="6">
-        <v>5.56</v>
-      </c>
-    </row>
-    <row r="50" spans="1:5">
-      <c r="A50" s="3" t="s">
-        <v>38</v>
-      </c>
-      <c r="B50" s="3" t="s">
-        <v>24</v>
-      </c>
-      <c r="C50" s="5">
-        <v>48.39</v>
-      </c>
-      <c r="D50" s="5">
-        <v>46.5</v>
-      </c>
-      <c r="E50" s="7">
-        <v>-1.89</v>
-      </c>
-    </row>
-    <row r="51" spans="1:5">
-      <c r="A51" s="3" t="s">
-        <v>39</v>
-      </c>
-      <c r="B51" s="3" t="s">
-        <v>24</v>
-      </c>
-      <c r="C51" s="5">
-        <v>41.76</v>
-      </c>
-      <c r="D51" s="5">
-        <v>38.2</v>
-      </c>
-      <c r="E51" s="7">
-        <v>-3.56</v>
-      </c>
-    </row>
-    <row r="52" spans="1:5">
-      <c r="A52" s="3" t="s">
-        <v>40</v>
-      </c>
-      <c r="B52" s="3" t="s">
-        <v>24</v>
-      </c>
-      <c r="C52" s="5">
-        <v>29.72</v>
-      </c>
-      <c r="D52" s="5">
-        <v>27.76</v>
-      </c>
-      <c r="E52" s="7">
-        <v>-1.96</v>
-      </c>
-    </row>
-    <row r="53" spans="1:5">
-      <c r="A53" s="3" t="s">
-        <v>41</v>
-      </c>
-      <c r="B53" s="3" t="s">
-        <v>24</v>
-      </c>
-      <c r="C53" s="5">
-        <v>47.66</v>
-      </c>
-      <c r="D53" s="5">
-        <v>43.01</v>
-      </c>
-      <c r="E53" s="7">
-        <v>-4.65</v>
-      </c>
-    </row>
-    <row r="54" spans="1:5">
-      <c r="A54" s="3" t="s">
-        <v>42</v>
-      </c>
-      <c r="B54" s="3" t="s">
-        <v>24</v>
-      </c>
-      <c r="C54" s="5">
-        <v>31.65</v>
-      </c>
-      <c r="D54" s="5">
-        <v>30.97</v>
-      </c>
-      <c r="E54" s="7">
-        <v>-0.68</v>
-      </c>
-    </row>
-    <row r="55" spans="1:5">
-      <c r="A55" s="3" t="s">
-        <v>43</v>
-      </c>
-      <c r="B55" s="3" t="s">
-        <v>24</v>
-      </c>
-      <c r="C55" s="5">
-        <v>46.1</v>
-      </c>
-      <c r="D55" s="5">
-        <v>44.68</v>
-      </c>
-      <c r="E55" s="7">
-        <v>-1.42</v>
-      </c>
-    </row>
-    <row r="56" spans="1:5">
-      <c r="A56" s="3" t="s">
-        <v>37</v>
-      </c>
-      <c r="B56" s="3" t="s">
+      <c r="B62" s="5" t="s">
         <v>31</v>
       </c>
-      <c r="C56" s="5">
-        <v>6.11</v>
-      </c>
-      <c r="D56" s="5">
-        <v>37.09</v>
-      </c>
-      <c r="E56" s="6">
-        <v>30.98</v>
-      </c>
-    </row>
-    <row r="57" spans="1:5">
-      <c r="A57" s="3" t="s">
-        <v>38</v>
-      </c>
-      <c r="B57" s="3" t="s">
-        <v>31</v>
-      </c>
-      <c r="C57" s="5">
-        <v>-20</v>
-      </c>
-      <c r="D57" s="5">
-        <v>-52.13</v>
-      </c>
-      <c r="E57" s="7">
-        <v>-32.13</v>
-      </c>
-    </row>
-    <row r="58" spans="1:5">
-      <c r="A58" s="3" t="s">
-        <v>39</v>
-      </c>
-      <c r="B58" s="3" t="s">
-        <v>31</v>
-      </c>
-      <c r="C58" s="5">
-        <v>-24.2</v>
-      </c>
-      <c r="D58" s="5">
-        <v>-40.98</v>
-      </c>
-      <c r="E58" s="7">
-        <v>-16.78</v>
-      </c>
-    </row>
-    <row r="59" spans="1:5">
-      <c r="A59" s="3" t="s">
-        <v>40</v>
-      </c>
-      <c r="B59" s="3" t="s">
-        <v>31</v>
-      </c>
-      <c r="C59" s="5">
-        <v>-23.58</v>
-      </c>
-      <c r="D59" s="5">
-        <v>0.01</v>
-      </c>
-      <c r="E59" s="6">
-        <v>23.59</v>
-      </c>
-    </row>
-    <row r="60" spans="1:5">
-      <c r="A60" s="3" t="s">
-        <v>41</v>
-      </c>
-      <c r="B60" s="3" t="s">
-        <v>31</v>
-      </c>
-      <c r="C60" s="5">
-        <v>23.5</v>
-      </c>
-      <c r="D60" s="5">
-        <v>-45.91</v>
-      </c>
-      <c r="E60" s="7">
-        <v>-69.41</v>
-      </c>
-    </row>
-    <row r="61" spans="1:5">
-      <c r="A61" s="3" t="s">
-        <v>42</v>
-      </c>
-      <c r="B61" s="3" t="s">
-        <v>31</v>
-      </c>
-      <c r="C61" s="5">
-        <v>22.75</v>
-      </c>
-      <c r="D61" s="5">
-        <v>-12.55</v>
-      </c>
-      <c r="E61" s="7">
-        <v>-35.3</v>
-      </c>
-    </row>
-    <row r="62" spans="1:5">
-      <c r="A62" s="3" t="s">
-        <v>43</v>
-      </c>
-      <c r="B62" s="3" t="s">
-        <v>31</v>
-      </c>
-      <c r="C62" s="5">
-        <v>-36.4</v>
-      </c>
-      <c r="D62" s="5">
+      <c r="C62" s="6">
         <v>62.21</v>
       </c>
-      <c r="E62" s="6">
-        <v>98.61</v>
+      <c r="D62" s="6">
+        <v>-70.84</v>
+      </c>
+      <c r="E62" s="7">
+        <v>-133.05</v>
       </c>
     </row>
   </sheetData>
@@ -2841,60 +2904,60 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:9" ht="28" customHeight="1">
-      <c r="A1" s="8" t="s">
+      <c r="A1" s="9" t="s">
         <v>1</v>
       </c>
-      <c r="B1" s="8" t="s">
-        <v>56</v>
-      </c>
-      <c r="C1" s="8" t="s">
+      <c r="B1" s="9" t="s">
+        <v>65</v>
+      </c>
+      <c r="C1" s="9" t="s">
+        <v>66</v>
+      </c>
+      <c r="D1" s="9" t="s">
+        <v>67</v>
+      </c>
+      <c r="E1" s="9" t="s">
+        <v>68</v>
+      </c>
+      <c r="F1" s="9" t="s">
+        <v>69</v>
+      </c>
+      <c r="G1" s="9" t="s">
+        <v>70</v>
+      </c>
+      <c r="H1" s="9" t="s">
+        <v>71</v>
+      </c>
+      <c r="I1" s="9" t="s">
+        <v>72</v>
+      </c>
+    </row>
+    <row r="2" spans="1:9">
+      <c r="A2" s="10" t="s">
+        <v>44</v>
+      </c>
+      <c r="B2" s="11">
+        <v>60.8</v>
+      </c>
+      <c r="C2" s="12">
+        <v>7</v>
+      </c>
+      <c r="D2" s="11">
+        <v>41.6</v>
+      </c>
+      <c r="E2" s="11">
+        <v>70</v>
+      </c>
+      <c r="F2" s="11">
+        <v>-3.4</v>
+      </c>
+      <c r="G2" s="11">
+        <v>0.8</v>
+      </c>
+      <c r="H2" s="11">
         <v>57</v>
       </c>
-      <c r="D1" s="8" t="s">
-        <v>58</v>
-      </c>
-      <c r="E1" s="8" t="s">
-        <v>59</v>
-      </c>
-      <c r="F1" s="8" t="s">
-        <v>60</v>
-      </c>
-      <c r="G1" s="8" t="s">
-        <v>61</v>
-      </c>
-      <c r="H1" s="8" t="s">
-        <v>62</v>
-      </c>
-      <c r="I1" s="8" t="s">
-        <v>63</v>
-      </c>
-    </row>
-    <row r="2" spans="1:9">
-      <c r="A2" s="9" t="s">
-        <v>44</v>
-      </c>
-      <c r="B2" s="10">
-        <v>60.8</v>
-      </c>
-      <c r="C2" s="11">
-        <v>7</v>
-      </c>
-      <c r="D2" s="10">
-        <v>39.8</v>
-      </c>
-      <c r="E2" s="10">
-        <v>70</v>
-      </c>
-      <c r="F2" s="10">
-        <v>-4.1</v>
-      </c>
-      <c r="G2" s="10">
-        <v>1.4</v>
-      </c>
-      <c r="H2" s="10">
-        <v>57</v>
-      </c>
-      <c r="I2" s="10">
+      <c r="I2" s="11">
         <v>40</v>
       </c>
     </row>
@@ -2996,49 +3059,49 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:7">
-      <c r="A1" s="12" t="s">
+      <c r="A1" s="13" t="s">
         <v>37</v>
       </c>
-      <c r="B1" s="12" t="s">
+      <c r="B1" s="13" t="s">
         <v>41</v>
       </c>
-      <c r="C1" s="12" t="s">
+      <c r="C1" s="13" t="s">
         <v>38</v>
       </c>
-      <c r="D1" s="12" t="s">
+      <c r="D1" s="13" t="s">
         <v>42</v>
       </c>
-      <c r="E1" s="12" t="s">
+      <c r="E1" s="13" t="s">
         <v>40</v>
       </c>
-      <c r="F1" s="12" t="s">
+      <c r="F1" s="13" t="s">
         <v>43</v>
       </c>
-      <c r="G1" s="12" t="s">
+      <c r="G1" s="13" t="s">
         <v>39</v>
       </c>
     </row>
     <row r="2" spans="1:7">
-      <c r="A2" s="13">
-        <v>0.2779</v>
-      </c>
-      <c r="B2" s="13">
-        <v>0.2216</v>
-      </c>
-      <c r="C2" s="13">
-        <v>0.1621</v>
-      </c>
-      <c r="D2" s="13">
-        <v>0.06709999999999999</v>
-      </c>
-      <c r="E2" s="13">
-        <v>0.0193</v>
-      </c>
-      <c r="F2" s="13">
-        <v>-0.0021</v>
-      </c>
-      <c r="G2" s="13">
-        <v>-0.2478</v>
+      <c r="A2" s="14">
+        <v>0.2753</v>
+      </c>
+      <c r="B2" s="14">
+        <v>0.2189</v>
+      </c>
+      <c r="C2" s="14">
+        <v>0.1611</v>
+      </c>
+      <c r="D2" s="14">
+        <v>0.06849999999999999</v>
+      </c>
+      <c r="E2" s="14">
+        <v>0.0204</v>
+      </c>
+      <c r="F2" s="14">
+        <v>-0.0018</v>
+      </c>
+      <c r="G2" s="14">
+        <v>-0.2514</v>
       </c>
     </row>
   </sheetData>

--- a/BAJAJ_GROUP_Technical_Metrics.xlsx
+++ b/BAJAJ_GROUP_Technical_Metrics.xlsx
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="264" uniqueCount="73">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="286" uniqueCount="79">
   <si>
     <t>Symbol</t>
   </si>
@@ -187,19 +187,37 @@
     <t>Curr Value</t>
   </si>
   <si>
-    <t>RSI Oversold Recovery</t>
-  </si>
-  <si>
-    <t>27.8 → 33.4</t>
+    <t>RSI Momentum</t>
+  </si>
+  <si>
+    <t>48.2 → 51.7</t>
   </si>
   <si>
     <t>🟢 BULLISH</t>
   </si>
   <si>
-    <t>27.8</t>
-  </si>
-  <si>
-    <t>33.4</t>
+    <t>48.2</t>
+  </si>
+  <si>
+    <t>51.7</t>
+  </si>
+  <si>
+    <t>45.7 → 53.7</t>
+  </si>
+  <si>
+    <t>45.7</t>
+  </si>
+  <si>
+    <t>53.7</t>
+  </si>
+  <si>
+    <t>Yes → No</t>
+  </si>
+  <si>
+    <t>🔴 BEARISH</t>
+  </si>
+  <si>
+    <t>20 DMA &gt; 50 DMA</t>
   </si>
   <si>
     <t>▶  NUMERIC METRIC CHANGES (vs Previous Run)</t>
@@ -401,7 +419,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="15">
+  <cellXfs count="16">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="2" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
@@ -409,6 +427,7 @@
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="5" fillId="6" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1"/>
     <xf numFmtId="165" fontId="5" fillId="6" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
@@ -783,8 +802,8 @@
     <col min="13" max="13" width="10.7109375" customWidth="1"/>
     <col min="14" max="14" width="11.7109375" customWidth="1"/>
     <col min="15" max="15" width="10.7109375" customWidth="1"/>
-    <col min="16" max="16" width="9.7109375" customWidth="1"/>
-    <col min="17" max="19" width="10.7109375" customWidth="1"/>
+    <col min="16" max="17" width="9.7109375" customWidth="1"/>
+    <col min="18" max="19" width="10.7109375" customWidth="1"/>
     <col min="20" max="20" width="22.7109375" customWidth="1"/>
     <col min="21" max="21" width="9.7109375" customWidth="1"/>
     <col min="22" max="22" width="10.7109375" customWidth="1"/>
@@ -924,10 +943,10 @@
         <v>44</v>
       </c>
       <c r="C2">
-        <v>11500</v>
+        <v>11414</v>
       </c>
       <c r="D2">
-        <v>-0.8</v>
+        <v>-0.75</v>
       </c>
       <c r="E2">
         <v>12361</v>
@@ -936,46 +955,46 @@
         <v>8506.780000000001</v>
       </c>
       <c r="G2">
-        <v>-6.97</v>
+        <v>-7.66</v>
       </c>
       <c r="H2">
-        <v>35.19</v>
+        <v>34.18</v>
       </c>
       <c r="I2">
-        <v>-2.46</v>
+        <v>-3.01</v>
       </c>
       <c r="J2">
-        <v>-0.92</v>
+        <v>-1.98</v>
       </c>
       <c r="K2">
-        <v>14.12</v>
+        <v>13.39</v>
       </c>
       <c r="L2">
-        <v>29.58</v>
+        <v>28.25</v>
       </c>
       <c r="M2">
-        <v>27.53</v>
+        <v>27.68</v>
       </c>
       <c r="N2">
         <v>85</v>
       </c>
       <c r="O2">
-        <v>82</v>
+        <v>80</v>
       </c>
       <c r="P2">
-        <v>11592.6</v>
+        <v>11521.8</v>
       </c>
       <c r="Q2">
-        <v>11823.35</v>
+        <v>11804.4</v>
       </c>
       <c r="R2">
-        <v>11431.07</v>
+        <v>11456.25</v>
       </c>
       <c r="S2">
-        <v>10031.42</v>
+        <v>10043.65</v>
       </c>
       <c r="T2">
-        <v>14.64</v>
+        <v>13.64</v>
       </c>
       <c r="U2" t="s">
         <v>45</v>
@@ -990,43 +1009,43 @@
         <v>3</v>
       </c>
       <c r="Y2">
-        <v>44.74</v>
+        <v>42.48</v>
       </c>
       <c r="Z2">
-        <v>29.1</v>
+        <v>3.5</v>
       </c>
       <c r="AA2">
-        <v>116.78</v>
+        <v>94.13</v>
       </c>
       <c r="AB2">
-        <v>-87.68000000000001</v>
+        <v>-90.62</v>
       </c>
       <c r="AC2">
-        <v>9.109999999999999</v>
+        <v>9.92</v>
       </c>
       <c r="AD2">
-        <v>5</v>
+        <v>8.31</v>
       </c>
       <c r="AE2">
-        <v>216.32</v>
+        <v>210.44</v>
       </c>
       <c r="AF2">
-        <v>-43.46</v>
+        <v>32.66</v>
       </c>
       <c r="AG2">
-        <v>12257.97</v>
+        <v>12276.07</v>
       </c>
       <c r="AH2">
-        <v>11388.73</v>
+        <v>11332.73</v>
       </c>
       <c r="AI2">
-        <v>12149.93</v>
+        <v>12104.33</v>
       </c>
       <c r="AJ2" t="s">
         <v>47</v>
       </c>
       <c r="AK2">
-        <v>31.21</v>
+        <v>32.65</v>
       </c>
     </row>
     <row r="3" spans="1:37">
@@ -1037,10 +1056,10 @@
         <v>44</v>
       </c>
       <c r="C3">
-        <v>502.45</v>
+        <v>512.15</v>
       </c>
       <c r="D3">
-        <v>0.88</v>
+        <v>1.93</v>
       </c>
       <c r="E3">
         <v>670.25</v>
@@ -1049,46 +1068,46 @@
         <v>228.14</v>
       </c>
       <c r="G3">
-        <v>-25.04</v>
+        <v>-23.59</v>
       </c>
       <c r="H3">
-        <v>120.24</v>
+        <v>124.49</v>
       </c>
       <c r="I3">
-        <v>-3.64</v>
+        <v>-2.35</v>
       </c>
       <c r="J3">
-        <v>3.8</v>
+        <v>2.29</v>
       </c>
       <c r="K3">
-        <v>-19.02</v>
+        <v>-18.09</v>
       </c>
       <c r="L3">
-        <v>124.39</v>
+        <v>122.71</v>
       </c>
       <c r="M3">
-        <v>16.11</v>
+        <v>16.9</v>
       </c>
       <c r="N3">
         <v>99</v>
       </c>
       <c r="O3">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="P3">
-        <v>509.85</v>
+        <v>507.39</v>
       </c>
       <c r="Q3">
-        <v>492.15</v>
+        <v>493.41</v>
       </c>
       <c r="R3">
-        <v>524.29</v>
+        <v>521.66</v>
       </c>
       <c r="S3">
-        <v>440.19</v>
+        <v>441.43</v>
       </c>
       <c r="T3">
-        <v>14.14</v>
+        <v>16.02</v>
       </c>
       <c r="U3" t="s">
         <v>46</v>
@@ -1103,34 +1122,34 @@
         <v>2</v>
       </c>
       <c r="Y3">
-        <v>48.17</v>
+        <v>51.74</v>
       </c>
       <c r="Z3">
-        <v>-1.68</v>
+        <v>-0.99</v>
       </c>
       <c r="AA3">
-        <v>-5.1</v>
+        <v>-4.28</v>
       </c>
       <c r="AB3">
-        <v>3.42</v>
+        <v>3.29</v>
       </c>
       <c r="AC3">
-        <v>59.26</v>
+        <v>60.06</v>
       </c>
       <c r="AD3">
-        <v>72.37</v>
+        <v>64.11</v>
       </c>
       <c r="AE3">
-        <v>20.58</v>
+        <v>21.22</v>
       </c>
       <c r="AF3">
-        <v>-68.7</v>
+        <v>-1.18</v>
       </c>
       <c r="AG3">
-        <v>541.41</v>
+        <v>543.39</v>
       </c>
       <c r="AH3">
-        <v>442.89</v>
+        <v>443.42</v>
       </c>
       <c r="AI3">
         <v>460.99</v>
@@ -1139,7 +1158,7 @@
         <v>48</v>
       </c>
       <c r="AK3">
-        <v>24.56</v>
+        <v>25.04</v>
       </c>
     </row>
     <row r="4" spans="1:37">
@@ -1150,10 +1169,10 @@
         <v>44</v>
       </c>
       <c r="C4">
-        <v>325.3</v>
+        <v>323.05</v>
       </c>
       <c r="D4">
-        <v>0.85</v>
+        <v>-0.6899999999999999</v>
       </c>
       <c r="E4">
         <v>604.85</v>
@@ -1162,25 +1181,25 @@
         <v>303.75</v>
       </c>
       <c r="G4">
-        <v>-46.22</v>
+        <v>-46.59</v>
       </c>
       <c r="H4">
-        <v>7.09</v>
+        <v>6.35</v>
       </c>
       <c r="I4">
-        <v>-4.27</v>
+        <v>-4.35</v>
       </c>
       <c r="J4">
-        <v>-8.51</v>
+        <v>-8.630000000000001</v>
       </c>
       <c r="K4">
-        <v>-1.14</v>
+        <v>-0.8</v>
       </c>
       <c r="L4">
-        <v>-44.65</v>
+        <v>-45.09</v>
       </c>
       <c r="M4">
-        <v>-25.14</v>
+        <v>-25.55</v>
       </c>
       <c r="N4">
         <v>15</v>
@@ -1189,19 +1208,19 @@
         <v>17</v>
       </c>
       <c r="P4">
-        <v>329.86</v>
+        <v>326.92</v>
       </c>
       <c r="Q4">
-        <v>335.19</v>
+        <v>333.63</v>
       </c>
       <c r="R4">
-        <v>339.87</v>
+        <v>339.79</v>
       </c>
       <c r="S4">
-        <v>376.12</v>
+        <v>375.31</v>
       </c>
       <c r="T4">
-        <v>-13.51</v>
+        <v>-13.93</v>
       </c>
       <c r="U4" t="s">
         <v>46</v>
@@ -1216,34 +1235,34 @@
         <v>0</v>
       </c>
       <c r="Y4">
-        <v>40.76</v>
+        <v>39.32</v>
       </c>
       <c r="Z4">
-        <v>-4.06</v>
+        <v>-4.51</v>
       </c>
       <c r="AA4">
-        <v>-2.87</v>
+        <v>-3.2</v>
       </c>
       <c r="AB4">
-        <v>-1.18</v>
+        <v>-1.31</v>
       </c>
       <c r="AC4">
-        <v>24.04</v>
+        <v>18.51</v>
       </c>
       <c r="AD4">
-        <v>40.41</v>
+        <v>26.55</v>
       </c>
       <c r="AE4">
-        <v>10.36</v>
+        <v>10.21</v>
       </c>
       <c r="AF4">
-        <v>-66.45</v>
+        <v>-18.61</v>
       </c>
       <c r="AG4">
-        <v>353.04</v>
+        <v>349.81</v>
       </c>
       <c r="AH4">
-        <v>317.35</v>
+        <v>317.45</v>
       </c>
       <c r="AI4">
         <v>354.2</v>
@@ -1252,7 +1271,7 @@
         <v>47</v>
       </c>
       <c r="AK4">
-        <v>21.07</v>
+        <v>19.14</v>
       </c>
     </row>
     <row r="5" spans="1:37">
@@ -1263,10 +1282,10 @@
         <v>44</v>
       </c>
       <c r="C5">
-        <v>1859.2</v>
+        <v>1852.5</v>
       </c>
       <c r="D5">
-        <v>1.21</v>
+        <v>-0.36</v>
       </c>
       <c r="E5">
         <v>2176.6</v>
@@ -1275,88 +1294,88 @@
         <v>1631.8</v>
       </c>
       <c r="G5">
-        <v>-14.58</v>
+        <v>-14.89</v>
       </c>
       <c r="H5">
-        <v>13.94</v>
+        <v>13.52</v>
       </c>
       <c r="I5">
-        <v>-3.52</v>
+        <v>-4.53</v>
       </c>
       <c r="J5">
-        <v>-7.56</v>
+        <v>-7.93</v>
       </c>
       <c r="K5">
-        <v>4.94</v>
+        <v>4.7</v>
       </c>
       <c r="L5">
-        <v>-10.68</v>
+        <v>-10.94</v>
       </c>
       <c r="M5">
-        <v>2.04</v>
+        <v>1.75</v>
       </c>
       <c r="N5">
-        <v>43</v>
+        <v>29</v>
       </c>
       <c r="O5">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="P5">
-        <v>1881.14</v>
+        <v>1863.54</v>
       </c>
       <c r="Q5">
-        <v>1961.58</v>
+        <v>1953.41</v>
       </c>
       <c r="R5">
-        <v>1959.76</v>
+        <v>1958.91</v>
       </c>
       <c r="S5">
-        <v>1898.78</v>
+        <v>1897.63</v>
       </c>
       <c r="T5">
-        <v>-2.08</v>
+        <v>-2.38</v>
       </c>
       <c r="U5" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="V5" t="s">
         <v>45</v>
       </c>
       <c r="W5" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="X5">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="Y5">
-        <v>33.43</v>
+        <v>32.6</v>
       </c>
       <c r="Z5">
-        <v>-29.37</v>
+        <v>-32.28</v>
       </c>
       <c r="AA5">
-        <v>-11.56</v>
+        <v>-15.71</v>
       </c>
       <c r="AB5">
-        <v>-17.8</v>
+        <v>-16.57</v>
       </c>
       <c r="AC5">
-        <v>6.34</v>
+        <v>11.75</v>
       </c>
       <c r="AD5">
-        <v>4.21</v>
+        <v>6.03</v>
       </c>
       <c r="AE5">
-        <v>37.82</v>
+        <v>36.55</v>
       </c>
       <c r="AF5">
-        <v>-22.51</v>
+        <v>20.65</v>
       </c>
       <c r="AG5">
-        <v>2079.06</v>
+        <v>2077.51</v>
       </c>
       <c r="AH5">
-        <v>1844.11</v>
+        <v>1829.31</v>
       </c>
       <c r="AI5">
         <v>1961</v>
@@ -1365,7 +1384,7 @@
         <v>47</v>
       </c>
       <c r="AK5">
-        <v>61.51</v>
+        <v>62.6</v>
       </c>
     </row>
     <row r="6" spans="1:37">
@@ -1376,10 +1395,10 @@
         <v>44</v>
       </c>
       <c r="C6">
-        <v>11010</v>
+        <v>11282</v>
       </c>
       <c r="D6">
-        <v>0.73</v>
+        <v>2.47</v>
       </c>
       <c r="E6">
         <v>13595.75</v>
@@ -1388,46 +1407,46 @@
         <v>8746</v>
       </c>
       <c r="G6">
-        <v>-19.02</v>
+        <v>-17.02</v>
       </c>
       <c r="H6">
-        <v>25.89</v>
+        <v>29</v>
       </c>
       <c r="I6">
-        <v>-0.61</v>
+        <v>2.64</v>
       </c>
       <c r="J6">
-        <v>-2.17</v>
+        <v>-0.86</v>
       </c>
       <c r="K6">
-        <v>3.13</v>
+        <v>5.67</v>
       </c>
       <c r="L6">
-        <v>-16.25</v>
+        <v>-14.09</v>
       </c>
       <c r="M6">
-        <v>21.89</v>
+        <v>22.05</v>
       </c>
       <c r="N6">
-        <v>29</v>
+        <v>43</v>
       </c>
       <c r="O6">
-        <v>50</v>
+        <v>53</v>
       </c>
       <c r="P6">
-        <v>11033.2</v>
+        <v>11091.2</v>
       </c>
       <c r="Q6">
-        <v>11200.2</v>
+        <v>11195.9</v>
       </c>
       <c r="R6">
-        <v>11082.3</v>
+        <v>11096.32</v>
       </c>
       <c r="S6">
-        <v>10680.32</v>
+        <v>10680.08</v>
       </c>
       <c r="T6">
-        <v>3.09</v>
+        <v>5.64</v>
       </c>
       <c r="U6" t="s">
         <v>45</v>
@@ -1442,34 +1461,34 @@
         <v>3</v>
       </c>
       <c r="Y6">
-        <v>45.69</v>
+        <v>53.69</v>
       </c>
       <c r="Z6">
-        <v>-49.38</v>
+        <v>-31</v>
       </c>
       <c r="AA6">
-        <v>-9.09</v>
+        <v>-13.47</v>
       </c>
       <c r="AB6">
-        <v>-40.28</v>
+        <v>-17.52</v>
       </c>
       <c r="AC6">
-        <v>14.44</v>
+        <v>25.43</v>
       </c>
       <c r="AD6">
-        <v>18.74</v>
+        <v>19.89</v>
       </c>
       <c r="AE6">
-        <v>217.26</v>
+        <v>226.95</v>
       </c>
       <c r="AF6">
-        <v>-28.52</v>
+        <v>34.14</v>
       </c>
       <c r="AG6">
-        <v>11589.15</v>
+        <v>11578.89</v>
       </c>
       <c r="AH6">
-        <v>10811.25</v>
+        <v>10812.91</v>
       </c>
       <c r="AI6">
         <v>10787.84</v>
@@ -1478,7 +1497,7 @@
         <v>48</v>
       </c>
       <c r="AK6">
-        <v>19.9</v>
+        <v>19.95</v>
       </c>
     </row>
     <row r="7" spans="1:37">
@@ -1489,10 +1508,10 @@
         <v>44</v>
       </c>
       <c r="C7">
-        <v>1015</v>
+        <v>1040.3</v>
       </c>
       <c r="D7">
-        <v>0.87</v>
+        <v>2.49</v>
       </c>
       <c r="E7">
         <v>1158.8</v>
@@ -1501,46 +1520,46 @@
         <v>801.55</v>
       </c>
       <c r="G7">
-        <v>-12.41</v>
+        <v>-10.23</v>
       </c>
       <c r="H7">
-        <v>26.63</v>
+        <v>29.79</v>
       </c>
       <c r="I7">
-        <v>-2.34</v>
+        <v>-0.31</v>
       </c>
       <c r="J7">
-        <v>-7.25</v>
+        <v>-3.69</v>
       </c>
       <c r="K7">
-        <v>5.86</v>
+        <v>8.16</v>
       </c>
       <c r="L7">
-        <v>1.17</v>
+        <v>3.02</v>
       </c>
       <c r="M7">
-        <v>6.85</v>
+        <v>7.34</v>
       </c>
       <c r="N7">
         <v>71</v>
       </c>
       <c r="O7">
-        <v>62</v>
+        <v>66</v>
       </c>
       <c r="P7">
-        <v>1021.68</v>
+        <v>1021.04</v>
       </c>
       <c r="Q7">
-        <v>1057.02</v>
+        <v>1054.29</v>
       </c>
       <c r="R7">
-        <v>1066.32</v>
+        <v>1067.05</v>
       </c>
       <c r="S7">
-        <v>977.63</v>
+        <v>977.73</v>
       </c>
       <c r="T7">
-        <v>3.82</v>
+        <v>6.4</v>
       </c>
       <c r="U7" t="s">
         <v>46</v>
@@ -1555,34 +1574,34 @@
         <v>2</v>
       </c>
       <c r="Y7">
-        <v>35.33</v>
+        <v>45.91</v>
       </c>
       <c r="Z7">
-        <v>-15.13</v>
+        <v>-13.78</v>
       </c>
       <c r="AA7">
-        <v>-8.4</v>
+        <v>-9.48</v>
       </c>
       <c r="AB7">
-        <v>-6.73</v>
+        <v>-4.3</v>
       </c>
       <c r="AC7">
-        <v>7.53</v>
+        <v>40.86</v>
       </c>
       <c r="AD7">
-        <v>4.08</v>
+        <v>16.13</v>
       </c>
       <c r="AE7">
-        <v>21.01</v>
+        <v>21.32</v>
       </c>
       <c r="AF7">
-        <v>-1.34</v>
+        <v>65.65000000000001</v>
       </c>
       <c r="AG7">
-        <v>1111.18</v>
+        <v>1105.83</v>
       </c>
       <c r="AH7">
-        <v>1002.86</v>
+        <v>1002.74</v>
       </c>
       <c r="AI7">
         <v>1075.64</v>
@@ -1591,7 +1610,7 @@
         <v>47</v>
       </c>
       <c r="AK7">
-        <v>45.65</v>
+        <v>41.79</v>
       </c>
     </row>
     <row r="8" spans="1:37">
@@ -1602,10 +1621,10 @@
         <v>44</v>
       </c>
       <c r="C8">
-        <v>134.2</v>
+        <v>134.78</v>
       </c>
       <c r="D8">
-        <v>-0.51</v>
+        <v>0.43</v>
       </c>
       <c r="E8">
         <v>148.95</v>
@@ -1614,46 +1633,46 @@
         <v>115.96</v>
       </c>
       <c r="G8">
-        <v>-9.9</v>
+        <v>-9.51</v>
       </c>
       <c r="H8">
-        <v>15.73</v>
+        <v>16.23</v>
       </c>
       <c r="I8">
-        <v>-3.93</v>
+        <v>-5.46</v>
       </c>
       <c r="J8">
-        <v>-1.1</v>
+        <v>0.16</v>
       </c>
       <c r="K8">
-        <v>-2.02</v>
+        <v>-0.76</v>
       </c>
       <c r="L8">
-        <v>-1.86</v>
+        <v>-2.76</v>
       </c>
       <c r="M8">
-        <v>-0.18</v>
+        <v>0.64</v>
       </c>
       <c r="N8">
         <v>57</v>
       </c>
       <c r="O8">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="P8">
-        <v>137.35</v>
+        <v>135.79</v>
       </c>
       <c r="Q8">
-        <v>136.58</v>
+        <v>136.47</v>
       </c>
       <c r="R8">
-        <v>138.34</v>
+        <v>138.42</v>
       </c>
       <c r="S8">
-        <v>133.81</v>
+        <v>133.82</v>
       </c>
       <c r="T8">
-        <v>0.29</v>
+        <v>0.72</v>
       </c>
       <c r="U8" t="s">
         <v>46</v>
@@ -1668,34 +1687,34 @@
         <v>2</v>
       </c>
       <c r="Y8">
-        <v>43.32</v>
+        <v>44.84</v>
       </c>
       <c r="Z8">
-        <v>-0.34</v>
+        <v>-0.46</v>
       </c>
       <c r="AA8">
-        <v>-0.26</v>
+        <v>-0.3</v>
       </c>
       <c r="AB8">
-        <v>-0.08</v>
+        <v>-0.16</v>
       </c>
       <c r="AC8">
-        <v>25.77</v>
+        <v>24.1</v>
       </c>
       <c r="AD8">
-        <v>44.04</v>
+        <v>30.22</v>
       </c>
       <c r="AE8">
-        <v>4.41</v>
+        <v>4.31</v>
       </c>
       <c r="AF8">
-        <v>-70.84</v>
+        <v>-42.72</v>
       </c>
       <c r="AG8">
-        <v>141.01</v>
+        <v>140.97</v>
       </c>
       <c r="AH8">
-        <v>132.15</v>
+        <v>131.97</v>
       </c>
       <c r="AI8">
         <v>131.91</v>
@@ -1704,7 +1723,7 @@
         <v>48</v>
       </c>
       <c r="AK8">
-        <v>26.34</v>
+        <v>24.26</v>
       </c>
     </row>
   </sheetData>
@@ -1845,7 +1864,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:F62"/>
+  <dimension ref="A1:F67"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="16.7109375" customWidth="1"/>
@@ -1885,7 +1904,7 @@
     </row>
     <row r="3" spans="1:6">
       <c r="A3" s="4" t="s">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="B3" s="4" t="s">
         <v>55</v>
@@ -1903,988 +1922,1082 @@
         <v>59</v>
       </c>
     </row>
+    <row r="4" spans="1:6">
+      <c r="A4" s="4" t="s">
+        <v>41</v>
+      </c>
+      <c r="B4" s="4" t="s">
+        <v>55</v>
+      </c>
+      <c r="C4" s="4" t="s">
+        <v>60</v>
+      </c>
+      <c r="D4" s="4" t="s">
+        <v>57</v>
+      </c>
+      <c r="E4" s="4" t="s">
+        <v>61</v>
+      </c>
+      <c r="F4" s="4" t="s">
+        <v>62</v>
+      </c>
+    </row>
     <row r="5" spans="1:6">
-      <c r="A5" s="2" t="s">
-        <v>60</v>
-      </c>
-      <c r="B5" s="2"/>
-      <c r="C5" s="2"/>
-      <c r="D5" s="2"/>
-      <c r="E5" s="2"/>
+      <c r="A5" s="5" t="s">
+        <v>40</v>
+      </c>
+      <c r="B5" s="5" t="s">
+        <v>22</v>
+      </c>
+      <c r="C5" s="5" t="s">
+        <v>63</v>
+      </c>
+      <c r="D5" s="5" t="s">
+        <v>64</v>
+      </c>
+      <c r="E5" s="5" t="s">
+        <v>45</v>
+      </c>
+      <c r="F5" s="5" t="s">
+        <v>46</v>
+      </c>
     </row>
     <row r="6" spans="1:6">
-      <c r="A6" s="3" t="s">
+      <c r="A6" s="5" t="s">
+        <v>40</v>
+      </c>
+      <c r="B6" s="5" t="s">
+        <v>65</v>
+      </c>
+      <c r="C6" s="5" t="s">
+        <v>63</v>
+      </c>
+      <c r="D6" s="5" t="s">
+        <v>64</v>
+      </c>
+      <c r="E6" s="5" t="s">
+        <v>45</v>
+      </c>
+      <c r="F6" s="5" t="s">
+        <v>46</v>
+      </c>
+    </row>
+    <row r="8" spans="1:6">
+      <c r="A8" s="2" t="s">
+        <v>66</v>
+      </c>
+      <c r="B8" s="2"/>
+      <c r="C8" s="2"/>
+      <c r="D8" s="2"/>
+      <c r="E8" s="2"/>
+    </row>
+    <row r="9" spans="1:6">
+      <c r="A9" s="3" t="s">
         <v>0</v>
       </c>
-      <c r="B6" s="3" t="s">
-        <v>61</v>
-      </c>
-      <c r="C6" s="3" t="s">
-        <v>62</v>
-      </c>
-      <c r="D6" s="3" t="s">
-        <v>63</v>
-      </c>
-      <c r="E6" s="3" t="s">
-        <v>64</v>
-      </c>
-    </row>
-    <row r="7" spans="1:6">
-      <c r="A7" s="5" t="s">
+      <c r="B9" s="3" t="s">
+        <v>67</v>
+      </c>
+      <c r="C9" s="3" t="s">
+        <v>68</v>
+      </c>
+      <c r="D9" s="3" t="s">
+        <v>69</v>
+      </c>
+      <c r="E9" s="3" t="s">
+        <v>70</v>
+      </c>
+    </row>
+    <row r="10" spans="1:6">
+      <c r="A10" s="6" t="s">
         <v>37</v>
       </c>
-      <c r="B7" s="5" t="s">
+      <c r="B10" s="6" t="s">
         <v>9</v>
       </c>
-      <c r="C7" s="6">
-        <v>-0.91</v>
-      </c>
-      <c r="D7" s="6">
+      <c r="C10" s="7">
         <v>-0.92</v>
       </c>
-      <c r="E7" s="7">
-        <v>-0.01</v>
-      </c>
-    </row>
-    <row r="8" spans="1:6">
-      <c r="A8" s="5" t="s">
+      <c r="D10" s="7">
+        <v>-1.98</v>
+      </c>
+      <c r="E10" s="8">
+        <v>-1.06</v>
+      </c>
+    </row>
+    <row r="11" spans="1:6">
+      <c r="A11" s="6" t="s">
         <v>38</v>
       </c>
-      <c r="B8" s="5" t="s">
+      <c r="B11" s="6" t="s">
         <v>9</v>
       </c>
-      <c r="C8" s="6">
-        <v>3.46</v>
-      </c>
-      <c r="D8" s="6">
+      <c r="C11" s="7">
         <v>3.8</v>
       </c>
-      <c r="E8" s="8">
+      <c r="D11" s="7">
+        <v>2.29</v>
+      </c>
+      <c r="E11" s="8">
+        <v>-1.51</v>
+      </c>
+    </row>
+    <row r="12" spans="1:6">
+      <c r="A12" s="6" t="s">
+        <v>39</v>
+      </c>
+      <c r="B12" s="6" t="s">
+        <v>9</v>
+      </c>
+      <c r="C12" s="7">
+        <v>-8.51</v>
+      </c>
+      <c r="D12" s="7">
+        <v>-8.630000000000001</v>
+      </c>
+      <c r="E12" s="8">
+        <v>-0.12</v>
+      </c>
+    </row>
+    <row r="13" spans="1:6">
+      <c r="A13" s="6" t="s">
+        <v>40</v>
+      </c>
+      <c r="B13" s="6" t="s">
+        <v>9</v>
+      </c>
+      <c r="C13" s="7">
+        <v>-7.56</v>
+      </c>
+      <c r="D13" s="7">
+        <v>-7.93</v>
+      </c>
+      <c r="E13" s="8">
+        <v>-0.37</v>
+      </c>
+    </row>
+    <row r="14" spans="1:6">
+      <c r="A14" s="6" t="s">
+        <v>41</v>
+      </c>
+      <c r="B14" s="6" t="s">
+        <v>9</v>
+      </c>
+      <c r="C14" s="7">
+        <v>-2.17</v>
+      </c>
+      <c r="D14" s="7">
+        <v>-0.86</v>
+      </c>
+      <c r="E14" s="9">
+        <v>1.31</v>
+      </c>
+    </row>
+    <row r="15" spans="1:6">
+      <c r="A15" s="6" t="s">
+        <v>42</v>
+      </c>
+      <c r="B15" s="6" t="s">
+        <v>9</v>
+      </c>
+      <c r="C15" s="7">
+        <v>-7.25</v>
+      </c>
+      <c r="D15" s="7">
+        <v>-3.69</v>
+      </c>
+      <c r="E15" s="9">
+        <v>3.56</v>
+      </c>
+    </row>
+    <row r="16" spans="1:6">
+      <c r="A16" s="6" t="s">
+        <v>43</v>
+      </c>
+      <c r="B16" s="6" t="s">
+        <v>9</v>
+      </c>
+      <c r="C16" s="7">
+        <v>-1.1</v>
+      </c>
+      <c r="D16" s="7">
+        <v>0.16</v>
+      </c>
+      <c r="E16" s="9">
+        <v>1.26</v>
+      </c>
+    </row>
+    <row r="17" spans="1:5">
+      <c r="A17" s="6" t="s">
+        <v>37</v>
+      </c>
+      <c r="B17" s="6" t="s">
+        <v>8</v>
+      </c>
+      <c r="C17" s="7">
+        <v>-2.46</v>
+      </c>
+      <c r="D17" s="7">
+        <v>-3.01</v>
+      </c>
+      <c r="E17" s="8">
+        <v>-0.55</v>
+      </c>
+    </row>
+    <row r="18" spans="1:5">
+      <c r="A18" s="6" t="s">
+        <v>38</v>
+      </c>
+      <c r="B18" s="6" t="s">
+        <v>8</v>
+      </c>
+      <c r="C18" s="7">
+        <v>-3.64</v>
+      </c>
+      <c r="D18" s="7">
+        <v>-2.35</v>
+      </c>
+      <c r="E18" s="9">
+        <v>1.29</v>
+      </c>
+    </row>
+    <row r="19" spans="1:5">
+      <c r="A19" s="6" t="s">
+        <v>39</v>
+      </c>
+      <c r="B19" s="6" t="s">
+        <v>8</v>
+      </c>
+      <c r="C19" s="7">
+        <v>-4.27</v>
+      </c>
+      <c r="D19" s="7">
+        <v>-4.35</v>
+      </c>
+      <c r="E19" s="8">
+        <v>-0.08</v>
+      </c>
+    </row>
+    <row r="20" spans="1:5">
+      <c r="A20" s="6" t="s">
+        <v>40</v>
+      </c>
+      <c r="B20" s="6" t="s">
+        <v>8</v>
+      </c>
+      <c r="C20" s="7">
+        <v>-3.52</v>
+      </c>
+      <c r="D20" s="7">
+        <v>-4.53</v>
+      </c>
+      <c r="E20" s="8">
+        <v>-1.01</v>
+      </c>
+    </row>
+    <row r="21" spans="1:5">
+      <c r="A21" s="6" t="s">
+        <v>41</v>
+      </c>
+      <c r="B21" s="6" t="s">
+        <v>8</v>
+      </c>
+      <c r="C21" s="7">
+        <v>-0.61</v>
+      </c>
+      <c r="D21" s="7">
+        <v>2.64</v>
+      </c>
+      <c r="E21" s="9">
+        <v>3.25</v>
+      </c>
+    </row>
+    <row r="22" spans="1:5">
+      <c r="A22" s="6" t="s">
+        <v>42</v>
+      </c>
+      <c r="B22" s="6" t="s">
+        <v>8</v>
+      </c>
+      <c r="C22" s="7">
+        <v>-2.34</v>
+      </c>
+      <c r="D22" s="7">
+        <v>-0.31</v>
+      </c>
+      <c r="E22" s="9">
+        <v>2.03</v>
+      </c>
+    </row>
+    <row r="23" spans="1:5">
+      <c r="A23" s="6" t="s">
+        <v>43</v>
+      </c>
+      <c r="B23" s="6" t="s">
+        <v>8</v>
+      </c>
+      <c r="C23" s="7">
+        <v>-3.93</v>
+      </c>
+      <c r="D23" s="7">
+        <v>-5.46</v>
+      </c>
+      <c r="E23" s="8">
+        <v>-1.53</v>
+      </c>
+    </row>
+    <row r="24" spans="1:5">
+      <c r="A24" s="6" t="s">
+        <v>37</v>
+      </c>
+      <c r="B24" s="6" t="s">
+        <v>11</v>
+      </c>
+      <c r="C24" s="7">
+        <v>29.58</v>
+      </c>
+      <c r="D24" s="7">
+        <v>28.25</v>
+      </c>
+      <c r="E24" s="8">
+        <v>-1.33</v>
+      </c>
+    </row>
+    <row r="25" spans="1:5">
+      <c r="A25" s="6" t="s">
+        <v>38</v>
+      </c>
+      <c r="B25" s="6" t="s">
+        <v>11</v>
+      </c>
+      <c r="C25" s="7">
+        <v>124.39</v>
+      </c>
+      <c r="D25" s="7">
+        <v>122.71</v>
+      </c>
+      <c r="E25" s="8">
+        <v>-1.68</v>
+      </c>
+    </row>
+    <row r="26" spans="1:5">
+      <c r="A26" s="6" t="s">
+        <v>39</v>
+      </c>
+      <c r="B26" s="6" t="s">
+        <v>11</v>
+      </c>
+      <c r="C26" s="7">
+        <v>-44.65</v>
+      </c>
+      <c r="D26" s="7">
+        <v>-45.09</v>
+      </c>
+      <c r="E26" s="8">
+        <v>-0.44</v>
+      </c>
+    </row>
+    <row r="27" spans="1:5">
+      <c r="A27" s="6" t="s">
+        <v>40</v>
+      </c>
+      <c r="B27" s="6" t="s">
+        <v>11</v>
+      </c>
+      <c r="C27" s="7">
+        <v>-10.68</v>
+      </c>
+      <c r="D27" s="7">
+        <v>-10.94</v>
+      </c>
+      <c r="E27" s="8">
+        <v>-0.26</v>
+      </c>
+    </row>
+    <row r="28" spans="1:5">
+      <c r="A28" s="6" t="s">
+        <v>41</v>
+      </c>
+      <c r="B28" s="6" t="s">
+        <v>11</v>
+      </c>
+      <c r="C28" s="7">
+        <v>-16.25</v>
+      </c>
+      <c r="D28" s="7">
+        <v>-14.09</v>
+      </c>
+      <c r="E28" s="9">
+        <v>2.16</v>
+      </c>
+    </row>
+    <row r="29" spans="1:5">
+      <c r="A29" s="6" t="s">
+        <v>42</v>
+      </c>
+      <c r="B29" s="6" t="s">
+        <v>11</v>
+      </c>
+      <c r="C29" s="7">
+        <v>1.17</v>
+      </c>
+      <c r="D29" s="7">
+        <v>3.02</v>
+      </c>
+      <c r="E29" s="9">
+        <v>1.85</v>
+      </c>
+    </row>
+    <row r="30" spans="1:5">
+      <c r="A30" s="6" t="s">
+        <v>43</v>
+      </c>
+      <c r="B30" s="6" t="s">
+        <v>11</v>
+      </c>
+      <c r="C30" s="7">
+        <v>-1.86</v>
+      </c>
+      <c r="D30" s="7">
+        <v>-2.76</v>
+      </c>
+      <c r="E30" s="8">
+        <v>-0.9</v>
+      </c>
+    </row>
+    <row r="31" spans="1:5">
+      <c r="A31" s="6" t="s">
+        <v>37</v>
+      </c>
+      <c r="B31" s="6" t="s">
+        <v>10</v>
+      </c>
+      <c r="C31" s="7">
+        <v>14.12</v>
+      </c>
+      <c r="D31" s="7">
+        <v>13.39</v>
+      </c>
+      <c r="E31" s="8">
+        <v>-0.73</v>
+      </c>
+    </row>
+    <row r="32" spans="1:5">
+      <c r="A32" s="6" t="s">
+        <v>38</v>
+      </c>
+      <c r="B32" s="6" t="s">
+        <v>10</v>
+      </c>
+      <c r="C32" s="7">
+        <v>-19.02</v>
+      </c>
+      <c r="D32" s="7">
+        <v>-18.09</v>
+      </c>
+      <c r="E32" s="9">
+        <v>0.93</v>
+      </c>
+    </row>
+    <row r="33" spans="1:5">
+      <c r="A33" s="6" t="s">
+        <v>39</v>
+      </c>
+      <c r="B33" s="6" t="s">
+        <v>10</v>
+      </c>
+      <c r="C33" s="7">
+        <v>-1.14</v>
+      </c>
+      <c r="D33" s="7">
+        <v>-0.8</v>
+      </c>
+      <c r="E33" s="9">
         <v>0.34</v>
       </c>
     </row>
-    <row r="9" spans="1:6">
-      <c r="A9" s="5" t="s">
+    <row r="34" spans="1:5">
+      <c r="A34" s="6" t="s">
+        <v>40</v>
+      </c>
+      <c r="B34" s="6" t="s">
+        <v>10</v>
+      </c>
+      <c r="C34" s="7">
+        <v>4.94</v>
+      </c>
+      <c r="D34" s="7">
+        <v>4.7</v>
+      </c>
+      <c r="E34" s="8">
+        <v>-0.24</v>
+      </c>
+    </row>
+    <row r="35" spans="1:5">
+      <c r="A35" s="6" t="s">
+        <v>41</v>
+      </c>
+      <c r="B35" s="6" t="s">
+        <v>10</v>
+      </c>
+      <c r="C35" s="7">
+        <v>3.13</v>
+      </c>
+      <c r="D35" s="7">
+        <v>5.67</v>
+      </c>
+      <c r="E35" s="9">
+        <v>2.54</v>
+      </c>
+    </row>
+    <row r="36" spans="1:5">
+      <c r="A36" s="6" t="s">
+        <v>42</v>
+      </c>
+      <c r="B36" s="6" t="s">
+        <v>10</v>
+      </c>
+      <c r="C36" s="7">
+        <v>5.86</v>
+      </c>
+      <c r="D36" s="7">
+        <v>8.16</v>
+      </c>
+      <c r="E36" s="9">
+        <v>2.3</v>
+      </c>
+    </row>
+    <row r="37" spans="1:5">
+      <c r="A37" s="6" t="s">
+        <v>43</v>
+      </c>
+      <c r="B37" s="6" t="s">
+        <v>10</v>
+      </c>
+      <c r="C37" s="7">
+        <v>-2.02</v>
+      </c>
+      <c r="D37" s="7">
+        <v>-0.76</v>
+      </c>
+      <c r="E37" s="9">
+        <v>1.26</v>
+      </c>
+    </row>
+    <row r="38" spans="1:5">
+      <c r="A38" s="6" t="s">
+        <v>37</v>
+      </c>
+      <c r="B38" s="6" t="s">
+        <v>6</v>
+      </c>
+      <c r="C38" s="7">
+        <v>-6.97</v>
+      </c>
+      <c r="D38" s="7">
+        <v>-7.66</v>
+      </c>
+      <c r="E38" s="8">
+        <v>-0.6899999999999999</v>
+      </c>
+    </row>
+    <row r="39" spans="1:5">
+      <c r="A39" s="6" t="s">
+        <v>38</v>
+      </c>
+      <c r="B39" s="6" t="s">
+        <v>6</v>
+      </c>
+      <c r="C39" s="7">
+        <v>-25.04</v>
+      </c>
+      <c r="D39" s="7">
+        <v>-23.59</v>
+      </c>
+      <c r="E39" s="9">
+        <v>1.45</v>
+      </c>
+    </row>
+    <row r="40" spans="1:5">
+      <c r="A40" s="6" t="s">
         <v>39</v>
       </c>
-      <c r="B9" s="5" t="s">
-        <v>9</v>
-      </c>
-      <c r="C9" s="6">
-        <v>-11</v>
-      </c>
-      <c r="D9" s="6">
-        <v>-8.51</v>
-      </c>
-      <c r="E9" s="8">
-        <v>2.49</v>
-      </c>
-    </row>
-    <row r="10" spans="1:6">
-      <c r="A10" s="5" t="s">
+      <c r="B40" s="6" t="s">
+        <v>6</v>
+      </c>
+      <c r="C40" s="7">
+        <v>-46.22</v>
+      </c>
+      <c r="D40" s="7">
+        <v>-46.59</v>
+      </c>
+      <c r="E40" s="8">
+        <v>-0.37</v>
+      </c>
+    </row>
+    <row r="41" spans="1:5">
+      <c r="A41" s="6" t="s">
         <v>40</v>
       </c>
-      <c r="B10" s="5" t="s">
-        <v>9</v>
-      </c>
-      <c r="C10" s="6">
-        <v>-8.380000000000001</v>
-      </c>
-      <c r="D10" s="6">
-        <v>-7.56</v>
-      </c>
-      <c r="E10" s="8">
-        <v>0.82</v>
-      </c>
-    </row>
-    <row r="11" spans="1:6">
-      <c r="A11" s="5" t="s">
+      <c r="B41" s="6" t="s">
+        <v>6</v>
+      </c>
+      <c r="C41" s="7">
+        <v>-14.58</v>
+      </c>
+      <c r="D41" s="7">
+        <v>-14.89</v>
+      </c>
+      <c r="E41" s="8">
+        <v>-0.31</v>
+      </c>
+    </row>
+    <row r="42" spans="1:5">
+      <c r="A42" s="6" t="s">
         <v>41</v>
       </c>
-      <c r="B11" s="5" t="s">
-        <v>9</v>
-      </c>
-      <c r="C11" s="6">
-        <v>-4.75</v>
-      </c>
-      <c r="D11" s="6">
-        <v>-2.17</v>
-      </c>
-      <c r="E11" s="8">
-        <v>2.58</v>
-      </c>
-    </row>
-    <row r="12" spans="1:6">
-      <c r="A12" s="5" t="s">
+      <c r="B42" s="6" t="s">
+        <v>6</v>
+      </c>
+      <c r="C42" s="7">
+        <v>-19.02</v>
+      </c>
+      <c r="D42" s="7">
+        <v>-17.02</v>
+      </c>
+      <c r="E42" s="9">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="43" spans="1:5">
+      <c r="A43" s="6" t="s">
         <v>42</v>
       </c>
-      <c r="B12" s="5" t="s">
-        <v>9</v>
-      </c>
-      <c r="C12" s="6">
-        <v>-7.63</v>
-      </c>
-      <c r="D12" s="6">
-        <v>-7.25</v>
-      </c>
-      <c r="E12" s="8">
-        <v>0.38</v>
-      </c>
-    </row>
-    <row r="13" spans="1:6">
-      <c r="A13" s="5" t="s">
+      <c r="B43" s="6" t="s">
+        <v>6</v>
+      </c>
+      <c r="C43" s="7">
+        <v>-12.41</v>
+      </c>
+      <c r="D43" s="7">
+        <v>-10.23</v>
+      </c>
+      <c r="E43" s="9">
+        <v>2.18</v>
+      </c>
+    </row>
+    <row r="44" spans="1:5">
+      <c r="A44" s="6" t="s">
         <v>43</v>
       </c>
-      <c r="B13" s="5" t="s">
-        <v>9</v>
-      </c>
-      <c r="C13" s="6">
-        <v>0.5600000000000001</v>
-      </c>
-      <c r="D13" s="6">
-        <v>-1.1</v>
-      </c>
-      <c r="E13" s="7">
-        <v>-1.66</v>
-      </c>
-    </row>
-    <row r="14" spans="1:6">
-      <c r="A14" s="5" t="s">
+      <c r="B44" s="6" t="s">
+        <v>6</v>
+      </c>
+      <c r="C44" s="7">
+        <v>-9.9</v>
+      </c>
+      <c r="D44" s="7">
+        <v>-9.51</v>
+      </c>
+      <c r="E44" s="9">
+        <v>0.39</v>
+      </c>
+    </row>
+    <row r="45" spans="1:5">
+      <c r="A45" s="6" t="s">
         <v>37</v>
       </c>
-      <c r="B14" s="5" t="s">
+      <c r="B45" s="6" t="s">
+        <v>2</v>
+      </c>
+      <c r="C45" s="7">
+        <v>11500</v>
+      </c>
+      <c r="D45" s="7">
+        <v>11414</v>
+      </c>
+      <c r="E45" s="8">
+        <v>-86</v>
+      </c>
+    </row>
+    <row r="46" spans="1:5">
+      <c r="A46" s="6" t="s">
+        <v>38</v>
+      </c>
+      <c r="B46" s="6" t="s">
+        <v>2</v>
+      </c>
+      <c r="C46" s="7">
+        <v>502.45</v>
+      </c>
+      <c r="D46" s="7">
+        <v>512.15</v>
+      </c>
+      <c r="E46" s="9">
+        <v>9.699999999999999</v>
+      </c>
+    </row>
+    <row r="47" spans="1:5">
+      <c r="A47" s="6" t="s">
+        <v>39</v>
+      </c>
+      <c r="B47" s="6" t="s">
+        <v>2</v>
+      </c>
+      <c r="C47" s="7">
+        <v>325.3</v>
+      </c>
+      <c r="D47" s="7">
+        <v>323.05</v>
+      </c>
+      <c r="E47" s="8">
+        <v>-2.25</v>
+      </c>
+    </row>
+    <row r="48" spans="1:5">
+      <c r="A48" s="6" t="s">
+        <v>40</v>
+      </c>
+      <c r="B48" s="6" t="s">
+        <v>2</v>
+      </c>
+      <c r="C48" s="7">
+        <v>1859.2</v>
+      </c>
+      <c r="D48" s="7">
+        <v>1852.5</v>
+      </c>
+      <c r="E48" s="8">
+        <v>-6.7</v>
+      </c>
+    </row>
+    <row r="49" spans="1:5">
+      <c r="A49" s="6" t="s">
+        <v>41</v>
+      </c>
+      <c r="B49" s="6" t="s">
+        <v>2</v>
+      </c>
+      <c r="C49" s="7">
+        <v>11010</v>
+      </c>
+      <c r="D49" s="7">
+        <v>11282</v>
+      </c>
+      <c r="E49" s="9">
+        <v>272</v>
+      </c>
+    </row>
+    <row r="50" spans="1:5">
+      <c r="A50" s="6" t="s">
+        <v>42</v>
+      </c>
+      <c r="B50" s="6" t="s">
+        <v>2</v>
+      </c>
+      <c r="C50" s="7">
+        <v>1015</v>
+      </c>
+      <c r="D50" s="7">
+        <v>1040.3</v>
+      </c>
+      <c r="E50" s="9">
+        <v>25.3</v>
+      </c>
+    </row>
+    <row r="51" spans="1:5">
+      <c r="A51" s="6" t="s">
+        <v>43</v>
+      </c>
+      <c r="B51" s="6" t="s">
+        <v>2</v>
+      </c>
+      <c r="C51" s="7">
+        <v>134.2</v>
+      </c>
+      <c r="D51" s="7">
+        <v>134.78</v>
+      </c>
+      <c r="E51" s="9">
+        <v>0.58</v>
+      </c>
+    </row>
+    <row r="52" spans="1:5">
+      <c r="A52" s="6" t="s">
+        <v>40</v>
+      </c>
+      <c r="B52" s="6" t="s">
+        <v>13</v>
+      </c>
+      <c r="C52" s="7">
+        <v>43</v>
+      </c>
+      <c r="D52" s="7">
+        <v>29</v>
+      </c>
+      <c r="E52" s="8">
+        <v>-14</v>
+      </c>
+    </row>
+    <row r="53" spans="1:5">
+      <c r="A53" s="6" t="s">
+        <v>41</v>
+      </c>
+      <c r="B53" s="6" t="s">
+        <v>13</v>
+      </c>
+      <c r="C53" s="7">
+        <v>29</v>
+      </c>
+      <c r="D53" s="7">
+        <v>43</v>
+      </c>
+      <c r="E53" s="9">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="54" spans="1:5">
+      <c r="A54" s="6" t="s">
+        <v>37</v>
+      </c>
+      <c r="B54" s="6" t="s">
+        <v>24</v>
+      </c>
+      <c r="C54" s="7">
+        <v>44.74</v>
+      </c>
+      <c r="D54" s="7">
+        <v>42.48</v>
+      </c>
+      <c r="E54" s="8">
+        <v>-2.26</v>
+      </c>
+    </row>
+    <row r="55" spans="1:5">
+      <c r="A55" s="6" t="s">
+        <v>38</v>
+      </c>
+      <c r="B55" s="6" t="s">
+        <v>24</v>
+      </c>
+      <c r="C55" s="7">
+        <v>48.17</v>
+      </c>
+      <c r="D55" s="7">
+        <v>51.74</v>
+      </c>
+      <c r="E55" s="9">
+        <v>3.57</v>
+      </c>
+    </row>
+    <row r="56" spans="1:5">
+      <c r="A56" s="6" t="s">
+        <v>39</v>
+      </c>
+      <c r="B56" s="6" t="s">
+        <v>24</v>
+      </c>
+      <c r="C56" s="7">
+        <v>40.76</v>
+      </c>
+      <c r="D56" s="7">
+        <v>39.32</v>
+      </c>
+      <c r="E56" s="8">
+        <v>-1.44</v>
+      </c>
+    </row>
+    <row r="57" spans="1:5">
+      <c r="A57" s="6" t="s">
+        <v>40</v>
+      </c>
+      <c r="B57" s="6" t="s">
+        <v>24</v>
+      </c>
+      <c r="C57" s="7">
+        <v>33.43</v>
+      </c>
+      <c r="D57" s="7">
+        <v>32.6</v>
+      </c>
+      <c r="E57" s="8">
+        <v>-0.83</v>
+      </c>
+    </row>
+    <row r="58" spans="1:5">
+      <c r="A58" s="6" t="s">
+        <v>41</v>
+      </c>
+      <c r="B58" s="6" t="s">
+        <v>24</v>
+      </c>
+      <c r="C58" s="7">
+        <v>45.69</v>
+      </c>
+      <c r="D58" s="7">
+        <v>53.69</v>
+      </c>
+      <c r="E58" s="9">
         <v>8</v>
       </c>
-      <c r="C14" s="6">
-        <v>-2.42</v>
-      </c>
-      <c r="D14" s="6">
-        <v>-2.46</v>
-      </c>
-      <c r="E14" s="7">
-        <v>-0.04</v>
-      </c>
-    </row>
-    <row r="15" spans="1:6">
-      <c r="A15" s="5" t="s">
+    </row>
+    <row r="59" spans="1:5">
+      <c r="A59" s="6" t="s">
+        <v>42</v>
+      </c>
+      <c r="B59" s="6" t="s">
+        <v>24</v>
+      </c>
+      <c r="C59" s="7">
+        <v>35.33</v>
+      </c>
+      <c r="D59" s="7">
+        <v>45.91</v>
+      </c>
+      <c r="E59" s="9">
+        <v>10.58</v>
+      </c>
+    </row>
+    <row r="60" spans="1:5">
+      <c r="A60" s="6" t="s">
+        <v>43</v>
+      </c>
+      <c r="B60" s="6" t="s">
+        <v>24</v>
+      </c>
+      <c r="C60" s="7">
+        <v>43.32</v>
+      </c>
+      <c r="D60" s="7">
+        <v>44.84</v>
+      </c>
+      <c r="E60" s="9">
+        <v>1.52</v>
+      </c>
+    </row>
+    <row r="61" spans="1:5">
+      <c r="A61" s="6" t="s">
+        <v>37</v>
+      </c>
+      <c r="B61" s="6" t="s">
+        <v>31</v>
+      </c>
+      <c r="C61" s="7">
+        <v>-43.46</v>
+      </c>
+      <c r="D61" s="7">
+        <v>32.66</v>
+      </c>
+      <c r="E61" s="9">
+        <v>76.12</v>
+      </c>
+    </row>
+    <row r="62" spans="1:5">
+      <c r="A62" s="6" t="s">
         <v>38</v>
       </c>
-      <c r="B15" s="5" t="s">
-        <v>8</v>
-      </c>
-      <c r="C15" s="6">
-        <v>-3.12</v>
-      </c>
-      <c r="D15" s="6">
-        <v>-3.64</v>
-      </c>
-      <c r="E15" s="7">
-        <v>-0.52</v>
-      </c>
-    </row>
-    <row r="16" spans="1:6">
-      <c r="A16" s="5" t="s">
+      <c r="B62" s="6" t="s">
+        <v>31</v>
+      </c>
+      <c r="C62" s="7">
+        <v>-68.7</v>
+      </c>
+      <c r="D62" s="7">
+        <v>-1.18</v>
+      </c>
+      <c r="E62" s="9">
+        <v>67.52</v>
+      </c>
+    </row>
+    <row r="63" spans="1:5">
+      <c r="A63" s="6" t="s">
         <v>39</v>
       </c>
-      <c r="B16" s="5" t="s">
-        <v>8</v>
-      </c>
-      <c r="C16" s="6">
-        <v>-5.12</v>
-      </c>
-      <c r="D16" s="6">
-        <v>-4.27</v>
-      </c>
-      <c r="E16" s="8">
-        <v>0.85</v>
-      </c>
-    </row>
-    <row r="17" spans="1:5">
-      <c r="A17" s="5" t="s">
+      <c r="B63" s="6" t="s">
+        <v>31</v>
+      </c>
+      <c r="C63" s="7">
+        <v>-66.45</v>
+      </c>
+      <c r="D63" s="7">
+        <v>-18.61</v>
+      </c>
+      <c r="E63" s="9">
+        <v>47.84</v>
+      </c>
+    </row>
+    <row r="64" spans="1:5">
+      <c r="A64" s="6" t="s">
         <v>40</v>
       </c>
-      <c r="B17" s="5" t="s">
-        <v>8</v>
-      </c>
-      <c r="C17" s="6">
-        <v>-5.22</v>
-      </c>
-      <c r="D17" s="6">
-        <v>-3.52</v>
-      </c>
-      <c r="E17" s="8">
-        <v>1.7</v>
-      </c>
-    </row>
-    <row r="18" spans="1:5">
-      <c r="A18" s="5" t="s">
+      <c r="B64" s="6" t="s">
+        <v>31</v>
+      </c>
+      <c r="C64" s="7">
+        <v>-22.51</v>
+      </c>
+      <c r="D64" s="7">
+        <v>20.65</v>
+      </c>
+      <c r="E64" s="9">
+        <v>43.16</v>
+      </c>
+    </row>
+    <row r="65" spans="1:5">
+      <c r="A65" s="6" t="s">
         <v>41</v>
       </c>
-      <c r="B18" s="5" t="s">
-        <v>8</v>
-      </c>
-      <c r="C18" s="6">
-        <v>-1.05</v>
-      </c>
-      <c r="D18" s="6">
-        <v>-0.61</v>
-      </c>
-      <c r="E18" s="8">
-        <v>0.44</v>
-      </c>
-    </row>
-    <row r="19" spans="1:5">
-      <c r="A19" s="5" t="s">
+      <c r="B65" s="6" t="s">
+        <v>31</v>
+      </c>
+      <c r="C65" s="7">
+        <v>-28.52</v>
+      </c>
+      <c r="D65" s="7">
+        <v>34.14</v>
+      </c>
+      <c r="E65" s="9">
+        <v>62.66</v>
+      </c>
+    </row>
+    <row r="66" spans="1:5">
+      <c r="A66" s="6" t="s">
         <v>42</v>
       </c>
-      <c r="B19" s="5" t="s">
-        <v>8</v>
-      </c>
-      <c r="C19" s="6">
-        <v>-4.54</v>
-      </c>
-      <c r="D19" s="6">
-        <v>-2.34</v>
-      </c>
-      <c r="E19" s="8">
-        <v>2.2</v>
-      </c>
-    </row>
-    <row r="20" spans="1:5">
-      <c r="A20" s="5" t="s">
+      <c r="B66" s="6" t="s">
+        <v>31</v>
+      </c>
+      <c r="C66" s="7">
+        <v>-1.34</v>
+      </c>
+      <c r="D66" s="7">
+        <v>65.65000000000001</v>
+      </c>
+      <c r="E66" s="9">
+        <v>66.98999999999999</v>
+      </c>
+    </row>
+    <row r="67" spans="1:5">
+      <c r="A67" s="6" t="s">
         <v>43</v>
       </c>
-      <c r="B20" s="5" t="s">
-        <v>8</v>
-      </c>
-      <c r="C20" s="6">
-        <v>-2.01</v>
-      </c>
-      <c r="D20" s="6">
-        <v>-3.93</v>
-      </c>
-      <c r="E20" s="7">
-        <v>-1.92</v>
-      </c>
-    </row>
-    <row r="21" spans="1:5">
-      <c r="A21" s="5" t="s">
-        <v>37</v>
-      </c>
-      <c r="B21" s="5" t="s">
-        <v>11</v>
-      </c>
-      <c r="C21" s="6">
-        <v>29</v>
-      </c>
-      <c r="D21" s="6">
-        <v>29.58</v>
-      </c>
-      <c r="E21" s="8">
-        <v>0.58</v>
-      </c>
-    </row>
-    <row r="22" spans="1:5">
-      <c r="A22" s="5" t="s">
-        <v>38</v>
-      </c>
-      <c r="B22" s="5" t="s">
-        <v>11</v>
-      </c>
-      <c r="C22" s="6">
-        <v>117.97</v>
-      </c>
-      <c r="D22" s="6">
-        <v>124.39</v>
-      </c>
-      <c r="E22" s="8">
-        <v>6.42</v>
-      </c>
-    </row>
-    <row r="23" spans="1:5">
-      <c r="A23" s="5" t="s">
-        <v>39</v>
-      </c>
-      <c r="B23" s="5" t="s">
-        <v>11</v>
-      </c>
-      <c r="C23" s="6">
-        <v>-44.94</v>
-      </c>
-      <c r="D23" s="6">
-        <v>-44.65</v>
-      </c>
-      <c r="E23" s="8">
-        <v>0.29</v>
-      </c>
-    </row>
-    <row r="24" spans="1:5">
-      <c r="A24" s="5" t="s">
-        <v>40</v>
-      </c>
-      <c r="B24" s="5" t="s">
-        <v>11</v>
-      </c>
-      <c r="C24" s="6">
-        <v>-9.85</v>
-      </c>
-      <c r="D24" s="6">
-        <v>-10.68</v>
-      </c>
-      <c r="E24" s="7">
-        <v>-0.83</v>
-      </c>
-    </row>
-    <row r="25" spans="1:5">
-      <c r="A25" s="5" t="s">
-        <v>41</v>
-      </c>
-      <c r="B25" s="5" t="s">
-        <v>11</v>
-      </c>
-      <c r="C25" s="6">
-        <v>-16.15</v>
-      </c>
-      <c r="D25" s="6">
-        <v>-16.25</v>
-      </c>
-      <c r="E25" s="7">
-        <v>-0.1</v>
-      </c>
-    </row>
-    <row r="26" spans="1:5">
-      <c r="A26" s="5" t="s">
-        <v>42</v>
-      </c>
-      <c r="B26" s="5" t="s">
-        <v>11</v>
-      </c>
-      <c r="C26" s="6">
-        <v>3.71</v>
-      </c>
-      <c r="D26" s="6">
-        <v>1.17</v>
-      </c>
-      <c r="E26" s="7">
-        <v>-2.54</v>
-      </c>
-    </row>
-    <row r="27" spans="1:5">
-      <c r="A27" s="5" t="s">
-        <v>43</v>
-      </c>
-      <c r="B27" s="5" t="s">
-        <v>11</v>
-      </c>
-      <c r="C27" s="6">
-        <v>-1.12</v>
-      </c>
-      <c r="D27" s="6">
-        <v>-1.86</v>
-      </c>
-      <c r="E27" s="7">
-        <v>-0.74</v>
-      </c>
-    </row>
-    <row r="28" spans="1:5">
-      <c r="A28" s="5" t="s">
-        <v>37</v>
-      </c>
-      <c r="B28" s="5" t="s">
-        <v>10</v>
-      </c>
-      <c r="C28" s="6">
-        <v>15.45</v>
-      </c>
-      <c r="D28" s="6">
-        <v>14.12</v>
-      </c>
-      <c r="E28" s="7">
-        <v>-1.33</v>
-      </c>
-    </row>
-    <row r="29" spans="1:5">
-      <c r="A29" s="5" t="s">
-        <v>38</v>
-      </c>
-      <c r="B29" s="5" t="s">
-        <v>10</v>
-      </c>
-      <c r="C29" s="6">
-        <v>-17.38</v>
-      </c>
-      <c r="D29" s="6">
-        <v>-19.02</v>
-      </c>
-      <c r="E29" s="7">
-        <v>-1.64</v>
-      </c>
-    </row>
-    <row r="30" spans="1:5">
-      <c r="A30" s="5" t="s">
-        <v>39</v>
-      </c>
-      <c r="B30" s="5" t="s">
-        <v>10</v>
-      </c>
-      <c r="C30" s="6">
-        <v>-1.6</v>
-      </c>
-      <c r="D30" s="6">
-        <v>-1.14</v>
-      </c>
-      <c r="E30" s="8">
-        <v>0.46</v>
-      </c>
-    </row>
-    <row r="31" spans="1:5">
-      <c r="A31" s="5" t="s">
-        <v>40</v>
-      </c>
-      <c r="B31" s="5" t="s">
-        <v>10</v>
-      </c>
-      <c r="C31" s="6">
-        <v>4.1</v>
-      </c>
-      <c r="D31" s="6">
-        <v>4.94</v>
-      </c>
-      <c r="E31" s="8">
-        <v>0.84</v>
-      </c>
-    </row>
-    <row r="32" spans="1:5">
-      <c r="A32" s="5" t="s">
-        <v>41</v>
-      </c>
-      <c r="B32" s="5" t="s">
-        <v>10</v>
-      </c>
-      <c r="C32" s="6">
-        <v>4.1</v>
-      </c>
-      <c r="D32" s="6">
-        <v>3.13</v>
-      </c>
-      <c r="E32" s="7">
-        <v>-0.97</v>
-      </c>
-    </row>
-    <row r="33" spans="1:5">
-      <c r="A33" s="5" t="s">
-        <v>42</v>
-      </c>
-      <c r="B33" s="5" t="s">
-        <v>10</v>
-      </c>
-      <c r="C33" s="6">
-        <v>4.99</v>
-      </c>
-      <c r="D33" s="6">
-        <v>5.86</v>
-      </c>
-      <c r="E33" s="8">
-        <v>0.87</v>
-      </c>
-    </row>
-    <row r="34" spans="1:5">
-      <c r="A34" s="5" t="s">
-        <v>43</v>
-      </c>
-      <c r="B34" s="5" t="s">
-        <v>10</v>
-      </c>
-      <c r="C34" s="6">
-        <v>0.46</v>
-      </c>
-      <c r="D34" s="6">
-        <v>-2.02</v>
-      </c>
-      <c r="E34" s="7">
-        <v>-2.48</v>
-      </c>
-    </row>
-    <row r="35" spans="1:5">
-      <c r="A35" s="5" t="s">
-        <v>37</v>
-      </c>
-      <c r="B35" s="5" t="s">
-        <v>6</v>
-      </c>
-      <c r="C35" s="6">
-        <v>-6.21</v>
-      </c>
-      <c r="D35" s="6">
-        <v>-6.97</v>
-      </c>
-      <c r="E35" s="7">
-        <v>-0.76</v>
-      </c>
-    </row>
-    <row r="36" spans="1:5">
-      <c r="A36" s="5" t="s">
-        <v>38</v>
-      </c>
-      <c r="B36" s="5" t="s">
-        <v>6</v>
-      </c>
-      <c r="C36" s="6">
-        <v>-25.69</v>
-      </c>
-      <c r="D36" s="6">
-        <v>-25.04</v>
-      </c>
-      <c r="E36" s="8">
-        <v>0.65</v>
-      </c>
-    </row>
-    <row r="37" spans="1:5">
-      <c r="A37" s="5" t="s">
-        <v>39</v>
-      </c>
-      <c r="B37" s="5" t="s">
-        <v>6</v>
-      </c>
-      <c r="C37" s="6">
-        <v>-46.67</v>
-      </c>
-      <c r="D37" s="6">
-        <v>-46.22</v>
-      </c>
-      <c r="E37" s="8">
-        <v>0.45</v>
-      </c>
-    </row>
-    <row r="38" spans="1:5">
-      <c r="A38" s="5" t="s">
-        <v>40</v>
-      </c>
-      <c r="B38" s="5" t="s">
-        <v>6</v>
-      </c>
-      <c r="C38" s="6">
-        <v>-15.6</v>
-      </c>
-      <c r="D38" s="6">
-        <v>-14.58</v>
-      </c>
-      <c r="E38" s="8">
-        <v>1.02</v>
-      </c>
-    </row>
-    <row r="39" spans="1:5">
-      <c r="A39" s="5" t="s">
-        <v>41</v>
-      </c>
-      <c r="B39" s="5" t="s">
-        <v>6</v>
-      </c>
-      <c r="C39" s="6">
-        <v>-19.61</v>
-      </c>
-      <c r="D39" s="6">
-        <v>-19.02</v>
-      </c>
-      <c r="E39" s="8">
-        <v>0.59</v>
-      </c>
-    </row>
-    <row r="40" spans="1:5">
-      <c r="A40" s="5" t="s">
-        <v>42</v>
-      </c>
-      <c r="B40" s="5" t="s">
-        <v>6</v>
-      </c>
-      <c r="C40" s="6">
-        <v>-13.17</v>
-      </c>
-      <c r="D40" s="6">
-        <v>-12.41</v>
-      </c>
-      <c r="E40" s="8">
-        <v>0.76</v>
-      </c>
-    </row>
-    <row r="41" spans="1:5">
-      <c r="A41" s="5" t="s">
-        <v>43</v>
-      </c>
-      <c r="B41" s="5" t="s">
-        <v>6</v>
-      </c>
-      <c r="C41" s="6">
-        <v>-9.44</v>
-      </c>
-      <c r="D41" s="6">
-        <v>-9.9</v>
-      </c>
-      <c r="E41" s="7">
-        <v>-0.46</v>
-      </c>
-    </row>
-    <row r="42" spans="1:5">
-      <c r="A42" s="5" t="s">
-        <v>37</v>
-      </c>
-      <c r="B42" s="5" t="s">
-        <v>2</v>
-      </c>
-      <c r="C42" s="6">
-        <v>11593</v>
-      </c>
-      <c r="D42" s="6">
-        <v>11500</v>
-      </c>
-      <c r="E42" s="7">
-        <v>-93</v>
-      </c>
-    </row>
-    <row r="43" spans="1:5">
-      <c r="A43" s="5" t="s">
-        <v>38</v>
-      </c>
-      <c r="B43" s="5" t="s">
-        <v>2</v>
-      </c>
-      <c r="C43" s="6">
-        <v>498.05</v>
-      </c>
-      <c r="D43" s="6">
-        <v>502.45</v>
-      </c>
-      <c r="E43" s="8">
-        <v>4.4</v>
-      </c>
-    </row>
-    <row r="44" spans="1:5">
-      <c r="A44" s="5" t="s">
-        <v>39</v>
-      </c>
-      <c r="B44" s="5" t="s">
-        <v>2</v>
-      </c>
-      <c r="C44" s="6">
-        <v>322.55</v>
-      </c>
-      <c r="D44" s="6">
-        <v>325.3</v>
-      </c>
-      <c r="E44" s="8">
-        <v>2.75</v>
-      </c>
-    </row>
-    <row r="45" spans="1:5">
-      <c r="A45" s="5" t="s">
-        <v>40</v>
-      </c>
-      <c r="B45" s="5" t="s">
-        <v>2</v>
-      </c>
-      <c r="C45" s="6">
-        <v>1837</v>
-      </c>
-      <c r="D45" s="6">
-        <v>1859.2</v>
-      </c>
-      <c r="E45" s="8">
-        <v>22.2</v>
-      </c>
-    </row>
-    <row r="46" spans="1:5">
-      <c r="A46" s="5" t="s">
-        <v>41</v>
-      </c>
-      <c r="B46" s="5" t="s">
-        <v>2</v>
-      </c>
-      <c r="C46" s="6">
-        <v>10930</v>
-      </c>
-      <c r="D46" s="6">
-        <v>11010</v>
-      </c>
-      <c r="E46" s="8">
-        <v>80</v>
-      </c>
-    </row>
-    <row r="47" spans="1:5">
-      <c r="A47" s="5" t="s">
-        <v>42</v>
-      </c>
-      <c r="B47" s="5" t="s">
-        <v>2</v>
-      </c>
-      <c r="C47" s="6">
-        <v>1006.2</v>
-      </c>
-      <c r="D47" s="6">
-        <v>1015</v>
-      </c>
-      <c r="E47" s="8">
-        <v>8.800000000000001</v>
-      </c>
-    </row>
-    <row r="48" spans="1:5">
-      <c r="A48" s="5" t="s">
-        <v>43</v>
-      </c>
-      <c r="B48" s="5" t="s">
-        <v>2</v>
-      </c>
-      <c r="C48" s="6">
-        <v>134.89</v>
-      </c>
-      <c r="D48" s="6">
-        <v>134.2</v>
-      </c>
-      <c r="E48" s="7">
-        <v>-0.6899999999999999</v>
-      </c>
-    </row>
-    <row r="49" spans="1:5">
-      <c r="A49" s="5" t="s">
-        <v>37</v>
-      </c>
-      <c r="B49" s="5" t="s">
-        <v>24</v>
-      </c>
-      <c r="C49" s="6">
-        <v>47.27</v>
-      </c>
-      <c r="D49" s="6">
-        <v>44.74</v>
-      </c>
-      <c r="E49" s="7">
-        <v>-2.53</v>
-      </c>
-    </row>
-    <row r="50" spans="1:5">
-      <c r="A50" s="5" t="s">
-        <v>38</v>
-      </c>
-      <c r="B50" s="5" t="s">
-        <v>24</v>
-      </c>
-      <c r="C50" s="6">
-        <v>46.5</v>
-      </c>
-      <c r="D50" s="6">
-        <v>48.17</v>
-      </c>
-      <c r="E50" s="8">
-        <v>1.67</v>
-      </c>
-    </row>
-    <row r="51" spans="1:5">
-      <c r="A51" s="5" t="s">
-        <v>39</v>
-      </c>
-      <c r="B51" s="5" t="s">
-        <v>24</v>
-      </c>
-      <c r="C51" s="6">
-        <v>38.2</v>
-      </c>
-      <c r="D51" s="6">
-        <v>40.76</v>
-      </c>
-      <c r="E51" s="8">
-        <v>2.56</v>
-      </c>
-    </row>
-    <row r="52" spans="1:5">
-      <c r="A52" s="5" t="s">
-        <v>40</v>
-      </c>
-      <c r="B52" s="5" t="s">
-        <v>24</v>
-      </c>
-      <c r="C52" s="6">
-        <v>27.76</v>
-      </c>
-      <c r="D52" s="6">
-        <v>33.43</v>
-      </c>
-      <c r="E52" s="8">
-        <v>5.67</v>
-      </c>
-    </row>
-    <row r="53" spans="1:5">
-      <c r="A53" s="5" t="s">
-        <v>41</v>
-      </c>
-      <c r="B53" s="5" t="s">
-        <v>24</v>
-      </c>
-      <c r="C53" s="6">
-        <v>43.01</v>
-      </c>
-      <c r="D53" s="6">
-        <v>45.69</v>
-      </c>
-      <c r="E53" s="8">
-        <v>2.68</v>
-      </c>
-    </row>
-    <row r="54" spans="1:5">
-      <c r="A54" s="5" t="s">
-        <v>42</v>
-      </c>
-      <c r="B54" s="5" t="s">
-        <v>24</v>
-      </c>
-      <c r="C54" s="6">
-        <v>30.97</v>
-      </c>
-      <c r="D54" s="6">
-        <v>35.33</v>
-      </c>
-      <c r="E54" s="8">
-        <v>4.36</v>
-      </c>
-    </row>
-    <row r="55" spans="1:5">
-      <c r="A55" s="5" t="s">
-        <v>43</v>
-      </c>
-      <c r="B55" s="5" t="s">
-        <v>24</v>
-      </c>
-      <c r="C55" s="6">
-        <v>44.68</v>
-      </c>
-      <c r="D55" s="6">
-        <v>43.32</v>
-      </c>
-      <c r="E55" s="7">
-        <v>-1.36</v>
-      </c>
-    </row>
-    <row r="56" spans="1:5">
-      <c r="A56" s="5" t="s">
-        <v>37</v>
-      </c>
-      <c r="B56" s="5" t="s">
+      <c r="B67" s="6" t="s">
         <v>31</v>
       </c>
-      <c r="C56" s="6">
-        <v>37.09</v>
-      </c>
-      <c r="D56" s="6">
-        <v>-43.46</v>
-      </c>
-      <c r="E56" s="7">
-        <v>-80.55</v>
-      </c>
-    </row>
-    <row r="57" spans="1:5">
-      <c r="A57" s="5" t="s">
-        <v>38</v>
-      </c>
-      <c r="B57" s="5" t="s">
-        <v>31</v>
-      </c>
-      <c r="C57" s="6">
-        <v>-52.13</v>
-      </c>
-      <c r="D57" s="6">
-        <v>-68.7</v>
-      </c>
-      <c r="E57" s="7">
-        <v>-16.57</v>
-      </c>
-    </row>
-    <row r="58" spans="1:5">
-      <c r="A58" s="5" t="s">
-        <v>39</v>
-      </c>
-      <c r="B58" s="5" t="s">
-        <v>31</v>
-      </c>
-      <c r="C58" s="6">
-        <v>-40.98</v>
-      </c>
-      <c r="D58" s="6">
-        <v>-66.45</v>
-      </c>
-      <c r="E58" s="7">
-        <v>-25.47</v>
-      </c>
-    </row>
-    <row r="59" spans="1:5">
-      <c r="A59" s="5" t="s">
-        <v>40</v>
-      </c>
-      <c r="B59" s="5" t="s">
-        <v>31</v>
-      </c>
-      <c r="C59" s="6">
-        <v>0.01</v>
-      </c>
-      <c r="D59" s="6">
-        <v>-22.51</v>
-      </c>
-      <c r="E59" s="7">
-        <v>-22.52</v>
-      </c>
-    </row>
-    <row r="60" spans="1:5">
-      <c r="A60" s="5" t="s">
-        <v>41</v>
-      </c>
-      <c r="B60" s="5" t="s">
-        <v>31</v>
-      </c>
-      <c r="C60" s="6">
-        <v>-45.91</v>
-      </c>
-      <c r="D60" s="6">
-        <v>-28.52</v>
-      </c>
-      <c r="E60" s="8">
-        <v>17.39</v>
-      </c>
-    </row>
-    <row r="61" spans="1:5">
-      <c r="A61" s="5" t="s">
-        <v>42</v>
-      </c>
-      <c r="B61" s="5" t="s">
-        <v>31</v>
-      </c>
-      <c r="C61" s="6">
-        <v>-12.55</v>
-      </c>
-      <c r="D61" s="6">
-        <v>-1.34</v>
-      </c>
-      <c r="E61" s="8">
-        <v>11.21</v>
-      </c>
-    </row>
-    <row r="62" spans="1:5">
-      <c r="A62" s="5" t="s">
-        <v>43</v>
-      </c>
-      <c r="B62" s="5" t="s">
-        <v>31</v>
-      </c>
-      <c r="C62" s="6">
-        <v>62.21</v>
-      </c>
-      <c r="D62" s="6">
+      <c r="C67" s="7">
         <v>-70.84</v>
       </c>
-      <c r="E62" s="7">
-        <v>-133.05</v>
+      <c r="D67" s="7">
+        <v>-42.72</v>
+      </c>
+      <c r="E67" s="9">
+        <v>28.12</v>
       </c>
     </row>
   </sheetData>
   <mergeCells count="2">
     <mergeCell ref="A1:F1"/>
-    <mergeCell ref="A5:E5"/>
+    <mergeCell ref="A8:E8"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -2904,61 +3017,61 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:9" ht="28" customHeight="1">
-      <c r="A1" s="9" t="s">
+      <c r="A1" s="10" t="s">
         <v>1</v>
       </c>
-      <c r="B1" s="9" t="s">
-        <v>65</v>
-      </c>
-      <c r="C1" s="9" t="s">
-        <v>66</v>
-      </c>
-      <c r="D1" s="9" t="s">
-        <v>67</v>
-      </c>
-      <c r="E1" s="9" t="s">
-        <v>68</v>
-      </c>
-      <c r="F1" s="9" t="s">
-        <v>69</v>
-      </c>
-      <c r="G1" s="9" t="s">
+      <c r="B1" s="10" t="s">
+        <v>71</v>
+      </c>
+      <c r="C1" s="10" t="s">
+        <v>72</v>
+      </c>
+      <c r="D1" s="10" t="s">
+        <v>73</v>
+      </c>
+      <c r="E1" s="10" t="s">
+        <v>74</v>
+      </c>
+      <c r="F1" s="10" t="s">
+        <v>75</v>
+      </c>
+      <c r="G1" s="10" t="s">
+        <v>76</v>
+      </c>
+      <c r="H1" s="10" t="s">
+        <v>77</v>
+      </c>
+      <c r="I1" s="10" t="s">
+        <v>78</v>
+      </c>
+    </row>
+    <row r="2" spans="1:9">
+      <c r="A2" s="11" t="s">
+        <v>44</v>
+      </c>
+      <c r="B2" s="12">
+        <v>60.8</v>
+      </c>
+      <c r="C2" s="13">
+        <v>7</v>
+      </c>
+      <c r="D2" s="12">
+        <v>44.4</v>
+      </c>
+      <c r="E2" s="12">
         <v>70</v>
       </c>
-      <c r="H1" s="9" t="s">
-        <v>71</v>
-      </c>
-      <c r="I1" s="9" t="s">
-        <v>72</v>
-      </c>
-    </row>
-    <row r="2" spans="1:9">
-      <c r="A2" s="10" t="s">
-        <v>44</v>
-      </c>
-      <c r="B2" s="11">
-        <v>60.8</v>
-      </c>
-      <c r="C2" s="12">
-        <v>7</v>
-      </c>
-      <c r="D2" s="11">
-        <v>41.6</v>
-      </c>
-      <c r="E2" s="11">
-        <v>70</v>
-      </c>
-      <c r="F2" s="11">
-        <v>-3.4</v>
-      </c>
-      <c r="G2" s="11">
-        <v>0.8</v>
-      </c>
-      <c r="H2" s="11">
+      <c r="F2" s="12">
+        <v>-2.9</v>
+      </c>
+      <c r="G2" s="12">
+        <v>1.8</v>
+      </c>
+      <c r="H2" s="12">
         <v>57</v>
       </c>
-      <c r="I2" s="11">
-        <v>40</v>
+      <c r="I2" s="12">
+        <v>30</v>
       </c>
     </row>
   </sheetData>
@@ -3059,49 +3172,49 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:7">
-      <c r="A1" s="13" t="s">
+      <c r="A1" s="14" t="s">
         <v>37</v>
       </c>
-      <c r="B1" s="13" t="s">
+      <c r="B1" s="14" t="s">
         <v>41</v>
       </c>
-      <c r="C1" s="13" t="s">
+      <c r="C1" s="14" t="s">
         <v>38</v>
       </c>
-      <c r="D1" s="13" t="s">
+      <c r="D1" s="14" t="s">
         <v>42</v>
       </c>
-      <c r="E1" s="13" t="s">
+      <c r="E1" s="14" t="s">
         <v>40</v>
       </c>
-      <c r="F1" s="13" t="s">
+      <c r="F1" s="14" t="s">
         <v>43</v>
       </c>
-      <c r="G1" s="13" t="s">
+      <c r="G1" s="14" t="s">
         <v>39</v>
       </c>
     </row>
     <row r="2" spans="1:7">
-      <c r="A2" s="14">
-        <v>0.2753</v>
-      </c>
-      <c r="B2" s="14">
-        <v>0.2189</v>
-      </c>
-      <c r="C2" s="14">
-        <v>0.1611</v>
-      </c>
-      <c r="D2" s="14">
-        <v>0.06849999999999999</v>
-      </c>
-      <c r="E2" s="14">
-        <v>0.0204</v>
-      </c>
-      <c r="F2" s="14">
-        <v>-0.0018</v>
-      </c>
-      <c r="G2" s="14">
-        <v>-0.2514</v>
+      <c r="A2" s="15">
+        <v>0.2768</v>
+      </c>
+      <c r="B2" s="15">
+        <v>0.2205</v>
+      </c>
+      <c r="C2" s="15">
+        <v>0.169</v>
+      </c>
+      <c r="D2" s="15">
+        <v>0.07339999999999999</v>
+      </c>
+      <c r="E2" s="15">
+        <v>0.0175</v>
+      </c>
+      <c r="F2" s="15">
+        <v>0.0064</v>
+      </c>
+      <c r="G2" s="15">
+        <v>-0.2555</v>
       </c>
     </row>
   </sheetData>

--- a/BAJAJ_GROUP_Technical_Metrics.xlsx
+++ b/BAJAJ_GROUP_Technical_Metrics.xlsx
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="286" uniqueCount="79">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="253" uniqueCount="64">
   <si>
     <t>Symbol</t>
   </si>
@@ -172,52 +172,7 @@
     <t>▶  SIGNAL EVENTS (vs Previous Run)</t>
   </si>
   <si>
-    <t>Signal</t>
-  </si>
-  <si>
-    <t>Change</t>
-  </si>
-  <si>
-    <t>Direction</t>
-  </si>
-  <si>
-    <t>Prev Value</t>
-  </si>
-  <si>
-    <t>Curr Value</t>
-  </si>
-  <si>
-    <t>RSI Momentum</t>
-  </si>
-  <si>
-    <t>48.2 → 51.7</t>
-  </si>
-  <si>
-    <t>🟢 BULLISH</t>
-  </si>
-  <si>
-    <t>48.2</t>
-  </si>
-  <si>
-    <t>51.7</t>
-  </si>
-  <si>
-    <t>45.7 → 53.7</t>
-  </si>
-  <si>
-    <t>45.7</t>
-  </si>
-  <si>
-    <t>53.7</t>
-  </si>
-  <si>
-    <t>Yes → No</t>
-  </si>
-  <si>
-    <t>🔴 BEARISH</t>
-  </si>
-  <si>
-    <t>20 DMA &gt; 50 DMA</t>
+    <t>No signal events detected since last run.</t>
   </si>
   <si>
     <t>▶  NUMERIC METRIC CHANGES (vs Previous Run)</t>
@@ -303,14 +258,14 @@
     </font>
     <font>
       <sz val="11"/>
-      <color rgb="FF006100"/>
+      <color rgb="FF9C0006"/>
       <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
     </font>
     <font>
       <sz val="11"/>
-      <color rgb="FF9C0006"/>
+      <color rgb="FF006100"/>
       <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
@@ -343,13 +298,13 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFC6EFCE"/>
+        <fgColor rgb="FFFFC7CE"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFFFC7CE"/>
+        <fgColor rgb="FFC6EFCE"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -419,19 +374,17 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="16">
+  <cellXfs count="14">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="2" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="3" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="5" fillId="6" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1"/>
+    <xf numFmtId="165" fontId="4" fillId="5" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="165" fontId="5" fillId="6" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="165" fontId="4" fillId="5" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="3" fillId="7" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
@@ -802,8 +755,8 @@
     <col min="13" max="13" width="10.7109375" customWidth="1"/>
     <col min="14" max="14" width="11.7109375" customWidth="1"/>
     <col min="15" max="15" width="10.7109375" customWidth="1"/>
-    <col min="16" max="17" width="9.7109375" customWidth="1"/>
-    <col min="18" max="19" width="10.7109375" customWidth="1"/>
+    <col min="16" max="16" width="9.7109375" customWidth="1"/>
+    <col min="17" max="19" width="10.7109375" customWidth="1"/>
     <col min="20" max="20" width="22.7109375" customWidth="1"/>
     <col min="21" max="21" width="9.7109375" customWidth="1"/>
     <col min="22" max="22" width="10.7109375" customWidth="1"/>
@@ -943,10 +896,10 @@
         <v>44</v>
       </c>
       <c r="C2">
-        <v>11414</v>
+        <v>11460</v>
       </c>
       <c r="D2">
-        <v>-0.75</v>
+        <v>0.4</v>
       </c>
       <c r="E2">
         <v>12361</v>
@@ -955,46 +908,46 @@
         <v>8506.780000000001</v>
       </c>
       <c r="G2">
-        <v>-7.66</v>
+        <v>-7.29</v>
       </c>
       <c r="H2">
-        <v>34.18</v>
+        <v>34.72</v>
       </c>
       <c r="I2">
-        <v>-3.01</v>
+        <v>-1.87</v>
       </c>
       <c r="J2">
-        <v>-1.98</v>
+        <v>-2.82</v>
       </c>
       <c r="K2">
-        <v>13.39</v>
+        <v>12.45</v>
       </c>
       <c r="L2">
-        <v>28.25</v>
+        <v>28.09</v>
       </c>
       <c r="M2">
-        <v>27.68</v>
+        <v>28.07</v>
       </c>
       <c r="N2">
         <v>85</v>
       </c>
       <c r="O2">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="P2">
-        <v>11521.8</v>
+        <v>11478.2</v>
       </c>
       <c r="Q2">
-        <v>11804.4</v>
+        <v>11792.4</v>
       </c>
       <c r="R2">
-        <v>11456.25</v>
+        <v>11482.33</v>
       </c>
       <c r="S2">
-        <v>10043.65</v>
+        <v>10056.15</v>
       </c>
       <c r="T2">
-        <v>13.64</v>
+        <v>13.96</v>
       </c>
       <c r="U2" t="s">
         <v>45</v>
@@ -1009,43 +962,43 @@
         <v>3</v>
       </c>
       <c r="Y2">
-        <v>42.48</v>
+        <v>44.1</v>
       </c>
       <c r="Z2">
-        <v>3.5</v>
+        <v>-12.92</v>
       </c>
       <c r="AA2">
-        <v>94.13</v>
+        <v>72.72</v>
       </c>
       <c r="AB2">
-        <v>-90.62</v>
+        <v>-85.64</v>
       </c>
       <c r="AC2">
-        <v>9.92</v>
+        <v>6.57</v>
       </c>
       <c r="AD2">
-        <v>8.31</v>
+        <v>8.529999999999999</v>
       </c>
       <c r="AE2">
-        <v>210.44</v>
+        <v>203.91</v>
       </c>
       <c r="AF2">
-        <v>32.66</v>
+        <v>-59.04</v>
       </c>
       <c r="AG2">
-        <v>12276.07</v>
+        <v>12286.91</v>
       </c>
       <c r="AH2">
-        <v>11332.73</v>
+        <v>11297.89</v>
       </c>
       <c r="AI2">
-        <v>12104.33</v>
+        <v>12103.24</v>
       </c>
       <c r="AJ2" t="s">
         <v>47</v>
       </c>
       <c r="AK2">
-        <v>32.65</v>
+        <v>33.9</v>
       </c>
     </row>
     <row r="3" spans="1:37">
@@ -1056,58 +1009,58 @@
         <v>44</v>
       </c>
       <c r="C3">
-        <v>512.15</v>
+        <v>515.3</v>
       </c>
       <c r="D3">
-        <v>1.93</v>
+        <v>0.62</v>
       </c>
       <c r="E3">
         <v>670.25</v>
       </c>
       <c r="F3">
-        <v>228.14</v>
+        <v>232.89</v>
       </c>
       <c r="G3">
-        <v>-23.59</v>
+        <v>-23.12</v>
       </c>
       <c r="H3">
-        <v>124.49</v>
+        <v>121.26</v>
       </c>
       <c r="I3">
-        <v>-2.35</v>
+        <v>-1</v>
       </c>
       <c r="J3">
-        <v>2.29</v>
+        <v>5.82</v>
       </c>
       <c r="K3">
-        <v>-18.09</v>
+        <v>-16.85</v>
       </c>
       <c r="L3">
-        <v>122.71</v>
+        <v>125.87</v>
       </c>
       <c r="M3">
-        <v>16.9</v>
+        <v>16.91</v>
       </c>
       <c r="N3">
         <v>99</v>
       </c>
       <c r="O3">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="P3">
-        <v>507.39</v>
+        <v>506.35</v>
       </c>
       <c r="Q3">
-        <v>493.41</v>
+        <v>495.26</v>
       </c>
       <c r="R3">
-        <v>521.66</v>
+        <v>518.5700000000001</v>
       </c>
       <c r="S3">
-        <v>441.43</v>
+        <v>442.68</v>
       </c>
       <c r="T3">
-        <v>16.02</v>
+        <v>16.4</v>
       </c>
       <c r="U3" t="s">
         <v>46</v>
@@ -1122,34 +1075,34 @@
         <v>2</v>
       </c>
       <c r="Y3">
-        <v>51.74</v>
+        <v>52.88</v>
       </c>
       <c r="Z3">
-        <v>-0.99</v>
+        <v>-0.19</v>
       </c>
       <c r="AA3">
-        <v>-4.28</v>
+        <v>-3.46</v>
       </c>
       <c r="AB3">
-        <v>3.29</v>
+        <v>3.27</v>
       </c>
       <c r="AC3">
-        <v>60.06</v>
+        <v>65.44</v>
       </c>
       <c r="AD3">
-        <v>64.11</v>
+        <v>61.59</v>
       </c>
       <c r="AE3">
-        <v>21.22</v>
+        <v>20.81</v>
       </c>
       <c r="AF3">
-        <v>-1.18</v>
+        <v>-36.72</v>
       </c>
       <c r="AG3">
-        <v>543.39</v>
+        <v>545.63</v>
       </c>
       <c r="AH3">
-        <v>443.42</v>
+        <v>444.88</v>
       </c>
       <c r="AI3">
         <v>460.99</v>
@@ -1158,7 +1111,7 @@
         <v>48</v>
       </c>
       <c r="AK3">
-        <v>25.04</v>
+        <v>25.46</v>
       </c>
     </row>
     <row r="4" spans="1:37">
@@ -1169,10 +1122,10 @@
         <v>44</v>
       </c>
       <c r="C4">
-        <v>323.05</v>
+        <v>326</v>
       </c>
       <c r="D4">
-        <v>-0.6899999999999999</v>
+        <v>0.91</v>
       </c>
       <c r="E4">
         <v>604.85</v>
@@ -1181,25 +1134,25 @@
         <v>303.75</v>
       </c>
       <c r="G4">
-        <v>-46.59</v>
+        <v>-46.1</v>
       </c>
       <c r="H4">
-        <v>6.35</v>
+        <v>7.33</v>
       </c>
       <c r="I4">
-        <v>-4.35</v>
+        <v>-2.77</v>
       </c>
       <c r="J4">
-        <v>-8.630000000000001</v>
+        <v>-8</v>
       </c>
       <c r="K4">
-        <v>-0.8</v>
+        <v>-1.29</v>
       </c>
       <c r="L4">
-        <v>-45.09</v>
+        <v>-44.97</v>
       </c>
       <c r="M4">
-        <v>-25.55</v>
+        <v>-25.39</v>
       </c>
       <c r="N4">
         <v>15</v>
@@ -1208,19 +1161,19 @@
         <v>17</v>
       </c>
       <c r="P4">
-        <v>326.92</v>
+        <v>325.06</v>
       </c>
       <c r="Q4">
-        <v>333.63</v>
+        <v>332.35</v>
       </c>
       <c r="R4">
-        <v>339.79</v>
+        <v>339.69</v>
       </c>
       <c r="S4">
-        <v>375.31</v>
+        <v>374.52</v>
       </c>
       <c r="T4">
-        <v>-13.93</v>
+        <v>-12.96</v>
       </c>
       <c r="U4" t="s">
         <v>46</v>
@@ -1235,34 +1188,34 @@
         <v>0</v>
       </c>
       <c r="Y4">
-        <v>39.32</v>
+        <v>42.2</v>
       </c>
       <c r="Z4">
-        <v>-4.51</v>
+        <v>-4.58</v>
       </c>
       <c r="AA4">
-        <v>-3.2</v>
+        <v>-3.47</v>
       </c>
       <c r="AB4">
-        <v>-1.31</v>
+        <v>-1.1</v>
       </c>
       <c r="AC4">
-        <v>18.51</v>
+        <v>27.58</v>
       </c>
       <c r="AD4">
-        <v>26.55</v>
+        <v>23.38</v>
       </c>
       <c r="AE4">
-        <v>10.21</v>
+        <v>9.880000000000001</v>
       </c>
       <c r="AF4">
-        <v>-18.61</v>
+        <v>-31.78</v>
       </c>
       <c r="AG4">
-        <v>349.81</v>
+        <v>346.45</v>
       </c>
       <c r="AH4">
-        <v>317.45</v>
+        <v>318.25</v>
       </c>
       <c r="AI4">
         <v>354.2</v>
@@ -1271,7 +1224,7 @@
         <v>47</v>
       </c>
       <c r="AK4">
-        <v>19.14</v>
+        <v>17.47</v>
       </c>
     </row>
     <row r="5" spans="1:37">
@@ -1282,10 +1235,10 @@
         <v>44</v>
       </c>
       <c r="C5">
-        <v>1852.5</v>
+        <v>1849.8</v>
       </c>
       <c r="D5">
-        <v>-0.36</v>
+        <v>-0.15</v>
       </c>
       <c r="E5">
         <v>2176.6</v>
@@ -1294,25 +1247,25 @@
         <v>1631.8</v>
       </c>
       <c r="G5">
-        <v>-14.89</v>
+        <v>-15.01</v>
       </c>
       <c r="H5">
-        <v>13.52</v>
+        <v>13.36</v>
       </c>
       <c r="I5">
-        <v>-4.53</v>
+        <v>-3.33</v>
       </c>
       <c r="J5">
-        <v>-7.93</v>
+        <v>-8.24</v>
       </c>
       <c r="K5">
-        <v>4.7</v>
+        <v>3.79</v>
       </c>
       <c r="L5">
-        <v>-10.94</v>
+        <v>-11.08</v>
       </c>
       <c r="M5">
-        <v>1.75</v>
+        <v>1.06</v>
       </c>
       <c r="N5">
         <v>29</v>
@@ -1321,19 +1274,19 @@
         <v>52</v>
       </c>
       <c r="P5">
-        <v>1863.54</v>
+        <v>1850.8</v>
       </c>
       <c r="Q5">
-        <v>1953.41</v>
+        <v>1944.27</v>
       </c>
       <c r="R5">
-        <v>1958.91</v>
+        <v>1957.58</v>
       </c>
       <c r="S5">
-        <v>1897.63</v>
+        <v>1896.55</v>
       </c>
       <c r="T5">
-        <v>-2.38</v>
+        <v>-2.47</v>
       </c>
       <c r="U5" t="s">
         <v>46</v>
@@ -1348,34 +1301,34 @@
         <v>1</v>
       </c>
       <c r="Y5">
-        <v>32.6</v>
+        <v>32.25</v>
       </c>
       <c r="Z5">
-        <v>-32.28</v>
+        <v>-34.41</v>
       </c>
       <c r="AA5">
-        <v>-15.71</v>
+        <v>-19.45</v>
       </c>
       <c r="AB5">
-        <v>-16.57</v>
+        <v>-14.96</v>
       </c>
       <c r="AC5">
-        <v>11.75</v>
+        <v>18.27</v>
       </c>
       <c r="AD5">
-        <v>6.03</v>
+        <v>12.12</v>
       </c>
       <c r="AE5">
-        <v>36.55</v>
+        <v>35</v>
       </c>
       <c r="AF5">
-        <v>20.65</v>
+        <v>-53.99</v>
       </c>
       <c r="AG5">
-        <v>2077.51</v>
+        <v>2070.74</v>
       </c>
       <c r="AH5">
-        <v>1829.31</v>
+        <v>1817.81</v>
       </c>
       <c r="AI5">
         <v>1961</v>
@@ -1384,7 +1337,7 @@
         <v>47</v>
       </c>
       <c r="AK5">
-        <v>62.6</v>
+        <v>63.69</v>
       </c>
     </row>
     <row r="6" spans="1:37">
@@ -1395,10 +1348,10 @@
         <v>44</v>
       </c>
       <c r="C6">
-        <v>11282</v>
+        <v>11409</v>
       </c>
       <c r="D6">
-        <v>2.47</v>
+        <v>1.13</v>
       </c>
       <c r="E6">
         <v>13595.75</v>
@@ -1407,25 +1360,25 @@
         <v>8746</v>
       </c>
       <c r="G6">
-        <v>-17.02</v>
+        <v>-16.08</v>
       </c>
       <c r="H6">
-        <v>29</v>
+        <v>30.45</v>
       </c>
       <c r="I6">
-        <v>2.64</v>
+        <v>2.47</v>
       </c>
       <c r="J6">
-        <v>-0.86</v>
+        <v>0.36</v>
       </c>
       <c r="K6">
-        <v>5.67</v>
+        <v>4.72</v>
       </c>
       <c r="L6">
-        <v>-14.09</v>
+        <v>-15.23</v>
       </c>
       <c r="M6">
-        <v>22.05</v>
+        <v>21.24</v>
       </c>
       <c r="N6">
         <v>43</v>
@@ -1434,19 +1387,19 @@
         <v>53</v>
       </c>
       <c r="P6">
-        <v>11091.2</v>
+        <v>11146.2</v>
       </c>
       <c r="Q6">
-        <v>11195.9</v>
+        <v>11200.35</v>
       </c>
       <c r="R6">
-        <v>11096.32</v>
+        <v>11111.42</v>
       </c>
       <c r="S6">
-        <v>10680.08</v>
+        <v>10681.88</v>
       </c>
       <c r="T6">
-        <v>5.64</v>
+        <v>6.81</v>
       </c>
       <c r="U6" t="s">
         <v>45</v>
@@ -1461,34 +1414,34 @@
         <v>3</v>
       </c>
       <c r="Y6">
-        <v>53.69</v>
+        <v>56.88</v>
       </c>
       <c r="Z6">
-        <v>-31</v>
+        <v>-6.11</v>
       </c>
       <c r="AA6">
-        <v>-13.47</v>
+        <v>-12</v>
       </c>
       <c r="AB6">
-        <v>-17.52</v>
+        <v>5.89</v>
       </c>
       <c r="AC6">
-        <v>25.43</v>
+        <v>58.41</v>
       </c>
       <c r="AD6">
-        <v>19.89</v>
+        <v>32.76</v>
       </c>
       <c r="AE6">
-        <v>226.95</v>
+        <v>225.53</v>
       </c>
       <c r="AF6">
-        <v>34.14</v>
+        <v>25.09</v>
       </c>
       <c r="AG6">
-        <v>11578.89</v>
+        <v>11591.4</v>
       </c>
       <c r="AH6">
-        <v>10812.91</v>
+        <v>10809.3</v>
       </c>
       <c r="AI6">
         <v>10787.84</v>
@@ -1497,7 +1450,7 @@
         <v>48</v>
       </c>
       <c r="AK6">
-        <v>19.95</v>
+        <v>20.99</v>
       </c>
     </row>
     <row r="7" spans="1:37">
@@ -1508,10 +1461,10 @@
         <v>44</v>
       </c>
       <c r="C7">
-        <v>1040.3</v>
+        <v>1021.3</v>
       </c>
       <c r="D7">
-        <v>2.49</v>
+        <v>-1.83</v>
       </c>
       <c r="E7">
         <v>1158.8</v>
@@ -1520,46 +1473,46 @@
         <v>801.55</v>
       </c>
       <c r="G7">
-        <v>-10.23</v>
+        <v>-11.87</v>
       </c>
       <c r="H7">
-        <v>29.79</v>
+        <v>27.42</v>
       </c>
       <c r="I7">
-        <v>-0.31</v>
+        <v>-1.28</v>
       </c>
       <c r="J7">
-        <v>-3.69</v>
+        <v>-6.73</v>
       </c>
       <c r="K7">
-        <v>8.16</v>
+        <v>5.47</v>
       </c>
       <c r="L7">
-        <v>3.02</v>
+        <v>1.8</v>
       </c>
       <c r="M7">
-        <v>7.34</v>
+        <v>5.9</v>
       </c>
       <c r="N7">
         <v>71</v>
       </c>
       <c r="O7">
-        <v>66</v>
+        <v>63</v>
       </c>
       <c r="P7">
-        <v>1021.04</v>
+        <v>1018.4</v>
       </c>
       <c r="Q7">
-        <v>1054.29</v>
+        <v>1050.6</v>
       </c>
       <c r="R7">
-        <v>1067.05</v>
+        <v>1067.06</v>
       </c>
       <c r="S7">
-        <v>977.73</v>
+        <v>977.71</v>
       </c>
       <c r="T7">
-        <v>6.4</v>
+        <v>4.46</v>
       </c>
       <c r="U7" t="s">
         <v>46</v>
@@ -1574,34 +1527,34 @@
         <v>2</v>
       </c>
       <c r="Y7">
-        <v>45.91</v>
+        <v>40.55</v>
       </c>
       <c r="Z7">
-        <v>-13.78</v>
+        <v>-14.09</v>
       </c>
       <c r="AA7">
-        <v>-9.48</v>
+        <v>-10.4</v>
       </c>
       <c r="AB7">
-        <v>-4.3</v>
+        <v>-3.69</v>
       </c>
       <c r="AC7">
-        <v>40.86</v>
+        <v>62.23</v>
       </c>
       <c r="AD7">
-        <v>16.13</v>
+        <v>36.87</v>
       </c>
       <c r="AE7">
-        <v>21.32</v>
+        <v>21.16</v>
       </c>
       <c r="AF7">
-        <v>65.65000000000001</v>
+        <v>-19.85</v>
       </c>
       <c r="AG7">
-        <v>1105.83</v>
+        <v>1100.4</v>
       </c>
       <c r="AH7">
-        <v>1002.74</v>
+        <v>1000.8</v>
       </c>
       <c r="AI7">
         <v>1075.64</v>
@@ -1610,7 +1563,7 @@
         <v>47</v>
       </c>
       <c r="AK7">
-        <v>41.79</v>
+        <v>38.45</v>
       </c>
     </row>
     <row r="8" spans="1:37">
@@ -1621,10 +1574,10 @@
         <v>44</v>
       </c>
       <c r="C8">
-        <v>134.78</v>
+        <v>136.03</v>
       </c>
       <c r="D8">
-        <v>0.43</v>
+        <v>0.93</v>
       </c>
       <c r="E8">
         <v>148.95</v>
@@ -1633,46 +1586,46 @@
         <v>115.96</v>
       </c>
       <c r="G8">
-        <v>-9.51</v>
+        <v>-8.67</v>
       </c>
       <c r="H8">
-        <v>16.23</v>
+        <v>17.31</v>
       </c>
       <c r="I8">
-        <v>-5.46</v>
+        <v>-2.47</v>
       </c>
       <c r="J8">
-        <v>0.16</v>
+        <v>-0.68</v>
       </c>
       <c r="K8">
-        <v>-0.76</v>
+        <v>-1.18</v>
       </c>
       <c r="L8">
-        <v>-2.76</v>
+        <v>-2.35</v>
       </c>
       <c r="M8">
-        <v>0.64</v>
+        <v>1.16</v>
       </c>
       <c r="N8">
         <v>57</v>
       </c>
       <c r="O8">
-        <v>56</v>
+        <v>58</v>
       </c>
       <c r="P8">
-        <v>135.79</v>
+        <v>135.1</v>
       </c>
       <c r="Q8">
-        <v>136.47</v>
+        <v>136.41</v>
       </c>
       <c r="R8">
-        <v>138.42</v>
+        <v>138.48</v>
       </c>
       <c r="S8">
-        <v>133.82</v>
+        <v>133.83</v>
       </c>
       <c r="T8">
-        <v>0.72</v>
+        <v>1.64</v>
       </c>
       <c r="U8" t="s">
         <v>46</v>
@@ -1687,34 +1640,34 @@
         <v>2</v>
       </c>
       <c r="Y8">
-        <v>44.84</v>
+        <v>48.06</v>
       </c>
       <c r="Z8">
-        <v>-0.46</v>
+        <v>-0.45</v>
       </c>
       <c r="AA8">
-        <v>-0.3</v>
+        <v>-0.33</v>
       </c>
       <c r="AB8">
-        <v>-0.16</v>
+        <v>-0.12</v>
       </c>
       <c r="AC8">
-        <v>24.1</v>
+        <v>28.6</v>
       </c>
       <c r="AD8">
-        <v>30.22</v>
+        <v>26.16</v>
       </c>
       <c r="AE8">
-        <v>4.31</v>
+        <v>4.25</v>
       </c>
       <c r="AF8">
-        <v>-42.72</v>
+        <v>-34.09</v>
       </c>
       <c r="AG8">
-        <v>140.97</v>
+        <v>140.9</v>
       </c>
       <c r="AH8">
-        <v>131.97</v>
+        <v>131.92</v>
       </c>
       <c r="AI8">
         <v>131.91</v>
@@ -1723,7 +1676,7 @@
         <v>48</v>
       </c>
       <c r="AK8">
-        <v>24.26</v>
+        <v>21.87</v>
       </c>
     </row>
   </sheetData>
@@ -1864,7 +1817,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:F67"/>
+  <dimension ref="A1:F62"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="16.7109375" customWidth="1"/>
@@ -1884,1120 +1837,991 @@
     </row>
     <row r="2" spans="1:6">
       <c r="A2" s="3" t="s">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="5" spans="1:6">
+      <c r="A5" s="2" t="s">
+        <v>51</v>
+      </c>
+      <c r="B5" s="2"/>
+      <c r="C5" s="2"/>
+      <c r="D5" s="2"/>
+      <c r="E5" s="2"/>
+    </row>
+    <row r="6" spans="1:6">
+      <c r="A6" s="4" t="s">
         <v>0</v>
       </c>
-      <c r="B2" s="3" t="s">
-        <v>50</v>
-      </c>
-      <c r="C2" s="3" t="s">
-        <v>51</v>
-      </c>
-      <c r="D2" s="3" t="s">
+      <c r="B6" s="4" t="s">
         <v>52</v>
       </c>
-      <c r="E2" s="3" t="s">
+      <c r="C6" s="4" t="s">
         <v>53</v>
       </c>
-      <c r="F2" s="3" t="s">
+      <c r="D6" s="4" t="s">
         <v>54</v>
       </c>
-    </row>
-    <row r="3" spans="1:6">
-      <c r="A3" s="4" t="s">
+      <c r="E6" s="4" t="s">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="7" spans="1:6">
+      <c r="A7" s="3" t="s">
+        <v>37</v>
+      </c>
+      <c r="B7" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="C7" s="5">
+        <v>-1.98</v>
+      </c>
+      <c r="D7" s="5">
+        <v>-2.82</v>
+      </c>
+      <c r="E7" s="6">
+        <v>-0.84</v>
+      </c>
+    </row>
+    <row r="8" spans="1:6">
+      <c r="A8" s="3" t="s">
         <v>38</v>
       </c>
-      <c r="B3" s="4" t="s">
-        <v>55</v>
-      </c>
-      <c r="C3" s="4" t="s">
-        <v>56</v>
-      </c>
-      <c r="D3" s="4" t="s">
-        <v>57</v>
-      </c>
-      <c r="E3" s="4" t="s">
-        <v>58</v>
-      </c>
-      <c r="F3" s="4" t="s">
-        <v>59</v>
-      </c>
-    </row>
-    <row r="4" spans="1:6">
-      <c r="A4" s="4" t="s">
-        <v>41</v>
-      </c>
-      <c r="B4" s="4" t="s">
-        <v>55</v>
-      </c>
-      <c r="C4" s="4" t="s">
-        <v>60</v>
-      </c>
-      <c r="D4" s="4" t="s">
-        <v>57</v>
-      </c>
-      <c r="E4" s="4" t="s">
-        <v>61</v>
-      </c>
-      <c r="F4" s="4" t="s">
-        <v>62</v>
-      </c>
-    </row>
-    <row r="5" spans="1:6">
-      <c r="A5" s="5" t="s">
-        <v>40</v>
-      </c>
-      <c r="B5" s="5" t="s">
-        <v>22</v>
-      </c>
-      <c r="C5" s="5" t="s">
-        <v>63</v>
-      </c>
-      <c r="D5" s="5" t="s">
-        <v>64</v>
-      </c>
-      <c r="E5" s="5" t="s">
-        <v>45</v>
-      </c>
-      <c r="F5" s="5" t="s">
-        <v>46</v>
-      </c>
-    </row>
-    <row r="6" spans="1:6">
-      <c r="A6" s="5" t="s">
-        <v>40</v>
-      </c>
-      <c r="B6" s="5" t="s">
-        <v>65</v>
-      </c>
-      <c r="C6" s="5" t="s">
-        <v>63</v>
-      </c>
-      <c r="D6" s="5" t="s">
-        <v>64</v>
-      </c>
-      <c r="E6" s="5" t="s">
-        <v>45</v>
-      </c>
-      <c r="F6" s="5" t="s">
-        <v>46</v>
-      </c>
-    </row>
-    <row r="8" spans="1:6">
-      <c r="A8" s="2" t="s">
-        <v>66</v>
-      </c>
-      <c r="B8" s="2"/>
-      <c r="C8" s="2"/>
-      <c r="D8" s="2"/>
-      <c r="E8" s="2"/>
+      <c r="B8" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="C8" s="5">
+        <v>2.29</v>
+      </c>
+      <c r="D8" s="5">
+        <v>5.82</v>
+      </c>
+      <c r="E8" s="7">
+        <v>3.53</v>
+      </c>
     </row>
     <row r="9" spans="1:6">
       <c r="A9" s="3" t="s">
-        <v>0</v>
+        <v>39</v>
       </c>
       <c r="B9" s="3" t="s">
-        <v>67</v>
-      </c>
-      <c r="C9" s="3" t="s">
-        <v>68</v>
-      </c>
-      <c r="D9" s="3" t="s">
-        <v>69</v>
-      </c>
-      <c r="E9" s="3" t="s">
-        <v>70</v>
+        <v>9</v>
+      </c>
+      <c r="C9" s="5">
+        <v>-8.630000000000001</v>
+      </c>
+      <c r="D9" s="5">
+        <v>-8</v>
+      </c>
+      <c r="E9" s="7">
+        <v>0.63</v>
       </c>
     </row>
     <row r="10" spans="1:6">
-      <c r="A10" s="6" t="s">
+      <c r="A10" s="3" t="s">
+        <v>40</v>
+      </c>
+      <c r="B10" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="C10" s="5">
+        <v>-7.93</v>
+      </c>
+      <c r="D10" s="5">
+        <v>-8.24</v>
+      </c>
+      <c r="E10" s="6">
+        <v>-0.31</v>
+      </c>
+    </row>
+    <row r="11" spans="1:6">
+      <c r="A11" s="3" t="s">
+        <v>41</v>
+      </c>
+      <c r="B11" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="C11" s="5">
+        <v>-0.86</v>
+      </c>
+      <c r="D11" s="5">
+        <v>0.36</v>
+      </c>
+      <c r="E11" s="7">
+        <v>1.22</v>
+      </c>
+    </row>
+    <row r="12" spans="1:6">
+      <c r="A12" s="3" t="s">
+        <v>42</v>
+      </c>
+      <c r="B12" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="C12" s="5">
+        <v>-3.69</v>
+      </c>
+      <c r="D12" s="5">
+        <v>-6.73</v>
+      </c>
+      <c r="E12" s="6">
+        <v>-3.04</v>
+      </c>
+    </row>
+    <row r="13" spans="1:6">
+      <c r="A13" s="3" t="s">
+        <v>43</v>
+      </c>
+      <c r="B13" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="C13" s="5">
+        <v>0.16</v>
+      </c>
+      <c r="D13" s="5">
+        <v>-0.68</v>
+      </c>
+      <c r="E13" s="6">
+        <v>-0.84</v>
+      </c>
+    </row>
+    <row r="14" spans="1:6">
+      <c r="A14" s="3" t="s">
         <v>37</v>
       </c>
-      <c r="B10" s="6" t="s">
-        <v>9</v>
-      </c>
-      <c r="C10" s="7">
-        <v>-0.92</v>
-      </c>
-      <c r="D10" s="7">
-        <v>-1.98</v>
-      </c>
-      <c r="E10" s="8">
-        <v>-1.06</v>
-      </c>
-    </row>
-    <row r="11" spans="1:6">
-      <c r="A11" s="6" t="s">
+      <c r="B14" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="C14" s="5">
+        <v>-3.01</v>
+      </c>
+      <c r="D14" s="5">
+        <v>-1.87</v>
+      </c>
+      <c r="E14" s="7">
+        <v>1.14</v>
+      </c>
+    </row>
+    <row r="15" spans="1:6">
+      <c r="A15" s="3" t="s">
         <v>38</v>
       </c>
-      <c r="B11" s="6" t="s">
-        <v>9</v>
-      </c>
-      <c r="C11" s="7">
-        <v>3.8</v>
-      </c>
-      <c r="D11" s="7">
-        <v>2.29</v>
-      </c>
-      <c r="E11" s="8">
-        <v>-1.51</v>
-      </c>
-    </row>
-    <row r="12" spans="1:6">
-      <c r="A12" s="6" t="s">
+      <c r="B15" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="C15" s="5">
+        <v>-2.35</v>
+      </c>
+      <c r="D15" s="5">
+        <v>-1</v>
+      </c>
+      <c r="E15" s="7">
+        <v>1.35</v>
+      </c>
+    </row>
+    <row r="16" spans="1:6">
+      <c r="A16" s="3" t="s">
         <v>39</v>
       </c>
-      <c r="B12" s="6" t="s">
-        <v>9</v>
-      </c>
-      <c r="C12" s="7">
-        <v>-8.51</v>
-      </c>
-      <c r="D12" s="7">
-        <v>-8.630000000000001</v>
-      </c>
-      <c r="E12" s="8">
+      <c r="B16" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="C16" s="5">
+        <v>-4.35</v>
+      </c>
+      <c r="D16" s="5">
+        <v>-2.77</v>
+      </c>
+      <c r="E16" s="7">
+        <v>1.58</v>
+      </c>
+    </row>
+    <row r="17" spans="1:5">
+      <c r="A17" s="3" t="s">
+        <v>40</v>
+      </c>
+      <c r="B17" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="C17" s="5">
+        <v>-4.53</v>
+      </c>
+      <c r="D17" s="5">
+        <v>-3.33</v>
+      </c>
+      <c r="E17" s="7">
+        <v>1.2</v>
+      </c>
+    </row>
+    <row r="18" spans="1:5">
+      <c r="A18" s="3" t="s">
+        <v>41</v>
+      </c>
+      <c r="B18" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="C18" s="5">
+        <v>2.64</v>
+      </c>
+      <c r="D18" s="5">
+        <v>2.47</v>
+      </c>
+      <c r="E18" s="6">
+        <v>-0.17</v>
+      </c>
+    </row>
+    <row r="19" spans="1:5">
+      <c r="A19" s="3" t="s">
+        <v>42</v>
+      </c>
+      <c r="B19" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="C19" s="5">
+        <v>-0.31</v>
+      </c>
+      <c r="D19" s="5">
+        <v>-1.28</v>
+      </c>
+      <c r="E19" s="6">
+        <v>-0.97</v>
+      </c>
+    </row>
+    <row r="20" spans="1:5">
+      <c r="A20" s="3" t="s">
+        <v>43</v>
+      </c>
+      <c r="B20" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="C20" s="5">
+        <v>-5.46</v>
+      </c>
+      <c r="D20" s="5">
+        <v>-2.47</v>
+      </c>
+      <c r="E20" s="7">
+        <v>2.99</v>
+      </c>
+    </row>
+    <row r="21" spans="1:5">
+      <c r="A21" s="3" t="s">
+        <v>37</v>
+      </c>
+      <c r="B21" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="C21" s="5">
+        <v>28.25</v>
+      </c>
+      <c r="D21" s="5">
+        <v>28.09</v>
+      </c>
+      <c r="E21" s="6">
+        <v>-0.16</v>
+      </c>
+    </row>
+    <row r="22" spans="1:5">
+      <c r="A22" s="3" t="s">
+        <v>38</v>
+      </c>
+      <c r="B22" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="C22" s="5">
+        <v>122.71</v>
+      </c>
+      <c r="D22" s="5">
+        <v>125.87</v>
+      </c>
+      <c r="E22" s="7">
+        <v>3.16</v>
+      </c>
+    </row>
+    <row r="23" spans="1:5">
+      <c r="A23" s="3" t="s">
+        <v>39</v>
+      </c>
+      <c r="B23" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="C23" s="5">
+        <v>-45.09</v>
+      </c>
+      <c r="D23" s="5">
+        <v>-44.97</v>
+      </c>
+      <c r="E23" s="7">
+        <v>0.12</v>
+      </c>
+    </row>
+    <row r="24" spans="1:5">
+      <c r="A24" s="3" t="s">
+        <v>40</v>
+      </c>
+      <c r="B24" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="C24" s="5">
+        <v>-10.94</v>
+      </c>
+      <c r="D24" s="5">
+        <v>-11.08</v>
+      </c>
+      <c r="E24" s="6">
+        <v>-0.14</v>
+      </c>
+    </row>
+    <row r="25" spans="1:5">
+      <c r="A25" s="3" t="s">
+        <v>41</v>
+      </c>
+      <c r="B25" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="C25" s="5">
+        <v>-14.09</v>
+      </c>
+      <c r="D25" s="5">
+        <v>-15.23</v>
+      </c>
+      <c r="E25" s="6">
+        <v>-1.14</v>
+      </c>
+    </row>
+    <row r="26" spans="1:5">
+      <c r="A26" s="3" t="s">
+        <v>42</v>
+      </c>
+      <c r="B26" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="C26" s="5">
+        <v>3.02</v>
+      </c>
+      <c r="D26" s="5">
+        <v>1.8</v>
+      </c>
+      <c r="E26" s="6">
+        <v>-1.22</v>
+      </c>
+    </row>
+    <row r="27" spans="1:5">
+      <c r="A27" s="3" t="s">
+        <v>43</v>
+      </c>
+      <c r="B27" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="C27" s="5">
+        <v>-2.76</v>
+      </c>
+      <c r="D27" s="5">
+        <v>-2.35</v>
+      </c>
+      <c r="E27" s="7">
+        <v>0.41</v>
+      </c>
+    </row>
+    <row r="28" spans="1:5">
+      <c r="A28" s="3" t="s">
+        <v>37</v>
+      </c>
+      <c r="B28" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="C28" s="5">
+        <v>13.39</v>
+      </c>
+      <c r="D28" s="5">
+        <v>12.45</v>
+      </c>
+      <c r="E28" s="6">
+        <v>-0.9399999999999999</v>
+      </c>
+    </row>
+    <row r="29" spans="1:5">
+      <c r="A29" s="3" t="s">
+        <v>38</v>
+      </c>
+      <c r="B29" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="C29" s="5">
+        <v>-18.09</v>
+      </c>
+      <c r="D29" s="5">
+        <v>-16.85</v>
+      </c>
+      <c r="E29" s="7">
+        <v>1.24</v>
+      </c>
+    </row>
+    <row r="30" spans="1:5">
+      <c r="A30" s="3" t="s">
+        <v>39</v>
+      </c>
+      <c r="B30" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="C30" s="5">
+        <v>-0.8</v>
+      </c>
+      <c r="D30" s="5">
+        <v>-1.29</v>
+      </c>
+      <c r="E30" s="6">
+        <v>-0.49</v>
+      </c>
+    </row>
+    <row r="31" spans="1:5">
+      <c r="A31" s="3" t="s">
+        <v>40</v>
+      </c>
+      <c r="B31" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="C31" s="5">
+        <v>4.7</v>
+      </c>
+      <c r="D31" s="5">
+        <v>3.79</v>
+      </c>
+      <c r="E31" s="6">
+        <v>-0.91</v>
+      </c>
+    </row>
+    <row r="32" spans="1:5">
+      <c r="A32" s="3" t="s">
+        <v>41</v>
+      </c>
+      <c r="B32" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="C32" s="5">
+        <v>5.67</v>
+      </c>
+      <c r="D32" s="5">
+        <v>4.72</v>
+      </c>
+      <c r="E32" s="6">
+        <v>-0.95</v>
+      </c>
+    </row>
+    <row r="33" spans="1:5">
+      <c r="A33" s="3" t="s">
+        <v>42</v>
+      </c>
+      <c r="B33" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="C33" s="5">
+        <v>8.16</v>
+      </c>
+      <c r="D33" s="5">
+        <v>5.47</v>
+      </c>
+      <c r="E33" s="6">
+        <v>-2.69</v>
+      </c>
+    </row>
+    <row r="34" spans="1:5">
+      <c r="A34" s="3" t="s">
+        <v>43</v>
+      </c>
+      <c r="B34" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="C34" s="5">
+        <v>-0.76</v>
+      </c>
+      <c r="D34" s="5">
+        <v>-1.18</v>
+      </c>
+      <c r="E34" s="6">
+        <v>-0.42</v>
+      </c>
+    </row>
+    <row r="35" spans="1:5">
+      <c r="A35" s="3" t="s">
+        <v>37</v>
+      </c>
+      <c r="B35" s="3" t="s">
+        <v>6</v>
+      </c>
+      <c r="C35" s="5">
+        <v>-7.66</v>
+      </c>
+      <c r="D35" s="5">
+        <v>-7.29</v>
+      </c>
+      <c r="E35" s="7">
+        <v>0.37</v>
+      </c>
+    </row>
+    <row r="36" spans="1:5">
+      <c r="A36" s="3" t="s">
+        <v>38</v>
+      </c>
+      <c r="B36" s="3" t="s">
+        <v>6</v>
+      </c>
+      <c r="C36" s="5">
+        <v>-23.59</v>
+      </c>
+      <c r="D36" s="5">
+        <v>-23.12</v>
+      </c>
+      <c r="E36" s="7">
+        <v>0.47</v>
+      </c>
+    </row>
+    <row r="37" spans="1:5">
+      <c r="A37" s="3" t="s">
+        <v>39</v>
+      </c>
+      <c r="B37" s="3" t="s">
+        <v>6</v>
+      </c>
+      <c r="C37" s="5">
+        <v>-46.59</v>
+      </c>
+      <c r="D37" s="5">
+        <v>-46.1</v>
+      </c>
+      <c r="E37" s="7">
+        <v>0.49</v>
+      </c>
+    </row>
+    <row r="38" spans="1:5">
+      <c r="A38" s="3" t="s">
+        <v>40</v>
+      </c>
+      <c r="B38" s="3" t="s">
+        <v>6</v>
+      </c>
+      <c r="C38" s="5">
+        <v>-14.89</v>
+      </c>
+      <c r="D38" s="5">
+        <v>-15.01</v>
+      </c>
+      <c r="E38" s="6">
         <v>-0.12</v>
       </c>
     </row>
-    <row r="13" spans="1:6">
-      <c r="A13" s="6" t="s">
+    <row r="39" spans="1:5">
+      <c r="A39" s="3" t="s">
+        <v>41</v>
+      </c>
+      <c r="B39" s="3" t="s">
+        <v>6</v>
+      </c>
+      <c r="C39" s="5">
+        <v>-17.02</v>
+      </c>
+      <c r="D39" s="5">
+        <v>-16.08</v>
+      </c>
+      <c r="E39" s="7">
+        <v>0.9399999999999999</v>
+      </c>
+    </row>
+    <row r="40" spans="1:5">
+      <c r="A40" s="3" t="s">
+        <v>42</v>
+      </c>
+      <c r="B40" s="3" t="s">
+        <v>6</v>
+      </c>
+      <c r="C40" s="5">
+        <v>-10.23</v>
+      </c>
+      <c r="D40" s="5">
+        <v>-11.87</v>
+      </c>
+      <c r="E40" s="6">
+        <v>-1.64</v>
+      </c>
+    </row>
+    <row r="41" spans="1:5">
+      <c r="A41" s="3" t="s">
+        <v>43</v>
+      </c>
+      <c r="B41" s="3" t="s">
+        <v>6</v>
+      </c>
+      <c r="C41" s="5">
+        <v>-9.51</v>
+      </c>
+      <c r="D41" s="5">
+        <v>-8.67</v>
+      </c>
+      <c r="E41" s="7">
+        <v>0.84</v>
+      </c>
+    </row>
+    <row r="42" spans="1:5">
+      <c r="A42" s="3" t="s">
+        <v>37</v>
+      </c>
+      <c r="B42" s="3" t="s">
+        <v>2</v>
+      </c>
+      <c r="C42" s="5">
+        <v>11414</v>
+      </c>
+      <c r="D42" s="5">
+        <v>11460</v>
+      </c>
+      <c r="E42" s="7">
+        <v>46</v>
+      </c>
+    </row>
+    <row r="43" spans="1:5">
+      <c r="A43" s="3" t="s">
+        <v>38</v>
+      </c>
+      <c r="B43" s="3" t="s">
+        <v>2</v>
+      </c>
+      <c r="C43" s="5">
+        <v>512.15</v>
+      </c>
+      <c r="D43" s="5">
+        <v>515.3</v>
+      </c>
+      <c r="E43" s="7">
+        <v>3.15</v>
+      </c>
+    </row>
+    <row r="44" spans="1:5">
+      <c r="A44" s="3" t="s">
+        <v>39</v>
+      </c>
+      <c r="B44" s="3" t="s">
+        <v>2</v>
+      </c>
+      <c r="C44" s="5">
+        <v>323.05</v>
+      </c>
+      <c r="D44" s="5">
+        <v>326</v>
+      </c>
+      <c r="E44" s="7">
+        <v>2.95</v>
+      </c>
+    </row>
+    <row r="45" spans="1:5">
+      <c r="A45" s="3" t="s">
         <v>40</v>
       </c>
-      <c r="B13" s="6" t="s">
-        <v>9</v>
-      </c>
-      <c r="C13" s="7">
-        <v>-7.56</v>
-      </c>
-      <c r="D13" s="7">
-        <v>-7.93</v>
-      </c>
-      <c r="E13" s="8">
-        <v>-0.37</v>
-      </c>
-    </row>
-    <row r="14" spans="1:6">
-      <c r="A14" s="6" t="s">
+      <c r="B45" s="3" t="s">
+        <v>2</v>
+      </c>
+      <c r="C45" s="5">
+        <v>1852.5</v>
+      </c>
+      <c r="D45" s="5">
+        <v>1849.8</v>
+      </c>
+      <c r="E45" s="6">
+        <v>-2.7</v>
+      </c>
+    </row>
+    <row r="46" spans="1:5">
+      <c r="A46" s="3" t="s">
         <v>41</v>
       </c>
-      <c r="B14" s="6" t="s">
-        <v>9</v>
-      </c>
-      <c r="C14" s="7">
-        <v>-2.17</v>
-      </c>
-      <c r="D14" s="7">
-        <v>-0.86</v>
-      </c>
-      <c r="E14" s="9">
-        <v>1.31</v>
-      </c>
-    </row>
-    <row r="15" spans="1:6">
-      <c r="A15" s="6" t="s">
+      <c r="B46" s="3" t="s">
+        <v>2</v>
+      </c>
+      <c r="C46" s="5">
+        <v>11282</v>
+      </c>
+      <c r="D46" s="5">
+        <v>11409</v>
+      </c>
+      <c r="E46" s="7">
+        <v>127</v>
+      </c>
+    </row>
+    <row r="47" spans="1:5">
+      <c r="A47" s="3" t="s">
         <v>42</v>
       </c>
-      <c r="B15" s="6" t="s">
-        <v>9</v>
-      </c>
-      <c r="C15" s="7">
-        <v>-7.25</v>
-      </c>
-      <c r="D15" s="7">
-        <v>-3.69</v>
-      </c>
-      <c r="E15" s="9">
-        <v>3.56</v>
-      </c>
-    </row>
-    <row r="16" spans="1:6">
-      <c r="A16" s="6" t="s">
+      <c r="B47" s="3" t="s">
+        <v>2</v>
+      </c>
+      <c r="C47" s="5">
+        <v>1040.3</v>
+      </c>
+      <c r="D47" s="5">
+        <v>1021.3</v>
+      </c>
+      <c r="E47" s="6">
+        <v>-19</v>
+      </c>
+    </row>
+    <row r="48" spans="1:5">
+      <c r="A48" s="3" t="s">
         <v>43</v>
       </c>
-      <c r="B16" s="6" t="s">
-        <v>9</v>
-      </c>
-      <c r="C16" s="7">
-        <v>-1.1</v>
-      </c>
-      <c r="D16" s="7">
-        <v>0.16</v>
-      </c>
-      <c r="E16" s="9">
-        <v>1.26</v>
-      </c>
-    </row>
-    <row r="17" spans="1:5">
-      <c r="A17" s="6" t="s">
+      <c r="B48" s="3" t="s">
+        <v>2</v>
+      </c>
+      <c r="C48" s="5">
+        <v>134.78</v>
+      </c>
+      <c r="D48" s="5">
+        <v>136.03</v>
+      </c>
+      <c r="E48" s="7">
+        <v>1.25</v>
+      </c>
+    </row>
+    <row r="49" spans="1:5">
+      <c r="A49" s="3" t="s">
         <v>37</v>
       </c>
-      <c r="B17" s="6" t="s">
-        <v>8</v>
-      </c>
-      <c r="C17" s="7">
-        <v>-2.46</v>
-      </c>
-      <c r="D17" s="7">
-        <v>-3.01</v>
-      </c>
-      <c r="E17" s="8">
-        <v>-0.55</v>
-      </c>
-    </row>
-    <row r="18" spans="1:5">
-      <c r="A18" s="6" t="s">
+      <c r="B49" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="C49" s="5">
+        <v>42.48</v>
+      </c>
+      <c r="D49" s="5">
+        <v>44.1</v>
+      </c>
+      <c r="E49" s="7">
+        <v>1.62</v>
+      </c>
+    </row>
+    <row r="50" spans="1:5">
+      <c r="A50" s="3" t="s">
         <v>38</v>
       </c>
-      <c r="B18" s="6" t="s">
-        <v>8</v>
-      </c>
-      <c r="C18" s="7">
-        <v>-3.64</v>
-      </c>
-      <c r="D18" s="7">
-        <v>-2.35</v>
-      </c>
-      <c r="E18" s="9">
-        <v>1.29</v>
-      </c>
-    </row>
-    <row r="19" spans="1:5">
-      <c r="A19" s="6" t="s">
+      <c r="B50" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="C50" s="5">
+        <v>51.74</v>
+      </c>
+      <c r="D50" s="5">
+        <v>52.88</v>
+      </c>
+      <c r="E50" s="7">
+        <v>1.14</v>
+      </c>
+    </row>
+    <row r="51" spans="1:5">
+      <c r="A51" s="3" t="s">
         <v>39</v>
       </c>
-      <c r="B19" s="6" t="s">
-        <v>8</v>
-      </c>
-      <c r="C19" s="7">
-        <v>-4.27</v>
-      </c>
-      <c r="D19" s="7">
-        <v>-4.35</v>
-      </c>
-      <c r="E19" s="8">
-        <v>-0.08</v>
-      </c>
-    </row>
-    <row r="20" spans="1:5">
-      <c r="A20" s="6" t="s">
+      <c r="B51" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="C51" s="5">
+        <v>39.32</v>
+      </c>
+      <c r="D51" s="5">
+        <v>42.2</v>
+      </c>
+      <c r="E51" s="7">
+        <v>2.88</v>
+      </c>
+    </row>
+    <row r="52" spans="1:5">
+      <c r="A52" s="3" t="s">
         <v>40</v>
       </c>
-      <c r="B20" s="6" t="s">
-        <v>8</v>
-      </c>
-      <c r="C20" s="7">
-        <v>-3.52</v>
-      </c>
-      <c r="D20" s="7">
-        <v>-4.53</v>
-      </c>
-      <c r="E20" s="8">
-        <v>-1.01</v>
-      </c>
-    </row>
-    <row r="21" spans="1:5">
-      <c r="A21" s="6" t="s">
+      <c r="B52" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="C52" s="5">
+        <v>32.6</v>
+      </c>
+      <c r="D52" s="5">
+        <v>32.25</v>
+      </c>
+      <c r="E52" s="6">
+        <v>-0.35</v>
+      </c>
+    </row>
+    <row r="53" spans="1:5">
+      <c r="A53" s="3" t="s">
         <v>41</v>
       </c>
-      <c r="B21" s="6" t="s">
-        <v>8</v>
-      </c>
-      <c r="C21" s="7">
-        <v>-0.61</v>
-      </c>
-      <c r="D21" s="7">
-        <v>2.64</v>
-      </c>
-      <c r="E21" s="9">
-        <v>3.25</v>
-      </c>
-    </row>
-    <row r="22" spans="1:5">
-      <c r="A22" s="6" t="s">
+      <c r="B53" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="C53" s="5">
+        <v>53.69</v>
+      </c>
+      <c r="D53" s="5">
+        <v>56.88</v>
+      </c>
+      <c r="E53" s="7">
+        <v>3.19</v>
+      </c>
+    </row>
+    <row r="54" spans="1:5">
+      <c r="A54" s="3" t="s">
         <v>42</v>
       </c>
-      <c r="B22" s="6" t="s">
-        <v>8</v>
-      </c>
-      <c r="C22" s="7">
-        <v>-2.34</v>
-      </c>
-      <c r="D22" s="7">
-        <v>-0.31</v>
-      </c>
-      <c r="E22" s="9">
-        <v>2.03</v>
-      </c>
-    </row>
-    <row r="23" spans="1:5">
-      <c r="A23" s="6" t="s">
+      <c r="B54" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="C54" s="5">
+        <v>45.91</v>
+      </c>
+      <c r="D54" s="5">
+        <v>40.55</v>
+      </c>
+      <c r="E54" s="6">
+        <v>-5.36</v>
+      </c>
+    </row>
+    <row r="55" spans="1:5">
+      <c r="A55" s="3" t="s">
         <v>43</v>
       </c>
-      <c r="B23" s="6" t="s">
-        <v>8</v>
-      </c>
-      <c r="C23" s="7">
-        <v>-3.93</v>
-      </c>
-      <c r="D23" s="7">
-        <v>-5.46</v>
-      </c>
-      <c r="E23" s="8">
-        <v>-1.53</v>
-      </c>
-    </row>
-    <row r="24" spans="1:5">
-      <c r="A24" s="6" t="s">
+      <c r="B55" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="C55" s="5">
+        <v>44.84</v>
+      </c>
+      <c r="D55" s="5">
+        <v>48.06</v>
+      </c>
+      <c r="E55" s="7">
+        <v>3.22</v>
+      </c>
+    </row>
+    <row r="56" spans="1:5">
+      <c r="A56" s="3" t="s">
         <v>37</v>
       </c>
-      <c r="B24" s="6" t="s">
-        <v>11</v>
-      </c>
-      <c r="C24" s="7">
-        <v>29.58</v>
-      </c>
-      <c r="D24" s="7">
-        <v>28.25</v>
-      </c>
-      <c r="E24" s="8">
-        <v>-1.33</v>
-      </c>
-    </row>
-    <row r="25" spans="1:5">
-      <c r="A25" s="6" t="s">
+      <c r="B56" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="C56" s="5">
+        <v>32.66</v>
+      </c>
+      <c r="D56" s="5">
+        <v>-59.04</v>
+      </c>
+      <c r="E56" s="6">
+        <v>-91.7</v>
+      </c>
+    </row>
+    <row r="57" spans="1:5">
+      <c r="A57" s="3" t="s">
         <v>38</v>
       </c>
-      <c r="B25" s="6" t="s">
-        <v>11</v>
-      </c>
-      <c r="C25" s="7">
-        <v>124.39</v>
-      </c>
-      <c r="D25" s="7">
-        <v>122.71</v>
-      </c>
-      <c r="E25" s="8">
-        <v>-1.68</v>
-      </c>
-    </row>
-    <row r="26" spans="1:5">
-      <c r="A26" s="6" t="s">
+      <c r="B57" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="C57" s="5">
+        <v>-1.18</v>
+      </c>
+      <c r="D57" s="5">
+        <v>-36.72</v>
+      </c>
+      <c r="E57" s="6">
+        <v>-35.54</v>
+      </c>
+    </row>
+    <row r="58" spans="1:5">
+      <c r="A58" s="3" t="s">
         <v>39</v>
       </c>
-      <c r="B26" s="6" t="s">
-        <v>11</v>
-      </c>
-      <c r="C26" s="7">
-        <v>-44.65</v>
-      </c>
-      <c r="D26" s="7">
-        <v>-45.09</v>
-      </c>
-      <c r="E26" s="8">
-        <v>-0.44</v>
-      </c>
-    </row>
-    <row r="27" spans="1:5">
-      <c r="A27" s="6" t="s">
+      <c r="B58" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="C58" s="5">
+        <v>-18.61</v>
+      </c>
+      <c r="D58" s="5">
+        <v>-31.78</v>
+      </c>
+      <c r="E58" s="6">
+        <v>-13.17</v>
+      </c>
+    </row>
+    <row r="59" spans="1:5">
+      <c r="A59" s="3" t="s">
         <v>40</v>
       </c>
-      <c r="B27" s="6" t="s">
-        <v>11</v>
-      </c>
-      <c r="C27" s="7">
-        <v>-10.68</v>
-      </c>
-      <c r="D27" s="7">
-        <v>-10.94</v>
-      </c>
-      <c r="E27" s="8">
-        <v>-0.26</v>
-      </c>
-    </row>
-    <row r="28" spans="1:5">
-      <c r="A28" s="6" t="s">
+      <c r="B59" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="C59" s="5">
+        <v>20.65</v>
+      </c>
+      <c r="D59" s="5">
+        <v>-53.99</v>
+      </c>
+      <c r="E59" s="6">
+        <v>-74.64</v>
+      </c>
+    </row>
+    <row r="60" spans="1:5">
+      <c r="A60" s="3" t="s">
         <v>41</v>
       </c>
-      <c r="B28" s="6" t="s">
-        <v>11</v>
-      </c>
-      <c r="C28" s="7">
-        <v>-16.25</v>
-      </c>
-      <c r="D28" s="7">
-        <v>-14.09</v>
-      </c>
-      <c r="E28" s="9">
-        <v>2.16</v>
-      </c>
-    </row>
-    <row r="29" spans="1:5">
-      <c r="A29" s="6" t="s">
+      <c r="B60" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="C60" s="5">
+        <v>34.14</v>
+      </c>
+      <c r="D60" s="5">
+        <v>25.09</v>
+      </c>
+      <c r="E60" s="6">
+        <v>-9.050000000000001</v>
+      </c>
+    </row>
+    <row r="61" spans="1:5">
+      <c r="A61" s="3" t="s">
         <v>42</v>
       </c>
-      <c r="B29" s="6" t="s">
-        <v>11</v>
-      </c>
-      <c r="C29" s="7">
-        <v>1.17</v>
-      </c>
-      <c r="D29" s="7">
-        <v>3.02</v>
-      </c>
-      <c r="E29" s="9">
-        <v>1.85</v>
-      </c>
-    </row>
-    <row r="30" spans="1:5">
-      <c r="A30" s="6" t="s">
+      <c r="B61" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="C61" s="5">
+        <v>65.65000000000001</v>
+      </c>
+      <c r="D61" s="5">
+        <v>-19.85</v>
+      </c>
+      <c r="E61" s="6">
+        <v>-85.5</v>
+      </c>
+    </row>
+    <row r="62" spans="1:5">
+      <c r="A62" s="3" t="s">
         <v>43</v>
       </c>
-      <c r="B30" s="6" t="s">
-        <v>11</v>
-      </c>
-      <c r="C30" s="7">
-        <v>-1.86</v>
-      </c>
-      <c r="D30" s="7">
-        <v>-2.76</v>
-      </c>
-      <c r="E30" s="8">
-        <v>-0.9</v>
-      </c>
-    </row>
-    <row r="31" spans="1:5">
-      <c r="A31" s="6" t="s">
-        <v>37</v>
-      </c>
-      <c r="B31" s="6" t="s">
-        <v>10</v>
-      </c>
-      <c r="C31" s="7">
-        <v>14.12</v>
-      </c>
-      <c r="D31" s="7">
-        <v>13.39</v>
-      </c>
-      <c r="E31" s="8">
-        <v>-0.73</v>
-      </c>
-    </row>
-    <row r="32" spans="1:5">
-      <c r="A32" s="6" t="s">
-        <v>38</v>
-      </c>
-      <c r="B32" s="6" t="s">
-        <v>10</v>
-      </c>
-      <c r="C32" s="7">
-        <v>-19.02</v>
-      </c>
-      <c r="D32" s="7">
-        <v>-18.09</v>
-      </c>
-      <c r="E32" s="9">
-        <v>0.93</v>
-      </c>
-    </row>
-    <row r="33" spans="1:5">
-      <c r="A33" s="6" t="s">
-        <v>39</v>
-      </c>
-      <c r="B33" s="6" t="s">
-        <v>10</v>
-      </c>
-      <c r="C33" s="7">
-        <v>-1.14</v>
-      </c>
-      <c r="D33" s="7">
-        <v>-0.8</v>
-      </c>
-      <c r="E33" s="9">
-        <v>0.34</v>
-      </c>
-    </row>
-    <row r="34" spans="1:5">
-      <c r="A34" s="6" t="s">
-        <v>40</v>
-      </c>
-      <c r="B34" s="6" t="s">
-        <v>10</v>
-      </c>
-      <c r="C34" s="7">
-        <v>4.94</v>
-      </c>
-      <c r="D34" s="7">
-        <v>4.7</v>
-      </c>
-      <c r="E34" s="8">
-        <v>-0.24</v>
-      </c>
-    </row>
-    <row r="35" spans="1:5">
-      <c r="A35" s="6" t="s">
-        <v>41</v>
-      </c>
-      <c r="B35" s="6" t="s">
-        <v>10</v>
-      </c>
-      <c r="C35" s="7">
-        <v>3.13</v>
-      </c>
-      <c r="D35" s="7">
-        <v>5.67</v>
-      </c>
-      <c r="E35" s="9">
-        <v>2.54</v>
-      </c>
-    </row>
-    <row r="36" spans="1:5">
-      <c r="A36" s="6" t="s">
-        <v>42</v>
-      </c>
-      <c r="B36" s="6" t="s">
-        <v>10</v>
-      </c>
-      <c r="C36" s="7">
-        <v>5.86</v>
-      </c>
-      <c r="D36" s="7">
-        <v>8.16</v>
-      </c>
-      <c r="E36" s="9">
-        <v>2.3</v>
-      </c>
-    </row>
-    <row r="37" spans="1:5">
-      <c r="A37" s="6" t="s">
-        <v>43</v>
-      </c>
-      <c r="B37" s="6" t="s">
-        <v>10</v>
-      </c>
-      <c r="C37" s="7">
-        <v>-2.02</v>
-      </c>
-      <c r="D37" s="7">
-        <v>-0.76</v>
-      </c>
-      <c r="E37" s="9">
-        <v>1.26</v>
-      </c>
-    </row>
-    <row r="38" spans="1:5">
-      <c r="A38" s="6" t="s">
-        <v>37</v>
-      </c>
-      <c r="B38" s="6" t="s">
-        <v>6</v>
-      </c>
-      <c r="C38" s="7">
-        <v>-6.97</v>
-      </c>
-      <c r="D38" s="7">
-        <v>-7.66</v>
-      </c>
-      <c r="E38" s="8">
-        <v>-0.6899999999999999</v>
-      </c>
-    </row>
-    <row r="39" spans="1:5">
-      <c r="A39" s="6" t="s">
-        <v>38</v>
-      </c>
-      <c r="B39" s="6" t="s">
-        <v>6</v>
-      </c>
-      <c r="C39" s="7">
-        <v>-25.04</v>
-      </c>
-      <c r="D39" s="7">
-        <v>-23.59</v>
-      </c>
-      <c r="E39" s="9">
-        <v>1.45</v>
-      </c>
-    </row>
-    <row r="40" spans="1:5">
-      <c r="A40" s="6" t="s">
-        <v>39</v>
-      </c>
-      <c r="B40" s="6" t="s">
-        <v>6</v>
-      </c>
-      <c r="C40" s="7">
-        <v>-46.22</v>
-      </c>
-      <c r="D40" s="7">
-        <v>-46.59</v>
-      </c>
-      <c r="E40" s="8">
-        <v>-0.37</v>
-      </c>
-    </row>
-    <row r="41" spans="1:5">
-      <c r="A41" s="6" t="s">
-        <v>40</v>
-      </c>
-      <c r="B41" s="6" t="s">
-        <v>6</v>
-      </c>
-      <c r="C41" s="7">
-        <v>-14.58</v>
-      </c>
-      <c r="D41" s="7">
-        <v>-14.89</v>
-      </c>
-      <c r="E41" s="8">
-        <v>-0.31</v>
-      </c>
-    </row>
-    <row r="42" spans="1:5">
-      <c r="A42" s="6" t="s">
-        <v>41</v>
-      </c>
-      <c r="B42" s="6" t="s">
-        <v>6</v>
-      </c>
-      <c r="C42" s="7">
-        <v>-19.02</v>
-      </c>
-      <c r="D42" s="7">
-        <v>-17.02</v>
-      </c>
-      <c r="E42" s="9">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="43" spans="1:5">
-      <c r="A43" s="6" t="s">
-        <v>42</v>
-      </c>
-      <c r="B43" s="6" t="s">
-        <v>6</v>
-      </c>
-      <c r="C43" s="7">
-        <v>-12.41</v>
-      </c>
-      <c r="D43" s="7">
-        <v>-10.23</v>
-      </c>
-      <c r="E43" s="9">
-        <v>2.18</v>
-      </c>
-    </row>
-    <row r="44" spans="1:5">
-      <c r="A44" s="6" t="s">
-        <v>43</v>
-      </c>
-      <c r="B44" s="6" t="s">
-        <v>6</v>
-      </c>
-      <c r="C44" s="7">
-        <v>-9.9</v>
-      </c>
-      <c r="D44" s="7">
-        <v>-9.51</v>
-      </c>
-      <c r="E44" s="9">
-        <v>0.39</v>
-      </c>
-    </row>
-    <row r="45" spans="1:5">
-      <c r="A45" s="6" t="s">
-        <v>37</v>
-      </c>
-      <c r="B45" s="6" t="s">
-        <v>2</v>
-      </c>
-      <c r="C45" s="7">
-        <v>11500</v>
-      </c>
-      <c r="D45" s="7">
-        <v>11414</v>
-      </c>
-      <c r="E45" s="8">
-        <v>-86</v>
-      </c>
-    </row>
-    <row r="46" spans="1:5">
-      <c r="A46" s="6" t="s">
-        <v>38</v>
-      </c>
-      <c r="B46" s="6" t="s">
-        <v>2</v>
-      </c>
-      <c r="C46" s="7">
-        <v>502.45</v>
-      </c>
-      <c r="D46" s="7">
-        <v>512.15</v>
-      </c>
-      <c r="E46" s="9">
-        <v>9.699999999999999</v>
-      </c>
-    </row>
-    <row r="47" spans="1:5">
-      <c r="A47" s="6" t="s">
-        <v>39</v>
-      </c>
-      <c r="B47" s="6" t="s">
-        <v>2</v>
-      </c>
-      <c r="C47" s="7">
-        <v>325.3</v>
-      </c>
-      <c r="D47" s="7">
-        <v>323.05</v>
-      </c>
-      <c r="E47" s="8">
-        <v>-2.25</v>
-      </c>
-    </row>
-    <row r="48" spans="1:5">
-      <c r="A48" s="6" t="s">
-        <v>40</v>
-      </c>
-      <c r="B48" s="6" t="s">
-        <v>2</v>
-      </c>
-      <c r="C48" s="7">
-        <v>1859.2</v>
-      </c>
-      <c r="D48" s="7">
-        <v>1852.5</v>
-      </c>
-      <c r="E48" s="8">
-        <v>-6.7</v>
-      </c>
-    </row>
-    <row r="49" spans="1:5">
-      <c r="A49" s="6" t="s">
-        <v>41</v>
-      </c>
-      <c r="B49" s="6" t="s">
-        <v>2</v>
-      </c>
-      <c r="C49" s="7">
-        <v>11010</v>
-      </c>
-      <c r="D49" s="7">
-        <v>11282</v>
-      </c>
-      <c r="E49" s="9">
-        <v>272</v>
-      </c>
-    </row>
-    <row r="50" spans="1:5">
-      <c r="A50" s="6" t="s">
-        <v>42</v>
-      </c>
-      <c r="B50" s="6" t="s">
-        <v>2</v>
-      </c>
-      <c r="C50" s="7">
-        <v>1015</v>
-      </c>
-      <c r="D50" s="7">
-        <v>1040.3</v>
-      </c>
-      <c r="E50" s="9">
-        <v>25.3</v>
-      </c>
-    </row>
-    <row r="51" spans="1:5">
-      <c r="A51" s="6" t="s">
-        <v>43</v>
-      </c>
-      <c r="B51" s="6" t="s">
-        <v>2</v>
-      </c>
-      <c r="C51" s="7">
-        <v>134.2</v>
-      </c>
-      <c r="D51" s="7">
-        <v>134.78</v>
-      </c>
-      <c r="E51" s="9">
-        <v>0.58</v>
-      </c>
-    </row>
-    <row r="52" spans="1:5">
-      <c r="A52" s="6" t="s">
-        <v>40</v>
-      </c>
-      <c r="B52" s="6" t="s">
-        <v>13</v>
-      </c>
-      <c r="C52" s="7">
-        <v>43</v>
-      </c>
-      <c r="D52" s="7">
-        <v>29</v>
-      </c>
-      <c r="E52" s="8">
-        <v>-14</v>
-      </c>
-    </row>
-    <row r="53" spans="1:5">
-      <c r="A53" s="6" t="s">
-        <v>41</v>
-      </c>
-      <c r="B53" s="6" t="s">
-        <v>13</v>
-      </c>
-      <c r="C53" s="7">
-        <v>29</v>
-      </c>
-      <c r="D53" s="7">
-        <v>43</v>
-      </c>
-      <c r="E53" s="9">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="54" spans="1:5">
-      <c r="A54" s="6" t="s">
-        <v>37</v>
-      </c>
-      <c r="B54" s="6" t="s">
-        <v>24</v>
-      </c>
-      <c r="C54" s="7">
-        <v>44.74</v>
-      </c>
-      <c r="D54" s="7">
-        <v>42.48</v>
-      </c>
-      <c r="E54" s="8">
-        <v>-2.26</v>
-      </c>
-    </row>
-    <row r="55" spans="1:5">
-      <c r="A55" s="6" t="s">
-        <v>38</v>
-      </c>
-      <c r="B55" s="6" t="s">
-        <v>24</v>
-      </c>
-      <c r="C55" s="7">
-        <v>48.17</v>
-      </c>
-      <c r="D55" s="7">
-        <v>51.74</v>
-      </c>
-      <c r="E55" s="9">
-        <v>3.57</v>
-      </c>
-    </row>
-    <row r="56" spans="1:5">
-      <c r="A56" s="6" t="s">
-        <v>39</v>
-      </c>
-      <c r="B56" s="6" t="s">
-        <v>24</v>
-      </c>
-      <c r="C56" s="7">
-        <v>40.76</v>
-      </c>
-      <c r="D56" s="7">
-        <v>39.32</v>
-      </c>
-      <c r="E56" s="8">
-        <v>-1.44</v>
-      </c>
-    </row>
-    <row r="57" spans="1:5">
-      <c r="A57" s="6" t="s">
-        <v>40</v>
-      </c>
-      <c r="B57" s="6" t="s">
-        <v>24</v>
-      </c>
-      <c r="C57" s="7">
-        <v>33.43</v>
-      </c>
-      <c r="D57" s="7">
-        <v>32.6</v>
-      </c>
-      <c r="E57" s="8">
-        <v>-0.83</v>
-      </c>
-    </row>
-    <row r="58" spans="1:5">
-      <c r="A58" s="6" t="s">
-        <v>41</v>
-      </c>
-      <c r="B58" s="6" t="s">
-        <v>24</v>
-      </c>
-      <c r="C58" s="7">
-        <v>45.69</v>
-      </c>
-      <c r="D58" s="7">
-        <v>53.69</v>
-      </c>
-      <c r="E58" s="9">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="59" spans="1:5">
-      <c r="A59" s="6" t="s">
-        <v>42</v>
-      </c>
-      <c r="B59" s="6" t="s">
-        <v>24</v>
-      </c>
-      <c r="C59" s="7">
-        <v>35.33</v>
-      </c>
-      <c r="D59" s="7">
-        <v>45.91</v>
-      </c>
-      <c r="E59" s="9">
-        <v>10.58</v>
-      </c>
-    </row>
-    <row r="60" spans="1:5">
-      <c r="A60" s="6" t="s">
-        <v>43</v>
-      </c>
-      <c r="B60" s="6" t="s">
-        <v>24</v>
-      </c>
-      <c r="C60" s="7">
-        <v>43.32</v>
-      </c>
-      <c r="D60" s="7">
-        <v>44.84</v>
-      </c>
-      <c r="E60" s="9">
-        <v>1.52</v>
-      </c>
-    </row>
-    <row r="61" spans="1:5">
-      <c r="A61" s="6" t="s">
-        <v>37</v>
-      </c>
-      <c r="B61" s="6" t="s">
+      <c r="B62" s="3" t="s">
         <v>31</v>
       </c>
-      <c r="C61" s="7">
-        <v>-43.46</v>
-      </c>
-      <c r="D61" s="7">
-        <v>32.66</v>
-      </c>
-      <c r="E61" s="9">
-        <v>76.12</v>
-      </c>
-    </row>
-    <row r="62" spans="1:5">
-      <c r="A62" s="6" t="s">
-        <v>38</v>
-      </c>
-      <c r="B62" s="6" t="s">
-        <v>31</v>
-      </c>
-      <c r="C62" s="7">
-        <v>-68.7</v>
-      </c>
-      <c r="D62" s="7">
-        <v>-1.18</v>
-      </c>
-      <c r="E62" s="9">
-        <v>67.52</v>
-      </c>
-    </row>
-    <row r="63" spans="1:5">
-      <c r="A63" s="6" t="s">
-        <v>39</v>
-      </c>
-      <c r="B63" s="6" t="s">
-        <v>31</v>
-      </c>
-      <c r="C63" s="7">
-        <v>-66.45</v>
-      </c>
-      <c r="D63" s="7">
-        <v>-18.61</v>
-      </c>
-      <c r="E63" s="9">
-        <v>47.84</v>
-      </c>
-    </row>
-    <row r="64" spans="1:5">
-      <c r="A64" s="6" t="s">
-        <v>40</v>
-      </c>
-      <c r="B64" s="6" t="s">
-        <v>31</v>
-      </c>
-      <c r="C64" s="7">
-        <v>-22.51</v>
-      </c>
-      <c r="D64" s="7">
-        <v>20.65</v>
-      </c>
-      <c r="E64" s="9">
-        <v>43.16</v>
-      </c>
-    </row>
-    <row r="65" spans="1:5">
-      <c r="A65" s="6" t="s">
-        <v>41</v>
-      </c>
-      <c r="B65" s="6" t="s">
-        <v>31</v>
-      </c>
-      <c r="C65" s="7">
-        <v>-28.52</v>
-      </c>
-      <c r="D65" s="7">
-        <v>34.14</v>
-      </c>
-      <c r="E65" s="9">
-        <v>62.66</v>
-      </c>
-    </row>
-    <row r="66" spans="1:5">
-      <c r="A66" s="6" t="s">
-        <v>42</v>
-      </c>
-      <c r="B66" s="6" t="s">
-        <v>31</v>
-      </c>
-      <c r="C66" s="7">
-        <v>-1.34</v>
-      </c>
-      <c r="D66" s="7">
-        <v>65.65000000000001</v>
-      </c>
-      <c r="E66" s="9">
-        <v>66.98999999999999</v>
-      </c>
-    </row>
-    <row r="67" spans="1:5">
-      <c r="A67" s="6" t="s">
-        <v>43</v>
-      </c>
-      <c r="B67" s="6" t="s">
-        <v>31</v>
-      </c>
-      <c r="C67" s="7">
-        <v>-70.84</v>
-      </c>
-      <c r="D67" s="7">
+      <c r="C62" s="5">
         <v>-42.72</v>
       </c>
-      <c r="E67" s="9">
-        <v>28.12</v>
+      <c r="D62" s="5">
+        <v>-34.09</v>
+      </c>
+      <c r="E62" s="7">
+        <v>8.630000000000001</v>
       </c>
     </row>
   </sheetData>
   <mergeCells count="2">
     <mergeCell ref="A1:F1"/>
-    <mergeCell ref="A8:E8"/>
+    <mergeCell ref="A5:E5"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -3017,60 +2841,60 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:9" ht="28" customHeight="1">
-      <c r="A1" s="10" t="s">
+      <c r="A1" s="8" t="s">
         <v>1</v>
       </c>
-      <c r="B1" s="10" t="s">
-        <v>71</v>
-      </c>
-      <c r="C1" s="10" t="s">
-        <v>72</v>
-      </c>
-      <c r="D1" s="10" t="s">
-        <v>73</v>
-      </c>
-      <c r="E1" s="10" t="s">
-        <v>74</v>
-      </c>
-      <c r="F1" s="10" t="s">
-        <v>75</v>
-      </c>
-      <c r="G1" s="10" t="s">
-        <v>76</v>
-      </c>
-      <c r="H1" s="10" t="s">
-        <v>77</v>
-      </c>
-      <c r="I1" s="10" t="s">
-        <v>78</v>
+      <c r="B1" s="8" t="s">
+        <v>56</v>
+      </c>
+      <c r="C1" s="8" t="s">
+        <v>57</v>
+      </c>
+      <c r="D1" s="8" t="s">
+        <v>58</v>
+      </c>
+      <c r="E1" s="8" t="s">
+        <v>59</v>
+      </c>
+      <c r="F1" s="8" t="s">
+        <v>60</v>
+      </c>
+      <c r="G1" s="8" t="s">
+        <v>61</v>
+      </c>
+      <c r="H1" s="8" t="s">
+        <v>62</v>
+      </c>
+      <c r="I1" s="8" t="s">
+        <v>63</v>
       </c>
     </row>
     <row r="2" spans="1:9">
-      <c r="A2" s="11" t="s">
+      <c r="A2" s="9" t="s">
         <v>44</v>
       </c>
-      <c r="B2" s="12">
+      <c r="B2" s="10">
         <v>60.8</v>
       </c>
-      <c r="C2" s="13">
+      <c r="C2" s="11">
         <v>7</v>
       </c>
-      <c r="D2" s="12">
-        <v>44.4</v>
-      </c>
-      <c r="E2" s="12">
+      <c r="D2" s="10">
+        <v>45.3</v>
+      </c>
+      <c r="E2" s="10">
         <v>70</v>
       </c>
-      <c r="F2" s="12">
+      <c r="F2" s="10">
         <v>-2.9</v>
       </c>
-      <c r="G2" s="12">
-        <v>1.8</v>
-      </c>
-      <c r="H2" s="12">
+      <c r="G2" s="10">
+        <v>1</v>
+      </c>
+      <c r="H2" s="10">
         <v>57</v>
       </c>
-      <c r="I2" s="12">
+      <c r="I2" s="10">
         <v>30</v>
       </c>
     </row>
@@ -3172,49 +2996,49 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:7">
-      <c r="A1" s="14" t="s">
+      <c r="A1" s="12" t="s">
         <v>37</v>
       </c>
-      <c r="B1" s="14" t="s">
+      <c r="B1" s="12" t="s">
         <v>41</v>
       </c>
-      <c r="C1" s="14" t="s">
+      <c r="C1" s="12" t="s">
         <v>38</v>
       </c>
-      <c r="D1" s="14" t="s">
+      <c r="D1" s="12" t="s">
         <v>42</v>
       </c>
-      <c r="E1" s="14" t="s">
+      <c r="E1" s="12" t="s">
+        <v>43</v>
+      </c>
+      <c r="F1" s="12" t="s">
         <v>40</v>
       </c>
-      <c r="F1" s="14" t="s">
-        <v>43</v>
-      </c>
-      <c r="G1" s="14" t="s">
+      <c r="G1" s="12" t="s">
         <v>39</v>
       </c>
     </row>
     <row r="2" spans="1:7">
-      <c r="A2" s="15">
-        <v>0.2768</v>
-      </c>
-      <c r="B2" s="15">
-        <v>0.2205</v>
-      </c>
-      <c r="C2" s="15">
-        <v>0.169</v>
-      </c>
-      <c r="D2" s="15">
-        <v>0.07339999999999999</v>
-      </c>
-      <c r="E2" s="15">
-        <v>0.0175</v>
-      </c>
-      <c r="F2" s="15">
-        <v>0.0064</v>
-      </c>
-      <c r="G2" s="15">
-        <v>-0.2555</v>
+      <c r="A2" s="13">
+        <v>0.2807</v>
+      </c>
+      <c r="B2" s="13">
+        <v>0.2124</v>
+      </c>
+      <c r="C2" s="13">
+        <v>0.1691</v>
+      </c>
+      <c r="D2" s="13">
+        <v>0.059</v>
+      </c>
+      <c r="E2" s="13">
+        <v>0.0116</v>
+      </c>
+      <c r="F2" s="13">
+        <v>0.0106</v>
+      </c>
+      <c r="G2" s="13">
+        <v>-0.2539</v>
       </c>
     </row>
   </sheetData>

--- a/BAJAJ_GROUP_Technical_Metrics.xlsx
+++ b/BAJAJ_GROUP_Technical_Metrics.xlsx
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="253" uniqueCount="64">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="268" uniqueCount="73">
   <si>
     <t>Symbol</t>
   </si>
@@ -172,7 +172,34 @@
     <t>▶  SIGNAL EVENTS (vs Previous Run)</t>
   </si>
   <si>
-    <t>No signal events detected since last run.</t>
+    <t>Signal</t>
+  </si>
+  <si>
+    <t>Change</t>
+  </si>
+  <si>
+    <t>Direction</t>
+  </si>
+  <si>
+    <t>Prev Value</t>
+  </si>
+  <si>
+    <t>Curr Value</t>
+  </si>
+  <si>
+    <t>RSI Momentum</t>
+  </si>
+  <si>
+    <t>48.1 → 59.1</t>
+  </si>
+  <si>
+    <t>🟢 BULLISH</t>
+  </si>
+  <si>
+    <t>48.1</t>
+  </si>
+  <si>
+    <t>59.1</t>
   </si>
   <si>
     <t>▶  NUMERIC METRIC CHANGES (vs Previous Run)</t>
@@ -258,14 +285,14 @@
     </font>
     <font>
       <sz val="11"/>
-      <color rgb="FF9C0006"/>
+      <color rgb="FF006100"/>
       <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
     </font>
     <font>
       <sz val="11"/>
-      <color rgb="FF006100"/>
+      <color rgb="FF9C0006"/>
       <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
@@ -298,13 +325,13 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFFFC7CE"/>
+        <fgColor rgb="FFC6EFCE"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFC6EFCE"/>
+        <fgColor rgb="FFFFC7CE"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -374,17 +401,18 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="14">
+  <cellXfs count="15">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="2" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="3" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
+    <xf numFmtId="0" fontId="4" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1"/>
+    <xf numFmtId="165" fontId="5" fillId="6" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="165" fontId="4" fillId="5" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="165" fontId="5" fillId="6" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="3" fillId="7" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
@@ -896,10 +924,10 @@
         <v>44</v>
       </c>
       <c r="C2">
-        <v>11460</v>
+        <v>11363</v>
       </c>
       <c r="D2">
-        <v>0.4</v>
+        <v>-0.85</v>
       </c>
       <c r="E2">
         <v>12361</v>
@@ -908,46 +936,46 @@
         <v>8506.780000000001</v>
       </c>
       <c r="G2">
-        <v>-7.29</v>
+        <v>-8.07</v>
       </c>
       <c r="H2">
-        <v>34.72</v>
+        <v>33.58</v>
       </c>
       <c r="I2">
-        <v>-1.87</v>
+        <v>-0.53</v>
       </c>
       <c r="J2">
-        <v>-2.82</v>
+        <v>-2.88</v>
       </c>
       <c r="K2">
-        <v>12.45</v>
+        <v>13.35</v>
       </c>
       <c r="L2">
-        <v>28.09</v>
+        <v>26.85</v>
       </c>
       <c r="M2">
-        <v>28.07</v>
+        <v>27.66</v>
       </c>
       <c r="N2">
         <v>85</v>
       </c>
       <c r="O2">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="P2">
-        <v>11478.2</v>
+        <v>11466</v>
       </c>
       <c r="Q2">
-        <v>11792.4</v>
+        <v>11770.55</v>
       </c>
       <c r="R2">
-        <v>11482.33</v>
+        <v>11501.97</v>
       </c>
       <c r="S2">
-        <v>10056.15</v>
+        <v>10068.59</v>
       </c>
       <c r="T2">
-        <v>13.96</v>
+        <v>12.86</v>
       </c>
       <c r="U2" t="s">
         <v>45</v>
@@ -962,43 +990,43 @@
         <v>3</v>
       </c>
       <c r="Y2">
-        <v>44.1</v>
+        <v>41.44</v>
       </c>
       <c r="Z2">
-        <v>-12.92</v>
+        <v>-33.38</v>
       </c>
       <c r="AA2">
-        <v>72.72</v>
+        <v>51.5</v>
       </c>
       <c r="AB2">
-        <v>-85.64</v>
+        <v>-84.88</v>
       </c>
       <c r="AC2">
-        <v>6.57</v>
+        <v>3.35</v>
       </c>
       <c r="AD2">
-        <v>8.529999999999999</v>
+        <v>6.61</v>
       </c>
       <c r="AE2">
-        <v>203.91</v>
+        <v>206.06</v>
       </c>
       <c r="AF2">
-        <v>-59.04</v>
+        <v>-31.02</v>
       </c>
       <c r="AG2">
-        <v>12286.91</v>
+        <v>12300.96</v>
       </c>
       <c r="AH2">
-        <v>11297.89</v>
+        <v>11240.14</v>
       </c>
       <c r="AI2">
-        <v>12103.24</v>
+        <v>12016.18</v>
       </c>
       <c r="AJ2" t="s">
         <v>47</v>
       </c>
       <c r="AK2">
-        <v>33.9</v>
+        <v>37.35</v>
       </c>
     </row>
     <row r="3" spans="1:37">
@@ -1009,10 +1037,10 @@
         <v>44</v>
       </c>
       <c r="C3">
-        <v>515.3</v>
+        <v>513.75</v>
       </c>
       <c r="D3">
-        <v>0.62</v>
+        <v>-0.3</v>
       </c>
       <c r="E3">
         <v>670.25</v>
@@ -1021,46 +1049,46 @@
         <v>232.89</v>
       </c>
       <c r="G3">
-        <v>-23.12</v>
+        <v>-23.35</v>
       </c>
       <c r="H3">
-        <v>121.26</v>
+        <v>120.6</v>
       </c>
       <c r="I3">
-        <v>-1</v>
+        <v>1.97</v>
       </c>
       <c r="J3">
-        <v>5.82</v>
+        <v>7.4</v>
       </c>
       <c r="K3">
-        <v>-16.85</v>
+        <v>-11.66</v>
       </c>
       <c r="L3">
-        <v>125.87</v>
+        <v>116.37</v>
       </c>
       <c r="M3">
-        <v>16.91</v>
+        <v>16.82</v>
       </c>
       <c r="N3">
         <v>99</v>
       </c>
       <c r="O3">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="P3">
-        <v>506.35</v>
+        <v>508.34</v>
       </c>
       <c r="Q3">
-        <v>495.26</v>
+        <v>497.78</v>
       </c>
       <c r="R3">
-        <v>518.5700000000001</v>
+        <v>515.63</v>
       </c>
       <c r="S3">
-        <v>442.68</v>
+        <v>443.88</v>
       </c>
       <c r="T3">
-        <v>16.4</v>
+        <v>15.74</v>
       </c>
       <c r="U3" t="s">
         <v>46</v>
@@ -1075,34 +1103,34 @@
         <v>2</v>
       </c>
       <c r="Y3">
-        <v>52.88</v>
+        <v>52.23</v>
       </c>
       <c r="Z3">
-        <v>-0.19</v>
+        <v>0.31</v>
       </c>
       <c r="AA3">
-        <v>-3.46</v>
+        <v>-2.71</v>
       </c>
       <c r="AB3">
-        <v>3.27</v>
+        <v>3.02</v>
       </c>
       <c r="AC3">
-        <v>65.44</v>
+        <v>69.84</v>
       </c>
       <c r="AD3">
-        <v>61.59</v>
+        <v>65.11</v>
       </c>
       <c r="AE3">
-        <v>20.81</v>
+        <v>20.26</v>
       </c>
       <c r="AF3">
-        <v>-36.72</v>
+        <v>-49.75</v>
       </c>
       <c r="AG3">
-        <v>545.63</v>
+        <v>546.42</v>
       </c>
       <c r="AH3">
-        <v>444.88</v>
+        <v>449.14</v>
       </c>
       <c r="AI3">
         <v>460.99</v>
@@ -1111,7 +1139,7 @@
         <v>48</v>
       </c>
       <c r="AK3">
-        <v>25.46</v>
+        <v>25.84</v>
       </c>
     </row>
     <row r="4" spans="1:37">
@@ -1122,58 +1150,58 @@
         <v>44</v>
       </c>
       <c r="C4">
-        <v>326</v>
+        <v>323.45</v>
       </c>
       <c r="D4">
-        <v>0.91</v>
+        <v>-0.78</v>
       </c>
       <c r="E4">
-        <v>604.85</v>
+        <v>597.3</v>
       </c>
       <c r="F4">
         <v>303.75</v>
       </c>
       <c r="G4">
-        <v>-46.1</v>
+        <v>-45.85</v>
       </c>
       <c r="H4">
-        <v>7.33</v>
+        <v>6.49</v>
       </c>
       <c r="I4">
-        <v>-2.77</v>
+        <v>-1.51</v>
       </c>
       <c r="J4">
-        <v>-8</v>
+        <v>-8.02</v>
       </c>
       <c r="K4">
-        <v>-1.29</v>
+        <v>0.08</v>
       </c>
       <c r="L4">
-        <v>-44.97</v>
+        <v>-46.52</v>
       </c>
       <c r="M4">
-        <v>-25.39</v>
+        <v>-25.46</v>
       </c>
       <c r="N4">
         <v>15</v>
       </c>
       <c r="O4">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="P4">
-        <v>325.06</v>
+        <v>324.07</v>
       </c>
       <c r="Q4">
-        <v>332.35</v>
+        <v>331.29</v>
       </c>
       <c r="R4">
-        <v>339.69</v>
+        <v>339.43</v>
       </c>
       <c r="S4">
-        <v>374.52</v>
+        <v>373.73</v>
       </c>
       <c r="T4">
-        <v>-12.96</v>
+        <v>-13.45</v>
       </c>
       <c r="U4" t="s">
         <v>46</v>
@@ -1188,34 +1216,34 @@
         <v>0</v>
       </c>
       <c r="Y4">
-        <v>42.2</v>
+        <v>40.41</v>
       </c>
       <c r="Z4">
-        <v>-4.58</v>
+        <v>-4.78</v>
       </c>
       <c r="AA4">
-        <v>-3.47</v>
+        <v>-3.74</v>
       </c>
       <c r="AB4">
-        <v>-1.1</v>
+        <v>-1.04</v>
       </c>
       <c r="AC4">
-        <v>27.58</v>
+        <v>26.8</v>
       </c>
       <c r="AD4">
-        <v>23.38</v>
+        <v>24.3</v>
       </c>
       <c r="AE4">
-        <v>9.880000000000001</v>
+        <v>9.710000000000001</v>
       </c>
       <c r="AF4">
-        <v>-31.78</v>
+        <v>-46.14</v>
       </c>
       <c r="AG4">
-        <v>346.45</v>
+        <v>344.66</v>
       </c>
       <c r="AH4">
-        <v>318.25</v>
+        <v>317.91</v>
       </c>
       <c r="AI4">
         <v>354.2</v>
@@ -1224,7 +1252,7 @@
         <v>47</v>
       </c>
       <c r="AK4">
-        <v>17.47</v>
+        <v>15.27</v>
       </c>
     </row>
     <row r="5" spans="1:37">
@@ -1235,10 +1263,10 @@
         <v>44</v>
       </c>
       <c r="C5">
-        <v>1849.8</v>
+        <v>1823.4</v>
       </c>
       <c r="D5">
-        <v>-0.15</v>
+        <v>-1.43</v>
       </c>
       <c r="E5">
         <v>2176.6</v>
@@ -1247,46 +1275,46 @@
         <v>1631.8</v>
       </c>
       <c r="G5">
-        <v>-15.01</v>
+        <v>-16.23</v>
       </c>
       <c r="H5">
-        <v>13.36</v>
+        <v>11.74</v>
       </c>
       <c r="I5">
-        <v>-3.33</v>
+        <v>-1.73</v>
       </c>
       <c r="J5">
-        <v>-8.24</v>
+        <v>-10.29</v>
       </c>
       <c r="K5">
-        <v>3.79</v>
+        <v>3.31</v>
       </c>
       <c r="L5">
-        <v>-11.08</v>
+        <v>-11.36</v>
       </c>
       <c r="M5">
-        <v>1.06</v>
+        <v>0.73</v>
       </c>
       <c r="N5">
         <v>29</v>
       </c>
       <c r="O5">
-        <v>52</v>
+        <v>50</v>
       </c>
       <c r="P5">
-        <v>1850.8</v>
+        <v>1844.38</v>
       </c>
       <c r="Q5">
-        <v>1944.27</v>
+        <v>1935.36</v>
       </c>
       <c r="R5">
-        <v>1957.58</v>
+        <v>1955.89</v>
       </c>
       <c r="S5">
-        <v>1896.55</v>
+        <v>1895.44</v>
       </c>
       <c r="T5">
-        <v>-2.47</v>
+        <v>-3.8</v>
       </c>
       <c r="U5" t="s">
         <v>46</v>
@@ -1301,43 +1329,43 @@
         <v>1</v>
       </c>
       <c r="Y5">
-        <v>32.25</v>
+        <v>28.99</v>
       </c>
       <c r="Z5">
-        <v>-34.41</v>
+        <v>-37.79</v>
       </c>
       <c r="AA5">
-        <v>-19.45</v>
+        <v>-23.12</v>
       </c>
       <c r="AB5">
-        <v>-14.96</v>
+        <v>-14.67</v>
       </c>
       <c r="AC5">
-        <v>18.27</v>
+        <v>13.71</v>
       </c>
       <c r="AD5">
-        <v>12.12</v>
+        <v>14.58</v>
       </c>
       <c r="AE5">
-        <v>35</v>
+        <v>35.33</v>
       </c>
       <c r="AF5">
-        <v>-53.99</v>
+        <v>-30.17</v>
       </c>
       <c r="AG5">
-        <v>2070.74</v>
+        <v>2069.68</v>
       </c>
       <c r="AH5">
-        <v>1817.81</v>
+        <v>1801.04</v>
       </c>
       <c r="AI5">
-        <v>1961</v>
+        <v>1949.18</v>
       </c>
       <c r="AJ5" t="s">
         <v>47</v>
       </c>
       <c r="AK5">
-        <v>63.69</v>
+        <v>65.55</v>
       </c>
     </row>
     <row r="6" spans="1:37">
@@ -1348,58 +1376,58 @@
         <v>44</v>
       </c>
       <c r="C6">
-        <v>11409</v>
+        <v>11185</v>
       </c>
       <c r="D6">
-        <v>1.13</v>
+        <v>-1.96</v>
       </c>
       <c r="E6">
-        <v>13595.75</v>
+        <v>13400.71</v>
       </c>
       <c r="F6">
         <v>8746</v>
       </c>
       <c r="G6">
-        <v>-16.08</v>
+        <v>-16.53</v>
       </c>
       <c r="H6">
-        <v>30.45</v>
+        <v>27.89</v>
       </c>
       <c r="I6">
-        <v>2.47</v>
+        <v>0.77</v>
       </c>
       <c r="J6">
-        <v>0.36</v>
+        <v>-1.19</v>
       </c>
       <c r="K6">
-        <v>4.72</v>
+        <v>5.37</v>
       </c>
       <c r="L6">
-        <v>-15.23</v>
+        <v>-17.73</v>
       </c>
       <c r="M6">
-        <v>21.24</v>
+        <v>20.57</v>
       </c>
       <c r="N6">
         <v>43</v>
       </c>
       <c r="O6">
-        <v>53</v>
+        <v>50</v>
       </c>
       <c r="P6">
-        <v>11146.2</v>
+        <v>11163.2</v>
       </c>
       <c r="Q6">
-        <v>11200.35</v>
+        <v>11203.6</v>
       </c>
       <c r="R6">
-        <v>11111.42</v>
+        <v>11120.08</v>
       </c>
       <c r="S6">
-        <v>10681.88</v>
+        <v>10681.69</v>
       </c>
       <c r="T6">
-        <v>6.81</v>
+        <v>4.71</v>
       </c>
       <c r="U6" t="s">
         <v>45</v>
@@ -1414,34 +1442,34 @@
         <v>3</v>
       </c>
       <c r="Y6">
-        <v>56.88</v>
+        <v>50.29</v>
       </c>
       <c r="Z6">
-        <v>-6.11</v>
+        <v>-4.41</v>
       </c>
       <c r="AA6">
-        <v>-12</v>
+        <v>-10.48</v>
       </c>
       <c r="AB6">
-        <v>5.89</v>
+        <v>6.07</v>
       </c>
       <c r="AC6">
-        <v>58.41</v>
+        <v>70.89</v>
       </c>
       <c r="AD6">
-        <v>32.76</v>
+        <v>51.58</v>
       </c>
       <c r="AE6">
-        <v>225.53</v>
+        <v>231.28</v>
       </c>
       <c r="AF6">
-        <v>25.09</v>
+        <v>60.33</v>
       </c>
       <c r="AG6">
-        <v>11591.4</v>
+        <v>11592.91</v>
       </c>
       <c r="AH6">
-        <v>10809.3</v>
+        <v>10814.29</v>
       </c>
       <c r="AI6">
         <v>10787.84</v>
@@ -1450,7 +1478,7 @@
         <v>48</v>
       </c>
       <c r="AK6">
-        <v>20.99</v>
+        <v>19.19</v>
       </c>
     </row>
     <row r="7" spans="1:37">
@@ -1461,10 +1489,10 @@
         <v>44</v>
       </c>
       <c r="C7">
-        <v>1021.3</v>
+        <v>1008.8</v>
       </c>
       <c r="D7">
-        <v>-1.83</v>
+        <v>-1.22</v>
       </c>
       <c r="E7">
         <v>1158.8</v>
@@ -1473,46 +1501,46 @@
         <v>801.55</v>
       </c>
       <c r="G7">
-        <v>-11.87</v>
+        <v>-12.94</v>
       </c>
       <c r="H7">
-        <v>27.42</v>
+        <v>25.86</v>
       </c>
       <c r="I7">
-        <v>-1.28</v>
+        <v>-0.04</v>
       </c>
       <c r="J7">
-        <v>-6.73</v>
+        <v>-7.87</v>
       </c>
       <c r="K7">
-        <v>5.47</v>
+        <v>4.82</v>
       </c>
       <c r="L7">
-        <v>1.8</v>
+        <v>0.13</v>
       </c>
       <c r="M7">
-        <v>5.9</v>
+        <v>5.7</v>
       </c>
       <c r="N7">
-        <v>71</v>
+        <v>57</v>
       </c>
       <c r="O7">
-        <v>63</v>
+        <v>60</v>
       </c>
       <c r="P7">
-        <v>1018.4</v>
+        <v>1018.32</v>
       </c>
       <c r="Q7">
-        <v>1050.6</v>
+        <v>1047.19</v>
       </c>
       <c r="R7">
-        <v>1067.06</v>
+        <v>1066.79</v>
       </c>
       <c r="S7">
-        <v>977.71</v>
+        <v>977.65</v>
       </c>
       <c r="T7">
-        <v>4.46</v>
+        <v>3.19</v>
       </c>
       <c r="U7" t="s">
         <v>46</v>
@@ -1527,34 +1555,34 @@
         <v>2</v>
       </c>
       <c r="Y7">
-        <v>40.55</v>
+        <v>37.45</v>
       </c>
       <c r="Z7">
-        <v>-14.09</v>
+        <v>-15.16</v>
       </c>
       <c r="AA7">
-        <v>-10.4</v>
+        <v>-11.35</v>
       </c>
       <c r="AB7">
-        <v>-3.69</v>
+        <v>-3.81</v>
       </c>
       <c r="AC7">
-        <v>62.23</v>
+        <v>69.15000000000001</v>
       </c>
       <c r="AD7">
-        <v>36.87</v>
+        <v>57.41</v>
       </c>
       <c r="AE7">
-        <v>21.16</v>
+        <v>21.37</v>
       </c>
       <c r="AF7">
-        <v>-19.85</v>
+        <v>-9.84</v>
       </c>
       <c r="AG7">
-        <v>1100.4</v>
+        <v>1098.69</v>
       </c>
       <c r="AH7">
-        <v>1000.8</v>
+        <v>995.6900000000001</v>
       </c>
       <c r="AI7">
         <v>1075.64</v>
@@ -1563,7 +1591,7 @@
         <v>47</v>
       </c>
       <c r="AK7">
-        <v>38.45</v>
+        <v>38.33</v>
       </c>
     </row>
     <row r="8" spans="1:37">
@@ -1574,10 +1602,10 @@
         <v>44</v>
       </c>
       <c r="C8">
-        <v>136.03</v>
+        <v>141.41</v>
       </c>
       <c r="D8">
-        <v>0.93</v>
+        <v>3.96</v>
       </c>
       <c r="E8">
         <v>148.95</v>
@@ -1586,46 +1614,46 @@
         <v>115.96</v>
       </c>
       <c r="G8">
-        <v>-8.67</v>
+        <v>-5.06</v>
       </c>
       <c r="H8">
-        <v>17.31</v>
+        <v>21.95</v>
       </c>
       <c r="I8">
-        <v>-2.47</v>
+        <v>4.27</v>
       </c>
       <c r="J8">
-        <v>-0.68</v>
+        <v>3.06</v>
       </c>
       <c r="K8">
-        <v>-1.18</v>
+        <v>4.61</v>
       </c>
       <c r="L8">
-        <v>-2.35</v>
+        <v>2.56</v>
       </c>
       <c r="M8">
-        <v>1.16</v>
+        <v>2.07</v>
       </c>
       <c r="N8">
-        <v>57</v>
+        <v>71</v>
       </c>
       <c r="O8">
-        <v>58</v>
+        <v>67</v>
       </c>
       <c r="P8">
-        <v>135.1</v>
+        <v>136.26</v>
       </c>
       <c r="Q8">
-        <v>136.41</v>
+        <v>136.69</v>
       </c>
       <c r="R8">
-        <v>138.48</v>
+        <v>138.59</v>
       </c>
       <c r="S8">
-        <v>133.83</v>
+        <v>133.87</v>
       </c>
       <c r="T8">
-        <v>1.64</v>
+        <v>5.63</v>
       </c>
       <c r="U8" t="s">
         <v>46</v>
@@ -1640,34 +1668,34 @@
         <v>2</v>
       </c>
       <c r="Y8">
-        <v>48.06</v>
+        <v>59.15</v>
       </c>
       <c r="Z8">
-        <v>-0.45</v>
+        <v>-0.01</v>
       </c>
       <c r="AA8">
-        <v>-0.33</v>
+        <v>-0.27</v>
       </c>
       <c r="AB8">
-        <v>-0.12</v>
+        <v>0.25</v>
       </c>
       <c r="AC8">
-        <v>28.6</v>
+        <v>49.62</v>
       </c>
       <c r="AD8">
-        <v>26.16</v>
+        <v>34.11</v>
       </c>
       <c r="AE8">
-        <v>4.25</v>
+        <v>4.45</v>
       </c>
       <c r="AF8">
-        <v>-34.09</v>
+        <v>149.29</v>
       </c>
       <c r="AG8">
-        <v>140.9</v>
+        <v>141.69</v>
       </c>
       <c r="AH8">
-        <v>131.92</v>
+        <v>131.7</v>
       </c>
       <c r="AI8">
         <v>131.91</v>
@@ -1676,7 +1704,7 @@
         <v>48</v>
       </c>
       <c r="AK8">
-        <v>21.87</v>
+        <v>23.08</v>
       </c>
     </row>
   </sheetData>
@@ -1817,7 +1845,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:F62"/>
+  <dimension ref="A1:F64"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="16.7109375" customWidth="1"/>
@@ -1837,12 +1865,47 @@
     </row>
     <row r="2" spans="1:6">
       <c r="A2" s="3" t="s">
+        <v>0</v>
+      </c>
+      <c r="B2" s="3" t="s">
         <v>50</v>
+      </c>
+      <c r="C2" s="3" t="s">
+        <v>51</v>
+      </c>
+      <c r="D2" s="3" t="s">
+        <v>52</v>
+      </c>
+      <c r="E2" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="F2" s="3" t="s">
+        <v>54</v>
+      </c>
+    </row>
+    <row r="3" spans="1:6">
+      <c r="A3" s="4" t="s">
+        <v>43</v>
+      </c>
+      <c r="B3" s="4" t="s">
+        <v>55</v>
+      </c>
+      <c r="C3" s="4" t="s">
+        <v>56</v>
+      </c>
+      <c r="D3" s="4" t="s">
+        <v>57</v>
+      </c>
+      <c r="E3" s="4" t="s">
+        <v>58</v>
+      </c>
+      <c r="F3" s="4" t="s">
+        <v>59</v>
       </c>
     </row>
     <row r="5" spans="1:6">
       <c r="A5" s="2" t="s">
-        <v>51</v>
+        <v>60</v>
       </c>
       <c r="B5" s="2"/>
       <c r="C5" s="2"/>
@@ -1850,972 +1913,1006 @@
       <c r="E5" s="2"/>
     </row>
     <row r="6" spans="1:6">
-      <c r="A6" s="4" t="s">
+      <c r="A6" s="3" t="s">
         <v>0</v>
       </c>
-      <c r="B6" s="4" t="s">
-        <v>52</v>
-      </c>
-      <c r="C6" s="4" t="s">
-        <v>53</v>
-      </c>
-      <c r="D6" s="4" t="s">
-        <v>54</v>
-      </c>
-      <c r="E6" s="4" t="s">
-        <v>55</v>
+      <c r="B6" s="3" t="s">
+        <v>61</v>
+      </c>
+      <c r="C6" s="3" t="s">
+        <v>62</v>
+      </c>
+      <c r="D6" s="3" t="s">
+        <v>63</v>
+      </c>
+      <c r="E6" s="3" t="s">
+        <v>64</v>
       </c>
     </row>
     <row r="7" spans="1:6">
-      <c r="A7" s="3" t="s">
+      <c r="A7" s="5" t="s">
         <v>37</v>
       </c>
-      <c r="B7" s="3" t="s">
+      <c r="B7" s="5" t="s">
         <v>9</v>
       </c>
-      <c r="C7" s="5">
-        <v>-1.98</v>
-      </c>
-      <c r="D7" s="5">
+      <c r="C7" s="6">
         <v>-2.82</v>
       </c>
-      <c r="E7" s="6">
-        <v>-0.84</v>
+      <c r="D7" s="6">
+        <v>-2.88</v>
+      </c>
+      <c r="E7" s="7">
+        <v>-0.06</v>
       </c>
     </row>
     <row r="8" spans="1:6">
-      <c r="A8" s="3" t="s">
+      <c r="A8" s="5" t="s">
         <v>38</v>
       </c>
-      <c r="B8" s="3" t="s">
+      <c r="B8" s="5" t="s">
         <v>9</v>
       </c>
-      <c r="C8" s="5">
-        <v>2.29</v>
-      </c>
-      <c r="D8" s="5">
+      <c r="C8" s="6">
         <v>5.82</v>
       </c>
-      <c r="E8" s="7">
-        <v>3.53</v>
+      <c r="D8" s="6">
+        <v>7.4</v>
+      </c>
+      <c r="E8" s="8">
+        <v>1.58</v>
       </c>
     </row>
     <row r="9" spans="1:6">
-      <c r="A9" s="3" t="s">
+      <c r="A9" s="5" t="s">
         <v>39</v>
       </c>
-      <c r="B9" s="3" t="s">
+      <c r="B9" s="5" t="s">
         <v>9</v>
       </c>
-      <c r="C9" s="5">
-        <v>-8.630000000000001</v>
-      </c>
-      <c r="D9" s="5">
+      <c r="C9" s="6">
         <v>-8</v>
       </c>
+      <c r="D9" s="6">
+        <v>-8.02</v>
+      </c>
       <c r="E9" s="7">
-        <v>0.63</v>
+        <v>-0.02</v>
       </c>
     </row>
     <row r="10" spans="1:6">
-      <c r="A10" s="3" t="s">
+      <c r="A10" s="5" t="s">
         <v>40</v>
       </c>
-      <c r="B10" s="3" t="s">
+      <c r="B10" s="5" t="s">
         <v>9</v>
       </c>
-      <c r="C10" s="5">
-        <v>-7.93</v>
-      </c>
-      <c r="D10" s="5">
+      <c r="C10" s="6">
         <v>-8.24</v>
       </c>
-      <c r="E10" s="6">
-        <v>-0.31</v>
+      <c r="D10" s="6">
+        <v>-10.29</v>
+      </c>
+      <c r="E10" s="7">
+        <v>-2.05</v>
       </c>
     </row>
     <row r="11" spans="1:6">
-      <c r="A11" s="3" t="s">
+      <c r="A11" s="5" t="s">
         <v>41</v>
       </c>
-      <c r="B11" s="3" t="s">
+      <c r="B11" s="5" t="s">
         <v>9</v>
       </c>
-      <c r="C11" s="5">
-        <v>-0.86</v>
-      </c>
-      <c r="D11" s="5">
+      <c r="C11" s="6">
         <v>0.36</v>
       </c>
+      <c r="D11" s="6">
+        <v>-1.19</v>
+      </c>
       <c r="E11" s="7">
-        <v>1.22</v>
+        <v>-1.55</v>
       </c>
     </row>
     <row r="12" spans="1:6">
-      <c r="A12" s="3" t="s">
+      <c r="A12" s="5" t="s">
         <v>42</v>
       </c>
-      <c r="B12" s="3" t="s">
+      <c r="B12" s="5" t="s">
         <v>9</v>
       </c>
-      <c r="C12" s="5">
-        <v>-3.69</v>
-      </c>
-      <c r="D12" s="5">
+      <c r="C12" s="6">
         <v>-6.73</v>
       </c>
-      <c r="E12" s="6">
-        <v>-3.04</v>
+      <c r="D12" s="6">
+        <v>-7.87</v>
+      </c>
+      <c r="E12" s="7">
+        <v>-1.14</v>
       </c>
     </row>
     <row r="13" spans="1:6">
-      <c r="A13" s="3" t="s">
+      <c r="A13" s="5" t="s">
         <v>43</v>
       </c>
-      <c r="B13" s="3" t="s">
+      <c r="B13" s="5" t="s">
         <v>9</v>
       </c>
-      <c r="C13" s="5">
-        <v>0.16</v>
-      </c>
-      <c r="D13" s="5">
+      <c r="C13" s="6">
         <v>-0.68</v>
       </c>
-      <c r="E13" s="6">
-        <v>-0.84</v>
+      <c r="D13" s="6">
+        <v>3.06</v>
+      </c>
+      <c r="E13" s="8">
+        <v>3.74</v>
       </c>
     </row>
     <row r="14" spans="1:6">
-      <c r="A14" s="3" t="s">
+      <c r="A14" s="5" t="s">
         <v>37</v>
       </c>
-      <c r="B14" s="3" t="s">
+      <c r="B14" s="5" t="s">
         <v>8</v>
       </c>
-      <c r="C14" s="5">
-        <v>-3.01</v>
-      </c>
-      <c r="D14" s="5">
+      <c r="C14" s="6">
         <v>-1.87</v>
       </c>
-      <c r="E14" s="7">
-        <v>1.14</v>
+      <c r="D14" s="6">
+        <v>-0.53</v>
+      </c>
+      <c r="E14" s="8">
+        <v>1.34</v>
       </c>
     </row>
     <row r="15" spans="1:6">
-      <c r="A15" s="3" t="s">
+      <c r="A15" s="5" t="s">
         <v>38</v>
       </c>
-      <c r="B15" s="3" t="s">
+      <c r="B15" s="5" t="s">
         <v>8</v>
       </c>
-      <c r="C15" s="5">
+      <c r="C15" s="6">
+        <v>-1</v>
+      </c>
+      <c r="D15" s="6">
+        <v>1.97</v>
+      </c>
+      <c r="E15" s="8">
+        <v>2.97</v>
+      </c>
+    </row>
+    <row r="16" spans="1:6">
+      <c r="A16" s="5" t="s">
+        <v>39</v>
+      </c>
+      <c r="B16" s="5" t="s">
+        <v>8</v>
+      </c>
+      <c r="C16" s="6">
+        <v>-2.77</v>
+      </c>
+      <c r="D16" s="6">
+        <v>-1.51</v>
+      </c>
+      <c r="E16" s="8">
+        <v>1.26</v>
+      </c>
+    </row>
+    <row r="17" spans="1:5">
+      <c r="A17" s="5" t="s">
+        <v>40</v>
+      </c>
+      <c r="B17" s="5" t="s">
+        <v>8</v>
+      </c>
+      <c r="C17" s="6">
+        <v>-3.33</v>
+      </c>
+      <c r="D17" s="6">
+        <v>-1.73</v>
+      </c>
+      <c r="E17" s="8">
+        <v>1.6</v>
+      </c>
+    </row>
+    <row r="18" spans="1:5">
+      <c r="A18" s="5" t="s">
+        <v>41</v>
+      </c>
+      <c r="B18" s="5" t="s">
+        <v>8</v>
+      </c>
+      <c r="C18" s="6">
+        <v>2.47</v>
+      </c>
+      <c r="D18" s="6">
+        <v>0.77</v>
+      </c>
+      <c r="E18" s="7">
+        <v>-1.7</v>
+      </c>
+    </row>
+    <row r="19" spans="1:5">
+      <c r="A19" s="5" t="s">
+        <v>42</v>
+      </c>
+      <c r="B19" s="5" t="s">
+        <v>8</v>
+      </c>
+      <c r="C19" s="6">
+        <v>-1.28</v>
+      </c>
+      <c r="D19" s="6">
+        <v>-0.04</v>
+      </c>
+      <c r="E19" s="8">
+        <v>1.24</v>
+      </c>
+    </row>
+    <row r="20" spans="1:5">
+      <c r="A20" s="5" t="s">
+        <v>43</v>
+      </c>
+      <c r="B20" s="5" t="s">
+        <v>8</v>
+      </c>
+      <c r="C20" s="6">
+        <v>-2.47</v>
+      </c>
+      <c r="D20" s="6">
+        <v>4.27</v>
+      </c>
+      <c r="E20" s="8">
+        <v>6.74</v>
+      </c>
+    </row>
+    <row r="21" spans="1:5">
+      <c r="A21" s="5" t="s">
+        <v>37</v>
+      </c>
+      <c r="B21" s="5" t="s">
+        <v>11</v>
+      </c>
+      <c r="C21" s="6">
+        <v>28.09</v>
+      </c>
+      <c r="D21" s="6">
+        <v>26.85</v>
+      </c>
+      <c r="E21" s="7">
+        <v>-1.24</v>
+      </c>
+    </row>
+    <row r="22" spans="1:5">
+      <c r="A22" s="5" t="s">
+        <v>38</v>
+      </c>
+      <c r="B22" s="5" t="s">
+        <v>11</v>
+      </c>
+      <c r="C22" s="6">
+        <v>125.87</v>
+      </c>
+      <c r="D22" s="6">
+        <v>116.37</v>
+      </c>
+      <c r="E22" s="7">
+        <v>-9.5</v>
+      </c>
+    </row>
+    <row r="23" spans="1:5">
+      <c r="A23" s="5" t="s">
+        <v>39</v>
+      </c>
+      <c r="B23" s="5" t="s">
+        <v>11</v>
+      </c>
+      <c r="C23" s="6">
+        <v>-44.97</v>
+      </c>
+      <c r="D23" s="6">
+        <v>-46.52</v>
+      </c>
+      <c r="E23" s="7">
+        <v>-1.55</v>
+      </c>
+    </row>
+    <row r="24" spans="1:5">
+      <c r="A24" s="5" t="s">
+        <v>40</v>
+      </c>
+      <c r="B24" s="5" t="s">
+        <v>11</v>
+      </c>
+      <c r="C24" s="6">
+        <v>-11.08</v>
+      </c>
+      <c r="D24" s="6">
+        <v>-11.36</v>
+      </c>
+      <c r="E24" s="7">
+        <v>-0.28</v>
+      </c>
+    </row>
+    <row r="25" spans="1:5">
+      <c r="A25" s="5" t="s">
+        <v>41</v>
+      </c>
+      <c r="B25" s="5" t="s">
+        <v>11</v>
+      </c>
+      <c r="C25" s="6">
+        <v>-15.23</v>
+      </c>
+      <c r="D25" s="6">
+        <v>-17.73</v>
+      </c>
+      <c r="E25" s="7">
+        <v>-2.5</v>
+      </c>
+    </row>
+    <row r="26" spans="1:5">
+      <c r="A26" s="5" t="s">
+        <v>42</v>
+      </c>
+      <c r="B26" s="5" t="s">
+        <v>11</v>
+      </c>
+      <c r="C26" s="6">
+        <v>1.8</v>
+      </c>
+      <c r="D26" s="6">
+        <v>0.13</v>
+      </c>
+      <c r="E26" s="7">
+        <v>-1.67</v>
+      </c>
+    </row>
+    <row r="27" spans="1:5">
+      <c r="A27" s="5" t="s">
+        <v>43</v>
+      </c>
+      <c r="B27" s="5" t="s">
+        <v>11</v>
+      </c>
+      <c r="C27" s="6">
         <v>-2.35</v>
       </c>
-      <c r="D15" s="5">
-        <v>-1</v>
-      </c>
-      <c r="E15" s="7">
-        <v>1.35</v>
-      </c>
-    </row>
-    <row r="16" spans="1:6">
-      <c r="A16" s="3" t="s">
+      <c r="D27" s="6">
+        <v>2.56</v>
+      </c>
+      <c r="E27" s="8">
+        <v>4.91</v>
+      </c>
+    </row>
+    <row r="28" spans="1:5">
+      <c r="A28" s="5" t="s">
+        <v>37</v>
+      </c>
+      <c r="B28" s="5" t="s">
+        <v>10</v>
+      </c>
+      <c r="C28" s="6">
+        <v>12.45</v>
+      </c>
+      <c r="D28" s="6">
+        <v>13.35</v>
+      </c>
+      <c r="E28" s="8">
+        <v>0.9</v>
+      </c>
+    </row>
+    <row r="29" spans="1:5">
+      <c r="A29" s="5" t="s">
+        <v>38</v>
+      </c>
+      <c r="B29" s="5" t="s">
+        <v>10</v>
+      </c>
+      <c r="C29" s="6">
+        <v>-16.85</v>
+      </c>
+      <c r="D29" s="6">
+        <v>-11.66</v>
+      </c>
+      <c r="E29" s="8">
+        <v>5.19</v>
+      </c>
+    </row>
+    <row r="30" spans="1:5">
+      <c r="A30" s="5" t="s">
         <v>39</v>
       </c>
-      <c r="B16" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="C16" s="5">
-        <v>-4.35</v>
-      </c>
-      <c r="D16" s="5">
-        <v>-2.77</v>
-      </c>
-      <c r="E16" s="7">
-        <v>1.58</v>
-      </c>
-    </row>
-    <row r="17" spans="1:5">
-      <c r="A17" s="3" t="s">
+      <c r="B30" s="5" t="s">
+        <v>10</v>
+      </c>
+      <c r="C30" s="6">
+        <v>-1.29</v>
+      </c>
+      <c r="D30" s="6">
+        <v>0.08</v>
+      </c>
+      <c r="E30" s="8">
+        <v>1.37</v>
+      </c>
+    </row>
+    <row r="31" spans="1:5">
+      <c r="A31" s="5" t="s">
         <v>40</v>
       </c>
-      <c r="B17" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="C17" s="5">
-        <v>-4.53</v>
-      </c>
-      <c r="D17" s="5">
-        <v>-3.33</v>
-      </c>
-      <c r="E17" s="7">
-        <v>1.2</v>
-      </c>
-    </row>
-    <row r="18" spans="1:5">
-      <c r="A18" s="3" t="s">
+      <c r="B31" s="5" t="s">
+        <v>10</v>
+      </c>
+      <c r="C31" s="6">
+        <v>3.79</v>
+      </c>
+      <c r="D31" s="6">
+        <v>3.31</v>
+      </c>
+      <c r="E31" s="7">
+        <v>-0.48</v>
+      </c>
+    </row>
+    <row r="32" spans="1:5">
+      <c r="A32" s="5" t="s">
         <v>41</v>
       </c>
-      <c r="B18" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="C18" s="5">
-        <v>2.64</v>
-      </c>
-      <c r="D18" s="5">
-        <v>2.47</v>
-      </c>
-      <c r="E18" s="6">
-        <v>-0.17</v>
-      </c>
-    </row>
-    <row r="19" spans="1:5">
-      <c r="A19" s="3" t="s">
+      <c r="B32" s="5" t="s">
+        <v>10</v>
+      </c>
+      <c r="C32" s="6">
+        <v>4.72</v>
+      </c>
+      <c r="D32" s="6">
+        <v>5.37</v>
+      </c>
+      <c r="E32" s="8">
+        <v>0.65</v>
+      </c>
+    </row>
+    <row r="33" spans="1:5">
+      <c r="A33" s="5" t="s">
         <v>42</v>
       </c>
-      <c r="B19" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="C19" s="5">
-        <v>-0.31</v>
-      </c>
-      <c r="D19" s="5">
-        <v>-1.28</v>
-      </c>
-      <c r="E19" s="6">
-        <v>-0.97</v>
-      </c>
-    </row>
-    <row r="20" spans="1:5">
-      <c r="A20" s="3" t="s">
+      <c r="B33" s="5" t="s">
+        <v>10</v>
+      </c>
+      <c r="C33" s="6">
+        <v>5.47</v>
+      </c>
+      <c r="D33" s="6">
+        <v>4.82</v>
+      </c>
+      <c r="E33" s="7">
+        <v>-0.65</v>
+      </c>
+    </row>
+    <row r="34" spans="1:5">
+      <c r="A34" s="5" t="s">
         <v>43</v>
       </c>
-      <c r="B20" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="C20" s="5">
-        <v>-5.46</v>
-      </c>
-      <c r="D20" s="5">
-        <v>-2.47</v>
-      </c>
-      <c r="E20" s="7">
-        <v>2.99</v>
-      </c>
-    </row>
-    <row r="21" spans="1:5">
-      <c r="A21" s="3" t="s">
+      <c r="B34" s="5" t="s">
+        <v>10</v>
+      </c>
+      <c r="C34" s="6">
+        <v>-1.18</v>
+      </c>
+      <c r="D34" s="6">
+        <v>4.61</v>
+      </c>
+      <c r="E34" s="8">
+        <v>5.79</v>
+      </c>
+    </row>
+    <row r="35" spans="1:5">
+      <c r="A35" s="5" t="s">
         <v>37</v>
       </c>
-      <c r="B21" s="3" t="s">
-        <v>11</v>
-      </c>
-      <c r="C21" s="5">
-        <v>28.25</v>
-      </c>
-      <c r="D21" s="5">
-        <v>28.09</v>
-      </c>
-      <c r="E21" s="6">
-        <v>-0.16</v>
-      </c>
-    </row>
-    <row r="22" spans="1:5">
-      <c r="A22" s="3" t="s">
+      <c r="B35" s="5" t="s">
+        <v>6</v>
+      </c>
+      <c r="C35" s="6">
+        <v>-7.29</v>
+      </c>
+      <c r="D35" s="6">
+        <v>-8.07</v>
+      </c>
+      <c r="E35" s="7">
+        <v>-0.78</v>
+      </c>
+    </row>
+    <row r="36" spans="1:5">
+      <c r="A36" s="5" t="s">
         <v>38</v>
       </c>
-      <c r="B22" s="3" t="s">
-        <v>11</v>
-      </c>
-      <c r="C22" s="5">
-        <v>122.71</v>
-      </c>
-      <c r="D22" s="5">
-        <v>125.87</v>
-      </c>
-      <c r="E22" s="7">
-        <v>3.16</v>
-      </c>
-    </row>
-    <row r="23" spans="1:5">
-      <c r="A23" s="3" t="s">
+      <c r="B36" s="5" t="s">
+        <v>6</v>
+      </c>
+      <c r="C36" s="6">
+        <v>-23.12</v>
+      </c>
+      <c r="D36" s="6">
+        <v>-23.35</v>
+      </c>
+      <c r="E36" s="7">
+        <v>-0.23</v>
+      </c>
+    </row>
+    <row r="37" spans="1:5">
+      <c r="A37" s="5" t="s">
         <v>39</v>
       </c>
-      <c r="B23" s="3" t="s">
-        <v>11</v>
-      </c>
-      <c r="C23" s="5">
-        <v>-45.09</v>
-      </c>
-      <c r="D23" s="5">
-        <v>-44.97</v>
-      </c>
-      <c r="E23" s="7">
-        <v>0.12</v>
-      </c>
-    </row>
-    <row r="24" spans="1:5">
-      <c r="A24" s="3" t="s">
+      <c r="B37" s="5" t="s">
+        <v>6</v>
+      </c>
+      <c r="C37" s="6">
+        <v>-46.1</v>
+      </c>
+      <c r="D37" s="6">
+        <v>-45.85</v>
+      </c>
+      <c r="E37" s="8">
+        <v>0.25</v>
+      </c>
+    </row>
+    <row r="38" spans="1:5">
+      <c r="A38" s="5" t="s">
         <v>40</v>
       </c>
-      <c r="B24" s="3" t="s">
-        <v>11</v>
-      </c>
-      <c r="C24" s="5">
-        <v>-10.94</v>
-      </c>
-      <c r="D24" s="5">
-        <v>-11.08</v>
-      </c>
-      <c r="E24" s="6">
-        <v>-0.14</v>
-      </c>
-    </row>
-    <row r="25" spans="1:5">
-      <c r="A25" s="3" t="s">
+      <c r="B38" s="5" t="s">
+        <v>6</v>
+      </c>
+      <c r="C38" s="6">
+        <v>-15.01</v>
+      </c>
+      <c r="D38" s="6">
+        <v>-16.23</v>
+      </c>
+      <c r="E38" s="7">
+        <v>-1.22</v>
+      </c>
+    </row>
+    <row r="39" spans="1:5">
+      <c r="A39" s="5" t="s">
         <v>41</v>
       </c>
-      <c r="B25" s="3" t="s">
-        <v>11</v>
-      </c>
-      <c r="C25" s="5">
-        <v>-14.09</v>
-      </c>
-      <c r="D25" s="5">
-        <v>-15.23</v>
-      </c>
-      <c r="E25" s="6">
-        <v>-1.14</v>
-      </c>
-    </row>
-    <row r="26" spans="1:5">
-      <c r="A26" s="3" t="s">
+      <c r="B39" s="5" t="s">
+        <v>6</v>
+      </c>
+      <c r="C39" s="6">
+        <v>-16.08</v>
+      </c>
+      <c r="D39" s="6">
+        <v>-16.53</v>
+      </c>
+      <c r="E39" s="7">
+        <v>-0.45</v>
+      </c>
+    </row>
+    <row r="40" spans="1:5">
+      <c r="A40" s="5" t="s">
         <v>42</v>
       </c>
-      <c r="B26" s="3" t="s">
-        <v>11</v>
-      </c>
-      <c r="C26" s="5">
-        <v>3.02</v>
-      </c>
-      <c r="D26" s="5">
-        <v>1.8</v>
-      </c>
-      <c r="E26" s="6">
-        <v>-1.22</v>
-      </c>
-    </row>
-    <row r="27" spans="1:5">
-      <c r="A27" s="3" t="s">
+      <c r="B40" s="5" t="s">
+        <v>6</v>
+      </c>
+      <c r="C40" s="6">
+        <v>-11.87</v>
+      </c>
+      <c r="D40" s="6">
+        <v>-12.94</v>
+      </c>
+      <c r="E40" s="7">
+        <v>-1.07</v>
+      </c>
+    </row>
+    <row r="41" spans="1:5">
+      <c r="A41" s="5" t="s">
         <v>43</v>
       </c>
-      <c r="B27" s="3" t="s">
-        <v>11</v>
-      </c>
-      <c r="C27" s="5">
-        <v>-2.76</v>
-      </c>
-      <c r="D27" s="5">
-        <v>-2.35</v>
-      </c>
-      <c r="E27" s="7">
-        <v>0.41</v>
-      </c>
-    </row>
-    <row r="28" spans="1:5">
-      <c r="A28" s="3" t="s">
+      <c r="B41" s="5" t="s">
+        <v>6</v>
+      </c>
+      <c r="C41" s="6">
+        <v>-8.67</v>
+      </c>
+      <c r="D41" s="6">
+        <v>-5.06</v>
+      </c>
+      <c r="E41" s="8">
+        <v>3.61</v>
+      </c>
+    </row>
+    <row r="42" spans="1:5">
+      <c r="A42" s="5" t="s">
         <v>37</v>
       </c>
-      <c r="B28" s="3" t="s">
-        <v>10</v>
-      </c>
-      <c r="C28" s="5">
-        <v>13.39</v>
-      </c>
-      <c r="D28" s="5">
-        <v>12.45</v>
-      </c>
-      <c r="E28" s="6">
-        <v>-0.9399999999999999</v>
-      </c>
-    </row>
-    <row r="29" spans="1:5">
-      <c r="A29" s="3" t="s">
+      <c r="B42" s="5" t="s">
+        <v>2</v>
+      </c>
+      <c r="C42" s="6">
+        <v>11460</v>
+      </c>
+      <c r="D42" s="6">
+        <v>11363</v>
+      </c>
+      <c r="E42" s="7">
+        <v>-97</v>
+      </c>
+    </row>
+    <row r="43" spans="1:5">
+      <c r="A43" s="5" t="s">
         <v>38</v>
       </c>
-      <c r="B29" s="3" t="s">
-        <v>10</v>
-      </c>
-      <c r="C29" s="5">
-        <v>-18.09</v>
-      </c>
-      <c r="D29" s="5">
-        <v>-16.85</v>
-      </c>
-      <c r="E29" s="7">
-        <v>1.24</v>
-      </c>
-    </row>
-    <row r="30" spans="1:5">
-      <c r="A30" s="3" t="s">
+      <c r="B43" s="5" t="s">
+        <v>2</v>
+      </c>
+      <c r="C43" s="6">
+        <v>515.3</v>
+      </c>
+      <c r="D43" s="6">
+        <v>513.75</v>
+      </c>
+      <c r="E43" s="7">
+        <v>-1.55</v>
+      </c>
+    </row>
+    <row r="44" spans="1:5">
+      <c r="A44" s="5" t="s">
         <v>39</v>
       </c>
-      <c r="B30" s="3" t="s">
-        <v>10</v>
-      </c>
-      <c r="C30" s="5">
-        <v>-0.8</v>
-      </c>
-      <c r="D30" s="5">
-        <v>-1.29</v>
-      </c>
-      <c r="E30" s="6">
-        <v>-0.49</v>
-      </c>
-    </row>
-    <row r="31" spans="1:5">
-      <c r="A31" s="3" t="s">
+      <c r="B44" s="5" t="s">
+        <v>2</v>
+      </c>
+      <c r="C44" s="6">
+        <v>326</v>
+      </c>
+      <c r="D44" s="6">
+        <v>323.45</v>
+      </c>
+      <c r="E44" s="7">
+        <v>-2.55</v>
+      </c>
+    </row>
+    <row r="45" spans="1:5">
+      <c r="A45" s="5" t="s">
         <v>40</v>
       </c>
-      <c r="B31" s="3" t="s">
-        <v>10</v>
-      </c>
-      <c r="C31" s="5">
-        <v>4.7</v>
-      </c>
-      <c r="D31" s="5">
-        <v>3.79</v>
-      </c>
-      <c r="E31" s="6">
-        <v>-0.91</v>
-      </c>
-    </row>
-    <row r="32" spans="1:5">
-      <c r="A32" s="3" t="s">
+      <c r="B45" s="5" t="s">
+        <v>2</v>
+      </c>
+      <c r="C45" s="6">
+        <v>1849.8</v>
+      </c>
+      <c r="D45" s="6">
+        <v>1823.4</v>
+      </c>
+      <c r="E45" s="7">
+        <v>-26.4</v>
+      </c>
+    </row>
+    <row r="46" spans="1:5">
+      <c r="A46" s="5" t="s">
         <v>41</v>
       </c>
-      <c r="B32" s="3" t="s">
-        <v>10</v>
-      </c>
-      <c r="C32" s="5">
-        <v>5.67</v>
-      </c>
-      <c r="D32" s="5">
-        <v>4.72</v>
-      </c>
-      <c r="E32" s="6">
-        <v>-0.95</v>
-      </c>
-    </row>
-    <row r="33" spans="1:5">
-      <c r="A33" s="3" t="s">
+      <c r="B46" s="5" t="s">
+        <v>2</v>
+      </c>
+      <c r="C46" s="6">
+        <v>11409</v>
+      </c>
+      <c r="D46" s="6">
+        <v>11185</v>
+      </c>
+      <c r="E46" s="7">
+        <v>-224</v>
+      </c>
+    </row>
+    <row r="47" spans="1:5">
+      <c r="A47" s="5" t="s">
         <v>42</v>
       </c>
-      <c r="B33" s="3" t="s">
-        <v>10</v>
-      </c>
-      <c r="C33" s="5">
-        <v>8.16</v>
-      </c>
-      <c r="D33" s="5">
-        <v>5.47</v>
-      </c>
-      <c r="E33" s="6">
-        <v>-2.69</v>
-      </c>
-    </row>
-    <row r="34" spans="1:5">
-      <c r="A34" s="3" t="s">
+      <c r="B47" s="5" t="s">
+        <v>2</v>
+      </c>
+      <c r="C47" s="6">
+        <v>1021.3</v>
+      </c>
+      <c r="D47" s="6">
+        <v>1008.8</v>
+      </c>
+      <c r="E47" s="7">
+        <v>-12.5</v>
+      </c>
+    </row>
+    <row r="48" spans="1:5">
+      <c r="A48" s="5" t="s">
         <v>43</v>
       </c>
-      <c r="B34" s="3" t="s">
-        <v>10</v>
-      </c>
-      <c r="C34" s="5">
-        <v>-0.76</v>
-      </c>
-      <c r="D34" s="5">
-        <v>-1.18</v>
-      </c>
-      <c r="E34" s="6">
-        <v>-0.42</v>
-      </c>
-    </row>
-    <row r="35" spans="1:5">
-      <c r="A35" s="3" t="s">
+      <c r="B48" s="5" t="s">
+        <v>2</v>
+      </c>
+      <c r="C48" s="6">
+        <v>136.03</v>
+      </c>
+      <c r="D48" s="6">
+        <v>141.41</v>
+      </c>
+      <c r="E48" s="8">
+        <v>5.38</v>
+      </c>
+    </row>
+    <row r="49" spans="1:5">
+      <c r="A49" s="5" t="s">
+        <v>42</v>
+      </c>
+      <c r="B49" s="5" t="s">
+        <v>13</v>
+      </c>
+      <c r="C49" s="6">
+        <v>71</v>
+      </c>
+      <c r="D49" s="6">
+        <v>57</v>
+      </c>
+      <c r="E49" s="7">
+        <v>-14</v>
+      </c>
+    </row>
+    <row r="50" spans="1:5">
+      <c r="A50" s="5" t="s">
+        <v>43</v>
+      </c>
+      <c r="B50" s="5" t="s">
+        <v>13</v>
+      </c>
+      <c r="C50" s="6">
+        <v>57</v>
+      </c>
+      <c r="D50" s="6">
+        <v>71</v>
+      </c>
+      <c r="E50" s="8">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="51" spans="1:5">
+      <c r="A51" s="5" t="s">
         <v>37</v>
       </c>
-      <c r="B35" s="3" t="s">
-        <v>6</v>
-      </c>
-      <c r="C35" s="5">
-        <v>-7.66</v>
-      </c>
-      <c r="D35" s="5">
-        <v>-7.29</v>
-      </c>
-      <c r="E35" s="7">
-        <v>0.37</v>
-      </c>
-    </row>
-    <row r="36" spans="1:5">
-      <c r="A36" s="3" t="s">
+      <c r="B51" s="5" t="s">
+        <v>24</v>
+      </c>
+      <c r="C51" s="6">
+        <v>44.1</v>
+      </c>
+      <c r="D51" s="6">
+        <v>41.44</v>
+      </c>
+      <c r="E51" s="7">
+        <v>-2.66</v>
+      </c>
+    </row>
+    <row r="52" spans="1:5">
+      <c r="A52" s="5" t="s">
         <v>38</v>
       </c>
-      <c r="B36" s="3" t="s">
-        <v>6</v>
-      </c>
-      <c r="C36" s="5">
-        <v>-23.59</v>
-      </c>
-      <c r="D36" s="5">
-        <v>-23.12</v>
-      </c>
-      <c r="E36" s="7">
-        <v>0.47</v>
-      </c>
-    </row>
-    <row r="37" spans="1:5">
-      <c r="A37" s="3" t="s">
+      <c r="B52" s="5" t="s">
+        <v>24</v>
+      </c>
+      <c r="C52" s="6">
+        <v>52.88</v>
+      </c>
+      <c r="D52" s="6">
+        <v>52.23</v>
+      </c>
+      <c r="E52" s="7">
+        <v>-0.65</v>
+      </c>
+    </row>
+    <row r="53" spans="1:5">
+      <c r="A53" s="5" t="s">
         <v>39</v>
       </c>
-      <c r="B37" s="3" t="s">
-        <v>6</v>
-      </c>
-      <c r="C37" s="5">
-        <v>-46.59</v>
-      </c>
-      <c r="D37" s="5">
-        <v>-46.1</v>
-      </c>
-      <c r="E37" s="7">
-        <v>0.49</v>
-      </c>
-    </row>
-    <row r="38" spans="1:5">
-      <c r="A38" s="3" t="s">
+      <c r="B53" s="5" t="s">
+        <v>24</v>
+      </c>
+      <c r="C53" s="6">
+        <v>42.2</v>
+      </c>
+      <c r="D53" s="6">
+        <v>40.41</v>
+      </c>
+      <c r="E53" s="7">
+        <v>-1.79</v>
+      </c>
+    </row>
+    <row r="54" spans="1:5">
+      <c r="A54" s="5" t="s">
         <v>40</v>
       </c>
-      <c r="B38" s="3" t="s">
-        <v>6</v>
-      </c>
-      <c r="C38" s="5">
-        <v>-14.89</v>
-      </c>
-      <c r="D38" s="5">
-        <v>-15.01</v>
-      </c>
-      <c r="E38" s="6">
-        <v>-0.12</v>
-      </c>
-    </row>
-    <row r="39" spans="1:5">
-      <c r="A39" s="3" t="s">
+      <c r="B54" s="5" t="s">
+        <v>24</v>
+      </c>
+      <c r="C54" s="6">
+        <v>32.25</v>
+      </c>
+      <c r="D54" s="6">
+        <v>28.99</v>
+      </c>
+      <c r="E54" s="7">
+        <v>-3.26</v>
+      </c>
+    </row>
+    <row r="55" spans="1:5">
+      <c r="A55" s="5" t="s">
         <v>41</v>
       </c>
-      <c r="B39" s="3" t="s">
-        <v>6</v>
-      </c>
-      <c r="C39" s="5">
-        <v>-17.02</v>
-      </c>
-      <c r="D39" s="5">
-        <v>-16.08</v>
-      </c>
-      <c r="E39" s="7">
-        <v>0.9399999999999999</v>
-      </c>
-    </row>
-    <row r="40" spans="1:5">
-      <c r="A40" s="3" t="s">
+      <c r="B55" s="5" t="s">
+        <v>24</v>
+      </c>
+      <c r="C55" s="6">
+        <v>56.88</v>
+      </c>
+      <c r="D55" s="6">
+        <v>50.29</v>
+      </c>
+      <c r="E55" s="7">
+        <v>-6.59</v>
+      </c>
+    </row>
+    <row r="56" spans="1:5">
+      <c r="A56" s="5" t="s">
         <v>42</v>
       </c>
-      <c r="B40" s="3" t="s">
-        <v>6</v>
-      </c>
-      <c r="C40" s="5">
-        <v>-10.23</v>
-      </c>
-      <c r="D40" s="5">
-        <v>-11.87</v>
-      </c>
-      <c r="E40" s="6">
-        <v>-1.64</v>
-      </c>
-    </row>
-    <row r="41" spans="1:5">
-      <c r="A41" s="3" t="s">
+      <c r="B56" s="5" t="s">
+        <v>24</v>
+      </c>
+      <c r="C56" s="6">
+        <v>40.55</v>
+      </c>
+      <c r="D56" s="6">
+        <v>37.45</v>
+      </c>
+      <c r="E56" s="7">
+        <v>-3.1</v>
+      </c>
+    </row>
+    <row r="57" spans="1:5">
+      <c r="A57" s="5" t="s">
         <v>43</v>
       </c>
-      <c r="B41" s="3" t="s">
-        <v>6</v>
-      </c>
-      <c r="C41" s="5">
-        <v>-9.51</v>
-      </c>
-      <c r="D41" s="5">
-        <v>-8.67</v>
-      </c>
-      <c r="E41" s="7">
-        <v>0.84</v>
-      </c>
-    </row>
-    <row r="42" spans="1:5">
-      <c r="A42" s="3" t="s">
+      <c r="B57" s="5" t="s">
+        <v>24</v>
+      </c>
+      <c r="C57" s="6">
+        <v>48.06</v>
+      </c>
+      <c r="D57" s="6">
+        <v>59.15</v>
+      </c>
+      <c r="E57" s="8">
+        <v>11.09</v>
+      </c>
+    </row>
+    <row r="58" spans="1:5">
+      <c r="A58" s="5" t="s">
         <v>37</v>
       </c>
-      <c r="B42" s="3" t="s">
-        <v>2</v>
-      </c>
-      <c r="C42" s="5">
-        <v>11414</v>
-      </c>
-      <c r="D42" s="5">
-        <v>11460</v>
-      </c>
-      <c r="E42" s="7">
-        <v>46</v>
-      </c>
-    </row>
-    <row r="43" spans="1:5">
-      <c r="A43" s="3" t="s">
+      <c r="B58" s="5" t="s">
+        <v>31</v>
+      </c>
+      <c r="C58" s="6">
+        <v>-59.04</v>
+      </c>
+      <c r="D58" s="6">
+        <v>-31.02</v>
+      </c>
+      <c r="E58" s="8">
+        <v>28.02</v>
+      </c>
+    </row>
+    <row r="59" spans="1:5">
+      <c r="A59" s="5" t="s">
         <v>38</v>
       </c>
-      <c r="B43" s="3" t="s">
-        <v>2</v>
-      </c>
-      <c r="C43" s="5">
-        <v>512.15</v>
-      </c>
-      <c r="D43" s="5">
-        <v>515.3</v>
-      </c>
-      <c r="E43" s="7">
-        <v>3.15</v>
-      </c>
-    </row>
-    <row r="44" spans="1:5">
-      <c r="A44" s="3" t="s">
+      <c r="B59" s="5" t="s">
+        <v>31</v>
+      </c>
+      <c r="C59" s="6">
+        <v>-36.72</v>
+      </c>
+      <c r="D59" s="6">
+        <v>-49.75</v>
+      </c>
+      <c r="E59" s="7">
+        <v>-13.03</v>
+      </c>
+    </row>
+    <row r="60" spans="1:5">
+      <c r="A60" s="5" t="s">
         <v>39</v>
       </c>
-      <c r="B44" s="3" t="s">
-        <v>2</v>
-      </c>
-      <c r="C44" s="5">
-        <v>323.05</v>
-      </c>
-      <c r="D44" s="5">
-        <v>326</v>
-      </c>
-      <c r="E44" s="7">
-        <v>2.95</v>
-      </c>
-    </row>
-    <row r="45" spans="1:5">
-      <c r="A45" s="3" t="s">
+      <c r="B60" s="5" t="s">
+        <v>31</v>
+      </c>
+      <c r="C60" s="6">
+        <v>-31.78</v>
+      </c>
+      <c r="D60" s="6">
+        <v>-46.14</v>
+      </c>
+      <c r="E60" s="7">
+        <v>-14.36</v>
+      </c>
+    </row>
+    <row r="61" spans="1:5">
+      <c r="A61" s="5" t="s">
         <v>40</v>
       </c>
-      <c r="B45" s="3" t="s">
-        <v>2</v>
-      </c>
-      <c r="C45" s="5">
-        <v>1852.5</v>
-      </c>
-      <c r="D45" s="5">
-        <v>1849.8</v>
-      </c>
-      <c r="E45" s="6">
-        <v>-2.7</v>
-      </c>
-    </row>
-    <row r="46" spans="1:5">
-      <c r="A46" s="3" t="s">
+      <c r="B61" s="5" t="s">
+        <v>31</v>
+      </c>
+      <c r="C61" s="6">
+        <v>-53.99</v>
+      </c>
+      <c r="D61" s="6">
+        <v>-30.17</v>
+      </c>
+      <c r="E61" s="8">
+        <v>23.82</v>
+      </c>
+    </row>
+    <row r="62" spans="1:5">
+      <c r="A62" s="5" t="s">
         <v>41</v>
       </c>
-      <c r="B46" s="3" t="s">
-        <v>2</v>
-      </c>
-      <c r="C46" s="5">
-        <v>11282</v>
-      </c>
-      <c r="D46" s="5">
-        <v>11409</v>
-      </c>
-      <c r="E46" s="7">
-        <v>127</v>
-      </c>
-    </row>
-    <row r="47" spans="1:5">
-      <c r="A47" s="3" t="s">
+      <c r="B62" s="5" t="s">
+        <v>31</v>
+      </c>
+      <c r="C62" s="6">
+        <v>25.09</v>
+      </c>
+      <c r="D62" s="6">
+        <v>60.33</v>
+      </c>
+      <c r="E62" s="8">
+        <v>35.24</v>
+      </c>
+    </row>
+    <row r="63" spans="1:5">
+      <c r="A63" s="5" t="s">
         <v>42</v>
       </c>
-      <c r="B47" s="3" t="s">
-        <v>2</v>
-      </c>
-      <c r="C47" s="5">
-        <v>1040.3</v>
-      </c>
-      <c r="D47" s="5">
-        <v>1021.3</v>
-      </c>
-      <c r="E47" s="6">
-        <v>-19</v>
-      </c>
-    </row>
-    <row r="48" spans="1:5">
-      <c r="A48" s="3" t="s">
+      <c r="B63" s="5" t="s">
+        <v>31</v>
+      </c>
+      <c r="C63" s="6">
+        <v>-19.85</v>
+      </c>
+      <c r="D63" s="6">
+        <v>-9.84</v>
+      </c>
+      <c r="E63" s="8">
+        <v>10.01</v>
+      </c>
+    </row>
+    <row r="64" spans="1:5">
+      <c r="A64" s="5" t="s">
         <v>43</v>
       </c>
-      <c r="B48" s="3" t="s">
-        <v>2</v>
-      </c>
-      <c r="C48" s="5">
-        <v>134.78</v>
-      </c>
-      <c r="D48" s="5">
-        <v>136.03</v>
-      </c>
-      <c r="E48" s="7">
-        <v>1.25</v>
-      </c>
-    </row>
-    <row r="49" spans="1:5">
-      <c r="A49" s="3" t="s">
-        <v>37</v>
-      </c>
-      <c r="B49" s="3" t="s">
-        <v>24</v>
-      </c>
-      <c r="C49" s="5">
-        <v>42.48</v>
-      </c>
-      <c r="D49" s="5">
-        <v>44.1</v>
-      </c>
-      <c r="E49" s="7">
-        <v>1.62</v>
-      </c>
-    </row>
-    <row r="50" spans="1:5">
-      <c r="A50" s="3" t="s">
-        <v>38</v>
-      </c>
-      <c r="B50" s="3" t="s">
-        <v>24</v>
-      </c>
-      <c r="C50" s="5">
-        <v>51.74</v>
-      </c>
-      <c r="D50" s="5">
-        <v>52.88</v>
-      </c>
-      <c r="E50" s="7">
-        <v>1.14</v>
-      </c>
-    </row>
-    <row r="51" spans="1:5">
-      <c r="A51" s="3" t="s">
-        <v>39</v>
-      </c>
-      <c r="B51" s="3" t="s">
-        <v>24</v>
-      </c>
-      <c r="C51" s="5">
-        <v>39.32</v>
-      </c>
-      <c r="D51" s="5">
-        <v>42.2</v>
-      </c>
-      <c r="E51" s="7">
-        <v>2.88</v>
-      </c>
-    </row>
-    <row r="52" spans="1:5">
-      <c r="A52" s="3" t="s">
-        <v>40</v>
-      </c>
-      <c r="B52" s="3" t="s">
-        <v>24</v>
-      </c>
-      <c r="C52" s="5">
-        <v>32.6</v>
-      </c>
-      <c r="D52" s="5">
-        <v>32.25</v>
-      </c>
-      <c r="E52" s="6">
-        <v>-0.35</v>
-      </c>
-    </row>
-    <row r="53" spans="1:5">
-      <c r="A53" s="3" t="s">
-        <v>41</v>
-      </c>
-      <c r="B53" s="3" t="s">
-        <v>24</v>
-      </c>
-      <c r="C53" s="5">
-        <v>53.69</v>
-      </c>
-      <c r="D53" s="5">
-        <v>56.88</v>
-      </c>
-      <c r="E53" s="7">
-        <v>3.19</v>
-      </c>
-    </row>
-    <row r="54" spans="1:5">
-      <c r="A54" s="3" t="s">
-        <v>42</v>
-      </c>
-      <c r="B54" s="3" t="s">
-        <v>24</v>
-      </c>
-      <c r="C54" s="5">
-        <v>45.91</v>
-      </c>
-      <c r="D54" s="5">
-        <v>40.55</v>
-      </c>
-      <c r="E54" s="6">
-        <v>-5.36</v>
-      </c>
-    </row>
-    <row r="55" spans="1:5">
-      <c r="A55" s="3" t="s">
-        <v>43</v>
-      </c>
-      <c r="B55" s="3" t="s">
-        <v>24</v>
-      </c>
-      <c r="C55" s="5">
-        <v>44.84</v>
-      </c>
-      <c r="D55" s="5">
-        <v>48.06</v>
-      </c>
-      <c r="E55" s="7">
-        <v>3.22</v>
-      </c>
-    </row>
-    <row r="56" spans="1:5">
-      <c r="A56" s="3" t="s">
-        <v>37</v>
-      </c>
-      <c r="B56" s="3" t="s">
+      <c r="B64" s="5" t="s">
         <v>31</v>
       </c>
-      <c r="C56" s="5">
-        <v>32.66</v>
-      </c>
-      <c r="D56" s="5">
-        <v>-59.04</v>
-      </c>
-      <c r="E56" s="6">
-        <v>-91.7</v>
-      </c>
-    </row>
-    <row r="57" spans="1:5">
-      <c r="A57" s="3" t="s">
-        <v>38</v>
-      </c>
-      <c r="B57" s="3" t="s">
-        <v>31</v>
-      </c>
-      <c r="C57" s="5">
-        <v>-1.18</v>
-      </c>
-      <c r="D57" s="5">
-        <v>-36.72</v>
-      </c>
-      <c r="E57" s="6">
-        <v>-35.54</v>
-      </c>
-    </row>
-    <row r="58" spans="1:5">
-      <c r="A58" s="3" t="s">
-        <v>39</v>
-      </c>
-      <c r="B58" s="3" t="s">
-        <v>31</v>
-      </c>
-      <c r="C58" s="5">
-        <v>-18.61</v>
-      </c>
-      <c r="D58" s="5">
-        <v>-31.78</v>
-      </c>
-      <c r="E58" s="6">
-        <v>-13.17</v>
-      </c>
-    </row>
-    <row r="59" spans="1:5">
-      <c r="A59" s="3" t="s">
-        <v>40</v>
-      </c>
-      <c r="B59" s="3" t="s">
-        <v>31</v>
-      </c>
-      <c r="C59" s="5">
-        <v>20.65</v>
-      </c>
-      <c r="D59" s="5">
-        <v>-53.99</v>
-      </c>
-      <c r="E59" s="6">
-        <v>-74.64</v>
-      </c>
-    </row>
-    <row r="60" spans="1:5">
-      <c r="A60" s="3" t="s">
-        <v>41</v>
-      </c>
-      <c r="B60" s="3" t="s">
-        <v>31</v>
-      </c>
-      <c r="C60" s="5">
-        <v>34.14</v>
-      </c>
-      <c r="D60" s="5">
-        <v>25.09</v>
-      </c>
-      <c r="E60" s="6">
-        <v>-9.050000000000001</v>
-      </c>
-    </row>
-    <row r="61" spans="1:5">
-      <c r="A61" s="3" t="s">
-        <v>42</v>
-      </c>
-      <c r="B61" s="3" t="s">
-        <v>31</v>
-      </c>
-      <c r="C61" s="5">
-        <v>65.65000000000001</v>
-      </c>
-      <c r="D61" s="5">
-        <v>-19.85</v>
-      </c>
-      <c r="E61" s="6">
-        <v>-85.5</v>
-      </c>
-    </row>
-    <row r="62" spans="1:5">
-      <c r="A62" s="3" t="s">
-        <v>43</v>
-      </c>
-      <c r="B62" s="3" t="s">
-        <v>31</v>
-      </c>
-      <c r="C62" s="5">
-        <v>-42.72</v>
-      </c>
-      <c r="D62" s="5">
+      <c r="C64" s="6">
         <v>-34.09</v>
       </c>
-      <c r="E62" s="7">
-        <v>8.630000000000001</v>
+      <c r="D64" s="6">
+        <v>149.29</v>
+      </c>
+      <c r="E64" s="8">
+        <v>183.38</v>
       </c>
     </row>
   </sheetData>
@@ -2841,60 +2938,60 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:9" ht="28" customHeight="1">
-      <c r="A1" s="8" t="s">
+      <c r="A1" s="9" t="s">
         <v>1</v>
       </c>
-      <c r="B1" s="8" t="s">
-        <v>56</v>
-      </c>
-      <c r="C1" s="8" t="s">
+      <c r="B1" s="9" t="s">
+        <v>65</v>
+      </c>
+      <c r="C1" s="9" t="s">
+        <v>66</v>
+      </c>
+      <c r="D1" s="9" t="s">
+        <v>67</v>
+      </c>
+      <c r="E1" s="9" t="s">
+        <v>68</v>
+      </c>
+      <c r="F1" s="9" t="s">
+        <v>69</v>
+      </c>
+      <c r="G1" s="9" t="s">
+        <v>70</v>
+      </c>
+      <c r="H1" s="9" t="s">
+        <v>71</v>
+      </c>
+      <c r="I1" s="9" t="s">
+        <v>72</v>
+      </c>
+    </row>
+    <row r="2" spans="1:9">
+      <c r="A2" s="10" t="s">
+        <v>44</v>
+      </c>
+      <c r="B2" s="11">
+        <v>60.8</v>
+      </c>
+      <c r="C2" s="12">
+        <v>7</v>
+      </c>
+      <c r="D2" s="11">
+        <v>44.3</v>
+      </c>
+      <c r="E2" s="11">
+        <v>70</v>
+      </c>
+      <c r="F2" s="11">
+        <v>-2.8</v>
+      </c>
+      <c r="G2" s="11">
+        <v>2.8</v>
+      </c>
+      <c r="H2" s="11">
         <v>57</v>
       </c>
-      <c r="D1" s="8" t="s">
-        <v>58</v>
-      </c>
-      <c r="E1" s="8" t="s">
-        <v>59</v>
-      </c>
-      <c r="F1" s="8" t="s">
-        <v>60</v>
-      </c>
-      <c r="G1" s="8" t="s">
-        <v>61</v>
-      </c>
-      <c r="H1" s="8" t="s">
-        <v>62</v>
-      </c>
-      <c r="I1" s="8" t="s">
-        <v>63</v>
-      </c>
-    </row>
-    <row r="2" spans="1:9">
-      <c r="A2" s="9" t="s">
-        <v>44</v>
-      </c>
-      <c r="B2" s="10">
-        <v>60.8</v>
-      </c>
-      <c r="C2" s="11">
-        <v>7</v>
-      </c>
-      <c r="D2" s="10">
-        <v>45.3</v>
-      </c>
-      <c r="E2" s="10">
-        <v>70</v>
-      </c>
-      <c r="F2" s="10">
-        <v>-2.9</v>
-      </c>
-      <c r="G2" s="10">
-        <v>1</v>
-      </c>
-      <c r="H2" s="10">
-        <v>57</v>
-      </c>
-      <c r="I2" s="10">
+      <c r="I2" s="11">
         <v>30</v>
       </c>
     </row>
@@ -2996,49 +3093,49 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:7">
-      <c r="A1" s="12" t="s">
+      <c r="A1" s="13" t="s">
         <v>37</v>
       </c>
-      <c r="B1" s="12" t="s">
+      <c r="B1" s="13" t="s">
         <v>41</v>
       </c>
-      <c r="C1" s="12" t="s">
+      <c r="C1" s="13" t="s">
         <v>38</v>
       </c>
-      <c r="D1" s="12" t="s">
+      <c r="D1" s="13" t="s">
         <v>42</v>
       </c>
-      <c r="E1" s="12" t="s">
+      <c r="E1" s="13" t="s">
         <v>43</v>
       </c>
-      <c r="F1" s="12" t="s">
+      <c r="F1" s="13" t="s">
         <v>40</v>
       </c>
-      <c r="G1" s="12" t="s">
+      <c r="G1" s="13" t="s">
         <v>39</v>
       </c>
     </row>
     <row r="2" spans="1:7">
-      <c r="A2" s="13">
-        <v>0.2807</v>
-      </c>
-      <c r="B2" s="13">
-        <v>0.2124</v>
-      </c>
-      <c r="C2" s="13">
-        <v>0.1691</v>
-      </c>
-      <c r="D2" s="13">
-        <v>0.059</v>
-      </c>
-      <c r="E2" s="13">
-        <v>0.0116</v>
-      </c>
-      <c r="F2" s="13">
-        <v>0.0106</v>
-      </c>
-      <c r="G2" s="13">
-        <v>-0.2539</v>
+      <c r="A2" s="14">
+        <v>0.2766</v>
+      </c>
+      <c r="B2" s="14">
+        <v>0.2057</v>
+      </c>
+      <c r="C2" s="14">
+        <v>0.1682</v>
+      </c>
+      <c r="D2" s="14">
+        <v>0.057</v>
+      </c>
+      <c r="E2" s="14">
+        <v>0.0207</v>
+      </c>
+      <c r="F2" s="14">
+        <v>0.0073</v>
+      </c>
+      <c r="G2" s="14">
+        <v>-0.2546</v>
       </c>
     </row>
   </sheetData>

--- a/BAJAJ_GROUP_Technical_Metrics.xlsx
+++ b/BAJAJ_GROUP_Technical_Metrics.xlsx
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="268" uniqueCount="73">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="282" uniqueCount="88">
   <si>
     <t>Symbol</t>
   </si>
@@ -187,19 +187,64 @@
     <t>Curr Value</t>
   </si>
   <si>
+    <t>Near 52W High</t>
+  </si>
+  <si>
+    <t>-5.1% → 0.0%</t>
+  </si>
+  <si>
+    <t>🟢 BREAKOUT WATCH</t>
+  </si>
+  <si>
+    <t>-5.1%</t>
+  </si>
+  <si>
+    <t>0.0%</t>
+  </si>
+  <si>
+    <t>RSI Oversold Recovery</t>
+  </si>
+  <si>
+    <t>29.0 → 35.2</t>
+  </si>
+  <si>
+    <t>🟢 BULLISH</t>
+  </si>
+  <si>
+    <t>29.0</t>
+  </si>
+  <si>
+    <t>35.2</t>
+  </si>
+  <si>
+    <t>RSI Overbought Entry</t>
+  </si>
+  <si>
+    <t>59.1 → 75.5</t>
+  </si>
+  <si>
+    <t>⚠️ CAUTION</t>
+  </si>
+  <si>
+    <t>59.1</t>
+  </si>
+  <si>
+    <t>75.5</t>
+  </si>
+  <si>
     <t>RSI Momentum</t>
   </si>
   <si>
-    <t>48.1 → 59.1</t>
-  </si>
-  <si>
-    <t>🟢 BULLISH</t>
-  </si>
-  <si>
-    <t>48.1</t>
-  </si>
-  <si>
-    <t>59.1</t>
+    <t>52.2 → 48.9</t>
+  </si>
+  <si>
+    <t>🔴 BEARISH</t>
+  </si>
+  <si>
+    <t>52.2</t>
+  </si>
+  <si>
+    <t>48.9</t>
   </si>
   <si>
     <t>▶  NUMERIC METRIC CHANGES (vs Previous Run)</t>
@@ -251,7 +296,7 @@
     <numFmt numFmtId="166" formatCode="0.0"/>
     <numFmt numFmtId="167" formatCode="0.00%"/>
   </numFmts>
-  <fonts count="6">
+  <fonts count="7">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -292,13 +337,20 @@
     </font>
     <font>
       <sz val="11"/>
+      <color rgb="FF9C6500"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
       <color rgb="FF9C0006"/>
       <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="9">
+  <fills count="10">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -326,6 +378,12 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="FFC6EFCE"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFEB9C"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -401,7 +459,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="15">
+  <cellXfs count="17">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="2" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
@@ -409,14 +467,16 @@
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="5" fillId="6" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="6" fillId="7" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1"/>
-    <xf numFmtId="165" fontId="5" fillId="6" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="165" fontId="6" fillId="7" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="165" fontId="4" fillId="5" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="3" fillId="7" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="8" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="8" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="9" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
     <xf numFmtId="166" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
@@ -425,7 +485,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="8" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="9" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="167" fontId="0" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
@@ -924,10 +984,10 @@
         <v>44</v>
       </c>
       <c r="C2">
-        <v>11363</v>
+        <v>11400</v>
       </c>
       <c r="D2">
-        <v>-0.85</v>
+        <v>0.33</v>
       </c>
       <c r="E2">
         <v>12361</v>
@@ -936,46 +996,46 @@
         <v>8506.780000000001</v>
       </c>
       <c r="G2">
-        <v>-8.07</v>
+        <v>-7.77</v>
       </c>
       <c r="H2">
-        <v>33.58</v>
+        <v>34.01</v>
       </c>
       <c r="I2">
-        <v>-0.53</v>
+        <v>-1.66</v>
       </c>
       <c r="J2">
-        <v>-2.88</v>
+        <v>-3.39</v>
       </c>
       <c r="K2">
-        <v>13.35</v>
+        <v>16.92</v>
       </c>
       <c r="L2">
-        <v>26.85</v>
+        <v>27.39</v>
       </c>
       <c r="M2">
-        <v>27.66</v>
+        <v>27.46</v>
       </c>
       <c r="N2">
         <v>85</v>
       </c>
       <c r="O2">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="P2">
-        <v>11466</v>
+        <v>11427.4</v>
       </c>
       <c r="Q2">
-        <v>11770.55</v>
+        <v>11744.2</v>
       </c>
       <c r="R2">
-        <v>11501.97</v>
+        <v>11526.65</v>
       </c>
       <c r="S2">
-        <v>10068.59</v>
+        <v>10080.79</v>
       </c>
       <c r="T2">
-        <v>12.86</v>
+        <v>13.09</v>
       </c>
       <c r="U2" t="s">
         <v>45</v>
@@ -990,43 +1050,43 @@
         <v>3</v>
       </c>
       <c r="Y2">
-        <v>41.44</v>
+        <v>42.86</v>
       </c>
       <c r="Z2">
-        <v>-33.38</v>
+        <v>-46.07</v>
       </c>
       <c r="AA2">
-        <v>51.5</v>
+        <v>31.98</v>
       </c>
       <c r="AB2">
-        <v>-84.88</v>
+        <v>-78.06</v>
       </c>
       <c r="AC2">
-        <v>3.35</v>
+        <v>5.55</v>
       </c>
       <c r="AD2">
-        <v>6.61</v>
+        <v>5.16</v>
       </c>
       <c r="AE2">
-        <v>206.06</v>
+        <v>200.77</v>
       </c>
       <c r="AF2">
-        <v>-31.02</v>
+        <v>-28.25</v>
       </c>
       <c r="AG2">
-        <v>12300.96</v>
+        <v>12293.9</v>
       </c>
       <c r="AH2">
-        <v>11240.14</v>
+        <v>11194.5</v>
       </c>
       <c r="AI2">
-        <v>12016.18</v>
+        <v>11961.31</v>
       </c>
       <c r="AJ2" t="s">
         <v>47</v>
       </c>
       <c r="AK2">
-        <v>37.35</v>
+        <v>40.35</v>
       </c>
     </row>
     <row r="3" spans="1:37">
@@ -1037,10 +1097,10 @@
         <v>44</v>
       </c>
       <c r="C3">
-        <v>513.75</v>
+        <v>505.85</v>
       </c>
       <c r="D3">
-        <v>-0.3</v>
+        <v>-1.54</v>
       </c>
       <c r="E3">
         <v>670.25</v>
@@ -1049,46 +1109,46 @@
         <v>232.89</v>
       </c>
       <c r="G3">
-        <v>-23.35</v>
+        <v>-24.53</v>
       </c>
       <c r="H3">
-        <v>120.6</v>
+        <v>117.21</v>
       </c>
       <c r="I3">
-        <v>1.97</v>
+        <v>1.57</v>
       </c>
       <c r="J3">
-        <v>7.4</v>
+        <v>9.210000000000001</v>
       </c>
       <c r="K3">
-        <v>-11.66</v>
+        <v>-14.27</v>
       </c>
       <c r="L3">
-        <v>116.37</v>
+        <v>96.19</v>
       </c>
       <c r="M3">
-        <v>16.82</v>
+        <v>16.2</v>
       </c>
       <c r="N3">
         <v>99</v>
       </c>
       <c r="O3">
-        <v>92</v>
+        <v>90</v>
       </c>
       <c r="P3">
-        <v>508.34</v>
+        <v>509.9</v>
       </c>
       <c r="Q3">
-        <v>497.78</v>
+        <v>500.32</v>
       </c>
       <c r="R3">
-        <v>515.63</v>
+        <v>513.9400000000001</v>
       </c>
       <c r="S3">
-        <v>443.88</v>
+        <v>445.05</v>
       </c>
       <c r="T3">
-        <v>15.74</v>
+        <v>13.66</v>
       </c>
       <c r="U3" t="s">
         <v>46</v>
@@ -1103,34 +1163,34 @@
         <v>2</v>
       </c>
       <c r="Y3">
-        <v>52.23</v>
+        <v>48.92</v>
       </c>
       <c r="Z3">
-        <v>0.31</v>
+        <v>0.08</v>
       </c>
       <c r="AA3">
-        <v>-2.71</v>
+        <v>-2.15</v>
       </c>
       <c r="AB3">
-        <v>3.02</v>
+        <v>2.23</v>
       </c>
       <c r="AC3">
-        <v>69.84</v>
+        <v>54.21</v>
       </c>
       <c r="AD3">
-        <v>65.11</v>
+        <v>63.16</v>
       </c>
       <c r="AE3">
-        <v>20.26</v>
+        <v>19.77</v>
       </c>
       <c r="AF3">
-        <v>-49.75</v>
+        <v>-37.56</v>
       </c>
       <c r="AG3">
-        <v>546.42</v>
+        <v>544.6900000000001</v>
       </c>
       <c r="AH3">
-        <v>449.14</v>
+        <v>455.96</v>
       </c>
       <c r="AI3">
         <v>460.99</v>
@@ -1139,7 +1199,7 @@
         <v>48</v>
       </c>
       <c r="AK3">
-        <v>25.84</v>
+        <v>22.88</v>
       </c>
     </row>
     <row r="4" spans="1:37">
@@ -1150,58 +1210,58 @@
         <v>44</v>
       </c>
       <c r="C4">
-        <v>323.45</v>
+        <v>329.4</v>
       </c>
       <c r="D4">
-        <v>-0.78</v>
+        <v>1.84</v>
       </c>
       <c r="E4">
-        <v>597.3</v>
+        <v>589.75</v>
       </c>
       <c r="F4">
         <v>303.75</v>
       </c>
       <c r="G4">
-        <v>-45.85</v>
+        <v>-44.15</v>
       </c>
       <c r="H4">
-        <v>6.49</v>
+        <v>8.44</v>
       </c>
       <c r="I4">
-        <v>-1.51</v>
+        <v>2.12</v>
       </c>
       <c r="J4">
-        <v>-8.02</v>
+        <v>-4.42</v>
       </c>
       <c r="K4">
-        <v>0.08</v>
+        <v>1.43</v>
       </c>
       <c r="L4">
-        <v>-46.52</v>
+        <v>-44.85</v>
       </c>
       <c r="M4">
-        <v>-25.46</v>
+        <v>-25.36</v>
       </c>
       <c r="N4">
         <v>15</v>
       </c>
       <c r="O4">
-        <v>16</v>
+        <v>19</v>
       </c>
       <c r="P4">
-        <v>324.07</v>
+        <v>325.44</v>
       </c>
       <c r="Q4">
-        <v>331.29</v>
+        <v>331.04</v>
       </c>
       <c r="R4">
-        <v>339.43</v>
+        <v>339.44</v>
       </c>
       <c r="S4">
-        <v>373.73</v>
+        <v>372.98</v>
       </c>
       <c r="T4">
-        <v>-13.45</v>
+        <v>-11.68</v>
       </c>
       <c r="U4" t="s">
         <v>46</v>
@@ -1216,34 +1276,34 @@
         <v>0</v>
       </c>
       <c r="Y4">
-        <v>40.41</v>
+        <v>46.13</v>
       </c>
       <c r="Z4">
-        <v>-4.78</v>
+        <v>-4.41</v>
       </c>
       <c r="AA4">
-        <v>-3.74</v>
+        <v>-3.87</v>
       </c>
       <c r="AB4">
-        <v>-1.04</v>
+        <v>-0.54</v>
       </c>
       <c r="AC4">
-        <v>26.8</v>
+        <v>40.89</v>
       </c>
       <c r="AD4">
-        <v>24.3</v>
+        <v>31.76</v>
       </c>
       <c r="AE4">
-        <v>9.710000000000001</v>
+        <v>9.619999999999999</v>
       </c>
       <c r="AF4">
-        <v>-46.14</v>
+        <v>-33.47</v>
       </c>
       <c r="AG4">
-        <v>344.66</v>
+        <v>344.36</v>
       </c>
       <c r="AH4">
-        <v>317.91</v>
+        <v>317.72</v>
       </c>
       <c r="AI4">
         <v>354.2</v>
@@ -1252,7 +1312,7 @@
         <v>47</v>
       </c>
       <c r="AK4">
-        <v>15.27</v>
+        <v>14.53</v>
       </c>
     </row>
     <row r="5" spans="1:37">
@@ -1263,10 +1323,10 @@
         <v>44</v>
       </c>
       <c r="C5">
-        <v>1823.4</v>
+        <v>1846.5</v>
       </c>
       <c r="D5">
-        <v>-1.43</v>
+        <v>1.27</v>
       </c>
       <c r="E5">
         <v>2176.6</v>
@@ -1275,25 +1335,25 @@
         <v>1631.8</v>
       </c>
       <c r="G5">
-        <v>-16.23</v>
+        <v>-15.17</v>
       </c>
       <c r="H5">
-        <v>11.74</v>
+        <v>13.16</v>
       </c>
       <c r="I5">
-        <v>-1.73</v>
+        <v>0.52</v>
       </c>
       <c r="J5">
-        <v>-10.29</v>
+        <v>-7.75</v>
       </c>
       <c r="K5">
-        <v>3.31</v>
+        <v>3.71</v>
       </c>
       <c r="L5">
-        <v>-11.36</v>
+        <v>-10.76</v>
       </c>
       <c r="M5">
-        <v>0.73</v>
+        <v>-0</v>
       </c>
       <c r="N5">
         <v>29</v>
@@ -1302,19 +1362,19 @@
         <v>50</v>
       </c>
       <c r="P5">
-        <v>1844.38</v>
+        <v>1846.28</v>
       </c>
       <c r="Q5">
-        <v>1935.36</v>
+        <v>1927.48</v>
       </c>
       <c r="R5">
-        <v>1955.89</v>
+        <v>1955.43</v>
       </c>
       <c r="S5">
-        <v>1895.44</v>
+        <v>1894.42</v>
       </c>
       <c r="T5">
-        <v>-3.8</v>
+        <v>-2.53</v>
       </c>
       <c r="U5" t="s">
         <v>46</v>
@@ -1329,34 +1389,34 @@
         <v>1</v>
       </c>
       <c r="Y5">
-        <v>28.99</v>
+        <v>35.17</v>
       </c>
       <c r="Z5">
-        <v>-37.79</v>
+        <v>-38.16</v>
       </c>
       <c r="AA5">
-        <v>-23.12</v>
+        <v>-26.13</v>
       </c>
       <c r="AB5">
-        <v>-14.67</v>
+        <v>-12.04</v>
       </c>
       <c r="AC5">
-        <v>13.71</v>
+        <v>19.05</v>
       </c>
       <c r="AD5">
-        <v>14.58</v>
+        <v>17.01</v>
       </c>
       <c r="AE5">
-        <v>35.33</v>
+        <v>35.76</v>
       </c>
       <c r="AF5">
-        <v>-30.17</v>
+        <v>33.45</v>
       </c>
       <c r="AG5">
-        <v>2069.68</v>
+        <v>2063.32</v>
       </c>
       <c r="AH5">
-        <v>1801.04</v>
+        <v>1791.65</v>
       </c>
       <c r="AI5">
         <v>1949.18</v>
@@ -1365,7 +1425,7 @@
         <v>47</v>
       </c>
       <c r="AK5">
-        <v>65.55</v>
+        <v>66.73</v>
       </c>
     </row>
     <row r="6" spans="1:37">
@@ -1376,58 +1436,58 @@
         <v>44</v>
       </c>
       <c r="C6">
-        <v>11185</v>
+        <v>11449</v>
       </c>
       <c r="D6">
-        <v>-1.96</v>
+        <v>2.36</v>
       </c>
       <c r="E6">
-        <v>13400.71</v>
+        <v>13279</v>
       </c>
       <c r="F6">
         <v>8746</v>
       </c>
       <c r="G6">
-        <v>-16.53</v>
+        <v>-13.78</v>
       </c>
       <c r="H6">
-        <v>27.89</v>
+        <v>30.91</v>
       </c>
       <c r="I6">
-        <v>0.77</v>
+        <v>4.75</v>
       </c>
       <c r="J6">
-        <v>-1.19</v>
+        <v>2.96</v>
       </c>
       <c r="K6">
-        <v>5.37</v>
+        <v>8.18</v>
       </c>
       <c r="L6">
-        <v>-17.73</v>
+        <v>-14.56</v>
       </c>
       <c r="M6">
-        <v>20.57</v>
+        <v>19.97</v>
       </c>
       <c r="N6">
         <v>43</v>
       </c>
       <c r="O6">
-        <v>50</v>
+        <v>54</v>
       </c>
       <c r="P6">
-        <v>11163.2</v>
+        <v>11267</v>
       </c>
       <c r="Q6">
-        <v>11203.6</v>
+        <v>11211.55</v>
       </c>
       <c r="R6">
-        <v>11120.08</v>
+        <v>11139.34</v>
       </c>
       <c r="S6">
-        <v>10681.69</v>
+        <v>10683.34</v>
       </c>
       <c r="T6">
-        <v>4.71</v>
+        <v>7.17</v>
       </c>
       <c r="U6" t="s">
         <v>45</v>
@@ -1442,34 +1502,34 @@
         <v>3</v>
       </c>
       <c r="Y6">
-        <v>50.29</v>
+        <v>56.66</v>
       </c>
       <c r="Z6">
-        <v>-4.41</v>
+        <v>18.03</v>
       </c>
       <c r="AA6">
-        <v>-10.48</v>
+        <v>-4.78</v>
       </c>
       <c r="AB6">
-        <v>6.07</v>
+        <v>22.81</v>
       </c>
       <c r="AC6">
-        <v>70.89</v>
+        <v>83.89</v>
       </c>
       <c r="AD6">
-        <v>51.58</v>
+        <v>71.06</v>
       </c>
       <c r="AE6">
-        <v>231.28</v>
+        <v>233.61</v>
       </c>
       <c r="AF6">
-        <v>60.33</v>
+        <v>-49.88</v>
       </c>
       <c r="AG6">
-        <v>11592.91</v>
+        <v>11614.55</v>
       </c>
       <c r="AH6">
-        <v>10814.29</v>
+        <v>10808.55</v>
       </c>
       <c r="AI6">
         <v>10787.84</v>
@@ -1478,7 +1538,7 @@
         <v>48</v>
       </c>
       <c r="AK6">
-        <v>19.19</v>
+        <v>18.64</v>
       </c>
     </row>
     <row r="7" spans="1:37">
@@ -1489,10 +1549,10 @@
         <v>44</v>
       </c>
       <c r="C7">
-        <v>1008.8</v>
+        <v>1043.2</v>
       </c>
       <c r="D7">
-        <v>-1.22</v>
+        <v>3.41</v>
       </c>
       <c r="E7">
         <v>1158.8</v>
@@ -1501,46 +1561,46 @@
         <v>801.55</v>
       </c>
       <c r="G7">
-        <v>-12.94</v>
+        <v>-9.98</v>
       </c>
       <c r="H7">
-        <v>25.86</v>
+        <v>30.15</v>
       </c>
       <c r="I7">
-        <v>-0.04</v>
+        <v>3.68</v>
       </c>
       <c r="J7">
-        <v>-7.87</v>
+        <v>-3.14</v>
       </c>
       <c r="K7">
-        <v>4.82</v>
+        <v>5.27</v>
       </c>
       <c r="L7">
-        <v>0.13</v>
+        <v>4.69</v>
       </c>
       <c r="M7">
-        <v>5.7</v>
+        <v>6.12</v>
       </c>
       <c r="N7">
         <v>57</v>
       </c>
       <c r="O7">
-        <v>60</v>
+        <v>63</v>
       </c>
       <c r="P7">
-        <v>1018.32</v>
+        <v>1025.72</v>
       </c>
       <c r="Q7">
-        <v>1047.19</v>
+        <v>1044.98</v>
       </c>
       <c r="R7">
-        <v>1066.79</v>
+        <v>1067.52</v>
       </c>
       <c r="S7">
-        <v>977.65</v>
+        <v>977.72</v>
       </c>
       <c r="T7">
-        <v>3.19</v>
+        <v>6.7</v>
       </c>
       <c r="U7" t="s">
         <v>46</v>
@@ -1555,34 +1615,34 @@
         <v>2</v>
       </c>
       <c r="Y7">
-        <v>37.45</v>
+        <v>49</v>
       </c>
       <c r="Z7">
-        <v>-15.16</v>
+        <v>-13.09</v>
       </c>
       <c r="AA7">
-        <v>-11.35</v>
+        <v>-11.7</v>
       </c>
       <c r="AB7">
-        <v>-3.81</v>
+        <v>-1.39</v>
       </c>
       <c r="AC7">
         <v>69.15000000000001</v>
       </c>
       <c r="AD7">
-        <v>57.41</v>
+        <v>66.84</v>
       </c>
       <c r="AE7">
-        <v>21.37</v>
+        <v>22.3</v>
       </c>
       <c r="AF7">
-        <v>-9.84</v>
+        <v>67.2</v>
       </c>
       <c r="AG7">
-        <v>1098.69</v>
+        <v>1092.88</v>
       </c>
       <c r="AH7">
-        <v>995.6900000000001</v>
+        <v>997.08</v>
       </c>
       <c r="AI7">
         <v>1075.64</v>
@@ -1591,7 +1651,7 @@
         <v>47</v>
       </c>
       <c r="AK7">
-        <v>38.33</v>
+        <v>34.59</v>
       </c>
     </row>
     <row r="8" spans="1:37">
@@ -1602,58 +1662,58 @@
         <v>44</v>
       </c>
       <c r="C8">
-        <v>141.41</v>
+        <v>157.11</v>
       </c>
       <c r="D8">
-        <v>3.96</v>
+        <v>11.1</v>
       </c>
       <c r="E8">
-        <v>148.95</v>
+        <v>157.11</v>
       </c>
       <c r="F8">
         <v>115.96</v>
       </c>
       <c r="G8">
-        <v>-5.06</v>
+        <v>0</v>
       </c>
       <c r="H8">
-        <v>21.95</v>
+        <v>35.49</v>
       </c>
       <c r="I8">
-        <v>4.27</v>
+        <v>16.47</v>
       </c>
       <c r="J8">
-        <v>3.06</v>
+        <v>15.79</v>
       </c>
       <c r="K8">
-        <v>4.61</v>
+        <v>16.98</v>
       </c>
       <c r="L8">
-        <v>2.56</v>
+        <v>16.09</v>
       </c>
       <c r="M8">
-        <v>2.07</v>
+        <v>4.25</v>
       </c>
       <c r="N8">
         <v>71</v>
       </c>
       <c r="O8">
-        <v>67</v>
+        <v>78</v>
       </c>
       <c r="P8">
-        <v>136.26</v>
+        <v>140.71</v>
       </c>
       <c r="Q8">
-        <v>136.69</v>
+        <v>137.79</v>
       </c>
       <c r="R8">
-        <v>138.59</v>
+        <v>139</v>
       </c>
       <c r="S8">
-        <v>133.87</v>
+        <v>133.99</v>
       </c>
       <c r="T8">
-        <v>5.63</v>
+        <v>17.25</v>
       </c>
       <c r="U8" t="s">
         <v>46</v>
@@ -1668,43 +1728,43 @@
         <v>2</v>
       </c>
       <c r="Y8">
-        <v>59.15</v>
+        <v>75.55</v>
       </c>
       <c r="Z8">
-        <v>-0.01</v>
+        <v>1.58</v>
       </c>
       <c r="AA8">
-        <v>-0.27</v>
+        <v>0.1</v>
       </c>
       <c r="AB8">
-        <v>0.25</v>
+        <v>1.48</v>
       </c>
       <c r="AC8">
-        <v>49.62</v>
+        <v>74.18000000000001</v>
       </c>
       <c r="AD8">
-        <v>34.11</v>
+        <v>50.8</v>
       </c>
       <c r="AE8">
-        <v>4.45</v>
+        <v>5.37</v>
       </c>
       <c r="AF8">
-        <v>149.29</v>
+        <v>2767.61</v>
       </c>
       <c r="AG8">
-        <v>141.69</v>
+        <v>148.14</v>
       </c>
       <c r="AH8">
-        <v>131.7</v>
+        <v>127.45</v>
       </c>
       <c r="AI8">
-        <v>131.91</v>
+        <v>133.99</v>
       </c>
       <c r="AJ8" t="s">
         <v>48</v>
       </c>
       <c r="AK8">
-        <v>23.08</v>
+        <v>28.87</v>
       </c>
     </row>
   </sheetData>
@@ -1845,7 +1905,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:F64"/>
+  <dimension ref="A1:F65"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="16.7109375" customWidth="1"/>
@@ -1903,1022 +1963,1048 @@
         <v>59</v>
       </c>
     </row>
+    <row r="4" spans="1:6">
+      <c r="A4" s="4" t="s">
+        <v>40</v>
+      </c>
+      <c r="B4" s="4" t="s">
+        <v>60</v>
+      </c>
+      <c r="C4" s="4" t="s">
+        <v>61</v>
+      </c>
+      <c r="D4" s="4" t="s">
+        <v>62</v>
+      </c>
+      <c r="E4" s="4" t="s">
+        <v>63</v>
+      </c>
+      <c r="F4" s="4" t="s">
+        <v>64</v>
+      </c>
+    </row>
     <row r="5" spans="1:6">
-      <c r="A5" s="2" t="s">
-        <v>60</v>
-      </c>
-      <c r="B5" s="2"/>
-      <c r="C5" s="2"/>
-      <c r="D5" s="2"/>
-      <c r="E5" s="2"/>
+      <c r="A5" s="5" t="s">
+        <v>43</v>
+      </c>
+      <c r="B5" s="5" t="s">
+        <v>65</v>
+      </c>
+      <c r="C5" s="5" t="s">
+        <v>66</v>
+      </c>
+      <c r="D5" s="5" t="s">
+        <v>67</v>
+      </c>
+      <c r="E5" s="5" t="s">
+        <v>68</v>
+      </c>
+      <c r="F5" s="5" t="s">
+        <v>69</v>
+      </c>
     </row>
     <row r="6" spans="1:6">
-      <c r="A6" s="3" t="s">
+      <c r="A6" s="6" t="s">
+        <v>38</v>
+      </c>
+      <c r="B6" s="6" t="s">
+        <v>70</v>
+      </c>
+      <c r="C6" s="6" t="s">
+        <v>71</v>
+      </c>
+      <c r="D6" s="6" t="s">
+        <v>72</v>
+      </c>
+      <c r="E6" s="6" t="s">
+        <v>73</v>
+      </c>
+      <c r="F6" s="6" t="s">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="8" spans="1:6">
+      <c r="A8" s="2" t="s">
+        <v>75</v>
+      </c>
+      <c r="B8" s="2"/>
+      <c r="C8" s="2"/>
+      <c r="D8" s="2"/>
+      <c r="E8" s="2"/>
+    </row>
+    <row r="9" spans="1:6">
+      <c r="A9" s="3" t="s">
         <v>0</v>
       </c>
-      <c r="B6" s="3" t="s">
-        <v>61</v>
-      </c>
-      <c r="C6" s="3" t="s">
-        <v>62</v>
-      </c>
-      <c r="D6" s="3" t="s">
-        <v>63</v>
-      </c>
-      <c r="E6" s="3" t="s">
-        <v>64</v>
-      </c>
-    </row>
-    <row r="7" spans="1:6">
-      <c r="A7" s="5" t="s">
+      <c r="B9" s="3" t="s">
+        <v>76</v>
+      </c>
+      <c r="C9" s="3" t="s">
+        <v>77</v>
+      </c>
+      <c r="D9" s="3" t="s">
+        <v>78</v>
+      </c>
+      <c r="E9" s="3" t="s">
+        <v>79</v>
+      </c>
+    </row>
+    <row r="10" spans="1:6">
+      <c r="A10" s="7" t="s">
         <v>37</v>
       </c>
-      <c r="B7" s="5" t="s">
+      <c r="B10" s="7" t="s">
         <v>9</v>
       </c>
-      <c r="C7" s="6">
-        <v>-2.82</v>
-      </c>
-      <c r="D7" s="6">
+      <c r="C10" s="8">
         <v>-2.88</v>
       </c>
-      <c r="E7" s="7">
-        <v>-0.06</v>
-      </c>
-    </row>
-    <row r="8" spans="1:6">
-      <c r="A8" s="5" t="s">
+      <c r="D10" s="8">
+        <v>-3.39</v>
+      </c>
+      <c r="E10" s="9">
+        <v>-0.51</v>
+      </c>
+    </row>
+    <row r="11" spans="1:6">
+      <c r="A11" s="7" t="s">
         <v>38</v>
       </c>
-      <c r="B8" s="5" t="s">
+      <c r="B11" s="7" t="s">
         <v>9</v>
       </c>
-      <c r="C8" s="6">
-        <v>5.82</v>
-      </c>
-      <c r="D8" s="6">
+      <c r="C11" s="8">
         <v>7.4</v>
       </c>
-      <c r="E8" s="8">
-        <v>1.58</v>
-      </c>
-    </row>
-    <row r="9" spans="1:6">
-      <c r="A9" s="5" t="s">
+      <c r="D11" s="8">
+        <v>9.210000000000001</v>
+      </c>
+      <c r="E11" s="10">
+        <v>1.81</v>
+      </c>
+    </row>
+    <row r="12" spans="1:6">
+      <c r="A12" s="7" t="s">
         <v>39</v>
       </c>
-      <c r="B9" s="5" t="s">
+      <c r="B12" s="7" t="s">
         <v>9</v>
       </c>
-      <c r="C9" s="6">
-        <v>-8</v>
-      </c>
-      <c r="D9" s="6">
+      <c r="C12" s="8">
         <v>-8.02</v>
       </c>
-      <c r="E9" s="7">
-        <v>-0.02</v>
-      </c>
-    </row>
-    <row r="10" spans="1:6">
-      <c r="A10" s="5" t="s">
+      <c r="D12" s="8">
+        <v>-4.42</v>
+      </c>
+      <c r="E12" s="10">
+        <v>3.6</v>
+      </c>
+    </row>
+    <row r="13" spans="1:6">
+      <c r="A13" s="7" t="s">
         <v>40</v>
       </c>
-      <c r="B10" s="5" t="s">
+      <c r="B13" s="7" t="s">
         <v>9</v>
       </c>
-      <c r="C10" s="6">
-        <v>-8.24</v>
-      </c>
-      <c r="D10" s="6">
+      <c r="C13" s="8">
         <v>-10.29</v>
       </c>
-      <c r="E10" s="7">
-        <v>-2.05</v>
-      </c>
-    </row>
-    <row r="11" spans="1:6">
-      <c r="A11" s="5" t="s">
+      <c r="D13" s="8">
+        <v>-7.75</v>
+      </c>
+      <c r="E13" s="10">
+        <v>2.54</v>
+      </c>
+    </row>
+    <row r="14" spans="1:6">
+      <c r="A14" s="7" t="s">
         <v>41</v>
       </c>
-      <c r="B11" s="5" t="s">
+      <c r="B14" s="7" t="s">
         <v>9</v>
       </c>
-      <c r="C11" s="6">
-        <v>0.36</v>
-      </c>
-      <c r="D11" s="6">
+      <c r="C14" s="8">
         <v>-1.19</v>
       </c>
-      <c r="E11" s="7">
-        <v>-1.55</v>
-      </c>
-    </row>
-    <row r="12" spans="1:6">
-      <c r="A12" s="5" t="s">
+      <c r="D14" s="8">
+        <v>2.96</v>
+      </c>
+      <c r="E14" s="10">
+        <v>4.15</v>
+      </c>
+    </row>
+    <row r="15" spans="1:6">
+      <c r="A15" s="7" t="s">
         <v>42</v>
       </c>
-      <c r="B12" s="5" t="s">
+      <c r="B15" s="7" t="s">
         <v>9</v>
       </c>
-      <c r="C12" s="6">
-        <v>-6.73</v>
-      </c>
-      <c r="D12" s="6">
+      <c r="C15" s="8">
         <v>-7.87</v>
       </c>
-      <c r="E12" s="7">
-        <v>-1.14</v>
-      </c>
-    </row>
-    <row r="13" spans="1:6">
-      <c r="A13" s="5" t="s">
+      <c r="D15" s="8">
+        <v>-3.14</v>
+      </c>
+      <c r="E15" s="10">
+        <v>4.73</v>
+      </c>
+    </row>
+    <row r="16" spans="1:6">
+      <c r="A16" s="7" t="s">
         <v>43</v>
       </c>
-      <c r="B13" s="5" t="s">
+      <c r="B16" s="7" t="s">
         <v>9</v>
       </c>
-      <c r="C13" s="6">
-        <v>-0.68</v>
-      </c>
-      <c r="D13" s="6">
+      <c r="C16" s="8">
         <v>3.06</v>
       </c>
-      <c r="E13" s="8">
-        <v>3.74</v>
-      </c>
-    </row>
-    <row r="14" spans="1:6">
-      <c r="A14" s="5" t="s">
+      <c r="D16" s="8">
+        <v>15.79</v>
+      </c>
+      <c r="E16" s="10">
+        <v>12.73</v>
+      </c>
+    </row>
+    <row r="17" spans="1:5">
+      <c r="A17" s="7" t="s">
         <v>37</v>
       </c>
-      <c r="B14" s="5" t="s">
+      <c r="B17" s="7" t="s">
         <v>8</v>
       </c>
-      <c r="C14" s="6">
-        <v>-1.87</v>
-      </c>
-      <c r="D14" s="6">
+      <c r="C17" s="8">
         <v>-0.53</v>
       </c>
-      <c r="E14" s="8">
-        <v>1.34</v>
-      </c>
-    </row>
-    <row r="15" spans="1:6">
-      <c r="A15" s="5" t="s">
+      <c r="D17" s="8">
+        <v>-1.66</v>
+      </c>
+      <c r="E17" s="9">
+        <v>-1.13</v>
+      </c>
+    </row>
+    <row r="18" spans="1:5">
+      <c r="A18" s="7" t="s">
         <v>38</v>
       </c>
-      <c r="B15" s="5" t="s">
+      <c r="B18" s="7" t="s">
         <v>8</v>
       </c>
-      <c r="C15" s="6">
-        <v>-1</v>
-      </c>
-      <c r="D15" s="6">
+      <c r="C18" s="8">
         <v>1.97</v>
       </c>
-      <c r="E15" s="8">
-        <v>2.97</v>
-      </c>
-    </row>
-    <row r="16" spans="1:6">
-      <c r="A16" s="5" t="s">
+      <c r="D18" s="8">
+        <v>1.57</v>
+      </c>
+      <c r="E18" s="9">
+        <v>-0.4</v>
+      </c>
+    </row>
+    <row r="19" spans="1:5">
+      <c r="A19" s="7" t="s">
         <v>39</v>
       </c>
-      <c r="B16" s="5" t="s">
+      <c r="B19" s="7" t="s">
         <v>8</v>
       </c>
-      <c r="C16" s="6">
-        <v>-2.77</v>
-      </c>
-      <c r="D16" s="6">
+      <c r="C19" s="8">
         <v>-1.51</v>
       </c>
-      <c r="E16" s="8">
-        <v>1.26</v>
-      </c>
-    </row>
-    <row r="17" spans="1:5">
-      <c r="A17" s="5" t="s">
+      <c r="D19" s="8">
+        <v>2.12</v>
+      </c>
+      <c r="E19" s="10">
+        <v>3.63</v>
+      </c>
+    </row>
+    <row r="20" spans="1:5">
+      <c r="A20" s="7" t="s">
         <v>40</v>
       </c>
-      <c r="B17" s="5" t="s">
+      <c r="B20" s="7" t="s">
         <v>8</v>
       </c>
-      <c r="C17" s="6">
-        <v>-3.33</v>
-      </c>
-      <c r="D17" s="6">
+      <c r="C20" s="8">
         <v>-1.73</v>
       </c>
-      <c r="E17" s="8">
-        <v>1.6</v>
-      </c>
-    </row>
-    <row r="18" spans="1:5">
-      <c r="A18" s="5" t="s">
+      <c r="D20" s="8">
+        <v>0.52</v>
+      </c>
+      <c r="E20" s="10">
+        <v>2.25</v>
+      </c>
+    </row>
+    <row r="21" spans="1:5">
+      <c r="A21" s="7" t="s">
         <v>41</v>
       </c>
-      <c r="B18" s="5" t="s">
+      <c r="B21" s="7" t="s">
         <v>8</v>
       </c>
-      <c r="C18" s="6">
-        <v>2.47</v>
-      </c>
-      <c r="D18" s="6">
+      <c r="C21" s="8">
         <v>0.77</v>
       </c>
-      <c r="E18" s="7">
-        <v>-1.7</v>
-      </c>
-    </row>
-    <row r="19" spans="1:5">
-      <c r="A19" s="5" t="s">
+      <c r="D21" s="8">
+        <v>4.75</v>
+      </c>
+      <c r="E21" s="10">
+        <v>3.98</v>
+      </c>
+    </row>
+    <row r="22" spans="1:5">
+      <c r="A22" s="7" t="s">
         <v>42</v>
       </c>
-      <c r="B19" s="5" t="s">
+      <c r="B22" s="7" t="s">
         <v>8</v>
       </c>
-      <c r="C19" s="6">
-        <v>-1.28</v>
-      </c>
-      <c r="D19" s="6">
+      <c r="C22" s="8">
         <v>-0.04</v>
       </c>
-      <c r="E19" s="8">
-        <v>1.24</v>
-      </c>
-    </row>
-    <row r="20" spans="1:5">
-      <c r="A20" s="5" t="s">
+      <c r="D22" s="8">
+        <v>3.68</v>
+      </c>
+      <c r="E22" s="10">
+        <v>3.72</v>
+      </c>
+    </row>
+    <row r="23" spans="1:5">
+      <c r="A23" s="7" t="s">
         <v>43</v>
       </c>
-      <c r="B20" s="5" t="s">
+      <c r="B23" s="7" t="s">
         <v>8</v>
       </c>
-      <c r="C20" s="6">
-        <v>-2.47</v>
-      </c>
-      <c r="D20" s="6">
+      <c r="C23" s="8">
         <v>4.27</v>
       </c>
-      <c r="E20" s="8">
-        <v>6.74</v>
-      </c>
-    </row>
-    <row r="21" spans="1:5">
-      <c r="A21" s="5" t="s">
+      <c r="D23" s="8">
+        <v>16.47</v>
+      </c>
+      <c r="E23" s="10">
+        <v>12.2</v>
+      </c>
+    </row>
+    <row r="24" spans="1:5">
+      <c r="A24" s="7" t="s">
         <v>37</v>
       </c>
-      <c r="B21" s="5" t="s">
+      <c r="B24" s="7" t="s">
         <v>11</v>
       </c>
-      <c r="C21" s="6">
-        <v>28.09</v>
-      </c>
-      <c r="D21" s="6">
+      <c r="C24" s="8">
         <v>26.85</v>
       </c>
-      <c r="E21" s="7">
-        <v>-1.24</v>
-      </c>
-    </row>
-    <row r="22" spans="1:5">
-      <c r="A22" s="5" t="s">
+      <c r="D24" s="8">
+        <v>27.39</v>
+      </c>
+      <c r="E24" s="10">
+        <v>0.54</v>
+      </c>
+    </row>
+    <row r="25" spans="1:5">
+      <c r="A25" s="7" t="s">
         <v>38</v>
       </c>
-      <c r="B22" s="5" t="s">
+      <c r="B25" s="7" t="s">
         <v>11</v>
       </c>
-      <c r="C22" s="6">
-        <v>125.87</v>
-      </c>
-      <c r="D22" s="6">
+      <c r="C25" s="8">
         <v>116.37</v>
       </c>
-      <c r="E22" s="7">
-        <v>-9.5</v>
-      </c>
-    </row>
-    <row r="23" spans="1:5">
-      <c r="A23" s="5" t="s">
+      <c r="D25" s="8">
+        <v>96.19</v>
+      </c>
+      <c r="E25" s="9">
+        <v>-20.18</v>
+      </c>
+    </row>
+    <row r="26" spans="1:5">
+      <c r="A26" s="7" t="s">
         <v>39</v>
       </c>
-      <c r="B23" s="5" t="s">
+      <c r="B26" s="7" t="s">
         <v>11</v>
       </c>
-      <c r="C23" s="6">
-        <v>-44.97</v>
-      </c>
-      <c r="D23" s="6">
+      <c r="C26" s="8">
         <v>-46.52</v>
       </c>
-      <c r="E23" s="7">
-        <v>-1.55</v>
-      </c>
-    </row>
-    <row r="24" spans="1:5">
-      <c r="A24" s="5" t="s">
+      <c r="D26" s="8">
+        <v>-44.85</v>
+      </c>
+      <c r="E26" s="10">
+        <v>1.67</v>
+      </c>
+    </row>
+    <row r="27" spans="1:5">
+      <c r="A27" s="7" t="s">
         <v>40</v>
       </c>
-      <c r="B24" s="5" t="s">
+      <c r="B27" s="7" t="s">
         <v>11</v>
       </c>
-      <c r="C24" s="6">
-        <v>-11.08</v>
-      </c>
-      <c r="D24" s="6">
+      <c r="C27" s="8">
         <v>-11.36</v>
       </c>
-      <c r="E24" s="7">
-        <v>-0.28</v>
-      </c>
-    </row>
-    <row r="25" spans="1:5">
-      <c r="A25" s="5" t="s">
+      <c r="D27" s="8">
+        <v>-10.76</v>
+      </c>
+      <c r="E27" s="10">
+        <v>0.6</v>
+      </c>
+    </row>
+    <row r="28" spans="1:5">
+      <c r="A28" s="7" t="s">
         <v>41</v>
       </c>
-      <c r="B25" s="5" t="s">
+      <c r="B28" s="7" t="s">
         <v>11</v>
       </c>
-      <c r="C25" s="6">
-        <v>-15.23</v>
-      </c>
-      <c r="D25" s="6">
+      <c r="C28" s="8">
         <v>-17.73</v>
       </c>
-      <c r="E25" s="7">
-        <v>-2.5</v>
-      </c>
-    </row>
-    <row r="26" spans="1:5">
-      <c r="A26" s="5" t="s">
+      <c r="D28" s="8">
+        <v>-14.56</v>
+      </c>
+      <c r="E28" s="10">
+        <v>3.17</v>
+      </c>
+    </row>
+    <row r="29" spans="1:5">
+      <c r="A29" s="7" t="s">
         <v>42</v>
       </c>
-      <c r="B26" s="5" t="s">
+      <c r="B29" s="7" t="s">
         <v>11</v>
       </c>
-      <c r="C26" s="6">
-        <v>1.8</v>
-      </c>
-      <c r="D26" s="6">
+      <c r="C29" s="8">
         <v>0.13</v>
       </c>
-      <c r="E26" s="7">
-        <v>-1.67</v>
-      </c>
-    </row>
-    <row r="27" spans="1:5">
-      <c r="A27" s="5" t="s">
+      <c r="D29" s="8">
+        <v>4.69</v>
+      </c>
+      <c r="E29" s="10">
+        <v>4.56</v>
+      </c>
+    </row>
+    <row r="30" spans="1:5">
+      <c r="A30" s="7" t="s">
         <v>43</v>
       </c>
-      <c r="B27" s="5" t="s">
+      <c r="B30" s="7" t="s">
         <v>11</v>
       </c>
-      <c r="C27" s="6">
-        <v>-2.35</v>
-      </c>
-      <c r="D27" s="6">
+      <c r="C30" s="8">
         <v>2.56</v>
       </c>
-      <c r="E27" s="8">
-        <v>4.91</v>
-      </c>
-    </row>
-    <row r="28" spans="1:5">
-      <c r="A28" s="5" t="s">
+      <c r="D30" s="8">
+        <v>16.09</v>
+      </c>
+      <c r="E30" s="10">
+        <v>13.53</v>
+      </c>
+    </row>
+    <row r="31" spans="1:5">
+      <c r="A31" s="7" t="s">
         <v>37</v>
       </c>
-      <c r="B28" s="5" t="s">
+      <c r="B31" s="7" t="s">
         <v>10</v>
       </c>
-      <c r="C28" s="6">
-        <v>12.45</v>
-      </c>
-      <c r="D28" s="6">
+      <c r="C31" s="8">
         <v>13.35</v>
       </c>
-      <c r="E28" s="8">
-        <v>0.9</v>
-      </c>
-    </row>
-    <row r="29" spans="1:5">
-      <c r="A29" s="5" t="s">
+      <c r="D31" s="8">
+        <v>16.92</v>
+      </c>
+      <c r="E31" s="10">
+        <v>3.57</v>
+      </c>
+    </row>
+    <row r="32" spans="1:5">
+      <c r="A32" s="7" t="s">
         <v>38</v>
       </c>
-      <c r="B29" s="5" t="s">
+      <c r="B32" s="7" t="s">
         <v>10</v>
       </c>
-      <c r="C29" s="6">
-        <v>-16.85</v>
-      </c>
-      <c r="D29" s="6">
+      <c r="C32" s="8">
         <v>-11.66</v>
       </c>
-      <c r="E29" s="8">
-        <v>5.19</v>
-      </c>
-    </row>
-    <row r="30" spans="1:5">
-      <c r="A30" s="5" t="s">
+      <c r="D32" s="8">
+        <v>-14.27</v>
+      </c>
+      <c r="E32" s="9">
+        <v>-2.61</v>
+      </c>
+    </row>
+    <row r="33" spans="1:5">
+      <c r="A33" s="7" t="s">
         <v>39</v>
       </c>
-      <c r="B30" s="5" t="s">
+      <c r="B33" s="7" t="s">
         <v>10</v>
       </c>
-      <c r="C30" s="6">
-        <v>-1.29</v>
-      </c>
-      <c r="D30" s="6">
+      <c r="C33" s="8">
         <v>0.08</v>
       </c>
-      <c r="E30" s="8">
-        <v>1.37</v>
-      </c>
-    </row>
-    <row r="31" spans="1:5">
-      <c r="A31" s="5" t="s">
+      <c r="D33" s="8">
+        <v>1.43</v>
+      </c>
+      <c r="E33" s="10">
+        <v>1.35</v>
+      </c>
+    </row>
+    <row r="34" spans="1:5">
+      <c r="A34" s="7" t="s">
         <v>40</v>
       </c>
-      <c r="B31" s="5" t="s">
+      <c r="B34" s="7" t="s">
         <v>10</v>
       </c>
-      <c r="C31" s="6">
-        <v>3.79</v>
-      </c>
-      <c r="D31" s="6">
+      <c r="C34" s="8">
         <v>3.31</v>
       </c>
-      <c r="E31" s="7">
-        <v>-0.48</v>
-      </c>
-    </row>
-    <row r="32" spans="1:5">
-      <c r="A32" s="5" t="s">
+      <c r="D34" s="8">
+        <v>3.71</v>
+      </c>
+      <c r="E34" s="10">
+        <v>0.4</v>
+      </c>
+    </row>
+    <row r="35" spans="1:5">
+      <c r="A35" s="7" t="s">
         <v>41</v>
       </c>
-      <c r="B32" s="5" t="s">
+      <c r="B35" s="7" t="s">
         <v>10</v>
       </c>
-      <c r="C32" s="6">
-        <v>4.72</v>
-      </c>
-      <c r="D32" s="6">
+      <c r="C35" s="8">
         <v>5.37</v>
       </c>
-      <c r="E32" s="8">
-        <v>0.65</v>
-      </c>
-    </row>
-    <row r="33" spans="1:5">
-      <c r="A33" s="5" t="s">
+      <c r="D35" s="8">
+        <v>8.18</v>
+      </c>
+      <c r="E35" s="10">
+        <v>2.81</v>
+      </c>
+    </row>
+    <row r="36" spans="1:5">
+      <c r="A36" s="7" t="s">
         <v>42</v>
       </c>
-      <c r="B33" s="5" t="s">
+      <c r="B36" s="7" t="s">
         <v>10</v>
       </c>
-      <c r="C33" s="6">
-        <v>5.47</v>
-      </c>
-      <c r="D33" s="6">
+      <c r="C36" s="8">
         <v>4.82</v>
       </c>
-      <c r="E33" s="7">
-        <v>-0.65</v>
-      </c>
-    </row>
-    <row r="34" spans="1:5">
-      <c r="A34" s="5" t="s">
+      <c r="D36" s="8">
+        <v>5.27</v>
+      </c>
+      <c r="E36" s="10">
+        <v>0.45</v>
+      </c>
+    </row>
+    <row r="37" spans="1:5">
+      <c r="A37" s="7" t="s">
         <v>43</v>
       </c>
-      <c r="B34" s="5" t="s">
+      <c r="B37" s="7" t="s">
         <v>10</v>
       </c>
-      <c r="C34" s="6">
+      <c r="C37" s="8">
+        <v>4.61</v>
+      </c>
+      <c r="D37" s="8">
+        <v>16.98</v>
+      </c>
+      <c r="E37" s="10">
+        <v>12.37</v>
+      </c>
+    </row>
+    <row r="38" spans="1:5">
+      <c r="A38" s="7" t="s">
+        <v>37</v>
+      </c>
+      <c r="B38" s="7" t="s">
+        <v>6</v>
+      </c>
+      <c r="C38" s="8">
+        <v>-8.07</v>
+      </c>
+      <c r="D38" s="8">
+        <v>-7.77</v>
+      </c>
+      <c r="E38" s="10">
+        <v>0.3</v>
+      </c>
+    </row>
+    <row r="39" spans="1:5">
+      <c r="A39" s="7" t="s">
+        <v>38</v>
+      </c>
+      <c r="B39" s="7" t="s">
+        <v>6</v>
+      </c>
+      <c r="C39" s="8">
+        <v>-23.35</v>
+      </c>
+      <c r="D39" s="8">
+        <v>-24.53</v>
+      </c>
+      <c r="E39" s="9">
         <v>-1.18</v>
       </c>
-      <c r="D34" s="6">
-        <v>4.61</v>
-      </c>
-      <c r="E34" s="8">
-        <v>5.79</v>
-      </c>
-    </row>
-    <row r="35" spans="1:5">
-      <c r="A35" s="5" t="s">
+    </row>
+    <row r="40" spans="1:5">
+      <c r="A40" s="7" t="s">
+        <v>39</v>
+      </c>
+      <c r="B40" s="7" t="s">
+        <v>6</v>
+      </c>
+      <c r="C40" s="8">
+        <v>-45.85</v>
+      </c>
+      <c r="D40" s="8">
+        <v>-44.15</v>
+      </c>
+      <c r="E40" s="10">
+        <v>1.7</v>
+      </c>
+    </row>
+    <row r="41" spans="1:5">
+      <c r="A41" s="7" t="s">
+        <v>40</v>
+      </c>
+      <c r="B41" s="7" t="s">
+        <v>6</v>
+      </c>
+      <c r="C41" s="8">
+        <v>-16.23</v>
+      </c>
+      <c r="D41" s="8">
+        <v>-15.17</v>
+      </c>
+      <c r="E41" s="10">
+        <v>1.06</v>
+      </c>
+    </row>
+    <row r="42" spans="1:5">
+      <c r="A42" s="7" t="s">
+        <v>41</v>
+      </c>
+      <c r="B42" s="7" t="s">
+        <v>6</v>
+      </c>
+      <c r="C42" s="8">
+        <v>-16.53</v>
+      </c>
+      <c r="D42" s="8">
+        <v>-13.78</v>
+      </c>
+      <c r="E42" s="10">
+        <v>2.75</v>
+      </c>
+    </row>
+    <row r="43" spans="1:5">
+      <c r="A43" s="7" t="s">
+        <v>42</v>
+      </c>
+      <c r="B43" s="7" t="s">
+        <v>6</v>
+      </c>
+      <c r="C43" s="8">
+        <v>-12.94</v>
+      </c>
+      <c r="D43" s="8">
+        <v>-9.98</v>
+      </c>
+      <c r="E43" s="10">
+        <v>2.96</v>
+      </c>
+    </row>
+    <row r="44" spans="1:5">
+      <c r="A44" s="7" t="s">
+        <v>43</v>
+      </c>
+      <c r="B44" s="7" t="s">
+        <v>6</v>
+      </c>
+      <c r="C44" s="8">
+        <v>-5.06</v>
+      </c>
+      <c r="D44" s="8">
+        <v>0</v>
+      </c>
+      <c r="E44" s="10">
+        <v>5.06</v>
+      </c>
+    </row>
+    <row r="45" spans="1:5">
+      <c r="A45" s="7" t="s">
         <v>37</v>
       </c>
-      <c r="B35" s="5" t="s">
-        <v>6</v>
-      </c>
-      <c r="C35" s="6">
-        <v>-7.29</v>
-      </c>
-      <c r="D35" s="6">
-        <v>-8.07</v>
-      </c>
-      <c r="E35" s="7">
-        <v>-0.78</v>
-      </c>
-    </row>
-    <row r="36" spans="1:5">
-      <c r="A36" s="5" t="s">
+      <c r="B45" s="7" t="s">
+        <v>2</v>
+      </c>
+      <c r="C45" s="8">
+        <v>11363</v>
+      </c>
+      <c r="D45" s="8">
+        <v>11400</v>
+      </c>
+      <c r="E45" s="10">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="46" spans="1:5">
+      <c r="A46" s="7" t="s">
         <v>38</v>
       </c>
-      <c r="B36" s="5" t="s">
-        <v>6</v>
-      </c>
-      <c r="C36" s="6">
-        <v>-23.12</v>
-      </c>
-      <c r="D36" s="6">
-        <v>-23.35</v>
-      </c>
-      <c r="E36" s="7">
-        <v>-0.23</v>
-      </c>
-    </row>
-    <row r="37" spans="1:5">
-      <c r="A37" s="5" t="s">
+      <c r="B46" s="7" t="s">
+        <v>2</v>
+      </c>
+      <c r="C46" s="8">
+        <v>513.75</v>
+      </c>
+      <c r="D46" s="8">
+        <v>505.85</v>
+      </c>
+      <c r="E46" s="9">
+        <v>-7.9</v>
+      </c>
+    </row>
+    <row r="47" spans="1:5">
+      <c r="A47" s="7" t="s">
         <v>39</v>
       </c>
-      <c r="B37" s="5" t="s">
-        <v>6</v>
-      </c>
-      <c r="C37" s="6">
-        <v>-46.1</v>
-      </c>
-      <c r="D37" s="6">
-        <v>-45.85</v>
-      </c>
-      <c r="E37" s="8">
-        <v>0.25</v>
-      </c>
-    </row>
-    <row r="38" spans="1:5">
-      <c r="A38" s="5" t="s">
+      <c r="B47" s="7" t="s">
+        <v>2</v>
+      </c>
+      <c r="C47" s="8">
+        <v>323.45</v>
+      </c>
+      <c r="D47" s="8">
+        <v>329.4</v>
+      </c>
+      <c r="E47" s="10">
+        <v>5.95</v>
+      </c>
+    </row>
+    <row r="48" spans="1:5">
+      <c r="A48" s="7" t="s">
         <v>40</v>
       </c>
-      <c r="B38" s="5" t="s">
-        <v>6</v>
-      </c>
-      <c r="C38" s="6">
-        <v>-15.01</v>
-      </c>
-      <c r="D38" s="6">
-        <v>-16.23</v>
-      </c>
-      <c r="E38" s="7">
-        <v>-1.22</v>
-      </c>
-    </row>
-    <row r="39" spans="1:5">
-      <c r="A39" s="5" t="s">
+      <c r="B48" s="7" t="s">
+        <v>2</v>
+      </c>
+      <c r="C48" s="8">
+        <v>1823.4</v>
+      </c>
+      <c r="D48" s="8">
+        <v>1846.5</v>
+      </c>
+      <c r="E48" s="10">
+        <v>23.1</v>
+      </c>
+    </row>
+    <row r="49" spans="1:5">
+      <c r="A49" s="7" t="s">
         <v>41</v>
       </c>
-      <c r="B39" s="5" t="s">
-        <v>6</v>
-      </c>
-      <c r="C39" s="6">
-        <v>-16.08</v>
-      </c>
-      <c r="D39" s="6">
-        <v>-16.53</v>
-      </c>
-      <c r="E39" s="7">
-        <v>-0.45</v>
-      </c>
-    </row>
-    <row r="40" spans="1:5">
-      <c r="A40" s="5" t="s">
+      <c r="B49" s="7" t="s">
+        <v>2</v>
+      </c>
+      <c r="C49" s="8">
+        <v>11185</v>
+      </c>
+      <c r="D49" s="8">
+        <v>11449</v>
+      </c>
+      <c r="E49" s="10">
+        <v>264</v>
+      </c>
+    </row>
+    <row r="50" spans="1:5">
+      <c r="A50" s="7" t="s">
         <v>42</v>
       </c>
-      <c r="B40" s="5" t="s">
-        <v>6</v>
-      </c>
-      <c r="C40" s="6">
-        <v>-11.87</v>
-      </c>
-      <c r="D40" s="6">
-        <v>-12.94</v>
-      </c>
-      <c r="E40" s="7">
-        <v>-1.07</v>
-      </c>
-    </row>
-    <row r="41" spans="1:5">
-      <c r="A41" s="5" t="s">
+      <c r="B50" s="7" t="s">
+        <v>2</v>
+      </c>
+      <c r="C50" s="8">
+        <v>1008.8</v>
+      </c>
+      <c r="D50" s="8">
+        <v>1043.2</v>
+      </c>
+      <c r="E50" s="10">
+        <v>34.4</v>
+      </c>
+    </row>
+    <row r="51" spans="1:5">
+      <c r="A51" s="7" t="s">
         <v>43</v>
       </c>
-      <c r="B41" s="5" t="s">
-        <v>6</v>
-      </c>
-      <c r="C41" s="6">
-        <v>-8.67</v>
-      </c>
-      <c r="D41" s="6">
-        <v>-5.06</v>
-      </c>
-      <c r="E41" s="8">
-        <v>3.61</v>
-      </c>
-    </row>
-    <row r="42" spans="1:5">
-      <c r="A42" s="5" t="s">
+      <c r="B51" s="7" t="s">
+        <v>2</v>
+      </c>
+      <c r="C51" s="8">
+        <v>141.41</v>
+      </c>
+      <c r="D51" s="8">
+        <v>157.11</v>
+      </c>
+      <c r="E51" s="10">
+        <v>15.7</v>
+      </c>
+    </row>
+    <row r="52" spans="1:5">
+      <c r="A52" s="7" t="s">
         <v>37</v>
       </c>
-      <c r="B42" s="5" t="s">
-        <v>2</v>
-      </c>
-      <c r="C42" s="6">
-        <v>11460</v>
-      </c>
-      <c r="D42" s="6">
-        <v>11363</v>
-      </c>
-      <c r="E42" s="7">
-        <v>-97</v>
-      </c>
-    </row>
-    <row r="43" spans="1:5">
-      <c r="A43" s="5" t="s">
+      <c r="B52" s="7" t="s">
+        <v>24</v>
+      </c>
+      <c r="C52" s="8">
+        <v>41.44</v>
+      </c>
+      <c r="D52" s="8">
+        <v>42.86</v>
+      </c>
+      <c r="E52" s="10">
+        <v>1.42</v>
+      </c>
+    </row>
+    <row r="53" spans="1:5">
+      <c r="A53" s="7" t="s">
         <v>38</v>
       </c>
-      <c r="B43" s="5" t="s">
-        <v>2</v>
-      </c>
-      <c r="C43" s="6">
-        <v>515.3</v>
-      </c>
-      <c r="D43" s="6">
-        <v>513.75</v>
-      </c>
-      <c r="E43" s="7">
-        <v>-1.55</v>
-      </c>
-    </row>
-    <row r="44" spans="1:5">
-      <c r="A44" s="5" t="s">
+      <c r="B53" s="7" t="s">
+        <v>24</v>
+      </c>
+      <c r="C53" s="8">
+        <v>52.23</v>
+      </c>
+      <c r="D53" s="8">
+        <v>48.92</v>
+      </c>
+      <c r="E53" s="9">
+        <v>-3.31</v>
+      </c>
+    </row>
+    <row r="54" spans="1:5">
+      <c r="A54" s="7" t="s">
         <v>39</v>
       </c>
-      <c r="B44" s="5" t="s">
-        <v>2</v>
-      </c>
-      <c r="C44" s="6">
-        <v>326</v>
-      </c>
-      <c r="D44" s="6">
-        <v>323.45</v>
-      </c>
-      <c r="E44" s="7">
-        <v>-2.55</v>
-      </c>
-    </row>
-    <row r="45" spans="1:5">
-      <c r="A45" s="5" t="s">
+      <c r="B54" s="7" t="s">
+        <v>24</v>
+      </c>
+      <c r="C54" s="8">
+        <v>40.41</v>
+      </c>
+      <c r="D54" s="8">
+        <v>46.13</v>
+      </c>
+      <c r="E54" s="10">
+        <v>5.72</v>
+      </c>
+    </row>
+    <row r="55" spans="1:5">
+      <c r="A55" s="7" t="s">
         <v>40</v>
       </c>
-      <c r="B45" s="5" t="s">
-        <v>2</v>
-      </c>
-      <c r="C45" s="6">
-        <v>1849.8</v>
-      </c>
-      <c r="D45" s="6">
-        <v>1823.4</v>
-      </c>
-      <c r="E45" s="7">
-        <v>-26.4</v>
-      </c>
-    </row>
-    <row r="46" spans="1:5">
-      <c r="A46" s="5" t="s">
+      <c r="B55" s="7" t="s">
+        <v>24</v>
+      </c>
+      <c r="C55" s="8">
+        <v>28.99</v>
+      </c>
+      <c r="D55" s="8">
+        <v>35.17</v>
+      </c>
+      <c r="E55" s="10">
+        <v>6.18</v>
+      </c>
+    </row>
+    <row r="56" spans="1:5">
+      <c r="A56" s="7" t="s">
         <v>41</v>
       </c>
-      <c r="B46" s="5" t="s">
-        <v>2</v>
-      </c>
-      <c r="C46" s="6">
-        <v>11409</v>
-      </c>
-      <c r="D46" s="6">
-        <v>11185</v>
-      </c>
-      <c r="E46" s="7">
-        <v>-224</v>
-      </c>
-    </row>
-    <row r="47" spans="1:5">
-      <c r="A47" s="5" t="s">
+      <c r="B56" s="7" t="s">
+        <v>24</v>
+      </c>
+      <c r="C56" s="8">
+        <v>50.29</v>
+      </c>
+      <c r="D56" s="8">
+        <v>56.66</v>
+      </c>
+      <c r="E56" s="10">
+        <v>6.37</v>
+      </c>
+    </row>
+    <row r="57" spans="1:5">
+      <c r="A57" s="7" t="s">
         <v>42</v>
       </c>
-      <c r="B47" s="5" t="s">
-        <v>2</v>
-      </c>
-      <c r="C47" s="6">
-        <v>1021.3</v>
-      </c>
-      <c r="D47" s="6">
-        <v>1008.8</v>
-      </c>
-      <c r="E47" s="7">
-        <v>-12.5</v>
-      </c>
-    </row>
-    <row r="48" spans="1:5">
-      <c r="A48" s="5" t="s">
+      <c r="B57" s="7" t="s">
+        <v>24</v>
+      </c>
+      <c r="C57" s="8">
+        <v>37.45</v>
+      </c>
+      <c r="D57" s="8">
+        <v>49</v>
+      </c>
+      <c r="E57" s="10">
+        <v>11.55</v>
+      </c>
+    </row>
+    <row r="58" spans="1:5">
+      <c r="A58" s="7" t="s">
         <v>43</v>
       </c>
-      <c r="B48" s="5" t="s">
-        <v>2</v>
-      </c>
-      <c r="C48" s="6">
-        <v>136.03</v>
-      </c>
-      <c r="D48" s="6">
-        <v>141.41</v>
-      </c>
-      <c r="E48" s="8">
-        <v>5.38</v>
-      </c>
-    </row>
-    <row r="49" spans="1:5">
-      <c r="A49" s="5" t="s">
+      <c r="B58" s="7" t="s">
+        <v>24</v>
+      </c>
+      <c r="C58" s="8">
+        <v>59.15</v>
+      </c>
+      <c r="D58" s="8">
+        <v>75.55</v>
+      </c>
+      <c r="E58" s="10">
+        <v>16.4</v>
+      </c>
+    </row>
+    <row r="59" spans="1:5">
+      <c r="A59" s="7" t="s">
+        <v>37</v>
+      </c>
+      <c r="B59" s="7" t="s">
+        <v>31</v>
+      </c>
+      <c r="C59" s="8">
+        <v>-31.02</v>
+      </c>
+      <c r="D59" s="8">
+        <v>-28.25</v>
+      </c>
+      <c r="E59" s="10">
+        <v>2.77</v>
+      </c>
+    </row>
+    <row r="60" spans="1:5">
+      <c r="A60" s="7" t="s">
+        <v>38</v>
+      </c>
+      <c r="B60" s="7" t="s">
+        <v>31</v>
+      </c>
+      <c r="C60" s="8">
+        <v>-49.75</v>
+      </c>
+      <c r="D60" s="8">
+        <v>-37.56</v>
+      </c>
+      <c r="E60" s="10">
+        <v>12.19</v>
+      </c>
+    </row>
+    <row r="61" spans="1:5">
+      <c r="A61" s="7" t="s">
+        <v>39</v>
+      </c>
+      <c r="B61" s="7" t="s">
+        <v>31</v>
+      </c>
+      <c r="C61" s="8">
+        <v>-46.14</v>
+      </c>
+      <c r="D61" s="8">
+        <v>-33.47</v>
+      </c>
+      <c r="E61" s="10">
+        <v>12.67</v>
+      </c>
+    </row>
+    <row r="62" spans="1:5">
+      <c r="A62" s="7" t="s">
+        <v>40</v>
+      </c>
+      <c r="B62" s="7" t="s">
+        <v>31</v>
+      </c>
+      <c r="C62" s="8">
+        <v>-30.17</v>
+      </c>
+      <c r="D62" s="8">
+        <v>33.45</v>
+      </c>
+      <c r="E62" s="10">
+        <v>63.62</v>
+      </c>
+    </row>
+    <row r="63" spans="1:5">
+      <c r="A63" s="7" t="s">
+        <v>41</v>
+      </c>
+      <c r="B63" s="7" t="s">
+        <v>31</v>
+      </c>
+      <c r="C63" s="8">
+        <v>60.33</v>
+      </c>
+      <c r="D63" s="8">
+        <v>-49.88</v>
+      </c>
+      <c r="E63" s="9">
+        <v>-110.21</v>
+      </c>
+    </row>
+    <row r="64" spans="1:5">
+      <c r="A64" s="7" t="s">
         <v>42</v>
       </c>
-      <c r="B49" s="5" t="s">
-        <v>13</v>
-      </c>
-      <c r="C49" s="6">
-        <v>71</v>
-      </c>
-      <c r="D49" s="6">
-        <v>57</v>
-      </c>
-      <c r="E49" s="7">
-        <v>-14</v>
-      </c>
-    </row>
-    <row r="50" spans="1:5">
-      <c r="A50" s="5" t="s">
+      <c r="B64" s="7" t="s">
+        <v>31</v>
+      </c>
+      <c r="C64" s="8">
+        <v>-9.84</v>
+      </c>
+      <c r="D64" s="8">
+        <v>67.2</v>
+      </c>
+      <c r="E64" s="10">
+        <v>77.04000000000001</v>
+      </c>
+    </row>
+    <row r="65" spans="1:5">
+      <c r="A65" s="7" t="s">
         <v>43</v>
       </c>
-      <c r="B50" s="5" t="s">
-        <v>13</v>
-      </c>
-      <c r="C50" s="6">
-        <v>57</v>
-      </c>
-      <c r="D50" s="6">
-        <v>71</v>
-      </c>
-      <c r="E50" s="8">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="51" spans="1:5">
-      <c r="A51" s="5" t="s">
-        <v>37</v>
-      </c>
-      <c r="B51" s="5" t="s">
-        <v>24</v>
-      </c>
-      <c r="C51" s="6">
-        <v>44.1</v>
-      </c>
-      <c r="D51" s="6">
-        <v>41.44</v>
-      </c>
-      <c r="E51" s="7">
-        <v>-2.66</v>
-      </c>
-    </row>
-    <row r="52" spans="1:5">
-      <c r="A52" s="5" t="s">
-        <v>38</v>
-      </c>
-      <c r="B52" s="5" t="s">
-        <v>24</v>
-      </c>
-      <c r="C52" s="6">
-        <v>52.88</v>
-      </c>
-      <c r="D52" s="6">
-        <v>52.23</v>
-      </c>
-      <c r="E52" s="7">
-        <v>-0.65</v>
-      </c>
-    </row>
-    <row r="53" spans="1:5">
-      <c r="A53" s="5" t="s">
-        <v>39</v>
-      </c>
-      <c r="B53" s="5" t="s">
-        <v>24</v>
-      </c>
-      <c r="C53" s="6">
-        <v>42.2</v>
-      </c>
-      <c r="D53" s="6">
-        <v>40.41</v>
-      </c>
-      <c r="E53" s="7">
-        <v>-1.79</v>
-      </c>
-    </row>
-    <row r="54" spans="1:5">
-      <c r="A54" s="5" t="s">
-        <v>40</v>
-      </c>
-      <c r="B54" s="5" t="s">
-        <v>24</v>
-      </c>
-      <c r="C54" s="6">
-        <v>32.25</v>
-      </c>
-      <c r="D54" s="6">
-        <v>28.99</v>
-      </c>
-      <c r="E54" s="7">
-        <v>-3.26</v>
-      </c>
-    </row>
-    <row r="55" spans="1:5">
-      <c r="A55" s="5" t="s">
-        <v>41</v>
-      </c>
-      <c r="B55" s="5" t="s">
-        <v>24</v>
-      </c>
-      <c r="C55" s="6">
-        <v>56.88</v>
-      </c>
-      <c r="D55" s="6">
-        <v>50.29</v>
-      </c>
-      <c r="E55" s="7">
-        <v>-6.59</v>
-      </c>
-    </row>
-    <row r="56" spans="1:5">
-      <c r="A56" s="5" t="s">
-        <v>42</v>
-      </c>
-      <c r="B56" s="5" t="s">
-        <v>24</v>
-      </c>
-      <c r="C56" s="6">
-        <v>40.55</v>
-      </c>
-      <c r="D56" s="6">
-        <v>37.45</v>
-      </c>
-      <c r="E56" s="7">
-        <v>-3.1</v>
-      </c>
-    </row>
-    <row r="57" spans="1:5">
-      <c r="A57" s="5" t="s">
-        <v>43</v>
-      </c>
-      <c r="B57" s="5" t="s">
-        <v>24</v>
-      </c>
-      <c r="C57" s="6">
-        <v>48.06</v>
-      </c>
-      <c r="D57" s="6">
-        <v>59.15</v>
-      </c>
-      <c r="E57" s="8">
-        <v>11.09</v>
-      </c>
-    </row>
-    <row r="58" spans="1:5">
-      <c r="A58" s="5" t="s">
-        <v>37</v>
-      </c>
-      <c r="B58" s="5" t="s">
+      <c r="B65" s="7" t="s">
         <v>31</v>
       </c>
-      <c r="C58" s="6">
-        <v>-59.04</v>
-      </c>
-      <c r="D58" s="6">
-        <v>-31.02</v>
-      </c>
-      <c r="E58" s="8">
-        <v>28.02</v>
-      </c>
-    </row>
-    <row r="59" spans="1:5">
-      <c r="A59" s="5" t="s">
-        <v>38</v>
-      </c>
-      <c r="B59" s="5" t="s">
-        <v>31</v>
-      </c>
-      <c r="C59" s="6">
-        <v>-36.72</v>
-      </c>
-      <c r="D59" s="6">
-        <v>-49.75</v>
-      </c>
-      <c r="E59" s="7">
-        <v>-13.03</v>
-      </c>
-    </row>
-    <row r="60" spans="1:5">
-      <c r="A60" s="5" t="s">
-        <v>39</v>
-      </c>
-      <c r="B60" s="5" t="s">
-        <v>31</v>
-      </c>
-      <c r="C60" s="6">
-        <v>-31.78</v>
-      </c>
-      <c r="D60" s="6">
-        <v>-46.14</v>
-      </c>
-      <c r="E60" s="7">
-        <v>-14.36</v>
-      </c>
-    </row>
-    <row r="61" spans="1:5">
-      <c r="A61" s="5" t="s">
-        <v>40</v>
-      </c>
-      <c r="B61" s="5" t="s">
-        <v>31</v>
-      </c>
-      <c r="C61" s="6">
-        <v>-53.99</v>
-      </c>
-      <c r="D61" s="6">
-        <v>-30.17</v>
-      </c>
-      <c r="E61" s="8">
-        <v>23.82</v>
-      </c>
-    </row>
-    <row r="62" spans="1:5">
-      <c r="A62" s="5" t="s">
-        <v>41</v>
-      </c>
-      <c r="B62" s="5" t="s">
-        <v>31</v>
-      </c>
-      <c r="C62" s="6">
-        <v>25.09</v>
-      </c>
-      <c r="D62" s="6">
-        <v>60.33</v>
-      </c>
-      <c r="E62" s="8">
-        <v>35.24</v>
-      </c>
-    </row>
-    <row r="63" spans="1:5">
-      <c r="A63" s="5" t="s">
-        <v>42</v>
-      </c>
-      <c r="B63" s="5" t="s">
-        <v>31</v>
-      </c>
-      <c r="C63" s="6">
-        <v>-19.85</v>
-      </c>
-      <c r="D63" s="6">
-        <v>-9.84</v>
-      </c>
-      <c r="E63" s="8">
-        <v>10.01</v>
-      </c>
-    </row>
-    <row r="64" spans="1:5">
-      <c r="A64" s="5" t="s">
-        <v>43</v>
-      </c>
-      <c r="B64" s="5" t="s">
-        <v>31</v>
-      </c>
-      <c r="C64" s="6">
-        <v>-34.09</v>
-      </c>
-      <c r="D64" s="6">
+      <c r="C65" s="8">
         <v>149.29</v>
       </c>
-      <c r="E64" s="8">
-        <v>183.38</v>
+      <c r="D65" s="8">
+        <v>2767.61</v>
+      </c>
+      <c r="E65" s="10">
+        <v>2618.32</v>
       </c>
     </row>
   </sheetData>
   <mergeCells count="2">
     <mergeCell ref="A1:F1"/>
-    <mergeCell ref="A5:E5"/>
+    <mergeCell ref="A8:E8"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -2938,60 +3024,60 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:9" ht="28" customHeight="1">
-      <c r="A1" s="9" t="s">
+      <c r="A1" s="11" t="s">
         <v>1</v>
       </c>
-      <c r="B1" s="9" t="s">
-        <v>65</v>
-      </c>
-      <c r="C1" s="9" t="s">
-        <v>66</v>
-      </c>
-      <c r="D1" s="9" t="s">
-        <v>67</v>
-      </c>
-      <c r="E1" s="9" t="s">
-        <v>68</v>
-      </c>
-      <c r="F1" s="9" t="s">
-        <v>69</v>
-      </c>
-      <c r="G1" s="9" t="s">
+      <c r="B1" s="11" t="s">
+        <v>80</v>
+      </c>
+      <c r="C1" s="11" t="s">
+        <v>81</v>
+      </c>
+      <c r="D1" s="11" t="s">
+        <v>82</v>
+      </c>
+      <c r="E1" s="11" t="s">
+        <v>83</v>
+      </c>
+      <c r="F1" s="11" t="s">
+        <v>84</v>
+      </c>
+      <c r="G1" s="11" t="s">
+        <v>85</v>
+      </c>
+      <c r="H1" s="11" t="s">
+        <v>86</v>
+      </c>
+      <c r="I1" s="11" t="s">
+        <v>87</v>
+      </c>
+    </row>
+    <row r="2" spans="1:9">
+      <c r="A2" s="12" t="s">
+        <v>44</v>
+      </c>
+      <c r="B2" s="13">
+        <v>60.8</v>
+      </c>
+      <c r="C2" s="14">
+        <v>7</v>
+      </c>
+      <c r="D2" s="13">
+        <v>50.6</v>
+      </c>
+      <c r="E2" s="13">
         <v>70</v>
       </c>
-      <c r="H1" s="9" t="s">
-        <v>71</v>
-      </c>
-      <c r="I1" s="9" t="s">
-        <v>72</v>
-      </c>
-    </row>
-    <row r="2" spans="1:9">
-      <c r="A2" s="10" t="s">
-        <v>44</v>
-      </c>
-      <c r="B2" s="11">
-        <v>60.8</v>
-      </c>
-      <c r="C2" s="12">
-        <v>7</v>
-      </c>
-      <c r="D2" s="11">
-        <v>44.3</v>
-      </c>
-      <c r="E2" s="11">
-        <v>70</v>
-      </c>
-      <c r="F2" s="11">
-        <v>-2.8</v>
-      </c>
-      <c r="G2" s="11">
-        <v>2.8</v>
-      </c>
-      <c r="H2" s="11">
+      <c r="F2" s="13">
+        <v>1.3</v>
+      </c>
+      <c r="G2" s="13">
+        <v>5.5</v>
+      </c>
+      <c r="H2" s="13">
         <v>57</v>
       </c>
-      <c r="I2" s="11">
+      <c r="I2" s="13">
         <v>30</v>
       </c>
     </row>
@@ -3093,49 +3179,49 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:7">
-      <c r="A1" s="13" t="s">
+      <c r="A1" s="15" t="s">
         <v>37</v>
       </c>
-      <c r="B1" s="13" t="s">
+      <c r="B1" s="15" t="s">
         <v>41</v>
       </c>
-      <c r="C1" s="13" t="s">
+      <c r="C1" s="15" t="s">
         <v>38</v>
       </c>
-      <c r="D1" s="13" t="s">
+      <c r="D1" s="15" t="s">
         <v>42</v>
       </c>
-      <c r="E1" s="13" t="s">
+      <c r="E1" s="15" t="s">
         <v>43</v>
       </c>
-      <c r="F1" s="13" t="s">
+      <c r="F1" s="15" t="s">
         <v>40</v>
       </c>
-      <c r="G1" s="13" t="s">
+      <c r="G1" s="15" t="s">
         <v>39</v>
       </c>
     </row>
     <row r="2" spans="1:7">
-      <c r="A2" s="14">
-        <v>0.2766</v>
-      </c>
-      <c r="B2" s="14">
-        <v>0.2057</v>
-      </c>
-      <c r="C2" s="14">
-        <v>0.1682</v>
-      </c>
-      <c r="D2" s="14">
-        <v>0.057</v>
-      </c>
-      <c r="E2" s="14">
-        <v>0.0207</v>
-      </c>
-      <c r="F2" s="14">
-        <v>0.0073</v>
-      </c>
-      <c r="G2" s="14">
-        <v>-0.2546</v>
+      <c r="A2" s="16">
+        <v>0.2746</v>
+      </c>
+      <c r="B2" s="16">
+        <v>0.1997</v>
+      </c>
+      <c r="C2" s="16">
+        <v>0.162</v>
+      </c>
+      <c r="D2" s="16">
+        <v>0.0612</v>
+      </c>
+      <c r="E2" s="16">
+        <v>0.0425</v>
+      </c>
+      <c r="F2" s="16">
+        <v>-0</v>
+      </c>
+      <c r="G2" s="16">
+        <v>-0.2536</v>
       </c>
     </row>
   </sheetData>

--- a/BAJAJ_GROUP_Technical_Metrics.xlsx
+++ b/BAJAJ_GROUP_Technical_Metrics.xlsx
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="282" uniqueCount="88">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="264" uniqueCount="73">
   <si>
     <t>Symbol</t>
   </si>
@@ -187,64 +187,19 @@
     <t>Curr Value</t>
   </si>
   <si>
-    <t>Near 52W High</t>
-  </si>
-  <si>
-    <t>-5.1% → 0.0%</t>
-  </si>
-  <si>
-    <t>🟢 BREAKOUT WATCH</t>
-  </si>
-  <si>
-    <t>-5.1%</t>
-  </si>
-  <si>
-    <t>0.0%</t>
-  </si>
-  <si>
-    <t>RSI Oversold Recovery</t>
-  </si>
-  <si>
-    <t>29.0 → 35.2</t>
-  </si>
-  <si>
-    <t>🟢 BULLISH</t>
-  </si>
-  <si>
-    <t>29.0</t>
-  </si>
-  <si>
-    <t>35.2</t>
-  </si>
-  <si>
-    <t>RSI Overbought Entry</t>
-  </si>
-  <si>
-    <t>59.1 → 75.5</t>
-  </si>
-  <si>
-    <t>⚠️ CAUTION</t>
-  </si>
-  <si>
-    <t>59.1</t>
-  </si>
-  <si>
-    <t>75.5</t>
-  </si>
-  <si>
     <t>RSI Momentum</t>
   </si>
   <si>
-    <t>52.2 → 48.9</t>
+    <t>56.7 → 44.3</t>
   </si>
   <si>
     <t>🔴 BEARISH</t>
   </si>
   <si>
-    <t>52.2</t>
-  </si>
-  <si>
-    <t>48.9</t>
+    <t>56.7</t>
+  </si>
+  <si>
+    <t>44.3</t>
   </si>
   <si>
     <t>▶  NUMERIC METRIC CHANGES (vs Previous Run)</t>
@@ -296,7 +251,7 @@
     <numFmt numFmtId="166" formatCode="0.0"/>
     <numFmt numFmtId="167" formatCode="0.00%"/>
   </numFmts>
-  <fonts count="7">
+  <fonts count="6">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -330,27 +285,20 @@
     </font>
     <font>
       <sz val="11"/>
-      <color rgb="FF006100"/>
+      <color rgb="FF9C0006"/>
       <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
     </font>
     <font>
       <sz val="11"/>
-      <color rgb="FF9C6500"/>
-      <name val="Calibri"/>
-      <family val="2"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF9C0006"/>
+      <color rgb="FF006100"/>
       <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="10">
+  <fills count="9">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -377,19 +325,13 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFC6EFCE"/>
+        <fgColor rgb="FFFFC7CE"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFFFEB9C"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFC7CE"/>
+        <fgColor rgb="FFC6EFCE"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -459,7 +401,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="17">
+  <cellXfs count="15">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="2" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
@@ -467,16 +409,14 @@
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="5" fillId="6" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="6" fillId="7" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1"/>
-    <xf numFmtId="165" fontId="6" fillId="7" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="165" fontId="4" fillId="5" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="3" fillId="8" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="165" fontId="5" fillId="6" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="3" fillId="7" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="9" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="8" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
     <xf numFmtId="166" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
@@ -485,7 +425,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="9" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="8" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="167" fontId="0" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
@@ -843,8 +783,8 @@
     <col min="13" max="13" width="10.7109375" customWidth="1"/>
     <col min="14" max="14" width="11.7109375" customWidth="1"/>
     <col min="15" max="15" width="10.7109375" customWidth="1"/>
-    <col min="16" max="16" width="9.7109375" customWidth="1"/>
-    <col min="17" max="19" width="10.7109375" customWidth="1"/>
+    <col min="16" max="17" width="9.7109375" customWidth="1"/>
+    <col min="18" max="19" width="10.7109375" customWidth="1"/>
     <col min="20" max="20" width="22.7109375" customWidth="1"/>
     <col min="21" max="21" width="9.7109375" customWidth="1"/>
     <col min="22" max="22" width="10.7109375" customWidth="1"/>
@@ -984,10 +924,10 @@
         <v>44</v>
       </c>
       <c r="C2">
-        <v>11400</v>
+        <v>11208</v>
       </c>
       <c r="D2">
-        <v>0.33</v>
+        <v>-1.68</v>
       </c>
       <c r="E2">
         <v>12361</v>
@@ -996,46 +936,46 @@
         <v>8506.780000000001</v>
       </c>
       <c r="G2">
-        <v>-7.77</v>
+        <v>-9.33</v>
       </c>
       <c r="H2">
-        <v>34.01</v>
+        <v>31.75</v>
       </c>
       <c r="I2">
-        <v>-1.66</v>
+        <v>-2.54</v>
       </c>
       <c r="J2">
-        <v>-3.39</v>
+        <v>-6.03</v>
       </c>
       <c r="K2">
-        <v>16.92</v>
+        <v>13.87</v>
       </c>
       <c r="L2">
-        <v>27.39</v>
+        <v>26.69</v>
       </c>
       <c r="M2">
-        <v>27.46</v>
+        <v>26.96</v>
       </c>
       <c r="N2">
         <v>85</v>
       </c>
       <c r="O2">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="P2">
-        <v>11427.4</v>
+        <v>11369</v>
       </c>
       <c r="Q2">
-        <v>11744.2</v>
+        <v>11718.4</v>
       </c>
       <c r="R2">
-        <v>11526.65</v>
+        <v>11544.35</v>
       </c>
       <c r="S2">
-        <v>10080.79</v>
+        <v>10091.92</v>
       </c>
       <c r="T2">
-        <v>13.09</v>
+        <v>11.06</v>
       </c>
       <c r="U2" t="s">
         <v>45</v>
@@ -1050,43 +990,43 @@
         <v>3</v>
       </c>
       <c r="Y2">
-        <v>42.86</v>
+        <v>37.75</v>
       </c>
       <c r="Z2">
-        <v>-46.07</v>
+        <v>-70.81</v>
       </c>
       <c r="AA2">
-        <v>31.98</v>
+        <v>11.43</v>
       </c>
       <c r="AB2">
-        <v>-78.06</v>
+        <v>-82.23999999999999</v>
       </c>
       <c r="AC2">
-        <v>5.55</v>
+        <v>3.01</v>
       </c>
       <c r="AD2">
-        <v>5.16</v>
+        <v>3.97</v>
       </c>
       <c r="AE2">
-        <v>200.77</v>
+        <v>200.64</v>
       </c>
       <c r="AF2">
-        <v>-28.25</v>
+        <v>-51.06</v>
       </c>
       <c r="AG2">
-        <v>12293.9</v>
+        <v>12318.24</v>
       </c>
       <c r="AH2">
-        <v>11194.5</v>
+        <v>11118.56</v>
       </c>
       <c r="AI2">
-        <v>11961.31</v>
+        <v>11893.93</v>
       </c>
       <c r="AJ2" t="s">
         <v>47</v>
       </c>
       <c r="AK2">
-        <v>40.35</v>
+        <v>43.92</v>
       </c>
     </row>
     <row r="3" spans="1:37">
@@ -1097,10 +1037,10 @@
         <v>44</v>
       </c>
       <c r="C3">
-        <v>505.85</v>
+        <v>501.7</v>
       </c>
       <c r="D3">
-        <v>-1.54</v>
+        <v>-0.82</v>
       </c>
       <c r="E3">
         <v>670.25</v>
@@ -1109,25 +1049,25 @@
         <v>232.89</v>
       </c>
       <c r="G3">
-        <v>-24.53</v>
+        <v>-25.15</v>
       </c>
       <c r="H3">
-        <v>117.21</v>
+        <v>115.42</v>
       </c>
       <c r="I3">
-        <v>1.57</v>
+        <v>-0.15</v>
       </c>
       <c r="J3">
-        <v>9.210000000000001</v>
+        <v>10.25</v>
       </c>
       <c r="K3">
-        <v>-14.27</v>
+        <v>-13.27</v>
       </c>
       <c r="L3">
-        <v>96.19</v>
+        <v>96.37</v>
       </c>
       <c r="M3">
-        <v>16.2</v>
+        <v>16.24</v>
       </c>
       <c r="N3">
         <v>99</v>
@@ -1136,19 +1076,19 @@
         <v>90</v>
       </c>
       <c r="P3">
-        <v>509.9</v>
+        <v>509.75</v>
       </c>
       <c r="Q3">
-        <v>500.32</v>
+        <v>502.23</v>
       </c>
       <c r="R3">
-        <v>513.9400000000001</v>
+        <v>512.6</v>
       </c>
       <c r="S3">
-        <v>445.05</v>
+        <v>446.21</v>
       </c>
       <c r="T3">
-        <v>13.66</v>
+        <v>12.44</v>
       </c>
       <c r="U3" t="s">
         <v>46</v>
@@ -1163,34 +1103,34 @@
         <v>2</v>
       </c>
       <c r="Y3">
-        <v>48.92</v>
+        <v>47.22</v>
       </c>
       <c r="Z3">
-        <v>0.08</v>
+        <v>-0.44</v>
       </c>
       <c r="AA3">
-        <v>-2.15</v>
+        <v>-1.81</v>
       </c>
       <c r="AB3">
-        <v>2.23</v>
+        <v>1.37</v>
       </c>
       <c r="AC3">
-        <v>54.21</v>
+        <v>30.97</v>
       </c>
       <c r="AD3">
-        <v>63.16</v>
+        <v>51.67</v>
       </c>
       <c r="AE3">
-        <v>19.77</v>
+        <v>19.4</v>
       </c>
       <c r="AF3">
-        <v>-37.56</v>
+        <v>-42.63</v>
       </c>
       <c r="AG3">
-        <v>544.6900000000001</v>
+        <v>543.0700000000001</v>
       </c>
       <c r="AH3">
-        <v>455.96</v>
+        <v>461.4</v>
       </c>
       <c r="AI3">
         <v>460.99</v>
@@ -1199,7 +1139,7 @@
         <v>48</v>
       </c>
       <c r="AK3">
-        <v>22.88</v>
+        <v>20.35</v>
       </c>
     </row>
     <row r="4" spans="1:37">
@@ -1210,10 +1150,10 @@
         <v>44</v>
       </c>
       <c r="C4">
-        <v>329.4</v>
+        <v>321.45</v>
       </c>
       <c r="D4">
-        <v>1.84</v>
+        <v>-2.41</v>
       </c>
       <c r="E4">
         <v>589.75</v>
@@ -1222,25 +1162,25 @@
         <v>303.75</v>
       </c>
       <c r="G4">
-        <v>-44.15</v>
+        <v>-45.49</v>
       </c>
       <c r="H4">
-        <v>8.44</v>
+        <v>5.83</v>
       </c>
       <c r="I4">
-        <v>2.12</v>
+        <v>-1.18</v>
       </c>
       <c r="J4">
-        <v>-4.42</v>
+        <v>-3.86</v>
       </c>
       <c r="K4">
-        <v>1.43</v>
+        <v>-0.28</v>
       </c>
       <c r="L4">
-        <v>-44.85</v>
+        <v>-45.49</v>
       </c>
       <c r="M4">
-        <v>-25.36</v>
+        <v>-25.13</v>
       </c>
       <c r="N4">
         <v>15</v>
@@ -1249,19 +1189,19 @@
         <v>19</v>
       </c>
       <c r="P4">
-        <v>325.44</v>
+        <v>324.67</v>
       </c>
       <c r="Q4">
-        <v>331.04</v>
+        <v>330.08</v>
       </c>
       <c r="R4">
-        <v>339.44</v>
+        <v>339.27</v>
       </c>
       <c r="S4">
-        <v>372.98</v>
+        <v>372.18</v>
       </c>
       <c r="T4">
-        <v>-11.68</v>
+        <v>-13.63</v>
       </c>
       <c r="U4" t="s">
         <v>46</v>
@@ -1276,43 +1216,43 @@
         <v>0</v>
       </c>
       <c r="Y4">
-        <v>46.13</v>
+        <v>40.53</v>
       </c>
       <c r="Z4">
-        <v>-4.41</v>
+        <v>-4.71</v>
       </c>
       <c r="AA4">
-        <v>-3.87</v>
+        <v>-4.04</v>
       </c>
       <c r="AB4">
-        <v>-0.54</v>
+        <v>-0.67</v>
       </c>
       <c r="AC4">
-        <v>40.89</v>
+        <v>34.34</v>
       </c>
       <c r="AD4">
-        <v>31.76</v>
+        <v>34.01</v>
       </c>
       <c r="AE4">
-        <v>9.619999999999999</v>
+        <v>9.6</v>
       </c>
       <c r="AF4">
-        <v>-33.47</v>
+        <v>-34.36</v>
       </c>
       <c r="AG4">
-        <v>344.36</v>
+        <v>343.26</v>
       </c>
       <c r="AH4">
-        <v>317.72</v>
+        <v>316.9</v>
       </c>
       <c r="AI4">
-        <v>354.2</v>
+        <v>352.86</v>
       </c>
       <c r="AJ4" t="s">
         <v>47</v>
       </c>
       <c r="AK4">
-        <v>14.53</v>
+        <v>13.24</v>
       </c>
     </row>
     <row r="5" spans="1:37">
@@ -1323,10 +1263,10 @@
         <v>44</v>
       </c>
       <c r="C5">
-        <v>1846.5</v>
+        <v>1762.3</v>
       </c>
       <c r="D5">
-        <v>1.27</v>
+        <v>-4.56</v>
       </c>
       <c r="E5">
         <v>2176.6</v>
@@ -1335,46 +1275,46 @@
         <v>1631.8</v>
       </c>
       <c r="G5">
-        <v>-15.17</v>
+        <v>-19.03</v>
       </c>
       <c r="H5">
-        <v>13.16</v>
+        <v>8</v>
       </c>
       <c r="I5">
-        <v>0.52</v>
+        <v>-5.21</v>
       </c>
       <c r="J5">
-        <v>-7.75</v>
+        <v>-12.06</v>
       </c>
       <c r="K5">
-        <v>3.71</v>
+        <v>-0.13</v>
       </c>
       <c r="L5">
-        <v>-10.76</v>
+        <v>-14.75</v>
       </c>
       <c r="M5">
-        <v>-0</v>
+        <v>-0.95</v>
       </c>
       <c r="N5">
         <v>29</v>
       </c>
       <c r="O5">
-        <v>50</v>
+        <v>44</v>
       </c>
       <c r="P5">
-        <v>1846.28</v>
+        <v>1826.9</v>
       </c>
       <c r="Q5">
-        <v>1927.48</v>
+        <v>1915.1</v>
       </c>
       <c r="R5">
-        <v>1955.43</v>
+        <v>1953.69</v>
       </c>
       <c r="S5">
-        <v>1894.42</v>
+        <v>1892.75</v>
       </c>
       <c r="T5">
-        <v>-2.53</v>
+        <v>-6.89</v>
       </c>
       <c r="U5" t="s">
         <v>46</v>
@@ -1389,43 +1329,43 @@
         <v>1</v>
       </c>
       <c r="Y5">
-        <v>35.17</v>
+        <v>26.21</v>
       </c>
       <c r="Z5">
-        <v>-38.16</v>
+        <v>-44.74</v>
       </c>
       <c r="AA5">
-        <v>-26.13</v>
+        <v>-29.85</v>
       </c>
       <c r="AB5">
-        <v>-12.04</v>
+        <v>-14.89</v>
       </c>
       <c r="AC5">
-        <v>19.05</v>
+        <v>12.53</v>
       </c>
       <c r="AD5">
-        <v>17.01</v>
+        <v>15.1</v>
       </c>
       <c r="AE5">
-        <v>35.76</v>
+        <v>39.32</v>
       </c>
       <c r="AF5">
-        <v>33.45</v>
+        <v>165.27</v>
       </c>
       <c r="AG5">
-        <v>2063.32</v>
+        <v>2063.81</v>
       </c>
       <c r="AH5">
-        <v>1791.65</v>
+        <v>1766.39</v>
       </c>
       <c r="AI5">
-        <v>1949.18</v>
+        <v>1907.41</v>
       </c>
       <c r="AJ5" t="s">
         <v>47</v>
       </c>
       <c r="AK5">
-        <v>66.73</v>
+        <v>69.23</v>
       </c>
     </row>
     <row r="6" spans="1:37">
@@ -1436,10 +1376,10 @@
         <v>44</v>
       </c>
       <c r="C6">
-        <v>11449</v>
+        <v>10917</v>
       </c>
       <c r="D6">
-        <v>2.36</v>
+        <v>-4.65</v>
       </c>
       <c r="E6">
         <v>13279</v>
@@ -1448,46 +1388,46 @@
         <v>8746</v>
       </c>
       <c r="G6">
-        <v>-13.78</v>
+        <v>-17.79</v>
       </c>
       <c r="H6">
-        <v>30.91</v>
+        <v>24.82</v>
       </c>
       <c r="I6">
-        <v>4.75</v>
+        <v>-0.84</v>
       </c>
       <c r="J6">
-        <v>2.96</v>
+        <v>-3.3</v>
       </c>
       <c r="K6">
-        <v>8.18</v>
+        <v>3</v>
       </c>
       <c r="L6">
-        <v>-14.56</v>
+        <v>-16.92</v>
       </c>
       <c r="M6">
-        <v>19.97</v>
+        <v>19.13</v>
       </c>
       <c r="N6">
         <v>43</v>
       </c>
       <c r="O6">
-        <v>54</v>
+        <v>48</v>
       </c>
       <c r="P6">
-        <v>11267</v>
+        <v>11248.4</v>
       </c>
       <c r="Q6">
-        <v>11211.55</v>
+        <v>11180.4</v>
       </c>
       <c r="R6">
-        <v>11139.34</v>
+        <v>11147.06</v>
       </c>
       <c r="S6">
-        <v>10683.34</v>
+        <v>10682.02</v>
       </c>
       <c r="T6">
-        <v>7.17</v>
+        <v>2.2</v>
       </c>
       <c r="U6" t="s">
         <v>45</v>
@@ -1502,34 +1442,34 @@
         <v>3</v>
       </c>
       <c r="Y6">
-        <v>56.66</v>
+        <v>44.34</v>
       </c>
       <c r="Z6">
-        <v>18.03</v>
+        <v>-7.03</v>
       </c>
       <c r="AA6">
-        <v>-4.78</v>
+        <v>-5.23</v>
       </c>
       <c r="AB6">
-        <v>22.81</v>
+        <v>-1.8</v>
       </c>
       <c r="AC6">
-        <v>83.89</v>
+        <v>54.17</v>
       </c>
       <c r="AD6">
-        <v>71.06</v>
+        <v>69.65000000000001</v>
       </c>
       <c r="AE6">
-        <v>233.61</v>
+        <v>256.28</v>
       </c>
       <c r="AF6">
-        <v>-49.88</v>
+        <v>-2.37</v>
       </c>
       <c r="AG6">
-        <v>11614.55</v>
+        <v>11572.67</v>
       </c>
       <c r="AH6">
-        <v>10808.55</v>
+        <v>10788.13</v>
       </c>
       <c r="AI6">
         <v>10787.84</v>
@@ -1538,7 +1478,7 @@
         <v>48</v>
       </c>
       <c r="AK6">
-        <v>18.64</v>
+        <v>19.01</v>
       </c>
     </row>
     <row r="7" spans="1:37">
@@ -1549,10 +1489,10 @@
         <v>44</v>
       </c>
       <c r="C7">
-        <v>1043.2</v>
+        <v>982</v>
       </c>
       <c r="D7">
-        <v>3.41</v>
+        <v>-5.87</v>
       </c>
       <c r="E7">
         <v>1158.8</v>
@@ -1561,46 +1501,46 @@
         <v>801.55</v>
       </c>
       <c r="G7">
-        <v>-9.98</v>
+        <v>-15.26</v>
       </c>
       <c r="H7">
-        <v>30.15</v>
+        <v>22.51</v>
       </c>
       <c r="I7">
-        <v>3.68</v>
+        <v>-3.25</v>
       </c>
       <c r="J7">
-        <v>-3.14</v>
+        <v>-9.69</v>
       </c>
       <c r="K7">
-        <v>5.27</v>
+        <v>0.16</v>
       </c>
       <c r="L7">
-        <v>4.69</v>
+        <v>-1.05</v>
       </c>
       <c r="M7">
-        <v>6.12</v>
+        <v>5.13</v>
       </c>
       <c r="N7">
         <v>57</v>
       </c>
       <c r="O7">
-        <v>63</v>
+        <v>55</v>
       </c>
       <c r="P7">
-        <v>1025.72</v>
+        <v>1019.12</v>
       </c>
       <c r="Q7">
-        <v>1044.98</v>
+        <v>1039.83</v>
       </c>
       <c r="R7">
-        <v>1067.52</v>
+        <v>1066.73</v>
       </c>
       <c r="S7">
-        <v>977.72</v>
+        <v>977.39</v>
       </c>
       <c r="T7">
-        <v>6.7</v>
+        <v>0.47</v>
       </c>
       <c r="U7" t="s">
         <v>46</v>
@@ -1615,43 +1555,43 @@
         <v>2</v>
       </c>
       <c r="Y7">
-        <v>49</v>
+        <v>36.19</v>
       </c>
       <c r="Z7">
-        <v>-13.09</v>
+        <v>-16.2</v>
       </c>
       <c r="AA7">
-        <v>-11.7</v>
+        <v>-12.6</v>
       </c>
       <c r="AB7">
-        <v>-1.39</v>
+        <v>-3.6</v>
       </c>
       <c r="AC7">
-        <v>69.15000000000001</v>
+        <v>57.43</v>
       </c>
       <c r="AD7">
-        <v>66.84</v>
+        <v>65.23999999999999</v>
       </c>
       <c r="AE7">
-        <v>22.3</v>
+        <v>25.65</v>
       </c>
       <c r="AF7">
-        <v>67.2</v>
+        <v>149.77</v>
       </c>
       <c r="AG7">
-        <v>1092.88</v>
+        <v>1091.6</v>
       </c>
       <c r="AH7">
-        <v>997.08</v>
+        <v>988.0599999999999</v>
       </c>
       <c r="AI7">
-        <v>1075.64</v>
+        <v>1071.46</v>
       </c>
       <c r="AJ7" t="s">
         <v>47</v>
       </c>
       <c r="AK7">
-        <v>34.59</v>
+        <v>36.6</v>
       </c>
     </row>
     <row r="8" spans="1:37">
@@ -1662,10 +1602,10 @@
         <v>44</v>
       </c>
       <c r="C8">
-        <v>157.11</v>
+        <v>155.26</v>
       </c>
       <c r="D8">
-        <v>11.1</v>
+        <v>-1.18</v>
       </c>
       <c r="E8">
         <v>157.11</v>
@@ -1674,46 +1614,46 @@
         <v>115.96</v>
       </c>
       <c r="G8">
-        <v>0</v>
+        <v>-1.18</v>
       </c>
       <c r="H8">
-        <v>35.49</v>
+        <v>33.89</v>
       </c>
       <c r="I8">
-        <v>16.47</v>
+        <v>15.69</v>
       </c>
       <c r="J8">
-        <v>15.79</v>
+        <v>14.91</v>
       </c>
       <c r="K8">
-        <v>16.98</v>
+        <v>16.68</v>
       </c>
       <c r="L8">
-        <v>16.09</v>
+        <v>12.97</v>
       </c>
       <c r="M8">
-        <v>4.25</v>
+        <v>4.35</v>
       </c>
       <c r="N8">
         <v>71</v>
       </c>
       <c r="O8">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="P8">
-        <v>140.71</v>
+        <v>144.92</v>
       </c>
       <c r="Q8">
-        <v>137.79</v>
+        <v>138.71</v>
       </c>
       <c r="R8">
-        <v>139</v>
+        <v>139.27</v>
       </c>
       <c r="S8">
-        <v>133.99</v>
+        <v>134.11</v>
       </c>
       <c r="T8">
-        <v>17.25</v>
+        <v>15.77</v>
       </c>
       <c r="U8" t="s">
         <v>46</v>
@@ -1728,43 +1668,43 @@
         <v>2</v>
       </c>
       <c r="Y8">
-        <v>75.55</v>
+        <v>71.89</v>
       </c>
       <c r="Z8">
-        <v>1.58</v>
+        <v>2.67</v>
       </c>
       <c r="AA8">
-        <v>0.1</v>
+        <v>0.62</v>
       </c>
       <c r="AB8">
-        <v>1.48</v>
+        <v>2.05</v>
       </c>
       <c r="AC8">
-        <v>74.18000000000001</v>
+        <v>90.67</v>
       </c>
       <c r="AD8">
-        <v>50.8</v>
+        <v>71.48999999999999</v>
       </c>
       <c r="AE8">
-        <v>5.37</v>
+        <v>5.51</v>
       </c>
       <c r="AF8">
-        <v>2767.61</v>
+        <v>398.73</v>
       </c>
       <c r="AG8">
-        <v>148.14</v>
+        <v>151.66</v>
       </c>
       <c r="AH8">
-        <v>127.45</v>
+        <v>125.76</v>
       </c>
       <c r="AI8">
-        <v>133.99</v>
+        <v>141.22</v>
       </c>
       <c r="AJ8" t="s">
         <v>48</v>
       </c>
       <c r="AK8">
-        <v>28.87</v>
+        <v>34.29</v>
       </c>
     </row>
   </sheetData>
@@ -1905,7 +1845,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:F65"/>
+  <dimension ref="A1:F62"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="16.7109375" customWidth="1"/>
@@ -1945,7 +1885,7 @@
     </row>
     <row r="3" spans="1:6">
       <c r="A3" s="4" t="s">
-        <v>43</v>
+        <v>41</v>
       </c>
       <c r="B3" s="4" t="s">
         <v>55</v>
@@ -1963,1048 +1903,988 @@
         <v>59</v>
       </c>
     </row>
-    <row r="4" spans="1:6">
-      <c r="A4" s="4" t="s">
+    <row r="5" spans="1:6">
+      <c r="A5" s="2" t="s">
+        <v>60</v>
+      </c>
+      <c r="B5" s="2"/>
+      <c r="C5" s="2"/>
+      <c r="D5" s="2"/>
+      <c r="E5" s="2"/>
+    </row>
+    <row r="6" spans="1:6">
+      <c r="A6" s="3" t="s">
+        <v>0</v>
+      </c>
+      <c r="B6" s="3" t="s">
+        <v>61</v>
+      </c>
+      <c r="C6" s="3" t="s">
+        <v>62</v>
+      </c>
+      <c r="D6" s="3" t="s">
+        <v>63</v>
+      </c>
+      <c r="E6" s="3" t="s">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="7" spans="1:6">
+      <c r="A7" s="5" t="s">
+        <v>37</v>
+      </c>
+      <c r="B7" s="5" t="s">
+        <v>9</v>
+      </c>
+      <c r="C7" s="6">
+        <v>-3.39</v>
+      </c>
+      <c r="D7" s="6">
+        <v>-6.03</v>
+      </c>
+      <c r="E7" s="7">
+        <v>-2.64</v>
+      </c>
+    </row>
+    <row r="8" spans="1:6">
+      <c r="A8" s="5" t="s">
+        <v>38</v>
+      </c>
+      <c r="B8" s="5" t="s">
+        <v>9</v>
+      </c>
+      <c r="C8" s="6">
+        <v>9.210000000000001</v>
+      </c>
+      <c r="D8" s="6">
+        <v>10.25</v>
+      </c>
+      <c r="E8" s="8">
+        <v>1.04</v>
+      </c>
+    </row>
+    <row r="9" spans="1:6">
+      <c r="A9" s="5" t="s">
+        <v>39</v>
+      </c>
+      <c r="B9" s="5" t="s">
+        <v>9</v>
+      </c>
+      <c r="C9" s="6">
+        <v>-4.42</v>
+      </c>
+      <c r="D9" s="6">
+        <v>-3.86</v>
+      </c>
+      <c r="E9" s="8">
+        <v>0.5600000000000001</v>
+      </c>
+    </row>
+    <row r="10" spans="1:6">
+      <c r="A10" s="5" t="s">
         <v>40</v>
       </c>
-      <c r="B4" s="4" t="s">
-        <v>60</v>
-      </c>
-      <c r="C4" s="4" t="s">
-        <v>61</v>
-      </c>
-      <c r="D4" s="4" t="s">
-        <v>62</v>
-      </c>
-      <c r="E4" s="4" t="s">
-        <v>63</v>
-      </c>
-      <c r="F4" s="4" t="s">
-        <v>64</v>
-      </c>
-    </row>
-    <row r="5" spans="1:6">
-      <c r="A5" s="5" t="s">
+      <c r="B10" s="5" t="s">
+        <v>9</v>
+      </c>
+      <c r="C10" s="6">
+        <v>-7.75</v>
+      </c>
+      <c r="D10" s="6">
+        <v>-12.06</v>
+      </c>
+      <c r="E10" s="7">
+        <v>-4.31</v>
+      </c>
+    </row>
+    <row r="11" spans="1:6">
+      <c r="A11" s="5" t="s">
+        <v>41</v>
+      </c>
+      <c r="B11" s="5" t="s">
+        <v>9</v>
+      </c>
+      <c r="C11" s="6">
+        <v>2.96</v>
+      </c>
+      <c r="D11" s="6">
+        <v>-3.3</v>
+      </c>
+      <c r="E11" s="7">
+        <v>-6.26</v>
+      </c>
+    </row>
+    <row r="12" spans="1:6">
+      <c r="A12" s="5" t="s">
+        <v>42</v>
+      </c>
+      <c r="B12" s="5" t="s">
+        <v>9</v>
+      </c>
+      <c r="C12" s="6">
+        <v>-3.14</v>
+      </c>
+      <c r="D12" s="6">
+        <v>-9.69</v>
+      </c>
+      <c r="E12" s="7">
+        <v>-6.55</v>
+      </c>
+    </row>
+    <row r="13" spans="1:6">
+      <c r="A13" s="5" t="s">
         <v>43</v>
       </c>
-      <c r="B5" s="5" t="s">
-        <v>65</v>
-      </c>
-      <c r="C5" s="5" t="s">
-        <v>66</v>
-      </c>
-      <c r="D5" s="5" t="s">
-        <v>67</v>
-      </c>
-      <c r="E5" s="5" t="s">
-        <v>68</v>
-      </c>
-      <c r="F5" s="5" t="s">
-        <v>69</v>
-      </c>
-    </row>
-    <row r="6" spans="1:6">
-      <c r="A6" s="6" t="s">
+      <c r="B13" s="5" t="s">
+        <v>9</v>
+      </c>
+      <c r="C13" s="6">
+        <v>15.79</v>
+      </c>
+      <c r="D13" s="6">
+        <v>14.91</v>
+      </c>
+      <c r="E13" s="7">
+        <v>-0.88</v>
+      </c>
+    </row>
+    <row r="14" spans="1:6">
+      <c r="A14" s="5" t="s">
+        <v>37</v>
+      </c>
+      <c r="B14" s="5" t="s">
+        <v>8</v>
+      </c>
+      <c r="C14" s="6">
+        <v>-1.66</v>
+      </c>
+      <c r="D14" s="6">
+        <v>-2.54</v>
+      </c>
+      <c r="E14" s="7">
+        <v>-0.88</v>
+      </c>
+    </row>
+    <row r="15" spans="1:6">
+      <c r="A15" s="5" t="s">
         <v>38</v>
       </c>
-      <c r="B6" s="6" t="s">
-        <v>70</v>
-      </c>
-      <c r="C6" s="6" t="s">
-        <v>71</v>
-      </c>
-      <c r="D6" s="6" t="s">
-        <v>72</v>
-      </c>
-      <c r="E6" s="6" t="s">
-        <v>73</v>
-      </c>
-      <c r="F6" s="6" t="s">
-        <v>74</v>
-      </c>
-    </row>
-    <row r="8" spans="1:6">
-      <c r="A8" s="2" t="s">
-        <v>75</v>
-      </c>
-      <c r="B8" s="2"/>
-      <c r="C8" s="2"/>
-      <c r="D8" s="2"/>
-      <c r="E8" s="2"/>
-    </row>
-    <row r="9" spans="1:6">
-      <c r="A9" s="3" t="s">
+      <c r="B15" s="5" t="s">
+        <v>8</v>
+      </c>
+      <c r="C15" s="6">
+        <v>1.57</v>
+      </c>
+      <c r="D15" s="6">
+        <v>-0.15</v>
+      </c>
+      <c r="E15" s="7">
+        <v>-1.72</v>
+      </c>
+    </row>
+    <row r="16" spans="1:6">
+      <c r="A16" s="5" t="s">
+        <v>39</v>
+      </c>
+      <c r="B16" s="5" t="s">
+        <v>8</v>
+      </c>
+      <c r="C16" s="6">
+        <v>2.12</v>
+      </c>
+      <c r="D16" s="6">
+        <v>-1.18</v>
+      </c>
+      <c r="E16" s="7">
+        <v>-3.3</v>
+      </c>
+    </row>
+    <row r="17" spans="1:5">
+      <c r="A17" s="5" t="s">
+        <v>40</v>
+      </c>
+      <c r="B17" s="5" t="s">
+        <v>8</v>
+      </c>
+      <c r="C17" s="6">
+        <v>0.52</v>
+      </c>
+      <c r="D17" s="6">
+        <v>-5.21</v>
+      </c>
+      <c r="E17" s="7">
+        <v>-5.73</v>
+      </c>
+    </row>
+    <row r="18" spans="1:5">
+      <c r="A18" s="5" t="s">
+        <v>41</v>
+      </c>
+      <c r="B18" s="5" t="s">
+        <v>8</v>
+      </c>
+      <c r="C18" s="6">
+        <v>4.75</v>
+      </c>
+      <c r="D18" s="6">
+        <v>-0.84</v>
+      </c>
+      <c r="E18" s="7">
+        <v>-5.59</v>
+      </c>
+    </row>
+    <row r="19" spans="1:5">
+      <c r="A19" s="5" t="s">
+        <v>42</v>
+      </c>
+      <c r="B19" s="5" t="s">
+        <v>8</v>
+      </c>
+      <c r="C19" s="6">
+        <v>3.68</v>
+      </c>
+      <c r="D19" s="6">
+        <v>-3.25</v>
+      </c>
+      <c r="E19" s="7">
+        <v>-6.93</v>
+      </c>
+    </row>
+    <row r="20" spans="1:5">
+      <c r="A20" s="5" t="s">
+        <v>43</v>
+      </c>
+      <c r="B20" s="5" t="s">
+        <v>8</v>
+      </c>
+      <c r="C20" s="6">
+        <v>16.47</v>
+      </c>
+      <c r="D20" s="6">
+        <v>15.69</v>
+      </c>
+      <c r="E20" s="7">
+        <v>-0.78</v>
+      </c>
+    </row>
+    <row r="21" spans="1:5">
+      <c r="A21" s="5" t="s">
+        <v>37</v>
+      </c>
+      <c r="B21" s="5" t="s">
+        <v>11</v>
+      </c>
+      <c r="C21" s="6">
+        <v>27.39</v>
+      </c>
+      <c r="D21" s="6">
+        <v>26.69</v>
+      </c>
+      <c r="E21" s="7">
+        <v>-0.7</v>
+      </c>
+    </row>
+    <row r="22" spans="1:5">
+      <c r="A22" s="5" t="s">
+        <v>38</v>
+      </c>
+      <c r="B22" s="5" t="s">
+        <v>11</v>
+      </c>
+      <c r="C22" s="6">
+        <v>96.19</v>
+      </c>
+      <c r="D22" s="6">
+        <v>96.37</v>
+      </c>
+      <c r="E22" s="8">
+        <v>0.18</v>
+      </c>
+    </row>
+    <row r="23" spans="1:5">
+      <c r="A23" s="5" t="s">
+        <v>39</v>
+      </c>
+      <c r="B23" s="5" t="s">
+        <v>11</v>
+      </c>
+      <c r="C23" s="6">
+        <v>-44.85</v>
+      </c>
+      <c r="D23" s="6">
+        <v>-45.49</v>
+      </c>
+      <c r="E23" s="7">
+        <v>-0.64</v>
+      </c>
+    </row>
+    <row r="24" spans="1:5">
+      <c r="A24" s="5" t="s">
+        <v>40</v>
+      </c>
+      <c r="B24" s="5" t="s">
+        <v>11</v>
+      </c>
+      <c r="C24" s="6">
+        <v>-10.76</v>
+      </c>
+      <c r="D24" s="6">
+        <v>-14.75</v>
+      </c>
+      <c r="E24" s="7">
+        <v>-3.99</v>
+      </c>
+    </row>
+    <row r="25" spans="1:5">
+      <c r="A25" s="5" t="s">
+        <v>41</v>
+      </c>
+      <c r="B25" s="5" t="s">
+        <v>11</v>
+      </c>
+      <c r="C25" s="6">
+        <v>-14.56</v>
+      </c>
+      <c r="D25" s="6">
+        <v>-16.92</v>
+      </c>
+      <c r="E25" s="7">
+        <v>-2.36</v>
+      </c>
+    </row>
+    <row r="26" spans="1:5">
+      <c r="A26" s="5" t="s">
+        <v>42</v>
+      </c>
+      <c r="B26" s="5" t="s">
+        <v>11</v>
+      </c>
+      <c r="C26" s="6">
+        <v>4.69</v>
+      </c>
+      <c r="D26" s="6">
+        <v>-1.05</v>
+      </c>
+      <c r="E26" s="7">
+        <v>-5.74</v>
+      </c>
+    </row>
+    <row r="27" spans="1:5">
+      <c r="A27" s="5" t="s">
+        <v>43</v>
+      </c>
+      <c r="B27" s="5" t="s">
+        <v>11</v>
+      </c>
+      <c r="C27" s="6">
+        <v>16.09</v>
+      </c>
+      <c r="D27" s="6">
+        <v>12.97</v>
+      </c>
+      <c r="E27" s="7">
+        <v>-3.12</v>
+      </c>
+    </row>
+    <row r="28" spans="1:5">
+      <c r="A28" s="5" t="s">
+        <v>37</v>
+      </c>
+      <c r="B28" s="5" t="s">
+        <v>10</v>
+      </c>
+      <c r="C28" s="6">
+        <v>16.92</v>
+      </c>
+      <c r="D28" s="6">
+        <v>13.87</v>
+      </c>
+      <c r="E28" s="7">
+        <v>-3.05</v>
+      </c>
+    </row>
+    <row r="29" spans="1:5">
+      <c r="A29" s="5" t="s">
+        <v>38</v>
+      </c>
+      <c r="B29" s="5" t="s">
+        <v>10</v>
+      </c>
+      <c r="C29" s="6">
+        <v>-14.27</v>
+      </c>
+      <c r="D29" s="6">
+        <v>-13.27</v>
+      </c>
+      <c r="E29" s="8">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="30" spans="1:5">
+      <c r="A30" s="5" t="s">
+        <v>39</v>
+      </c>
+      <c r="B30" s="5" t="s">
+        <v>10</v>
+      </c>
+      <c r="C30" s="6">
+        <v>1.43</v>
+      </c>
+      <c r="D30" s="6">
+        <v>-0.28</v>
+      </c>
+      <c r="E30" s="7">
+        <v>-1.71</v>
+      </c>
+    </row>
+    <row r="31" spans="1:5">
+      <c r="A31" s="5" t="s">
+        <v>40</v>
+      </c>
+      <c r="B31" s="5" t="s">
+        <v>10</v>
+      </c>
+      <c r="C31" s="6">
+        <v>3.71</v>
+      </c>
+      <c r="D31" s="6">
+        <v>-0.13</v>
+      </c>
+      <c r="E31" s="7">
+        <v>-3.84</v>
+      </c>
+    </row>
+    <row r="32" spans="1:5">
+      <c r="A32" s="5" t="s">
+        <v>41</v>
+      </c>
+      <c r="B32" s="5" t="s">
+        <v>10</v>
+      </c>
+      <c r="C32" s="6">
+        <v>8.18</v>
+      </c>
+      <c r="D32" s="6">
+        <v>3</v>
+      </c>
+      <c r="E32" s="7">
+        <v>-5.18</v>
+      </c>
+    </row>
+    <row r="33" spans="1:5">
+      <c r="A33" s="5" t="s">
+        <v>42</v>
+      </c>
+      <c r="B33" s="5" t="s">
+        <v>10</v>
+      </c>
+      <c r="C33" s="6">
+        <v>5.27</v>
+      </c>
+      <c r="D33" s="6">
+        <v>0.16</v>
+      </c>
+      <c r="E33" s="7">
+        <v>-5.11</v>
+      </c>
+    </row>
+    <row r="34" spans="1:5">
+      <c r="A34" s="5" t="s">
+        <v>43</v>
+      </c>
+      <c r="B34" s="5" t="s">
+        <v>10</v>
+      </c>
+      <c r="C34" s="6">
+        <v>16.98</v>
+      </c>
+      <c r="D34" s="6">
+        <v>16.68</v>
+      </c>
+      <c r="E34" s="7">
+        <v>-0.3</v>
+      </c>
+    </row>
+    <row r="35" spans="1:5">
+      <c r="A35" s="5" t="s">
+        <v>37</v>
+      </c>
+      <c r="B35" s="5" t="s">
+        <v>6</v>
+      </c>
+      <c r="C35" s="6">
+        <v>-7.77</v>
+      </c>
+      <c r="D35" s="6">
+        <v>-9.33</v>
+      </c>
+      <c r="E35" s="7">
+        <v>-1.56</v>
+      </c>
+    </row>
+    <row r="36" spans="1:5">
+      <c r="A36" s="5" t="s">
+        <v>38</v>
+      </c>
+      <c r="B36" s="5" t="s">
+        <v>6</v>
+      </c>
+      <c r="C36" s="6">
+        <v>-24.53</v>
+      </c>
+      <c r="D36" s="6">
+        <v>-25.15</v>
+      </c>
+      <c r="E36" s="7">
+        <v>-0.62</v>
+      </c>
+    </row>
+    <row r="37" spans="1:5">
+      <c r="A37" s="5" t="s">
+        <v>39</v>
+      </c>
+      <c r="B37" s="5" t="s">
+        <v>6</v>
+      </c>
+      <c r="C37" s="6">
+        <v>-44.15</v>
+      </c>
+      <c r="D37" s="6">
+        <v>-45.49</v>
+      </c>
+      <c r="E37" s="7">
+        <v>-1.34</v>
+      </c>
+    </row>
+    <row r="38" spans="1:5">
+      <c r="A38" s="5" t="s">
+        <v>40</v>
+      </c>
+      <c r="B38" s="5" t="s">
+        <v>6</v>
+      </c>
+      <c r="C38" s="6">
+        <v>-15.17</v>
+      </c>
+      <c r="D38" s="6">
+        <v>-19.03</v>
+      </c>
+      <c r="E38" s="7">
+        <v>-3.86</v>
+      </c>
+    </row>
+    <row r="39" spans="1:5">
+      <c r="A39" s="5" t="s">
+        <v>41</v>
+      </c>
+      <c r="B39" s="5" t="s">
+        <v>6</v>
+      </c>
+      <c r="C39" s="6">
+        <v>-13.78</v>
+      </c>
+      <c r="D39" s="6">
+        <v>-17.79</v>
+      </c>
+      <c r="E39" s="7">
+        <v>-4.01</v>
+      </c>
+    </row>
+    <row r="40" spans="1:5">
+      <c r="A40" s="5" t="s">
+        <v>42</v>
+      </c>
+      <c r="B40" s="5" t="s">
+        <v>6</v>
+      </c>
+      <c r="C40" s="6">
+        <v>-9.98</v>
+      </c>
+      <c r="D40" s="6">
+        <v>-15.26</v>
+      </c>
+      <c r="E40" s="7">
+        <v>-5.28</v>
+      </c>
+    </row>
+    <row r="41" spans="1:5">
+      <c r="A41" s="5" t="s">
+        <v>43</v>
+      </c>
+      <c r="B41" s="5" t="s">
+        <v>6</v>
+      </c>
+      <c r="C41" s="6">
         <v>0</v>
       </c>
-      <c r="B9" s="3" t="s">
-        <v>76</v>
-      </c>
-      <c r="C9" s="3" t="s">
-        <v>77</v>
-      </c>
-      <c r="D9" s="3" t="s">
-        <v>78</v>
-      </c>
-      <c r="E9" s="3" t="s">
-        <v>79</v>
-      </c>
-    </row>
-    <row r="10" spans="1:6">
-      <c r="A10" s="7" t="s">
+      <c r="D41" s="6">
+        <v>-1.18</v>
+      </c>
+      <c r="E41" s="7">
+        <v>-1.18</v>
+      </c>
+    </row>
+    <row r="42" spans="1:5">
+      <c r="A42" s="5" t="s">
         <v>37</v>
       </c>
-      <c r="B10" s="7" t="s">
-        <v>9</v>
-      </c>
-      <c r="C10" s="8">
-        <v>-2.88</v>
-      </c>
-      <c r="D10" s="8">
-        <v>-3.39</v>
-      </c>
-      <c r="E10" s="9">
-        <v>-0.51</v>
-      </c>
-    </row>
-    <row r="11" spans="1:6">
-      <c r="A11" s="7" t="s">
+      <c r="B42" s="5" t="s">
+        <v>2</v>
+      </c>
+      <c r="C42" s="6">
+        <v>11400</v>
+      </c>
+      <c r="D42" s="6">
+        <v>11208</v>
+      </c>
+      <c r="E42" s="7">
+        <v>-192</v>
+      </c>
+    </row>
+    <row r="43" spans="1:5">
+      <c r="A43" s="5" t="s">
         <v>38</v>
       </c>
-      <c r="B11" s="7" t="s">
-        <v>9</v>
-      </c>
-      <c r="C11" s="8">
-        <v>7.4</v>
-      </c>
-      <c r="D11" s="8">
-        <v>9.210000000000001</v>
-      </c>
-      <c r="E11" s="10">
-        <v>1.81</v>
-      </c>
-    </row>
-    <row r="12" spans="1:6">
-      <c r="A12" s="7" t="s">
+      <c r="B43" s="5" t="s">
+        <v>2</v>
+      </c>
+      <c r="C43" s="6">
+        <v>505.85</v>
+      </c>
+      <c r="D43" s="6">
+        <v>501.7</v>
+      </c>
+      <c r="E43" s="7">
+        <v>-4.15</v>
+      </c>
+    </row>
+    <row r="44" spans="1:5">
+      <c r="A44" s="5" t="s">
         <v>39</v>
       </c>
-      <c r="B12" s="7" t="s">
-        <v>9</v>
-      </c>
-      <c r="C12" s="8">
-        <v>-8.02</v>
-      </c>
-      <c r="D12" s="8">
-        <v>-4.42</v>
-      </c>
-      <c r="E12" s="10">
-        <v>3.6</v>
-      </c>
-    </row>
-    <row r="13" spans="1:6">
-      <c r="A13" s="7" t="s">
+      <c r="B44" s="5" t="s">
+        <v>2</v>
+      </c>
+      <c r="C44" s="6">
+        <v>329.4</v>
+      </c>
+      <c r="D44" s="6">
+        <v>321.45</v>
+      </c>
+      <c r="E44" s="7">
+        <v>-7.95</v>
+      </c>
+    </row>
+    <row r="45" spans="1:5">
+      <c r="A45" s="5" t="s">
         <v>40</v>
       </c>
-      <c r="B13" s="7" t="s">
-        <v>9</v>
-      </c>
-      <c r="C13" s="8">
-        <v>-10.29</v>
-      </c>
-      <c r="D13" s="8">
-        <v>-7.75</v>
-      </c>
-      <c r="E13" s="10">
-        <v>2.54</v>
-      </c>
-    </row>
-    <row r="14" spans="1:6">
-      <c r="A14" s="7" t="s">
+      <c r="B45" s="5" t="s">
+        <v>2</v>
+      </c>
+      <c r="C45" s="6">
+        <v>1846.5</v>
+      </c>
+      <c r="D45" s="6">
+        <v>1762.3</v>
+      </c>
+      <c r="E45" s="7">
+        <v>-84.2</v>
+      </c>
+    </row>
+    <row r="46" spans="1:5">
+      <c r="A46" s="5" t="s">
         <v>41</v>
       </c>
-      <c r="B14" s="7" t="s">
-        <v>9</v>
-      </c>
-      <c r="C14" s="8">
-        <v>-1.19</v>
-      </c>
-      <c r="D14" s="8">
-        <v>2.96</v>
-      </c>
-      <c r="E14" s="10">
-        <v>4.15</v>
-      </c>
-    </row>
-    <row r="15" spans="1:6">
-      <c r="A15" s="7" t="s">
+      <c r="B46" s="5" t="s">
+        <v>2</v>
+      </c>
+      <c r="C46" s="6">
+        <v>11449</v>
+      </c>
+      <c r="D46" s="6">
+        <v>10917</v>
+      </c>
+      <c r="E46" s="7">
+        <v>-532</v>
+      </c>
+    </row>
+    <row r="47" spans="1:5">
+      <c r="A47" s="5" t="s">
         <v>42</v>
       </c>
-      <c r="B15" s="7" t="s">
-        <v>9</v>
-      </c>
-      <c r="C15" s="8">
-        <v>-7.87</v>
-      </c>
-      <c r="D15" s="8">
-        <v>-3.14</v>
-      </c>
-      <c r="E15" s="10">
-        <v>4.73</v>
-      </c>
-    </row>
-    <row r="16" spans="1:6">
-      <c r="A16" s="7" t="s">
+      <c r="B47" s="5" t="s">
+        <v>2</v>
+      </c>
+      <c r="C47" s="6">
+        <v>1043.2</v>
+      </c>
+      <c r="D47" s="6">
+        <v>982</v>
+      </c>
+      <c r="E47" s="7">
+        <v>-61.2</v>
+      </c>
+    </row>
+    <row r="48" spans="1:5">
+      <c r="A48" s="5" t="s">
         <v>43</v>
       </c>
-      <c r="B16" s="7" t="s">
-        <v>9</v>
-      </c>
-      <c r="C16" s="8">
-        <v>3.06</v>
-      </c>
-      <c r="D16" s="8">
-        <v>15.79</v>
-      </c>
-      <c r="E16" s="10">
-        <v>12.73</v>
-      </c>
-    </row>
-    <row r="17" spans="1:5">
-      <c r="A17" s="7" t="s">
+      <c r="B48" s="5" t="s">
+        <v>2</v>
+      </c>
+      <c r="C48" s="6">
+        <v>157.11</v>
+      </c>
+      <c r="D48" s="6">
+        <v>155.26</v>
+      </c>
+      <c r="E48" s="7">
+        <v>-1.85</v>
+      </c>
+    </row>
+    <row r="49" spans="1:5">
+      <c r="A49" s="5" t="s">
         <v>37</v>
       </c>
-      <c r="B17" s="7" t="s">
-        <v>8</v>
-      </c>
-      <c r="C17" s="8">
-        <v>-0.53</v>
-      </c>
-      <c r="D17" s="8">
-        <v>-1.66</v>
-      </c>
-      <c r="E17" s="9">
-        <v>-1.13</v>
-      </c>
-    </row>
-    <row r="18" spans="1:5">
-      <c r="A18" s="7" t="s">
+      <c r="B49" s="5" t="s">
+        <v>24</v>
+      </c>
+      <c r="C49" s="6">
+        <v>42.86</v>
+      </c>
+      <c r="D49" s="6">
+        <v>37.75</v>
+      </c>
+      <c r="E49" s="7">
+        <v>-5.11</v>
+      </c>
+    </row>
+    <row r="50" spans="1:5">
+      <c r="A50" s="5" t="s">
         <v>38</v>
       </c>
-      <c r="B18" s="7" t="s">
-        <v>8</v>
-      </c>
-      <c r="C18" s="8">
-        <v>1.97</v>
-      </c>
-      <c r="D18" s="8">
-        <v>1.57</v>
-      </c>
-      <c r="E18" s="9">
-        <v>-0.4</v>
-      </c>
-    </row>
-    <row r="19" spans="1:5">
-      <c r="A19" s="7" t="s">
+      <c r="B50" s="5" t="s">
+        <v>24</v>
+      </c>
+      <c r="C50" s="6">
+        <v>48.92</v>
+      </c>
+      <c r="D50" s="6">
+        <v>47.22</v>
+      </c>
+      <c r="E50" s="7">
+        <v>-1.7</v>
+      </c>
+    </row>
+    <row r="51" spans="1:5">
+      <c r="A51" s="5" t="s">
         <v>39</v>
       </c>
-      <c r="B19" s="7" t="s">
-        <v>8</v>
-      </c>
-      <c r="C19" s="8">
-        <v>-1.51</v>
-      </c>
-      <c r="D19" s="8">
-        <v>2.12</v>
-      </c>
-      <c r="E19" s="10">
-        <v>3.63</v>
-      </c>
-    </row>
-    <row r="20" spans="1:5">
-      <c r="A20" s="7" t="s">
+      <c r="B51" s="5" t="s">
+        <v>24</v>
+      </c>
+      <c r="C51" s="6">
+        <v>46.13</v>
+      </c>
+      <c r="D51" s="6">
+        <v>40.53</v>
+      </c>
+      <c r="E51" s="7">
+        <v>-5.6</v>
+      </c>
+    </row>
+    <row r="52" spans="1:5">
+      <c r="A52" s="5" t="s">
         <v>40</v>
       </c>
-      <c r="B20" s="7" t="s">
-        <v>8</v>
-      </c>
-      <c r="C20" s="8">
-        <v>-1.73</v>
-      </c>
-      <c r="D20" s="8">
-        <v>0.52</v>
-      </c>
-      <c r="E20" s="10">
-        <v>2.25</v>
-      </c>
-    </row>
-    <row r="21" spans="1:5">
-      <c r="A21" s="7" t="s">
+      <c r="B52" s="5" t="s">
+        <v>24</v>
+      </c>
+      <c r="C52" s="6">
+        <v>35.17</v>
+      </c>
+      <c r="D52" s="6">
+        <v>26.21</v>
+      </c>
+      <c r="E52" s="7">
+        <v>-8.960000000000001</v>
+      </c>
+    </row>
+    <row r="53" spans="1:5">
+      <c r="A53" s="5" t="s">
         <v>41</v>
       </c>
-      <c r="B21" s="7" t="s">
-        <v>8</v>
-      </c>
-      <c r="C21" s="8">
-        <v>0.77</v>
-      </c>
-      <c r="D21" s="8">
-        <v>4.75</v>
-      </c>
-      <c r="E21" s="10">
-        <v>3.98</v>
-      </c>
-    </row>
-    <row r="22" spans="1:5">
-      <c r="A22" s="7" t="s">
+      <c r="B53" s="5" t="s">
+        <v>24</v>
+      </c>
+      <c r="C53" s="6">
+        <v>56.66</v>
+      </c>
+      <c r="D53" s="6">
+        <v>44.34</v>
+      </c>
+      <c r="E53" s="7">
+        <v>-12.32</v>
+      </c>
+    </row>
+    <row r="54" spans="1:5">
+      <c r="A54" s="5" t="s">
         <v>42</v>
       </c>
-      <c r="B22" s="7" t="s">
-        <v>8</v>
-      </c>
-      <c r="C22" s="8">
-        <v>-0.04</v>
-      </c>
-      <c r="D22" s="8">
-        <v>3.68</v>
-      </c>
-      <c r="E22" s="10">
-        <v>3.72</v>
-      </c>
-    </row>
-    <row r="23" spans="1:5">
-      <c r="A23" s="7" t="s">
+      <c r="B54" s="5" t="s">
+        <v>24</v>
+      </c>
+      <c r="C54" s="6">
+        <v>49</v>
+      </c>
+      <c r="D54" s="6">
+        <v>36.19</v>
+      </c>
+      <c r="E54" s="7">
+        <v>-12.81</v>
+      </c>
+    </row>
+    <row r="55" spans="1:5">
+      <c r="A55" s="5" t="s">
         <v>43</v>
       </c>
-      <c r="B23" s="7" t="s">
-        <v>8</v>
-      </c>
-      <c r="C23" s="8">
-        <v>4.27</v>
-      </c>
-      <c r="D23" s="8">
-        <v>16.47</v>
-      </c>
-      <c r="E23" s="10">
-        <v>12.2</v>
-      </c>
-    </row>
-    <row r="24" spans="1:5">
-      <c r="A24" s="7" t="s">
+      <c r="B55" s="5" t="s">
+        <v>24</v>
+      </c>
+      <c r="C55" s="6">
+        <v>75.55</v>
+      </c>
+      <c r="D55" s="6">
+        <v>71.89</v>
+      </c>
+      <c r="E55" s="7">
+        <v>-3.66</v>
+      </c>
+    </row>
+    <row r="56" spans="1:5">
+      <c r="A56" s="5" t="s">
         <v>37</v>
       </c>
-      <c r="B24" s="7" t="s">
-        <v>11</v>
-      </c>
-      <c r="C24" s="8">
-        <v>26.85</v>
-      </c>
-      <c r="D24" s="8">
-        <v>27.39</v>
-      </c>
-      <c r="E24" s="10">
-        <v>0.54</v>
-      </c>
-    </row>
-    <row r="25" spans="1:5">
-      <c r="A25" s="7" t="s">
+      <c r="B56" s="5" t="s">
+        <v>31</v>
+      </c>
+      <c r="C56" s="6">
+        <v>-28.25</v>
+      </c>
+      <c r="D56" s="6">
+        <v>-51.06</v>
+      </c>
+      <c r="E56" s="7">
+        <v>-22.81</v>
+      </c>
+    </row>
+    <row r="57" spans="1:5">
+      <c r="A57" s="5" t="s">
         <v>38</v>
       </c>
-      <c r="B25" s="7" t="s">
-        <v>11</v>
-      </c>
-      <c r="C25" s="8">
-        <v>116.37</v>
-      </c>
-      <c r="D25" s="8">
-        <v>96.19</v>
-      </c>
-      <c r="E25" s="9">
-        <v>-20.18</v>
-      </c>
-    </row>
-    <row r="26" spans="1:5">
-      <c r="A26" s="7" t="s">
+      <c r="B57" s="5" t="s">
+        <v>31</v>
+      </c>
+      <c r="C57" s="6">
+        <v>-37.56</v>
+      </c>
+      <c r="D57" s="6">
+        <v>-42.63</v>
+      </c>
+      <c r="E57" s="7">
+        <v>-5.07</v>
+      </c>
+    </row>
+    <row r="58" spans="1:5">
+      <c r="A58" s="5" t="s">
         <v>39</v>
       </c>
-      <c r="B26" s="7" t="s">
-        <v>11</v>
-      </c>
-      <c r="C26" s="8">
-        <v>-46.52</v>
-      </c>
-      <c r="D26" s="8">
-        <v>-44.85</v>
-      </c>
-      <c r="E26" s="10">
-        <v>1.67</v>
-      </c>
-    </row>
-    <row r="27" spans="1:5">
-      <c r="A27" s="7" t="s">
+      <c r="B58" s="5" t="s">
+        <v>31</v>
+      </c>
+      <c r="C58" s="6">
+        <v>-33.47</v>
+      </c>
+      <c r="D58" s="6">
+        <v>-34.36</v>
+      </c>
+      <c r="E58" s="7">
+        <v>-0.89</v>
+      </c>
+    </row>
+    <row r="59" spans="1:5">
+      <c r="A59" s="5" t="s">
         <v>40</v>
       </c>
-      <c r="B27" s="7" t="s">
-        <v>11</v>
-      </c>
-      <c r="C27" s="8">
-        <v>-11.36</v>
-      </c>
-      <c r="D27" s="8">
-        <v>-10.76</v>
-      </c>
-      <c r="E27" s="10">
-        <v>0.6</v>
-      </c>
-    </row>
-    <row r="28" spans="1:5">
-      <c r="A28" s="7" t="s">
+      <c r="B59" s="5" t="s">
+        <v>31</v>
+      </c>
+      <c r="C59" s="6">
+        <v>33.45</v>
+      </c>
+      <c r="D59" s="6">
+        <v>165.27</v>
+      </c>
+      <c r="E59" s="8">
+        <v>131.82</v>
+      </c>
+    </row>
+    <row r="60" spans="1:5">
+      <c r="A60" s="5" t="s">
         <v>41</v>
       </c>
-      <c r="B28" s="7" t="s">
-        <v>11</v>
-      </c>
-      <c r="C28" s="8">
-        <v>-17.73</v>
-      </c>
-      <c r="D28" s="8">
-        <v>-14.56</v>
-      </c>
-      <c r="E28" s="10">
-        <v>3.17</v>
-      </c>
-    </row>
-    <row r="29" spans="1:5">
-      <c r="A29" s="7" t="s">
+      <c r="B60" s="5" t="s">
+        <v>31</v>
+      </c>
+      <c r="C60" s="6">
+        <v>-49.88</v>
+      </c>
+      <c r="D60" s="6">
+        <v>-2.37</v>
+      </c>
+      <c r="E60" s="8">
+        <v>47.51</v>
+      </c>
+    </row>
+    <row r="61" spans="1:5">
+      <c r="A61" s="5" t="s">
         <v>42</v>
       </c>
-      <c r="B29" s="7" t="s">
-        <v>11</v>
-      </c>
-      <c r="C29" s="8">
-        <v>0.13</v>
-      </c>
-      <c r="D29" s="8">
-        <v>4.69</v>
-      </c>
-      <c r="E29" s="10">
-        <v>4.56</v>
-      </c>
-    </row>
-    <row r="30" spans="1:5">
-      <c r="A30" s="7" t="s">
+      <c r="B61" s="5" t="s">
+        <v>31</v>
+      </c>
+      <c r="C61" s="6">
+        <v>67.2</v>
+      </c>
+      <c r="D61" s="6">
+        <v>149.77</v>
+      </c>
+      <c r="E61" s="8">
+        <v>82.56999999999999</v>
+      </c>
+    </row>
+    <row r="62" spans="1:5">
+      <c r="A62" s="5" t="s">
         <v>43</v>
       </c>
-      <c r="B30" s="7" t="s">
-        <v>11</v>
-      </c>
-      <c r="C30" s="8">
-        <v>2.56</v>
-      </c>
-      <c r="D30" s="8">
-        <v>16.09</v>
-      </c>
-      <c r="E30" s="10">
-        <v>13.53</v>
-      </c>
-    </row>
-    <row r="31" spans="1:5">
-      <c r="A31" s="7" t="s">
-        <v>37</v>
-      </c>
-      <c r="B31" s="7" t="s">
-        <v>10</v>
-      </c>
-      <c r="C31" s="8">
-        <v>13.35</v>
-      </c>
-      <c r="D31" s="8">
-        <v>16.92</v>
-      </c>
-      <c r="E31" s="10">
-        <v>3.57</v>
-      </c>
-    </row>
-    <row r="32" spans="1:5">
-      <c r="A32" s="7" t="s">
-        <v>38</v>
-      </c>
-      <c r="B32" s="7" t="s">
-        <v>10</v>
-      </c>
-      <c r="C32" s="8">
-        <v>-11.66</v>
-      </c>
-      <c r="D32" s="8">
-        <v>-14.27</v>
-      </c>
-      <c r="E32" s="9">
-        <v>-2.61</v>
-      </c>
-    </row>
-    <row r="33" spans="1:5">
-      <c r="A33" s="7" t="s">
-        <v>39</v>
-      </c>
-      <c r="B33" s="7" t="s">
-        <v>10</v>
-      </c>
-      <c r="C33" s="8">
-        <v>0.08</v>
-      </c>
-      <c r="D33" s="8">
-        <v>1.43</v>
-      </c>
-      <c r="E33" s="10">
-        <v>1.35</v>
-      </c>
-    </row>
-    <row r="34" spans="1:5">
-      <c r="A34" s="7" t="s">
-        <v>40</v>
-      </c>
-      <c r="B34" s="7" t="s">
-        <v>10</v>
-      </c>
-      <c r="C34" s="8">
-        <v>3.31</v>
-      </c>
-      <c r="D34" s="8">
-        <v>3.71</v>
-      </c>
-      <c r="E34" s="10">
-        <v>0.4</v>
-      </c>
-    </row>
-    <row r="35" spans="1:5">
-      <c r="A35" s="7" t="s">
-        <v>41</v>
-      </c>
-      <c r="B35" s="7" t="s">
-        <v>10</v>
-      </c>
-      <c r="C35" s="8">
-        <v>5.37</v>
-      </c>
-      <c r="D35" s="8">
-        <v>8.18</v>
-      </c>
-      <c r="E35" s="10">
-        <v>2.81</v>
-      </c>
-    </row>
-    <row r="36" spans="1:5">
-      <c r="A36" s="7" t="s">
-        <v>42</v>
-      </c>
-      <c r="B36" s="7" t="s">
-        <v>10</v>
-      </c>
-      <c r="C36" s="8">
-        <v>4.82</v>
-      </c>
-      <c r="D36" s="8">
-        <v>5.27</v>
-      </c>
-      <c r="E36" s="10">
-        <v>0.45</v>
-      </c>
-    </row>
-    <row r="37" spans="1:5">
-      <c r="A37" s="7" t="s">
-        <v>43</v>
-      </c>
-      <c r="B37" s="7" t="s">
-        <v>10</v>
-      </c>
-      <c r="C37" s="8">
-        <v>4.61</v>
-      </c>
-      <c r="D37" s="8">
-        <v>16.98</v>
-      </c>
-      <c r="E37" s="10">
-        <v>12.37</v>
-      </c>
-    </row>
-    <row r="38" spans="1:5">
-      <c r="A38" s="7" t="s">
-        <v>37</v>
-      </c>
-      <c r="B38" s="7" t="s">
-        <v>6</v>
-      </c>
-      <c r="C38" s="8">
-        <v>-8.07</v>
-      </c>
-      <c r="D38" s="8">
-        <v>-7.77</v>
-      </c>
-      <c r="E38" s="10">
-        <v>0.3</v>
-      </c>
-    </row>
-    <row r="39" spans="1:5">
-      <c r="A39" s="7" t="s">
-        <v>38</v>
-      </c>
-      <c r="B39" s="7" t="s">
-        <v>6</v>
-      </c>
-      <c r="C39" s="8">
-        <v>-23.35</v>
-      </c>
-      <c r="D39" s="8">
-        <v>-24.53</v>
-      </c>
-      <c r="E39" s="9">
-        <v>-1.18</v>
-      </c>
-    </row>
-    <row r="40" spans="1:5">
-      <c r="A40" s="7" t="s">
-        <v>39</v>
-      </c>
-      <c r="B40" s="7" t="s">
-        <v>6</v>
-      </c>
-      <c r="C40" s="8">
-        <v>-45.85</v>
-      </c>
-      <c r="D40" s="8">
-        <v>-44.15</v>
-      </c>
-      <c r="E40" s="10">
-        <v>1.7</v>
-      </c>
-    </row>
-    <row r="41" spans="1:5">
-      <c r="A41" s="7" t="s">
-        <v>40</v>
-      </c>
-      <c r="B41" s="7" t="s">
-        <v>6</v>
-      </c>
-      <c r="C41" s="8">
-        <v>-16.23</v>
-      </c>
-      <c r="D41" s="8">
-        <v>-15.17</v>
-      </c>
-      <c r="E41" s="10">
-        <v>1.06</v>
-      </c>
-    </row>
-    <row r="42" spans="1:5">
-      <c r="A42" s="7" t="s">
-        <v>41</v>
-      </c>
-      <c r="B42" s="7" t="s">
-        <v>6</v>
-      </c>
-      <c r="C42" s="8">
-        <v>-16.53</v>
-      </c>
-      <c r="D42" s="8">
-        <v>-13.78</v>
-      </c>
-      <c r="E42" s="10">
-        <v>2.75</v>
-      </c>
-    </row>
-    <row r="43" spans="1:5">
-      <c r="A43" s="7" t="s">
-        <v>42</v>
-      </c>
-      <c r="B43" s="7" t="s">
-        <v>6</v>
-      </c>
-      <c r="C43" s="8">
-        <v>-12.94</v>
-      </c>
-      <c r="D43" s="8">
-        <v>-9.98</v>
-      </c>
-      <c r="E43" s="10">
-        <v>2.96</v>
-      </c>
-    </row>
-    <row r="44" spans="1:5">
-      <c r="A44" s="7" t="s">
-        <v>43</v>
-      </c>
-      <c r="B44" s="7" t="s">
-        <v>6</v>
-      </c>
-      <c r="C44" s="8">
-        <v>-5.06</v>
-      </c>
-      <c r="D44" s="8">
-        <v>0</v>
-      </c>
-      <c r="E44" s="10">
-        <v>5.06</v>
-      </c>
-    </row>
-    <row r="45" spans="1:5">
-      <c r="A45" s="7" t="s">
-        <v>37</v>
-      </c>
-      <c r="B45" s="7" t="s">
-        <v>2</v>
-      </c>
-      <c r="C45" s="8">
-        <v>11363</v>
-      </c>
-      <c r="D45" s="8">
-        <v>11400</v>
-      </c>
-      <c r="E45" s="10">
-        <v>37</v>
-      </c>
-    </row>
-    <row r="46" spans="1:5">
-      <c r="A46" s="7" t="s">
-        <v>38</v>
-      </c>
-      <c r="B46" s="7" t="s">
-        <v>2</v>
-      </c>
-      <c r="C46" s="8">
-        <v>513.75</v>
-      </c>
-      <c r="D46" s="8">
-        <v>505.85</v>
-      </c>
-      <c r="E46" s="9">
-        <v>-7.9</v>
-      </c>
-    </row>
-    <row r="47" spans="1:5">
-      <c r="A47" s="7" t="s">
-        <v>39</v>
-      </c>
-      <c r="B47" s="7" t="s">
-        <v>2</v>
-      </c>
-      <c r="C47" s="8">
-        <v>323.45</v>
-      </c>
-      <c r="D47" s="8">
-        <v>329.4</v>
-      </c>
-      <c r="E47" s="10">
-        <v>5.95</v>
-      </c>
-    </row>
-    <row r="48" spans="1:5">
-      <c r="A48" s="7" t="s">
-        <v>40</v>
-      </c>
-      <c r="B48" s="7" t="s">
-        <v>2</v>
-      </c>
-      <c r="C48" s="8">
-        <v>1823.4</v>
-      </c>
-      <c r="D48" s="8">
-        <v>1846.5</v>
-      </c>
-      <c r="E48" s="10">
-        <v>23.1</v>
-      </c>
-    </row>
-    <row r="49" spans="1:5">
-      <c r="A49" s="7" t="s">
-        <v>41</v>
-      </c>
-      <c r="B49" s="7" t="s">
-        <v>2</v>
-      </c>
-      <c r="C49" s="8">
-        <v>11185</v>
-      </c>
-      <c r="D49" s="8">
-        <v>11449</v>
-      </c>
-      <c r="E49" s="10">
-        <v>264</v>
-      </c>
-    </row>
-    <row r="50" spans="1:5">
-      <c r="A50" s="7" t="s">
-        <v>42</v>
-      </c>
-      <c r="B50" s="7" t="s">
-        <v>2</v>
-      </c>
-      <c r="C50" s="8">
-        <v>1008.8</v>
-      </c>
-      <c r="D50" s="8">
-        <v>1043.2</v>
-      </c>
-      <c r="E50" s="10">
-        <v>34.4</v>
-      </c>
-    </row>
-    <row r="51" spans="1:5">
-      <c r="A51" s="7" t="s">
-        <v>43</v>
-      </c>
-      <c r="B51" s="7" t="s">
-        <v>2</v>
-      </c>
-      <c r="C51" s="8">
-        <v>141.41</v>
-      </c>
-      <c r="D51" s="8">
-        <v>157.11</v>
-      </c>
-      <c r="E51" s="10">
-        <v>15.7</v>
-      </c>
-    </row>
-    <row r="52" spans="1:5">
-      <c r="A52" s="7" t="s">
-        <v>37</v>
-      </c>
-      <c r="B52" s="7" t="s">
-        <v>24</v>
-      </c>
-      <c r="C52" s="8">
-        <v>41.44</v>
-      </c>
-      <c r="D52" s="8">
-        <v>42.86</v>
-      </c>
-      <c r="E52" s="10">
-        <v>1.42</v>
-      </c>
-    </row>
-    <row r="53" spans="1:5">
-      <c r="A53" s="7" t="s">
-        <v>38</v>
-      </c>
-      <c r="B53" s="7" t="s">
-        <v>24</v>
-      </c>
-      <c r="C53" s="8">
-        <v>52.23</v>
-      </c>
-      <c r="D53" s="8">
-        <v>48.92</v>
-      </c>
-      <c r="E53" s="9">
-        <v>-3.31</v>
-      </c>
-    </row>
-    <row r="54" spans="1:5">
-      <c r="A54" s="7" t="s">
-        <v>39</v>
-      </c>
-      <c r="B54" s="7" t="s">
-        <v>24</v>
-      </c>
-      <c r="C54" s="8">
-        <v>40.41</v>
-      </c>
-      <c r="D54" s="8">
-        <v>46.13</v>
-      </c>
-      <c r="E54" s="10">
-        <v>5.72</v>
-      </c>
-    </row>
-    <row r="55" spans="1:5">
-      <c r="A55" s="7" t="s">
-        <v>40</v>
-      </c>
-      <c r="B55" s="7" t="s">
-        <v>24</v>
-      </c>
-      <c r="C55" s="8">
-        <v>28.99</v>
-      </c>
-      <c r="D55" s="8">
-        <v>35.17</v>
-      </c>
-      <c r="E55" s="10">
-        <v>6.18</v>
-      </c>
-    </row>
-    <row r="56" spans="1:5">
-      <c r="A56" s="7" t="s">
-        <v>41</v>
-      </c>
-      <c r="B56" s="7" t="s">
-        <v>24</v>
-      </c>
-      <c r="C56" s="8">
-        <v>50.29</v>
-      </c>
-      <c r="D56" s="8">
-        <v>56.66</v>
-      </c>
-      <c r="E56" s="10">
-        <v>6.37</v>
-      </c>
-    </row>
-    <row r="57" spans="1:5">
-      <c r="A57" s="7" t="s">
-        <v>42</v>
-      </c>
-      <c r="B57" s="7" t="s">
-        <v>24</v>
-      </c>
-      <c r="C57" s="8">
-        <v>37.45</v>
-      </c>
-      <c r="D57" s="8">
-        <v>49</v>
-      </c>
-      <c r="E57" s="10">
-        <v>11.55</v>
-      </c>
-    </row>
-    <row r="58" spans="1:5">
-      <c r="A58" s="7" t="s">
-        <v>43</v>
-      </c>
-      <c r="B58" s="7" t="s">
-        <v>24</v>
-      </c>
-      <c r="C58" s="8">
-        <v>59.15</v>
-      </c>
-      <c r="D58" s="8">
-        <v>75.55</v>
-      </c>
-      <c r="E58" s="10">
-        <v>16.4</v>
-      </c>
-    </row>
-    <row r="59" spans="1:5">
-      <c r="A59" s="7" t="s">
-        <v>37</v>
-      </c>
-      <c r="B59" s="7" t="s">
+      <c r="B62" s="5" t="s">
         <v>31</v>
       </c>
-      <c r="C59" s="8">
-        <v>-31.02</v>
-      </c>
-      <c r="D59" s="8">
-        <v>-28.25</v>
-      </c>
-      <c r="E59" s="10">
-        <v>2.77</v>
-      </c>
-    </row>
-    <row r="60" spans="1:5">
-      <c r="A60" s="7" t="s">
-        <v>38</v>
-      </c>
-      <c r="B60" s="7" t="s">
-        <v>31</v>
-      </c>
-      <c r="C60" s="8">
-        <v>-49.75</v>
-      </c>
-      <c r="D60" s="8">
-        <v>-37.56</v>
-      </c>
-      <c r="E60" s="10">
-        <v>12.19</v>
-      </c>
-    </row>
-    <row r="61" spans="1:5">
-      <c r="A61" s="7" t="s">
-        <v>39</v>
-      </c>
-      <c r="B61" s="7" t="s">
-        <v>31</v>
-      </c>
-      <c r="C61" s="8">
-        <v>-46.14</v>
-      </c>
-      <c r="D61" s="8">
-        <v>-33.47</v>
-      </c>
-      <c r="E61" s="10">
-        <v>12.67</v>
-      </c>
-    </row>
-    <row r="62" spans="1:5">
-      <c r="A62" s="7" t="s">
-        <v>40</v>
-      </c>
-      <c r="B62" s="7" t="s">
-        <v>31</v>
-      </c>
-      <c r="C62" s="8">
-        <v>-30.17</v>
-      </c>
-      <c r="D62" s="8">
-        <v>33.45</v>
-      </c>
-      <c r="E62" s="10">
-        <v>63.62</v>
-      </c>
-    </row>
-    <row r="63" spans="1:5">
-      <c r="A63" s="7" t="s">
-        <v>41</v>
-      </c>
-      <c r="B63" s="7" t="s">
-        <v>31</v>
-      </c>
-      <c r="C63" s="8">
-        <v>60.33</v>
-      </c>
-      <c r="D63" s="8">
-        <v>-49.88</v>
-      </c>
-      <c r="E63" s="9">
-        <v>-110.21</v>
-      </c>
-    </row>
-    <row r="64" spans="1:5">
-      <c r="A64" s="7" t="s">
-        <v>42</v>
-      </c>
-      <c r="B64" s="7" t="s">
-        <v>31</v>
-      </c>
-      <c r="C64" s="8">
-        <v>-9.84</v>
-      </c>
-      <c r="D64" s="8">
-        <v>67.2</v>
-      </c>
-      <c r="E64" s="10">
-        <v>77.04000000000001</v>
-      </c>
-    </row>
-    <row r="65" spans="1:5">
-      <c r="A65" s="7" t="s">
-        <v>43</v>
-      </c>
-      <c r="B65" s="7" t="s">
-        <v>31</v>
-      </c>
-      <c r="C65" s="8">
-        <v>149.29</v>
-      </c>
-      <c r="D65" s="8">
+      <c r="C62" s="6">
         <v>2767.61</v>
       </c>
-      <c r="E65" s="10">
-        <v>2618.32</v>
+      <c r="D62" s="6">
+        <v>398.73</v>
+      </c>
+      <c r="E62" s="7">
+        <v>-2368.88</v>
       </c>
     </row>
   </sheetData>
   <mergeCells count="2">
     <mergeCell ref="A1:F1"/>
-    <mergeCell ref="A8:E8"/>
+    <mergeCell ref="A5:E5"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -3024,60 +2904,60 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:9" ht="28" customHeight="1">
-      <c r="A1" s="11" t="s">
+      <c r="A1" s="9" t="s">
         <v>1</v>
       </c>
-      <c r="B1" s="11" t="s">
-        <v>80</v>
-      </c>
-      <c r="C1" s="11" t="s">
-        <v>81</v>
-      </c>
-      <c r="D1" s="11" t="s">
-        <v>82</v>
-      </c>
-      <c r="E1" s="11" t="s">
-        <v>83</v>
-      </c>
-      <c r="F1" s="11" t="s">
-        <v>84</v>
-      </c>
-      <c r="G1" s="11" t="s">
-        <v>85</v>
-      </c>
-      <c r="H1" s="11" t="s">
-        <v>86</v>
-      </c>
-      <c r="I1" s="11" t="s">
-        <v>87</v>
+      <c r="B1" s="9" t="s">
+        <v>65</v>
+      </c>
+      <c r="C1" s="9" t="s">
+        <v>66</v>
+      </c>
+      <c r="D1" s="9" t="s">
+        <v>67</v>
+      </c>
+      <c r="E1" s="9" t="s">
+        <v>68</v>
+      </c>
+      <c r="F1" s="9" t="s">
+        <v>69</v>
+      </c>
+      <c r="G1" s="9" t="s">
+        <v>70</v>
+      </c>
+      <c r="H1" s="9" t="s">
+        <v>71</v>
+      </c>
+      <c r="I1" s="9" t="s">
+        <v>72</v>
       </c>
     </row>
     <row r="2" spans="1:9">
-      <c r="A2" s="12" t="s">
+      <c r="A2" s="10" t="s">
         <v>44</v>
       </c>
-      <c r="B2" s="13">
+      <c r="B2" s="11">
         <v>60.8</v>
       </c>
-      <c r="C2" s="14">
+      <c r="C2" s="12">
         <v>7</v>
       </c>
-      <c r="D2" s="13">
-        <v>50.6</v>
-      </c>
-      <c r="E2" s="13">
+      <c r="D2" s="11">
+        <v>43.4</v>
+      </c>
+      <c r="E2" s="11">
         <v>70</v>
       </c>
-      <c r="F2" s="13">
-        <v>1.3</v>
-      </c>
-      <c r="G2" s="13">
-        <v>5.5</v>
-      </c>
-      <c r="H2" s="13">
+      <c r="F2" s="11">
+        <v>-1.4</v>
+      </c>
+      <c r="G2" s="11">
+        <v>2.9</v>
+      </c>
+      <c r="H2" s="11">
         <v>57</v>
       </c>
-      <c r="I2" s="13">
+      <c r="I2" s="11">
         <v>30</v>
       </c>
     </row>
@@ -3179,49 +3059,49 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:7">
-      <c r="A1" s="15" t="s">
+      <c r="A1" s="13" t="s">
         <v>37</v>
       </c>
-      <c r="B1" s="15" t="s">
+      <c r="B1" s="13" t="s">
         <v>41</v>
       </c>
-      <c r="C1" s="15" t="s">
+      <c r="C1" s="13" t="s">
         <v>38</v>
       </c>
-      <c r="D1" s="15" t="s">
+      <c r="D1" s="13" t="s">
         <v>42</v>
       </c>
-      <c r="E1" s="15" t="s">
+      <c r="E1" s="13" t="s">
         <v>43</v>
       </c>
-      <c r="F1" s="15" t="s">
+      <c r="F1" s="13" t="s">
         <v>40</v>
       </c>
-      <c r="G1" s="15" t="s">
+      <c r="G1" s="13" t="s">
         <v>39</v>
       </c>
     </row>
     <row r="2" spans="1:7">
-      <c r="A2" s="16">
-        <v>0.2746</v>
-      </c>
-      <c r="B2" s="16">
-        <v>0.1997</v>
-      </c>
-      <c r="C2" s="16">
-        <v>0.162</v>
-      </c>
-      <c r="D2" s="16">
-        <v>0.0612</v>
-      </c>
-      <c r="E2" s="16">
-        <v>0.0425</v>
-      </c>
-      <c r="F2" s="16">
-        <v>-0</v>
-      </c>
-      <c r="G2" s="16">
-        <v>-0.2536</v>
+      <c r="A2" s="14">
+        <v>0.2696</v>
+      </c>
+      <c r="B2" s="14">
+        <v>0.1913</v>
+      </c>
+      <c r="C2" s="14">
+        <v>0.1624</v>
+      </c>
+      <c r="D2" s="14">
+        <v>0.0513</v>
+      </c>
+      <c r="E2" s="14">
+        <v>0.0435</v>
+      </c>
+      <c r="F2" s="14">
+        <v>-0.0095</v>
+      </c>
+      <c r="G2" s="14">
+        <v>-0.2513</v>
       </c>
     </row>
   </sheetData>

--- a/BAJAJ_GROUP_Technical_Metrics.xlsx
+++ b/BAJAJ_GROUP_Technical_Metrics.xlsx
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="264" uniqueCount="73">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="286" uniqueCount="73">
   <si>
     <t>Symbol</t>
   </si>
@@ -187,19 +187,19 @@
     <t>Curr Value</t>
   </si>
   <si>
-    <t>RSI Momentum</t>
-  </si>
-  <si>
-    <t>56.7 → 44.3</t>
+    <t>No → Yes</t>
+  </si>
+  <si>
+    <t>🟢 BULLISH</t>
+  </si>
+  <si>
+    <t>20 DMA &gt; 50 DMA</t>
+  </si>
+  <si>
+    <t>Yes → No</t>
   </si>
   <si>
     <t>🔴 BEARISH</t>
-  </si>
-  <si>
-    <t>56.7</t>
-  </si>
-  <si>
-    <t>44.3</t>
   </si>
   <si>
     <t>▶  NUMERIC METRIC CHANGES (vs Previous Run)</t>
@@ -285,14 +285,14 @@
     </font>
     <font>
       <sz val="11"/>
-      <color rgb="FF9C0006"/>
+      <color rgb="FF006100"/>
       <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
     </font>
     <font>
       <sz val="11"/>
-      <color rgb="FF006100"/>
+      <color rgb="FF9C0006"/>
       <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
@@ -325,13 +325,13 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFFFC7CE"/>
+        <fgColor rgb="FFC6EFCE"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFC6EFCE"/>
+        <fgColor rgb="FFFFC7CE"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -401,7 +401,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="15">
+  <cellXfs count="16">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="2" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
@@ -409,6 +409,7 @@
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="5" fillId="6" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1"/>
     <xf numFmtId="165" fontId="4" fillId="5" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
@@ -783,8 +784,8 @@
     <col min="13" max="13" width="10.7109375" customWidth="1"/>
     <col min="14" max="14" width="11.7109375" customWidth="1"/>
     <col min="15" max="15" width="10.7109375" customWidth="1"/>
-    <col min="16" max="17" width="9.7109375" customWidth="1"/>
-    <col min="18" max="19" width="10.7109375" customWidth="1"/>
+    <col min="16" max="16" width="9.7109375" customWidth="1"/>
+    <col min="17" max="19" width="10.7109375" customWidth="1"/>
     <col min="20" max="20" width="22.7109375" customWidth="1"/>
     <col min="21" max="21" width="9.7109375" customWidth="1"/>
     <col min="22" max="22" width="10.7109375" customWidth="1"/>
@@ -924,10 +925,10 @@
         <v>44</v>
       </c>
       <c r="C2">
-        <v>11208</v>
+        <v>11281</v>
       </c>
       <c r="D2">
-        <v>-1.68</v>
+        <v>0.65</v>
       </c>
       <c r="E2">
         <v>12361</v>
@@ -936,46 +937,46 @@
         <v>8506.780000000001</v>
       </c>
       <c r="G2">
-        <v>-9.33</v>
+        <v>-8.74</v>
       </c>
       <c r="H2">
-        <v>31.75</v>
+        <v>32.61</v>
       </c>
       <c r="I2">
-        <v>-2.54</v>
+        <v>-1.17</v>
       </c>
       <c r="J2">
-        <v>-6.03</v>
+        <v>-3.78</v>
       </c>
       <c r="K2">
-        <v>13.87</v>
+        <v>17.14</v>
       </c>
       <c r="L2">
-        <v>26.69</v>
+        <v>26.34</v>
       </c>
       <c r="M2">
-        <v>26.96</v>
+        <v>26.47</v>
       </c>
       <c r="N2">
-        <v>85</v>
+        <v>71</v>
       </c>
       <c r="O2">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="P2">
-        <v>11369</v>
+        <v>11342.4</v>
       </c>
       <c r="Q2">
-        <v>11718.4</v>
+        <v>11696.45</v>
       </c>
       <c r="R2">
-        <v>11544.35</v>
+        <v>11563.34</v>
       </c>
       <c r="S2">
-        <v>10091.92</v>
+        <v>10103.82</v>
       </c>
       <c r="T2">
-        <v>11.06</v>
+        <v>11.65</v>
       </c>
       <c r="U2" t="s">
         <v>45</v>
@@ -990,43 +991,43 @@
         <v>3</v>
       </c>
       <c r="Y2">
-        <v>37.75</v>
+        <v>40.65</v>
       </c>
       <c r="Z2">
-        <v>-70.81</v>
+        <v>-83.56</v>
       </c>
       <c r="AA2">
-        <v>11.43</v>
+        <v>-7.57</v>
       </c>
       <c r="AB2">
-        <v>-82.23999999999999</v>
+        <v>-75.98999999999999</v>
       </c>
       <c r="AC2">
-        <v>3.01</v>
+        <v>8.449999999999999</v>
       </c>
       <c r="AD2">
-        <v>3.97</v>
+        <v>5.67</v>
       </c>
       <c r="AE2">
-        <v>200.64</v>
+        <v>195.17</v>
       </c>
       <c r="AF2">
-        <v>-51.06</v>
+        <v>-43.61</v>
       </c>
       <c r="AG2">
-        <v>12318.24</v>
+        <v>12327.36</v>
       </c>
       <c r="AH2">
-        <v>11118.56</v>
+        <v>11065.54</v>
       </c>
       <c r="AI2">
-        <v>11893.93</v>
+        <v>11857.51</v>
       </c>
       <c r="AJ2" t="s">
         <v>47</v>
       </c>
       <c r="AK2">
-        <v>43.92</v>
+        <v>47.01</v>
       </c>
     </row>
     <row r="3" spans="1:37">
@@ -1037,10 +1038,10 @@
         <v>44</v>
       </c>
       <c r="C3">
-        <v>501.7</v>
+        <v>499.5</v>
       </c>
       <c r="D3">
-        <v>-0.82</v>
+        <v>-0.44</v>
       </c>
       <c r="E3">
         <v>670.25</v>
@@ -1049,46 +1050,46 @@
         <v>232.89</v>
       </c>
       <c r="G3">
-        <v>-25.15</v>
+        <v>-25.48</v>
       </c>
       <c r="H3">
-        <v>115.42</v>
+        <v>114.48</v>
       </c>
       <c r="I3">
-        <v>-0.15</v>
+        <v>-2.47</v>
       </c>
       <c r="J3">
-        <v>10.25</v>
+        <v>7.77</v>
       </c>
       <c r="K3">
-        <v>-13.27</v>
+        <v>-16.35</v>
       </c>
       <c r="L3">
-        <v>96.37</v>
+        <v>93.87</v>
       </c>
       <c r="M3">
-        <v>16.24</v>
+        <v>16.19</v>
       </c>
       <c r="N3">
         <v>99</v>
       </c>
       <c r="O3">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="P3">
-        <v>509.75</v>
+        <v>507.22</v>
       </c>
       <c r="Q3">
-        <v>502.23</v>
+        <v>504.68</v>
       </c>
       <c r="R3">
-        <v>512.6</v>
+        <v>511.52</v>
       </c>
       <c r="S3">
-        <v>446.21</v>
+        <v>447.42</v>
       </c>
       <c r="T3">
-        <v>12.44</v>
+        <v>11.64</v>
       </c>
       <c r="U3" t="s">
         <v>46</v>
@@ -1103,34 +1104,34 @@
         <v>2</v>
       </c>
       <c r="Y3">
-        <v>47.22</v>
+        <v>46.31</v>
       </c>
       <c r="Z3">
-        <v>-0.44</v>
+        <v>-1.02</v>
       </c>
       <c r="AA3">
-        <v>-1.81</v>
+        <v>-1.65</v>
       </c>
       <c r="AB3">
-        <v>1.37</v>
+        <v>0.63</v>
       </c>
       <c r="AC3">
-        <v>30.97</v>
+        <v>10.07</v>
       </c>
       <c r="AD3">
-        <v>51.67</v>
+        <v>31.75</v>
       </c>
       <c r="AE3">
-        <v>19.4</v>
+        <v>19.02</v>
       </c>
       <c r="AF3">
-        <v>-42.63</v>
+        <v>-67.02</v>
       </c>
       <c r="AG3">
-        <v>543.0700000000001</v>
+        <v>537.58</v>
       </c>
       <c r="AH3">
-        <v>461.4</v>
+        <v>471.77</v>
       </c>
       <c r="AI3">
         <v>460.99</v>
@@ -1139,7 +1140,7 @@
         <v>48</v>
       </c>
       <c r="AK3">
-        <v>20.35</v>
+        <v>20.14</v>
       </c>
     </row>
     <row r="4" spans="1:37">
@@ -1150,10 +1151,10 @@
         <v>44</v>
       </c>
       <c r="C4">
-        <v>321.45</v>
+        <v>318.95</v>
       </c>
       <c r="D4">
-        <v>-2.41</v>
+        <v>-0.78</v>
       </c>
       <c r="E4">
         <v>589.75</v>
@@ -1162,46 +1163,46 @@
         <v>303.75</v>
       </c>
       <c r="G4">
-        <v>-45.49</v>
+        <v>-45.92</v>
       </c>
       <c r="H4">
-        <v>5.83</v>
+        <v>5</v>
       </c>
       <c r="I4">
-        <v>-1.18</v>
+        <v>-1.27</v>
       </c>
       <c r="J4">
-        <v>-3.86</v>
+        <v>-6.36</v>
       </c>
       <c r="K4">
-        <v>-0.28</v>
+        <v>0.58</v>
       </c>
       <c r="L4">
-        <v>-45.49</v>
+        <v>-45.34</v>
       </c>
       <c r="M4">
-        <v>-25.13</v>
+        <v>-24.66</v>
       </c>
       <c r="N4">
         <v>15</v>
       </c>
       <c r="O4">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="P4">
-        <v>324.67</v>
+        <v>323.85</v>
       </c>
       <c r="Q4">
-        <v>330.08</v>
+        <v>329.29</v>
       </c>
       <c r="R4">
-        <v>339.27</v>
+        <v>338.93</v>
       </c>
       <c r="S4">
-        <v>372.18</v>
+        <v>371.37</v>
       </c>
       <c r="T4">
-        <v>-13.63</v>
+        <v>-14.12</v>
       </c>
       <c r="U4" t="s">
         <v>46</v>
@@ -1216,43 +1217,43 @@
         <v>0</v>
       </c>
       <c r="Y4">
-        <v>40.53</v>
+        <v>38.94</v>
       </c>
       <c r="Z4">
-        <v>-4.71</v>
+        <v>-5.08</v>
       </c>
       <c r="AA4">
-        <v>-4.04</v>
+        <v>-4.25</v>
       </c>
       <c r="AB4">
-        <v>-0.67</v>
+        <v>-0.84</v>
       </c>
       <c r="AC4">
+        <v>27.79</v>
+      </c>
+      <c r="AD4">
         <v>34.34</v>
       </c>
-      <c r="AD4">
-        <v>34.01</v>
-      </c>
       <c r="AE4">
-        <v>9.6</v>
+        <v>9.279999999999999</v>
       </c>
       <c r="AF4">
-        <v>-34.36</v>
+        <v>-7.62</v>
       </c>
       <c r="AG4">
-        <v>343.26</v>
+        <v>343.16</v>
       </c>
       <c r="AH4">
-        <v>316.9</v>
+        <v>315.42</v>
       </c>
       <c r="AI4">
-        <v>352.86</v>
+        <v>348.41</v>
       </c>
       <c r="AJ4" t="s">
         <v>47</v>
       </c>
       <c r="AK4">
-        <v>13.24</v>
+        <v>13.44</v>
       </c>
     </row>
     <row r="5" spans="1:37">
@@ -1263,10 +1264,10 @@
         <v>44</v>
       </c>
       <c r="C5">
-        <v>1762.3</v>
+        <v>1771</v>
       </c>
       <c r="D5">
-        <v>-4.56</v>
+        <v>0.49</v>
       </c>
       <c r="E5">
         <v>2176.6</v>
@@ -1275,25 +1276,25 @@
         <v>1631.8</v>
       </c>
       <c r="G5">
-        <v>-19.03</v>
+        <v>-18.63</v>
       </c>
       <c r="H5">
-        <v>8</v>
+        <v>8.529999999999999</v>
       </c>
       <c r="I5">
-        <v>-5.21</v>
+        <v>-4.4</v>
       </c>
       <c r="J5">
-        <v>-12.06</v>
+        <v>-11.89</v>
       </c>
       <c r="K5">
-        <v>-0.13</v>
+        <v>0.67</v>
       </c>
       <c r="L5">
-        <v>-14.75</v>
+        <v>-14.42</v>
       </c>
       <c r="M5">
-        <v>-0.95</v>
+        <v>-0.32</v>
       </c>
       <c r="N5">
         <v>29</v>
@@ -1302,19 +1303,19 @@
         <v>44</v>
       </c>
       <c r="P5">
-        <v>1826.9</v>
+        <v>1810.6</v>
       </c>
       <c r="Q5">
-        <v>1915.1</v>
+        <v>1903.1</v>
       </c>
       <c r="R5">
-        <v>1953.69</v>
+        <v>1952.34</v>
       </c>
       <c r="S5">
-        <v>1892.75</v>
+        <v>1891.31</v>
       </c>
       <c r="T5">
-        <v>-6.89</v>
+        <v>-6.36</v>
       </c>
       <c r="U5" t="s">
         <v>46</v>
@@ -1329,43 +1330,43 @@
         <v>1</v>
       </c>
       <c r="Y5">
-        <v>26.21</v>
+        <v>28.25</v>
       </c>
       <c r="Z5">
-        <v>-44.74</v>
+        <v>-48.69</v>
       </c>
       <c r="AA5">
-        <v>-29.85</v>
+        <v>-33.62</v>
       </c>
       <c r="AB5">
-        <v>-14.89</v>
+        <v>-15.07</v>
       </c>
       <c r="AC5">
-        <v>12.53</v>
+        <v>15</v>
       </c>
       <c r="AD5">
-        <v>15.1</v>
+        <v>15.53</v>
       </c>
       <c r="AE5">
-        <v>39.32</v>
+        <v>38.16</v>
       </c>
       <c r="AF5">
-        <v>165.27</v>
+        <v>126.8</v>
       </c>
       <c r="AG5">
-        <v>2063.81</v>
+        <v>2057.84</v>
       </c>
       <c r="AH5">
-        <v>1766.39</v>
+        <v>1748.36</v>
       </c>
       <c r="AI5">
-        <v>1907.41</v>
+        <v>1881.03</v>
       </c>
       <c r="AJ5" t="s">
         <v>47</v>
       </c>
       <c r="AK5">
-        <v>69.23</v>
+        <v>71.48</v>
       </c>
     </row>
     <row r="6" spans="1:37">
@@ -1376,100 +1377,100 @@
         <v>44</v>
       </c>
       <c r="C6">
-        <v>10917</v>
+        <v>10940</v>
       </c>
       <c r="D6">
-        <v>-4.65</v>
+        <v>0.21</v>
       </c>
       <c r="E6">
-        <v>13279</v>
+        <v>13265</v>
       </c>
       <c r="F6">
         <v>8746</v>
       </c>
       <c r="G6">
-        <v>-17.79</v>
+        <v>-17.53</v>
       </c>
       <c r="H6">
-        <v>24.82</v>
+        <v>25.09</v>
       </c>
       <c r="I6">
-        <v>-0.84</v>
+        <v>-3.03</v>
       </c>
       <c r="J6">
-        <v>-3.3</v>
+        <v>-5.2</v>
       </c>
       <c r="K6">
-        <v>3</v>
+        <v>3.29</v>
       </c>
       <c r="L6">
-        <v>-16.92</v>
+        <v>-17.61</v>
       </c>
       <c r="M6">
-        <v>19.13</v>
+        <v>18.71</v>
       </c>
       <c r="N6">
         <v>43</v>
       </c>
       <c r="O6">
-        <v>48</v>
+        <v>46</v>
       </c>
       <c r="P6">
-        <v>11248.4</v>
+        <v>11180</v>
       </c>
       <c r="Q6">
-        <v>11180.4</v>
+        <v>11157.45</v>
       </c>
       <c r="R6">
-        <v>11147.06</v>
+        <v>11157.52</v>
       </c>
       <c r="S6">
-        <v>10682.02</v>
+        <v>10681.88</v>
       </c>
       <c r="T6">
-        <v>2.2</v>
+        <v>2.42</v>
       </c>
       <c r="U6" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="V6" t="s">
         <v>45</v>
       </c>
       <c r="W6" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="X6">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="Y6">
-        <v>44.34</v>
+        <v>44.89</v>
       </c>
       <c r="Z6">
-        <v>-7.03</v>
+        <v>-24.76</v>
       </c>
       <c r="AA6">
-        <v>-5.23</v>
+        <v>-9.140000000000001</v>
       </c>
       <c r="AB6">
-        <v>-1.8</v>
+        <v>-15.62</v>
       </c>
       <c r="AC6">
-        <v>54.17</v>
+        <v>41.37</v>
       </c>
       <c r="AD6">
-        <v>69.65000000000001</v>
+        <v>59.81</v>
       </c>
       <c r="AE6">
-        <v>256.28</v>
+        <v>258.62</v>
       </c>
       <c r="AF6">
-        <v>-2.37</v>
+        <v>-4.66</v>
       </c>
       <c r="AG6">
-        <v>11572.67</v>
+        <v>11549.58</v>
       </c>
       <c r="AH6">
-        <v>10788.13</v>
+        <v>10765.32</v>
       </c>
       <c r="AI6">
         <v>10787.84</v>
@@ -1478,7 +1479,7 @@
         <v>48</v>
       </c>
       <c r="AK6">
-        <v>19.01</v>
+        <v>21.06</v>
       </c>
     </row>
     <row r="7" spans="1:37">
@@ -1489,10 +1490,10 @@
         <v>44</v>
       </c>
       <c r="C7">
-        <v>982</v>
+        <v>996.9</v>
       </c>
       <c r="D7">
-        <v>-5.87</v>
+        <v>1.52</v>
       </c>
       <c r="E7">
         <v>1158.8</v>
@@ -1501,46 +1502,46 @@
         <v>801.55</v>
       </c>
       <c r="G7">
-        <v>-15.26</v>
+        <v>-13.97</v>
       </c>
       <c r="H7">
-        <v>22.51</v>
+        <v>24.37</v>
       </c>
       <c r="I7">
-        <v>-3.25</v>
+        <v>-4.17</v>
       </c>
       <c r="J7">
-        <v>-9.69</v>
+        <v>-8.119999999999999</v>
       </c>
       <c r="K7">
-        <v>0.16</v>
+        <v>1.51</v>
       </c>
       <c r="L7">
-        <v>-1.05</v>
+        <v>-0.95</v>
       </c>
       <c r="M7">
-        <v>5.13</v>
+        <v>5.45</v>
       </c>
       <c r="N7">
         <v>57</v>
       </c>
       <c r="O7">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="P7">
-        <v>1019.12</v>
+        <v>1010.44</v>
       </c>
       <c r="Q7">
-        <v>1039.83</v>
+        <v>1035.53</v>
       </c>
       <c r="R7">
-        <v>1066.73</v>
+        <v>1065.92</v>
       </c>
       <c r="S7">
-        <v>977.39</v>
+        <v>977.24</v>
       </c>
       <c r="T7">
-        <v>0.47</v>
+        <v>2.01</v>
       </c>
       <c r="U7" t="s">
         <v>46</v>
@@ -1555,43 +1556,43 @@
         <v>2</v>
       </c>
       <c r="Y7">
-        <v>36.19</v>
+        <v>40.29</v>
       </c>
       <c r="Z7">
-        <v>-16.2</v>
+        <v>-17.26</v>
       </c>
       <c r="AA7">
-        <v>-12.6</v>
+        <v>-13.53</v>
       </c>
       <c r="AB7">
-        <v>-3.6</v>
+        <v>-3.73</v>
       </c>
       <c r="AC7">
-        <v>57.43</v>
+        <v>60.21</v>
       </c>
       <c r="AD7">
-        <v>65.23999999999999</v>
+        <v>62.26</v>
       </c>
       <c r="AE7">
-        <v>25.65</v>
+        <v>25.03</v>
       </c>
       <c r="AF7">
-        <v>149.77</v>
+        <v>-6.76</v>
       </c>
       <c r="AG7">
-        <v>1091.6</v>
+        <v>1086.5</v>
       </c>
       <c r="AH7">
-        <v>988.0599999999999</v>
+        <v>984.55</v>
       </c>
       <c r="AI7">
-        <v>1071.46</v>
+        <v>1063.8</v>
       </c>
       <c r="AJ7" t="s">
         <v>47</v>
       </c>
       <c r="AK7">
-        <v>36.6</v>
+        <v>38.35</v>
       </c>
     </row>
     <row r="8" spans="1:37">
@@ -1602,100 +1603,100 @@
         <v>44</v>
       </c>
       <c r="C8">
-        <v>155.26</v>
+        <v>167.05</v>
       </c>
       <c r="D8">
-        <v>-1.18</v>
+        <v>7.59</v>
       </c>
       <c r="E8">
-        <v>157.11</v>
+        <v>167.05</v>
       </c>
       <c r="F8">
         <v>115.96</v>
       </c>
       <c r="G8">
-        <v>-1.18</v>
+        <v>0</v>
       </c>
       <c r="H8">
-        <v>33.89</v>
+        <v>44.06</v>
       </c>
       <c r="I8">
-        <v>15.69</v>
+        <v>23.94</v>
       </c>
       <c r="J8">
-        <v>14.91</v>
+        <v>21.91</v>
       </c>
       <c r="K8">
-        <v>16.68</v>
+        <v>27.41</v>
       </c>
       <c r="L8">
-        <v>12.97</v>
+        <v>23.27</v>
       </c>
       <c r="M8">
-        <v>4.35</v>
+        <v>5.58</v>
       </c>
       <c r="N8">
-        <v>71</v>
+        <v>85</v>
       </c>
       <c r="O8">
-        <v>79</v>
+        <v>84</v>
       </c>
       <c r="P8">
-        <v>144.92</v>
+        <v>151.37</v>
       </c>
       <c r="Q8">
-        <v>138.71</v>
+        <v>140.25</v>
       </c>
       <c r="R8">
-        <v>139.27</v>
+        <v>139.69</v>
       </c>
       <c r="S8">
-        <v>134.11</v>
+        <v>134.29</v>
       </c>
       <c r="T8">
-        <v>15.77</v>
+        <v>24.4</v>
       </c>
       <c r="U8" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="V8" t="s">
         <v>45</v>
       </c>
       <c r="W8" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="X8">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="Y8">
-        <v>71.89</v>
+        <v>78.91</v>
       </c>
       <c r="Z8">
-        <v>2.67</v>
+        <v>4.43</v>
       </c>
       <c r="AA8">
-        <v>0.62</v>
+        <v>1.38</v>
       </c>
       <c r="AB8">
-        <v>2.05</v>
+        <v>3.05</v>
       </c>
       <c r="AC8">
-        <v>90.67</v>
+        <v>96.22</v>
       </c>
       <c r="AD8">
-        <v>71.48999999999999</v>
+        <v>87.02</v>
       </c>
       <c r="AE8">
-        <v>5.51</v>
+        <v>6.26</v>
       </c>
       <c r="AF8">
-        <v>398.73</v>
+        <v>340.67</v>
       </c>
       <c r="AG8">
-        <v>151.66</v>
+        <v>158.29</v>
       </c>
       <c r="AH8">
-        <v>125.76</v>
+        <v>122.2</v>
       </c>
       <c r="AI8">
         <v>141.22</v>
@@ -1704,7 +1705,7 @@
         <v>48</v>
       </c>
       <c r="AK8">
-        <v>34.29</v>
+        <v>39.82</v>
       </c>
     </row>
   </sheetData>
@@ -1845,7 +1846,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:F62"/>
+  <dimension ref="A1:F67"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="16.7109375" customWidth="1"/>
@@ -1885,1006 +1886,1100 @@
     </row>
     <row r="3" spans="1:6">
       <c r="A3" s="4" t="s">
+        <v>43</v>
+      </c>
+      <c r="B3" s="4" t="s">
+        <v>22</v>
+      </c>
+      <c r="C3" s="4" t="s">
+        <v>55</v>
+      </c>
+      <c r="D3" s="4" t="s">
+        <v>56</v>
+      </c>
+      <c r="E3" s="4" t="s">
+        <v>46</v>
+      </c>
+      <c r="F3" s="4" t="s">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="4" spans="1:6">
+      <c r="A4" s="4" t="s">
+        <v>43</v>
+      </c>
+      <c r="B4" s="4" t="s">
+        <v>57</v>
+      </c>
+      <c r="C4" s="4" t="s">
+        <v>55</v>
+      </c>
+      <c r="D4" s="4" t="s">
+        <v>56</v>
+      </c>
+      <c r="E4" s="4" t="s">
+        <v>46</v>
+      </c>
+      <c r="F4" s="4" t="s">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="5" spans="1:6">
+      <c r="A5" s="5" t="s">
         <v>41</v>
       </c>
-      <c r="B3" s="4" t="s">
-        <v>55</v>
-      </c>
-      <c r="C3" s="4" t="s">
-        <v>56</v>
-      </c>
-      <c r="D3" s="4" t="s">
+      <c r="B5" s="5" t="s">
+        <v>22</v>
+      </c>
+      <c r="C5" s="5" t="s">
+        <v>58</v>
+      </c>
+      <c r="D5" s="5" t="s">
+        <v>59</v>
+      </c>
+      <c r="E5" s="5" t="s">
+        <v>45</v>
+      </c>
+      <c r="F5" s="5" t="s">
+        <v>46</v>
+      </c>
+    </row>
+    <row r="6" spans="1:6">
+      <c r="A6" s="5" t="s">
+        <v>41</v>
+      </c>
+      <c r="B6" s="5" t="s">
         <v>57</v>
       </c>
-      <c r="E3" s="4" t="s">
+      <c r="C6" s="5" t="s">
         <v>58</v>
       </c>
-      <c r="F3" s="4" t="s">
+      <c r="D6" s="5" t="s">
         <v>59</v>
       </c>
-    </row>
-    <row r="5" spans="1:6">
-      <c r="A5" s="2" t="s">
+      <c r="E6" s="5" t="s">
+        <v>45</v>
+      </c>
+      <c r="F6" s="5" t="s">
+        <v>46</v>
+      </c>
+    </row>
+    <row r="8" spans="1:6">
+      <c r="A8" s="2" t="s">
         <v>60</v>
       </c>
-      <c r="B5" s="2"/>
-      <c r="C5" s="2"/>
-      <c r="D5" s="2"/>
-      <c r="E5" s="2"/>
-    </row>
-    <row r="6" spans="1:6">
-      <c r="A6" s="3" t="s">
+      <c r="B8" s="2"/>
+      <c r="C8" s="2"/>
+      <c r="D8" s="2"/>
+      <c r="E8" s="2"/>
+    </row>
+    <row r="9" spans="1:6">
+      <c r="A9" s="3" t="s">
         <v>0</v>
       </c>
-      <c r="B6" s="3" t="s">
+      <c r="B9" s="3" t="s">
         <v>61</v>
       </c>
-      <c r="C6" s="3" t="s">
+      <c r="C9" s="3" t="s">
         <v>62</v>
       </c>
-      <c r="D6" s="3" t="s">
+      <c r="D9" s="3" t="s">
         <v>63</v>
       </c>
-      <c r="E6" s="3" t="s">
+      <c r="E9" s="3" t="s">
         <v>64</v>
       </c>
     </row>
-    <row r="7" spans="1:6">
-      <c r="A7" s="5" t="s">
+    <row r="10" spans="1:6">
+      <c r="A10" s="6" t="s">
         <v>37</v>
       </c>
-      <c r="B7" s="5" t="s">
+      <c r="B10" s="6" t="s">
         <v>9</v>
       </c>
-      <c r="C7" s="6">
-        <v>-3.39</v>
-      </c>
-      <c r="D7" s="6">
+      <c r="C10" s="7">
         <v>-6.03</v>
       </c>
-      <c r="E7" s="7">
-        <v>-2.64</v>
-      </c>
-    </row>
-    <row r="8" spans="1:6">
-      <c r="A8" s="5" t="s">
+      <c r="D10" s="7">
+        <v>-3.78</v>
+      </c>
+      <c r="E10" s="8">
+        <v>2.25</v>
+      </c>
+    </row>
+    <row r="11" spans="1:6">
+      <c r="A11" s="6" t="s">
         <v>38</v>
       </c>
-      <c r="B8" s="5" t="s">
+      <c r="B11" s="6" t="s">
         <v>9</v>
       </c>
-      <c r="C8" s="6">
-        <v>9.210000000000001</v>
-      </c>
-      <c r="D8" s="6">
+      <c r="C11" s="7">
         <v>10.25</v>
       </c>
-      <c r="E8" s="8">
-        <v>1.04</v>
-      </c>
-    </row>
-    <row r="9" spans="1:6">
-      <c r="A9" s="5" t="s">
+      <c r="D11" s="7">
+        <v>7.77</v>
+      </c>
+      <c r="E11" s="9">
+        <v>-2.48</v>
+      </c>
+    </row>
+    <row r="12" spans="1:6">
+      <c r="A12" s="6" t="s">
         <v>39</v>
       </c>
-      <c r="B9" s="5" t="s">
+      <c r="B12" s="6" t="s">
         <v>9</v>
       </c>
-      <c r="C9" s="6">
-        <v>-4.42</v>
-      </c>
-      <c r="D9" s="6">
+      <c r="C12" s="7">
         <v>-3.86</v>
       </c>
-      <c r="E9" s="8">
-        <v>0.5600000000000001</v>
-      </c>
-    </row>
-    <row r="10" spans="1:6">
-      <c r="A10" s="5" t="s">
+      <c r="D12" s="7">
+        <v>-6.36</v>
+      </c>
+      <c r="E12" s="9">
+        <v>-2.5</v>
+      </c>
+    </row>
+    <row r="13" spans="1:6">
+      <c r="A13" s="6" t="s">
         <v>40</v>
       </c>
-      <c r="B10" s="5" t="s">
+      <c r="B13" s="6" t="s">
         <v>9</v>
       </c>
-      <c r="C10" s="6">
-        <v>-7.75</v>
-      </c>
-      <c r="D10" s="6">
+      <c r="C13" s="7">
         <v>-12.06</v>
       </c>
-      <c r="E10" s="7">
-        <v>-4.31</v>
-      </c>
-    </row>
-    <row r="11" spans="1:6">
-      <c r="A11" s="5" t="s">
+      <c r="D13" s="7">
+        <v>-11.89</v>
+      </c>
+      <c r="E13" s="8">
+        <v>0.17</v>
+      </c>
+    </row>
+    <row r="14" spans="1:6">
+      <c r="A14" s="6" t="s">
         <v>41</v>
       </c>
-      <c r="B11" s="5" t="s">
+      <c r="B14" s="6" t="s">
         <v>9</v>
       </c>
-      <c r="C11" s="6">
-        <v>2.96</v>
-      </c>
-      <c r="D11" s="6">
+      <c r="C14" s="7">
         <v>-3.3</v>
       </c>
-      <c r="E11" s="7">
-        <v>-6.26</v>
-      </c>
-    </row>
-    <row r="12" spans="1:6">
-      <c r="A12" s="5" t="s">
+      <c r="D14" s="7">
+        <v>-5.2</v>
+      </c>
+      <c r="E14" s="9">
+        <v>-1.9</v>
+      </c>
+    </row>
+    <row r="15" spans="1:6">
+      <c r="A15" s="6" t="s">
         <v>42</v>
       </c>
-      <c r="B12" s="5" t="s">
+      <c r="B15" s="6" t="s">
         <v>9</v>
       </c>
-      <c r="C12" s="6">
-        <v>-3.14</v>
-      </c>
-      <c r="D12" s="6">
+      <c r="C15" s="7">
         <v>-9.69</v>
       </c>
-      <c r="E12" s="7">
-        <v>-6.55</v>
-      </c>
-    </row>
-    <row r="13" spans="1:6">
-      <c r="A13" s="5" t="s">
+      <c r="D15" s="7">
+        <v>-8.119999999999999</v>
+      </c>
+      <c r="E15" s="8">
+        <v>1.57</v>
+      </c>
+    </row>
+    <row r="16" spans="1:6">
+      <c r="A16" s="6" t="s">
         <v>43</v>
       </c>
-      <c r="B13" s="5" t="s">
+      <c r="B16" s="6" t="s">
         <v>9</v>
       </c>
-      <c r="C13" s="6">
-        <v>15.79</v>
-      </c>
-      <c r="D13" s="6">
+      <c r="C16" s="7">
         <v>14.91</v>
       </c>
-      <c r="E13" s="7">
-        <v>-0.88</v>
-      </c>
-    </row>
-    <row r="14" spans="1:6">
-      <c r="A14" s="5" t="s">
+      <c r="D16" s="7">
+        <v>21.91</v>
+      </c>
+      <c r="E16" s="8">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="17" spans="1:5">
+      <c r="A17" s="6" t="s">
         <v>37</v>
       </c>
-      <c r="B14" s="5" t="s">
+      <c r="B17" s="6" t="s">
         <v>8</v>
       </c>
-      <c r="C14" s="6">
-        <v>-1.66</v>
-      </c>
-      <c r="D14" s="6">
+      <c r="C17" s="7">
         <v>-2.54</v>
       </c>
-      <c r="E14" s="7">
-        <v>-0.88</v>
-      </c>
-    </row>
-    <row r="15" spans="1:6">
-      <c r="A15" s="5" t="s">
+      <c r="D17" s="7">
+        <v>-1.17</v>
+      </c>
+      <c r="E17" s="8">
+        <v>1.37</v>
+      </c>
+    </row>
+    <row r="18" spans="1:5">
+      <c r="A18" s="6" t="s">
         <v>38</v>
       </c>
-      <c r="B15" s="5" t="s">
+      <c r="B18" s="6" t="s">
         <v>8</v>
       </c>
-      <c r="C15" s="6">
-        <v>1.57</v>
-      </c>
-      <c r="D15" s="6">
+      <c r="C18" s="7">
         <v>-0.15</v>
       </c>
-      <c r="E15" s="7">
-        <v>-1.72</v>
-      </c>
-    </row>
-    <row r="16" spans="1:6">
-      <c r="A16" s="5" t="s">
+      <c r="D18" s="7">
+        <v>-2.47</v>
+      </c>
+      <c r="E18" s="9">
+        <v>-2.32</v>
+      </c>
+    </row>
+    <row r="19" spans="1:5">
+      <c r="A19" s="6" t="s">
         <v>39</v>
       </c>
-      <c r="B16" s="5" t="s">
+      <c r="B19" s="6" t="s">
         <v>8</v>
       </c>
-      <c r="C16" s="6">
-        <v>2.12</v>
-      </c>
-      <c r="D16" s="6">
+      <c r="C19" s="7">
         <v>-1.18</v>
       </c>
-      <c r="E16" s="7">
-        <v>-3.3</v>
-      </c>
-    </row>
-    <row r="17" spans="1:5">
-      <c r="A17" s="5" t="s">
+      <c r="D19" s="7">
+        <v>-1.27</v>
+      </c>
+      <c r="E19" s="9">
+        <v>-0.09</v>
+      </c>
+    </row>
+    <row r="20" spans="1:5">
+      <c r="A20" s="6" t="s">
         <v>40</v>
       </c>
-      <c r="B17" s="5" t="s">
+      <c r="B20" s="6" t="s">
         <v>8</v>
       </c>
-      <c r="C17" s="6">
-        <v>0.52</v>
-      </c>
-      <c r="D17" s="6">
+      <c r="C20" s="7">
         <v>-5.21</v>
       </c>
-      <c r="E17" s="7">
-        <v>-5.73</v>
-      </c>
-    </row>
-    <row r="18" spans="1:5">
-      <c r="A18" s="5" t="s">
+      <c r="D20" s="7">
+        <v>-4.4</v>
+      </c>
+      <c r="E20" s="8">
+        <v>0.8100000000000001</v>
+      </c>
+    </row>
+    <row r="21" spans="1:5">
+      <c r="A21" s="6" t="s">
         <v>41</v>
       </c>
-      <c r="B18" s="5" t="s">
+      <c r="B21" s="6" t="s">
         <v>8</v>
       </c>
-      <c r="C18" s="6">
-        <v>4.75</v>
-      </c>
-      <c r="D18" s="6">
+      <c r="C21" s="7">
         <v>-0.84</v>
       </c>
-      <c r="E18" s="7">
-        <v>-5.59</v>
-      </c>
-    </row>
-    <row r="19" spans="1:5">
-      <c r="A19" s="5" t="s">
+      <c r="D21" s="7">
+        <v>-3.03</v>
+      </c>
+      <c r="E21" s="9">
+        <v>-2.19</v>
+      </c>
+    </row>
+    <row r="22" spans="1:5">
+      <c r="A22" s="6" t="s">
         <v>42</v>
       </c>
-      <c r="B19" s="5" t="s">
+      <c r="B22" s="6" t="s">
         <v>8</v>
       </c>
-      <c r="C19" s="6">
-        <v>3.68</v>
-      </c>
-      <c r="D19" s="6">
+      <c r="C22" s="7">
         <v>-3.25</v>
       </c>
-      <c r="E19" s="7">
-        <v>-6.93</v>
-      </c>
-    </row>
-    <row r="20" spans="1:5">
-      <c r="A20" s="5" t="s">
+      <c r="D22" s="7">
+        <v>-4.17</v>
+      </c>
+      <c r="E22" s="9">
+        <v>-0.92</v>
+      </c>
+    </row>
+    <row r="23" spans="1:5">
+      <c r="A23" s="6" t="s">
         <v>43</v>
       </c>
-      <c r="B20" s="5" t="s">
+      <c r="B23" s="6" t="s">
         <v>8</v>
       </c>
-      <c r="C20" s="6">
-        <v>16.47</v>
-      </c>
-      <c r="D20" s="6">
+      <c r="C23" s="7">
         <v>15.69</v>
       </c>
-      <c r="E20" s="7">
-        <v>-0.78</v>
-      </c>
-    </row>
-    <row r="21" spans="1:5">
-      <c r="A21" s="5" t="s">
+      <c r="D23" s="7">
+        <v>23.94</v>
+      </c>
+      <c r="E23" s="8">
+        <v>8.25</v>
+      </c>
+    </row>
+    <row r="24" spans="1:5">
+      <c r="A24" s="6" t="s">
         <v>37</v>
       </c>
-      <c r="B21" s="5" t="s">
+      <c r="B24" s="6" t="s">
         <v>11</v>
       </c>
-      <c r="C21" s="6">
-        <v>27.39</v>
-      </c>
-      <c r="D21" s="6">
+      <c r="C24" s="7">
         <v>26.69</v>
       </c>
-      <c r="E21" s="7">
-        <v>-0.7</v>
-      </c>
-    </row>
-    <row r="22" spans="1:5">
-      <c r="A22" s="5" t="s">
+      <c r="D24" s="7">
+        <v>26.34</v>
+      </c>
+      <c r="E24" s="9">
+        <v>-0.35</v>
+      </c>
+    </row>
+    <row r="25" spans="1:5">
+      <c r="A25" s="6" t="s">
         <v>38</v>
       </c>
-      <c r="B22" s="5" t="s">
+      <c r="B25" s="6" t="s">
         <v>11</v>
       </c>
-      <c r="C22" s="6">
-        <v>96.19</v>
-      </c>
-      <c r="D22" s="6">
+      <c r="C25" s="7">
         <v>96.37</v>
       </c>
-      <c r="E22" s="8">
-        <v>0.18</v>
-      </c>
-    </row>
-    <row r="23" spans="1:5">
-      <c r="A23" s="5" t="s">
+      <c r="D25" s="7">
+        <v>93.87</v>
+      </c>
+      <c r="E25" s="9">
+        <v>-2.5</v>
+      </c>
+    </row>
+    <row r="26" spans="1:5">
+      <c r="A26" s="6" t="s">
         <v>39</v>
       </c>
-      <c r="B23" s="5" t="s">
+      <c r="B26" s="6" t="s">
         <v>11</v>
       </c>
-      <c r="C23" s="6">
-        <v>-44.85</v>
-      </c>
-      <c r="D23" s="6">
+      <c r="C26" s="7">
         <v>-45.49</v>
       </c>
-      <c r="E23" s="7">
-        <v>-0.64</v>
-      </c>
-    </row>
-    <row r="24" spans="1:5">
-      <c r="A24" s="5" t="s">
+      <c r="D26" s="7">
+        <v>-45.34</v>
+      </c>
+      <c r="E26" s="8">
+        <v>0.15</v>
+      </c>
+    </row>
+    <row r="27" spans="1:5">
+      <c r="A27" s="6" t="s">
         <v>40</v>
       </c>
-      <c r="B24" s="5" t="s">
+      <c r="B27" s="6" t="s">
         <v>11</v>
       </c>
-      <c r="C24" s="6">
-        <v>-10.76</v>
-      </c>
-      <c r="D24" s="6">
+      <c r="C27" s="7">
         <v>-14.75</v>
       </c>
-      <c r="E24" s="7">
-        <v>-3.99</v>
-      </c>
-    </row>
-    <row r="25" spans="1:5">
-      <c r="A25" s="5" t="s">
+      <c r="D27" s="7">
+        <v>-14.42</v>
+      </c>
+      <c r="E27" s="8">
+        <v>0.33</v>
+      </c>
+    </row>
+    <row r="28" spans="1:5">
+      <c r="A28" s="6" t="s">
         <v>41</v>
       </c>
-      <c r="B25" s="5" t="s">
+      <c r="B28" s="6" t="s">
         <v>11</v>
       </c>
-      <c r="C25" s="6">
-        <v>-14.56</v>
-      </c>
-      <c r="D25" s="6">
+      <c r="C28" s="7">
         <v>-16.92</v>
       </c>
-      <c r="E25" s="7">
-        <v>-2.36</v>
-      </c>
-    </row>
-    <row r="26" spans="1:5">
-      <c r="A26" s="5" t="s">
+      <c r="D28" s="7">
+        <v>-17.61</v>
+      </c>
+      <c r="E28" s="9">
+        <v>-0.6899999999999999</v>
+      </c>
+    </row>
+    <row r="29" spans="1:5">
+      <c r="A29" s="6" t="s">
         <v>42</v>
       </c>
-      <c r="B26" s="5" t="s">
+      <c r="B29" s="6" t="s">
         <v>11</v>
       </c>
-      <c r="C26" s="6">
-        <v>4.69</v>
-      </c>
-      <c r="D26" s="6">
+      <c r="C29" s="7">
         <v>-1.05</v>
       </c>
-      <c r="E26" s="7">
-        <v>-5.74</v>
-      </c>
-    </row>
-    <row r="27" spans="1:5">
-      <c r="A27" s="5" t="s">
+      <c r="D29" s="7">
+        <v>-0.95</v>
+      </c>
+      <c r="E29" s="8">
+        <v>0.1</v>
+      </c>
+    </row>
+    <row r="30" spans="1:5">
+      <c r="A30" s="6" t="s">
         <v>43</v>
       </c>
-      <c r="B27" s="5" t="s">
+      <c r="B30" s="6" t="s">
         <v>11</v>
       </c>
-      <c r="C27" s="6">
-        <v>16.09</v>
-      </c>
-      <c r="D27" s="6">
+      <c r="C30" s="7">
         <v>12.97</v>
       </c>
-      <c r="E27" s="7">
-        <v>-3.12</v>
-      </c>
-    </row>
-    <row r="28" spans="1:5">
-      <c r="A28" s="5" t="s">
+      <c r="D30" s="7">
+        <v>23.27</v>
+      </c>
+      <c r="E30" s="8">
+        <v>10.3</v>
+      </c>
+    </row>
+    <row r="31" spans="1:5">
+      <c r="A31" s="6" t="s">
         <v>37</v>
       </c>
-      <c r="B28" s="5" t="s">
+      <c r="B31" s="6" t="s">
         <v>10</v>
       </c>
-      <c r="C28" s="6">
-        <v>16.92</v>
-      </c>
-      <c r="D28" s="6">
+      <c r="C31" s="7">
         <v>13.87</v>
       </c>
-      <c r="E28" s="7">
-        <v>-3.05</v>
-      </c>
-    </row>
-    <row r="29" spans="1:5">
-      <c r="A29" s="5" t="s">
+      <c r="D31" s="7">
+        <v>17.14</v>
+      </c>
+      <c r="E31" s="8">
+        <v>3.27</v>
+      </c>
+    </row>
+    <row r="32" spans="1:5">
+      <c r="A32" s="6" t="s">
         <v>38</v>
       </c>
-      <c r="B29" s="5" t="s">
+      <c r="B32" s="6" t="s">
         <v>10</v>
       </c>
-      <c r="C29" s="6">
-        <v>-14.27</v>
-      </c>
-      <c r="D29" s="6">
+      <c r="C32" s="7">
         <v>-13.27</v>
       </c>
-      <c r="E29" s="8">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="30" spans="1:5">
-      <c r="A30" s="5" t="s">
+      <c r="D32" s="7">
+        <v>-16.35</v>
+      </c>
+      <c r="E32" s="9">
+        <v>-3.08</v>
+      </c>
+    </row>
+    <row r="33" spans="1:5">
+      <c r="A33" s="6" t="s">
         <v>39</v>
       </c>
-      <c r="B30" s="5" t="s">
+      <c r="B33" s="6" t="s">
         <v>10</v>
       </c>
-      <c r="C30" s="6">
-        <v>1.43</v>
-      </c>
-      <c r="D30" s="6">
+      <c r="C33" s="7">
         <v>-0.28</v>
       </c>
-      <c r="E30" s="7">
-        <v>-1.71</v>
-      </c>
-    </row>
-    <row r="31" spans="1:5">
-      <c r="A31" s="5" t="s">
+      <c r="D33" s="7">
+        <v>0.58</v>
+      </c>
+      <c r="E33" s="8">
+        <v>0.86</v>
+      </c>
+    </row>
+    <row r="34" spans="1:5">
+      <c r="A34" s="6" t="s">
         <v>40</v>
       </c>
-      <c r="B31" s="5" t="s">
+      <c r="B34" s="6" t="s">
         <v>10</v>
       </c>
-      <c r="C31" s="6">
-        <v>3.71</v>
-      </c>
-      <c r="D31" s="6">
+      <c r="C34" s="7">
         <v>-0.13</v>
       </c>
-      <c r="E31" s="7">
-        <v>-3.84</v>
-      </c>
-    </row>
-    <row r="32" spans="1:5">
-      <c r="A32" s="5" t="s">
+      <c r="D34" s="7">
+        <v>0.67</v>
+      </c>
+      <c r="E34" s="8">
+        <v>0.8</v>
+      </c>
+    </row>
+    <row r="35" spans="1:5">
+      <c r="A35" s="6" t="s">
         <v>41</v>
       </c>
-      <c r="B32" s="5" t="s">
+      <c r="B35" s="6" t="s">
         <v>10</v>
       </c>
-      <c r="C32" s="6">
-        <v>8.18</v>
-      </c>
-      <c r="D32" s="6">
+      <c r="C35" s="7">
         <v>3</v>
       </c>
-      <c r="E32" s="7">
-        <v>-5.18</v>
-      </c>
-    </row>
-    <row r="33" spans="1:5">
-      <c r="A33" s="5" t="s">
+      <c r="D35" s="7">
+        <v>3.29</v>
+      </c>
+      <c r="E35" s="8">
+        <v>0.29</v>
+      </c>
+    </row>
+    <row r="36" spans="1:5">
+      <c r="A36" s="6" t="s">
         <v>42</v>
       </c>
-      <c r="B33" s="5" t="s">
+      <c r="B36" s="6" t="s">
         <v>10</v>
       </c>
-      <c r="C33" s="6">
-        <v>5.27</v>
-      </c>
-      <c r="D33" s="6">
+      <c r="C36" s="7">
         <v>0.16</v>
       </c>
-      <c r="E33" s="7">
-        <v>-5.11</v>
-      </c>
-    </row>
-    <row r="34" spans="1:5">
-      <c r="A34" s="5" t="s">
+      <c r="D36" s="7">
+        <v>1.51</v>
+      </c>
+      <c r="E36" s="8">
+        <v>1.35</v>
+      </c>
+    </row>
+    <row r="37" spans="1:5">
+      <c r="A37" s="6" t="s">
         <v>43</v>
       </c>
-      <c r="B34" s="5" t="s">
+      <c r="B37" s="6" t="s">
         <v>10</v>
       </c>
-      <c r="C34" s="6">
-        <v>16.98</v>
-      </c>
-      <c r="D34" s="6">
+      <c r="C37" s="7">
         <v>16.68</v>
       </c>
-      <c r="E34" s="7">
-        <v>-0.3</v>
-      </c>
-    </row>
-    <row r="35" spans="1:5">
-      <c r="A35" s="5" t="s">
+      <c r="D37" s="7">
+        <v>27.41</v>
+      </c>
+      <c r="E37" s="8">
+        <v>10.73</v>
+      </c>
+    </row>
+    <row r="38" spans="1:5">
+      <c r="A38" s="6" t="s">
         <v>37</v>
       </c>
-      <c r="B35" s="5" t="s">
+      <c r="B38" s="6" t="s">
         <v>6</v>
       </c>
-      <c r="C35" s="6">
-        <v>-7.77</v>
-      </c>
-      <c r="D35" s="6">
+      <c r="C38" s="7">
         <v>-9.33</v>
       </c>
-      <c r="E35" s="7">
-        <v>-1.56</v>
-      </c>
-    </row>
-    <row r="36" spans="1:5">
-      <c r="A36" s="5" t="s">
+      <c r="D38" s="7">
+        <v>-8.74</v>
+      </c>
+      <c r="E38" s="8">
+        <v>0.59</v>
+      </c>
+    </row>
+    <row r="39" spans="1:5">
+      <c r="A39" s="6" t="s">
         <v>38</v>
       </c>
-      <c r="B36" s="5" t="s">
+      <c r="B39" s="6" t="s">
         <v>6</v>
       </c>
-      <c r="C36" s="6">
-        <v>-24.53</v>
-      </c>
-      <c r="D36" s="6">
+      <c r="C39" s="7">
         <v>-25.15</v>
       </c>
-      <c r="E36" s="7">
-        <v>-0.62</v>
-      </c>
-    </row>
-    <row r="37" spans="1:5">
-      <c r="A37" s="5" t="s">
+      <c r="D39" s="7">
+        <v>-25.48</v>
+      </c>
+      <c r="E39" s="9">
+        <v>-0.33</v>
+      </c>
+    </row>
+    <row r="40" spans="1:5">
+      <c r="A40" s="6" t="s">
         <v>39</v>
       </c>
-      <c r="B37" s="5" t="s">
+      <c r="B40" s="6" t="s">
         <v>6</v>
       </c>
-      <c r="C37" s="6">
-        <v>-44.15</v>
-      </c>
-      <c r="D37" s="6">
+      <c r="C40" s="7">
         <v>-45.49</v>
       </c>
-      <c r="E37" s="7">
-        <v>-1.34</v>
-      </c>
-    </row>
-    <row r="38" spans="1:5">
-      <c r="A38" s="5" t="s">
+      <c r="D40" s="7">
+        <v>-45.92</v>
+      </c>
+      <c r="E40" s="9">
+        <v>-0.43</v>
+      </c>
+    </row>
+    <row r="41" spans="1:5">
+      <c r="A41" s="6" t="s">
         <v>40</v>
       </c>
-      <c r="B38" s="5" t="s">
+      <c r="B41" s="6" t="s">
         <v>6</v>
       </c>
-      <c r="C38" s="6">
-        <v>-15.17</v>
-      </c>
-      <c r="D38" s="6">
+      <c r="C41" s="7">
         <v>-19.03</v>
       </c>
-      <c r="E38" s="7">
-        <v>-3.86</v>
-      </c>
-    </row>
-    <row r="39" spans="1:5">
-      <c r="A39" s="5" t="s">
+      <c r="D41" s="7">
+        <v>-18.63</v>
+      </c>
+      <c r="E41" s="8">
+        <v>0.4</v>
+      </c>
+    </row>
+    <row r="42" spans="1:5">
+      <c r="A42" s="6" t="s">
         <v>41</v>
       </c>
-      <c r="B39" s="5" t="s">
+      <c r="B42" s="6" t="s">
         <v>6</v>
       </c>
-      <c r="C39" s="6">
-        <v>-13.78</v>
-      </c>
-      <c r="D39" s="6">
+      <c r="C42" s="7">
         <v>-17.79</v>
       </c>
-      <c r="E39" s="7">
-        <v>-4.01</v>
-      </c>
-    </row>
-    <row r="40" spans="1:5">
-      <c r="A40" s="5" t="s">
+      <c r="D42" s="7">
+        <v>-17.53</v>
+      </c>
+      <c r="E42" s="8">
+        <v>0.26</v>
+      </c>
+    </row>
+    <row r="43" spans="1:5">
+      <c r="A43" s="6" t="s">
         <v>42</v>
       </c>
-      <c r="B40" s="5" t="s">
+      <c r="B43" s="6" t="s">
         <v>6</v>
       </c>
-      <c r="C40" s="6">
-        <v>-9.98</v>
-      </c>
-      <c r="D40" s="6">
+      <c r="C43" s="7">
         <v>-15.26</v>
       </c>
-      <c r="E40" s="7">
-        <v>-5.28</v>
-      </c>
-    </row>
-    <row r="41" spans="1:5">
-      <c r="A41" s="5" t="s">
+      <c r="D43" s="7">
+        <v>-13.97</v>
+      </c>
+      <c r="E43" s="8">
+        <v>1.29</v>
+      </c>
+    </row>
+    <row r="44" spans="1:5">
+      <c r="A44" s="6" t="s">
         <v>43</v>
       </c>
-      <c r="B41" s="5" t="s">
+      <c r="B44" s="6" t="s">
         <v>6</v>
       </c>
-      <c r="C41" s="6">
+      <c r="C44" s="7">
+        <v>-1.18</v>
+      </c>
+      <c r="D44" s="7">
         <v>0</v>
       </c>
-      <c r="D41" s="6">
-        <v>-1.18</v>
-      </c>
-      <c r="E41" s="7">
-        <v>-1.18</v>
-      </c>
-    </row>
-    <row r="42" spans="1:5">
-      <c r="A42" s="5" t="s">
+      <c r="E44" s="8">
+        <v>1.18</v>
+      </c>
+    </row>
+    <row r="45" spans="1:5">
+      <c r="A45" s="6" t="s">
         <v>37</v>
       </c>
-      <c r="B42" s="5" t="s">
+      <c r="B45" s="6" t="s">
         <v>2</v>
       </c>
-      <c r="C42" s="6">
-        <v>11400</v>
-      </c>
-      <c r="D42" s="6">
+      <c r="C45" s="7">
         <v>11208</v>
       </c>
-      <c r="E42" s="7">
-        <v>-192</v>
-      </c>
-    </row>
-    <row r="43" spans="1:5">
-      <c r="A43" s="5" t="s">
+      <c r="D45" s="7">
+        <v>11281</v>
+      </c>
+      <c r="E45" s="8">
+        <v>73</v>
+      </c>
+    </row>
+    <row r="46" spans="1:5">
+      <c r="A46" s="6" t="s">
         <v>38</v>
       </c>
-      <c r="B43" s="5" t="s">
+      <c r="B46" s="6" t="s">
         <v>2</v>
       </c>
-      <c r="C43" s="6">
-        <v>505.85</v>
-      </c>
-      <c r="D43" s="6">
+      <c r="C46" s="7">
         <v>501.7</v>
       </c>
-      <c r="E43" s="7">
-        <v>-4.15</v>
-      </c>
-    </row>
-    <row r="44" spans="1:5">
-      <c r="A44" s="5" t="s">
+      <c r="D46" s="7">
+        <v>499.5</v>
+      </c>
+      <c r="E46" s="9">
+        <v>-2.2</v>
+      </c>
+    </row>
+    <row r="47" spans="1:5">
+      <c r="A47" s="6" t="s">
         <v>39</v>
       </c>
-      <c r="B44" s="5" t="s">
+      <c r="B47" s="6" t="s">
         <v>2</v>
       </c>
-      <c r="C44" s="6">
-        <v>329.4</v>
-      </c>
-      <c r="D44" s="6">
+      <c r="C47" s="7">
         <v>321.45</v>
       </c>
-      <c r="E44" s="7">
-        <v>-7.95</v>
-      </c>
-    </row>
-    <row r="45" spans="1:5">
-      <c r="A45" s="5" t="s">
+      <c r="D47" s="7">
+        <v>318.95</v>
+      </c>
+      <c r="E47" s="9">
+        <v>-2.5</v>
+      </c>
+    </row>
+    <row r="48" spans="1:5">
+      <c r="A48" s="6" t="s">
         <v>40</v>
       </c>
-      <c r="B45" s="5" t="s">
+      <c r="B48" s="6" t="s">
         <v>2</v>
       </c>
-      <c r="C45" s="6">
-        <v>1846.5</v>
-      </c>
-      <c r="D45" s="6">
+      <c r="C48" s="7">
         <v>1762.3</v>
       </c>
-      <c r="E45" s="7">
-        <v>-84.2</v>
-      </c>
-    </row>
-    <row r="46" spans="1:5">
-      <c r="A46" s="5" t="s">
+      <c r="D48" s="7">
+        <v>1771</v>
+      </c>
+      <c r="E48" s="8">
+        <v>8.699999999999999</v>
+      </c>
+    </row>
+    <row r="49" spans="1:5">
+      <c r="A49" s="6" t="s">
         <v>41</v>
       </c>
-      <c r="B46" s="5" t="s">
+      <c r="B49" s="6" t="s">
         <v>2</v>
       </c>
-      <c r="C46" s="6">
-        <v>11449</v>
-      </c>
-      <c r="D46" s="6">
+      <c r="C49" s="7">
         <v>10917</v>
       </c>
-      <c r="E46" s="7">
-        <v>-532</v>
-      </c>
-    </row>
-    <row r="47" spans="1:5">
-      <c r="A47" s="5" t="s">
+      <c r="D49" s="7">
+        <v>10940</v>
+      </c>
+      <c r="E49" s="8">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="50" spans="1:5">
+      <c r="A50" s="6" t="s">
         <v>42</v>
       </c>
-      <c r="B47" s="5" t="s">
+      <c r="B50" s="6" t="s">
         <v>2</v>
       </c>
-      <c r="C47" s="6">
-        <v>1043.2</v>
-      </c>
-      <c r="D47" s="6">
+      <c r="C50" s="7">
         <v>982</v>
       </c>
-      <c r="E47" s="7">
-        <v>-61.2</v>
-      </c>
-    </row>
-    <row r="48" spans="1:5">
-      <c r="A48" s="5" t="s">
+      <c r="D50" s="7">
+        <v>996.9</v>
+      </c>
+      <c r="E50" s="8">
+        <v>14.9</v>
+      </c>
+    </row>
+    <row r="51" spans="1:5">
+      <c r="A51" s="6" t="s">
         <v>43</v>
       </c>
-      <c r="B48" s="5" t="s">
+      <c r="B51" s="6" t="s">
         <v>2</v>
       </c>
-      <c r="C48" s="6">
-        <v>157.11</v>
-      </c>
-      <c r="D48" s="6">
+      <c r="C51" s="7">
         <v>155.26</v>
       </c>
-      <c r="E48" s="7">
-        <v>-1.85</v>
-      </c>
-    </row>
-    <row r="49" spans="1:5">
-      <c r="A49" s="5" t="s">
+      <c r="D51" s="7">
+        <v>167.05</v>
+      </c>
+      <c r="E51" s="8">
+        <v>11.79</v>
+      </c>
+    </row>
+    <row r="52" spans="1:5">
+      <c r="A52" s="6" t="s">
         <v>37</v>
       </c>
-      <c r="B49" s="5" t="s">
+      <c r="B52" s="6" t="s">
+        <v>13</v>
+      </c>
+      <c r="C52" s="7">
+        <v>85</v>
+      </c>
+      <c r="D52" s="7">
+        <v>71</v>
+      </c>
+      <c r="E52" s="9">
+        <v>-14</v>
+      </c>
+    </row>
+    <row r="53" spans="1:5">
+      <c r="A53" s="6" t="s">
+        <v>43</v>
+      </c>
+      <c r="B53" s="6" t="s">
+        <v>13</v>
+      </c>
+      <c r="C53" s="7">
+        <v>71</v>
+      </c>
+      <c r="D53" s="7">
+        <v>85</v>
+      </c>
+      <c r="E53" s="8">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="54" spans="1:5">
+      <c r="A54" s="6" t="s">
+        <v>37</v>
+      </c>
+      <c r="B54" s="6" t="s">
         <v>24</v>
       </c>
-      <c r="C49" s="6">
-        <v>42.86</v>
-      </c>
-      <c r="D49" s="6">
+      <c r="C54" s="7">
         <v>37.75</v>
       </c>
-      <c r="E49" s="7">
-        <v>-5.11</v>
-      </c>
-    </row>
-    <row r="50" spans="1:5">
-      <c r="A50" s="5" t="s">
+      <c r="D54" s="7">
+        <v>40.65</v>
+      </c>
+      <c r="E54" s="8">
+        <v>2.9</v>
+      </c>
+    </row>
+    <row r="55" spans="1:5">
+      <c r="A55" s="6" t="s">
         <v>38</v>
       </c>
-      <c r="B50" s="5" t="s">
+      <c r="B55" s="6" t="s">
         <v>24</v>
       </c>
-      <c r="C50" s="6">
-        <v>48.92</v>
-      </c>
-      <c r="D50" s="6">
+      <c r="C55" s="7">
         <v>47.22</v>
       </c>
-      <c r="E50" s="7">
-        <v>-1.7</v>
-      </c>
-    </row>
-    <row r="51" spans="1:5">
-      <c r="A51" s="5" t="s">
+      <c r="D55" s="7">
+        <v>46.31</v>
+      </c>
+      <c r="E55" s="9">
+        <v>-0.91</v>
+      </c>
+    </row>
+    <row r="56" spans="1:5">
+      <c r="A56" s="6" t="s">
         <v>39</v>
       </c>
-      <c r="B51" s="5" t="s">
+      <c r="B56" s="6" t="s">
         <v>24</v>
       </c>
-      <c r="C51" s="6">
-        <v>46.13</v>
-      </c>
-      <c r="D51" s="6">
+      <c r="C56" s="7">
         <v>40.53</v>
       </c>
-      <c r="E51" s="7">
-        <v>-5.6</v>
-      </c>
-    </row>
-    <row r="52" spans="1:5">
-      <c r="A52" s="5" t="s">
+      <c r="D56" s="7">
+        <v>38.94</v>
+      </c>
+      <c r="E56" s="9">
+        <v>-1.59</v>
+      </c>
+    </row>
+    <row r="57" spans="1:5">
+      <c r="A57" s="6" t="s">
         <v>40</v>
       </c>
-      <c r="B52" s="5" t="s">
+      <c r="B57" s="6" t="s">
         <v>24</v>
       </c>
-      <c r="C52" s="6">
-        <v>35.17</v>
-      </c>
-      <c r="D52" s="6">
+      <c r="C57" s="7">
         <v>26.21</v>
       </c>
-      <c r="E52" s="7">
-        <v>-8.960000000000001</v>
-      </c>
-    </row>
-    <row r="53" spans="1:5">
-      <c r="A53" s="5" t="s">
+      <c r="D57" s="7">
+        <v>28.25</v>
+      </c>
+      <c r="E57" s="8">
+        <v>2.04</v>
+      </c>
+    </row>
+    <row r="58" spans="1:5">
+      <c r="A58" s="6" t="s">
         <v>41</v>
       </c>
-      <c r="B53" s="5" t="s">
+      <c r="B58" s="6" t="s">
         <v>24</v>
       </c>
-      <c r="C53" s="6">
-        <v>56.66</v>
-      </c>
-      <c r="D53" s="6">
+      <c r="C58" s="7">
         <v>44.34</v>
       </c>
-      <c r="E53" s="7">
-        <v>-12.32</v>
-      </c>
-    </row>
-    <row r="54" spans="1:5">
-      <c r="A54" s="5" t="s">
+      <c r="D58" s="7">
+        <v>44.89</v>
+      </c>
+      <c r="E58" s="8">
+        <v>0.55</v>
+      </c>
+    </row>
+    <row r="59" spans="1:5">
+      <c r="A59" s="6" t="s">
         <v>42</v>
       </c>
-      <c r="B54" s="5" t="s">
+      <c r="B59" s="6" t="s">
         <v>24</v>
       </c>
-      <c r="C54" s="6">
-        <v>49</v>
-      </c>
-      <c r="D54" s="6">
+      <c r="C59" s="7">
         <v>36.19</v>
       </c>
-      <c r="E54" s="7">
-        <v>-12.81</v>
-      </c>
-    </row>
-    <row r="55" spans="1:5">
-      <c r="A55" s="5" t="s">
+      <c r="D59" s="7">
+        <v>40.29</v>
+      </c>
+      <c r="E59" s="8">
+        <v>4.1</v>
+      </c>
+    </row>
+    <row r="60" spans="1:5">
+      <c r="A60" s="6" t="s">
         <v>43</v>
       </c>
-      <c r="B55" s="5" t="s">
+      <c r="B60" s="6" t="s">
         <v>24</v>
       </c>
-      <c r="C55" s="6">
-        <v>75.55</v>
-      </c>
-      <c r="D55" s="6">
+      <c r="C60" s="7">
         <v>71.89</v>
       </c>
-      <c r="E55" s="7">
-        <v>-3.66</v>
-      </c>
-    </row>
-    <row r="56" spans="1:5">
-      <c r="A56" s="5" t="s">
+      <c r="D60" s="7">
+        <v>78.91</v>
+      </c>
+      <c r="E60" s="8">
+        <v>7.02</v>
+      </c>
+    </row>
+    <row r="61" spans="1:5">
+      <c r="A61" s="6" t="s">
         <v>37</v>
       </c>
-      <c r="B56" s="5" t="s">
+      <c r="B61" s="6" t="s">
         <v>31</v>
       </c>
-      <c r="C56" s="6">
-        <v>-28.25</v>
-      </c>
-      <c r="D56" s="6">
+      <c r="C61" s="7">
         <v>-51.06</v>
       </c>
-      <c r="E56" s="7">
-        <v>-22.81</v>
-      </c>
-    </row>
-    <row r="57" spans="1:5">
-      <c r="A57" s="5" t="s">
+      <c r="D61" s="7">
+        <v>-43.61</v>
+      </c>
+      <c r="E61" s="8">
+        <v>7.45</v>
+      </c>
+    </row>
+    <row r="62" spans="1:5">
+      <c r="A62" s="6" t="s">
         <v>38</v>
       </c>
-      <c r="B57" s="5" t="s">
+      <c r="B62" s="6" t="s">
         <v>31</v>
       </c>
-      <c r="C57" s="6">
-        <v>-37.56</v>
-      </c>
-      <c r="D57" s="6">
+      <c r="C62" s="7">
         <v>-42.63</v>
       </c>
-      <c r="E57" s="7">
-        <v>-5.07</v>
-      </c>
-    </row>
-    <row r="58" spans="1:5">
-      <c r="A58" s="5" t="s">
+      <c r="D62" s="7">
+        <v>-67.02</v>
+      </c>
+      <c r="E62" s="9">
+        <v>-24.39</v>
+      </c>
+    </row>
+    <row r="63" spans="1:5">
+      <c r="A63" s="6" t="s">
         <v>39</v>
       </c>
-      <c r="B58" s="5" t="s">
+      <c r="B63" s="6" t="s">
         <v>31</v>
       </c>
-      <c r="C58" s="6">
-        <v>-33.47</v>
-      </c>
-      <c r="D58" s="6">
+      <c r="C63" s="7">
         <v>-34.36</v>
       </c>
-      <c r="E58" s="7">
-        <v>-0.89</v>
-      </c>
-    </row>
-    <row r="59" spans="1:5">
-      <c r="A59" s="5" t="s">
+      <c r="D63" s="7">
+        <v>-7.62</v>
+      </c>
+      <c r="E63" s="8">
+        <v>26.74</v>
+      </c>
+    </row>
+    <row r="64" spans="1:5">
+      <c r="A64" s="6" t="s">
         <v>40</v>
       </c>
-      <c r="B59" s="5" t="s">
+      <c r="B64" s="6" t="s">
         <v>31</v>
       </c>
-      <c r="C59" s="6">
-        <v>33.45</v>
-      </c>
-      <c r="D59" s="6">
+      <c r="C64" s="7">
         <v>165.27</v>
       </c>
-      <c r="E59" s="8">
-        <v>131.82</v>
-      </c>
-    </row>
-    <row r="60" spans="1:5">
-      <c r="A60" s="5" t="s">
+      <c r="D64" s="7">
+        <v>126.8</v>
+      </c>
+      <c r="E64" s="9">
+        <v>-38.47</v>
+      </c>
+    </row>
+    <row r="65" spans="1:5">
+      <c r="A65" s="6" t="s">
         <v>41</v>
       </c>
-      <c r="B60" s="5" t="s">
+      <c r="B65" s="6" t="s">
         <v>31</v>
       </c>
-      <c r="C60" s="6">
-        <v>-49.88</v>
-      </c>
-      <c r="D60" s="6">
+      <c r="C65" s="7">
         <v>-2.37</v>
       </c>
-      <c r="E60" s="8">
-        <v>47.51</v>
-      </c>
-    </row>
-    <row r="61" spans="1:5">
-      <c r="A61" s="5" t="s">
+      <c r="D65" s="7">
+        <v>-4.66</v>
+      </c>
+      <c r="E65" s="9">
+        <v>-2.29</v>
+      </c>
+    </row>
+    <row r="66" spans="1:5">
+      <c r="A66" s="6" t="s">
         <v>42</v>
       </c>
-      <c r="B61" s="5" t="s">
+      <c r="B66" s="6" t="s">
         <v>31</v>
       </c>
-      <c r="C61" s="6">
-        <v>67.2</v>
-      </c>
-      <c r="D61" s="6">
+      <c r="C66" s="7">
         <v>149.77</v>
       </c>
-      <c r="E61" s="8">
-        <v>82.56999999999999</v>
-      </c>
-    </row>
-    <row r="62" spans="1:5">
-      <c r="A62" s="5" t="s">
+      <c r="D66" s="7">
+        <v>-6.76</v>
+      </c>
+      <c r="E66" s="9">
+        <v>-156.53</v>
+      </c>
+    </row>
+    <row r="67" spans="1:5">
+      <c r="A67" s="6" t="s">
         <v>43</v>
       </c>
-      <c r="B62" s="5" t="s">
+      <c r="B67" s="6" t="s">
         <v>31</v>
       </c>
-      <c r="C62" s="6">
-        <v>2767.61</v>
-      </c>
-      <c r="D62" s="6">
+      <c r="C67" s="7">
         <v>398.73</v>
       </c>
-      <c r="E62" s="7">
-        <v>-2368.88</v>
+      <c r="D67" s="7">
+        <v>340.67</v>
+      </c>
+      <c r="E67" s="9">
+        <v>-58.06</v>
       </c>
     </row>
   </sheetData>
   <mergeCells count="2">
     <mergeCell ref="A1:F1"/>
-    <mergeCell ref="A5:E5"/>
+    <mergeCell ref="A8:E8"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -2904,60 +2999,60 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:9" ht="28" customHeight="1">
-      <c r="A1" s="9" t="s">
+      <c r="A1" s="10" t="s">
         <v>1</v>
       </c>
-      <c r="B1" s="9" t="s">
+      <c r="B1" s="10" t="s">
         <v>65</v>
       </c>
-      <c r="C1" s="9" t="s">
+      <c r="C1" s="10" t="s">
         <v>66</v>
       </c>
-      <c r="D1" s="9" t="s">
+      <c r="D1" s="10" t="s">
         <v>67</v>
       </c>
-      <c r="E1" s="9" t="s">
+      <c r="E1" s="10" t="s">
         <v>68</v>
       </c>
-      <c r="F1" s="9" t="s">
+      <c r="F1" s="10" t="s">
         <v>69</v>
       </c>
-      <c r="G1" s="9" t="s">
+      <c r="G1" s="10" t="s">
         <v>70</v>
       </c>
-      <c r="H1" s="9" t="s">
+      <c r="H1" s="10" t="s">
         <v>71</v>
       </c>
-      <c r="I1" s="9" t="s">
+      <c r="I1" s="10" t="s">
         <v>72</v>
       </c>
     </row>
     <row r="2" spans="1:9">
-      <c r="A2" s="10" t="s">
+      <c r="A2" s="11" t="s">
         <v>44</v>
       </c>
-      <c r="B2" s="11">
+      <c r="B2" s="12">
         <v>60.8</v>
       </c>
-      <c r="C2" s="12">
+      <c r="C2" s="13">
         <v>7</v>
       </c>
-      <c r="D2" s="11">
-        <v>43.4</v>
-      </c>
-      <c r="E2" s="11">
+      <c r="D2" s="12">
+        <v>45.5</v>
+      </c>
+      <c r="E2" s="12">
         <v>70</v>
       </c>
-      <c r="F2" s="11">
-        <v>-1.4</v>
-      </c>
-      <c r="G2" s="11">
-        <v>2.9</v>
-      </c>
-      <c r="H2" s="11">
+      <c r="F2" s="12">
+        <v>-0.8</v>
+      </c>
+      <c r="G2" s="12">
+        <v>4.9</v>
+      </c>
+      <c r="H2" s="12">
         <v>57</v>
       </c>
-      <c r="I2" s="11">
+      <c r="I2" s="12">
         <v>30</v>
       </c>
     </row>
@@ -3059,49 +3154,49 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:7">
-      <c r="A1" s="13" t="s">
+      <c r="A1" s="14" t="s">
         <v>37</v>
       </c>
-      <c r="B1" s="13" t="s">
+      <c r="B1" s="14" t="s">
         <v>41</v>
       </c>
-      <c r="C1" s="13" t="s">
+      <c r="C1" s="14" t="s">
         <v>38</v>
       </c>
-      <c r="D1" s="13" t="s">
+      <c r="D1" s="14" t="s">
+        <v>43</v>
+      </c>
+      <c r="E1" s="14" t="s">
         <v>42</v>
       </c>
-      <c r="E1" s="13" t="s">
-        <v>43</v>
-      </c>
-      <c r="F1" s="13" t="s">
+      <c r="F1" s="14" t="s">
         <v>40</v>
       </c>
-      <c r="G1" s="13" t="s">
+      <c r="G1" s="14" t="s">
         <v>39</v>
       </c>
     </row>
     <row r="2" spans="1:7">
-      <c r="A2" s="14">
-        <v>0.2696</v>
-      </c>
-      <c r="B2" s="14">
-        <v>0.1913</v>
-      </c>
-      <c r="C2" s="14">
-        <v>0.1624</v>
-      </c>
-      <c r="D2" s="14">
-        <v>0.0513</v>
-      </c>
-      <c r="E2" s="14">
-        <v>0.0435</v>
-      </c>
-      <c r="F2" s="14">
-        <v>-0.0095</v>
-      </c>
-      <c r="G2" s="14">
-        <v>-0.2513</v>
+      <c r="A2" s="15">
+        <v>0.2647</v>
+      </c>
+      <c r="B2" s="15">
+        <v>0.1871</v>
+      </c>
+      <c r="C2" s="15">
+        <v>0.1619</v>
+      </c>
+      <c r="D2" s="15">
+        <v>0.0558</v>
+      </c>
+      <c r="E2" s="15">
+        <v>0.0545</v>
+      </c>
+      <c r="F2" s="15">
+        <v>-0.0032</v>
+      </c>
+      <c r="G2" s="15">
+        <v>-0.2466</v>
       </c>
     </row>
   </sheetData>

--- a/BAJAJ_GROUP_Technical_Metrics.xlsx
+++ b/BAJAJ_GROUP_Technical_Metrics.xlsx
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="286" uniqueCount="73">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="251" uniqueCount="64">
   <si>
     <t>Symbol</t>
   </si>
@@ -172,34 +172,7 @@
     <t>▶  SIGNAL EVENTS (vs Previous Run)</t>
   </si>
   <si>
-    <t>Signal</t>
-  </si>
-  <si>
-    <t>Change</t>
-  </si>
-  <si>
-    <t>Direction</t>
-  </si>
-  <si>
-    <t>Prev Value</t>
-  </si>
-  <si>
-    <t>Curr Value</t>
-  </si>
-  <si>
-    <t>No → Yes</t>
-  </si>
-  <si>
-    <t>🟢 BULLISH</t>
-  </si>
-  <si>
-    <t>20 DMA &gt; 50 DMA</t>
-  </si>
-  <si>
-    <t>Yes → No</t>
-  </si>
-  <si>
-    <t>🔴 BEARISH</t>
+    <t>No signal events detected since last run.</t>
   </si>
   <si>
     <t>▶  NUMERIC METRIC CHANGES (vs Previous Run)</t>
@@ -285,14 +258,14 @@
     </font>
     <font>
       <sz val="11"/>
-      <color rgb="FF006100"/>
+      <color rgb="FF9C0006"/>
       <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
     </font>
     <font>
       <sz val="11"/>
-      <color rgb="FF9C0006"/>
+      <color rgb="FF006100"/>
       <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
@@ -325,13 +298,13 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFC6EFCE"/>
+        <fgColor rgb="FFFFC7CE"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFFFC7CE"/>
+        <fgColor rgb="FFC6EFCE"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -401,16 +374,14 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="16">
+  <cellXfs count="14">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="2" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="3" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="5" fillId="6" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1"/>
     <xf numFmtId="165" fontId="4" fillId="5" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="165" fontId="5" fillId="6" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
@@ -925,10 +896,10 @@
         <v>44</v>
       </c>
       <c r="C2">
-        <v>11281</v>
+        <v>11024</v>
       </c>
       <c r="D2">
-        <v>0.65</v>
+        <v>-2.28</v>
       </c>
       <c r="E2">
         <v>12361</v>
@@ -937,25 +908,25 @@
         <v>8506.780000000001</v>
       </c>
       <c r="G2">
-        <v>-8.74</v>
+        <v>-10.82</v>
       </c>
       <c r="H2">
-        <v>32.61</v>
+        <v>29.59</v>
       </c>
       <c r="I2">
-        <v>-1.17</v>
+        <v>-3.8</v>
       </c>
       <c r="J2">
-        <v>-3.78</v>
+        <v>-5.94</v>
       </c>
       <c r="K2">
-        <v>17.14</v>
+        <v>13.46</v>
       </c>
       <c r="L2">
-        <v>26.34</v>
+        <v>24.43</v>
       </c>
       <c r="M2">
-        <v>26.47</v>
+        <v>25.89</v>
       </c>
       <c r="N2">
         <v>71</v>
@@ -964,19 +935,19 @@
         <v>79</v>
       </c>
       <c r="P2">
-        <v>11342.4</v>
+        <v>11255.2</v>
       </c>
       <c r="Q2">
-        <v>11696.45</v>
+        <v>11652.15</v>
       </c>
       <c r="R2">
-        <v>11563.34</v>
+        <v>11574.96</v>
       </c>
       <c r="S2">
-        <v>10103.82</v>
+        <v>10114.76</v>
       </c>
       <c r="T2">
-        <v>11.65</v>
+        <v>8.99</v>
       </c>
       <c r="U2" t="s">
         <v>45</v>
@@ -991,43 +962,43 @@
         <v>3</v>
       </c>
       <c r="Y2">
-        <v>40.65</v>
+        <v>34.55</v>
       </c>
       <c r="Z2">
-        <v>-83.56</v>
+        <v>-113.1</v>
       </c>
       <c r="AA2">
-        <v>-7.57</v>
+        <v>-28.68</v>
       </c>
       <c r="AB2">
-        <v>-75.98999999999999</v>
+        <v>-84.42</v>
       </c>
       <c r="AC2">
-        <v>8.449999999999999</v>
+        <v>5.45</v>
       </c>
       <c r="AD2">
-        <v>5.67</v>
+        <v>5.64</v>
       </c>
       <c r="AE2">
-        <v>195.17</v>
+        <v>204.66</v>
       </c>
       <c r="AF2">
-        <v>-43.61</v>
+        <v>13.03</v>
       </c>
       <c r="AG2">
-        <v>12327.36</v>
+        <v>12341.63</v>
       </c>
       <c r="AH2">
-        <v>11065.54</v>
+        <v>10962.67</v>
       </c>
       <c r="AI2">
-        <v>11857.51</v>
+        <v>11725.47</v>
       </c>
       <c r="AJ2" t="s">
         <v>47</v>
       </c>
       <c r="AK2">
-        <v>47.01</v>
+        <v>51.47</v>
       </c>
     </row>
     <row r="3" spans="1:37">
@@ -1038,10 +1009,10 @@
         <v>44</v>
       </c>
       <c r="C3">
-        <v>499.5</v>
+        <v>480.05</v>
       </c>
       <c r="D3">
-        <v>-0.44</v>
+        <v>-3.89</v>
       </c>
       <c r="E3">
         <v>670.25</v>
@@ -1050,46 +1021,46 @@
         <v>232.89</v>
       </c>
       <c r="G3">
-        <v>-25.48</v>
+        <v>-28.38</v>
       </c>
       <c r="H3">
-        <v>114.48</v>
+        <v>106.13</v>
       </c>
       <c r="I3">
-        <v>-2.47</v>
+        <v>-6.84</v>
       </c>
       <c r="J3">
-        <v>7.77</v>
+        <v>6.54</v>
       </c>
       <c r="K3">
-        <v>-16.35</v>
+        <v>-19.86</v>
       </c>
       <c r="L3">
-        <v>93.87</v>
+        <v>89.12</v>
       </c>
       <c r="M3">
-        <v>16.19</v>
+        <v>15.3</v>
       </c>
       <c r="N3">
         <v>99</v>
       </c>
       <c r="O3">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="P3">
-        <v>507.22</v>
+        <v>500.17</v>
       </c>
       <c r="Q3">
-        <v>504.68</v>
+        <v>504.81</v>
       </c>
       <c r="R3">
-        <v>511.52</v>
+        <v>510.61</v>
       </c>
       <c r="S3">
-        <v>447.42</v>
+        <v>448.53</v>
       </c>
       <c r="T3">
-        <v>11.64</v>
+        <v>7.03</v>
       </c>
       <c r="U3" t="s">
         <v>46</v>
@@ -1104,34 +1075,34 @@
         <v>2</v>
       </c>
       <c r="Y3">
-        <v>46.31</v>
+        <v>39.09</v>
       </c>
       <c r="Z3">
-        <v>-1.02</v>
+        <v>-3.01</v>
       </c>
       <c r="AA3">
-        <v>-1.65</v>
+        <v>-1.92</v>
       </c>
       <c r="AB3">
-        <v>0.63</v>
+        <v>-1.09</v>
       </c>
       <c r="AC3">
-        <v>10.07</v>
+        <v>2.32</v>
       </c>
       <c r="AD3">
-        <v>31.75</v>
+        <v>14.45</v>
       </c>
       <c r="AE3">
-        <v>19.02</v>
+        <v>19.29</v>
       </c>
       <c r="AF3">
-        <v>-67.02</v>
+        <v>-54.79</v>
       </c>
       <c r="AG3">
-        <v>537.58</v>
+        <v>537.28</v>
       </c>
       <c r="AH3">
-        <v>471.77</v>
+        <v>472.34</v>
       </c>
       <c r="AI3">
         <v>460.99</v>
@@ -1140,7 +1111,7 @@
         <v>48</v>
       </c>
       <c r="AK3">
-        <v>20.14</v>
+        <v>22.94</v>
       </c>
     </row>
     <row r="4" spans="1:37">
@@ -1151,10 +1122,10 @@
         <v>44</v>
       </c>
       <c r="C4">
-        <v>318.95</v>
+        <v>314.65</v>
       </c>
       <c r="D4">
-        <v>-0.78</v>
+        <v>-1.35</v>
       </c>
       <c r="E4">
         <v>589.75</v>
@@ -1163,46 +1134,46 @@
         <v>303.75</v>
       </c>
       <c r="G4">
-        <v>-45.92</v>
+        <v>-46.65</v>
       </c>
       <c r="H4">
-        <v>5</v>
+        <v>3.59</v>
       </c>
       <c r="I4">
-        <v>-1.27</v>
+        <v>-3.48</v>
       </c>
       <c r="J4">
-        <v>-6.36</v>
+        <v>-6.02</v>
       </c>
       <c r="K4">
-        <v>0.58</v>
+        <v>-1.52</v>
       </c>
       <c r="L4">
-        <v>-45.34</v>
+        <v>-45.48</v>
       </c>
       <c r="M4">
-        <v>-24.66</v>
+        <v>-24.39</v>
       </c>
       <c r="N4">
         <v>15</v>
       </c>
       <c r="O4">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="P4">
-        <v>323.85</v>
+        <v>321.58</v>
       </c>
       <c r="Q4">
-        <v>329.29</v>
+        <v>328.38</v>
       </c>
       <c r="R4">
-        <v>338.93</v>
+        <v>338.59</v>
       </c>
       <c r="S4">
-        <v>371.37</v>
+        <v>370.58</v>
       </c>
       <c r="T4">
-        <v>-14.12</v>
+        <v>-15.09</v>
       </c>
       <c r="U4" t="s">
         <v>46</v>
@@ -1217,43 +1188,43 @@
         <v>0</v>
       </c>
       <c r="Y4">
-        <v>38.94</v>
+        <v>36.28</v>
       </c>
       <c r="Z4">
-        <v>-5.08</v>
+        <v>-5.66</v>
       </c>
       <c r="AA4">
-        <v>-4.25</v>
+        <v>-4.53</v>
       </c>
       <c r="AB4">
-        <v>-0.84</v>
+        <v>-1.13</v>
       </c>
       <c r="AC4">
-        <v>27.79</v>
+        <v>7.77</v>
       </c>
       <c r="AD4">
-        <v>34.34</v>
+        <v>23.3</v>
       </c>
       <c r="AE4">
-        <v>9.279999999999999</v>
+        <v>9.43</v>
       </c>
       <c r="AF4">
-        <v>-7.62</v>
+        <v>-12.03</v>
       </c>
       <c r="AG4">
-        <v>343.16</v>
+        <v>343.6</v>
       </c>
       <c r="AH4">
-        <v>315.42</v>
+        <v>313.17</v>
       </c>
       <c r="AI4">
-        <v>348.41</v>
+        <v>346.95</v>
       </c>
       <c r="AJ4" t="s">
         <v>47</v>
       </c>
       <c r="AK4">
-        <v>13.44</v>
+        <v>16.08</v>
       </c>
     </row>
     <row r="5" spans="1:37">
@@ -1264,10 +1235,10 @@
         <v>44</v>
       </c>
       <c r="C5">
-        <v>1771</v>
+        <v>1752</v>
       </c>
       <c r="D5">
-        <v>0.49</v>
+        <v>-1.07</v>
       </c>
       <c r="E5">
         <v>2176.6</v>
@@ -1276,46 +1247,46 @@
         <v>1631.8</v>
       </c>
       <c r="G5">
-        <v>-18.63</v>
+        <v>-19.51</v>
       </c>
       <c r="H5">
-        <v>8.529999999999999</v>
+        <v>7.37</v>
       </c>
       <c r="I5">
-        <v>-4.4</v>
+        <v>-5.29</v>
       </c>
       <c r="J5">
-        <v>-11.89</v>
+        <v>-12.88</v>
       </c>
       <c r="K5">
-        <v>0.67</v>
+        <v>-1.58</v>
       </c>
       <c r="L5">
-        <v>-14.42</v>
+        <v>-15.95</v>
       </c>
       <c r="M5">
-        <v>-0.32</v>
+        <v>0.01</v>
       </c>
       <c r="N5">
         <v>29</v>
       </c>
       <c r="O5">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="P5">
-        <v>1810.6</v>
+        <v>1791.04</v>
       </c>
       <c r="Q5">
-        <v>1903.1</v>
+        <v>1890.6</v>
       </c>
       <c r="R5">
-        <v>1952.34</v>
+        <v>1950.3</v>
       </c>
       <c r="S5">
-        <v>1891.31</v>
+        <v>1889.73</v>
       </c>
       <c r="T5">
-        <v>-6.36</v>
+        <v>-7.29</v>
       </c>
       <c r="U5" t="s">
         <v>46</v>
@@ -1330,43 +1301,43 @@
         <v>1</v>
       </c>
       <c r="Y5">
-        <v>28.25</v>
+        <v>26.53</v>
       </c>
       <c r="Z5">
-        <v>-48.69</v>
+        <v>-52.74</v>
       </c>
       <c r="AA5">
-        <v>-33.62</v>
+        <v>-37.44</v>
       </c>
       <c r="AB5">
-        <v>-15.07</v>
+        <v>-15.3</v>
       </c>
       <c r="AC5">
-        <v>15</v>
+        <v>4.92</v>
       </c>
       <c r="AD5">
-        <v>15.53</v>
+        <v>10.82</v>
       </c>
       <c r="AE5">
-        <v>38.16</v>
+        <v>37.71</v>
       </c>
       <c r="AF5">
-        <v>126.8</v>
+        <v>-19.44</v>
       </c>
       <c r="AG5">
-        <v>2057.84</v>
+        <v>2051.95</v>
       </c>
       <c r="AH5">
-        <v>1748.36</v>
+        <v>1729.25</v>
       </c>
       <c r="AI5">
-        <v>1881.03</v>
+        <v>1867.19</v>
       </c>
       <c r="AJ5" t="s">
         <v>47</v>
       </c>
       <c r="AK5">
-        <v>71.48</v>
+        <v>73.65000000000001</v>
       </c>
     </row>
     <row r="6" spans="1:37">
@@ -1377,58 +1348,58 @@
         <v>44</v>
       </c>
       <c r="C6">
-        <v>10940</v>
+        <v>10800</v>
       </c>
       <c r="D6">
-        <v>0.21</v>
+        <v>-1.28</v>
       </c>
       <c r="E6">
-        <v>13265</v>
+        <v>13203</v>
       </c>
       <c r="F6">
         <v>8746</v>
       </c>
       <c r="G6">
-        <v>-17.53</v>
+        <v>-18.2</v>
       </c>
       <c r="H6">
-        <v>25.09</v>
+        <v>23.49</v>
       </c>
       <c r="I6">
-        <v>-3.03</v>
+        <v>-5.34</v>
       </c>
       <c r="J6">
-        <v>-5.2</v>
+        <v>-5.25</v>
       </c>
       <c r="K6">
-        <v>3.29</v>
+        <v>1.86</v>
       </c>
       <c r="L6">
-        <v>-17.61</v>
+        <v>-18.58</v>
       </c>
       <c r="M6">
-        <v>18.71</v>
+        <v>18.89</v>
       </c>
       <c r="N6">
         <v>43</v>
       </c>
       <c r="O6">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="P6">
-        <v>11180</v>
+        <v>11058.2</v>
       </c>
       <c r="Q6">
-        <v>11157.45</v>
+        <v>11130.45</v>
       </c>
       <c r="R6">
-        <v>11157.52</v>
+        <v>11165.56</v>
       </c>
       <c r="S6">
-        <v>10681.88</v>
+        <v>10680.57</v>
       </c>
       <c r="T6">
-        <v>2.42</v>
+        <v>1.12</v>
       </c>
       <c r="U6" t="s">
         <v>46</v>
@@ -1443,34 +1414,34 @@
         <v>2</v>
       </c>
       <c r="Y6">
-        <v>44.89</v>
+        <v>42.13</v>
       </c>
       <c r="Z6">
-        <v>-24.76</v>
+        <v>-49.53</v>
       </c>
       <c r="AA6">
-        <v>-9.140000000000001</v>
+        <v>-17.21</v>
       </c>
       <c r="AB6">
-        <v>-15.62</v>
+        <v>-32.31</v>
       </c>
       <c r="AC6">
-        <v>41.37</v>
+        <v>8.550000000000001</v>
       </c>
       <c r="AD6">
-        <v>59.81</v>
+        <v>34.7</v>
       </c>
       <c r="AE6">
-        <v>258.62</v>
+        <v>250.79</v>
       </c>
       <c r="AF6">
-        <v>-4.66</v>
+        <v>-28.52</v>
       </c>
       <c r="AG6">
-        <v>11549.58</v>
+        <v>11543.46</v>
       </c>
       <c r="AH6">
-        <v>10765.32</v>
+        <v>10717.44</v>
       </c>
       <c r="AI6">
         <v>10787.84</v>
@@ -1479,7 +1450,7 @@
         <v>48</v>
       </c>
       <c r="AK6">
-        <v>21.06</v>
+        <v>22.83</v>
       </c>
     </row>
     <row r="7" spans="1:37">
@@ -1490,10 +1461,10 @@
         <v>44</v>
       </c>
       <c r="C7">
-        <v>996.9</v>
+        <v>985</v>
       </c>
       <c r="D7">
-        <v>1.52</v>
+        <v>-1.19</v>
       </c>
       <c r="E7">
         <v>1158.8</v>
@@ -1502,46 +1473,46 @@
         <v>801.55</v>
       </c>
       <c r="G7">
-        <v>-13.97</v>
+        <v>-15</v>
       </c>
       <c r="H7">
-        <v>24.37</v>
+        <v>22.89</v>
       </c>
       <c r="I7">
-        <v>-4.17</v>
+        <v>-3.55</v>
       </c>
       <c r="J7">
-        <v>-8.119999999999999</v>
+        <v>-9.050000000000001</v>
       </c>
       <c r="K7">
-        <v>1.51</v>
+        <v>-1.97</v>
       </c>
       <c r="L7">
-        <v>-0.95</v>
+        <v>-3.95</v>
       </c>
       <c r="M7">
-        <v>5.45</v>
+        <v>5.88</v>
       </c>
       <c r="N7">
         <v>57</v>
       </c>
       <c r="O7">
-        <v>56</v>
+        <v>53</v>
       </c>
       <c r="P7">
-        <v>1010.44</v>
+        <v>1003.18</v>
       </c>
       <c r="Q7">
-        <v>1035.53</v>
+        <v>1030.78</v>
       </c>
       <c r="R7">
-        <v>1065.92</v>
+        <v>1064.49</v>
       </c>
       <c r="S7">
-        <v>977.24</v>
+        <v>977.08</v>
       </c>
       <c r="T7">
-        <v>2.01</v>
+        <v>0.8100000000000001</v>
       </c>
       <c r="U7" t="s">
         <v>46</v>
@@ -1556,43 +1527,43 @@
         <v>2</v>
       </c>
       <c r="Y7">
-        <v>40.29</v>
+        <v>38.18</v>
       </c>
       <c r="Z7">
-        <v>-17.26</v>
+        <v>-18.84</v>
       </c>
       <c r="AA7">
-        <v>-13.53</v>
+        <v>-14.59</v>
       </c>
       <c r="AB7">
-        <v>-3.73</v>
+        <v>-4.25</v>
       </c>
       <c r="AC7">
-        <v>60.21</v>
+        <v>40.2</v>
       </c>
       <c r="AD7">
-        <v>62.26</v>
+        <v>52.61</v>
       </c>
       <c r="AE7">
-        <v>25.03</v>
+        <v>24.88</v>
       </c>
       <c r="AF7">
-        <v>-6.76</v>
+        <v>29.1</v>
       </c>
       <c r="AG7">
-        <v>1086.5</v>
+        <v>1082.03</v>
       </c>
       <c r="AH7">
-        <v>984.55</v>
+        <v>979.53</v>
       </c>
       <c r="AI7">
-        <v>1063.8</v>
+        <v>1057.8</v>
       </c>
       <c r="AJ7" t="s">
         <v>47</v>
       </c>
       <c r="AK7">
-        <v>38.35</v>
+        <v>40.33</v>
       </c>
     </row>
     <row r="8" spans="1:37">
@@ -1603,13 +1574,13 @@
         <v>44</v>
       </c>
       <c r="C8">
-        <v>167.05</v>
+        <v>171.03</v>
       </c>
       <c r="D8">
-        <v>7.59</v>
+        <v>2.38</v>
       </c>
       <c r="E8">
-        <v>167.05</v>
+        <v>171.03</v>
       </c>
       <c r="F8">
         <v>115.96</v>
@@ -1618,43 +1589,43 @@
         <v>0</v>
       </c>
       <c r="H8">
-        <v>44.06</v>
+        <v>47.49</v>
       </c>
       <c r="I8">
-        <v>23.94</v>
+        <v>25.73</v>
       </c>
       <c r="J8">
-        <v>21.91</v>
+        <v>25.52</v>
       </c>
       <c r="K8">
-        <v>27.41</v>
+        <v>29.41</v>
       </c>
       <c r="L8">
-        <v>23.27</v>
+        <v>22.87</v>
       </c>
       <c r="M8">
-        <v>5.58</v>
+        <v>6.27</v>
       </c>
       <c r="N8">
         <v>85</v>
       </c>
       <c r="O8">
-        <v>84</v>
+        <v>87</v>
       </c>
       <c r="P8">
-        <v>151.37</v>
+        <v>158.37</v>
       </c>
       <c r="Q8">
-        <v>140.25</v>
+        <v>141.93</v>
       </c>
       <c r="R8">
-        <v>139.69</v>
+        <v>140.2</v>
       </c>
       <c r="S8">
-        <v>134.29</v>
+        <v>134.49</v>
       </c>
       <c r="T8">
-        <v>24.4</v>
+        <v>27.17</v>
       </c>
       <c r="U8" t="s">
         <v>45</v>
@@ -1669,43 +1640,43 @@
         <v>3</v>
       </c>
       <c r="Y8">
-        <v>78.91</v>
+        <v>80.66</v>
       </c>
       <c r="Z8">
-        <v>4.43</v>
+        <v>6.08</v>
       </c>
       <c r="AA8">
-        <v>1.38</v>
+        <v>2.32</v>
       </c>
       <c r="AB8">
-        <v>3.05</v>
+        <v>3.76</v>
       </c>
       <c r="AC8">
         <v>96.22</v>
       </c>
       <c r="AD8">
-        <v>87.02</v>
+        <v>94.37</v>
       </c>
       <c r="AE8">
-        <v>6.26</v>
+        <v>6.3</v>
       </c>
       <c r="AF8">
-        <v>340.67</v>
+        <v>431.13</v>
       </c>
       <c r="AG8">
-        <v>158.29</v>
+        <v>164.54</v>
       </c>
       <c r="AH8">
-        <v>122.2</v>
+        <v>119.32</v>
       </c>
       <c r="AI8">
-        <v>141.22</v>
+        <v>151.8</v>
       </c>
       <c r="AJ8" t="s">
         <v>48</v>
       </c>
       <c r="AK8">
-        <v>39.82</v>
+        <v>45.19</v>
       </c>
     </row>
   </sheetData>
@@ -1846,7 +1817,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:F67"/>
+  <dimension ref="A1:F61"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="16.7109375" customWidth="1"/>
@@ -1866,1120 +1837,974 @@
     </row>
     <row r="2" spans="1:6">
       <c r="A2" s="3" t="s">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="5" spans="1:6">
+      <c r="A5" s="2" t="s">
+        <v>51</v>
+      </c>
+      <c r="B5" s="2"/>
+      <c r="C5" s="2"/>
+      <c r="D5" s="2"/>
+      <c r="E5" s="2"/>
+    </row>
+    <row r="6" spans="1:6">
+      <c r="A6" s="4" t="s">
         <v>0</v>
       </c>
-      <c r="B2" s="3" t="s">
-        <v>50</v>
-      </c>
-      <c r="C2" s="3" t="s">
-        <v>51</v>
-      </c>
-      <c r="D2" s="3" t="s">
+      <c r="B6" s="4" t="s">
         <v>52</v>
       </c>
-      <c r="E2" s="3" t="s">
+      <c r="C6" s="4" t="s">
         <v>53</v>
       </c>
-      <c r="F2" s="3" t="s">
+      <c r="D6" s="4" t="s">
         <v>54</v>
       </c>
-    </row>
-    <row r="3" spans="1:6">
-      <c r="A3" s="4" t="s">
-        <v>43</v>
-      </c>
-      <c r="B3" s="4" t="s">
-        <v>22</v>
-      </c>
-      <c r="C3" s="4" t="s">
+      <c r="E6" s="4" t="s">
         <v>55</v>
       </c>
-      <c r="D3" s="4" t="s">
-        <v>56</v>
-      </c>
-      <c r="E3" s="4" t="s">
-        <v>46</v>
-      </c>
-      <c r="F3" s="4" t="s">
-        <v>45</v>
-      </c>
-    </row>
-    <row r="4" spans="1:6">
-      <c r="A4" s="4" t="s">
-        <v>43</v>
-      </c>
-      <c r="B4" s="4" t="s">
-        <v>57</v>
-      </c>
-      <c r="C4" s="4" t="s">
-        <v>55</v>
-      </c>
-      <c r="D4" s="4" t="s">
-        <v>56</v>
-      </c>
-      <c r="E4" s="4" t="s">
-        <v>46</v>
-      </c>
-      <c r="F4" s="4" t="s">
-        <v>45</v>
-      </c>
-    </row>
-    <row r="5" spans="1:6">
-      <c r="A5" s="5" t="s">
-        <v>41</v>
-      </c>
-      <c r="B5" s="5" t="s">
-        <v>22</v>
-      </c>
-      <c r="C5" s="5" t="s">
-        <v>58</v>
-      </c>
-      <c r="D5" s="5" t="s">
-        <v>59</v>
-      </c>
-      <c r="E5" s="5" t="s">
-        <v>45</v>
-      </c>
-      <c r="F5" s="5" t="s">
-        <v>46</v>
-      </c>
-    </row>
-    <row r="6" spans="1:6">
-      <c r="A6" s="5" t="s">
-        <v>41</v>
-      </c>
-      <c r="B6" s="5" t="s">
-        <v>57</v>
-      </c>
-      <c r="C6" s="5" t="s">
-        <v>58</v>
-      </c>
-      <c r="D6" s="5" t="s">
-        <v>59</v>
-      </c>
-      <c r="E6" s="5" t="s">
-        <v>45</v>
-      </c>
-      <c r="F6" s="5" t="s">
-        <v>46</v>
+    </row>
+    <row r="7" spans="1:6">
+      <c r="A7" s="3" t="s">
+        <v>37</v>
+      </c>
+      <c r="B7" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="C7" s="5">
+        <v>-3.78</v>
+      </c>
+      <c r="D7" s="5">
+        <v>-5.94</v>
+      </c>
+      <c r="E7" s="6">
+        <v>-2.16</v>
       </c>
     </row>
     <row r="8" spans="1:6">
-      <c r="A8" s="2" t="s">
-        <v>60</v>
-      </c>
-      <c r="B8" s="2"/>
-      <c r="C8" s="2"/>
-      <c r="D8" s="2"/>
-      <c r="E8" s="2"/>
+      <c r="A8" s="3" t="s">
+        <v>38</v>
+      </c>
+      <c r="B8" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="C8" s="5">
+        <v>7.77</v>
+      </c>
+      <c r="D8" s="5">
+        <v>6.54</v>
+      </c>
+      <c r="E8" s="6">
+        <v>-1.23</v>
+      </c>
     </row>
     <row r="9" spans="1:6">
       <c r="A9" s="3" t="s">
-        <v>0</v>
+        <v>39</v>
       </c>
       <c r="B9" s="3" t="s">
-        <v>61</v>
-      </c>
-      <c r="C9" s="3" t="s">
-        <v>62</v>
-      </c>
-      <c r="D9" s="3" t="s">
-        <v>63</v>
-      </c>
-      <c r="E9" s="3" t="s">
-        <v>64</v>
+        <v>9</v>
+      </c>
+      <c r="C9" s="5">
+        <v>-6.36</v>
+      </c>
+      <c r="D9" s="5">
+        <v>-6.02</v>
+      </c>
+      <c r="E9" s="7">
+        <v>0.34</v>
       </c>
     </row>
     <row r="10" spans="1:6">
-      <c r="A10" s="6" t="s">
+      <c r="A10" s="3" t="s">
+        <v>40</v>
+      </c>
+      <c r="B10" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="C10" s="5">
+        <v>-11.89</v>
+      </c>
+      <c r="D10" s="5">
+        <v>-12.88</v>
+      </c>
+      <c r="E10" s="6">
+        <v>-0.99</v>
+      </c>
+    </row>
+    <row r="11" spans="1:6">
+      <c r="A11" s="3" t="s">
+        <v>41</v>
+      </c>
+      <c r="B11" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="C11" s="5">
+        <v>-5.2</v>
+      </c>
+      <c r="D11" s="5">
+        <v>-5.25</v>
+      </c>
+      <c r="E11" s="6">
+        <v>-0.05</v>
+      </c>
+    </row>
+    <row r="12" spans="1:6">
+      <c r="A12" s="3" t="s">
+        <v>42</v>
+      </c>
+      <c r="B12" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="C12" s="5">
+        <v>-8.119999999999999</v>
+      </c>
+      <c r="D12" s="5">
+        <v>-9.050000000000001</v>
+      </c>
+      <c r="E12" s="6">
+        <v>-0.93</v>
+      </c>
+    </row>
+    <row r="13" spans="1:6">
+      <c r="A13" s="3" t="s">
+        <v>43</v>
+      </c>
+      <c r="B13" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="C13" s="5">
+        <v>21.91</v>
+      </c>
+      <c r="D13" s="5">
+        <v>25.52</v>
+      </c>
+      <c r="E13" s="7">
+        <v>3.61</v>
+      </c>
+    </row>
+    <row r="14" spans="1:6">
+      <c r="A14" s="3" t="s">
         <v>37</v>
       </c>
-      <c r="B10" s="6" t="s">
-        <v>9</v>
-      </c>
-      <c r="C10" s="7">
-        <v>-6.03</v>
-      </c>
-      <c r="D10" s="7">
-        <v>-3.78</v>
-      </c>
-      <c r="E10" s="8">
-        <v>2.25</v>
-      </c>
-    </row>
-    <row r="11" spans="1:6">
-      <c r="A11" s="6" t="s">
+      <c r="B14" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="C14" s="5">
+        <v>-1.17</v>
+      </c>
+      <c r="D14" s="5">
+        <v>-3.8</v>
+      </c>
+      <c r="E14" s="6">
+        <v>-2.63</v>
+      </c>
+    </row>
+    <row r="15" spans="1:6">
+      <c r="A15" s="3" t="s">
         <v>38</v>
       </c>
-      <c r="B11" s="6" t="s">
-        <v>9</v>
-      </c>
-      <c r="C11" s="7">
-        <v>10.25</v>
-      </c>
-      <c r="D11" s="7">
-        <v>7.77</v>
-      </c>
-      <c r="E11" s="9">
-        <v>-2.48</v>
-      </c>
-    </row>
-    <row r="12" spans="1:6">
-      <c r="A12" s="6" t="s">
+      <c r="B15" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="C15" s="5">
+        <v>-2.47</v>
+      </c>
+      <c r="D15" s="5">
+        <v>-6.84</v>
+      </c>
+      <c r="E15" s="6">
+        <v>-4.37</v>
+      </c>
+    </row>
+    <row r="16" spans="1:6">
+      <c r="A16" s="3" t="s">
         <v>39</v>
       </c>
-      <c r="B12" s="6" t="s">
-        <v>9</v>
-      </c>
-      <c r="C12" s="7">
-        <v>-3.86</v>
-      </c>
-      <c r="D12" s="7">
-        <v>-6.36</v>
-      </c>
-      <c r="E12" s="9">
-        <v>-2.5</v>
-      </c>
-    </row>
-    <row r="13" spans="1:6">
-      <c r="A13" s="6" t="s">
+      <c r="B16" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="C16" s="5">
+        <v>-1.27</v>
+      </c>
+      <c r="D16" s="5">
+        <v>-3.48</v>
+      </c>
+      <c r="E16" s="6">
+        <v>-2.21</v>
+      </c>
+    </row>
+    <row r="17" spans="1:5">
+      <c r="A17" s="3" t="s">
         <v>40</v>
       </c>
-      <c r="B13" s="6" t="s">
-        <v>9</v>
-      </c>
-      <c r="C13" s="7">
-        <v>-12.06</v>
-      </c>
-      <c r="D13" s="7">
-        <v>-11.89</v>
-      </c>
-      <c r="E13" s="8">
-        <v>0.17</v>
-      </c>
-    </row>
-    <row r="14" spans="1:6">
-      <c r="A14" s="6" t="s">
+      <c r="B17" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="C17" s="5">
+        <v>-4.4</v>
+      </c>
+      <c r="D17" s="5">
+        <v>-5.29</v>
+      </c>
+      <c r="E17" s="6">
+        <v>-0.89</v>
+      </c>
+    </row>
+    <row r="18" spans="1:5">
+      <c r="A18" s="3" t="s">
         <v>41</v>
       </c>
-      <c r="B14" s="6" t="s">
-        <v>9</v>
-      </c>
-      <c r="C14" s="7">
-        <v>-3.3</v>
-      </c>
-      <c r="D14" s="7">
-        <v>-5.2</v>
-      </c>
-      <c r="E14" s="9">
-        <v>-1.9</v>
-      </c>
-    </row>
-    <row r="15" spans="1:6">
-      <c r="A15" s="6" t="s">
+      <c r="B18" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="C18" s="5">
+        <v>-3.03</v>
+      </c>
+      <c r="D18" s="5">
+        <v>-5.34</v>
+      </c>
+      <c r="E18" s="6">
+        <v>-2.31</v>
+      </c>
+    </row>
+    <row r="19" spans="1:5">
+      <c r="A19" s="3" t="s">
         <v>42</v>
       </c>
-      <c r="B15" s="6" t="s">
-        <v>9</v>
-      </c>
-      <c r="C15" s="7">
-        <v>-9.69</v>
-      </c>
-      <c r="D15" s="7">
-        <v>-8.119999999999999</v>
-      </c>
-      <c r="E15" s="8">
-        <v>1.57</v>
-      </c>
-    </row>
-    <row r="16" spans="1:6">
-      <c r="A16" s="6" t="s">
+      <c r="B19" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="C19" s="5">
+        <v>-4.17</v>
+      </c>
+      <c r="D19" s="5">
+        <v>-3.55</v>
+      </c>
+      <c r="E19" s="7">
+        <v>0.62</v>
+      </c>
+    </row>
+    <row r="20" spans="1:5">
+      <c r="A20" s="3" t="s">
         <v>43</v>
       </c>
-      <c r="B16" s="6" t="s">
-        <v>9</v>
-      </c>
-      <c r="C16" s="7">
-        <v>14.91</v>
-      </c>
-      <c r="D16" s="7">
-        <v>21.91</v>
-      </c>
-      <c r="E16" s="8">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="17" spans="1:5">
-      <c r="A17" s="6" t="s">
+      <c r="B20" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="C20" s="5">
+        <v>23.94</v>
+      </c>
+      <c r="D20" s="5">
+        <v>25.73</v>
+      </c>
+      <c r="E20" s="7">
+        <v>1.79</v>
+      </c>
+    </row>
+    <row r="21" spans="1:5">
+      <c r="A21" s="3" t="s">
         <v>37</v>
       </c>
-      <c r="B17" s="6" t="s">
-        <v>8</v>
-      </c>
-      <c r="C17" s="7">
-        <v>-2.54</v>
-      </c>
-      <c r="D17" s="7">
-        <v>-1.17</v>
-      </c>
-      <c r="E17" s="8">
-        <v>1.37</v>
-      </c>
-    </row>
-    <row r="18" spans="1:5">
-      <c r="A18" s="6" t="s">
+      <c r="B21" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="C21" s="5">
+        <v>26.34</v>
+      </c>
+      <c r="D21" s="5">
+        <v>24.43</v>
+      </c>
+      <c r="E21" s="6">
+        <v>-1.91</v>
+      </c>
+    </row>
+    <row r="22" spans="1:5">
+      <c r="A22" s="3" t="s">
         <v>38</v>
       </c>
-      <c r="B18" s="6" t="s">
-        <v>8</v>
-      </c>
-      <c r="C18" s="7">
-        <v>-0.15</v>
-      </c>
-      <c r="D18" s="7">
-        <v>-2.47</v>
-      </c>
-      <c r="E18" s="9">
-        <v>-2.32</v>
-      </c>
-    </row>
-    <row r="19" spans="1:5">
-      <c r="A19" s="6" t="s">
+      <c r="B22" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="C22" s="5">
+        <v>93.87</v>
+      </c>
+      <c r="D22" s="5">
+        <v>89.12</v>
+      </c>
+      <c r="E22" s="6">
+        <v>-4.75</v>
+      </c>
+    </row>
+    <row r="23" spans="1:5">
+      <c r="A23" s="3" t="s">
         <v>39</v>
       </c>
-      <c r="B19" s="6" t="s">
-        <v>8</v>
-      </c>
-      <c r="C19" s="7">
-        <v>-1.18</v>
-      </c>
-      <c r="D19" s="7">
-        <v>-1.27</v>
-      </c>
-      <c r="E19" s="9">
-        <v>-0.09</v>
-      </c>
-    </row>
-    <row r="20" spans="1:5">
-      <c r="A20" s="6" t="s">
+      <c r="B23" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="C23" s="5">
+        <v>-45.34</v>
+      </c>
+      <c r="D23" s="5">
+        <v>-45.48</v>
+      </c>
+      <c r="E23" s="6">
+        <v>-0.14</v>
+      </c>
+    </row>
+    <row r="24" spans="1:5">
+      <c r="A24" s="3" t="s">
         <v>40</v>
       </c>
-      <c r="B20" s="6" t="s">
-        <v>8</v>
-      </c>
-      <c r="C20" s="7">
-        <v>-5.21</v>
-      </c>
-      <c r="D20" s="7">
-        <v>-4.4</v>
-      </c>
-      <c r="E20" s="8">
-        <v>0.8100000000000001</v>
-      </c>
-    </row>
-    <row r="21" spans="1:5">
-      <c r="A21" s="6" t="s">
+      <c r="B24" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="C24" s="5">
+        <v>-14.42</v>
+      </c>
+      <c r="D24" s="5">
+        <v>-15.95</v>
+      </c>
+      <c r="E24" s="6">
+        <v>-1.53</v>
+      </c>
+    </row>
+    <row r="25" spans="1:5">
+      <c r="A25" s="3" t="s">
         <v>41</v>
       </c>
-      <c r="B21" s="6" t="s">
-        <v>8</v>
-      </c>
-      <c r="C21" s="7">
-        <v>-0.84</v>
-      </c>
-      <c r="D21" s="7">
-        <v>-3.03</v>
-      </c>
-      <c r="E21" s="9">
-        <v>-2.19</v>
-      </c>
-    </row>
-    <row r="22" spans="1:5">
-      <c r="A22" s="6" t="s">
+      <c r="B25" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="C25" s="5">
+        <v>-17.61</v>
+      </c>
+      <c r="D25" s="5">
+        <v>-18.58</v>
+      </c>
+      <c r="E25" s="6">
+        <v>-0.97</v>
+      </c>
+    </row>
+    <row r="26" spans="1:5">
+      <c r="A26" s="3" t="s">
         <v>42</v>
       </c>
-      <c r="B22" s="6" t="s">
-        <v>8</v>
-      </c>
-      <c r="C22" s="7">
-        <v>-3.25</v>
-      </c>
-      <c r="D22" s="7">
-        <v>-4.17</v>
-      </c>
-      <c r="E22" s="9">
-        <v>-0.92</v>
-      </c>
-    </row>
-    <row r="23" spans="1:5">
-      <c r="A23" s="6" t="s">
+      <c r="B26" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="C26" s="5">
+        <v>-0.95</v>
+      </c>
+      <c r="D26" s="5">
+        <v>-3.95</v>
+      </c>
+      <c r="E26" s="6">
+        <v>-3</v>
+      </c>
+    </row>
+    <row r="27" spans="1:5">
+      <c r="A27" s="3" t="s">
         <v>43</v>
       </c>
-      <c r="B23" s="6" t="s">
-        <v>8</v>
-      </c>
-      <c r="C23" s="7">
-        <v>15.69</v>
-      </c>
-      <c r="D23" s="7">
-        <v>23.94</v>
-      </c>
-      <c r="E23" s="8">
-        <v>8.25</v>
-      </c>
-    </row>
-    <row r="24" spans="1:5">
-      <c r="A24" s="6" t="s">
+      <c r="B27" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="C27" s="5">
+        <v>23.27</v>
+      </c>
+      <c r="D27" s="5">
+        <v>22.87</v>
+      </c>
+      <c r="E27" s="6">
+        <v>-0.4</v>
+      </c>
+    </row>
+    <row r="28" spans="1:5">
+      <c r="A28" s="3" t="s">
         <v>37</v>
       </c>
-      <c r="B24" s="6" t="s">
-        <v>11</v>
-      </c>
-      <c r="C24" s="7">
-        <v>26.69</v>
-      </c>
-      <c r="D24" s="7">
-        <v>26.34</v>
-      </c>
-      <c r="E24" s="9">
-        <v>-0.35</v>
-      </c>
-    </row>
-    <row r="25" spans="1:5">
-      <c r="A25" s="6" t="s">
+      <c r="B28" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="C28" s="5">
+        <v>17.14</v>
+      </c>
+      <c r="D28" s="5">
+        <v>13.46</v>
+      </c>
+      <c r="E28" s="6">
+        <v>-3.68</v>
+      </c>
+    </row>
+    <row r="29" spans="1:5">
+      <c r="A29" s="3" t="s">
         <v>38</v>
       </c>
-      <c r="B25" s="6" t="s">
-        <v>11</v>
-      </c>
-      <c r="C25" s="7">
-        <v>96.37</v>
-      </c>
-      <c r="D25" s="7">
-        <v>93.87</v>
-      </c>
-      <c r="E25" s="9">
-        <v>-2.5</v>
-      </c>
-    </row>
-    <row r="26" spans="1:5">
-      <c r="A26" s="6" t="s">
+      <c r="B29" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="C29" s="5">
+        <v>-16.35</v>
+      </c>
+      <c r="D29" s="5">
+        <v>-19.86</v>
+      </c>
+      <c r="E29" s="6">
+        <v>-3.51</v>
+      </c>
+    </row>
+    <row r="30" spans="1:5">
+      <c r="A30" s="3" t="s">
         <v>39</v>
       </c>
-      <c r="B26" s="6" t="s">
-        <v>11</v>
-      </c>
-      <c r="C26" s="7">
-        <v>-45.49</v>
-      </c>
-      <c r="D26" s="7">
-        <v>-45.34</v>
-      </c>
-      <c r="E26" s="8">
-        <v>0.15</v>
-      </c>
-    </row>
-    <row r="27" spans="1:5">
-      <c r="A27" s="6" t="s">
+      <c r="B30" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="C30" s="5">
+        <v>0.58</v>
+      </c>
+      <c r="D30" s="5">
+        <v>-1.52</v>
+      </c>
+      <c r="E30" s="6">
+        <v>-2.1</v>
+      </c>
+    </row>
+    <row r="31" spans="1:5">
+      <c r="A31" s="3" t="s">
         <v>40</v>
       </c>
-      <c r="B27" s="6" t="s">
-        <v>11</v>
-      </c>
-      <c r="C27" s="7">
-        <v>-14.75</v>
-      </c>
-      <c r="D27" s="7">
-        <v>-14.42</v>
-      </c>
-      <c r="E27" s="8">
-        <v>0.33</v>
-      </c>
-    </row>
-    <row r="28" spans="1:5">
-      <c r="A28" s="6" t="s">
+      <c r="B31" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="C31" s="5">
+        <v>0.67</v>
+      </c>
+      <c r="D31" s="5">
+        <v>-1.58</v>
+      </c>
+      <c r="E31" s="6">
+        <v>-2.25</v>
+      </c>
+    </row>
+    <row r="32" spans="1:5">
+      <c r="A32" s="3" t="s">
         <v>41</v>
       </c>
-      <c r="B28" s="6" t="s">
-        <v>11</v>
-      </c>
-      <c r="C28" s="7">
-        <v>-16.92</v>
-      </c>
-      <c r="D28" s="7">
-        <v>-17.61</v>
-      </c>
-      <c r="E28" s="9">
-        <v>-0.6899999999999999</v>
-      </c>
-    </row>
-    <row r="29" spans="1:5">
-      <c r="A29" s="6" t="s">
+      <c r="B32" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="C32" s="5">
+        <v>3.29</v>
+      </c>
+      <c r="D32" s="5">
+        <v>1.86</v>
+      </c>
+      <c r="E32" s="6">
+        <v>-1.43</v>
+      </c>
+    </row>
+    <row r="33" spans="1:5">
+      <c r="A33" s="3" t="s">
         <v>42</v>
       </c>
-      <c r="B29" s="6" t="s">
-        <v>11</v>
-      </c>
-      <c r="C29" s="7">
-        <v>-1.05</v>
-      </c>
-      <c r="D29" s="7">
-        <v>-0.95</v>
-      </c>
-      <c r="E29" s="8">
-        <v>0.1</v>
-      </c>
-    </row>
-    <row r="30" spans="1:5">
-      <c r="A30" s="6" t="s">
+      <c r="B33" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="C33" s="5">
+        <v>1.51</v>
+      </c>
+      <c r="D33" s="5">
+        <v>-1.97</v>
+      </c>
+      <c r="E33" s="6">
+        <v>-3.48</v>
+      </c>
+    </row>
+    <row r="34" spans="1:5">
+      <c r="A34" s="3" t="s">
         <v>43</v>
       </c>
-      <c r="B30" s="6" t="s">
-        <v>11</v>
-      </c>
-      <c r="C30" s="7">
-        <v>12.97</v>
-      </c>
-      <c r="D30" s="7">
-        <v>23.27</v>
-      </c>
-      <c r="E30" s="8">
-        <v>10.3</v>
-      </c>
-    </row>
-    <row r="31" spans="1:5">
-      <c r="A31" s="6" t="s">
+      <c r="B34" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="C34" s="5">
+        <v>27.41</v>
+      </c>
+      <c r="D34" s="5">
+        <v>29.41</v>
+      </c>
+      <c r="E34" s="7">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="35" spans="1:5">
+      <c r="A35" s="3" t="s">
         <v>37</v>
       </c>
-      <c r="B31" s="6" t="s">
-        <v>10</v>
-      </c>
-      <c r="C31" s="7">
-        <v>13.87</v>
-      </c>
-      <c r="D31" s="7">
-        <v>17.14</v>
-      </c>
-      <c r="E31" s="8">
-        <v>3.27</v>
-      </c>
-    </row>
-    <row r="32" spans="1:5">
-      <c r="A32" s="6" t="s">
+      <c r="B35" s="3" t="s">
+        <v>6</v>
+      </c>
+      <c r="C35" s="5">
+        <v>-8.74</v>
+      </c>
+      <c r="D35" s="5">
+        <v>-10.82</v>
+      </c>
+      <c r="E35" s="6">
+        <v>-2.08</v>
+      </c>
+    </row>
+    <row r="36" spans="1:5">
+      <c r="A36" s="3" t="s">
         <v>38</v>
       </c>
-      <c r="B32" s="6" t="s">
-        <v>10</v>
-      </c>
-      <c r="C32" s="7">
-        <v>-13.27</v>
-      </c>
-      <c r="D32" s="7">
-        <v>-16.35</v>
-      </c>
-      <c r="E32" s="9">
-        <v>-3.08</v>
-      </c>
-    </row>
-    <row r="33" spans="1:5">
-      <c r="A33" s="6" t="s">
+      <c r="B36" s="3" t="s">
+        <v>6</v>
+      </c>
+      <c r="C36" s="5">
+        <v>-25.48</v>
+      </c>
+      <c r="D36" s="5">
+        <v>-28.38</v>
+      </c>
+      <c r="E36" s="6">
+        <v>-2.9</v>
+      </c>
+    </row>
+    <row r="37" spans="1:5">
+      <c r="A37" s="3" t="s">
         <v>39</v>
       </c>
-      <c r="B33" s="6" t="s">
-        <v>10</v>
-      </c>
-      <c r="C33" s="7">
-        <v>-0.28</v>
-      </c>
-      <c r="D33" s="7">
-        <v>0.58</v>
-      </c>
-      <c r="E33" s="8">
-        <v>0.86</v>
-      </c>
-    </row>
-    <row r="34" spans="1:5">
-      <c r="A34" s="6" t="s">
+      <c r="B37" s="3" t="s">
+        <v>6</v>
+      </c>
+      <c r="C37" s="5">
+        <v>-45.92</v>
+      </c>
+      <c r="D37" s="5">
+        <v>-46.65</v>
+      </c>
+      <c r="E37" s="6">
+        <v>-0.73</v>
+      </c>
+    </row>
+    <row r="38" spans="1:5">
+      <c r="A38" s="3" t="s">
         <v>40</v>
       </c>
-      <c r="B34" s="6" t="s">
-        <v>10</v>
-      </c>
-      <c r="C34" s="7">
-        <v>-0.13</v>
-      </c>
-      <c r="D34" s="7">
-        <v>0.67</v>
-      </c>
-      <c r="E34" s="8">
-        <v>0.8</v>
-      </c>
-    </row>
-    <row r="35" spans="1:5">
-      <c r="A35" s="6" t="s">
+      <c r="B38" s="3" t="s">
+        <v>6</v>
+      </c>
+      <c r="C38" s="5">
+        <v>-18.63</v>
+      </c>
+      <c r="D38" s="5">
+        <v>-19.51</v>
+      </c>
+      <c r="E38" s="6">
+        <v>-0.88</v>
+      </c>
+    </row>
+    <row r="39" spans="1:5">
+      <c r="A39" s="3" t="s">
         <v>41</v>
       </c>
-      <c r="B35" s="6" t="s">
-        <v>10</v>
-      </c>
-      <c r="C35" s="7">
-        <v>3</v>
-      </c>
-      <c r="D35" s="7">
-        <v>3.29</v>
-      </c>
-      <c r="E35" s="8">
-        <v>0.29</v>
-      </c>
-    </row>
-    <row r="36" spans="1:5">
-      <c r="A36" s="6" t="s">
+      <c r="B39" s="3" t="s">
+        <v>6</v>
+      </c>
+      <c r="C39" s="5">
+        <v>-17.53</v>
+      </c>
+      <c r="D39" s="5">
+        <v>-18.2</v>
+      </c>
+      <c r="E39" s="6">
+        <v>-0.67</v>
+      </c>
+    </row>
+    <row r="40" spans="1:5">
+      <c r="A40" s="3" t="s">
         <v>42</v>
       </c>
-      <c r="B36" s="6" t="s">
-        <v>10</v>
-      </c>
-      <c r="C36" s="7">
-        <v>0.16</v>
-      </c>
-      <c r="D36" s="7">
-        <v>1.51</v>
-      </c>
-      <c r="E36" s="8">
-        <v>1.35</v>
-      </c>
-    </row>
-    <row r="37" spans="1:5">
-      <c r="A37" s="6" t="s">
+      <c r="B40" s="3" t="s">
+        <v>6</v>
+      </c>
+      <c r="C40" s="5">
+        <v>-13.97</v>
+      </c>
+      <c r="D40" s="5">
+        <v>-15</v>
+      </c>
+      <c r="E40" s="6">
+        <v>-1.03</v>
+      </c>
+    </row>
+    <row r="41" spans="1:5">
+      <c r="A41" s="3" t="s">
+        <v>37</v>
+      </c>
+      <c r="B41" s="3" t="s">
+        <v>2</v>
+      </c>
+      <c r="C41" s="5">
+        <v>11281</v>
+      </c>
+      <c r="D41" s="5">
+        <v>11024</v>
+      </c>
+      <c r="E41" s="6">
+        <v>-257</v>
+      </c>
+    </row>
+    <row r="42" spans="1:5">
+      <c r="A42" s="3" t="s">
+        <v>38</v>
+      </c>
+      <c r="B42" s="3" t="s">
+        <v>2</v>
+      </c>
+      <c r="C42" s="5">
+        <v>499.5</v>
+      </c>
+      <c r="D42" s="5">
+        <v>480.05</v>
+      </c>
+      <c r="E42" s="6">
+        <v>-19.45</v>
+      </c>
+    </row>
+    <row r="43" spans="1:5">
+      <c r="A43" s="3" t="s">
+        <v>39</v>
+      </c>
+      <c r="B43" s="3" t="s">
+        <v>2</v>
+      </c>
+      <c r="C43" s="5">
+        <v>318.95</v>
+      </c>
+      <c r="D43" s="5">
+        <v>314.65</v>
+      </c>
+      <c r="E43" s="6">
+        <v>-4.3</v>
+      </c>
+    </row>
+    <row r="44" spans="1:5">
+      <c r="A44" s="3" t="s">
+        <v>40</v>
+      </c>
+      <c r="B44" s="3" t="s">
+        <v>2</v>
+      </c>
+      <c r="C44" s="5">
+        <v>1771</v>
+      </c>
+      <c r="D44" s="5">
+        <v>1752</v>
+      </c>
+      <c r="E44" s="6">
+        <v>-19</v>
+      </c>
+    </row>
+    <row r="45" spans="1:5">
+      <c r="A45" s="3" t="s">
+        <v>41</v>
+      </c>
+      <c r="B45" s="3" t="s">
+        <v>2</v>
+      </c>
+      <c r="C45" s="5">
+        <v>10940</v>
+      </c>
+      <c r="D45" s="5">
+        <v>10800</v>
+      </c>
+      <c r="E45" s="6">
+        <v>-140</v>
+      </c>
+    </row>
+    <row r="46" spans="1:5">
+      <c r="A46" s="3" t="s">
+        <v>42</v>
+      </c>
+      <c r="B46" s="3" t="s">
+        <v>2</v>
+      </c>
+      <c r="C46" s="5">
+        <v>996.9</v>
+      </c>
+      <c r="D46" s="5">
+        <v>985</v>
+      </c>
+      <c r="E46" s="6">
+        <v>-11.9</v>
+      </c>
+    </row>
+    <row r="47" spans="1:5">
+      <c r="A47" s="3" t="s">
         <v>43</v>
       </c>
-      <c r="B37" s="6" t="s">
-        <v>10</v>
-      </c>
-      <c r="C37" s="7">
-        <v>16.68</v>
-      </c>
-      <c r="D37" s="7">
-        <v>27.41</v>
-      </c>
-      <c r="E37" s="8">
-        <v>10.73</v>
-      </c>
-    </row>
-    <row r="38" spans="1:5">
-      <c r="A38" s="6" t="s">
+      <c r="B47" s="3" t="s">
+        <v>2</v>
+      </c>
+      <c r="C47" s="5">
+        <v>167.05</v>
+      </c>
+      <c r="D47" s="5">
+        <v>171.03</v>
+      </c>
+      <c r="E47" s="7">
+        <v>3.98</v>
+      </c>
+    </row>
+    <row r="48" spans="1:5">
+      <c r="A48" s="3" t="s">
         <v>37</v>
       </c>
-      <c r="B38" s="6" t="s">
-        <v>6</v>
-      </c>
-      <c r="C38" s="7">
-        <v>-9.33</v>
-      </c>
-      <c r="D38" s="7">
-        <v>-8.74</v>
-      </c>
-      <c r="E38" s="8">
-        <v>0.59</v>
-      </c>
-    </row>
-    <row r="39" spans="1:5">
-      <c r="A39" s="6" t="s">
+      <c r="B48" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="C48" s="5">
+        <v>40.65</v>
+      </c>
+      <c r="D48" s="5">
+        <v>34.55</v>
+      </c>
+      <c r="E48" s="6">
+        <v>-6.1</v>
+      </c>
+    </row>
+    <row r="49" spans="1:5">
+      <c r="A49" s="3" t="s">
         <v>38</v>
       </c>
-      <c r="B39" s="6" t="s">
-        <v>6</v>
-      </c>
-      <c r="C39" s="7">
-        <v>-25.15</v>
-      </c>
-      <c r="D39" s="7">
-        <v>-25.48</v>
-      </c>
-      <c r="E39" s="9">
-        <v>-0.33</v>
-      </c>
-    </row>
-    <row r="40" spans="1:5">
-      <c r="A40" s="6" t="s">
+      <c r="B49" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="C49" s="5">
+        <v>46.31</v>
+      </c>
+      <c r="D49" s="5">
+        <v>39.09</v>
+      </c>
+      <c r="E49" s="6">
+        <v>-7.22</v>
+      </c>
+    </row>
+    <row r="50" spans="1:5">
+      <c r="A50" s="3" t="s">
         <v>39</v>
       </c>
-      <c r="B40" s="6" t="s">
-        <v>6</v>
-      </c>
-      <c r="C40" s="7">
-        <v>-45.49</v>
-      </c>
-      <c r="D40" s="7">
-        <v>-45.92</v>
-      </c>
-      <c r="E40" s="9">
-        <v>-0.43</v>
-      </c>
-    </row>
-    <row r="41" spans="1:5">
-      <c r="A41" s="6" t="s">
+      <c r="B50" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="C50" s="5">
+        <v>38.94</v>
+      </c>
+      <c r="D50" s="5">
+        <v>36.28</v>
+      </c>
+      <c r="E50" s="6">
+        <v>-2.66</v>
+      </c>
+    </row>
+    <row r="51" spans="1:5">
+      <c r="A51" s="3" t="s">
         <v>40</v>
       </c>
-      <c r="B41" s="6" t="s">
-        <v>6</v>
-      </c>
-      <c r="C41" s="7">
-        <v>-19.03</v>
-      </c>
-      <c r="D41" s="7">
-        <v>-18.63</v>
-      </c>
-      <c r="E41" s="8">
-        <v>0.4</v>
-      </c>
-    </row>
-    <row r="42" spans="1:5">
-      <c r="A42" s="6" t="s">
+      <c r="B51" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="C51" s="5">
+        <v>28.25</v>
+      </c>
+      <c r="D51" s="5">
+        <v>26.53</v>
+      </c>
+      <c r="E51" s="6">
+        <v>-1.72</v>
+      </c>
+    </row>
+    <row r="52" spans="1:5">
+      <c r="A52" s="3" t="s">
         <v>41</v>
       </c>
-      <c r="B42" s="6" t="s">
-        <v>6</v>
-      </c>
-      <c r="C42" s="7">
-        <v>-17.79</v>
-      </c>
-      <c r="D42" s="7">
-        <v>-17.53</v>
-      </c>
-      <c r="E42" s="8">
-        <v>0.26</v>
-      </c>
-    </row>
-    <row r="43" spans="1:5">
-      <c r="A43" s="6" t="s">
+      <c r="B52" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="C52" s="5">
+        <v>44.89</v>
+      </c>
+      <c r="D52" s="5">
+        <v>42.13</v>
+      </c>
+      <c r="E52" s="6">
+        <v>-2.76</v>
+      </c>
+    </row>
+    <row r="53" spans="1:5">
+      <c r="A53" s="3" t="s">
         <v>42</v>
       </c>
-      <c r="B43" s="6" t="s">
-        <v>6</v>
-      </c>
-      <c r="C43" s="7">
-        <v>-15.26</v>
-      </c>
-      <c r="D43" s="7">
-        <v>-13.97</v>
-      </c>
-      <c r="E43" s="8">
-        <v>1.29</v>
-      </c>
-    </row>
-    <row r="44" spans="1:5">
-      <c r="A44" s="6" t="s">
+      <c r="B53" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="C53" s="5">
+        <v>40.29</v>
+      </c>
+      <c r="D53" s="5">
+        <v>38.18</v>
+      </c>
+      <c r="E53" s="6">
+        <v>-2.11</v>
+      </c>
+    </row>
+    <row r="54" spans="1:5">
+      <c r="A54" s="3" t="s">
         <v>43</v>
       </c>
-      <c r="B44" s="6" t="s">
-        <v>6</v>
-      </c>
-      <c r="C44" s="7">
-        <v>-1.18</v>
-      </c>
-      <c r="D44" s="7">
-        <v>0</v>
-      </c>
-      <c r="E44" s="8">
-        <v>1.18</v>
-      </c>
-    </row>
-    <row r="45" spans="1:5">
-      <c r="A45" s="6" t="s">
+      <c r="B54" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="C54" s="5">
+        <v>78.91</v>
+      </c>
+      <c r="D54" s="5">
+        <v>80.66</v>
+      </c>
+      <c r="E54" s="7">
+        <v>1.75</v>
+      </c>
+    </row>
+    <row r="55" spans="1:5">
+      <c r="A55" s="3" t="s">
         <v>37</v>
       </c>
-      <c r="B45" s="6" t="s">
-        <v>2</v>
-      </c>
-      <c r="C45" s="7">
-        <v>11208</v>
-      </c>
-      <c r="D45" s="7">
-        <v>11281</v>
-      </c>
-      <c r="E45" s="8">
-        <v>73</v>
-      </c>
-    </row>
-    <row r="46" spans="1:5">
-      <c r="A46" s="6" t="s">
+      <c r="B55" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="C55" s="5">
+        <v>-43.61</v>
+      </c>
+      <c r="D55" s="5">
+        <v>13.03</v>
+      </c>
+      <c r="E55" s="7">
+        <v>56.64</v>
+      </c>
+    </row>
+    <row r="56" spans="1:5">
+      <c r="A56" s="3" t="s">
         <v>38</v>
       </c>
-      <c r="B46" s="6" t="s">
-        <v>2</v>
-      </c>
-      <c r="C46" s="7">
-        <v>501.7</v>
-      </c>
-      <c r="D46" s="7">
-        <v>499.5</v>
-      </c>
-      <c r="E46" s="9">
-        <v>-2.2</v>
-      </c>
-    </row>
-    <row r="47" spans="1:5">
-      <c r="A47" s="6" t="s">
+      <c r="B56" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="C56" s="5">
+        <v>-67.02</v>
+      </c>
+      <c r="D56" s="5">
+        <v>-54.79</v>
+      </c>
+      <c r="E56" s="7">
+        <v>12.23</v>
+      </c>
+    </row>
+    <row r="57" spans="1:5">
+      <c r="A57" s="3" t="s">
         <v>39</v>
       </c>
-      <c r="B47" s="6" t="s">
-        <v>2</v>
-      </c>
-      <c r="C47" s="7">
-        <v>321.45</v>
-      </c>
-      <c r="D47" s="7">
-        <v>318.95</v>
-      </c>
-      <c r="E47" s="9">
-        <v>-2.5</v>
-      </c>
-    </row>
-    <row r="48" spans="1:5">
-      <c r="A48" s="6" t="s">
+      <c r="B57" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="C57" s="5">
+        <v>-7.62</v>
+      </c>
+      <c r="D57" s="5">
+        <v>-12.03</v>
+      </c>
+      <c r="E57" s="6">
+        <v>-4.41</v>
+      </c>
+    </row>
+    <row r="58" spans="1:5">
+      <c r="A58" s="3" t="s">
         <v>40</v>
       </c>
-      <c r="B48" s="6" t="s">
-        <v>2</v>
-      </c>
-      <c r="C48" s="7">
-        <v>1762.3</v>
-      </c>
-      <c r="D48" s="7">
-        <v>1771</v>
-      </c>
-      <c r="E48" s="8">
-        <v>8.699999999999999</v>
-      </c>
-    </row>
-    <row r="49" spans="1:5">
-      <c r="A49" s="6" t="s">
+      <c r="B58" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="C58" s="5">
+        <v>126.8</v>
+      </c>
+      <c r="D58" s="5">
+        <v>-19.44</v>
+      </c>
+      <c r="E58" s="6">
+        <v>-146.24</v>
+      </c>
+    </row>
+    <row r="59" spans="1:5">
+      <c r="A59" s="3" t="s">
         <v>41</v>
       </c>
-      <c r="B49" s="6" t="s">
-        <v>2</v>
-      </c>
-      <c r="C49" s="7">
-        <v>10917</v>
-      </c>
-      <c r="D49" s="7">
-        <v>10940</v>
-      </c>
-      <c r="E49" s="8">
-        <v>23</v>
-      </c>
-    </row>
-    <row r="50" spans="1:5">
-      <c r="A50" s="6" t="s">
+      <c r="B59" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="C59" s="5">
+        <v>-4.66</v>
+      </c>
+      <c r="D59" s="5">
+        <v>-28.52</v>
+      </c>
+      <c r="E59" s="6">
+        <v>-23.86</v>
+      </c>
+    </row>
+    <row r="60" spans="1:5">
+      <c r="A60" s="3" t="s">
         <v>42</v>
       </c>
-      <c r="B50" s="6" t="s">
-        <v>2</v>
-      </c>
-      <c r="C50" s="7">
-        <v>982</v>
-      </c>
-      <c r="D50" s="7">
-        <v>996.9</v>
-      </c>
-      <c r="E50" s="8">
-        <v>14.9</v>
-      </c>
-    </row>
-    <row r="51" spans="1:5">
-      <c r="A51" s="6" t="s">
+      <c r="B60" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="C60" s="5">
+        <v>-6.76</v>
+      </c>
+      <c r="D60" s="5">
+        <v>29.1</v>
+      </c>
+      <c r="E60" s="7">
+        <v>35.86</v>
+      </c>
+    </row>
+    <row r="61" spans="1:5">
+      <c r="A61" s="3" t="s">
         <v>43</v>
       </c>
-      <c r="B51" s="6" t="s">
-        <v>2</v>
-      </c>
-      <c r="C51" s="7">
-        <v>155.26</v>
-      </c>
-      <c r="D51" s="7">
-        <v>167.05</v>
-      </c>
-      <c r="E51" s="8">
-        <v>11.79</v>
-      </c>
-    </row>
-    <row r="52" spans="1:5">
-      <c r="A52" s="6" t="s">
-        <v>37</v>
-      </c>
-      <c r="B52" s="6" t="s">
-        <v>13</v>
-      </c>
-      <c r="C52" s="7">
-        <v>85</v>
-      </c>
-      <c r="D52" s="7">
-        <v>71</v>
-      </c>
-      <c r="E52" s="9">
-        <v>-14</v>
-      </c>
-    </row>
-    <row r="53" spans="1:5">
-      <c r="A53" s="6" t="s">
-        <v>43</v>
-      </c>
-      <c r="B53" s="6" t="s">
-        <v>13</v>
-      </c>
-      <c r="C53" s="7">
-        <v>71</v>
-      </c>
-      <c r="D53" s="7">
-        <v>85</v>
-      </c>
-      <c r="E53" s="8">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="54" spans="1:5">
-      <c r="A54" s="6" t="s">
-        <v>37</v>
-      </c>
-      <c r="B54" s="6" t="s">
-        <v>24</v>
-      </c>
-      <c r="C54" s="7">
-        <v>37.75</v>
-      </c>
-      <c r="D54" s="7">
-        <v>40.65</v>
-      </c>
-      <c r="E54" s="8">
-        <v>2.9</v>
-      </c>
-    </row>
-    <row r="55" spans="1:5">
-      <c r="A55" s="6" t="s">
-        <v>38</v>
-      </c>
-      <c r="B55" s="6" t="s">
-        <v>24</v>
-      </c>
-      <c r="C55" s="7">
-        <v>47.22</v>
-      </c>
-      <c r="D55" s="7">
-        <v>46.31</v>
-      </c>
-      <c r="E55" s="9">
-        <v>-0.91</v>
-      </c>
-    </row>
-    <row r="56" spans="1:5">
-      <c r="A56" s="6" t="s">
-        <v>39</v>
-      </c>
-      <c r="B56" s="6" t="s">
-        <v>24</v>
-      </c>
-      <c r="C56" s="7">
-        <v>40.53</v>
-      </c>
-      <c r="D56" s="7">
-        <v>38.94</v>
-      </c>
-      <c r="E56" s="9">
-        <v>-1.59</v>
-      </c>
-    </row>
-    <row r="57" spans="1:5">
-      <c r="A57" s="6" t="s">
-        <v>40</v>
-      </c>
-      <c r="B57" s="6" t="s">
-        <v>24</v>
-      </c>
-      <c r="C57" s="7">
-        <v>26.21</v>
-      </c>
-      <c r="D57" s="7">
-        <v>28.25</v>
-      </c>
-      <c r="E57" s="8">
-        <v>2.04</v>
-      </c>
-    </row>
-    <row r="58" spans="1:5">
-      <c r="A58" s="6" t="s">
-        <v>41</v>
-      </c>
-      <c r="B58" s="6" t="s">
-        <v>24</v>
-      </c>
-      <c r="C58" s="7">
-        <v>44.34</v>
-      </c>
-      <c r="D58" s="7">
-        <v>44.89</v>
-      </c>
-      <c r="E58" s="8">
-        <v>0.55</v>
-      </c>
-    </row>
-    <row r="59" spans="1:5">
-      <c r="A59" s="6" t="s">
-        <v>42</v>
-      </c>
-      <c r="B59" s="6" t="s">
-        <v>24</v>
-      </c>
-      <c r="C59" s="7">
-        <v>36.19</v>
-      </c>
-      <c r="D59" s="7">
-        <v>40.29</v>
-      </c>
-      <c r="E59" s="8">
-        <v>4.1</v>
-      </c>
-    </row>
-    <row r="60" spans="1:5">
-      <c r="A60" s="6" t="s">
-        <v>43</v>
-      </c>
-      <c r="B60" s="6" t="s">
-        <v>24</v>
-      </c>
-      <c r="C60" s="7">
-        <v>71.89</v>
-      </c>
-      <c r="D60" s="7">
-        <v>78.91</v>
-      </c>
-      <c r="E60" s="8">
-        <v>7.02</v>
-      </c>
-    </row>
-    <row r="61" spans="1:5">
-      <c r="A61" s="6" t="s">
-        <v>37</v>
-      </c>
-      <c r="B61" s="6" t="s">
+      <c r="B61" s="3" t="s">
         <v>31</v>
       </c>
-      <c r="C61" s="7">
-        <v>-51.06</v>
-      </c>
-      <c r="D61" s="7">
-        <v>-43.61</v>
-      </c>
-      <c r="E61" s="8">
-        <v>7.45</v>
-      </c>
-    </row>
-    <row r="62" spans="1:5">
-      <c r="A62" s="6" t="s">
-        <v>38</v>
-      </c>
-      <c r="B62" s="6" t="s">
-        <v>31</v>
-      </c>
-      <c r="C62" s="7">
-        <v>-42.63</v>
-      </c>
-      <c r="D62" s="7">
-        <v>-67.02</v>
-      </c>
-      <c r="E62" s="9">
-        <v>-24.39</v>
-      </c>
-    </row>
-    <row r="63" spans="1:5">
-      <c r="A63" s="6" t="s">
-        <v>39</v>
-      </c>
-      <c r="B63" s="6" t="s">
-        <v>31</v>
-      </c>
-      <c r="C63" s="7">
-        <v>-34.36</v>
-      </c>
-      <c r="D63" s="7">
-        <v>-7.62</v>
-      </c>
-      <c r="E63" s="8">
-        <v>26.74</v>
-      </c>
-    </row>
-    <row r="64" spans="1:5">
-      <c r="A64" s="6" t="s">
-        <v>40</v>
-      </c>
-      <c r="B64" s="6" t="s">
-        <v>31</v>
-      </c>
-      <c r="C64" s="7">
-        <v>165.27</v>
-      </c>
-      <c r="D64" s="7">
-        <v>126.8</v>
-      </c>
-      <c r="E64" s="9">
-        <v>-38.47</v>
-      </c>
-    </row>
-    <row r="65" spans="1:5">
-      <c r="A65" s="6" t="s">
-        <v>41</v>
-      </c>
-      <c r="B65" s="6" t="s">
-        <v>31</v>
-      </c>
-      <c r="C65" s="7">
-        <v>-2.37</v>
-      </c>
-      <c r="D65" s="7">
-        <v>-4.66</v>
-      </c>
-      <c r="E65" s="9">
-        <v>-2.29</v>
-      </c>
-    </row>
-    <row r="66" spans="1:5">
-      <c r="A66" s="6" t="s">
-        <v>42</v>
-      </c>
-      <c r="B66" s="6" t="s">
-        <v>31</v>
-      </c>
-      <c r="C66" s="7">
-        <v>149.77</v>
-      </c>
-      <c r="D66" s="7">
-        <v>-6.76</v>
-      </c>
-      <c r="E66" s="9">
-        <v>-156.53</v>
-      </c>
-    </row>
-    <row r="67" spans="1:5">
-      <c r="A67" s="6" t="s">
-        <v>43</v>
-      </c>
-      <c r="B67" s="6" t="s">
-        <v>31</v>
-      </c>
-      <c r="C67" s="7">
-        <v>398.73</v>
-      </c>
-      <c r="D67" s="7">
+      <c r="C61" s="5">
         <v>340.67</v>
       </c>
-      <c r="E67" s="9">
-        <v>-58.06</v>
+      <c r="D61" s="5">
+        <v>431.13</v>
+      </c>
+      <c r="E61" s="7">
+        <v>90.45999999999999</v>
       </c>
     </row>
   </sheetData>
   <mergeCells count="2">
     <mergeCell ref="A1:F1"/>
-    <mergeCell ref="A8:E8"/>
+    <mergeCell ref="A5:E5"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -2999,60 +2824,60 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:9" ht="28" customHeight="1">
-      <c r="A1" s="10" t="s">
+      <c r="A1" s="8" t="s">
         <v>1</v>
       </c>
-      <c r="B1" s="10" t="s">
-        <v>65</v>
-      </c>
-      <c r="C1" s="10" t="s">
-        <v>66</v>
-      </c>
-      <c r="D1" s="10" t="s">
-        <v>67</v>
-      </c>
-      <c r="E1" s="10" t="s">
-        <v>68</v>
-      </c>
-      <c r="F1" s="10" t="s">
-        <v>69</v>
-      </c>
-      <c r="G1" s="10" t="s">
+      <c r="B1" s="8" t="s">
+        <v>56</v>
+      </c>
+      <c r="C1" s="8" t="s">
+        <v>57</v>
+      </c>
+      <c r="D1" s="8" t="s">
+        <v>58</v>
+      </c>
+      <c r="E1" s="8" t="s">
+        <v>59</v>
+      </c>
+      <c r="F1" s="8" t="s">
+        <v>60</v>
+      </c>
+      <c r="G1" s="8" t="s">
+        <v>61</v>
+      </c>
+      <c r="H1" s="8" t="s">
+        <v>62</v>
+      </c>
+      <c r="I1" s="8" t="s">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="2" spans="1:9">
+      <c r="A2" s="9" t="s">
+        <v>44</v>
+      </c>
+      <c r="B2" s="10">
+        <v>60.8</v>
+      </c>
+      <c r="C2" s="11">
+        <v>7</v>
+      </c>
+      <c r="D2" s="10">
+        <v>42.5</v>
+      </c>
+      <c r="E2" s="10">
         <v>70</v>
       </c>
-      <c r="H1" s="10" t="s">
-        <v>71</v>
-      </c>
-      <c r="I1" s="10" t="s">
-        <v>72</v>
-      </c>
-    </row>
-    <row r="2" spans="1:9">
-      <c r="A2" s="11" t="s">
-        <v>44</v>
-      </c>
-      <c r="B2" s="12">
-        <v>60.8</v>
-      </c>
-      <c r="C2" s="13">
-        <v>7</v>
-      </c>
-      <c r="D2" s="12">
-        <v>45.5</v>
-      </c>
-      <c r="E2" s="12">
-        <v>70</v>
-      </c>
-      <c r="F2" s="12">
-        <v>-0.8</v>
-      </c>
-      <c r="G2" s="12">
-        <v>4.9</v>
-      </c>
-      <c r="H2" s="12">
+      <c r="F2" s="10">
+        <v>-1</v>
+      </c>
+      <c r="G2" s="10">
+        <v>2.8</v>
+      </c>
+      <c r="H2" s="10">
         <v>57</v>
       </c>
-      <c r="I2" s="12">
+      <c r="I2" s="10">
         <v>30</v>
       </c>
     </row>
@@ -3154,49 +2979,49 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:7">
-      <c r="A1" s="14" t="s">
+      <c r="A1" s="12" t="s">
         <v>37</v>
       </c>
-      <c r="B1" s="14" t="s">
+      <c r="B1" s="12" t="s">
         <v>41</v>
       </c>
-      <c r="C1" s="14" t="s">
+      <c r="C1" s="12" t="s">
         <v>38</v>
       </c>
-      <c r="D1" s="14" t="s">
+      <c r="D1" s="12" t="s">
         <v>43</v>
       </c>
-      <c r="E1" s="14" t="s">
+      <c r="E1" s="12" t="s">
         <v>42</v>
       </c>
-      <c r="F1" s="14" t="s">
+      <c r="F1" s="12" t="s">
         <v>40</v>
       </c>
-      <c r="G1" s="14" t="s">
+      <c r="G1" s="12" t="s">
         <v>39</v>
       </c>
     </row>
     <row r="2" spans="1:7">
-      <c r="A2" s="15">
-        <v>0.2647</v>
-      </c>
-      <c r="B2" s="15">
-        <v>0.1871</v>
-      </c>
-      <c r="C2" s="15">
-        <v>0.1619</v>
-      </c>
-      <c r="D2" s="15">
-        <v>0.0558</v>
-      </c>
-      <c r="E2" s="15">
-        <v>0.0545</v>
-      </c>
-      <c r="F2" s="15">
-        <v>-0.0032</v>
-      </c>
-      <c r="G2" s="15">
-        <v>-0.2466</v>
+      <c r="A2" s="13">
+        <v>0.2589</v>
+      </c>
+      <c r="B2" s="13">
+        <v>0.1889</v>
+      </c>
+      <c r="C2" s="13">
+        <v>0.153</v>
+      </c>
+      <c r="D2" s="13">
+        <v>0.06269999999999999</v>
+      </c>
+      <c r="E2" s="13">
+        <v>0.0588</v>
+      </c>
+      <c r="F2" s="13">
+        <v>0.0001</v>
+      </c>
+      <c r="G2" s="13">
+        <v>-0.2439</v>
       </c>
     </row>
   </sheetData>

--- a/BAJAJ_GROUP_Technical_Metrics.xlsx
+++ b/BAJAJ_GROUP_Technical_Metrics.xlsx
@@ -763,7 +763,7 @@
     <col min="23" max="23" width="16.7109375" customWidth="1"/>
     <col min="24" max="24" width="13.7109375" customWidth="1"/>
     <col min="25" max="25" width="7.7109375" customWidth="1"/>
-    <col min="26" max="26" width="8.7109375" customWidth="1"/>
+    <col min="26" max="26" width="9.7109375" customWidth="1"/>
     <col min="27" max="27" width="13.7109375" customWidth="1"/>
     <col min="28" max="28" width="11.7109375" customWidth="1"/>
     <col min="29" max="30" width="13.7109375" customWidth="1"/>
@@ -896,10 +896,10 @@
         <v>44</v>
       </c>
       <c r="C2">
-        <v>11024</v>
+        <v>10811</v>
       </c>
       <c r="D2">
-        <v>-2.28</v>
+        <v>-1.93</v>
       </c>
       <c r="E2">
         <v>12361</v>
@@ -908,46 +908,46 @@
         <v>8506.780000000001</v>
       </c>
       <c r="G2">
-        <v>-10.82</v>
+        <v>-12.54</v>
       </c>
       <c r="H2">
-        <v>29.59</v>
+        <v>27.09</v>
       </c>
       <c r="I2">
-        <v>-3.8</v>
+        <v>-4.86</v>
       </c>
       <c r="J2">
-        <v>-5.94</v>
+        <v>-9.23</v>
       </c>
       <c r="K2">
-        <v>13.46</v>
+        <v>9.85</v>
       </c>
       <c r="L2">
-        <v>24.43</v>
+        <v>24.03</v>
       </c>
       <c r="M2">
-        <v>25.89</v>
+        <v>25.46</v>
       </c>
       <c r="N2">
         <v>71</v>
       </c>
       <c r="O2">
-        <v>79</v>
+        <v>77</v>
       </c>
       <c r="P2">
-        <v>11255.2</v>
+        <v>11144.8</v>
       </c>
       <c r="Q2">
-        <v>11652.15</v>
+        <v>11586.2</v>
       </c>
       <c r="R2">
-        <v>11574.96</v>
+        <v>11580.73</v>
       </c>
       <c r="S2">
-        <v>10114.76</v>
+        <v>10124.48</v>
       </c>
       <c r="T2">
-        <v>8.99</v>
+        <v>6.78</v>
       </c>
       <c r="U2" t="s">
         <v>45</v>
@@ -962,43 +962,43 @@
         <v>3</v>
       </c>
       <c r="Y2">
-        <v>34.55</v>
+        <v>30.48</v>
       </c>
       <c r="Z2">
-        <v>-113.1</v>
+        <v>-151.95</v>
       </c>
       <c r="AA2">
-        <v>-28.68</v>
+        <v>-53.33</v>
       </c>
       <c r="AB2">
-        <v>-84.42</v>
+        <v>-98.62</v>
       </c>
       <c r="AC2">
         <v>5.45</v>
       </c>
       <c r="AD2">
-        <v>5.64</v>
+        <v>6.45</v>
       </c>
       <c r="AE2">
-        <v>204.66</v>
+        <v>205.68</v>
       </c>
       <c r="AF2">
-        <v>13.03</v>
+        <v>146.13</v>
       </c>
       <c r="AG2">
-        <v>12341.63</v>
+        <v>12333.16</v>
       </c>
       <c r="AH2">
-        <v>10962.67</v>
+        <v>10839.24</v>
       </c>
       <c r="AI2">
-        <v>11725.47</v>
+        <v>11529.55</v>
       </c>
       <c r="AJ2" t="s">
         <v>47</v>
       </c>
       <c r="AK2">
-        <v>51.47</v>
+        <v>55.89</v>
       </c>
     </row>
     <row r="3" spans="1:37">
@@ -1009,10 +1009,10 @@
         <v>44</v>
       </c>
       <c r="C3">
-        <v>480.05</v>
+        <v>493</v>
       </c>
       <c r="D3">
-        <v>-3.89</v>
+        <v>2.7</v>
       </c>
       <c r="E3">
         <v>670.25</v>
@@ -1021,46 +1021,46 @@
         <v>232.89</v>
       </c>
       <c r="G3">
-        <v>-28.38</v>
+        <v>-26.45</v>
       </c>
       <c r="H3">
-        <v>106.13</v>
+        <v>111.69</v>
       </c>
       <c r="I3">
-        <v>-6.84</v>
+        <v>-4.04</v>
       </c>
       <c r="J3">
-        <v>6.54</v>
+        <v>3.26</v>
       </c>
       <c r="K3">
-        <v>-19.86</v>
+        <v>-19.78</v>
       </c>
       <c r="L3">
-        <v>89.12</v>
+        <v>100.05</v>
       </c>
       <c r="M3">
-        <v>15.3</v>
+        <v>15.91</v>
       </c>
       <c r="N3">
         <v>99</v>
       </c>
       <c r="O3">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="P3">
-        <v>500.17</v>
+        <v>496.02</v>
       </c>
       <c r="Q3">
-        <v>504.81</v>
+        <v>505.76</v>
       </c>
       <c r="R3">
-        <v>510.61</v>
+        <v>509.69</v>
       </c>
       <c r="S3">
-        <v>448.53</v>
+        <v>449.72</v>
       </c>
       <c r="T3">
-        <v>7.03</v>
+        <v>9.619999999999999</v>
       </c>
       <c r="U3" t="s">
         <v>46</v>
@@ -1075,34 +1075,34 @@
         <v>2</v>
       </c>
       <c r="Y3">
-        <v>39.09</v>
+        <v>45.21</v>
       </c>
       <c r="Z3">
-        <v>-3.01</v>
+        <v>-3.5</v>
       </c>
       <c r="AA3">
-        <v>-1.92</v>
+        <v>-2.24</v>
       </c>
       <c r="AB3">
-        <v>-1.09</v>
+        <v>-1.26</v>
       </c>
       <c r="AC3">
-        <v>2.32</v>
+        <v>12.16</v>
       </c>
       <c r="AD3">
-        <v>14.45</v>
+        <v>8.18</v>
       </c>
       <c r="AE3">
-        <v>19.29</v>
+        <v>19.72</v>
       </c>
       <c r="AF3">
-        <v>-54.79</v>
+        <v>10.68</v>
       </c>
       <c r="AG3">
-        <v>537.28</v>
+        <v>535.4299999999999</v>
       </c>
       <c r="AH3">
-        <v>472.34</v>
+        <v>476.08</v>
       </c>
       <c r="AI3">
         <v>460.99</v>
@@ -1111,7 +1111,7 @@
         <v>48</v>
       </c>
       <c r="AK3">
-        <v>22.94</v>
+        <v>25.96</v>
       </c>
     </row>
     <row r="4" spans="1:37">
@@ -1122,58 +1122,58 @@
         <v>44</v>
       </c>
       <c r="C4">
-        <v>314.65</v>
+        <v>309.85</v>
       </c>
       <c r="D4">
-        <v>-1.35</v>
+        <v>-1.53</v>
       </c>
       <c r="E4">
-        <v>589.75</v>
+        <v>564.95</v>
       </c>
       <c r="F4">
         <v>303.75</v>
       </c>
       <c r="G4">
-        <v>-46.65</v>
+        <v>-45.15</v>
       </c>
       <c r="H4">
-        <v>3.59</v>
+        <v>2.01</v>
       </c>
       <c r="I4">
-        <v>-3.48</v>
+        <v>-4.2</v>
       </c>
       <c r="J4">
-        <v>-6.02</v>
+        <v>-6.88</v>
       </c>
       <c r="K4">
-        <v>-1.52</v>
+        <v>-3.11</v>
       </c>
       <c r="L4">
-        <v>-45.48</v>
+        <v>-47.46</v>
       </c>
       <c r="M4">
-        <v>-24.39</v>
+        <v>-24.31</v>
       </c>
       <c r="N4">
         <v>15</v>
       </c>
       <c r="O4">
-        <v>18</v>
+        <v>15</v>
       </c>
       <c r="P4">
-        <v>321.58</v>
+        <v>318.86</v>
       </c>
       <c r="Q4">
-        <v>328.38</v>
+        <v>327.64</v>
       </c>
       <c r="R4">
-        <v>338.59</v>
+        <v>338.1</v>
       </c>
       <c r="S4">
-        <v>370.58</v>
+        <v>369.76</v>
       </c>
       <c r="T4">
-        <v>-15.09</v>
+        <v>-16.2</v>
       </c>
       <c r="U4" t="s">
         <v>46</v>
@@ -1188,43 +1188,43 @@
         <v>0</v>
       </c>
       <c r="Y4">
-        <v>36.28</v>
+        <v>33.54</v>
       </c>
       <c r="Z4">
-        <v>-5.66</v>
+        <v>-6.44</v>
       </c>
       <c r="AA4">
-        <v>-4.53</v>
+        <v>-4.91</v>
       </c>
       <c r="AB4">
-        <v>-1.13</v>
+        <v>-1.53</v>
       </c>
       <c r="AC4">
-        <v>7.77</v>
+        <v>1.86</v>
       </c>
       <c r="AD4">
-        <v>23.3</v>
+        <v>12.47</v>
       </c>
       <c r="AE4">
-        <v>9.43</v>
+        <v>9.51</v>
       </c>
       <c r="AF4">
-        <v>-12.03</v>
+        <v>217.44</v>
       </c>
       <c r="AG4">
-        <v>343.6</v>
+        <v>344.93</v>
       </c>
       <c r="AH4">
-        <v>313.17</v>
+        <v>310.35</v>
       </c>
       <c r="AI4">
-        <v>346.95</v>
+        <v>337.22</v>
       </c>
       <c r="AJ4" t="s">
         <v>47</v>
       </c>
       <c r="AK4">
-        <v>16.08</v>
+        <v>21.15</v>
       </c>
     </row>
     <row r="5" spans="1:37">
@@ -1235,10 +1235,10 @@
         <v>44</v>
       </c>
       <c r="C5">
-        <v>1752</v>
+        <v>1742.4</v>
       </c>
       <c r="D5">
-        <v>-1.07</v>
+        <v>-0.55</v>
       </c>
       <c r="E5">
         <v>2176.6</v>
@@ -1247,25 +1247,25 @@
         <v>1631.8</v>
       </c>
       <c r="G5">
-        <v>-19.51</v>
+        <v>-19.95</v>
       </c>
       <c r="H5">
-        <v>7.37</v>
+        <v>6.78</v>
       </c>
       <c r="I5">
-        <v>-5.29</v>
+        <v>-4.44</v>
       </c>
       <c r="J5">
-        <v>-12.88</v>
+        <v>-12.97</v>
       </c>
       <c r="K5">
-        <v>-1.58</v>
+        <v>-3.07</v>
       </c>
       <c r="L5">
-        <v>-15.95</v>
+        <v>-15.79</v>
       </c>
       <c r="M5">
-        <v>0.01</v>
+        <v>0.03</v>
       </c>
       <c r="N5">
         <v>29</v>
@@ -1274,19 +1274,19 @@
         <v>43</v>
       </c>
       <c r="P5">
-        <v>1791.04</v>
+        <v>1774.84</v>
       </c>
       <c r="Q5">
-        <v>1890.6</v>
+        <v>1876.67</v>
       </c>
       <c r="R5">
-        <v>1950.3</v>
+        <v>1947.91</v>
       </c>
       <c r="S5">
-        <v>1889.73</v>
+        <v>1888.11</v>
       </c>
       <c r="T5">
-        <v>-7.29</v>
+        <v>-7.72</v>
       </c>
       <c r="U5" t="s">
         <v>46</v>
@@ -1301,43 +1301,43 @@
         <v>1</v>
       </c>
       <c r="Y5">
-        <v>26.53</v>
+        <v>25.68</v>
       </c>
       <c r="Z5">
-        <v>-52.74</v>
+        <v>-56.08</v>
       </c>
       <c r="AA5">
-        <v>-37.44</v>
+        <v>-41.17</v>
       </c>
       <c r="AB5">
-        <v>-15.3</v>
+        <v>-14.91</v>
       </c>
       <c r="AC5">
         <v>4.92</v>
       </c>
       <c r="AD5">
-        <v>10.82</v>
+        <v>8.279999999999999</v>
       </c>
       <c r="AE5">
-        <v>37.71</v>
+        <v>37.08</v>
       </c>
       <c r="AF5">
-        <v>-19.44</v>
+        <v>27.93</v>
       </c>
       <c r="AG5">
-        <v>2051.95</v>
+        <v>2038.72</v>
       </c>
       <c r="AH5">
-        <v>1729.25</v>
+        <v>1714.62</v>
       </c>
       <c r="AI5">
-        <v>1867.19</v>
+        <v>1855.63</v>
       </c>
       <c r="AJ5" t="s">
         <v>47</v>
       </c>
       <c r="AK5">
-        <v>73.65000000000001</v>
+        <v>75.66</v>
       </c>
     </row>
     <row r="6" spans="1:37">
@@ -1348,58 +1348,58 @@
         <v>44</v>
       </c>
       <c r="C6">
-        <v>10800</v>
+        <v>10600</v>
       </c>
       <c r="D6">
-        <v>-1.28</v>
+        <v>-1.85</v>
       </c>
       <c r="E6">
-        <v>13203</v>
+        <v>13144</v>
       </c>
       <c r="F6">
         <v>8746</v>
       </c>
       <c r="G6">
-        <v>-18.2</v>
+        <v>-19.35</v>
       </c>
       <c r="H6">
-        <v>23.49</v>
+        <v>21.2</v>
       </c>
       <c r="I6">
-        <v>-5.34</v>
+        <v>-5.23</v>
       </c>
       <c r="J6">
-        <v>-5.25</v>
+        <v>-6.53</v>
       </c>
       <c r="K6">
-        <v>1.86</v>
+        <v>-1.11</v>
       </c>
       <c r="L6">
-        <v>-18.58</v>
+        <v>-19.72</v>
       </c>
       <c r="M6">
-        <v>18.89</v>
+        <v>18.88</v>
       </c>
       <c r="N6">
         <v>43</v>
       </c>
       <c r="O6">
-        <v>47</v>
+        <v>44</v>
       </c>
       <c r="P6">
-        <v>11058.2</v>
+        <v>10941.2</v>
       </c>
       <c r="Q6">
-        <v>11130.45</v>
+        <v>11078.25</v>
       </c>
       <c r="R6">
-        <v>11165.56</v>
+        <v>11171.58</v>
       </c>
       <c r="S6">
-        <v>10680.57</v>
+        <v>10678.06</v>
       </c>
       <c r="T6">
-        <v>1.12</v>
+        <v>-0.73</v>
       </c>
       <c r="U6" t="s">
         <v>46</v>
@@ -1411,46 +1411,46 @@
         <v>46</v>
       </c>
       <c r="X6">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="Y6">
-        <v>42.13</v>
+        <v>38.48</v>
       </c>
       <c r="Z6">
-        <v>-49.53</v>
+        <v>-84.31999999999999</v>
       </c>
       <c r="AA6">
-        <v>-17.21</v>
+        <v>-30.64</v>
       </c>
       <c r="AB6">
-        <v>-32.31</v>
+        <v>-53.69</v>
       </c>
       <c r="AC6">
-        <v>8.550000000000001</v>
+        <v>4.94</v>
       </c>
       <c r="AD6">
-        <v>34.7</v>
+        <v>18.29</v>
       </c>
       <c r="AE6">
-        <v>250.79</v>
+        <v>252.38</v>
       </c>
       <c r="AF6">
-        <v>-28.52</v>
+        <v>51.72</v>
       </c>
       <c r="AG6">
-        <v>11543.46</v>
+        <v>11481.76</v>
       </c>
       <c r="AH6">
-        <v>10717.44</v>
+        <v>10674.74</v>
       </c>
       <c r="AI6">
-        <v>10787.84</v>
+        <v>11493.63</v>
       </c>
       <c r="AJ6" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="AK6">
-        <v>22.83</v>
+        <v>26.19</v>
       </c>
     </row>
     <row r="7" spans="1:37">
@@ -1461,10 +1461,10 @@
         <v>44</v>
       </c>
       <c r="C7">
-        <v>985</v>
+        <v>973.8</v>
       </c>
       <c r="D7">
-        <v>-1.19</v>
+        <v>-1.14</v>
       </c>
       <c r="E7">
         <v>1158.8</v>
@@ -1473,46 +1473,46 @@
         <v>801.55</v>
       </c>
       <c r="G7">
-        <v>-15</v>
+        <v>-15.96</v>
       </c>
       <c r="H7">
-        <v>22.89</v>
+        <v>21.49</v>
       </c>
       <c r="I7">
-        <v>-3.55</v>
+        <v>-3.47</v>
       </c>
       <c r="J7">
-        <v>-9.050000000000001</v>
+        <v>-9.82</v>
       </c>
       <c r="K7">
-        <v>-1.97</v>
+        <v>-4.05</v>
       </c>
       <c r="L7">
-        <v>-3.95</v>
+        <v>-5.43</v>
       </c>
       <c r="M7">
-        <v>5.88</v>
+        <v>5.72</v>
       </c>
       <c r="N7">
         <v>57</v>
       </c>
       <c r="O7">
-        <v>53</v>
+        <v>51</v>
       </c>
       <c r="P7">
-        <v>1003.18</v>
+        <v>996.1799999999999</v>
       </c>
       <c r="Q7">
-        <v>1030.78</v>
+        <v>1026.62</v>
       </c>
       <c r="R7">
-        <v>1064.49</v>
+        <v>1062.69</v>
       </c>
       <c r="S7">
-        <v>977.08</v>
+        <v>976.9</v>
       </c>
       <c r="T7">
-        <v>0.8100000000000001</v>
+        <v>-0.32</v>
       </c>
       <c r="U7" t="s">
         <v>46</v>
@@ -1524,46 +1524,46 @@
         <v>46</v>
       </c>
       <c r="X7">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="Y7">
-        <v>38.18</v>
+        <v>36.26</v>
       </c>
       <c r="Z7">
-        <v>-18.84</v>
+        <v>-20.76</v>
       </c>
       <c r="AA7">
-        <v>-14.59</v>
+        <v>-15.83</v>
       </c>
       <c r="AB7">
-        <v>-4.25</v>
+        <v>-4.93</v>
       </c>
       <c r="AC7">
-        <v>40.2</v>
+        <v>40.32</v>
       </c>
       <c r="AD7">
-        <v>52.61</v>
+        <v>46.91</v>
       </c>
       <c r="AE7">
-        <v>24.88</v>
+        <v>24.79</v>
       </c>
       <c r="AF7">
-        <v>29.1</v>
+        <v>41.38</v>
       </c>
       <c r="AG7">
-        <v>1082.03</v>
+        <v>1082.23</v>
       </c>
       <c r="AH7">
-        <v>979.53</v>
+        <v>971.01</v>
       </c>
       <c r="AI7">
-        <v>1057.8</v>
+        <v>1044.92</v>
       </c>
       <c r="AJ7" t="s">
         <v>47</v>
       </c>
       <c r="AK7">
-        <v>40.33</v>
+        <v>42.94</v>
       </c>
     </row>
     <row r="8" spans="1:37">
@@ -1574,13 +1574,13 @@
         <v>44</v>
       </c>
       <c r="C8">
-        <v>171.03</v>
+        <v>172.49</v>
       </c>
       <c r="D8">
-        <v>2.38</v>
+        <v>0.85</v>
       </c>
       <c r="E8">
-        <v>171.03</v>
+        <v>172.49</v>
       </c>
       <c r="F8">
         <v>115.96</v>
@@ -1589,22 +1589,22 @@
         <v>0</v>
       </c>
       <c r="H8">
-        <v>47.49</v>
+        <v>48.75</v>
       </c>
       <c r="I8">
-        <v>25.73</v>
+        <v>21.98</v>
       </c>
       <c r="J8">
-        <v>25.52</v>
+        <v>25.66</v>
       </c>
       <c r="K8">
-        <v>29.41</v>
+        <v>30.01</v>
       </c>
       <c r="L8">
-        <v>22.87</v>
+        <v>27.32</v>
       </c>
       <c r="M8">
-        <v>6.27</v>
+        <v>6.53</v>
       </c>
       <c r="N8">
         <v>85</v>
@@ -1613,19 +1613,19 @@
         <v>87</v>
       </c>
       <c r="P8">
-        <v>158.37</v>
+        <v>164.59</v>
       </c>
       <c r="Q8">
-        <v>141.93</v>
+        <v>143.69</v>
       </c>
       <c r="R8">
-        <v>140.2</v>
+        <v>140.77</v>
       </c>
       <c r="S8">
-        <v>134.49</v>
+        <v>134.7</v>
       </c>
       <c r="T8">
-        <v>27.17</v>
+        <v>28.06</v>
       </c>
       <c r="U8" t="s">
         <v>45</v>
@@ -1640,34 +1640,34 @@
         <v>3</v>
       </c>
       <c r="Y8">
-        <v>80.66</v>
+        <v>81.28</v>
       </c>
       <c r="Z8">
-        <v>6.08</v>
+        <v>7.41</v>
       </c>
       <c r="AA8">
-        <v>2.32</v>
+        <v>3.34</v>
       </c>
       <c r="AB8">
-        <v>3.76</v>
+        <v>4.08</v>
       </c>
       <c r="AC8">
-        <v>96.22</v>
+        <v>100</v>
       </c>
       <c r="AD8">
-        <v>94.37</v>
+        <v>97.48</v>
       </c>
       <c r="AE8">
-        <v>6.3</v>
+        <v>6.48</v>
       </c>
       <c r="AF8">
-        <v>431.13</v>
+        <v>119.63</v>
       </c>
       <c r="AG8">
-        <v>164.54</v>
+        <v>169.97</v>
       </c>
       <c r="AH8">
-        <v>119.32</v>
+        <v>117.41</v>
       </c>
       <c r="AI8">
         <v>151.8</v>
@@ -1676,7 +1676,7 @@
         <v>48</v>
       </c>
       <c r="AK8">
-        <v>45.19</v>
+        <v>48.26</v>
       </c>
     </row>
   </sheetData>
@@ -1874,13 +1874,13 @@
         <v>9</v>
       </c>
       <c r="C7" s="5">
-        <v>-3.78</v>
+        <v>-5.94</v>
       </c>
       <c r="D7" s="5">
-        <v>-5.94</v>
+        <v>-9.23</v>
       </c>
       <c r="E7" s="6">
-        <v>-2.16</v>
+        <v>-3.29</v>
       </c>
     </row>
     <row r="8" spans="1:6">
@@ -1891,13 +1891,13 @@
         <v>9</v>
       </c>
       <c r="C8" s="5">
-        <v>7.77</v>
+        <v>6.54</v>
       </c>
       <c r="D8" s="5">
-        <v>6.54</v>
+        <v>3.26</v>
       </c>
       <c r="E8" s="6">
-        <v>-1.23</v>
+        <v>-3.28</v>
       </c>
     </row>
     <row r="9" spans="1:6">
@@ -1908,13 +1908,13 @@
         <v>9</v>
       </c>
       <c r="C9" s="5">
-        <v>-6.36</v>
+        <v>-6.02</v>
       </c>
       <c r="D9" s="5">
-        <v>-6.02</v>
-      </c>
-      <c r="E9" s="7">
-        <v>0.34</v>
+        <v>-6.88</v>
+      </c>
+      <c r="E9" s="6">
+        <v>-0.86</v>
       </c>
     </row>
     <row r="10" spans="1:6">
@@ -1925,13 +1925,13 @@
         <v>9</v>
       </c>
       <c r="C10" s="5">
-        <v>-11.89</v>
+        <v>-12.88</v>
       </c>
       <c r="D10" s="5">
-        <v>-12.88</v>
+        <v>-12.97</v>
       </c>
       <c r="E10" s="6">
-        <v>-0.99</v>
+        <v>-0.09</v>
       </c>
     </row>
     <row r="11" spans="1:6">
@@ -1942,13 +1942,13 @@
         <v>9</v>
       </c>
       <c r="C11" s="5">
-        <v>-5.2</v>
+        <v>-5.25</v>
       </c>
       <c r="D11" s="5">
-        <v>-5.25</v>
+        <v>-6.53</v>
       </c>
       <c r="E11" s="6">
-        <v>-0.05</v>
+        <v>-1.28</v>
       </c>
     </row>
     <row r="12" spans="1:6">
@@ -1959,13 +1959,13 @@
         <v>9</v>
       </c>
       <c r="C12" s="5">
-        <v>-8.119999999999999</v>
+        <v>-9.050000000000001</v>
       </c>
       <c r="D12" s="5">
-        <v>-9.050000000000001</v>
+        <v>-9.82</v>
       </c>
       <c r="E12" s="6">
-        <v>-0.93</v>
+        <v>-0.77</v>
       </c>
     </row>
     <row r="13" spans="1:6">
@@ -1976,13 +1976,13 @@
         <v>9</v>
       </c>
       <c r="C13" s="5">
-        <v>21.91</v>
+        <v>25.52</v>
       </c>
       <c r="D13" s="5">
-        <v>25.52</v>
+        <v>25.66</v>
       </c>
       <c r="E13" s="7">
-        <v>3.61</v>
+        <v>0.14</v>
       </c>
     </row>
     <row r="14" spans="1:6">
@@ -1993,13 +1993,13 @@
         <v>8</v>
       </c>
       <c r="C14" s="5">
-        <v>-1.17</v>
+        <v>-3.8</v>
       </c>
       <c r="D14" s="5">
-        <v>-3.8</v>
+        <v>-4.86</v>
       </c>
       <c r="E14" s="6">
-        <v>-2.63</v>
+        <v>-1.06</v>
       </c>
     </row>
     <row r="15" spans="1:6">
@@ -2010,13 +2010,13 @@
         <v>8</v>
       </c>
       <c r="C15" s="5">
-        <v>-2.47</v>
+        <v>-6.84</v>
       </c>
       <c r="D15" s="5">
-        <v>-6.84</v>
-      </c>
-      <c r="E15" s="6">
-        <v>-4.37</v>
+        <v>-4.04</v>
+      </c>
+      <c r="E15" s="7">
+        <v>2.8</v>
       </c>
     </row>
     <row r="16" spans="1:6">
@@ -2027,13 +2027,13 @@
         <v>8</v>
       </c>
       <c r="C16" s="5">
-        <v>-1.27</v>
+        <v>-3.48</v>
       </c>
       <c r="D16" s="5">
-        <v>-3.48</v>
+        <v>-4.2</v>
       </c>
       <c r="E16" s="6">
-        <v>-2.21</v>
+        <v>-0.72</v>
       </c>
     </row>
     <row r="17" spans="1:5">
@@ -2044,13 +2044,13 @@
         <v>8</v>
       </c>
       <c r="C17" s="5">
-        <v>-4.4</v>
+        <v>-5.29</v>
       </c>
       <c r="D17" s="5">
-        <v>-5.29</v>
-      </c>
-      <c r="E17" s="6">
-        <v>-0.89</v>
+        <v>-4.44</v>
+      </c>
+      <c r="E17" s="7">
+        <v>0.85</v>
       </c>
     </row>
     <row r="18" spans="1:5">
@@ -2061,13 +2061,13 @@
         <v>8</v>
       </c>
       <c r="C18" s="5">
-        <v>-3.03</v>
+        <v>-5.34</v>
       </c>
       <c r="D18" s="5">
-        <v>-5.34</v>
-      </c>
-      <c r="E18" s="6">
-        <v>-2.31</v>
+        <v>-5.23</v>
+      </c>
+      <c r="E18" s="7">
+        <v>0.11</v>
       </c>
     </row>
     <row r="19" spans="1:5">
@@ -2078,13 +2078,13 @@
         <v>8</v>
       </c>
       <c r="C19" s="5">
-        <v>-4.17</v>
+        <v>-3.55</v>
       </c>
       <c r="D19" s="5">
-        <v>-3.55</v>
+        <v>-3.47</v>
       </c>
       <c r="E19" s="7">
-        <v>0.62</v>
+        <v>0.08</v>
       </c>
     </row>
     <row r="20" spans="1:5">
@@ -2095,13 +2095,13 @@
         <v>8</v>
       </c>
       <c r="C20" s="5">
-        <v>23.94</v>
+        <v>25.73</v>
       </c>
       <c r="D20" s="5">
-        <v>25.73</v>
-      </c>
-      <c r="E20" s="7">
-        <v>1.79</v>
+        <v>21.98</v>
+      </c>
+      <c r="E20" s="6">
+        <v>-3.75</v>
       </c>
     </row>
     <row r="21" spans="1:5">
@@ -2112,13 +2112,13 @@
         <v>11</v>
       </c>
       <c r="C21" s="5">
-        <v>26.34</v>
+        <v>24.43</v>
       </c>
       <c r="D21" s="5">
-        <v>24.43</v>
+        <v>24.03</v>
       </c>
       <c r="E21" s="6">
-        <v>-1.91</v>
+        <v>-0.4</v>
       </c>
     </row>
     <row r="22" spans="1:5">
@@ -2129,13 +2129,13 @@
         <v>11</v>
       </c>
       <c r="C22" s="5">
-        <v>93.87</v>
+        <v>89.12</v>
       </c>
       <c r="D22" s="5">
-        <v>89.12</v>
-      </c>
-      <c r="E22" s="6">
-        <v>-4.75</v>
+        <v>100.05</v>
+      </c>
+      <c r="E22" s="7">
+        <v>10.93</v>
       </c>
     </row>
     <row r="23" spans="1:5">
@@ -2146,13 +2146,13 @@
         <v>11</v>
       </c>
       <c r="C23" s="5">
-        <v>-45.34</v>
+        <v>-45.48</v>
       </c>
       <c r="D23" s="5">
-        <v>-45.48</v>
+        <v>-47.46</v>
       </c>
       <c r="E23" s="6">
-        <v>-0.14</v>
+        <v>-1.98</v>
       </c>
     </row>
     <row r="24" spans="1:5">
@@ -2163,13 +2163,13 @@
         <v>11</v>
       </c>
       <c r="C24" s="5">
-        <v>-14.42</v>
+        <v>-15.95</v>
       </c>
       <c r="D24" s="5">
-        <v>-15.95</v>
-      </c>
-      <c r="E24" s="6">
-        <v>-1.53</v>
+        <v>-15.79</v>
+      </c>
+      <c r="E24" s="7">
+        <v>0.16</v>
       </c>
     </row>
     <row r="25" spans="1:5">
@@ -2180,13 +2180,13 @@
         <v>11</v>
       </c>
       <c r="C25" s="5">
-        <v>-17.61</v>
+        <v>-18.58</v>
       </c>
       <c r="D25" s="5">
-        <v>-18.58</v>
+        <v>-19.72</v>
       </c>
       <c r="E25" s="6">
-        <v>-0.97</v>
+        <v>-1.14</v>
       </c>
     </row>
     <row r="26" spans="1:5">
@@ -2197,13 +2197,13 @@
         <v>11</v>
       </c>
       <c r="C26" s="5">
-        <v>-0.95</v>
+        <v>-3.95</v>
       </c>
       <c r="D26" s="5">
-        <v>-3.95</v>
+        <v>-5.43</v>
       </c>
       <c r="E26" s="6">
-        <v>-3</v>
+        <v>-1.48</v>
       </c>
     </row>
     <row r="27" spans="1:5">
@@ -2214,13 +2214,13 @@
         <v>11</v>
       </c>
       <c r="C27" s="5">
-        <v>23.27</v>
+        <v>22.87</v>
       </c>
       <c r="D27" s="5">
-        <v>22.87</v>
-      </c>
-      <c r="E27" s="6">
-        <v>-0.4</v>
+        <v>27.32</v>
+      </c>
+      <c r="E27" s="7">
+        <v>4.45</v>
       </c>
     </row>
     <row r="28" spans="1:5">
@@ -2231,13 +2231,13 @@
         <v>10</v>
       </c>
       <c r="C28" s="5">
-        <v>17.14</v>
+        <v>13.46</v>
       </c>
       <c r="D28" s="5">
-        <v>13.46</v>
+        <v>9.85</v>
       </c>
       <c r="E28" s="6">
-        <v>-3.68</v>
+        <v>-3.61</v>
       </c>
     </row>
     <row r="29" spans="1:5">
@@ -2248,13 +2248,13 @@
         <v>10</v>
       </c>
       <c r="C29" s="5">
-        <v>-16.35</v>
+        <v>-19.86</v>
       </c>
       <c r="D29" s="5">
-        <v>-19.86</v>
-      </c>
-      <c r="E29" s="6">
-        <v>-3.51</v>
+        <v>-19.78</v>
+      </c>
+      <c r="E29" s="7">
+        <v>0.08</v>
       </c>
     </row>
     <row r="30" spans="1:5">
@@ -2265,13 +2265,13 @@
         <v>10</v>
       </c>
       <c r="C30" s="5">
-        <v>0.58</v>
+        <v>-1.52</v>
       </c>
       <c r="D30" s="5">
-        <v>-1.52</v>
+        <v>-3.11</v>
       </c>
       <c r="E30" s="6">
-        <v>-2.1</v>
+        <v>-1.59</v>
       </c>
     </row>
     <row r="31" spans="1:5">
@@ -2282,13 +2282,13 @@
         <v>10</v>
       </c>
       <c r="C31" s="5">
-        <v>0.67</v>
+        <v>-1.58</v>
       </c>
       <c r="D31" s="5">
-        <v>-1.58</v>
+        <v>-3.07</v>
       </c>
       <c r="E31" s="6">
-        <v>-2.25</v>
+        <v>-1.49</v>
       </c>
     </row>
     <row r="32" spans="1:5">
@@ -2299,13 +2299,13 @@
         <v>10</v>
       </c>
       <c r="C32" s="5">
-        <v>3.29</v>
+        <v>1.86</v>
       </c>
       <c r="D32" s="5">
-        <v>1.86</v>
+        <v>-1.11</v>
       </c>
       <c r="E32" s="6">
-        <v>-1.43</v>
+        <v>-2.97</v>
       </c>
     </row>
     <row r="33" spans="1:5">
@@ -2316,13 +2316,13 @@
         <v>10</v>
       </c>
       <c r="C33" s="5">
-        <v>1.51</v>
+        <v>-1.97</v>
       </c>
       <c r="D33" s="5">
-        <v>-1.97</v>
+        <v>-4.05</v>
       </c>
       <c r="E33" s="6">
-        <v>-3.48</v>
+        <v>-2.08</v>
       </c>
     </row>
     <row r="34" spans="1:5">
@@ -2333,13 +2333,13 @@
         <v>10</v>
       </c>
       <c r="C34" s="5">
-        <v>27.41</v>
+        <v>29.41</v>
       </c>
       <c r="D34" s="5">
-        <v>29.41</v>
+        <v>30.01</v>
       </c>
       <c r="E34" s="7">
-        <v>2</v>
+        <v>0.6</v>
       </c>
     </row>
     <row r="35" spans="1:5">
@@ -2350,13 +2350,13 @@
         <v>6</v>
       </c>
       <c r="C35" s="5">
-        <v>-8.74</v>
+        <v>-10.82</v>
       </c>
       <c r="D35" s="5">
-        <v>-10.82</v>
+        <v>-12.54</v>
       </c>
       <c r="E35" s="6">
-        <v>-2.08</v>
+        <v>-1.72</v>
       </c>
     </row>
     <row r="36" spans="1:5">
@@ -2367,13 +2367,13 @@
         <v>6</v>
       </c>
       <c r="C36" s="5">
-        <v>-25.48</v>
+        <v>-28.38</v>
       </c>
       <c r="D36" s="5">
-        <v>-28.38</v>
-      </c>
-      <c r="E36" s="6">
-        <v>-2.9</v>
+        <v>-26.45</v>
+      </c>
+      <c r="E36" s="7">
+        <v>1.93</v>
       </c>
     </row>
     <row r="37" spans="1:5">
@@ -2384,13 +2384,13 @@
         <v>6</v>
       </c>
       <c r="C37" s="5">
-        <v>-45.92</v>
+        <v>-46.65</v>
       </c>
       <c r="D37" s="5">
-        <v>-46.65</v>
-      </c>
-      <c r="E37" s="6">
-        <v>-0.73</v>
+        <v>-45.15</v>
+      </c>
+      <c r="E37" s="7">
+        <v>1.5</v>
       </c>
     </row>
     <row r="38" spans="1:5">
@@ -2401,13 +2401,13 @@
         <v>6</v>
       </c>
       <c r="C38" s="5">
-        <v>-18.63</v>
+        <v>-19.51</v>
       </c>
       <c r="D38" s="5">
-        <v>-19.51</v>
+        <v>-19.95</v>
       </c>
       <c r="E38" s="6">
-        <v>-0.88</v>
+        <v>-0.44</v>
       </c>
     </row>
     <row r="39" spans="1:5">
@@ -2418,13 +2418,13 @@
         <v>6</v>
       </c>
       <c r="C39" s="5">
-        <v>-17.53</v>
+        <v>-18.2</v>
       </c>
       <c r="D39" s="5">
-        <v>-18.2</v>
+        <v>-19.35</v>
       </c>
       <c r="E39" s="6">
-        <v>-0.67</v>
+        <v>-1.15</v>
       </c>
     </row>
     <row r="40" spans="1:5">
@@ -2435,13 +2435,13 @@
         <v>6</v>
       </c>
       <c r="C40" s="5">
-        <v>-13.97</v>
+        <v>-15</v>
       </c>
       <c r="D40" s="5">
-        <v>-15</v>
+        <v>-15.96</v>
       </c>
       <c r="E40" s="6">
-        <v>-1.03</v>
+        <v>-0.96</v>
       </c>
     </row>
     <row r="41" spans="1:5">
@@ -2452,13 +2452,13 @@
         <v>2</v>
       </c>
       <c r="C41" s="5">
-        <v>11281</v>
+        <v>11024</v>
       </c>
       <c r="D41" s="5">
-        <v>11024</v>
+        <v>10811</v>
       </c>
       <c r="E41" s="6">
-        <v>-257</v>
+        <v>-213</v>
       </c>
     </row>
     <row r="42" spans="1:5">
@@ -2469,13 +2469,13 @@
         <v>2</v>
       </c>
       <c r="C42" s="5">
-        <v>499.5</v>
+        <v>480.05</v>
       </c>
       <c r="D42" s="5">
-        <v>480.05</v>
-      </c>
-      <c r="E42" s="6">
-        <v>-19.45</v>
+        <v>493</v>
+      </c>
+      <c r="E42" s="7">
+        <v>12.95</v>
       </c>
     </row>
     <row r="43" spans="1:5">
@@ -2486,13 +2486,13 @@
         <v>2</v>
       </c>
       <c r="C43" s="5">
-        <v>318.95</v>
+        <v>314.65</v>
       </c>
       <c r="D43" s="5">
-        <v>314.65</v>
+        <v>309.85</v>
       </c>
       <c r="E43" s="6">
-        <v>-4.3</v>
+        <v>-4.8</v>
       </c>
     </row>
     <row r="44" spans="1:5">
@@ -2503,13 +2503,13 @@
         <v>2</v>
       </c>
       <c r="C44" s="5">
-        <v>1771</v>
+        <v>1752</v>
       </c>
       <c r="D44" s="5">
-        <v>1752</v>
+        <v>1742.4</v>
       </c>
       <c r="E44" s="6">
-        <v>-19</v>
+        <v>-9.6</v>
       </c>
     </row>
     <row r="45" spans="1:5">
@@ -2520,13 +2520,13 @@
         <v>2</v>
       </c>
       <c r="C45" s="5">
-        <v>10940</v>
+        <v>10800</v>
       </c>
       <c r="D45" s="5">
-        <v>10800</v>
+        <v>10600</v>
       </c>
       <c r="E45" s="6">
-        <v>-140</v>
+        <v>-200</v>
       </c>
     </row>
     <row r="46" spans="1:5">
@@ -2537,13 +2537,13 @@
         <v>2</v>
       </c>
       <c r="C46" s="5">
-        <v>996.9</v>
+        <v>985</v>
       </c>
       <c r="D46" s="5">
-        <v>985</v>
+        <v>973.8</v>
       </c>
       <c r="E46" s="6">
-        <v>-11.9</v>
+        <v>-11.2</v>
       </c>
     </row>
     <row r="47" spans="1:5">
@@ -2554,13 +2554,13 @@
         <v>2</v>
       </c>
       <c r="C47" s="5">
-        <v>167.05</v>
+        <v>171.03</v>
       </c>
       <c r="D47" s="5">
-        <v>171.03</v>
+        <v>172.49</v>
       </c>
       <c r="E47" s="7">
-        <v>3.98</v>
+        <v>1.46</v>
       </c>
     </row>
     <row r="48" spans="1:5">
@@ -2571,13 +2571,13 @@
         <v>24</v>
       </c>
       <c r="C48" s="5">
-        <v>40.65</v>
+        <v>34.55</v>
       </c>
       <c r="D48" s="5">
-        <v>34.55</v>
+        <v>30.48</v>
       </c>
       <c r="E48" s="6">
-        <v>-6.1</v>
+        <v>-4.07</v>
       </c>
     </row>
     <row r="49" spans="1:5">
@@ -2588,13 +2588,13 @@
         <v>24</v>
       </c>
       <c r="C49" s="5">
-        <v>46.31</v>
+        <v>39.09</v>
       </c>
       <c r="D49" s="5">
-        <v>39.09</v>
-      </c>
-      <c r="E49" s="6">
-        <v>-7.22</v>
+        <v>45.21</v>
+      </c>
+      <c r="E49" s="7">
+        <v>6.12</v>
       </c>
     </row>
     <row r="50" spans="1:5">
@@ -2605,13 +2605,13 @@
         <v>24</v>
       </c>
       <c r="C50" s="5">
-        <v>38.94</v>
+        <v>36.28</v>
       </c>
       <c r="D50" s="5">
-        <v>36.28</v>
+        <v>33.54</v>
       </c>
       <c r="E50" s="6">
-        <v>-2.66</v>
+        <v>-2.74</v>
       </c>
     </row>
     <row r="51" spans="1:5">
@@ -2622,13 +2622,13 @@
         <v>24</v>
       </c>
       <c r="C51" s="5">
-        <v>28.25</v>
+        <v>26.53</v>
       </c>
       <c r="D51" s="5">
-        <v>26.53</v>
+        <v>25.68</v>
       </c>
       <c r="E51" s="6">
-        <v>-1.72</v>
+        <v>-0.85</v>
       </c>
     </row>
     <row r="52" spans="1:5">
@@ -2639,13 +2639,13 @@
         <v>24</v>
       </c>
       <c r="C52" s="5">
-        <v>44.89</v>
+        <v>42.13</v>
       </c>
       <c r="D52" s="5">
-        <v>42.13</v>
+        <v>38.48</v>
       </c>
       <c r="E52" s="6">
-        <v>-2.76</v>
+        <v>-3.65</v>
       </c>
     </row>
     <row r="53" spans="1:5">
@@ -2656,13 +2656,13 @@
         <v>24</v>
       </c>
       <c r="C53" s="5">
-        <v>40.29</v>
+        <v>38.18</v>
       </c>
       <c r="D53" s="5">
-        <v>38.18</v>
+        <v>36.26</v>
       </c>
       <c r="E53" s="6">
-        <v>-2.11</v>
+        <v>-1.92</v>
       </c>
     </row>
     <row r="54" spans="1:5">
@@ -2673,13 +2673,13 @@
         <v>24</v>
       </c>
       <c r="C54" s="5">
-        <v>78.91</v>
+        <v>80.66</v>
       </c>
       <c r="D54" s="5">
-        <v>80.66</v>
+        <v>81.28</v>
       </c>
       <c r="E54" s="7">
-        <v>1.75</v>
+        <v>0.62</v>
       </c>
     </row>
     <row r="55" spans="1:5">
@@ -2690,13 +2690,13 @@
         <v>31</v>
       </c>
       <c r="C55" s="5">
-        <v>-43.61</v>
+        <v>13.03</v>
       </c>
       <c r="D55" s="5">
-        <v>13.03</v>
+        <v>146.13</v>
       </c>
       <c r="E55" s="7">
-        <v>56.64</v>
+        <v>133.1</v>
       </c>
     </row>
     <row r="56" spans="1:5">
@@ -2707,13 +2707,13 @@
         <v>31</v>
       </c>
       <c r="C56" s="5">
-        <v>-67.02</v>
+        <v>-54.79</v>
       </c>
       <c r="D56" s="5">
-        <v>-54.79</v>
+        <v>10.68</v>
       </c>
       <c r="E56" s="7">
-        <v>12.23</v>
+        <v>65.47</v>
       </c>
     </row>
     <row r="57" spans="1:5">
@@ -2724,13 +2724,13 @@
         <v>31</v>
       </c>
       <c r="C57" s="5">
-        <v>-7.62</v>
+        <v>-12.03</v>
       </c>
       <c r="D57" s="5">
-        <v>-12.03</v>
-      </c>
-      <c r="E57" s="6">
-        <v>-4.41</v>
+        <v>217.44</v>
+      </c>
+      <c r="E57" s="7">
+        <v>229.47</v>
       </c>
     </row>
     <row r="58" spans="1:5">
@@ -2741,13 +2741,13 @@
         <v>31</v>
       </c>
       <c r="C58" s="5">
-        <v>126.8</v>
+        <v>-19.44</v>
       </c>
       <c r="D58" s="5">
-        <v>-19.44</v>
-      </c>
-      <c r="E58" s="6">
-        <v>-146.24</v>
+        <v>27.93</v>
+      </c>
+      <c r="E58" s="7">
+        <v>47.37</v>
       </c>
     </row>
     <row r="59" spans="1:5">
@@ -2758,13 +2758,13 @@
         <v>31</v>
       </c>
       <c r="C59" s="5">
-        <v>-4.66</v>
+        <v>-28.52</v>
       </c>
       <c r="D59" s="5">
-        <v>-28.52</v>
-      </c>
-      <c r="E59" s="6">
-        <v>-23.86</v>
+        <v>51.72</v>
+      </c>
+      <c r="E59" s="7">
+        <v>80.23999999999999</v>
       </c>
     </row>
     <row r="60" spans="1:5">
@@ -2775,13 +2775,13 @@
         <v>31</v>
       </c>
       <c r="C60" s="5">
-        <v>-6.76</v>
+        <v>29.1</v>
       </c>
       <c r="D60" s="5">
-        <v>29.1</v>
+        <v>41.38</v>
       </c>
       <c r="E60" s="7">
-        <v>35.86</v>
+        <v>12.28</v>
       </c>
     </row>
     <row r="61" spans="1:5">
@@ -2792,13 +2792,13 @@
         <v>31</v>
       </c>
       <c r="C61" s="5">
-        <v>340.67</v>
+        <v>431.13</v>
       </c>
       <c r="D61" s="5">
-        <v>431.13</v>
-      </c>
-      <c r="E61" s="7">
-        <v>90.45999999999999</v>
+        <v>119.63</v>
+      </c>
+      <c r="E61" s="6">
+        <v>-311.5</v>
       </c>
     </row>
   </sheetData>
@@ -2857,22 +2857,22 @@
         <v>44</v>
       </c>
       <c r="B2" s="10">
-        <v>60.8</v>
+        <v>48.8</v>
       </c>
       <c r="C2" s="11">
         <v>7</v>
       </c>
       <c r="D2" s="10">
-        <v>42.5</v>
+        <v>41.6</v>
       </c>
       <c r="E2" s="10">
-        <v>70</v>
+        <v>40</v>
       </c>
       <c r="F2" s="10">
-        <v>-1</v>
+        <v>-2.4</v>
       </c>
       <c r="G2" s="10">
-        <v>2.8</v>
+        <v>1.2</v>
       </c>
       <c r="H2" s="10">
         <v>57</v>
@@ -3003,25 +3003,25 @@
     </row>
     <row r="2" spans="1:7">
       <c r="A2" s="13">
-        <v>0.2589</v>
+        <v>0.2546</v>
       </c>
       <c r="B2" s="13">
-        <v>0.1889</v>
+        <v>0.1888</v>
       </c>
       <c r="C2" s="13">
-        <v>0.153</v>
+        <v>0.1591</v>
       </c>
       <c r="D2" s="13">
-        <v>0.06269999999999999</v>
+        <v>0.0653</v>
       </c>
       <c r="E2" s="13">
-        <v>0.0588</v>
+        <v>0.0572</v>
       </c>
       <c r="F2" s="13">
-        <v>0.0001</v>
+        <v>0.0003</v>
       </c>
       <c r="G2" s="13">
-        <v>-0.2439</v>
+        <v>-0.2431</v>
       </c>
     </row>
   </sheetData>

--- a/BAJAJ_GROUP_Technical_Metrics.xlsx
+++ b/BAJAJ_GROUP_Technical_Metrics.xlsx
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="251" uniqueCount="64">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="268" uniqueCount="71">
   <si>
     <t>Symbol</t>
   </si>
@@ -157,12 +157,12 @@
     <t>Unknown</t>
   </si>
   <si>
+    <t>No</t>
+  </si>
+  <si>
     <t>Yes</t>
   </si>
   <si>
-    <t>No</t>
-  </si>
-  <si>
     <t>DOWN</t>
   </si>
   <si>
@@ -172,7 +172,28 @@
     <t>▶  SIGNAL EVENTS (vs Previous Run)</t>
   </si>
   <si>
-    <t>No signal events detected since last run.</t>
+    <t>Signal</t>
+  </si>
+  <si>
+    <t>Change</t>
+  </si>
+  <si>
+    <t>Direction</t>
+  </si>
+  <si>
+    <t>Prev Value</t>
+  </si>
+  <si>
+    <t>Curr Value</t>
+  </si>
+  <si>
+    <t>Yes → No</t>
+  </si>
+  <si>
+    <t>🔴 BEARISH</t>
+  </si>
+  <si>
+    <t>20 DMA &gt; 50 DMA</t>
   </si>
   <si>
     <t>▶  NUMERIC METRIC CHANGES (vs Previous Run)</t>
@@ -374,14 +395,15 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="14">
+  <cellXfs count="15">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="2" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="3" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
+    <xf numFmtId="0" fontId="4" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1"/>
     <xf numFmtId="165" fontId="4" fillId="5" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="165" fontId="5" fillId="6" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
@@ -896,10 +918,10 @@
         <v>44</v>
       </c>
       <c r="C2">
-        <v>10811</v>
+        <v>10874</v>
       </c>
       <c r="D2">
-        <v>-1.93</v>
+        <v>0.58</v>
       </c>
       <c r="E2">
         <v>12361</v>
@@ -908,97 +930,97 @@
         <v>8506.780000000001</v>
       </c>
       <c r="G2">
-        <v>-12.54</v>
+        <v>-12.03</v>
       </c>
       <c r="H2">
-        <v>27.09</v>
+        <v>27.83</v>
       </c>
       <c r="I2">
-        <v>-4.86</v>
+        <v>-4.61</v>
       </c>
       <c r="J2">
-        <v>-9.23</v>
+        <v>-10.35</v>
       </c>
       <c r="K2">
-        <v>9.85</v>
+        <v>10.32</v>
       </c>
       <c r="L2">
-        <v>24.03</v>
+        <v>24.7</v>
       </c>
       <c r="M2">
-        <v>25.46</v>
+        <v>26.04</v>
       </c>
       <c r="N2">
         <v>71</v>
       </c>
       <c r="O2">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="P2">
-        <v>11144.8</v>
+        <v>11039.6</v>
       </c>
       <c r="Q2">
-        <v>11586.2</v>
+        <v>11511.85</v>
       </c>
       <c r="R2">
-        <v>11580.73</v>
+        <v>11590.14</v>
       </c>
       <c r="S2">
-        <v>10124.48</v>
+        <v>10134.21</v>
       </c>
       <c r="T2">
-        <v>6.78</v>
+        <v>7.3</v>
       </c>
       <c r="U2" t="s">
         <v>45</v>
       </c>
       <c r="V2" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="W2" t="s">
         <v>45</v>
       </c>
       <c r="X2">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="Y2">
-        <v>30.48</v>
+        <v>32.99</v>
       </c>
       <c r="Z2">
-        <v>-151.95</v>
+        <v>-175.63</v>
       </c>
       <c r="AA2">
-        <v>-53.33</v>
+        <v>-77.79000000000001</v>
       </c>
       <c r="AB2">
-        <v>-98.62</v>
+        <v>-97.83</v>
       </c>
       <c r="AC2">
-        <v>5.45</v>
+        <v>3.93</v>
       </c>
       <c r="AD2">
-        <v>6.45</v>
+        <v>4.94</v>
       </c>
       <c r="AE2">
-        <v>205.68</v>
+        <v>203.42</v>
       </c>
       <c r="AF2">
-        <v>146.13</v>
+        <v>38.15</v>
       </c>
       <c r="AG2">
-        <v>12333.16</v>
+        <v>12229.54</v>
       </c>
       <c r="AH2">
-        <v>10839.24</v>
+        <v>10794.16</v>
       </c>
       <c r="AI2">
-        <v>11529.55</v>
+        <v>11476.26</v>
       </c>
       <c r="AJ2" t="s">
         <v>47</v>
       </c>
       <c r="AK2">
-        <v>55.89</v>
+        <v>59.8</v>
       </c>
     </row>
     <row r="3" spans="1:37">
@@ -1009,10 +1031,10 @@
         <v>44</v>
       </c>
       <c r="C3">
-        <v>493</v>
+        <v>495.55</v>
       </c>
       <c r="D3">
-        <v>2.7</v>
+        <v>0.52</v>
       </c>
       <c r="E3">
         <v>670.25</v>
@@ -1021,25 +1043,25 @@
         <v>232.89</v>
       </c>
       <c r="G3">
-        <v>-26.45</v>
+        <v>-26.06</v>
       </c>
       <c r="H3">
-        <v>111.69</v>
+        <v>112.78</v>
       </c>
       <c r="I3">
-        <v>-4.04</v>
+        <v>-2.04</v>
       </c>
       <c r="J3">
-        <v>3.26</v>
+        <v>4.54</v>
       </c>
       <c r="K3">
-        <v>-19.78</v>
+        <v>-19.02</v>
       </c>
       <c r="L3">
-        <v>100.05</v>
+        <v>103.11</v>
       </c>
       <c r="M3">
-        <v>15.91</v>
+        <v>16.4</v>
       </c>
       <c r="N3">
         <v>99</v>
@@ -1048,61 +1070,61 @@
         <v>89</v>
       </c>
       <c r="P3">
-        <v>496.02</v>
+        <v>493.96</v>
       </c>
       <c r="Q3">
-        <v>505.76</v>
+        <v>506.93</v>
       </c>
       <c r="R3">
-        <v>509.69</v>
+        <v>509.09</v>
       </c>
       <c r="S3">
-        <v>449.72</v>
+        <v>450.92</v>
       </c>
       <c r="T3">
-        <v>9.619999999999999</v>
+        <v>9.9</v>
       </c>
       <c r="U3" t="s">
+        <v>45</v>
+      </c>
+      <c r="V3" t="s">
         <v>46</v>
       </c>
-      <c r="V3" t="s">
+      <c r="W3" t="s">
         <v>45</v>
-      </c>
-      <c r="W3" t="s">
-        <v>46</v>
       </c>
       <c r="X3">
         <v>2</v>
       </c>
       <c r="Y3">
-        <v>45.21</v>
+        <v>46.36</v>
       </c>
       <c r="Z3">
-        <v>-3.5</v>
+        <v>-3.65</v>
       </c>
       <c r="AA3">
-        <v>-2.24</v>
+        <v>-2.52</v>
       </c>
       <c r="AB3">
-        <v>-1.26</v>
+        <v>-1.13</v>
       </c>
       <c r="AC3">
-        <v>12.16</v>
+        <v>26.6</v>
       </c>
       <c r="AD3">
-        <v>8.18</v>
+        <v>13.69</v>
       </c>
       <c r="AE3">
-        <v>19.72</v>
+        <v>19.09</v>
       </c>
       <c r="AF3">
-        <v>10.68</v>
+        <v>-70.44</v>
       </c>
       <c r="AG3">
-        <v>535.4299999999999</v>
+        <v>532.55</v>
       </c>
       <c r="AH3">
-        <v>476.08</v>
+        <v>481.32</v>
       </c>
       <c r="AI3">
         <v>460.99</v>
@@ -1111,7 +1133,7 @@
         <v>48</v>
       </c>
       <c r="AK3">
-        <v>25.96</v>
+        <v>26.88</v>
       </c>
     </row>
     <row r="4" spans="1:37">
@@ -1122,100 +1144,100 @@
         <v>44</v>
       </c>
       <c r="C4">
-        <v>309.85</v>
+        <v>303.4</v>
       </c>
       <c r="D4">
-        <v>-1.53</v>
+        <v>-2.08</v>
       </c>
       <c r="E4">
-        <v>564.95</v>
+        <v>554.95</v>
       </c>
       <c r="F4">
-        <v>303.75</v>
+        <v>303.4</v>
       </c>
       <c r="G4">
-        <v>-45.15</v>
+        <v>-45.33</v>
       </c>
       <c r="H4">
-        <v>2.01</v>
+        <v>0</v>
       </c>
       <c r="I4">
-        <v>-4.2</v>
+        <v>-7.89</v>
       </c>
       <c r="J4">
-        <v>-6.88</v>
+        <v>-6.59</v>
       </c>
       <c r="K4">
-        <v>-3.11</v>
+        <v>-8.119999999999999</v>
       </c>
       <c r="L4">
-        <v>-47.46</v>
+        <v>-46.3</v>
       </c>
       <c r="M4">
-        <v>-24.31</v>
+        <v>-24.2</v>
       </c>
       <c r="N4">
         <v>15</v>
       </c>
       <c r="O4">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="P4">
-        <v>318.86</v>
+        <v>313.66</v>
       </c>
       <c r="Q4">
-        <v>327.64</v>
+        <v>326.51</v>
       </c>
       <c r="R4">
-        <v>338.1</v>
+        <v>337.51</v>
       </c>
       <c r="S4">
-        <v>369.76</v>
+        <v>368.9</v>
       </c>
       <c r="T4">
-        <v>-16.2</v>
+        <v>-17.76</v>
       </c>
       <c r="U4" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="V4" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="W4" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="X4">
         <v>0</v>
       </c>
       <c r="Y4">
-        <v>33.54</v>
+        <v>30.23</v>
       </c>
       <c r="Z4">
-        <v>-6.44</v>
+        <v>-7.48</v>
       </c>
       <c r="AA4">
-        <v>-4.91</v>
+        <v>-5.43</v>
       </c>
       <c r="AB4">
-        <v>-1.53</v>
+        <v>-2.06</v>
       </c>
       <c r="AC4">
-        <v>1.86</v>
+        <v>0</v>
       </c>
       <c r="AD4">
-        <v>12.47</v>
+        <v>3.21</v>
       </c>
       <c r="AE4">
-        <v>9.51</v>
+        <v>9.75</v>
       </c>
       <c r="AF4">
-        <v>217.44</v>
+        <v>29.63</v>
       </c>
       <c r="AG4">
-        <v>344.93</v>
+        <v>346.93</v>
       </c>
       <c r="AH4">
-        <v>310.35</v>
+        <v>306.1</v>
       </c>
       <c r="AI4">
         <v>337.22</v>
@@ -1224,7 +1246,7 @@
         <v>47</v>
       </c>
       <c r="AK4">
-        <v>21.15</v>
+        <v>25.96</v>
       </c>
     </row>
     <row r="5" spans="1:37">
@@ -1235,10 +1257,10 @@
         <v>44</v>
       </c>
       <c r="C5">
-        <v>1742.4</v>
+        <v>1731</v>
       </c>
       <c r="D5">
-        <v>-0.55</v>
+        <v>-0.65</v>
       </c>
       <c r="E5">
         <v>2176.6</v>
@@ -1247,97 +1269,97 @@
         <v>1631.8</v>
       </c>
       <c r="G5">
-        <v>-19.95</v>
+        <v>-20.47</v>
       </c>
       <c r="H5">
-        <v>6.78</v>
+        <v>6.08</v>
       </c>
       <c r="I5">
-        <v>-4.44</v>
+        <v>-6.26</v>
       </c>
       <c r="J5">
-        <v>-12.97</v>
+        <v>-14.35</v>
       </c>
       <c r="K5">
-        <v>-3.07</v>
+        <v>-6.72</v>
       </c>
       <c r="L5">
-        <v>-15.79</v>
+        <v>-14.96</v>
       </c>
       <c r="M5">
-        <v>0.03</v>
+        <v>-0.5</v>
       </c>
       <c r="N5">
         <v>29</v>
       </c>
       <c r="O5">
-        <v>43</v>
+        <v>39</v>
       </c>
       <c r="P5">
-        <v>1774.84</v>
+        <v>1751.74</v>
       </c>
       <c r="Q5">
-        <v>1876.67</v>
+        <v>1864.62</v>
       </c>
       <c r="R5">
-        <v>1947.91</v>
+        <v>1944.52</v>
       </c>
       <c r="S5">
-        <v>1888.11</v>
+        <v>1886.43</v>
       </c>
       <c r="T5">
-        <v>-7.72</v>
+        <v>-8.24</v>
       </c>
       <c r="U5" t="s">
+        <v>45</v>
+      </c>
+      <c r="V5" t="s">
         <v>46</v>
       </c>
-      <c r="V5" t="s">
+      <c r="W5" t="s">
         <v>45</v>
-      </c>
-      <c r="W5" t="s">
-        <v>46</v>
       </c>
       <c r="X5">
         <v>1</v>
       </c>
       <c r="Y5">
-        <v>25.68</v>
+        <v>24.67</v>
       </c>
       <c r="Z5">
-        <v>-56.08</v>
+        <v>-58.97</v>
       </c>
       <c r="AA5">
-        <v>-41.17</v>
+        <v>-44.73</v>
       </c>
       <c r="AB5">
-        <v>-14.91</v>
+        <v>-14.24</v>
       </c>
       <c r="AC5">
-        <v>4.92</v>
+        <v>0.66</v>
       </c>
       <c r="AD5">
-        <v>8.279999999999999</v>
+        <v>3.5</v>
       </c>
       <c r="AE5">
-        <v>37.08</v>
+        <v>37.71</v>
       </c>
       <c r="AF5">
-        <v>27.93</v>
+        <v>58.48</v>
       </c>
       <c r="AG5">
-        <v>2038.72</v>
+        <v>2032.56</v>
       </c>
       <c r="AH5">
-        <v>1714.62</v>
+        <v>1696.68</v>
       </c>
       <c r="AI5">
-        <v>1855.63</v>
+        <v>1838.17</v>
       </c>
       <c r="AJ5" t="s">
         <v>47</v>
       </c>
       <c r="AK5">
-        <v>75.66</v>
+        <v>77.70999999999999</v>
       </c>
     </row>
     <row r="6" spans="1:37">
@@ -1348,10 +1370,10 @@
         <v>44</v>
       </c>
       <c r="C6">
-        <v>10600</v>
+        <v>10788</v>
       </c>
       <c r="D6">
-        <v>-1.85</v>
+        <v>1.77</v>
       </c>
       <c r="E6">
         <v>13144</v>
@@ -1360,97 +1382,97 @@
         <v>8746</v>
       </c>
       <c r="G6">
-        <v>-19.35</v>
+        <v>-17.92</v>
       </c>
       <c r="H6">
-        <v>21.2</v>
+        <v>23.35</v>
       </c>
       <c r="I6">
-        <v>-5.23</v>
+        <v>-5.77</v>
       </c>
       <c r="J6">
-        <v>-6.53</v>
+        <v>-7.35</v>
       </c>
       <c r="K6">
-        <v>-1.11</v>
+        <v>-0.64</v>
       </c>
       <c r="L6">
-        <v>-19.72</v>
+        <v>-16.37</v>
       </c>
       <c r="M6">
-        <v>18.88</v>
+        <v>18.82</v>
       </c>
       <c r="N6">
         <v>43</v>
       </c>
       <c r="O6">
-        <v>44</v>
+        <v>46</v>
       </c>
       <c r="P6">
-        <v>10941.2</v>
+        <v>10809</v>
       </c>
       <c r="Q6">
-        <v>11078.25</v>
+        <v>11052.15</v>
       </c>
       <c r="R6">
-        <v>11171.58</v>
+        <v>11178.42</v>
       </c>
       <c r="S6">
-        <v>10678.06</v>
+        <v>10677.08</v>
       </c>
       <c r="T6">
-        <v>-0.73</v>
+        <v>1.04</v>
       </c>
       <c r="U6" t="s">
+        <v>45</v>
+      </c>
+      <c r="V6" t="s">
         <v>46</v>
       </c>
-      <c r="V6" t="s">
+      <c r="W6" t="s">
         <v>45</v>
       </c>
-      <c r="W6" t="s">
-        <v>46</v>
-      </c>
       <c r="X6">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="Y6">
-        <v>38.48</v>
+        <v>43.44</v>
       </c>
       <c r="Z6">
-        <v>-84.31999999999999</v>
+        <v>-95.63</v>
       </c>
       <c r="AA6">
-        <v>-30.64</v>
+        <v>-43.63</v>
       </c>
       <c r="AB6">
-        <v>-53.69</v>
+        <v>-51.99</v>
       </c>
       <c r="AC6">
-        <v>4.94</v>
+        <v>8.99</v>
       </c>
       <c r="AD6">
-        <v>18.29</v>
+        <v>7.49</v>
       </c>
       <c r="AE6">
-        <v>252.38</v>
+        <v>248.99</v>
       </c>
       <c r="AF6">
-        <v>51.72</v>
+        <v>-9.91</v>
       </c>
       <c r="AG6">
-        <v>11481.76</v>
+        <v>11460.04</v>
       </c>
       <c r="AH6">
-        <v>10674.74</v>
+        <v>10644.26</v>
       </c>
       <c r="AI6">
-        <v>11493.63</v>
+        <v>11476.98</v>
       </c>
       <c r="AJ6" t="s">
         <v>47</v>
       </c>
       <c r="AK6">
-        <v>26.19</v>
+        <v>29.09</v>
       </c>
     </row>
     <row r="7" spans="1:37">
@@ -1461,10 +1483,10 @@
         <v>44</v>
       </c>
       <c r="C7">
-        <v>973.8</v>
+        <v>959.4</v>
       </c>
       <c r="D7">
-        <v>-1.14</v>
+        <v>-1.48</v>
       </c>
       <c r="E7">
         <v>1158.8</v>
@@ -1473,97 +1495,97 @@
         <v>801.55</v>
       </c>
       <c r="G7">
-        <v>-15.96</v>
+        <v>-17.21</v>
       </c>
       <c r="H7">
-        <v>21.49</v>
+        <v>19.69</v>
       </c>
       <c r="I7">
-        <v>-3.47</v>
+        <v>-8.029999999999999</v>
       </c>
       <c r="J7">
-        <v>-9.82</v>
+        <v>-9.23</v>
       </c>
       <c r="K7">
-        <v>-4.05</v>
+        <v>-5.79</v>
       </c>
       <c r="L7">
-        <v>-5.43</v>
+        <v>-5.27</v>
       </c>
       <c r="M7">
-        <v>5.72</v>
+        <v>4.98</v>
       </c>
       <c r="N7">
         <v>57</v>
       </c>
       <c r="O7">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="P7">
-        <v>996.1799999999999</v>
+        <v>979.42</v>
       </c>
       <c r="Q7">
-        <v>1026.62</v>
+        <v>1021.9</v>
       </c>
       <c r="R7">
-        <v>1062.69</v>
+        <v>1060.49</v>
       </c>
       <c r="S7">
-        <v>976.9</v>
+        <v>976.66</v>
       </c>
       <c r="T7">
-        <v>-0.32</v>
+        <v>-1.77</v>
       </c>
       <c r="U7" t="s">
+        <v>45</v>
+      </c>
+      <c r="V7" t="s">
         <v>46</v>
       </c>
-      <c r="V7" t="s">
+      <c r="W7" t="s">
         <v>45</v>
-      </c>
-      <c r="W7" t="s">
-        <v>46</v>
       </c>
       <c r="X7">
         <v>1</v>
       </c>
       <c r="Y7">
-        <v>36.26</v>
+        <v>33.9</v>
       </c>
       <c r="Z7">
-        <v>-20.76</v>
+        <v>-23.18</v>
       </c>
       <c r="AA7">
-        <v>-15.83</v>
+        <v>-17.3</v>
       </c>
       <c r="AB7">
-        <v>-4.93</v>
+        <v>-5.88</v>
       </c>
       <c r="AC7">
-        <v>40.32</v>
+        <v>28.5</v>
       </c>
       <c r="AD7">
-        <v>46.91</v>
+        <v>36.34</v>
       </c>
       <c r="AE7">
-        <v>24.79</v>
+        <v>24.86</v>
       </c>
       <c r="AF7">
-        <v>41.38</v>
+        <v>5.48</v>
       </c>
       <c r="AG7">
-        <v>1082.23</v>
+        <v>1083.48</v>
       </c>
       <c r="AH7">
-        <v>971.01</v>
+        <v>960.3099999999999</v>
       </c>
       <c r="AI7">
-        <v>1044.92</v>
+        <v>1043.22</v>
       </c>
       <c r="AJ7" t="s">
         <v>47</v>
       </c>
       <c r="AK7">
-        <v>42.94</v>
+        <v>45.56</v>
       </c>
     </row>
     <row r="8" spans="1:37">
@@ -1574,13 +1596,13 @@
         <v>44</v>
       </c>
       <c r="C8">
-        <v>172.49</v>
+        <v>180.13</v>
       </c>
       <c r="D8">
-        <v>0.85</v>
+        <v>4.43</v>
       </c>
       <c r="E8">
-        <v>172.49</v>
+        <v>180.13</v>
       </c>
       <c r="F8">
         <v>115.96</v>
@@ -1589,94 +1611,94 @@
         <v>0</v>
       </c>
       <c r="H8">
-        <v>48.75</v>
+        <v>55.34</v>
       </c>
       <c r="I8">
-        <v>21.98</v>
+        <v>14.65</v>
       </c>
       <c r="J8">
-        <v>25.66</v>
+        <v>31.12</v>
       </c>
       <c r="K8">
-        <v>30.01</v>
+        <v>35.48</v>
       </c>
       <c r="L8">
-        <v>27.32</v>
+        <v>34.2</v>
       </c>
       <c r="M8">
-        <v>6.53</v>
+        <v>6.8</v>
       </c>
       <c r="N8">
         <v>85</v>
       </c>
       <c r="O8">
-        <v>87</v>
+        <v>90</v>
       </c>
       <c r="P8">
-        <v>164.59</v>
+        <v>169.19</v>
       </c>
       <c r="Q8">
-        <v>143.69</v>
+        <v>145.89</v>
       </c>
       <c r="R8">
-        <v>140.77</v>
+        <v>141.45</v>
       </c>
       <c r="S8">
-        <v>134.7</v>
+        <v>134.94</v>
       </c>
       <c r="T8">
-        <v>28.06</v>
+        <v>33.49</v>
       </c>
       <c r="U8" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="V8" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="W8" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="X8">
         <v>3</v>
       </c>
       <c r="Y8">
-        <v>81.28</v>
+        <v>84.12</v>
       </c>
       <c r="Z8">
-        <v>7.41</v>
+        <v>8.99</v>
       </c>
       <c r="AA8">
-        <v>3.34</v>
+        <v>4.47</v>
       </c>
       <c r="AB8">
-        <v>4.08</v>
+        <v>4.52</v>
       </c>
       <c r="AC8">
         <v>100</v>
       </c>
       <c r="AD8">
-        <v>97.48</v>
+        <v>98.73999999999999</v>
       </c>
       <c r="AE8">
-        <v>6.48</v>
+        <v>6.9</v>
       </c>
       <c r="AF8">
-        <v>119.63</v>
+        <v>249.72</v>
       </c>
       <c r="AG8">
-        <v>169.97</v>
+        <v>176.51</v>
       </c>
       <c r="AH8">
-        <v>117.41</v>
+        <v>115.28</v>
       </c>
       <c r="AI8">
-        <v>151.8</v>
+        <v>158.84</v>
       </c>
       <c r="AJ8" t="s">
         <v>48</v>
       </c>
       <c r="AK8">
-        <v>48.26</v>
+        <v>52.12</v>
       </c>
     </row>
   </sheetData>
@@ -1817,7 +1839,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:F61"/>
+  <dimension ref="A1:F62"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="16.7109375" customWidth="1"/>
@@ -1837,974 +1859,1029 @@
     </row>
     <row r="2" spans="1:6">
       <c r="A2" s="3" t="s">
+        <v>0</v>
+      </c>
+      <c r="B2" s="3" t="s">
         <v>50</v>
       </c>
-    </row>
-    <row r="5" spans="1:6">
-      <c r="A5" s="2" t="s">
+      <c r="C2" s="3" t="s">
         <v>51</v>
       </c>
-      <c r="B5" s="2"/>
-      <c r="C5" s="2"/>
-      <c r="D5" s="2"/>
-      <c r="E5" s="2"/>
+      <c r="D2" s="3" t="s">
+        <v>52</v>
+      </c>
+      <c r="E2" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="F2" s="3" t="s">
+        <v>54</v>
+      </c>
+    </row>
+    <row r="3" spans="1:6">
+      <c r="A3" s="4" t="s">
+        <v>37</v>
+      </c>
+      <c r="B3" s="4" t="s">
+        <v>22</v>
+      </c>
+      <c r="C3" s="4" t="s">
+        <v>55</v>
+      </c>
+      <c r="D3" s="4" t="s">
+        <v>56</v>
+      </c>
+      <c r="E3" s="4" t="s">
+        <v>46</v>
+      </c>
+      <c r="F3" s="4" t="s">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="4" spans="1:6">
+      <c r="A4" s="4" t="s">
+        <v>37</v>
+      </c>
+      <c r="B4" s="4" t="s">
+        <v>57</v>
+      </c>
+      <c r="C4" s="4" t="s">
+        <v>55</v>
+      </c>
+      <c r="D4" s="4" t="s">
+        <v>56</v>
+      </c>
+      <c r="E4" s="4" t="s">
+        <v>46</v>
+      </c>
+      <c r="F4" s="4" t="s">
+        <v>45</v>
+      </c>
     </row>
     <row r="6" spans="1:6">
-      <c r="A6" s="4" t="s">
-        <v>0</v>
-      </c>
-      <c r="B6" s="4" t="s">
-        <v>52</v>
-      </c>
-      <c r="C6" s="4" t="s">
-        <v>53</v>
-      </c>
-      <c r="D6" s="4" t="s">
-        <v>54</v>
-      </c>
-      <c r="E6" s="4" t="s">
-        <v>55</v>
-      </c>
+      <c r="A6" s="2" t="s">
+        <v>58</v>
+      </c>
+      <c r="B6" s="2"/>
+      <c r="C6" s="2"/>
+      <c r="D6" s="2"/>
+      <c r="E6" s="2"/>
     </row>
     <row r="7" spans="1:6">
       <c r="A7" s="3" t="s">
+        <v>0</v>
+      </c>
+      <c r="B7" s="3" t="s">
+        <v>59</v>
+      </c>
+      <c r="C7" s="3" t="s">
+        <v>60</v>
+      </c>
+      <c r="D7" s="3" t="s">
+        <v>61</v>
+      </c>
+      <c r="E7" s="3" t="s">
+        <v>62</v>
+      </c>
+    </row>
+    <row r="8" spans="1:6">
+      <c r="A8" s="5" t="s">
         <v>37</v>
       </c>
-      <c r="B7" s="3" t="s">
+      <c r="B8" s="5" t="s">
         <v>9</v>
       </c>
-      <c r="C7" s="5">
-        <v>-5.94</v>
-      </c>
-      <c r="D7" s="5">
+      <c r="C8" s="6">
         <v>-9.23</v>
       </c>
-      <c r="E7" s="6">
-        <v>-3.29</v>
-      </c>
-    </row>
-    <row r="8" spans="1:6">
-      <c r="A8" s="3" t="s">
+      <c r="D8" s="6">
+        <v>-10.35</v>
+      </c>
+      <c r="E8" s="7">
+        <v>-1.12</v>
+      </c>
+    </row>
+    <row r="9" spans="1:6">
+      <c r="A9" s="5" t="s">
         <v>38</v>
       </c>
-      <c r="B8" s="3" t="s">
+      <c r="B9" s="5" t="s">
         <v>9</v>
       </c>
-      <c r="C8" s="5">
-        <v>6.54</v>
-      </c>
-      <c r="D8" s="5">
+      <c r="C9" s="6">
         <v>3.26</v>
       </c>
-      <c r="E8" s="6">
-        <v>-3.28</v>
-      </c>
-    </row>
-    <row r="9" spans="1:6">
-      <c r="A9" s="3" t="s">
+      <c r="D9" s="6">
+        <v>4.54</v>
+      </c>
+      <c r="E9" s="8">
+        <v>1.28</v>
+      </c>
+    </row>
+    <row r="10" spans="1:6">
+      <c r="A10" s="5" t="s">
         <v>39</v>
       </c>
-      <c r="B9" s="3" t="s">
+      <c r="B10" s="5" t="s">
         <v>9</v>
       </c>
-      <c r="C9" s="5">
-        <v>-6.02</v>
-      </c>
-      <c r="D9" s="5">
+      <c r="C10" s="6">
         <v>-6.88</v>
       </c>
-      <c r="E9" s="6">
-        <v>-0.86</v>
-      </c>
-    </row>
-    <row r="10" spans="1:6">
-      <c r="A10" s="3" t="s">
+      <c r="D10" s="6">
+        <v>-6.59</v>
+      </c>
+      <c r="E10" s="8">
+        <v>0.29</v>
+      </c>
+    </row>
+    <row r="11" spans="1:6">
+      <c r="A11" s="5" t="s">
         <v>40</v>
       </c>
-      <c r="B10" s="3" t="s">
+      <c r="B11" s="5" t="s">
         <v>9</v>
       </c>
-      <c r="C10" s="5">
-        <v>-12.88</v>
-      </c>
-      <c r="D10" s="5">
+      <c r="C11" s="6">
         <v>-12.97</v>
       </c>
-      <c r="E10" s="6">
-        <v>-0.09</v>
-      </c>
-    </row>
-    <row r="11" spans="1:6">
-      <c r="A11" s="3" t="s">
+      <c r="D11" s="6">
+        <v>-14.35</v>
+      </c>
+      <c r="E11" s="7">
+        <v>-1.38</v>
+      </c>
+    </row>
+    <row r="12" spans="1:6">
+      <c r="A12" s="5" t="s">
         <v>41</v>
       </c>
-      <c r="B11" s="3" t="s">
+      <c r="B12" s="5" t="s">
         <v>9</v>
       </c>
-      <c r="C11" s="5">
-        <v>-5.25</v>
-      </c>
-      <c r="D11" s="5">
+      <c r="C12" s="6">
         <v>-6.53</v>
       </c>
-      <c r="E11" s="6">
-        <v>-1.28</v>
-      </c>
-    </row>
-    <row r="12" spans="1:6">
-      <c r="A12" s="3" t="s">
+      <c r="D12" s="6">
+        <v>-7.35</v>
+      </c>
+      <c r="E12" s="7">
+        <v>-0.82</v>
+      </c>
+    </row>
+    <row r="13" spans="1:6">
+      <c r="A13" s="5" t="s">
         <v>42</v>
       </c>
-      <c r="B12" s="3" t="s">
+      <c r="B13" s="5" t="s">
         <v>9</v>
       </c>
-      <c r="C12" s="5">
-        <v>-9.050000000000001</v>
-      </c>
-      <c r="D12" s="5">
+      <c r="C13" s="6">
         <v>-9.82</v>
       </c>
-      <c r="E12" s="6">
-        <v>-0.77</v>
-      </c>
-    </row>
-    <row r="13" spans="1:6">
-      <c r="A13" s="3" t="s">
+      <c r="D13" s="6">
+        <v>-9.23</v>
+      </c>
+      <c r="E13" s="8">
+        <v>0.59</v>
+      </c>
+    </row>
+    <row r="14" spans="1:6">
+      <c r="A14" s="5" t="s">
         <v>43</v>
       </c>
-      <c r="B13" s="3" t="s">
+      <c r="B14" s="5" t="s">
         <v>9</v>
       </c>
-      <c r="C13" s="5">
-        <v>25.52</v>
-      </c>
-      <c r="D13" s="5">
+      <c r="C14" s="6">
         <v>25.66</v>
       </c>
-      <c r="E13" s="7">
-        <v>0.14</v>
-      </c>
-    </row>
-    <row r="14" spans="1:6">
-      <c r="A14" s="3" t="s">
+      <c r="D14" s="6">
+        <v>31.12</v>
+      </c>
+      <c r="E14" s="8">
+        <v>5.46</v>
+      </c>
+    </row>
+    <row r="15" spans="1:6">
+      <c r="A15" s="5" t="s">
         <v>37</v>
       </c>
-      <c r="B14" s="3" t="s">
+      <c r="B15" s="5" t="s">
         <v>8</v>
       </c>
-      <c r="C14" s="5">
-        <v>-3.8</v>
-      </c>
-      <c r="D14" s="5">
+      <c r="C15" s="6">
         <v>-4.86</v>
       </c>
-      <c r="E14" s="6">
-        <v>-1.06</v>
-      </c>
-    </row>
-    <row r="15" spans="1:6">
-      <c r="A15" s="3" t="s">
+      <c r="D15" s="6">
+        <v>-4.61</v>
+      </c>
+      <c r="E15" s="8">
+        <v>0.25</v>
+      </c>
+    </row>
+    <row r="16" spans="1:6">
+      <c r="A16" s="5" t="s">
         <v>38</v>
       </c>
-      <c r="B15" s="3" t="s">
+      <c r="B16" s="5" t="s">
         <v>8</v>
       </c>
-      <c r="C15" s="5">
-        <v>-6.84</v>
-      </c>
-      <c r="D15" s="5">
+      <c r="C16" s="6">
         <v>-4.04</v>
       </c>
-      <c r="E15" s="7">
-        <v>2.8</v>
-      </c>
-    </row>
-    <row r="16" spans="1:6">
-      <c r="A16" s="3" t="s">
+      <c r="D16" s="6">
+        <v>-2.04</v>
+      </c>
+      <c r="E16" s="8">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="17" spans="1:5">
+      <c r="A17" s="5" t="s">
         <v>39</v>
       </c>
-      <c r="B16" s="3" t="s">
+      <c r="B17" s="5" t="s">
         <v>8</v>
       </c>
-      <c r="C16" s="5">
-        <v>-3.48</v>
-      </c>
-      <c r="D16" s="5">
+      <c r="C17" s="6">
         <v>-4.2</v>
       </c>
-      <c r="E16" s="6">
-        <v>-0.72</v>
-      </c>
-    </row>
-    <row r="17" spans="1:5">
-      <c r="A17" s="3" t="s">
+      <c r="D17" s="6">
+        <v>-7.89</v>
+      </c>
+      <c r="E17" s="7">
+        <v>-3.69</v>
+      </c>
+    </row>
+    <row r="18" spans="1:5">
+      <c r="A18" s="5" t="s">
         <v>40</v>
       </c>
-      <c r="B17" s="3" t="s">
+      <c r="B18" s="5" t="s">
         <v>8</v>
       </c>
-      <c r="C17" s="5">
-        <v>-5.29</v>
-      </c>
-      <c r="D17" s="5">
+      <c r="C18" s="6">
         <v>-4.44</v>
       </c>
-      <c r="E17" s="7">
-        <v>0.85</v>
-      </c>
-    </row>
-    <row r="18" spans="1:5">
-      <c r="A18" s="3" t="s">
+      <c r="D18" s="6">
+        <v>-6.26</v>
+      </c>
+      <c r="E18" s="7">
+        <v>-1.82</v>
+      </c>
+    </row>
+    <row r="19" spans="1:5">
+      <c r="A19" s="5" t="s">
         <v>41</v>
       </c>
-      <c r="B18" s="3" t="s">
+      <c r="B19" s="5" t="s">
         <v>8</v>
       </c>
-      <c r="C18" s="5">
-        <v>-5.34</v>
-      </c>
-      <c r="D18" s="5">
+      <c r="C19" s="6">
         <v>-5.23</v>
       </c>
-      <c r="E18" s="7">
-        <v>0.11</v>
-      </c>
-    </row>
-    <row r="19" spans="1:5">
-      <c r="A19" s="3" t="s">
+      <c r="D19" s="6">
+        <v>-5.77</v>
+      </c>
+      <c r="E19" s="7">
+        <v>-0.54</v>
+      </c>
+    </row>
+    <row r="20" spans="1:5">
+      <c r="A20" s="5" t="s">
         <v>42</v>
       </c>
-      <c r="B19" s="3" t="s">
+      <c r="B20" s="5" t="s">
         <v>8</v>
       </c>
-      <c r="C19" s="5">
-        <v>-3.55</v>
-      </c>
-      <c r="D19" s="5">
+      <c r="C20" s="6">
         <v>-3.47</v>
       </c>
-      <c r="E19" s="7">
-        <v>0.08</v>
-      </c>
-    </row>
-    <row r="20" spans="1:5">
-      <c r="A20" s="3" t="s">
+      <c r="D20" s="6">
+        <v>-8.029999999999999</v>
+      </c>
+      <c r="E20" s="7">
+        <v>-4.56</v>
+      </c>
+    </row>
+    <row r="21" spans="1:5">
+      <c r="A21" s="5" t="s">
         <v>43</v>
       </c>
-      <c r="B20" s="3" t="s">
+      <c r="B21" s="5" t="s">
         <v>8</v>
       </c>
-      <c r="C20" s="5">
-        <v>25.73</v>
-      </c>
-      <c r="D20" s="5">
+      <c r="C21" s="6">
         <v>21.98</v>
       </c>
-      <c r="E20" s="6">
-        <v>-3.75</v>
-      </c>
-    </row>
-    <row r="21" spans="1:5">
-      <c r="A21" s="3" t="s">
+      <c r="D21" s="6">
+        <v>14.65</v>
+      </c>
+      <c r="E21" s="7">
+        <v>-7.33</v>
+      </c>
+    </row>
+    <row r="22" spans="1:5">
+      <c r="A22" s="5" t="s">
         <v>37</v>
       </c>
-      <c r="B21" s="3" t="s">
+      <c r="B22" s="5" t="s">
         <v>11</v>
       </c>
-      <c r="C21" s="5">
-        <v>24.43</v>
-      </c>
-      <c r="D21" s="5">
+      <c r="C22" s="6">
         <v>24.03</v>
       </c>
-      <c r="E21" s="6">
-        <v>-0.4</v>
-      </c>
-    </row>
-    <row r="22" spans="1:5">
-      <c r="A22" s="3" t="s">
+      <c r="D22" s="6">
+        <v>24.7</v>
+      </c>
+      <c r="E22" s="8">
+        <v>0.67</v>
+      </c>
+    </row>
+    <row r="23" spans="1:5">
+      <c r="A23" s="5" t="s">
         <v>38</v>
       </c>
-      <c r="B22" s="3" t="s">
+      <c r="B23" s="5" t="s">
         <v>11</v>
       </c>
-      <c r="C22" s="5">
-        <v>89.12</v>
-      </c>
-      <c r="D22" s="5">
+      <c r="C23" s="6">
         <v>100.05</v>
       </c>
-      <c r="E22" s="7">
-        <v>10.93</v>
-      </c>
-    </row>
-    <row r="23" spans="1:5">
-      <c r="A23" s="3" t="s">
+      <c r="D23" s="6">
+        <v>103.11</v>
+      </c>
+      <c r="E23" s="8">
+        <v>3.06</v>
+      </c>
+    </row>
+    <row r="24" spans="1:5">
+      <c r="A24" s="5" t="s">
         <v>39</v>
       </c>
-      <c r="B23" s="3" t="s">
+      <c r="B24" s="5" t="s">
         <v>11</v>
       </c>
-      <c r="C23" s="5">
-        <v>-45.48</v>
-      </c>
-      <c r="D23" s="5">
+      <c r="C24" s="6">
         <v>-47.46</v>
       </c>
-      <c r="E23" s="6">
-        <v>-1.98</v>
-      </c>
-    </row>
-    <row r="24" spans="1:5">
-      <c r="A24" s="3" t="s">
+      <c r="D24" s="6">
+        <v>-46.3</v>
+      </c>
+      <c r="E24" s="8">
+        <v>1.16</v>
+      </c>
+    </row>
+    <row r="25" spans="1:5">
+      <c r="A25" s="5" t="s">
         <v>40</v>
       </c>
-      <c r="B24" s="3" t="s">
+      <c r="B25" s="5" t="s">
         <v>11</v>
       </c>
-      <c r="C24" s="5">
-        <v>-15.95</v>
-      </c>
-      <c r="D24" s="5">
+      <c r="C25" s="6">
         <v>-15.79</v>
       </c>
-      <c r="E24" s="7">
+      <c r="D25" s="6">
+        <v>-14.96</v>
+      </c>
+      <c r="E25" s="8">
+        <v>0.83</v>
+      </c>
+    </row>
+    <row r="26" spans="1:5">
+      <c r="A26" s="5" t="s">
+        <v>41</v>
+      </c>
+      <c r="B26" s="5" t="s">
+        <v>11</v>
+      </c>
+      <c r="C26" s="6">
+        <v>-19.72</v>
+      </c>
+      <c r="D26" s="6">
+        <v>-16.37</v>
+      </c>
+      <c r="E26" s="8">
+        <v>3.35</v>
+      </c>
+    </row>
+    <row r="27" spans="1:5">
+      <c r="A27" s="5" t="s">
+        <v>42</v>
+      </c>
+      <c r="B27" s="5" t="s">
+        <v>11</v>
+      </c>
+      <c r="C27" s="6">
+        <v>-5.43</v>
+      </c>
+      <c r="D27" s="6">
+        <v>-5.27</v>
+      </c>
+      <c r="E27" s="8">
         <v>0.16</v>
       </c>
     </row>
-    <row r="25" spans="1:5">
-      <c r="A25" s="3" t="s">
+    <row r="28" spans="1:5">
+      <c r="A28" s="5" t="s">
+        <v>43</v>
+      </c>
+      <c r="B28" s="5" t="s">
+        <v>11</v>
+      </c>
+      <c r="C28" s="6">
+        <v>27.32</v>
+      </c>
+      <c r="D28" s="6">
+        <v>34.2</v>
+      </c>
+      <c r="E28" s="8">
+        <v>6.88</v>
+      </c>
+    </row>
+    <row r="29" spans="1:5">
+      <c r="A29" s="5" t="s">
+        <v>37</v>
+      </c>
+      <c r="B29" s="5" t="s">
+        <v>10</v>
+      </c>
+      <c r="C29" s="6">
+        <v>9.85</v>
+      </c>
+      <c r="D29" s="6">
+        <v>10.32</v>
+      </c>
+      <c r="E29" s="8">
+        <v>0.47</v>
+      </c>
+    </row>
+    <row r="30" spans="1:5">
+      <c r="A30" s="5" t="s">
+        <v>38</v>
+      </c>
+      <c r="B30" s="5" t="s">
+        <v>10</v>
+      </c>
+      <c r="C30" s="6">
+        <v>-19.78</v>
+      </c>
+      <c r="D30" s="6">
+        <v>-19.02</v>
+      </c>
+      <c r="E30" s="8">
+        <v>0.76</v>
+      </c>
+    </row>
+    <row r="31" spans="1:5">
+      <c r="A31" s="5" t="s">
+        <v>39</v>
+      </c>
+      <c r="B31" s="5" t="s">
+        <v>10</v>
+      </c>
+      <c r="C31" s="6">
+        <v>-3.11</v>
+      </c>
+      <c r="D31" s="6">
+        <v>-8.119999999999999</v>
+      </c>
+      <c r="E31" s="7">
+        <v>-5.01</v>
+      </c>
+    </row>
+    <row r="32" spans="1:5">
+      <c r="A32" s="5" t="s">
+        <v>40</v>
+      </c>
+      <c r="B32" s="5" t="s">
+        <v>10</v>
+      </c>
+      <c r="C32" s="6">
+        <v>-3.07</v>
+      </c>
+      <c r="D32" s="6">
+        <v>-6.72</v>
+      </c>
+      <c r="E32" s="7">
+        <v>-3.65</v>
+      </c>
+    </row>
+    <row r="33" spans="1:5">
+      <c r="A33" s="5" t="s">
         <v>41</v>
       </c>
-      <c r="B25" s="3" t="s">
-        <v>11</v>
-      </c>
-      <c r="C25" s="5">
-        <v>-18.58</v>
-      </c>
-      <c r="D25" s="5">
-        <v>-19.72</v>
-      </c>
-      <c r="E25" s="6">
-        <v>-1.14</v>
-      </c>
-    </row>
-    <row r="26" spans="1:5">
-      <c r="A26" s="3" t="s">
+      <c r="B33" s="5" t="s">
+        <v>10</v>
+      </c>
+      <c r="C33" s="6">
+        <v>-1.11</v>
+      </c>
+      <c r="D33" s="6">
+        <v>-0.64</v>
+      </c>
+      <c r="E33" s="8">
+        <v>0.47</v>
+      </c>
+    </row>
+    <row r="34" spans="1:5">
+      <c r="A34" s="5" t="s">
         <v>42</v>
       </c>
-      <c r="B26" s="3" t="s">
-        <v>11</v>
-      </c>
-      <c r="C26" s="5">
-        <v>-3.95</v>
-      </c>
-      <c r="D26" s="5">
-        <v>-5.43</v>
-      </c>
-      <c r="E26" s="6">
-        <v>-1.48</v>
-      </c>
-    </row>
-    <row r="27" spans="1:5">
-      <c r="A27" s="3" t="s">
+      <c r="B34" s="5" t="s">
+        <v>10</v>
+      </c>
+      <c r="C34" s="6">
+        <v>-4.05</v>
+      </c>
+      <c r="D34" s="6">
+        <v>-5.79</v>
+      </c>
+      <c r="E34" s="7">
+        <v>-1.74</v>
+      </c>
+    </row>
+    <row r="35" spans="1:5">
+      <c r="A35" s="5" t="s">
         <v>43</v>
       </c>
-      <c r="B27" s="3" t="s">
-        <v>11</v>
-      </c>
-      <c r="C27" s="5">
-        <v>22.87</v>
-      </c>
-      <c r="D27" s="5">
-        <v>27.32</v>
-      </c>
-      <c r="E27" s="7">
-        <v>4.45</v>
-      </c>
-    </row>
-    <row r="28" spans="1:5">
-      <c r="A28" s="3" t="s">
+      <c r="B35" s="5" t="s">
+        <v>10</v>
+      </c>
+      <c r="C35" s="6">
+        <v>30.01</v>
+      </c>
+      <c r="D35" s="6">
+        <v>35.48</v>
+      </c>
+      <c r="E35" s="8">
+        <v>5.47</v>
+      </c>
+    </row>
+    <row r="36" spans="1:5">
+      <c r="A36" s="5" t="s">
         <v>37</v>
       </c>
-      <c r="B28" s="3" t="s">
-        <v>10</v>
-      </c>
-      <c r="C28" s="5">
-        <v>13.46</v>
-      </c>
-      <c r="D28" s="5">
-        <v>9.85</v>
-      </c>
-      <c r="E28" s="6">
-        <v>-3.61</v>
-      </c>
-    </row>
-    <row r="29" spans="1:5">
-      <c r="A29" s="3" t="s">
+      <c r="B36" s="5" t="s">
+        <v>6</v>
+      </c>
+      <c r="C36" s="6">
+        <v>-12.54</v>
+      </c>
+      <c r="D36" s="6">
+        <v>-12.03</v>
+      </c>
+      <c r="E36" s="8">
+        <v>0.51</v>
+      </c>
+    </row>
+    <row r="37" spans="1:5">
+      <c r="A37" s="5" t="s">
         <v>38</v>
       </c>
-      <c r="B29" s="3" t="s">
-        <v>10</v>
-      </c>
-      <c r="C29" s="5">
-        <v>-19.86</v>
-      </c>
-      <c r="D29" s="5">
-        <v>-19.78</v>
-      </c>
-      <c r="E29" s="7">
-        <v>0.08</v>
-      </c>
-    </row>
-    <row r="30" spans="1:5">
-      <c r="A30" s="3" t="s">
+      <c r="B37" s="5" t="s">
+        <v>6</v>
+      </c>
+      <c r="C37" s="6">
+        <v>-26.45</v>
+      </c>
+      <c r="D37" s="6">
+        <v>-26.06</v>
+      </c>
+      <c r="E37" s="8">
+        <v>0.39</v>
+      </c>
+    </row>
+    <row r="38" spans="1:5">
+      <c r="A38" s="5" t="s">
         <v>39</v>
       </c>
-      <c r="B30" s="3" t="s">
-        <v>10</v>
-      </c>
-      <c r="C30" s="5">
-        <v>-1.52</v>
-      </c>
-      <c r="D30" s="5">
-        <v>-3.11</v>
-      </c>
-      <c r="E30" s="6">
-        <v>-1.59</v>
-      </c>
-    </row>
-    <row r="31" spans="1:5">
-      <c r="A31" s="3" t="s">
+      <c r="B38" s="5" t="s">
+        <v>6</v>
+      </c>
+      <c r="C38" s="6">
+        <v>-45.15</v>
+      </c>
+      <c r="D38" s="6">
+        <v>-45.33</v>
+      </c>
+      <c r="E38" s="7">
+        <v>-0.18</v>
+      </c>
+    </row>
+    <row r="39" spans="1:5">
+      <c r="A39" s="5" t="s">
         <v>40</v>
       </c>
-      <c r="B31" s="3" t="s">
-        <v>10</v>
-      </c>
-      <c r="C31" s="5">
-        <v>-1.58</v>
-      </c>
-      <c r="D31" s="5">
-        <v>-3.07</v>
-      </c>
-      <c r="E31" s="6">
-        <v>-1.49</v>
-      </c>
-    </row>
-    <row r="32" spans="1:5">
-      <c r="A32" s="3" t="s">
+      <c r="B39" s="5" t="s">
+        <v>6</v>
+      </c>
+      <c r="C39" s="6">
+        <v>-19.95</v>
+      </c>
+      <c r="D39" s="6">
+        <v>-20.47</v>
+      </c>
+      <c r="E39" s="7">
+        <v>-0.52</v>
+      </c>
+    </row>
+    <row r="40" spans="1:5">
+      <c r="A40" s="5" t="s">
         <v>41</v>
       </c>
-      <c r="B32" s="3" t="s">
-        <v>10</v>
-      </c>
-      <c r="C32" s="5">
-        <v>1.86</v>
-      </c>
-      <c r="D32" s="5">
-        <v>-1.11</v>
-      </c>
-      <c r="E32" s="6">
-        <v>-2.97</v>
-      </c>
-    </row>
-    <row r="33" spans="1:5">
-      <c r="A33" s="3" t="s">
+      <c r="B40" s="5" t="s">
+        <v>6</v>
+      </c>
+      <c r="C40" s="6">
+        <v>-19.35</v>
+      </c>
+      <c r="D40" s="6">
+        <v>-17.92</v>
+      </c>
+      <c r="E40" s="8">
+        <v>1.43</v>
+      </c>
+    </row>
+    <row r="41" spans="1:5">
+      <c r="A41" s="5" t="s">
         <v>42</v>
       </c>
-      <c r="B33" s="3" t="s">
-        <v>10</v>
-      </c>
-      <c r="C33" s="5">
-        <v>-1.97</v>
-      </c>
-      <c r="D33" s="5">
-        <v>-4.05</v>
-      </c>
-      <c r="E33" s="6">
-        <v>-2.08</v>
-      </c>
-    </row>
-    <row r="34" spans="1:5">
-      <c r="A34" s="3" t="s">
+      <c r="B41" s="5" t="s">
+        <v>6</v>
+      </c>
+      <c r="C41" s="6">
+        <v>-15.96</v>
+      </c>
+      <c r="D41" s="6">
+        <v>-17.21</v>
+      </c>
+      <c r="E41" s="7">
+        <v>-1.25</v>
+      </c>
+    </row>
+    <row r="42" spans="1:5">
+      <c r="A42" s="5" t="s">
+        <v>37</v>
+      </c>
+      <c r="B42" s="5" t="s">
+        <v>2</v>
+      </c>
+      <c r="C42" s="6">
+        <v>10811</v>
+      </c>
+      <c r="D42" s="6">
+        <v>10874</v>
+      </c>
+      <c r="E42" s="8">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="43" spans="1:5">
+      <c r="A43" s="5" t="s">
+        <v>38</v>
+      </c>
+      <c r="B43" s="5" t="s">
+        <v>2</v>
+      </c>
+      <c r="C43" s="6">
+        <v>493</v>
+      </c>
+      <c r="D43" s="6">
+        <v>495.55</v>
+      </c>
+      <c r="E43" s="8">
+        <v>2.55</v>
+      </c>
+    </row>
+    <row r="44" spans="1:5">
+      <c r="A44" s="5" t="s">
+        <v>39</v>
+      </c>
+      <c r="B44" s="5" t="s">
+        <v>2</v>
+      </c>
+      <c r="C44" s="6">
+        <v>309.85</v>
+      </c>
+      <c r="D44" s="6">
+        <v>303.4</v>
+      </c>
+      <c r="E44" s="7">
+        <v>-6.45</v>
+      </c>
+    </row>
+    <row r="45" spans="1:5">
+      <c r="A45" s="5" t="s">
+        <v>40</v>
+      </c>
+      <c r="B45" s="5" t="s">
+        <v>2</v>
+      </c>
+      <c r="C45" s="6">
+        <v>1742.4</v>
+      </c>
+      <c r="D45" s="6">
+        <v>1731</v>
+      </c>
+      <c r="E45" s="7">
+        <v>-11.4</v>
+      </c>
+    </row>
+    <row r="46" spans="1:5">
+      <c r="A46" s="5" t="s">
+        <v>41</v>
+      </c>
+      <c r="B46" s="5" t="s">
+        <v>2</v>
+      </c>
+      <c r="C46" s="6">
+        <v>10600</v>
+      </c>
+      <c r="D46" s="6">
+        <v>10788</v>
+      </c>
+      <c r="E46" s="8">
+        <v>188</v>
+      </c>
+    </row>
+    <row r="47" spans="1:5">
+      <c r="A47" s="5" t="s">
+        <v>42</v>
+      </c>
+      <c r="B47" s="5" t="s">
+        <v>2</v>
+      </c>
+      <c r="C47" s="6">
+        <v>973.8</v>
+      </c>
+      <c r="D47" s="6">
+        <v>959.4</v>
+      </c>
+      <c r="E47" s="7">
+        <v>-14.4</v>
+      </c>
+    </row>
+    <row r="48" spans="1:5">
+      <c r="A48" s="5" t="s">
         <v>43</v>
       </c>
-      <c r="B34" s="3" t="s">
-        <v>10</v>
-      </c>
-      <c r="C34" s="5">
-        <v>29.41</v>
-      </c>
-      <c r="D34" s="5">
-        <v>30.01</v>
-      </c>
-      <c r="E34" s="7">
-        <v>0.6</v>
-      </c>
-    </row>
-    <row r="35" spans="1:5">
-      <c r="A35" s="3" t="s">
+      <c r="B48" s="5" t="s">
+        <v>2</v>
+      </c>
+      <c r="C48" s="6">
+        <v>172.49</v>
+      </c>
+      <c r="D48" s="6">
+        <v>180.13</v>
+      </c>
+      <c r="E48" s="8">
+        <v>7.64</v>
+      </c>
+    </row>
+    <row r="49" spans="1:5">
+      <c r="A49" s="5" t="s">
         <v>37</v>
       </c>
-      <c r="B35" s="3" t="s">
-        <v>6</v>
-      </c>
-      <c r="C35" s="5">
-        <v>-10.82</v>
-      </c>
-      <c r="D35" s="5">
-        <v>-12.54</v>
-      </c>
-      <c r="E35" s="6">
-        <v>-1.72</v>
-      </c>
-    </row>
-    <row r="36" spans="1:5">
-      <c r="A36" s="3" t="s">
+      <c r="B49" s="5" t="s">
+        <v>24</v>
+      </c>
+      <c r="C49" s="6">
+        <v>30.48</v>
+      </c>
+      <c r="D49" s="6">
+        <v>32.99</v>
+      </c>
+      <c r="E49" s="8">
+        <v>2.51</v>
+      </c>
+    </row>
+    <row r="50" spans="1:5">
+      <c r="A50" s="5" t="s">
         <v>38</v>
       </c>
-      <c r="B36" s="3" t="s">
-        <v>6</v>
-      </c>
-      <c r="C36" s="5">
-        <v>-28.38</v>
-      </c>
-      <c r="D36" s="5">
-        <v>-26.45</v>
-      </c>
-      <c r="E36" s="7">
-        <v>1.93</v>
-      </c>
-    </row>
-    <row r="37" spans="1:5">
-      <c r="A37" s="3" t="s">
+      <c r="B50" s="5" t="s">
+        <v>24</v>
+      </c>
+      <c r="C50" s="6">
+        <v>45.21</v>
+      </c>
+      <c r="D50" s="6">
+        <v>46.36</v>
+      </c>
+      <c r="E50" s="8">
+        <v>1.15</v>
+      </c>
+    </row>
+    <row r="51" spans="1:5">
+      <c r="A51" s="5" t="s">
         <v>39</v>
       </c>
-      <c r="B37" s="3" t="s">
-        <v>6</v>
-      </c>
-      <c r="C37" s="5">
-        <v>-46.65</v>
-      </c>
-      <c r="D37" s="5">
-        <v>-45.15</v>
-      </c>
-      <c r="E37" s="7">
-        <v>1.5</v>
-      </c>
-    </row>
-    <row r="38" spans="1:5">
-      <c r="A38" s="3" t="s">
+      <c r="B51" s="5" t="s">
+        <v>24</v>
+      </c>
+      <c r="C51" s="6">
+        <v>33.54</v>
+      </c>
+      <c r="D51" s="6">
+        <v>30.23</v>
+      </c>
+      <c r="E51" s="7">
+        <v>-3.31</v>
+      </c>
+    </row>
+    <row r="52" spans="1:5">
+      <c r="A52" s="5" t="s">
         <v>40</v>
       </c>
-      <c r="B38" s="3" t="s">
-        <v>6</v>
-      </c>
-      <c r="C38" s="5">
-        <v>-19.51</v>
-      </c>
-      <c r="D38" s="5">
-        <v>-19.95</v>
-      </c>
-      <c r="E38" s="6">
-        <v>-0.44</v>
-      </c>
-    </row>
-    <row r="39" spans="1:5">
-      <c r="A39" s="3" t="s">
+      <c r="B52" s="5" t="s">
+        <v>24</v>
+      </c>
+      <c r="C52" s="6">
+        <v>25.68</v>
+      </c>
+      <c r="D52" s="6">
+        <v>24.67</v>
+      </c>
+      <c r="E52" s="7">
+        <v>-1.01</v>
+      </c>
+    </row>
+    <row r="53" spans="1:5">
+      <c r="A53" s="5" t="s">
         <v>41</v>
       </c>
-      <c r="B39" s="3" t="s">
-        <v>6</v>
-      </c>
-      <c r="C39" s="5">
-        <v>-18.2</v>
-      </c>
-      <c r="D39" s="5">
-        <v>-19.35</v>
-      </c>
-      <c r="E39" s="6">
-        <v>-1.15</v>
-      </c>
-    </row>
-    <row r="40" spans="1:5">
-      <c r="A40" s="3" t="s">
+      <c r="B53" s="5" t="s">
+        <v>24</v>
+      </c>
+      <c r="C53" s="6">
+        <v>38.48</v>
+      </c>
+      <c r="D53" s="6">
+        <v>43.44</v>
+      </c>
+      <c r="E53" s="8">
+        <v>4.96</v>
+      </c>
+    </row>
+    <row r="54" spans="1:5">
+      <c r="A54" s="5" t="s">
         <v>42</v>
       </c>
-      <c r="B40" s="3" t="s">
-        <v>6</v>
-      </c>
-      <c r="C40" s="5">
-        <v>-15</v>
-      </c>
-      <c r="D40" s="5">
-        <v>-15.96</v>
-      </c>
-      <c r="E40" s="6">
-        <v>-0.96</v>
-      </c>
-    </row>
-    <row r="41" spans="1:5">
-      <c r="A41" s="3" t="s">
+      <c r="B54" s="5" t="s">
+        <v>24</v>
+      </c>
+      <c r="C54" s="6">
+        <v>36.26</v>
+      </c>
+      <c r="D54" s="6">
+        <v>33.9</v>
+      </c>
+      <c r="E54" s="7">
+        <v>-2.36</v>
+      </c>
+    </row>
+    <row r="55" spans="1:5">
+      <c r="A55" s="5" t="s">
+        <v>43</v>
+      </c>
+      <c r="B55" s="5" t="s">
+        <v>24</v>
+      </c>
+      <c r="C55" s="6">
+        <v>81.28</v>
+      </c>
+      <c r="D55" s="6">
+        <v>84.12</v>
+      </c>
+      <c r="E55" s="8">
+        <v>2.84</v>
+      </c>
+    </row>
+    <row r="56" spans="1:5">
+      <c r="A56" s="5" t="s">
         <v>37</v>
       </c>
-      <c r="B41" s="3" t="s">
-        <v>2</v>
-      </c>
-      <c r="C41" s="5">
-        <v>11024</v>
-      </c>
-      <c r="D41" s="5">
-        <v>10811</v>
-      </c>
-      <c r="E41" s="6">
-        <v>-213</v>
-      </c>
-    </row>
-    <row r="42" spans="1:5">
-      <c r="A42" s="3" t="s">
+      <c r="B56" s="5" t="s">
+        <v>31</v>
+      </c>
+      <c r="C56" s="6">
+        <v>146.13</v>
+      </c>
+      <c r="D56" s="6">
+        <v>38.15</v>
+      </c>
+      <c r="E56" s="7">
+        <v>-107.98</v>
+      </c>
+    </row>
+    <row r="57" spans="1:5">
+      <c r="A57" s="5" t="s">
         <v>38</v>
       </c>
-      <c r="B42" s="3" t="s">
-        <v>2</v>
-      </c>
-      <c r="C42" s="5">
-        <v>480.05</v>
-      </c>
-      <c r="D42" s="5">
-        <v>493</v>
-      </c>
-      <c r="E42" s="7">
-        <v>12.95</v>
-      </c>
-    </row>
-    <row r="43" spans="1:5">
-      <c r="A43" s="3" t="s">
+      <c r="B57" s="5" t="s">
+        <v>31</v>
+      </c>
+      <c r="C57" s="6">
+        <v>10.68</v>
+      </c>
+      <c r="D57" s="6">
+        <v>-70.44</v>
+      </c>
+      <c r="E57" s="7">
+        <v>-81.12</v>
+      </c>
+    </row>
+    <row r="58" spans="1:5">
+      <c r="A58" s="5" t="s">
         <v>39</v>
       </c>
-      <c r="B43" s="3" t="s">
-        <v>2</v>
-      </c>
-      <c r="C43" s="5">
-        <v>314.65</v>
-      </c>
-      <c r="D43" s="5">
-        <v>309.85</v>
-      </c>
-      <c r="E43" s="6">
-        <v>-4.8</v>
-      </c>
-    </row>
-    <row r="44" spans="1:5">
-      <c r="A44" s="3" t="s">
+      <c r="B58" s="5" t="s">
+        <v>31</v>
+      </c>
+      <c r="C58" s="6">
+        <v>217.44</v>
+      </c>
+      <c r="D58" s="6">
+        <v>29.63</v>
+      </c>
+      <c r="E58" s="7">
+        <v>-187.81</v>
+      </c>
+    </row>
+    <row r="59" spans="1:5">
+      <c r="A59" s="5" t="s">
         <v>40</v>
       </c>
-      <c r="B44" s="3" t="s">
-        <v>2</v>
-      </c>
-      <c r="C44" s="5">
-        <v>1752</v>
-      </c>
-      <c r="D44" s="5">
-        <v>1742.4</v>
-      </c>
-      <c r="E44" s="6">
-        <v>-9.6</v>
-      </c>
-    </row>
-    <row r="45" spans="1:5">
-      <c r="A45" s="3" t="s">
+      <c r="B59" s="5" t="s">
+        <v>31</v>
+      </c>
+      <c r="C59" s="6">
+        <v>27.93</v>
+      </c>
+      <c r="D59" s="6">
+        <v>58.48</v>
+      </c>
+      <c r="E59" s="8">
+        <v>30.55</v>
+      </c>
+    </row>
+    <row r="60" spans="1:5">
+      <c r="A60" s="5" t="s">
         <v>41</v>
       </c>
-      <c r="B45" s="3" t="s">
-        <v>2</v>
-      </c>
-      <c r="C45" s="5">
-        <v>10800</v>
-      </c>
-      <c r="D45" s="5">
-        <v>10600</v>
-      </c>
-      <c r="E45" s="6">
-        <v>-200</v>
-      </c>
-    </row>
-    <row r="46" spans="1:5">
-      <c r="A46" s="3" t="s">
+      <c r="B60" s="5" t="s">
+        <v>31</v>
+      </c>
+      <c r="C60" s="6">
+        <v>51.72</v>
+      </c>
+      <c r="D60" s="6">
+        <v>-9.91</v>
+      </c>
+      <c r="E60" s="7">
+        <v>-61.63</v>
+      </c>
+    </row>
+    <row r="61" spans="1:5">
+      <c r="A61" s="5" t="s">
         <v>42</v>
       </c>
-      <c r="B46" s="3" t="s">
-        <v>2</v>
-      </c>
-      <c r="C46" s="5">
-        <v>985</v>
-      </c>
-      <c r="D46" s="5">
-        <v>973.8</v>
-      </c>
-      <c r="E46" s="6">
-        <v>-11.2</v>
-      </c>
-    </row>
-    <row r="47" spans="1:5">
-      <c r="A47" s="3" t="s">
+      <c r="B61" s="5" t="s">
+        <v>31</v>
+      </c>
+      <c r="C61" s="6">
+        <v>41.38</v>
+      </c>
+      <c r="D61" s="6">
+        <v>5.48</v>
+      </c>
+      <c r="E61" s="7">
+        <v>-35.9</v>
+      </c>
+    </row>
+    <row r="62" spans="1:5">
+      <c r="A62" s="5" t="s">
         <v>43</v>
       </c>
-      <c r="B47" s="3" t="s">
-        <v>2</v>
-      </c>
-      <c r="C47" s="5">
-        <v>171.03</v>
-      </c>
-      <c r="D47" s="5">
-        <v>172.49</v>
-      </c>
-      <c r="E47" s="7">
-        <v>1.46</v>
-      </c>
-    </row>
-    <row r="48" spans="1:5">
-      <c r="A48" s="3" t="s">
-        <v>37</v>
-      </c>
-      <c r="B48" s="3" t="s">
-        <v>24</v>
-      </c>
-      <c r="C48" s="5">
-        <v>34.55</v>
-      </c>
-      <c r="D48" s="5">
-        <v>30.48</v>
-      </c>
-      <c r="E48" s="6">
-        <v>-4.07</v>
-      </c>
-    </row>
-    <row r="49" spans="1:5">
-      <c r="A49" s="3" t="s">
-        <v>38</v>
-      </c>
-      <c r="B49" s="3" t="s">
-        <v>24</v>
-      </c>
-      <c r="C49" s="5">
-        <v>39.09</v>
-      </c>
-      <c r="D49" s="5">
-        <v>45.21</v>
-      </c>
-      <c r="E49" s="7">
-        <v>6.12</v>
-      </c>
-    </row>
-    <row r="50" spans="1:5">
-      <c r="A50" s="3" t="s">
-        <v>39</v>
-      </c>
-      <c r="B50" s="3" t="s">
-        <v>24</v>
-      </c>
-      <c r="C50" s="5">
-        <v>36.28</v>
-      </c>
-      <c r="D50" s="5">
-        <v>33.54</v>
-      </c>
-      <c r="E50" s="6">
-        <v>-2.74</v>
-      </c>
-    </row>
-    <row r="51" spans="1:5">
-      <c r="A51" s="3" t="s">
-        <v>40</v>
-      </c>
-      <c r="B51" s="3" t="s">
-        <v>24</v>
-      </c>
-      <c r="C51" s="5">
-        <v>26.53</v>
-      </c>
-      <c r="D51" s="5">
-        <v>25.68</v>
-      </c>
-      <c r="E51" s="6">
-        <v>-0.85</v>
-      </c>
-    </row>
-    <row r="52" spans="1:5">
-      <c r="A52" s="3" t="s">
-        <v>41</v>
-      </c>
-      <c r="B52" s="3" t="s">
-        <v>24</v>
-      </c>
-      <c r="C52" s="5">
-        <v>42.13</v>
-      </c>
-      <c r="D52" s="5">
-        <v>38.48</v>
-      </c>
-      <c r="E52" s="6">
-        <v>-3.65</v>
-      </c>
-    </row>
-    <row r="53" spans="1:5">
-      <c r="A53" s="3" t="s">
-        <v>42</v>
-      </c>
-      <c r="B53" s="3" t="s">
-        <v>24</v>
-      </c>
-      <c r="C53" s="5">
-        <v>38.18</v>
-      </c>
-      <c r="D53" s="5">
-        <v>36.26</v>
-      </c>
-      <c r="E53" s="6">
-        <v>-1.92</v>
-      </c>
-    </row>
-    <row r="54" spans="1:5">
-      <c r="A54" s="3" t="s">
-        <v>43</v>
-      </c>
-      <c r="B54" s="3" t="s">
-        <v>24</v>
-      </c>
-      <c r="C54" s="5">
-        <v>80.66</v>
-      </c>
-      <c r="D54" s="5">
-        <v>81.28</v>
-      </c>
-      <c r="E54" s="7">
-        <v>0.62</v>
-      </c>
-    </row>
-    <row r="55" spans="1:5">
-      <c r="A55" s="3" t="s">
-        <v>37</v>
-      </c>
-      <c r="B55" s="3" t="s">
+      <c r="B62" s="5" t="s">
         <v>31</v>
       </c>
-      <c r="C55" s="5">
-        <v>13.03</v>
-      </c>
-      <c r="D55" s="5">
-        <v>146.13</v>
-      </c>
-      <c r="E55" s="7">
-        <v>133.1</v>
-      </c>
-    </row>
-    <row r="56" spans="1:5">
-      <c r="A56" s="3" t="s">
-        <v>38</v>
-      </c>
-      <c r="B56" s="3" t="s">
-        <v>31</v>
-      </c>
-      <c r="C56" s="5">
-        <v>-54.79</v>
-      </c>
-      <c r="D56" s="5">
-        <v>10.68</v>
-      </c>
-      <c r="E56" s="7">
-        <v>65.47</v>
-      </c>
-    </row>
-    <row r="57" spans="1:5">
-      <c r="A57" s="3" t="s">
-        <v>39</v>
-      </c>
-      <c r="B57" s="3" t="s">
-        <v>31</v>
-      </c>
-      <c r="C57" s="5">
-        <v>-12.03</v>
-      </c>
-      <c r="D57" s="5">
-        <v>217.44</v>
-      </c>
-      <c r="E57" s="7">
-        <v>229.47</v>
-      </c>
-    </row>
-    <row r="58" spans="1:5">
-      <c r="A58" s="3" t="s">
-        <v>40</v>
-      </c>
-      <c r="B58" s="3" t="s">
-        <v>31</v>
-      </c>
-      <c r="C58" s="5">
-        <v>-19.44</v>
-      </c>
-      <c r="D58" s="5">
-        <v>27.93</v>
-      </c>
-      <c r="E58" s="7">
-        <v>47.37</v>
-      </c>
-    </row>
-    <row r="59" spans="1:5">
-      <c r="A59" s="3" t="s">
-        <v>41</v>
-      </c>
-      <c r="B59" s="3" t="s">
-        <v>31</v>
-      </c>
-      <c r="C59" s="5">
-        <v>-28.52</v>
-      </c>
-      <c r="D59" s="5">
-        <v>51.72</v>
-      </c>
-      <c r="E59" s="7">
-        <v>80.23999999999999</v>
-      </c>
-    </row>
-    <row r="60" spans="1:5">
-      <c r="A60" s="3" t="s">
-        <v>42</v>
-      </c>
-      <c r="B60" s="3" t="s">
-        <v>31</v>
-      </c>
-      <c r="C60" s="5">
-        <v>29.1</v>
-      </c>
-      <c r="D60" s="5">
-        <v>41.38</v>
-      </c>
-      <c r="E60" s="7">
-        <v>12.28</v>
-      </c>
-    </row>
-    <row r="61" spans="1:5">
-      <c r="A61" s="3" t="s">
-        <v>43</v>
-      </c>
-      <c r="B61" s="3" t="s">
-        <v>31</v>
-      </c>
-      <c r="C61" s="5">
-        <v>431.13</v>
-      </c>
-      <c r="D61" s="5">
+      <c r="C62" s="6">
         <v>119.63</v>
       </c>
-      <c r="E61" s="6">
-        <v>-311.5</v>
+      <c r="D62" s="6">
+        <v>249.72</v>
+      </c>
+      <c r="E62" s="8">
+        <v>130.09</v>
       </c>
     </row>
   </sheetData>
   <mergeCells count="2">
     <mergeCell ref="A1:F1"/>
-    <mergeCell ref="A5:E5"/>
+    <mergeCell ref="A6:E6"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -2824,61 +2901,61 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:9" ht="28" customHeight="1">
-      <c r="A1" s="8" t="s">
+      <c r="A1" s="9" t="s">
         <v>1</v>
       </c>
-      <c r="B1" s="8" t="s">
-        <v>56</v>
-      </c>
-      <c r="C1" s="8" t="s">
+      <c r="B1" s="9" t="s">
+        <v>63</v>
+      </c>
+      <c r="C1" s="9" t="s">
+        <v>64</v>
+      </c>
+      <c r="D1" s="9" t="s">
+        <v>65</v>
+      </c>
+      <c r="E1" s="9" t="s">
+        <v>66</v>
+      </c>
+      <c r="F1" s="9" t="s">
+        <v>67</v>
+      </c>
+      <c r="G1" s="9" t="s">
+        <v>68</v>
+      </c>
+      <c r="H1" s="9" t="s">
+        <v>69</v>
+      </c>
+      <c r="I1" s="9" t="s">
+        <v>70</v>
+      </c>
+    </row>
+    <row r="2" spans="1:9">
+      <c r="A2" s="10" t="s">
+        <v>44</v>
+      </c>
+      <c r="B2" s="11">
+        <v>56.8</v>
+      </c>
+      <c r="C2" s="12">
+        <v>7</v>
+      </c>
+      <c r="D2" s="11">
+        <v>42.2</v>
+      </c>
+      <c r="E2" s="11">
+        <v>60</v>
+      </c>
+      <c r="F2" s="11">
+        <v>-1.7</v>
+      </c>
+      <c r="G2" s="11">
+        <v>0.8</v>
+      </c>
+      <c r="H2" s="11">
         <v>57</v>
       </c>
-      <c r="D1" s="8" t="s">
-        <v>58</v>
-      </c>
-      <c r="E1" s="8" t="s">
-        <v>59</v>
-      </c>
-      <c r="F1" s="8" t="s">
-        <v>60</v>
-      </c>
-      <c r="G1" s="8" t="s">
-        <v>61</v>
-      </c>
-      <c r="H1" s="8" t="s">
-        <v>62</v>
-      </c>
-      <c r="I1" s="8" t="s">
-        <v>63</v>
-      </c>
-    </row>
-    <row r="2" spans="1:9">
-      <c r="A2" s="9" t="s">
-        <v>44</v>
-      </c>
-      <c r="B2" s="10">
-        <v>48.8</v>
-      </c>
-      <c r="C2" s="11">
-        <v>7</v>
-      </c>
-      <c r="D2" s="10">
-        <v>41.6</v>
-      </c>
-      <c r="E2" s="10">
-        <v>40</v>
-      </c>
-      <c r="F2" s="10">
-        <v>-2.4</v>
-      </c>
-      <c r="G2" s="10">
-        <v>1.2</v>
-      </c>
-      <c r="H2" s="10">
-        <v>57</v>
-      </c>
-      <c r="I2" s="10">
-        <v>30</v>
+      <c r="I2" s="11">
+        <v>10</v>
       </c>
     </row>
   </sheetData>
@@ -2979,49 +3056,49 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:7">
-      <c r="A1" s="12" t="s">
+      <c r="A1" s="13" t="s">
         <v>37</v>
       </c>
-      <c r="B1" s="12" t="s">
+      <c r="B1" s="13" t="s">
         <v>41</v>
       </c>
-      <c r="C1" s="12" t="s">
+      <c r="C1" s="13" t="s">
         <v>38</v>
       </c>
-      <c r="D1" s="12" t="s">
+      <c r="D1" s="13" t="s">
         <v>43</v>
       </c>
-      <c r="E1" s="12" t="s">
+      <c r="E1" s="13" t="s">
         <v>42</v>
       </c>
-      <c r="F1" s="12" t="s">
+      <c r="F1" s="13" t="s">
         <v>40</v>
       </c>
-      <c r="G1" s="12" t="s">
+      <c r="G1" s="13" t="s">
         <v>39</v>
       </c>
     </row>
     <row r="2" spans="1:7">
-      <c r="A2" s="13">
-        <v>0.2546</v>
-      </c>
-      <c r="B2" s="13">
-        <v>0.1888</v>
-      </c>
-      <c r="C2" s="13">
-        <v>0.1591</v>
-      </c>
-      <c r="D2" s="13">
-        <v>0.0653</v>
-      </c>
-      <c r="E2" s="13">
-        <v>0.0572</v>
-      </c>
-      <c r="F2" s="13">
-        <v>0.0003</v>
-      </c>
-      <c r="G2" s="13">
-        <v>-0.2431</v>
+      <c r="A2" s="14">
+        <v>0.2604</v>
+      </c>
+      <c r="B2" s="14">
+        <v>0.1882</v>
+      </c>
+      <c r="C2" s="14">
+        <v>0.164</v>
+      </c>
+      <c r="D2" s="14">
+        <v>0.068</v>
+      </c>
+      <c r="E2" s="14">
+        <v>0.0498</v>
+      </c>
+      <c r="F2" s="14">
+        <v>-0.005</v>
+      </c>
+      <c r="G2" s="14">
+        <v>-0.242</v>
       </c>
     </row>
   </sheetData>

--- a/BAJAJ_GROUP_Technical_Metrics.xlsx
+++ b/BAJAJ_GROUP_Technical_Metrics.xlsx
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="268" uniqueCount="71">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="264" uniqueCount="73">
   <si>
     <t>Symbol</t>
   </si>
@@ -187,13 +187,19 @@
     <t>Curr Value</t>
   </si>
   <si>
-    <t>Yes → No</t>
-  </si>
-  <si>
-    <t>🔴 BEARISH</t>
-  </si>
-  <si>
-    <t>20 DMA &gt; 50 DMA</t>
+    <t>Left 52W High Zone</t>
+  </si>
+  <si>
+    <t>0.0% → -4.2%</t>
+  </si>
+  <si>
+    <t>⚪ NEUTRAL</t>
+  </si>
+  <si>
+    <t>0.0%</t>
+  </si>
+  <si>
+    <t>-4.2%</t>
   </si>
   <si>
     <t>▶  NUMERIC METRIC CHANGES (vs Previous Run)</t>
@@ -245,7 +251,7 @@
     <numFmt numFmtId="166" formatCode="0.0"/>
     <numFmt numFmtId="167" formatCode="0.00%"/>
   </numFmts>
-  <fonts count="6">
+  <fonts count="7">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -279,6 +285,13 @@
     </font>
     <font>
       <sz val="11"/>
+      <color rgb="FF1F4E79"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
       <color rgb="FF9C0006"/>
       <name val="Calibri"/>
       <family val="2"/>
@@ -292,7 +305,7 @@
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="9">
+  <fills count="10">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -314,6 +327,12 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="FF4A6FA5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFDDEBF7"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -405,12 +424,12 @@
     <xf numFmtId="0" fontId="4" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1"/>
-    <xf numFmtId="165" fontId="4" fillId="5" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="165" fontId="5" fillId="6" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="3" fillId="7" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="165" fontId="6" fillId="7" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="3" fillId="8" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="8" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="9" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
     <xf numFmtId="166" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
@@ -419,7 +438,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="8" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="9" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="167" fontId="0" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
@@ -918,10 +937,10 @@
         <v>44</v>
       </c>
       <c r="C2">
-        <v>10874</v>
+        <v>10045</v>
       </c>
       <c r="D2">
-        <v>0.58</v>
+        <v>-7.62</v>
       </c>
       <c r="E2">
         <v>12361</v>
@@ -930,46 +949,46 @@
         <v>8506.780000000001</v>
       </c>
       <c r="G2">
-        <v>-12.03</v>
+        <v>-18.74</v>
       </c>
       <c r="H2">
-        <v>27.83</v>
+        <v>18.08</v>
       </c>
       <c r="I2">
-        <v>-4.61</v>
+        <v>-10.38</v>
       </c>
       <c r="J2">
-        <v>-10.35</v>
+        <v>-18.74</v>
       </c>
       <c r="K2">
-        <v>10.32</v>
+        <v>2.65</v>
       </c>
       <c r="L2">
-        <v>24.7</v>
+        <v>17.06</v>
       </c>
       <c r="M2">
-        <v>26.04</v>
+        <v>23.93</v>
       </c>
       <c r="N2">
         <v>71</v>
       </c>
       <c r="O2">
-        <v>76</v>
+        <v>70</v>
       </c>
       <c r="P2">
-        <v>11039.6</v>
+        <v>10807</v>
       </c>
       <c r="Q2">
-        <v>11511.85</v>
+        <v>11407.6</v>
       </c>
       <c r="R2">
-        <v>11590.14</v>
+        <v>11571.07</v>
       </c>
       <c r="S2">
-        <v>10134.21</v>
+        <v>10139.99</v>
       </c>
       <c r="T2">
-        <v>7.3</v>
+        <v>-0.9399999999999999</v>
       </c>
       <c r="U2" t="s">
         <v>45</v>
@@ -981,46 +1000,46 @@
         <v>45</v>
       </c>
       <c r="X2">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="Y2">
-        <v>32.99</v>
+        <v>21.8</v>
       </c>
       <c r="Z2">
-        <v>-175.63</v>
+        <v>-258.31</v>
       </c>
       <c r="AA2">
-        <v>-77.79000000000001</v>
+        <v>-113.89</v>
       </c>
       <c r="AB2">
-        <v>-97.83</v>
+        <v>-144.41</v>
       </c>
       <c r="AC2">
         <v>3.93</v>
       </c>
       <c r="AD2">
-        <v>4.94</v>
+        <v>4.44</v>
       </c>
       <c r="AE2">
-        <v>203.42</v>
+        <v>258.46</v>
       </c>
       <c r="AF2">
-        <v>38.15</v>
+        <v>562.46</v>
       </c>
       <c r="AG2">
-        <v>12229.54</v>
+        <v>12325.13</v>
       </c>
       <c r="AH2">
-        <v>10794.16</v>
+        <v>10490.07</v>
       </c>
       <c r="AI2">
-        <v>11476.26</v>
+        <v>11082.38</v>
       </c>
       <c r="AJ2" t="s">
         <v>47</v>
       </c>
       <c r="AK2">
-        <v>59.8</v>
+        <v>64.40000000000001</v>
       </c>
     </row>
     <row r="3" spans="1:37">
@@ -1031,58 +1050,58 @@
         <v>44</v>
       </c>
       <c r="C3">
-        <v>495.55</v>
+        <v>497.05</v>
       </c>
       <c r="D3">
-        <v>0.52</v>
+        <v>0.3</v>
       </c>
       <c r="E3">
         <v>670.25</v>
       </c>
       <c r="F3">
-        <v>232.89</v>
+        <v>235.4</v>
       </c>
       <c r="G3">
-        <v>-26.06</v>
+        <v>-25.84</v>
       </c>
       <c r="H3">
-        <v>112.78</v>
+        <v>111.15</v>
       </c>
       <c r="I3">
-        <v>-2.04</v>
+        <v>-0.93</v>
       </c>
       <c r="J3">
-        <v>4.54</v>
+        <v>5.32</v>
       </c>
       <c r="K3">
-        <v>-19.02</v>
+        <v>-19.34</v>
       </c>
       <c r="L3">
-        <v>103.11</v>
+        <v>113.43</v>
       </c>
       <c r="M3">
-        <v>16.4</v>
+        <v>16.38</v>
       </c>
       <c r="N3">
         <v>99</v>
       </c>
       <c r="O3">
-        <v>89</v>
+        <v>91</v>
       </c>
       <c r="P3">
-        <v>493.96</v>
+        <v>493.03</v>
       </c>
       <c r="Q3">
-        <v>506.93</v>
+        <v>507.56</v>
       </c>
       <c r="R3">
-        <v>509.09</v>
+        <v>508.44</v>
       </c>
       <c r="S3">
-        <v>450.92</v>
+        <v>452.13</v>
       </c>
       <c r="T3">
-        <v>9.9</v>
+        <v>9.93</v>
       </c>
       <c r="U3" t="s">
         <v>45</v>
@@ -1097,34 +1116,34 @@
         <v>2</v>
       </c>
       <c r="Y3">
-        <v>46.36</v>
+        <v>47.06</v>
       </c>
       <c r="Z3">
-        <v>-3.65</v>
+        <v>-3.6</v>
       </c>
       <c r="AA3">
-        <v>-2.52</v>
+        <v>-2.74</v>
       </c>
       <c r="AB3">
-        <v>-1.13</v>
+        <v>-0.86</v>
       </c>
       <c r="AC3">
-        <v>26.6</v>
+        <v>43.99</v>
       </c>
       <c r="AD3">
-        <v>13.69</v>
+        <v>27.58</v>
       </c>
       <c r="AE3">
-        <v>19.09</v>
+        <v>18.84</v>
       </c>
       <c r="AF3">
-        <v>-70.44</v>
+        <v>-39.15</v>
       </c>
       <c r="AG3">
-        <v>532.55</v>
+        <v>531.4299999999999</v>
       </c>
       <c r="AH3">
-        <v>481.32</v>
+        <v>483.69</v>
       </c>
       <c r="AI3">
         <v>460.99</v>
@@ -1133,7 +1152,7 @@
         <v>48</v>
       </c>
       <c r="AK3">
-        <v>26.88</v>
+        <v>28.9</v>
       </c>
     </row>
     <row r="4" spans="1:37">
@@ -1144,58 +1163,58 @@
         <v>44</v>
       </c>
       <c r="C4">
-        <v>303.4</v>
+        <v>299.8</v>
       </c>
       <c r="D4">
-        <v>-2.08</v>
+        <v>-1.19</v>
       </c>
       <c r="E4">
         <v>554.95</v>
       </c>
       <c r="F4">
-        <v>303.4</v>
+        <v>299.8</v>
       </c>
       <c r="G4">
-        <v>-45.33</v>
+        <v>-45.98</v>
       </c>
       <c r="H4">
         <v>0</v>
       </c>
       <c r="I4">
-        <v>-7.89</v>
+        <v>-6.74</v>
       </c>
       <c r="J4">
-        <v>-6.59</v>
+        <v>-7.99</v>
       </c>
       <c r="K4">
-        <v>-8.119999999999999</v>
+        <v>-8.859999999999999</v>
       </c>
       <c r="L4">
-        <v>-46.3</v>
+        <v>-44.82</v>
       </c>
       <c r="M4">
-        <v>-24.2</v>
+        <v>-24.39</v>
       </c>
       <c r="N4">
         <v>15</v>
       </c>
       <c r="O4">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="P4">
-        <v>313.66</v>
+        <v>309.33</v>
       </c>
       <c r="Q4">
-        <v>326.51</v>
+        <v>325.32</v>
       </c>
       <c r="R4">
-        <v>337.51</v>
+        <v>336.9</v>
       </c>
       <c r="S4">
-        <v>368.9</v>
+        <v>368.02</v>
       </c>
       <c r="T4">
-        <v>-17.76</v>
+        <v>-18.54</v>
       </c>
       <c r="U4" t="s">
         <v>45</v>
@@ -1210,43 +1229,43 @@
         <v>0</v>
       </c>
       <c r="Y4">
-        <v>30.23</v>
+        <v>28.53</v>
       </c>
       <c r="Z4">
-        <v>-7.48</v>
+        <v>-8.51</v>
       </c>
       <c r="AA4">
-        <v>-5.43</v>
+        <v>-6.04</v>
       </c>
       <c r="AB4">
-        <v>-2.06</v>
+        <v>-2.46</v>
       </c>
       <c r="AC4">
         <v>0</v>
       </c>
       <c r="AD4">
-        <v>3.21</v>
+        <v>0.62</v>
       </c>
       <c r="AE4">
-        <v>9.75</v>
+        <v>9.779999999999999</v>
       </c>
       <c r="AF4">
-        <v>29.63</v>
+        <v>-12.05</v>
       </c>
       <c r="AG4">
-        <v>346.93</v>
+        <v>348.97</v>
       </c>
       <c r="AH4">
-        <v>306.1</v>
+        <v>301.68</v>
       </c>
       <c r="AI4">
-        <v>337.22</v>
+        <v>330.42</v>
       </c>
       <c r="AJ4" t="s">
         <v>47</v>
       </c>
       <c r="AK4">
-        <v>25.96</v>
+        <v>31.31</v>
       </c>
     </row>
     <row r="5" spans="1:37">
@@ -1257,10 +1276,10 @@
         <v>44</v>
       </c>
       <c r="C5">
-        <v>1731</v>
+        <v>1732.6</v>
       </c>
       <c r="D5">
-        <v>-0.65</v>
+        <v>0.09</v>
       </c>
       <c r="E5">
         <v>2176.6</v>
@@ -1269,46 +1288,46 @@
         <v>1631.8</v>
       </c>
       <c r="G5">
-        <v>-20.47</v>
+        <v>-20.4</v>
       </c>
       <c r="H5">
-        <v>6.08</v>
+        <v>6.18</v>
       </c>
       <c r="I5">
-        <v>-6.26</v>
+        <v>-1.69</v>
       </c>
       <c r="J5">
-        <v>-14.35</v>
+        <v>-12.14</v>
       </c>
       <c r="K5">
-        <v>-6.72</v>
+        <v>-8.6</v>
       </c>
       <c r="L5">
-        <v>-14.96</v>
+        <v>-13.51</v>
       </c>
       <c r="M5">
-        <v>-0.5</v>
+        <v>0.21</v>
       </c>
       <c r="N5">
         <v>29</v>
       </c>
       <c r="O5">
-        <v>39</v>
+        <v>41</v>
       </c>
       <c r="P5">
-        <v>1751.74</v>
+        <v>1745.8</v>
       </c>
       <c r="Q5">
-        <v>1864.62</v>
+        <v>1851.75</v>
       </c>
       <c r="R5">
-        <v>1944.52</v>
+        <v>1941.65</v>
       </c>
       <c r="S5">
-        <v>1886.43</v>
+        <v>1884.68</v>
       </c>
       <c r="T5">
-        <v>-8.24</v>
+        <v>-8.07</v>
       </c>
       <c r="U5" t="s">
         <v>45</v>
@@ -1323,43 +1342,43 @@
         <v>1</v>
       </c>
       <c r="Y5">
-        <v>24.67</v>
+        <v>25.11</v>
       </c>
       <c r="Z5">
-        <v>-58.97</v>
+        <v>-60.44</v>
       </c>
       <c r="AA5">
-        <v>-44.73</v>
+        <v>-47.87</v>
       </c>
       <c r="AB5">
-        <v>-14.24</v>
+        <v>-12.56</v>
       </c>
       <c r="AC5">
-        <v>0.66</v>
+        <v>1.17</v>
       </c>
       <c r="AD5">
-        <v>3.5</v>
+        <v>2.25</v>
       </c>
       <c r="AE5">
-        <v>37.71</v>
+        <v>37.26</v>
       </c>
       <c r="AF5">
-        <v>58.48</v>
+        <v>226.11</v>
       </c>
       <c r="AG5">
-        <v>2032.56</v>
+        <v>2018.68</v>
       </c>
       <c r="AH5">
-        <v>1696.68</v>
+        <v>1684.82</v>
       </c>
       <c r="AI5">
-        <v>1838.17</v>
+        <v>1830.94</v>
       </c>
       <c r="AJ5" t="s">
         <v>47</v>
       </c>
       <c r="AK5">
-        <v>77.70999999999999</v>
+        <v>79.48</v>
       </c>
     </row>
     <row r="6" spans="1:37">
@@ -1370,10 +1389,10 @@
         <v>44</v>
       </c>
       <c r="C6">
-        <v>10788</v>
+        <v>10666</v>
       </c>
       <c r="D6">
-        <v>1.77</v>
+        <v>-1.13</v>
       </c>
       <c r="E6">
         <v>13144</v>
@@ -1382,25 +1401,25 @@
         <v>8746</v>
       </c>
       <c r="G6">
-        <v>-17.92</v>
+        <v>-18.85</v>
       </c>
       <c r="H6">
-        <v>23.35</v>
+        <v>21.95</v>
       </c>
       <c r="I6">
-        <v>-5.77</v>
+        <v>-2.3</v>
       </c>
       <c r="J6">
-        <v>-7.35</v>
+        <v>-5.69</v>
       </c>
       <c r="K6">
-        <v>-0.64</v>
+        <v>-3.73</v>
       </c>
       <c r="L6">
-        <v>-16.37</v>
+        <v>-16</v>
       </c>
       <c r="M6">
-        <v>18.82</v>
+        <v>18.9</v>
       </c>
       <c r="N6">
         <v>43</v>
@@ -1409,19 +1428,19 @@
         <v>46</v>
       </c>
       <c r="P6">
-        <v>10809</v>
+        <v>10758.8</v>
       </c>
       <c r="Q6">
-        <v>11052.15</v>
+        <v>11030.45</v>
       </c>
       <c r="R6">
-        <v>11178.42</v>
+        <v>11183.24</v>
       </c>
       <c r="S6">
-        <v>10677.08</v>
+        <v>10675.91</v>
       </c>
       <c r="T6">
-        <v>1.04</v>
+        <v>-0.09</v>
       </c>
       <c r="U6" t="s">
         <v>45</v>
@@ -1433,46 +1452,46 @@
         <v>45</v>
       </c>
       <c r="X6">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="Y6">
-        <v>43.44</v>
+        <v>41.12</v>
       </c>
       <c r="Z6">
-        <v>-95.63</v>
+        <v>-113.13</v>
       </c>
       <c r="AA6">
-        <v>-43.63</v>
+        <v>-57.53</v>
       </c>
       <c r="AB6">
-        <v>-51.99</v>
+        <v>-55.59</v>
       </c>
       <c r="AC6">
-        <v>8.99</v>
+        <v>13.78</v>
       </c>
       <c r="AD6">
-        <v>7.49</v>
+        <v>9.23</v>
       </c>
       <c r="AE6">
-        <v>248.99</v>
+        <v>257.85</v>
       </c>
       <c r="AF6">
-        <v>-9.91</v>
+        <v>-9.199999999999999</v>
       </c>
       <c r="AG6">
-        <v>11460.04</v>
+        <v>11472.38</v>
       </c>
       <c r="AH6">
-        <v>10644.26</v>
+        <v>10588.52</v>
       </c>
       <c r="AI6">
-        <v>11476.98</v>
+        <v>11368.55</v>
       </c>
       <c r="AJ6" t="s">
         <v>47</v>
       </c>
       <c r="AK6">
-        <v>29.09</v>
+        <v>33.4</v>
       </c>
     </row>
     <row r="7" spans="1:37">
@@ -1483,10 +1502,10 @@
         <v>44</v>
       </c>
       <c r="C7">
-        <v>959.4</v>
+        <v>948.3</v>
       </c>
       <c r="D7">
-        <v>-1.48</v>
+        <v>-1.16</v>
       </c>
       <c r="E7">
         <v>1158.8</v>
@@ -1495,46 +1514,46 @@
         <v>801.55</v>
       </c>
       <c r="G7">
-        <v>-17.21</v>
+        <v>-18.17</v>
       </c>
       <c r="H7">
-        <v>19.69</v>
+        <v>18.31</v>
       </c>
       <c r="I7">
-        <v>-8.029999999999999</v>
+        <v>-3.43</v>
       </c>
       <c r="J7">
-        <v>-9.23</v>
+        <v>-10.02</v>
       </c>
       <c r="K7">
-        <v>-5.79</v>
+        <v>-8.06</v>
       </c>
       <c r="L7">
-        <v>-5.27</v>
+        <v>-3.74</v>
       </c>
       <c r="M7">
-        <v>4.98</v>
+        <v>5.14</v>
       </c>
       <c r="N7">
         <v>57</v>
       </c>
       <c r="O7">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="P7">
-        <v>979.42</v>
+        <v>972.6799999999999</v>
       </c>
       <c r="Q7">
-        <v>1021.9</v>
+        <v>1016.52</v>
       </c>
       <c r="R7">
-        <v>1060.49</v>
+        <v>1058.25</v>
       </c>
       <c r="S7">
-        <v>976.66</v>
+        <v>976.3200000000001</v>
       </c>
       <c r="T7">
-        <v>-1.77</v>
+        <v>-2.87</v>
       </c>
       <c r="U7" t="s">
         <v>45</v>
@@ -1549,43 +1568,43 @@
         <v>1</v>
       </c>
       <c r="Y7">
-        <v>33.9</v>
+        <v>32.16</v>
       </c>
       <c r="Z7">
-        <v>-23.18</v>
+        <v>-25.69</v>
       </c>
       <c r="AA7">
-        <v>-17.3</v>
+        <v>-18.98</v>
       </c>
       <c r="AB7">
-        <v>-5.88</v>
+        <v>-6.72</v>
       </c>
       <c r="AC7">
-        <v>28.5</v>
+        <v>17.37</v>
       </c>
       <c r="AD7">
-        <v>36.34</v>
+        <v>28.73</v>
       </c>
       <c r="AE7">
-        <v>24.86</v>
+        <v>24.66</v>
       </c>
       <c r="AF7">
-        <v>5.48</v>
+        <v>-9.74</v>
       </c>
       <c r="AG7">
-        <v>1083.48</v>
+        <v>1084.1</v>
       </c>
       <c r="AH7">
-        <v>960.3099999999999</v>
+        <v>948.9299999999999</v>
       </c>
       <c r="AI7">
-        <v>1043.22</v>
+        <v>1020.6</v>
       </c>
       <c r="AJ7" t="s">
         <v>47</v>
       </c>
       <c r="AK7">
-        <v>45.56</v>
+        <v>48.85</v>
       </c>
     </row>
     <row r="8" spans="1:37">
@@ -1596,10 +1615,10 @@
         <v>44</v>
       </c>
       <c r="C8">
-        <v>180.13</v>
+        <v>172.66</v>
       </c>
       <c r="D8">
-        <v>4.43</v>
+        <v>-4.15</v>
       </c>
       <c r="E8">
         <v>180.13</v>
@@ -1608,46 +1627,46 @@
         <v>115.96</v>
       </c>
       <c r="G8">
-        <v>0</v>
+        <v>-4.15</v>
       </c>
       <c r="H8">
-        <v>55.34</v>
+        <v>48.9</v>
       </c>
       <c r="I8">
-        <v>14.65</v>
+        <v>11.21</v>
       </c>
       <c r="J8">
-        <v>31.12</v>
+        <v>26.93</v>
       </c>
       <c r="K8">
-        <v>35.48</v>
+        <v>29.83</v>
       </c>
       <c r="L8">
-        <v>34.2</v>
+        <v>33.75</v>
       </c>
       <c r="M8">
-        <v>6.8</v>
+        <v>4.88</v>
       </c>
       <c r="N8">
         <v>85</v>
       </c>
       <c r="O8">
-        <v>90</v>
+        <v>88</v>
       </c>
       <c r="P8">
-        <v>169.19</v>
+        <v>172.67</v>
       </c>
       <c r="Q8">
-        <v>145.89</v>
+        <v>147.82</v>
       </c>
       <c r="R8">
-        <v>141.45</v>
+        <v>142.06</v>
       </c>
       <c r="S8">
-        <v>134.94</v>
+        <v>135.12</v>
       </c>
       <c r="T8">
-        <v>33.49</v>
+        <v>27.78</v>
       </c>
       <c r="U8" t="s">
         <v>46</v>
@@ -1662,34 +1681,34 @@
         <v>3</v>
       </c>
       <c r="Y8">
-        <v>84.12</v>
+        <v>72.51000000000001</v>
       </c>
       <c r="Z8">
-        <v>8.99</v>
+        <v>9.52</v>
       </c>
       <c r="AA8">
-        <v>4.47</v>
+        <v>5.48</v>
       </c>
       <c r="AB8">
-        <v>4.52</v>
+        <v>4.04</v>
       </c>
       <c r="AC8">
-        <v>100</v>
+        <v>90.52</v>
       </c>
       <c r="AD8">
-        <v>98.73999999999999</v>
+        <v>96.84</v>
       </c>
       <c r="AE8">
-        <v>6.9</v>
+        <v>7.4</v>
       </c>
       <c r="AF8">
-        <v>249.72</v>
+        <v>80.64</v>
       </c>
       <c r="AG8">
-        <v>176.51</v>
+        <v>180.12</v>
       </c>
       <c r="AH8">
-        <v>115.28</v>
+        <v>115.52</v>
       </c>
       <c r="AI8">
         <v>158.84</v>
@@ -1698,7 +1717,7 @@
         <v>48</v>
       </c>
       <c r="AK8">
-        <v>52.12</v>
+        <v>52.76</v>
       </c>
     </row>
   </sheetData>
@@ -1879,646 +1898,643 @@
     </row>
     <row r="3" spans="1:6">
       <c r="A3" s="4" t="s">
+        <v>43</v>
+      </c>
+      <c r="B3" s="4" t="s">
+        <v>55</v>
+      </c>
+      <c r="C3" s="4" t="s">
+        <v>56</v>
+      </c>
+      <c r="D3" s="4" t="s">
+        <v>57</v>
+      </c>
+      <c r="E3" s="4" t="s">
+        <v>58</v>
+      </c>
+      <c r="F3" s="4" t="s">
+        <v>59</v>
+      </c>
+    </row>
+    <row r="5" spans="1:6">
+      <c r="A5" s="2" t="s">
+        <v>60</v>
+      </c>
+      <c r="B5" s="2"/>
+      <c r="C5" s="2"/>
+      <c r="D5" s="2"/>
+      <c r="E5" s="2"/>
+    </row>
+    <row r="6" spans="1:6">
+      <c r="A6" s="3" t="s">
+        <v>0</v>
+      </c>
+      <c r="B6" s="3" t="s">
+        <v>61</v>
+      </c>
+      <c r="C6" s="3" t="s">
+        <v>62</v>
+      </c>
+      <c r="D6" s="3" t="s">
+        <v>63</v>
+      </c>
+      <c r="E6" s="3" t="s">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="7" spans="1:6">
+      <c r="A7" s="5" t="s">
         <v>37</v>
       </c>
-      <c r="B3" s="4" t="s">
-        <v>22</v>
-      </c>
-      <c r="C3" s="4" t="s">
-        <v>55</v>
-      </c>
-      <c r="D3" s="4" t="s">
-        <v>56</v>
-      </c>
-      <c r="E3" s="4" t="s">
-        <v>46</v>
-      </c>
-      <c r="F3" s="4" t="s">
-        <v>45</v>
-      </c>
-    </row>
-    <row r="4" spans="1:6">
-      <c r="A4" s="4" t="s">
-        <v>37</v>
-      </c>
-      <c r="B4" s="4" t="s">
-        <v>57</v>
-      </c>
-      <c r="C4" s="4" t="s">
-        <v>55</v>
-      </c>
-      <c r="D4" s="4" t="s">
-        <v>56</v>
-      </c>
-      <c r="E4" s="4" t="s">
-        <v>46</v>
-      </c>
-      <c r="F4" s="4" t="s">
-        <v>45</v>
-      </c>
-    </row>
-    <row r="6" spans="1:6">
-      <c r="A6" s="2" t="s">
-        <v>58</v>
-      </c>
-      <c r="B6" s="2"/>
-      <c r="C6" s="2"/>
-      <c r="D6" s="2"/>
-      <c r="E6" s="2"/>
-    </row>
-    <row r="7" spans="1:6">
-      <c r="A7" s="3" t="s">
-        <v>0</v>
-      </c>
-      <c r="B7" s="3" t="s">
-        <v>59</v>
-      </c>
-      <c r="C7" s="3" t="s">
-        <v>60</v>
-      </c>
-      <c r="D7" s="3" t="s">
-        <v>61</v>
-      </c>
-      <c r="E7" s="3" t="s">
-        <v>62</v>
+      <c r="B7" s="5" t="s">
+        <v>9</v>
+      </c>
+      <c r="C7" s="6">
+        <v>-10.35</v>
+      </c>
+      <c r="D7" s="6">
+        <v>-18.74</v>
+      </c>
+      <c r="E7" s="7">
+        <v>-8.390000000000001</v>
       </c>
     </row>
     <row r="8" spans="1:6">
       <c r="A8" s="5" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="B8" s="5" t="s">
         <v>9</v>
       </c>
       <c r="C8" s="6">
-        <v>-9.23</v>
+        <v>4.54</v>
       </c>
       <c r="D8" s="6">
-        <v>-10.35</v>
-      </c>
-      <c r="E8" s="7">
-        <v>-1.12</v>
+        <v>5.32</v>
+      </c>
+      <c r="E8" s="8">
+        <v>0.78</v>
       </c>
     </row>
     <row r="9" spans="1:6">
       <c r="A9" s="5" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="B9" s="5" t="s">
         <v>9</v>
       </c>
       <c r="C9" s="6">
-        <v>3.26</v>
+        <v>-6.59</v>
       </c>
       <c r="D9" s="6">
-        <v>4.54</v>
-      </c>
-      <c r="E9" s="8">
-        <v>1.28</v>
+        <v>-7.99</v>
+      </c>
+      <c r="E9" s="7">
+        <v>-1.4</v>
       </c>
     </row>
     <row r="10" spans="1:6">
       <c r="A10" s="5" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="B10" s="5" t="s">
         <v>9</v>
       </c>
       <c r="C10" s="6">
-        <v>-6.88</v>
+        <v>-14.35</v>
       </c>
       <c r="D10" s="6">
-        <v>-6.59</v>
+        <v>-12.14</v>
       </c>
       <c r="E10" s="8">
-        <v>0.29</v>
+        <v>2.21</v>
       </c>
     </row>
     <row r="11" spans="1:6">
       <c r="A11" s="5" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="B11" s="5" t="s">
         <v>9</v>
       </c>
       <c r="C11" s="6">
-        <v>-12.97</v>
+        <v>-7.35</v>
       </c>
       <c r="D11" s="6">
-        <v>-14.35</v>
-      </c>
-      <c r="E11" s="7">
-        <v>-1.38</v>
+        <v>-5.69</v>
+      </c>
+      <c r="E11" s="8">
+        <v>1.66</v>
       </c>
     </row>
     <row r="12" spans="1:6">
       <c r="A12" s="5" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="B12" s="5" t="s">
         <v>9</v>
       </c>
       <c r="C12" s="6">
-        <v>-6.53</v>
+        <v>-9.23</v>
       </c>
       <c r="D12" s="6">
-        <v>-7.35</v>
+        <v>-10.02</v>
       </c>
       <c r="E12" s="7">
-        <v>-0.82</v>
+        <v>-0.79</v>
       </c>
     </row>
     <row r="13" spans="1:6">
       <c r="A13" s="5" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="B13" s="5" t="s">
         <v>9</v>
       </c>
       <c r="C13" s="6">
-        <v>-9.82</v>
+        <v>31.12</v>
       </c>
       <c r="D13" s="6">
-        <v>-9.23</v>
-      </c>
-      <c r="E13" s="8">
-        <v>0.59</v>
+        <v>26.93</v>
+      </c>
+      <c r="E13" s="7">
+        <v>-4.19</v>
       </c>
     </row>
     <row r="14" spans="1:6">
       <c r="A14" s="5" t="s">
-        <v>43</v>
+        <v>37</v>
       </c>
       <c r="B14" s="5" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="C14" s="6">
-        <v>25.66</v>
+        <v>-4.61</v>
       </c>
       <c r="D14" s="6">
-        <v>31.12</v>
-      </c>
-      <c r="E14" s="8">
-        <v>5.46</v>
+        <v>-10.38</v>
+      </c>
+      <c r="E14" s="7">
+        <v>-5.77</v>
       </c>
     </row>
     <row r="15" spans="1:6">
       <c r="A15" s="5" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="B15" s="5" t="s">
         <v>8</v>
       </c>
       <c r="C15" s="6">
-        <v>-4.86</v>
+        <v>-2.04</v>
       </c>
       <c r="D15" s="6">
-        <v>-4.61</v>
+        <v>-0.93</v>
       </c>
       <c r="E15" s="8">
-        <v>0.25</v>
+        <v>1.11</v>
       </c>
     </row>
     <row r="16" spans="1:6">
       <c r="A16" s="5" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="B16" s="5" t="s">
         <v>8</v>
       </c>
       <c r="C16" s="6">
-        <v>-4.04</v>
+        <v>-7.89</v>
       </c>
       <c r="D16" s="6">
-        <v>-2.04</v>
+        <v>-6.74</v>
       </c>
       <c r="E16" s="8">
-        <v>2</v>
+        <v>1.15</v>
       </c>
     </row>
     <row r="17" spans="1:5">
       <c r="A17" s="5" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="B17" s="5" t="s">
         <v>8</v>
       </c>
       <c r="C17" s="6">
-        <v>-4.2</v>
+        <v>-6.26</v>
       </c>
       <c r="D17" s="6">
-        <v>-7.89</v>
-      </c>
-      <c r="E17" s="7">
-        <v>-3.69</v>
+        <v>-1.69</v>
+      </c>
+      <c r="E17" s="8">
+        <v>4.57</v>
       </c>
     </row>
     <row r="18" spans="1:5">
       <c r="A18" s="5" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="B18" s="5" t="s">
         <v>8</v>
       </c>
       <c r="C18" s="6">
-        <v>-4.44</v>
+        <v>-5.77</v>
       </c>
       <c r="D18" s="6">
-        <v>-6.26</v>
-      </c>
-      <c r="E18" s="7">
-        <v>-1.82</v>
+        <v>-2.3</v>
+      </c>
+      <c r="E18" s="8">
+        <v>3.47</v>
       </c>
     </row>
     <row r="19" spans="1:5">
       <c r="A19" s="5" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="B19" s="5" t="s">
         <v>8</v>
       </c>
       <c r="C19" s="6">
-        <v>-5.23</v>
+        <v>-8.029999999999999</v>
       </c>
       <c r="D19" s="6">
-        <v>-5.77</v>
-      </c>
-      <c r="E19" s="7">
-        <v>-0.54</v>
+        <v>-3.43</v>
+      </c>
+      <c r="E19" s="8">
+        <v>4.6</v>
       </c>
     </row>
     <row r="20" spans="1:5">
       <c r="A20" s="5" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="B20" s="5" t="s">
         <v>8</v>
       </c>
       <c r="C20" s="6">
-        <v>-3.47</v>
+        <v>14.65</v>
       </c>
       <c r="D20" s="6">
-        <v>-8.029999999999999</v>
+        <v>11.21</v>
       </c>
       <c r="E20" s="7">
-        <v>-4.56</v>
+        <v>-3.44</v>
       </c>
     </row>
     <row r="21" spans="1:5">
       <c r="A21" s="5" t="s">
-        <v>43</v>
+        <v>37</v>
       </c>
       <c r="B21" s="5" t="s">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="C21" s="6">
-        <v>21.98</v>
+        <v>24.7</v>
       </c>
       <c r="D21" s="6">
-        <v>14.65</v>
+        <v>17.06</v>
       </c>
       <c r="E21" s="7">
-        <v>-7.33</v>
+        <v>-7.64</v>
       </c>
     </row>
     <row r="22" spans="1:5">
       <c r="A22" s="5" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="B22" s="5" t="s">
         <v>11</v>
       </c>
       <c r="C22" s="6">
-        <v>24.03</v>
+        <v>103.11</v>
       </c>
       <c r="D22" s="6">
-        <v>24.7</v>
+        <v>113.43</v>
       </c>
       <c r="E22" s="8">
-        <v>0.67</v>
+        <v>10.32</v>
       </c>
     </row>
     <row r="23" spans="1:5">
       <c r="A23" s="5" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="B23" s="5" t="s">
         <v>11</v>
       </c>
       <c r="C23" s="6">
-        <v>100.05</v>
+        <v>-46.3</v>
       </c>
       <c r="D23" s="6">
-        <v>103.11</v>
+        <v>-44.82</v>
       </c>
       <c r="E23" s="8">
-        <v>3.06</v>
+        <v>1.48</v>
       </c>
     </row>
     <row r="24" spans="1:5">
       <c r="A24" s="5" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="B24" s="5" t="s">
         <v>11</v>
       </c>
       <c r="C24" s="6">
-        <v>-47.46</v>
+        <v>-14.96</v>
       </c>
       <c r="D24" s="6">
-        <v>-46.3</v>
+        <v>-13.51</v>
       </c>
       <c r="E24" s="8">
-        <v>1.16</v>
+        <v>1.45</v>
       </c>
     </row>
     <row r="25" spans="1:5">
       <c r="A25" s="5" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="B25" s="5" t="s">
         <v>11</v>
       </c>
       <c r="C25" s="6">
-        <v>-15.79</v>
+        <v>-16.37</v>
       </c>
       <c r="D25" s="6">
-        <v>-14.96</v>
+        <v>-16</v>
       </c>
       <c r="E25" s="8">
-        <v>0.83</v>
+        <v>0.37</v>
       </c>
     </row>
     <row r="26" spans="1:5">
       <c r="A26" s="5" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="B26" s="5" t="s">
         <v>11</v>
       </c>
       <c r="C26" s="6">
-        <v>-19.72</v>
+        <v>-5.27</v>
       </c>
       <c r="D26" s="6">
-        <v>-16.37</v>
+        <v>-3.74</v>
       </c>
       <c r="E26" s="8">
-        <v>3.35</v>
+        <v>1.53</v>
       </c>
     </row>
     <row r="27" spans="1:5">
       <c r="A27" s="5" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="B27" s="5" t="s">
         <v>11</v>
       </c>
       <c r="C27" s="6">
-        <v>-5.43</v>
+        <v>34.2</v>
       </c>
       <c r="D27" s="6">
-        <v>-5.27</v>
-      </c>
-      <c r="E27" s="8">
-        <v>0.16</v>
+        <v>33.75</v>
+      </c>
+      <c r="E27" s="7">
+        <v>-0.45</v>
       </c>
     </row>
     <row r="28" spans="1:5">
       <c r="A28" s="5" t="s">
-        <v>43</v>
+        <v>37</v>
       </c>
       <c r="B28" s="5" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="C28" s="6">
-        <v>27.32</v>
+        <v>10.32</v>
       </c>
       <c r="D28" s="6">
-        <v>34.2</v>
-      </c>
-      <c r="E28" s="8">
-        <v>6.88</v>
+        <v>2.65</v>
+      </c>
+      <c r="E28" s="7">
+        <v>-7.67</v>
       </c>
     </row>
     <row r="29" spans="1:5">
       <c r="A29" s="5" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="B29" s="5" t="s">
         <v>10</v>
       </c>
       <c r="C29" s="6">
-        <v>9.85</v>
+        <v>-19.02</v>
       </c>
       <c r="D29" s="6">
-        <v>10.32</v>
-      </c>
-      <c r="E29" s="8">
-        <v>0.47</v>
+        <v>-19.34</v>
+      </c>
+      <c r="E29" s="7">
+        <v>-0.32</v>
       </c>
     </row>
     <row r="30" spans="1:5">
       <c r="A30" s="5" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="B30" s="5" t="s">
         <v>10</v>
       </c>
       <c r="C30" s="6">
-        <v>-19.78</v>
+        <v>-8.119999999999999</v>
       </c>
       <c r="D30" s="6">
-        <v>-19.02</v>
-      </c>
-      <c r="E30" s="8">
-        <v>0.76</v>
+        <v>-8.859999999999999</v>
+      </c>
+      <c r="E30" s="7">
+        <v>-0.74</v>
       </c>
     </row>
     <row r="31" spans="1:5">
       <c r="A31" s="5" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="B31" s="5" t="s">
         <v>10</v>
       </c>
       <c r="C31" s="6">
-        <v>-3.11</v>
+        <v>-6.72</v>
       </c>
       <c r="D31" s="6">
-        <v>-8.119999999999999</v>
+        <v>-8.6</v>
       </c>
       <c r="E31" s="7">
-        <v>-5.01</v>
+        <v>-1.88</v>
       </c>
     </row>
     <row r="32" spans="1:5">
       <c r="A32" s="5" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="B32" s="5" t="s">
         <v>10</v>
       </c>
       <c r="C32" s="6">
-        <v>-3.07</v>
+        <v>-0.64</v>
       </c>
       <c r="D32" s="6">
-        <v>-6.72</v>
+        <v>-3.73</v>
       </c>
       <c r="E32" s="7">
-        <v>-3.65</v>
+        <v>-3.09</v>
       </c>
     </row>
     <row r="33" spans="1:5">
       <c r="A33" s="5" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="B33" s="5" t="s">
         <v>10</v>
       </c>
       <c r="C33" s="6">
-        <v>-1.11</v>
+        <v>-5.79</v>
       </c>
       <c r="D33" s="6">
-        <v>-0.64</v>
-      </c>
-      <c r="E33" s="8">
-        <v>0.47</v>
+        <v>-8.06</v>
+      </c>
+      <c r="E33" s="7">
+        <v>-2.27</v>
       </c>
     </row>
     <row r="34" spans="1:5">
       <c r="A34" s="5" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="B34" s="5" t="s">
         <v>10</v>
       </c>
       <c r="C34" s="6">
-        <v>-4.05</v>
+        <v>35.48</v>
       </c>
       <c r="D34" s="6">
-        <v>-5.79</v>
+        <v>29.83</v>
       </c>
       <c r="E34" s="7">
-        <v>-1.74</v>
+        <v>-5.65</v>
       </c>
     </row>
     <row r="35" spans="1:5">
       <c r="A35" s="5" t="s">
-        <v>43</v>
+        <v>37</v>
       </c>
       <c r="B35" s="5" t="s">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="C35" s="6">
-        <v>30.01</v>
+        <v>-12.03</v>
       </c>
       <c r="D35" s="6">
-        <v>35.48</v>
-      </c>
-      <c r="E35" s="8">
-        <v>5.47</v>
+        <v>-18.74</v>
+      </c>
+      <c r="E35" s="7">
+        <v>-6.71</v>
       </c>
     </row>
     <row r="36" spans="1:5">
       <c r="A36" s="5" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="B36" s="5" t="s">
         <v>6</v>
       </c>
       <c r="C36" s="6">
-        <v>-12.54</v>
+        <v>-26.06</v>
       </c>
       <c r="D36" s="6">
-        <v>-12.03</v>
+        <v>-25.84</v>
       </c>
       <c r="E36" s="8">
-        <v>0.51</v>
+        <v>0.22</v>
       </c>
     </row>
     <row r="37" spans="1:5">
       <c r="A37" s="5" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="B37" s="5" t="s">
         <v>6</v>
       </c>
       <c r="C37" s="6">
-        <v>-26.45</v>
+        <v>-45.33</v>
       </c>
       <c r="D37" s="6">
-        <v>-26.06</v>
-      </c>
-      <c r="E37" s="8">
-        <v>0.39</v>
+        <v>-45.98</v>
+      </c>
+      <c r="E37" s="7">
+        <v>-0.65</v>
       </c>
     </row>
     <row r="38" spans="1:5">
       <c r="A38" s="5" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="B38" s="5" t="s">
         <v>6</v>
       </c>
       <c r="C38" s="6">
-        <v>-45.15</v>
+        <v>-20.47</v>
       </c>
       <c r="D38" s="6">
-        <v>-45.33</v>
-      </c>
-      <c r="E38" s="7">
-        <v>-0.18</v>
+        <v>-20.4</v>
+      </c>
+      <c r="E38" s="8">
+        <v>0.07000000000000001</v>
       </c>
     </row>
     <row r="39" spans="1:5">
       <c r="A39" s="5" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="B39" s="5" t="s">
         <v>6</v>
       </c>
       <c r="C39" s="6">
-        <v>-19.95</v>
+        <v>-17.92</v>
       </c>
       <c r="D39" s="6">
-        <v>-20.47</v>
+        <v>-18.85</v>
       </c>
       <c r="E39" s="7">
-        <v>-0.52</v>
+        <v>-0.93</v>
       </c>
     </row>
     <row r="40" spans="1:5">
       <c r="A40" s="5" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="B40" s="5" t="s">
         <v>6</v>
       </c>
       <c r="C40" s="6">
-        <v>-19.35</v>
+        <v>-17.21</v>
       </c>
       <c r="D40" s="6">
-        <v>-17.92</v>
-      </c>
-      <c r="E40" s="8">
-        <v>1.43</v>
+        <v>-18.17</v>
+      </c>
+      <c r="E40" s="7">
+        <v>-0.96</v>
       </c>
     </row>
     <row r="41" spans="1:5">
       <c r="A41" s="5" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="B41" s="5" t="s">
         <v>6</v>
       </c>
       <c r="C41" s="6">
-        <v>-15.96</v>
+        <v>0</v>
       </c>
       <c r="D41" s="6">
-        <v>-17.21</v>
+        <v>-4.15</v>
       </c>
       <c r="E41" s="7">
-        <v>-1.25</v>
+        <v>-4.15</v>
       </c>
     </row>
     <row r="42" spans="1:5">
@@ -2529,13 +2545,13 @@
         <v>2</v>
       </c>
       <c r="C42" s="6">
-        <v>10811</v>
+        <v>10874</v>
       </c>
       <c r="D42" s="6">
-        <v>10874</v>
-      </c>
-      <c r="E42" s="8">
-        <v>63</v>
+        <v>10045</v>
+      </c>
+      <c r="E42" s="7">
+        <v>-829</v>
       </c>
     </row>
     <row r="43" spans="1:5">
@@ -2546,13 +2562,13 @@
         <v>2</v>
       </c>
       <c r="C43" s="6">
-        <v>493</v>
+        <v>495.55</v>
       </c>
       <c r="D43" s="6">
-        <v>495.55</v>
+        <v>497.05</v>
       </c>
       <c r="E43" s="8">
-        <v>2.55</v>
+        <v>1.5</v>
       </c>
     </row>
     <row r="44" spans="1:5">
@@ -2563,13 +2579,13 @@
         <v>2</v>
       </c>
       <c r="C44" s="6">
-        <v>309.85</v>
+        <v>303.4</v>
       </c>
       <c r="D44" s="6">
-        <v>303.4</v>
+        <v>299.8</v>
       </c>
       <c r="E44" s="7">
-        <v>-6.45</v>
+        <v>-3.6</v>
       </c>
     </row>
     <row r="45" spans="1:5">
@@ -2580,13 +2596,13 @@
         <v>2</v>
       </c>
       <c r="C45" s="6">
-        <v>1742.4</v>
+        <v>1731</v>
       </c>
       <c r="D45" s="6">
-        <v>1731</v>
-      </c>
-      <c r="E45" s="7">
-        <v>-11.4</v>
+        <v>1732.6</v>
+      </c>
+      <c r="E45" s="8">
+        <v>1.6</v>
       </c>
     </row>
     <row r="46" spans="1:5">
@@ -2597,13 +2613,13 @@
         <v>2</v>
       </c>
       <c r="C46" s="6">
-        <v>10600</v>
+        <v>10788</v>
       </c>
       <c r="D46" s="6">
-        <v>10788</v>
-      </c>
-      <c r="E46" s="8">
-        <v>188</v>
+        <v>10666</v>
+      </c>
+      <c r="E46" s="7">
+        <v>-122</v>
       </c>
     </row>
     <row r="47" spans="1:5">
@@ -2614,13 +2630,13 @@
         <v>2</v>
       </c>
       <c r="C47" s="6">
-        <v>973.8</v>
+        <v>959.4</v>
       </c>
       <c r="D47" s="6">
-        <v>959.4</v>
+        <v>948.3</v>
       </c>
       <c r="E47" s="7">
-        <v>-14.4</v>
+        <v>-11.1</v>
       </c>
     </row>
     <row r="48" spans="1:5">
@@ -2631,13 +2647,13 @@
         <v>2</v>
       </c>
       <c r="C48" s="6">
-        <v>172.49</v>
+        <v>180.13</v>
       </c>
       <c r="D48" s="6">
-        <v>180.13</v>
-      </c>
-      <c r="E48" s="8">
-        <v>7.64</v>
+        <v>172.66</v>
+      </c>
+      <c r="E48" s="7">
+        <v>-7.47</v>
       </c>
     </row>
     <row r="49" spans="1:5">
@@ -2648,13 +2664,13 @@
         <v>24</v>
       </c>
       <c r="C49" s="6">
-        <v>30.48</v>
+        <v>32.99</v>
       </c>
       <c r="D49" s="6">
-        <v>32.99</v>
-      </c>
-      <c r="E49" s="8">
-        <v>2.51</v>
+        <v>21.8</v>
+      </c>
+      <c r="E49" s="7">
+        <v>-11.19</v>
       </c>
     </row>
     <row r="50" spans="1:5">
@@ -2665,13 +2681,13 @@
         <v>24</v>
       </c>
       <c r="C50" s="6">
-        <v>45.21</v>
+        <v>46.36</v>
       </c>
       <c r="D50" s="6">
-        <v>46.36</v>
+        <v>47.06</v>
       </c>
       <c r="E50" s="8">
-        <v>1.15</v>
+        <v>0.7</v>
       </c>
     </row>
     <row r="51" spans="1:5">
@@ -2682,13 +2698,13 @@
         <v>24</v>
       </c>
       <c r="C51" s="6">
-        <v>33.54</v>
+        <v>30.23</v>
       </c>
       <c r="D51" s="6">
-        <v>30.23</v>
+        <v>28.53</v>
       </c>
       <c r="E51" s="7">
-        <v>-3.31</v>
+        <v>-1.7</v>
       </c>
     </row>
     <row r="52" spans="1:5">
@@ -2699,13 +2715,13 @@
         <v>24</v>
       </c>
       <c r="C52" s="6">
-        <v>25.68</v>
+        <v>24.67</v>
       </c>
       <c r="D52" s="6">
-        <v>24.67</v>
-      </c>
-      <c r="E52" s="7">
-        <v>-1.01</v>
+        <v>25.11</v>
+      </c>
+      <c r="E52" s="8">
+        <v>0.44</v>
       </c>
     </row>
     <row r="53" spans="1:5">
@@ -2716,13 +2732,13 @@
         <v>24</v>
       </c>
       <c r="C53" s="6">
-        <v>38.48</v>
+        <v>43.44</v>
       </c>
       <c r="D53" s="6">
-        <v>43.44</v>
-      </c>
-      <c r="E53" s="8">
-        <v>4.96</v>
+        <v>41.12</v>
+      </c>
+      <c r="E53" s="7">
+        <v>-2.32</v>
       </c>
     </row>
     <row r="54" spans="1:5">
@@ -2733,13 +2749,13 @@
         <v>24</v>
       </c>
       <c r="C54" s="6">
-        <v>36.26</v>
+        <v>33.9</v>
       </c>
       <c r="D54" s="6">
-        <v>33.9</v>
+        <v>32.16</v>
       </c>
       <c r="E54" s="7">
-        <v>-2.36</v>
+        <v>-1.74</v>
       </c>
     </row>
     <row r="55" spans="1:5">
@@ -2750,13 +2766,13 @@
         <v>24</v>
       </c>
       <c r="C55" s="6">
-        <v>81.28</v>
+        <v>84.12</v>
       </c>
       <c r="D55" s="6">
-        <v>84.12</v>
-      </c>
-      <c r="E55" s="8">
-        <v>2.84</v>
+        <v>72.51000000000001</v>
+      </c>
+      <c r="E55" s="7">
+        <v>-11.61</v>
       </c>
     </row>
     <row r="56" spans="1:5">
@@ -2767,13 +2783,13 @@
         <v>31</v>
       </c>
       <c r="C56" s="6">
-        <v>146.13</v>
+        <v>38.15</v>
       </c>
       <c r="D56" s="6">
-        <v>38.15</v>
-      </c>
-      <c r="E56" s="7">
-        <v>-107.98</v>
+        <v>562.46</v>
+      </c>
+      <c r="E56" s="8">
+        <v>524.3099999999999</v>
       </c>
     </row>
     <row r="57" spans="1:5">
@@ -2784,13 +2800,13 @@
         <v>31</v>
       </c>
       <c r="C57" s="6">
-        <v>10.68</v>
+        <v>-70.44</v>
       </c>
       <c r="D57" s="6">
-        <v>-70.44</v>
-      </c>
-      <c r="E57" s="7">
-        <v>-81.12</v>
+        <v>-39.15</v>
+      </c>
+      <c r="E57" s="8">
+        <v>31.29</v>
       </c>
     </row>
     <row r="58" spans="1:5">
@@ -2801,13 +2817,13 @@
         <v>31</v>
       </c>
       <c r="C58" s="6">
-        <v>217.44</v>
+        <v>29.63</v>
       </c>
       <c r="D58" s="6">
-        <v>29.63</v>
+        <v>-12.05</v>
       </c>
       <c r="E58" s="7">
-        <v>-187.81</v>
+        <v>-41.68</v>
       </c>
     </row>
     <row r="59" spans="1:5">
@@ -2818,13 +2834,13 @@
         <v>31</v>
       </c>
       <c r="C59" s="6">
-        <v>27.93</v>
+        <v>58.48</v>
       </c>
       <c r="D59" s="6">
-        <v>58.48</v>
+        <v>226.11</v>
       </c>
       <c r="E59" s="8">
-        <v>30.55</v>
+        <v>167.63</v>
       </c>
     </row>
     <row r="60" spans="1:5">
@@ -2835,13 +2851,13 @@
         <v>31</v>
       </c>
       <c r="C60" s="6">
-        <v>51.72</v>
+        <v>-9.91</v>
       </c>
       <c r="D60" s="6">
-        <v>-9.91</v>
-      </c>
-      <c r="E60" s="7">
-        <v>-61.63</v>
+        <v>-9.199999999999999</v>
+      </c>
+      <c r="E60" s="8">
+        <v>0.71</v>
       </c>
     </row>
     <row r="61" spans="1:5">
@@ -2852,13 +2868,13 @@
         <v>31</v>
       </c>
       <c r="C61" s="6">
-        <v>41.38</v>
+        <v>5.48</v>
       </c>
       <c r="D61" s="6">
-        <v>5.48</v>
+        <v>-9.74</v>
       </c>
       <c r="E61" s="7">
-        <v>-35.9</v>
+        <v>-15.22</v>
       </c>
     </row>
     <row r="62" spans="1:5">
@@ -2869,19 +2885,19 @@
         <v>31</v>
       </c>
       <c r="C62" s="6">
-        <v>119.63</v>
+        <v>249.72</v>
       </c>
       <c r="D62" s="6">
-        <v>249.72</v>
-      </c>
-      <c r="E62" s="8">
-        <v>130.09</v>
+        <v>80.64</v>
+      </c>
+      <c r="E62" s="7">
+        <v>-169.08</v>
       </c>
     </row>
   </sheetData>
   <mergeCells count="2">
     <mergeCell ref="A1:F1"/>
-    <mergeCell ref="A6:E6"/>
+    <mergeCell ref="A5:E5"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -2905,28 +2921,28 @@
         <v>1</v>
       </c>
       <c r="B1" s="9" t="s">
-        <v>63</v>
+        <v>65</v>
       </c>
       <c r="C1" s="9" t="s">
-        <v>64</v>
+        <v>66</v>
       </c>
       <c r="D1" s="9" t="s">
-        <v>65</v>
+        <v>67</v>
       </c>
       <c r="E1" s="9" t="s">
-        <v>66</v>
+        <v>68</v>
       </c>
       <c r="F1" s="9" t="s">
-        <v>67</v>
+        <v>69</v>
       </c>
       <c r="G1" s="9" t="s">
-        <v>68</v>
+        <v>70</v>
       </c>
       <c r="H1" s="9" t="s">
-        <v>69</v>
+        <v>71</v>
       </c>
       <c r="I1" s="9" t="s">
-        <v>70</v>
+        <v>72</v>
       </c>
     </row>
     <row r="2" spans="1:9">
@@ -2934,22 +2950,22 @@
         <v>44</v>
       </c>
       <c r="B2" s="11">
-        <v>56.8</v>
+        <v>44.8</v>
       </c>
       <c r="C2" s="12">
         <v>7</v>
       </c>
       <c r="D2" s="11">
-        <v>42.2</v>
+        <v>38.3</v>
       </c>
       <c r="E2" s="11">
-        <v>60</v>
+        <v>30</v>
       </c>
       <c r="F2" s="11">
-        <v>-1.7</v>
+        <v>-3.2</v>
       </c>
       <c r="G2" s="11">
-        <v>0.8</v>
+        <v>-2.3</v>
       </c>
       <c r="H2" s="11">
         <v>57</v>
@@ -3066,10 +3082,10 @@
         <v>38</v>
       </c>
       <c r="D1" s="13" t="s">
+        <v>42</v>
+      </c>
+      <c r="E1" s="13" t="s">
         <v>43</v>
-      </c>
-      <c r="E1" s="13" t="s">
-        <v>42</v>
       </c>
       <c r="F1" s="13" t="s">
         <v>40</v>
@@ -3080,25 +3096,25 @@
     </row>
     <row r="2" spans="1:7">
       <c r="A2" s="14">
-        <v>0.2604</v>
+        <v>0.2393</v>
       </c>
       <c r="B2" s="14">
-        <v>0.1882</v>
+        <v>0.189</v>
       </c>
       <c r="C2" s="14">
-        <v>0.164</v>
+        <v>0.1638</v>
       </c>
       <c r="D2" s="14">
-        <v>0.068</v>
+        <v>0.05139999999999999</v>
       </c>
       <c r="E2" s="14">
-        <v>0.0498</v>
+        <v>0.0488</v>
       </c>
       <c r="F2" s="14">
-        <v>-0.005</v>
+        <v>0.0021</v>
       </c>
       <c r="G2" s="14">
-        <v>-0.242</v>
+        <v>-0.2439</v>
       </c>
     </row>
   </sheetData>

--- a/BAJAJ_GROUP_Technical_Metrics.xlsx
+++ b/BAJAJ_GROUP_Technical_Metrics.xlsx
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="264" uniqueCount="73">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="274" uniqueCount="78">
   <si>
     <t>Symbol</t>
   </si>
@@ -187,19 +187,34 @@
     <t>Curr Value</t>
   </si>
   <si>
-    <t>Left 52W High Zone</t>
-  </si>
-  <si>
-    <t>0.0% → -4.2%</t>
-  </si>
-  <si>
-    <t>⚪ NEUTRAL</t>
+    <t>Near 52W High</t>
+  </si>
+  <si>
+    <t>-4.2% → 0.0%</t>
+  </si>
+  <si>
+    <t>🟢 BREAKOUT WATCH</t>
+  </si>
+  <si>
+    <t>-4.2%</t>
   </si>
   <si>
     <t>0.0%</t>
   </si>
   <si>
-    <t>-4.2%</t>
+    <t>RSI Oversold Recovery</t>
+  </si>
+  <si>
+    <t>25.1 → 30.3</t>
+  </si>
+  <si>
+    <t>🟢 BULLISH</t>
+  </si>
+  <si>
+    <t>25.1</t>
+  </si>
+  <si>
+    <t>30.3</t>
   </si>
   <si>
     <t>▶  NUMERIC METRIC CHANGES (vs Previous Run)</t>
@@ -251,7 +266,7 @@
     <numFmt numFmtId="166" formatCode="0.0"/>
     <numFmt numFmtId="167" formatCode="0.00%"/>
   </numFmts>
-  <fonts count="7">
+  <fonts count="6">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -285,7 +300,7 @@
     </font>
     <font>
       <sz val="11"/>
-      <color rgb="FF1F4E79"/>
+      <color rgb="FF006100"/>
       <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
@@ -297,15 +312,8 @@
       <family val="2"/>
       <scheme val="minor"/>
     </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF006100"/>
-      <name val="Calibri"/>
-      <family val="2"/>
-      <scheme val="minor"/>
-    </font>
   </fonts>
-  <fills count="10">
+  <fills count="9">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -332,19 +340,13 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFDDEBF7"/>
+        <fgColor rgb="FFC6EFCE"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="FFFFC7CE"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFC6EFCE"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -424,12 +426,12 @@
     <xf numFmtId="0" fontId="4" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1"/>
+    <xf numFmtId="165" fontId="4" fillId="5" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="165" fontId="5" fillId="6" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="165" fontId="6" fillId="7" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="3" fillId="8" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="7" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="9" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="8" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
     <xf numFmtId="166" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
@@ -438,7 +440,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="9" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="8" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="167" fontId="0" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
@@ -796,8 +798,8 @@
     <col min="13" max="13" width="10.7109375" customWidth="1"/>
     <col min="14" max="14" width="11.7109375" customWidth="1"/>
     <col min="15" max="15" width="10.7109375" customWidth="1"/>
-    <col min="16" max="16" width="9.7109375" customWidth="1"/>
-    <col min="17" max="19" width="10.7109375" customWidth="1"/>
+    <col min="16" max="17" width="9.7109375" customWidth="1"/>
+    <col min="18" max="19" width="10.7109375" customWidth="1"/>
     <col min="20" max="20" width="22.7109375" customWidth="1"/>
     <col min="21" max="21" width="9.7109375" customWidth="1"/>
     <col min="22" max="22" width="10.7109375" customWidth="1"/>
@@ -937,10 +939,10 @@
         <v>44</v>
       </c>
       <c r="C2">
-        <v>10045</v>
+        <v>10024</v>
       </c>
       <c r="D2">
-        <v>-7.62</v>
+        <v>-0.21</v>
       </c>
       <c r="E2">
         <v>12361</v>
@@ -949,46 +951,46 @@
         <v>8506.780000000001</v>
       </c>
       <c r="G2">
-        <v>-18.74</v>
+        <v>-18.91</v>
       </c>
       <c r="H2">
-        <v>18.08</v>
+        <v>17.84</v>
       </c>
       <c r="I2">
-        <v>-10.38</v>
+        <v>-11.14</v>
       </c>
       <c r="J2">
-        <v>-18.74</v>
+        <v>-17.36</v>
       </c>
       <c r="K2">
-        <v>2.65</v>
+        <v>-0.12</v>
       </c>
       <c r="L2">
-        <v>17.06</v>
+        <v>16.61</v>
       </c>
       <c r="M2">
-        <v>23.93</v>
+        <v>23.8</v>
       </c>
       <c r="N2">
         <v>71</v>
       </c>
       <c r="O2">
-        <v>70</v>
+        <v>68</v>
       </c>
       <c r="P2">
-        <v>10807</v>
+        <v>10555.6</v>
       </c>
       <c r="Q2">
-        <v>11407.6</v>
+        <v>11312.8</v>
       </c>
       <c r="R2">
-        <v>11571.07</v>
+        <v>11545.88</v>
       </c>
       <c r="S2">
-        <v>10139.99</v>
+        <v>10146.03</v>
       </c>
       <c r="T2">
-        <v>-0.9399999999999999</v>
+        <v>-1.2</v>
       </c>
       <c r="U2" t="s">
         <v>45</v>
@@ -1003,43 +1005,43 @@
         <v>1</v>
       </c>
       <c r="Y2">
-        <v>21.8</v>
+        <v>21.6</v>
       </c>
       <c r="Z2">
-        <v>-258.31</v>
+        <v>-321.82</v>
       </c>
       <c r="AA2">
-        <v>-113.89</v>
+        <v>-155.48</v>
       </c>
       <c r="AB2">
-        <v>-144.41</v>
+        <v>-166.34</v>
       </c>
       <c r="AC2">
         <v>3.93</v>
       </c>
       <c r="AD2">
-        <v>4.44</v>
+        <v>3.93</v>
       </c>
       <c r="AE2">
-        <v>258.46</v>
+        <v>252.07</v>
       </c>
       <c r="AF2">
-        <v>562.46</v>
+        <v>29.94</v>
       </c>
       <c r="AG2">
-        <v>12325.13</v>
+        <v>12386</v>
       </c>
       <c r="AH2">
-        <v>10490.07</v>
+        <v>10239.6</v>
       </c>
       <c r="AI2">
-        <v>11082.38</v>
+        <v>10760.71</v>
       </c>
       <c r="AJ2" t="s">
         <v>47</v>
       </c>
       <c r="AK2">
-        <v>64.40000000000001</v>
+        <v>68.39</v>
       </c>
     </row>
     <row r="3" spans="1:37">
@@ -1050,58 +1052,58 @@
         <v>44</v>
       </c>
       <c r="C3">
-        <v>497.05</v>
+        <v>480.35</v>
       </c>
       <c r="D3">
-        <v>0.3</v>
+        <v>-3.36</v>
       </c>
       <c r="E3">
         <v>670.25</v>
       </c>
       <c r="F3">
-        <v>235.4</v>
+        <v>236.06</v>
       </c>
       <c r="G3">
-        <v>-25.84</v>
+        <v>-28.33</v>
       </c>
       <c r="H3">
-        <v>111.15</v>
+        <v>103.49</v>
       </c>
       <c r="I3">
-        <v>-0.93</v>
+        <v>-3.83</v>
       </c>
       <c r="J3">
-        <v>5.32</v>
+        <v>-0.87</v>
       </c>
       <c r="K3">
-        <v>-19.34</v>
+        <v>-22.49</v>
       </c>
       <c r="L3">
-        <v>113.43</v>
+        <v>104.06</v>
       </c>
       <c r="M3">
-        <v>16.38</v>
+        <v>15.42</v>
       </c>
       <c r="N3">
-        <v>99</v>
+        <v>85</v>
       </c>
       <c r="O3">
-        <v>91</v>
+        <v>89</v>
       </c>
       <c r="P3">
-        <v>493.03</v>
+        <v>489.2</v>
       </c>
       <c r="Q3">
-        <v>507.56</v>
+        <v>506.13</v>
       </c>
       <c r="R3">
-        <v>508.44</v>
+        <v>506.93</v>
       </c>
       <c r="S3">
-        <v>452.13</v>
+        <v>453.25</v>
       </c>
       <c r="T3">
-        <v>9.93</v>
+        <v>5.98</v>
       </c>
       <c r="U3" t="s">
         <v>45</v>
@@ -1116,34 +1118,34 @@
         <v>2</v>
       </c>
       <c r="Y3">
-        <v>47.06</v>
+        <v>40.69</v>
       </c>
       <c r="Z3">
-        <v>-3.6</v>
+        <v>-4.85</v>
       </c>
       <c r="AA3">
-        <v>-2.74</v>
+        <v>-3.16</v>
       </c>
       <c r="AB3">
-        <v>-0.86</v>
+        <v>-1.69</v>
       </c>
       <c r="AC3">
-        <v>43.99</v>
+        <v>35.69</v>
       </c>
       <c r="AD3">
-        <v>27.58</v>
+        <v>35.43</v>
       </c>
       <c r="AE3">
-        <v>18.84</v>
+        <v>19.02</v>
       </c>
       <c r="AF3">
-        <v>-39.15</v>
+        <v>-55.41</v>
       </c>
       <c r="AG3">
-        <v>531.4299999999999</v>
+        <v>532.9</v>
       </c>
       <c r="AH3">
-        <v>483.69</v>
+        <v>479.36</v>
       </c>
       <c r="AI3">
         <v>460.99</v>
@@ -1152,7 +1154,7 @@
         <v>48</v>
       </c>
       <c r="AK3">
-        <v>28.9</v>
+        <v>32.06</v>
       </c>
     </row>
     <row r="4" spans="1:37">
@@ -1163,58 +1165,58 @@
         <v>44</v>
       </c>
       <c r="C4">
-        <v>299.8</v>
+        <v>299.25</v>
       </c>
       <c r="D4">
-        <v>-1.19</v>
+        <v>-0.18</v>
       </c>
       <c r="E4">
-        <v>554.95</v>
+        <v>548</v>
       </c>
       <c r="F4">
-        <v>299.8</v>
+        <v>299.25</v>
       </c>
       <c r="G4">
-        <v>-45.98</v>
+        <v>-45.39</v>
       </c>
       <c r="H4">
         <v>0</v>
       </c>
       <c r="I4">
-        <v>-6.74</v>
+        <v>-6.18</v>
       </c>
       <c r="J4">
-        <v>-7.99</v>
+        <v>-7.52</v>
       </c>
       <c r="K4">
-        <v>-8.859999999999999</v>
+        <v>-8.210000000000001</v>
       </c>
       <c r="L4">
-        <v>-44.82</v>
+        <v>-46.08</v>
       </c>
       <c r="M4">
-        <v>-24.39</v>
+        <v>-24.15</v>
       </c>
       <c r="N4">
         <v>15</v>
       </c>
       <c r="O4">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="P4">
-        <v>309.33</v>
+        <v>305.39</v>
       </c>
       <c r="Q4">
-        <v>325.32</v>
+        <v>323.58</v>
       </c>
       <c r="R4">
-        <v>336.9</v>
+        <v>336.36</v>
       </c>
       <c r="S4">
-        <v>368.02</v>
+        <v>367.13</v>
       </c>
       <c r="T4">
-        <v>-18.54</v>
+        <v>-18.49</v>
       </c>
       <c r="U4" t="s">
         <v>45</v>
@@ -1229,43 +1231,43 @@
         <v>0</v>
       </c>
       <c r="Y4">
-        <v>28.53</v>
+        <v>28.27</v>
       </c>
       <c r="Z4">
-        <v>-8.51</v>
+        <v>-9.25</v>
       </c>
       <c r="AA4">
-        <v>-6.04</v>
+        <v>-6.68</v>
       </c>
       <c r="AB4">
-        <v>-2.46</v>
+        <v>-2.57</v>
       </c>
       <c r="AC4">
         <v>0</v>
       </c>
       <c r="AD4">
-        <v>0.62</v>
+        <v>0</v>
       </c>
       <c r="AE4">
-        <v>9.779999999999999</v>
+        <v>9.640000000000001</v>
       </c>
       <c r="AF4">
-        <v>-12.05</v>
+        <v>-23.9</v>
       </c>
       <c r="AG4">
-        <v>348.97</v>
+        <v>349.52</v>
       </c>
       <c r="AH4">
-        <v>301.68</v>
+        <v>297.64</v>
       </c>
       <c r="AI4">
-        <v>330.42</v>
+        <v>330.22</v>
       </c>
       <c r="AJ4" t="s">
         <v>47</v>
       </c>
       <c r="AK4">
-        <v>31.31</v>
+        <v>35.96</v>
       </c>
     </row>
     <row r="5" spans="1:37">
@@ -1276,10 +1278,10 @@
         <v>44</v>
       </c>
       <c r="C5">
-        <v>1732.6</v>
+        <v>1751.4</v>
       </c>
       <c r="D5">
-        <v>0.09</v>
+        <v>1.09</v>
       </c>
       <c r="E5">
         <v>2176.6</v>
@@ -1288,46 +1290,46 @@
         <v>1631.8</v>
       </c>
       <c r="G5">
-        <v>-20.4</v>
+        <v>-19.54</v>
       </c>
       <c r="H5">
-        <v>6.18</v>
+        <v>7.33</v>
       </c>
       <c r="I5">
-        <v>-1.69</v>
+        <v>-1.11</v>
       </c>
       <c r="J5">
-        <v>-12.14</v>
+        <v>-11.99</v>
       </c>
       <c r="K5">
-        <v>-8.6</v>
+        <v>-6.38</v>
       </c>
       <c r="L5">
-        <v>-13.51</v>
+        <v>-13.5</v>
       </c>
       <c r="M5">
-        <v>0.21</v>
+        <v>-0.34</v>
       </c>
       <c r="N5">
         <v>29</v>
       </c>
       <c r="O5">
-        <v>41</v>
+        <v>43</v>
       </c>
       <c r="P5">
-        <v>1745.8</v>
+        <v>1741.88</v>
       </c>
       <c r="Q5">
-        <v>1851.75</v>
+        <v>1839.72</v>
       </c>
       <c r="R5">
-        <v>1941.65</v>
+        <v>1938.89</v>
       </c>
       <c r="S5">
-        <v>1884.68</v>
+        <v>1883.09</v>
       </c>
       <c r="T5">
-        <v>-8.07</v>
+        <v>-6.99</v>
       </c>
       <c r="U5" t="s">
         <v>45</v>
@@ -1342,34 +1344,34 @@
         <v>1</v>
       </c>
       <c r="Y5">
-        <v>25.11</v>
+        <v>30.33</v>
       </c>
       <c r="Z5">
-        <v>-60.44</v>
+        <v>-59.39</v>
       </c>
       <c r="AA5">
-        <v>-47.87</v>
+        <v>-50.18</v>
       </c>
       <c r="AB5">
-        <v>-12.56</v>
+        <v>-9.220000000000001</v>
       </c>
       <c r="AC5">
-        <v>1.17</v>
+        <v>19.13</v>
       </c>
       <c r="AD5">
-        <v>2.25</v>
+        <v>6.99</v>
       </c>
       <c r="AE5">
-        <v>37.26</v>
+        <v>36.62</v>
       </c>
       <c r="AF5">
-        <v>226.11</v>
+        <v>38.9</v>
       </c>
       <c r="AG5">
-        <v>2018.68</v>
+        <v>1998.55</v>
       </c>
       <c r="AH5">
-        <v>1684.82</v>
+        <v>1680.88</v>
       </c>
       <c r="AI5">
         <v>1830.94</v>
@@ -1378,7 +1380,7 @@
         <v>47</v>
       </c>
       <c r="AK5">
-        <v>79.48</v>
+        <v>75.81999999999999</v>
       </c>
     </row>
     <row r="6" spans="1:37">
@@ -1389,10 +1391,10 @@
         <v>44</v>
       </c>
       <c r="C6">
-        <v>10666</v>
+        <v>10732</v>
       </c>
       <c r="D6">
-        <v>-1.13</v>
+        <v>0.62</v>
       </c>
       <c r="E6">
         <v>13144</v>
@@ -1401,46 +1403,46 @@
         <v>8746</v>
       </c>
       <c r="G6">
-        <v>-18.85</v>
+        <v>-18.35</v>
       </c>
       <c r="H6">
-        <v>21.95</v>
+        <v>22.71</v>
       </c>
       <c r="I6">
-        <v>-2.3</v>
+        <v>-1.9</v>
       </c>
       <c r="J6">
-        <v>-5.69</v>
+        <v>-3.32</v>
       </c>
       <c r="K6">
-        <v>-3.73</v>
+        <v>-0.8</v>
       </c>
       <c r="L6">
-        <v>-16</v>
+        <v>-13.88</v>
       </c>
       <c r="M6">
-        <v>18.9</v>
+        <v>18.56</v>
       </c>
       <c r="N6">
         <v>43</v>
       </c>
       <c r="O6">
-        <v>46</v>
+        <v>50</v>
       </c>
       <c r="P6">
-        <v>10758.8</v>
+        <v>10717.2</v>
       </c>
       <c r="Q6">
-        <v>11030.45</v>
+        <v>11008.8</v>
       </c>
       <c r="R6">
-        <v>11183.24</v>
+        <v>11185.16</v>
       </c>
       <c r="S6">
-        <v>10675.91</v>
+        <v>10674.26</v>
       </c>
       <c r="T6">
-        <v>-0.09</v>
+        <v>0.54</v>
       </c>
       <c r="U6" t="s">
         <v>45</v>
@@ -1452,37 +1454,37 @@
         <v>45</v>
       </c>
       <c r="X6">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="Y6">
-        <v>41.12</v>
+        <v>42.89</v>
       </c>
       <c r="Z6">
-        <v>-113.13</v>
+        <v>-120.28</v>
       </c>
       <c r="AA6">
-        <v>-57.53</v>
+        <v>-70.08</v>
       </c>
       <c r="AB6">
-        <v>-55.59</v>
+        <v>-50.2</v>
       </c>
       <c r="AC6">
-        <v>13.78</v>
+        <v>21.78</v>
       </c>
       <c r="AD6">
-        <v>9.23</v>
+        <v>14.85</v>
       </c>
       <c r="AE6">
-        <v>257.85</v>
+        <v>263.58</v>
       </c>
       <c r="AF6">
-        <v>-9.199999999999999</v>
+        <v>14.58</v>
       </c>
       <c r="AG6">
-        <v>11472.38</v>
+        <v>11465.17</v>
       </c>
       <c r="AH6">
-        <v>10588.52</v>
+        <v>10552.43</v>
       </c>
       <c r="AI6">
         <v>11368.55</v>
@@ -1491,7 +1493,7 @@
         <v>47</v>
       </c>
       <c r="AK6">
-        <v>33.4</v>
+        <v>34.41</v>
       </c>
     </row>
     <row r="7" spans="1:37">
@@ -1502,10 +1504,10 @@
         <v>44</v>
       </c>
       <c r="C7">
-        <v>948.3</v>
+        <v>970</v>
       </c>
       <c r="D7">
-        <v>-1.16</v>
+        <v>2.29</v>
       </c>
       <c r="E7">
         <v>1158.8</v>
@@ -1514,46 +1516,46 @@
         <v>801.55</v>
       </c>
       <c r="G7">
-        <v>-18.17</v>
+        <v>-16.29</v>
       </c>
       <c r="H7">
-        <v>18.31</v>
+        <v>21.02</v>
       </c>
       <c r="I7">
-        <v>-3.43</v>
+        <v>-2.7</v>
       </c>
       <c r="J7">
-        <v>-10.02</v>
+        <v>-8.140000000000001</v>
       </c>
       <c r="K7">
-        <v>-8.06</v>
+        <v>-5.74</v>
       </c>
       <c r="L7">
-        <v>-3.74</v>
+        <v>-2.11</v>
       </c>
       <c r="M7">
-        <v>5.14</v>
+        <v>5.06</v>
       </c>
       <c r="N7">
         <v>57</v>
       </c>
       <c r="O7">
-        <v>51</v>
+        <v>54</v>
       </c>
       <c r="P7">
-        <v>972.6799999999999</v>
+        <v>967.3</v>
       </c>
       <c r="Q7">
-        <v>1016.52</v>
+        <v>1012.57</v>
       </c>
       <c r="R7">
-        <v>1058.25</v>
+        <v>1056.86</v>
       </c>
       <c r="S7">
-        <v>976.3200000000001</v>
+        <v>976.11</v>
       </c>
       <c r="T7">
-        <v>-2.87</v>
+        <v>-0.63</v>
       </c>
       <c r="U7" t="s">
         <v>45</v>
@@ -1568,34 +1570,34 @@
         <v>1</v>
       </c>
       <c r="Y7">
-        <v>32.16</v>
+        <v>38.77</v>
       </c>
       <c r="Z7">
-        <v>-25.69</v>
+        <v>-25.64</v>
       </c>
       <c r="AA7">
-        <v>-18.98</v>
+        <v>-20.31</v>
       </c>
       <c r="AB7">
-        <v>-6.72</v>
+        <v>-5.33</v>
       </c>
       <c r="AC7">
-        <v>17.37</v>
+        <v>22.02</v>
       </c>
       <c r="AD7">
-        <v>28.73</v>
+        <v>22.63</v>
       </c>
       <c r="AE7">
-        <v>24.66</v>
+        <v>26.29</v>
       </c>
       <c r="AF7">
-        <v>-9.74</v>
+        <v>101.19</v>
       </c>
       <c r="AG7">
-        <v>1084.1</v>
+        <v>1081.38</v>
       </c>
       <c r="AH7">
-        <v>948.9299999999999</v>
+        <v>943.75</v>
       </c>
       <c r="AI7">
         <v>1020.6</v>
@@ -1604,7 +1606,7 @@
         <v>47</v>
       </c>
       <c r="AK7">
-        <v>48.85</v>
+        <v>44.04</v>
       </c>
     </row>
     <row r="8" spans="1:37">
@@ -1615,58 +1617,58 @@
         <v>44</v>
       </c>
       <c r="C8">
-        <v>172.66</v>
+        <v>182.2</v>
       </c>
       <c r="D8">
-        <v>-4.15</v>
+        <v>5.53</v>
       </c>
       <c r="E8">
-        <v>180.13</v>
+        <v>182.2</v>
       </c>
       <c r="F8">
         <v>115.96</v>
       </c>
       <c r="G8">
-        <v>-4.15</v>
+        <v>0</v>
       </c>
       <c r="H8">
-        <v>48.9</v>
+        <v>57.12</v>
       </c>
       <c r="I8">
-        <v>11.21</v>
+        <v>9.07</v>
       </c>
       <c r="J8">
-        <v>26.93</v>
+        <v>35.79</v>
       </c>
       <c r="K8">
-        <v>29.83</v>
+        <v>37.03</v>
       </c>
       <c r="L8">
-        <v>33.75</v>
+        <v>40.27</v>
       </c>
       <c r="M8">
-        <v>4.88</v>
+        <v>4.56</v>
       </c>
       <c r="N8">
-        <v>85</v>
+        <v>99</v>
       </c>
       <c r="O8">
-        <v>88</v>
+        <v>91</v>
       </c>
       <c r="P8">
-        <v>172.67</v>
+        <v>175.7</v>
       </c>
       <c r="Q8">
-        <v>147.82</v>
+        <v>150.28</v>
       </c>
       <c r="R8">
-        <v>142.06</v>
+        <v>142.93</v>
       </c>
       <c r="S8">
-        <v>135.12</v>
+        <v>135.37</v>
       </c>
       <c r="T8">
-        <v>27.78</v>
+        <v>34.59</v>
       </c>
       <c r="U8" t="s">
         <v>46</v>
@@ -1681,34 +1683,34 @@
         <v>3</v>
       </c>
       <c r="Y8">
-        <v>72.51000000000001</v>
+        <v>76.90000000000001</v>
       </c>
       <c r="Z8">
-        <v>9.52</v>
+        <v>10.59</v>
       </c>
       <c r="AA8">
-        <v>5.48</v>
+        <v>6.5</v>
       </c>
       <c r="AB8">
-        <v>4.04</v>
+        <v>4.09</v>
       </c>
       <c r="AC8">
-        <v>90.52</v>
+        <v>84.61</v>
       </c>
       <c r="AD8">
-        <v>96.84</v>
+        <v>91.70999999999999</v>
       </c>
       <c r="AE8">
-        <v>7.4</v>
+        <v>8.1</v>
       </c>
       <c r="AF8">
-        <v>80.64</v>
+        <v>283.43</v>
       </c>
       <c r="AG8">
-        <v>180.12</v>
+        <v>185.21</v>
       </c>
       <c r="AH8">
-        <v>115.52</v>
+        <v>115.35</v>
       </c>
       <c r="AI8">
         <v>158.84</v>
@@ -1717,7 +1719,7 @@
         <v>48</v>
       </c>
       <c r="AK8">
-        <v>52.76</v>
+        <v>54.22</v>
       </c>
     </row>
   </sheetData>
@@ -1858,7 +1860,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:F62"/>
+  <dimension ref="A1:F65"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="16.7109375" customWidth="1"/>
@@ -1916,761 +1918,764 @@
         <v>59</v>
       </c>
     </row>
-    <row r="5" spans="1:6">
-      <c r="A5" s="2" t="s">
+    <row r="4" spans="1:6">
+      <c r="A4" s="4" t="s">
+        <v>40</v>
+      </c>
+      <c r="B4" s="4" t="s">
         <v>60</v>
       </c>
-      <c r="B5" s="2"/>
-      <c r="C5" s="2"/>
-      <c r="D5" s="2"/>
-      <c r="E5" s="2"/>
+      <c r="C4" s="4" t="s">
+        <v>61</v>
+      </c>
+      <c r="D4" s="4" t="s">
+        <v>62</v>
+      </c>
+      <c r="E4" s="4" t="s">
+        <v>63</v>
+      </c>
+      <c r="F4" s="4" t="s">
+        <v>64</v>
+      </c>
     </row>
     <row r="6" spans="1:6">
-      <c r="A6" s="3" t="s">
+      <c r="A6" s="2" t="s">
+        <v>65</v>
+      </c>
+      <c r="B6" s="2"/>
+      <c r="C6" s="2"/>
+      <c r="D6" s="2"/>
+      <c r="E6" s="2"/>
+    </row>
+    <row r="7" spans="1:6">
+      <c r="A7" s="3" t="s">
         <v>0</v>
       </c>
-      <c r="B6" s="3" t="s">
-        <v>61</v>
-      </c>
-      <c r="C6" s="3" t="s">
-        <v>62</v>
-      </c>
-      <c r="D6" s="3" t="s">
-        <v>63</v>
-      </c>
-      <c r="E6" s="3" t="s">
-        <v>64</v>
-      </c>
-    </row>
-    <row r="7" spans="1:6">
-      <c r="A7" s="5" t="s">
-        <v>37</v>
-      </c>
-      <c r="B7" s="5" t="s">
-        <v>9</v>
-      </c>
-      <c r="C7" s="6">
-        <v>-10.35</v>
-      </c>
-      <c r="D7" s="6">
-        <v>-18.74</v>
-      </c>
-      <c r="E7" s="7">
-        <v>-8.390000000000001</v>
+      <c r="B7" s="3" t="s">
+        <v>66</v>
+      </c>
+      <c r="C7" s="3" t="s">
+        <v>67</v>
+      </c>
+      <c r="D7" s="3" t="s">
+        <v>68</v>
+      </c>
+      <c r="E7" s="3" t="s">
+        <v>69</v>
       </c>
     </row>
     <row r="8" spans="1:6">
       <c r="A8" s="5" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="B8" s="5" t="s">
         <v>9</v>
       </c>
       <c r="C8" s="6">
-        <v>4.54</v>
+        <v>-18.74</v>
       </c>
       <c r="D8" s="6">
-        <v>5.32</v>
-      </c>
-      <c r="E8" s="8">
-        <v>0.78</v>
+        <v>-17.36</v>
+      </c>
+      <c r="E8" s="7">
+        <v>1.38</v>
       </c>
     </row>
     <row r="9" spans="1:6">
       <c r="A9" s="5" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="B9" s="5" t="s">
         <v>9</v>
       </c>
       <c r="C9" s="6">
-        <v>-6.59</v>
+        <v>5.32</v>
       </c>
       <c r="D9" s="6">
-        <v>-7.99</v>
-      </c>
-      <c r="E9" s="7">
-        <v>-1.4</v>
+        <v>-0.87</v>
+      </c>
+      <c r="E9" s="8">
+        <v>-6.19</v>
       </c>
     </row>
     <row r="10" spans="1:6">
       <c r="A10" s="5" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="B10" s="5" t="s">
         <v>9</v>
       </c>
       <c r="C10" s="6">
-        <v>-14.35</v>
+        <v>-7.99</v>
       </c>
       <c r="D10" s="6">
-        <v>-12.14</v>
-      </c>
-      <c r="E10" s="8">
-        <v>2.21</v>
+        <v>-7.52</v>
+      </c>
+      <c r="E10" s="7">
+        <v>0.47</v>
       </c>
     </row>
     <row r="11" spans="1:6">
       <c r="A11" s="5" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="B11" s="5" t="s">
         <v>9</v>
       </c>
       <c r="C11" s="6">
-        <v>-7.35</v>
+        <v>-12.14</v>
       </c>
       <c r="D11" s="6">
-        <v>-5.69</v>
-      </c>
-      <c r="E11" s="8">
-        <v>1.66</v>
+        <v>-11.99</v>
+      </c>
+      <c r="E11" s="7">
+        <v>0.15</v>
       </c>
     </row>
     <row r="12" spans="1:6">
       <c r="A12" s="5" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="B12" s="5" t="s">
         <v>9</v>
       </c>
       <c r="C12" s="6">
-        <v>-9.23</v>
+        <v>-5.69</v>
       </c>
       <c r="D12" s="6">
-        <v>-10.02</v>
+        <v>-3.32</v>
       </c>
       <c r="E12" s="7">
-        <v>-0.79</v>
+        <v>2.37</v>
       </c>
     </row>
     <row r="13" spans="1:6">
       <c r="A13" s="5" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="B13" s="5" t="s">
         <v>9</v>
       </c>
       <c r="C13" s="6">
-        <v>31.12</v>
+        <v>-10.02</v>
       </c>
       <c r="D13" s="6">
-        <v>26.93</v>
+        <v>-8.140000000000001</v>
       </c>
       <c r="E13" s="7">
-        <v>-4.19</v>
+        <v>1.88</v>
       </c>
     </row>
     <row r="14" spans="1:6">
       <c r="A14" s="5" t="s">
-        <v>37</v>
+        <v>43</v>
       </c>
       <c r="B14" s="5" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="C14" s="6">
-        <v>-4.61</v>
+        <v>26.93</v>
       </c>
       <c r="D14" s="6">
-        <v>-10.38</v>
+        <v>35.79</v>
       </c>
       <c r="E14" s="7">
-        <v>-5.77</v>
+        <v>8.859999999999999</v>
       </c>
     </row>
     <row r="15" spans="1:6">
       <c r="A15" s="5" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="B15" s="5" t="s">
         <v>8</v>
       </c>
       <c r="C15" s="6">
-        <v>-2.04</v>
+        <v>-10.38</v>
       </c>
       <c r="D15" s="6">
-        <v>-0.93</v>
+        <v>-11.14</v>
       </c>
       <c r="E15" s="8">
-        <v>1.11</v>
+        <v>-0.76</v>
       </c>
     </row>
     <row r="16" spans="1:6">
       <c r="A16" s="5" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="B16" s="5" t="s">
         <v>8</v>
       </c>
       <c r="C16" s="6">
-        <v>-7.89</v>
+        <v>-0.93</v>
       </c>
       <c r="D16" s="6">
-        <v>-6.74</v>
+        <v>-3.83</v>
       </c>
       <c r="E16" s="8">
-        <v>1.15</v>
+        <v>-2.9</v>
       </c>
     </row>
     <row r="17" spans="1:5">
       <c r="A17" s="5" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="B17" s="5" t="s">
         <v>8</v>
       </c>
       <c r="C17" s="6">
-        <v>-6.26</v>
+        <v>-6.74</v>
       </c>
       <c r="D17" s="6">
-        <v>-1.69</v>
-      </c>
-      <c r="E17" s="8">
-        <v>4.57</v>
+        <v>-6.18</v>
+      </c>
+      <c r="E17" s="7">
+        <v>0.5600000000000001</v>
       </c>
     </row>
     <row r="18" spans="1:5">
       <c r="A18" s="5" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="B18" s="5" t="s">
         <v>8</v>
       </c>
       <c r="C18" s="6">
-        <v>-5.77</v>
+        <v>-1.69</v>
       </c>
       <c r="D18" s="6">
-        <v>-2.3</v>
-      </c>
-      <c r="E18" s="8">
-        <v>3.47</v>
+        <v>-1.11</v>
+      </c>
+      <c r="E18" s="7">
+        <v>0.58</v>
       </c>
     </row>
     <row r="19" spans="1:5">
       <c r="A19" s="5" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="B19" s="5" t="s">
         <v>8</v>
       </c>
       <c r="C19" s="6">
-        <v>-8.029999999999999</v>
+        <v>-2.3</v>
       </c>
       <c r="D19" s="6">
-        <v>-3.43</v>
-      </c>
-      <c r="E19" s="8">
-        <v>4.6</v>
+        <v>-1.9</v>
+      </c>
+      <c r="E19" s="7">
+        <v>0.4</v>
       </c>
     </row>
     <row r="20" spans="1:5">
       <c r="A20" s="5" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="B20" s="5" t="s">
         <v>8</v>
       </c>
       <c r="C20" s="6">
-        <v>14.65</v>
+        <v>-3.43</v>
       </c>
       <c r="D20" s="6">
-        <v>11.21</v>
+        <v>-2.7</v>
       </c>
       <c r="E20" s="7">
-        <v>-3.44</v>
+        <v>0.73</v>
       </c>
     </row>
     <row r="21" spans="1:5">
       <c r="A21" s="5" t="s">
-        <v>37</v>
+        <v>43</v>
       </c>
       <c r="B21" s="5" t="s">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="C21" s="6">
-        <v>24.7</v>
+        <v>11.21</v>
       </c>
       <c r="D21" s="6">
-        <v>17.06</v>
-      </c>
-      <c r="E21" s="7">
-        <v>-7.64</v>
+        <v>9.07</v>
+      </c>
+      <c r="E21" s="8">
+        <v>-2.14</v>
       </c>
     </row>
     <row r="22" spans="1:5">
       <c r="A22" s="5" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="B22" s="5" t="s">
         <v>11</v>
       </c>
       <c r="C22" s="6">
-        <v>103.11</v>
+        <v>17.06</v>
       </c>
       <c r="D22" s="6">
-        <v>113.43</v>
+        <v>16.61</v>
       </c>
       <c r="E22" s="8">
-        <v>10.32</v>
+        <v>-0.45</v>
       </c>
     </row>
     <row r="23" spans="1:5">
       <c r="A23" s="5" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="B23" s="5" t="s">
         <v>11</v>
       </c>
       <c r="C23" s="6">
-        <v>-46.3</v>
+        <v>113.43</v>
       </c>
       <c r="D23" s="6">
-        <v>-44.82</v>
+        <v>104.06</v>
       </c>
       <c r="E23" s="8">
-        <v>1.48</v>
+        <v>-9.369999999999999</v>
       </c>
     </row>
     <row r="24" spans="1:5">
       <c r="A24" s="5" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="B24" s="5" t="s">
         <v>11</v>
       </c>
       <c r="C24" s="6">
-        <v>-14.96</v>
+        <v>-44.82</v>
       </c>
       <c r="D24" s="6">
-        <v>-13.51</v>
+        <v>-46.08</v>
       </c>
       <c r="E24" s="8">
-        <v>1.45</v>
+        <v>-1.26</v>
       </c>
     </row>
     <row r="25" spans="1:5">
       <c r="A25" s="5" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="B25" s="5" t="s">
         <v>11</v>
       </c>
       <c r="C25" s="6">
-        <v>-16.37</v>
+        <v>-13.51</v>
       </c>
       <c r="D25" s="6">
-        <v>-16</v>
-      </c>
-      <c r="E25" s="8">
-        <v>0.37</v>
+        <v>-13.5</v>
+      </c>
+      <c r="E25" s="7">
+        <v>0.01</v>
       </c>
     </row>
     <row r="26" spans="1:5">
       <c r="A26" s="5" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="B26" s="5" t="s">
         <v>11</v>
       </c>
       <c r="C26" s="6">
-        <v>-5.27</v>
+        <v>-16</v>
       </c>
       <c r="D26" s="6">
-        <v>-3.74</v>
-      </c>
-      <c r="E26" s="8">
-        <v>1.53</v>
+        <v>-13.88</v>
+      </c>
+      <c r="E26" s="7">
+        <v>2.12</v>
       </c>
     </row>
     <row r="27" spans="1:5">
       <c r="A27" s="5" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="B27" s="5" t="s">
         <v>11</v>
       </c>
       <c r="C27" s="6">
-        <v>34.2</v>
+        <v>-3.74</v>
       </c>
       <c r="D27" s="6">
-        <v>33.75</v>
+        <v>-2.11</v>
       </c>
       <c r="E27" s="7">
-        <v>-0.45</v>
+        <v>1.63</v>
       </c>
     </row>
     <row r="28" spans="1:5">
       <c r="A28" s="5" t="s">
-        <v>37</v>
+        <v>43</v>
       </c>
       <c r="B28" s="5" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="C28" s="6">
-        <v>10.32</v>
+        <v>33.75</v>
       </c>
       <c r="D28" s="6">
-        <v>2.65</v>
+        <v>40.27</v>
       </c>
       <c r="E28" s="7">
-        <v>-7.67</v>
+        <v>6.52</v>
       </c>
     </row>
     <row r="29" spans="1:5">
       <c r="A29" s="5" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="B29" s="5" t="s">
         <v>10</v>
       </c>
       <c r="C29" s="6">
-        <v>-19.02</v>
+        <v>2.65</v>
       </c>
       <c r="D29" s="6">
-        <v>-19.34</v>
-      </c>
-      <c r="E29" s="7">
-        <v>-0.32</v>
+        <v>-0.12</v>
+      </c>
+      <c r="E29" s="8">
+        <v>-2.77</v>
       </c>
     </row>
     <row r="30" spans="1:5">
       <c r="A30" s="5" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="B30" s="5" t="s">
         <v>10</v>
       </c>
       <c r="C30" s="6">
-        <v>-8.119999999999999</v>
+        <v>-19.34</v>
       </c>
       <c r="D30" s="6">
-        <v>-8.859999999999999</v>
-      </c>
-      <c r="E30" s="7">
-        <v>-0.74</v>
+        <v>-22.49</v>
+      </c>
+      <c r="E30" s="8">
+        <v>-3.15</v>
       </c>
     </row>
     <row r="31" spans="1:5">
       <c r="A31" s="5" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="B31" s="5" t="s">
         <v>10</v>
       </c>
       <c r="C31" s="6">
-        <v>-6.72</v>
+        <v>-8.859999999999999</v>
       </c>
       <c r="D31" s="6">
-        <v>-8.6</v>
+        <v>-8.210000000000001</v>
       </c>
       <c r="E31" s="7">
-        <v>-1.88</v>
+        <v>0.65</v>
       </c>
     </row>
     <row r="32" spans="1:5">
       <c r="A32" s="5" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="B32" s="5" t="s">
         <v>10</v>
       </c>
       <c r="C32" s="6">
-        <v>-0.64</v>
+        <v>-8.6</v>
       </c>
       <c r="D32" s="6">
-        <v>-3.73</v>
+        <v>-6.38</v>
       </c>
       <c r="E32" s="7">
-        <v>-3.09</v>
+        <v>2.22</v>
       </c>
     </row>
     <row r="33" spans="1:5">
       <c r="A33" s="5" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="B33" s="5" t="s">
         <v>10</v>
       </c>
       <c r="C33" s="6">
-        <v>-5.79</v>
+        <v>-3.73</v>
       </c>
       <c r="D33" s="6">
-        <v>-8.06</v>
+        <v>-0.8</v>
       </c>
       <c r="E33" s="7">
-        <v>-2.27</v>
+        <v>2.93</v>
       </c>
     </row>
     <row r="34" spans="1:5">
       <c r="A34" s="5" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="B34" s="5" t="s">
         <v>10</v>
       </c>
       <c r="C34" s="6">
-        <v>35.48</v>
+        <v>-8.06</v>
       </c>
       <c r="D34" s="6">
-        <v>29.83</v>
+        <v>-5.74</v>
       </c>
       <c r="E34" s="7">
-        <v>-5.65</v>
+        <v>2.32</v>
       </c>
     </row>
     <row r="35" spans="1:5">
       <c r="A35" s="5" t="s">
-        <v>37</v>
+        <v>43</v>
       </c>
       <c r="B35" s="5" t="s">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="C35" s="6">
-        <v>-12.03</v>
+        <v>29.83</v>
       </c>
       <c r="D35" s="6">
-        <v>-18.74</v>
+        <v>37.03</v>
       </c>
       <c r="E35" s="7">
-        <v>-6.71</v>
+        <v>7.2</v>
       </c>
     </row>
     <row r="36" spans="1:5">
       <c r="A36" s="5" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="B36" s="5" t="s">
         <v>6</v>
       </c>
       <c r="C36" s="6">
-        <v>-26.06</v>
+        <v>-18.74</v>
       </c>
       <c r="D36" s="6">
-        <v>-25.84</v>
+        <v>-18.91</v>
       </c>
       <c r="E36" s="8">
-        <v>0.22</v>
+        <v>-0.17</v>
       </c>
     </row>
     <row r="37" spans="1:5">
       <c r="A37" s="5" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="B37" s="5" t="s">
         <v>6</v>
       </c>
       <c r="C37" s="6">
-        <v>-45.33</v>
+        <v>-25.84</v>
       </c>
       <c r="D37" s="6">
-        <v>-45.98</v>
-      </c>
-      <c r="E37" s="7">
-        <v>-0.65</v>
+        <v>-28.33</v>
+      </c>
+      <c r="E37" s="8">
+        <v>-2.49</v>
       </c>
     </row>
     <row r="38" spans="1:5">
       <c r="A38" s="5" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="B38" s="5" t="s">
         <v>6</v>
       </c>
       <c r="C38" s="6">
-        <v>-20.47</v>
+        <v>-45.98</v>
       </c>
       <c r="D38" s="6">
-        <v>-20.4</v>
-      </c>
-      <c r="E38" s="8">
-        <v>0.07000000000000001</v>
+        <v>-45.39</v>
+      </c>
+      <c r="E38" s="7">
+        <v>0.59</v>
       </c>
     </row>
     <row r="39" spans="1:5">
       <c r="A39" s="5" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="B39" s="5" t="s">
         <v>6</v>
       </c>
       <c r="C39" s="6">
-        <v>-17.92</v>
+        <v>-20.4</v>
       </c>
       <c r="D39" s="6">
-        <v>-18.85</v>
+        <v>-19.54</v>
       </c>
       <c r="E39" s="7">
-        <v>-0.93</v>
+        <v>0.86</v>
       </c>
     </row>
     <row r="40" spans="1:5">
       <c r="A40" s="5" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="B40" s="5" t="s">
         <v>6</v>
       </c>
       <c r="C40" s="6">
-        <v>-17.21</v>
+        <v>-18.85</v>
       </c>
       <c r="D40" s="6">
-        <v>-18.17</v>
+        <v>-18.35</v>
       </c>
       <c r="E40" s="7">
-        <v>-0.96</v>
+        <v>0.5</v>
       </c>
     </row>
     <row r="41" spans="1:5">
       <c r="A41" s="5" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="B41" s="5" t="s">
         <v>6</v>
       </c>
       <c r="C41" s="6">
-        <v>0</v>
+        <v>-18.17</v>
       </c>
       <c r="D41" s="6">
-        <v>-4.15</v>
+        <v>-16.29</v>
       </c>
       <c r="E41" s="7">
-        <v>-4.15</v>
+        <v>1.88</v>
       </c>
     </row>
     <row r="42" spans="1:5">
       <c r="A42" s="5" t="s">
-        <v>37</v>
+        <v>43</v>
       </c>
       <c r="B42" s="5" t="s">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="C42" s="6">
-        <v>10874</v>
+        <v>-4.15</v>
       </c>
       <c r="D42" s="6">
-        <v>10045</v>
+        <v>0</v>
       </c>
       <c r="E42" s="7">
-        <v>-829</v>
+        <v>4.15</v>
       </c>
     </row>
     <row r="43" spans="1:5">
       <c r="A43" s="5" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="B43" s="5" t="s">
         <v>2</v>
       </c>
       <c r="C43" s="6">
-        <v>495.55</v>
+        <v>10045</v>
       </c>
       <c r="D43" s="6">
-        <v>497.05</v>
+        <v>10024</v>
       </c>
       <c r="E43" s="8">
-        <v>1.5</v>
+        <v>-21</v>
       </c>
     </row>
     <row r="44" spans="1:5">
       <c r="A44" s="5" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="B44" s="5" t="s">
         <v>2</v>
       </c>
       <c r="C44" s="6">
-        <v>303.4</v>
+        <v>497.05</v>
       </c>
       <c r="D44" s="6">
-        <v>299.8</v>
-      </c>
-      <c r="E44" s="7">
-        <v>-3.6</v>
+        <v>480.35</v>
+      </c>
+      <c r="E44" s="8">
+        <v>-16.7</v>
       </c>
     </row>
     <row r="45" spans="1:5">
       <c r="A45" s="5" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="B45" s="5" t="s">
         <v>2</v>
       </c>
       <c r="C45" s="6">
-        <v>1731</v>
+        <v>299.8</v>
       </c>
       <c r="D45" s="6">
-        <v>1732.6</v>
+        <v>299.25</v>
       </c>
       <c r="E45" s="8">
-        <v>1.6</v>
+        <v>-0.55</v>
       </c>
     </row>
     <row r="46" spans="1:5">
       <c r="A46" s="5" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="B46" s="5" t="s">
         <v>2</v>
       </c>
       <c r="C46" s="6">
-        <v>10788</v>
+        <v>1732.6</v>
       </c>
       <c r="D46" s="6">
-        <v>10666</v>
+        <v>1751.4</v>
       </c>
       <c r="E46" s="7">
-        <v>-122</v>
+        <v>18.8</v>
       </c>
     </row>
     <row r="47" spans="1:5">
       <c r="A47" s="5" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="B47" s="5" t="s">
         <v>2</v>
       </c>
       <c r="C47" s="6">
-        <v>959.4</v>
+        <v>10666</v>
       </c>
       <c r="D47" s="6">
-        <v>948.3</v>
+        <v>10732</v>
       </c>
       <c r="E47" s="7">
-        <v>-11.1</v>
+        <v>66</v>
       </c>
     </row>
     <row r="48" spans="1:5">
       <c r="A48" s="5" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="B48" s="5" t="s">
         <v>2</v>
       </c>
       <c r="C48" s="6">
-        <v>180.13</v>
+        <v>948.3</v>
       </c>
       <c r="D48" s="6">
-        <v>172.66</v>
+        <v>970</v>
       </c>
       <c r="E48" s="7">
-        <v>-7.47</v>
+        <v>21.7</v>
       </c>
     </row>
     <row r="49" spans="1:5">
       <c r="A49" s="5" t="s">
-        <v>37</v>
+        <v>43</v>
       </c>
       <c r="B49" s="5" t="s">
-        <v>24</v>
+        <v>2</v>
       </c>
       <c r="C49" s="6">
-        <v>32.99</v>
+        <v>172.66</v>
       </c>
       <c r="D49" s="6">
-        <v>21.8</v>
+        <v>182.2</v>
       </c>
       <c r="E49" s="7">
-        <v>-11.19</v>
+        <v>9.539999999999999</v>
       </c>
     </row>
     <row r="50" spans="1:5">
@@ -2678,226 +2683,277 @@
         <v>38</v>
       </c>
       <c r="B50" s="5" t="s">
-        <v>24</v>
+        <v>13</v>
       </c>
       <c r="C50" s="6">
-        <v>46.36</v>
+        <v>99</v>
       </c>
       <c r="D50" s="6">
-        <v>47.06</v>
+        <v>85</v>
       </c>
       <c r="E50" s="8">
-        <v>0.7</v>
+        <v>-14</v>
       </c>
     </row>
     <row r="51" spans="1:5">
       <c r="A51" s="5" t="s">
-        <v>39</v>
+        <v>43</v>
       </c>
       <c r="B51" s="5" t="s">
-        <v>24</v>
+        <v>13</v>
       </c>
       <c r="C51" s="6">
-        <v>30.23</v>
+        <v>85</v>
       </c>
       <c r="D51" s="6">
-        <v>28.53</v>
+        <v>99</v>
       </c>
       <c r="E51" s="7">
-        <v>-1.7</v>
+        <v>14</v>
       </c>
     </row>
     <row r="52" spans="1:5">
       <c r="A52" s="5" t="s">
-        <v>40</v>
+        <v>37</v>
       </c>
       <c r="B52" s="5" t="s">
         <v>24</v>
       </c>
       <c r="C52" s="6">
-        <v>24.67</v>
+        <v>21.8</v>
       </c>
       <c r="D52" s="6">
-        <v>25.11</v>
+        <v>21.6</v>
       </c>
       <c r="E52" s="8">
-        <v>0.44</v>
+        <v>-0.2</v>
       </c>
     </row>
     <row r="53" spans="1:5">
       <c r="A53" s="5" t="s">
-        <v>41</v>
+        <v>38</v>
       </c>
       <c r="B53" s="5" t="s">
         <v>24</v>
       </c>
       <c r="C53" s="6">
-        <v>43.44</v>
+        <v>47.06</v>
       </c>
       <c r="D53" s="6">
-        <v>41.12</v>
-      </c>
-      <c r="E53" s="7">
-        <v>-2.32</v>
+        <v>40.69</v>
+      </c>
+      <c r="E53" s="8">
+        <v>-6.37</v>
       </c>
     </row>
     <row r="54" spans="1:5">
       <c r="A54" s="5" t="s">
-        <v>42</v>
+        <v>39</v>
       </c>
       <c r="B54" s="5" t="s">
         <v>24</v>
       </c>
       <c r="C54" s="6">
-        <v>33.9</v>
+        <v>28.53</v>
       </c>
       <c r="D54" s="6">
-        <v>32.16</v>
-      </c>
-      <c r="E54" s="7">
-        <v>-1.74</v>
+        <v>28.27</v>
+      </c>
+      <c r="E54" s="8">
+        <v>-0.26</v>
       </c>
     </row>
     <row r="55" spans="1:5">
       <c r="A55" s="5" t="s">
-        <v>43</v>
+        <v>40</v>
       </c>
       <c r="B55" s="5" t="s">
         <v>24</v>
       </c>
       <c r="C55" s="6">
-        <v>84.12</v>
+        <v>25.11</v>
       </c>
       <c r="D55" s="6">
-        <v>72.51000000000001</v>
+        <v>30.33</v>
       </c>
       <c r="E55" s="7">
-        <v>-11.61</v>
+        <v>5.22</v>
       </c>
     </row>
     <row r="56" spans="1:5">
       <c r="A56" s="5" t="s">
-        <v>37</v>
+        <v>41</v>
       </c>
       <c r="B56" s="5" t="s">
-        <v>31</v>
+        <v>24</v>
       </c>
       <c r="C56" s="6">
-        <v>38.15</v>
+        <v>41.12</v>
       </c>
       <c r="D56" s="6">
-        <v>562.46</v>
-      </c>
-      <c r="E56" s="8">
-        <v>524.3099999999999</v>
+        <v>42.89</v>
+      </c>
+      <c r="E56" s="7">
+        <v>1.77</v>
       </c>
     </row>
     <row r="57" spans="1:5">
       <c r="A57" s="5" t="s">
-        <v>38</v>
+        <v>42</v>
       </c>
       <c r="B57" s="5" t="s">
-        <v>31</v>
+        <v>24</v>
       </c>
       <c r="C57" s="6">
-        <v>-70.44</v>
+        <v>32.16</v>
       </c>
       <c r="D57" s="6">
-        <v>-39.15</v>
-      </c>
-      <c r="E57" s="8">
-        <v>31.29</v>
+        <v>38.77</v>
+      </c>
+      <c r="E57" s="7">
+        <v>6.61</v>
       </c>
     </row>
     <row r="58" spans="1:5">
       <c r="A58" s="5" t="s">
-        <v>39</v>
+        <v>43</v>
       </c>
       <c r="B58" s="5" t="s">
-        <v>31</v>
+        <v>24</v>
       </c>
       <c r="C58" s="6">
-        <v>29.63</v>
+        <v>72.51000000000001</v>
       </c>
       <c r="D58" s="6">
-        <v>-12.05</v>
+        <v>76.90000000000001</v>
       </c>
       <c r="E58" s="7">
-        <v>-41.68</v>
+        <v>4.39</v>
       </c>
     </row>
     <row r="59" spans="1:5">
       <c r="A59" s="5" t="s">
-        <v>40</v>
+        <v>37</v>
       </c>
       <c r="B59" s="5" t="s">
         <v>31</v>
       </c>
       <c r="C59" s="6">
-        <v>58.48</v>
+        <v>562.46</v>
       </c>
       <c r="D59" s="6">
-        <v>226.11</v>
+        <v>29.94</v>
       </c>
       <c r="E59" s="8">
-        <v>167.63</v>
+        <v>-532.52</v>
       </c>
     </row>
     <row r="60" spans="1:5">
       <c r="A60" s="5" t="s">
-        <v>41</v>
+        <v>38</v>
       </c>
       <c r="B60" s="5" t="s">
         <v>31</v>
       </c>
       <c r="C60" s="6">
-        <v>-9.91</v>
+        <v>-39.15</v>
       </c>
       <c r="D60" s="6">
-        <v>-9.199999999999999</v>
+        <v>-55.41</v>
       </c>
       <c r="E60" s="8">
-        <v>0.71</v>
+        <v>-16.26</v>
       </c>
     </row>
     <row r="61" spans="1:5">
       <c r="A61" s="5" t="s">
-        <v>42</v>
+        <v>39</v>
       </c>
       <c r="B61" s="5" t="s">
         <v>31</v>
       </c>
       <c r="C61" s="6">
-        <v>5.48</v>
+        <v>-12.05</v>
       </c>
       <c r="D61" s="6">
-        <v>-9.74</v>
-      </c>
-      <c r="E61" s="7">
-        <v>-15.22</v>
+        <v>-23.9</v>
+      </c>
+      <c r="E61" s="8">
+        <v>-11.85</v>
       </c>
     </row>
     <row r="62" spans="1:5">
       <c r="A62" s="5" t="s">
-        <v>43</v>
+        <v>40</v>
       </c>
       <c r="B62" s="5" t="s">
         <v>31</v>
       </c>
       <c r="C62" s="6">
-        <v>249.72</v>
+        <v>226.11</v>
       </c>
       <c r="D62" s="6">
+        <v>38.9</v>
+      </c>
+      <c r="E62" s="8">
+        <v>-187.21</v>
+      </c>
+    </row>
+    <row r="63" spans="1:5">
+      <c r="A63" s="5" t="s">
+        <v>41</v>
+      </c>
+      <c r="B63" s="5" t="s">
+        <v>31</v>
+      </c>
+      <c r="C63" s="6">
+        <v>-9.199999999999999</v>
+      </c>
+      <c r="D63" s="6">
+        <v>14.58</v>
+      </c>
+      <c r="E63" s="7">
+        <v>23.78</v>
+      </c>
+    </row>
+    <row r="64" spans="1:5">
+      <c r="A64" s="5" t="s">
+        <v>42</v>
+      </c>
+      <c r="B64" s="5" t="s">
+        <v>31</v>
+      </c>
+      <c r="C64" s="6">
+        <v>-9.74</v>
+      </c>
+      <c r="D64" s="6">
+        <v>101.19</v>
+      </c>
+      <c r="E64" s="7">
+        <v>110.93</v>
+      </c>
+    </row>
+    <row r="65" spans="1:5">
+      <c r="A65" s="5" t="s">
+        <v>43</v>
+      </c>
+      <c r="B65" s="5" t="s">
+        <v>31</v>
+      </c>
+      <c r="C65" s="6">
         <v>80.64</v>
       </c>
-      <c r="E62" s="7">
-        <v>-169.08</v>
+      <c r="D65" s="6">
+        <v>283.43</v>
+      </c>
+      <c r="E65" s="7">
+        <v>202.79</v>
       </c>
     </row>
   </sheetData>
   <mergeCells count="2">
     <mergeCell ref="A1:F1"/>
-    <mergeCell ref="A5:E5"/>
+    <mergeCell ref="A6:E6"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -2921,28 +2977,28 @@
         <v>1</v>
       </c>
       <c r="B1" s="9" t="s">
-        <v>65</v>
+        <v>70</v>
       </c>
       <c r="C1" s="9" t="s">
-        <v>66</v>
+        <v>71</v>
       </c>
       <c r="D1" s="9" t="s">
-        <v>67</v>
+        <v>72</v>
       </c>
       <c r="E1" s="9" t="s">
-        <v>68</v>
+        <v>73</v>
       </c>
       <c r="F1" s="9" t="s">
-        <v>69</v>
+        <v>74</v>
       </c>
       <c r="G1" s="9" t="s">
-        <v>70</v>
+        <v>75</v>
       </c>
       <c r="H1" s="9" t="s">
-        <v>71</v>
+        <v>76</v>
       </c>
       <c r="I1" s="9" t="s">
-        <v>72</v>
+        <v>77</v>
       </c>
     </row>
     <row r="2" spans="1:9">
@@ -2950,22 +3006,22 @@
         <v>44</v>
       </c>
       <c r="B2" s="11">
-        <v>44.8</v>
+        <v>48.8</v>
       </c>
       <c r="C2" s="12">
         <v>7</v>
       </c>
       <c r="D2" s="11">
-        <v>38.3</v>
+        <v>39.9</v>
       </c>
       <c r="E2" s="11">
-        <v>30</v>
+        <v>40</v>
       </c>
       <c r="F2" s="11">
-        <v>-3.2</v>
+        <v>-1.9</v>
       </c>
       <c r="G2" s="11">
-        <v>-2.3</v>
+        <v>-1</v>
       </c>
       <c r="H2" s="11">
         <v>57</v>
@@ -3096,25 +3152,25 @@
     </row>
     <row r="2" spans="1:7">
       <c r="A2" s="14">
-        <v>0.2393</v>
+        <v>0.238</v>
       </c>
       <c r="B2" s="14">
-        <v>0.189</v>
+        <v>0.1856</v>
       </c>
       <c r="C2" s="14">
-        <v>0.1638</v>
+        <v>0.1542</v>
       </c>
       <c r="D2" s="14">
-        <v>0.05139999999999999</v>
+        <v>0.0506</v>
       </c>
       <c r="E2" s="14">
-        <v>0.0488</v>
+        <v>0.04559999999999999</v>
       </c>
       <c r="F2" s="14">
-        <v>0.0021</v>
+        <v>-0.0034</v>
       </c>
       <c r="G2" s="14">
-        <v>-0.2439</v>
+        <v>-0.2415</v>
       </c>
     </row>
   </sheetData>

--- a/BAJAJ_GROUP_Technical_Metrics.xlsx
+++ b/BAJAJ_GROUP_Technical_Metrics.xlsx
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="274" uniqueCount="78">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="253" uniqueCount="64">
   <si>
     <t>Symbol</t>
   </si>
@@ -172,49 +172,7 @@
     <t>▶  SIGNAL EVENTS (vs Previous Run)</t>
   </si>
   <si>
-    <t>Signal</t>
-  </si>
-  <si>
-    <t>Change</t>
-  </si>
-  <si>
-    <t>Direction</t>
-  </si>
-  <si>
-    <t>Prev Value</t>
-  </si>
-  <si>
-    <t>Curr Value</t>
-  </si>
-  <si>
-    <t>Near 52W High</t>
-  </si>
-  <si>
-    <t>-4.2% → 0.0%</t>
-  </si>
-  <si>
-    <t>🟢 BREAKOUT WATCH</t>
-  </si>
-  <si>
-    <t>-4.2%</t>
-  </si>
-  <si>
-    <t>0.0%</t>
-  </si>
-  <si>
-    <t>RSI Oversold Recovery</t>
-  </si>
-  <si>
-    <t>25.1 → 30.3</t>
-  </si>
-  <si>
-    <t>🟢 BULLISH</t>
-  </si>
-  <si>
-    <t>25.1</t>
-  </si>
-  <si>
-    <t>30.3</t>
+    <t>No signal events detected since last run.</t>
   </si>
   <si>
     <t>▶  NUMERIC METRIC CHANGES (vs Previous Run)</t>
@@ -416,15 +374,14 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="15">
+  <cellXfs count="14">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="2" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="3" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1"/>
     <xf numFmtId="165" fontId="4" fillId="5" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="165" fontId="5" fillId="6" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
@@ -939,10 +896,10 @@
         <v>44</v>
       </c>
       <c r="C2">
-        <v>10024</v>
+        <v>10017</v>
       </c>
       <c r="D2">
-        <v>-0.21</v>
+        <v>-0.07000000000000001</v>
       </c>
       <c r="E2">
         <v>12361</v>
@@ -951,46 +908,46 @@
         <v>8506.780000000001</v>
       </c>
       <c r="G2">
-        <v>-18.91</v>
+        <v>-18.96</v>
       </c>
       <c r="H2">
-        <v>17.84</v>
+        <v>17.75</v>
       </c>
       <c r="I2">
-        <v>-11.14</v>
+        <v>-9.130000000000001</v>
       </c>
       <c r="J2">
-        <v>-17.36</v>
+        <v>-15.96</v>
       </c>
       <c r="K2">
-        <v>-0.12</v>
+        <v>-0.91</v>
       </c>
       <c r="L2">
-        <v>16.61</v>
+        <v>17.05</v>
       </c>
       <c r="M2">
-        <v>23.8</v>
+        <v>24.39</v>
       </c>
       <c r="N2">
         <v>71</v>
       </c>
       <c r="O2">
-        <v>68</v>
+        <v>66</v>
       </c>
       <c r="P2">
-        <v>10555.6</v>
+        <v>10354.2</v>
       </c>
       <c r="Q2">
-        <v>11312.8</v>
+        <v>11217.7</v>
       </c>
       <c r="R2">
-        <v>11545.88</v>
+        <v>11523.62</v>
       </c>
       <c r="S2">
-        <v>10146.03</v>
+        <v>10151.7</v>
       </c>
       <c r="T2">
-        <v>-1.2</v>
+        <v>-1.33</v>
       </c>
       <c r="U2" t="s">
         <v>45</v>
@@ -1005,43 +962,43 @@
         <v>1</v>
       </c>
       <c r="Y2">
-        <v>21.6</v>
+        <v>21.53</v>
       </c>
       <c r="Z2">
-        <v>-321.82</v>
+        <v>-368.47</v>
       </c>
       <c r="AA2">
-        <v>-155.48</v>
+        <v>-198.08</v>
       </c>
       <c r="AB2">
-        <v>-166.34</v>
+        <v>-170.39</v>
       </c>
       <c r="AC2">
-        <v>3.93</v>
+        <v>0</v>
       </c>
       <c r="AD2">
-        <v>3.93</v>
+        <v>2.62</v>
       </c>
       <c r="AE2">
-        <v>252.07</v>
+        <v>241.71</v>
       </c>
       <c r="AF2">
-        <v>29.94</v>
+        <v>-41.85</v>
       </c>
       <c r="AG2">
-        <v>12386</v>
+        <v>12396.6</v>
       </c>
       <c r="AH2">
-        <v>10239.6</v>
+        <v>10038.8</v>
       </c>
       <c r="AI2">
-        <v>10760.71</v>
+        <v>10733.63</v>
       </c>
       <c r="AJ2" t="s">
         <v>47</v>
       </c>
       <c r="AK2">
-        <v>68.39</v>
+        <v>71.84999999999999</v>
       </c>
     </row>
     <row r="3" spans="1:37">
@@ -1052,10 +1009,10 @@
         <v>44</v>
       </c>
       <c r="C3">
-        <v>480.35</v>
+        <v>493.5</v>
       </c>
       <c r="D3">
-        <v>-3.36</v>
+        <v>2.74</v>
       </c>
       <c r="E3">
         <v>670.25</v>
@@ -1064,25 +1021,25 @@
         <v>236.06</v>
       </c>
       <c r="G3">
-        <v>-28.33</v>
+        <v>-26.37</v>
       </c>
       <c r="H3">
-        <v>103.49</v>
+        <v>109.06</v>
       </c>
       <c r="I3">
-        <v>-3.83</v>
+        <v>2.8</v>
       </c>
       <c r="J3">
-        <v>-0.87</v>
+        <v>-3.04</v>
       </c>
       <c r="K3">
-        <v>-22.49</v>
+        <v>-20.44</v>
       </c>
       <c r="L3">
-        <v>104.06</v>
+        <v>108.32</v>
       </c>
       <c r="M3">
-        <v>15.42</v>
+        <v>16.15</v>
       </c>
       <c r="N3">
         <v>85</v>
@@ -1091,19 +1048,19 @@
         <v>89</v>
       </c>
       <c r="P3">
-        <v>489.2</v>
+        <v>491.89</v>
       </c>
       <c r="Q3">
-        <v>506.13</v>
+        <v>504.93</v>
       </c>
       <c r="R3">
-        <v>506.93</v>
+        <v>505.81</v>
       </c>
       <c r="S3">
-        <v>453.25</v>
+        <v>454.44</v>
       </c>
       <c r="T3">
-        <v>5.98</v>
+        <v>8.6</v>
       </c>
       <c r="U3" t="s">
         <v>45</v>
@@ -1118,34 +1075,34 @@
         <v>2</v>
       </c>
       <c r="Y3">
-        <v>40.69</v>
+        <v>46.79</v>
       </c>
       <c r="Z3">
-        <v>-4.85</v>
+        <v>-4.73</v>
       </c>
       <c r="AA3">
-        <v>-3.16</v>
+        <v>-3.47</v>
       </c>
       <c r="AB3">
-        <v>-1.69</v>
+        <v>-1.25</v>
       </c>
       <c r="AC3">
-        <v>35.69</v>
+        <v>39.88</v>
       </c>
       <c r="AD3">
-        <v>35.43</v>
+        <v>39.85</v>
       </c>
       <c r="AE3">
-        <v>19.02</v>
+        <v>18.82</v>
       </c>
       <c r="AF3">
-        <v>-55.41</v>
+        <v>-60.5</v>
       </c>
       <c r="AG3">
-        <v>532.9</v>
+        <v>531.7</v>
       </c>
       <c r="AH3">
-        <v>479.36</v>
+        <v>478.16</v>
       </c>
       <c r="AI3">
         <v>460.99</v>
@@ -1154,7 +1111,7 @@
         <v>48</v>
       </c>
       <c r="AK3">
-        <v>32.06</v>
+        <v>34.8</v>
       </c>
     </row>
     <row r="4" spans="1:37">
@@ -1165,10 +1122,10 @@
         <v>44</v>
       </c>
       <c r="C4">
-        <v>299.25</v>
+        <v>300.25</v>
       </c>
       <c r="D4">
-        <v>-0.18</v>
+        <v>0.33</v>
       </c>
       <c r="E4">
         <v>548</v>
@@ -1177,46 +1134,46 @@
         <v>299.25</v>
       </c>
       <c r="G4">
-        <v>-45.39</v>
+        <v>-45.21</v>
       </c>
       <c r="H4">
-        <v>0</v>
+        <v>0.33</v>
       </c>
       <c r="I4">
-        <v>-6.18</v>
+        <v>-4.58</v>
       </c>
       <c r="J4">
-        <v>-7.52</v>
+        <v>-10.16</v>
       </c>
       <c r="K4">
-        <v>-8.210000000000001</v>
+        <v>-9.210000000000001</v>
       </c>
       <c r="L4">
-        <v>-46.08</v>
+        <v>-44.91</v>
       </c>
       <c r="M4">
-        <v>-24.15</v>
+        <v>-23.84</v>
       </c>
       <c r="N4">
         <v>15</v>
       </c>
       <c r="O4">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="P4">
-        <v>305.39</v>
+        <v>302.51</v>
       </c>
       <c r="Q4">
-        <v>323.58</v>
+        <v>322.03</v>
       </c>
       <c r="R4">
-        <v>336.36</v>
+        <v>335.79</v>
       </c>
       <c r="S4">
-        <v>367.13</v>
+        <v>366.24</v>
       </c>
       <c r="T4">
-        <v>-18.49</v>
+        <v>-18.02</v>
       </c>
       <c r="U4" t="s">
         <v>45</v>
@@ -1231,34 +1188,34 @@
         <v>0</v>
       </c>
       <c r="Y4">
-        <v>28.27</v>
+        <v>29.53</v>
       </c>
       <c r="Z4">
-        <v>-9.25</v>
+        <v>-9.65</v>
       </c>
       <c r="AA4">
-        <v>-6.68</v>
+        <v>-7.28</v>
       </c>
       <c r="AB4">
-        <v>-2.57</v>
+        <v>-2.38</v>
       </c>
       <c r="AC4">
-        <v>0</v>
+        <v>2.35</v>
       </c>
       <c r="AD4">
-        <v>0</v>
+        <v>0.78</v>
       </c>
       <c r="AE4">
-        <v>9.640000000000001</v>
+        <v>9.41</v>
       </c>
       <c r="AF4">
-        <v>-23.9</v>
+        <v>-13.15</v>
       </c>
       <c r="AG4">
-        <v>349.52</v>
+        <v>349.7</v>
       </c>
       <c r="AH4">
-        <v>297.64</v>
+        <v>294.37</v>
       </c>
       <c r="AI4">
         <v>330.22</v>
@@ -1267,7 +1224,7 @@
         <v>47</v>
       </c>
       <c r="AK4">
-        <v>35.96</v>
+        <v>39.93</v>
       </c>
     </row>
     <row r="5" spans="1:37">
@@ -1278,10 +1235,10 @@
         <v>44</v>
       </c>
       <c r="C5">
-        <v>1751.4</v>
+        <v>1752.4</v>
       </c>
       <c r="D5">
-        <v>1.09</v>
+        <v>0.06</v>
       </c>
       <c r="E5">
         <v>2176.6</v>
@@ -1290,46 +1247,46 @@
         <v>1631.8</v>
       </c>
       <c r="G5">
-        <v>-19.54</v>
+        <v>-19.49</v>
       </c>
       <c r="H5">
-        <v>7.33</v>
+        <v>7.39</v>
       </c>
       <c r="I5">
-        <v>-1.11</v>
+        <v>0.02</v>
       </c>
       <c r="J5">
-        <v>-11.99</v>
+        <v>-12.03</v>
       </c>
       <c r="K5">
-        <v>-6.38</v>
+        <v>-7.05</v>
       </c>
       <c r="L5">
-        <v>-13.5</v>
+        <v>-12.66</v>
       </c>
       <c r="M5">
-        <v>-0.34</v>
+        <v>-0.07000000000000001</v>
       </c>
       <c r="N5">
         <v>29</v>
       </c>
       <c r="O5">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="P5">
-        <v>1741.88</v>
+        <v>1741.96</v>
       </c>
       <c r="Q5">
-        <v>1839.72</v>
+        <v>1828.84</v>
       </c>
       <c r="R5">
-        <v>1938.89</v>
+        <v>1936.4</v>
       </c>
       <c r="S5">
-        <v>1883.09</v>
+        <v>1881.67</v>
       </c>
       <c r="T5">
-        <v>-6.99</v>
+        <v>-6.87</v>
       </c>
       <c r="U5" t="s">
         <v>45</v>
@@ -1344,34 +1301,34 @@
         <v>1</v>
       </c>
       <c r="Y5">
-        <v>30.33</v>
+        <v>30.61</v>
       </c>
       <c r="Z5">
-        <v>-59.39</v>
+        <v>-57.82</v>
       </c>
       <c r="AA5">
-        <v>-50.18</v>
+        <v>-51.71</v>
       </c>
       <c r="AB5">
-        <v>-9.220000000000001</v>
+        <v>-6.12</v>
       </c>
       <c r="AC5">
-        <v>19.13</v>
+        <v>37.98</v>
       </c>
       <c r="AD5">
-        <v>6.99</v>
+        <v>19.43</v>
       </c>
       <c r="AE5">
-        <v>36.62</v>
+        <v>35.16</v>
       </c>
       <c r="AF5">
-        <v>38.9</v>
+        <v>-30.16</v>
       </c>
       <c r="AG5">
-        <v>1998.55</v>
+        <v>1979.71</v>
       </c>
       <c r="AH5">
-        <v>1680.88</v>
+        <v>1677.96</v>
       </c>
       <c r="AI5">
         <v>1830.94</v>
@@ -1380,7 +1337,7 @@
         <v>47</v>
       </c>
       <c r="AK5">
-        <v>75.81999999999999</v>
+        <v>72.65000000000001</v>
       </c>
     </row>
     <row r="6" spans="1:37">
@@ -1391,10 +1348,10 @@
         <v>44</v>
       </c>
       <c r="C6">
-        <v>10732</v>
+        <v>10600</v>
       </c>
       <c r="D6">
-        <v>0.62</v>
+        <v>-1.23</v>
       </c>
       <c r="E6">
         <v>13144</v>
@@ -1403,46 +1360,46 @@
         <v>8746</v>
       </c>
       <c r="G6">
-        <v>-18.35</v>
+        <v>-19.35</v>
       </c>
       <c r="H6">
-        <v>22.71</v>
+        <v>21.2</v>
       </c>
       <c r="I6">
-        <v>-1.9</v>
+        <v>-1.85</v>
       </c>
       <c r="J6">
-        <v>-3.32</v>
+        <v>-5.06</v>
       </c>
       <c r="K6">
-        <v>-0.8</v>
+        <v>-1.48</v>
       </c>
       <c r="L6">
-        <v>-13.88</v>
+        <v>-13.45</v>
       </c>
       <c r="M6">
-        <v>18.56</v>
+        <v>18.6</v>
       </c>
       <c r="N6">
         <v>43</v>
       </c>
       <c r="O6">
-        <v>50</v>
+        <v>48</v>
       </c>
       <c r="P6">
-        <v>10717.2</v>
+        <v>10677.2</v>
       </c>
       <c r="Q6">
-        <v>11008.8</v>
+        <v>10980.7</v>
       </c>
       <c r="R6">
-        <v>11185.16</v>
+        <v>11183.58</v>
       </c>
       <c r="S6">
-        <v>10674.26</v>
+        <v>10671.92</v>
       </c>
       <c r="T6">
-        <v>0.54</v>
+        <v>-0.67</v>
       </c>
       <c r="U6" t="s">
         <v>45</v>
@@ -1454,37 +1411,37 @@
         <v>45</v>
       </c>
       <c r="X6">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="Y6">
-        <v>42.89</v>
+        <v>40.28</v>
       </c>
       <c r="Z6">
-        <v>-120.28</v>
+        <v>-135.05</v>
       </c>
       <c r="AA6">
-        <v>-70.08</v>
+        <v>-83.08</v>
       </c>
       <c r="AB6">
-        <v>-50.2</v>
+        <v>-51.97</v>
       </c>
       <c r="AC6">
-        <v>21.78</v>
+        <v>16.06</v>
       </c>
       <c r="AD6">
-        <v>14.85</v>
+        <v>17.21</v>
       </c>
       <c r="AE6">
-        <v>263.58</v>
+        <v>262.11</v>
       </c>
       <c r="AF6">
-        <v>14.58</v>
+        <v>-10.62</v>
       </c>
       <c r="AG6">
-        <v>11465.17</v>
+        <v>11465.66</v>
       </c>
       <c r="AH6">
-        <v>10552.43</v>
+        <v>10495.74</v>
       </c>
       <c r="AI6">
         <v>11368.55</v>
@@ -1493,7 +1450,7 @@
         <v>47</v>
       </c>
       <c r="AK6">
-        <v>34.41</v>
+        <v>35.28</v>
       </c>
     </row>
     <row r="7" spans="1:37">
@@ -1504,10 +1461,10 @@
         <v>44</v>
       </c>
       <c r="C7">
-        <v>970</v>
+        <v>963.1</v>
       </c>
       <c r="D7">
-        <v>2.29</v>
+        <v>-0.71</v>
       </c>
       <c r="E7">
         <v>1158.8</v>
@@ -1516,46 +1473,46 @@
         <v>801.55</v>
       </c>
       <c r="G7">
-        <v>-16.29</v>
+        <v>-16.89</v>
       </c>
       <c r="H7">
-        <v>21.02</v>
+        <v>20.15</v>
       </c>
       <c r="I7">
-        <v>-2.7</v>
+        <v>-2.22</v>
       </c>
       <c r="J7">
-        <v>-8.140000000000001</v>
+        <v>-8.19</v>
       </c>
       <c r="K7">
-        <v>-5.74</v>
+        <v>-7.62</v>
       </c>
       <c r="L7">
-        <v>-2.11</v>
+        <v>-3.58</v>
       </c>
       <c r="M7">
-        <v>5.06</v>
+        <v>4.88</v>
       </c>
       <c r="N7">
         <v>57</v>
       </c>
       <c r="O7">
-        <v>54</v>
+        <v>50</v>
       </c>
       <c r="P7">
-        <v>967.3</v>
+        <v>962.92</v>
       </c>
       <c r="Q7">
-        <v>1012.57</v>
+        <v>1007.7</v>
       </c>
       <c r="R7">
-        <v>1056.86</v>
+        <v>1055.86</v>
       </c>
       <c r="S7">
-        <v>976.11</v>
+        <v>975.9299999999999</v>
       </c>
       <c r="T7">
-        <v>-0.63</v>
+        <v>-1.31</v>
       </c>
       <c r="U7" t="s">
         <v>45</v>
@@ -1570,34 +1527,34 @@
         <v>1</v>
       </c>
       <c r="Y7">
-        <v>38.77</v>
+        <v>37.52</v>
       </c>
       <c r="Z7">
-        <v>-25.64</v>
+        <v>-25.85</v>
       </c>
       <c r="AA7">
-        <v>-20.31</v>
+        <v>-21.42</v>
       </c>
       <c r="AB7">
-        <v>-5.33</v>
+        <v>-4.44</v>
       </c>
       <c r="AC7">
-        <v>22.02</v>
+        <v>28.71</v>
       </c>
       <c r="AD7">
-        <v>22.63</v>
+        <v>22.7</v>
       </c>
       <c r="AE7">
-        <v>26.29</v>
+        <v>25.57</v>
       </c>
       <c r="AF7">
-        <v>101.19</v>
+        <v>-33.75</v>
       </c>
       <c r="AG7">
-        <v>1081.38</v>
+        <v>1076.01</v>
       </c>
       <c r="AH7">
-        <v>943.75</v>
+        <v>939.38</v>
       </c>
       <c r="AI7">
         <v>1020.6</v>
@@ -1606,7 +1563,7 @@
         <v>47</v>
       </c>
       <c r="AK7">
-        <v>44.04</v>
+        <v>40.47</v>
       </c>
     </row>
     <row r="8" spans="1:37">
@@ -1617,10 +1574,10 @@
         <v>44</v>
       </c>
       <c r="C8">
-        <v>182.2</v>
+        <v>181.55</v>
       </c>
       <c r="D8">
-        <v>5.53</v>
+        <v>-0.36</v>
       </c>
       <c r="E8">
         <v>182.2</v>
@@ -1629,46 +1586,46 @@
         <v>115.96</v>
       </c>
       <c r="G8">
-        <v>0</v>
+        <v>-0.36</v>
       </c>
       <c r="H8">
-        <v>57.12</v>
+        <v>56.56</v>
       </c>
       <c r="I8">
-        <v>9.07</v>
+        <v>6.15</v>
       </c>
       <c r="J8">
-        <v>35.79</v>
+        <v>36.53</v>
       </c>
       <c r="K8">
-        <v>37.03</v>
+        <v>38.33</v>
       </c>
       <c r="L8">
-        <v>40.27</v>
+        <v>37.07</v>
       </c>
       <c r="M8">
-        <v>4.56</v>
+        <v>4.96</v>
       </c>
       <c r="N8">
         <v>99</v>
       </c>
       <c r="O8">
-        <v>91</v>
+        <v>89</v>
       </c>
       <c r="P8">
-        <v>175.7</v>
+        <v>177.81</v>
       </c>
       <c r="Q8">
-        <v>150.28</v>
+        <v>152.64</v>
       </c>
       <c r="R8">
-        <v>142.93</v>
+        <v>143.79</v>
       </c>
       <c r="S8">
-        <v>135.37</v>
+        <v>135.62</v>
       </c>
       <c r="T8">
-        <v>34.59</v>
+        <v>33.87</v>
       </c>
       <c r="U8" t="s">
         <v>46</v>
@@ -1683,34 +1640,34 @@
         <v>3</v>
       </c>
       <c r="Y8">
-        <v>76.90000000000001</v>
+        <v>76.01000000000001</v>
       </c>
       <c r="Z8">
-        <v>10.59</v>
+        <v>11.26</v>
       </c>
       <c r="AA8">
-        <v>6.5</v>
+        <v>7.45</v>
       </c>
       <c r="AB8">
-        <v>4.09</v>
+        <v>3.81</v>
       </c>
       <c r="AC8">
-        <v>84.61</v>
+        <v>77.98</v>
       </c>
       <c r="AD8">
-        <v>91.70999999999999</v>
+        <v>84.37</v>
       </c>
       <c r="AE8">
-        <v>8.1</v>
+        <v>8.23</v>
       </c>
       <c r="AF8">
-        <v>283.43</v>
+        <v>-21.31</v>
       </c>
       <c r="AG8">
-        <v>185.21</v>
+        <v>189.38</v>
       </c>
       <c r="AH8">
-        <v>115.35</v>
+        <v>115.89</v>
       </c>
       <c r="AI8">
         <v>158.84</v>
@@ -1719,7 +1676,7 @@
         <v>48</v>
       </c>
       <c r="AK8">
-        <v>54.22</v>
+        <v>55.48</v>
       </c>
     </row>
   </sheetData>
@@ -1860,7 +1817,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:F65"/>
+  <dimension ref="A1:F62"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="16.7109375" customWidth="1"/>
@@ -1880,1080 +1837,991 @@
     </row>
     <row r="2" spans="1:6">
       <c r="A2" s="3" t="s">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="5" spans="1:6">
+      <c r="A5" s="2" t="s">
+        <v>51</v>
+      </c>
+      <c r="B5" s="2"/>
+      <c r="C5" s="2"/>
+      <c r="D5" s="2"/>
+      <c r="E5" s="2"/>
+    </row>
+    <row r="6" spans="1:6">
+      <c r="A6" s="4" t="s">
         <v>0</v>
       </c>
-      <c r="B2" s="3" t="s">
-        <v>50</v>
-      </c>
-      <c r="C2" s="3" t="s">
-        <v>51</v>
-      </c>
-      <c r="D2" s="3" t="s">
+      <c r="B6" s="4" t="s">
         <v>52</v>
       </c>
-      <c r="E2" s="3" t="s">
+      <c r="C6" s="4" t="s">
         <v>53</v>
       </c>
-      <c r="F2" s="3" t="s">
+      <c r="D6" s="4" t="s">
         <v>54</v>
       </c>
-    </row>
-    <row r="3" spans="1:6">
-      <c r="A3" s="4" t="s">
-        <v>43</v>
-      </c>
-      <c r="B3" s="4" t="s">
+      <c r="E6" s="4" t="s">
         <v>55</v>
       </c>
-      <c r="C3" s="4" t="s">
-        <v>56</v>
-      </c>
-      <c r="D3" s="4" t="s">
-        <v>57</v>
-      </c>
-      <c r="E3" s="4" t="s">
-        <v>58</v>
-      </c>
-      <c r="F3" s="4" t="s">
-        <v>59</v>
-      </c>
-    </row>
-    <row r="4" spans="1:6">
-      <c r="A4" s="4" t="s">
-        <v>40</v>
-      </c>
-      <c r="B4" s="4" t="s">
-        <v>60</v>
-      </c>
-      <c r="C4" s="4" t="s">
-        <v>61</v>
-      </c>
-      <c r="D4" s="4" t="s">
-        <v>62</v>
-      </c>
-      <c r="E4" s="4" t="s">
-        <v>63</v>
-      </c>
-      <c r="F4" s="4" t="s">
-        <v>64</v>
-      </c>
-    </row>
-    <row r="6" spans="1:6">
-      <c r="A6" s="2" t="s">
-        <v>65</v>
-      </c>
-      <c r="B6" s="2"/>
-      <c r="C6" s="2"/>
-      <c r="D6" s="2"/>
-      <c r="E6" s="2"/>
     </row>
     <row r="7" spans="1:6">
       <c r="A7" s="3" t="s">
+        <v>37</v>
+      </c>
+      <c r="B7" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="C7" s="5">
+        <v>-17.36</v>
+      </c>
+      <c r="D7" s="5">
+        <v>-15.96</v>
+      </c>
+      <c r="E7" s="6">
+        <v>1.4</v>
+      </c>
+    </row>
+    <row r="8" spans="1:6">
+      <c r="A8" s="3" t="s">
+        <v>38</v>
+      </c>
+      <c r="B8" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="C8" s="5">
+        <v>-0.87</v>
+      </c>
+      <c r="D8" s="5">
+        <v>-3.04</v>
+      </c>
+      <c r="E8" s="7">
+        <v>-2.17</v>
+      </c>
+    </row>
+    <row r="9" spans="1:6">
+      <c r="A9" s="3" t="s">
+        <v>39</v>
+      </c>
+      <c r="B9" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="C9" s="5">
+        <v>-7.52</v>
+      </c>
+      <c r="D9" s="5">
+        <v>-10.16</v>
+      </c>
+      <c r="E9" s="7">
+        <v>-2.64</v>
+      </c>
+    </row>
+    <row r="10" spans="1:6">
+      <c r="A10" s="3" t="s">
+        <v>40</v>
+      </c>
+      <c r="B10" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="C10" s="5">
+        <v>-11.99</v>
+      </c>
+      <c r="D10" s="5">
+        <v>-12.03</v>
+      </c>
+      <c r="E10" s="7">
+        <v>-0.04</v>
+      </c>
+    </row>
+    <row r="11" spans="1:6">
+      <c r="A11" s="3" t="s">
+        <v>41</v>
+      </c>
+      <c r="B11" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="C11" s="5">
+        <v>-3.32</v>
+      </c>
+      <c r="D11" s="5">
+        <v>-5.06</v>
+      </c>
+      <c r="E11" s="7">
+        <v>-1.74</v>
+      </c>
+    </row>
+    <row r="12" spans="1:6">
+      <c r="A12" s="3" t="s">
+        <v>42</v>
+      </c>
+      <c r="B12" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="C12" s="5">
+        <v>-8.140000000000001</v>
+      </c>
+      <c r="D12" s="5">
+        <v>-8.19</v>
+      </c>
+      <c r="E12" s="7">
+        <v>-0.05</v>
+      </c>
+    </row>
+    <row r="13" spans="1:6">
+      <c r="A13" s="3" t="s">
+        <v>43</v>
+      </c>
+      <c r="B13" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="C13" s="5">
+        <v>35.79</v>
+      </c>
+      <c r="D13" s="5">
+        <v>36.53</v>
+      </c>
+      <c r="E13" s="6">
+        <v>0.74</v>
+      </c>
+    </row>
+    <row r="14" spans="1:6">
+      <c r="A14" s="3" t="s">
+        <v>37</v>
+      </c>
+      <c r="B14" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="C14" s="5">
+        <v>-11.14</v>
+      </c>
+      <c r="D14" s="5">
+        <v>-9.130000000000001</v>
+      </c>
+      <c r="E14" s="6">
+        <v>2.01</v>
+      </c>
+    </row>
+    <row r="15" spans="1:6">
+      <c r="A15" s="3" t="s">
+        <v>38</v>
+      </c>
+      <c r="B15" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="C15" s="5">
+        <v>-3.83</v>
+      </c>
+      <c r="D15" s="5">
+        <v>2.8</v>
+      </c>
+      <c r="E15" s="6">
+        <v>6.63</v>
+      </c>
+    </row>
+    <row r="16" spans="1:6">
+      <c r="A16" s="3" t="s">
+        <v>39</v>
+      </c>
+      <c r="B16" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="C16" s="5">
+        <v>-6.18</v>
+      </c>
+      <c r="D16" s="5">
+        <v>-4.58</v>
+      </c>
+      <c r="E16" s="6">
+        <v>1.6</v>
+      </c>
+    </row>
+    <row r="17" spans="1:5">
+      <c r="A17" s="3" t="s">
+        <v>40</v>
+      </c>
+      <c r="B17" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="C17" s="5">
+        <v>-1.11</v>
+      </c>
+      <c r="D17" s="5">
+        <v>0.02</v>
+      </c>
+      <c r="E17" s="6">
+        <v>1.13</v>
+      </c>
+    </row>
+    <row r="18" spans="1:5">
+      <c r="A18" s="3" t="s">
+        <v>41</v>
+      </c>
+      <c r="B18" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="C18" s="5">
+        <v>-1.9</v>
+      </c>
+      <c r="D18" s="5">
+        <v>-1.85</v>
+      </c>
+      <c r="E18" s="6">
+        <v>0.05</v>
+      </c>
+    </row>
+    <row r="19" spans="1:5">
+      <c r="A19" s="3" t="s">
+        <v>42</v>
+      </c>
+      <c r="B19" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="C19" s="5">
+        <v>-2.7</v>
+      </c>
+      <c r="D19" s="5">
+        <v>-2.22</v>
+      </c>
+      <c r="E19" s="6">
+        <v>0.48</v>
+      </c>
+    </row>
+    <row r="20" spans="1:5">
+      <c r="A20" s="3" t="s">
+        <v>43</v>
+      </c>
+      <c r="B20" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="C20" s="5">
+        <v>9.07</v>
+      </c>
+      <c r="D20" s="5">
+        <v>6.15</v>
+      </c>
+      <c r="E20" s="7">
+        <v>-2.92</v>
+      </c>
+    </row>
+    <row r="21" spans="1:5">
+      <c r="A21" s="3" t="s">
+        <v>37</v>
+      </c>
+      <c r="B21" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="C21" s="5">
+        <v>16.61</v>
+      </c>
+      <c r="D21" s="5">
+        <v>17.05</v>
+      </c>
+      <c r="E21" s="6">
+        <v>0.44</v>
+      </c>
+    </row>
+    <row r="22" spans="1:5">
+      <c r="A22" s="3" t="s">
+        <v>38</v>
+      </c>
+      <c r="B22" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="C22" s="5">
+        <v>104.06</v>
+      </c>
+      <c r="D22" s="5">
+        <v>108.32</v>
+      </c>
+      <c r="E22" s="6">
+        <v>4.26</v>
+      </c>
+    </row>
+    <row r="23" spans="1:5">
+      <c r="A23" s="3" t="s">
+        <v>39</v>
+      </c>
+      <c r="B23" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="C23" s="5">
+        <v>-46.08</v>
+      </c>
+      <c r="D23" s="5">
+        <v>-44.91</v>
+      </c>
+      <c r="E23" s="6">
+        <v>1.17</v>
+      </c>
+    </row>
+    <row r="24" spans="1:5">
+      <c r="A24" s="3" t="s">
+        <v>40</v>
+      </c>
+      <c r="B24" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="C24" s="5">
+        <v>-13.5</v>
+      </c>
+      <c r="D24" s="5">
+        <v>-12.66</v>
+      </c>
+      <c r="E24" s="6">
+        <v>0.84</v>
+      </c>
+    </row>
+    <row r="25" spans="1:5">
+      <c r="A25" s="3" t="s">
+        <v>41</v>
+      </c>
+      <c r="B25" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="C25" s="5">
+        <v>-13.88</v>
+      </c>
+      <c r="D25" s="5">
+        <v>-13.45</v>
+      </c>
+      <c r="E25" s="6">
+        <v>0.43</v>
+      </c>
+    </row>
+    <row r="26" spans="1:5">
+      <c r="A26" s="3" t="s">
+        <v>42</v>
+      </c>
+      <c r="B26" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="C26" s="5">
+        <v>-2.11</v>
+      </c>
+      <c r="D26" s="5">
+        <v>-3.58</v>
+      </c>
+      <c r="E26" s="7">
+        <v>-1.47</v>
+      </c>
+    </row>
+    <row r="27" spans="1:5">
+      <c r="A27" s="3" t="s">
+        <v>43</v>
+      </c>
+      <c r="B27" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="C27" s="5">
+        <v>40.27</v>
+      </c>
+      <c r="D27" s="5">
+        <v>37.07</v>
+      </c>
+      <c r="E27" s="7">
+        <v>-3.2</v>
+      </c>
+    </row>
+    <row r="28" spans="1:5">
+      <c r="A28" s="3" t="s">
+        <v>37</v>
+      </c>
+      <c r="B28" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="C28" s="5">
+        <v>-0.12</v>
+      </c>
+      <c r="D28" s="5">
+        <v>-0.91</v>
+      </c>
+      <c r="E28" s="7">
+        <v>-0.79</v>
+      </c>
+    </row>
+    <row r="29" spans="1:5">
+      <c r="A29" s="3" t="s">
+        <v>38</v>
+      </c>
+      <c r="B29" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="C29" s="5">
+        <v>-22.49</v>
+      </c>
+      <c r="D29" s="5">
+        <v>-20.44</v>
+      </c>
+      <c r="E29" s="6">
+        <v>2.05</v>
+      </c>
+    </row>
+    <row r="30" spans="1:5">
+      <c r="A30" s="3" t="s">
+        <v>39</v>
+      </c>
+      <c r="B30" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="C30" s="5">
+        <v>-8.210000000000001</v>
+      </c>
+      <c r="D30" s="5">
+        <v>-9.210000000000001</v>
+      </c>
+      <c r="E30" s="7">
+        <v>-1</v>
+      </c>
+    </row>
+    <row r="31" spans="1:5">
+      <c r="A31" s="3" t="s">
+        <v>40</v>
+      </c>
+      <c r="B31" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="C31" s="5">
+        <v>-6.38</v>
+      </c>
+      <c r="D31" s="5">
+        <v>-7.05</v>
+      </c>
+      <c r="E31" s="7">
+        <v>-0.67</v>
+      </c>
+    </row>
+    <row r="32" spans="1:5">
+      <c r="A32" s="3" t="s">
+        <v>41</v>
+      </c>
+      <c r="B32" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="C32" s="5">
+        <v>-0.8</v>
+      </c>
+      <c r="D32" s="5">
+        <v>-1.48</v>
+      </c>
+      <c r="E32" s="7">
+        <v>-0.68</v>
+      </c>
+    </row>
+    <row r="33" spans="1:5">
+      <c r="A33" s="3" t="s">
+        <v>42</v>
+      </c>
+      <c r="B33" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="C33" s="5">
+        <v>-5.74</v>
+      </c>
+      <c r="D33" s="5">
+        <v>-7.62</v>
+      </c>
+      <c r="E33" s="7">
+        <v>-1.88</v>
+      </c>
+    </row>
+    <row r="34" spans="1:5">
+      <c r="A34" s="3" t="s">
+        <v>43</v>
+      </c>
+      <c r="B34" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="C34" s="5">
+        <v>37.03</v>
+      </c>
+      <c r="D34" s="5">
+        <v>38.33</v>
+      </c>
+      <c r="E34" s="6">
+        <v>1.3</v>
+      </c>
+    </row>
+    <row r="35" spans="1:5">
+      <c r="A35" s="3" t="s">
+        <v>37</v>
+      </c>
+      <c r="B35" s="3" t="s">
+        <v>6</v>
+      </c>
+      <c r="C35" s="5">
+        <v>-18.91</v>
+      </c>
+      <c r="D35" s="5">
+        <v>-18.96</v>
+      </c>
+      <c r="E35" s="7">
+        <v>-0.05</v>
+      </c>
+    </row>
+    <row r="36" spans="1:5">
+      <c r="A36" s="3" t="s">
+        <v>38</v>
+      </c>
+      <c r="B36" s="3" t="s">
+        <v>6</v>
+      </c>
+      <c r="C36" s="5">
+        <v>-28.33</v>
+      </c>
+      <c r="D36" s="5">
+        <v>-26.37</v>
+      </c>
+      <c r="E36" s="6">
+        <v>1.96</v>
+      </c>
+    </row>
+    <row r="37" spans="1:5">
+      <c r="A37" s="3" t="s">
+        <v>39</v>
+      </c>
+      <c r="B37" s="3" t="s">
+        <v>6</v>
+      </c>
+      <c r="C37" s="5">
+        <v>-45.39</v>
+      </c>
+      <c r="D37" s="5">
+        <v>-45.21</v>
+      </c>
+      <c r="E37" s="6">
+        <v>0.18</v>
+      </c>
+    </row>
+    <row r="38" spans="1:5">
+      <c r="A38" s="3" t="s">
+        <v>40</v>
+      </c>
+      <c r="B38" s="3" t="s">
+        <v>6</v>
+      </c>
+      <c r="C38" s="5">
+        <v>-19.54</v>
+      </c>
+      <c r="D38" s="5">
+        <v>-19.49</v>
+      </c>
+      <c r="E38" s="6">
+        <v>0.05</v>
+      </c>
+    </row>
+    <row r="39" spans="1:5">
+      <c r="A39" s="3" t="s">
+        <v>41</v>
+      </c>
+      <c r="B39" s="3" t="s">
+        <v>6</v>
+      </c>
+      <c r="C39" s="5">
+        <v>-18.35</v>
+      </c>
+      <c r="D39" s="5">
+        <v>-19.35</v>
+      </c>
+      <c r="E39" s="7">
+        <v>-1</v>
+      </c>
+    </row>
+    <row r="40" spans="1:5">
+      <c r="A40" s="3" t="s">
+        <v>42</v>
+      </c>
+      <c r="B40" s="3" t="s">
+        <v>6</v>
+      </c>
+      <c r="C40" s="5">
+        <v>-16.29</v>
+      </c>
+      <c r="D40" s="5">
+        <v>-16.89</v>
+      </c>
+      <c r="E40" s="7">
+        <v>-0.6</v>
+      </c>
+    </row>
+    <row r="41" spans="1:5">
+      <c r="A41" s="3" t="s">
+        <v>43</v>
+      </c>
+      <c r="B41" s="3" t="s">
+        <v>6</v>
+      </c>
+      <c r="C41" s="5">
         <v>0</v>
       </c>
-      <c r="B7" s="3" t="s">
-        <v>66</v>
-      </c>
-      <c r="C7" s="3" t="s">
-        <v>67</v>
-      </c>
-      <c r="D7" s="3" t="s">
-        <v>68</v>
-      </c>
-      <c r="E7" s="3" t="s">
-        <v>69</v>
-      </c>
-    </row>
-    <row r="8" spans="1:6">
-      <c r="A8" s="5" t="s">
+      <c r="D41" s="5">
+        <v>-0.36</v>
+      </c>
+      <c r="E41" s="7">
+        <v>-0.36</v>
+      </c>
+    </row>
+    <row r="42" spans="1:5">
+      <c r="A42" s="3" t="s">
         <v>37</v>
       </c>
-      <c r="B8" s="5" t="s">
-        <v>9</v>
-      </c>
-      <c r="C8" s="6">
-        <v>-18.74</v>
-      </c>
-      <c r="D8" s="6">
-        <v>-17.36</v>
-      </c>
-      <c r="E8" s="7">
-        <v>1.38</v>
-      </c>
-    </row>
-    <row r="9" spans="1:6">
-      <c r="A9" s="5" t="s">
+      <c r="B42" s="3" t="s">
+        <v>2</v>
+      </c>
+      <c r="C42" s="5">
+        <v>10024</v>
+      </c>
+      <c r="D42" s="5">
+        <v>10017</v>
+      </c>
+      <c r="E42" s="7">
+        <v>-7</v>
+      </c>
+    </row>
+    <row r="43" spans="1:5">
+      <c r="A43" s="3" t="s">
         <v>38</v>
       </c>
-      <c r="B9" s="5" t="s">
-        <v>9</v>
-      </c>
-      <c r="C9" s="6">
-        <v>5.32</v>
-      </c>
-      <c r="D9" s="6">
-        <v>-0.87</v>
-      </c>
-      <c r="E9" s="8">
-        <v>-6.19</v>
-      </c>
-    </row>
-    <row r="10" spans="1:6">
-      <c r="A10" s="5" t="s">
+      <c r="B43" s="3" t="s">
+        <v>2</v>
+      </c>
+      <c r="C43" s="5">
+        <v>480.35</v>
+      </c>
+      <c r="D43" s="5">
+        <v>493.5</v>
+      </c>
+      <c r="E43" s="6">
+        <v>13.15</v>
+      </c>
+    </row>
+    <row r="44" spans="1:5">
+      <c r="A44" s="3" t="s">
         <v>39</v>
       </c>
-      <c r="B10" s="5" t="s">
-        <v>9</v>
-      </c>
-      <c r="C10" s="6">
-        <v>-7.99</v>
-      </c>
-      <c r="D10" s="6">
-        <v>-7.52</v>
-      </c>
-      <c r="E10" s="7">
-        <v>0.47</v>
-      </c>
-    </row>
-    <row r="11" spans="1:6">
-      <c r="A11" s="5" t="s">
+      <c r="B44" s="3" t="s">
+        <v>2</v>
+      </c>
+      <c r="C44" s="5">
+        <v>299.25</v>
+      </c>
+      <c r="D44" s="5">
+        <v>300.25</v>
+      </c>
+      <c r="E44" s="6">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="45" spans="1:5">
+      <c r="A45" s="3" t="s">
         <v>40</v>
       </c>
-      <c r="B11" s="5" t="s">
-        <v>9</v>
-      </c>
-      <c r="C11" s="6">
-        <v>-12.14</v>
-      </c>
-      <c r="D11" s="6">
-        <v>-11.99</v>
-      </c>
-      <c r="E11" s="7">
-        <v>0.15</v>
-      </c>
-    </row>
-    <row r="12" spans="1:6">
-      <c r="A12" s="5" t="s">
+      <c r="B45" s="3" t="s">
+        <v>2</v>
+      </c>
+      <c r="C45" s="5">
+        <v>1751.4</v>
+      </c>
+      <c r="D45" s="5">
+        <v>1752.4</v>
+      </c>
+      <c r="E45" s="6">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="46" spans="1:5">
+      <c r="A46" s="3" t="s">
         <v>41</v>
       </c>
-      <c r="B12" s="5" t="s">
-        <v>9</v>
-      </c>
-      <c r="C12" s="6">
-        <v>-5.69</v>
-      </c>
-      <c r="D12" s="6">
-        <v>-3.32</v>
-      </c>
-      <c r="E12" s="7">
-        <v>2.37</v>
-      </c>
-    </row>
-    <row r="13" spans="1:6">
-      <c r="A13" s="5" t="s">
+      <c r="B46" s="3" t="s">
+        <v>2</v>
+      </c>
+      <c r="C46" s="5">
+        <v>10732</v>
+      </c>
+      <c r="D46" s="5">
+        <v>10600</v>
+      </c>
+      <c r="E46" s="7">
+        <v>-132</v>
+      </c>
+    </row>
+    <row r="47" spans="1:5">
+      <c r="A47" s="3" t="s">
         <v>42</v>
       </c>
-      <c r="B13" s="5" t="s">
-        <v>9</v>
-      </c>
-      <c r="C13" s="6">
-        <v>-10.02</v>
-      </c>
-      <c r="D13" s="6">
-        <v>-8.140000000000001</v>
-      </c>
-      <c r="E13" s="7">
-        <v>1.88</v>
-      </c>
-    </row>
-    <row r="14" spans="1:6">
-      <c r="A14" s="5" t="s">
+      <c r="B47" s="3" t="s">
+        <v>2</v>
+      </c>
+      <c r="C47" s="5">
+        <v>970</v>
+      </c>
+      <c r="D47" s="5">
+        <v>963.1</v>
+      </c>
+      <c r="E47" s="7">
+        <v>-6.9</v>
+      </c>
+    </row>
+    <row r="48" spans="1:5">
+      <c r="A48" s="3" t="s">
         <v>43</v>
       </c>
-      <c r="B14" s="5" t="s">
-        <v>9</v>
-      </c>
-      <c r="C14" s="6">
-        <v>26.93</v>
-      </c>
-      <c r="D14" s="6">
-        <v>35.79</v>
-      </c>
-      <c r="E14" s="7">
-        <v>8.859999999999999</v>
-      </c>
-    </row>
-    <row r="15" spans="1:6">
-      <c r="A15" s="5" t="s">
+      <c r="B48" s="3" t="s">
+        <v>2</v>
+      </c>
+      <c r="C48" s="5">
+        <v>182.2</v>
+      </c>
+      <c r="D48" s="5">
+        <v>181.55</v>
+      </c>
+      <c r="E48" s="7">
+        <v>-0.65</v>
+      </c>
+    </row>
+    <row r="49" spans="1:5">
+      <c r="A49" s="3" t="s">
         <v>37</v>
       </c>
-      <c r="B15" s="5" t="s">
-        <v>8</v>
-      </c>
-      <c r="C15" s="6">
-        <v>-10.38</v>
-      </c>
-      <c r="D15" s="6">
-        <v>-11.14</v>
-      </c>
-      <c r="E15" s="8">
-        <v>-0.76</v>
-      </c>
-    </row>
-    <row r="16" spans="1:6">
-      <c r="A16" s="5" t="s">
+      <c r="B49" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="C49" s="5">
+        <v>21.6</v>
+      </c>
+      <c r="D49" s="5">
+        <v>21.53</v>
+      </c>
+      <c r="E49" s="7">
+        <v>-0.07000000000000001</v>
+      </c>
+    </row>
+    <row r="50" spans="1:5">
+      <c r="A50" s="3" t="s">
         <v>38</v>
       </c>
-      <c r="B16" s="5" t="s">
-        <v>8</v>
-      </c>
-      <c r="C16" s="6">
-        <v>-0.93</v>
-      </c>
-      <c r="D16" s="6">
-        <v>-3.83</v>
-      </c>
-      <c r="E16" s="8">
-        <v>-2.9</v>
-      </c>
-    </row>
-    <row r="17" spans="1:5">
-      <c r="A17" s="5" t="s">
+      <c r="B50" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="C50" s="5">
+        <v>40.69</v>
+      </c>
+      <c r="D50" s="5">
+        <v>46.79</v>
+      </c>
+      <c r="E50" s="6">
+        <v>6.1</v>
+      </c>
+    </row>
+    <row r="51" spans="1:5">
+      <c r="A51" s="3" t="s">
         <v>39</v>
       </c>
-      <c r="B17" s="5" t="s">
-        <v>8</v>
-      </c>
-      <c r="C17" s="6">
-        <v>-6.74</v>
-      </c>
-      <c r="D17" s="6">
-        <v>-6.18</v>
-      </c>
-      <c r="E17" s="7">
-        <v>0.5600000000000001</v>
-      </c>
-    </row>
-    <row r="18" spans="1:5">
-      <c r="A18" s="5" t="s">
+      <c r="B51" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="C51" s="5">
+        <v>28.27</v>
+      </c>
+      <c r="D51" s="5">
+        <v>29.53</v>
+      </c>
+      <c r="E51" s="6">
+        <v>1.26</v>
+      </c>
+    </row>
+    <row r="52" spans="1:5">
+      <c r="A52" s="3" t="s">
         <v>40</v>
       </c>
-      <c r="B18" s="5" t="s">
-        <v>8</v>
-      </c>
-      <c r="C18" s="6">
-        <v>-1.69</v>
-      </c>
-      <c r="D18" s="6">
-        <v>-1.11</v>
-      </c>
-      <c r="E18" s="7">
-        <v>0.58</v>
-      </c>
-    </row>
-    <row r="19" spans="1:5">
-      <c r="A19" s="5" t="s">
+      <c r="B52" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="C52" s="5">
+        <v>30.33</v>
+      </c>
+      <c r="D52" s="5">
+        <v>30.61</v>
+      </c>
+      <c r="E52" s="6">
+        <v>0.28</v>
+      </c>
+    </row>
+    <row r="53" spans="1:5">
+      <c r="A53" s="3" t="s">
         <v>41</v>
       </c>
-      <c r="B19" s="5" t="s">
-        <v>8</v>
-      </c>
-      <c r="C19" s="6">
-        <v>-2.3</v>
-      </c>
-      <c r="D19" s="6">
-        <v>-1.9</v>
-      </c>
-      <c r="E19" s="7">
-        <v>0.4</v>
-      </c>
-    </row>
-    <row r="20" spans="1:5">
-      <c r="A20" s="5" t="s">
+      <c r="B53" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="C53" s="5">
+        <v>42.89</v>
+      </c>
+      <c r="D53" s="5">
+        <v>40.28</v>
+      </c>
+      <c r="E53" s="7">
+        <v>-2.61</v>
+      </c>
+    </row>
+    <row r="54" spans="1:5">
+      <c r="A54" s="3" t="s">
         <v>42</v>
       </c>
-      <c r="B20" s="5" t="s">
-        <v>8</v>
-      </c>
-      <c r="C20" s="6">
-        <v>-3.43</v>
-      </c>
-      <c r="D20" s="6">
-        <v>-2.7</v>
-      </c>
-      <c r="E20" s="7">
-        <v>0.73</v>
-      </c>
-    </row>
-    <row r="21" spans="1:5">
-      <c r="A21" s="5" t="s">
+      <c r="B54" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="C54" s="5">
+        <v>38.77</v>
+      </c>
+      <c r="D54" s="5">
+        <v>37.52</v>
+      </c>
+      <c r="E54" s="7">
+        <v>-1.25</v>
+      </c>
+    </row>
+    <row r="55" spans="1:5">
+      <c r="A55" s="3" t="s">
         <v>43</v>
       </c>
-      <c r="B21" s="5" t="s">
-        <v>8</v>
-      </c>
-      <c r="C21" s="6">
-        <v>11.21</v>
-      </c>
-      <c r="D21" s="6">
-        <v>9.07</v>
-      </c>
-      <c r="E21" s="8">
-        <v>-2.14</v>
-      </c>
-    </row>
-    <row r="22" spans="1:5">
-      <c r="A22" s="5" t="s">
+      <c r="B55" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="C55" s="5">
+        <v>76.90000000000001</v>
+      </c>
+      <c r="D55" s="5">
+        <v>76.01000000000001</v>
+      </c>
+      <c r="E55" s="7">
+        <v>-0.89</v>
+      </c>
+    </row>
+    <row r="56" spans="1:5">
+      <c r="A56" s="3" t="s">
         <v>37</v>
       </c>
-      <c r="B22" s="5" t="s">
-        <v>11</v>
-      </c>
-      <c r="C22" s="6">
-        <v>17.06</v>
-      </c>
-      <c r="D22" s="6">
-        <v>16.61</v>
-      </c>
-      <c r="E22" s="8">
-        <v>-0.45</v>
-      </c>
-    </row>
-    <row r="23" spans="1:5">
-      <c r="A23" s="5" t="s">
+      <c r="B56" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="C56" s="5">
+        <v>29.94</v>
+      </c>
+      <c r="D56" s="5">
+        <v>-41.85</v>
+      </c>
+      <c r="E56" s="7">
+        <v>-71.79000000000001</v>
+      </c>
+    </row>
+    <row r="57" spans="1:5">
+      <c r="A57" s="3" t="s">
         <v>38</v>
       </c>
-      <c r="B23" s="5" t="s">
-        <v>11</v>
-      </c>
-      <c r="C23" s="6">
-        <v>113.43</v>
-      </c>
-      <c r="D23" s="6">
-        <v>104.06</v>
-      </c>
-      <c r="E23" s="8">
-        <v>-9.369999999999999</v>
-      </c>
-    </row>
-    <row r="24" spans="1:5">
-      <c r="A24" s="5" t="s">
+      <c r="B57" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="C57" s="5">
+        <v>-55.41</v>
+      </c>
+      <c r="D57" s="5">
+        <v>-60.5</v>
+      </c>
+      <c r="E57" s="7">
+        <v>-5.09</v>
+      </c>
+    </row>
+    <row r="58" spans="1:5">
+      <c r="A58" s="3" t="s">
         <v>39</v>
       </c>
-      <c r="B24" s="5" t="s">
-        <v>11</v>
-      </c>
-      <c r="C24" s="6">
-        <v>-44.82</v>
-      </c>
-      <c r="D24" s="6">
-        <v>-46.08</v>
-      </c>
-      <c r="E24" s="8">
-        <v>-1.26</v>
-      </c>
-    </row>
-    <row r="25" spans="1:5">
-      <c r="A25" s="5" t="s">
+      <c r="B58" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="C58" s="5">
+        <v>-23.9</v>
+      </c>
+      <c r="D58" s="5">
+        <v>-13.15</v>
+      </c>
+      <c r="E58" s="6">
+        <v>10.75</v>
+      </c>
+    </row>
+    <row r="59" spans="1:5">
+      <c r="A59" s="3" t="s">
         <v>40</v>
       </c>
-      <c r="B25" s="5" t="s">
-        <v>11</v>
-      </c>
-      <c r="C25" s="6">
-        <v>-13.51</v>
-      </c>
-      <c r="D25" s="6">
-        <v>-13.5</v>
-      </c>
-      <c r="E25" s="7">
-        <v>0.01</v>
-      </c>
-    </row>
-    <row r="26" spans="1:5">
-      <c r="A26" s="5" t="s">
+      <c r="B59" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="C59" s="5">
+        <v>38.9</v>
+      </c>
+      <c r="D59" s="5">
+        <v>-30.16</v>
+      </c>
+      <c r="E59" s="7">
+        <v>-69.06</v>
+      </c>
+    </row>
+    <row r="60" spans="1:5">
+      <c r="A60" s="3" t="s">
         <v>41</v>
       </c>
-      <c r="B26" s="5" t="s">
-        <v>11</v>
-      </c>
-      <c r="C26" s="6">
-        <v>-16</v>
-      </c>
-      <c r="D26" s="6">
-        <v>-13.88</v>
-      </c>
-      <c r="E26" s="7">
-        <v>2.12</v>
-      </c>
-    </row>
-    <row r="27" spans="1:5">
-      <c r="A27" s="5" t="s">
+      <c r="B60" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="C60" s="5">
+        <v>14.58</v>
+      </c>
+      <c r="D60" s="5">
+        <v>-10.62</v>
+      </c>
+      <c r="E60" s="7">
+        <v>-25.2</v>
+      </c>
+    </row>
+    <row r="61" spans="1:5">
+      <c r="A61" s="3" t="s">
         <v>42</v>
       </c>
-      <c r="B27" s="5" t="s">
-        <v>11</v>
-      </c>
-      <c r="C27" s="6">
-        <v>-3.74</v>
-      </c>
-      <c r="D27" s="6">
-        <v>-2.11</v>
-      </c>
-      <c r="E27" s="7">
-        <v>1.63</v>
-      </c>
-    </row>
-    <row r="28" spans="1:5">
-      <c r="A28" s="5" t="s">
+      <c r="B61" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="C61" s="5">
+        <v>101.19</v>
+      </c>
+      <c r="D61" s="5">
+        <v>-33.75</v>
+      </c>
+      <c r="E61" s="7">
+        <v>-134.94</v>
+      </c>
+    </row>
+    <row r="62" spans="1:5">
+      <c r="A62" s="3" t="s">
         <v>43</v>
       </c>
-      <c r="B28" s="5" t="s">
-        <v>11</v>
-      </c>
-      <c r="C28" s="6">
-        <v>33.75</v>
-      </c>
-      <c r="D28" s="6">
-        <v>40.27</v>
-      </c>
-      <c r="E28" s="7">
-        <v>6.52</v>
-      </c>
-    </row>
-    <row r="29" spans="1:5">
-      <c r="A29" s="5" t="s">
-        <v>37</v>
-      </c>
-      <c r="B29" s="5" t="s">
-        <v>10</v>
-      </c>
-      <c r="C29" s="6">
-        <v>2.65</v>
-      </c>
-      <c r="D29" s="6">
-        <v>-0.12</v>
-      </c>
-      <c r="E29" s="8">
-        <v>-2.77</v>
-      </c>
-    </row>
-    <row r="30" spans="1:5">
-      <c r="A30" s="5" t="s">
-        <v>38</v>
-      </c>
-      <c r="B30" s="5" t="s">
-        <v>10</v>
-      </c>
-      <c r="C30" s="6">
-        <v>-19.34</v>
-      </c>
-      <c r="D30" s="6">
-        <v>-22.49</v>
-      </c>
-      <c r="E30" s="8">
-        <v>-3.15</v>
-      </c>
-    </row>
-    <row r="31" spans="1:5">
-      <c r="A31" s="5" t="s">
-        <v>39</v>
-      </c>
-      <c r="B31" s="5" t="s">
-        <v>10</v>
-      </c>
-      <c r="C31" s="6">
-        <v>-8.859999999999999</v>
-      </c>
-      <c r="D31" s="6">
-        <v>-8.210000000000001</v>
-      </c>
-      <c r="E31" s="7">
-        <v>0.65</v>
-      </c>
-    </row>
-    <row r="32" spans="1:5">
-      <c r="A32" s="5" t="s">
-        <v>40</v>
-      </c>
-      <c r="B32" s="5" t="s">
-        <v>10</v>
-      </c>
-      <c r="C32" s="6">
-        <v>-8.6</v>
-      </c>
-      <c r="D32" s="6">
-        <v>-6.38</v>
-      </c>
-      <c r="E32" s="7">
-        <v>2.22</v>
-      </c>
-    </row>
-    <row r="33" spans="1:5">
-      <c r="A33" s="5" t="s">
-        <v>41</v>
-      </c>
-      <c r="B33" s="5" t="s">
-        <v>10</v>
-      </c>
-      <c r="C33" s="6">
-        <v>-3.73</v>
-      </c>
-      <c r="D33" s="6">
-        <v>-0.8</v>
-      </c>
-      <c r="E33" s="7">
-        <v>2.93</v>
-      </c>
-    </row>
-    <row r="34" spans="1:5">
-      <c r="A34" s="5" t="s">
-        <v>42</v>
-      </c>
-      <c r="B34" s="5" t="s">
-        <v>10</v>
-      </c>
-      <c r="C34" s="6">
-        <v>-8.06</v>
-      </c>
-      <c r="D34" s="6">
-        <v>-5.74</v>
-      </c>
-      <c r="E34" s="7">
-        <v>2.32</v>
-      </c>
-    </row>
-    <row r="35" spans="1:5">
-      <c r="A35" s="5" t="s">
-        <v>43</v>
-      </c>
-      <c r="B35" s="5" t="s">
-        <v>10</v>
-      </c>
-      <c r="C35" s="6">
-        <v>29.83</v>
-      </c>
-      <c r="D35" s="6">
-        <v>37.03</v>
-      </c>
-      <c r="E35" s="7">
-        <v>7.2</v>
-      </c>
-    </row>
-    <row r="36" spans="1:5">
-      <c r="A36" s="5" t="s">
-        <v>37</v>
-      </c>
-      <c r="B36" s="5" t="s">
-        <v>6</v>
-      </c>
-      <c r="C36" s="6">
-        <v>-18.74</v>
-      </c>
-      <c r="D36" s="6">
-        <v>-18.91</v>
-      </c>
-      <c r="E36" s="8">
-        <v>-0.17</v>
-      </c>
-    </row>
-    <row r="37" spans="1:5">
-      <c r="A37" s="5" t="s">
-        <v>38</v>
-      </c>
-      <c r="B37" s="5" t="s">
-        <v>6</v>
-      </c>
-      <c r="C37" s="6">
-        <v>-25.84</v>
-      </c>
-      <c r="D37" s="6">
-        <v>-28.33</v>
-      </c>
-      <c r="E37" s="8">
-        <v>-2.49</v>
-      </c>
-    </row>
-    <row r="38" spans="1:5">
-      <c r="A38" s="5" t="s">
-        <v>39</v>
-      </c>
-      <c r="B38" s="5" t="s">
-        <v>6</v>
-      </c>
-      <c r="C38" s="6">
-        <v>-45.98</v>
-      </c>
-      <c r="D38" s="6">
-        <v>-45.39</v>
-      </c>
-      <c r="E38" s="7">
-        <v>0.59</v>
-      </c>
-    </row>
-    <row r="39" spans="1:5">
-      <c r="A39" s="5" t="s">
-        <v>40</v>
-      </c>
-      <c r="B39" s="5" t="s">
-        <v>6</v>
-      </c>
-      <c r="C39" s="6">
-        <v>-20.4</v>
-      </c>
-      <c r="D39" s="6">
-        <v>-19.54</v>
-      </c>
-      <c r="E39" s="7">
-        <v>0.86</v>
-      </c>
-    </row>
-    <row r="40" spans="1:5">
-      <c r="A40" s="5" t="s">
-        <v>41</v>
-      </c>
-      <c r="B40" s="5" t="s">
-        <v>6</v>
-      </c>
-      <c r="C40" s="6">
-        <v>-18.85</v>
-      </c>
-      <c r="D40" s="6">
-        <v>-18.35</v>
-      </c>
-      <c r="E40" s="7">
-        <v>0.5</v>
-      </c>
-    </row>
-    <row r="41" spans="1:5">
-      <c r="A41" s="5" t="s">
-        <v>42</v>
-      </c>
-      <c r="B41" s="5" t="s">
-        <v>6</v>
-      </c>
-      <c r="C41" s="6">
-        <v>-18.17</v>
-      </c>
-      <c r="D41" s="6">
-        <v>-16.29</v>
-      </c>
-      <c r="E41" s="7">
-        <v>1.88</v>
-      </c>
-    </row>
-    <row r="42" spans="1:5">
-      <c r="A42" s="5" t="s">
-        <v>43</v>
-      </c>
-      <c r="B42" s="5" t="s">
-        <v>6</v>
-      </c>
-      <c r="C42" s="6">
-        <v>-4.15</v>
-      </c>
-      <c r="D42" s="6">
-        <v>0</v>
-      </c>
-      <c r="E42" s="7">
-        <v>4.15</v>
-      </c>
-    </row>
-    <row r="43" spans="1:5">
-      <c r="A43" s="5" t="s">
-        <v>37</v>
-      </c>
-      <c r="B43" s="5" t="s">
-        <v>2</v>
-      </c>
-      <c r="C43" s="6">
-        <v>10045</v>
-      </c>
-      <c r="D43" s="6">
-        <v>10024</v>
-      </c>
-      <c r="E43" s="8">
-        <v>-21</v>
-      </c>
-    </row>
-    <row r="44" spans="1:5">
-      <c r="A44" s="5" t="s">
-        <v>38</v>
-      </c>
-      <c r="B44" s="5" t="s">
-        <v>2</v>
-      </c>
-      <c r="C44" s="6">
-        <v>497.05</v>
-      </c>
-      <c r="D44" s="6">
-        <v>480.35</v>
-      </c>
-      <c r="E44" s="8">
-        <v>-16.7</v>
-      </c>
-    </row>
-    <row r="45" spans="1:5">
-      <c r="A45" s="5" t="s">
-        <v>39</v>
-      </c>
-      <c r="B45" s="5" t="s">
-        <v>2</v>
-      </c>
-      <c r="C45" s="6">
-        <v>299.8</v>
-      </c>
-      <c r="D45" s="6">
-        <v>299.25</v>
-      </c>
-      <c r="E45" s="8">
-        <v>-0.55</v>
-      </c>
-    </row>
-    <row r="46" spans="1:5">
-      <c r="A46" s="5" t="s">
-        <v>40</v>
-      </c>
-      <c r="B46" s="5" t="s">
-        <v>2</v>
-      </c>
-      <c r="C46" s="6">
-        <v>1732.6</v>
-      </c>
-      <c r="D46" s="6">
-        <v>1751.4</v>
-      </c>
-      <c r="E46" s="7">
-        <v>18.8</v>
-      </c>
-    </row>
-    <row r="47" spans="1:5">
-      <c r="A47" s="5" t="s">
-        <v>41</v>
-      </c>
-      <c r="B47" s="5" t="s">
-        <v>2</v>
-      </c>
-      <c r="C47" s="6">
-        <v>10666</v>
-      </c>
-      <c r="D47" s="6">
-        <v>10732</v>
-      </c>
-      <c r="E47" s="7">
-        <v>66</v>
-      </c>
-    </row>
-    <row r="48" spans="1:5">
-      <c r="A48" s="5" t="s">
-        <v>42</v>
-      </c>
-      <c r="B48" s="5" t="s">
-        <v>2</v>
-      </c>
-      <c r="C48" s="6">
-        <v>948.3</v>
-      </c>
-      <c r="D48" s="6">
-        <v>970</v>
-      </c>
-      <c r="E48" s="7">
-        <v>21.7</v>
-      </c>
-    </row>
-    <row r="49" spans="1:5">
-      <c r="A49" s="5" t="s">
-        <v>43</v>
-      </c>
-      <c r="B49" s="5" t="s">
-        <v>2</v>
-      </c>
-      <c r="C49" s="6">
-        <v>172.66</v>
-      </c>
-      <c r="D49" s="6">
-        <v>182.2</v>
-      </c>
-      <c r="E49" s="7">
-        <v>9.539999999999999</v>
-      </c>
-    </row>
-    <row r="50" spans="1:5">
-      <c r="A50" s="5" t="s">
-        <v>38</v>
-      </c>
-      <c r="B50" s="5" t="s">
-        <v>13</v>
-      </c>
-      <c r="C50" s="6">
-        <v>99</v>
-      </c>
-      <c r="D50" s="6">
-        <v>85</v>
-      </c>
-      <c r="E50" s="8">
-        <v>-14</v>
-      </c>
-    </row>
-    <row r="51" spans="1:5">
-      <c r="A51" s="5" t="s">
-        <v>43</v>
-      </c>
-      <c r="B51" s="5" t="s">
-        <v>13</v>
-      </c>
-      <c r="C51" s="6">
-        <v>85</v>
-      </c>
-      <c r="D51" s="6">
-        <v>99</v>
-      </c>
-      <c r="E51" s="7">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="52" spans="1:5">
-      <c r="A52" s="5" t="s">
-        <v>37</v>
-      </c>
-      <c r="B52" s="5" t="s">
-        <v>24</v>
-      </c>
-      <c r="C52" s="6">
-        <v>21.8</v>
-      </c>
-      <c r="D52" s="6">
-        <v>21.6</v>
-      </c>
-      <c r="E52" s="8">
-        <v>-0.2</v>
-      </c>
-    </row>
-    <row r="53" spans="1:5">
-      <c r="A53" s="5" t="s">
-        <v>38</v>
-      </c>
-      <c r="B53" s="5" t="s">
-        <v>24</v>
-      </c>
-      <c r="C53" s="6">
-        <v>47.06</v>
-      </c>
-      <c r="D53" s="6">
-        <v>40.69</v>
-      </c>
-      <c r="E53" s="8">
-        <v>-6.37</v>
-      </c>
-    </row>
-    <row r="54" spans="1:5">
-      <c r="A54" s="5" t="s">
-        <v>39</v>
-      </c>
-      <c r="B54" s="5" t="s">
-        <v>24</v>
-      </c>
-      <c r="C54" s="6">
-        <v>28.53</v>
-      </c>
-      <c r="D54" s="6">
-        <v>28.27</v>
-      </c>
-      <c r="E54" s="8">
-        <v>-0.26</v>
-      </c>
-    </row>
-    <row r="55" spans="1:5">
-      <c r="A55" s="5" t="s">
-        <v>40</v>
-      </c>
-      <c r="B55" s="5" t="s">
-        <v>24</v>
-      </c>
-      <c r="C55" s="6">
-        <v>25.11</v>
-      </c>
-      <c r="D55" s="6">
-        <v>30.33</v>
-      </c>
-      <c r="E55" s="7">
-        <v>5.22</v>
-      </c>
-    </row>
-    <row r="56" spans="1:5">
-      <c r="A56" s="5" t="s">
-        <v>41</v>
-      </c>
-      <c r="B56" s="5" t="s">
-        <v>24</v>
-      </c>
-      <c r="C56" s="6">
-        <v>41.12</v>
-      </c>
-      <c r="D56" s="6">
-        <v>42.89</v>
-      </c>
-      <c r="E56" s="7">
-        <v>1.77</v>
-      </c>
-    </row>
-    <row r="57" spans="1:5">
-      <c r="A57" s="5" t="s">
-        <v>42</v>
-      </c>
-      <c r="B57" s="5" t="s">
-        <v>24</v>
-      </c>
-      <c r="C57" s="6">
-        <v>32.16</v>
-      </c>
-      <c r="D57" s="6">
-        <v>38.77</v>
-      </c>
-      <c r="E57" s="7">
-        <v>6.61</v>
-      </c>
-    </row>
-    <row r="58" spans="1:5">
-      <c r="A58" s="5" t="s">
-        <v>43</v>
-      </c>
-      <c r="B58" s="5" t="s">
-        <v>24</v>
-      </c>
-      <c r="C58" s="6">
-        <v>72.51000000000001</v>
-      </c>
-      <c r="D58" s="6">
-        <v>76.90000000000001</v>
-      </c>
-      <c r="E58" s="7">
-        <v>4.39</v>
-      </c>
-    </row>
-    <row r="59" spans="1:5">
-      <c r="A59" s="5" t="s">
-        <v>37</v>
-      </c>
-      <c r="B59" s="5" t="s">
+      <c r="B62" s="3" t="s">
         <v>31</v>
       </c>
-      <c r="C59" s="6">
-        <v>562.46</v>
-      </c>
-      <c r="D59" s="6">
-        <v>29.94</v>
-      </c>
-      <c r="E59" s="8">
-        <v>-532.52</v>
-      </c>
-    </row>
-    <row r="60" spans="1:5">
-      <c r="A60" s="5" t="s">
-        <v>38</v>
-      </c>
-      <c r="B60" s="5" t="s">
-        <v>31</v>
-      </c>
-      <c r="C60" s="6">
-        <v>-39.15</v>
-      </c>
-      <c r="D60" s="6">
-        <v>-55.41</v>
-      </c>
-      <c r="E60" s="8">
-        <v>-16.26</v>
-      </c>
-    </row>
-    <row r="61" spans="1:5">
-      <c r="A61" s="5" t="s">
-        <v>39</v>
-      </c>
-      <c r="B61" s="5" t="s">
-        <v>31</v>
-      </c>
-      <c r="C61" s="6">
-        <v>-12.05</v>
-      </c>
-      <c r="D61" s="6">
-        <v>-23.9</v>
-      </c>
-      <c r="E61" s="8">
-        <v>-11.85</v>
-      </c>
-    </row>
-    <row r="62" spans="1:5">
-      <c r="A62" s="5" t="s">
-        <v>40</v>
-      </c>
-      <c r="B62" s="5" t="s">
-        <v>31</v>
-      </c>
-      <c r="C62" s="6">
-        <v>226.11</v>
-      </c>
-      <c r="D62" s="6">
-        <v>38.9</v>
-      </c>
-      <c r="E62" s="8">
-        <v>-187.21</v>
-      </c>
-    </row>
-    <row r="63" spans="1:5">
-      <c r="A63" s="5" t="s">
-        <v>41</v>
-      </c>
-      <c r="B63" s="5" t="s">
-        <v>31</v>
-      </c>
-      <c r="C63" s="6">
-        <v>-9.199999999999999</v>
-      </c>
-      <c r="D63" s="6">
-        <v>14.58</v>
-      </c>
-      <c r="E63" s="7">
-        <v>23.78</v>
-      </c>
-    </row>
-    <row r="64" spans="1:5">
-      <c r="A64" s="5" t="s">
-        <v>42</v>
-      </c>
-      <c r="B64" s="5" t="s">
-        <v>31</v>
-      </c>
-      <c r="C64" s="6">
-        <v>-9.74</v>
-      </c>
-      <c r="D64" s="6">
-        <v>101.19</v>
-      </c>
-      <c r="E64" s="7">
-        <v>110.93</v>
-      </c>
-    </row>
-    <row r="65" spans="1:5">
-      <c r="A65" s="5" t="s">
-        <v>43</v>
-      </c>
-      <c r="B65" s="5" t="s">
-        <v>31</v>
-      </c>
-      <c r="C65" s="6">
-        <v>80.64</v>
-      </c>
-      <c r="D65" s="6">
+      <c r="C62" s="5">
         <v>283.43</v>
       </c>
-      <c r="E65" s="7">
-        <v>202.79</v>
+      <c r="D62" s="5">
+        <v>-21.31</v>
+      </c>
+      <c r="E62" s="7">
+        <v>-304.74</v>
       </c>
     </row>
   </sheetData>
   <mergeCells count="2">
     <mergeCell ref="A1:F1"/>
-    <mergeCell ref="A6:E6"/>
+    <mergeCell ref="A5:E5"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -2973,60 +2841,60 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:9" ht="28" customHeight="1">
-      <c r="A1" s="9" t="s">
+      <c r="A1" s="8" t="s">
         <v>1</v>
       </c>
-      <c r="B1" s="9" t="s">
-        <v>70</v>
-      </c>
-      <c r="C1" s="9" t="s">
-        <v>71</v>
-      </c>
-      <c r="D1" s="9" t="s">
-        <v>72</v>
-      </c>
-      <c r="E1" s="9" t="s">
-        <v>73</v>
-      </c>
-      <c r="F1" s="9" t="s">
-        <v>74</v>
-      </c>
-      <c r="G1" s="9" t="s">
-        <v>75</v>
-      </c>
-      <c r="H1" s="9" t="s">
-        <v>76</v>
-      </c>
-      <c r="I1" s="9" t="s">
-        <v>77</v>
+      <c r="B1" s="8" t="s">
+        <v>56</v>
+      </c>
+      <c r="C1" s="8" t="s">
+        <v>57</v>
+      </c>
+      <c r="D1" s="8" t="s">
+        <v>58</v>
+      </c>
+      <c r="E1" s="8" t="s">
+        <v>59</v>
+      </c>
+      <c r="F1" s="8" t="s">
+        <v>60</v>
+      </c>
+      <c r="G1" s="8" t="s">
+        <v>61</v>
+      </c>
+      <c r="H1" s="8" t="s">
+        <v>62</v>
+      </c>
+      <c r="I1" s="8" t="s">
+        <v>63</v>
       </c>
     </row>
     <row r="2" spans="1:9">
-      <c r="A2" s="10" t="s">
+      <c r="A2" s="9" t="s">
         <v>44</v>
       </c>
-      <c r="B2" s="11">
-        <v>48.8</v>
-      </c>
-      <c r="C2" s="12">
+      <c r="B2" s="10">
+        <v>44.8</v>
+      </c>
+      <c r="C2" s="11">
         <v>7</v>
       </c>
-      <c r="D2" s="11">
-        <v>39.9</v>
-      </c>
-      <c r="E2" s="11">
-        <v>40</v>
-      </c>
-      <c r="F2" s="11">
-        <v>-1.9</v>
-      </c>
-      <c r="G2" s="11">
-        <v>-1</v>
-      </c>
-      <c r="H2" s="11">
+      <c r="D2" s="10">
+        <v>40.3</v>
+      </c>
+      <c r="E2" s="10">
+        <v>30</v>
+      </c>
+      <c r="F2" s="10">
+        <v>-2.6</v>
+      </c>
+      <c r="G2" s="10">
+        <v>-1.2</v>
+      </c>
+      <c r="H2" s="10">
         <v>57</v>
       </c>
-      <c r="I2" s="11">
+      <c r="I2" s="10">
         <v>10</v>
       </c>
     </row>
@@ -3128,49 +2996,49 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:7">
-      <c r="A1" s="13" t="s">
+      <c r="A1" s="12" t="s">
         <v>37</v>
       </c>
-      <c r="B1" s="13" t="s">
+      <c r="B1" s="12" t="s">
         <v>41</v>
       </c>
-      <c r="C1" s="13" t="s">
+      <c r="C1" s="12" t="s">
         <v>38</v>
       </c>
-      <c r="D1" s="13" t="s">
+      <c r="D1" s="12" t="s">
+        <v>43</v>
+      </c>
+      <c r="E1" s="12" t="s">
         <v>42</v>
       </c>
-      <c r="E1" s="13" t="s">
-        <v>43</v>
-      </c>
-      <c r="F1" s="13" t="s">
+      <c r="F1" s="12" t="s">
         <v>40</v>
       </c>
-      <c r="G1" s="13" t="s">
+      <c r="G1" s="12" t="s">
         <v>39</v>
       </c>
     </row>
     <row r="2" spans="1:7">
-      <c r="A2" s="14">
-        <v>0.238</v>
-      </c>
-      <c r="B2" s="14">
-        <v>0.1856</v>
-      </c>
-      <c r="C2" s="14">
-        <v>0.1542</v>
-      </c>
-      <c r="D2" s="14">
-        <v>0.0506</v>
-      </c>
-      <c r="E2" s="14">
-        <v>0.04559999999999999</v>
-      </c>
-      <c r="F2" s="14">
-        <v>-0.0034</v>
-      </c>
-      <c r="G2" s="14">
-        <v>-0.2415</v>
+      <c r="A2" s="13">
+        <v>0.2439</v>
+      </c>
+      <c r="B2" s="13">
+        <v>0.186</v>
+      </c>
+      <c r="C2" s="13">
+        <v>0.1615</v>
+      </c>
+      <c r="D2" s="13">
+        <v>0.0496</v>
+      </c>
+      <c r="E2" s="13">
+        <v>0.0488</v>
+      </c>
+      <c r="F2" s="13">
+        <v>-0.0007000000000000001</v>
+      </c>
+      <c r="G2" s="13">
+        <v>-0.2384</v>
       </c>
     </row>
   </sheetData>

--- a/BAJAJ_GROUP_Technical_Metrics.xlsx
+++ b/BAJAJ_GROUP_Technical_Metrics.xlsx
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="253" uniqueCount="64">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="268" uniqueCount="73">
   <si>
     <t>Symbol</t>
   </si>
@@ -172,7 +172,34 @@
     <t>▶  SIGNAL EVENTS (vs Previous Run)</t>
   </si>
   <si>
-    <t>No signal events detected since last run.</t>
+    <t>Signal</t>
+  </si>
+  <si>
+    <t>Change</t>
+  </si>
+  <si>
+    <t>Direction</t>
+  </si>
+  <si>
+    <t>Prev Value</t>
+  </si>
+  <si>
+    <t>Curr Value</t>
+  </si>
+  <si>
+    <t>RSI Oversold Recovery</t>
+  </si>
+  <si>
+    <t>29.5 → 30.1</t>
+  </si>
+  <si>
+    <t>🟢 BULLISH</t>
+  </si>
+  <si>
+    <t>29.5</t>
+  </si>
+  <si>
+    <t>30.1</t>
   </si>
   <si>
     <t>▶  NUMERIC METRIC CHANGES (vs Previous Run)</t>
@@ -374,17 +401,18 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="14">
+  <cellXfs count="15">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="2" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="3" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
+    <xf numFmtId="0" fontId="4" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1"/>
+    <xf numFmtId="165" fontId="5" fillId="6" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="165" fontId="4" fillId="5" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="165" fontId="5" fillId="6" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="3" fillId="7" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
@@ -896,58 +924,58 @@
         <v>44</v>
       </c>
       <c r="C2">
-        <v>10017</v>
+        <v>9884</v>
       </c>
       <c r="D2">
-        <v>-0.07000000000000001</v>
+        <v>-1.33</v>
       </c>
       <c r="E2">
         <v>12361</v>
       </c>
       <c r="F2">
-        <v>8506.780000000001</v>
+        <v>8559.049999999999</v>
       </c>
       <c r="G2">
-        <v>-18.96</v>
+        <v>-20.04</v>
       </c>
       <c r="H2">
-        <v>17.75</v>
+        <v>15.48</v>
       </c>
       <c r="I2">
-        <v>-9.130000000000001</v>
+        <v>-8.57</v>
       </c>
       <c r="J2">
-        <v>-15.96</v>
+        <v>-17.07</v>
       </c>
       <c r="K2">
-        <v>-0.91</v>
+        <v>-2.75</v>
       </c>
       <c r="L2">
-        <v>17.05</v>
+        <v>16.19</v>
       </c>
       <c r="M2">
-        <v>24.39</v>
+        <v>23.68</v>
       </c>
       <c r="N2">
         <v>71</v>
       </c>
       <c r="O2">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="P2">
-        <v>10354.2</v>
+        <v>10168.8</v>
       </c>
       <c r="Q2">
-        <v>11217.7</v>
+        <v>11121.9</v>
       </c>
       <c r="R2">
-        <v>11523.62</v>
+        <v>11497.63</v>
       </c>
       <c r="S2">
-        <v>10151.7</v>
+        <v>10157.26</v>
       </c>
       <c r="T2">
-        <v>-1.33</v>
+        <v>-2.69</v>
       </c>
       <c r="U2" t="s">
         <v>45</v>
@@ -962,43 +990,43 @@
         <v>1</v>
       </c>
       <c r="Y2">
-        <v>21.53</v>
+        <v>20.18</v>
       </c>
       <c r="Z2">
-        <v>-368.47</v>
+        <v>-411.42</v>
       </c>
       <c r="AA2">
-        <v>-198.08</v>
+        <v>-240.75</v>
       </c>
       <c r="AB2">
-        <v>-170.39</v>
+        <v>-170.68</v>
       </c>
       <c r="AC2">
         <v>0</v>
       </c>
       <c r="AD2">
-        <v>2.62</v>
+        <v>1.31</v>
       </c>
       <c r="AE2">
-        <v>241.71</v>
+        <v>245.16</v>
       </c>
       <c r="AF2">
-        <v>-41.85</v>
+        <v>65.89</v>
       </c>
       <c r="AG2">
-        <v>12396.6</v>
+        <v>12408.08</v>
       </c>
       <c r="AH2">
-        <v>10038.8</v>
+        <v>9835.719999999999</v>
       </c>
       <c r="AI2">
-        <v>10733.63</v>
+        <v>10597.47</v>
       </c>
       <c r="AJ2" t="s">
         <v>47</v>
       </c>
       <c r="AK2">
-        <v>71.84999999999999</v>
+        <v>74.98999999999999</v>
       </c>
     </row>
     <row r="3" spans="1:37">
@@ -1009,37 +1037,37 @@
         <v>44</v>
       </c>
       <c r="C3">
-        <v>493.5</v>
+        <v>483</v>
       </c>
       <c r="D3">
-        <v>2.74</v>
+        <v>-2.13</v>
       </c>
       <c r="E3">
         <v>670.25</v>
       </c>
       <c r="F3">
-        <v>236.06</v>
+        <v>239.33</v>
       </c>
       <c r="G3">
-        <v>-26.37</v>
+        <v>-27.94</v>
       </c>
       <c r="H3">
-        <v>109.06</v>
+        <v>101.81</v>
       </c>
       <c r="I3">
-        <v>2.8</v>
+        <v>-2.03</v>
       </c>
       <c r="J3">
-        <v>-3.04</v>
+        <v>-6.68</v>
       </c>
       <c r="K3">
-        <v>-20.44</v>
+        <v>-21.32</v>
       </c>
       <c r="L3">
-        <v>108.32</v>
+        <v>104.61</v>
       </c>
       <c r="M3">
-        <v>16.15</v>
+        <v>15.75</v>
       </c>
       <c r="N3">
         <v>85</v>
@@ -1048,19 +1076,19 @@
         <v>89</v>
       </c>
       <c r="P3">
-        <v>491.89</v>
+        <v>489.89</v>
       </c>
       <c r="Q3">
-        <v>504.93</v>
+        <v>502.78</v>
       </c>
       <c r="R3">
-        <v>505.81</v>
+        <v>504.65</v>
       </c>
       <c r="S3">
-        <v>454.44</v>
+        <v>455.59</v>
       </c>
       <c r="T3">
-        <v>8.6</v>
+        <v>6.02</v>
       </c>
       <c r="U3" t="s">
         <v>45</v>
@@ -1075,34 +1103,34 @@
         <v>2</v>
       </c>
       <c r="Y3">
-        <v>46.79</v>
+        <v>42.99</v>
       </c>
       <c r="Z3">
-        <v>-4.73</v>
+        <v>-5.41</v>
       </c>
       <c r="AA3">
-        <v>-3.47</v>
+        <v>-3.86</v>
       </c>
       <c r="AB3">
-        <v>-1.25</v>
+        <v>-1.55</v>
       </c>
       <c r="AC3">
-        <v>39.88</v>
+        <v>31.9</v>
       </c>
       <c r="AD3">
-        <v>39.85</v>
+        <v>35.82</v>
       </c>
       <c r="AE3">
-        <v>18.82</v>
+        <v>18.36</v>
       </c>
       <c r="AF3">
-        <v>-60.5</v>
+        <v>-70.94</v>
       </c>
       <c r="AG3">
-        <v>531.7</v>
+        <v>529.33</v>
       </c>
       <c r="AH3">
-        <v>478.16</v>
+        <v>476.23</v>
       </c>
       <c r="AI3">
         <v>460.99</v>
@@ -1111,7 +1139,7 @@
         <v>48</v>
       </c>
       <c r="AK3">
-        <v>34.8</v>
+        <v>37.5</v>
       </c>
     </row>
     <row r="4" spans="1:37">
@@ -1122,10 +1150,10 @@
         <v>44</v>
       </c>
       <c r="C4">
-        <v>300.25</v>
+        <v>300.7</v>
       </c>
       <c r="D4">
-        <v>0.33</v>
+        <v>0.15</v>
       </c>
       <c r="E4">
         <v>548</v>
@@ -1134,46 +1162,46 @@
         <v>299.25</v>
       </c>
       <c r="G4">
-        <v>-45.21</v>
+        <v>-45.13</v>
       </c>
       <c r="H4">
-        <v>0.33</v>
+        <v>0.48</v>
       </c>
       <c r="I4">
-        <v>-4.58</v>
+        <v>-2.95</v>
       </c>
       <c r="J4">
-        <v>-10.16</v>
+        <v>-9.199999999999999</v>
       </c>
       <c r="K4">
-        <v>-9.210000000000001</v>
+        <v>-6.31</v>
       </c>
       <c r="L4">
-        <v>-44.91</v>
+        <v>-45.11</v>
       </c>
       <c r="M4">
-        <v>-23.84</v>
+        <v>-23.7</v>
       </c>
       <c r="N4">
         <v>15</v>
       </c>
       <c r="O4">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="P4">
-        <v>302.51</v>
+        <v>300.68</v>
       </c>
       <c r="Q4">
-        <v>322.03</v>
+        <v>319.96</v>
       </c>
       <c r="R4">
-        <v>335.79</v>
+        <v>335.22</v>
       </c>
       <c r="S4">
-        <v>366.24</v>
+        <v>365.35</v>
       </c>
       <c r="T4">
-        <v>-18.02</v>
+        <v>-17.69</v>
       </c>
       <c r="U4" t="s">
         <v>45</v>
@@ -1188,43 +1216,43 @@
         <v>0</v>
       </c>
       <c r="Y4">
-        <v>29.53</v>
+        <v>30.13</v>
       </c>
       <c r="Z4">
-        <v>-9.65</v>
+        <v>-9.82</v>
       </c>
       <c r="AA4">
-        <v>-7.28</v>
+        <v>-7.79</v>
       </c>
       <c r="AB4">
-        <v>-2.38</v>
+        <v>-2.03</v>
       </c>
       <c r="AC4">
-        <v>2.35</v>
+        <v>5.81</v>
       </c>
       <c r="AD4">
-        <v>0.78</v>
+        <v>2.72</v>
       </c>
       <c r="AE4">
-        <v>9.41</v>
+        <v>9.130000000000001</v>
       </c>
       <c r="AF4">
-        <v>-13.15</v>
+        <v>-24.23</v>
       </c>
       <c r="AG4">
-        <v>349.7</v>
+        <v>347.5</v>
       </c>
       <c r="AH4">
-        <v>294.37</v>
+        <v>292.43</v>
       </c>
       <c r="AI4">
-        <v>330.22</v>
+        <v>327.68</v>
       </c>
       <c r="AJ4" t="s">
         <v>47</v>
       </c>
       <c r="AK4">
-        <v>39.93</v>
+        <v>43.64</v>
       </c>
     </row>
     <row r="5" spans="1:37">
@@ -1235,10 +1263,10 @@
         <v>44</v>
       </c>
       <c r="C5">
-        <v>1752.4</v>
+        <v>1743.3</v>
       </c>
       <c r="D5">
-        <v>0.06</v>
+        <v>-0.52</v>
       </c>
       <c r="E5">
         <v>2176.6</v>
@@ -1247,46 +1275,46 @@
         <v>1631.8</v>
       </c>
       <c r="G5">
-        <v>-19.49</v>
+        <v>-19.91</v>
       </c>
       <c r="H5">
-        <v>7.39</v>
+        <v>6.83</v>
       </c>
       <c r="I5">
-        <v>0.02</v>
+        <v>0.05</v>
       </c>
       <c r="J5">
-        <v>-12.03</v>
+        <v>-11.51</v>
       </c>
       <c r="K5">
-        <v>-7.05</v>
+        <v>-6.02</v>
       </c>
       <c r="L5">
-        <v>-12.66</v>
+        <v>-13.14</v>
       </c>
       <c r="M5">
-        <v>-0.07000000000000001</v>
+        <v>-0</v>
       </c>
       <c r="N5">
         <v>29</v>
       </c>
       <c r="O5">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="P5">
-        <v>1741.96</v>
+        <v>1742.14</v>
       </c>
       <c r="Q5">
-        <v>1828.84</v>
+        <v>1819.07</v>
       </c>
       <c r="R5">
-        <v>1936.4</v>
+        <v>1933.01</v>
       </c>
       <c r="S5">
-        <v>1881.67</v>
+        <v>1880.28</v>
       </c>
       <c r="T5">
-        <v>-6.87</v>
+        <v>-7.29</v>
       </c>
       <c r="U5" t="s">
         <v>45</v>
@@ -1301,34 +1329,34 @@
         <v>1</v>
       </c>
       <c r="Y5">
-        <v>30.61</v>
+        <v>29.46</v>
       </c>
       <c r="Z5">
-        <v>-57.82</v>
+        <v>-56.65</v>
       </c>
       <c r="AA5">
-        <v>-51.71</v>
+        <v>-52.7</v>
       </c>
       <c r="AB5">
-        <v>-6.12</v>
+        <v>-3.96</v>
       </c>
       <c r="AC5">
-        <v>37.98</v>
+        <v>52.02</v>
       </c>
       <c r="AD5">
-        <v>19.43</v>
+        <v>36.38</v>
       </c>
       <c r="AE5">
-        <v>35.16</v>
+        <v>34.83</v>
       </c>
       <c r="AF5">
-        <v>-30.16</v>
+        <v>24.35</v>
       </c>
       <c r="AG5">
-        <v>1979.71</v>
+        <v>1965.24</v>
       </c>
       <c r="AH5">
-        <v>1677.96</v>
+        <v>1672.9</v>
       </c>
       <c r="AI5">
         <v>1830.94</v>
@@ -1337,7 +1365,7 @@
         <v>47</v>
       </c>
       <c r="AK5">
-        <v>72.65000000000001</v>
+        <v>70.48999999999999</v>
       </c>
     </row>
     <row r="6" spans="1:37">
@@ -1348,10 +1376,10 @@
         <v>44</v>
       </c>
       <c r="C6">
-        <v>10600</v>
+        <v>10662</v>
       </c>
       <c r="D6">
-        <v>-1.23</v>
+        <v>0.58</v>
       </c>
       <c r="E6">
         <v>13144</v>
@@ -1360,46 +1388,46 @@
         <v>8746</v>
       </c>
       <c r="G6">
-        <v>-19.35</v>
+        <v>-18.88</v>
       </c>
       <c r="H6">
-        <v>21.2</v>
+        <v>21.91</v>
       </c>
       <c r="I6">
-        <v>-1.85</v>
+        <v>0.58</v>
       </c>
       <c r="J6">
-        <v>-5.06</v>
+        <v>-4.48</v>
       </c>
       <c r="K6">
-        <v>-1.48</v>
+        <v>3.15</v>
       </c>
       <c r="L6">
-        <v>-13.45</v>
+        <v>-11.12</v>
       </c>
       <c r="M6">
-        <v>18.6</v>
+        <v>18.88</v>
       </c>
       <c r="N6">
-        <v>43</v>
+        <v>57</v>
       </c>
       <c r="O6">
-        <v>48</v>
+        <v>55</v>
       </c>
       <c r="P6">
-        <v>10677.2</v>
+        <v>10689.6</v>
       </c>
       <c r="Q6">
-        <v>10980.7</v>
+        <v>10966</v>
       </c>
       <c r="R6">
-        <v>11183.58</v>
+        <v>11180.62</v>
       </c>
       <c r="S6">
-        <v>10671.92</v>
+        <v>10669.87</v>
       </c>
       <c r="T6">
-        <v>-0.67</v>
+        <v>-0.07000000000000001</v>
       </c>
       <c r="U6" t="s">
         <v>45</v>
@@ -1414,34 +1442,34 @@
         <v>1</v>
       </c>
       <c r="Y6">
-        <v>40.28</v>
+        <v>42.07</v>
       </c>
       <c r="Z6">
-        <v>-135.05</v>
+        <v>-140.13</v>
       </c>
       <c r="AA6">
-        <v>-83.08</v>
+        <v>-94.48999999999999</v>
       </c>
       <c r="AB6">
-        <v>-51.97</v>
+        <v>-45.64</v>
       </c>
       <c r="AC6">
-        <v>16.06</v>
+        <v>17.78</v>
       </c>
       <c r="AD6">
-        <v>17.21</v>
+        <v>18.54</v>
       </c>
       <c r="AE6">
-        <v>262.11</v>
+        <v>258.46</v>
       </c>
       <c r="AF6">
-        <v>-10.62</v>
+        <v>-4.65</v>
       </c>
       <c r="AG6">
-        <v>11465.66</v>
+        <v>11471.5</v>
       </c>
       <c r="AH6">
-        <v>10495.74</v>
+        <v>10460.5</v>
       </c>
       <c r="AI6">
         <v>11368.55</v>
@@ -1450,7 +1478,7 @@
         <v>47</v>
       </c>
       <c r="AK6">
-        <v>35.28</v>
+        <v>36.04</v>
       </c>
     </row>
     <row r="7" spans="1:37">
@@ -1461,10 +1489,10 @@
         <v>44</v>
       </c>
       <c r="C7">
-        <v>963.1</v>
+        <v>963.85</v>
       </c>
       <c r="D7">
-        <v>-0.71</v>
+        <v>0.08</v>
       </c>
       <c r="E7">
         <v>1158.8</v>
@@ -1473,46 +1501,46 @@
         <v>801.55</v>
       </c>
       <c r="G7">
-        <v>-16.89</v>
+        <v>-16.82</v>
       </c>
       <c r="H7">
-        <v>20.15</v>
+        <v>20.25</v>
       </c>
       <c r="I7">
-        <v>-2.22</v>
+        <v>-1.02</v>
       </c>
       <c r="J7">
-        <v>-8.19</v>
+        <v>-9.109999999999999</v>
       </c>
       <c r="K7">
-        <v>-7.62</v>
+        <v>-4.61</v>
       </c>
       <c r="L7">
-        <v>-3.58</v>
+        <v>-2.41</v>
       </c>
       <c r="M7">
-        <v>4.88</v>
+        <v>4.86</v>
       </c>
       <c r="N7">
-        <v>57</v>
+        <v>43</v>
       </c>
       <c r="O7">
-        <v>50</v>
+        <v>54</v>
       </c>
       <c r="P7">
-        <v>962.92</v>
+        <v>960.9299999999999</v>
       </c>
       <c r="Q7">
-        <v>1007.7</v>
+        <v>1002.89</v>
       </c>
       <c r="R7">
-        <v>1055.86</v>
+        <v>1054.18</v>
       </c>
       <c r="S7">
-        <v>975.9299999999999</v>
+        <v>975.75</v>
       </c>
       <c r="T7">
-        <v>-1.31</v>
+        <v>-1.22</v>
       </c>
       <c r="U7" t="s">
         <v>45</v>
@@ -1527,34 +1555,34 @@
         <v>1</v>
       </c>
       <c r="Y7">
-        <v>37.52</v>
+        <v>37.75</v>
       </c>
       <c r="Z7">
-        <v>-25.85</v>
+        <v>-25.67</v>
       </c>
       <c r="AA7">
-        <v>-21.42</v>
+        <v>-22.27</v>
       </c>
       <c r="AB7">
-        <v>-4.44</v>
+        <v>-3.4</v>
       </c>
       <c r="AC7">
-        <v>28.71</v>
+        <v>37.6</v>
       </c>
       <c r="AD7">
-        <v>22.7</v>
+        <v>29.44</v>
       </c>
       <c r="AE7">
-        <v>25.57</v>
+        <v>26.04</v>
       </c>
       <c r="AF7">
-        <v>-33.75</v>
+        <v>75.48999999999999</v>
       </c>
       <c r="AG7">
-        <v>1076.01</v>
+        <v>1069.21</v>
       </c>
       <c r="AH7">
-        <v>939.38</v>
+        <v>936.5700000000001</v>
       </c>
       <c r="AI7">
         <v>1020.6</v>
@@ -1563,7 +1591,7 @@
         <v>47</v>
       </c>
       <c r="AK7">
-        <v>40.47</v>
+        <v>35.71</v>
       </c>
     </row>
     <row r="8" spans="1:37">
@@ -1574,58 +1602,58 @@
         <v>44</v>
       </c>
       <c r="C8">
-        <v>181.55</v>
+        <v>185.92</v>
       </c>
       <c r="D8">
-        <v>-0.36</v>
+        <v>2.41</v>
       </c>
       <c r="E8">
-        <v>182.2</v>
+        <v>185.92</v>
       </c>
       <c r="F8">
         <v>115.96</v>
       </c>
       <c r="G8">
-        <v>-0.36</v>
+        <v>0</v>
       </c>
       <c r="H8">
-        <v>56.56</v>
+        <v>60.33</v>
       </c>
       <c r="I8">
-        <v>6.15</v>
+        <v>7.79</v>
       </c>
       <c r="J8">
-        <v>36.53</v>
+        <v>38.29</v>
       </c>
       <c r="K8">
-        <v>38.33</v>
+        <v>42.69</v>
       </c>
       <c r="L8">
-        <v>37.07</v>
+        <v>35.17</v>
       </c>
       <c r="M8">
-        <v>4.96</v>
+        <v>5.6</v>
       </c>
       <c r="N8">
         <v>99</v>
       </c>
       <c r="O8">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="P8">
-        <v>177.81</v>
+        <v>180.49</v>
       </c>
       <c r="Q8">
-        <v>152.64</v>
+        <v>155.09</v>
       </c>
       <c r="R8">
-        <v>143.79</v>
+        <v>144.7</v>
       </c>
       <c r="S8">
-        <v>135.62</v>
+        <v>135.89</v>
       </c>
       <c r="T8">
-        <v>33.87</v>
+        <v>36.81</v>
       </c>
       <c r="U8" t="s">
         <v>46</v>
@@ -1640,43 +1668,43 @@
         <v>3</v>
       </c>
       <c r="Y8">
-        <v>76.01000000000001</v>
+        <v>77.86</v>
       </c>
       <c r="Z8">
-        <v>11.26</v>
+        <v>12</v>
       </c>
       <c r="AA8">
-        <v>7.45</v>
+        <v>8.359999999999999</v>
       </c>
       <c r="AB8">
-        <v>3.81</v>
+        <v>3.64</v>
       </c>
       <c r="AC8">
-        <v>77.98</v>
+        <v>82.34999999999999</v>
       </c>
       <c r="AD8">
-        <v>84.37</v>
+        <v>81.65000000000001</v>
       </c>
       <c r="AE8">
-        <v>8.23</v>
+        <v>8.42</v>
       </c>
       <c r="AF8">
-        <v>-21.31</v>
+        <v>24.92</v>
       </c>
       <c r="AG8">
-        <v>189.38</v>
+        <v>193.89</v>
       </c>
       <c r="AH8">
-        <v>115.89</v>
+        <v>116.28</v>
       </c>
       <c r="AI8">
-        <v>158.84</v>
+        <v>159.98</v>
       </c>
       <c r="AJ8" t="s">
         <v>48</v>
       </c>
       <c r="AK8">
-        <v>55.48</v>
+        <v>57.39</v>
       </c>
     </row>
   </sheetData>
@@ -1817,7 +1845,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:F62"/>
+  <dimension ref="A1:F64"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="16.7109375" customWidth="1"/>
@@ -1837,12 +1865,47 @@
     </row>
     <row r="2" spans="1:6">
       <c r="A2" s="3" t="s">
+        <v>0</v>
+      </c>
+      <c r="B2" s="3" t="s">
         <v>50</v>
+      </c>
+      <c r="C2" s="3" t="s">
+        <v>51</v>
+      </c>
+      <c r="D2" s="3" t="s">
+        <v>52</v>
+      </c>
+      <c r="E2" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="F2" s="3" t="s">
+        <v>54</v>
+      </c>
+    </row>
+    <row r="3" spans="1:6">
+      <c r="A3" s="4" t="s">
+        <v>39</v>
+      </c>
+      <c r="B3" s="4" t="s">
+        <v>55</v>
+      </c>
+      <c r="C3" s="4" t="s">
+        <v>56</v>
+      </c>
+      <c r="D3" s="4" t="s">
+        <v>57</v>
+      </c>
+      <c r="E3" s="4" t="s">
+        <v>58</v>
+      </c>
+      <c r="F3" s="4" t="s">
+        <v>59</v>
       </c>
     </row>
     <row r="5" spans="1:6">
       <c r="A5" s="2" t="s">
-        <v>51</v>
+        <v>60</v>
       </c>
       <c r="B5" s="2"/>
       <c r="C5" s="2"/>
@@ -1850,972 +1913,1006 @@
       <c r="E5" s="2"/>
     </row>
     <row r="6" spans="1:6">
-      <c r="A6" s="4" t="s">
+      <c r="A6" s="3" t="s">
         <v>0</v>
       </c>
-      <c r="B6" s="4" t="s">
-        <v>52</v>
-      </c>
-      <c r="C6" s="4" t="s">
-        <v>53</v>
-      </c>
-      <c r="D6" s="4" t="s">
-        <v>54</v>
-      </c>
-      <c r="E6" s="4" t="s">
-        <v>55</v>
+      <c r="B6" s="3" t="s">
+        <v>61</v>
+      </c>
+      <c r="C6" s="3" t="s">
+        <v>62</v>
+      </c>
+      <c r="D6" s="3" t="s">
+        <v>63</v>
+      </c>
+      <c r="E6" s="3" t="s">
+        <v>64</v>
       </c>
     </row>
     <row r="7" spans="1:6">
-      <c r="A7" s="3" t="s">
+      <c r="A7" s="5" t="s">
         <v>37</v>
       </c>
-      <c r="B7" s="3" t="s">
+      <c r="B7" s="5" t="s">
         <v>9</v>
       </c>
-      <c r="C7" s="5">
-        <v>-17.36</v>
-      </c>
-      <c r="D7" s="5">
+      <c r="C7" s="6">
         <v>-15.96</v>
       </c>
-      <c r="E7" s="6">
-        <v>1.4</v>
+      <c r="D7" s="6">
+        <v>-17.07</v>
+      </c>
+      <c r="E7" s="7">
+        <v>-1.11</v>
       </c>
     </row>
     <row r="8" spans="1:6">
-      <c r="A8" s="3" t="s">
+      <c r="A8" s="5" t="s">
         <v>38</v>
       </c>
-      <c r="B8" s="3" t="s">
+      <c r="B8" s="5" t="s">
         <v>9</v>
       </c>
-      <c r="C8" s="5">
-        <v>-0.87</v>
-      </c>
-      <c r="D8" s="5">
+      <c r="C8" s="6">
         <v>-3.04</v>
       </c>
+      <c r="D8" s="6">
+        <v>-6.68</v>
+      </c>
       <c r="E8" s="7">
-        <v>-2.17</v>
+        <v>-3.64</v>
       </c>
     </row>
     <row r="9" spans="1:6">
-      <c r="A9" s="3" t="s">
+      <c r="A9" s="5" t="s">
         <v>39</v>
       </c>
-      <c r="B9" s="3" t="s">
+      <c r="B9" s="5" t="s">
         <v>9</v>
       </c>
-      <c r="C9" s="5">
-        <v>-7.52</v>
-      </c>
-      <c r="D9" s="5">
+      <c r="C9" s="6">
         <v>-10.16</v>
       </c>
-      <c r="E9" s="7">
-        <v>-2.64</v>
+      <c r="D9" s="6">
+        <v>-9.199999999999999</v>
+      </c>
+      <c r="E9" s="8">
+        <v>0.96</v>
       </c>
     </row>
     <row r="10" spans="1:6">
-      <c r="A10" s="3" t="s">
+      <c r="A10" s="5" t="s">
         <v>40</v>
       </c>
-      <c r="B10" s="3" t="s">
+      <c r="B10" s="5" t="s">
         <v>9</v>
       </c>
-      <c r="C10" s="5">
-        <v>-11.99</v>
-      </c>
-      <c r="D10" s="5">
+      <c r="C10" s="6">
         <v>-12.03</v>
       </c>
-      <c r="E10" s="7">
-        <v>-0.04</v>
+      <c r="D10" s="6">
+        <v>-11.51</v>
+      </c>
+      <c r="E10" s="8">
+        <v>0.52</v>
       </c>
     </row>
     <row r="11" spans="1:6">
-      <c r="A11" s="3" t="s">
+      <c r="A11" s="5" t="s">
         <v>41</v>
       </c>
-      <c r="B11" s="3" t="s">
+      <c r="B11" s="5" t="s">
         <v>9</v>
       </c>
-      <c r="C11" s="5">
-        <v>-3.32</v>
-      </c>
-      <c r="D11" s="5">
+      <c r="C11" s="6">
         <v>-5.06</v>
       </c>
-      <c r="E11" s="7">
-        <v>-1.74</v>
+      <c r="D11" s="6">
+        <v>-4.48</v>
+      </c>
+      <c r="E11" s="8">
+        <v>0.58</v>
       </c>
     </row>
     <row r="12" spans="1:6">
-      <c r="A12" s="3" t="s">
+      <c r="A12" s="5" t="s">
         <v>42</v>
       </c>
-      <c r="B12" s="3" t="s">
+      <c r="B12" s="5" t="s">
         <v>9</v>
       </c>
-      <c r="C12" s="5">
-        <v>-8.140000000000001</v>
-      </c>
-      <c r="D12" s="5">
+      <c r="C12" s="6">
         <v>-8.19</v>
       </c>
+      <c r="D12" s="6">
+        <v>-9.109999999999999</v>
+      </c>
       <c r="E12" s="7">
-        <v>-0.05</v>
+        <v>-0.92</v>
       </c>
     </row>
     <row r="13" spans="1:6">
-      <c r="A13" s="3" t="s">
+      <c r="A13" s="5" t="s">
         <v>43</v>
       </c>
-      <c r="B13" s="3" t="s">
+      <c r="B13" s="5" t="s">
         <v>9</v>
       </c>
-      <c r="C13" s="5">
-        <v>35.79</v>
-      </c>
-      <c r="D13" s="5">
+      <c r="C13" s="6">
         <v>36.53</v>
       </c>
-      <c r="E13" s="6">
-        <v>0.74</v>
+      <c r="D13" s="6">
+        <v>38.29</v>
+      </c>
+      <c r="E13" s="8">
+        <v>1.76</v>
       </c>
     </row>
     <row r="14" spans="1:6">
-      <c r="A14" s="3" t="s">
+      <c r="A14" s="5" t="s">
         <v>37</v>
       </c>
-      <c r="B14" s="3" t="s">
+      <c r="B14" s="5" t="s">
         <v>8</v>
       </c>
-      <c r="C14" s="5">
-        <v>-11.14</v>
-      </c>
-      <c r="D14" s="5">
+      <c r="C14" s="6">
         <v>-9.130000000000001</v>
       </c>
-      <c r="E14" s="6">
-        <v>2.01</v>
+      <c r="D14" s="6">
+        <v>-8.57</v>
+      </c>
+      <c r="E14" s="8">
+        <v>0.5600000000000001</v>
       </c>
     </row>
     <row r="15" spans="1:6">
-      <c r="A15" s="3" t="s">
+      <c r="A15" s="5" t="s">
         <v>38</v>
       </c>
-      <c r="B15" s="3" t="s">
+      <c r="B15" s="5" t="s">
         <v>8</v>
       </c>
-      <c r="C15" s="5">
-        <v>-3.83</v>
-      </c>
-      <c r="D15" s="5">
+      <c r="C15" s="6">
         <v>2.8</v>
       </c>
-      <c r="E15" s="6">
-        <v>6.63</v>
+      <c r="D15" s="6">
+        <v>-2.03</v>
+      </c>
+      <c r="E15" s="7">
+        <v>-4.83</v>
       </c>
     </row>
     <row r="16" spans="1:6">
-      <c r="A16" s="3" t="s">
+      <c r="A16" s="5" t="s">
         <v>39</v>
       </c>
-      <c r="B16" s="3" t="s">
+      <c r="B16" s="5" t="s">
         <v>8</v>
       </c>
-      <c r="C16" s="5">
-        <v>-6.18</v>
-      </c>
-      <c r="D16" s="5">
+      <c r="C16" s="6">
         <v>-4.58</v>
       </c>
-      <c r="E16" s="6">
-        <v>1.6</v>
+      <c r="D16" s="6">
+        <v>-2.95</v>
+      </c>
+      <c r="E16" s="8">
+        <v>1.63</v>
       </c>
     </row>
     <row r="17" spans="1:5">
-      <c r="A17" s="3" t="s">
+      <c r="A17" s="5" t="s">
         <v>40</v>
       </c>
-      <c r="B17" s="3" t="s">
+      <c r="B17" s="5" t="s">
         <v>8</v>
       </c>
-      <c r="C17" s="5">
-        <v>-1.11</v>
-      </c>
-      <c r="D17" s="5">
+      <c r="C17" s="6">
         <v>0.02</v>
       </c>
-      <c r="E17" s="6">
-        <v>1.13</v>
+      <c r="D17" s="6">
+        <v>0.05</v>
+      </c>
+      <c r="E17" s="8">
+        <v>0.03</v>
       </c>
     </row>
     <row r="18" spans="1:5">
-      <c r="A18" s="3" t="s">
+      <c r="A18" s="5" t="s">
         <v>41</v>
       </c>
-      <c r="B18" s="3" t="s">
+      <c r="B18" s="5" t="s">
         <v>8</v>
       </c>
-      <c r="C18" s="5">
+      <c r="C18" s="6">
+        <v>-1.85</v>
+      </c>
+      <c r="D18" s="6">
+        <v>0.58</v>
+      </c>
+      <c r="E18" s="8">
+        <v>2.43</v>
+      </c>
+    </row>
+    <row r="19" spans="1:5">
+      <c r="A19" s="5" t="s">
+        <v>42</v>
+      </c>
+      <c r="B19" s="5" t="s">
+        <v>8</v>
+      </c>
+      <c r="C19" s="6">
+        <v>-2.22</v>
+      </c>
+      <c r="D19" s="6">
+        <v>-1.02</v>
+      </c>
+      <c r="E19" s="8">
+        <v>1.2</v>
+      </c>
+    </row>
+    <row r="20" spans="1:5">
+      <c r="A20" s="5" t="s">
+        <v>43</v>
+      </c>
+      <c r="B20" s="5" t="s">
+        <v>8</v>
+      </c>
+      <c r="C20" s="6">
+        <v>6.15</v>
+      </c>
+      <c r="D20" s="6">
+        <v>7.79</v>
+      </c>
+      <c r="E20" s="8">
+        <v>1.64</v>
+      </c>
+    </row>
+    <row r="21" spans="1:5">
+      <c r="A21" s="5" t="s">
+        <v>37</v>
+      </c>
+      <c r="B21" s="5" t="s">
+        <v>11</v>
+      </c>
+      <c r="C21" s="6">
+        <v>17.05</v>
+      </c>
+      <c r="D21" s="6">
+        <v>16.19</v>
+      </c>
+      <c r="E21" s="7">
+        <v>-0.86</v>
+      </c>
+    </row>
+    <row r="22" spans="1:5">
+      <c r="A22" s="5" t="s">
+        <v>38</v>
+      </c>
+      <c r="B22" s="5" t="s">
+        <v>11</v>
+      </c>
+      <c r="C22" s="6">
+        <v>108.32</v>
+      </c>
+      <c r="D22" s="6">
+        <v>104.61</v>
+      </c>
+      <c r="E22" s="7">
+        <v>-3.71</v>
+      </c>
+    </row>
+    <row r="23" spans="1:5">
+      <c r="A23" s="5" t="s">
+        <v>39</v>
+      </c>
+      <c r="B23" s="5" t="s">
+        <v>11</v>
+      </c>
+      <c r="C23" s="6">
+        <v>-44.91</v>
+      </c>
+      <c r="D23" s="6">
+        <v>-45.11</v>
+      </c>
+      <c r="E23" s="7">
+        <v>-0.2</v>
+      </c>
+    </row>
+    <row r="24" spans="1:5">
+      <c r="A24" s="5" t="s">
+        <v>40</v>
+      </c>
+      <c r="B24" s="5" t="s">
+        <v>11</v>
+      </c>
+      <c r="C24" s="6">
+        <v>-12.66</v>
+      </c>
+      <c r="D24" s="6">
+        <v>-13.14</v>
+      </c>
+      <c r="E24" s="7">
+        <v>-0.48</v>
+      </c>
+    </row>
+    <row r="25" spans="1:5">
+      <c r="A25" s="5" t="s">
+        <v>41</v>
+      </c>
+      <c r="B25" s="5" t="s">
+        <v>11</v>
+      </c>
+      <c r="C25" s="6">
+        <v>-13.45</v>
+      </c>
+      <c r="D25" s="6">
+        <v>-11.12</v>
+      </c>
+      <c r="E25" s="8">
+        <v>2.33</v>
+      </c>
+    </row>
+    <row r="26" spans="1:5">
+      <c r="A26" s="5" t="s">
+        <v>42</v>
+      </c>
+      <c r="B26" s="5" t="s">
+        <v>11</v>
+      </c>
+      <c r="C26" s="6">
+        <v>-3.58</v>
+      </c>
+      <c r="D26" s="6">
+        <v>-2.41</v>
+      </c>
+      <c r="E26" s="8">
+        <v>1.17</v>
+      </c>
+    </row>
+    <row r="27" spans="1:5">
+      <c r="A27" s="5" t="s">
+        <v>43</v>
+      </c>
+      <c r="B27" s="5" t="s">
+        <v>11</v>
+      </c>
+      <c r="C27" s="6">
+        <v>37.07</v>
+      </c>
+      <c r="D27" s="6">
+        <v>35.17</v>
+      </c>
+      <c r="E27" s="7">
         <v>-1.9</v>
       </c>
-      <c r="D18" s="5">
-        <v>-1.85</v>
-      </c>
-      <c r="E18" s="6">
-        <v>0.05</v>
-      </c>
-    </row>
-    <row r="19" spans="1:5">
-      <c r="A19" s="3" t="s">
+    </row>
+    <row r="28" spans="1:5">
+      <c r="A28" s="5" t="s">
+        <v>37</v>
+      </c>
+      <c r="B28" s="5" t="s">
+        <v>10</v>
+      </c>
+      <c r="C28" s="6">
+        <v>-0.91</v>
+      </c>
+      <c r="D28" s="6">
+        <v>-2.75</v>
+      </c>
+      <c r="E28" s="7">
+        <v>-1.84</v>
+      </c>
+    </row>
+    <row r="29" spans="1:5">
+      <c r="A29" s="5" t="s">
+        <v>38</v>
+      </c>
+      <c r="B29" s="5" t="s">
+        <v>10</v>
+      </c>
+      <c r="C29" s="6">
+        <v>-20.44</v>
+      </c>
+      <c r="D29" s="6">
+        <v>-21.32</v>
+      </c>
+      <c r="E29" s="7">
+        <v>-0.88</v>
+      </c>
+    </row>
+    <row r="30" spans="1:5">
+      <c r="A30" s="5" t="s">
+        <v>39</v>
+      </c>
+      <c r="B30" s="5" t="s">
+        <v>10</v>
+      </c>
+      <c r="C30" s="6">
+        <v>-9.210000000000001</v>
+      </c>
+      <c r="D30" s="6">
+        <v>-6.31</v>
+      </c>
+      <c r="E30" s="8">
+        <v>2.9</v>
+      </c>
+    </row>
+    <row r="31" spans="1:5">
+      <c r="A31" s="5" t="s">
+        <v>40</v>
+      </c>
+      <c r="B31" s="5" t="s">
+        <v>10</v>
+      </c>
+      <c r="C31" s="6">
+        <v>-7.05</v>
+      </c>
+      <c r="D31" s="6">
+        <v>-6.02</v>
+      </c>
+      <c r="E31" s="8">
+        <v>1.03</v>
+      </c>
+    </row>
+    <row r="32" spans="1:5">
+      <c r="A32" s="5" t="s">
+        <v>41</v>
+      </c>
+      <c r="B32" s="5" t="s">
+        <v>10</v>
+      </c>
+      <c r="C32" s="6">
+        <v>-1.48</v>
+      </c>
+      <c r="D32" s="6">
+        <v>3.15</v>
+      </c>
+      <c r="E32" s="8">
+        <v>4.63</v>
+      </c>
+    </row>
+    <row r="33" spans="1:5">
+      <c r="A33" s="5" t="s">
         <v>42</v>
       </c>
-      <c r="B19" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="C19" s="5">
-        <v>-2.7</v>
-      </c>
-      <c r="D19" s="5">
-        <v>-2.22</v>
-      </c>
-      <c r="E19" s="6">
-        <v>0.48</v>
-      </c>
-    </row>
-    <row r="20" spans="1:5">
-      <c r="A20" s="3" t="s">
+      <c r="B33" s="5" t="s">
+        <v>10</v>
+      </c>
+      <c r="C33" s="6">
+        <v>-7.62</v>
+      </c>
+      <c r="D33" s="6">
+        <v>-4.61</v>
+      </c>
+      <c r="E33" s="8">
+        <v>3.01</v>
+      </c>
+    </row>
+    <row r="34" spans="1:5">
+      <c r="A34" s="5" t="s">
         <v>43</v>
       </c>
-      <c r="B20" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="C20" s="5">
-        <v>9.07</v>
-      </c>
-      <c r="D20" s="5">
-        <v>6.15</v>
-      </c>
-      <c r="E20" s="7">
-        <v>-2.92</v>
-      </c>
-    </row>
-    <row r="21" spans="1:5">
-      <c r="A21" s="3" t="s">
+      <c r="B34" s="5" t="s">
+        <v>10</v>
+      </c>
+      <c r="C34" s="6">
+        <v>38.33</v>
+      </c>
+      <c r="D34" s="6">
+        <v>42.69</v>
+      </c>
+      <c r="E34" s="8">
+        <v>4.36</v>
+      </c>
+    </row>
+    <row r="35" spans="1:5">
+      <c r="A35" s="5" t="s">
         <v>37</v>
       </c>
-      <c r="B21" s="3" t="s">
-        <v>11</v>
-      </c>
-      <c r="C21" s="5">
-        <v>16.61</v>
-      </c>
-      <c r="D21" s="5">
-        <v>17.05</v>
-      </c>
-      <c r="E21" s="6">
-        <v>0.44</v>
-      </c>
-    </row>
-    <row r="22" spans="1:5">
-      <c r="A22" s="3" t="s">
+      <c r="B35" s="5" t="s">
+        <v>6</v>
+      </c>
+      <c r="C35" s="6">
+        <v>-18.96</v>
+      </c>
+      <c r="D35" s="6">
+        <v>-20.04</v>
+      </c>
+      <c r="E35" s="7">
+        <v>-1.08</v>
+      </c>
+    </row>
+    <row r="36" spans="1:5">
+      <c r="A36" s="5" t="s">
         <v>38</v>
       </c>
-      <c r="B22" s="3" t="s">
-        <v>11</v>
-      </c>
-      <c r="C22" s="5">
-        <v>104.06</v>
-      </c>
-      <c r="D22" s="5">
-        <v>108.32</v>
-      </c>
-      <c r="E22" s="6">
-        <v>4.26</v>
-      </c>
-    </row>
-    <row r="23" spans="1:5">
-      <c r="A23" s="3" t="s">
+      <c r="B36" s="5" t="s">
+        <v>6</v>
+      </c>
+      <c r="C36" s="6">
+        <v>-26.37</v>
+      </c>
+      <c r="D36" s="6">
+        <v>-27.94</v>
+      </c>
+      <c r="E36" s="7">
+        <v>-1.57</v>
+      </c>
+    </row>
+    <row r="37" spans="1:5">
+      <c r="A37" s="5" t="s">
         <v>39</v>
       </c>
-      <c r="B23" s="3" t="s">
-        <v>11</v>
-      </c>
-      <c r="C23" s="5">
-        <v>-46.08</v>
-      </c>
-      <c r="D23" s="5">
-        <v>-44.91</v>
-      </c>
-      <c r="E23" s="6">
-        <v>1.17</v>
-      </c>
-    </row>
-    <row r="24" spans="1:5">
-      <c r="A24" s="3" t="s">
+      <c r="B37" s="5" t="s">
+        <v>6</v>
+      </c>
+      <c r="C37" s="6">
+        <v>-45.21</v>
+      </c>
+      <c r="D37" s="6">
+        <v>-45.13</v>
+      </c>
+      <c r="E37" s="8">
+        <v>0.08</v>
+      </c>
+    </row>
+    <row r="38" spans="1:5">
+      <c r="A38" s="5" t="s">
         <v>40</v>
       </c>
-      <c r="B24" s="3" t="s">
-        <v>11</v>
-      </c>
-      <c r="C24" s="5">
-        <v>-13.5</v>
-      </c>
-      <c r="D24" s="5">
-        <v>-12.66</v>
-      </c>
-      <c r="E24" s="6">
-        <v>0.84</v>
-      </c>
-    </row>
-    <row r="25" spans="1:5">
-      <c r="A25" s="3" t="s">
+      <c r="B38" s="5" t="s">
+        <v>6</v>
+      </c>
+      <c r="C38" s="6">
+        <v>-19.49</v>
+      </c>
+      <c r="D38" s="6">
+        <v>-19.91</v>
+      </c>
+      <c r="E38" s="7">
+        <v>-0.42</v>
+      </c>
+    </row>
+    <row r="39" spans="1:5">
+      <c r="A39" s="5" t="s">
         <v>41</v>
       </c>
-      <c r="B25" s="3" t="s">
-        <v>11</v>
-      </c>
-      <c r="C25" s="5">
-        <v>-13.88</v>
-      </c>
-      <c r="D25" s="5">
-        <v>-13.45</v>
-      </c>
-      <c r="E25" s="6">
-        <v>0.43</v>
-      </c>
-    </row>
-    <row r="26" spans="1:5">
-      <c r="A26" s="3" t="s">
+      <c r="B39" s="5" t="s">
+        <v>6</v>
+      </c>
+      <c r="C39" s="6">
+        <v>-19.35</v>
+      </c>
+      <c r="D39" s="6">
+        <v>-18.88</v>
+      </c>
+      <c r="E39" s="8">
+        <v>0.47</v>
+      </c>
+    </row>
+    <row r="40" spans="1:5">
+      <c r="A40" s="5" t="s">
         <v>42</v>
       </c>
-      <c r="B26" s="3" t="s">
-        <v>11</v>
-      </c>
-      <c r="C26" s="5">
-        <v>-2.11</v>
-      </c>
-      <c r="D26" s="5">
-        <v>-3.58</v>
-      </c>
-      <c r="E26" s="7">
-        <v>-1.47</v>
-      </c>
-    </row>
-    <row r="27" spans="1:5">
-      <c r="A27" s="3" t="s">
+      <c r="B40" s="5" t="s">
+        <v>6</v>
+      </c>
+      <c r="C40" s="6">
+        <v>-16.89</v>
+      </c>
+      <c r="D40" s="6">
+        <v>-16.82</v>
+      </c>
+      <c r="E40" s="8">
+        <v>0.07000000000000001</v>
+      </c>
+    </row>
+    <row r="41" spans="1:5">
+      <c r="A41" s="5" t="s">
         <v>43</v>
       </c>
-      <c r="B27" s="3" t="s">
-        <v>11</v>
-      </c>
-      <c r="C27" s="5">
-        <v>40.27</v>
-      </c>
-      <c r="D27" s="5">
-        <v>37.07</v>
-      </c>
-      <c r="E27" s="7">
-        <v>-3.2</v>
-      </c>
-    </row>
-    <row r="28" spans="1:5">
-      <c r="A28" s="3" t="s">
+      <c r="B41" s="5" t="s">
+        <v>6</v>
+      </c>
+      <c r="C41" s="6">
+        <v>-0.36</v>
+      </c>
+      <c r="D41" s="6">
+        <v>0</v>
+      </c>
+      <c r="E41" s="8">
+        <v>0.36</v>
+      </c>
+    </row>
+    <row r="42" spans="1:5">
+      <c r="A42" s="5" t="s">
         <v>37</v>
       </c>
-      <c r="B28" s="3" t="s">
-        <v>10</v>
-      </c>
-      <c r="C28" s="5">
-        <v>-0.12</v>
-      </c>
-      <c r="D28" s="5">
-        <v>-0.91</v>
-      </c>
-      <c r="E28" s="7">
-        <v>-0.79</v>
-      </c>
-    </row>
-    <row r="29" spans="1:5">
-      <c r="A29" s="3" t="s">
+      <c r="B42" s="5" t="s">
+        <v>2</v>
+      </c>
+      <c r="C42" s="6">
+        <v>10017</v>
+      </c>
+      <c r="D42" s="6">
+        <v>9884</v>
+      </c>
+      <c r="E42" s="7">
+        <v>-133</v>
+      </c>
+    </row>
+    <row r="43" spans="1:5">
+      <c r="A43" s="5" t="s">
         <v>38</v>
       </c>
-      <c r="B29" s="3" t="s">
-        <v>10</v>
-      </c>
-      <c r="C29" s="5">
-        <v>-22.49</v>
-      </c>
-      <c r="D29" s="5">
-        <v>-20.44</v>
-      </c>
-      <c r="E29" s="6">
-        <v>2.05</v>
-      </c>
-    </row>
-    <row r="30" spans="1:5">
-      <c r="A30" s="3" t="s">
+      <c r="B43" s="5" t="s">
+        <v>2</v>
+      </c>
+      <c r="C43" s="6">
+        <v>493.5</v>
+      </c>
+      <c r="D43" s="6">
+        <v>483</v>
+      </c>
+      <c r="E43" s="7">
+        <v>-10.5</v>
+      </c>
+    </row>
+    <row r="44" spans="1:5">
+      <c r="A44" s="5" t="s">
         <v>39</v>
       </c>
-      <c r="B30" s="3" t="s">
-        <v>10</v>
-      </c>
-      <c r="C30" s="5">
-        <v>-8.210000000000001</v>
-      </c>
-      <c r="D30" s="5">
-        <v>-9.210000000000001</v>
-      </c>
-      <c r="E30" s="7">
-        <v>-1</v>
-      </c>
-    </row>
-    <row r="31" spans="1:5">
-      <c r="A31" s="3" t="s">
+      <c r="B44" s="5" t="s">
+        <v>2</v>
+      </c>
+      <c r="C44" s="6">
+        <v>300.25</v>
+      </c>
+      <c r="D44" s="6">
+        <v>300.7</v>
+      </c>
+      <c r="E44" s="8">
+        <v>0.45</v>
+      </c>
+    </row>
+    <row r="45" spans="1:5">
+      <c r="A45" s="5" t="s">
         <v>40</v>
       </c>
-      <c r="B31" s="3" t="s">
-        <v>10</v>
-      </c>
-      <c r="C31" s="5">
-        <v>-6.38</v>
-      </c>
-      <c r="D31" s="5">
-        <v>-7.05</v>
-      </c>
-      <c r="E31" s="7">
-        <v>-0.67</v>
-      </c>
-    </row>
-    <row r="32" spans="1:5">
-      <c r="A32" s="3" t="s">
+      <c r="B45" s="5" t="s">
+        <v>2</v>
+      </c>
+      <c r="C45" s="6">
+        <v>1752.4</v>
+      </c>
+      <c r="D45" s="6">
+        <v>1743.3</v>
+      </c>
+      <c r="E45" s="7">
+        <v>-9.1</v>
+      </c>
+    </row>
+    <row r="46" spans="1:5">
+      <c r="A46" s="5" t="s">
         <v>41</v>
       </c>
-      <c r="B32" s="3" t="s">
-        <v>10</v>
-      </c>
-      <c r="C32" s="5">
-        <v>-0.8</v>
-      </c>
-      <c r="D32" s="5">
-        <v>-1.48</v>
-      </c>
-      <c r="E32" s="7">
-        <v>-0.68</v>
-      </c>
-    </row>
-    <row r="33" spans="1:5">
-      <c r="A33" s="3" t="s">
+      <c r="B46" s="5" t="s">
+        <v>2</v>
+      </c>
+      <c r="C46" s="6">
+        <v>10600</v>
+      </c>
+      <c r="D46" s="6">
+        <v>10662</v>
+      </c>
+      <c r="E46" s="8">
+        <v>62</v>
+      </c>
+    </row>
+    <row r="47" spans="1:5">
+      <c r="A47" s="5" t="s">
         <v>42</v>
       </c>
-      <c r="B33" s="3" t="s">
-        <v>10</v>
-      </c>
-      <c r="C33" s="5">
-        <v>-5.74</v>
-      </c>
-      <c r="D33" s="5">
-        <v>-7.62</v>
-      </c>
-      <c r="E33" s="7">
-        <v>-1.88</v>
-      </c>
-    </row>
-    <row r="34" spans="1:5">
-      <c r="A34" s="3" t="s">
+      <c r="B47" s="5" t="s">
+        <v>2</v>
+      </c>
+      <c r="C47" s="6">
+        <v>963.1</v>
+      </c>
+      <c r="D47" s="6">
+        <v>963.85</v>
+      </c>
+      <c r="E47" s="8">
+        <v>0.75</v>
+      </c>
+    </row>
+    <row r="48" spans="1:5">
+      <c r="A48" s="5" t="s">
         <v>43</v>
       </c>
-      <c r="B34" s="3" t="s">
-        <v>10</v>
-      </c>
-      <c r="C34" s="5">
-        <v>37.03</v>
-      </c>
-      <c r="D34" s="5">
-        <v>38.33</v>
-      </c>
-      <c r="E34" s="6">
-        <v>1.3</v>
-      </c>
-    </row>
-    <row r="35" spans="1:5">
-      <c r="A35" s="3" t="s">
+      <c r="B48" s="5" t="s">
+        <v>2</v>
+      </c>
+      <c r="C48" s="6">
+        <v>181.55</v>
+      </c>
+      <c r="D48" s="6">
+        <v>185.92</v>
+      </c>
+      <c r="E48" s="8">
+        <v>4.37</v>
+      </c>
+    </row>
+    <row r="49" spans="1:5">
+      <c r="A49" s="5" t="s">
+        <v>41</v>
+      </c>
+      <c r="B49" s="5" t="s">
+        <v>13</v>
+      </c>
+      <c r="C49" s="6">
+        <v>43</v>
+      </c>
+      <c r="D49" s="6">
+        <v>57</v>
+      </c>
+      <c r="E49" s="8">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="50" spans="1:5">
+      <c r="A50" s="5" t="s">
+        <v>42</v>
+      </c>
+      <c r="B50" s="5" t="s">
+        <v>13</v>
+      </c>
+      <c r="C50" s="6">
+        <v>57</v>
+      </c>
+      <c r="D50" s="6">
+        <v>43</v>
+      </c>
+      <c r="E50" s="7">
+        <v>-14</v>
+      </c>
+    </row>
+    <row r="51" spans="1:5">
+      <c r="A51" s="5" t="s">
         <v>37</v>
       </c>
-      <c r="B35" s="3" t="s">
-        <v>6</v>
-      </c>
-      <c r="C35" s="5">
-        <v>-18.91</v>
-      </c>
-      <c r="D35" s="5">
-        <v>-18.96</v>
-      </c>
-      <c r="E35" s="7">
-        <v>-0.05</v>
-      </c>
-    </row>
-    <row r="36" spans="1:5">
-      <c r="A36" s="3" t="s">
+      <c r="B51" s="5" t="s">
+        <v>24</v>
+      </c>
+      <c r="C51" s="6">
+        <v>21.53</v>
+      </c>
+      <c r="D51" s="6">
+        <v>20.18</v>
+      </c>
+      <c r="E51" s="7">
+        <v>-1.35</v>
+      </c>
+    </row>
+    <row r="52" spans="1:5">
+      <c r="A52" s="5" t="s">
         <v>38</v>
       </c>
-      <c r="B36" s="3" t="s">
-        <v>6</v>
-      </c>
-      <c r="C36" s="5">
-        <v>-28.33</v>
-      </c>
-      <c r="D36" s="5">
-        <v>-26.37</v>
-      </c>
-      <c r="E36" s="6">
-        <v>1.96</v>
-      </c>
-    </row>
-    <row r="37" spans="1:5">
-      <c r="A37" s="3" t="s">
+      <c r="B52" s="5" t="s">
+        <v>24</v>
+      </c>
+      <c r="C52" s="6">
+        <v>46.79</v>
+      </c>
+      <c r="D52" s="6">
+        <v>42.99</v>
+      </c>
+      <c r="E52" s="7">
+        <v>-3.8</v>
+      </c>
+    </row>
+    <row r="53" spans="1:5">
+      <c r="A53" s="5" t="s">
         <v>39</v>
       </c>
-      <c r="B37" s="3" t="s">
-        <v>6</v>
-      </c>
-      <c r="C37" s="5">
-        <v>-45.39</v>
-      </c>
-      <c r="D37" s="5">
-        <v>-45.21</v>
-      </c>
-      <c r="E37" s="6">
-        <v>0.18</v>
-      </c>
-    </row>
-    <row r="38" spans="1:5">
-      <c r="A38" s="3" t="s">
+      <c r="B53" s="5" t="s">
+        <v>24</v>
+      </c>
+      <c r="C53" s="6">
+        <v>29.53</v>
+      </c>
+      <c r="D53" s="6">
+        <v>30.13</v>
+      </c>
+      <c r="E53" s="8">
+        <v>0.6</v>
+      </c>
+    </row>
+    <row r="54" spans="1:5">
+      <c r="A54" s="5" t="s">
         <v>40</v>
       </c>
-      <c r="B38" s="3" t="s">
-        <v>6</v>
-      </c>
-      <c r="C38" s="5">
-        <v>-19.54</v>
-      </c>
-      <c r="D38" s="5">
-        <v>-19.49</v>
-      </c>
-      <c r="E38" s="6">
-        <v>0.05</v>
-      </c>
-    </row>
-    <row r="39" spans="1:5">
-      <c r="A39" s="3" t="s">
+      <c r="B54" s="5" t="s">
+        <v>24</v>
+      </c>
+      <c r="C54" s="6">
+        <v>30.61</v>
+      </c>
+      <c r="D54" s="6">
+        <v>29.46</v>
+      </c>
+      <c r="E54" s="7">
+        <v>-1.15</v>
+      </c>
+    </row>
+    <row r="55" spans="1:5">
+      <c r="A55" s="5" t="s">
         <v>41</v>
       </c>
-      <c r="B39" s="3" t="s">
-        <v>6</v>
-      </c>
-      <c r="C39" s="5">
-        <v>-18.35</v>
-      </c>
-      <c r="D39" s="5">
-        <v>-19.35</v>
-      </c>
-      <c r="E39" s="7">
-        <v>-1</v>
-      </c>
-    </row>
-    <row r="40" spans="1:5">
-      <c r="A40" s="3" t="s">
+      <c r="B55" s="5" t="s">
+        <v>24</v>
+      </c>
+      <c r="C55" s="6">
+        <v>40.28</v>
+      </c>
+      <c r="D55" s="6">
+        <v>42.07</v>
+      </c>
+      <c r="E55" s="8">
+        <v>1.79</v>
+      </c>
+    </row>
+    <row r="56" spans="1:5">
+      <c r="A56" s="5" t="s">
         <v>42</v>
       </c>
-      <c r="B40" s="3" t="s">
-        <v>6</v>
-      </c>
-      <c r="C40" s="5">
-        <v>-16.29</v>
-      </c>
-      <c r="D40" s="5">
-        <v>-16.89</v>
-      </c>
-      <c r="E40" s="7">
-        <v>-0.6</v>
-      </c>
-    </row>
-    <row r="41" spans="1:5">
-      <c r="A41" s="3" t="s">
+      <c r="B56" s="5" t="s">
+        <v>24</v>
+      </c>
+      <c r="C56" s="6">
+        <v>37.52</v>
+      </c>
+      <c r="D56" s="6">
+        <v>37.75</v>
+      </c>
+      <c r="E56" s="8">
+        <v>0.23</v>
+      </c>
+    </row>
+    <row r="57" spans="1:5">
+      <c r="A57" s="5" t="s">
         <v>43</v>
       </c>
-      <c r="B41" s="3" t="s">
-        <v>6</v>
-      </c>
-      <c r="C41" s="5">
-        <v>0</v>
-      </c>
-      <c r="D41" s="5">
-        <v>-0.36</v>
-      </c>
-      <c r="E41" s="7">
-        <v>-0.36</v>
-      </c>
-    </row>
-    <row r="42" spans="1:5">
-      <c r="A42" s="3" t="s">
+      <c r="B57" s="5" t="s">
+        <v>24</v>
+      </c>
+      <c r="C57" s="6">
+        <v>76.01000000000001</v>
+      </c>
+      <c r="D57" s="6">
+        <v>77.86</v>
+      </c>
+      <c r="E57" s="8">
+        <v>1.85</v>
+      </c>
+    </row>
+    <row r="58" spans="1:5">
+      <c r="A58" s="5" t="s">
         <v>37</v>
       </c>
-      <c r="B42" s="3" t="s">
-        <v>2</v>
-      </c>
-      <c r="C42" s="5">
-        <v>10024</v>
-      </c>
-      <c r="D42" s="5">
-        <v>10017</v>
-      </c>
-      <c r="E42" s="7">
-        <v>-7</v>
-      </c>
-    </row>
-    <row r="43" spans="1:5">
-      <c r="A43" s="3" t="s">
+      <c r="B58" s="5" t="s">
+        <v>31</v>
+      </c>
+      <c r="C58" s="6">
+        <v>-41.85</v>
+      </c>
+      <c r="D58" s="6">
+        <v>65.89</v>
+      </c>
+      <c r="E58" s="8">
+        <v>107.74</v>
+      </c>
+    </row>
+    <row r="59" spans="1:5">
+      <c r="A59" s="5" t="s">
         <v>38</v>
       </c>
-      <c r="B43" s="3" t="s">
-        <v>2</v>
-      </c>
-      <c r="C43" s="5">
-        <v>480.35</v>
-      </c>
-      <c r="D43" s="5">
-        <v>493.5</v>
-      </c>
-      <c r="E43" s="6">
-        <v>13.15</v>
-      </c>
-    </row>
-    <row r="44" spans="1:5">
-      <c r="A44" s="3" t="s">
+      <c r="B59" s="5" t="s">
+        <v>31</v>
+      </c>
+      <c r="C59" s="6">
+        <v>-60.5</v>
+      </c>
+      <c r="D59" s="6">
+        <v>-70.94</v>
+      </c>
+      <c r="E59" s="7">
+        <v>-10.44</v>
+      </c>
+    </row>
+    <row r="60" spans="1:5">
+      <c r="A60" s="5" t="s">
         <v>39</v>
       </c>
-      <c r="B44" s="3" t="s">
-        <v>2</v>
-      </c>
-      <c r="C44" s="5">
-        <v>299.25</v>
-      </c>
-      <c r="D44" s="5">
-        <v>300.25</v>
-      </c>
-      <c r="E44" s="6">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="45" spans="1:5">
-      <c r="A45" s="3" t="s">
+      <c r="B60" s="5" t="s">
+        <v>31</v>
+      </c>
+      <c r="C60" s="6">
+        <v>-13.15</v>
+      </c>
+      <c r="D60" s="6">
+        <v>-24.23</v>
+      </c>
+      <c r="E60" s="7">
+        <v>-11.08</v>
+      </c>
+    </row>
+    <row r="61" spans="1:5">
+      <c r="A61" s="5" t="s">
         <v>40</v>
       </c>
-      <c r="B45" s="3" t="s">
-        <v>2</v>
-      </c>
-      <c r="C45" s="5">
-        <v>1751.4</v>
-      </c>
-      <c r="D45" s="5">
-        <v>1752.4</v>
-      </c>
-      <c r="E45" s="6">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="46" spans="1:5">
-      <c r="A46" s="3" t="s">
+      <c r="B61" s="5" t="s">
+        <v>31</v>
+      </c>
+      <c r="C61" s="6">
+        <v>-30.16</v>
+      </c>
+      <c r="D61" s="6">
+        <v>24.35</v>
+      </c>
+      <c r="E61" s="8">
+        <v>54.51</v>
+      </c>
+    </row>
+    <row r="62" spans="1:5">
+      <c r="A62" s="5" t="s">
         <v>41</v>
       </c>
-      <c r="B46" s="3" t="s">
-        <v>2</v>
-      </c>
-      <c r="C46" s="5">
-        <v>10732</v>
-      </c>
-      <c r="D46" s="5">
-        <v>10600</v>
-      </c>
-      <c r="E46" s="7">
-        <v>-132</v>
-      </c>
-    </row>
-    <row r="47" spans="1:5">
-      <c r="A47" s="3" t="s">
+      <c r="B62" s="5" t="s">
+        <v>31</v>
+      </c>
+      <c r="C62" s="6">
+        <v>-10.62</v>
+      </c>
+      <c r="D62" s="6">
+        <v>-4.65</v>
+      </c>
+      <c r="E62" s="8">
+        <v>5.97</v>
+      </c>
+    </row>
+    <row r="63" spans="1:5">
+      <c r="A63" s="5" t="s">
         <v>42</v>
       </c>
-      <c r="B47" s="3" t="s">
-        <v>2</v>
-      </c>
-      <c r="C47" s="5">
-        <v>970</v>
-      </c>
-      <c r="D47" s="5">
-        <v>963.1</v>
-      </c>
-      <c r="E47" s="7">
-        <v>-6.9</v>
-      </c>
-    </row>
-    <row r="48" spans="1:5">
-      <c r="A48" s="3" t="s">
+      <c r="B63" s="5" t="s">
+        <v>31</v>
+      </c>
+      <c r="C63" s="6">
+        <v>-33.75</v>
+      </c>
+      <c r="D63" s="6">
+        <v>75.48999999999999</v>
+      </c>
+      <c r="E63" s="8">
+        <v>109.24</v>
+      </c>
+    </row>
+    <row r="64" spans="1:5">
+      <c r="A64" s="5" t="s">
         <v>43</v>
       </c>
-      <c r="B48" s="3" t="s">
-        <v>2</v>
-      </c>
-      <c r="C48" s="5">
-        <v>182.2</v>
-      </c>
-      <c r="D48" s="5">
-        <v>181.55</v>
-      </c>
-      <c r="E48" s="7">
-        <v>-0.65</v>
-      </c>
-    </row>
-    <row r="49" spans="1:5">
-      <c r="A49" s="3" t="s">
-        <v>37</v>
-      </c>
-      <c r="B49" s="3" t="s">
-        <v>24</v>
-      </c>
-      <c r="C49" s="5">
-        <v>21.6</v>
-      </c>
-      <c r="D49" s="5">
-        <v>21.53</v>
-      </c>
-      <c r="E49" s="7">
-        <v>-0.07000000000000001</v>
-      </c>
-    </row>
-    <row r="50" spans="1:5">
-      <c r="A50" s="3" t="s">
-        <v>38</v>
-      </c>
-      <c r="B50" s="3" t="s">
-        <v>24</v>
-      </c>
-      <c r="C50" s="5">
-        <v>40.69</v>
-      </c>
-      <c r="D50" s="5">
-        <v>46.79</v>
-      </c>
-      <c r="E50" s="6">
-        <v>6.1</v>
-      </c>
-    </row>
-    <row r="51" spans="1:5">
-      <c r="A51" s="3" t="s">
-        <v>39</v>
-      </c>
-      <c r="B51" s="3" t="s">
-        <v>24</v>
-      </c>
-      <c r="C51" s="5">
-        <v>28.27</v>
-      </c>
-      <c r="D51" s="5">
-        <v>29.53</v>
-      </c>
-      <c r="E51" s="6">
-        <v>1.26</v>
-      </c>
-    </row>
-    <row r="52" spans="1:5">
-      <c r="A52" s="3" t="s">
-        <v>40</v>
-      </c>
-      <c r="B52" s="3" t="s">
-        <v>24</v>
-      </c>
-      <c r="C52" s="5">
-        <v>30.33</v>
-      </c>
-      <c r="D52" s="5">
-        <v>30.61</v>
-      </c>
-      <c r="E52" s="6">
-        <v>0.28</v>
-      </c>
-    </row>
-    <row r="53" spans="1:5">
-      <c r="A53" s="3" t="s">
-        <v>41</v>
-      </c>
-      <c r="B53" s="3" t="s">
-        <v>24</v>
-      </c>
-      <c r="C53" s="5">
-        <v>42.89</v>
-      </c>
-      <c r="D53" s="5">
-        <v>40.28</v>
-      </c>
-      <c r="E53" s="7">
-        <v>-2.61</v>
-      </c>
-    </row>
-    <row r="54" spans="1:5">
-      <c r="A54" s="3" t="s">
-        <v>42</v>
-      </c>
-      <c r="B54" s="3" t="s">
-        <v>24</v>
-      </c>
-      <c r="C54" s="5">
-        <v>38.77</v>
-      </c>
-      <c r="D54" s="5">
-        <v>37.52</v>
-      </c>
-      <c r="E54" s="7">
-        <v>-1.25</v>
-      </c>
-    </row>
-    <row r="55" spans="1:5">
-      <c r="A55" s="3" t="s">
-        <v>43</v>
-      </c>
-      <c r="B55" s="3" t="s">
-        <v>24</v>
-      </c>
-      <c r="C55" s="5">
-        <v>76.90000000000001</v>
-      </c>
-      <c r="D55" s="5">
-        <v>76.01000000000001</v>
-      </c>
-      <c r="E55" s="7">
-        <v>-0.89</v>
-      </c>
-    </row>
-    <row r="56" spans="1:5">
-      <c r="A56" s="3" t="s">
-        <v>37</v>
-      </c>
-      <c r="B56" s="3" t="s">
+      <c r="B64" s="5" t="s">
         <v>31</v>
       </c>
-      <c r="C56" s="5">
-        <v>29.94</v>
-      </c>
-      <c r="D56" s="5">
-        <v>-41.85</v>
-      </c>
-      <c r="E56" s="7">
-        <v>-71.79000000000001</v>
-      </c>
-    </row>
-    <row r="57" spans="1:5">
-      <c r="A57" s="3" t="s">
-        <v>38</v>
-      </c>
-      <c r="B57" s="3" t="s">
-        <v>31</v>
-      </c>
-      <c r="C57" s="5">
-        <v>-55.41</v>
-      </c>
-      <c r="D57" s="5">
-        <v>-60.5</v>
-      </c>
-      <c r="E57" s="7">
-        <v>-5.09</v>
-      </c>
-    </row>
-    <row r="58" spans="1:5">
-      <c r="A58" s="3" t="s">
-        <v>39</v>
-      </c>
-      <c r="B58" s="3" t="s">
-        <v>31</v>
-      </c>
-      <c r="C58" s="5">
-        <v>-23.9</v>
-      </c>
-      <c r="D58" s="5">
-        <v>-13.15</v>
-      </c>
-      <c r="E58" s="6">
-        <v>10.75</v>
-      </c>
-    </row>
-    <row r="59" spans="1:5">
-      <c r="A59" s="3" t="s">
-        <v>40</v>
-      </c>
-      <c r="B59" s="3" t="s">
-        <v>31</v>
-      </c>
-      <c r="C59" s="5">
-        <v>38.9</v>
-      </c>
-      <c r="D59" s="5">
-        <v>-30.16</v>
-      </c>
-      <c r="E59" s="7">
-        <v>-69.06</v>
-      </c>
-    </row>
-    <row r="60" spans="1:5">
-      <c r="A60" s="3" t="s">
-        <v>41</v>
-      </c>
-      <c r="B60" s="3" t="s">
-        <v>31</v>
-      </c>
-      <c r="C60" s="5">
-        <v>14.58</v>
-      </c>
-      <c r="D60" s="5">
-        <v>-10.62</v>
-      </c>
-      <c r="E60" s="7">
-        <v>-25.2</v>
-      </c>
-    </row>
-    <row r="61" spans="1:5">
-      <c r="A61" s="3" t="s">
-        <v>42</v>
-      </c>
-      <c r="B61" s="3" t="s">
-        <v>31</v>
-      </c>
-      <c r="C61" s="5">
-        <v>101.19</v>
-      </c>
-      <c r="D61" s="5">
-        <v>-33.75</v>
-      </c>
-      <c r="E61" s="7">
-        <v>-134.94</v>
-      </c>
-    </row>
-    <row r="62" spans="1:5">
-      <c r="A62" s="3" t="s">
-        <v>43</v>
-      </c>
-      <c r="B62" s="3" t="s">
-        <v>31</v>
-      </c>
-      <c r="C62" s="5">
-        <v>283.43</v>
-      </c>
-      <c r="D62" s="5">
+      <c r="C64" s="6">
         <v>-21.31</v>
       </c>
-      <c r="E62" s="7">
-        <v>-304.74</v>
+      <c r="D64" s="6">
+        <v>24.92</v>
+      </c>
+      <c r="E64" s="8">
+        <v>46.23</v>
       </c>
     </row>
   </sheetData>
@@ -2841,60 +2938,60 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:9" ht="28" customHeight="1">
-      <c r="A1" s="8" t="s">
+      <c r="A1" s="9" t="s">
         <v>1</v>
       </c>
-      <c r="B1" s="8" t="s">
-        <v>56</v>
-      </c>
-      <c r="C1" s="8" t="s">
+      <c r="B1" s="9" t="s">
+        <v>65</v>
+      </c>
+      <c r="C1" s="9" t="s">
+        <v>66</v>
+      </c>
+      <c r="D1" s="9" t="s">
+        <v>67</v>
+      </c>
+      <c r="E1" s="9" t="s">
+        <v>68</v>
+      </c>
+      <c r="F1" s="9" t="s">
+        <v>69</v>
+      </c>
+      <c r="G1" s="9" t="s">
+        <v>70</v>
+      </c>
+      <c r="H1" s="9" t="s">
+        <v>71</v>
+      </c>
+      <c r="I1" s="9" t="s">
+        <v>72</v>
+      </c>
+    </row>
+    <row r="2" spans="1:9">
+      <c r="A2" s="10" t="s">
+        <v>44</v>
+      </c>
+      <c r="B2" s="11">
+        <v>44.8</v>
+      </c>
+      <c r="C2" s="12">
+        <v>7</v>
+      </c>
+      <c r="D2" s="11">
+        <v>40.1</v>
+      </c>
+      <c r="E2" s="11">
+        <v>30</v>
+      </c>
+      <c r="F2" s="11">
+        <v>-2.8</v>
+      </c>
+      <c r="G2" s="11">
+        <v>0.7</v>
+      </c>
+      <c r="H2" s="11">
         <v>57</v>
       </c>
-      <c r="D1" s="8" t="s">
-        <v>58</v>
-      </c>
-      <c r="E1" s="8" t="s">
-        <v>59</v>
-      </c>
-      <c r="F1" s="8" t="s">
-        <v>60</v>
-      </c>
-      <c r="G1" s="8" t="s">
-        <v>61</v>
-      </c>
-      <c r="H1" s="8" t="s">
-        <v>62</v>
-      </c>
-      <c r="I1" s="8" t="s">
-        <v>63</v>
-      </c>
-    </row>
-    <row r="2" spans="1:9">
-      <c r="A2" s="9" t="s">
-        <v>44</v>
-      </c>
-      <c r="B2" s="10">
-        <v>44.8</v>
-      </c>
-      <c r="C2" s="11">
-        <v>7</v>
-      </c>
-      <c r="D2" s="10">
-        <v>40.3</v>
-      </c>
-      <c r="E2" s="10">
-        <v>30</v>
-      </c>
-      <c r="F2" s="10">
-        <v>-2.6</v>
-      </c>
-      <c r="G2" s="10">
-        <v>-1.2</v>
-      </c>
-      <c r="H2" s="10">
-        <v>57</v>
-      </c>
-      <c r="I2" s="10">
+      <c r="I2" s="11">
         <v>10</v>
       </c>
     </row>
@@ -2996,49 +3093,49 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:7">
-      <c r="A1" s="12" t="s">
+      <c r="A1" s="13" t="s">
         <v>37</v>
       </c>
-      <c r="B1" s="12" t="s">
+      <c r="B1" s="13" t="s">
         <v>41</v>
       </c>
-      <c r="C1" s="12" t="s">
+      <c r="C1" s="13" t="s">
         <v>38</v>
       </c>
-      <c r="D1" s="12" t="s">
+      <c r="D1" s="13" t="s">
         <v>43</v>
       </c>
-      <c r="E1" s="12" t="s">
+      <c r="E1" s="13" t="s">
         <v>42</v>
       </c>
-      <c r="F1" s="12" t="s">
+      <c r="F1" s="13" t="s">
         <v>40</v>
       </c>
-      <c r="G1" s="12" t="s">
+      <c r="G1" s="13" t="s">
         <v>39</v>
       </c>
     </row>
     <row r="2" spans="1:7">
-      <c r="A2" s="13">
-        <v>0.2439</v>
-      </c>
-      <c r="B2" s="13">
-        <v>0.186</v>
-      </c>
-      <c r="C2" s="13">
-        <v>0.1615</v>
-      </c>
-      <c r="D2" s="13">
-        <v>0.0496</v>
-      </c>
-      <c r="E2" s="13">
-        <v>0.0488</v>
-      </c>
-      <c r="F2" s="13">
-        <v>-0.0007000000000000001</v>
-      </c>
-      <c r="G2" s="13">
-        <v>-0.2384</v>
+      <c r="A2" s="14">
+        <v>0.2368</v>
+      </c>
+      <c r="B2" s="14">
+        <v>0.1888</v>
+      </c>
+      <c r="C2" s="14">
+        <v>0.1575</v>
+      </c>
+      <c r="D2" s="14">
+        <v>0.05599999999999999</v>
+      </c>
+      <c r="E2" s="14">
+        <v>0.0486</v>
+      </c>
+      <c r="F2" s="14">
+        <v>-0</v>
+      </c>
+      <c r="G2" s="14">
+        <v>-0.237</v>
       </c>
     </row>
   </sheetData>

--- a/BAJAJ_GROUP_Technical_Metrics.xlsx
+++ b/BAJAJ_GROUP_Technical_Metrics.xlsx
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="268" uniqueCount="73">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="274" uniqueCount="78">
   <si>
     <t>Symbol</t>
   </si>
@@ -187,19 +187,34 @@
     <t>Curr Value</t>
   </si>
   <si>
-    <t>RSI Oversold Recovery</t>
-  </si>
-  <si>
-    <t>29.5 → 30.1</t>
-  </si>
-  <si>
-    <t>🟢 BULLISH</t>
-  </si>
-  <si>
-    <t>29.5</t>
-  </si>
-  <si>
-    <t>30.1</t>
+    <t>RSI Overbought Exit</t>
+  </si>
+  <si>
+    <t>77.9 → 63.7</t>
+  </si>
+  <si>
+    <t>🔵 COOLING</t>
+  </si>
+  <si>
+    <t>77.9</t>
+  </si>
+  <si>
+    <t>63.7</t>
+  </si>
+  <si>
+    <t>Left 52W High Zone</t>
+  </si>
+  <si>
+    <t>0.0% → -6.3%</t>
+  </si>
+  <si>
+    <t>⚪ NEUTRAL</t>
+  </si>
+  <si>
+    <t>0.0%</t>
+  </si>
+  <si>
+    <t>-6.3%</t>
   </si>
   <si>
     <t>▶  NUMERIC METRIC CHANGES (vs Previous Run)</t>
@@ -251,7 +266,7 @@
     <numFmt numFmtId="166" formatCode="0.0"/>
     <numFmt numFmtId="167" formatCode="0.00%"/>
   </numFmts>
-  <fonts count="6">
+  <fonts count="7">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -285,7 +300,7 @@
     </font>
     <font>
       <sz val="11"/>
-      <color rgb="FF006100"/>
+      <color rgb="FF1F4E79"/>
       <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
@@ -297,8 +312,15 @@
       <family val="2"/>
       <scheme val="minor"/>
     </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF006100"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
   </fonts>
-  <fills count="9">
+  <fills count="10">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -325,13 +347,19 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFC6EFCE"/>
+        <fgColor rgb="FFDDEBF7"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="FFFFC7CE"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFC6EFCE"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -412,11 +440,11 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1"/>
     <xf numFmtId="165" fontId="5" fillId="6" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="165" fontId="4" fillId="5" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="3" fillId="7" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="165" fontId="6" fillId="7" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="3" fillId="8" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="8" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="9" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
     <xf numFmtId="166" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
@@ -425,7 +453,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="8" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="9" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="167" fontId="0" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
@@ -783,8 +811,8 @@
     <col min="13" max="13" width="10.7109375" customWidth="1"/>
     <col min="14" max="14" width="11.7109375" customWidth="1"/>
     <col min="15" max="15" width="10.7109375" customWidth="1"/>
-    <col min="16" max="17" width="9.7109375" customWidth="1"/>
-    <col min="18" max="19" width="10.7109375" customWidth="1"/>
+    <col min="16" max="16" width="9.7109375" customWidth="1"/>
+    <col min="17" max="19" width="10.7109375" customWidth="1"/>
     <col min="20" max="20" width="22.7109375" customWidth="1"/>
     <col min="21" max="21" width="9.7109375" customWidth="1"/>
     <col min="22" max="22" width="10.7109375" customWidth="1"/>
@@ -924,58 +952,58 @@
         <v>44</v>
       </c>
       <c r="C2">
-        <v>9884</v>
+        <v>9637</v>
       </c>
       <c r="D2">
-        <v>-1.33</v>
+        <v>-2.5</v>
       </c>
       <c r="E2">
         <v>12361</v>
       </c>
       <c r="F2">
-        <v>8559.049999999999</v>
+        <v>8599.48</v>
       </c>
       <c r="G2">
-        <v>-20.04</v>
+        <v>-22.04</v>
       </c>
       <c r="H2">
-        <v>15.48</v>
+        <v>12.06</v>
       </c>
       <c r="I2">
-        <v>-8.57</v>
+        <v>-11.38</v>
       </c>
       <c r="J2">
-        <v>-17.07</v>
+        <v>-18.33</v>
       </c>
       <c r="K2">
-        <v>-2.75</v>
+        <v>-5.1</v>
       </c>
       <c r="L2">
-        <v>16.19</v>
+        <v>12.59</v>
       </c>
       <c r="M2">
-        <v>23.68</v>
+        <v>23.14</v>
       </c>
       <c r="N2">
         <v>71</v>
       </c>
       <c r="O2">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="P2">
-        <v>10168.8</v>
+        <v>9921.4</v>
       </c>
       <c r="Q2">
-        <v>11121.9</v>
+        <v>11009.75</v>
       </c>
       <c r="R2">
-        <v>11497.63</v>
+        <v>11462.89</v>
       </c>
       <c r="S2">
-        <v>10157.26</v>
+        <v>10161.9</v>
       </c>
       <c r="T2">
-        <v>-2.69</v>
+        <v>-5.17</v>
       </c>
       <c r="U2" t="s">
         <v>45</v>
@@ -990,43 +1018,43 @@
         <v>1</v>
       </c>
       <c r="Y2">
-        <v>20.18</v>
+        <v>17.92</v>
       </c>
       <c r="Z2">
-        <v>-411.42</v>
+        <v>-460.1</v>
       </c>
       <c r="AA2">
-        <v>-240.75</v>
+        <v>-284.62</v>
       </c>
       <c r="AB2">
-        <v>-170.68</v>
+        <v>-175.48</v>
       </c>
       <c r="AC2">
         <v>0</v>
       </c>
       <c r="AD2">
-        <v>1.31</v>
+        <v>0</v>
       </c>
       <c r="AE2">
-        <v>245.16</v>
+        <v>246</v>
       </c>
       <c r="AF2">
-        <v>65.89</v>
+        <v>-29.09</v>
       </c>
       <c r="AG2">
-        <v>12408.08</v>
+        <v>12404.21</v>
       </c>
       <c r="AH2">
-        <v>9835.719999999999</v>
+        <v>9615.290000000001</v>
       </c>
       <c r="AI2">
-        <v>10597.47</v>
+        <v>10503.51</v>
       </c>
       <c r="AJ2" t="s">
         <v>47</v>
       </c>
       <c r="AK2">
-        <v>74.98999999999999</v>
+        <v>77.77</v>
       </c>
     </row>
     <row r="3" spans="1:37">
@@ -1037,58 +1065,58 @@
         <v>44</v>
       </c>
       <c r="C3">
-        <v>483</v>
+        <v>489.15</v>
       </c>
       <c r="D3">
-        <v>-2.13</v>
+        <v>1.27</v>
       </c>
       <c r="E3">
         <v>670.25</v>
       </c>
       <c r="F3">
-        <v>239.33</v>
+        <v>241.91</v>
       </c>
       <c r="G3">
-        <v>-27.94</v>
+        <v>-27.02</v>
       </c>
       <c r="H3">
-        <v>101.81</v>
+        <v>102.2</v>
       </c>
       <c r="I3">
-        <v>-2.03</v>
+        <v>-1.29</v>
       </c>
       <c r="J3">
-        <v>-6.68</v>
+        <v>-7.01</v>
       </c>
       <c r="K3">
-        <v>-21.32</v>
+        <v>-23.99</v>
       </c>
       <c r="L3">
-        <v>104.61</v>
+        <v>104.38</v>
       </c>
       <c r="M3">
-        <v>15.75</v>
+        <v>16.05</v>
       </c>
       <c r="N3">
-        <v>85</v>
+        <v>99</v>
       </c>
       <c r="O3">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="P3">
-        <v>489.89</v>
+        <v>488.61</v>
       </c>
       <c r="Q3">
-        <v>502.78</v>
+        <v>501.53</v>
       </c>
       <c r="R3">
-        <v>504.65</v>
+        <v>503.81</v>
       </c>
       <c r="S3">
-        <v>455.59</v>
+        <v>456.79</v>
       </c>
       <c r="T3">
-        <v>6.02</v>
+        <v>7.08</v>
       </c>
       <c r="U3" t="s">
         <v>45</v>
@@ -1103,34 +1131,34 @@
         <v>2</v>
       </c>
       <c r="Y3">
-        <v>42.99</v>
+        <v>45.77</v>
       </c>
       <c r="Z3">
-        <v>-5.41</v>
+        <v>-5.4</v>
       </c>
       <c r="AA3">
-        <v>-3.86</v>
+        <v>-4.17</v>
       </c>
       <c r="AB3">
-        <v>-1.55</v>
+        <v>-1.23</v>
       </c>
       <c r="AC3">
-        <v>31.9</v>
+        <v>44.18</v>
       </c>
       <c r="AD3">
-        <v>35.82</v>
+        <v>38.65</v>
       </c>
       <c r="AE3">
-        <v>18.36</v>
+        <v>19.16</v>
       </c>
       <c r="AF3">
-        <v>-70.94</v>
+        <v>60.11</v>
       </c>
       <c r="AG3">
-        <v>529.33</v>
+        <v>528.1799999999999</v>
       </c>
       <c r="AH3">
-        <v>476.23</v>
+        <v>474.88</v>
       </c>
       <c r="AI3">
         <v>460.99</v>
@@ -1139,7 +1167,7 @@
         <v>48</v>
       </c>
       <c r="AK3">
-        <v>37.5</v>
+        <v>32.93</v>
       </c>
     </row>
     <row r="4" spans="1:37">
@@ -1150,58 +1178,58 @@
         <v>44</v>
       </c>
       <c r="C4">
-        <v>300.7</v>
+        <v>290.05</v>
       </c>
       <c r="D4">
-        <v>0.15</v>
+        <v>-3.54</v>
       </c>
       <c r="E4">
         <v>548</v>
       </c>
       <c r="F4">
-        <v>299.25</v>
+        <v>290.05</v>
       </c>
       <c r="G4">
-        <v>-45.13</v>
+        <v>-47.07</v>
       </c>
       <c r="H4">
-        <v>0.48</v>
+        <v>0</v>
       </c>
       <c r="I4">
-        <v>-2.95</v>
+        <v>-4.4</v>
       </c>
       <c r="J4">
-        <v>-9.199999999999999</v>
+        <v>-15.21</v>
       </c>
       <c r="K4">
-        <v>-6.31</v>
+        <v>-11.23</v>
       </c>
       <c r="L4">
-        <v>-45.11</v>
+        <v>-46.68</v>
       </c>
       <c r="M4">
-        <v>-23.7</v>
+        <v>-23.99</v>
       </c>
       <c r="N4">
         <v>15</v>
       </c>
       <c r="O4">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="P4">
-        <v>300.68</v>
+        <v>298.01</v>
       </c>
       <c r="Q4">
-        <v>319.96</v>
+        <v>317.47</v>
       </c>
       <c r="R4">
-        <v>335.22</v>
+        <v>334.48</v>
       </c>
       <c r="S4">
-        <v>365.35</v>
+        <v>364.4</v>
       </c>
       <c r="T4">
-        <v>-17.69</v>
+        <v>-20.4</v>
       </c>
       <c r="U4" t="s">
         <v>45</v>
@@ -1216,43 +1244,43 @@
         <v>0</v>
       </c>
       <c r="Y4">
-        <v>30.13</v>
+        <v>24.79</v>
       </c>
       <c r="Z4">
-        <v>-9.82</v>
+        <v>-10.69</v>
       </c>
       <c r="AA4">
-        <v>-7.79</v>
+        <v>-8.369999999999999</v>
       </c>
       <c r="AB4">
-        <v>-2.03</v>
+        <v>-2.32</v>
       </c>
       <c r="AC4">
         <v>5.81</v>
       </c>
       <c r="AD4">
-        <v>2.72</v>
+        <v>4.66</v>
       </c>
       <c r="AE4">
-        <v>9.130000000000001</v>
+        <v>9.31</v>
       </c>
       <c r="AF4">
-        <v>-24.23</v>
+        <v>18.01</v>
       </c>
       <c r="AG4">
-        <v>347.5</v>
+        <v>346.39</v>
       </c>
       <c r="AH4">
-        <v>292.43</v>
+        <v>288.55</v>
       </c>
       <c r="AI4">
-        <v>327.68</v>
+        <v>322.52</v>
       </c>
       <c r="AJ4" t="s">
         <v>47</v>
       </c>
       <c r="AK4">
-        <v>43.64</v>
+        <v>48.25</v>
       </c>
     </row>
     <row r="5" spans="1:37">
@@ -1263,10 +1291,10 @@
         <v>44</v>
       </c>
       <c r="C5">
-        <v>1743.3</v>
+        <v>1708</v>
       </c>
       <c r="D5">
-        <v>-0.52</v>
+        <v>-2.02</v>
       </c>
       <c r="E5">
         <v>2176.6</v>
@@ -1275,46 +1303,46 @@
         <v>1631.8</v>
       </c>
       <c r="G5">
-        <v>-19.91</v>
+        <v>-21.53</v>
       </c>
       <c r="H5">
-        <v>6.83</v>
+        <v>4.67</v>
       </c>
       <c r="I5">
-        <v>0.05</v>
+        <v>-1.33</v>
       </c>
       <c r="J5">
-        <v>-11.51</v>
+        <v>-11.9</v>
       </c>
       <c r="K5">
-        <v>-6.02</v>
+        <v>-9.869999999999999</v>
       </c>
       <c r="L5">
-        <v>-13.14</v>
+        <v>-14.64</v>
       </c>
       <c r="M5">
-        <v>-0</v>
+        <v>-0.5</v>
       </c>
       <c r="N5">
         <v>29</v>
       </c>
       <c r="O5">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="P5">
-        <v>1742.14</v>
+        <v>1737.54</v>
       </c>
       <c r="Q5">
-        <v>1819.07</v>
+        <v>1807.57</v>
       </c>
       <c r="R5">
-        <v>1933.01</v>
+        <v>1928.61</v>
       </c>
       <c r="S5">
-        <v>1880.28</v>
+        <v>1878.69</v>
       </c>
       <c r="T5">
-        <v>-7.29</v>
+        <v>-9.09</v>
       </c>
       <c r="U5" t="s">
         <v>45</v>
@@ -1329,43 +1357,43 @@
         <v>1</v>
       </c>
       <c r="Y5">
-        <v>29.46</v>
+        <v>25.47</v>
       </c>
       <c r="Z5">
-        <v>-56.65</v>
+        <v>-57.91</v>
       </c>
       <c r="AA5">
-        <v>-52.7</v>
+        <v>-53.74</v>
       </c>
       <c r="AB5">
-        <v>-3.96</v>
+        <v>-4.17</v>
       </c>
       <c r="AC5">
-        <v>52.02</v>
+        <v>36.6</v>
       </c>
       <c r="AD5">
-        <v>36.38</v>
+        <v>42.2</v>
       </c>
       <c r="AE5">
-        <v>34.83</v>
+        <v>35.44</v>
       </c>
       <c r="AF5">
-        <v>24.35</v>
+        <v>45.15</v>
       </c>
       <c r="AG5">
-        <v>1965.24</v>
+        <v>1950.47</v>
       </c>
       <c r="AH5">
-        <v>1672.9</v>
+        <v>1664.66</v>
       </c>
       <c r="AI5">
-        <v>1830.94</v>
+        <v>1825.61</v>
       </c>
       <c r="AJ5" t="s">
         <v>47</v>
       </c>
       <c r="AK5">
-        <v>70.48999999999999</v>
+        <v>69.98</v>
       </c>
     </row>
     <row r="6" spans="1:37">
@@ -1376,10 +1404,10 @@
         <v>44</v>
       </c>
       <c r="C6">
-        <v>10662</v>
+        <v>10600</v>
       </c>
       <c r="D6">
-        <v>0.58</v>
+        <v>-0.58</v>
       </c>
       <c r="E6">
         <v>13144</v>
@@ -1388,46 +1416,46 @@
         <v>8746</v>
       </c>
       <c r="G6">
-        <v>-18.88</v>
+        <v>-19.35</v>
       </c>
       <c r="H6">
-        <v>21.91</v>
+        <v>21.2</v>
       </c>
       <c r="I6">
-        <v>0.58</v>
+        <v>-1.74</v>
       </c>
       <c r="J6">
-        <v>-4.48</v>
+        <v>-3.25</v>
       </c>
       <c r="K6">
-        <v>3.15</v>
+        <v>0.18</v>
       </c>
       <c r="L6">
-        <v>-11.12</v>
+        <v>-10.31</v>
       </c>
       <c r="M6">
-        <v>18.88</v>
+        <v>18.86</v>
       </c>
       <c r="N6">
         <v>57</v>
       </c>
       <c r="O6">
-        <v>55</v>
+        <v>59</v>
       </c>
       <c r="P6">
-        <v>10689.6</v>
+        <v>10652</v>
       </c>
       <c r="Q6">
-        <v>10966</v>
+        <v>10943.7</v>
       </c>
       <c r="R6">
-        <v>11180.62</v>
+        <v>11176</v>
       </c>
       <c r="S6">
-        <v>10669.87</v>
+        <v>10668.16</v>
       </c>
       <c r="T6">
-        <v>-0.07000000000000001</v>
+        <v>-0.64</v>
       </c>
       <c r="U6" t="s">
         <v>45</v>
@@ -1442,34 +1470,34 @@
         <v>1</v>
       </c>
       <c r="Y6">
-        <v>42.07</v>
+        <v>40.75</v>
       </c>
       <c r="Z6">
-        <v>-140.13</v>
+        <v>-147.46</v>
       </c>
       <c r="AA6">
-        <v>-94.48999999999999</v>
+        <v>-105.08</v>
       </c>
       <c r="AB6">
-        <v>-45.64</v>
+        <v>-42.38</v>
       </c>
       <c r="AC6">
-        <v>17.78</v>
+        <v>13.9</v>
       </c>
       <c r="AD6">
-        <v>18.54</v>
+        <v>15.91</v>
       </c>
       <c r="AE6">
-        <v>258.46</v>
+        <v>258.57</v>
       </c>
       <c r="AF6">
-        <v>-4.65</v>
+        <v>32.58</v>
       </c>
       <c r="AG6">
-        <v>11471.5</v>
+        <v>11473.13</v>
       </c>
       <c r="AH6">
-        <v>10460.5</v>
+        <v>10414.27</v>
       </c>
       <c r="AI6">
         <v>11368.55</v>
@@ -1478,7 +1506,7 @@
         <v>47</v>
       </c>
       <c r="AK6">
-        <v>36.04</v>
+        <v>34.46</v>
       </c>
     </row>
     <row r="7" spans="1:37">
@@ -1489,10 +1517,10 @@
         <v>44</v>
       </c>
       <c r="C7">
-        <v>963.85</v>
+        <v>955.95</v>
       </c>
       <c r="D7">
-        <v>0.08</v>
+        <v>-0.82</v>
       </c>
       <c r="E7">
         <v>1158.8</v>
@@ -1501,46 +1529,46 @@
         <v>801.55</v>
       </c>
       <c r="G7">
-        <v>-16.82</v>
+        <v>-17.51</v>
       </c>
       <c r="H7">
-        <v>20.25</v>
+        <v>19.26</v>
       </c>
       <c r="I7">
-        <v>-1.02</v>
+        <v>-0.36</v>
       </c>
       <c r="J7">
-        <v>-9.109999999999999</v>
+        <v>-9.82</v>
       </c>
       <c r="K7">
-        <v>-4.61</v>
+        <v>-4.77</v>
       </c>
       <c r="L7">
-        <v>-2.41</v>
+        <v>-3.42</v>
       </c>
       <c r="M7">
-        <v>4.86</v>
+        <v>4.73</v>
       </c>
       <c r="N7">
         <v>43</v>
       </c>
       <c r="O7">
-        <v>54</v>
+        <v>58</v>
       </c>
       <c r="P7">
-        <v>960.9299999999999</v>
+        <v>960.24</v>
       </c>
       <c r="Q7">
-        <v>1002.89</v>
+        <v>997.98</v>
       </c>
       <c r="R7">
-        <v>1054.18</v>
+        <v>1052.33</v>
       </c>
       <c r="S7">
-        <v>975.75</v>
+        <v>975.53</v>
       </c>
       <c r="T7">
-        <v>-1.22</v>
+        <v>-2.01</v>
       </c>
       <c r="U7" t="s">
         <v>45</v>
@@ -1555,34 +1583,34 @@
         <v>1</v>
       </c>
       <c r="Y7">
-        <v>37.75</v>
+        <v>36.21</v>
       </c>
       <c r="Z7">
-        <v>-25.67</v>
+        <v>-25.86</v>
       </c>
       <c r="AA7">
-        <v>-22.27</v>
+        <v>-22.99</v>
       </c>
       <c r="AB7">
-        <v>-3.4</v>
+        <v>-2.88</v>
       </c>
       <c r="AC7">
-        <v>37.6</v>
+        <v>31.19</v>
       </c>
       <c r="AD7">
-        <v>29.44</v>
+        <v>32.5</v>
       </c>
       <c r="AE7">
-        <v>26.04</v>
+        <v>25.43</v>
       </c>
       <c r="AF7">
-        <v>75.48999999999999</v>
+        <v>38.49</v>
       </c>
       <c r="AG7">
-        <v>1069.21</v>
+        <v>1062.85</v>
       </c>
       <c r="AH7">
-        <v>936.5700000000001</v>
+        <v>933.11</v>
       </c>
       <c r="AI7">
         <v>1020.6</v>
@@ -1591,7 +1619,7 @@
         <v>47</v>
       </c>
       <c r="AK7">
-        <v>35.71</v>
+        <v>32.37</v>
       </c>
     </row>
     <row r="8" spans="1:37">
@@ -1602,10 +1630,10 @@
         <v>44</v>
       </c>
       <c r="C8">
-        <v>185.92</v>
+        <v>174.29</v>
       </c>
       <c r="D8">
-        <v>2.41</v>
+        <v>-6.26</v>
       </c>
       <c r="E8">
         <v>185.92</v>
@@ -1614,46 +1642,46 @@
         <v>115.96</v>
       </c>
       <c r="G8">
-        <v>0</v>
+        <v>-6.26</v>
       </c>
       <c r="H8">
-        <v>60.33</v>
+        <v>50.3</v>
       </c>
       <c r="I8">
-        <v>7.79</v>
+        <v>-3.24</v>
       </c>
       <c r="J8">
-        <v>38.29</v>
+        <v>27.31</v>
       </c>
       <c r="K8">
-        <v>42.69</v>
+        <v>33.27</v>
       </c>
       <c r="L8">
-        <v>35.17</v>
+        <v>22.3</v>
       </c>
       <c r="M8">
-        <v>5.6</v>
+        <v>4.79</v>
       </c>
       <c r="N8">
-        <v>99</v>
+        <v>85</v>
       </c>
       <c r="O8">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="P8">
-        <v>180.49</v>
+        <v>179.32</v>
       </c>
       <c r="Q8">
-        <v>155.09</v>
+        <v>156.92</v>
       </c>
       <c r="R8">
-        <v>144.7</v>
+        <v>145.4</v>
       </c>
       <c r="S8">
-        <v>135.89</v>
+        <v>136.11</v>
       </c>
       <c r="T8">
-        <v>36.81</v>
+        <v>28.05</v>
       </c>
       <c r="U8" t="s">
         <v>46</v>
@@ -1668,34 +1696,34 @@
         <v>3</v>
       </c>
       <c r="Y8">
-        <v>77.86</v>
+        <v>63.74</v>
       </c>
       <c r="Z8">
-        <v>12</v>
+        <v>11.52</v>
       </c>
       <c r="AA8">
-        <v>8.359999999999999</v>
+        <v>8.99</v>
       </c>
       <c r="AB8">
-        <v>3.64</v>
+        <v>2.52</v>
       </c>
       <c r="AC8">
-        <v>82.34999999999999</v>
+        <v>70.95999999999999</v>
       </c>
       <c r="AD8">
-        <v>81.65000000000001</v>
+        <v>77.09999999999999</v>
       </c>
       <c r="AE8">
-        <v>8.42</v>
+        <v>8.890000000000001</v>
       </c>
       <c r="AF8">
-        <v>24.92</v>
+        <v>-20.14</v>
       </c>
       <c r="AG8">
-        <v>193.89</v>
+        <v>195.72</v>
       </c>
       <c r="AH8">
-        <v>116.28</v>
+        <v>118.12</v>
       </c>
       <c r="AI8">
         <v>159.98</v>
@@ -1704,7 +1732,7 @@
         <v>48</v>
       </c>
       <c r="AK8">
-        <v>57.39</v>
+        <v>54.09</v>
       </c>
     </row>
   </sheetData>
@@ -1845,7 +1873,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:F64"/>
+  <dimension ref="A1:F65"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="16.7109375" customWidth="1"/>
@@ -1885,7 +1913,7 @@
     </row>
     <row r="3" spans="1:6">
       <c r="A3" s="4" t="s">
-        <v>39</v>
+        <v>43</v>
       </c>
       <c r="B3" s="4" t="s">
         <v>55</v>
@@ -1903,1022 +1931,1042 @@
         <v>59</v>
       </c>
     </row>
-    <row r="5" spans="1:6">
-      <c r="A5" s="2" t="s">
+    <row r="4" spans="1:6">
+      <c r="A4" s="4" t="s">
+        <v>43</v>
+      </c>
+      <c r="B4" s="4" t="s">
         <v>60</v>
       </c>
-      <c r="B5" s="2"/>
-      <c r="C5" s="2"/>
-      <c r="D5" s="2"/>
-      <c r="E5" s="2"/>
+      <c r="C4" s="4" t="s">
+        <v>61</v>
+      </c>
+      <c r="D4" s="4" t="s">
+        <v>62</v>
+      </c>
+      <c r="E4" s="4" t="s">
+        <v>63</v>
+      </c>
+      <c r="F4" s="4" t="s">
+        <v>64</v>
+      </c>
     </row>
     <row r="6" spans="1:6">
-      <c r="A6" s="3" t="s">
+      <c r="A6" s="2" t="s">
+        <v>65</v>
+      </c>
+      <c r="B6" s="2"/>
+      <c r="C6" s="2"/>
+      <c r="D6" s="2"/>
+      <c r="E6" s="2"/>
+    </row>
+    <row r="7" spans="1:6">
+      <c r="A7" s="3" t="s">
         <v>0</v>
       </c>
-      <c r="B6" s="3" t="s">
-        <v>61</v>
-      </c>
-      <c r="C6" s="3" t="s">
-        <v>62</v>
-      </c>
-      <c r="D6" s="3" t="s">
-        <v>63</v>
-      </c>
-      <c r="E6" s="3" t="s">
-        <v>64</v>
-      </c>
-    </row>
-    <row r="7" spans="1:6">
-      <c r="A7" s="5" t="s">
-        <v>37</v>
-      </c>
-      <c r="B7" s="5" t="s">
-        <v>9</v>
-      </c>
-      <c r="C7" s="6">
-        <v>-15.96</v>
-      </c>
-      <c r="D7" s="6">
-        <v>-17.07</v>
-      </c>
-      <c r="E7" s="7">
-        <v>-1.11</v>
+      <c r="B7" s="3" t="s">
+        <v>66</v>
+      </c>
+      <c r="C7" s="3" t="s">
+        <v>67</v>
+      </c>
+      <c r="D7" s="3" t="s">
+        <v>68</v>
+      </c>
+      <c r="E7" s="3" t="s">
+        <v>69</v>
       </c>
     </row>
     <row r="8" spans="1:6">
       <c r="A8" s="5" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="B8" s="5" t="s">
         <v>9</v>
       </c>
       <c r="C8" s="6">
-        <v>-3.04</v>
+        <v>-17.07</v>
       </c>
       <c r="D8" s="6">
-        <v>-6.68</v>
+        <v>-18.33</v>
       </c>
       <c r="E8" s="7">
-        <v>-3.64</v>
+        <v>-1.26</v>
       </c>
     </row>
     <row r="9" spans="1:6">
       <c r="A9" s="5" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="B9" s="5" t="s">
         <v>9</v>
       </c>
       <c r="C9" s="6">
-        <v>-10.16</v>
+        <v>-6.68</v>
       </c>
       <c r="D9" s="6">
-        <v>-9.199999999999999</v>
-      </c>
-      <c r="E9" s="8">
-        <v>0.96</v>
+        <v>-7.01</v>
+      </c>
+      <c r="E9" s="7">
+        <v>-0.33</v>
       </c>
     </row>
     <row r="10" spans="1:6">
       <c r="A10" s="5" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="B10" s="5" t="s">
         <v>9</v>
       </c>
       <c r="C10" s="6">
-        <v>-12.03</v>
+        <v>-9.199999999999999</v>
       </c>
       <c r="D10" s="6">
-        <v>-11.51</v>
-      </c>
-      <c r="E10" s="8">
-        <v>0.52</v>
+        <v>-15.21</v>
+      </c>
+      <c r="E10" s="7">
+        <v>-6.01</v>
       </c>
     </row>
     <row r="11" spans="1:6">
       <c r="A11" s="5" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="B11" s="5" t="s">
         <v>9</v>
       </c>
       <c r="C11" s="6">
-        <v>-5.06</v>
+        <v>-11.51</v>
       </c>
       <c r="D11" s="6">
-        <v>-4.48</v>
-      </c>
-      <c r="E11" s="8">
-        <v>0.58</v>
+        <v>-11.9</v>
+      </c>
+      <c r="E11" s="7">
+        <v>-0.39</v>
       </c>
     </row>
     <row r="12" spans="1:6">
       <c r="A12" s="5" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="B12" s="5" t="s">
         <v>9</v>
       </c>
       <c r="C12" s="6">
-        <v>-8.19</v>
+        <v>-4.48</v>
       </c>
       <c r="D12" s="6">
-        <v>-9.109999999999999</v>
-      </c>
-      <c r="E12" s="7">
-        <v>-0.92</v>
+        <v>-3.25</v>
+      </c>
+      <c r="E12" s="8">
+        <v>1.23</v>
       </c>
     </row>
     <row r="13" spans="1:6">
       <c r="A13" s="5" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="B13" s="5" t="s">
         <v>9</v>
       </c>
       <c r="C13" s="6">
-        <v>36.53</v>
+        <v>-9.109999999999999</v>
       </c>
       <c r="D13" s="6">
-        <v>38.29</v>
-      </c>
-      <c r="E13" s="8">
-        <v>1.76</v>
+        <v>-9.82</v>
+      </c>
+      <c r="E13" s="7">
+        <v>-0.71</v>
       </c>
     </row>
     <row r="14" spans="1:6">
       <c r="A14" s="5" t="s">
-        <v>37</v>
+        <v>43</v>
       </c>
       <c r="B14" s="5" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="C14" s="6">
-        <v>-9.130000000000001</v>
+        <v>38.29</v>
       </c>
       <c r="D14" s="6">
-        <v>-8.57</v>
-      </c>
-      <c r="E14" s="8">
-        <v>0.5600000000000001</v>
+        <v>27.31</v>
+      </c>
+      <c r="E14" s="7">
+        <v>-10.98</v>
       </c>
     </row>
     <row r="15" spans="1:6">
       <c r="A15" s="5" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="B15" s="5" t="s">
         <v>8</v>
       </c>
       <c r="C15" s="6">
-        <v>2.8</v>
+        <v>-8.57</v>
       </c>
       <c r="D15" s="6">
-        <v>-2.03</v>
+        <v>-11.38</v>
       </c>
       <c r="E15" s="7">
-        <v>-4.83</v>
+        <v>-2.81</v>
       </c>
     </row>
     <row r="16" spans="1:6">
       <c r="A16" s="5" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="B16" s="5" t="s">
         <v>8</v>
       </c>
       <c r="C16" s="6">
-        <v>-4.58</v>
+        <v>-2.03</v>
       </c>
       <c r="D16" s="6">
-        <v>-2.95</v>
+        <v>-1.29</v>
       </c>
       <c r="E16" s="8">
-        <v>1.63</v>
+        <v>0.74</v>
       </c>
     </row>
     <row r="17" spans="1:5">
       <c r="A17" s="5" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="B17" s="5" t="s">
         <v>8</v>
       </c>
       <c r="C17" s="6">
-        <v>0.02</v>
+        <v>-2.95</v>
       </c>
       <c r="D17" s="6">
-        <v>0.05</v>
-      </c>
-      <c r="E17" s="8">
-        <v>0.03</v>
+        <v>-4.4</v>
+      </c>
+      <c r="E17" s="7">
+        <v>-1.45</v>
       </c>
     </row>
     <row r="18" spans="1:5">
       <c r="A18" s="5" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="B18" s="5" t="s">
         <v>8</v>
       </c>
       <c r="C18" s="6">
-        <v>-1.85</v>
+        <v>0.05</v>
       </c>
       <c r="D18" s="6">
-        <v>0.58</v>
-      </c>
-      <c r="E18" s="8">
-        <v>2.43</v>
+        <v>-1.33</v>
+      </c>
+      <c r="E18" s="7">
+        <v>-1.38</v>
       </c>
     </row>
     <row r="19" spans="1:5">
       <c r="A19" s="5" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="B19" s="5" t="s">
         <v>8</v>
       </c>
       <c r="C19" s="6">
-        <v>-2.22</v>
+        <v>0.58</v>
       </c>
       <c r="D19" s="6">
-        <v>-1.02</v>
-      </c>
-      <c r="E19" s="8">
-        <v>1.2</v>
+        <v>-1.74</v>
+      </c>
+      <c r="E19" s="7">
+        <v>-2.32</v>
       </c>
     </row>
     <row r="20" spans="1:5">
       <c r="A20" s="5" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="B20" s="5" t="s">
         <v>8</v>
       </c>
       <c r="C20" s="6">
-        <v>6.15</v>
+        <v>-1.02</v>
       </c>
       <c r="D20" s="6">
-        <v>7.79</v>
+        <v>-0.36</v>
       </c>
       <c r="E20" s="8">
-        <v>1.64</v>
+        <v>0.66</v>
       </c>
     </row>
     <row r="21" spans="1:5">
       <c r="A21" s="5" t="s">
-        <v>37</v>
+        <v>43</v>
       </c>
       <c r="B21" s="5" t="s">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="C21" s="6">
-        <v>17.05</v>
+        <v>7.79</v>
       </c>
       <c r="D21" s="6">
-        <v>16.19</v>
+        <v>-3.24</v>
       </c>
       <c r="E21" s="7">
-        <v>-0.86</v>
+        <v>-11.03</v>
       </c>
     </row>
     <row r="22" spans="1:5">
       <c r="A22" s="5" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="B22" s="5" t="s">
         <v>11</v>
       </c>
       <c r="C22" s="6">
-        <v>108.32</v>
+        <v>16.19</v>
       </c>
       <c r="D22" s="6">
-        <v>104.61</v>
+        <v>12.59</v>
       </c>
       <c r="E22" s="7">
-        <v>-3.71</v>
+        <v>-3.6</v>
       </c>
     </row>
     <row r="23" spans="1:5">
       <c r="A23" s="5" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="B23" s="5" t="s">
         <v>11</v>
       </c>
       <c r="C23" s="6">
-        <v>-44.91</v>
+        <v>104.61</v>
       </c>
       <c r="D23" s="6">
-        <v>-45.11</v>
+        <v>104.38</v>
       </c>
       <c r="E23" s="7">
-        <v>-0.2</v>
+        <v>-0.23</v>
       </c>
     </row>
     <row r="24" spans="1:5">
       <c r="A24" s="5" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="B24" s="5" t="s">
         <v>11</v>
       </c>
       <c r="C24" s="6">
-        <v>-12.66</v>
+        <v>-45.11</v>
       </c>
       <c r="D24" s="6">
-        <v>-13.14</v>
+        <v>-46.68</v>
       </c>
       <c r="E24" s="7">
-        <v>-0.48</v>
+        <v>-1.57</v>
       </c>
     </row>
     <row r="25" spans="1:5">
       <c r="A25" s="5" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="B25" s="5" t="s">
         <v>11</v>
       </c>
       <c r="C25" s="6">
-        <v>-13.45</v>
+        <v>-13.14</v>
       </c>
       <c r="D25" s="6">
-        <v>-11.12</v>
-      </c>
-      <c r="E25" s="8">
-        <v>2.33</v>
+        <v>-14.64</v>
+      </c>
+      <c r="E25" s="7">
+        <v>-1.5</v>
       </c>
     </row>
     <row r="26" spans="1:5">
       <c r="A26" s="5" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="B26" s="5" t="s">
         <v>11</v>
       </c>
       <c r="C26" s="6">
-        <v>-3.58</v>
+        <v>-11.12</v>
       </c>
       <c r="D26" s="6">
-        <v>-2.41</v>
+        <v>-10.31</v>
       </c>
       <c r="E26" s="8">
-        <v>1.17</v>
+        <v>0.8100000000000001</v>
       </c>
     </row>
     <row r="27" spans="1:5">
       <c r="A27" s="5" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="B27" s="5" t="s">
         <v>11</v>
       </c>
       <c r="C27" s="6">
-        <v>37.07</v>
+        <v>-2.41</v>
       </c>
       <c r="D27" s="6">
-        <v>35.17</v>
+        <v>-3.42</v>
       </c>
       <c r="E27" s="7">
-        <v>-1.9</v>
+        <v>-1.01</v>
       </c>
     </row>
     <row r="28" spans="1:5">
       <c r="A28" s="5" t="s">
-        <v>37</v>
+        <v>43</v>
       </c>
       <c r="B28" s="5" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="C28" s="6">
-        <v>-0.91</v>
+        <v>35.17</v>
       </c>
       <c r="D28" s="6">
-        <v>-2.75</v>
+        <v>22.3</v>
       </c>
       <c r="E28" s="7">
-        <v>-1.84</v>
+        <v>-12.87</v>
       </c>
     </row>
     <row r="29" spans="1:5">
       <c r="A29" s="5" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="B29" s="5" t="s">
         <v>10</v>
       </c>
       <c r="C29" s="6">
-        <v>-20.44</v>
+        <v>-2.75</v>
       </c>
       <c r="D29" s="6">
-        <v>-21.32</v>
+        <v>-5.1</v>
       </c>
       <c r="E29" s="7">
-        <v>-0.88</v>
+        <v>-2.35</v>
       </c>
     </row>
     <row r="30" spans="1:5">
       <c r="A30" s="5" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="B30" s="5" t="s">
         <v>10</v>
       </c>
       <c r="C30" s="6">
-        <v>-9.210000000000001</v>
+        <v>-21.32</v>
       </c>
       <c r="D30" s="6">
-        <v>-6.31</v>
-      </c>
-      <c r="E30" s="8">
-        <v>2.9</v>
+        <v>-23.99</v>
+      </c>
+      <c r="E30" s="7">
+        <v>-2.67</v>
       </c>
     </row>
     <row r="31" spans="1:5">
       <c r="A31" s="5" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="B31" s="5" t="s">
         <v>10</v>
       </c>
       <c r="C31" s="6">
-        <v>-7.05</v>
+        <v>-6.31</v>
       </c>
       <c r="D31" s="6">
-        <v>-6.02</v>
-      </c>
-      <c r="E31" s="8">
-        <v>1.03</v>
+        <v>-11.23</v>
+      </c>
+      <c r="E31" s="7">
+        <v>-4.92</v>
       </c>
     </row>
     <row r="32" spans="1:5">
       <c r="A32" s="5" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="B32" s="5" t="s">
         <v>10</v>
       </c>
       <c r="C32" s="6">
-        <v>-1.48</v>
+        <v>-6.02</v>
       </c>
       <c r="D32" s="6">
-        <v>3.15</v>
-      </c>
-      <c r="E32" s="8">
-        <v>4.63</v>
+        <v>-9.869999999999999</v>
+      </c>
+      <c r="E32" s="7">
+        <v>-3.85</v>
       </c>
     </row>
     <row r="33" spans="1:5">
       <c r="A33" s="5" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="B33" s="5" t="s">
         <v>10</v>
       </c>
       <c r="C33" s="6">
-        <v>-7.62</v>
+        <v>3.15</v>
       </c>
       <c r="D33" s="6">
-        <v>-4.61</v>
-      </c>
-      <c r="E33" s="8">
-        <v>3.01</v>
+        <v>0.18</v>
+      </c>
+      <c r="E33" s="7">
+        <v>-2.97</v>
       </c>
     </row>
     <row r="34" spans="1:5">
       <c r="A34" s="5" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="B34" s="5" t="s">
         <v>10</v>
       </c>
       <c r="C34" s="6">
-        <v>38.33</v>
+        <v>-4.61</v>
       </c>
       <c r="D34" s="6">
-        <v>42.69</v>
-      </c>
-      <c r="E34" s="8">
-        <v>4.36</v>
+        <v>-4.77</v>
+      </c>
+      <c r="E34" s="7">
+        <v>-0.16</v>
       </c>
     </row>
     <row r="35" spans="1:5">
       <c r="A35" s="5" t="s">
-        <v>37</v>
+        <v>43</v>
       </c>
       <c r="B35" s="5" t="s">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="C35" s="6">
-        <v>-18.96</v>
+        <v>42.69</v>
       </c>
       <c r="D35" s="6">
-        <v>-20.04</v>
+        <v>33.27</v>
       </c>
       <c r="E35" s="7">
-        <v>-1.08</v>
+        <v>-9.42</v>
       </c>
     </row>
     <row r="36" spans="1:5">
       <c r="A36" s="5" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="B36" s="5" t="s">
         <v>6</v>
       </c>
       <c r="C36" s="6">
-        <v>-26.37</v>
+        <v>-20.04</v>
       </c>
       <c r="D36" s="6">
-        <v>-27.94</v>
+        <v>-22.04</v>
       </c>
       <c r="E36" s="7">
-        <v>-1.57</v>
+        <v>-2</v>
       </c>
     </row>
     <row r="37" spans="1:5">
       <c r="A37" s="5" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="B37" s="5" t="s">
         <v>6</v>
       </c>
       <c r="C37" s="6">
-        <v>-45.21</v>
+        <v>-27.94</v>
       </c>
       <c r="D37" s="6">
-        <v>-45.13</v>
+        <v>-27.02</v>
       </c>
       <c r="E37" s="8">
-        <v>0.08</v>
+        <v>0.92</v>
       </c>
     </row>
     <row r="38" spans="1:5">
       <c r="A38" s="5" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="B38" s="5" t="s">
         <v>6</v>
       </c>
       <c r="C38" s="6">
-        <v>-19.49</v>
+        <v>-45.13</v>
       </c>
       <c r="D38" s="6">
-        <v>-19.91</v>
+        <v>-47.07</v>
       </c>
       <c r="E38" s="7">
-        <v>-0.42</v>
+        <v>-1.94</v>
       </c>
     </row>
     <row r="39" spans="1:5">
       <c r="A39" s="5" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="B39" s="5" t="s">
         <v>6</v>
       </c>
       <c r="C39" s="6">
-        <v>-19.35</v>
+        <v>-19.91</v>
       </c>
       <c r="D39" s="6">
-        <v>-18.88</v>
-      </c>
-      <c r="E39" s="8">
-        <v>0.47</v>
+        <v>-21.53</v>
+      </c>
+      <c r="E39" s="7">
+        <v>-1.62</v>
       </c>
     </row>
     <row r="40" spans="1:5">
       <c r="A40" s="5" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="B40" s="5" t="s">
         <v>6</v>
       </c>
       <c r="C40" s="6">
-        <v>-16.89</v>
+        <v>-18.88</v>
       </c>
       <c r="D40" s="6">
-        <v>-16.82</v>
-      </c>
-      <c r="E40" s="8">
-        <v>0.07000000000000001</v>
+        <v>-19.35</v>
+      </c>
+      <c r="E40" s="7">
+        <v>-0.47</v>
       </c>
     </row>
     <row r="41" spans="1:5">
       <c r="A41" s="5" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="B41" s="5" t="s">
         <v>6</v>
       </c>
       <c r="C41" s="6">
-        <v>-0.36</v>
+        <v>-16.82</v>
       </c>
       <c r="D41" s="6">
-        <v>0</v>
-      </c>
-      <c r="E41" s="8">
-        <v>0.36</v>
+        <v>-17.51</v>
+      </c>
+      <c r="E41" s="7">
+        <v>-0.6899999999999999</v>
       </c>
     </row>
     <row r="42" spans="1:5">
       <c r="A42" s="5" t="s">
-        <v>37</v>
+        <v>43</v>
       </c>
       <c r="B42" s="5" t="s">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="C42" s="6">
-        <v>10017</v>
+        <v>0</v>
       </c>
       <c r="D42" s="6">
-        <v>9884</v>
+        <v>-6.26</v>
       </c>
       <c r="E42" s="7">
-        <v>-133</v>
+        <v>-6.26</v>
       </c>
     </row>
     <row r="43" spans="1:5">
       <c r="A43" s="5" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="B43" s="5" t="s">
         <v>2</v>
       </c>
       <c r="C43" s="6">
-        <v>493.5</v>
+        <v>9884</v>
       </c>
       <c r="D43" s="6">
-        <v>483</v>
+        <v>9637</v>
       </c>
       <c r="E43" s="7">
-        <v>-10.5</v>
+        <v>-247</v>
       </c>
     </row>
     <row r="44" spans="1:5">
       <c r="A44" s="5" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="B44" s="5" t="s">
         <v>2</v>
       </c>
       <c r="C44" s="6">
-        <v>300.25</v>
+        <v>483</v>
       </c>
       <c r="D44" s="6">
-        <v>300.7</v>
+        <v>489.15</v>
       </c>
       <c r="E44" s="8">
-        <v>0.45</v>
+        <v>6.15</v>
       </c>
     </row>
     <row r="45" spans="1:5">
       <c r="A45" s="5" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="B45" s="5" t="s">
         <v>2</v>
       </c>
       <c r="C45" s="6">
-        <v>1752.4</v>
+        <v>300.7</v>
       </c>
       <c r="D45" s="6">
-        <v>1743.3</v>
+        <v>290.05</v>
       </c>
       <c r="E45" s="7">
-        <v>-9.1</v>
+        <v>-10.65</v>
       </c>
     </row>
     <row r="46" spans="1:5">
       <c r="A46" s="5" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="B46" s="5" t="s">
         <v>2</v>
       </c>
       <c r="C46" s="6">
-        <v>10600</v>
+        <v>1743.3</v>
       </c>
       <c r="D46" s="6">
-        <v>10662</v>
-      </c>
-      <c r="E46" s="8">
-        <v>62</v>
+        <v>1708</v>
+      </c>
+      <c r="E46" s="7">
+        <v>-35.3</v>
       </c>
     </row>
     <row r="47" spans="1:5">
       <c r="A47" s="5" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="B47" s="5" t="s">
         <v>2</v>
       </c>
       <c r="C47" s="6">
-        <v>963.1</v>
+        <v>10662</v>
       </c>
       <c r="D47" s="6">
-        <v>963.85</v>
-      </c>
-      <c r="E47" s="8">
-        <v>0.75</v>
+        <v>10600</v>
+      </c>
+      <c r="E47" s="7">
+        <v>-62</v>
       </c>
     </row>
     <row r="48" spans="1:5">
       <c r="A48" s="5" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="B48" s="5" t="s">
         <v>2</v>
       </c>
       <c r="C48" s="6">
-        <v>181.55</v>
+        <v>963.85</v>
       </c>
       <c r="D48" s="6">
-        <v>185.92</v>
-      </c>
-      <c r="E48" s="8">
-        <v>4.37</v>
+        <v>955.95</v>
+      </c>
+      <c r="E48" s="7">
+        <v>-7.9</v>
       </c>
     </row>
     <row r="49" spans="1:5">
       <c r="A49" s="5" t="s">
-        <v>41</v>
+        <v>43</v>
       </c>
       <c r="B49" s="5" t="s">
-        <v>13</v>
+        <v>2</v>
       </c>
       <c r="C49" s="6">
-        <v>43</v>
+        <v>185.92</v>
       </c>
       <c r="D49" s="6">
-        <v>57</v>
-      </c>
-      <c r="E49" s="8">
-        <v>14</v>
+        <v>174.29</v>
+      </c>
+      <c r="E49" s="7">
+        <v>-11.63</v>
       </c>
     </row>
     <row r="50" spans="1:5">
       <c r="A50" s="5" t="s">
-        <v>42</v>
+        <v>38</v>
       </c>
       <c r="B50" s="5" t="s">
         <v>13</v>
       </c>
       <c r="C50" s="6">
-        <v>57</v>
+        <v>85</v>
       </c>
       <c r="D50" s="6">
-        <v>43</v>
-      </c>
-      <c r="E50" s="7">
-        <v>-14</v>
+        <v>99</v>
+      </c>
+      <c r="E50" s="8">
+        <v>14</v>
       </c>
     </row>
     <row r="51" spans="1:5">
       <c r="A51" s="5" t="s">
-        <v>37</v>
+        <v>43</v>
       </c>
       <c r="B51" s="5" t="s">
-        <v>24</v>
+        <v>13</v>
       </c>
       <c r="C51" s="6">
-        <v>21.53</v>
+        <v>99</v>
       </c>
       <c r="D51" s="6">
-        <v>20.18</v>
+        <v>85</v>
       </c>
       <c r="E51" s="7">
-        <v>-1.35</v>
+        <v>-14</v>
       </c>
     </row>
     <row r="52" spans="1:5">
       <c r="A52" s="5" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="B52" s="5" t="s">
         <v>24</v>
       </c>
       <c r="C52" s="6">
-        <v>46.79</v>
+        <v>20.18</v>
       </c>
       <c r="D52" s="6">
-        <v>42.99</v>
+        <v>17.92</v>
       </c>
       <c r="E52" s="7">
-        <v>-3.8</v>
+        <v>-2.26</v>
       </c>
     </row>
     <row r="53" spans="1:5">
       <c r="A53" s="5" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="B53" s="5" t="s">
         <v>24</v>
       </c>
       <c r="C53" s="6">
-        <v>29.53</v>
+        <v>42.99</v>
       </c>
       <c r="D53" s="6">
-        <v>30.13</v>
+        <v>45.77</v>
       </c>
       <c r="E53" s="8">
-        <v>0.6</v>
+        <v>2.78</v>
       </c>
     </row>
     <row r="54" spans="1:5">
       <c r="A54" s="5" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="B54" s="5" t="s">
         <v>24</v>
       </c>
       <c r="C54" s="6">
-        <v>30.61</v>
+        <v>30.13</v>
       </c>
       <c r="D54" s="6">
-        <v>29.46</v>
+        <v>24.79</v>
       </c>
       <c r="E54" s="7">
-        <v>-1.15</v>
+        <v>-5.34</v>
       </c>
     </row>
     <row r="55" spans="1:5">
       <c r="A55" s="5" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="B55" s="5" t="s">
         <v>24</v>
       </c>
       <c r="C55" s="6">
-        <v>40.28</v>
+        <v>29.46</v>
       </c>
       <c r="D55" s="6">
-        <v>42.07</v>
-      </c>
-      <c r="E55" s="8">
-        <v>1.79</v>
+        <v>25.47</v>
+      </c>
+      <c r="E55" s="7">
+        <v>-3.99</v>
       </c>
     </row>
     <row r="56" spans="1:5">
       <c r="A56" s="5" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="B56" s="5" t="s">
         <v>24</v>
       </c>
       <c r="C56" s="6">
-        <v>37.52</v>
+        <v>42.07</v>
       </c>
       <c r="D56" s="6">
-        <v>37.75</v>
-      </c>
-      <c r="E56" s="8">
-        <v>0.23</v>
+        <v>40.75</v>
+      </c>
+      <c r="E56" s="7">
+        <v>-1.32</v>
       </c>
     </row>
     <row r="57" spans="1:5">
       <c r="A57" s="5" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="B57" s="5" t="s">
         <v>24</v>
       </c>
       <c r="C57" s="6">
-        <v>76.01000000000001</v>
+        <v>37.75</v>
       </c>
       <c r="D57" s="6">
-        <v>77.86</v>
-      </c>
-      <c r="E57" s="8">
-        <v>1.85</v>
+        <v>36.21</v>
+      </c>
+      <c r="E57" s="7">
+        <v>-1.54</v>
       </c>
     </row>
     <row r="58" spans="1:5">
       <c r="A58" s="5" t="s">
-        <v>37</v>
+        <v>43</v>
       </c>
       <c r="B58" s="5" t="s">
-        <v>31</v>
+        <v>24</v>
       </c>
       <c r="C58" s="6">
-        <v>-41.85</v>
+        <v>77.86</v>
       </c>
       <c r="D58" s="6">
-        <v>65.89</v>
-      </c>
-      <c r="E58" s="8">
-        <v>107.74</v>
+        <v>63.74</v>
+      </c>
+      <c r="E58" s="7">
+        <v>-14.12</v>
       </c>
     </row>
     <row r="59" spans="1:5">
       <c r="A59" s="5" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="B59" s="5" t="s">
         <v>31</v>
       </c>
       <c r="C59" s="6">
-        <v>-60.5</v>
+        <v>65.89</v>
       </c>
       <c r="D59" s="6">
-        <v>-70.94</v>
+        <v>-29.09</v>
       </c>
       <c r="E59" s="7">
-        <v>-10.44</v>
+        <v>-94.98</v>
       </c>
     </row>
     <row r="60" spans="1:5">
       <c r="A60" s="5" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="B60" s="5" t="s">
         <v>31</v>
       </c>
       <c r="C60" s="6">
-        <v>-13.15</v>
+        <v>-70.94</v>
       </c>
       <c r="D60" s="6">
-        <v>-24.23</v>
-      </c>
-      <c r="E60" s="7">
-        <v>-11.08</v>
+        <v>60.11</v>
+      </c>
+      <c r="E60" s="8">
+        <v>131.05</v>
       </c>
     </row>
     <row r="61" spans="1:5">
       <c r="A61" s="5" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="B61" s="5" t="s">
         <v>31</v>
       </c>
       <c r="C61" s="6">
-        <v>-30.16</v>
+        <v>-24.23</v>
       </c>
       <c r="D61" s="6">
-        <v>24.35</v>
+        <v>18.01</v>
       </c>
       <c r="E61" s="8">
-        <v>54.51</v>
+        <v>42.24</v>
       </c>
     </row>
     <row r="62" spans="1:5">
       <c r="A62" s="5" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="B62" s="5" t="s">
         <v>31</v>
       </c>
       <c r="C62" s="6">
-        <v>-10.62</v>
+        <v>24.35</v>
       </c>
       <c r="D62" s="6">
-        <v>-4.65</v>
+        <v>45.15</v>
       </c>
       <c r="E62" s="8">
-        <v>5.97</v>
+        <v>20.8</v>
       </c>
     </row>
     <row r="63" spans="1:5">
       <c r="A63" s="5" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="B63" s="5" t="s">
         <v>31</v>
       </c>
       <c r="C63" s="6">
-        <v>-33.75</v>
+        <v>-4.65</v>
       </c>
       <c r="D63" s="6">
-        <v>75.48999999999999</v>
+        <v>32.58</v>
       </c>
       <c r="E63" s="8">
-        <v>109.24</v>
+        <v>37.23</v>
       </c>
     </row>
     <row r="64" spans="1:5">
       <c r="A64" s="5" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="B64" s="5" t="s">
         <v>31</v>
       </c>
       <c r="C64" s="6">
-        <v>-21.31</v>
+        <v>75.48999999999999</v>
       </c>
       <c r="D64" s="6">
+        <v>38.49</v>
+      </c>
+      <c r="E64" s="7">
+        <v>-37</v>
+      </c>
+    </row>
+    <row r="65" spans="1:5">
+      <c r="A65" s="5" t="s">
+        <v>43</v>
+      </c>
+      <c r="B65" s="5" t="s">
+        <v>31</v>
+      </c>
+      <c r="C65" s="6">
         <v>24.92</v>
       </c>
-      <c r="E64" s="8">
-        <v>46.23</v>
+      <c r="D65" s="6">
+        <v>-20.14</v>
+      </c>
+      <c r="E65" s="7">
+        <v>-45.06</v>
       </c>
     </row>
   </sheetData>
   <mergeCells count="2">
     <mergeCell ref="A1:F1"/>
-    <mergeCell ref="A5:E5"/>
+    <mergeCell ref="A6:E6"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -2942,28 +2990,28 @@
         <v>1</v>
       </c>
       <c r="B1" s="9" t="s">
-        <v>65</v>
+        <v>70</v>
       </c>
       <c r="C1" s="9" t="s">
-        <v>66</v>
+        <v>71</v>
       </c>
       <c r="D1" s="9" t="s">
-        <v>67</v>
+        <v>72</v>
       </c>
       <c r="E1" s="9" t="s">
-        <v>68</v>
+        <v>73</v>
       </c>
       <c r="F1" s="9" t="s">
-        <v>69</v>
+        <v>74</v>
       </c>
       <c r="G1" s="9" t="s">
-        <v>70</v>
+        <v>75</v>
       </c>
       <c r="H1" s="9" t="s">
-        <v>71</v>
+        <v>76</v>
       </c>
       <c r="I1" s="9" t="s">
-        <v>72</v>
+        <v>77</v>
       </c>
     </row>
     <row r="2" spans="1:9">
@@ -2977,16 +3025,16 @@
         <v>7</v>
       </c>
       <c r="D2" s="11">
-        <v>40.1</v>
+        <v>36.4</v>
       </c>
       <c r="E2" s="11">
         <v>30</v>
       </c>
       <c r="F2" s="11">
-        <v>-2.8</v>
+        <v>-5.5</v>
       </c>
       <c r="G2" s="11">
-        <v>0.7</v>
+        <v>-3.1</v>
       </c>
       <c r="H2" s="11">
         <v>57</v>
@@ -3117,25 +3165,25 @@
     </row>
     <row r="2" spans="1:7">
       <c r="A2" s="14">
-        <v>0.2368</v>
+        <v>0.2314</v>
       </c>
       <c r="B2" s="14">
-        <v>0.1888</v>
+        <v>0.1886</v>
       </c>
       <c r="C2" s="14">
-        <v>0.1575</v>
+        <v>0.1605</v>
       </c>
       <c r="D2" s="14">
-        <v>0.05599999999999999</v>
+        <v>0.0479</v>
       </c>
       <c r="E2" s="14">
-        <v>0.0486</v>
+        <v>0.0473</v>
       </c>
       <c r="F2" s="14">
-        <v>-0</v>
+        <v>-0.005</v>
       </c>
       <c r="G2" s="14">
-        <v>-0.237</v>
+        <v>-0.2399</v>
       </c>
     </row>
   </sheetData>

--- a/BAJAJ_GROUP_Technical_Metrics.xlsx
+++ b/BAJAJ_GROUP_Technical_Metrics.xlsx
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="274" uniqueCount="78">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="137" uniqueCount="61">
   <si>
     <t>Symbol</t>
   </si>
@@ -172,64 +172,13 @@
     <t>▶  SIGNAL EVENTS (vs Previous Run)</t>
   </si>
   <si>
-    <t>Signal</t>
-  </si>
-  <si>
-    <t>Change</t>
-  </si>
-  <si>
-    <t>Direction</t>
-  </si>
-  <si>
-    <t>Prev Value</t>
-  </si>
-  <si>
-    <t>Curr Value</t>
-  </si>
-  <si>
-    <t>RSI Overbought Exit</t>
-  </si>
-  <si>
-    <t>77.9 → 63.7</t>
-  </si>
-  <si>
-    <t>🔵 COOLING</t>
-  </si>
-  <si>
-    <t>77.9</t>
-  </si>
-  <si>
-    <t>63.7</t>
-  </si>
-  <si>
-    <t>Left 52W High Zone</t>
-  </si>
-  <si>
-    <t>0.0% → -6.3%</t>
-  </si>
-  <si>
-    <t>⚪ NEUTRAL</t>
-  </si>
-  <si>
-    <t>0.0%</t>
-  </si>
-  <si>
-    <t>-6.3%</t>
+    <t>No signal events detected since last run.</t>
   </si>
   <si>
     <t>▶  NUMERIC METRIC CHANGES (vs Previous Run)</t>
   </si>
   <si>
-    <t>Metric</t>
-  </si>
-  <si>
-    <t>Previous</t>
-  </si>
-  <si>
-    <t>Current</t>
-  </si>
-  <si>
-    <t>Delta</t>
+    <t>No numeric changes detected since last run.</t>
   </si>
   <si>
     <t>Rank</t>
@@ -260,13 +209,11 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="4">
-    <numFmt numFmtId="164" formatCode="0.00"/>
-    <numFmt numFmtId="165" formatCode="+0.00;-0.00"/>
-    <numFmt numFmtId="166" formatCode="0.0"/>
-    <numFmt numFmtId="167" formatCode="0.00%"/>
+  <numFmts count="2">
+    <numFmt numFmtId="164" formatCode="0.0"/>
+    <numFmt numFmtId="165" formatCode="0.00%"/>
   </numFmts>
-  <fonts count="7">
+  <fonts count="4">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -298,29 +245,8 @@
       <family val="2"/>
       <scheme val="minor"/>
     </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF1F4E79"/>
-      <name val="Calibri"/>
-      <family val="2"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF9C0006"/>
-      <name val="Calibri"/>
-      <family val="2"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF006100"/>
-      <name val="Calibri"/>
-      <family val="2"/>
-      <scheme val="minor"/>
-    </font>
   </fonts>
-  <fills count="10">
+  <fills count="6">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -336,30 +262,6 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="FF2E4057"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF4A6FA5"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFDDEBF7"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFC7CE"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFC6EFCE"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -429,34 +331,27 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="15">
+  <cellXfs count="10">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="2" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="3" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1"/>
-    <xf numFmtId="165" fontId="5" fillId="6" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="165" fontId="6" fillId="7" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="3" fillId="8" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="9" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="166" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="9" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="5" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="167" fontId="0" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="165" fontId="0" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
     </xf>
   </cellXfs>
@@ -1873,7 +1768,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:F65"/>
+  <dimension ref="A1:F6"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="16.7109375" customWidth="1"/>
@@ -1893,1080 +1788,27 @@
     </row>
     <row r="2" spans="1:6">
       <c r="A2" s="3" t="s">
-        <v>0</v>
-      </c>
-      <c r="B2" s="3" t="s">
         <v>50</v>
       </c>
-      <c r="C2" s="3" t="s">
+    </row>
+    <row r="5" spans="1:6">
+      <c r="A5" s="2" t="s">
         <v>51</v>
       </c>
-      <c r="D2" s="3" t="s">
-        <v>52</v>
-      </c>
-      <c r="E2" s="3" t="s">
-        <v>53</v>
-      </c>
-      <c r="F2" s="3" t="s">
-        <v>54</v>
-      </c>
-    </row>
-    <row r="3" spans="1:6">
-      <c r="A3" s="4" t="s">
-        <v>43</v>
-      </c>
-      <c r="B3" s="4" t="s">
-        <v>55</v>
-      </c>
-      <c r="C3" s="4" t="s">
-        <v>56</v>
-      </c>
-      <c r="D3" s="4" t="s">
-        <v>57</v>
-      </c>
-      <c r="E3" s="4" t="s">
-        <v>58</v>
-      </c>
-      <c r="F3" s="4" t="s">
-        <v>59</v>
-      </c>
-    </row>
-    <row r="4" spans="1:6">
-      <c r="A4" s="4" t="s">
-        <v>43</v>
-      </c>
-      <c r="B4" s="4" t="s">
-        <v>60</v>
-      </c>
-      <c r="C4" s="4" t="s">
-        <v>61</v>
-      </c>
-      <c r="D4" s="4" t="s">
-        <v>62</v>
-      </c>
-      <c r="E4" s="4" t="s">
-        <v>63</v>
-      </c>
-      <c r="F4" s="4" t="s">
-        <v>64</v>
-      </c>
+      <c r="B5" s="2"/>
+      <c r="C5" s="2"/>
+      <c r="D5" s="2"/>
+      <c r="E5" s="2"/>
     </row>
     <row r="6" spans="1:6">
-      <c r="A6" s="2" t="s">
-        <v>65</v>
-      </c>
-      <c r="B6" s="2"/>
-      <c r="C6" s="2"/>
-      <c r="D6" s="2"/>
-      <c r="E6" s="2"/>
-    </row>
-    <row r="7" spans="1:6">
-      <c r="A7" s="3" t="s">
-        <v>0</v>
-      </c>
-      <c r="B7" s="3" t="s">
-        <v>66</v>
-      </c>
-      <c r="C7" s="3" t="s">
-        <v>67</v>
-      </c>
-      <c r="D7" s="3" t="s">
-        <v>68</v>
-      </c>
-      <c r="E7" s="3" t="s">
-        <v>69</v>
-      </c>
-    </row>
-    <row r="8" spans="1:6">
-      <c r="A8" s="5" t="s">
-        <v>37</v>
-      </c>
-      <c r="B8" s="5" t="s">
-        <v>9</v>
-      </c>
-      <c r="C8" s="6">
-        <v>-17.07</v>
-      </c>
-      <c r="D8" s="6">
-        <v>-18.33</v>
-      </c>
-      <c r="E8" s="7">
-        <v>-1.26</v>
-      </c>
-    </row>
-    <row r="9" spans="1:6">
-      <c r="A9" s="5" t="s">
-        <v>38</v>
-      </c>
-      <c r="B9" s="5" t="s">
-        <v>9</v>
-      </c>
-      <c r="C9" s="6">
-        <v>-6.68</v>
-      </c>
-      <c r="D9" s="6">
-        <v>-7.01</v>
-      </c>
-      <c r="E9" s="7">
-        <v>-0.33</v>
-      </c>
-    </row>
-    <row r="10" spans="1:6">
-      <c r="A10" s="5" t="s">
-        <v>39</v>
-      </c>
-      <c r="B10" s="5" t="s">
-        <v>9</v>
-      </c>
-      <c r="C10" s="6">
-        <v>-9.199999999999999</v>
-      </c>
-      <c r="D10" s="6">
-        <v>-15.21</v>
-      </c>
-      <c r="E10" s="7">
-        <v>-6.01</v>
-      </c>
-    </row>
-    <row r="11" spans="1:6">
-      <c r="A11" s="5" t="s">
-        <v>40</v>
-      </c>
-      <c r="B11" s="5" t="s">
-        <v>9</v>
-      </c>
-      <c r="C11" s="6">
-        <v>-11.51</v>
-      </c>
-      <c r="D11" s="6">
-        <v>-11.9</v>
-      </c>
-      <c r="E11" s="7">
-        <v>-0.39</v>
-      </c>
-    </row>
-    <row r="12" spans="1:6">
-      <c r="A12" s="5" t="s">
-        <v>41</v>
-      </c>
-      <c r="B12" s="5" t="s">
-        <v>9</v>
-      </c>
-      <c r="C12" s="6">
-        <v>-4.48</v>
-      </c>
-      <c r="D12" s="6">
-        <v>-3.25</v>
-      </c>
-      <c r="E12" s="8">
-        <v>1.23</v>
-      </c>
-    </row>
-    <row r="13" spans="1:6">
-      <c r="A13" s="5" t="s">
-        <v>42</v>
-      </c>
-      <c r="B13" s="5" t="s">
-        <v>9</v>
-      </c>
-      <c r="C13" s="6">
-        <v>-9.109999999999999</v>
-      </c>
-      <c r="D13" s="6">
-        <v>-9.82</v>
-      </c>
-      <c r="E13" s="7">
-        <v>-0.71</v>
-      </c>
-    </row>
-    <row r="14" spans="1:6">
-      <c r="A14" s="5" t="s">
-        <v>43</v>
-      </c>
-      <c r="B14" s="5" t="s">
-        <v>9</v>
-      </c>
-      <c r="C14" s="6">
-        <v>38.29</v>
-      </c>
-      <c r="D14" s="6">
-        <v>27.31</v>
-      </c>
-      <c r="E14" s="7">
-        <v>-10.98</v>
-      </c>
-    </row>
-    <row r="15" spans="1:6">
-      <c r="A15" s="5" t="s">
-        <v>37</v>
-      </c>
-      <c r="B15" s="5" t="s">
-        <v>8</v>
-      </c>
-      <c r="C15" s="6">
-        <v>-8.57</v>
-      </c>
-      <c r="D15" s="6">
-        <v>-11.38</v>
-      </c>
-      <c r="E15" s="7">
-        <v>-2.81</v>
-      </c>
-    </row>
-    <row r="16" spans="1:6">
-      <c r="A16" s="5" t="s">
-        <v>38</v>
-      </c>
-      <c r="B16" s="5" t="s">
-        <v>8</v>
-      </c>
-      <c r="C16" s="6">
-        <v>-2.03</v>
-      </c>
-      <c r="D16" s="6">
-        <v>-1.29</v>
-      </c>
-      <c r="E16" s="8">
-        <v>0.74</v>
-      </c>
-    </row>
-    <row r="17" spans="1:5">
-      <c r="A17" s="5" t="s">
-        <v>39</v>
-      </c>
-      <c r="B17" s="5" t="s">
-        <v>8</v>
-      </c>
-      <c r="C17" s="6">
-        <v>-2.95</v>
-      </c>
-      <c r="D17" s="6">
-        <v>-4.4</v>
-      </c>
-      <c r="E17" s="7">
-        <v>-1.45</v>
-      </c>
-    </row>
-    <row r="18" spans="1:5">
-      <c r="A18" s="5" t="s">
-        <v>40</v>
-      </c>
-      <c r="B18" s="5" t="s">
-        <v>8</v>
-      </c>
-      <c r="C18" s="6">
-        <v>0.05</v>
-      </c>
-      <c r="D18" s="6">
-        <v>-1.33</v>
-      </c>
-      <c r="E18" s="7">
-        <v>-1.38</v>
-      </c>
-    </row>
-    <row r="19" spans="1:5">
-      <c r="A19" s="5" t="s">
-        <v>41</v>
-      </c>
-      <c r="B19" s="5" t="s">
-        <v>8</v>
-      </c>
-      <c r="C19" s="6">
-        <v>0.58</v>
-      </c>
-      <c r="D19" s="6">
-        <v>-1.74</v>
-      </c>
-      <c r="E19" s="7">
-        <v>-2.32</v>
-      </c>
-    </row>
-    <row r="20" spans="1:5">
-      <c r="A20" s="5" t="s">
-        <v>42</v>
-      </c>
-      <c r="B20" s="5" t="s">
-        <v>8</v>
-      </c>
-      <c r="C20" s="6">
-        <v>-1.02</v>
-      </c>
-      <c r="D20" s="6">
-        <v>-0.36</v>
-      </c>
-      <c r="E20" s="8">
-        <v>0.66</v>
-      </c>
-    </row>
-    <row r="21" spans="1:5">
-      <c r="A21" s="5" t="s">
-        <v>43</v>
-      </c>
-      <c r="B21" s="5" t="s">
-        <v>8</v>
-      </c>
-      <c r="C21" s="6">
-        <v>7.79</v>
-      </c>
-      <c r="D21" s="6">
-        <v>-3.24</v>
-      </c>
-      <c r="E21" s="7">
-        <v>-11.03</v>
-      </c>
-    </row>
-    <row r="22" spans="1:5">
-      <c r="A22" s="5" t="s">
-        <v>37</v>
-      </c>
-      <c r="B22" s="5" t="s">
-        <v>11</v>
-      </c>
-      <c r="C22" s="6">
-        <v>16.19</v>
-      </c>
-      <c r="D22" s="6">
-        <v>12.59</v>
-      </c>
-      <c r="E22" s="7">
-        <v>-3.6</v>
-      </c>
-    </row>
-    <row r="23" spans="1:5">
-      <c r="A23" s="5" t="s">
-        <v>38</v>
-      </c>
-      <c r="B23" s="5" t="s">
-        <v>11</v>
-      </c>
-      <c r="C23" s="6">
-        <v>104.61</v>
-      </c>
-      <c r="D23" s="6">
-        <v>104.38</v>
-      </c>
-      <c r="E23" s="7">
-        <v>-0.23</v>
-      </c>
-    </row>
-    <row r="24" spans="1:5">
-      <c r="A24" s="5" t="s">
-        <v>39</v>
-      </c>
-      <c r="B24" s="5" t="s">
-        <v>11</v>
-      </c>
-      <c r="C24" s="6">
-        <v>-45.11</v>
-      </c>
-      <c r="D24" s="6">
-        <v>-46.68</v>
-      </c>
-      <c r="E24" s="7">
-        <v>-1.57</v>
-      </c>
-    </row>
-    <row r="25" spans="1:5">
-      <c r="A25" s="5" t="s">
-        <v>40</v>
-      </c>
-      <c r="B25" s="5" t="s">
-        <v>11</v>
-      </c>
-      <c r="C25" s="6">
-        <v>-13.14</v>
-      </c>
-      <c r="D25" s="6">
-        <v>-14.64</v>
-      </c>
-      <c r="E25" s="7">
-        <v>-1.5</v>
-      </c>
-    </row>
-    <row r="26" spans="1:5">
-      <c r="A26" s="5" t="s">
-        <v>41</v>
-      </c>
-      <c r="B26" s="5" t="s">
-        <v>11</v>
-      </c>
-      <c r="C26" s="6">
-        <v>-11.12</v>
-      </c>
-      <c r="D26" s="6">
-        <v>-10.31</v>
-      </c>
-      <c r="E26" s="8">
-        <v>0.8100000000000001</v>
-      </c>
-    </row>
-    <row r="27" spans="1:5">
-      <c r="A27" s="5" t="s">
-        <v>42</v>
-      </c>
-      <c r="B27" s="5" t="s">
-        <v>11</v>
-      </c>
-      <c r="C27" s="6">
-        <v>-2.41</v>
-      </c>
-      <c r="D27" s="6">
-        <v>-3.42</v>
-      </c>
-      <c r="E27" s="7">
-        <v>-1.01</v>
-      </c>
-    </row>
-    <row r="28" spans="1:5">
-      <c r="A28" s="5" t="s">
-        <v>43</v>
-      </c>
-      <c r="B28" s="5" t="s">
-        <v>11</v>
-      </c>
-      <c r="C28" s="6">
-        <v>35.17</v>
-      </c>
-      <c r="D28" s="6">
-        <v>22.3</v>
-      </c>
-      <c r="E28" s="7">
-        <v>-12.87</v>
-      </c>
-    </row>
-    <row r="29" spans="1:5">
-      <c r="A29" s="5" t="s">
-        <v>37</v>
-      </c>
-      <c r="B29" s="5" t="s">
-        <v>10</v>
-      </c>
-      <c r="C29" s="6">
-        <v>-2.75</v>
-      </c>
-      <c r="D29" s="6">
-        <v>-5.1</v>
-      </c>
-      <c r="E29" s="7">
-        <v>-2.35</v>
-      </c>
-    </row>
-    <row r="30" spans="1:5">
-      <c r="A30" s="5" t="s">
-        <v>38</v>
-      </c>
-      <c r="B30" s="5" t="s">
-        <v>10</v>
-      </c>
-      <c r="C30" s="6">
-        <v>-21.32</v>
-      </c>
-      <c r="D30" s="6">
-        <v>-23.99</v>
-      </c>
-      <c r="E30" s="7">
-        <v>-2.67</v>
-      </c>
-    </row>
-    <row r="31" spans="1:5">
-      <c r="A31" s="5" t="s">
-        <v>39</v>
-      </c>
-      <c r="B31" s="5" t="s">
-        <v>10</v>
-      </c>
-      <c r="C31" s="6">
-        <v>-6.31</v>
-      </c>
-      <c r="D31" s="6">
-        <v>-11.23</v>
-      </c>
-      <c r="E31" s="7">
-        <v>-4.92</v>
-      </c>
-    </row>
-    <row r="32" spans="1:5">
-      <c r="A32" s="5" t="s">
-        <v>40</v>
-      </c>
-      <c r="B32" s="5" t="s">
-        <v>10</v>
-      </c>
-      <c r="C32" s="6">
-        <v>-6.02</v>
-      </c>
-      <c r="D32" s="6">
-        <v>-9.869999999999999</v>
-      </c>
-      <c r="E32" s="7">
-        <v>-3.85</v>
-      </c>
-    </row>
-    <row r="33" spans="1:5">
-      <c r="A33" s="5" t="s">
-        <v>41</v>
-      </c>
-      <c r="B33" s="5" t="s">
-        <v>10</v>
-      </c>
-      <c r="C33" s="6">
-        <v>3.15</v>
-      </c>
-      <c r="D33" s="6">
-        <v>0.18</v>
-      </c>
-      <c r="E33" s="7">
-        <v>-2.97</v>
-      </c>
-    </row>
-    <row r="34" spans="1:5">
-      <c r="A34" s="5" t="s">
-        <v>42</v>
-      </c>
-      <c r="B34" s="5" t="s">
-        <v>10</v>
-      </c>
-      <c r="C34" s="6">
-        <v>-4.61</v>
-      </c>
-      <c r="D34" s="6">
-        <v>-4.77</v>
-      </c>
-      <c r="E34" s="7">
-        <v>-0.16</v>
-      </c>
-    </row>
-    <row r="35" spans="1:5">
-      <c r="A35" s="5" t="s">
-        <v>43</v>
-      </c>
-      <c r="B35" s="5" t="s">
-        <v>10</v>
-      </c>
-      <c r="C35" s="6">
-        <v>42.69</v>
-      </c>
-      <c r="D35" s="6">
-        <v>33.27</v>
-      </c>
-      <c r="E35" s="7">
-        <v>-9.42</v>
-      </c>
-    </row>
-    <row r="36" spans="1:5">
-      <c r="A36" s="5" t="s">
-        <v>37</v>
-      </c>
-      <c r="B36" s="5" t="s">
-        <v>6</v>
-      </c>
-      <c r="C36" s="6">
-        <v>-20.04</v>
-      </c>
-      <c r="D36" s="6">
-        <v>-22.04</v>
-      </c>
-      <c r="E36" s="7">
-        <v>-2</v>
-      </c>
-    </row>
-    <row r="37" spans="1:5">
-      <c r="A37" s="5" t="s">
-        <v>38</v>
-      </c>
-      <c r="B37" s="5" t="s">
-        <v>6</v>
-      </c>
-      <c r="C37" s="6">
-        <v>-27.94</v>
-      </c>
-      <c r="D37" s="6">
-        <v>-27.02</v>
-      </c>
-      <c r="E37" s="8">
-        <v>0.92</v>
-      </c>
-    </row>
-    <row r="38" spans="1:5">
-      <c r="A38" s="5" t="s">
-        <v>39</v>
-      </c>
-      <c r="B38" s="5" t="s">
-        <v>6</v>
-      </c>
-      <c r="C38" s="6">
-        <v>-45.13</v>
-      </c>
-      <c r="D38" s="6">
-        <v>-47.07</v>
-      </c>
-      <c r="E38" s="7">
-        <v>-1.94</v>
-      </c>
-    </row>
-    <row r="39" spans="1:5">
-      <c r="A39" s="5" t="s">
-        <v>40</v>
-      </c>
-      <c r="B39" s="5" t="s">
-        <v>6</v>
-      </c>
-      <c r="C39" s="6">
-        <v>-19.91</v>
-      </c>
-      <c r="D39" s="6">
-        <v>-21.53</v>
-      </c>
-      <c r="E39" s="7">
-        <v>-1.62</v>
-      </c>
-    </row>
-    <row r="40" spans="1:5">
-      <c r="A40" s="5" t="s">
-        <v>41</v>
-      </c>
-      <c r="B40" s="5" t="s">
-        <v>6</v>
-      </c>
-      <c r="C40" s="6">
-        <v>-18.88</v>
-      </c>
-      <c r="D40" s="6">
-        <v>-19.35</v>
-      </c>
-      <c r="E40" s="7">
-        <v>-0.47</v>
-      </c>
-    </row>
-    <row r="41" spans="1:5">
-      <c r="A41" s="5" t="s">
-        <v>42</v>
-      </c>
-      <c r="B41" s="5" t="s">
-        <v>6</v>
-      </c>
-      <c r="C41" s="6">
-        <v>-16.82</v>
-      </c>
-      <c r="D41" s="6">
-        <v>-17.51</v>
-      </c>
-      <c r="E41" s="7">
-        <v>-0.6899999999999999</v>
-      </c>
-    </row>
-    <row r="42" spans="1:5">
-      <c r="A42" s="5" t="s">
-        <v>43</v>
-      </c>
-      <c r="B42" s="5" t="s">
-        <v>6</v>
-      </c>
-      <c r="C42" s="6">
-        <v>0</v>
-      </c>
-      <c r="D42" s="6">
-        <v>-6.26</v>
-      </c>
-      <c r="E42" s="7">
-        <v>-6.26</v>
-      </c>
-    </row>
-    <row r="43" spans="1:5">
-      <c r="A43" s="5" t="s">
-        <v>37</v>
-      </c>
-      <c r="B43" s="5" t="s">
-        <v>2</v>
-      </c>
-      <c r="C43" s="6">
-        <v>9884</v>
-      </c>
-      <c r="D43" s="6">
-        <v>9637</v>
-      </c>
-      <c r="E43" s="7">
-        <v>-247</v>
-      </c>
-    </row>
-    <row r="44" spans="1:5">
-      <c r="A44" s="5" t="s">
-        <v>38</v>
-      </c>
-      <c r="B44" s="5" t="s">
-        <v>2</v>
-      </c>
-      <c r="C44" s="6">
-        <v>483</v>
-      </c>
-      <c r="D44" s="6">
-        <v>489.15</v>
-      </c>
-      <c r="E44" s="8">
-        <v>6.15</v>
-      </c>
-    </row>
-    <row r="45" spans="1:5">
-      <c r="A45" s="5" t="s">
-        <v>39</v>
-      </c>
-      <c r="B45" s="5" t="s">
-        <v>2</v>
-      </c>
-      <c r="C45" s="6">
-        <v>300.7</v>
-      </c>
-      <c r="D45" s="6">
-        <v>290.05</v>
-      </c>
-      <c r="E45" s="7">
-        <v>-10.65</v>
-      </c>
-    </row>
-    <row r="46" spans="1:5">
-      <c r="A46" s="5" t="s">
-        <v>40</v>
-      </c>
-      <c r="B46" s="5" t="s">
-        <v>2</v>
-      </c>
-      <c r="C46" s="6">
-        <v>1743.3</v>
-      </c>
-      <c r="D46" s="6">
-        <v>1708</v>
-      </c>
-      <c r="E46" s="7">
-        <v>-35.3</v>
-      </c>
-    </row>
-    <row r="47" spans="1:5">
-      <c r="A47" s="5" t="s">
-        <v>41</v>
-      </c>
-      <c r="B47" s="5" t="s">
-        <v>2</v>
-      </c>
-      <c r="C47" s="6">
-        <v>10662</v>
-      </c>
-      <c r="D47" s="6">
-        <v>10600</v>
-      </c>
-      <c r="E47" s="7">
-        <v>-62</v>
-      </c>
-    </row>
-    <row r="48" spans="1:5">
-      <c r="A48" s="5" t="s">
-        <v>42</v>
-      </c>
-      <c r="B48" s="5" t="s">
-        <v>2</v>
-      </c>
-      <c r="C48" s="6">
-        <v>963.85</v>
-      </c>
-      <c r="D48" s="6">
-        <v>955.95</v>
-      </c>
-      <c r="E48" s="7">
-        <v>-7.9</v>
-      </c>
-    </row>
-    <row r="49" spans="1:5">
-      <c r="A49" s="5" t="s">
-        <v>43</v>
-      </c>
-      <c r="B49" s="5" t="s">
-        <v>2</v>
-      </c>
-      <c r="C49" s="6">
-        <v>185.92</v>
-      </c>
-      <c r="D49" s="6">
-        <v>174.29</v>
-      </c>
-      <c r="E49" s="7">
-        <v>-11.63</v>
-      </c>
-    </row>
-    <row r="50" spans="1:5">
-      <c r="A50" s="5" t="s">
-        <v>38</v>
-      </c>
-      <c r="B50" s="5" t="s">
-        <v>13</v>
-      </c>
-      <c r="C50" s="6">
-        <v>85</v>
-      </c>
-      <c r="D50" s="6">
-        <v>99</v>
-      </c>
-      <c r="E50" s="8">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="51" spans="1:5">
-      <c r="A51" s="5" t="s">
-        <v>43</v>
-      </c>
-      <c r="B51" s="5" t="s">
-        <v>13</v>
-      </c>
-      <c r="C51" s="6">
-        <v>99</v>
-      </c>
-      <c r="D51" s="6">
-        <v>85</v>
-      </c>
-      <c r="E51" s="7">
-        <v>-14</v>
-      </c>
-    </row>
-    <row r="52" spans="1:5">
-      <c r="A52" s="5" t="s">
-        <v>37</v>
-      </c>
-      <c r="B52" s="5" t="s">
-        <v>24</v>
-      </c>
-      <c r="C52" s="6">
-        <v>20.18</v>
-      </c>
-      <c r="D52" s="6">
-        <v>17.92</v>
-      </c>
-      <c r="E52" s="7">
-        <v>-2.26</v>
-      </c>
-    </row>
-    <row r="53" spans="1:5">
-      <c r="A53" s="5" t="s">
-        <v>38</v>
-      </c>
-      <c r="B53" s="5" t="s">
-        <v>24</v>
-      </c>
-      <c r="C53" s="6">
-        <v>42.99</v>
-      </c>
-      <c r="D53" s="6">
-        <v>45.77</v>
-      </c>
-      <c r="E53" s="8">
-        <v>2.78</v>
-      </c>
-    </row>
-    <row r="54" spans="1:5">
-      <c r="A54" s="5" t="s">
-        <v>39</v>
-      </c>
-      <c r="B54" s="5" t="s">
-        <v>24</v>
-      </c>
-      <c r="C54" s="6">
-        <v>30.13</v>
-      </c>
-      <c r="D54" s="6">
-        <v>24.79</v>
-      </c>
-      <c r="E54" s="7">
-        <v>-5.34</v>
-      </c>
-    </row>
-    <row r="55" spans="1:5">
-      <c r="A55" s="5" t="s">
-        <v>40</v>
-      </c>
-      <c r="B55" s="5" t="s">
-        <v>24</v>
-      </c>
-      <c r="C55" s="6">
-        <v>29.46</v>
-      </c>
-      <c r="D55" s="6">
-        <v>25.47</v>
-      </c>
-      <c r="E55" s="7">
-        <v>-3.99</v>
-      </c>
-    </row>
-    <row r="56" spans="1:5">
-      <c r="A56" s="5" t="s">
-        <v>41</v>
-      </c>
-      <c r="B56" s="5" t="s">
-        <v>24</v>
-      </c>
-      <c r="C56" s="6">
-        <v>42.07</v>
-      </c>
-      <c r="D56" s="6">
-        <v>40.75</v>
-      </c>
-      <c r="E56" s="7">
-        <v>-1.32</v>
-      </c>
-    </row>
-    <row r="57" spans="1:5">
-      <c r="A57" s="5" t="s">
-        <v>42</v>
-      </c>
-      <c r="B57" s="5" t="s">
-        <v>24</v>
-      </c>
-      <c r="C57" s="6">
-        <v>37.75</v>
-      </c>
-      <c r="D57" s="6">
-        <v>36.21</v>
-      </c>
-      <c r="E57" s="7">
-        <v>-1.54</v>
-      </c>
-    </row>
-    <row r="58" spans="1:5">
-      <c r="A58" s="5" t="s">
-        <v>43</v>
-      </c>
-      <c r="B58" s="5" t="s">
-        <v>24</v>
-      </c>
-      <c r="C58" s="6">
-        <v>77.86</v>
-      </c>
-      <c r="D58" s="6">
-        <v>63.74</v>
-      </c>
-      <c r="E58" s="7">
-        <v>-14.12</v>
-      </c>
-    </row>
-    <row r="59" spans="1:5">
-      <c r="A59" s="5" t="s">
-        <v>37</v>
-      </c>
-      <c r="B59" s="5" t="s">
-        <v>31</v>
-      </c>
-      <c r="C59" s="6">
-        <v>65.89</v>
-      </c>
-      <c r="D59" s="6">
-        <v>-29.09</v>
-      </c>
-      <c r="E59" s="7">
-        <v>-94.98</v>
-      </c>
-    </row>
-    <row r="60" spans="1:5">
-      <c r="A60" s="5" t="s">
-        <v>38</v>
-      </c>
-      <c r="B60" s="5" t="s">
-        <v>31</v>
-      </c>
-      <c r="C60" s="6">
-        <v>-70.94</v>
-      </c>
-      <c r="D60" s="6">
-        <v>60.11</v>
-      </c>
-      <c r="E60" s="8">
-        <v>131.05</v>
-      </c>
-    </row>
-    <row r="61" spans="1:5">
-      <c r="A61" s="5" t="s">
-        <v>39</v>
-      </c>
-      <c r="B61" s="5" t="s">
-        <v>31</v>
-      </c>
-      <c r="C61" s="6">
-        <v>-24.23</v>
-      </c>
-      <c r="D61" s="6">
-        <v>18.01</v>
-      </c>
-      <c r="E61" s="8">
-        <v>42.24</v>
-      </c>
-    </row>
-    <row r="62" spans="1:5">
-      <c r="A62" s="5" t="s">
-        <v>40</v>
-      </c>
-      <c r="B62" s="5" t="s">
-        <v>31</v>
-      </c>
-      <c r="C62" s="6">
-        <v>24.35</v>
-      </c>
-      <c r="D62" s="6">
-        <v>45.15</v>
-      </c>
-      <c r="E62" s="8">
-        <v>20.8</v>
-      </c>
-    </row>
-    <row r="63" spans="1:5">
-      <c r="A63" s="5" t="s">
-        <v>41</v>
-      </c>
-      <c r="B63" s="5" t="s">
-        <v>31</v>
-      </c>
-      <c r="C63" s="6">
-        <v>-4.65</v>
-      </c>
-      <c r="D63" s="6">
-        <v>32.58</v>
-      </c>
-      <c r="E63" s="8">
-        <v>37.23</v>
-      </c>
-    </row>
-    <row r="64" spans="1:5">
-      <c r="A64" s="5" t="s">
-        <v>42</v>
-      </c>
-      <c r="B64" s="5" t="s">
-        <v>31</v>
-      </c>
-      <c r="C64" s="6">
-        <v>75.48999999999999</v>
-      </c>
-      <c r="D64" s="6">
-        <v>38.49</v>
-      </c>
-      <c r="E64" s="7">
-        <v>-37</v>
-      </c>
-    </row>
-    <row r="65" spans="1:5">
-      <c r="A65" s="5" t="s">
-        <v>43</v>
-      </c>
-      <c r="B65" s="5" t="s">
-        <v>31</v>
-      </c>
-      <c r="C65" s="6">
-        <v>24.92</v>
-      </c>
-      <c r="D65" s="6">
-        <v>-20.14</v>
-      </c>
-      <c r="E65" s="7">
-        <v>-45.06</v>
+      <c r="A6" s="3" t="s">
+        <v>52</v>
       </c>
     </row>
   </sheetData>
   <mergeCells count="2">
     <mergeCell ref="A1:F1"/>
-    <mergeCell ref="A6:E6"/>
+    <mergeCell ref="A5:E5"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -2986,60 +1828,60 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:9" ht="28" customHeight="1">
-      <c r="A1" s="9" t="s">
+      <c r="A1" s="4" t="s">
         <v>1</v>
       </c>
-      <c r="B1" s="9" t="s">
-        <v>70</v>
-      </c>
-      <c r="C1" s="9" t="s">
-        <v>71</v>
-      </c>
-      <c r="D1" s="9" t="s">
-        <v>72</v>
-      </c>
-      <c r="E1" s="9" t="s">
-        <v>73</v>
-      </c>
-      <c r="F1" s="9" t="s">
-        <v>74</v>
-      </c>
-      <c r="G1" s="9" t="s">
-        <v>75</v>
-      </c>
-      <c r="H1" s="9" t="s">
-        <v>76</v>
-      </c>
-      <c r="I1" s="9" t="s">
-        <v>77</v>
+      <c r="B1" s="4" t="s">
+        <v>53</v>
+      </c>
+      <c r="C1" s="4" t="s">
+        <v>54</v>
+      </c>
+      <c r="D1" s="4" t="s">
+        <v>55</v>
+      </c>
+      <c r="E1" s="4" t="s">
+        <v>56</v>
+      </c>
+      <c r="F1" s="4" t="s">
+        <v>57</v>
+      </c>
+      <c r="G1" s="4" t="s">
+        <v>58</v>
+      </c>
+      <c r="H1" s="4" t="s">
+        <v>59</v>
+      </c>
+      <c r="I1" s="4" t="s">
+        <v>60</v>
       </c>
     </row>
     <row r="2" spans="1:9">
-      <c r="A2" s="10" t="s">
+      <c r="A2" s="5" t="s">
         <v>44</v>
       </c>
-      <c r="B2" s="11">
+      <c r="B2" s="6">
         <v>44.8</v>
       </c>
-      <c r="C2" s="12">
+      <c r="C2" s="7">
         <v>7</v>
       </c>
-      <c r="D2" s="11">
+      <c r="D2" s="6">
         <v>36.4</v>
       </c>
-      <c r="E2" s="11">
+      <c r="E2" s="6">
         <v>30</v>
       </c>
-      <c r="F2" s="11">
+      <c r="F2" s="6">
         <v>-5.5</v>
       </c>
-      <c r="G2" s="11">
+      <c r="G2" s="6">
         <v>-3.1</v>
       </c>
-      <c r="H2" s="11">
+      <c r="H2" s="6">
         <v>57</v>
       </c>
-      <c r="I2" s="11">
+      <c r="I2" s="6">
         <v>10</v>
       </c>
     </row>
@@ -3141,48 +1983,48 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:7">
-      <c r="A1" s="13" t="s">
+      <c r="A1" s="8" t="s">
         <v>37</v>
       </c>
-      <c r="B1" s="13" t="s">
+      <c r="B1" s="8" t="s">
         <v>41</v>
       </c>
-      <c r="C1" s="13" t="s">
+      <c r="C1" s="8" t="s">
         <v>38</v>
       </c>
-      <c r="D1" s="13" t="s">
+      <c r="D1" s="8" t="s">
         <v>43</v>
       </c>
-      <c r="E1" s="13" t="s">
+      <c r="E1" s="8" t="s">
         <v>42</v>
       </c>
-      <c r="F1" s="13" t="s">
+      <c r="F1" s="8" t="s">
         <v>40</v>
       </c>
-      <c r="G1" s="13" t="s">
+      <c r="G1" s="8" t="s">
         <v>39</v>
       </c>
     </row>
     <row r="2" spans="1:7">
-      <c r="A2" s="14">
+      <c r="A2" s="9">
         <v>0.2314</v>
       </c>
-      <c r="B2" s="14">
+      <c r="B2" s="9">
         <v>0.1886</v>
       </c>
-      <c r="C2" s="14">
+      <c r="C2" s="9">
         <v>0.1605</v>
       </c>
-      <c r="D2" s="14">
+      <c r="D2" s="9">
         <v>0.0479</v>
       </c>
-      <c r="E2" s="14">
+      <c r="E2" s="9">
         <v>0.0473</v>
       </c>
-      <c r="F2" s="14">
+      <c r="F2" s="9">
         <v>-0.005</v>
       </c>
-      <c r="G2" s="14">
+      <c r="G2" s="9">
         <v>-0.2399</v>
       </c>
     </row>

--- a/BAJAJ_GROUP_Technical_Metrics.xlsx
+++ b/BAJAJ_GROUP_Technical_Metrics.xlsx
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="137" uniqueCount="61">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="276" uniqueCount="80">
   <si>
     <t>Symbol</t>
   </si>
@@ -172,13 +172,70 @@
     <t>▶  SIGNAL EVENTS (vs Previous Run)</t>
   </si>
   <si>
-    <t>No signal events detected since last run.</t>
+    <t>Signal</t>
+  </si>
+  <si>
+    <t>Change</t>
+  </si>
+  <si>
+    <t>Direction</t>
+  </si>
+  <si>
+    <t>Prev Value</t>
+  </si>
+  <si>
+    <t>Curr Value</t>
+  </si>
+  <si>
+    <t>RSI Momentum</t>
+  </si>
+  <si>
+    <t>45.8 → 52.9</t>
+  </si>
+  <si>
+    <t>🟢 BULLISH</t>
+  </si>
+  <si>
+    <t>45.8</t>
+  </si>
+  <si>
+    <t>52.9</t>
+  </si>
+  <si>
+    <t>RSI Oversold Recovery</t>
+  </si>
+  <si>
+    <t>24.8 → 34.2</t>
+  </si>
+  <si>
+    <t>24.8</t>
+  </si>
+  <si>
+    <t>34.2</t>
+  </si>
+  <si>
+    <t>25.5 → 32.9</t>
+  </si>
+  <si>
+    <t>25.5</t>
+  </si>
+  <si>
+    <t>32.9</t>
   </si>
   <si>
     <t>▶  NUMERIC METRIC CHANGES (vs Previous Run)</t>
   </si>
   <si>
-    <t>No numeric changes detected since last run.</t>
+    <t>Metric</t>
+  </si>
+  <si>
+    <t>Previous</t>
+  </si>
+  <si>
+    <t>Current</t>
+  </si>
+  <si>
+    <t>Delta</t>
   </si>
   <si>
     <t>Rank</t>
@@ -209,11 +266,13 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="2">
-    <numFmt numFmtId="164" formatCode="0.0"/>
-    <numFmt numFmtId="165" formatCode="0.00%"/>
+  <numFmts count="4">
+    <numFmt numFmtId="164" formatCode="0.00"/>
+    <numFmt numFmtId="165" formatCode="+0.00;-0.00"/>
+    <numFmt numFmtId="166" formatCode="0.0"/>
+    <numFmt numFmtId="167" formatCode="0.00%"/>
   </numFmts>
-  <fonts count="4">
+  <fonts count="6">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -245,8 +304,22 @@
       <family val="2"/>
       <scheme val="minor"/>
     </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF006100"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF9C0006"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
   </fonts>
-  <fills count="6">
+  <fills count="9">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -262,6 +335,24 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="FF2E4057"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF4A6FA5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFC6EFCE"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFC7CE"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -331,27 +422,34 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="10">
+  <cellXfs count="15">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="2" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="3" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="3" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1"/>
+    <xf numFmtId="165" fontId="4" fillId="5" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="165" fontId="5" fillId="6" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="3" fillId="7" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="8" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="166" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="5" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="8" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="165" fontId="0" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="167" fontId="0" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
     </xf>
   </cellXfs>
@@ -847,10 +945,10 @@
         <v>44</v>
       </c>
       <c r="C2">
-        <v>9637</v>
+        <v>9778</v>
       </c>
       <c r="D2">
-        <v>-2.5</v>
+        <v>1.46</v>
       </c>
       <c r="E2">
         <v>12361</v>
@@ -859,25 +957,25 @@
         <v>8599.48</v>
       </c>
       <c r="G2">
-        <v>-22.04</v>
+        <v>-20.9</v>
       </c>
       <c r="H2">
-        <v>12.06</v>
+        <v>13.7</v>
       </c>
       <c r="I2">
-        <v>-11.38</v>
+        <v>-2.66</v>
       </c>
       <c r="J2">
-        <v>-18.33</v>
+        <v>-17.69</v>
       </c>
       <c r="K2">
-        <v>-5.1</v>
+        <v>-3.72</v>
       </c>
       <c r="L2">
-        <v>12.59</v>
+        <v>12.78</v>
       </c>
       <c r="M2">
-        <v>23.14</v>
+        <v>23.29</v>
       </c>
       <c r="N2">
         <v>71</v>
@@ -886,19 +984,19 @@
         <v>66</v>
       </c>
       <c r="P2">
-        <v>9921.4</v>
+        <v>9868</v>
       </c>
       <c r="Q2">
-        <v>11009.75</v>
+        <v>10909.15</v>
       </c>
       <c r="R2">
-        <v>11462.89</v>
+        <v>11431.69</v>
       </c>
       <c r="S2">
-        <v>10161.9</v>
+        <v>10166.41</v>
       </c>
       <c r="T2">
-        <v>-5.17</v>
+        <v>-3.82</v>
       </c>
       <c r="U2" t="s">
         <v>45</v>
@@ -913,34 +1011,34 @@
         <v>1</v>
       </c>
       <c r="Y2">
-        <v>17.92</v>
+        <v>23.2</v>
       </c>
       <c r="Z2">
-        <v>-460.1</v>
+        <v>-481.74</v>
       </c>
       <c r="AA2">
-        <v>-284.62</v>
+        <v>-324.04</v>
       </c>
       <c r="AB2">
-        <v>-175.48</v>
+        <v>-157.7</v>
       </c>
       <c r="AC2">
-        <v>0</v>
+        <v>6.72</v>
       </c>
       <c r="AD2">
-        <v>0</v>
+        <v>2.24</v>
       </c>
       <c r="AE2">
-        <v>246</v>
+        <v>252.07</v>
       </c>
       <c r="AF2">
-        <v>-29.09</v>
+        <v>-12.39</v>
       </c>
       <c r="AG2">
-        <v>12404.21</v>
+        <v>12355.92</v>
       </c>
       <c r="AH2">
-        <v>9615.290000000001</v>
+        <v>9462.379999999999</v>
       </c>
       <c r="AI2">
         <v>10503.51</v>
@@ -949,7 +1047,7 @@
         <v>47</v>
       </c>
       <c r="AK2">
-        <v>77.77</v>
+        <v>78.28</v>
       </c>
     </row>
     <row r="3" spans="1:37">
@@ -960,10 +1058,10 @@
         <v>44</v>
       </c>
       <c r="C3">
-        <v>489.15</v>
+        <v>506.95</v>
       </c>
       <c r="D3">
-        <v>1.27</v>
+        <v>3.64</v>
       </c>
       <c r="E3">
         <v>670.25</v>
@@ -972,25 +1070,25 @@
         <v>241.91</v>
       </c>
       <c r="G3">
-        <v>-27.02</v>
+        <v>-24.36</v>
       </c>
       <c r="H3">
-        <v>102.2</v>
+        <v>109.56</v>
       </c>
       <c r="I3">
-        <v>-1.29</v>
+        <v>1.99</v>
       </c>
       <c r="J3">
-        <v>-7.01</v>
+        <v>-1.39</v>
       </c>
       <c r="K3">
-        <v>-23.99</v>
+        <v>-24.36</v>
       </c>
       <c r="L3">
-        <v>104.38</v>
+        <v>108.96</v>
       </c>
       <c r="M3">
-        <v>16.05</v>
+        <v>16.29</v>
       </c>
       <c r="N3">
         <v>99</v>
@@ -999,19 +1097,19 @@
         <v>90</v>
       </c>
       <c r="P3">
-        <v>488.61</v>
+        <v>490.59</v>
       </c>
       <c r="Q3">
-        <v>501.53</v>
+        <v>500.81</v>
       </c>
       <c r="R3">
-        <v>503.81</v>
+        <v>503.22</v>
       </c>
       <c r="S3">
-        <v>456.79</v>
+        <v>458.06</v>
       </c>
       <c r="T3">
-        <v>7.08</v>
+        <v>10.67</v>
       </c>
       <c r="U3" t="s">
         <v>45</v>
@@ -1026,34 +1124,34 @@
         <v>2</v>
       </c>
       <c r="Y3">
-        <v>45.77</v>
+        <v>52.93</v>
       </c>
       <c r="Z3">
-        <v>-5.4</v>
+        <v>-3.91</v>
       </c>
       <c r="AA3">
-        <v>-4.17</v>
+        <v>-4.12</v>
       </c>
       <c r="AB3">
-        <v>-1.23</v>
+        <v>0.21</v>
       </c>
       <c r="AC3">
-        <v>44.18</v>
+        <v>58.9</v>
       </c>
       <c r="AD3">
-        <v>38.65</v>
+        <v>45</v>
       </c>
       <c r="AE3">
-        <v>19.16</v>
+        <v>19.19</v>
       </c>
       <c r="AF3">
-        <v>60.11</v>
+        <v>-8.09</v>
       </c>
       <c r="AG3">
-        <v>528.1799999999999</v>
+        <v>525.92</v>
       </c>
       <c r="AH3">
-        <v>474.88</v>
+        <v>475.69</v>
       </c>
       <c r="AI3">
         <v>460.99</v>
@@ -1062,7 +1160,7 @@
         <v>48</v>
       </c>
       <c r="AK3">
-        <v>32.93</v>
+        <v>28.97</v>
       </c>
     </row>
     <row r="4" spans="1:37">
@@ -1073,10 +1171,10 @@
         <v>44</v>
       </c>
       <c r="C4">
-        <v>290.05</v>
+        <v>298</v>
       </c>
       <c r="D4">
-        <v>-3.54</v>
+        <v>2.74</v>
       </c>
       <c r="E4">
         <v>548</v>
@@ -1085,25 +1183,25 @@
         <v>290.05</v>
       </c>
       <c r="G4">
-        <v>-47.07</v>
+        <v>-45.62</v>
       </c>
       <c r="H4">
-        <v>0</v>
+        <v>2.74</v>
       </c>
       <c r="I4">
-        <v>-4.4</v>
+        <v>-0.6</v>
       </c>
       <c r="J4">
-        <v>-15.21</v>
+        <v>-12.34</v>
       </c>
       <c r="K4">
-        <v>-11.23</v>
+        <v>-10</v>
       </c>
       <c r="L4">
-        <v>-46.68</v>
+        <v>-45.06</v>
       </c>
       <c r="M4">
-        <v>-23.99</v>
+        <v>-23.69</v>
       </c>
       <c r="N4">
         <v>15</v>
@@ -1112,19 +1210,19 @@
         <v>12</v>
       </c>
       <c r="P4">
-        <v>298.01</v>
+        <v>297.65</v>
       </c>
       <c r="Q4">
-        <v>317.47</v>
+        <v>315.38</v>
       </c>
       <c r="R4">
-        <v>334.48</v>
+        <v>333.83</v>
       </c>
       <c r="S4">
-        <v>364.4</v>
+        <v>363.49</v>
       </c>
       <c r="T4">
-        <v>-20.4</v>
+        <v>-18.02</v>
       </c>
       <c r="U4" t="s">
         <v>45</v>
@@ -1139,34 +1237,34 @@
         <v>0</v>
       </c>
       <c r="Y4">
-        <v>24.79</v>
+        <v>34.16</v>
       </c>
       <c r="Z4">
-        <v>-10.69</v>
+        <v>-10.62</v>
       </c>
       <c r="AA4">
-        <v>-8.369999999999999</v>
+        <v>-8.82</v>
       </c>
       <c r="AB4">
-        <v>-2.32</v>
+        <v>-1.8</v>
       </c>
       <c r="AC4">
-        <v>5.81</v>
+        <v>18.1</v>
       </c>
       <c r="AD4">
-        <v>4.66</v>
+        <v>9.91</v>
       </c>
       <c r="AE4">
-        <v>9.31</v>
+        <v>9.380000000000001</v>
       </c>
       <c r="AF4">
-        <v>18.01</v>
+        <v>-23.71</v>
       </c>
       <c r="AG4">
-        <v>346.39</v>
+        <v>343.53</v>
       </c>
       <c r="AH4">
-        <v>288.55</v>
+        <v>287.22</v>
       </c>
       <c r="AI4">
         <v>322.52</v>
@@ -1175,7 +1273,7 @@
         <v>47</v>
       </c>
       <c r="AK4">
-        <v>48.25</v>
+        <v>52.04</v>
       </c>
     </row>
     <row r="5" spans="1:37">
@@ -1186,10 +1284,10 @@
         <v>44</v>
       </c>
       <c r="C5">
-        <v>1708</v>
+        <v>1734.7</v>
       </c>
       <c r="D5">
-        <v>-2.02</v>
+        <v>1.56</v>
       </c>
       <c r="E5">
         <v>2176.6</v>
@@ -1198,25 +1296,25 @@
         <v>1631.8</v>
       </c>
       <c r="G5">
-        <v>-21.53</v>
+        <v>-20.3</v>
       </c>
       <c r="H5">
-        <v>4.67</v>
+        <v>6.31</v>
       </c>
       <c r="I5">
-        <v>-1.33</v>
+        <v>0.12</v>
       </c>
       <c r="J5">
-        <v>-11.9</v>
+        <v>-10.49</v>
       </c>
       <c r="K5">
-        <v>-9.869999999999999</v>
+        <v>-9.460000000000001</v>
       </c>
       <c r="L5">
-        <v>-14.64</v>
+        <v>-14.68</v>
       </c>
       <c r="M5">
-        <v>-0.5</v>
+        <v>-0.38</v>
       </c>
       <c r="N5">
         <v>29</v>
@@ -1225,19 +1323,19 @@
         <v>42</v>
       </c>
       <c r="P5">
-        <v>1737.54</v>
+        <v>1737.96</v>
       </c>
       <c r="Q5">
-        <v>1807.57</v>
+        <v>1797.95</v>
       </c>
       <c r="R5">
-        <v>1928.61</v>
+        <v>1924.81</v>
       </c>
       <c r="S5">
-        <v>1878.69</v>
+        <v>1877.15</v>
       </c>
       <c r="T5">
-        <v>-9.09</v>
+        <v>-7.59</v>
       </c>
       <c r="U5" t="s">
         <v>45</v>
@@ -1252,34 +1350,34 @@
         <v>1</v>
       </c>
       <c r="Y5">
-        <v>25.47</v>
+        <v>32.87</v>
       </c>
       <c r="Z5">
-        <v>-57.91</v>
+        <v>-56.11</v>
       </c>
       <c r="AA5">
-        <v>-53.74</v>
+        <v>-54.21</v>
       </c>
       <c r="AB5">
-        <v>-4.17</v>
+        <v>-1.89</v>
       </c>
       <c r="AC5">
-        <v>36.6</v>
+        <v>43.8</v>
       </c>
       <c r="AD5">
-        <v>42.2</v>
+        <v>44.14</v>
       </c>
       <c r="AE5">
-        <v>35.44</v>
+        <v>35.98</v>
       </c>
       <c r="AF5">
-        <v>45.15</v>
+        <v>-9.69</v>
       </c>
       <c r="AG5">
-        <v>1950.47</v>
+        <v>1932.66</v>
       </c>
       <c r="AH5">
-        <v>1664.66</v>
+        <v>1663.24</v>
       </c>
       <c r="AI5">
         <v>1825.61</v>
@@ -1288,7 +1386,7 @@
         <v>47</v>
       </c>
       <c r="AK5">
-        <v>69.98</v>
+        <v>67.17</v>
       </c>
     </row>
     <row r="6" spans="1:37">
@@ -1299,10 +1397,10 @@
         <v>44</v>
       </c>
       <c r="C6">
-        <v>10600</v>
+        <v>10820</v>
       </c>
       <c r="D6">
-        <v>-0.58</v>
+        <v>2.08</v>
       </c>
       <c r="E6">
         <v>13144</v>
@@ -1311,25 +1409,25 @@
         <v>8746</v>
       </c>
       <c r="G6">
-        <v>-19.35</v>
+        <v>-17.68</v>
       </c>
       <c r="H6">
-        <v>21.2</v>
+        <v>23.71</v>
       </c>
       <c r="I6">
-        <v>-1.74</v>
+        <v>1.44</v>
       </c>
       <c r="J6">
-        <v>-3.25</v>
+        <v>-2.05</v>
       </c>
       <c r="K6">
-        <v>0.18</v>
+        <v>1.56</v>
       </c>
       <c r="L6">
-        <v>-10.31</v>
+        <v>-8.32</v>
       </c>
       <c r="M6">
-        <v>18.86</v>
+        <v>19.45</v>
       </c>
       <c r="N6">
         <v>57</v>
@@ -1338,19 +1436,19 @@
         <v>59</v>
       </c>
       <c r="P6">
-        <v>10652</v>
+        <v>10682.8</v>
       </c>
       <c r="Q6">
-        <v>10943.7</v>
+        <v>10930.8</v>
       </c>
       <c r="R6">
-        <v>11176</v>
+        <v>11173.42</v>
       </c>
       <c r="S6">
-        <v>10668.16</v>
+        <v>10666.52</v>
       </c>
       <c r="T6">
-        <v>-0.64</v>
+        <v>1.44</v>
       </c>
       <c r="U6" t="s">
         <v>45</v>
@@ -1362,37 +1460,37 @@
         <v>45</v>
       </c>
       <c r="X6">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="Y6">
-        <v>40.75</v>
+        <v>47.07</v>
       </c>
       <c r="Z6">
-        <v>-147.46</v>
+        <v>-133.98</v>
       </c>
       <c r="AA6">
-        <v>-105.08</v>
+        <v>-110.86</v>
       </c>
       <c r="AB6">
-        <v>-42.38</v>
+        <v>-23.12</v>
       </c>
       <c r="AC6">
-        <v>13.9</v>
+        <v>26.19</v>
       </c>
       <c r="AD6">
-        <v>15.91</v>
+        <v>19.29</v>
       </c>
       <c r="AE6">
-        <v>258.57</v>
+        <v>256.1</v>
       </c>
       <c r="AF6">
-        <v>32.58</v>
+        <v>-72.03</v>
       </c>
       <c r="AG6">
-        <v>11473.13</v>
+        <v>11459.02</v>
       </c>
       <c r="AH6">
-        <v>10414.27</v>
+        <v>10402.58</v>
       </c>
       <c r="AI6">
         <v>11368.55</v>
@@ -1401,7 +1499,7 @@
         <v>47</v>
       </c>
       <c r="AK6">
-        <v>34.46</v>
+        <v>33.17</v>
       </c>
     </row>
     <row r="7" spans="1:37">
@@ -1412,10 +1510,10 @@
         <v>44</v>
       </c>
       <c r="C7">
-        <v>955.95</v>
+        <v>960</v>
       </c>
       <c r="D7">
-        <v>-0.82</v>
+        <v>0.42</v>
       </c>
       <c r="E7">
         <v>1158.8</v>
@@ -1424,25 +1522,25 @@
         <v>801.55</v>
       </c>
       <c r="G7">
-        <v>-17.51</v>
+        <v>-17.16</v>
       </c>
       <c r="H7">
-        <v>19.26</v>
+        <v>19.77</v>
       </c>
       <c r="I7">
-        <v>-0.36</v>
+        <v>1.23</v>
       </c>
       <c r="J7">
-        <v>-9.82</v>
+        <v>-8.93</v>
       </c>
       <c r="K7">
-        <v>-4.77</v>
+        <v>-5.93</v>
       </c>
       <c r="L7">
-        <v>-3.42</v>
+        <v>-4.85</v>
       </c>
       <c r="M7">
-        <v>4.73</v>
+        <v>4.6</v>
       </c>
       <c r="N7">
         <v>43</v>
@@ -1451,19 +1549,19 @@
         <v>58</v>
       </c>
       <c r="P7">
-        <v>960.24</v>
+        <v>962.58</v>
       </c>
       <c r="Q7">
-        <v>997.98</v>
+        <v>994.01</v>
       </c>
       <c r="R7">
-        <v>1052.33</v>
+        <v>1050.44</v>
       </c>
       <c r="S7">
-        <v>975.53</v>
+        <v>975.29</v>
       </c>
       <c r="T7">
-        <v>-2.01</v>
+        <v>-1.57</v>
       </c>
       <c r="U7" t="s">
         <v>45</v>
@@ -1478,34 +1576,34 @@
         <v>1</v>
       </c>
       <c r="Y7">
-        <v>36.21</v>
+        <v>37.62</v>
       </c>
       <c r="Z7">
-        <v>-25.86</v>
+        <v>-25.39</v>
       </c>
       <c r="AA7">
-        <v>-22.99</v>
+        <v>-23.47</v>
       </c>
       <c r="AB7">
-        <v>-2.88</v>
+        <v>-1.93</v>
       </c>
       <c r="AC7">
-        <v>31.19</v>
+        <v>29.89</v>
       </c>
       <c r="AD7">
-        <v>32.5</v>
+        <v>32.89</v>
       </c>
       <c r="AE7">
-        <v>25.43</v>
+        <v>24.85</v>
       </c>
       <c r="AF7">
-        <v>38.49</v>
+        <v>9.17</v>
       </c>
       <c r="AG7">
-        <v>1062.85</v>
+        <v>1057.94</v>
       </c>
       <c r="AH7">
-        <v>933.11</v>
+        <v>930.09</v>
       </c>
       <c r="AI7">
         <v>1020.6</v>
@@ -1514,7 +1612,7 @@
         <v>47</v>
       </c>
       <c r="AK7">
-        <v>32.37</v>
+        <v>28.61</v>
       </c>
     </row>
     <row r="8" spans="1:37">
@@ -1525,10 +1623,10 @@
         <v>44</v>
       </c>
       <c r="C8">
-        <v>174.29</v>
+        <v>175.99</v>
       </c>
       <c r="D8">
-        <v>-6.26</v>
+        <v>0.98</v>
       </c>
       <c r="E8">
         <v>185.92</v>
@@ -1537,25 +1635,25 @@
         <v>115.96</v>
       </c>
       <c r="G8">
-        <v>-6.26</v>
+        <v>-5.34</v>
       </c>
       <c r="H8">
-        <v>50.3</v>
+        <v>51.77</v>
       </c>
       <c r="I8">
-        <v>-3.24</v>
+        <v>1.93</v>
       </c>
       <c r="J8">
-        <v>27.31</v>
+        <v>27.84</v>
       </c>
       <c r="K8">
-        <v>33.27</v>
+        <v>32.44</v>
       </c>
       <c r="L8">
-        <v>22.3</v>
+        <v>26.58</v>
       </c>
       <c r="M8">
-        <v>4.79</v>
+        <v>4.85</v>
       </c>
       <c r="N8">
         <v>85</v>
@@ -1564,19 +1662,19 @@
         <v>89</v>
       </c>
       <c r="P8">
-        <v>179.32</v>
+        <v>179.99</v>
       </c>
       <c r="Q8">
-        <v>156.92</v>
+        <v>158.73</v>
       </c>
       <c r="R8">
-        <v>145.4</v>
+        <v>146.13</v>
       </c>
       <c r="S8">
-        <v>136.11</v>
+        <v>136.33</v>
       </c>
       <c r="T8">
-        <v>28.05</v>
+        <v>29.09</v>
       </c>
       <c r="U8" t="s">
         <v>46</v>
@@ -1591,34 +1689,34 @@
         <v>3</v>
       </c>
       <c r="Y8">
-        <v>63.74</v>
+        <v>64.75</v>
       </c>
       <c r="Z8">
-        <v>11.52</v>
+        <v>11.14</v>
       </c>
       <c r="AA8">
-        <v>8.99</v>
+        <v>9.42</v>
       </c>
       <c r="AB8">
-        <v>2.52</v>
+        <v>1.72</v>
       </c>
       <c r="AC8">
-        <v>70.95999999999999</v>
+        <v>59.68</v>
       </c>
       <c r="AD8">
-        <v>77.09999999999999</v>
+        <v>71</v>
       </c>
       <c r="AE8">
-        <v>8.890000000000001</v>
+        <v>8.58</v>
       </c>
       <c r="AF8">
-        <v>-20.14</v>
+        <v>-58.21</v>
       </c>
       <c r="AG8">
-        <v>195.72</v>
+        <v>197.54</v>
       </c>
       <c r="AH8">
-        <v>118.12</v>
+        <v>119.93</v>
       </c>
       <c r="AI8">
         <v>159.98</v>
@@ -1627,7 +1725,7 @@
         <v>48</v>
       </c>
       <c r="AK8">
-        <v>54.09</v>
+        <v>51.22</v>
       </c>
     </row>
   </sheetData>
@@ -1768,7 +1866,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:F6"/>
+  <dimension ref="A1:F64"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="16.7109375" customWidth="1"/>
@@ -1788,27 +1886,1066 @@
     </row>
     <row r="2" spans="1:6">
       <c r="A2" s="3" t="s">
+        <v>0</v>
+      </c>
+      <c r="B2" s="3" t="s">
         <v>50</v>
       </c>
+      <c r="C2" s="3" t="s">
+        <v>51</v>
+      </c>
+      <c r="D2" s="3" t="s">
+        <v>52</v>
+      </c>
+      <c r="E2" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="F2" s="3" t="s">
+        <v>54</v>
+      </c>
+    </row>
+    <row r="3" spans="1:6">
+      <c r="A3" s="4" t="s">
+        <v>38</v>
+      </c>
+      <c r="B3" s="4" t="s">
+        <v>55</v>
+      </c>
+      <c r="C3" s="4" t="s">
+        <v>56</v>
+      </c>
+      <c r="D3" s="4" t="s">
+        <v>57</v>
+      </c>
+      <c r="E3" s="4" t="s">
+        <v>58</v>
+      </c>
+      <c r="F3" s="4" t="s">
+        <v>59</v>
+      </c>
+    </row>
+    <row r="4" spans="1:6">
+      <c r="A4" s="4" t="s">
+        <v>39</v>
+      </c>
+      <c r="B4" s="4" t="s">
+        <v>60</v>
+      </c>
+      <c r="C4" s="4" t="s">
+        <v>61</v>
+      </c>
+      <c r="D4" s="4" t="s">
+        <v>57</v>
+      </c>
+      <c r="E4" s="4" t="s">
+        <v>62</v>
+      </c>
+      <c r="F4" s="4" t="s">
+        <v>63</v>
+      </c>
     </row>
     <row r="5" spans="1:6">
-      <c r="A5" s="2" t="s">
-        <v>51</v>
-      </c>
-      <c r="B5" s="2"/>
-      <c r="C5" s="2"/>
-      <c r="D5" s="2"/>
-      <c r="E5" s="2"/>
-    </row>
-    <row r="6" spans="1:6">
-      <c r="A6" s="3" t="s">
-        <v>52</v>
+      <c r="A5" s="4" t="s">
+        <v>40</v>
+      </c>
+      <c r="B5" s="4" t="s">
+        <v>60</v>
+      </c>
+      <c r="C5" s="4" t="s">
+        <v>64</v>
+      </c>
+      <c r="D5" s="4" t="s">
+        <v>57</v>
+      </c>
+      <c r="E5" s="4" t="s">
+        <v>65</v>
+      </c>
+      <c r="F5" s="4" t="s">
+        <v>66</v>
+      </c>
+    </row>
+    <row r="7" spans="1:6">
+      <c r="A7" s="2" t="s">
+        <v>67</v>
+      </c>
+      <c r="B7" s="2"/>
+      <c r="C7" s="2"/>
+      <c r="D7" s="2"/>
+      <c r="E7" s="2"/>
+    </row>
+    <row r="8" spans="1:6">
+      <c r="A8" s="3" t="s">
+        <v>0</v>
+      </c>
+      <c r="B8" s="3" t="s">
+        <v>68</v>
+      </c>
+      <c r="C8" s="3" t="s">
+        <v>69</v>
+      </c>
+      <c r="D8" s="3" t="s">
+        <v>70</v>
+      </c>
+      <c r="E8" s="3" t="s">
+        <v>71</v>
+      </c>
+    </row>
+    <row r="9" spans="1:6">
+      <c r="A9" s="5" t="s">
+        <v>37</v>
+      </c>
+      <c r="B9" s="5" t="s">
+        <v>9</v>
+      </c>
+      <c r="C9" s="6">
+        <v>-18.33</v>
+      </c>
+      <c r="D9" s="6">
+        <v>-17.69</v>
+      </c>
+      <c r="E9" s="7">
+        <v>0.64</v>
+      </c>
+    </row>
+    <row r="10" spans="1:6">
+      <c r="A10" s="5" t="s">
+        <v>38</v>
+      </c>
+      <c r="B10" s="5" t="s">
+        <v>9</v>
+      </c>
+      <c r="C10" s="6">
+        <v>-7.01</v>
+      </c>
+      <c r="D10" s="6">
+        <v>-1.39</v>
+      </c>
+      <c r="E10" s="7">
+        <v>5.62</v>
+      </c>
+    </row>
+    <row r="11" spans="1:6">
+      <c r="A11" s="5" t="s">
+        <v>39</v>
+      </c>
+      <c r="B11" s="5" t="s">
+        <v>9</v>
+      </c>
+      <c r="C11" s="6">
+        <v>-15.21</v>
+      </c>
+      <c r="D11" s="6">
+        <v>-12.34</v>
+      </c>
+      <c r="E11" s="7">
+        <v>2.87</v>
+      </c>
+    </row>
+    <row r="12" spans="1:6">
+      <c r="A12" s="5" t="s">
+        <v>40</v>
+      </c>
+      <c r="B12" s="5" t="s">
+        <v>9</v>
+      </c>
+      <c r="C12" s="6">
+        <v>-11.9</v>
+      </c>
+      <c r="D12" s="6">
+        <v>-10.49</v>
+      </c>
+      <c r="E12" s="7">
+        <v>1.41</v>
+      </c>
+    </row>
+    <row r="13" spans="1:6">
+      <c r="A13" s="5" t="s">
+        <v>41</v>
+      </c>
+      <c r="B13" s="5" t="s">
+        <v>9</v>
+      </c>
+      <c r="C13" s="6">
+        <v>-3.25</v>
+      </c>
+      <c r="D13" s="6">
+        <v>-2.05</v>
+      </c>
+      <c r="E13" s="7">
+        <v>1.2</v>
+      </c>
+    </row>
+    <row r="14" spans="1:6">
+      <c r="A14" s="5" t="s">
+        <v>42</v>
+      </c>
+      <c r="B14" s="5" t="s">
+        <v>9</v>
+      </c>
+      <c r="C14" s="6">
+        <v>-9.82</v>
+      </c>
+      <c r="D14" s="6">
+        <v>-8.93</v>
+      </c>
+      <c r="E14" s="7">
+        <v>0.89</v>
+      </c>
+    </row>
+    <row r="15" spans="1:6">
+      <c r="A15" s="5" t="s">
+        <v>43</v>
+      </c>
+      <c r="B15" s="5" t="s">
+        <v>9</v>
+      </c>
+      <c r="C15" s="6">
+        <v>27.31</v>
+      </c>
+      <c r="D15" s="6">
+        <v>27.84</v>
+      </c>
+      <c r="E15" s="7">
+        <v>0.53</v>
+      </c>
+    </row>
+    <row r="16" spans="1:6">
+      <c r="A16" s="5" t="s">
+        <v>37</v>
+      </c>
+      <c r="B16" s="5" t="s">
+        <v>8</v>
+      </c>
+      <c r="C16" s="6">
+        <v>-11.38</v>
+      </c>
+      <c r="D16" s="6">
+        <v>-2.66</v>
+      </c>
+      <c r="E16" s="7">
+        <v>8.720000000000001</v>
+      </c>
+    </row>
+    <row r="17" spans="1:5">
+      <c r="A17" s="5" t="s">
+        <v>38</v>
+      </c>
+      <c r="B17" s="5" t="s">
+        <v>8</v>
+      </c>
+      <c r="C17" s="6">
+        <v>-1.29</v>
+      </c>
+      <c r="D17" s="6">
+        <v>1.99</v>
+      </c>
+      <c r="E17" s="7">
+        <v>3.28</v>
+      </c>
+    </row>
+    <row r="18" spans="1:5">
+      <c r="A18" s="5" t="s">
+        <v>39</v>
+      </c>
+      <c r="B18" s="5" t="s">
+        <v>8</v>
+      </c>
+      <c r="C18" s="6">
+        <v>-4.4</v>
+      </c>
+      <c r="D18" s="6">
+        <v>-0.6</v>
+      </c>
+      <c r="E18" s="7">
+        <v>3.8</v>
+      </c>
+    </row>
+    <row r="19" spans="1:5">
+      <c r="A19" s="5" t="s">
+        <v>40</v>
+      </c>
+      <c r="B19" s="5" t="s">
+        <v>8</v>
+      </c>
+      <c r="C19" s="6">
+        <v>-1.33</v>
+      </c>
+      <c r="D19" s="6">
+        <v>0.12</v>
+      </c>
+      <c r="E19" s="7">
+        <v>1.45</v>
+      </c>
+    </row>
+    <row r="20" spans="1:5">
+      <c r="A20" s="5" t="s">
+        <v>41</v>
+      </c>
+      <c r="B20" s="5" t="s">
+        <v>8</v>
+      </c>
+      <c r="C20" s="6">
+        <v>-1.74</v>
+      </c>
+      <c r="D20" s="6">
+        <v>1.44</v>
+      </c>
+      <c r="E20" s="7">
+        <v>3.18</v>
+      </c>
+    </row>
+    <row r="21" spans="1:5">
+      <c r="A21" s="5" t="s">
+        <v>42</v>
+      </c>
+      <c r="B21" s="5" t="s">
+        <v>8</v>
+      </c>
+      <c r="C21" s="6">
+        <v>-0.36</v>
+      </c>
+      <c r="D21" s="6">
+        <v>1.23</v>
+      </c>
+      <c r="E21" s="7">
+        <v>1.59</v>
+      </c>
+    </row>
+    <row r="22" spans="1:5">
+      <c r="A22" s="5" t="s">
+        <v>43</v>
+      </c>
+      <c r="B22" s="5" t="s">
+        <v>8</v>
+      </c>
+      <c r="C22" s="6">
+        <v>-3.24</v>
+      </c>
+      <c r="D22" s="6">
+        <v>1.93</v>
+      </c>
+      <c r="E22" s="7">
+        <v>5.17</v>
+      </c>
+    </row>
+    <row r="23" spans="1:5">
+      <c r="A23" s="5" t="s">
+        <v>37</v>
+      </c>
+      <c r="B23" s="5" t="s">
+        <v>11</v>
+      </c>
+      <c r="C23" s="6">
+        <v>12.59</v>
+      </c>
+      <c r="D23" s="6">
+        <v>12.78</v>
+      </c>
+      <c r="E23" s="7">
+        <v>0.19</v>
+      </c>
+    </row>
+    <row r="24" spans="1:5">
+      <c r="A24" s="5" t="s">
+        <v>38</v>
+      </c>
+      <c r="B24" s="5" t="s">
+        <v>11</v>
+      </c>
+      <c r="C24" s="6">
+        <v>104.38</v>
+      </c>
+      <c r="D24" s="6">
+        <v>108.96</v>
+      </c>
+      <c r="E24" s="7">
+        <v>4.58</v>
+      </c>
+    </row>
+    <row r="25" spans="1:5">
+      <c r="A25" s="5" t="s">
+        <v>39</v>
+      </c>
+      <c r="B25" s="5" t="s">
+        <v>11</v>
+      </c>
+      <c r="C25" s="6">
+        <v>-46.68</v>
+      </c>
+      <c r="D25" s="6">
+        <v>-45.06</v>
+      </c>
+      <c r="E25" s="7">
+        <v>1.62</v>
+      </c>
+    </row>
+    <row r="26" spans="1:5">
+      <c r="A26" s="5" t="s">
+        <v>40</v>
+      </c>
+      <c r="B26" s="5" t="s">
+        <v>11</v>
+      </c>
+      <c r="C26" s="6">
+        <v>-14.64</v>
+      </c>
+      <c r="D26" s="6">
+        <v>-14.68</v>
+      </c>
+      <c r="E26" s="8">
+        <v>-0.04</v>
+      </c>
+    </row>
+    <row r="27" spans="1:5">
+      <c r="A27" s="5" t="s">
+        <v>41</v>
+      </c>
+      <c r="B27" s="5" t="s">
+        <v>11</v>
+      </c>
+      <c r="C27" s="6">
+        <v>-10.31</v>
+      </c>
+      <c r="D27" s="6">
+        <v>-8.32</v>
+      </c>
+      <c r="E27" s="7">
+        <v>1.99</v>
+      </c>
+    </row>
+    <row r="28" spans="1:5">
+      <c r="A28" s="5" t="s">
+        <v>42</v>
+      </c>
+      <c r="B28" s="5" t="s">
+        <v>11</v>
+      </c>
+      <c r="C28" s="6">
+        <v>-3.42</v>
+      </c>
+      <c r="D28" s="6">
+        <v>-4.85</v>
+      </c>
+      <c r="E28" s="8">
+        <v>-1.43</v>
+      </c>
+    </row>
+    <row r="29" spans="1:5">
+      <c r="A29" s="5" t="s">
+        <v>43</v>
+      </c>
+      <c r="B29" s="5" t="s">
+        <v>11</v>
+      </c>
+      <c r="C29" s="6">
+        <v>22.3</v>
+      </c>
+      <c r="D29" s="6">
+        <v>26.58</v>
+      </c>
+      <c r="E29" s="7">
+        <v>4.28</v>
+      </c>
+    </row>
+    <row r="30" spans="1:5">
+      <c r="A30" s="5" t="s">
+        <v>37</v>
+      </c>
+      <c r="B30" s="5" t="s">
+        <v>10</v>
+      </c>
+      <c r="C30" s="6">
+        <v>-5.1</v>
+      </c>
+      <c r="D30" s="6">
+        <v>-3.72</v>
+      </c>
+      <c r="E30" s="7">
+        <v>1.38</v>
+      </c>
+    </row>
+    <row r="31" spans="1:5">
+      <c r="A31" s="5" t="s">
+        <v>38</v>
+      </c>
+      <c r="B31" s="5" t="s">
+        <v>10</v>
+      </c>
+      <c r="C31" s="6">
+        <v>-23.99</v>
+      </c>
+      <c r="D31" s="6">
+        <v>-24.36</v>
+      </c>
+      <c r="E31" s="8">
+        <v>-0.37</v>
+      </c>
+    </row>
+    <row r="32" spans="1:5">
+      <c r="A32" s="5" t="s">
+        <v>39</v>
+      </c>
+      <c r="B32" s="5" t="s">
+        <v>10</v>
+      </c>
+      <c r="C32" s="6">
+        <v>-11.23</v>
+      </c>
+      <c r="D32" s="6">
+        <v>-10</v>
+      </c>
+      <c r="E32" s="7">
+        <v>1.23</v>
+      </c>
+    </row>
+    <row r="33" spans="1:5">
+      <c r="A33" s="5" t="s">
+        <v>40</v>
+      </c>
+      <c r="B33" s="5" t="s">
+        <v>10</v>
+      </c>
+      <c r="C33" s="6">
+        <v>-9.869999999999999</v>
+      </c>
+      <c r="D33" s="6">
+        <v>-9.460000000000001</v>
+      </c>
+      <c r="E33" s="7">
+        <v>0.41</v>
+      </c>
+    </row>
+    <row r="34" spans="1:5">
+      <c r="A34" s="5" t="s">
+        <v>41</v>
+      </c>
+      <c r="B34" s="5" t="s">
+        <v>10</v>
+      </c>
+      <c r="C34" s="6">
+        <v>0.18</v>
+      </c>
+      <c r="D34" s="6">
+        <v>1.56</v>
+      </c>
+      <c r="E34" s="7">
+        <v>1.38</v>
+      </c>
+    </row>
+    <row r="35" spans="1:5">
+      <c r="A35" s="5" t="s">
+        <v>42</v>
+      </c>
+      <c r="B35" s="5" t="s">
+        <v>10</v>
+      </c>
+      <c r="C35" s="6">
+        <v>-4.77</v>
+      </c>
+      <c r="D35" s="6">
+        <v>-5.93</v>
+      </c>
+      <c r="E35" s="8">
+        <v>-1.16</v>
+      </c>
+    </row>
+    <row r="36" spans="1:5">
+      <c r="A36" s="5" t="s">
+        <v>43</v>
+      </c>
+      <c r="B36" s="5" t="s">
+        <v>10</v>
+      </c>
+      <c r="C36" s="6">
+        <v>33.27</v>
+      </c>
+      <c r="D36" s="6">
+        <v>32.44</v>
+      </c>
+      <c r="E36" s="8">
+        <v>-0.83</v>
+      </c>
+    </row>
+    <row r="37" spans="1:5">
+      <c r="A37" s="5" t="s">
+        <v>37</v>
+      </c>
+      <c r="B37" s="5" t="s">
+        <v>6</v>
+      </c>
+      <c r="C37" s="6">
+        <v>-22.04</v>
+      </c>
+      <c r="D37" s="6">
+        <v>-20.9</v>
+      </c>
+      <c r="E37" s="7">
+        <v>1.14</v>
+      </c>
+    </row>
+    <row r="38" spans="1:5">
+      <c r="A38" s="5" t="s">
+        <v>38</v>
+      </c>
+      <c r="B38" s="5" t="s">
+        <v>6</v>
+      </c>
+      <c r="C38" s="6">
+        <v>-27.02</v>
+      </c>
+      <c r="D38" s="6">
+        <v>-24.36</v>
+      </c>
+      <c r="E38" s="7">
+        <v>2.66</v>
+      </c>
+    </row>
+    <row r="39" spans="1:5">
+      <c r="A39" s="5" t="s">
+        <v>39</v>
+      </c>
+      <c r="B39" s="5" t="s">
+        <v>6</v>
+      </c>
+      <c r="C39" s="6">
+        <v>-47.07</v>
+      </c>
+      <c r="D39" s="6">
+        <v>-45.62</v>
+      </c>
+      <c r="E39" s="7">
+        <v>1.45</v>
+      </c>
+    </row>
+    <row r="40" spans="1:5">
+      <c r="A40" s="5" t="s">
+        <v>40</v>
+      </c>
+      <c r="B40" s="5" t="s">
+        <v>6</v>
+      </c>
+      <c r="C40" s="6">
+        <v>-21.53</v>
+      </c>
+      <c r="D40" s="6">
+        <v>-20.3</v>
+      </c>
+      <c r="E40" s="7">
+        <v>1.23</v>
+      </c>
+    </row>
+    <row r="41" spans="1:5">
+      <c r="A41" s="5" t="s">
+        <v>41</v>
+      </c>
+      <c r="B41" s="5" t="s">
+        <v>6</v>
+      </c>
+      <c r="C41" s="6">
+        <v>-19.35</v>
+      </c>
+      <c r="D41" s="6">
+        <v>-17.68</v>
+      </c>
+      <c r="E41" s="7">
+        <v>1.67</v>
+      </c>
+    </row>
+    <row r="42" spans="1:5">
+      <c r="A42" s="5" t="s">
+        <v>42</v>
+      </c>
+      <c r="B42" s="5" t="s">
+        <v>6</v>
+      </c>
+      <c r="C42" s="6">
+        <v>-17.51</v>
+      </c>
+      <c r="D42" s="6">
+        <v>-17.16</v>
+      </c>
+      <c r="E42" s="7">
+        <v>0.35</v>
+      </c>
+    </row>
+    <row r="43" spans="1:5">
+      <c r="A43" s="5" t="s">
+        <v>43</v>
+      </c>
+      <c r="B43" s="5" t="s">
+        <v>6</v>
+      </c>
+      <c r="C43" s="6">
+        <v>-6.26</v>
+      </c>
+      <c r="D43" s="6">
+        <v>-5.34</v>
+      </c>
+      <c r="E43" s="7">
+        <v>0.92</v>
+      </c>
+    </row>
+    <row r="44" spans="1:5">
+      <c r="A44" s="5" t="s">
+        <v>37</v>
+      </c>
+      <c r="B44" s="5" t="s">
+        <v>2</v>
+      </c>
+      <c r="C44" s="6">
+        <v>9637</v>
+      </c>
+      <c r="D44" s="6">
+        <v>9778</v>
+      </c>
+      <c r="E44" s="7">
+        <v>141</v>
+      </c>
+    </row>
+    <row r="45" spans="1:5">
+      <c r="A45" s="5" t="s">
+        <v>38</v>
+      </c>
+      <c r="B45" s="5" t="s">
+        <v>2</v>
+      </c>
+      <c r="C45" s="6">
+        <v>489.15</v>
+      </c>
+      <c r="D45" s="6">
+        <v>506.95</v>
+      </c>
+      <c r="E45" s="7">
+        <v>17.8</v>
+      </c>
+    </row>
+    <row r="46" spans="1:5">
+      <c r="A46" s="5" t="s">
+        <v>39</v>
+      </c>
+      <c r="B46" s="5" t="s">
+        <v>2</v>
+      </c>
+      <c r="C46" s="6">
+        <v>290.05</v>
+      </c>
+      <c r="D46" s="6">
+        <v>298</v>
+      </c>
+      <c r="E46" s="7">
+        <v>7.95</v>
+      </c>
+    </row>
+    <row r="47" spans="1:5">
+      <c r="A47" s="5" t="s">
+        <v>40</v>
+      </c>
+      <c r="B47" s="5" t="s">
+        <v>2</v>
+      </c>
+      <c r="C47" s="6">
+        <v>1708</v>
+      </c>
+      <c r="D47" s="6">
+        <v>1734.7</v>
+      </c>
+      <c r="E47" s="7">
+        <v>26.7</v>
+      </c>
+    </row>
+    <row r="48" spans="1:5">
+      <c r="A48" s="5" t="s">
+        <v>41</v>
+      </c>
+      <c r="B48" s="5" t="s">
+        <v>2</v>
+      </c>
+      <c r="C48" s="6">
+        <v>10600</v>
+      </c>
+      <c r="D48" s="6">
+        <v>10820</v>
+      </c>
+      <c r="E48" s="7">
+        <v>220</v>
+      </c>
+    </row>
+    <row r="49" spans="1:5">
+      <c r="A49" s="5" t="s">
+        <v>42</v>
+      </c>
+      <c r="B49" s="5" t="s">
+        <v>2</v>
+      </c>
+      <c r="C49" s="6">
+        <v>955.95</v>
+      </c>
+      <c r="D49" s="6">
+        <v>960</v>
+      </c>
+      <c r="E49" s="7">
+        <v>4.05</v>
+      </c>
+    </row>
+    <row r="50" spans="1:5">
+      <c r="A50" s="5" t="s">
+        <v>43</v>
+      </c>
+      <c r="B50" s="5" t="s">
+        <v>2</v>
+      </c>
+      <c r="C50" s="6">
+        <v>174.29</v>
+      </c>
+      <c r="D50" s="6">
+        <v>175.99</v>
+      </c>
+      <c r="E50" s="7">
+        <v>1.7</v>
+      </c>
+    </row>
+    <row r="51" spans="1:5">
+      <c r="A51" s="5" t="s">
+        <v>37</v>
+      </c>
+      <c r="B51" s="5" t="s">
+        <v>24</v>
+      </c>
+      <c r="C51" s="6">
+        <v>17.92</v>
+      </c>
+      <c r="D51" s="6">
+        <v>23.2</v>
+      </c>
+      <c r="E51" s="7">
+        <v>5.28</v>
+      </c>
+    </row>
+    <row r="52" spans="1:5">
+      <c r="A52" s="5" t="s">
+        <v>38</v>
+      </c>
+      <c r="B52" s="5" t="s">
+        <v>24</v>
+      </c>
+      <c r="C52" s="6">
+        <v>45.77</v>
+      </c>
+      <c r="D52" s="6">
+        <v>52.93</v>
+      </c>
+      <c r="E52" s="7">
+        <v>7.16</v>
+      </c>
+    </row>
+    <row r="53" spans="1:5">
+      <c r="A53" s="5" t="s">
+        <v>39</v>
+      </c>
+      <c r="B53" s="5" t="s">
+        <v>24</v>
+      </c>
+      <c r="C53" s="6">
+        <v>24.79</v>
+      </c>
+      <c r="D53" s="6">
+        <v>34.16</v>
+      </c>
+      <c r="E53" s="7">
+        <v>9.369999999999999</v>
+      </c>
+    </row>
+    <row r="54" spans="1:5">
+      <c r="A54" s="5" t="s">
+        <v>40</v>
+      </c>
+      <c r="B54" s="5" t="s">
+        <v>24</v>
+      </c>
+      <c r="C54" s="6">
+        <v>25.47</v>
+      </c>
+      <c r="D54" s="6">
+        <v>32.87</v>
+      </c>
+      <c r="E54" s="7">
+        <v>7.4</v>
+      </c>
+    </row>
+    <row r="55" spans="1:5">
+      <c r="A55" s="5" t="s">
+        <v>41</v>
+      </c>
+      <c r="B55" s="5" t="s">
+        <v>24</v>
+      </c>
+      <c r="C55" s="6">
+        <v>40.75</v>
+      </c>
+      <c r="D55" s="6">
+        <v>47.07</v>
+      </c>
+      <c r="E55" s="7">
+        <v>6.32</v>
+      </c>
+    </row>
+    <row r="56" spans="1:5">
+      <c r="A56" s="5" t="s">
+        <v>42</v>
+      </c>
+      <c r="B56" s="5" t="s">
+        <v>24</v>
+      </c>
+      <c r="C56" s="6">
+        <v>36.21</v>
+      </c>
+      <c r="D56" s="6">
+        <v>37.62</v>
+      </c>
+      <c r="E56" s="7">
+        <v>1.41</v>
+      </c>
+    </row>
+    <row r="57" spans="1:5">
+      <c r="A57" s="5" t="s">
+        <v>43</v>
+      </c>
+      <c r="B57" s="5" t="s">
+        <v>24</v>
+      </c>
+      <c r="C57" s="6">
+        <v>63.74</v>
+      </c>
+      <c r="D57" s="6">
+        <v>64.75</v>
+      </c>
+      <c r="E57" s="7">
+        <v>1.01</v>
+      </c>
+    </row>
+    <row r="58" spans="1:5">
+      <c r="A58" s="5" t="s">
+        <v>37</v>
+      </c>
+      <c r="B58" s="5" t="s">
+        <v>31</v>
+      </c>
+      <c r="C58" s="6">
+        <v>-29.09</v>
+      </c>
+      <c r="D58" s="6">
+        <v>-12.39</v>
+      </c>
+      <c r="E58" s="7">
+        <v>16.7</v>
+      </c>
+    </row>
+    <row r="59" spans="1:5">
+      <c r="A59" s="5" t="s">
+        <v>38</v>
+      </c>
+      <c r="B59" s="5" t="s">
+        <v>31</v>
+      </c>
+      <c r="C59" s="6">
+        <v>60.11</v>
+      </c>
+      <c r="D59" s="6">
+        <v>-8.09</v>
+      </c>
+      <c r="E59" s="8">
+        <v>-68.2</v>
+      </c>
+    </row>
+    <row r="60" spans="1:5">
+      <c r="A60" s="5" t="s">
+        <v>39</v>
+      </c>
+      <c r="B60" s="5" t="s">
+        <v>31</v>
+      </c>
+      <c r="C60" s="6">
+        <v>18.01</v>
+      </c>
+      <c r="D60" s="6">
+        <v>-23.71</v>
+      </c>
+      <c r="E60" s="8">
+        <v>-41.72</v>
+      </c>
+    </row>
+    <row r="61" spans="1:5">
+      <c r="A61" s="5" t="s">
+        <v>40</v>
+      </c>
+      <c r="B61" s="5" t="s">
+        <v>31</v>
+      </c>
+      <c r="C61" s="6">
+        <v>45.15</v>
+      </c>
+      <c r="D61" s="6">
+        <v>-9.69</v>
+      </c>
+      <c r="E61" s="8">
+        <v>-54.84</v>
+      </c>
+    </row>
+    <row r="62" spans="1:5">
+      <c r="A62" s="5" t="s">
+        <v>41</v>
+      </c>
+      <c r="B62" s="5" t="s">
+        <v>31</v>
+      </c>
+      <c r="C62" s="6">
+        <v>32.58</v>
+      </c>
+      <c r="D62" s="6">
+        <v>-72.03</v>
+      </c>
+      <c r="E62" s="8">
+        <v>-104.61</v>
+      </c>
+    </row>
+    <row r="63" spans="1:5">
+      <c r="A63" s="5" t="s">
+        <v>42</v>
+      </c>
+      <c r="B63" s="5" t="s">
+        <v>31</v>
+      </c>
+      <c r="C63" s="6">
+        <v>38.49</v>
+      </c>
+      <c r="D63" s="6">
+        <v>9.17</v>
+      </c>
+      <c r="E63" s="8">
+        <v>-29.32</v>
+      </c>
+    </row>
+    <row r="64" spans="1:5">
+      <c r="A64" s="5" t="s">
+        <v>43</v>
+      </c>
+      <c r="B64" s="5" t="s">
+        <v>31</v>
+      </c>
+      <c r="C64" s="6">
+        <v>-20.14</v>
+      </c>
+      <c r="D64" s="6">
+        <v>-58.21</v>
+      </c>
+      <c r="E64" s="8">
+        <v>-38.07</v>
       </c>
     </row>
   </sheetData>
   <mergeCells count="2">
     <mergeCell ref="A1:F1"/>
-    <mergeCell ref="A5:E5"/>
+    <mergeCell ref="A7:E7"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -1828,60 +2965,60 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:9" ht="28" customHeight="1">
-      <c r="A1" s="4" t="s">
+      <c r="A1" s="9" t="s">
         <v>1</v>
       </c>
-      <c r="B1" s="4" t="s">
-        <v>53</v>
-      </c>
-      <c r="C1" s="4" t="s">
-        <v>54</v>
-      </c>
-      <c r="D1" s="4" t="s">
-        <v>55</v>
-      </c>
-      <c r="E1" s="4" t="s">
-        <v>56</v>
-      </c>
-      <c r="F1" s="4" t="s">
+      <c r="B1" s="9" t="s">
+        <v>72</v>
+      </c>
+      <c r="C1" s="9" t="s">
+        <v>73</v>
+      </c>
+      <c r="D1" s="9" t="s">
+        <v>74</v>
+      </c>
+      <c r="E1" s="9" t="s">
+        <v>75</v>
+      </c>
+      <c r="F1" s="9" t="s">
+        <v>76</v>
+      </c>
+      <c r="G1" s="9" t="s">
+        <v>77</v>
+      </c>
+      <c r="H1" s="9" t="s">
+        <v>78</v>
+      </c>
+      <c r="I1" s="9" t="s">
+        <v>79</v>
+      </c>
+    </row>
+    <row r="2" spans="1:9">
+      <c r="A2" s="10" t="s">
+        <v>44</v>
+      </c>
+      <c r="B2" s="11">
+        <v>48.8</v>
+      </c>
+      <c r="C2" s="12">
+        <v>7</v>
+      </c>
+      <c r="D2" s="11">
+        <v>41.8</v>
+      </c>
+      <c r="E2" s="11">
+        <v>40</v>
+      </c>
+      <c r="F2" s="11">
+        <v>-3.6</v>
+      </c>
+      <c r="G2" s="11">
+        <v>-2.8</v>
+      </c>
+      <c r="H2" s="11">
         <v>57</v>
       </c>
-      <c r="G1" s="4" t="s">
-        <v>58</v>
-      </c>
-      <c r="H1" s="4" t="s">
-        <v>59</v>
-      </c>
-      <c r="I1" s="4" t="s">
-        <v>60</v>
-      </c>
-    </row>
-    <row r="2" spans="1:9">
-      <c r="A2" s="5" t="s">
-        <v>44</v>
-      </c>
-      <c r="B2" s="6">
-        <v>44.8</v>
-      </c>
-      <c r="C2" s="7">
-        <v>7</v>
-      </c>
-      <c r="D2" s="6">
-        <v>36.4</v>
-      </c>
-      <c r="E2" s="6">
-        <v>30</v>
-      </c>
-      <c r="F2" s="6">
-        <v>-5.5</v>
-      </c>
-      <c r="G2" s="6">
-        <v>-3.1</v>
-      </c>
-      <c r="H2" s="6">
-        <v>57</v>
-      </c>
-      <c r="I2" s="6">
+      <c r="I2" s="11">
         <v>10</v>
       </c>
     </row>
@@ -1983,49 +3120,49 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:7">
-      <c r="A1" s="8" t="s">
+      <c r="A1" s="13" t="s">
         <v>37</v>
       </c>
-      <c r="B1" s="8" t="s">
+      <c r="B1" s="13" t="s">
         <v>41</v>
       </c>
-      <c r="C1" s="8" t="s">
+      <c r="C1" s="13" t="s">
         <v>38</v>
       </c>
-      <c r="D1" s="8" t="s">
+      <c r="D1" s="13" t="s">
         <v>43</v>
       </c>
-      <c r="E1" s="8" t="s">
+      <c r="E1" s="13" t="s">
         <v>42</v>
       </c>
-      <c r="F1" s="8" t="s">
+      <c r="F1" s="13" t="s">
         <v>40</v>
       </c>
-      <c r="G1" s="8" t="s">
+      <c r="G1" s="13" t="s">
         <v>39</v>
       </c>
     </row>
     <row r="2" spans="1:7">
-      <c r="A2" s="9">
-        <v>0.2314</v>
-      </c>
-      <c r="B2" s="9">
-        <v>0.1886</v>
-      </c>
-      <c r="C2" s="9">
-        <v>0.1605</v>
-      </c>
-      <c r="D2" s="9">
-        <v>0.0479</v>
-      </c>
-      <c r="E2" s="9">
-        <v>0.0473</v>
-      </c>
-      <c r="F2" s="9">
-        <v>-0.005</v>
-      </c>
-      <c r="G2" s="9">
-        <v>-0.2399</v>
+      <c r="A2" s="14">
+        <v>0.2329</v>
+      </c>
+      <c r="B2" s="14">
+        <v>0.1945</v>
+      </c>
+      <c r="C2" s="14">
+        <v>0.1629</v>
+      </c>
+      <c r="D2" s="14">
+        <v>0.04849999999999999</v>
+      </c>
+      <c r="E2" s="14">
+        <v>0.046</v>
+      </c>
+      <c r="F2" s="14">
+        <v>-0.0038</v>
+      </c>
+      <c r="G2" s="14">
+        <v>-0.2369</v>
       </c>
     </row>
   </sheetData>

--- a/BAJAJ_GROUP_Technical_Metrics.xlsx
+++ b/BAJAJ_GROUP_Technical_Metrics.xlsx
@@ -1094,7 +1094,7 @@
         <v>99</v>
       </c>
       <c r="O3">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="P3">
         <v>490.59</v>
@@ -1207,7 +1207,7 @@
         <v>15</v>
       </c>
       <c r="O4">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="P4">
         <v>297.65</v>
@@ -1320,7 +1320,7 @@
         <v>29</v>
       </c>
       <c r="O5">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="P5">
         <v>1737.96</v>
@@ -1433,7 +1433,7 @@
         <v>57</v>
       </c>
       <c r="O6">
-        <v>59</v>
+        <v>62</v>
       </c>
       <c r="P6">
         <v>10682.8</v>
@@ -1546,7 +1546,7 @@
         <v>43</v>
       </c>
       <c r="O7">
-        <v>58</v>
+        <v>55</v>
       </c>
       <c r="P7">
         <v>962.58</v>
@@ -1659,7 +1659,7 @@
         <v>85</v>
       </c>
       <c r="O8">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="P8">
         <v>179.99</v>

--- a/BAJAJ_GROUP_Technical_Metrics.xlsx
+++ b/BAJAJ_GROUP_Technical_Metrics.xlsx
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="276" uniqueCount="80">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="270" uniqueCount="78">
   <si>
     <t>Symbol</t>
   </si>
@@ -187,40 +187,34 @@
     <t>Curr Value</t>
   </si>
   <si>
+    <t>RSI Oversold Recovery</t>
+  </si>
+  <si>
+    <t>23.2 → 31.8</t>
+  </si>
+  <si>
+    <t>🟢 BULLISH</t>
+  </si>
+  <si>
+    <t>23.2</t>
+  </si>
+  <si>
+    <t>31.8</t>
+  </si>
+  <si>
     <t>RSI Momentum</t>
   </si>
   <si>
-    <t>45.8 → 52.9</t>
-  </si>
-  <si>
-    <t>🟢 BULLISH</t>
-  </si>
-  <si>
-    <t>45.8</t>
+    <t>52.9 → 47.4</t>
+  </si>
+  <si>
+    <t>🔴 BEARISH</t>
   </si>
   <si>
     <t>52.9</t>
   </si>
   <si>
-    <t>RSI Oversold Recovery</t>
-  </si>
-  <si>
-    <t>24.8 → 34.2</t>
-  </si>
-  <si>
-    <t>24.8</t>
-  </si>
-  <si>
-    <t>34.2</t>
-  </si>
-  <si>
-    <t>25.5 → 32.9</t>
-  </si>
-  <si>
-    <t>25.5</t>
-  </si>
-  <si>
-    <t>32.9</t>
+    <t>47.4</t>
   </si>
   <si>
     <t>▶  NUMERIC METRIC CHANGES (vs Previous Run)</t>
@@ -422,7 +416,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="15">
+  <cellXfs count="16">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="2" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
@@ -430,6 +424,7 @@
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="5" fillId="6" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1"/>
     <xf numFmtId="165" fontId="4" fillId="5" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
@@ -945,10 +940,10 @@
         <v>44</v>
       </c>
       <c r="C2">
-        <v>9778</v>
+        <v>10034</v>
       </c>
       <c r="D2">
-        <v>1.46</v>
+        <v>2.62</v>
       </c>
       <c r="E2">
         <v>12361</v>
@@ -957,46 +952,46 @@
         <v>8599.48</v>
       </c>
       <c r="G2">
-        <v>-20.9</v>
+        <v>-18.83</v>
       </c>
       <c r="H2">
-        <v>13.7</v>
+        <v>16.68</v>
       </c>
       <c r="I2">
-        <v>-2.66</v>
+        <v>0.1</v>
       </c>
       <c r="J2">
-        <v>-17.69</v>
+        <v>-14.89</v>
       </c>
       <c r="K2">
-        <v>-3.72</v>
+        <v>-3.34</v>
       </c>
       <c r="L2">
-        <v>12.78</v>
+        <v>14.28</v>
       </c>
       <c r="M2">
-        <v>23.29</v>
+        <v>23.1</v>
       </c>
       <c r="N2">
         <v>71</v>
       </c>
       <c r="O2">
-        <v>66</v>
+        <v>68</v>
       </c>
       <c r="P2">
-        <v>9868</v>
+        <v>9870</v>
       </c>
       <c r="Q2">
-        <v>10909.15</v>
+        <v>10822.45</v>
       </c>
       <c r="R2">
-        <v>11431.69</v>
+        <v>11403.73</v>
       </c>
       <c r="S2">
-        <v>10166.41</v>
+        <v>10171.39</v>
       </c>
       <c r="T2">
-        <v>-3.82</v>
+        <v>-1.35</v>
       </c>
       <c r="U2" t="s">
         <v>45</v>
@@ -1011,34 +1006,34 @@
         <v>1</v>
       </c>
       <c r="Y2">
-        <v>23.2</v>
+        <v>31.77</v>
       </c>
       <c r="Z2">
-        <v>-481.74</v>
+        <v>-472.79</v>
       </c>
       <c r="AA2">
-        <v>-324.04</v>
+        <v>-353.79</v>
       </c>
       <c r="AB2">
-        <v>-157.7</v>
+        <v>-119</v>
       </c>
       <c r="AC2">
-        <v>6.72</v>
+        <v>25.23</v>
       </c>
       <c r="AD2">
-        <v>2.24</v>
+        <v>10.65</v>
       </c>
       <c r="AE2">
-        <v>252.07</v>
+        <v>259.78</v>
       </c>
       <c r="AF2">
-        <v>-12.39</v>
+        <v>9.17</v>
       </c>
       <c r="AG2">
-        <v>12355.92</v>
+        <v>12260.31</v>
       </c>
       <c r="AH2">
-        <v>9462.379999999999</v>
+        <v>9384.59</v>
       </c>
       <c r="AI2">
         <v>10503.51</v>
@@ -1047,7 +1042,7 @@
         <v>47</v>
       </c>
       <c r="AK2">
-        <v>78.28</v>
+        <v>74.83</v>
       </c>
     </row>
     <row r="3" spans="1:37">
@@ -1058,58 +1053,58 @@
         <v>44</v>
       </c>
       <c r="C3">
-        <v>506.95</v>
+        <v>492.4</v>
       </c>
       <c r="D3">
-        <v>3.64</v>
+        <v>-2.87</v>
       </c>
       <c r="E3">
         <v>670.25</v>
       </c>
       <c r="F3">
-        <v>241.91</v>
+        <v>246.55</v>
       </c>
       <c r="G3">
-        <v>-24.36</v>
+        <v>-26.53</v>
       </c>
       <c r="H3">
-        <v>109.56</v>
+        <v>99.72</v>
       </c>
       <c r="I3">
-        <v>1.99</v>
+        <v>2.51</v>
       </c>
       <c r="J3">
-        <v>-1.39</v>
+        <v>-5.57</v>
       </c>
       <c r="K3">
-        <v>-24.36</v>
+        <v>-25.44</v>
       </c>
       <c r="L3">
-        <v>108.96</v>
+        <v>103.55</v>
       </c>
       <c r="M3">
-        <v>16.29</v>
+        <v>15.67</v>
       </c>
       <c r="N3">
         <v>99</v>
       </c>
       <c r="O3">
-        <v>91</v>
+        <v>89</v>
       </c>
       <c r="P3">
-        <v>490.59</v>
+        <v>493</v>
       </c>
       <c r="Q3">
-        <v>500.81</v>
+        <v>499.2</v>
       </c>
       <c r="R3">
-        <v>503.22</v>
+        <v>502.31</v>
       </c>
       <c r="S3">
-        <v>458.06</v>
+        <v>459.2</v>
       </c>
       <c r="T3">
-        <v>10.67</v>
+        <v>7.23</v>
       </c>
       <c r="U3" t="s">
         <v>45</v>
@@ -1124,34 +1119,34 @@
         <v>2</v>
       </c>
       <c r="Y3">
-        <v>52.93</v>
+        <v>47.42</v>
       </c>
       <c r="Z3">
-        <v>-3.91</v>
+        <v>-3.86</v>
       </c>
       <c r="AA3">
-        <v>-4.12</v>
+        <v>-4.06</v>
       </c>
       <c r="AB3">
         <v>0.21</v>
       </c>
       <c r="AC3">
-        <v>58.9</v>
+        <v>69.54000000000001</v>
       </c>
       <c r="AD3">
-        <v>45</v>
+        <v>57.54</v>
       </c>
       <c r="AE3">
-        <v>19.19</v>
+        <v>19.12</v>
       </c>
       <c r="AF3">
-        <v>-8.09</v>
+        <v>-41.08</v>
       </c>
       <c r="AG3">
-        <v>525.92</v>
+        <v>521.9400000000001</v>
       </c>
       <c r="AH3">
-        <v>475.69</v>
+        <v>476.46</v>
       </c>
       <c r="AI3">
         <v>460.99</v>
@@ -1160,7 +1155,7 @@
         <v>48</v>
       </c>
       <c r="AK3">
-        <v>28.97</v>
+        <v>26.1</v>
       </c>
     </row>
     <row r="4" spans="1:37">
@@ -1171,10 +1166,10 @@
         <v>44</v>
       </c>
       <c r="C4">
-        <v>298</v>
+        <v>298.85</v>
       </c>
       <c r="D4">
-        <v>2.74</v>
+        <v>0.29</v>
       </c>
       <c r="E4">
         <v>548</v>
@@ -1183,46 +1178,46 @@
         <v>290.05</v>
       </c>
       <c r="G4">
-        <v>-45.62</v>
+        <v>-45.47</v>
       </c>
       <c r="H4">
-        <v>2.74</v>
+        <v>3.03</v>
       </c>
       <c r="I4">
-        <v>-0.6</v>
+        <v>-0.13</v>
       </c>
       <c r="J4">
-        <v>-12.34</v>
+        <v>-12.05</v>
       </c>
       <c r="K4">
-        <v>-10</v>
+        <v>-11.2</v>
       </c>
       <c r="L4">
-        <v>-45.06</v>
+        <v>-44.37</v>
       </c>
       <c r="M4">
-        <v>-23.69</v>
+        <v>-23.56</v>
       </c>
       <c r="N4">
         <v>15</v>
       </c>
       <c r="O4">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="P4">
-        <v>297.65</v>
+        <v>297.57</v>
       </c>
       <c r="Q4">
-        <v>315.38</v>
+        <v>313.43</v>
       </c>
       <c r="R4">
-        <v>333.83</v>
+        <v>333.22</v>
       </c>
       <c r="S4">
-        <v>363.49</v>
+        <v>362.56</v>
       </c>
       <c r="T4">
-        <v>-18.02</v>
+        <v>-17.57</v>
       </c>
       <c r="U4" t="s">
         <v>45</v>
@@ -1237,34 +1232,34 @@
         <v>0</v>
       </c>
       <c r="Y4">
-        <v>34.16</v>
+        <v>35.1</v>
       </c>
       <c r="Z4">
-        <v>-10.62</v>
+        <v>-10.37</v>
       </c>
       <c r="AA4">
-        <v>-8.82</v>
+        <v>-9.130000000000001</v>
       </c>
       <c r="AB4">
-        <v>-1.8</v>
+        <v>-1.24</v>
       </c>
       <c r="AC4">
-        <v>18.1</v>
+        <v>30.73</v>
       </c>
       <c r="AD4">
-        <v>9.91</v>
+        <v>18.22</v>
       </c>
       <c r="AE4">
-        <v>9.380000000000001</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AF4">
-        <v>-23.71</v>
+        <v>-38.62</v>
       </c>
       <c r="AG4">
-        <v>343.53</v>
+        <v>340.43</v>
       </c>
       <c r="AH4">
-        <v>287.22</v>
+        <v>286.44</v>
       </c>
       <c r="AI4">
         <v>322.52</v>
@@ -1273,7 +1268,7 @@
         <v>47</v>
       </c>
       <c r="AK4">
-        <v>52.04</v>
+        <v>53.57</v>
       </c>
     </row>
     <row r="5" spans="1:37">
@@ -1284,10 +1279,10 @@
         <v>44</v>
       </c>
       <c r="C5">
-        <v>1734.7</v>
+        <v>1719.9</v>
       </c>
       <c r="D5">
-        <v>1.56</v>
+        <v>-0.85</v>
       </c>
       <c r="E5">
         <v>2176.6</v>
@@ -1296,46 +1291,46 @@
         <v>1631.8</v>
       </c>
       <c r="G5">
-        <v>-20.3</v>
+        <v>-20.98</v>
       </c>
       <c r="H5">
-        <v>6.31</v>
+        <v>5.4</v>
       </c>
       <c r="I5">
-        <v>0.12</v>
+        <v>-1.8</v>
       </c>
       <c r="J5">
-        <v>-10.49</v>
+        <v>-10.75</v>
       </c>
       <c r="K5">
-        <v>-9.460000000000001</v>
+        <v>-9.859999999999999</v>
       </c>
       <c r="L5">
-        <v>-14.68</v>
+        <v>-15.38</v>
       </c>
       <c r="M5">
-        <v>-0.38</v>
+        <v>-1.11</v>
       </c>
       <c r="N5">
         <v>29</v>
       </c>
       <c r="O5">
-        <v>43</v>
+        <v>41</v>
       </c>
       <c r="P5">
-        <v>1737.96</v>
+        <v>1731.66</v>
       </c>
       <c r="Q5">
-        <v>1797.95</v>
+        <v>1786.92</v>
       </c>
       <c r="R5">
-        <v>1924.81</v>
+        <v>1921.02</v>
       </c>
       <c r="S5">
-        <v>1877.15</v>
+        <v>1875.5</v>
       </c>
       <c r="T5">
-        <v>-7.59</v>
+        <v>-8.300000000000001</v>
       </c>
       <c r="U5" t="s">
         <v>45</v>
@@ -1350,34 +1345,34 @@
         <v>1</v>
       </c>
       <c r="Y5">
-        <v>32.87</v>
+        <v>31.03</v>
       </c>
       <c r="Z5">
-        <v>-56.11</v>
+        <v>-55.23</v>
       </c>
       <c r="AA5">
-        <v>-54.21</v>
+        <v>-54.42</v>
       </c>
       <c r="AB5">
-        <v>-1.89</v>
+        <v>-0.82</v>
       </c>
       <c r="AC5">
-        <v>43.8</v>
+        <v>48.79</v>
       </c>
       <c r="AD5">
-        <v>44.14</v>
+        <v>43.06</v>
       </c>
       <c r="AE5">
-        <v>35.98</v>
+        <v>36.38</v>
       </c>
       <c r="AF5">
-        <v>-9.69</v>
+        <v>-34.16</v>
       </c>
       <c r="AG5">
-        <v>1932.66</v>
+        <v>1907.91</v>
       </c>
       <c r="AH5">
-        <v>1663.24</v>
+        <v>1665.93</v>
       </c>
       <c r="AI5">
         <v>1825.61</v>
@@ -1386,7 +1381,7 @@
         <v>47</v>
       </c>
       <c r="AK5">
-        <v>67.17</v>
+        <v>64.47</v>
       </c>
     </row>
     <row r="6" spans="1:37">
@@ -1397,10 +1392,10 @@
         <v>44</v>
       </c>
       <c r="C6">
-        <v>10820</v>
+        <v>10750</v>
       </c>
       <c r="D6">
-        <v>2.08</v>
+        <v>-0.65</v>
       </c>
       <c r="E6">
         <v>13144</v>
@@ -1409,46 +1404,46 @@
         <v>8746</v>
       </c>
       <c r="G6">
-        <v>-17.68</v>
+        <v>-18.21</v>
       </c>
       <c r="H6">
-        <v>23.71</v>
+        <v>22.91</v>
       </c>
       <c r="I6">
-        <v>1.44</v>
+        <v>0.17</v>
       </c>
       <c r="J6">
-        <v>-2.05</v>
+        <v>-2.96</v>
       </c>
       <c r="K6">
-        <v>1.56</v>
+        <v>-0.02</v>
       </c>
       <c r="L6">
-        <v>-8.32</v>
+        <v>-11.08</v>
       </c>
       <c r="M6">
-        <v>19.45</v>
+        <v>19.04</v>
       </c>
       <c r="N6">
         <v>57</v>
       </c>
       <c r="O6">
-        <v>62</v>
+        <v>57</v>
       </c>
       <c r="P6">
-        <v>10682.8</v>
+        <v>10686.4</v>
       </c>
       <c r="Q6">
-        <v>10930.8</v>
+        <v>10918.7</v>
       </c>
       <c r="R6">
-        <v>11173.42</v>
+        <v>11169.02</v>
       </c>
       <c r="S6">
-        <v>10666.52</v>
+        <v>10664</v>
       </c>
       <c r="T6">
-        <v>1.44</v>
+        <v>0.8100000000000001</v>
       </c>
       <c r="U6" t="s">
         <v>45</v>
@@ -1463,34 +1458,34 @@
         <v>2</v>
       </c>
       <c r="Y6">
-        <v>47.07</v>
+        <v>45.41</v>
       </c>
       <c r="Z6">
-        <v>-133.98</v>
+        <v>-127.47</v>
       </c>
       <c r="AA6">
-        <v>-110.86</v>
+        <v>-114.18</v>
       </c>
       <c r="AB6">
-        <v>-23.12</v>
+        <v>-13.29</v>
       </c>
       <c r="AC6">
-        <v>26.19</v>
+        <v>32.4</v>
       </c>
       <c r="AD6">
-        <v>19.29</v>
+        <v>24.16</v>
       </c>
       <c r="AE6">
-        <v>256.1</v>
+        <v>256.02</v>
       </c>
       <c r="AF6">
-        <v>-72.03</v>
+        <v>-38.37</v>
       </c>
       <c r="AG6">
-        <v>11459.02</v>
+        <v>11452.08</v>
       </c>
       <c r="AH6">
-        <v>10402.58</v>
+        <v>10385.32</v>
       </c>
       <c r="AI6">
         <v>11368.55</v>
@@ -1499,7 +1494,7 @@
         <v>47</v>
       </c>
       <c r="AK6">
-        <v>33.17</v>
+        <v>29.17</v>
       </c>
     </row>
     <row r="7" spans="1:37">
@@ -1510,10 +1505,10 @@
         <v>44</v>
       </c>
       <c r="C7">
-        <v>960</v>
+        <v>957.25</v>
       </c>
       <c r="D7">
-        <v>0.42</v>
+        <v>-0.29</v>
       </c>
       <c r="E7">
         <v>1158.8</v>
@@ -1522,46 +1517,46 @@
         <v>801.55</v>
       </c>
       <c r="G7">
-        <v>-17.16</v>
+        <v>-17.39</v>
       </c>
       <c r="H7">
-        <v>19.77</v>
+        <v>19.42</v>
       </c>
       <c r="I7">
-        <v>1.23</v>
+        <v>-1.31</v>
       </c>
       <c r="J7">
-        <v>-8.93</v>
+        <v>-7.89</v>
       </c>
       <c r="K7">
-        <v>-5.93</v>
+        <v>-6.39</v>
       </c>
       <c r="L7">
-        <v>-4.85</v>
+        <v>-5.83</v>
       </c>
       <c r="M7">
-        <v>4.6</v>
+        <v>4.43</v>
       </c>
       <c r="N7">
         <v>43</v>
       </c>
       <c r="O7">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="P7">
-        <v>962.58</v>
+        <v>960.03</v>
       </c>
       <c r="Q7">
-        <v>994.01</v>
+        <v>989.7</v>
       </c>
       <c r="R7">
-        <v>1050.44</v>
+        <v>1048.51</v>
       </c>
       <c r="S7">
-        <v>975.29</v>
+        <v>975.03</v>
       </c>
       <c r="T7">
-        <v>-1.57</v>
+        <v>-1.82</v>
       </c>
       <c r="U7" t="s">
         <v>45</v>
@@ -1576,34 +1571,34 @@
         <v>1</v>
       </c>
       <c r="Y7">
-        <v>37.62</v>
+        <v>37.02</v>
       </c>
       <c r="Z7">
-        <v>-25.39</v>
+        <v>-24.96</v>
       </c>
       <c r="AA7">
-        <v>-23.47</v>
+        <v>-23.77</v>
       </c>
       <c r="AB7">
-        <v>-1.93</v>
+        <v>-1.19</v>
       </c>
       <c r="AC7">
-        <v>29.89</v>
+        <v>28.44</v>
       </c>
       <c r="AD7">
-        <v>32.89</v>
+        <v>29.84</v>
       </c>
       <c r="AE7">
-        <v>24.85</v>
+        <v>24.42</v>
       </c>
       <c r="AF7">
-        <v>9.17</v>
+        <v>-30.26</v>
       </c>
       <c r="AG7">
-        <v>1057.94</v>
+        <v>1051.16</v>
       </c>
       <c r="AH7">
-        <v>930.09</v>
+        <v>928.24</v>
       </c>
       <c r="AI7">
         <v>1020.6</v>
@@ -1612,7 +1607,7 @@
         <v>47</v>
       </c>
       <c r="AK7">
-        <v>28.61</v>
+        <v>25.06</v>
       </c>
     </row>
     <row r="8" spans="1:37">
@@ -1623,10 +1618,10 @@
         <v>44</v>
       </c>
       <c r="C8">
-        <v>175.99</v>
+        <v>177.58</v>
       </c>
       <c r="D8">
-        <v>0.98</v>
+        <v>0.9</v>
       </c>
       <c r="E8">
         <v>185.92</v>
@@ -1635,25 +1630,25 @@
         <v>115.96</v>
       </c>
       <c r="G8">
-        <v>-5.34</v>
+        <v>-4.49</v>
       </c>
       <c r="H8">
-        <v>51.77</v>
+        <v>53.14</v>
       </c>
       <c r="I8">
-        <v>1.93</v>
+        <v>-2.54</v>
       </c>
       <c r="J8">
-        <v>27.84</v>
+        <v>27.12</v>
       </c>
       <c r="K8">
-        <v>32.44</v>
+        <v>30.72</v>
       </c>
       <c r="L8">
-        <v>26.58</v>
+        <v>30.71</v>
       </c>
       <c r="M8">
-        <v>4.85</v>
+        <v>5.16</v>
       </c>
       <c r="N8">
         <v>85</v>
@@ -1662,19 +1657,19 @@
         <v>90</v>
       </c>
       <c r="P8">
-        <v>179.99</v>
+        <v>179.07</v>
       </c>
       <c r="Q8">
-        <v>158.73</v>
+        <v>160.48</v>
       </c>
       <c r="R8">
-        <v>146.13</v>
+        <v>146.89</v>
       </c>
       <c r="S8">
-        <v>136.33</v>
+        <v>136.55</v>
       </c>
       <c r="T8">
-        <v>29.09</v>
+        <v>30.05</v>
       </c>
       <c r="U8" t="s">
         <v>46</v>
@@ -1689,34 +1684,34 @@
         <v>3</v>
       </c>
       <c r="Y8">
-        <v>64.75</v>
+        <v>65.70999999999999</v>
       </c>
       <c r="Z8">
-        <v>11.14</v>
+        <v>10.85</v>
       </c>
       <c r="AA8">
-        <v>9.42</v>
+        <v>9.710000000000001</v>
       </c>
       <c r="AB8">
-        <v>1.72</v>
+        <v>1.14</v>
       </c>
       <c r="AC8">
-        <v>59.68</v>
+        <v>40.21</v>
       </c>
       <c r="AD8">
-        <v>71</v>
+        <v>56.95</v>
       </c>
       <c r="AE8">
-        <v>8.58</v>
+        <v>8.460000000000001</v>
       </c>
       <c r="AF8">
-        <v>-58.21</v>
+        <v>-64.44</v>
       </c>
       <c r="AG8">
-        <v>197.54</v>
+        <v>199.38</v>
       </c>
       <c r="AH8">
-        <v>119.93</v>
+        <v>121.59</v>
       </c>
       <c r="AI8">
         <v>159.98</v>
@@ -1725,7 +1720,7 @@
         <v>48</v>
       </c>
       <c r="AK8">
-        <v>51.22</v>
+        <v>50.05</v>
       </c>
     </row>
   </sheetData>
@@ -1866,7 +1861,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:F64"/>
+  <dimension ref="A1:F63"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="16.7109375" customWidth="1"/>
@@ -1906,7 +1901,7 @@
     </row>
     <row r="3" spans="1:6">
       <c r="A3" s="4" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="B3" s="4" t="s">
         <v>55</v>
@@ -1925,1027 +1920,1007 @@
       </c>
     </row>
     <row r="4" spans="1:6">
-      <c r="A4" s="4" t="s">
+      <c r="A4" s="5" t="s">
+        <v>38</v>
+      </c>
+      <c r="B4" s="5" t="s">
+        <v>60</v>
+      </c>
+      <c r="C4" s="5" t="s">
+        <v>61</v>
+      </c>
+      <c r="D4" s="5" t="s">
+        <v>62</v>
+      </c>
+      <c r="E4" s="5" t="s">
+        <v>63</v>
+      </c>
+      <c r="F4" s="5" t="s">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="6" spans="1:6">
+      <c r="A6" s="2" t="s">
+        <v>65</v>
+      </c>
+      <c r="B6" s="2"/>
+      <c r="C6" s="2"/>
+      <c r="D6" s="2"/>
+      <c r="E6" s="2"/>
+    </row>
+    <row r="7" spans="1:6">
+      <c r="A7" s="3" t="s">
+        <v>0</v>
+      </c>
+      <c r="B7" s="3" t="s">
+        <v>66</v>
+      </c>
+      <c r="C7" s="3" t="s">
+        <v>67</v>
+      </c>
+      <c r="D7" s="3" t="s">
+        <v>68</v>
+      </c>
+      <c r="E7" s="3" t="s">
+        <v>69</v>
+      </c>
+    </row>
+    <row r="8" spans="1:6">
+      <c r="A8" s="6" t="s">
+        <v>37</v>
+      </c>
+      <c r="B8" s="6" t="s">
+        <v>9</v>
+      </c>
+      <c r="C8" s="7">
+        <v>-17.69</v>
+      </c>
+      <c r="D8" s="7">
+        <v>-14.89</v>
+      </c>
+      <c r="E8" s="8">
+        <v>2.8</v>
+      </c>
+    </row>
+    <row r="9" spans="1:6">
+      <c r="A9" s="6" t="s">
+        <v>38</v>
+      </c>
+      <c r="B9" s="6" t="s">
+        <v>9</v>
+      </c>
+      <c r="C9" s="7">
+        <v>-1.39</v>
+      </c>
+      <c r="D9" s="7">
+        <v>-5.57</v>
+      </c>
+      <c r="E9" s="9">
+        <v>-4.18</v>
+      </c>
+    </row>
+    <row r="10" spans="1:6">
+      <c r="A10" s="6" t="s">
         <v>39</v>
       </c>
-      <c r="B4" s="4" t="s">
-        <v>60</v>
-      </c>
-      <c r="C4" s="4" t="s">
-        <v>61</v>
-      </c>
-      <c r="D4" s="4" t="s">
-        <v>57</v>
-      </c>
-      <c r="E4" s="4" t="s">
-        <v>62</v>
-      </c>
-      <c r="F4" s="4" t="s">
-        <v>63</v>
-      </c>
-    </row>
-    <row r="5" spans="1:6">
-      <c r="A5" s="4" t="s">
+      <c r="B10" s="6" t="s">
+        <v>9</v>
+      </c>
+      <c r="C10" s="7">
+        <v>-12.34</v>
+      </c>
+      <c r="D10" s="7">
+        <v>-12.05</v>
+      </c>
+      <c r="E10" s="8">
+        <v>0.29</v>
+      </c>
+    </row>
+    <row r="11" spans="1:6">
+      <c r="A11" s="6" t="s">
         <v>40</v>
       </c>
-      <c r="B5" s="4" t="s">
-        <v>60</v>
-      </c>
-      <c r="C5" s="4" t="s">
-        <v>64</v>
-      </c>
-      <c r="D5" s="4" t="s">
-        <v>57</v>
-      </c>
-      <c r="E5" s="4" t="s">
-        <v>65</v>
-      </c>
-      <c r="F5" s="4" t="s">
-        <v>66</v>
-      </c>
-    </row>
-    <row r="7" spans="1:6">
-      <c r="A7" s="2" t="s">
-        <v>67</v>
-      </c>
-      <c r="B7" s="2"/>
-      <c r="C7" s="2"/>
-      <c r="D7" s="2"/>
-      <c r="E7" s="2"/>
-    </row>
-    <row r="8" spans="1:6">
-      <c r="A8" s="3" t="s">
-        <v>0</v>
-      </c>
-      <c r="B8" s="3" t="s">
-        <v>68</v>
-      </c>
-      <c r="C8" s="3" t="s">
-        <v>69</v>
-      </c>
-      <c r="D8" s="3" t="s">
-        <v>70</v>
-      </c>
-      <c r="E8" s="3" t="s">
-        <v>71</v>
-      </c>
-    </row>
-    <row r="9" spans="1:6">
-      <c r="A9" s="5" t="s">
+      <c r="B11" s="6" t="s">
+        <v>9</v>
+      </c>
+      <c r="C11" s="7">
+        <v>-10.49</v>
+      </c>
+      <c r="D11" s="7">
+        <v>-10.75</v>
+      </c>
+      <c r="E11" s="9">
+        <v>-0.26</v>
+      </c>
+    </row>
+    <row r="12" spans="1:6">
+      <c r="A12" s="6" t="s">
+        <v>41</v>
+      </c>
+      <c r="B12" s="6" t="s">
+        <v>9</v>
+      </c>
+      <c r="C12" s="7">
+        <v>-2.05</v>
+      </c>
+      <c r="D12" s="7">
+        <v>-2.96</v>
+      </c>
+      <c r="E12" s="9">
+        <v>-0.91</v>
+      </c>
+    </row>
+    <row r="13" spans="1:6">
+      <c r="A13" s="6" t="s">
+        <v>42</v>
+      </c>
+      <c r="B13" s="6" t="s">
+        <v>9</v>
+      </c>
+      <c r="C13" s="7">
+        <v>-8.93</v>
+      </c>
+      <c r="D13" s="7">
+        <v>-7.89</v>
+      </c>
+      <c r="E13" s="8">
+        <v>1.04</v>
+      </c>
+    </row>
+    <row r="14" spans="1:6">
+      <c r="A14" s="6" t="s">
+        <v>43</v>
+      </c>
+      <c r="B14" s="6" t="s">
+        <v>9</v>
+      </c>
+      <c r="C14" s="7">
+        <v>27.84</v>
+      </c>
+      <c r="D14" s="7">
+        <v>27.12</v>
+      </c>
+      <c r="E14" s="9">
+        <v>-0.72</v>
+      </c>
+    </row>
+    <row r="15" spans="1:6">
+      <c r="A15" s="6" t="s">
         <v>37</v>
       </c>
-      <c r="B9" s="5" t="s">
-        <v>9</v>
-      </c>
-      <c r="C9" s="6">
-        <v>-18.33</v>
-      </c>
-      <c r="D9" s="6">
-        <v>-17.69</v>
-      </c>
-      <c r="E9" s="7">
-        <v>0.64</v>
-      </c>
-    </row>
-    <row r="10" spans="1:6">
-      <c r="A10" s="5" t="s">
+      <c r="B15" s="6" t="s">
+        <v>8</v>
+      </c>
+      <c r="C15" s="7">
+        <v>-2.66</v>
+      </c>
+      <c r="D15" s="7">
+        <v>0.1</v>
+      </c>
+      <c r="E15" s="8">
+        <v>2.76</v>
+      </c>
+    </row>
+    <row r="16" spans="1:6">
+      <c r="A16" s="6" t="s">
         <v>38</v>
       </c>
-      <c r="B10" s="5" t="s">
-        <v>9</v>
-      </c>
-      <c r="C10" s="6">
-        <v>-7.01</v>
-      </c>
-      <c r="D10" s="6">
-        <v>-1.39</v>
-      </c>
-      <c r="E10" s="7">
-        <v>5.62</v>
-      </c>
-    </row>
-    <row r="11" spans="1:6">
-      <c r="A11" s="5" t="s">
+      <c r="B16" s="6" t="s">
+        <v>8</v>
+      </c>
+      <c r="C16" s="7">
+        <v>1.99</v>
+      </c>
+      <c r="D16" s="7">
+        <v>2.51</v>
+      </c>
+      <c r="E16" s="8">
+        <v>0.52</v>
+      </c>
+    </row>
+    <row r="17" spans="1:5">
+      <c r="A17" s="6" t="s">
         <v>39</v>
       </c>
-      <c r="B11" s="5" t="s">
-        <v>9</v>
-      </c>
-      <c r="C11" s="6">
-        <v>-15.21</v>
-      </c>
-      <c r="D11" s="6">
-        <v>-12.34</v>
-      </c>
-      <c r="E11" s="7">
-        <v>2.87</v>
-      </c>
-    </row>
-    <row r="12" spans="1:6">
-      <c r="A12" s="5" t="s">
+      <c r="B17" s="6" t="s">
+        <v>8</v>
+      </c>
+      <c r="C17" s="7">
+        <v>-0.6</v>
+      </c>
+      <c r="D17" s="7">
+        <v>-0.13</v>
+      </c>
+      <c r="E17" s="8">
+        <v>0.47</v>
+      </c>
+    </row>
+    <row r="18" spans="1:5">
+      <c r="A18" s="6" t="s">
         <v>40</v>
       </c>
-      <c r="B12" s="5" t="s">
-        <v>9</v>
-      </c>
-      <c r="C12" s="6">
-        <v>-11.9</v>
-      </c>
-      <c r="D12" s="6">
-        <v>-10.49</v>
-      </c>
-      <c r="E12" s="7">
-        <v>1.41</v>
-      </c>
-    </row>
-    <row r="13" spans="1:6">
-      <c r="A13" s="5" t="s">
+      <c r="B18" s="6" t="s">
+        <v>8</v>
+      </c>
+      <c r="C18" s="7">
+        <v>0.12</v>
+      </c>
+      <c r="D18" s="7">
+        <v>-1.8</v>
+      </c>
+      <c r="E18" s="9">
+        <v>-1.92</v>
+      </c>
+    </row>
+    <row r="19" spans="1:5">
+      <c r="A19" s="6" t="s">
         <v>41</v>
       </c>
-      <c r="B13" s="5" t="s">
-        <v>9</v>
-      </c>
-      <c r="C13" s="6">
-        <v>-3.25</v>
-      </c>
-      <c r="D13" s="6">
-        <v>-2.05</v>
-      </c>
-      <c r="E13" s="7">
-        <v>1.2</v>
-      </c>
-    </row>
-    <row r="14" spans="1:6">
-      <c r="A14" s="5" t="s">
+      <c r="B19" s="6" t="s">
+        <v>8</v>
+      </c>
+      <c r="C19" s="7">
+        <v>1.44</v>
+      </c>
+      <c r="D19" s="7">
+        <v>0.17</v>
+      </c>
+      <c r="E19" s="9">
+        <v>-1.27</v>
+      </c>
+    </row>
+    <row r="20" spans="1:5">
+      <c r="A20" s="6" t="s">
         <v>42</v>
       </c>
-      <c r="B14" s="5" t="s">
-        <v>9</v>
-      </c>
-      <c r="C14" s="6">
-        <v>-9.82</v>
-      </c>
-      <c r="D14" s="6">
-        <v>-8.93</v>
-      </c>
-      <c r="E14" s="7">
-        <v>0.89</v>
-      </c>
-    </row>
-    <row r="15" spans="1:6">
-      <c r="A15" s="5" t="s">
+      <c r="B20" s="6" t="s">
+        <v>8</v>
+      </c>
+      <c r="C20" s="7">
+        <v>1.23</v>
+      </c>
+      <c r="D20" s="7">
+        <v>-1.31</v>
+      </c>
+      <c r="E20" s="9">
+        <v>-2.54</v>
+      </c>
+    </row>
+    <row r="21" spans="1:5">
+      <c r="A21" s="6" t="s">
         <v>43</v>
       </c>
-      <c r="B15" s="5" t="s">
-        <v>9</v>
-      </c>
-      <c r="C15" s="6">
-        <v>27.31</v>
-      </c>
-      <c r="D15" s="6">
-        <v>27.84</v>
-      </c>
-      <c r="E15" s="7">
-        <v>0.53</v>
-      </c>
-    </row>
-    <row r="16" spans="1:6">
-      <c r="A16" s="5" t="s">
+      <c r="B21" s="6" t="s">
+        <v>8</v>
+      </c>
+      <c r="C21" s="7">
+        <v>1.93</v>
+      </c>
+      <c r="D21" s="7">
+        <v>-2.54</v>
+      </c>
+      <c r="E21" s="9">
+        <v>-4.47</v>
+      </c>
+    </row>
+    <row r="22" spans="1:5">
+      <c r="A22" s="6" t="s">
         <v>37</v>
       </c>
-      <c r="B16" s="5" t="s">
-        <v>8</v>
-      </c>
-      <c r="C16" s="6">
-        <v>-11.38</v>
-      </c>
-      <c r="D16" s="6">
-        <v>-2.66</v>
-      </c>
-      <c r="E16" s="7">
-        <v>8.720000000000001</v>
-      </c>
-    </row>
-    <row r="17" spans="1:5">
-      <c r="A17" s="5" t="s">
+      <c r="B22" s="6" t="s">
+        <v>11</v>
+      </c>
+      <c r="C22" s="7">
+        <v>12.78</v>
+      </c>
+      <c r="D22" s="7">
+        <v>14.28</v>
+      </c>
+      <c r="E22" s="8">
+        <v>1.5</v>
+      </c>
+    </row>
+    <row r="23" spans="1:5">
+      <c r="A23" s="6" t="s">
         <v>38</v>
       </c>
-      <c r="B17" s="5" t="s">
-        <v>8</v>
-      </c>
-      <c r="C17" s="6">
-        <v>-1.29</v>
-      </c>
-      <c r="D17" s="6">
-        <v>1.99</v>
-      </c>
-      <c r="E17" s="7">
-        <v>3.28</v>
-      </c>
-    </row>
-    <row r="18" spans="1:5">
-      <c r="A18" s="5" t="s">
+      <c r="B23" s="6" t="s">
+        <v>11</v>
+      </c>
+      <c r="C23" s="7">
+        <v>108.96</v>
+      </c>
+      <c r="D23" s="7">
+        <v>103.55</v>
+      </c>
+      <c r="E23" s="9">
+        <v>-5.41</v>
+      </c>
+    </row>
+    <row r="24" spans="1:5">
+      <c r="A24" s="6" t="s">
         <v>39</v>
       </c>
-      <c r="B18" s="5" t="s">
-        <v>8</v>
-      </c>
-      <c r="C18" s="6">
-        <v>-4.4</v>
-      </c>
-      <c r="D18" s="6">
+      <c r="B24" s="6" t="s">
+        <v>11</v>
+      </c>
+      <c r="C24" s="7">
+        <v>-45.06</v>
+      </c>
+      <c r="D24" s="7">
+        <v>-44.37</v>
+      </c>
+      <c r="E24" s="8">
+        <v>0.6899999999999999</v>
+      </c>
+    </row>
+    <row r="25" spans="1:5">
+      <c r="A25" s="6" t="s">
+        <v>40</v>
+      </c>
+      <c r="B25" s="6" t="s">
+        <v>11</v>
+      </c>
+      <c r="C25" s="7">
+        <v>-14.68</v>
+      </c>
+      <c r="D25" s="7">
+        <v>-15.38</v>
+      </c>
+      <c r="E25" s="9">
+        <v>-0.7</v>
+      </c>
+    </row>
+    <row r="26" spans="1:5">
+      <c r="A26" s="6" t="s">
+        <v>41</v>
+      </c>
+      <c r="B26" s="6" t="s">
+        <v>11</v>
+      </c>
+      <c r="C26" s="7">
+        <v>-8.32</v>
+      </c>
+      <c r="D26" s="7">
+        <v>-11.08</v>
+      </c>
+      <c r="E26" s="9">
+        <v>-2.76</v>
+      </c>
+    </row>
+    <row r="27" spans="1:5">
+      <c r="A27" s="6" t="s">
+        <v>42</v>
+      </c>
+      <c r="B27" s="6" t="s">
+        <v>11</v>
+      </c>
+      <c r="C27" s="7">
+        <v>-4.85</v>
+      </c>
+      <c r="D27" s="7">
+        <v>-5.83</v>
+      </c>
+      <c r="E27" s="9">
+        <v>-0.98</v>
+      </c>
+    </row>
+    <row r="28" spans="1:5">
+      <c r="A28" s="6" t="s">
+        <v>43</v>
+      </c>
+      <c r="B28" s="6" t="s">
+        <v>11</v>
+      </c>
+      <c r="C28" s="7">
+        <v>26.58</v>
+      </c>
+      <c r="D28" s="7">
+        <v>30.71</v>
+      </c>
+      <c r="E28" s="8">
+        <v>4.13</v>
+      </c>
+    </row>
+    <row r="29" spans="1:5">
+      <c r="A29" s="6" t="s">
+        <v>37</v>
+      </c>
+      <c r="B29" s="6" t="s">
+        <v>10</v>
+      </c>
+      <c r="C29" s="7">
+        <v>-3.72</v>
+      </c>
+      <c r="D29" s="7">
+        <v>-3.34</v>
+      </c>
+      <c r="E29" s="8">
+        <v>0.38</v>
+      </c>
+    </row>
+    <row r="30" spans="1:5">
+      <c r="A30" s="6" t="s">
+        <v>38</v>
+      </c>
+      <c r="B30" s="6" t="s">
+        <v>10</v>
+      </c>
+      <c r="C30" s="7">
+        <v>-24.36</v>
+      </c>
+      <c r="D30" s="7">
+        <v>-25.44</v>
+      </c>
+      <c r="E30" s="9">
+        <v>-1.08</v>
+      </c>
+    </row>
+    <row r="31" spans="1:5">
+      <c r="A31" s="6" t="s">
+        <v>39</v>
+      </c>
+      <c r="B31" s="6" t="s">
+        <v>10</v>
+      </c>
+      <c r="C31" s="7">
+        <v>-10</v>
+      </c>
+      <c r="D31" s="7">
+        <v>-11.2</v>
+      </c>
+      <c r="E31" s="9">
+        <v>-1.2</v>
+      </c>
+    </row>
+    <row r="32" spans="1:5">
+      <c r="A32" s="6" t="s">
+        <v>40</v>
+      </c>
+      <c r="B32" s="6" t="s">
+        <v>10</v>
+      </c>
+      <c r="C32" s="7">
+        <v>-9.460000000000001</v>
+      </c>
+      <c r="D32" s="7">
+        <v>-9.859999999999999</v>
+      </c>
+      <c r="E32" s="9">
+        <v>-0.4</v>
+      </c>
+    </row>
+    <row r="33" spans="1:5">
+      <c r="A33" s="6" t="s">
+        <v>41</v>
+      </c>
+      <c r="B33" s="6" t="s">
+        <v>10</v>
+      </c>
+      <c r="C33" s="7">
+        <v>1.56</v>
+      </c>
+      <c r="D33" s="7">
+        <v>-0.02</v>
+      </c>
+      <c r="E33" s="9">
+        <v>-1.58</v>
+      </c>
+    </row>
+    <row r="34" spans="1:5">
+      <c r="A34" s="6" t="s">
+        <v>42</v>
+      </c>
+      <c r="B34" s="6" t="s">
+        <v>10</v>
+      </c>
+      <c r="C34" s="7">
+        <v>-5.93</v>
+      </c>
+      <c r="D34" s="7">
+        <v>-6.39</v>
+      </c>
+      <c r="E34" s="9">
+        <v>-0.46</v>
+      </c>
+    </row>
+    <row r="35" spans="1:5">
+      <c r="A35" s="6" t="s">
+        <v>43</v>
+      </c>
+      <c r="B35" s="6" t="s">
+        <v>10</v>
+      </c>
+      <c r="C35" s="7">
+        <v>32.44</v>
+      </c>
+      <c r="D35" s="7">
+        <v>30.72</v>
+      </c>
+      <c r="E35" s="9">
+        <v>-1.72</v>
+      </c>
+    </row>
+    <row r="36" spans="1:5">
+      <c r="A36" s="6" t="s">
+        <v>37</v>
+      </c>
+      <c r="B36" s="6" t="s">
+        <v>6</v>
+      </c>
+      <c r="C36" s="7">
+        <v>-20.9</v>
+      </c>
+      <c r="D36" s="7">
+        <v>-18.83</v>
+      </c>
+      <c r="E36" s="8">
+        <v>2.07</v>
+      </c>
+    </row>
+    <row r="37" spans="1:5">
+      <c r="A37" s="6" t="s">
+        <v>38</v>
+      </c>
+      <c r="B37" s="6" t="s">
+        <v>6</v>
+      </c>
+      <c r="C37" s="7">
+        <v>-24.36</v>
+      </c>
+      <c r="D37" s="7">
+        <v>-26.53</v>
+      </c>
+      <c r="E37" s="9">
+        <v>-2.17</v>
+      </c>
+    </row>
+    <row r="38" spans="1:5">
+      <c r="A38" s="6" t="s">
+        <v>39</v>
+      </c>
+      <c r="B38" s="6" t="s">
+        <v>6</v>
+      </c>
+      <c r="C38" s="7">
+        <v>-45.62</v>
+      </c>
+      <c r="D38" s="7">
+        <v>-45.47</v>
+      </c>
+      <c r="E38" s="8">
+        <v>0.15</v>
+      </c>
+    </row>
+    <row r="39" spans="1:5">
+      <c r="A39" s="6" t="s">
+        <v>40</v>
+      </c>
+      <c r="B39" s="6" t="s">
+        <v>6</v>
+      </c>
+      <c r="C39" s="7">
+        <v>-20.3</v>
+      </c>
+      <c r="D39" s="7">
+        <v>-20.98</v>
+      </c>
+      <c r="E39" s="9">
+        <v>-0.68</v>
+      </c>
+    </row>
+    <row r="40" spans="1:5">
+      <c r="A40" s="6" t="s">
+        <v>41</v>
+      </c>
+      <c r="B40" s="6" t="s">
+        <v>6</v>
+      </c>
+      <c r="C40" s="7">
+        <v>-17.68</v>
+      </c>
+      <c r="D40" s="7">
+        <v>-18.21</v>
+      </c>
+      <c r="E40" s="9">
+        <v>-0.53</v>
+      </c>
+    </row>
+    <row r="41" spans="1:5">
+      <c r="A41" s="6" t="s">
+        <v>42</v>
+      </c>
+      <c r="B41" s="6" t="s">
+        <v>6</v>
+      </c>
+      <c r="C41" s="7">
+        <v>-17.16</v>
+      </c>
+      <c r="D41" s="7">
+        <v>-17.39</v>
+      </c>
+      <c r="E41" s="9">
+        <v>-0.23</v>
+      </c>
+    </row>
+    <row r="42" spans="1:5">
+      <c r="A42" s="6" t="s">
+        <v>43</v>
+      </c>
+      <c r="B42" s="6" t="s">
+        <v>6</v>
+      </c>
+      <c r="C42" s="7">
+        <v>-5.34</v>
+      </c>
+      <c r="D42" s="7">
+        <v>-4.49</v>
+      </c>
+      <c r="E42" s="8">
+        <v>0.85</v>
+      </c>
+    </row>
+    <row r="43" spans="1:5">
+      <c r="A43" s="6" t="s">
+        <v>37</v>
+      </c>
+      <c r="B43" s="6" t="s">
+        <v>2</v>
+      </c>
+      <c r="C43" s="7">
+        <v>9778</v>
+      </c>
+      <c r="D43" s="7">
+        <v>10034</v>
+      </c>
+      <c r="E43" s="8">
+        <v>256</v>
+      </c>
+    </row>
+    <row r="44" spans="1:5">
+      <c r="A44" s="6" t="s">
+        <v>38</v>
+      </c>
+      <c r="B44" s="6" t="s">
+        <v>2</v>
+      </c>
+      <c r="C44" s="7">
+        <v>506.95</v>
+      </c>
+      <c r="D44" s="7">
+        <v>492.4</v>
+      </c>
+      <c r="E44" s="9">
+        <v>-14.55</v>
+      </c>
+    </row>
+    <row r="45" spans="1:5">
+      <c r="A45" s="6" t="s">
+        <v>39</v>
+      </c>
+      <c r="B45" s="6" t="s">
+        <v>2</v>
+      </c>
+      <c r="C45" s="7">
+        <v>298</v>
+      </c>
+      <c r="D45" s="7">
+        <v>298.85</v>
+      </c>
+      <c r="E45" s="8">
+        <v>0.85</v>
+      </c>
+    </row>
+    <row r="46" spans="1:5">
+      <c r="A46" s="6" t="s">
+        <v>40</v>
+      </c>
+      <c r="B46" s="6" t="s">
+        <v>2</v>
+      </c>
+      <c r="C46" s="7">
+        <v>1734.7</v>
+      </c>
+      <c r="D46" s="7">
+        <v>1719.9</v>
+      </c>
+      <c r="E46" s="9">
+        <v>-14.8</v>
+      </c>
+    </row>
+    <row r="47" spans="1:5">
+      <c r="A47" s="6" t="s">
+        <v>41</v>
+      </c>
+      <c r="B47" s="6" t="s">
+        <v>2</v>
+      </c>
+      <c r="C47" s="7">
+        <v>10820</v>
+      </c>
+      <c r="D47" s="7">
+        <v>10750</v>
+      </c>
+      <c r="E47" s="9">
+        <v>-70</v>
+      </c>
+    </row>
+    <row r="48" spans="1:5">
+      <c r="A48" s="6" t="s">
+        <v>42</v>
+      </c>
+      <c r="B48" s="6" t="s">
+        <v>2</v>
+      </c>
+      <c r="C48" s="7">
+        <v>960</v>
+      </c>
+      <c r="D48" s="7">
+        <v>957.25</v>
+      </c>
+      <c r="E48" s="9">
+        <v>-2.75</v>
+      </c>
+    </row>
+    <row r="49" spans="1:5">
+      <c r="A49" s="6" t="s">
+        <v>43</v>
+      </c>
+      <c r="B49" s="6" t="s">
+        <v>2</v>
+      </c>
+      <c r="C49" s="7">
+        <v>175.99</v>
+      </c>
+      <c r="D49" s="7">
+        <v>177.58</v>
+      </c>
+      <c r="E49" s="8">
+        <v>1.59</v>
+      </c>
+    </row>
+    <row r="50" spans="1:5">
+      <c r="A50" s="6" t="s">
+        <v>37</v>
+      </c>
+      <c r="B50" s="6" t="s">
+        <v>24</v>
+      </c>
+      <c r="C50" s="7">
+        <v>23.2</v>
+      </c>
+      <c r="D50" s="7">
+        <v>31.77</v>
+      </c>
+      <c r="E50" s="8">
+        <v>8.57</v>
+      </c>
+    </row>
+    <row r="51" spans="1:5">
+      <c r="A51" s="6" t="s">
+        <v>38</v>
+      </c>
+      <c r="B51" s="6" t="s">
+        <v>24</v>
+      </c>
+      <c r="C51" s="7">
+        <v>52.93</v>
+      </c>
+      <c r="D51" s="7">
+        <v>47.42</v>
+      </c>
+      <c r="E51" s="9">
+        <v>-5.51</v>
+      </c>
+    </row>
+    <row r="52" spans="1:5">
+      <c r="A52" s="6" t="s">
+        <v>39</v>
+      </c>
+      <c r="B52" s="6" t="s">
+        <v>24</v>
+      </c>
+      <c r="C52" s="7">
+        <v>34.16</v>
+      </c>
+      <c r="D52" s="7">
+        <v>35.1</v>
+      </c>
+      <c r="E52" s="8">
+        <v>0.9399999999999999</v>
+      </c>
+    </row>
+    <row r="53" spans="1:5">
+      <c r="A53" s="6" t="s">
+        <v>40</v>
+      </c>
+      <c r="B53" s="6" t="s">
+        <v>24</v>
+      </c>
+      <c r="C53" s="7">
+        <v>32.87</v>
+      </c>
+      <c r="D53" s="7">
+        <v>31.03</v>
+      </c>
+      <c r="E53" s="9">
+        <v>-1.84</v>
+      </c>
+    </row>
+    <row r="54" spans="1:5">
+      <c r="A54" s="6" t="s">
+        <v>41</v>
+      </c>
+      <c r="B54" s="6" t="s">
+        <v>24</v>
+      </c>
+      <c r="C54" s="7">
+        <v>47.07</v>
+      </c>
+      <c r="D54" s="7">
+        <v>45.41</v>
+      </c>
+      <c r="E54" s="9">
+        <v>-1.66</v>
+      </c>
+    </row>
+    <row r="55" spans="1:5">
+      <c r="A55" s="6" t="s">
+        <v>42</v>
+      </c>
+      <c r="B55" s="6" t="s">
+        <v>24</v>
+      </c>
+      <c r="C55" s="7">
+        <v>37.62</v>
+      </c>
+      <c r="D55" s="7">
+        <v>37.02</v>
+      </c>
+      <c r="E55" s="9">
         <v>-0.6</v>
       </c>
-      <c r="E18" s="7">
-        <v>3.8</v>
-      </c>
-    </row>
-    <row r="19" spans="1:5">
-      <c r="A19" s="5" t="s">
+    </row>
+    <row r="56" spans="1:5">
+      <c r="A56" s="6" t="s">
+        <v>43</v>
+      </c>
+      <c r="B56" s="6" t="s">
+        <v>24</v>
+      </c>
+      <c r="C56" s="7">
+        <v>64.75</v>
+      </c>
+      <c r="D56" s="7">
+        <v>65.70999999999999</v>
+      </c>
+      <c r="E56" s="8">
+        <v>0.96</v>
+      </c>
+    </row>
+    <row r="57" spans="1:5">
+      <c r="A57" s="6" t="s">
+        <v>37</v>
+      </c>
+      <c r="B57" s="6" t="s">
+        <v>31</v>
+      </c>
+      <c r="C57" s="7">
+        <v>-12.39</v>
+      </c>
+      <c r="D57" s="7">
+        <v>9.17</v>
+      </c>
+      <c r="E57" s="8">
+        <v>21.56</v>
+      </c>
+    </row>
+    <row r="58" spans="1:5">
+      <c r="A58" s="6" t="s">
+        <v>38</v>
+      </c>
+      <c r="B58" s="6" t="s">
+        <v>31</v>
+      </c>
+      <c r="C58" s="7">
+        <v>-8.09</v>
+      </c>
+      <c r="D58" s="7">
+        <v>-41.08</v>
+      </c>
+      <c r="E58" s="9">
+        <v>-32.99</v>
+      </c>
+    </row>
+    <row r="59" spans="1:5">
+      <c r="A59" s="6" t="s">
+        <v>39</v>
+      </c>
+      <c r="B59" s="6" t="s">
+        <v>31</v>
+      </c>
+      <c r="C59" s="7">
+        <v>-23.71</v>
+      </c>
+      <c r="D59" s="7">
+        <v>-38.62</v>
+      </c>
+      <c r="E59" s="9">
+        <v>-14.91</v>
+      </c>
+    </row>
+    <row r="60" spans="1:5">
+      <c r="A60" s="6" t="s">
         <v>40</v>
       </c>
-      <c r="B19" s="5" t="s">
-        <v>8</v>
-      </c>
-      <c r="C19" s="6">
-        <v>-1.33</v>
-      </c>
-      <c r="D19" s="6">
-        <v>0.12</v>
-      </c>
-      <c r="E19" s="7">
-        <v>1.45</v>
-      </c>
-    </row>
-    <row r="20" spans="1:5">
-      <c r="A20" s="5" t="s">
+      <c r="B60" s="6" t="s">
+        <v>31</v>
+      </c>
+      <c r="C60" s="7">
+        <v>-9.69</v>
+      </c>
+      <c r="D60" s="7">
+        <v>-34.16</v>
+      </c>
+      <c r="E60" s="9">
+        <v>-24.47</v>
+      </c>
+    </row>
+    <row r="61" spans="1:5">
+      <c r="A61" s="6" t="s">
         <v>41</v>
       </c>
-      <c r="B20" s="5" t="s">
-        <v>8</v>
-      </c>
-      <c r="C20" s="6">
-        <v>-1.74</v>
-      </c>
-      <c r="D20" s="6">
-        <v>1.44</v>
-      </c>
-      <c r="E20" s="7">
-        <v>3.18</v>
-      </c>
-    </row>
-    <row r="21" spans="1:5">
-      <c r="A21" s="5" t="s">
+      <c r="B61" s="6" t="s">
+        <v>31</v>
+      </c>
+      <c r="C61" s="7">
+        <v>-72.03</v>
+      </c>
+      <c r="D61" s="7">
+        <v>-38.37</v>
+      </c>
+      <c r="E61" s="8">
+        <v>33.66</v>
+      </c>
+    </row>
+    <row r="62" spans="1:5">
+      <c r="A62" s="6" t="s">
         <v>42</v>
       </c>
-      <c r="B21" s="5" t="s">
-        <v>8</v>
-      </c>
-      <c r="C21" s="6">
-        <v>-0.36</v>
-      </c>
-      <c r="D21" s="6">
-        <v>1.23</v>
-      </c>
-      <c r="E21" s="7">
-        <v>1.59</v>
-      </c>
-    </row>
-    <row r="22" spans="1:5">
-      <c r="A22" s="5" t="s">
+      <c r="B62" s="6" t="s">
+        <v>31</v>
+      </c>
+      <c r="C62" s="7">
+        <v>9.17</v>
+      </c>
+      <c r="D62" s="7">
+        <v>-30.26</v>
+      </c>
+      <c r="E62" s="9">
+        <v>-39.43</v>
+      </c>
+    </row>
+    <row r="63" spans="1:5">
+      <c r="A63" s="6" t="s">
         <v>43</v>
       </c>
-      <c r="B22" s="5" t="s">
-        <v>8</v>
-      </c>
-      <c r="C22" s="6">
-        <v>-3.24</v>
-      </c>
-      <c r="D22" s="6">
-        <v>1.93</v>
-      </c>
-      <c r="E22" s="7">
-        <v>5.17</v>
-      </c>
-    </row>
-    <row r="23" spans="1:5">
-      <c r="A23" s="5" t="s">
-        <v>37</v>
-      </c>
-      <c r="B23" s="5" t="s">
-        <v>11</v>
-      </c>
-      <c r="C23" s="6">
-        <v>12.59</v>
-      </c>
-      <c r="D23" s="6">
-        <v>12.78</v>
-      </c>
-      <c r="E23" s="7">
-        <v>0.19</v>
-      </c>
-    </row>
-    <row r="24" spans="1:5">
-      <c r="A24" s="5" t="s">
-        <v>38</v>
-      </c>
-      <c r="B24" s="5" t="s">
-        <v>11</v>
-      </c>
-      <c r="C24" s="6">
-        <v>104.38</v>
-      </c>
-      <c r="D24" s="6">
-        <v>108.96</v>
-      </c>
-      <c r="E24" s="7">
-        <v>4.58</v>
-      </c>
-    </row>
-    <row r="25" spans="1:5">
-      <c r="A25" s="5" t="s">
-        <v>39</v>
-      </c>
-      <c r="B25" s="5" t="s">
-        <v>11</v>
-      </c>
-      <c r="C25" s="6">
-        <v>-46.68</v>
-      </c>
-      <c r="D25" s="6">
-        <v>-45.06</v>
-      </c>
-      <c r="E25" s="7">
-        <v>1.62</v>
-      </c>
-    </row>
-    <row r="26" spans="1:5">
-      <c r="A26" s="5" t="s">
-        <v>40</v>
-      </c>
-      <c r="B26" s="5" t="s">
-        <v>11</v>
-      </c>
-      <c r="C26" s="6">
-        <v>-14.64</v>
-      </c>
-      <c r="D26" s="6">
-        <v>-14.68</v>
-      </c>
-      <c r="E26" s="8">
-        <v>-0.04</v>
-      </c>
-    </row>
-    <row r="27" spans="1:5">
-      <c r="A27" s="5" t="s">
-        <v>41</v>
-      </c>
-      <c r="B27" s="5" t="s">
-        <v>11</v>
-      </c>
-      <c r="C27" s="6">
-        <v>-10.31</v>
-      </c>
-      <c r="D27" s="6">
-        <v>-8.32</v>
-      </c>
-      <c r="E27" s="7">
-        <v>1.99</v>
-      </c>
-    </row>
-    <row r="28" spans="1:5">
-      <c r="A28" s="5" t="s">
-        <v>42</v>
-      </c>
-      <c r="B28" s="5" t="s">
-        <v>11</v>
-      </c>
-      <c r="C28" s="6">
-        <v>-3.42</v>
-      </c>
-      <c r="D28" s="6">
-        <v>-4.85</v>
-      </c>
-      <c r="E28" s="8">
-        <v>-1.43</v>
-      </c>
-    </row>
-    <row r="29" spans="1:5">
-      <c r="A29" s="5" t="s">
-        <v>43</v>
-      </c>
-      <c r="B29" s="5" t="s">
-        <v>11</v>
-      </c>
-      <c r="C29" s="6">
-        <v>22.3</v>
-      </c>
-      <c r="D29" s="6">
-        <v>26.58</v>
-      </c>
-      <c r="E29" s="7">
-        <v>4.28</v>
-      </c>
-    </row>
-    <row r="30" spans="1:5">
-      <c r="A30" s="5" t="s">
-        <v>37</v>
-      </c>
-      <c r="B30" s="5" t="s">
-        <v>10</v>
-      </c>
-      <c r="C30" s="6">
-        <v>-5.1</v>
-      </c>
-      <c r="D30" s="6">
-        <v>-3.72</v>
-      </c>
-      <c r="E30" s="7">
-        <v>1.38</v>
-      </c>
-    </row>
-    <row r="31" spans="1:5">
-      <c r="A31" s="5" t="s">
-        <v>38</v>
-      </c>
-      <c r="B31" s="5" t="s">
-        <v>10</v>
-      </c>
-      <c r="C31" s="6">
-        <v>-23.99</v>
-      </c>
-      <c r="D31" s="6">
-        <v>-24.36</v>
-      </c>
-      <c r="E31" s="8">
-        <v>-0.37</v>
-      </c>
-    </row>
-    <row r="32" spans="1:5">
-      <c r="A32" s="5" t="s">
-        <v>39</v>
-      </c>
-      <c r="B32" s="5" t="s">
-        <v>10</v>
-      </c>
-      <c r="C32" s="6">
-        <v>-11.23</v>
-      </c>
-      <c r="D32" s="6">
-        <v>-10</v>
-      </c>
-      <c r="E32" s="7">
-        <v>1.23</v>
-      </c>
-    </row>
-    <row r="33" spans="1:5">
-      <c r="A33" s="5" t="s">
-        <v>40</v>
-      </c>
-      <c r="B33" s="5" t="s">
-        <v>10</v>
-      </c>
-      <c r="C33" s="6">
-        <v>-9.869999999999999</v>
-      </c>
-      <c r="D33" s="6">
-        <v>-9.460000000000001</v>
-      </c>
-      <c r="E33" s="7">
-        <v>0.41</v>
-      </c>
-    </row>
-    <row r="34" spans="1:5">
-      <c r="A34" s="5" t="s">
-        <v>41</v>
-      </c>
-      <c r="B34" s="5" t="s">
-        <v>10</v>
-      </c>
-      <c r="C34" s="6">
-        <v>0.18</v>
-      </c>
-      <c r="D34" s="6">
-        <v>1.56</v>
-      </c>
-      <c r="E34" s="7">
-        <v>1.38</v>
-      </c>
-    </row>
-    <row r="35" spans="1:5">
-      <c r="A35" s="5" t="s">
-        <v>42</v>
-      </c>
-      <c r="B35" s="5" t="s">
-        <v>10</v>
-      </c>
-      <c r="C35" s="6">
-        <v>-4.77</v>
-      </c>
-      <c r="D35" s="6">
-        <v>-5.93</v>
-      </c>
-      <c r="E35" s="8">
-        <v>-1.16</v>
-      </c>
-    </row>
-    <row r="36" spans="1:5">
-      <c r="A36" s="5" t="s">
-        <v>43</v>
-      </c>
-      <c r="B36" s="5" t="s">
-        <v>10</v>
-      </c>
-      <c r="C36" s="6">
-        <v>33.27</v>
-      </c>
-      <c r="D36" s="6">
-        <v>32.44</v>
-      </c>
-      <c r="E36" s="8">
-        <v>-0.83</v>
-      </c>
-    </row>
-    <row r="37" spans="1:5">
-      <c r="A37" s="5" t="s">
-        <v>37</v>
-      </c>
-      <c r="B37" s="5" t="s">
-        <v>6</v>
-      </c>
-      <c r="C37" s="6">
-        <v>-22.04</v>
-      </c>
-      <c r="D37" s="6">
-        <v>-20.9</v>
-      </c>
-      <c r="E37" s="7">
-        <v>1.14</v>
-      </c>
-    </row>
-    <row r="38" spans="1:5">
-      <c r="A38" s="5" t="s">
-        <v>38</v>
-      </c>
-      <c r="B38" s="5" t="s">
-        <v>6</v>
-      </c>
-      <c r="C38" s="6">
-        <v>-27.02</v>
-      </c>
-      <c r="D38" s="6">
-        <v>-24.36</v>
-      </c>
-      <c r="E38" s="7">
-        <v>2.66</v>
-      </c>
-    </row>
-    <row r="39" spans="1:5">
-      <c r="A39" s="5" t="s">
-        <v>39</v>
-      </c>
-      <c r="B39" s="5" t="s">
-        <v>6</v>
-      </c>
-      <c r="C39" s="6">
-        <v>-47.07</v>
-      </c>
-      <c r="D39" s="6">
-        <v>-45.62</v>
-      </c>
-      <c r="E39" s="7">
-        <v>1.45</v>
-      </c>
-    </row>
-    <row r="40" spans="1:5">
-      <c r="A40" s="5" t="s">
-        <v>40</v>
-      </c>
-      <c r="B40" s="5" t="s">
-        <v>6</v>
-      </c>
-      <c r="C40" s="6">
-        <v>-21.53</v>
-      </c>
-      <c r="D40" s="6">
-        <v>-20.3</v>
-      </c>
-      <c r="E40" s="7">
-        <v>1.23</v>
-      </c>
-    </row>
-    <row r="41" spans="1:5">
-      <c r="A41" s="5" t="s">
-        <v>41</v>
-      </c>
-      <c r="B41" s="5" t="s">
-        <v>6</v>
-      </c>
-      <c r="C41" s="6">
-        <v>-19.35</v>
-      </c>
-      <c r="D41" s="6">
-        <v>-17.68</v>
-      </c>
-      <c r="E41" s="7">
-        <v>1.67</v>
-      </c>
-    </row>
-    <row r="42" spans="1:5">
-      <c r="A42" s="5" t="s">
-        <v>42</v>
-      </c>
-      <c r="B42" s="5" t="s">
-        <v>6</v>
-      </c>
-      <c r="C42" s="6">
-        <v>-17.51</v>
-      </c>
-      <c r="D42" s="6">
-        <v>-17.16</v>
-      </c>
-      <c r="E42" s="7">
-        <v>0.35</v>
-      </c>
-    </row>
-    <row r="43" spans="1:5">
-      <c r="A43" s="5" t="s">
-        <v>43</v>
-      </c>
-      <c r="B43" s="5" t="s">
-        <v>6</v>
-      </c>
-      <c r="C43" s="6">
-        <v>-6.26</v>
-      </c>
-      <c r="D43" s="6">
-        <v>-5.34</v>
-      </c>
-      <c r="E43" s="7">
-        <v>0.92</v>
-      </c>
-    </row>
-    <row r="44" spans="1:5">
-      <c r="A44" s="5" t="s">
-        <v>37</v>
-      </c>
-      <c r="B44" s="5" t="s">
-        <v>2</v>
-      </c>
-      <c r="C44" s="6">
-        <v>9637</v>
-      </c>
-      <c r="D44" s="6">
-        <v>9778</v>
-      </c>
-      <c r="E44" s="7">
-        <v>141</v>
-      </c>
-    </row>
-    <row r="45" spans="1:5">
-      <c r="A45" s="5" t="s">
-        <v>38</v>
-      </c>
-      <c r="B45" s="5" t="s">
-        <v>2</v>
-      </c>
-      <c r="C45" s="6">
-        <v>489.15</v>
-      </c>
-      <c r="D45" s="6">
-        <v>506.95</v>
-      </c>
-      <c r="E45" s="7">
-        <v>17.8</v>
-      </c>
-    </row>
-    <row r="46" spans="1:5">
-      <c r="A46" s="5" t="s">
-        <v>39</v>
-      </c>
-      <c r="B46" s="5" t="s">
-        <v>2</v>
-      </c>
-      <c r="C46" s="6">
-        <v>290.05</v>
-      </c>
-      <c r="D46" s="6">
-        <v>298</v>
-      </c>
-      <c r="E46" s="7">
-        <v>7.95</v>
-      </c>
-    </row>
-    <row r="47" spans="1:5">
-      <c r="A47" s="5" t="s">
-        <v>40</v>
-      </c>
-      <c r="B47" s="5" t="s">
-        <v>2</v>
-      </c>
-      <c r="C47" s="6">
-        <v>1708</v>
-      </c>
-      <c r="D47" s="6">
-        <v>1734.7</v>
-      </c>
-      <c r="E47" s="7">
-        <v>26.7</v>
-      </c>
-    </row>
-    <row r="48" spans="1:5">
-      <c r="A48" s="5" t="s">
-        <v>41</v>
-      </c>
-      <c r="B48" s="5" t="s">
-        <v>2</v>
-      </c>
-      <c r="C48" s="6">
-        <v>10600</v>
-      </c>
-      <c r="D48" s="6">
-        <v>10820</v>
-      </c>
-      <c r="E48" s="7">
-        <v>220</v>
-      </c>
-    </row>
-    <row r="49" spans="1:5">
-      <c r="A49" s="5" t="s">
-        <v>42</v>
-      </c>
-      <c r="B49" s="5" t="s">
-        <v>2</v>
-      </c>
-      <c r="C49" s="6">
-        <v>955.95</v>
-      </c>
-      <c r="D49" s="6">
-        <v>960</v>
-      </c>
-      <c r="E49" s="7">
-        <v>4.05</v>
-      </c>
-    </row>
-    <row r="50" spans="1:5">
-      <c r="A50" s="5" t="s">
-        <v>43</v>
-      </c>
-      <c r="B50" s="5" t="s">
-        <v>2</v>
-      </c>
-      <c r="C50" s="6">
-        <v>174.29</v>
-      </c>
-      <c r="D50" s="6">
-        <v>175.99</v>
-      </c>
-      <c r="E50" s="7">
-        <v>1.7</v>
-      </c>
-    </row>
-    <row r="51" spans="1:5">
-      <c r="A51" s="5" t="s">
-        <v>37</v>
-      </c>
-      <c r="B51" s="5" t="s">
-        <v>24</v>
-      </c>
-      <c r="C51" s="6">
-        <v>17.92</v>
-      </c>
-      <c r="D51" s="6">
-        <v>23.2</v>
-      </c>
-      <c r="E51" s="7">
-        <v>5.28</v>
-      </c>
-    </row>
-    <row r="52" spans="1:5">
-      <c r="A52" s="5" t="s">
-        <v>38</v>
-      </c>
-      <c r="B52" s="5" t="s">
-        <v>24</v>
-      </c>
-      <c r="C52" s="6">
-        <v>45.77</v>
-      </c>
-      <c r="D52" s="6">
-        <v>52.93</v>
-      </c>
-      <c r="E52" s="7">
-        <v>7.16</v>
-      </c>
-    </row>
-    <row r="53" spans="1:5">
-      <c r="A53" s="5" t="s">
-        <v>39</v>
-      </c>
-      <c r="B53" s="5" t="s">
-        <v>24</v>
-      </c>
-      <c r="C53" s="6">
-        <v>24.79</v>
-      </c>
-      <c r="D53" s="6">
-        <v>34.16</v>
-      </c>
-      <c r="E53" s="7">
-        <v>9.369999999999999</v>
-      </c>
-    </row>
-    <row r="54" spans="1:5">
-      <c r="A54" s="5" t="s">
-        <v>40</v>
-      </c>
-      <c r="B54" s="5" t="s">
-        <v>24</v>
-      </c>
-      <c r="C54" s="6">
-        <v>25.47</v>
-      </c>
-      <c r="D54" s="6">
-        <v>32.87</v>
-      </c>
-      <c r="E54" s="7">
-        <v>7.4</v>
-      </c>
-    </row>
-    <row r="55" spans="1:5">
-      <c r="A55" s="5" t="s">
-        <v>41</v>
-      </c>
-      <c r="B55" s="5" t="s">
-        <v>24</v>
-      </c>
-      <c r="C55" s="6">
-        <v>40.75</v>
-      </c>
-      <c r="D55" s="6">
-        <v>47.07</v>
-      </c>
-      <c r="E55" s="7">
-        <v>6.32</v>
-      </c>
-    </row>
-    <row r="56" spans="1:5">
-      <c r="A56" s="5" t="s">
-        <v>42</v>
-      </c>
-      <c r="B56" s="5" t="s">
-        <v>24</v>
-      </c>
-      <c r="C56" s="6">
-        <v>36.21</v>
-      </c>
-      <c r="D56" s="6">
-        <v>37.62</v>
-      </c>
-      <c r="E56" s="7">
-        <v>1.41</v>
-      </c>
-    </row>
-    <row r="57" spans="1:5">
-      <c r="A57" s="5" t="s">
-        <v>43</v>
-      </c>
-      <c r="B57" s="5" t="s">
-        <v>24</v>
-      </c>
-      <c r="C57" s="6">
-        <v>63.74</v>
-      </c>
-      <c r="D57" s="6">
-        <v>64.75</v>
-      </c>
-      <c r="E57" s="7">
-        <v>1.01</v>
-      </c>
-    </row>
-    <row r="58" spans="1:5">
-      <c r="A58" s="5" t="s">
-        <v>37</v>
-      </c>
-      <c r="B58" s="5" t="s">
+      <c r="B63" s="6" t="s">
         <v>31</v>
       </c>
-      <c r="C58" s="6">
-        <v>-29.09</v>
-      </c>
-      <c r="D58" s="6">
-        <v>-12.39</v>
-      </c>
-      <c r="E58" s="7">
-        <v>16.7</v>
-      </c>
-    </row>
-    <row r="59" spans="1:5">
-      <c r="A59" s="5" t="s">
-        <v>38</v>
-      </c>
-      <c r="B59" s="5" t="s">
-        <v>31</v>
-      </c>
-      <c r="C59" s="6">
-        <v>60.11</v>
-      </c>
-      <c r="D59" s="6">
-        <v>-8.09</v>
-      </c>
-      <c r="E59" s="8">
-        <v>-68.2</v>
-      </c>
-    </row>
-    <row r="60" spans="1:5">
-      <c r="A60" s="5" t="s">
-        <v>39</v>
-      </c>
-      <c r="B60" s="5" t="s">
-        <v>31</v>
-      </c>
-      <c r="C60" s="6">
-        <v>18.01</v>
-      </c>
-      <c r="D60" s="6">
-        <v>-23.71</v>
-      </c>
-      <c r="E60" s="8">
-        <v>-41.72</v>
-      </c>
-    </row>
-    <row r="61" spans="1:5">
-      <c r="A61" s="5" t="s">
-        <v>40</v>
-      </c>
-      <c r="B61" s="5" t="s">
-        <v>31</v>
-      </c>
-      <c r="C61" s="6">
-        <v>45.15</v>
-      </c>
-      <c r="D61" s="6">
-        <v>-9.69</v>
-      </c>
-      <c r="E61" s="8">
-        <v>-54.84</v>
-      </c>
-    </row>
-    <row r="62" spans="1:5">
-      <c r="A62" s="5" t="s">
-        <v>41</v>
-      </c>
-      <c r="B62" s="5" t="s">
-        <v>31</v>
-      </c>
-      <c r="C62" s="6">
-        <v>32.58</v>
-      </c>
-      <c r="D62" s="6">
-        <v>-72.03</v>
-      </c>
-      <c r="E62" s="8">
-        <v>-104.61</v>
-      </c>
-    </row>
-    <row r="63" spans="1:5">
-      <c r="A63" s="5" t="s">
-        <v>42</v>
-      </c>
-      <c r="B63" s="5" t="s">
-        <v>31</v>
-      </c>
-      <c r="C63" s="6">
-        <v>38.49</v>
-      </c>
-      <c r="D63" s="6">
-        <v>9.17</v>
-      </c>
-      <c r="E63" s="8">
-        <v>-29.32</v>
-      </c>
-    </row>
-    <row r="64" spans="1:5">
-      <c r="A64" s="5" t="s">
-        <v>43</v>
-      </c>
-      <c r="B64" s="5" t="s">
-        <v>31</v>
-      </c>
-      <c r="C64" s="6">
-        <v>-20.14</v>
-      </c>
-      <c r="D64" s="6">
+      <c r="C63" s="7">
         <v>-58.21</v>
       </c>
-      <c r="E64" s="8">
-        <v>-38.07</v>
+      <c r="D63" s="7">
+        <v>-64.44</v>
+      </c>
+      <c r="E63" s="9">
+        <v>-6.23</v>
       </c>
     </row>
   </sheetData>
   <mergeCells count="2">
     <mergeCell ref="A1:F1"/>
-    <mergeCell ref="A7:E7"/>
+    <mergeCell ref="A6:E6"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -2965,60 +2940,60 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:9" ht="28" customHeight="1">
-      <c r="A1" s="9" t="s">
+      <c r="A1" s="10" t="s">
         <v>1</v>
       </c>
-      <c r="B1" s="9" t="s">
+      <c r="B1" s="10" t="s">
+        <v>70</v>
+      </c>
+      <c r="C1" s="10" t="s">
+        <v>71</v>
+      </c>
+      <c r="D1" s="10" t="s">
         <v>72</v>
       </c>
-      <c r="C1" s="9" t="s">
+      <c r="E1" s="10" t="s">
         <v>73</v>
       </c>
-      <c r="D1" s="9" t="s">
+      <c r="F1" s="10" t="s">
         <v>74</v>
       </c>
-      <c r="E1" s="9" t="s">
+      <c r="G1" s="10" t="s">
         <v>75</v>
       </c>
-      <c r="F1" s="9" t="s">
+      <c r="H1" s="10" t="s">
         <v>76</v>
       </c>
-      <c r="G1" s="9" t="s">
+      <c r="I1" s="10" t="s">
         <v>77</v>
       </c>
-      <c r="H1" s="9" t="s">
-        <v>78</v>
-      </c>
-      <c r="I1" s="9" t="s">
-        <v>79</v>
-      </c>
     </row>
     <row r="2" spans="1:9">
-      <c r="A2" s="10" t="s">
+      <c r="A2" s="11" t="s">
         <v>44</v>
       </c>
-      <c r="B2" s="11">
+      <c r="B2" s="12">
         <v>48.8</v>
       </c>
-      <c r="C2" s="12">
+      <c r="C2" s="13">
         <v>7</v>
       </c>
-      <c r="D2" s="11">
-        <v>41.8</v>
-      </c>
-      <c r="E2" s="11">
+      <c r="D2" s="12">
+        <v>41.9</v>
+      </c>
+      <c r="E2" s="12">
         <v>40</v>
       </c>
-      <c r="F2" s="11">
+      <c r="F2" s="12">
+        <v>-3.9</v>
+      </c>
+      <c r="G2" s="12">
         <v>-3.6</v>
       </c>
-      <c r="G2" s="11">
-        <v>-2.8</v>
-      </c>
-      <c r="H2" s="11">
+      <c r="H2" s="12">
         <v>57</v>
       </c>
-      <c r="I2" s="11">
+      <c r="I2" s="12">
         <v>10</v>
       </c>
     </row>
@@ -3120,49 +3095,49 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:7">
-      <c r="A1" s="13" t="s">
+      <c r="A1" s="14" t="s">
         <v>37</v>
       </c>
-      <c r="B1" s="13" t="s">
+      <c r="B1" s="14" t="s">
         <v>41</v>
       </c>
-      <c r="C1" s="13" t="s">
+      <c r="C1" s="14" t="s">
         <v>38</v>
       </c>
-      <c r="D1" s="13" t="s">
+      <c r="D1" s="14" t="s">
         <v>43</v>
       </c>
-      <c r="E1" s="13" t="s">
+      <c r="E1" s="14" t="s">
         <v>42</v>
       </c>
-      <c r="F1" s="13" t="s">
+      <c r="F1" s="14" t="s">
         <v>40</v>
       </c>
-      <c r="G1" s="13" t="s">
+      <c r="G1" s="14" t="s">
         <v>39</v>
       </c>
     </row>
     <row r="2" spans="1:7">
-      <c r="A2" s="14">
-        <v>0.2329</v>
-      </c>
-      <c r="B2" s="14">
-        <v>0.1945</v>
-      </c>
-      <c r="C2" s="14">
-        <v>0.1629</v>
-      </c>
-      <c r="D2" s="14">
-        <v>0.04849999999999999</v>
-      </c>
-      <c r="E2" s="14">
-        <v>0.046</v>
-      </c>
-      <c r="F2" s="14">
-        <v>-0.0038</v>
-      </c>
-      <c r="G2" s="14">
-        <v>-0.2369</v>
+      <c r="A2" s="15">
+        <v>0.231</v>
+      </c>
+      <c r="B2" s="15">
+        <v>0.1904</v>
+      </c>
+      <c r="C2" s="15">
+        <v>0.1567</v>
+      </c>
+      <c r="D2" s="15">
+        <v>0.0516</v>
+      </c>
+      <c r="E2" s="15">
+        <v>0.0443</v>
+      </c>
+      <c r="F2" s="15">
+        <v>-0.0111</v>
+      </c>
+      <c r="G2" s="15">
+        <v>-0.2356</v>
       </c>
     </row>
   </sheetData>

--- a/BAJAJ_GROUP_Technical_Metrics.xlsx
+++ b/BAJAJ_GROUP_Technical_Metrics.xlsx
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="270" uniqueCount="78">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="264" uniqueCount="73">
   <si>
     <t>Symbol</t>
   </si>
@@ -187,34 +187,19 @@
     <t>Curr Value</t>
   </si>
   <si>
-    <t>RSI Oversold Recovery</t>
-  </si>
-  <si>
-    <t>23.2 → 31.8</t>
+    <t>RSI Momentum</t>
+  </si>
+  <si>
+    <t>47.4 → 53.1</t>
   </si>
   <si>
     <t>🟢 BULLISH</t>
   </si>
   <si>
-    <t>23.2</t>
-  </si>
-  <si>
-    <t>31.8</t>
-  </si>
-  <si>
-    <t>RSI Momentum</t>
-  </si>
-  <si>
-    <t>52.9 → 47.4</t>
-  </si>
-  <si>
-    <t>🔴 BEARISH</t>
-  </si>
-  <si>
-    <t>52.9</t>
-  </si>
-  <si>
     <t>47.4</t>
+  </si>
+  <si>
+    <t>53.1</t>
   </si>
   <si>
     <t>▶  NUMERIC METRIC CHANGES (vs Previous Run)</t>
@@ -416,7 +401,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="16">
+  <cellXfs count="15">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="2" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
@@ -424,7 +409,6 @@
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="5" fillId="6" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1"/>
     <xf numFmtId="165" fontId="4" fillId="5" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
@@ -940,10 +924,10 @@
         <v>44</v>
       </c>
       <c r="C2">
-        <v>10034</v>
+        <v>10318</v>
       </c>
       <c r="D2">
-        <v>2.62</v>
+        <v>2.83</v>
       </c>
       <c r="E2">
         <v>12361</v>
@@ -952,46 +936,46 @@
         <v>8599.48</v>
       </c>
       <c r="G2">
-        <v>-18.83</v>
+        <v>-16.53</v>
       </c>
       <c r="H2">
-        <v>16.68</v>
+        <v>19.98</v>
       </c>
       <c r="I2">
-        <v>0.1</v>
+        <v>3</v>
       </c>
       <c r="J2">
-        <v>-14.89</v>
+        <v>-12.32</v>
       </c>
       <c r="K2">
-        <v>-3.34</v>
+        <v>1.5</v>
       </c>
       <c r="L2">
-        <v>14.28</v>
+        <v>19.01</v>
       </c>
       <c r="M2">
-        <v>23.1</v>
+        <v>23.86</v>
       </c>
       <c r="N2">
         <v>71</v>
       </c>
       <c r="O2">
-        <v>68</v>
+        <v>72</v>
       </c>
       <c r="P2">
-        <v>9870</v>
+        <v>9930.200000000001</v>
       </c>
       <c r="Q2">
-        <v>10822.45</v>
+        <v>10754.45</v>
       </c>
       <c r="R2">
-        <v>11403.73</v>
+        <v>11379.68</v>
       </c>
       <c r="S2">
-        <v>10171.39</v>
+        <v>10178.12</v>
       </c>
       <c r="T2">
-        <v>-1.35</v>
+        <v>1.37</v>
       </c>
       <c r="U2" t="s">
         <v>45</v>
@@ -1003,37 +987,37 @@
         <v>45</v>
       </c>
       <c r="X2">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="Y2">
-        <v>31.77</v>
+        <v>39.8</v>
       </c>
       <c r="Z2">
-        <v>-472.79</v>
+        <v>-437.73</v>
       </c>
       <c r="AA2">
-        <v>-353.79</v>
+        <v>-370.58</v>
       </c>
       <c r="AB2">
-        <v>-119</v>
+        <v>-67.15000000000001</v>
       </c>
       <c r="AC2">
-        <v>25.23</v>
+        <v>54.49</v>
       </c>
       <c r="AD2">
-        <v>10.65</v>
+        <v>28.81</v>
       </c>
       <c r="AE2">
-        <v>259.78</v>
+        <v>269.58</v>
       </c>
       <c r="AF2">
-        <v>9.17</v>
+        <v>14.9</v>
       </c>
       <c r="AG2">
-        <v>12260.31</v>
+        <v>12149.96</v>
       </c>
       <c r="AH2">
-        <v>9384.59</v>
+        <v>9358.940000000001</v>
       </c>
       <c r="AI2">
         <v>10503.51</v>
@@ -1042,7 +1026,7 @@
         <v>47</v>
       </c>
       <c r="AK2">
-        <v>74.83</v>
+        <v>67.72</v>
       </c>
     </row>
     <row r="3" spans="1:37">
@@ -1053,58 +1037,58 @@
         <v>44</v>
       </c>
       <c r="C3">
-        <v>492.4</v>
+        <v>508.25</v>
       </c>
       <c r="D3">
-        <v>-2.87</v>
+        <v>3.22</v>
       </c>
       <c r="E3">
         <v>670.25</v>
       </c>
       <c r="F3">
-        <v>246.55</v>
+        <v>247.45</v>
       </c>
       <c r="G3">
-        <v>-26.53</v>
+        <v>-24.17</v>
       </c>
       <c r="H3">
-        <v>99.72</v>
+        <v>105.4</v>
       </c>
       <c r="I3">
-        <v>2.51</v>
+        <v>2.99</v>
       </c>
       <c r="J3">
-        <v>-5.57</v>
+        <v>-3.09</v>
       </c>
       <c r="K3">
-        <v>-25.44</v>
+        <v>-13.93</v>
       </c>
       <c r="L3">
-        <v>103.55</v>
+        <v>106.14</v>
       </c>
       <c r="M3">
-        <v>15.67</v>
+        <v>16.39</v>
       </c>
       <c r="N3">
         <v>99</v>
       </c>
       <c r="O3">
-        <v>89</v>
+        <v>91</v>
       </c>
       <c r="P3">
-        <v>493</v>
+        <v>495.95</v>
       </c>
       <c r="Q3">
-        <v>499.2</v>
+        <v>498.59</v>
       </c>
       <c r="R3">
-        <v>502.31</v>
+        <v>501.99</v>
       </c>
       <c r="S3">
-        <v>459.2</v>
+        <v>460.42</v>
       </c>
       <c r="T3">
-        <v>7.23</v>
+        <v>10.39</v>
       </c>
       <c r="U3" t="s">
         <v>45</v>
@@ -1119,34 +1103,34 @@
         <v>2</v>
       </c>
       <c r="Y3">
-        <v>47.42</v>
+        <v>53.14</v>
       </c>
       <c r="Z3">
-        <v>-3.86</v>
+        <v>-2.51</v>
       </c>
       <c r="AA3">
-        <v>-4.06</v>
+        <v>-3.75</v>
       </c>
       <c r="AB3">
-        <v>0.21</v>
+        <v>1.25</v>
       </c>
       <c r="AC3">
-        <v>69.54000000000001</v>
+        <v>86.73</v>
       </c>
       <c r="AD3">
-        <v>57.54</v>
+        <v>71.72</v>
       </c>
       <c r="AE3">
-        <v>19.12</v>
+        <v>19.38</v>
       </c>
       <c r="AF3">
-        <v>-41.08</v>
+        <v>-3.22</v>
       </c>
       <c r="AG3">
-        <v>521.9400000000001</v>
+        <v>519.5</v>
       </c>
       <c r="AH3">
-        <v>476.46</v>
+        <v>477.68</v>
       </c>
       <c r="AI3">
         <v>460.99</v>
@@ -1155,7 +1139,7 @@
         <v>48</v>
       </c>
       <c r="AK3">
-        <v>26.1</v>
+        <v>22.69</v>
       </c>
     </row>
     <row r="4" spans="1:37">
@@ -1166,10 +1150,10 @@
         <v>44</v>
       </c>
       <c r="C4">
-        <v>298.85</v>
+        <v>303.05</v>
       </c>
       <c r="D4">
-        <v>0.29</v>
+        <v>1.41</v>
       </c>
       <c r="E4">
         <v>548</v>
@@ -1178,46 +1162,46 @@
         <v>290.05</v>
       </c>
       <c r="G4">
-        <v>-45.47</v>
+        <v>-44.7</v>
       </c>
       <c r="H4">
-        <v>3.03</v>
+        <v>4.48</v>
       </c>
       <c r="I4">
-        <v>-0.13</v>
+        <v>0.93</v>
       </c>
       <c r="J4">
-        <v>-12.05</v>
+        <v>-10.27</v>
       </c>
       <c r="K4">
-        <v>-11.2</v>
+        <v>-7.87</v>
       </c>
       <c r="L4">
-        <v>-44.37</v>
+        <v>-43.33</v>
       </c>
       <c r="M4">
-        <v>-23.56</v>
+        <v>-23.32</v>
       </c>
       <c r="N4">
         <v>15</v>
       </c>
       <c r="O4">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="P4">
-        <v>297.57</v>
+        <v>298.13</v>
       </c>
       <c r="Q4">
-        <v>313.43</v>
+        <v>311.82</v>
       </c>
       <c r="R4">
-        <v>333.22</v>
+        <v>332.62</v>
       </c>
       <c r="S4">
-        <v>362.56</v>
+        <v>361.65</v>
       </c>
       <c r="T4">
-        <v>-17.57</v>
+        <v>-16.2</v>
       </c>
       <c r="U4" t="s">
         <v>45</v>
@@ -1232,34 +1216,34 @@
         <v>0</v>
       </c>
       <c r="Y4">
-        <v>35.1</v>
+        <v>39.64</v>
       </c>
       <c r="Z4">
-        <v>-10.37</v>
+        <v>-9.720000000000001</v>
       </c>
       <c r="AA4">
-        <v>-9.130000000000001</v>
+        <v>-9.25</v>
       </c>
       <c r="AB4">
-        <v>-1.24</v>
+        <v>-0.47</v>
       </c>
       <c r="AC4">
-        <v>30.73</v>
+        <v>53.92</v>
       </c>
       <c r="AD4">
-        <v>18.22</v>
+        <v>34.25</v>
       </c>
       <c r="AE4">
-        <v>9.199999999999999</v>
+        <v>9.210000000000001</v>
       </c>
       <c r="AF4">
-        <v>-38.62</v>
+        <v>-24.33</v>
       </c>
       <c r="AG4">
-        <v>340.43</v>
+        <v>337.12</v>
       </c>
       <c r="AH4">
-        <v>286.44</v>
+        <v>286.52</v>
       </c>
       <c r="AI4">
         <v>322.52</v>
@@ -1268,7 +1252,7 @@
         <v>47</v>
       </c>
       <c r="AK4">
-        <v>53.57</v>
+        <v>52.4</v>
       </c>
     </row>
     <row r="5" spans="1:37">
@@ -1279,10 +1263,10 @@
         <v>44</v>
       </c>
       <c r="C5">
-        <v>1719.9</v>
+        <v>1755.7</v>
       </c>
       <c r="D5">
-        <v>-0.85</v>
+        <v>2.08</v>
       </c>
       <c r="E5">
         <v>2176.6</v>
@@ -1291,46 +1275,46 @@
         <v>1631.8</v>
       </c>
       <c r="G5">
-        <v>-20.98</v>
+        <v>-19.34</v>
       </c>
       <c r="H5">
-        <v>5.4</v>
+        <v>7.59</v>
       </c>
       <c r="I5">
-        <v>-1.8</v>
+        <v>0.19</v>
       </c>
       <c r="J5">
-        <v>-10.75</v>
+        <v>-9.52</v>
       </c>
       <c r="K5">
-        <v>-9.859999999999999</v>
+        <v>-6.07</v>
       </c>
       <c r="L5">
-        <v>-15.38</v>
+        <v>-12.81</v>
       </c>
       <c r="M5">
-        <v>-1.11</v>
+        <v>-0.66</v>
       </c>
       <c r="N5">
         <v>29</v>
       </c>
       <c r="O5">
-        <v>41</v>
+        <v>46</v>
       </c>
       <c r="P5">
-        <v>1731.66</v>
+        <v>1732.32</v>
       </c>
       <c r="Q5">
-        <v>1786.92</v>
+        <v>1779.03</v>
       </c>
       <c r="R5">
-        <v>1921.02</v>
+        <v>1915.56</v>
       </c>
       <c r="S5">
-        <v>1875.5</v>
+        <v>1874.04</v>
       </c>
       <c r="T5">
-        <v>-8.300000000000001</v>
+        <v>-6.31</v>
       </c>
       <c r="U5" t="s">
         <v>45</v>
@@ -1345,34 +1329,34 @@
         <v>1</v>
       </c>
       <c r="Y5">
-        <v>31.03</v>
+        <v>39.81</v>
       </c>
       <c r="Z5">
-        <v>-55.23</v>
+        <v>-51.06</v>
       </c>
       <c r="AA5">
-        <v>-54.42</v>
+        <v>-53.75</v>
       </c>
       <c r="AB5">
-        <v>-0.82</v>
+        <v>2.68</v>
       </c>
       <c r="AC5">
-        <v>48.79</v>
+        <v>79.58</v>
       </c>
       <c r="AD5">
-        <v>43.06</v>
+        <v>57.39</v>
       </c>
       <c r="AE5">
-        <v>36.38</v>
+        <v>37.39</v>
       </c>
       <c r="AF5">
-        <v>-34.16</v>
+        <v>84.88</v>
       </c>
       <c r="AG5">
-        <v>1907.91</v>
+        <v>1884.9</v>
       </c>
       <c r="AH5">
-        <v>1665.93</v>
+        <v>1673.16</v>
       </c>
       <c r="AI5">
         <v>1825.61</v>
@@ -1381,7 +1365,7 @@
         <v>47</v>
       </c>
       <c r="AK5">
-        <v>64.47</v>
+        <v>60.96</v>
       </c>
     </row>
     <row r="6" spans="1:37">
@@ -1392,10 +1376,10 @@
         <v>44</v>
       </c>
       <c r="C6">
-        <v>10750</v>
+        <v>10808</v>
       </c>
       <c r="D6">
-        <v>-0.65</v>
+        <v>0.54</v>
       </c>
       <c r="E6">
         <v>13144</v>
@@ -1404,46 +1388,46 @@
         <v>8746</v>
       </c>
       <c r="G6">
-        <v>-18.21</v>
+        <v>-17.77</v>
       </c>
       <c r="H6">
-        <v>22.91</v>
+        <v>23.58</v>
       </c>
       <c r="I6">
-        <v>0.17</v>
+        <v>1.96</v>
       </c>
       <c r="J6">
-        <v>-2.96</v>
+        <v>-1.67</v>
       </c>
       <c r="K6">
-        <v>-0.02</v>
+        <v>3.07</v>
       </c>
       <c r="L6">
-        <v>-11.08</v>
+        <v>-10.63</v>
       </c>
       <c r="M6">
-        <v>19.04</v>
+        <v>19.24</v>
       </c>
       <c r="N6">
         <v>57</v>
       </c>
       <c r="O6">
-        <v>57</v>
+        <v>59</v>
       </c>
       <c r="P6">
-        <v>10686.4</v>
+        <v>10728</v>
       </c>
       <c r="Q6">
-        <v>10918.7</v>
+        <v>10902.4</v>
       </c>
       <c r="R6">
-        <v>11169.02</v>
+        <v>11158.32</v>
       </c>
       <c r="S6">
-        <v>10664</v>
+        <v>10661.64</v>
       </c>
       <c r="T6">
-        <v>0.8100000000000001</v>
+        <v>1.37</v>
       </c>
       <c r="U6" t="s">
         <v>45</v>
@@ -1458,34 +1442,34 @@
         <v>2</v>
       </c>
       <c r="Y6">
-        <v>45.41</v>
+        <v>47.07</v>
       </c>
       <c r="Z6">
-        <v>-127.47</v>
+        <v>-116.29</v>
       </c>
       <c r="AA6">
-        <v>-114.18</v>
+        <v>-114.6</v>
       </c>
       <c r="AB6">
-        <v>-13.29</v>
+        <v>-1.69</v>
       </c>
       <c r="AC6">
-        <v>32.4</v>
+        <v>44.03</v>
       </c>
       <c r="AD6">
-        <v>24.16</v>
+        <v>34.21</v>
       </c>
       <c r="AE6">
-        <v>256.02</v>
+        <v>255.87</v>
       </c>
       <c r="AF6">
-        <v>-38.37</v>
+        <v>-37.1</v>
       </c>
       <c r="AG6">
-        <v>11452.08</v>
+        <v>11427.94</v>
       </c>
       <c r="AH6">
-        <v>10385.32</v>
+        <v>10376.86</v>
       </c>
       <c r="AI6">
         <v>11368.55</v>
@@ -1494,7 +1478,7 @@
         <v>47</v>
       </c>
       <c r="AK6">
-        <v>29.17</v>
+        <v>27.84</v>
       </c>
     </row>
     <row r="7" spans="1:37">
@@ -1505,10 +1489,10 @@
         <v>44</v>
       </c>
       <c r="C7">
-        <v>957.25</v>
+        <v>982.75</v>
       </c>
       <c r="D7">
-        <v>-0.29</v>
+        <v>2.66</v>
       </c>
       <c r="E7">
         <v>1158.8</v>
@@ -1517,46 +1501,46 @@
         <v>801.55</v>
       </c>
       <c r="G7">
-        <v>-17.39</v>
+        <v>-15.19</v>
       </c>
       <c r="H7">
-        <v>19.42</v>
+        <v>22.61</v>
       </c>
       <c r="I7">
-        <v>-1.31</v>
+        <v>2.04</v>
       </c>
       <c r="J7">
-        <v>-7.89</v>
+        <v>-5.82</v>
       </c>
       <c r="K7">
-        <v>-6.39</v>
+        <v>-2.37</v>
       </c>
       <c r="L7">
-        <v>-5.83</v>
+        <v>-3.95</v>
       </c>
       <c r="M7">
-        <v>4.43</v>
+        <v>4.78</v>
       </c>
       <c r="N7">
         <v>43</v>
       </c>
       <c r="O7">
-        <v>54</v>
+        <v>58</v>
       </c>
       <c r="P7">
-        <v>960.03</v>
+        <v>963.96</v>
       </c>
       <c r="Q7">
-        <v>989.7</v>
+        <v>987.11</v>
       </c>
       <c r="R7">
-        <v>1048.51</v>
+        <v>1045.34</v>
       </c>
       <c r="S7">
-        <v>975.03</v>
+        <v>974.89</v>
       </c>
       <c r="T7">
-        <v>-1.82</v>
+        <v>0.8100000000000001</v>
       </c>
       <c r="U7" t="s">
         <v>45</v>
@@ -1568,37 +1552,37 @@
         <v>45</v>
       </c>
       <c r="X7">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="Y7">
-        <v>37.02</v>
+        <v>45.66</v>
       </c>
       <c r="Z7">
-        <v>-24.96</v>
+        <v>-22.3</v>
       </c>
       <c r="AA7">
-        <v>-23.77</v>
+        <v>-23.47</v>
       </c>
       <c r="AB7">
-        <v>-1.19</v>
+        <v>1.17</v>
       </c>
       <c r="AC7">
-        <v>28.44</v>
+        <v>47.14</v>
       </c>
       <c r="AD7">
-        <v>29.84</v>
+        <v>35.16</v>
       </c>
       <c r="AE7">
-        <v>24.42</v>
+        <v>25.56</v>
       </c>
       <c r="AF7">
-        <v>-30.26</v>
+        <v>7.47</v>
       </c>
       <c r="AG7">
-        <v>1051.16</v>
+        <v>1044.88</v>
       </c>
       <c r="AH7">
-        <v>928.24</v>
+        <v>929.35</v>
       </c>
       <c r="AI7">
         <v>1020.6</v>
@@ -1607,7 +1591,7 @@
         <v>47</v>
       </c>
       <c r="AK7">
-        <v>25.06</v>
+        <v>24.09</v>
       </c>
     </row>
     <row r="8" spans="1:37">
@@ -1618,10 +1602,10 @@
         <v>44</v>
       </c>
       <c r="C8">
-        <v>177.58</v>
+        <v>176.53</v>
       </c>
       <c r="D8">
-        <v>0.9</v>
+        <v>-0.59</v>
       </c>
       <c r="E8">
         <v>185.92</v>
@@ -1630,46 +1614,46 @@
         <v>115.96</v>
       </c>
       <c r="G8">
-        <v>-4.49</v>
+        <v>-5.05</v>
       </c>
       <c r="H8">
-        <v>53.14</v>
+        <v>52.23</v>
       </c>
       <c r="I8">
-        <v>-2.54</v>
+        <v>-2.77</v>
       </c>
       <c r="J8">
-        <v>27.12</v>
+        <v>23.82</v>
       </c>
       <c r="K8">
-        <v>30.72</v>
+        <v>29.12</v>
       </c>
       <c r="L8">
-        <v>30.71</v>
+        <v>33.12</v>
       </c>
       <c r="M8">
-        <v>5.16</v>
+        <v>5.35</v>
       </c>
       <c r="N8">
         <v>85</v>
       </c>
       <c r="O8">
-        <v>90</v>
+        <v>88</v>
       </c>
       <c r="P8">
-        <v>179.07</v>
+        <v>178.06</v>
       </c>
       <c r="Q8">
-        <v>160.48</v>
+        <v>162.34</v>
       </c>
       <c r="R8">
-        <v>146.89</v>
+        <v>147.59</v>
       </c>
       <c r="S8">
-        <v>136.55</v>
+        <v>136.77</v>
       </c>
       <c r="T8">
-        <v>30.05</v>
+        <v>29.07</v>
       </c>
       <c r="U8" t="s">
         <v>46</v>
@@ -1684,34 +1668,34 @@
         <v>3</v>
       </c>
       <c r="Y8">
-        <v>65.70999999999999</v>
+        <v>64.45999999999999</v>
       </c>
       <c r="Z8">
-        <v>10.85</v>
+        <v>10.41</v>
       </c>
       <c r="AA8">
-        <v>9.710000000000001</v>
+        <v>9.85</v>
       </c>
       <c r="AB8">
-        <v>1.14</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="AC8">
-        <v>40.21</v>
+        <v>25.35</v>
       </c>
       <c r="AD8">
-        <v>56.95</v>
+        <v>41.75</v>
       </c>
       <c r="AE8">
-        <v>8.460000000000001</v>
+        <v>8.390000000000001</v>
       </c>
       <c r="AF8">
-        <v>-64.44</v>
+        <v>-56.03</v>
       </c>
       <c r="AG8">
-        <v>199.38</v>
+        <v>200.54</v>
       </c>
       <c r="AH8">
-        <v>121.59</v>
+        <v>124.13</v>
       </c>
       <c r="AI8">
         <v>159.98</v>
@@ -1720,7 +1704,7 @@
         <v>48</v>
       </c>
       <c r="AK8">
-        <v>50.05</v>
+        <v>46.57</v>
       </c>
     </row>
   </sheetData>
@@ -1861,7 +1845,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:F63"/>
+  <dimension ref="A1:F62"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="16.7109375" customWidth="1"/>
@@ -1901,7 +1885,7 @@
     </row>
     <row r="3" spans="1:6">
       <c r="A3" s="4" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="B3" s="4" t="s">
         <v>55</v>
@@ -1919,1008 +1903,988 @@
         <v>59</v>
       </c>
     </row>
-    <row r="4" spans="1:6">
-      <c r="A4" s="5" t="s">
+    <row r="5" spans="1:6">
+      <c r="A5" s="2" t="s">
+        <v>60</v>
+      </c>
+      <c r="B5" s="2"/>
+      <c r="C5" s="2"/>
+      <c r="D5" s="2"/>
+      <c r="E5" s="2"/>
+    </row>
+    <row r="6" spans="1:6">
+      <c r="A6" s="3" t="s">
+        <v>0</v>
+      </c>
+      <c r="B6" s="3" t="s">
+        <v>61</v>
+      </c>
+      <c r="C6" s="3" t="s">
+        <v>62</v>
+      </c>
+      <c r="D6" s="3" t="s">
+        <v>63</v>
+      </c>
+      <c r="E6" s="3" t="s">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="7" spans="1:6">
+      <c r="A7" s="5" t="s">
+        <v>37</v>
+      </c>
+      <c r="B7" s="5" t="s">
+        <v>9</v>
+      </c>
+      <c r="C7" s="6">
+        <v>-14.89</v>
+      </c>
+      <c r="D7" s="6">
+        <v>-12.32</v>
+      </c>
+      <c r="E7" s="7">
+        <v>2.57</v>
+      </c>
+    </row>
+    <row r="8" spans="1:6">
+      <c r="A8" s="5" t="s">
         <v>38</v>
       </c>
-      <c r="B4" s="5" t="s">
-        <v>60</v>
-      </c>
-      <c r="C4" s="5" t="s">
-        <v>61</v>
-      </c>
-      <c r="D4" s="5" t="s">
-        <v>62</v>
-      </c>
-      <c r="E4" s="5" t="s">
-        <v>63</v>
-      </c>
-      <c r="F4" s="5" t="s">
-        <v>64</v>
-      </c>
-    </row>
-    <row r="6" spans="1:6">
-      <c r="A6" s="2" t="s">
-        <v>65</v>
-      </c>
-      <c r="B6" s="2"/>
-      <c r="C6" s="2"/>
-      <c r="D6" s="2"/>
-      <c r="E6" s="2"/>
-    </row>
-    <row r="7" spans="1:6">
-      <c r="A7" s="3" t="s">
-        <v>0</v>
-      </c>
-      <c r="B7" s="3" t="s">
-        <v>66</v>
-      </c>
-      <c r="C7" s="3" t="s">
-        <v>67</v>
-      </c>
-      <c r="D7" s="3" t="s">
-        <v>68</v>
-      </c>
-      <c r="E7" s="3" t="s">
-        <v>69</v>
-      </c>
-    </row>
-    <row r="8" spans="1:6">
-      <c r="A8" s="6" t="s">
+      <c r="B8" s="5" t="s">
+        <v>9</v>
+      </c>
+      <c r="C8" s="6">
+        <v>-5.57</v>
+      </c>
+      <c r="D8" s="6">
+        <v>-3.09</v>
+      </c>
+      <c r="E8" s="7">
+        <v>2.48</v>
+      </c>
+    </row>
+    <row r="9" spans="1:6">
+      <c r="A9" s="5" t="s">
+        <v>39</v>
+      </c>
+      <c r="B9" s="5" t="s">
+        <v>9</v>
+      </c>
+      <c r="C9" s="6">
+        <v>-12.05</v>
+      </c>
+      <c r="D9" s="6">
+        <v>-10.27</v>
+      </c>
+      <c r="E9" s="7">
+        <v>1.78</v>
+      </c>
+    </row>
+    <row r="10" spans="1:6">
+      <c r="A10" s="5" t="s">
+        <v>40</v>
+      </c>
+      <c r="B10" s="5" t="s">
+        <v>9</v>
+      </c>
+      <c r="C10" s="6">
+        <v>-10.75</v>
+      </c>
+      <c r="D10" s="6">
+        <v>-9.52</v>
+      </c>
+      <c r="E10" s="7">
+        <v>1.23</v>
+      </c>
+    </row>
+    <row r="11" spans="1:6">
+      <c r="A11" s="5" t="s">
+        <v>41</v>
+      </c>
+      <c r="B11" s="5" t="s">
+        <v>9</v>
+      </c>
+      <c r="C11" s="6">
+        <v>-2.96</v>
+      </c>
+      <c r="D11" s="6">
+        <v>-1.67</v>
+      </c>
+      <c r="E11" s="7">
+        <v>1.29</v>
+      </c>
+    </row>
+    <row r="12" spans="1:6">
+      <c r="A12" s="5" t="s">
+        <v>42</v>
+      </c>
+      <c r="B12" s="5" t="s">
+        <v>9</v>
+      </c>
+      <c r="C12" s="6">
+        <v>-7.89</v>
+      </c>
+      <c r="D12" s="6">
+        <v>-5.82</v>
+      </c>
+      <c r="E12" s="7">
+        <v>2.07</v>
+      </c>
+    </row>
+    <row r="13" spans="1:6">
+      <c r="A13" s="5" t="s">
+        <v>43</v>
+      </c>
+      <c r="B13" s="5" t="s">
+        <v>9</v>
+      </c>
+      <c r="C13" s="6">
+        <v>27.12</v>
+      </c>
+      <c r="D13" s="6">
+        <v>23.82</v>
+      </c>
+      <c r="E13" s="8">
+        <v>-3.3</v>
+      </c>
+    </row>
+    <row r="14" spans="1:6">
+      <c r="A14" s="5" t="s">
         <v>37</v>
       </c>
-      <c r="B8" s="6" t="s">
-        <v>9</v>
-      </c>
-      <c r="C8" s="7">
-        <v>-17.69</v>
-      </c>
-      <c r="D8" s="7">
-        <v>-14.89</v>
-      </c>
-      <c r="E8" s="8">
-        <v>2.8</v>
-      </c>
-    </row>
-    <row r="9" spans="1:6">
-      <c r="A9" s="6" t="s">
+      <c r="B14" s="5" t="s">
+        <v>8</v>
+      </c>
+      <c r="C14" s="6">
+        <v>0.1</v>
+      </c>
+      <c r="D14" s="6">
+        <v>3</v>
+      </c>
+      <c r="E14" s="7">
+        <v>2.9</v>
+      </c>
+    </row>
+    <row r="15" spans="1:6">
+      <c r="A15" s="5" t="s">
         <v>38</v>
       </c>
-      <c r="B9" s="6" t="s">
-        <v>9</v>
-      </c>
-      <c r="C9" s="7">
-        <v>-1.39</v>
-      </c>
-      <c r="D9" s="7">
-        <v>-5.57</v>
-      </c>
-      <c r="E9" s="9">
-        <v>-4.18</v>
-      </c>
-    </row>
-    <row r="10" spans="1:6">
-      <c r="A10" s="6" t="s">
+      <c r="B15" s="5" t="s">
+        <v>8</v>
+      </c>
+      <c r="C15" s="6">
+        <v>2.51</v>
+      </c>
+      <c r="D15" s="6">
+        <v>2.99</v>
+      </c>
+      <c r="E15" s="7">
+        <v>0.48</v>
+      </c>
+    </row>
+    <row r="16" spans="1:6">
+      <c r="A16" s="5" t="s">
         <v>39</v>
       </c>
-      <c r="B10" s="6" t="s">
-        <v>9</v>
-      </c>
-      <c r="C10" s="7">
-        <v>-12.34</v>
-      </c>
-      <c r="D10" s="7">
-        <v>-12.05</v>
-      </c>
-      <c r="E10" s="8">
-        <v>0.29</v>
-      </c>
-    </row>
-    <row r="11" spans="1:6">
-      <c r="A11" s="6" t="s">
+      <c r="B16" s="5" t="s">
+        <v>8</v>
+      </c>
+      <c r="C16" s="6">
+        <v>-0.13</v>
+      </c>
+      <c r="D16" s="6">
+        <v>0.93</v>
+      </c>
+      <c r="E16" s="7">
+        <v>1.06</v>
+      </c>
+    </row>
+    <row r="17" spans="1:5">
+      <c r="A17" s="5" t="s">
         <v>40</v>
       </c>
-      <c r="B11" s="6" t="s">
-        <v>9</v>
-      </c>
-      <c r="C11" s="7">
-        <v>-10.49</v>
-      </c>
-      <c r="D11" s="7">
-        <v>-10.75</v>
-      </c>
-      <c r="E11" s="9">
-        <v>-0.26</v>
-      </c>
-    </row>
-    <row r="12" spans="1:6">
-      <c r="A12" s="6" t="s">
+      <c r="B17" s="5" t="s">
+        <v>8</v>
+      </c>
+      <c r="C17" s="6">
+        <v>-1.8</v>
+      </c>
+      <c r="D17" s="6">
+        <v>0.19</v>
+      </c>
+      <c r="E17" s="7">
+        <v>1.99</v>
+      </c>
+    </row>
+    <row r="18" spans="1:5">
+      <c r="A18" s="5" t="s">
         <v>41</v>
       </c>
-      <c r="B12" s="6" t="s">
-        <v>9</v>
-      </c>
-      <c r="C12" s="7">
-        <v>-2.05</v>
-      </c>
-      <c r="D12" s="7">
-        <v>-2.96</v>
-      </c>
-      <c r="E12" s="9">
-        <v>-0.91</v>
-      </c>
-    </row>
-    <row r="13" spans="1:6">
-      <c r="A13" s="6" t="s">
+      <c r="B18" s="5" t="s">
+        <v>8</v>
+      </c>
+      <c r="C18" s="6">
+        <v>0.17</v>
+      </c>
+      <c r="D18" s="6">
+        <v>1.96</v>
+      </c>
+      <c r="E18" s="7">
+        <v>1.79</v>
+      </c>
+    </row>
+    <row r="19" spans="1:5">
+      <c r="A19" s="5" t="s">
         <v>42</v>
       </c>
-      <c r="B13" s="6" t="s">
-        <v>9</v>
-      </c>
-      <c r="C13" s="7">
-        <v>-8.93</v>
-      </c>
-      <c r="D13" s="7">
-        <v>-7.89</v>
-      </c>
-      <c r="E13" s="8">
+      <c r="B19" s="5" t="s">
+        <v>8</v>
+      </c>
+      <c r="C19" s="6">
+        <v>-1.31</v>
+      </c>
+      <c r="D19" s="6">
+        <v>2.04</v>
+      </c>
+      <c r="E19" s="7">
+        <v>3.35</v>
+      </c>
+    </row>
+    <row r="20" spans="1:5">
+      <c r="A20" s="5" t="s">
+        <v>43</v>
+      </c>
+      <c r="B20" s="5" t="s">
+        <v>8</v>
+      </c>
+      <c r="C20" s="6">
+        <v>-2.54</v>
+      </c>
+      <c r="D20" s="6">
+        <v>-2.77</v>
+      </c>
+      <c r="E20" s="8">
+        <v>-0.23</v>
+      </c>
+    </row>
+    <row r="21" spans="1:5">
+      <c r="A21" s="5" t="s">
+        <v>37</v>
+      </c>
+      <c r="B21" s="5" t="s">
+        <v>11</v>
+      </c>
+      <c r="C21" s="6">
+        <v>14.28</v>
+      </c>
+      <c r="D21" s="6">
+        <v>19.01</v>
+      </c>
+      <c r="E21" s="7">
+        <v>4.73</v>
+      </c>
+    </row>
+    <row r="22" spans="1:5">
+      <c r="A22" s="5" t="s">
+        <v>38</v>
+      </c>
+      <c r="B22" s="5" t="s">
+        <v>11</v>
+      </c>
+      <c r="C22" s="6">
+        <v>103.55</v>
+      </c>
+      <c r="D22" s="6">
+        <v>106.14</v>
+      </c>
+      <c r="E22" s="7">
+        <v>2.59</v>
+      </c>
+    </row>
+    <row r="23" spans="1:5">
+      <c r="A23" s="5" t="s">
+        <v>39</v>
+      </c>
+      <c r="B23" s="5" t="s">
+        <v>11</v>
+      </c>
+      <c r="C23" s="6">
+        <v>-44.37</v>
+      </c>
+      <c r="D23" s="6">
+        <v>-43.33</v>
+      </c>
+      <c r="E23" s="7">
         <v>1.04</v>
       </c>
     </row>
-    <row r="14" spans="1:6">
-      <c r="A14" s="6" t="s">
+    <row r="24" spans="1:5">
+      <c r="A24" s="5" t="s">
+        <v>40</v>
+      </c>
+      <c r="B24" s="5" t="s">
+        <v>11</v>
+      </c>
+      <c r="C24" s="6">
+        <v>-15.38</v>
+      </c>
+      <c r="D24" s="6">
+        <v>-12.81</v>
+      </c>
+      <c r="E24" s="7">
+        <v>2.57</v>
+      </c>
+    </row>
+    <row r="25" spans="1:5">
+      <c r="A25" s="5" t="s">
+        <v>41</v>
+      </c>
+      <c r="B25" s="5" t="s">
+        <v>11</v>
+      </c>
+      <c r="C25" s="6">
+        <v>-11.08</v>
+      </c>
+      <c r="D25" s="6">
+        <v>-10.63</v>
+      </c>
+      <c r="E25" s="7">
+        <v>0.45</v>
+      </c>
+    </row>
+    <row r="26" spans="1:5">
+      <c r="A26" s="5" t="s">
+        <v>42</v>
+      </c>
+      <c r="B26" s="5" t="s">
+        <v>11</v>
+      </c>
+      <c r="C26" s="6">
+        <v>-5.83</v>
+      </c>
+      <c r="D26" s="6">
+        <v>-3.95</v>
+      </c>
+      <c r="E26" s="7">
+        <v>1.88</v>
+      </c>
+    </row>
+    <row r="27" spans="1:5">
+      <c r="A27" s="5" t="s">
         <v>43</v>
       </c>
-      <c r="B14" s="6" t="s">
-        <v>9</v>
-      </c>
-      <c r="C14" s="7">
-        <v>27.84</v>
-      </c>
-      <c r="D14" s="7">
-        <v>27.12</v>
-      </c>
-      <c r="E14" s="9">
-        <v>-0.72</v>
-      </c>
-    </row>
-    <row r="15" spans="1:6">
-      <c r="A15" s="6" t="s">
+      <c r="B27" s="5" t="s">
+        <v>11</v>
+      </c>
+      <c r="C27" s="6">
+        <v>30.71</v>
+      </c>
+      <c r="D27" s="6">
+        <v>33.12</v>
+      </c>
+      <c r="E27" s="7">
+        <v>2.41</v>
+      </c>
+    </row>
+    <row r="28" spans="1:5">
+      <c r="A28" s="5" t="s">
         <v>37</v>
       </c>
-      <c r="B15" s="6" t="s">
-        <v>8</v>
-      </c>
-      <c r="C15" s="7">
-        <v>-2.66</v>
-      </c>
-      <c r="D15" s="7">
-        <v>0.1</v>
-      </c>
-      <c r="E15" s="8">
-        <v>2.76</v>
-      </c>
-    </row>
-    <row r="16" spans="1:6">
-      <c r="A16" s="6" t="s">
+      <c r="B28" s="5" t="s">
+        <v>10</v>
+      </c>
+      <c r="C28" s="6">
+        <v>-3.34</v>
+      </c>
+      <c r="D28" s="6">
+        <v>1.5</v>
+      </c>
+      <c r="E28" s="7">
+        <v>4.84</v>
+      </c>
+    </row>
+    <row r="29" spans="1:5">
+      <c r="A29" s="5" t="s">
         <v>38</v>
       </c>
-      <c r="B16" s="6" t="s">
-        <v>8</v>
-      </c>
-      <c r="C16" s="7">
-        <v>1.99</v>
-      </c>
-      <c r="D16" s="7">
-        <v>2.51</v>
-      </c>
-      <c r="E16" s="8">
-        <v>0.52</v>
-      </c>
-    </row>
-    <row r="17" spans="1:5">
-      <c r="A17" s="6" t="s">
+      <c r="B29" s="5" t="s">
+        <v>10</v>
+      </c>
+      <c r="C29" s="6">
+        <v>-25.44</v>
+      </c>
+      <c r="D29" s="6">
+        <v>-13.93</v>
+      </c>
+      <c r="E29" s="7">
+        <v>11.51</v>
+      </c>
+    </row>
+    <row r="30" spans="1:5">
+      <c r="A30" s="5" t="s">
         <v>39</v>
       </c>
-      <c r="B17" s="6" t="s">
-        <v>8</v>
-      </c>
-      <c r="C17" s="7">
-        <v>-0.6</v>
-      </c>
-      <c r="D17" s="7">
-        <v>-0.13</v>
-      </c>
-      <c r="E17" s="8">
-        <v>0.47</v>
-      </c>
-    </row>
-    <row r="18" spans="1:5">
-      <c r="A18" s="6" t="s">
+      <c r="B30" s="5" t="s">
+        <v>10</v>
+      </c>
+      <c r="C30" s="6">
+        <v>-11.2</v>
+      </c>
+      <c r="D30" s="6">
+        <v>-7.87</v>
+      </c>
+      <c r="E30" s="7">
+        <v>3.33</v>
+      </c>
+    </row>
+    <row r="31" spans="1:5">
+      <c r="A31" s="5" t="s">
         <v>40</v>
       </c>
-      <c r="B18" s="6" t="s">
-        <v>8</v>
-      </c>
-      <c r="C18" s="7">
-        <v>0.12</v>
-      </c>
-      <c r="D18" s="7">
-        <v>-1.8</v>
-      </c>
-      <c r="E18" s="9">
-        <v>-1.92</v>
-      </c>
-    </row>
-    <row r="19" spans="1:5">
-      <c r="A19" s="6" t="s">
+      <c r="B31" s="5" t="s">
+        <v>10</v>
+      </c>
+      <c r="C31" s="6">
+        <v>-9.859999999999999</v>
+      </c>
+      <c r="D31" s="6">
+        <v>-6.07</v>
+      </c>
+      <c r="E31" s="7">
+        <v>3.79</v>
+      </c>
+    </row>
+    <row r="32" spans="1:5">
+      <c r="A32" s="5" t="s">
         <v>41</v>
       </c>
-      <c r="B19" s="6" t="s">
-        <v>8</v>
-      </c>
-      <c r="C19" s="7">
-        <v>1.44</v>
-      </c>
-      <c r="D19" s="7">
-        <v>0.17</v>
-      </c>
-      <c r="E19" s="9">
-        <v>-1.27</v>
-      </c>
-    </row>
-    <row r="20" spans="1:5">
-      <c r="A20" s="6" t="s">
+      <c r="B32" s="5" t="s">
+        <v>10</v>
+      </c>
+      <c r="C32" s="6">
+        <v>-0.02</v>
+      </c>
+      <c r="D32" s="6">
+        <v>3.07</v>
+      </c>
+      <c r="E32" s="7">
+        <v>3.09</v>
+      </c>
+    </row>
+    <row r="33" spans="1:5">
+      <c r="A33" s="5" t="s">
         <v>42</v>
       </c>
-      <c r="B20" s="6" t="s">
-        <v>8</v>
-      </c>
-      <c r="C20" s="7">
-        <v>1.23</v>
-      </c>
-      <c r="D20" s="7">
-        <v>-1.31</v>
-      </c>
-      <c r="E20" s="9">
-        <v>-2.54</v>
-      </c>
-    </row>
-    <row r="21" spans="1:5">
-      <c r="A21" s="6" t="s">
+      <c r="B33" s="5" t="s">
+        <v>10</v>
+      </c>
+      <c r="C33" s="6">
+        <v>-6.39</v>
+      </c>
+      <c r="D33" s="6">
+        <v>-2.37</v>
+      </c>
+      <c r="E33" s="7">
+        <v>4.02</v>
+      </c>
+    </row>
+    <row r="34" spans="1:5">
+      <c r="A34" s="5" t="s">
         <v>43</v>
       </c>
-      <c r="B21" s="6" t="s">
-        <v>8</v>
-      </c>
-      <c r="C21" s="7">
-        <v>1.93</v>
-      </c>
-      <c r="D21" s="7">
-        <v>-2.54</v>
-      </c>
-      <c r="E21" s="9">
-        <v>-4.47</v>
-      </c>
-    </row>
-    <row r="22" spans="1:5">
-      <c r="A22" s="6" t="s">
+      <c r="B34" s="5" t="s">
+        <v>10</v>
+      </c>
+      <c r="C34" s="6">
+        <v>30.72</v>
+      </c>
+      <c r="D34" s="6">
+        <v>29.12</v>
+      </c>
+      <c r="E34" s="8">
+        <v>-1.6</v>
+      </c>
+    </row>
+    <row r="35" spans="1:5">
+      <c r="A35" s="5" t="s">
         <v>37</v>
       </c>
-      <c r="B22" s="6" t="s">
-        <v>11</v>
-      </c>
-      <c r="C22" s="7">
-        <v>12.78</v>
-      </c>
-      <c r="D22" s="7">
-        <v>14.28</v>
-      </c>
-      <c r="E22" s="8">
-        <v>1.5</v>
-      </c>
-    </row>
-    <row r="23" spans="1:5">
-      <c r="A23" s="6" t="s">
+      <c r="B35" s="5" t="s">
+        <v>6</v>
+      </c>
+      <c r="C35" s="6">
+        <v>-18.83</v>
+      </c>
+      <c r="D35" s="6">
+        <v>-16.53</v>
+      </c>
+      <c r="E35" s="7">
+        <v>2.3</v>
+      </c>
+    </row>
+    <row r="36" spans="1:5">
+      <c r="A36" s="5" t="s">
         <v>38</v>
       </c>
-      <c r="B23" s="6" t="s">
-        <v>11</v>
-      </c>
-      <c r="C23" s="7">
-        <v>108.96</v>
-      </c>
-      <c r="D23" s="7">
-        <v>103.55</v>
-      </c>
-      <c r="E23" s="9">
-        <v>-5.41</v>
-      </c>
-    </row>
-    <row r="24" spans="1:5">
-      <c r="A24" s="6" t="s">
+      <c r="B36" s="5" t="s">
+        <v>6</v>
+      </c>
+      <c r="C36" s="6">
+        <v>-26.53</v>
+      </c>
+      <c r="D36" s="6">
+        <v>-24.17</v>
+      </c>
+      <c r="E36" s="7">
+        <v>2.36</v>
+      </c>
+    </row>
+    <row r="37" spans="1:5">
+      <c r="A37" s="5" t="s">
         <v>39</v>
       </c>
-      <c r="B24" s="6" t="s">
-        <v>11</v>
-      </c>
-      <c r="C24" s="7">
-        <v>-45.06</v>
-      </c>
-      <c r="D24" s="7">
-        <v>-44.37</v>
-      </c>
-      <c r="E24" s="8">
-        <v>0.6899999999999999</v>
-      </c>
-    </row>
-    <row r="25" spans="1:5">
-      <c r="A25" s="6" t="s">
+      <c r="B37" s="5" t="s">
+        <v>6</v>
+      </c>
+      <c r="C37" s="6">
+        <v>-45.47</v>
+      </c>
+      <c r="D37" s="6">
+        <v>-44.7</v>
+      </c>
+      <c r="E37" s="7">
+        <v>0.77</v>
+      </c>
+    </row>
+    <row r="38" spans="1:5">
+      <c r="A38" s="5" t="s">
         <v>40</v>
       </c>
-      <c r="B25" s="6" t="s">
-        <v>11</v>
-      </c>
-      <c r="C25" s="7">
-        <v>-14.68</v>
-      </c>
-      <c r="D25" s="7">
-        <v>-15.38</v>
-      </c>
-      <c r="E25" s="9">
-        <v>-0.7</v>
-      </c>
-    </row>
-    <row r="26" spans="1:5">
-      <c r="A26" s="6" t="s">
+      <c r="B38" s="5" t="s">
+        <v>6</v>
+      </c>
+      <c r="C38" s="6">
+        <v>-20.98</v>
+      </c>
+      <c r="D38" s="6">
+        <v>-19.34</v>
+      </c>
+      <c r="E38" s="7">
+        <v>1.64</v>
+      </c>
+    </row>
+    <row r="39" spans="1:5">
+      <c r="A39" s="5" t="s">
         <v>41</v>
       </c>
-      <c r="B26" s="6" t="s">
-        <v>11</v>
-      </c>
-      <c r="C26" s="7">
-        <v>-8.32</v>
-      </c>
-      <c r="D26" s="7">
-        <v>-11.08</v>
-      </c>
-      <c r="E26" s="9">
-        <v>-2.76</v>
-      </c>
-    </row>
-    <row r="27" spans="1:5">
-      <c r="A27" s="6" t="s">
+      <c r="B39" s="5" t="s">
+        <v>6</v>
+      </c>
+      <c r="C39" s="6">
+        <v>-18.21</v>
+      </c>
+      <c r="D39" s="6">
+        <v>-17.77</v>
+      </c>
+      <c r="E39" s="7">
+        <v>0.44</v>
+      </c>
+    </row>
+    <row r="40" spans="1:5">
+      <c r="A40" s="5" t="s">
         <v>42</v>
       </c>
-      <c r="B27" s="6" t="s">
-        <v>11</v>
-      </c>
-      <c r="C27" s="7">
-        <v>-4.85</v>
-      </c>
-      <c r="D27" s="7">
-        <v>-5.83</v>
-      </c>
-      <c r="E27" s="9">
-        <v>-0.98</v>
-      </c>
-    </row>
-    <row r="28" spans="1:5">
-      <c r="A28" s="6" t="s">
+      <c r="B40" s="5" t="s">
+        <v>6</v>
+      </c>
+      <c r="C40" s="6">
+        <v>-17.39</v>
+      </c>
+      <c r="D40" s="6">
+        <v>-15.19</v>
+      </c>
+      <c r="E40" s="7">
+        <v>2.2</v>
+      </c>
+    </row>
+    <row r="41" spans="1:5">
+      <c r="A41" s="5" t="s">
         <v>43</v>
       </c>
-      <c r="B28" s="6" t="s">
-        <v>11</v>
-      </c>
-      <c r="C28" s="7">
-        <v>26.58</v>
-      </c>
-      <c r="D28" s="7">
-        <v>30.71</v>
-      </c>
-      <c r="E28" s="8">
-        <v>4.13</v>
-      </c>
-    </row>
-    <row r="29" spans="1:5">
-      <c r="A29" s="6" t="s">
+      <c r="B41" s="5" t="s">
+        <v>6</v>
+      </c>
+      <c r="C41" s="6">
+        <v>-4.49</v>
+      </c>
+      <c r="D41" s="6">
+        <v>-5.05</v>
+      </c>
+      <c r="E41" s="8">
+        <v>-0.5600000000000001</v>
+      </c>
+    </row>
+    <row r="42" spans="1:5">
+      <c r="A42" s="5" t="s">
         <v>37</v>
       </c>
-      <c r="B29" s="6" t="s">
-        <v>10</v>
-      </c>
-      <c r="C29" s="7">
-        <v>-3.72</v>
-      </c>
-      <c r="D29" s="7">
-        <v>-3.34</v>
-      </c>
-      <c r="E29" s="8">
-        <v>0.38</v>
-      </c>
-    </row>
-    <row r="30" spans="1:5">
-      <c r="A30" s="6" t="s">
+      <c r="B42" s="5" t="s">
+        <v>2</v>
+      </c>
+      <c r="C42" s="6">
+        <v>10034</v>
+      </c>
+      <c r="D42" s="6">
+        <v>10318</v>
+      </c>
+      <c r="E42" s="7">
+        <v>284</v>
+      </c>
+    </row>
+    <row r="43" spans="1:5">
+      <c r="A43" s="5" t="s">
         <v>38</v>
       </c>
-      <c r="B30" s="6" t="s">
-        <v>10</v>
-      </c>
-      <c r="C30" s="7">
-        <v>-24.36</v>
-      </c>
-      <c r="D30" s="7">
-        <v>-25.44</v>
-      </c>
-      <c r="E30" s="9">
-        <v>-1.08</v>
-      </c>
-    </row>
-    <row r="31" spans="1:5">
-      <c r="A31" s="6" t="s">
+      <c r="B43" s="5" t="s">
+        <v>2</v>
+      </c>
+      <c r="C43" s="6">
+        <v>492.4</v>
+      </c>
+      <c r="D43" s="6">
+        <v>508.25</v>
+      </c>
+      <c r="E43" s="7">
+        <v>15.85</v>
+      </c>
+    </row>
+    <row r="44" spans="1:5">
+      <c r="A44" s="5" t="s">
         <v>39</v>
       </c>
-      <c r="B31" s="6" t="s">
-        <v>10</v>
-      </c>
-      <c r="C31" s="7">
-        <v>-10</v>
-      </c>
-      <c r="D31" s="7">
-        <v>-11.2</v>
-      </c>
-      <c r="E31" s="9">
-        <v>-1.2</v>
-      </c>
-    </row>
-    <row r="32" spans="1:5">
-      <c r="A32" s="6" t="s">
+      <c r="B44" s="5" t="s">
+        <v>2</v>
+      </c>
+      <c r="C44" s="6">
+        <v>298.85</v>
+      </c>
+      <c r="D44" s="6">
+        <v>303.05</v>
+      </c>
+      <c r="E44" s="7">
+        <v>4.2</v>
+      </c>
+    </row>
+    <row r="45" spans="1:5">
+      <c r="A45" s="5" t="s">
         <v>40</v>
       </c>
-      <c r="B32" s="6" t="s">
-        <v>10</v>
-      </c>
-      <c r="C32" s="7">
-        <v>-9.460000000000001</v>
-      </c>
-      <c r="D32" s="7">
-        <v>-9.859999999999999</v>
-      </c>
-      <c r="E32" s="9">
-        <v>-0.4</v>
-      </c>
-    </row>
-    <row r="33" spans="1:5">
-      <c r="A33" s="6" t="s">
+      <c r="B45" s="5" t="s">
+        <v>2</v>
+      </c>
+      <c r="C45" s="6">
+        <v>1719.9</v>
+      </c>
+      <c r="D45" s="6">
+        <v>1755.7</v>
+      </c>
+      <c r="E45" s="7">
+        <v>35.8</v>
+      </c>
+    </row>
+    <row r="46" spans="1:5">
+      <c r="A46" s="5" t="s">
         <v>41</v>
       </c>
-      <c r="B33" s="6" t="s">
-        <v>10</v>
-      </c>
-      <c r="C33" s="7">
-        <v>1.56</v>
-      </c>
-      <c r="D33" s="7">
-        <v>-0.02</v>
-      </c>
-      <c r="E33" s="9">
-        <v>-1.58</v>
-      </c>
-    </row>
-    <row r="34" spans="1:5">
-      <c r="A34" s="6" t="s">
+      <c r="B46" s="5" t="s">
+        <v>2</v>
+      </c>
+      <c r="C46" s="6">
+        <v>10750</v>
+      </c>
+      <c r="D46" s="6">
+        <v>10808</v>
+      </c>
+      <c r="E46" s="7">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="47" spans="1:5">
+      <c r="A47" s="5" t="s">
         <v>42</v>
       </c>
-      <c r="B34" s="6" t="s">
-        <v>10</v>
-      </c>
-      <c r="C34" s="7">
-        <v>-5.93</v>
-      </c>
-      <c r="D34" s="7">
-        <v>-6.39</v>
-      </c>
-      <c r="E34" s="9">
-        <v>-0.46</v>
-      </c>
-    </row>
-    <row r="35" spans="1:5">
-      <c r="A35" s="6" t="s">
+      <c r="B47" s="5" t="s">
+        <v>2</v>
+      </c>
+      <c r="C47" s="6">
+        <v>957.25</v>
+      </c>
+      <c r="D47" s="6">
+        <v>982.75</v>
+      </c>
+      <c r="E47" s="7">
+        <v>25.5</v>
+      </c>
+    </row>
+    <row r="48" spans="1:5">
+      <c r="A48" s="5" t="s">
         <v>43</v>
       </c>
-      <c r="B35" s="6" t="s">
-        <v>10</v>
-      </c>
-      <c r="C35" s="7">
-        <v>32.44</v>
-      </c>
-      <c r="D35" s="7">
-        <v>30.72</v>
-      </c>
-      <c r="E35" s="9">
-        <v>-1.72</v>
-      </c>
-    </row>
-    <row r="36" spans="1:5">
-      <c r="A36" s="6" t="s">
+      <c r="B48" s="5" t="s">
+        <v>2</v>
+      </c>
+      <c r="C48" s="6">
+        <v>177.58</v>
+      </c>
+      <c r="D48" s="6">
+        <v>176.53</v>
+      </c>
+      <c r="E48" s="8">
+        <v>-1.05</v>
+      </c>
+    </row>
+    <row r="49" spans="1:5">
+      <c r="A49" s="5" t="s">
         <v>37</v>
       </c>
-      <c r="B36" s="6" t="s">
-        <v>6</v>
-      </c>
-      <c r="C36" s="7">
-        <v>-20.9</v>
-      </c>
-      <c r="D36" s="7">
-        <v>-18.83</v>
-      </c>
-      <c r="E36" s="8">
-        <v>2.07</v>
-      </c>
-    </row>
-    <row r="37" spans="1:5">
-      <c r="A37" s="6" t="s">
+      <c r="B49" s="5" t="s">
+        <v>24</v>
+      </c>
+      <c r="C49" s="6">
+        <v>31.77</v>
+      </c>
+      <c r="D49" s="6">
+        <v>39.8</v>
+      </c>
+      <c r="E49" s="7">
+        <v>8.029999999999999</v>
+      </c>
+    </row>
+    <row r="50" spans="1:5">
+      <c r="A50" s="5" t="s">
         <v>38</v>
       </c>
-      <c r="B37" s="6" t="s">
-        <v>6</v>
-      </c>
-      <c r="C37" s="7">
-        <v>-24.36</v>
-      </c>
-      <c r="D37" s="7">
-        <v>-26.53</v>
-      </c>
-      <c r="E37" s="9">
-        <v>-2.17</v>
-      </c>
-    </row>
-    <row r="38" spans="1:5">
-      <c r="A38" s="6" t="s">
+      <c r="B50" s="5" t="s">
+        <v>24</v>
+      </c>
+      <c r="C50" s="6">
+        <v>47.42</v>
+      </c>
+      <c r="D50" s="6">
+        <v>53.14</v>
+      </c>
+      <c r="E50" s="7">
+        <v>5.72</v>
+      </c>
+    </row>
+    <row r="51" spans="1:5">
+      <c r="A51" s="5" t="s">
         <v>39</v>
       </c>
-      <c r="B38" s="6" t="s">
-        <v>6</v>
-      </c>
-      <c r="C38" s="7">
-        <v>-45.62</v>
-      </c>
-      <c r="D38" s="7">
-        <v>-45.47</v>
-      </c>
-      <c r="E38" s="8">
-        <v>0.15</v>
-      </c>
-    </row>
-    <row r="39" spans="1:5">
-      <c r="A39" s="6" t="s">
+      <c r="B51" s="5" t="s">
+        <v>24</v>
+      </c>
+      <c r="C51" s="6">
+        <v>35.1</v>
+      </c>
+      <c r="D51" s="6">
+        <v>39.64</v>
+      </c>
+      <c r="E51" s="7">
+        <v>4.54</v>
+      </c>
+    </row>
+    <row r="52" spans="1:5">
+      <c r="A52" s="5" t="s">
         <v>40</v>
       </c>
-      <c r="B39" s="6" t="s">
-        <v>6</v>
-      </c>
-      <c r="C39" s="7">
-        <v>-20.3</v>
-      </c>
-      <c r="D39" s="7">
-        <v>-20.98</v>
-      </c>
-      <c r="E39" s="9">
-        <v>-0.68</v>
-      </c>
-    </row>
-    <row r="40" spans="1:5">
-      <c r="A40" s="6" t="s">
+      <c r="B52" s="5" t="s">
+        <v>24</v>
+      </c>
+      <c r="C52" s="6">
+        <v>31.03</v>
+      </c>
+      <c r="D52" s="6">
+        <v>39.81</v>
+      </c>
+      <c r="E52" s="7">
+        <v>8.779999999999999</v>
+      </c>
+    </row>
+    <row r="53" spans="1:5">
+      <c r="A53" s="5" t="s">
         <v>41</v>
       </c>
-      <c r="B40" s="6" t="s">
-        <v>6</v>
-      </c>
-      <c r="C40" s="7">
-        <v>-17.68</v>
-      </c>
-      <c r="D40" s="7">
-        <v>-18.21</v>
-      </c>
-      <c r="E40" s="9">
-        <v>-0.53</v>
-      </c>
-    </row>
-    <row r="41" spans="1:5">
-      <c r="A41" s="6" t="s">
+      <c r="B53" s="5" t="s">
+        <v>24</v>
+      </c>
+      <c r="C53" s="6">
+        <v>45.41</v>
+      </c>
+      <c r="D53" s="6">
+        <v>47.07</v>
+      </c>
+      <c r="E53" s="7">
+        <v>1.66</v>
+      </c>
+    </row>
+    <row r="54" spans="1:5">
+      <c r="A54" s="5" t="s">
         <v>42</v>
       </c>
-      <c r="B41" s="6" t="s">
-        <v>6</v>
-      </c>
-      <c r="C41" s="7">
-        <v>-17.16</v>
-      </c>
-      <c r="D41" s="7">
-        <v>-17.39</v>
-      </c>
-      <c r="E41" s="9">
-        <v>-0.23</v>
-      </c>
-    </row>
-    <row r="42" spans="1:5">
-      <c r="A42" s="6" t="s">
+      <c r="B54" s="5" t="s">
+        <v>24</v>
+      </c>
+      <c r="C54" s="6">
+        <v>37.02</v>
+      </c>
+      <c r="D54" s="6">
+        <v>45.66</v>
+      </c>
+      <c r="E54" s="7">
+        <v>8.640000000000001</v>
+      </c>
+    </row>
+    <row r="55" spans="1:5">
+      <c r="A55" s="5" t="s">
         <v>43</v>
       </c>
-      <c r="B42" s="6" t="s">
-        <v>6</v>
-      </c>
-      <c r="C42" s="7">
-        <v>-5.34</v>
-      </c>
-      <c r="D42" s="7">
-        <v>-4.49</v>
-      </c>
-      <c r="E42" s="8">
-        <v>0.85</v>
-      </c>
-    </row>
-    <row r="43" spans="1:5">
-      <c r="A43" s="6" t="s">
+      <c r="B55" s="5" t="s">
+        <v>24</v>
+      </c>
+      <c r="C55" s="6">
+        <v>65.70999999999999</v>
+      </c>
+      <c r="D55" s="6">
+        <v>64.45999999999999</v>
+      </c>
+      <c r="E55" s="8">
+        <v>-1.25</v>
+      </c>
+    </row>
+    <row r="56" spans="1:5">
+      <c r="A56" s="5" t="s">
         <v>37</v>
       </c>
-      <c r="B43" s="6" t="s">
-        <v>2</v>
-      </c>
-      <c r="C43" s="7">
-        <v>9778</v>
-      </c>
-      <c r="D43" s="7">
-        <v>10034</v>
-      </c>
-      <c r="E43" s="8">
-        <v>256</v>
-      </c>
-    </row>
-    <row r="44" spans="1:5">
-      <c r="A44" s="6" t="s">
+      <c r="B56" s="5" t="s">
+        <v>31</v>
+      </c>
+      <c r="C56" s="6">
+        <v>9.17</v>
+      </c>
+      <c r="D56" s="6">
+        <v>14.9</v>
+      </c>
+      <c r="E56" s="7">
+        <v>5.73</v>
+      </c>
+    </row>
+    <row r="57" spans="1:5">
+      <c r="A57" s="5" t="s">
         <v>38</v>
       </c>
-      <c r="B44" s="6" t="s">
-        <v>2</v>
-      </c>
-      <c r="C44" s="7">
-        <v>506.95</v>
-      </c>
-      <c r="D44" s="7">
-        <v>492.4</v>
-      </c>
-      <c r="E44" s="9">
-        <v>-14.55</v>
-      </c>
-    </row>
-    <row r="45" spans="1:5">
-      <c r="A45" s="6" t="s">
+      <c r="B57" s="5" t="s">
+        <v>31</v>
+      </c>
+      <c r="C57" s="6">
+        <v>-41.08</v>
+      </c>
+      <c r="D57" s="6">
+        <v>-3.22</v>
+      </c>
+      <c r="E57" s="7">
+        <v>37.86</v>
+      </c>
+    </row>
+    <row r="58" spans="1:5">
+      <c r="A58" s="5" t="s">
         <v>39</v>
       </c>
-      <c r="B45" s="6" t="s">
-        <v>2</v>
-      </c>
-      <c r="C45" s="7">
-        <v>298</v>
-      </c>
-      <c r="D45" s="7">
-        <v>298.85</v>
-      </c>
-      <c r="E45" s="8">
-        <v>0.85</v>
-      </c>
-    </row>
-    <row r="46" spans="1:5">
-      <c r="A46" s="6" t="s">
+      <c r="B58" s="5" t="s">
+        <v>31</v>
+      </c>
+      <c r="C58" s="6">
+        <v>-38.62</v>
+      </c>
+      <c r="D58" s="6">
+        <v>-24.33</v>
+      </c>
+      <c r="E58" s="7">
+        <v>14.29</v>
+      </c>
+    </row>
+    <row r="59" spans="1:5">
+      <c r="A59" s="5" t="s">
         <v>40</v>
       </c>
-      <c r="B46" s="6" t="s">
-        <v>2</v>
-      </c>
-      <c r="C46" s="7">
-        <v>1734.7</v>
-      </c>
-      <c r="D46" s="7">
-        <v>1719.9</v>
-      </c>
-      <c r="E46" s="9">
-        <v>-14.8</v>
-      </c>
-    </row>
-    <row r="47" spans="1:5">
-      <c r="A47" s="6" t="s">
+      <c r="B59" s="5" t="s">
+        <v>31</v>
+      </c>
+      <c r="C59" s="6">
+        <v>-34.16</v>
+      </c>
+      <c r="D59" s="6">
+        <v>84.88</v>
+      </c>
+      <c r="E59" s="7">
+        <v>119.04</v>
+      </c>
+    </row>
+    <row r="60" spans="1:5">
+      <c r="A60" s="5" t="s">
         <v>41</v>
       </c>
-      <c r="B47" s="6" t="s">
-        <v>2</v>
-      </c>
-      <c r="C47" s="7">
-        <v>10820</v>
-      </c>
-      <c r="D47" s="7">
-        <v>10750</v>
-      </c>
-      <c r="E47" s="9">
-        <v>-70</v>
-      </c>
-    </row>
-    <row r="48" spans="1:5">
-      <c r="A48" s="6" t="s">
+      <c r="B60" s="5" t="s">
+        <v>31</v>
+      </c>
+      <c r="C60" s="6">
+        <v>-38.37</v>
+      </c>
+      <c r="D60" s="6">
+        <v>-37.1</v>
+      </c>
+      <c r="E60" s="7">
+        <v>1.27</v>
+      </c>
+    </row>
+    <row r="61" spans="1:5">
+      <c r="A61" s="5" t="s">
         <v>42</v>
       </c>
-      <c r="B48" s="6" t="s">
-        <v>2</v>
-      </c>
-      <c r="C48" s="7">
-        <v>960</v>
-      </c>
-      <c r="D48" s="7">
-        <v>957.25</v>
-      </c>
-      <c r="E48" s="9">
-        <v>-2.75</v>
-      </c>
-    </row>
-    <row r="49" spans="1:5">
-      <c r="A49" s="6" t="s">
+      <c r="B61" s="5" t="s">
+        <v>31</v>
+      </c>
+      <c r="C61" s="6">
+        <v>-30.26</v>
+      </c>
+      <c r="D61" s="6">
+        <v>7.47</v>
+      </c>
+      <c r="E61" s="7">
+        <v>37.73</v>
+      </c>
+    </row>
+    <row r="62" spans="1:5">
+      <c r="A62" s="5" t="s">
         <v>43</v>
       </c>
-      <c r="B49" s="6" t="s">
-        <v>2</v>
-      </c>
-      <c r="C49" s="7">
-        <v>175.99</v>
-      </c>
-      <c r="D49" s="7">
-        <v>177.58</v>
-      </c>
-      <c r="E49" s="8">
-        <v>1.59</v>
-      </c>
-    </row>
-    <row r="50" spans="1:5">
-      <c r="A50" s="6" t="s">
-        <v>37</v>
-      </c>
-      <c r="B50" s="6" t="s">
-        <v>24</v>
-      </c>
-      <c r="C50" s="7">
-        <v>23.2</v>
-      </c>
-      <c r="D50" s="7">
-        <v>31.77</v>
-      </c>
-      <c r="E50" s="8">
-        <v>8.57</v>
-      </c>
-    </row>
-    <row r="51" spans="1:5">
-      <c r="A51" s="6" t="s">
-        <v>38</v>
-      </c>
-      <c r="B51" s="6" t="s">
-        <v>24</v>
-      </c>
-      <c r="C51" s="7">
-        <v>52.93</v>
-      </c>
-      <c r="D51" s="7">
-        <v>47.42</v>
-      </c>
-      <c r="E51" s="9">
-        <v>-5.51</v>
-      </c>
-    </row>
-    <row r="52" spans="1:5">
-      <c r="A52" s="6" t="s">
-        <v>39</v>
-      </c>
-      <c r="B52" s="6" t="s">
-        <v>24</v>
-      </c>
-      <c r="C52" s="7">
-        <v>34.16</v>
-      </c>
-      <c r="D52" s="7">
-        <v>35.1</v>
-      </c>
-      <c r="E52" s="8">
-        <v>0.9399999999999999</v>
-      </c>
-    </row>
-    <row r="53" spans="1:5">
-      <c r="A53" s="6" t="s">
-        <v>40</v>
-      </c>
-      <c r="B53" s="6" t="s">
-        <v>24</v>
-      </c>
-      <c r="C53" s="7">
-        <v>32.87</v>
-      </c>
-      <c r="D53" s="7">
-        <v>31.03</v>
-      </c>
-      <c r="E53" s="9">
-        <v>-1.84</v>
-      </c>
-    </row>
-    <row r="54" spans="1:5">
-      <c r="A54" s="6" t="s">
-        <v>41</v>
-      </c>
-      <c r="B54" s="6" t="s">
-        <v>24</v>
-      </c>
-      <c r="C54" s="7">
-        <v>47.07</v>
-      </c>
-      <c r="D54" s="7">
-        <v>45.41</v>
-      </c>
-      <c r="E54" s="9">
-        <v>-1.66</v>
-      </c>
-    </row>
-    <row r="55" spans="1:5">
-      <c r="A55" s="6" t="s">
-        <v>42</v>
-      </c>
-      <c r="B55" s="6" t="s">
-        <v>24</v>
-      </c>
-      <c r="C55" s="7">
-        <v>37.62</v>
-      </c>
-      <c r="D55" s="7">
-        <v>37.02</v>
-      </c>
-      <c r="E55" s="9">
-        <v>-0.6</v>
-      </c>
-    </row>
-    <row r="56" spans="1:5">
-      <c r="A56" s="6" t="s">
-        <v>43</v>
-      </c>
-      <c r="B56" s="6" t="s">
-        <v>24</v>
-      </c>
-      <c r="C56" s="7">
-        <v>64.75</v>
-      </c>
-      <c r="D56" s="7">
-        <v>65.70999999999999</v>
-      </c>
-      <c r="E56" s="8">
-        <v>0.96</v>
-      </c>
-    </row>
-    <row r="57" spans="1:5">
-      <c r="A57" s="6" t="s">
-        <v>37</v>
-      </c>
-      <c r="B57" s="6" t="s">
+      <c r="B62" s="5" t="s">
         <v>31</v>
       </c>
-      <c r="C57" s="7">
-        <v>-12.39</v>
-      </c>
-      <c r="D57" s="7">
-        <v>9.17</v>
-      </c>
-      <c r="E57" s="8">
-        <v>21.56</v>
-      </c>
-    </row>
-    <row r="58" spans="1:5">
-      <c r="A58" s="6" t="s">
-        <v>38</v>
-      </c>
-      <c r="B58" s="6" t="s">
-        <v>31</v>
-      </c>
-      <c r="C58" s="7">
-        <v>-8.09</v>
-      </c>
-      <c r="D58" s="7">
-        <v>-41.08</v>
-      </c>
-      <c r="E58" s="9">
-        <v>-32.99</v>
-      </c>
-    </row>
-    <row r="59" spans="1:5">
-      <c r="A59" s="6" t="s">
-        <v>39</v>
-      </c>
-      <c r="B59" s="6" t="s">
-        <v>31</v>
-      </c>
-      <c r="C59" s="7">
-        <v>-23.71</v>
-      </c>
-      <c r="D59" s="7">
-        <v>-38.62</v>
-      </c>
-      <c r="E59" s="9">
-        <v>-14.91</v>
-      </c>
-    </row>
-    <row r="60" spans="1:5">
-      <c r="A60" s="6" t="s">
-        <v>40</v>
-      </c>
-      <c r="B60" s="6" t="s">
-        <v>31</v>
-      </c>
-      <c r="C60" s="7">
-        <v>-9.69</v>
-      </c>
-      <c r="D60" s="7">
-        <v>-34.16</v>
-      </c>
-      <c r="E60" s="9">
-        <v>-24.47</v>
-      </c>
-    </row>
-    <row r="61" spans="1:5">
-      <c r="A61" s="6" t="s">
-        <v>41</v>
-      </c>
-      <c r="B61" s="6" t="s">
-        <v>31</v>
-      </c>
-      <c r="C61" s="7">
-        <v>-72.03</v>
-      </c>
-      <c r="D61" s="7">
-        <v>-38.37</v>
-      </c>
-      <c r="E61" s="8">
-        <v>33.66</v>
-      </c>
-    </row>
-    <row r="62" spans="1:5">
-      <c r="A62" s="6" t="s">
-        <v>42</v>
-      </c>
-      <c r="B62" s="6" t="s">
-        <v>31</v>
-      </c>
-      <c r="C62" s="7">
-        <v>9.17</v>
-      </c>
-      <c r="D62" s="7">
-        <v>-30.26</v>
-      </c>
-      <c r="E62" s="9">
-        <v>-39.43</v>
-      </c>
-    </row>
-    <row r="63" spans="1:5">
-      <c r="A63" s="6" t="s">
-        <v>43</v>
-      </c>
-      <c r="B63" s="6" t="s">
-        <v>31</v>
-      </c>
-      <c r="C63" s="7">
-        <v>-58.21</v>
-      </c>
-      <c r="D63" s="7">
+      <c r="C62" s="6">
         <v>-64.44</v>
       </c>
-      <c r="E63" s="9">
-        <v>-6.23</v>
+      <c r="D62" s="6">
+        <v>-56.03</v>
+      </c>
+      <c r="E62" s="7">
+        <v>8.41</v>
       </c>
     </row>
   </sheetData>
   <mergeCells count="2">
     <mergeCell ref="A1:F1"/>
-    <mergeCell ref="A6:E6"/>
+    <mergeCell ref="A5:E5"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -2940,60 +2904,60 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:9" ht="28" customHeight="1">
-      <c r="A1" s="10" t="s">
+      <c r="A1" s="9" t="s">
         <v>1</v>
       </c>
-      <c r="B1" s="10" t="s">
+      <c r="B1" s="9" t="s">
+        <v>65</v>
+      </c>
+      <c r="C1" s="9" t="s">
+        <v>66</v>
+      </c>
+      <c r="D1" s="9" t="s">
+        <v>67</v>
+      </c>
+      <c r="E1" s="9" t="s">
+        <v>68</v>
+      </c>
+      <c r="F1" s="9" t="s">
+        <v>69</v>
+      </c>
+      <c r="G1" s="9" t="s">
         <v>70</v>
       </c>
-      <c r="C1" s="10" t="s">
+      <c r="H1" s="9" t="s">
         <v>71</v>
       </c>
-      <c r="D1" s="10" t="s">
+      <c r="I1" s="9" t="s">
         <v>72</v>
       </c>
-      <c r="E1" s="10" t="s">
-        <v>73</v>
-      </c>
-      <c r="F1" s="10" t="s">
-        <v>74</v>
-      </c>
-      <c r="G1" s="10" t="s">
-        <v>75</v>
-      </c>
-      <c r="H1" s="10" t="s">
-        <v>76</v>
-      </c>
-      <c r="I1" s="10" t="s">
-        <v>77</v>
-      </c>
     </row>
     <row r="2" spans="1:9">
-      <c r="A2" s="11" t="s">
+      <c r="A2" s="10" t="s">
         <v>44</v>
       </c>
-      <c r="B2" s="12">
-        <v>48.8</v>
-      </c>
-      <c r="C2" s="13">
+      <c r="B2" s="11">
+        <v>60.8</v>
+      </c>
+      <c r="C2" s="12">
         <v>7</v>
       </c>
-      <c r="D2" s="12">
-        <v>41.9</v>
-      </c>
-      <c r="E2" s="12">
-        <v>40</v>
-      </c>
-      <c r="F2" s="12">
-        <v>-3.9</v>
-      </c>
-      <c r="G2" s="12">
-        <v>-3.6</v>
-      </c>
-      <c r="H2" s="12">
+      <c r="D2" s="11">
+        <v>47.1</v>
+      </c>
+      <c r="E2" s="11">
+        <v>70</v>
+      </c>
+      <c r="F2" s="11">
+        <v>-2.7</v>
+      </c>
+      <c r="G2" s="11">
+        <v>0.5</v>
+      </c>
+      <c r="H2" s="11">
         <v>57</v>
       </c>
-      <c r="I2" s="12">
+      <c r="I2" s="11">
         <v>10</v>
       </c>
     </row>
@@ -3095,49 +3059,49 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:7">
-      <c r="A1" s="14" t="s">
+      <c r="A1" s="13" t="s">
         <v>37</v>
       </c>
-      <c r="B1" s="14" t="s">
+      <c r="B1" s="13" t="s">
         <v>41</v>
       </c>
-      <c r="C1" s="14" t="s">
+      <c r="C1" s="13" t="s">
         <v>38</v>
       </c>
-      <c r="D1" s="14" t="s">
+      <c r="D1" s="13" t="s">
         <v>43</v>
       </c>
-      <c r="E1" s="14" t="s">
+      <c r="E1" s="13" t="s">
         <v>42</v>
       </c>
-      <c r="F1" s="14" t="s">
+      <c r="F1" s="13" t="s">
         <v>40</v>
       </c>
-      <c r="G1" s="14" t="s">
+      <c r="G1" s="13" t="s">
         <v>39</v>
       </c>
     </row>
     <row r="2" spans="1:7">
-      <c r="A2" s="15">
-        <v>0.231</v>
-      </c>
-      <c r="B2" s="15">
-        <v>0.1904</v>
-      </c>
-      <c r="C2" s="15">
-        <v>0.1567</v>
-      </c>
-      <c r="D2" s="15">
-        <v>0.0516</v>
-      </c>
-      <c r="E2" s="15">
-        <v>0.0443</v>
-      </c>
-      <c r="F2" s="15">
-        <v>-0.0111</v>
-      </c>
-      <c r="G2" s="15">
-        <v>-0.2356</v>
+      <c r="A2" s="14">
+        <v>0.2386</v>
+      </c>
+      <c r="B2" s="14">
+        <v>0.1924</v>
+      </c>
+      <c r="C2" s="14">
+        <v>0.1639</v>
+      </c>
+      <c r="D2" s="14">
+        <v>0.0535</v>
+      </c>
+      <c r="E2" s="14">
+        <v>0.0478</v>
+      </c>
+      <c r="F2" s="14">
+        <v>-0.0066</v>
+      </c>
+      <c r="G2" s="14">
+        <v>-0.2332</v>
       </c>
     </row>
   </sheetData>

--- a/BAJAJ_GROUP_Technical_Metrics.xlsx
+++ b/BAJAJ_GROUP_Technical_Metrics.xlsx
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="264" uniqueCount="73">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="253" uniqueCount="64">
   <si>
     <t>Symbol</t>
   </si>
@@ -172,34 +172,7 @@
     <t>▶  SIGNAL EVENTS (vs Previous Run)</t>
   </si>
   <si>
-    <t>Signal</t>
-  </si>
-  <si>
-    <t>Change</t>
-  </si>
-  <si>
-    <t>Direction</t>
-  </si>
-  <si>
-    <t>Prev Value</t>
-  </si>
-  <si>
-    <t>Curr Value</t>
-  </si>
-  <si>
-    <t>RSI Momentum</t>
-  </si>
-  <si>
-    <t>47.4 → 53.1</t>
-  </si>
-  <si>
-    <t>🟢 BULLISH</t>
-  </si>
-  <si>
-    <t>47.4</t>
-  </si>
-  <si>
-    <t>53.1</t>
+    <t>No signal events detected since last run.</t>
   </si>
   <si>
     <t>▶  NUMERIC METRIC CHANGES (vs Previous Run)</t>
@@ -401,15 +374,14 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="15">
+  <cellXfs count="14">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="2" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="3" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1"/>
     <xf numFmtId="165" fontId="4" fillId="5" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="165" fontId="5" fillId="6" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
@@ -924,10 +896,10 @@
         <v>44</v>
       </c>
       <c r="C2">
-        <v>10318</v>
+        <v>10250</v>
       </c>
       <c r="D2">
-        <v>2.83</v>
+        <v>-0.66</v>
       </c>
       <c r="E2">
         <v>12361</v>
@@ -936,46 +908,46 @@
         <v>8599.48</v>
       </c>
       <c r="G2">
-        <v>-16.53</v>
+        <v>-17.08</v>
       </c>
       <c r="H2">
-        <v>19.98</v>
+        <v>19.19</v>
       </c>
       <c r="I2">
-        <v>3</v>
+        <v>3.7</v>
       </c>
       <c r="J2">
-        <v>-12.32</v>
+        <v>-12.23</v>
       </c>
       <c r="K2">
-        <v>1.5</v>
+        <v>-0.71</v>
       </c>
       <c r="L2">
-        <v>19.01</v>
+        <v>17.98</v>
       </c>
       <c r="M2">
-        <v>23.86</v>
+        <v>23.71</v>
       </c>
       <c r="N2">
         <v>71</v>
       </c>
       <c r="O2">
-        <v>72</v>
+        <v>69</v>
       </c>
       <c r="P2">
-        <v>9930.200000000001</v>
+        <v>10003.4</v>
       </c>
       <c r="Q2">
-        <v>10754.45</v>
+        <v>10695.75</v>
       </c>
       <c r="R2">
-        <v>11379.68</v>
+        <v>11347.56</v>
       </c>
       <c r="S2">
-        <v>10178.12</v>
+        <v>10184.15</v>
       </c>
       <c r="T2">
-        <v>1.37</v>
+        <v>0.65</v>
       </c>
       <c r="U2" t="s">
         <v>45</v>
@@ -990,34 +962,34 @@
         <v>2</v>
       </c>
       <c r="Y2">
-        <v>39.8</v>
+        <v>38.63</v>
       </c>
       <c r="Z2">
-        <v>-437.73</v>
+        <v>-410.69</v>
       </c>
       <c r="AA2">
-        <v>-370.58</v>
+        <v>-378.6</v>
       </c>
       <c r="AB2">
-        <v>-67.15000000000001</v>
+        <v>-32.09</v>
       </c>
       <c r="AC2">
-        <v>54.49</v>
+        <v>78.14</v>
       </c>
       <c r="AD2">
-        <v>28.81</v>
+        <v>52.62</v>
       </c>
       <c r="AE2">
-        <v>269.58</v>
+        <v>264.97</v>
       </c>
       <c r="AF2">
-        <v>14.9</v>
+        <v>-22.12</v>
       </c>
       <c r="AG2">
-        <v>12149.96</v>
+        <v>12071.3</v>
       </c>
       <c r="AH2">
-        <v>9358.940000000001</v>
+        <v>9320.200000000001</v>
       </c>
       <c r="AI2">
         <v>10503.51</v>
@@ -1026,7 +998,7 @@
         <v>47</v>
       </c>
       <c r="AK2">
-        <v>67.72</v>
+        <v>60.98</v>
       </c>
     </row>
     <row r="3" spans="1:37">
@@ -1037,10 +1009,10 @@
         <v>44</v>
       </c>
       <c r="C3">
-        <v>508.25</v>
+        <v>520.05</v>
       </c>
       <c r="D3">
-        <v>3.22</v>
+        <v>2.32</v>
       </c>
       <c r="E3">
         <v>670.25</v>
@@ -1049,46 +1021,46 @@
         <v>247.45</v>
       </c>
       <c r="G3">
-        <v>-24.17</v>
+        <v>-22.41</v>
       </c>
       <c r="H3">
-        <v>105.4</v>
+        <v>110.16</v>
       </c>
       <c r="I3">
-        <v>2.99</v>
+        <v>7.67</v>
       </c>
       <c r="J3">
-        <v>-3.09</v>
+        <v>-0.09</v>
       </c>
       <c r="K3">
-        <v>-13.93</v>
+        <v>-8.51</v>
       </c>
       <c r="L3">
-        <v>106.14</v>
+        <v>109.99</v>
       </c>
       <c r="M3">
-        <v>16.39</v>
+        <v>16.88</v>
       </c>
       <c r="N3">
         <v>99</v>
       </c>
       <c r="O3">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="P3">
-        <v>495.95</v>
+        <v>503.36</v>
       </c>
       <c r="Q3">
-        <v>498.59</v>
+        <v>499.4</v>
       </c>
       <c r="R3">
-        <v>501.99</v>
+        <v>501.92</v>
       </c>
       <c r="S3">
-        <v>460.42</v>
+        <v>461.69</v>
       </c>
       <c r="T3">
-        <v>10.39</v>
+        <v>12.64</v>
       </c>
       <c r="U3" t="s">
         <v>45</v>
@@ -1103,34 +1075,34 @@
         <v>2</v>
       </c>
       <c r="Y3">
-        <v>53.14</v>
+        <v>56.9</v>
       </c>
       <c r="Z3">
-        <v>-2.51</v>
+        <v>-0.48</v>
       </c>
       <c r="AA3">
-        <v>-3.75</v>
+        <v>-3.1</v>
       </c>
       <c r="AB3">
-        <v>1.25</v>
+        <v>2.62</v>
       </c>
       <c r="AC3">
         <v>86.73</v>
       </c>
       <c r="AD3">
-        <v>71.72</v>
+        <v>81</v>
       </c>
       <c r="AE3">
-        <v>19.38</v>
+        <v>19.75</v>
       </c>
       <c r="AF3">
-        <v>-3.22</v>
+        <v>87.65000000000001</v>
       </c>
       <c r="AG3">
-        <v>519.5</v>
+        <v>522.33</v>
       </c>
       <c r="AH3">
-        <v>477.68</v>
+        <v>476.47</v>
       </c>
       <c r="AI3">
         <v>460.99</v>
@@ -1139,7 +1111,7 @@
         <v>48</v>
       </c>
       <c r="AK3">
-        <v>22.69</v>
+        <v>23.68</v>
       </c>
     </row>
     <row r="4" spans="1:37">
@@ -1150,10 +1122,10 @@
         <v>44</v>
       </c>
       <c r="C4">
-        <v>303.05</v>
+        <v>305.4</v>
       </c>
       <c r="D4">
-        <v>1.41</v>
+        <v>0.78</v>
       </c>
       <c r="E4">
         <v>548</v>
@@ -1162,25 +1134,25 @@
         <v>290.05</v>
       </c>
       <c r="G4">
-        <v>-44.7</v>
+        <v>-44.27</v>
       </c>
       <c r="H4">
-        <v>4.48</v>
+        <v>5.29</v>
       </c>
       <c r="I4">
-        <v>0.93</v>
+        <v>1.56</v>
       </c>
       <c r="J4">
-        <v>-10.27</v>
+        <v>-8.92</v>
       </c>
       <c r="K4">
-        <v>-7.87</v>
+        <v>-7.47</v>
       </c>
       <c r="L4">
-        <v>-43.33</v>
+        <v>-43.26</v>
       </c>
       <c r="M4">
-        <v>-23.32</v>
+        <v>-23.73</v>
       </c>
       <c r="N4">
         <v>15</v>
@@ -1189,19 +1161,19 @@
         <v>15</v>
       </c>
       <c r="P4">
-        <v>298.13</v>
+        <v>299.07</v>
       </c>
       <c r="Q4">
-        <v>311.82</v>
+        <v>310.67</v>
       </c>
       <c r="R4">
-        <v>332.62</v>
+        <v>331.98</v>
       </c>
       <c r="S4">
-        <v>361.65</v>
+        <v>360.75</v>
       </c>
       <c r="T4">
-        <v>-16.2</v>
+        <v>-15.34</v>
       </c>
       <c r="U4" t="s">
         <v>45</v>
@@ -1216,34 +1188,34 @@
         <v>0</v>
       </c>
       <c r="Y4">
-        <v>39.64</v>
+        <v>42.08</v>
       </c>
       <c r="Z4">
-        <v>-9.720000000000001</v>
+        <v>-8.92</v>
       </c>
       <c r="AA4">
-        <v>-9.25</v>
+        <v>-9.18</v>
       </c>
       <c r="AB4">
-        <v>-0.47</v>
+        <v>0.26</v>
       </c>
       <c r="AC4">
-        <v>53.92</v>
+        <v>72.62</v>
       </c>
       <c r="AD4">
-        <v>34.25</v>
+        <v>52.42</v>
       </c>
       <c r="AE4">
-        <v>9.210000000000001</v>
+        <v>9.050000000000001</v>
       </c>
       <c r="AF4">
-        <v>-24.33</v>
+        <v>-65.81999999999999</v>
       </c>
       <c r="AG4">
-        <v>337.12</v>
+        <v>334.86</v>
       </c>
       <c r="AH4">
-        <v>286.52</v>
+        <v>286.48</v>
       </c>
       <c r="AI4">
         <v>322.52</v>
@@ -1252,7 +1224,7 @@
         <v>47</v>
       </c>
       <c r="AK4">
-        <v>52.4</v>
+        <v>48.9</v>
       </c>
     </row>
     <row r="5" spans="1:37">
@@ -1263,10 +1235,10 @@
         <v>44</v>
       </c>
       <c r="C5">
-        <v>1755.7</v>
+        <v>1721.7</v>
       </c>
       <c r="D5">
-        <v>2.08</v>
+        <v>-1.94</v>
       </c>
       <c r="E5">
         <v>2176.6</v>
@@ -1275,46 +1247,46 @@
         <v>1631.8</v>
       </c>
       <c r="G5">
-        <v>-19.34</v>
+        <v>-20.9</v>
       </c>
       <c r="H5">
-        <v>7.59</v>
+        <v>5.51</v>
       </c>
       <c r="I5">
-        <v>0.19</v>
+        <v>-1.24</v>
       </c>
       <c r="J5">
-        <v>-9.52</v>
+        <v>-10.02</v>
       </c>
       <c r="K5">
-        <v>-6.07</v>
+        <v>-6.92</v>
       </c>
       <c r="L5">
-        <v>-12.81</v>
+        <v>-14.54</v>
       </c>
       <c r="M5">
-        <v>-0.66</v>
+        <v>-1.38</v>
       </c>
       <c r="N5">
         <v>29</v>
       </c>
       <c r="O5">
-        <v>46</v>
+        <v>42</v>
       </c>
       <c r="P5">
-        <v>1732.32</v>
+        <v>1728</v>
       </c>
       <c r="Q5">
-        <v>1779.03</v>
+        <v>1772.34</v>
       </c>
       <c r="R5">
-        <v>1915.56</v>
+        <v>1908.07</v>
       </c>
       <c r="S5">
-        <v>1874.04</v>
+        <v>1872.47</v>
       </c>
       <c r="T5">
-        <v>-6.31</v>
+        <v>-8.050000000000001</v>
       </c>
       <c r="U5" t="s">
         <v>45</v>
@@ -1329,34 +1301,34 @@
         <v>1</v>
       </c>
       <c r="Y5">
-        <v>39.81</v>
+        <v>35.23</v>
       </c>
       <c r="Z5">
-        <v>-51.06</v>
+        <v>-49.93</v>
       </c>
       <c r="AA5">
-        <v>-53.75</v>
+        <v>-52.98</v>
       </c>
       <c r="AB5">
-        <v>2.68</v>
+        <v>3.05</v>
       </c>
       <c r="AC5">
-        <v>79.58</v>
+        <v>76.78</v>
       </c>
       <c r="AD5">
-        <v>57.39</v>
+        <v>68.38</v>
       </c>
       <c r="AE5">
-        <v>37.39</v>
+        <v>38.29</v>
       </c>
       <c r="AF5">
-        <v>84.88</v>
+        <v>-1.12</v>
       </c>
       <c r="AG5">
-        <v>1884.9</v>
+        <v>1874.72</v>
       </c>
       <c r="AH5">
-        <v>1673.16</v>
+        <v>1669.96</v>
       </c>
       <c r="AI5">
         <v>1825.61</v>
@@ -1365,7 +1337,7 @@
         <v>47</v>
       </c>
       <c r="AK5">
-        <v>60.96</v>
+        <v>57.9</v>
       </c>
     </row>
     <row r="6" spans="1:37">
@@ -1376,10 +1348,10 @@
         <v>44</v>
       </c>
       <c r="C6">
-        <v>10808</v>
+        <v>10774</v>
       </c>
       <c r="D6">
-        <v>0.54</v>
+        <v>-0.31</v>
       </c>
       <c r="E6">
         <v>13144</v>
@@ -1388,46 +1360,46 @@
         <v>8746</v>
       </c>
       <c r="G6">
-        <v>-17.77</v>
+        <v>-18.03</v>
       </c>
       <c r="H6">
-        <v>23.58</v>
+        <v>23.19</v>
       </c>
       <c r="I6">
-        <v>1.96</v>
+        <v>1.05</v>
       </c>
       <c r="J6">
-        <v>-1.67</v>
+        <v>-3.23</v>
       </c>
       <c r="K6">
-        <v>3.07</v>
+        <v>2.31</v>
       </c>
       <c r="L6">
-        <v>-10.63</v>
+        <v>-9.529999999999999</v>
       </c>
       <c r="M6">
-        <v>19.24</v>
+        <v>19.1</v>
       </c>
       <c r="N6">
         <v>57</v>
       </c>
       <c r="O6">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="P6">
-        <v>10728</v>
+        <v>10750.4</v>
       </c>
       <c r="Q6">
-        <v>10902.4</v>
+        <v>10886.1</v>
       </c>
       <c r="R6">
-        <v>11158.32</v>
+        <v>11141.82</v>
       </c>
       <c r="S6">
-        <v>10661.64</v>
+        <v>10659.4</v>
       </c>
       <c r="T6">
-        <v>1.37</v>
+        <v>1.08</v>
       </c>
       <c r="U6" t="s">
         <v>45</v>
@@ -1442,34 +1414,34 @@
         <v>2</v>
       </c>
       <c r="Y6">
-        <v>47.07</v>
+        <v>46.18</v>
       </c>
       <c r="Z6">
-        <v>-116.29</v>
+        <v>-108.92</v>
       </c>
       <c r="AA6">
-        <v>-114.6</v>
+        <v>-113.47</v>
       </c>
       <c r="AB6">
-        <v>-1.69</v>
+        <v>4.55</v>
       </c>
       <c r="AC6">
-        <v>44.03</v>
+        <v>58.35</v>
       </c>
       <c r="AD6">
-        <v>34.21</v>
+        <v>44.93</v>
       </c>
       <c r="AE6">
-        <v>255.87</v>
+        <v>249.46</v>
       </c>
       <c r="AF6">
-        <v>-37.1</v>
+        <v>-35.35</v>
       </c>
       <c r="AG6">
-        <v>11427.94</v>
+        <v>11406.03</v>
       </c>
       <c r="AH6">
-        <v>10376.86</v>
+        <v>10366.17</v>
       </c>
       <c r="AI6">
         <v>11368.55</v>
@@ -1478,7 +1450,7 @@
         <v>47</v>
       </c>
       <c r="AK6">
-        <v>27.84</v>
+        <v>24.36</v>
       </c>
     </row>
     <row r="7" spans="1:37">
@@ -1489,10 +1461,10 @@
         <v>44</v>
       </c>
       <c r="C7">
-        <v>982.75</v>
+        <v>957</v>
       </c>
       <c r="D7">
-        <v>2.66</v>
+        <v>-2.62</v>
       </c>
       <c r="E7">
         <v>1158.8</v>
@@ -1501,46 +1473,46 @@
         <v>801.55</v>
       </c>
       <c r="G7">
-        <v>-15.19</v>
+        <v>-17.41</v>
       </c>
       <c r="H7">
-        <v>22.61</v>
+        <v>19.39</v>
       </c>
       <c r="I7">
-        <v>2.04</v>
+        <v>-0.71</v>
       </c>
       <c r="J7">
-        <v>-5.82</v>
+        <v>-7.49</v>
       </c>
       <c r="K7">
-        <v>-2.37</v>
+        <v>-6.3</v>
       </c>
       <c r="L7">
-        <v>-3.95</v>
+        <v>-6.55</v>
       </c>
       <c r="M7">
-        <v>4.78</v>
+        <v>4.4</v>
       </c>
       <c r="N7">
         <v>43</v>
       </c>
       <c r="O7">
-        <v>58</v>
+        <v>51</v>
       </c>
       <c r="P7">
-        <v>963.96</v>
+        <v>962.59</v>
       </c>
       <c r="Q7">
-        <v>987.11</v>
+        <v>984.5</v>
       </c>
       <c r="R7">
-        <v>1045.34</v>
+        <v>1041.42</v>
       </c>
       <c r="S7">
-        <v>974.89</v>
+        <v>974.62</v>
       </c>
       <c r="T7">
-        <v>0.8100000000000001</v>
+        <v>-1.81</v>
       </c>
       <c r="U7" t="s">
         <v>45</v>
@@ -1552,37 +1524,37 @@
         <v>45</v>
       </c>
       <c r="X7">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="Y7">
-        <v>45.66</v>
+        <v>39.73</v>
       </c>
       <c r="Z7">
-        <v>-22.3</v>
+        <v>-22.01</v>
       </c>
       <c r="AA7">
-        <v>-23.47</v>
+        <v>-23.18</v>
       </c>
       <c r="AB7">
         <v>1.17</v>
       </c>
       <c r="AC7">
-        <v>47.14</v>
+        <v>55.04</v>
       </c>
       <c r="AD7">
-        <v>35.16</v>
+        <v>43.54</v>
       </c>
       <c r="AE7">
-        <v>25.56</v>
+        <v>25.72</v>
       </c>
       <c r="AF7">
-        <v>7.47</v>
+        <v>-0.9399999999999999</v>
       </c>
       <c r="AG7">
-        <v>1044.88</v>
+        <v>1042.78</v>
       </c>
       <c r="AH7">
-        <v>929.35</v>
+        <v>926.23</v>
       </c>
       <c r="AI7">
         <v>1020.6</v>
@@ -1591,7 +1563,7 @@
         <v>47</v>
       </c>
       <c r="AK7">
-        <v>24.09</v>
+        <v>23.25</v>
       </c>
     </row>
     <row r="8" spans="1:37">
@@ -1602,10 +1574,10 @@
         <v>44</v>
       </c>
       <c r="C8">
-        <v>176.53</v>
+        <v>175.02</v>
       </c>
       <c r="D8">
-        <v>-0.59</v>
+        <v>-0.86</v>
       </c>
       <c r="E8">
         <v>185.92</v>
@@ -1614,25 +1586,25 @@
         <v>115.96</v>
       </c>
       <c r="G8">
-        <v>-5.05</v>
+        <v>-5.86</v>
       </c>
       <c r="H8">
-        <v>52.23</v>
+        <v>50.93</v>
       </c>
       <c r="I8">
-        <v>-2.77</v>
+        <v>-5.86</v>
       </c>
       <c r="J8">
-        <v>23.82</v>
+        <v>25.48</v>
       </c>
       <c r="K8">
-        <v>29.12</v>
+        <v>23.56</v>
       </c>
       <c r="L8">
-        <v>33.12</v>
+        <v>29.65</v>
       </c>
       <c r="M8">
-        <v>5.35</v>
+        <v>5.42</v>
       </c>
       <c r="N8">
         <v>85</v>
@@ -1641,19 +1613,19 @@
         <v>88</v>
       </c>
       <c r="P8">
-        <v>178.06</v>
+        <v>175.88</v>
       </c>
       <c r="Q8">
-        <v>162.34</v>
+        <v>164.31</v>
       </c>
       <c r="R8">
-        <v>147.59</v>
+        <v>148.22</v>
       </c>
       <c r="S8">
-        <v>136.77</v>
+        <v>136.97</v>
       </c>
       <c r="T8">
-        <v>29.07</v>
+        <v>27.78</v>
       </c>
       <c r="U8" t="s">
         <v>46</v>
@@ -1668,34 +1640,34 @@
         <v>3</v>
       </c>
       <c r="Y8">
-        <v>64.45999999999999</v>
+        <v>62.62</v>
       </c>
       <c r="Z8">
-        <v>10.41</v>
+        <v>9.83</v>
       </c>
       <c r="AA8">
         <v>9.85</v>
       </c>
       <c r="AB8">
-        <v>0.5600000000000001</v>
+        <v>-0.01</v>
       </c>
       <c r="AC8">
-        <v>25.35</v>
+        <v>9.93</v>
       </c>
       <c r="AD8">
-        <v>41.75</v>
+        <v>25.16</v>
       </c>
       <c r="AE8">
-        <v>8.390000000000001</v>
+        <v>8.08</v>
       </c>
       <c r="AF8">
-        <v>-56.03</v>
+        <v>-84.72</v>
       </c>
       <c r="AG8">
-        <v>200.54</v>
+        <v>200.73</v>
       </c>
       <c r="AH8">
-        <v>124.13</v>
+        <v>127.88</v>
       </c>
       <c r="AI8">
         <v>159.98</v>
@@ -1704,7 +1676,7 @@
         <v>48</v>
       </c>
       <c r="AK8">
-        <v>46.57</v>
+        <v>43.55</v>
       </c>
     </row>
   </sheetData>
@@ -1865,47 +1837,12 @@
     </row>
     <row r="2" spans="1:6">
       <c r="A2" s="3" t="s">
-        <v>0</v>
-      </c>
-      <c r="B2" s="3" t="s">
         <v>50</v>
-      </c>
-      <c r="C2" s="3" t="s">
-        <v>51</v>
-      </c>
-      <c r="D2" s="3" t="s">
-        <v>52</v>
-      </c>
-      <c r="E2" s="3" t="s">
-        <v>53</v>
-      </c>
-      <c r="F2" s="3" t="s">
-        <v>54</v>
-      </c>
-    </row>
-    <row r="3" spans="1:6">
-      <c r="A3" s="4" t="s">
-        <v>38</v>
-      </c>
-      <c r="B3" s="4" t="s">
-        <v>55</v>
-      </c>
-      <c r="C3" s="4" t="s">
-        <v>56</v>
-      </c>
-      <c r="D3" s="4" t="s">
-        <v>57</v>
-      </c>
-      <c r="E3" s="4" t="s">
-        <v>58</v>
-      </c>
-      <c r="F3" s="4" t="s">
-        <v>59</v>
       </c>
     </row>
     <row r="5" spans="1:6">
       <c r="A5" s="2" t="s">
-        <v>60</v>
+        <v>51</v>
       </c>
       <c r="B5" s="2"/>
       <c r="C5" s="2"/>
@@ -1913,972 +1850,972 @@
       <c r="E5" s="2"/>
     </row>
     <row r="6" spans="1:6">
-      <c r="A6" s="3" t="s">
+      <c r="A6" s="4" t="s">
         <v>0</v>
       </c>
-      <c r="B6" s="3" t="s">
-        <v>61</v>
-      </c>
-      <c r="C6" s="3" t="s">
-        <v>62</v>
-      </c>
-      <c r="D6" s="3" t="s">
-        <v>63</v>
-      </c>
-      <c r="E6" s="3" t="s">
-        <v>64</v>
+      <c r="B6" s="4" t="s">
+        <v>52</v>
+      </c>
+      <c r="C6" s="4" t="s">
+        <v>53</v>
+      </c>
+      <c r="D6" s="4" t="s">
+        <v>54</v>
+      </c>
+      <c r="E6" s="4" t="s">
+        <v>55</v>
       </c>
     </row>
     <row r="7" spans="1:6">
-      <c r="A7" s="5" t="s">
+      <c r="A7" s="3" t="s">
         <v>37</v>
       </c>
-      <c r="B7" s="5" t="s">
+      <c r="B7" s="3" t="s">
         <v>9</v>
       </c>
-      <c r="C7" s="6">
-        <v>-14.89</v>
-      </c>
-      <c r="D7" s="6">
+      <c r="C7" s="5">
         <v>-12.32</v>
       </c>
-      <c r="E7" s="7">
-        <v>2.57</v>
+      <c r="D7" s="5">
+        <v>-12.23</v>
+      </c>
+      <c r="E7" s="6">
+        <v>0.09</v>
       </c>
     </row>
     <row r="8" spans="1:6">
-      <c r="A8" s="5" t="s">
+      <c r="A8" s="3" t="s">
         <v>38</v>
       </c>
-      <c r="B8" s="5" t="s">
+      <c r="B8" s="3" t="s">
         <v>9</v>
       </c>
-      <c r="C8" s="6">
-        <v>-5.57</v>
-      </c>
-      <c r="D8" s="6">
+      <c r="C8" s="5">
         <v>-3.09</v>
       </c>
-      <c r="E8" s="7">
-        <v>2.48</v>
+      <c r="D8" s="5">
+        <v>-0.09</v>
+      </c>
+      <c r="E8" s="6">
+        <v>3</v>
       </c>
     </row>
     <row r="9" spans="1:6">
-      <c r="A9" s="5" t="s">
+      <c r="A9" s="3" t="s">
         <v>39</v>
       </c>
-      <c r="B9" s="5" t="s">
+      <c r="B9" s="3" t="s">
         <v>9</v>
       </c>
-      <c r="C9" s="6">
-        <v>-12.05</v>
-      </c>
-      <c r="D9" s="6">
+      <c r="C9" s="5">
         <v>-10.27</v>
       </c>
-      <c r="E9" s="7">
-        <v>1.78</v>
+      <c r="D9" s="5">
+        <v>-8.92</v>
+      </c>
+      <c r="E9" s="6">
+        <v>1.35</v>
       </c>
     </row>
     <row r="10" spans="1:6">
-      <c r="A10" s="5" t="s">
+      <c r="A10" s="3" t="s">
         <v>40</v>
       </c>
-      <c r="B10" s="5" t="s">
+      <c r="B10" s="3" t="s">
         <v>9</v>
       </c>
-      <c r="C10" s="6">
-        <v>-10.75</v>
-      </c>
-      <c r="D10" s="6">
+      <c r="C10" s="5">
         <v>-9.52</v>
       </c>
+      <c r="D10" s="5">
+        <v>-10.02</v>
+      </c>
       <c r="E10" s="7">
-        <v>1.23</v>
+        <v>-0.5</v>
       </c>
     </row>
     <row r="11" spans="1:6">
-      <c r="A11" s="5" t="s">
+      <c r="A11" s="3" t="s">
         <v>41</v>
       </c>
-      <c r="B11" s="5" t="s">
+      <c r="B11" s="3" t="s">
         <v>9</v>
       </c>
-      <c r="C11" s="6">
-        <v>-2.96</v>
-      </c>
-      <c r="D11" s="6">
+      <c r="C11" s="5">
         <v>-1.67</v>
       </c>
+      <c r="D11" s="5">
+        <v>-3.23</v>
+      </c>
       <c r="E11" s="7">
-        <v>1.29</v>
+        <v>-1.56</v>
       </c>
     </row>
     <row r="12" spans="1:6">
-      <c r="A12" s="5" t="s">
+      <c r="A12" s="3" t="s">
         <v>42</v>
       </c>
-      <c r="B12" s="5" t="s">
+      <c r="B12" s="3" t="s">
         <v>9</v>
       </c>
-      <c r="C12" s="6">
-        <v>-7.89</v>
-      </c>
-      <c r="D12" s="6">
+      <c r="C12" s="5">
         <v>-5.82</v>
       </c>
+      <c r="D12" s="5">
+        <v>-7.49</v>
+      </c>
       <c r="E12" s="7">
-        <v>2.07</v>
+        <v>-1.67</v>
       </c>
     </row>
     <row r="13" spans="1:6">
-      <c r="A13" s="5" t="s">
+      <c r="A13" s="3" t="s">
         <v>43</v>
       </c>
-      <c r="B13" s="5" t="s">
+      <c r="B13" s="3" t="s">
         <v>9</v>
       </c>
-      <c r="C13" s="6">
-        <v>27.12</v>
-      </c>
-      <c r="D13" s="6">
+      <c r="C13" s="5">
         <v>23.82</v>
       </c>
-      <c r="E13" s="8">
-        <v>-3.3</v>
+      <c r="D13" s="5">
+        <v>25.48</v>
+      </c>
+      <c r="E13" s="6">
+        <v>1.66</v>
       </c>
     </row>
     <row r="14" spans="1:6">
-      <c r="A14" s="5" t="s">
+      <c r="A14" s="3" t="s">
         <v>37</v>
       </c>
-      <c r="B14" s="5" t="s">
+      <c r="B14" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="C14" s="6">
-        <v>0.1</v>
-      </c>
-      <c r="D14" s="6">
+      <c r="C14" s="5">
         <v>3</v>
       </c>
-      <c r="E14" s="7">
-        <v>2.9</v>
+      <c r="D14" s="5">
+        <v>3.7</v>
+      </c>
+      <c r="E14" s="6">
+        <v>0.7</v>
       </c>
     </row>
     <row r="15" spans="1:6">
-      <c r="A15" s="5" t="s">
+      <c r="A15" s="3" t="s">
         <v>38</v>
       </c>
-      <c r="B15" s="5" t="s">
+      <c r="B15" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="C15" s="6">
-        <v>2.51</v>
-      </c>
-      <c r="D15" s="6">
+      <c r="C15" s="5">
         <v>2.99</v>
       </c>
-      <c r="E15" s="7">
-        <v>0.48</v>
+      <c r="D15" s="5">
+        <v>7.67</v>
+      </c>
+      <c r="E15" s="6">
+        <v>4.68</v>
       </c>
     </row>
     <row r="16" spans="1:6">
-      <c r="A16" s="5" t="s">
+      <c r="A16" s="3" t="s">
         <v>39</v>
       </c>
-      <c r="B16" s="5" t="s">
+      <c r="B16" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="C16" s="6">
-        <v>-0.13</v>
-      </c>
-      <c r="D16" s="6">
+      <c r="C16" s="5">
         <v>0.93</v>
       </c>
-      <c r="E16" s="7">
-        <v>1.06</v>
+      <c r="D16" s="5">
+        <v>1.56</v>
+      </c>
+      <c r="E16" s="6">
+        <v>0.63</v>
       </c>
     </row>
     <row r="17" spans="1:5">
-      <c r="A17" s="5" t="s">
+      <c r="A17" s="3" t="s">
         <v>40</v>
       </c>
-      <c r="B17" s="5" t="s">
+      <c r="B17" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="C17" s="6">
-        <v>-1.8</v>
-      </c>
-      <c r="D17" s="6">
+      <c r="C17" s="5">
         <v>0.19</v>
       </c>
+      <c r="D17" s="5">
+        <v>-1.24</v>
+      </c>
       <c r="E17" s="7">
-        <v>1.99</v>
+        <v>-1.43</v>
       </c>
     </row>
     <row r="18" spans="1:5">
-      <c r="A18" s="5" t="s">
+      <c r="A18" s="3" t="s">
         <v>41</v>
       </c>
-      <c r="B18" s="5" t="s">
+      <c r="B18" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="C18" s="6">
-        <v>0.17</v>
-      </c>
-      <c r="D18" s="6">
+      <c r="C18" s="5">
         <v>1.96</v>
       </c>
+      <c r="D18" s="5">
+        <v>1.05</v>
+      </c>
       <c r="E18" s="7">
-        <v>1.79</v>
+        <v>-0.91</v>
       </c>
     </row>
     <row r="19" spans="1:5">
-      <c r="A19" s="5" t="s">
+      <c r="A19" s="3" t="s">
         <v>42</v>
       </c>
-      <c r="B19" s="5" t="s">
+      <c r="B19" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="C19" s="6">
-        <v>-1.31</v>
-      </c>
-      <c r="D19" s="6">
+      <c r="C19" s="5">
         <v>2.04</v>
       </c>
+      <c r="D19" s="5">
+        <v>-0.71</v>
+      </c>
       <c r="E19" s="7">
-        <v>3.35</v>
+        <v>-2.75</v>
       </c>
     </row>
     <row r="20" spans="1:5">
-      <c r="A20" s="5" t="s">
+      <c r="A20" s="3" t="s">
         <v>43</v>
       </c>
-      <c r="B20" s="5" t="s">
+      <c r="B20" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="C20" s="6">
-        <v>-2.54</v>
-      </c>
-      <c r="D20" s="6">
+      <c r="C20" s="5">
         <v>-2.77</v>
       </c>
-      <c r="E20" s="8">
-        <v>-0.23</v>
+      <c r="D20" s="5">
+        <v>-5.86</v>
+      </c>
+      <c r="E20" s="7">
+        <v>-3.09</v>
       </c>
     </row>
     <row r="21" spans="1:5">
-      <c r="A21" s="5" t="s">
+      <c r="A21" s="3" t="s">
         <v>37</v>
       </c>
-      <c r="B21" s="5" t="s">
+      <c r="B21" s="3" t="s">
         <v>11</v>
       </c>
-      <c r="C21" s="6">
-        <v>14.28</v>
-      </c>
-      <c r="D21" s="6">
+      <c r="C21" s="5">
         <v>19.01</v>
       </c>
+      <c r="D21" s="5">
+        <v>17.98</v>
+      </c>
       <c r="E21" s="7">
-        <v>4.73</v>
+        <v>-1.03</v>
       </c>
     </row>
     <row r="22" spans="1:5">
-      <c r="A22" s="5" t="s">
+      <c r="A22" s="3" t="s">
         <v>38</v>
       </c>
-      <c r="B22" s="5" t="s">
+      <c r="B22" s="3" t="s">
         <v>11</v>
       </c>
-      <c r="C22" s="6">
-        <v>103.55</v>
-      </c>
-      <c r="D22" s="6">
+      <c r="C22" s="5">
         <v>106.14</v>
       </c>
-      <c r="E22" s="7">
-        <v>2.59</v>
+      <c r="D22" s="5">
+        <v>109.99</v>
+      </c>
+      <c r="E22" s="6">
+        <v>3.85</v>
       </c>
     </row>
     <row r="23" spans="1:5">
-      <c r="A23" s="5" t="s">
+      <c r="A23" s="3" t="s">
         <v>39</v>
       </c>
-      <c r="B23" s="5" t="s">
+      <c r="B23" s="3" t="s">
         <v>11</v>
       </c>
-      <c r="C23" s="6">
-        <v>-44.37</v>
-      </c>
-      <c r="D23" s="6">
+      <c r="C23" s="5">
         <v>-43.33</v>
       </c>
-      <c r="E23" s="7">
-        <v>1.04</v>
+      <c r="D23" s="5">
+        <v>-43.26</v>
+      </c>
+      <c r="E23" s="6">
+        <v>0.07000000000000001</v>
       </c>
     </row>
     <row r="24" spans="1:5">
-      <c r="A24" s="5" t="s">
+      <c r="A24" s="3" t="s">
         <v>40</v>
       </c>
-      <c r="B24" s="5" t="s">
+      <c r="B24" s="3" t="s">
         <v>11</v>
       </c>
-      <c r="C24" s="6">
-        <v>-15.38</v>
-      </c>
-      <c r="D24" s="6">
+      <c r="C24" s="5">
         <v>-12.81</v>
       </c>
+      <c r="D24" s="5">
+        <v>-14.54</v>
+      </c>
       <c r="E24" s="7">
-        <v>2.57</v>
+        <v>-1.73</v>
       </c>
     </row>
     <row r="25" spans="1:5">
-      <c r="A25" s="5" t="s">
+      <c r="A25" s="3" t="s">
         <v>41</v>
       </c>
-      <c r="B25" s="5" t="s">
+      <c r="B25" s="3" t="s">
         <v>11</v>
       </c>
-      <c r="C25" s="6">
-        <v>-11.08</v>
-      </c>
-      <c r="D25" s="6">
+      <c r="C25" s="5">
         <v>-10.63</v>
       </c>
-      <c r="E25" s="7">
-        <v>0.45</v>
+      <c r="D25" s="5">
+        <v>-9.529999999999999</v>
+      </c>
+      <c r="E25" s="6">
+        <v>1.1</v>
       </c>
     </row>
     <row r="26" spans="1:5">
-      <c r="A26" s="5" t="s">
+      <c r="A26" s="3" t="s">
         <v>42</v>
       </c>
-      <c r="B26" s="5" t="s">
+      <c r="B26" s="3" t="s">
         <v>11</v>
       </c>
-      <c r="C26" s="6">
-        <v>-5.83</v>
-      </c>
-      <c r="D26" s="6">
+      <c r="C26" s="5">
         <v>-3.95</v>
       </c>
+      <c r="D26" s="5">
+        <v>-6.55</v>
+      </c>
       <c r="E26" s="7">
-        <v>1.88</v>
+        <v>-2.6</v>
       </c>
     </row>
     <row r="27" spans="1:5">
-      <c r="A27" s="5" t="s">
+      <c r="A27" s="3" t="s">
         <v>43</v>
       </c>
-      <c r="B27" s="5" t="s">
+      <c r="B27" s="3" t="s">
         <v>11</v>
       </c>
-      <c r="C27" s="6">
-        <v>30.71</v>
-      </c>
-      <c r="D27" s="6">
+      <c r="C27" s="5">
         <v>33.12</v>
       </c>
+      <c r="D27" s="5">
+        <v>29.65</v>
+      </c>
       <c r="E27" s="7">
-        <v>2.41</v>
+        <v>-3.47</v>
       </c>
     </row>
     <row r="28" spans="1:5">
-      <c r="A28" s="5" t="s">
+      <c r="A28" s="3" t="s">
         <v>37</v>
       </c>
-      <c r="B28" s="5" t="s">
+      <c r="B28" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="C28" s="6">
-        <v>-3.34</v>
-      </c>
-      <c r="D28" s="6">
+      <c r="C28" s="5">
         <v>1.5</v>
       </c>
+      <c r="D28" s="5">
+        <v>-0.71</v>
+      </c>
       <c r="E28" s="7">
-        <v>4.84</v>
+        <v>-2.21</v>
       </c>
     </row>
     <row r="29" spans="1:5">
-      <c r="A29" s="5" t="s">
+      <c r="A29" s="3" t="s">
         <v>38</v>
       </c>
-      <c r="B29" s="5" t="s">
+      <c r="B29" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="C29" s="6">
-        <v>-25.44</v>
-      </c>
-      <c r="D29" s="6">
+      <c r="C29" s="5">
         <v>-13.93</v>
       </c>
-      <c r="E29" s="7">
-        <v>11.51</v>
+      <c r="D29" s="5">
+        <v>-8.51</v>
+      </c>
+      <c r="E29" s="6">
+        <v>5.42</v>
       </c>
     </row>
     <row r="30" spans="1:5">
-      <c r="A30" s="5" t="s">
+      <c r="A30" s="3" t="s">
         <v>39</v>
       </c>
-      <c r="B30" s="5" t="s">
+      <c r="B30" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="C30" s="6">
-        <v>-11.2</v>
-      </c>
-      <c r="D30" s="6">
+      <c r="C30" s="5">
         <v>-7.87</v>
       </c>
-      <c r="E30" s="7">
-        <v>3.33</v>
+      <c r="D30" s="5">
+        <v>-7.47</v>
+      </c>
+      <c r="E30" s="6">
+        <v>0.4</v>
       </c>
     </row>
     <row r="31" spans="1:5">
-      <c r="A31" s="5" t="s">
+      <c r="A31" s="3" t="s">
         <v>40</v>
       </c>
-      <c r="B31" s="5" t="s">
+      <c r="B31" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="C31" s="6">
-        <v>-9.859999999999999</v>
-      </c>
-      <c r="D31" s="6">
+      <c r="C31" s="5">
         <v>-6.07</v>
       </c>
+      <c r="D31" s="5">
+        <v>-6.92</v>
+      </c>
       <c r="E31" s="7">
-        <v>3.79</v>
+        <v>-0.85</v>
       </c>
     </row>
     <row r="32" spans="1:5">
-      <c r="A32" s="5" t="s">
+      <c r="A32" s="3" t="s">
         <v>41</v>
       </c>
-      <c r="B32" s="5" t="s">
+      <c r="B32" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="C32" s="6">
-        <v>-0.02</v>
-      </c>
-      <c r="D32" s="6">
+      <c r="C32" s="5">
         <v>3.07</v>
       </c>
+      <c r="D32" s="5">
+        <v>2.31</v>
+      </c>
       <c r="E32" s="7">
-        <v>3.09</v>
+        <v>-0.76</v>
       </c>
     </row>
     <row r="33" spans="1:5">
-      <c r="A33" s="5" t="s">
+      <c r="A33" s="3" t="s">
         <v>42</v>
       </c>
-      <c r="B33" s="5" t="s">
+      <c r="B33" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="C33" s="6">
-        <v>-6.39</v>
-      </c>
-      <c r="D33" s="6">
+      <c r="C33" s="5">
         <v>-2.37</v>
       </c>
+      <c r="D33" s="5">
+        <v>-6.3</v>
+      </c>
       <c r="E33" s="7">
-        <v>4.02</v>
+        <v>-3.93</v>
       </c>
     </row>
     <row r="34" spans="1:5">
-      <c r="A34" s="5" t="s">
+      <c r="A34" s="3" t="s">
         <v>43</v>
       </c>
-      <c r="B34" s="5" t="s">
+      <c r="B34" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="C34" s="6">
-        <v>30.72</v>
-      </c>
-      <c r="D34" s="6">
+      <c r="C34" s="5">
         <v>29.12</v>
       </c>
-      <c r="E34" s="8">
-        <v>-1.6</v>
+      <c r="D34" s="5">
+        <v>23.56</v>
+      </c>
+      <c r="E34" s="7">
+        <v>-5.56</v>
       </c>
     </row>
     <row r="35" spans="1:5">
-      <c r="A35" s="5" t="s">
+      <c r="A35" s="3" t="s">
         <v>37</v>
       </c>
-      <c r="B35" s="5" t="s">
+      <c r="B35" s="3" t="s">
         <v>6</v>
       </c>
-      <c r="C35" s="6">
-        <v>-18.83</v>
-      </c>
-      <c r="D35" s="6">
+      <c r="C35" s="5">
         <v>-16.53</v>
       </c>
+      <c r="D35" s="5">
+        <v>-17.08</v>
+      </c>
       <c r="E35" s="7">
-        <v>2.3</v>
+        <v>-0.55</v>
       </c>
     </row>
     <row r="36" spans="1:5">
-      <c r="A36" s="5" t="s">
+      <c r="A36" s="3" t="s">
         <v>38</v>
       </c>
-      <c r="B36" s="5" t="s">
+      <c r="B36" s="3" t="s">
         <v>6</v>
       </c>
-      <c r="C36" s="6">
-        <v>-26.53</v>
-      </c>
-      <c r="D36" s="6">
+      <c r="C36" s="5">
         <v>-24.17</v>
       </c>
-      <c r="E36" s="7">
-        <v>2.36</v>
+      <c r="D36" s="5">
+        <v>-22.41</v>
+      </c>
+      <c r="E36" s="6">
+        <v>1.76</v>
       </c>
     </row>
     <row r="37" spans="1:5">
-      <c r="A37" s="5" t="s">
+      <c r="A37" s="3" t="s">
         <v>39</v>
       </c>
-      <c r="B37" s="5" t="s">
+      <c r="B37" s="3" t="s">
         <v>6</v>
       </c>
-      <c r="C37" s="6">
-        <v>-45.47</v>
-      </c>
-      <c r="D37" s="6">
+      <c r="C37" s="5">
         <v>-44.7</v>
       </c>
-      <c r="E37" s="7">
-        <v>0.77</v>
+      <c r="D37" s="5">
+        <v>-44.27</v>
+      </c>
+      <c r="E37" s="6">
+        <v>0.43</v>
       </c>
     </row>
     <row r="38" spans="1:5">
-      <c r="A38" s="5" t="s">
+      <c r="A38" s="3" t="s">
         <v>40</v>
       </c>
-      <c r="B38" s="5" t="s">
+      <c r="B38" s="3" t="s">
         <v>6</v>
       </c>
-      <c r="C38" s="6">
-        <v>-20.98</v>
-      </c>
-      <c r="D38" s="6">
+      <c r="C38" s="5">
         <v>-19.34</v>
       </c>
+      <c r="D38" s="5">
+        <v>-20.9</v>
+      </c>
       <c r="E38" s="7">
-        <v>1.64</v>
+        <v>-1.56</v>
       </c>
     </row>
     <row r="39" spans="1:5">
-      <c r="A39" s="5" t="s">
+      <c r="A39" s="3" t="s">
         <v>41</v>
       </c>
-      <c r="B39" s="5" t="s">
+      <c r="B39" s="3" t="s">
         <v>6</v>
       </c>
-      <c r="C39" s="6">
-        <v>-18.21</v>
-      </c>
-      <c r="D39" s="6">
+      <c r="C39" s="5">
         <v>-17.77</v>
       </c>
+      <c r="D39" s="5">
+        <v>-18.03</v>
+      </c>
       <c r="E39" s="7">
-        <v>0.44</v>
+        <v>-0.26</v>
       </c>
     </row>
     <row r="40" spans="1:5">
-      <c r="A40" s="5" t="s">
+      <c r="A40" s="3" t="s">
         <v>42</v>
       </c>
-      <c r="B40" s="5" t="s">
+      <c r="B40" s="3" t="s">
         <v>6</v>
       </c>
-      <c r="C40" s="6">
-        <v>-17.39</v>
-      </c>
-      <c r="D40" s="6">
+      <c r="C40" s="5">
         <v>-15.19</v>
       </c>
+      <c r="D40" s="5">
+        <v>-17.41</v>
+      </c>
       <c r="E40" s="7">
-        <v>2.2</v>
+        <v>-2.22</v>
       </c>
     </row>
     <row r="41" spans="1:5">
-      <c r="A41" s="5" t="s">
+      <c r="A41" s="3" t="s">
         <v>43</v>
       </c>
-      <c r="B41" s="5" t="s">
+      <c r="B41" s="3" t="s">
         <v>6</v>
       </c>
-      <c r="C41" s="6">
-        <v>-4.49</v>
-      </c>
-      <c r="D41" s="6">
+      <c r="C41" s="5">
         <v>-5.05</v>
       </c>
-      <c r="E41" s="8">
-        <v>-0.5600000000000001</v>
+      <c r="D41" s="5">
+        <v>-5.86</v>
+      </c>
+      <c r="E41" s="7">
+        <v>-0.8100000000000001</v>
       </c>
     </row>
     <row r="42" spans="1:5">
-      <c r="A42" s="5" t="s">
+      <c r="A42" s="3" t="s">
         <v>37</v>
       </c>
-      <c r="B42" s="5" t="s">
+      <c r="B42" s="3" t="s">
         <v>2</v>
       </c>
-      <c r="C42" s="6">
-        <v>10034</v>
-      </c>
-      <c r="D42" s="6">
+      <c r="C42" s="5">
         <v>10318</v>
       </c>
+      <c r="D42" s="5">
+        <v>10250</v>
+      </c>
       <c r="E42" s="7">
-        <v>284</v>
+        <v>-68</v>
       </c>
     </row>
     <row r="43" spans="1:5">
-      <c r="A43" s="5" t="s">
+      <c r="A43" s="3" t="s">
         <v>38</v>
       </c>
-      <c r="B43" s="5" t="s">
+      <c r="B43" s="3" t="s">
         <v>2</v>
       </c>
-      <c r="C43" s="6">
-        <v>492.4</v>
-      </c>
-      <c r="D43" s="6">
+      <c r="C43" s="5">
         <v>508.25</v>
       </c>
-      <c r="E43" s="7">
-        <v>15.85</v>
+      <c r="D43" s="5">
+        <v>520.05</v>
+      </c>
+      <c r="E43" s="6">
+        <v>11.8</v>
       </c>
     </row>
     <row r="44" spans="1:5">
-      <c r="A44" s="5" t="s">
+      <c r="A44" s="3" t="s">
         <v>39</v>
       </c>
-      <c r="B44" s="5" t="s">
+      <c r="B44" s="3" t="s">
         <v>2</v>
       </c>
-      <c r="C44" s="6">
-        <v>298.85</v>
-      </c>
-      <c r="D44" s="6">
+      <c r="C44" s="5">
         <v>303.05</v>
       </c>
-      <c r="E44" s="7">
-        <v>4.2</v>
+      <c r="D44" s="5">
+        <v>305.4</v>
+      </c>
+      <c r="E44" s="6">
+        <v>2.35</v>
       </c>
     </row>
     <row r="45" spans="1:5">
-      <c r="A45" s="5" t="s">
+      <c r="A45" s="3" t="s">
         <v>40</v>
       </c>
-      <c r="B45" s="5" t="s">
+      <c r="B45" s="3" t="s">
         <v>2</v>
       </c>
-      <c r="C45" s="6">
-        <v>1719.9</v>
-      </c>
-      <c r="D45" s="6">
+      <c r="C45" s="5">
         <v>1755.7</v>
       </c>
+      <c r="D45" s="5">
+        <v>1721.7</v>
+      </c>
       <c r="E45" s="7">
-        <v>35.8</v>
+        <v>-34</v>
       </c>
     </row>
     <row r="46" spans="1:5">
-      <c r="A46" s="5" t="s">
+      <c r="A46" s="3" t="s">
         <v>41</v>
       </c>
-      <c r="B46" s="5" t="s">
+      <c r="B46" s="3" t="s">
         <v>2</v>
       </c>
-      <c r="C46" s="6">
-        <v>10750</v>
-      </c>
-      <c r="D46" s="6">
+      <c r="C46" s="5">
         <v>10808</v>
       </c>
+      <c r="D46" s="5">
+        <v>10774</v>
+      </c>
       <c r="E46" s="7">
-        <v>58</v>
+        <v>-34</v>
       </c>
     </row>
     <row r="47" spans="1:5">
-      <c r="A47" s="5" t="s">
+      <c r="A47" s="3" t="s">
         <v>42</v>
       </c>
-      <c r="B47" s="5" t="s">
+      <c r="B47" s="3" t="s">
         <v>2</v>
       </c>
-      <c r="C47" s="6">
-        <v>957.25</v>
-      </c>
-      <c r="D47" s="6">
+      <c r="C47" s="5">
         <v>982.75</v>
       </c>
+      <c r="D47" s="5">
+        <v>957</v>
+      </c>
       <c r="E47" s="7">
-        <v>25.5</v>
+        <v>-25.75</v>
       </c>
     </row>
     <row r="48" spans="1:5">
-      <c r="A48" s="5" t="s">
+      <c r="A48" s="3" t="s">
         <v>43</v>
       </c>
-      <c r="B48" s="5" t="s">
+      <c r="B48" s="3" t="s">
         <v>2</v>
       </c>
-      <c r="C48" s="6">
-        <v>177.58</v>
-      </c>
-      <c r="D48" s="6">
+      <c r="C48" s="5">
         <v>176.53</v>
       </c>
-      <c r="E48" s="8">
-        <v>-1.05</v>
+      <c r="D48" s="5">
+        <v>175.02</v>
+      </c>
+      <c r="E48" s="7">
+        <v>-1.51</v>
       </c>
     </row>
     <row r="49" spans="1:5">
-      <c r="A49" s="5" t="s">
+      <c r="A49" s="3" t="s">
         <v>37</v>
       </c>
-      <c r="B49" s="5" t="s">
+      <c r="B49" s="3" t="s">
         <v>24</v>
       </c>
-      <c r="C49" s="6">
-        <v>31.77</v>
-      </c>
-      <c r="D49" s="6">
+      <c r="C49" s="5">
         <v>39.8</v>
       </c>
+      <c r="D49" s="5">
+        <v>38.63</v>
+      </c>
       <c r="E49" s="7">
-        <v>8.029999999999999</v>
+        <v>-1.17</v>
       </c>
     </row>
     <row r="50" spans="1:5">
-      <c r="A50" s="5" t="s">
+      <c r="A50" s="3" t="s">
         <v>38</v>
       </c>
-      <c r="B50" s="5" t="s">
+      <c r="B50" s="3" t="s">
         <v>24</v>
       </c>
-      <c r="C50" s="6">
-        <v>47.42</v>
-      </c>
-      <c r="D50" s="6">
+      <c r="C50" s="5">
         <v>53.14</v>
       </c>
-      <c r="E50" s="7">
-        <v>5.72</v>
+      <c r="D50" s="5">
+        <v>56.9</v>
+      </c>
+      <c r="E50" s="6">
+        <v>3.76</v>
       </c>
     </row>
     <row r="51" spans="1:5">
-      <c r="A51" s="5" t="s">
+      <c r="A51" s="3" t="s">
         <v>39</v>
       </c>
-      <c r="B51" s="5" t="s">
+      <c r="B51" s="3" t="s">
         <v>24</v>
       </c>
-      <c r="C51" s="6">
-        <v>35.1</v>
-      </c>
-      <c r="D51" s="6">
+      <c r="C51" s="5">
         <v>39.64</v>
       </c>
-      <c r="E51" s="7">
-        <v>4.54</v>
+      <c r="D51" s="5">
+        <v>42.08</v>
+      </c>
+      <c r="E51" s="6">
+        <v>2.44</v>
       </c>
     </row>
     <row r="52" spans="1:5">
-      <c r="A52" s="5" t="s">
+      <c r="A52" s="3" t="s">
         <v>40</v>
       </c>
-      <c r="B52" s="5" t="s">
+      <c r="B52" s="3" t="s">
         <v>24</v>
       </c>
-      <c r="C52" s="6">
-        <v>31.03</v>
-      </c>
-      <c r="D52" s="6">
+      <c r="C52" s="5">
         <v>39.81</v>
       </c>
+      <c r="D52" s="5">
+        <v>35.23</v>
+      </c>
       <c r="E52" s="7">
-        <v>8.779999999999999</v>
+        <v>-4.58</v>
       </c>
     </row>
     <row r="53" spans="1:5">
-      <c r="A53" s="5" t="s">
+      <c r="A53" s="3" t="s">
         <v>41</v>
       </c>
-      <c r="B53" s="5" t="s">
+      <c r="B53" s="3" t="s">
         <v>24</v>
       </c>
-      <c r="C53" s="6">
-        <v>45.41</v>
-      </c>
-      <c r="D53" s="6">
+      <c r="C53" s="5">
         <v>47.07</v>
       </c>
+      <c r="D53" s="5">
+        <v>46.18</v>
+      </c>
       <c r="E53" s="7">
-        <v>1.66</v>
+        <v>-0.89</v>
       </c>
     </row>
     <row r="54" spans="1:5">
-      <c r="A54" s="5" t="s">
+      <c r="A54" s="3" t="s">
         <v>42</v>
       </c>
-      <c r="B54" s="5" t="s">
+      <c r="B54" s="3" t="s">
         <v>24</v>
       </c>
-      <c r="C54" s="6">
-        <v>37.02</v>
-      </c>
-      <c r="D54" s="6">
+      <c r="C54" s="5">
         <v>45.66</v>
       </c>
+      <c r="D54" s="5">
+        <v>39.73</v>
+      </c>
       <c r="E54" s="7">
-        <v>8.640000000000001</v>
+        <v>-5.93</v>
       </c>
     </row>
     <row r="55" spans="1:5">
-      <c r="A55" s="5" t="s">
+      <c r="A55" s="3" t="s">
         <v>43</v>
       </c>
-      <c r="B55" s="5" t="s">
+      <c r="B55" s="3" t="s">
         <v>24</v>
       </c>
-      <c r="C55" s="6">
-        <v>65.70999999999999</v>
-      </c>
-      <c r="D55" s="6">
+      <c r="C55" s="5">
         <v>64.45999999999999</v>
       </c>
-      <c r="E55" s="8">
-        <v>-1.25</v>
+      <c r="D55" s="5">
+        <v>62.62</v>
+      </c>
+      <c r="E55" s="7">
+        <v>-1.84</v>
       </c>
     </row>
     <row r="56" spans="1:5">
-      <c r="A56" s="5" t="s">
+      <c r="A56" s="3" t="s">
         <v>37</v>
       </c>
-      <c r="B56" s="5" t="s">
+      <c r="B56" s="3" t="s">
         <v>31</v>
       </c>
-      <c r="C56" s="6">
-        <v>9.17</v>
-      </c>
-      <c r="D56" s="6">
+      <c r="C56" s="5">
         <v>14.9</v>
       </c>
+      <c r="D56" s="5">
+        <v>-22.12</v>
+      </c>
       <c r="E56" s="7">
-        <v>5.73</v>
+        <v>-37.02</v>
       </c>
     </row>
     <row r="57" spans="1:5">
-      <c r="A57" s="5" t="s">
+      <c r="A57" s="3" t="s">
         <v>38</v>
       </c>
-      <c r="B57" s="5" t="s">
+      <c r="B57" s="3" t="s">
         <v>31</v>
       </c>
-      <c r="C57" s="6">
-        <v>-41.08</v>
-      </c>
-      <c r="D57" s="6">
+      <c r="C57" s="5">
         <v>-3.22</v>
       </c>
-      <c r="E57" s="7">
-        <v>37.86</v>
+      <c r="D57" s="5">
+        <v>87.65000000000001</v>
+      </c>
+      <c r="E57" s="6">
+        <v>90.87</v>
       </c>
     </row>
     <row r="58" spans="1:5">
-      <c r="A58" s="5" t="s">
+      <c r="A58" s="3" t="s">
         <v>39</v>
       </c>
-      <c r="B58" s="5" t="s">
+      <c r="B58" s="3" t="s">
         <v>31</v>
       </c>
-      <c r="C58" s="6">
-        <v>-38.62</v>
-      </c>
-      <c r="D58" s="6">
+      <c r="C58" s="5">
         <v>-24.33</v>
       </c>
+      <c r="D58" s="5">
+        <v>-65.81999999999999</v>
+      </c>
       <c r="E58" s="7">
-        <v>14.29</v>
+        <v>-41.49</v>
       </c>
     </row>
     <row r="59" spans="1:5">
-      <c r="A59" s="5" t="s">
+      <c r="A59" s="3" t="s">
         <v>40</v>
       </c>
-      <c r="B59" s="5" t="s">
+      <c r="B59" s="3" t="s">
         <v>31</v>
       </c>
-      <c r="C59" s="6">
-        <v>-34.16</v>
-      </c>
-      <c r="D59" s="6">
+      <c r="C59" s="5">
         <v>84.88</v>
       </c>
+      <c r="D59" s="5">
+        <v>-1.12</v>
+      </c>
       <c r="E59" s="7">
-        <v>119.04</v>
+        <v>-86</v>
       </c>
     </row>
     <row r="60" spans="1:5">
-      <c r="A60" s="5" t="s">
+      <c r="A60" s="3" t="s">
         <v>41</v>
       </c>
-      <c r="B60" s="5" t="s">
+      <c r="B60" s="3" t="s">
         <v>31</v>
       </c>
-      <c r="C60" s="6">
-        <v>-38.37</v>
-      </c>
-      <c r="D60" s="6">
+      <c r="C60" s="5">
         <v>-37.1</v>
       </c>
-      <c r="E60" s="7">
-        <v>1.27</v>
+      <c r="D60" s="5">
+        <v>-35.35</v>
+      </c>
+      <c r="E60" s="6">
+        <v>1.75</v>
       </c>
     </row>
     <row r="61" spans="1:5">
-      <c r="A61" s="5" t="s">
+      <c r="A61" s="3" t="s">
         <v>42</v>
       </c>
-      <c r="B61" s="5" t="s">
+      <c r="B61" s="3" t="s">
         <v>31</v>
       </c>
-      <c r="C61" s="6">
-        <v>-30.26</v>
-      </c>
-      <c r="D61" s="6">
+      <c r="C61" s="5">
         <v>7.47</v>
       </c>
+      <c r="D61" s="5">
+        <v>-0.9399999999999999</v>
+      </c>
       <c r="E61" s="7">
-        <v>37.73</v>
+        <v>-8.41</v>
       </c>
     </row>
     <row r="62" spans="1:5">
-      <c r="A62" s="5" t="s">
+      <c r="A62" s="3" t="s">
         <v>43</v>
       </c>
-      <c r="B62" s="5" t="s">
+      <c r="B62" s="3" t="s">
         <v>31</v>
       </c>
-      <c r="C62" s="6">
-        <v>-64.44</v>
-      </c>
-      <c r="D62" s="6">
+      <c r="C62" s="5">
         <v>-56.03</v>
       </c>
+      <c r="D62" s="5">
+        <v>-84.72</v>
+      </c>
       <c r="E62" s="7">
-        <v>8.41</v>
+        <v>-28.69</v>
       </c>
     </row>
   </sheetData>
@@ -2904,60 +2841,60 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:9" ht="28" customHeight="1">
-      <c r="A1" s="9" t="s">
+      <c r="A1" s="8" t="s">
         <v>1</v>
       </c>
-      <c r="B1" s="9" t="s">
-        <v>65</v>
-      </c>
-      <c r="C1" s="9" t="s">
-        <v>66</v>
-      </c>
-      <c r="D1" s="9" t="s">
-        <v>67</v>
-      </c>
-      <c r="E1" s="9" t="s">
-        <v>68</v>
-      </c>
-      <c r="F1" s="9" t="s">
-        <v>69</v>
-      </c>
-      <c r="G1" s="9" t="s">
-        <v>70</v>
-      </c>
-      <c r="H1" s="9" t="s">
-        <v>71</v>
-      </c>
-      <c r="I1" s="9" t="s">
-        <v>72</v>
+      <c r="B1" s="8" t="s">
+        <v>56</v>
+      </c>
+      <c r="C1" s="8" t="s">
+        <v>57</v>
+      </c>
+      <c r="D1" s="8" t="s">
+        <v>58</v>
+      </c>
+      <c r="E1" s="8" t="s">
+        <v>59</v>
+      </c>
+      <c r="F1" s="8" t="s">
+        <v>60</v>
+      </c>
+      <c r="G1" s="8" t="s">
+        <v>61</v>
+      </c>
+      <c r="H1" s="8" t="s">
+        <v>62</v>
+      </c>
+      <c r="I1" s="8" t="s">
+        <v>63</v>
       </c>
     </row>
     <row r="2" spans="1:9">
-      <c r="A2" s="10" t="s">
+      <c r="A2" s="9" t="s">
         <v>44</v>
       </c>
-      <c r="B2" s="11">
-        <v>60.8</v>
-      </c>
-      <c r="C2" s="12">
+      <c r="B2" s="10">
+        <v>56.8</v>
+      </c>
+      <c r="C2" s="11">
         <v>7</v>
       </c>
-      <c r="D2" s="11">
-        <v>47.1</v>
-      </c>
-      <c r="E2" s="11">
-        <v>70</v>
-      </c>
-      <c r="F2" s="11">
-        <v>-2.7</v>
-      </c>
-      <c r="G2" s="11">
-        <v>0.5</v>
-      </c>
-      <c r="H2" s="11">
+      <c r="D2" s="10">
+        <v>45.9</v>
+      </c>
+      <c r="E2" s="10">
+        <v>60</v>
+      </c>
+      <c r="F2" s="10">
+        <v>-2.4</v>
+      </c>
+      <c r="G2" s="10">
+        <v>-0.6</v>
+      </c>
+      <c r="H2" s="10">
         <v>57</v>
       </c>
-      <c r="I2" s="11">
+      <c r="I2" s="10">
         <v>10</v>
       </c>
     </row>
@@ -3059,49 +2996,49 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:7">
-      <c r="A1" s="13" t="s">
+      <c r="A1" s="12" t="s">
         <v>37</v>
       </c>
-      <c r="B1" s="13" t="s">
+      <c r="B1" s="12" t="s">
         <v>41</v>
       </c>
-      <c r="C1" s="13" t="s">
+      <c r="C1" s="12" t="s">
         <v>38</v>
       </c>
-      <c r="D1" s="13" t="s">
+      <c r="D1" s="12" t="s">
         <v>43</v>
       </c>
-      <c r="E1" s="13" t="s">
+      <c r="E1" s="12" t="s">
         <v>42</v>
       </c>
-      <c r="F1" s="13" t="s">
+      <c r="F1" s="12" t="s">
         <v>40</v>
       </c>
-      <c r="G1" s="13" t="s">
+      <c r="G1" s="12" t="s">
         <v>39</v>
       </c>
     </row>
     <row r="2" spans="1:7">
-      <c r="A2" s="14">
-        <v>0.2386</v>
-      </c>
-      <c r="B2" s="14">
-        <v>0.1924</v>
-      </c>
-      <c r="C2" s="14">
-        <v>0.1639</v>
-      </c>
-      <c r="D2" s="14">
-        <v>0.0535</v>
-      </c>
-      <c r="E2" s="14">
-        <v>0.0478</v>
-      </c>
-      <c r="F2" s="14">
-        <v>-0.0066</v>
-      </c>
-      <c r="G2" s="14">
-        <v>-0.2332</v>
+      <c r="A2" s="13">
+        <v>0.2371</v>
+      </c>
+      <c r="B2" s="13">
+        <v>0.191</v>
+      </c>
+      <c r="C2" s="13">
+        <v>0.1688</v>
+      </c>
+      <c r="D2" s="13">
+        <v>0.0542</v>
+      </c>
+      <c r="E2" s="13">
+        <v>0.044</v>
+      </c>
+      <c r="F2" s="13">
+        <v>-0.0138</v>
+      </c>
+      <c r="G2" s="13">
+        <v>-0.2373</v>
       </c>
     </row>
   </sheetData>

--- a/BAJAJ_GROUP_Technical_Metrics.xlsx
+++ b/BAJAJ_GROUP_Technical_Metrics.xlsx
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="253" uniqueCount="64">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="270" uniqueCount="77">
   <si>
     <t>Symbol</t>
   </si>
@@ -172,7 +172,46 @@
     <t>▶  SIGNAL EVENTS (vs Previous Run)</t>
   </si>
   <si>
-    <t>No signal events detected since last run.</t>
+    <t>Signal</t>
+  </si>
+  <si>
+    <t>Change</t>
+  </si>
+  <si>
+    <t>Direction</t>
+  </si>
+  <si>
+    <t>Prev Value</t>
+  </si>
+  <si>
+    <t>Curr Value</t>
+  </si>
+  <si>
+    <t>RSI Momentum</t>
+  </si>
+  <si>
+    <t>46.2 → 57.6</t>
+  </si>
+  <si>
+    <t>🟢 BULLISH</t>
+  </si>
+  <si>
+    <t>46.2</t>
+  </si>
+  <si>
+    <t>57.6</t>
+  </si>
+  <si>
+    <t>56.9 → 41.3</t>
+  </si>
+  <si>
+    <t>🔴 BEARISH</t>
+  </si>
+  <si>
+    <t>56.9</t>
+  </si>
+  <si>
+    <t>41.3</t>
   </si>
   <si>
     <t>▶  NUMERIC METRIC CHANGES (vs Previous Run)</t>
@@ -374,14 +413,16 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="14">
+  <cellXfs count="16">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="2" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="3" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
+    <xf numFmtId="0" fontId="4" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="5" fillId="6" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1"/>
     <xf numFmtId="165" fontId="4" fillId="5" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="165" fontId="5" fillId="6" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
@@ -896,10 +937,10 @@
         <v>44</v>
       </c>
       <c r="C2">
-        <v>10250</v>
+        <v>10385</v>
       </c>
       <c r="D2">
-        <v>-0.66</v>
+        <v>1.32</v>
       </c>
       <c r="E2">
         <v>12361</v>
@@ -908,46 +949,46 @@
         <v>8599.48</v>
       </c>
       <c r="G2">
-        <v>-17.08</v>
+        <v>-15.99</v>
       </c>
       <c r="H2">
-        <v>19.19</v>
+        <v>20.76</v>
       </c>
       <c r="I2">
-        <v>3.7</v>
+        <v>7.76</v>
       </c>
       <c r="J2">
-        <v>-12.23</v>
+        <v>-9.09</v>
       </c>
       <c r="K2">
-        <v>-0.71</v>
+        <v>0.52</v>
       </c>
       <c r="L2">
-        <v>17.98</v>
+        <v>17.71</v>
       </c>
       <c r="M2">
-        <v>23.71</v>
+        <v>24.39</v>
       </c>
       <c r="N2">
         <v>71</v>
       </c>
       <c r="O2">
-        <v>69</v>
+        <v>71</v>
       </c>
       <c r="P2">
-        <v>10003.4</v>
+        <v>10153</v>
       </c>
       <c r="Q2">
-        <v>10695.75</v>
+        <v>10635.35</v>
       </c>
       <c r="R2">
-        <v>11347.56</v>
+        <v>11323.26</v>
       </c>
       <c r="S2">
-        <v>10184.15</v>
+        <v>10191.39</v>
       </c>
       <c r="T2">
-        <v>0.65</v>
+        <v>1.9</v>
       </c>
       <c r="U2" t="s">
         <v>45</v>
@@ -962,34 +1003,34 @@
         <v>2</v>
       </c>
       <c r="Y2">
-        <v>38.63</v>
+        <v>42.27</v>
       </c>
       <c r="Z2">
-        <v>-410.69</v>
+        <v>-374.07</v>
       </c>
       <c r="AA2">
-        <v>-378.6</v>
+        <v>-377.69</v>
       </c>
       <c r="AB2">
-        <v>-32.09</v>
+        <v>3.63</v>
       </c>
       <c r="AC2">
-        <v>78.14</v>
+        <v>92.95999999999999</v>
       </c>
       <c r="AD2">
-        <v>52.62</v>
+        <v>75.2</v>
       </c>
       <c r="AE2">
-        <v>264.97</v>
+        <v>260.55</v>
       </c>
       <c r="AF2">
-        <v>-22.12</v>
+        <v>-31.77</v>
       </c>
       <c r="AG2">
-        <v>12071.3</v>
+        <v>11949.74</v>
       </c>
       <c r="AH2">
-        <v>9320.200000000001</v>
+        <v>9320.959999999999</v>
       </c>
       <c r="AI2">
         <v>10503.51</v>
@@ -998,7 +1039,7 @@
         <v>47</v>
       </c>
       <c r="AK2">
-        <v>60.98</v>
+        <v>55.14</v>
       </c>
     </row>
     <row r="3" spans="1:37">
@@ -1009,10 +1050,10 @@
         <v>44</v>
       </c>
       <c r="C3">
-        <v>520.05</v>
+        <v>468.5</v>
       </c>
       <c r="D3">
-        <v>2.32</v>
+        <v>-9.91</v>
       </c>
       <c r="E3">
         <v>670.25</v>
@@ -1021,46 +1062,46 @@
         <v>247.45</v>
       </c>
       <c r="G3">
-        <v>-22.41</v>
+        <v>-30.1</v>
       </c>
       <c r="H3">
-        <v>110.16</v>
+        <v>89.33</v>
       </c>
       <c r="I3">
-        <v>7.67</v>
+        <v>-4.22</v>
       </c>
       <c r="J3">
-        <v>-0.09</v>
+        <v>-7.01</v>
       </c>
       <c r="K3">
-        <v>-8.51</v>
+        <v>-15.39</v>
       </c>
       <c r="L3">
-        <v>109.99</v>
+        <v>77.38</v>
       </c>
       <c r="M3">
-        <v>16.88</v>
+        <v>14.87</v>
       </c>
       <c r="N3">
         <v>99</v>
       </c>
       <c r="O3">
-        <v>92</v>
+        <v>87</v>
       </c>
       <c r="P3">
-        <v>503.36</v>
+        <v>499.23</v>
       </c>
       <c r="Q3">
-        <v>499.4</v>
+        <v>497.92</v>
       </c>
       <c r="R3">
-        <v>501.92</v>
+        <v>500.4</v>
       </c>
       <c r="S3">
-        <v>461.69</v>
+        <v>462.72</v>
       </c>
       <c r="T3">
-        <v>12.64</v>
+        <v>1.25</v>
       </c>
       <c r="U3" t="s">
         <v>45</v>
@@ -1075,34 +1116,34 @@
         <v>2</v>
       </c>
       <c r="Y3">
-        <v>56.9</v>
+        <v>41.31</v>
       </c>
       <c r="Z3">
-        <v>-0.48</v>
+        <v>-3</v>
       </c>
       <c r="AA3">
-        <v>-3.1</v>
+        <v>-3.08</v>
       </c>
       <c r="AB3">
-        <v>2.62</v>
+        <v>0.08</v>
       </c>
       <c r="AC3">
-        <v>86.73</v>
+        <v>70.81</v>
       </c>
       <c r="AD3">
-        <v>81</v>
+        <v>81.42</v>
       </c>
       <c r="AE3">
-        <v>19.75</v>
+        <v>23.98</v>
       </c>
       <c r="AF3">
-        <v>87.65000000000001</v>
+        <v>1243.02</v>
       </c>
       <c r="AG3">
-        <v>522.33</v>
+        <v>524.71</v>
       </c>
       <c r="AH3">
-        <v>476.47</v>
+        <v>471.14</v>
       </c>
       <c r="AI3">
         <v>460.99</v>
@@ -1111,7 +1152,7 @@
         <v>48</v>
       </c>
       <c r="AK3">
-        <v>23.68</v>
+        <v>24.94</v>
       </c>
     </row>
     <row r="4" spans="1:37">
@@ -1122,10 +1163,10 @@
         <v>44</v>
       </c>
       <c r="C4">
-        <v>305.4</v>
+        <v>306.7</v>
       </c>
       <c r="D4">
-        <v>0.78</v>
+        <v>0.43</v>
       </c>
       <c r="E4">
         <v>548</v>
@@ -1134,25 +1175,25 @@
         <v>290.05</v>
       </c>
       <c r="G4">
-        <v>-44.27</v>
+        <v>-44.03</v>
       </c>
       <c r="H4">
-        <v>5.29</v>
+        <v>5.74</v>
       </c>
       <c r="I4">
-        <v>1.56</v>
+        <v>5.74</v>
       </c>
       <c r="J4">
-        <v>-8.92</v>
+        <v>-6.61</v>
       </c>
       <c r="K4">
-        <v>-7.47</v>
+        <v>-8.69</v>
       </c>
       <c r="L4">
-        <v>-43.26</v>
+        <v>-43.53</v>
       </c>
       <c r="M4">
-        <v>-23.73</v>
+        <v>-23.91</v>
       </c>
       <c r="N4">
         <v>15</v>
@@ -1161,19 +1202,19 @@
         <v>15</v>
       </c>
       <c r="P4">
-        <v>299.07</v>
+        <v>302.4</v>
       </c>
       <c r="Q4">
-        <v>310.67</v>
+        <v>309.88</v>
       </c>
       <c r="R4">
-        <v>331.98</v>
+        <v>331.12</v>
       </c>
       <c r="S4">
-        <v>360.75</v>
+        <v>359.87</v>
       </c>
       <c r="T4">
-        <v>-15.34</v>
+        <v>-14.78</v>
       </c>
       <c r="U4" t="s">
         <v>45</v>
@@ -1188,34 +1229,34 @@
         <v>0</v>
       </c>
       <c r="Y4">
-        <v>42.08</v>
+        <v>43.44</v>
       </c>
       <c r="Z4">
-        <v>-8.92</v>
+        <v>-8.08</v>
       </c>
       <c r="AA4">
-        <v>-9.18</v>
+        <v>-8.960000000000001</v>
       </c>
       <c r="AB4">
-        <v>0.26</v>
+        <v>0.88</v>
       </c>
       <c r="AC4">
-        <v>72.62</v>
+        <v>89.86</v>
       </c>
       <c r="AD4">
-        <v>52.42</v>
+        <v>72.13</v>
       </c>
       <c r="AE4">
-        <v>9.050000000000001</v>
+        <v>11.64</v>
       </c>
       <c r="AF4">
-        <v>-65.81999999999999</v>
+        <v>8636.33</v>
       </c>
       <c r="AG4">
-        <v>334.86</v>
+        <v>333.46</v>
       </c>
       <c r="AH4">
-        <v>286.48</v>
+        <v>286.3</v>
       </c>
       <c r="AI4">
         <v>322.52</v>
@@ -1224,7 +1265,7 @@
         <v>47</v>
       </c>
       <c r="AK4">
-        <v>48.9</v>
+        <v>50.53</v>
       </c>
     </row>
     <row r="5" spans="1:37">
@@ -1235,10 +1276,10 @@
         <v>44</v>
       </c>
       <c r="C5">
-        <v>1721.7</v>
+        <v>1732</v>
       </c>
       <c r="D5">
-        <v>-1.94</v>
+        <v>0.6</v>
       </c>
       <c r="E5">
         <v>2176.6</v>
@@ -1247,46 +1288,46 @@
         <v>1631.8</v>
       </c>
       <c r="G5">
-        <v>-20.9</v>
+        <v>-20.43</v>
       </c>
       <c r="H5">
-        <v>5.51</v>
+        <v>6.14</v>
       </c>
       <c r="I5">
-        <v>-1.24</v>
+        <v>1.41</v>
       </c>
       <c r="J5">
-        <v>-10.02</v>
+        <v>-6.66</v>
       </c>
       <c r="K5">
-        <v>-6.92</v>
+        <v>-5.8</v>
       </c>
       <c r="L5">
-        <v>-14.54</v>
+        <v>-13.59</v>
       </c>
       <c r="M5">
-        <v>-1.38</v>
+        <v>-1.46</v>
       </c>
       <c r="N5">
         <v>29</v>
       </c>
       <c r="O5">
-        <v>42</v>
+        <v>45</v>
       </c>
       <c r="P5">
-        <v>1728</v>
+        <v>1732.8</v>
       </c>
       <c r="Q5">
-        <v>1772.34</v>
+        <v>1767.09</v>
       </c>
       <c r="R5">
-        <v>1908.07</v>
+        <v>1900.61</v>
       </c>
       <c r="S5">
-        <v>1872.47</v>
+        <v>1871.04</v>
       </c>
       <c r="T5">
-        <v>-8.050000000000001</v>
+        <v>-7.43</v>
       </c>
       <c r="U5" t="s">
         <v>45</v>
@@ -1301,34 +1342,34 @@
         <v>1</v>
       </c>
       <c r="Y5">
-        <v>35.23</v>
+        <v>37.57</v>
       </c>
       <c r="Z5">
-        <v>-49.93</v>
+        <v>-47.65</v>
       </c>
       <c r="AA5">
-        <v>-52.98</v>
+        <v>-51.92</v>
       </c>
       <c r="AB5">
-        <v>3.05</v>
+        <v>4.27</v>
       </c>
       <c r="AC5">
-        <v>76.78</v>
+        <v>84.98</v>
       </c>
       <c r="AD5">
-        <v>68.38</v>
+        <v>80.44</v>
       </c>
       <c r="AE5">
-        <v>38.29</v>
+        <v>38.49</v>
       </c>
       <c r="AF5">
-        <v>-1.12</v>
+        <v>7.06</v>
       </c>
       <c r="AG5">
-        <v>1874.72</v>
+        <v>1866.22</v>
       </c>
       <c r="AH5">
-        <v>1669.96</v>
+        <v>1667.96</v>
       </c>
       <c r="AI5">
         <v>1825.61</v>
@@ -1337,7 +1378,7 @@
         <v>47</v>
       </c>
       <c r="AK5">
-        <v>57.9</v>
+        <v>55.59</v>
       </c>
     </row>
     <row r="6" spans="1:37">
@@ -1348,10 +1389,10 @@
         <v>44</v>
       </c>
       <c r="C6">
-        <v>10774</v>
+        <v>11225</v>
       </c>
       <c r="D6">
-        <v>-0.31</v>
+        <v>4.19</v>
       </c>
       <c r="E6">
         <v>13144</v>
@@ -1360,46 +1401,46 @@
         <v>8746</v>
       </c>
       <c r="G6">
-        <v>-18.03</v>
+        <v>-14.6</v>
       </c>
       <c r="H6">
-        <v>23.19</v>
+        <v>28.34</v>
       </c>
       <c r="I6">
-        <v>1.05</v>
+        <v>5.9</v>
       </c>
       <c r="J6">
-        <v>-3.23</v>
+        <v>1.13</v>
       </c>
       <c r="K6">
-        <v>2.31</v>
+        <v>7.76</v>
       </c>
       <c r="L6">
-        <v>-9.529999999999999</v>
+        <v>-7.03</v>
       </c>
       <c r="M6">
-        <v>19.1</v>
+        <v>19.98</v>
       </c>
       <c r="N6">
         <v>57</v>
       </c>
       <c r="O6">
-        <v>58</v>
+        <v>64</v>
       </c>
       <c r="P6">
-        <v>10750.4</v>
+        <v>10875.4</v>
       </c>
       <c r="Q6">
-        <v>10886.1</v>
+        <v>10900.85</v>
       </c>
       <c r="R6">
-        <v>11141.82</v>
+        <v>11136.82</v>
       </c>
       <c r="S6">
-        <v>10659.4</v>
+        <v>10659.74</v>
       </c>
       <c r="T6">
-        <v>1.08</v>
+        <v>5.3</v>
       </c>
       <c r="U6" t="s">
         <v>45</v>
@@ -1414,34 +1455,34 @@
         <v>2</v>
       </c>
       <c r="Y6">
-        <v>46.18</v>
+        <v>57.61</v>
       </c>
       <c r="Z6">
-        <v>-108.92</v>
+        <v>-65.92</v>
       </c>
       <c r="AA6">
-        <v>-113.47</v>
+        <v>-103.96</v>
       </c>
       <c r="AB6">
-        <v>4.55</v>
+        <v>38.03</v>
       </c>
       <c r="AC6">
-        <v>58.35</v>
+        <v>78.98</v>
       </c>
       <c r="AD6">
-        <v>44.93</v>
+        <v>60.45</v>
       </c>
       <c r="AE6">
-        <v>249.46</v>
+        <v>271.28</v>
       </c>
       <c r="AF6">
-        <v>-35.35</v>
+        <v>98.14</v>
       </c>
       <c r="AG6">
-        <v>11406.03</v>
+        <v>11442.32</v>
       </c>
       <c r="AH6">
-        <v>10366.17</v>
+        <v>10359.38</v>
       </c>
       <c r="AI6">
         <v>11368.55</v>
@@ -1450,7 +1491,7 @@
         <v>47</v>
       </c>
       <c r="AK6">
-        <v>24.36</v>
+        <v>25.47</v>
       </c>
     </row>
     <row r="7" spans="1:37">
@@ -1461,10 +1502,10 @@
         <v>44</v>
       </c>
       <c r="C7">
-        <v>957</v>
+        <v>965.25</v>
       </c>
       <c r="D7">
-        <v>-2.62</v>
+        <v>0.86</v>
       </c>
       <c r="E7">
         <v>1158.8</v>
@@ -1473,46 +1514,46 @@
         <v>801.55</v>
       </c>
       <c r="G7">
-        <v>-17.41</v>
+        <v>-16.7</v>
       </c>
       <c r="H7">
-        <v>19.39</v>
+        <v>20.42</v>
       </c>
       <c r="I7">
-        <v>-0.71</v>
+        <v>0.97</v>
       </c>
       <c r="J7">
-        <v>-7.49</v>
+        <v>-4.35</v>
       </c>
       <c r="K7">
-        <v>-6.3</v>
+        <v>-6.97</v>
       </c>
       <c r="L7">
-        <v>-6.55</v>
+        <v>-5.72</v>
       </c>
       <c r="M7">
-        <v>4.4</v>
+        <v>4.59</v>
       </c>
       <c r="N7">
         <v>43</v>
       </c>
       <c r="O7">
-        <v>51</v>
+        <v>53</v>
       </c>
       <c r="P7">
-        <v>962.59</v>
+        <v>964.45</v>
       </c>
       <c r="Q7">
-        <v>984.5</v>
+        <v>982.46</v>
       </c>
       <c r="R7">
-        <v>1041.42</v>
+        <v>1037.75</v>
       </c>
       <c r="S7">
-        <v>974.62</v>
+        <v>974.4400000000001</v>
       </c>
       <c r="T7">
-        <v>-1.81</v>
+        <v>-0.9399999999999999</v>
       </c>
       <c r="U7" t="s">
         <v>45</v>
@@ -1527,34 +1568,34 @@
         <v>1</v>
       </c>
       <c r="Y7">
-        <v>39.73</v>
+        <v>42.31</v>
       </c>
       <c r="Z7">
-        <v>-22.01</v>
+        <v>-20.88</v>
       </c>
       <c r="AA7">
-        <v>-23.18</v>
+        <v>-22.72</v>
       </c>
       <c r="AB7">
-        <v>1.17</v>
+        <v>1.84</v>
       </c>
       <c r="AC7">
-        <v>55.04</v>
+        <v>70.5</v>
       </c>
       <c r="AD7">
-        <v>43.54</v>
+        <v>57.56</v>
       </c>
       <c r="AE7">
-        <v>25.72</v>
+        <v>25.84</v>
       </c>
       <c r="AF7">
-        <v>-0.9399999999999999</v>
+        <v>48.19</v>
       </c>
       <c r="AG7">
-        <v>1042.78</v>
+        <v>1040.4</v>
       </c>
       <c r="AH7">
-        <v>926.23</v>
+        <v>924.51</v>
       </c>
       <c r="AI7">
         <v>1020.6</v>
@@ -1563,7 +1604,7 @@
         <v>47</v>
       </c>
       <c r="AK7">
-        <v>23.25</v>
+        <v>20.51</v>
       </c>
     </row>
     <row r="8" spans="1:37">
@@ -1574,10 +1615,10 @@
         <v>44</v>
       </c>
       <c r="C8">
-        <v>175.02</v>
+        <v>170.35</v>
       </c>
       <c r="D8">
-        <v>-0.86</v>
+        <v>-2.67</v>
       </c>
       <c r="E8">
         <v>185.92</v>
@@ -1586,46 +1627,46 @@
         <v>115.96</v>
       </c>
       <c r="G8">
-        <v>-5.86</v>
+        <v>-8.369999999999999</v>
       </c>
       <c r="H8">
-        <v>50.93</v>
+        <v>46.9</v>
       </c>
       <c r="I8">
-        <v>-5.86</v>
+        <v>-2.26</v>
       </c>
       <c r="J8">
-        <v>25.48</v>
+        <v>25.61</v>
       </c>
       <c r="K8">
-        <v>23.56</v>
+        <v>16.52</v>
       </c>
       <c r="L8">
-        <v>29.65</v>
+        <v>28.89</v>
       </c>
       <c r="M8">
-        <v>5.42</v>
+        <v>4.92</v>
       </c>
       <c r="N8">
         <v>85</v>
       </c>
       <c r="O8">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="P8">
-        <v>175.88</v>
+        <v>175.09</v>
       </c>
       <c r="Q8">
-        <v>164.31</v>
+        <v>166.08</v>
       </c>
       <c r="R8">
-        <v>148.22</v>
+        <v>148.78</v>
       </c>
       <c r="S8">
-        <v>136.97</v>
+        <v>137.15</v>
       </c>
       <c r="T8">
-        <v>27.78</v>
+        <v>24.2</v>
       </c>
       <c r="U8" t="s">
         <v>46</v>
@@ -1640,34 +1681,34 @@
         <v>3</v>
       </c>
       <c r="Y8">
-        <v>62.62</v>
+        <v>57.18</v>
       </c>
       <c r="Z8">
-        <v>9.83</v>
+        <v>8.890000000000001</v>
       </c>
       <c r="AA8">
-        <v>9.85</v>
+        <v>9.65</v>
       </c>
       <c r="AB8">
-        <v>-0.01</v>
+        <v>-0.76</v>
       </c>
       <c r="AC8">
-        <v>9.93</v>
+        <v>1.17</v>
       </c>
       <c r="AD8">
-        <v>25.16</v>
+        <v>12.15</v>
       </c>
       <c r="AE8">
-        <v>8.08</v>
+        <v>7.9</v>
       </c>
       <c r="AF8">
-        <v>-84.72</v>
+        <v>-69.31999999999999</v>
       </c>
       <c r="AG8">
-        <v>200.73</v>
+        <v>199.83</v>
       </c>
       <c r="AH8">
-        <v>127.88</v>
+        <v>132.33</v>
       </c>
       <c r="AI8">
         <v>159.98</v>
@@ -1676,7 +1717,7 @@
         <v>48</v>
       </c>
       <c r="AK8">
-        <v>43.55</v>
+        <v>38.41</v>
       </c>
     </row>
   </sheetData>
@@ -1817,7 +1858,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:F62"/>
+  <dimension ref="A1:F63"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="16.7109375" customWidth="1"/>
@@ -1837,991 +1878,1046 @@
     </row>
     <row r="2" spans="1:6">
       <c r="A2" s="3" t="s">
+        <v>0</v>
+      </c>
+      <c r="B2" s="3" t="s">
         <v>50</v>
       </c>
-    </row>
-    <row r="5" spans="1:6">
-      <c r="A5" s="2" t="s">
+      <c r="C2" s="3" t="s">
         <v>51</v>
       </c>
-      <c r="B5" s="2"/>
-      <c r="C5" s="2"/>
-      <c r="D5" s="2"/>
-      <c r="E5" s="2"/>
+      <c r="D2" s="3" t="s">
+        <v>52</v>
+      </c>
+      <c r="E2" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="F2" s="3" t="s">
+        <v>54</v>
+      </c>
+    </row>
+    <row r="3" spans="1:6">
+      <c r="A3" s="4" t="s">
+        <v>41</v>
+      </c>
+      <c r="B3" s="4" t="s">
+        <v>55</v>
+      </c>
+      <c r="C3" s="4" t="s">
+        <v>56</v>
+      </c>
+      <c r="D3" s="4" t="s">
+        <v>57</v>
+      </c>
+      <c r="E3" s="4" t="s">
+        <v>58</v>
+      </c>
+      <c r="F3" s="4" t="s">
+        <v>59</v>
+      </c>
+    </row>
+    <row r="4" spans="1:6">
+      <c r="A4" s="5" t="s">
+        <v>38</v>
+      </c>
+      <c r="B4" s="5" t="s">
+        <v>55</v>
+      </c>
+      <c r="C4" s="5" t="s">
+        <v>60</v>
+      </c>
+      <c r="D4" s="5" t="s">
+        <v>61</v>
+      </c>
+      <c r="E4" s="5" t="s">
+        <v>62</v>
+      </c>
+      <c r="F4" s="5" t="s">
+        <v>63</v>
+      </c>
     </row>
     <row r="6" spans="1:6">
-      <c r="A6" s="4" t="s">
-        <v>0</v>
-      </c>
-      <c r="B6" s="4" t="s">
-        <v>52</v>
-      </c>
-      <c r="C6" s="4" t="s">
-        <v>53</v>
-      </c>
-      <c r="D6" s="4" t="s">
-        <v>54</v>
-      </c>
-      <c r="E6" s="4" t="s">
-        <v>55</v>
-      </c>
+      <c r="A6" s="2" t="s">
+        <v>64</v>
+      </c>
+      <c r="B6" s="2"/>
+      <c r="C6" s="2"/>
+      <c r="D6" s="2"/>
+      <c r="E6" s="2"/>
     </row>
     <row r="7" spans="1:6">
       <c r="A7" s="3" t="s">
+        <v>0</v>
+      </c>
+      <c r="B7" s="3" t="s">
+        <v>65</v>
+      </c>
+      <c r="C7" s="3" t="s">
+        <v>66</v>
+      </c>
+      <c r="D7" s="3" t="s">
+        <v>67</v>
+      </c>
+      <c r="E7" s="3" t="s">
+        <v>68</v>
+      </c>
+    </row>
+    <row r="8" spans="1:6">
+      <c r="A8" s="6" t="s">
         <v>37</v>
       </c>
-      <c r="B7" s="3" t="s">
+      <c r="B8" s="6" t="s">
         <v>9</v>
       </c>
-      <c r="C7" s="5">
-        <v>-12.32</v>
-      </c>
-      <c r="D7" s="5">
+      <c r="C8" s="7">
         <v>-12.23</v>
       </c>
-      <c r="E7" s="6">
-        <v>0.09</v>
-      </c>
-    </row>
-    <row r="8" spans="1:6">
-      <c r="A8" s="3" t="s">
+      <c r="D8" s="7">
+        <v>-9.09</v>
+      </c>
+      <c r="E8" s="8">
+        <v>3.14</v>
+      </c>
+    </row>
+    <row r="9" spans="1:6">
+      <c r="A9" s="6" t="s">
         <v>38</v>
       </c>
-      <c r="B8" s="3" t="s">
+      <c r="B9" s="6" t="s">
         <v>9</v>
       </c>
-      <c r="C8" s="5">
-        <v>-3.09</v>
-      </c>
-      <c r="D8" s="5">
+      <c r="C9" s="7">
         <v>-0.09</v>
       </c>
-      <c r="E8" s="6">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="9" spans="1:6">
-      <c r="A9" s="3" t="s">
+      <c r="D9" s="7">
+        <v>-7.01</v>
+      </c>
+      <c r="E9" s="9">
+        <v>-6.92</v>
+      </c>
+    </row>
+    <row r="10" spans="1:6">
+      <c r="A10" s="6" t="s">
         <v>39</v>
       </c>
-      <c r="B9" s="3" t="s">
+      <c r="B10" s="6" t="s">
         <v>9</v>
       </c>
-      <c r="C9" s="5">
-        <v>-10.27</v>
-      </c>
-      <c r="D9" s="5">
+      <c r="C10" s="7">
         <v>-8.92</v>
       </c>
-      <c r="E9" s="6">
-        <v>1.35</v>
-      </c>
-    </row>
-    <row r="10" spans="1:6">
-      <c r="A10" s="3" t="s">
+      <c r="D10" s="7">
+        <v>-6.61</v>
+      </c>
+      <c r="E10" s="8">
+        <v>2.31</v>
+      </c>
+    </row>
+    <row r="11" spans="1:6">
+      <c r="A11" s="6" t="s">
         <v>40</v>
       </c>
-      <c r="B10" s="3" t="s">
+      <c r="B11" s="6" t="s">
         <v>9</v>
       </c>
-      <c r="C10" s="5">
-        <v>-9.52</v>
-      </c>
-      <c r="D10" s="5">
+      <c r="C11" s="7">
         <v>-10.02</v>
       </c>
-      <c r="E10" s="7">
-        <v>-0.5</v>
-      </c>
-    </row>
-    <row r="11" spans="1:6">
-      <c r="A11" s="3" t="s">
+      <c r="D11" s="7">
+        <v>-6.66</v>
+      </c>
+      <c r="E11" s="8">
+        <v>3.36</v>
+      </c>
+    </row>
+    <row r="12" spans="1:6">
+      <c r="A12" s="6" t="s">
         <v>41</v>
       </c>
-      <c r="B11" s="3" t="s">
+      <c r="B12" s="6" t="s">
         <v>9</v>
       </c>
-      <c r="C11" s="5">
-        <v>-1.67</v>
-      </c>
-      <c r="D11" s="5">
+      <c r="C12" s="7">
         <v>-3.23</v>
       </c>
-      <c r="E11" s="7">
-        <v>-1.56</v>
-      </c>
-    </row>
-    <row r="12" spans="1:6">
-      <c r="A12" s="3" t="s">
+      <c r="D12" s="7">
+        <v>1.13</v>
+      </c>
+      <c r="E12" s="8">
+        <v>4.36</v>
+      </c>
+    </row>
+    <row r="13" spans="1:6">
+      <c r="A13" s="6" t="s">
         <v>42</v>
       </c>
-      <c r="B12" s="3" t="s">
+      <c r="B13" s="6" t="s">
         <v>9</v>
       </c>
-      <c r="C12" s="5">
-        <v>-5.82</v>
-      </c>
-      <c r="D12" s="5">
+      <c r="C13" s="7">
         <v>-7.49</v>
       </c>
-      <c r="E12" s="7">
-        <v>-1.67</v>
-      </c>
-    </row>
-    <row r="13" spans="1:6">
-      <c r="A13" s="3" t="s">
+      <c r="D13" s="7">
+        <v>-4.35</v>
+      </c>
+      <c r="E13" s="8">
+        <v>3.14</v>
+      </c>
+    </row>
+    <row r="14" spans="1:6">
+      <c r="A14" s="6" t="s">
         <v>43</v>
       </c>
-      <c r="B13" s="3" t="s">
+      <c r="B14" s="6" t="s">
         <v>9</v>
       </c>
-      <c r="C13" s="5">
-        <v>23.82</v>
-      </c>
-      <c r="D13" s="5">
+      <c r="C14" s="7">
         <v>25.48</v>
       </c>
-      <c r="E13" s="6">
-        <v>1.66</v>
-      </c>
-    </row>
-    <row r="14" spans="1:6">
-      <c r="A14" s="3" t="s">
+      <c r="D14" s="7">
+        <v>25.61</v>
+      </c>
+      <c r="E14" s="8">
+        <v>0.13</v>
+      </c>
+    </row>
+    <row r="15" spans="1:6">
+      <c r="A15" s="6" t="s">
         <v>37</v>
       </c>
-      <c r="B14" s="3" t="s">
+      <c r="B15" s="6" t="s">
         <v>8</v>
       </c>
-      <c r="C14" s="5">
-        <v>3</v>
-      </c>
-      <c r="D14" s="5">
+      <c r="C15" s="7">
         <v>3.7</v>
       </c>
-      <c r="E14" s="6">
-        <v>0.7</v>
-      </c>
-    </row>
-    <row r="15" spans="1:6">
-      <c r="A15" s="3" t="s">
+      <c r="D15" s="7">
+        <v>7.76</v>
+      </c>
+      <c r="E15" s="8">
+        <v>4.06</v>
+      </c>
+    </row>
+    <row r="16" spans="1:6">
+      <c r="A16" s="6" t="s">
         <v>38</v>
       </c>
-      <c r="B15" s="3" t="s">
+      <c r="B16" s="6" t="s">
         <v>8</v>
       </c>
-      <c r="C15" s="5">
-        <v>2.99</v>
-      </c>
-      <c r="D15" s="5">
+      <c r="C16" s="7">
         <v>7.67</v>
       </c>
-      <c r="E15" s="6">
-        <v>4.68</v>
-      </c>
-    </row>
-    <row r="16" spans="1:6">
-      <c r="A16" s="3" t="s">
+      <c r="D16" s="7">
+        <v>-4.22</v>
+      </c>
+      <c r="E16" s="9">
+        <v>-11.89</v>
+      </c>
+    </row>
+    <row r="17" spans="1:5">
+      <c r="A17" s="6" t="s">
         <v>39</v>
       </c>
-      <c r="B16" s="3" t="s">
+      <c r="B17" s="6" t="s">
         <v>8</v>
       </c>
-      <c r="C16" s="5">
-        <v>0.93</v>
-      </c>
-      <c r="D16" s="5">
+      <c r="C17" s="7">
         <v>1.56</v>
       </c>
-      <c r="E16" s="6">
-        <v>0.63</v>
-      </c>
-    </row>
-    <row r="17" spans="1:5">
-      <c r="A17" s="3" t="s">
+      <c r="D17" s="7">
+        <v>5.74</v>
+      </c>
+      <c r="E17" s="8">
+        <v>4.18</v>
+      </c>
+    </row>
+    <row r="18" spans="1:5">
+      <c r="A18" s="6" t="s">
         <v>40</v>
       </c>
-      <c r="B17" s="3" t="s">
+      <c r="B18" s="6" t="s">
         <v>8</v>
       </c>
-      <c r="C17" s="5">
-        <v>0.19</v>
-      </c>
-      <c r="D17" s="5">
+      <c r="C18" s="7">
         <v>-1.24</v>
       </c>
-      <c r="E17" s="7">
-        <v>-1.43</v>
-      </c>
-    </row>
-    <row r="18" spans="1:5">
-      <c r="A18" s="3" t="s">
+      <c r="D18" s="7">
+        <v>1.41</v>
+      </c>
+      <c r="E18" s="8">
+        <v>2.65</v>
+      </c>
+    </row>
+    <row r="19" spans="1:5">
+      <c r="A19" s="6" t="s">
         <v>41</v>
       </c>
-      <c r="B18" s="3" t="s">
+      <c r="B19" s="6" t="s">
         <v>8</v>
       </c>
-      <c r="C18" s="5">
-        <v>1.96</v>
-      </c>
-      <c r="D18" s="5">
+      <c r="C19" s="7">
         <v>1.05</v>
       </c>
-      <c r="E18" s="7">
-        <v>-0.91</v>
-      </c>
-    </row>
-    <row r="19" spans="1:5">
-      <c r="A19" s="3" t="s">
+      <c r="D19" s="7">
+        <v>5.9</v>
+      </c>
+      <c r="E19" s="8">
+        <v>4.85</v>
+      </c>
+    </row>
+    <row r="20" spans="1:5">
+      <c r="A20" s="6" t="s">
         <v>42</v>
       </c>
-      <c r="B19" s="3" t="s">
+      <c r="B20" s="6" t="s">
         <v>8</v>
       </c>
-      <c r="C19" s="5">
-        <v>2.04</v>
-      </c>
-      <c r="D19" s="5">
+      <c r="C20" s="7">
         <v>-0.71</v>
       </c>
-      <c r="E19" s="7">
-        <v>-2.75</v>
-      </c>
-    </row>
-    <row r="20" spans="1:5">
-      <c r="A20" s="3" t="s">
+      <c r="D20" s="7">
+        <v>0.97</v>
+      </c>
+      <c r="E20" s="8">
+        <v>1.68</v>
+      </c>
+    </row>
+    <row r="21" spans="1:5">
+      <c r="A21" s="6" t="s">
         <v>43</v>
       </c>
-      <c r="B20" s="3" t="s">
+      <c r="B21" s="6" t="s">
         <v>8</v>
       </c>
-      <c r="C20" s="5">
-        <v>-2.77</v>
-      </c>
-      <c r="D20" s="5">
+      <c r="C21" s="7">
         <v>-5.86</v>
       </c>
-      <c r="E20" s="7">
-        <v>-3.09</v>
-      </c>
-    </row>
-    <row r="21" spans="1:5">
-      <c r="A21" s="3" t="s">
+      <c r="D21" s="7">
+        <v>-2.26</v>
+      </c>
+      <c r="E21" s="8">
+        <v>3.6</v>
+      </c>
+    </row>
+    <row r="22" spans="1:5">
+      <c r="A22" s="6" t="s">
         <v>37</v>
       </c>
-      <c r="B21" s="3" t="s">
+      <c r="B22" s="6" t="s">
         <v>11</v>
       </c>
-      <c r="C21" s="5">
-        <v>19.01</v>
-      </c>
-      <c r="D21" s="5">
+      <c r="C22" s="7">
         <v>17.98</v>
       </c>
-      <c r="E21" s="7">
-        <v>-1.03</v>
-      </c>
-    </row>
-    <row r="22" spans="1:5">
-      <c r="A22" s="3" t="s">
+      <c r="D22" s="7">
+        <v>17.71</v>
+      </c>
+      <c r="E22" s="9">
+        <v>-0.27</v>
+      </c>
+    </row>
+    <row r="23" spans="1:5">
+      <c r="A23" s="6" t="s">
         <v>38</v>
       </c>
-      <c r="B22" s="3" t="s">
+      <c r="B23" s="6" t="s">
         <v>11</v>
       </c>
-      <c r="C22" s="5">
-        <v>106.14</v>
-      </c>
-      <c r="D22" s="5">
+      <c r="C23" s="7">
         <v>109.99</v>
       </c>
-      <c r="E22" s="6">
-        <v>3.85</v>
-      </c>
-    </row>
-    <row r="23" spans="1:5">
-      <c r="A23" s="3" t="s">
+      <c r="D23" s="7">
+        <v>77.38</v>
+      </c>
+      <c r="E23" s="9">
+        <v>-32.61</v>
+      </c>
+    </row>
+    <row r="24" spans="1:5">
+      <c r="A24" s="6" t="s">
         <v>39</v>
       </c>
-      <c r="B23" s="3" t="s">
+      <c r="B24" s="6" t="s">
         <v>11</v>
       </c>
-      <c r="C23" s="5">
-        <v>-43.33</v>
-      </c>
-      <c r="D23" s="5">
+      <c r="C24" s="7">
         <v>-43.26</v>
       </c>
-      <c r="E23" s="6">
-        <v>0.07000000000000001</v>
-      </c>
-    </row>
-    <row r="24" spans="1:5">
-      <c r="A24" s="3" t="s">
+      <c r="D24" s="7">
+        <v>-43.53</v>
+      </c>
+      <c r="E24" s="9">
+        <v>-0.27</v>
+      </c>
+    </row>
+    <row r="25" spans="1:5">
+      <c r="A25" s="6" t="s">
         <v>40</v>
       </c>
-      <c r="B24" s="3" t="s">
+      <c r="B25" s="6" t="s">
         <v>11</v>
       </c>
-      <c r="C24" s="5">
-        <v>-12.81</v>
-      </c>
-      <c r="D24" s="5">
+      <c r="C25" s="7">
         <v>-14.54</v>
       </c>
-      <c r="E24" s="7">
-        <v>-1.73</v>
-      </c>
-    </row>
-    <row r="25" spans="1:5">
-      <c r="A25" s="3" t="s">
+      <c r="D25" s="7">
+        <v>-13.59</v>
+      </c>
+      <c r="E25" s="8">
+        <v>0.95</v>
+      </c>
+    </row>
+    <row r="26" spans="1:5">
+      <c r="A26" s="6" t="s">
         <v>41</v>
       </c>
-      <c r="B25" s="3" t="s">
+      <c r="B26" s="6" t="s">
         <v>11</v>
       </c>
-      <c r="C25" s="5">
-        <v>-10.63</v>
-      </c>
-      <c r="D25" s="5">
+      <c r="C26" s="7">
         <v>-9.529999999999999</v>
       </c>
-      <c r="E25" s="6">
-        <v>1.1</v>
-      </c>
-    </row>
-    <row r="26" spans="1:5">
-      <c r="A26" s="3" t="s">
+      <c r="D26" s="7">
+        <v>-7.03</v>
+      </c>
+      <c r="E26" s="8">
+        <v>2.5</v>
+      </c>
+    </row>
+    <row r="27" spans="1:5">
+      <c r="A27" s="6" t="s">
         <v>42</v>
       </c>
-      <c r="B26" s="3" t="s">
+      <c r="B27" s="6" t="s">
         <v>11</v>
       </c>
-      <c r="C26" s="5">
-        <v>-3.95</v>
-      </c>
-      <c r="D26" s="5">
+      <c r="C27" s="7">
         <v>-6.55</v>
       </c>
-      <c r="E26" s="7">
-        <v>-2.6</v>
-      </c>
-    </row>
-    <row r="27" spans="1:5">
-      <c r="A27" s="3" t="s">
+      <c r="D27" s="7">
+        <v>-5.72</v>
+      </c>
+      <c r="E27" s="8">
+        <v>0.83</v>
+      </c>
+    </row>
+    <row r="28" spans="1:5">
+      <c r="A28" s="6" t="s">
         <v>43</v>
       </c>
-      <c r="B27" s="3" t="s">
+      <c r="B28" s="6" t="s">
         <v>11</v>
       </c>
-      <c r="C27" s="5">
-        <v>33.12</v>
-      </c>
-      <c r="D27" s="5">
+      <c r="C28" s="7">
         <v>29.65</v>
       </c>
-      <c r="E27" s="7">
-        <v>-3.47</v>
-      </c>
-    </row>
-    <row r="28" spans="1:5">
-      <c r="A28" s="3" t="s">
+      <c r="D28" s="7">
+        <v>28.89</v>
+      </c>
+      <c r="E28" s="9">
+        <v>-0.76</v>
+      </c>
+    </row>
+    <row r="29" spans="1:5">
+      <c r="A29" s="6" t="s">
         <v>37</v>
       </c>
-      <c r="B28" s="3" t="s">
+      <c r="B29" s="6" t="s">
         <v>10</v>
       </c>
-      <c r="C28" s="5">
-        <v>1.5</v>
-      </c>
-      <c r="D28" s="5">
+      <c r="C29" s="7">
         <v>-0.71</v>
       </c>
-      <c r="E28" s="7">
-        <v>-2.21</v>
-      </c>
-    </row>
-    <row r="29" spans="1:5">
-      <c r="A29" s="3" t="s">
+      <c r="D29" s="7">
+        <v>0.52</v>
+      </c>
+      <c r="E29" s="8">
+        <v>1.23</v>
+      </c>
+    </row>
+    <row r="30" spans="1:5">
+      <c r="A30" s="6" t="s">
         <v>38</v>
       </c>
-      <c r="B29" s="3" t="s">
+      <c r="B30" s="6" t="s">
         <v>10</v>
       </c>
-      <c r="C29" s="5">
-        <v>-13.93</v>
-      </c>
-      <c r="D29" s="5">
+      <c r="C30" s="7">
         <v>-8.51</v>
       </c>
-      <c r="E29" s="6">
-        <v>5.42</v>
-      </c>
-    </row>
-    <row r="30" spans="1:5">
-      <c r="A30" s="3" t="s">
+      <c r="D30" s="7">
+        <v>-15.39</v>
+      </c>
+      <c r="E30" s="9">
+        <v>-6.88</v>
+      </c>
+    </row>
+    <row r="31" spans="1:5">
+      <c r="A31" s="6" t="s">
         <v>39</v>
       </c>
-      <c r="B30" s="3" t="s">
+      <c r="B31" s="6" t="s">
         <v>10</v>
       </c>
-      <c r="C30" s="5">
-        <v>-7.87</v>
-      </c>
-      <c r="D30" s="5">
+      <c r="C31" s="7">
         <v>-7.47</v>
       </c>
-      <c r="E30" s="6">
-        <v>0.4</v>
-      </c>
-    </row>
-    <row r="31" spans="1:5">
-      <c r="A31" s="3" t="s">
+      <c r="D31" s="7">
+        <v>-8.69</v>
+      </c>
+      <c r="E31" s="9">
+        <v>-1.22</v>
+      </c>
+    </row>
+    <row r="32" spans="1:5">
+      <c r="A32" s="6" t="s">
         <v>40</v>
       </c>
-      <c r="B31" s="3" t="s">
+      <c r="B32" s="6" t="s">
         <v>10</v>
       </c>
-      <c r="C31" s="5">
-        <v>-6.07</v>
-      </c>
-      <c r="D31" s="5">
+      <c r="C32" s="7">
         <v>-6.92</v>
       </c>
-      <c r="E31" s="7">
-        <v>-0.85</v>
-      </c>
-    </row>
-    <row r="32" spans="1:5">
-      <c r="A32" s="3" t="s">
+      <c r="D32" s="7">
+        <v>-5.8</v>
+      </c>
+      <c r="E32" s="8">
+        <v>1.12</v>
+      </c>
+    </row>
+    <row r="33" spans="1:5">
+      <c r="A33" s="6" t="s">
         <v>41</v>
       </c>
-      <c r="B32" s="3" t="s">
+      <c r="B33" s="6" t="s">
         <v>10</v>
       </c>
-      <c r="C32" s="5">
-        <v>3.07</v>
-      </c>
-      <c r="D32" s="5">
+      <c r="C33" s="7">
         <v>2.31</v>
       </c>
-      <c r="E32" s="7">
-        <v>-0.76</v>
-      </c>
-    </row>
-    <row r="33" spans="1:5">
-      <c r="A33" s="3" t="s">
+      <c r="D33" s="7">
+        <v>7.76</v>
+      </c>
+      <c r="E33" s="8">
+        <v>5.45</v>
+      </c>
+    </row>
+    <row r="34" spans="1:5">
+      <c r="A34" s="6" t="s">
         <v>42</v>
       </c>
-      <c r="B33" s="3" t="s">
+      <c r="B34" s="6" t="s">
         <v>10</v>
       </c>
-      <c r="C33" s="5">
-        <v>-2.37</v>
-      </c>
-      <c r="D33" s="5">
+      <c r="C34" s="7">
         <v>-6.3</v>
       </c>
-      <c r="E33" s="7">
-        <v>-3.93</v>
-      </c>
-    </row>
-    <row r="34" spans="1:5">
-      <c r="A34" s="3" t="s">
+      <c r="D34" s="7">
+        <v>-6.97</v>
+      </c>
+      <c r="E34" s="9">
+        <v>-0.67</v>
+      </c>
+    </row>
+    <row r="35" spans="1:5">
+      <c r="A35" s="6" t="s">
         <v>43</v>
       </c>
-      <c r="B34" s="3" t="s">
+      <c r="B35" s="6" t="s">
         <v>10</v>
       </c>
-      <c r="C34" s="5">
-        <v>29.12</v>
-      </c>
-      <c r="D34" s="5">
+      <c r="C35" s="7">
         <v>23.56</v>
       </c>
-      <c r="E34" s="7">
-        <v>-5.56</v>
-      </c>
-    </row>
-    <row r="35" spans="1:5">
-      <c r="A35" s="3" t="s">
+      <c r="D35" s="7">
+        <v>16.52</v>
+      </c>
+      <c r="E35" s="9">
+        <v>-7.04</v>
+      </c>
+    </row>
+    <row r="36" spans="1:5">
+      <c r="A36" s="6" t="s">
         <v>37</v>
       </c>
-      <c r="B35" s="3" t="s">
+      <c r="B36" s="6" t="s">
         <v>6</v>
       </c>
-      <c r="C35" s="5">
-        <v>-16.53</v>
-      </c>
-      <c r="D35" s="5">
+      <c r="C36" s="7">
         <v>-17.08</v>
       </c>
-      <c r="E35" s="7">
-        <v>-0.55</v>
-      </c>
-    </row>
-    <row r="36" spans="1:5">
-      <c r="A36" s="3" t="s">
+      <c r="D36" s="7">
+        <v>-15.99</v>
+      </c>
+      <c r="E36" s="8">
+        <v>1.09</v>
+      </c>
+    </row>
+    <row r="37" spans="1:5">
+      <c r="A37" s="6" t="s">
         <v>38</v>
       </c>
-      <c r="B36" s="3" t="s">
+      <c r="B37" s="6" t="s">
         <v>6</v>
       </c>
-      <c r="C36" s="5">
-        <v>-24.17</v>
-      </c>
-      <c r="D36" s="5">
+      <c r="C37" s="7">
         <v>-22.41</v>
       </c>
-      <c r="E36" s="6">
-        <v>1.76</v>
-      </c>
-    </row>
-    <row r="37" spans="1:5">
-      <c r="A37" s="3" t="s">
+      <c r="D37" s="7">
+        <v>-30.1</v>
+      </c>
+      <c r="E37" s="9">
+        <v>-7.69</v>
+      </c>
+    </row>
+    <row r="38" spans="1:5">
+      <c r="A38" s="6" t="s">
         <v>39</v>
       </c>
-      <c r="B37" s="3" t="s">
+      <c r="B38" s="6" t="s">
         <v>6</v>
       </c>
-      <c r="C37" s="5">
-        <v>-44.7</v>
-      </c>
-      <c r="D37" s="5">
+      <c r="C38" s="7">
         <v>-44.27</v>
       </c>
-      <c r="E37" s="6">
-        <v>0.43</v>
-      </c>
-    </row>
-    <row r="38" spans="1:5">
-      <c r="A38" s="3" t="s">
+      <c r="D38" s="7">
+        <v>-44.03</v>
+      </c>
+      <c r="E38" s="8">
+        <v>0.24</v>
+      </c>
+    </row>
+    <row r="39" spans="1:5">
+      <c r="A39" s="6" t="s">
         <v>40</v>
       </c>
-      <c r="B38" s="3" t="s">
+      <c r="B39" s="6" t="s">
         <v>6</v>
       </c>
-      <c r="C38" s="5">
-        <v>-19.34</v>
-      </c>
-      <c r="D38" s="5">
+      <c r="C39" s="7">
         <v>-20.9</v>
       </c>
-      <c r="E38" s="7">
-        <v>-1.56</v>
-      </c>
-    </row>
-    <row r="39" spans="1:5">
-      <c r="A39" s="3" t="s">
+      <c r="D39" s="7">
+        <v>-20.43</v>
+      </c>
+      <c r="E39" s="8">
+        <v>0.47</v>
+      </c>
+    </row>
+    <row r="40" spans="1:5">
+      <c r="A40" s="6" t="s">
         <v>41</v>
       </c>
-      <c r="B39" s="3" t="s">
+      <c r="B40" s="6" t="s">
         <v>6</v>
       </c>
-      <c r="C39" s="5">
-        <v>-17.77</v>
-      </c>
-      <c r="D39" s="5">
+      <c r="C40" s="7">
         <v>-18.03</v>
       </c>
-      <c r="E39" s="7">
-        <v>-0.26</v>
-      </c>
-    </row>
-    <row r="40" spans="1:5">
-      <c r="A40" s="3" t="s">
+      <c r="D40" s="7">
+        <v>-14.6</v>
+      </c>
+      <c r="E40" s="8">
+        <v>3.43</v>
+      </c>
+    </row>
+    <row r="41" spans="1:5">
+      <c r="A41" s="6" t="s">
         <v>42</v>
       </c>
-      <c r="B40" s="3" t="s">
+      <c r="B41" s="6" t="s">
         <v>6</v>
       </c>
-      <c r="C40" s="5">
-        <v>-15.19</v>
-      </c>
-      <c r="D40" s="5">
+      <c r="C41" s="7">
         <v>-17.41</v>
       </c>
-      <c r="E40" s="7">
-        <v>-2.22</v>
-      </c>
-    </row>
-    <row r="41" spans="1:5">
-      <c r="A41" s="3" t="s">
+      <c r="D41" s="7">
+        <v>-16.7</v>
+      </c>
+      <c r="E41" s="8">
+        <v>0.71</v>
+      </c>
+    </row>
+    <row r="42" spans="1:5">
+      <c r="A42" s="6" t="s">
         <v>43</v>
       </c>
-      <c r="B41" s="3" t="s">
+      <c r="B42" s="6" t="s">
         <v>6</v>
       </c>
-      <c r="C41" s="5">
-        <v>-5.05</v>
-      </c>
-      <c r="D41" s="5">
+      <c r="C42" s="7">
         <v>-5.86</v>
       </c>
-      <c r="E41" s="7">
-        <v>-0.8100000000000001</v>
-      </c>
-    </row>
-    <row r="42" spans="1:5">
-      <c r="A42" s="3" t="s">
+      <c r="D42" s="7">
+        <v>-8.369999999999999</v>
+      </c>
+      <c r="E42" s="9">
+        <v>-2.51</v>
+      </c>
+    </row>
+    <row r="43" spans="1:5">
+      <c r="A43" s="6" t="s">
         <v>37</v>
       </c>
-      <c r="B42" s="3" t="s">
+      <c r="B43" s="6" t="s">
         <v>2</v>
       </c>
-      <c r="C42" s="5">
-        <v>10318</v>
-      </c>
-      <c r="D42" s="5">
+      <c r="C43" s="7">
         <v>10250</v>
       </c>
-      <c r="E42" s="7">
-        <v>-68</v>
-      </c>
-    </row>
-    <row r="43" spans="1:5">
-      <c r="A43" s="3" t="s">
+      <c r="D43" s="7">
+        <v>10385</v>
+      </c>
+      <c r="E43" s="8">
+        <v>135</v>
+      </c>
+    </row>
+    <row r="44" spans="1:5">
+      <c r="A44" s="6" t="s">
         <v>38</v>
       </c>
-      <c r="B43" s="3" t="s">
+      <c r="B44" s="6" t="s">
         <v>2</v>
       </c>
-      <c r="C43" s="5">
-        <v>508.25</v>
-      </c>
-      <c r="D43" s="5">
+      <c r="C44" s="7">
         <v>520.05</v>
       </c>
-      <c r="E43" s="6">
-        <v>11.8</v>
-      </c>
-    </row>
-    <row r="44" spans="1:5">
-      <c r="A44" s="3" t="s">
+      <c r="D44" s="7">
+        <v>468.5</v>
+      </c>
+      <c r="E44" s="9">
+        <v>-51.55</v>
+      </c>
+    </row>
+    <row r="45" spans="1:5">
+      <c r="A45" s="6" t="s">
         <v>39</v>
       </c>
-      <c r="B44" s="3" t="s">
+      <c r="B45" s="6" t="s">
         <v>2</v>
       </c>
-      <c r="C44" s="5">
-        <v>303.05</v>
-      </c>
-      <c r="D44" s="5">
+      <c r="C45" s="7">
         <v>305.4</v>
       </c>
-      <c r="E44" s="6">
-        <v>2.35</v>
-      </c>
-    </row>
-    <row r="45" spans="1:5">
-      <c r="A45" s="3" t="s">
+      <c r="D45" s="7">
+        <v>306.7</v>
+      </c>
+      <c r="E45" s="8">
+        <v>1.3</v>
+      </c>
+    </row>
+    <row r="46" spans="1:5">
+      <c r="A46" s="6" t="s">
         <v>40</v>
       </c>
-      <c r="B45" s="3" t="s">
+      <c r="B46" s="6" t="s">
         <v>2</v>
       </c>
-      <c r="C45" s="5">
-        <v>1755.7</v>
-      </c>
-      <c r="D45" s="5">
+      <c r="C46" s="7">
         <v>1721.7</v>
       </c>
-      <c r="E45" s="7">
-        <v>-34</v>
-      </c>
-    </row>
-    <row r="46" spans="1:5">
-      <c r="A46" s="3" t="s">
+      <c r="D46" s="7">
+        <v>1732</v>
+      </c>
+      <c r="E46" s="8">
+        <v>10.3</v>
+      </c>
+    </row>
+    <row r="47" spans="1:5">
+      <c r="A47" s="6" t="s">
         <v>41</v>
       </c>
-      <c r="B46" s="3" t="s">
+      <c r="B47" s="6" t="s">
         <v>2</v>
       </c>
-      <c r="C46" s="5">
-        <v>10808</v>
-      </c>
-      <c r="D46" s="5">
+      <c r="C47" s="7">
         <v>10774</v>
       </c>
-      <c r="E46" s="7">
-        <v>-34</v>
-      </c>
-    </row>
-    <row r="47" spans="1:5">
-      <c r="A47" s="3" t="s">
+      <c r="D47" s="7">
+        <v>11225</v>
+      </c>
+      <c r="E47" s="8">
+        <v>451</v>
+      </c>
+    </row>
+    <row r="48" spans="1:5">
+      <c r="A48" s="6" t="s">
         <v>42</v>
       </c>
-      <c r="B47" s="3" t="s">
+      <c r="B48" s="6" t="s">
         <v>2</v>
       </c>
-      <c r="C47" s="5">
-        <v>982.75</v>
-      </c>
-      <c r="D47" s="5">
+      <c r="C48" s="7">
         <v>957</v>
       </c>
-      <c r="E47" s="7">
-        <v>-25.75</v>
-      </c>
-    </row>
-    <row r="48" spans="1:5">
-      <c r="A48" s="3" t="s">
+      <c r="D48" s="7">
+        <v>965.25</v>
+      </c>
+      <c r="E48" s="8">
+        <v>8.25</v>
+      </c>
+    </row>
+    <row r="49" spans="1:5">
+      <c r="A49" s="6" t="s">
         <v>43</v>
       </c>
-      <c r="B48" s="3" t="s">
+      <c r="B49" s="6" t="s">
         <v>2</v>
       </c>
-      <c r="C48" s="5">
-        <v>176.53</v>
-      </c>
-      <c r="D48" s="5">
+      <c r="C49" s="7">
         <v>175.02</v>
       </c>
-      <c r="E48" s="7">
-        <v>-1.51</v>
-      </c>
-    </row>
-    <row r="49" spans="1:5">
-      <c r="A49" s="3" t="s">
+      <c r="D49" s="7">
+        <v>170.35</v>
+      </c>
+      <c r="E49" s="9">
+        <v>-4.67</v>
+      </c>
+    </row>
+    <row r="50" spans="1:5">
+      <c r="A50" s="6" t="s">
         <v>37</v>
       </c>
-      <c r="B49" s="3" t="s">
+      <c r="B50" s="6" t="s">
         <v>24</v>
       </c>
-      <c r="C49" s="5">
-        <v>39.8</v>
-      </c>
-      <c r="D49" s="5">
+      <c r="C50" s="7">
         <v>38.63</v>
       </c>
-      <c r="E49" s="7">
-        <v>-1.17</v>
-      </c>
-    </row>
-    <row r="50" spans="1:5">
-      <c r="A50" s="3" t="s">
+      <c r="D50" s="7">
+        <v>42.27</v>
+      </c>
+      <c r="E50" s="8">
+        <v>3.64</v>
+      </c>
+    </row>
+    <row r="51" spans="1:5">
+      <c r="A51" s="6" t="s">
         <v>38</v>
       </c>
-      <c r="B50" s="3" t="s">
+      <c r="B51" s="6" t="s">
         <v>24</v>
       </c>
-      <c r="C50" s="5">
-        <v>53.14</v>
-      </c>
-      <c r="D50" s="5">
+      <c r="C51" s="7">
         <v>56.9</v>
       </c>
-      <c r="E50" s="6">
-        <v>3.76</v>
-      </c>
-    </row>
-    <row r="51" spans="1:5">
-      <c r="A51" s="3" t="s">
+      <c r="D51" s="7">
+        <v>41.31</v>
+      </c>
+      <c r="E51" s="9">
+        <v>-15.59</v>
+      </c>
+    </row>
+    <row r="52" spans="1:5">
+      <c r="A52" s="6" t="s">
         <v>39</v>
       </c>
-      <c r="B51" s="3" t="s">
+      <c r="B52" s="6" t="s">
         <v>24</v>
       </c>
-      <c r="C51" s="5">
-        <v>39.64</v>
-      </c>
-      <c r="D51" s="5">
+      <c r="C52" s="7">
         <v>42.08</v>
       </c>
-      <c r="E51" s="6">
-        <v>2.44</v>
-      </c>
-    </row>
-    <row r="52" spans="1:5">
-      <c r="A52" s="3" t="s">
+      <c r="D52" s="7">
+        <v>43.44</v>
+      </c>
+      <c r="E52" s="8">
+        <v>1.36</v>
+      </c>
+    </row>
+    <row r="53" spans="1:5">
+      <c r="A53" s="6" t="s">
         <v>40</v>
       </c>
-      <c r="B52" s="3" t="s">
+      <c r="B53" s="6" t="s">
         <v>24</v>
       </c>
-      <c r="C52" s="5">
-        <v>39.81</v>
-      </c>
-      <c r="D52" s="5">
+      <c r="C53" s="7">
         <v>35.23</v>
       </c>
-      <c r="E52" s="7">
-        <v>-4.58</v>
-      </c>
-    </row>
-    <row r="53" spans="1:5">
-      <c r="A53" s="3" t="s">
+      <c r="D53" s="7">
+        <v>37.57</v>
+      </c>
+      <c r="E53" s="8">
+        <v>2.34</v>
+      </c>
+    </row>
+    <row r="54" spans="1:5">
+      <c r="A54" s="6" t="s">
         <v>41</v>
       </c>
-      <c r="B53" s="3" t="s">
+      <c r="B54" s="6" t="s">
         <v>24</v>
       </c>
-      <c r="C53" s="5">
-        <v>47.07</v>
-      </c>
-      <c r="D53" s="5">
+      <c r="C54" s="7">
         <v>46.18</v>
       </c>
-      <c r="E53" s="7">
-        <v>-0.89</v>
-      </c>
-    </row>
-    <row r="54" spans="1:5">
-      <c r="A54" s="3" t="s">
+      <c r="D54" s="7">
+        <v>57.61</v>
+      </c>
+      <c r="E54" s="8">
+        <v>11.43</v>
+      </c>
+    </row>
+    <row r="55" spans="1:5">
+      <c r="A55" s="6" t="s">
         <v>42</v>
       </c>
-      <c r="B54" s="3" t="s">
+      <c r="B55" s="6" t="s">
         <v>24</v>
       </c>
-      <c r="C54" s="5">
-        <v>45.66</v>
-      </c>
-      <c r="D54" s="5">
+      <c r="C55" s="7">
         <v>39.73</v>
       </c>
-      <c r="E54" s="7">
-        <v>-5.93</v>
-      </c>
-    </row>
-    <row r="55" spans="1:5">
-      <c r="A55" s="3" t="s">
+      <c r="D55" s="7">
+        <v>42.31</v>
+      </c>
+      <c r="E55" s="8">
+        <v>2.58</v>
+      </c>
+    </row>
+    <row r="56" spans="1:5">
+      <c r="A56" s="6" t="s">
         <v>43</v>
       </c>
-      <c r="B55" s="3" t="s">
+      <c r="B56" s="6" t="s">
         <v>24</v>
       </c>
-      <c r="C55" s="5">
-        <v>64.45999999999999</v>
-      </c>
-      <c r="D55" s="5">
+      <c r="C56" s="7">
         <v>62.62</v>
       </c>
-      <c r="E55" s="7">
-        <v>-1.84</v>
-      </c>
-    </row>
-    <row r="56" spans="1:5">
-      <c r="A56" s="3" t="s">
+      <c r="D56" s="7">
+        <v>57.18</v>
+      </c>
+      <c r="E56" s="9">
+        <v>-5.44</v>
+      </c>
+    </row>
+    <row r="57" spans="1:5">
+      <c r="A57" s="6" t="s">
         <v>37</v>
       </c>
-      <c r="B56" s="3" t="s">
+      <c r="B57" s="6" t="s">
         <v>31</v>
       </c>
-      <c r="C56" s="5">
-        <v>14.9</v>
-      </c>
-      <c r="D56" s="5">
+      <c r="C57" s="7">
         <v>-22.12</v>
       </c>
-      <c r="E56" s="7">
-        <v>-37.02</v>
-      </c>
-    </row>
-    <row r="57" spans="1:5">
-      <c r="A57" s="3" t="s">
+      <c r="D57" s="7">
+        <v>-31.77</v>
+      </c>
+      <c r="E57" s="9">
+        <v>-9.65</v>
+      </c>
+    </row>
+    <row r="58" spans="1:5">
+      <c r="A58" s="6" t="s">
         <v>38</v>
       </c>
-      <c r="B57" s="3" t="s">
+      <c r="B58" s="6" t="s">
         <v>31</v>
       </c>
-      <c r="C57" s="5">
-        <v>-3.22</v>
-      </c>
-      <c r="D57" s="5">
+      <c r="C58" s="7">
         <v>87.65000000000001</v>
       </c>
-      <c r="E57" s="6">
-        <v>90.87</v>
-      </c>
-    </row>
-    <row r="58" spans="1:5">
-      <c r="A58" s="3" t="s">
+      <c r="D58" s="7">
+        <v>1243.02</v>
+      </c>
+      <c r="E58" s="8">
+        <v>1155.37</v>
+      </c>
+    </row>
+    <row r="59" spans="1:5">
+      <c r="A59" s="6" t="s">
         <v>39</v>
       </c>
-      <c r="B58" s="3" t="s">
+      <c r="B59" s="6" t="s">
         <v>31</v>
       </c>
-      <c r="C58" s="5">
-        <v>-24.33</v>
-      </c>
-      <c r="D58" s="5">
+      <c r="C59" s="7">
         <v>-65.81999999999999</v>
       </c>
-      <c r="E58" s="7">
-        <v>-41.49</v>
-      </c>
-    </row>
-    <row r="59" spans="1:5">
-      <c r="A59" s="3" t="s">
+      <c r="D59" s="7">
+        <v>8636.33</v>
+      </c>
+      <c r="E59" s="8">
+        <v>8702.15</v>
+      </c>
+    </row>
+    <row r="60" spans="1:5">
+      <c r="A60" s="6" t="s">
         <v>40</v>
       </c>
-      <c r="B59" s="3" t="s">
+      <c r="B60" s="6" t="s">
         <v>31</v>
       </c>
-      <c r="C59" s="5">
-        <v>84.88</v>
-      </c>
-      <c r="D59" s="5">
+      <c r="C60" s="7">
         <v>-1.12</v>
       </c>
-      <c r="E59" s="7">
-        <v>-86</v>
-      </c>
-    </row>
-    <row r="60" spans="1:5">
-      <c r="A60" s="3" t="s">
+      <c r="D60" s="7">
+        <v>7.06</v>
+      </c>
+      <c r="E60" s="8">
+        <v>8.18</v>
+      </c>
+    </row>
+    <row r="61" spans="1:5">
+      <c r="A61" s="6" t="s">
         <v>41</v>
       </c>
-      <c r="B60" s="3" t="s">
+      <c r="B61" s="6" t="s">
         <v>31</v>
       </c>
-      <c r="C60" s="5">
-        <v>-37.1</v>
-      </c>
-      <c r="D60" s="5">
+      <c r="C61" s="7">
         <v>-35.35</v>
       </c>
-      <c r="E60" s="6">
-        <v>1.75</v>
-      </c>
-    </row>
-    <row r="61" spans="1:5">
-      <c r="A61" s="3" t="s">
+      <c r="D61" s="7">
+        <v>98.14</v>
+      </c>
+      <c r="E61" s="8">
+        <v>133.49</v>
+      </c>
+    </row>
+    <row r="62" spans="1:5">
+      <c r="A62" s="6" t="s">
         <v>42</v>
       </c>
-      <c r="B61" s="3" t="s">
+      <c r="B62" s="6" t="s">
         <v>31</v>
       </c>
-      <c r="C61" s="5">
-        <v>7.47</v>
-      </c>
-      <c r="D61" s="5">
+      <c r="C62" s="7">
         <v>-0.9399999999999999</v>
       </c>
-      <c r="E61" s="7">
-        <v>-8.41</v>
-      </c>
-    </row>
-    <row r="62" spans="1:5">
-      <c r="A62" s="3" t="s">
+      <c r="D62" s="7">
+        <v>48.19</v>
+      </c>
+      <c r="E62" s="8">
+        <v>49.13</v>
+      </c>
+    </row>
+    <row r="63" spans="1:5">
+      <c r="A63" s="6" t="s">
         <v>43</v>
       </c>
-      <c r="B62" s="3" t="s">
+      <c r="B63" s="6" t="s">
         <v>31</v>
       </c>
-      <c r="C62" s="5">
-        <v>-56.03</v>
-      </c>
-      <c r="D62" s="5">
+      <c r="C63" s="7">
         <v>-84.72</v>
       </c>
-      <c r="E62" s="7">
-        <v>-28.69</v>
+      <c r="D63" s="7">
+        <v>-69.31999999999999</v>
+      </c>
+      <c r="E63" s="8">
+        <v>15.4</v>
       </c>
     </row>
   </sheetData>
   <mergeCells count="2">
     <mergeCell ref="A1:F1"/>
-    <mergeCell ref="A5:E5"/>
+    <mergeCell ref="A6:E6"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -2841,60 +2937,60 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:9" ht="28" customHeight="1">
-      <c r="A1" s="8" t="s">
+      <c r="A1" s="10" t="s">
         <v>1</v>
       </c>
-      <c r="B1" s="8" t="s">
-        <v>56</v>
-      </c>
-      <c r="C1" s="8" t="s">
+      <c r="B1" s="10" t="s">
+        <v>69</v>
+      </c>
+      <c r="C1" s="10" t="s">
+        <v>70</v>
+      </c>
+      <c r="D1" s="10" t="s">
+        <v>71</v>
+      </c>
+      <c r="E1" s="10" t="s">
+        <v>72</v>
+      </c>
+      <c r="F1" s="10" t="s">
+        <v>73</v>
+      </c>
+      <c r="G1" s="10" t="s">
+        <v>74</v>
+      </c>
+      <c r="H1" s="10" t="s">
+        <v>75</v>
+      </c>
+      <c r="I1" s="10" t="s">
+        <v>76</v>
+      </c>
+    </row>
+    <row r="2" spans="1:9">
+      <c r="A2" s="11" t="s">
+        <v>44</v>
+      </c>
+      <c r="B2" s="12">
+        <v>56.8</v>
+      </c>
+      <c r="C2" s="13">
+        <v>7</v>
+      </c>
+      <c r="D2" s="12">
+        <v>46</v>
+      </c>
+      <c r="E2" s="12">
+        <v>60</v>
+      </c>
+      <c r="F2" s="12">
+        <v>-1</v>
+      </c>
+      <c r="G2" s="12">
+        <v>-1.7</v>
+      </c>
+      <c r="H2" s="12">
         <v>57</v>
       </c>
-      <c r="D1" s="8" t="s">
-        <v>58</v>
-      </c>
-      <c r="E1" s="8" t="s">
-        <v>59</v>
-      </c>
-      <c r="F1" s="8" t="s">
-        <v>60</v>
-      </c>
-      <c r="G1" s="8" t="s">
-        <v>61</v>
-      </c>
-      <c r="H1" s="8" t="s">
-        <v>62</v>
-      </c>
-      <c r="I1" s="8" t="s">
-        <v>63</v>
-      </c>
-    </row>
-    <row r="2" spans="1:9">
-      <c r="A2" s="9" t="s">
-        <v>44</v>
-      </c>
-      <c r="B2" s="10">
-        <v>56.8</v>
-      </c>
-      <c r="C2" s="11">
-        <v>7</v>
-      </c>
-      <c r="D2" s="10">
-        <v>45.9</v>
-      </c>
-      <c r="E2" s="10">
-        <v>60</v>
-      </c>
-      <c r="F2" s="10">
-        <v>-2.4</v>
-      </c>
-      <c r="G2" s="10">
-        <v>-0.6</v>
-      </c>
-      <c r="H2" s="10">
-        <v>57</v>
-      </c>
-      <c r="I2" s="10">
+      <c r="I2" s="12">
         <v>10</v>
       </c>
     </row>
@@ -2996,49 +3092,49 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:7">
-      <c r="A1" s="12" t="s">
+      <c r="A1" s="14" t="s">
         <v>37</v>
       </c>
-      <c r="B1" s="12" t="s">
+      <c r="B1" s="14" t="s">
         <v>41</v>
       </c>
-      <c r="C1" s="12" t="s">
+      <c r="C1" s="14" t="s">
         <v>38</v>
       </c>
-      <c r="D1" s="12" t="s">
+      <c r="D1" s="14" t="s">
         <v>43</v>
       </c>
-      <c r="E1" s="12" t="s">
+      <c r="E1" s="14" t="s">
         <v>42</v>
       </c>
-      <c r="F1" s="12" t="s">
+      <c r="F1" s="14" t="s">
         <v>40</v>
       </c>
-      <c r="G1" s="12" t="s">
+      <c r="G1" s="14" t="s">
         <v>39</v>
       </c>
     </row>
     <row r="2" spans="1:7">
-      <c r="A2" s="13">
-        <v>0.2371</v>
-      </c>
-      <c r="B2" s="13">
-        <v>0.191</v>
-      </c>
-      <c r="C2" s="13">
-        <v>0.1688</v>
-      </c>
-      <c r="D2" s="13">
-        <v>0.0542</v>
-      </c>
-      <c r="E2" s="13">
-        <v>0.044</v>
-      </c>
-      <c r="F2" s="13">
-        <v>-0.0138</v>
-      </c>
-      <c r="G2" s="13">
-        <v>-0.2373</v>
+      <c r="A2" s="15">
+        <v>0.2439</v>
+      </c>
+      <c r="B2" s="15">
+        <v>0.1998</v>
+      </c>
+      <c r="C2" s="15">
+        <v>0.1487</v>
+      </c>
+      <c r="D2" s="15">
+        <v>0.0492</v>
+      </c>
+      <c r="E2" s="15">
+        <v>0.0459</v>
+      </c>
+      <c r="F2" s="15">
+        <v>-0.0146</v>
+      </c>
+      <c r="G2" s="15">
+        <v>-0.2391</v>
       </c>
     </row>
   </sheetData>

--- a/BAJAJ_GROUP_Technical_Metrics.xlsx
+++ b/BAJAJ_GROUP_Technical_Metrics.xlsx
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="270" uniqueCount="77">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="253" uniqueCount="64">
   <si>
     <t>Symbol</t>
   </si>
@@ -172,46 +172,7 @@
     <t>▶  SIGNAL EVENTS (vs Previous Run)</t>
   </si>
   <si>
-    <t>Signal</t>
-  </si>
-  <si>
-    <t>Change</t>
-  </si>
-  <si>
-    <t>Direction</t>
-  </si>
-  <si>
-    <t>Prev Value</t>
-  </si>
-  <si>
-    <t>Curr Value</t>
-  </si>
-  <si>
-    <t>RSI Momentum</t>
-  </si>
-  <si>
-    <t>46.2 → 57.6</t>
-  </si>
-  <si>
-    <t>🟢 BULLISH</t>
-  </si>
-  <si>
-    <t>46.2</t>
-  </si>
-  <si>
-    <t>57.6</t>
-  </si>
-  <si>
-    <t>56.9 → 41.3</t>
-  </si>
-  <si>
-    <t>🔴 BEARISH</t>
-  </si>
-  <si>
-    <t>56.9</t>
-  </si>
-  <si>
-    <t>41.3</t>
+    <t>No signal events detected since last run.</t>
   </si>
   <si>
     <t>▶  NUMERIC METRIC CHANGES (vs Previous Run)</t>
@@ -297,14 +258,14 @@
     </font>
     <font>
       <sz val="11"/>
-      <color rgb="FF006100"/>
+      <color rgb="FF9C0006"/>
       <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
     </font>
     <font>
       <sz val="11"/>
-      <color rgb="FF9C0006"/>
+      <color rgb="FF006100"/>
       <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
@@ -337,13 +298,13 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFC6EFCE"/>
+        <fgColor rgb="FFFFC7CE"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFFFC7CE"/>
+        <fgColor rgb="FFC6EFCE"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -413,16 +374,14 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="16">
+  <cellXfs count="14">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="2" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="3" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="5" fillId="6" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1"/>
     <xf numFmtId="165" fontId="4" fillId="5" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="165" fontId="5" fillId="6" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
@@ -937,10 +896,10 @@
         <v>44</v>
       </c>
       <c r="C2">
-        <v>10385</v>
+        <v>10405</v>
       </c>
       <c r="D2">
-        <v>1.32</v>
+        <v>0.19</v>
       </c>
       <c r="E2">
         <v>12361</v>
@@ -949,46 +908,46 @@
         <v>8599.48</v>
       </c>
       <c r="G2">
-        <v>-15.99</v>
+        <v>-15.82</v>
       </c>
       <c r="H2">
-        <v>20.76</v>
+        <v>21</v>
       </c>
       <c r="I2">
-        <v>7.76</v>
+        <v>6.41</v>
       </c>
       <c r="J2">
-        <v>-9.09</v>
+        <v>-10.25</v>
       </c>
       <c r="K2">
-        <v>0.52</v>
+        <v>-0.36</v>
       </c>
       <c r="L2">
-        <v>17.71</v>
+        <v>16.38</v>
       </c>
       <c r="M2">
-        <v>24.39</v>
+        <v>24.43</v>
       </c>
       <c r="N2">
         <v>71</v>
       </c>
       <c r="O2">
-        <v>71</v>
+        <v>69</v>
       </c>
       <c r="P2">
-        <v>10153</v>
+        <v>10278.4</v>
       </c>
       <c r="Q2">
-        <v>10635.35</v>
+        <v>10580.6</v>
       </c>
       <c r="R2">
-        <v>11323.26</v>
+        <v>11295.36</v>
       </c>
       <c r="S2">
-        <v>10191.39</v>
+        <v>10198.61</v>
       </c>
       <c r="T2">
-        <v>1.9</v>
+        <v>2.02</v>
       </c>
       <c r="U2" t="s">
         <v>45</v>
@@ -1003,34 +962,34 @@
         <v>2</v>
       </c>
       <c r="Y2">
-        <v>42.27</v>
+        <v>42.81</v>
       </c>
       <c r="Z2">
-        <v>-374.07</v>
+        <v>-339.51</v>
       </c>
       <c r="AA2">
-        <v>-377.69</v>
+        <v>-370.06</v>
       </c>
       <c r="AB2">
-        <v>3.63</v>
+        <v>30.55</v>
       </c>
       <c r="AC2">
-        <v>92.95999999999999</v>
+        <v>97.04000000000001</v>
       </c>
       <c r="AD2">
-        <v>75.2</v>
+        <v>89.38</v>
       </c>
       <c r="AE2">
-        <v>260.55</v>
+        <v>257.29</v>
       </c>
       <c r="AF2">
-        <v>-31.77</v>
+        <v>-39.09</v>
       </c>
       <c r="AG2">
-        <v>11949.74</v>
+        <v>11833.11</v>
       </c>
       <c r="AH2">
-        <v>9320.959999999999</v>
+        <v>9328.09</v>
       </c>
       <c r="AI2">
         <v>10503.51</v>
@@ -1039,7 +998,7 @@
         <v>47</v>
       </c>
       <c r="AK2">
-        <v>55.14</v>
+        <v>48.8</v>
       </c>
     </row>
     <row r="3" spans="1:37">
@@ -1050,10 +1009,10 @@
         <v>44</v>
       </c>
       <c r="C3">
-        <v>468.5</v>
+        <v>472</v>
       </c>
       <c r="D3">
-        <v>-9.91</v>
+        <v>0.75</v>
       </c>
       <c r="E3">
         <v>670.25</v>
@@ -1062,25 +1021,25 @@
         <v>247.45</v>
       </c>
       <c r="G3">
-        <v>-30.1</v>
+        <v>-29.58</v>
       </c>
       <c r="H3">
-        <v>89.33</v>
+        <v>90.75</v>
       </c>
       <c r="I3">
-        <v>-4.22</v>
+        <v>-6.89</v>
       </c>
       <c r="J3">
-        <v>-7.01</v>
+        <v>-5.23</v>
       </c>
       <c r="K3">
-        <v>-15.39</v>
+        <v>-10.21</v>
       </c>
       <c r="L3">
-        <v>77.38</v>
+        <v>77.61</v>
       </c>
       <c r="M3">
-        <v>14.87</v>
+        <v>15.04</v>
       </c>
       <c r="N3">
         <v>99</v>
@@ -1089,19 +1048,19 @@
         <v>87</v>
       </c>
       <c r="P3">
+        <v>492.24</v>
+      </c>
+      <c r="Q3">
+        <v>496.4</v>
+      </c>
+      <c r="R3">
         <v>499.23</v>
       </c>
-      <c r="Q3">
-        <v>497.92</v>
-      </c>
-      <c r="R3">
-        <v>500.4</v>
-      </c>
       <c r="S3">
-        <v>462.72</v>
+        <v>463.78</v>
       </c>
       <c r="T3">
-        <v>1.25</v>
+        <v>1.77</v>
       </c>
       <c r="U3" t="s">
         <v>45</v>
@@ -1116,34 +1075,34 @@
         <v>2</v>
       </c>
       <c r="Y3">
-        <v>41.31</v>
+        <v>42.46</v>
       </c>
       <c r="Z3">
-        <v>-3</v>
+        <v>-4.66</v>
       </c>
       <c r="AA3">
-        <v>-3.08</v>
+        <v>-3.39</v>
       </c>
       <c r="AB3">
-        <v>0.08</v>
+        <v>-1.26</v>
       </c>
       <c r="AC3">
-        <v>70.81</v>
+        <v>43.78</v>
       </c>
       <c r="AD3">
-        <v>81.42</v>
+        <v>67.09999999999999</v>
       </c>
       <c r="AE3">
-        <v>23.98</v>
+        <v>23.44</v>
       </c>
       <c r="AF3">
-        <v>1243.02</v>
+        <v>26.05</v>
       </c>
       <c r="AG3">
-        <v>524.71</v>
+        <v>525.47</v>
       </c>
       <c r="AH3">
-        <v>471.14</v>
+        <v>467.34</v>
       </c>
       <c r="AI3">
         <v>460.99</v>
@@ -1152,7 +1111,7 @@
         <v>48</v>
       </c>
       <c r="AK3">
-        <v>24.94</v>
+        <v>26.02</v>
       </c>
     </row>
     <row r="4" spans="1:37">
@@ -1163,10 +1122,10 @@
         <v>44</v>
       </c>
       <c r="C4">
-        <v>306.7</v>
+        <v>301.3</v>
       </c>
       <c r="D4">
-        <v>0.43</v>
+        <v>-1.76</v>
       </c>
       <c r="E4">
         <v>548</v>
@@ -1175,46 +1134,46 @@
         <v>290.05</v>
       </c>
       <c r="G4">
-        <v>-44.03</v>
+        <v>-45.02</v>
       </c>
       <c r="H4">
-        <v>5.74</v>
+        <v>3.88</v>
       </c>
       <c r="I4">
-        <v>5.74</v>
+        <v>1.11</v>
       </c>
       <c r="J4">
-        <v>-6.61</v>
+        <v>-6.59</v>
       </c>
       <c r="K4">
-        <v>-8.69</v>
+        <v>-9.1</v>
       </c>
       <c r="L4">
-        <v>-43.53</v>
+        <v>-44.71</v>
       </c>
       <c r="M4">
-        <v>-23.91</v>
+        <v>-24.17</v>
       </c>
       <c r="N4">
         <v>15</v>
       </c>
       <c r="O4">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="P4">
-        <v>302.4</v>
+        <v>303.06</v>
       </c>
       <c r="Q4">
-        <v>309.88</v>
+        <v>308.68</v>
       </c>
       <c r="R4">
-        <v>331.12</v>
+        <v>330.18</v>
       </c>
       <c r="S4">
-        <v>359.87</v>
+        <v>358.96</v>
       </c>
       <c r="T4">
-        <v>-14.78</v>
+        <v>-16.06</v>
       </c>
       <c r="U4" t="s">
         <v>45</v>
@@ -1229,34 +1188,34 @@
         <v>0</v>
       </c>
       <c r="Y4">
-        <v>43.44</v>
+        <v>39.3</v>
       </c>
       <c r="Z4">
-        <v>-8.08</v>
+        <v>-7.76</v>
       </c>
       <c r="AA4">
-        <v>-8.960000000000001</v>
+        <v>-8.720000000000001</v>
       </c>
       <c r="AB4">
-        <v>0.88</v>
+        <v>0.96</v>
       </c>
       <c r="AC4">
-        <v>89.86</v>
+        <v>92.59999999999999</v>
       </c>
       <c r="AD4">
-        <v>72.13</v>
+        <v>85.03</v>
       </c>
       <c r="AE4">
-        <v>11.64</v>
+        <v>11.58</v>
       </c>
       <c r="AF4">
-        <v>8636.33</v>
+        <v>-16.85</v>
       </c>
       <c r="AG4">
-        <v>333.46</v>
+        <v>331.38</v>
       </c>
       <c r="AH4">
-        <v>286.3</v>
+        <v>285.97</v>
       </c>
       <c r="AI4">
         <v>322.52</v>
@@ -1265,7 +1224,7 @@
         <v>47</v>
       </c>
       <c r="AK4">
-        <v>50.53</v>
+        <v>50.65</v>
       </c>
     </row>
     <row r="5" spans="1:37">
@@ -1276,10 +1235,10 @@
         <v>44</v>
       </c>
       <c r="C5">
-        <v>1732</v>
+        <v>1729</v>
       </c>
       <c r="D5">
-        <v>0.6</v>
+        <v>-0.17</v>
       </c>
       <c r="E5">
         <v>2176.6</v>
@@ -1288,46 +1247,46 @@
         <v>1631.8</v>
       </c>
       <c r="G5">
-        <v>-20.43</v>
+        <v>-20.56</v>
       </c>
       <c r="H5">
-        <v>6.14</v>
+        <v>5.96</v>
       </c>
       <c r="I5">
-        <v>1.41</v>
+        <v>-0.33</v>
       </c>
       <c r="J5">
-        <v>-6.66</v>
+        <v>-5.88</v>
       </c>
       <c r="K5">
-        <v>-5.8</v>
+        <v>-6.74</v>
       </c>
       <c r="L5">
-        <v>-13.59</v>
+        <v>-14.42</v>
       </c>
       <c r="M5">
-        <v>-1.46</v>
+        <v>-1.49</v>
       </c>
       <c r="N5">
         <v>29</v>
       </c>
       <c r="O5">
-        <v>45</v>
+        <v>42</v>
       </c>
       <c r="P5">
-        <v>1732.8</v>
+        <v>1731.66</v>
       </c>
       <c r="Q5">
-        <v>1767.09</v>
+        <v>1760.58</v>
       </c>
       <c r="R5">
-        <v>1900.61</v>
+        <v>1893.47</v>
       </c>
       <c r="S5">
-        <v>1871.04</v>
+        <v>1869.62</v>
       </c>
       <c r="T5">
-        <v>-7.43</v>
+        <v>-7.52</v>
       </c>
       <c r="U5" t="s">
         <v>45</v>
@@ -1342,34 +1301,34 @@
         <v>1</v>
       </c>
       <c r="Y5">
-        <v>37.57</v>
+        <v>37.15</v>
       </c>
       <c r="Z5">
-        <v>-47.65</v>
+        <v>-45.56</v>
       </c>
       <c r="AA5">
-        <v>-51.92</v>
+        <v>-50.64</v>
       </c>
       <c r="AB5">
-        <v>4.27</v>
+        <v>5.09</v>
       </c>
       <c r="AC5">
-        <v>84.98</v>
+        <v>79.12</v>
       </c>
       <c r="AD5">
-        <v>80.44</v>
+        <v>80.29000000000001</v>
       </c>
       <c r="AE5">
-        <v>38.49</v>
+        <v>38.22</v>
       </c>
       <c r="AF5">
-        <v>7.06</v>
+        <v>26.53</v>
       </c>
       <c r="AG5">
-        <v>1866.22</v>
+        <v>1850.96</v>
       </c>
       <c r="AH5">
-        <v>1667.96</v>
+        <v>1670.2</v>
       </c>
       <c r="AI5">
         <v>1825.61</v>
@@ -1378,7 +1337,7 @@
         <v>47</v>
       </c>
       <c r="AK5">
-        <v>55.59</v>
+        <v>53.7</v>
       </c>
     </row>
     <row r="6" spans="1:37">
@@ -1389,10 +1348,10 @@
         <v>44</v>
       </c>
       <c r="C6">
-        <v>11225</v>
+        <v>11198</v>
       </c>
       <c r="D6">
-        <v>4.19</v>
+        <v>-0.24</v>
       </c>
       <c r="E6">
         <v>13144</v>
@@ -1401,46 +1360,46 @@
         <v>8746</v>
       </c>
       <c r="G6">
-        <v>-14.6</v>
+        <v>-14.81</v>
       </c>
       <c r="H6">
-        <v>28.34</v>
+        <v>28.04</v>
       </c>
       <c r="I6">
-        <v>5.9</v>
+        <v>3.49</v>
       </c>
       <c r="J6">
-        <v>1.13</v>
+        <v>2.45</v>
       </c>
       <c r="K6">
-        <v>7.76</v>
+        <v>7.69</v>
       </c>
       <c r="L6">
-        <v>-7.03</v>
+        <v>-9.359999999999999</v>
       </c>
       <c r="M6">
-        <v>19.98</v>
+        <v>19.91</v>
       </c>
       <c r="N6">
         <v>57</v>
       </c>
       <c r="O6">
-        <v>64</v>
+        <v>62</v>
       </c>
       <c r="P6">
-        <v>10875.4</v>
+        <v>10951</v>
       </c>
       <c r="Q6">
-        <v>10900.85</v>
+        <v>10910.25</v>
       </c>
       <c r="R6">
-        <v>11136.82</v>
+        <v>11130.86</v>
       </c>
       <c r="S6">
-        <v>10659.74</v>
+        <v>10659.48</v>
       </c>
       <c r="T6">
-        <v>5.3</v>
+        <v>5.05</v>
       </c>
       <c r="U6" t="s">
         <v>45</v>
@@ -1455,34 +1414,34 @@
         <v>2</v>
       </c>
       <c r="Y6">
-        <v>57.61</v>
+        <v>56.84</v>
       </c>
       <c r="Z6">
-        <v>-65.92</v>
+        <v>-33.64</v>
       </c>
       <c r="AA6">
-        <v>-103.96</v>
+        <v>-89.89</v>
       </c>
       <c r="AB6">
-        <v>38.03</v>
+        <v>56.25</v>
       </c>
       <c r="AC6">
-        <v>78.98</v>
+        <v>95.2</v>
       </c>
       <c r="AD6">
-        <v>60.45</v>
+        <v>77.51000000000001</v>
       </c>
       <c r="AE6">
-        <v>271.28</v>
+        <v>268.76</v>
       </c>
       <c r="AF6">
-        <v>98.14</v>
+        <v>-37</v>
       </c>
       <c r="AG6">
-        <v>11442.32</v>
+        <v>11466.03</v>
       </c>
       <c r="AH6">
-        <v>10359.38</v>
+        <v>10354.47</v>
       </c>
       <c r="AI6">
         <v>11368.55</v>
@@ -1491,7 +1450,7 @@
         <v>47</v>
       </c>
       <c r="AK6">
-        <v>25.47</v>
+        <v>26.86</v>
       </c>
     </row>
     <row r="7" spans="1:37">
@@ -1502,10 +1461,10 @@
         <v>44</v>
       </c>
       <c r="C7">
-        <v>965.25</v>
+        <v>982.1</v>
       </c>
       <c r="D7">
-        <v>0.86</v>
+        <v>1.75</v>
       </c>
       <c r="E7">
         <v>1158.8</v>
@@ -1514,46 +1473,46 @@
         <v>801.55</v>
       </c>
       <c r="G7">
-        <v>-16.7</v>
+        <v>-15.25</v>
       </c>
       <c r="H7">
-        <v>20.42</v>
+        <v>22.53</v>
       </c>
       <c r="I7">
-        <v>0.97</v>
+        <v>2.3</v>
       </c>
       <c r="J7">
-        <v>-4.35</v>
+        <v>-2.4</v>
       </c>
       <c r="K7">
-        <v>-6.97</v>
+        <v>-7.02</v>
       </c>
       <c r="L7">
-        <v>-5.72</v>
+        <v>-5.27</v>
       </c>
       <c r="M7">
-        <v>4.59</v>
+        <v>4.95</v>
       </c>
       <c r="N7">
         <v>43</v>
       </c>
       <c r="O7">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="P7">
-        <v>964.45</v>
+        <v>968.87</v>
       </c>
       <c r="Q7">
-        <v>982.46</v>
+        <v>980.8099999999999</v>
       </c>
       <c r="R7">
-        <v>1037.75</v>
+        <v>1034.22</v>
       </c>
       <c r="S7">
-        <v>974.4400000000001</v>
+        <v>974.36</v>
       </c>
       <c r="T7">
-        <v>-0.9399999999999999</v>
+        <v>0.79</v>
       </c>
       <c r="U7" t="s">
         <v>45</v>
@@ -1565,37 +1524,37 @@
         <v>45</v>
       </c>
       <c r="X7">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="Y7">
-        <v>42.31</v>
+        <v>47.29</v>
       </c>
       <c r="Z7">
-        <v>-20.88</v>
+        <v>-18.41</v>
       </c>
       <c r="AA7">
-        <v>-22.72</v>
+        <v>-21.86</v>
       </c>
       <c r="AB7">
-        <v>1.84</v>
+        <v>3.45</v>
       </c>
       <c r="AC7">
-        <v>70.5</v>
+        <v>77.11</v>
       </c>
       <c r="AD7">
-        <v>57.56</v>
+        <v>67.55</v>
       </c>
       <c r="AE7">
-        <v>25.84</v>
+        <v>25.68</v>
       </c>
       <c r="AF7">
-        <v>48.19</v>
+        <v>3.74</v>
       </c>
       <c r="AG7">
-        <v>1040.4</v>
+        <v>1036.7</v>
       </c>
       <c r="AH7">
-        <v>924.51</v>
+        <v>924.9299999999999</v>
       </c>
       <c r="AI7">
         <v>1020.6</v>
@@ -1604,7 +1563,7 @@
         <v>47</v>
       </c>
       <c r="AK7">
-        <v>20.51</v>
+        <v>19.45</v>
       </c>
     </row>
     <row r="8" spans="1:37">
@@ -1615,10 +1574,10 @@
         <v>44</v>
       </c>
       <c r="C8">
-        <v>170.35</v>
+        <v>171.99</v>
       </c>
       <c r="D8">
-        <v>-2.67</v>
+        <v>0.96</v>
       </c>
       <c r="E8">
         <v>185.92</v>
@@ -1627,46 +1586,46 @@
         <v>115.96</v>
       </c>
       <c r="G8">
-        <v>-8.369999999999999</v>
+        <v>-7.49</v>
       </c>
       <c r="H8">
-        <v>46.9</v>
+        <v>48.32</v>
       </c>
       <c r="I8">
-        <v>-2.26</v>
+        <v>-2.27</v>
       </c>
       <c r="J8">
-        <v>25.61</v>
+        <v>27.5</v>
       </c>
       <c r="K8">
-        <v>16.52</v>
+        <v>18.05</v>
       </c>
       <c r="L8">
-        <v>28.89</v>
+        <v>32.62</v>
       </c>
       <c r="M8">
-        <v>4.92</v>
+        <v>5.12</v>
       </c>
       <c r="N8">
         <v>85</v>
       </c>
       <c r="O8">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="P8">
-        <v>175.09</v>
+        <v>174.29</v>
       </c>
       <c r="Q8">
-        <v>166.08</v>
+        <v>167.97</v>
       </c>
       <c r="R8">
-        <v>148.78</v>
+        <v>149.38</v>
       </c>
       <c r="S8">
-        <v>137.15</v>
+        <v>137.35</v>
       </c>
       <c r="T8">
-        <v>24.2</v>
+        <v>25.22</v>
       </c>
       <c r="U8" t="s">
         <v>46</v>
@@ -1681,34 +1640,34 @@
         <v>3</v>
       </c>
       <c r="Y8">
-        <v>57.18</v>
+        <v>58.54</v>
       </c>
       <c r="Z8">
-        <v>8.890000000000001</v>
+        <v>8.18</v>
       </c>
       <c r="AA8">
-        <v>9.65</v>
+        <v>9.359999999999999</v>
       </c>
       <c r="AB8">
-        <v>-0.76</v>
+        <v>-1.18</v>
       </c>
       <c r="AC8">
-        <v>1.17</v>
+        <v>1.68</v>
       </c>
       <c r="AD8">
-        <v>12.15</v>
+        <v>4.26</v>
       </c>
       <c r="AE8">
-        <v>7.9</v>
+        <v>7.71</v>
       </c>
       <c r="AF8">
-        <v>-69.31999999999999</v>
+        <v>-80.87</v>
       </c>
       <c r="AG8">
-        <v>199.83</v>
+        <v>198.26</v>
       </c>
       <c r="AH8">
-        <v>132.33</v>
+        <v>137.68</v>
       </c>
       <c r="AI8">
         <v>159.98</v>
@@ -1717,7 +1676,7 @@
         <v>48</v>
       </c>
       <c r="AK8">
-        <v>38.41</v>
+        <v>33.87</v>
       </c>
     </row>
   </sheetData>
@@ -1858,7 +1817,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:F63"/>
+  <dimension ref="A1:F62"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="16.7109375" customWidth="1"/>
@@ -1878,1046 +1837,991 @@
     </row>
     <row r="2" spans="1:6">
       <c r="A2" s="3" t="s">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="5" spans="1:6">
+      <c r="A5" s="2" t="s">
+        <v>51</v>
+      </c>
+      <c r="B5" s="2"/>
+      <c r="C5" s="2"/>
+      <c r="D5" s="2"/>
+      <c r="E5" s="2"/>
+    </row>
+    <row r="6" spans="1:6">
+      <c r="A6" s="4" t="s">
         <v>0</v>
       </c>
-      <c r="B2" s="3" t="s">
-        <v>50</v>
-      </c>
-      <c r="C2" s="3" t="s">
-        <v>51</v>
-      </c>
-      <c r="D2" s="3" t="s">
+      <c r="B6" s="4" t="s">
         <v>52</v>
       </c>
-      <c r="E2" s="3" t="s">
+      <c r="C6" s="4" t="s">
         <v>53</v>
       </c>
-      <c r="F2" s="3" t="s">
+      <c r="D6" s="4" t="s">
         <v>54</v>
       </c>
-    </row>
-    <row r="3" spans="1:6">
-      <c r="A3" s="4" t="s">
-        <v>41</v>
-      </c>
-      <c r="B3" s="4" t="s">
+      <c r="E6" s="4" t="s">
         <v>55</v>
       </c>
-      <c r="C3" s="4" t="s">
-        <v>56</v>
-      </c>
-      <c r="D3" s="4" t="s">
-        <v>57</v>
-      </c>
-      <c r="E3" s="4" t="s">
-        <v>58</v>
-      </c>
-      <c r="F3" s="4" t="s">
-        <v>59</v>
-      </c>
-    </row>
-    <row r="4" spans="1:6">
-      <c r="A4" s="5" t="s">
-        <v>38</v>
-      </c>
-      <c r="B4" s="5" t="s">
-        <v>55</v>
-      </c>
-      <c r="C4" s="5" t="s">
-        <v>60</v>
-      </c>
-      <c r="D4" s="5" t="s">
-        <v>61</v>
-      </c>
-      <c r="E4" s="5" t="s">
-        <v>62</v>
-      </c>
-      <c r="F4" s="5" t="s">
-        <v>63</v>
-      </c>
-    </row>
-    <row r="6" spans="1:6">
-      <c r="A6" s="2" t="s">
-        <v>64</v>
-      </c>
-      <c r="B6" s="2"/>
-      <c r="C6" s="2"/>
-      <c r="D6" s="2"/>
-      <c r="E6" s="2"/>
     </row>
     <row r="7" spans="1:6">
       <c r="A7" s="3" t="s">
-        <v>0</v>
+        <v>37</v>
       </c>
       <c r="B7" s="3" t="s">
-        <v>65</v>
-      </c>
-      <c r="C7" s="3" t="s">
-        <v>66</v>
-      </c>
-      <c r="D7" s="3" t="s">
-        <v>67</v>
-      </c>
-      <c r="E7" s="3" t="s">
-        <v>68</v>
+        <v>9</v>
+      </c>
+      <c r="C7" s="5">
+        <v>-9.09</v>
+      </c>
+      <c r="D7" s="5">
+        <v>-10.25</v>
+      </c>
+      <c r="E7" s="6">
+        <v>-1.16</v>
       </c>
     </row>
     <row r="8" spans="1:6">
-      <c r="A8" s="6" t="s">
+      <c r="A8" s="3" t="s">
+        <v>38</v>
+      </c>
+      <c r="B8" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="C8" s="5">
+        <v>-7.01</v>
+      </c>
+      <c r="D8" s="5">
+        <v>-5.23</v>
+      </c>
+      <c r="E8" s="7">
+        <v>1.78</v>
+      </c>
+    </row>
+    <row r="9" spans="1:6">
+      <c r="A9" s="3" t="s">
+        <v>39</v>
+      </c>
+      <c r="B9" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="C9" s="5">
+        <v>-6.61</v>
+      </c>
+      <c r="D9" s="5">
+        <v>-6.59</v>
+      </c>
+      <c r="E9" s="7">
+        <v>0.02</v>
+      </c>
+    </row>
+    <row r="10" spans="1:6">
+      <c r="A10" s="3" t="s">
+        <v>40</v>
+      </c>
+      <c r="B10" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="C10" s="5">
+        <v>-6.66</v>
+      </c>
+      <c r="D10" s="5">
+        <v>-5.88</v>
+      </c>
+      <c r="E10" s="7">
+        <v>0.78</v>
+      </c>
+    </row>
+    <row r="11" spans="1:6">
+      <c r="A11" s="3" t="s">
+        <v>41</v>
+      </c>
+      <c r="B11" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="C11" s="5">
+        <v>1.13</v>
+      </c>
+      <c r="D11" s="5">
+        <v>2.45</v>
+      </c>
+      <c r="E11" s="7">
+        <v>1.32</v>
+      </c>
+    </row>
+    <row r="12" spans="1:6">
+      <c r="A12" s="3" t="s">
+        <v>42</v>
+      </c>
+      <c r="B12" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="C12" s="5">
+        <v>-4.35</v>
+      </c>
+      <c r="D12" s="5">
+        <v>-2.4</v>
+      </c>
+      <c r="E12" s="7">
+        <v>1.95</v>
+      </c>
+    </row>
+    <row r="13" spans="1:6">
+      <c r="A13" s="3" t="s">
+        <v>43</v>
+      </c>
+      <c r="B13" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="C13" s="5">
+        <v>25.61</v>
+      </c>
+      <c r="D13" s="5">
+        <v>27.5</v>
+      </c>
+      <c r="E13" s="7">
+        <v>1.89</v>
+      </c>
+    </row>
+    <row r="14" spans="1:6">
+      <c r="A14" s="3" t="s">
         <v>37</v>
       </c>
-      <c r="B8" s="6" t="s">
-        <v>9</v>
-      </c>
-      <c r="C8" s="7">
-        <v>-12.23</v>
-      </c>
-      <c r="D8" s="7">
-        <v>-9.09</v>
-      </c>
-      <c r="E8" s="8">
-        <v>3.14</v>
-      </c>
-    </row>
-    <row r="9" spans="1:6">
-      <c r="A9" s="6" t="s">
+      <c r="B14" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="C14" s="5">
+        <v>7.76</v>
+      </c>
+      <c r="D14" s="5">
+        <v>6.41</v>
+      </c>
+      <c r="E14" s="6">
+        <v>-1.35</v>
+      </c>
+    </row>
+    <row r="15" spans="1:6">
+      <c r="A15" s="3" t="s">
         <v>38</v>
       </c>
-      <c r="B9" s="6" t="s">
-        <v>9</v>
-      </c>
-      <c r="C9" s="7">
-        <v>-0.09</v>
-      </c>
-      <c r="D9" s="7">
-        <v>-7.01</v>
-      </c>
-      <c r="E9" s="9">
-        <v>-6.92</v>
-      </c>
-    </row>
-    <row r="10" spans="1:6">
-      <c r="A10" s="6" t="s">
+      <c r="B15" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="C15" s="5">
+        <v>-4.22</v>
+      </c>
+      <c r="D15" s="5">
+        <v>-6.89</v>
+      </c>
+      <c r="E15" s="6">
+        <v>-2.67</v>
+      </c>
+    </row>
+    <row r="16" spans="1:6">
+      <c r="A16" s="3" t="s">
         <v>39</v>
       </c>
-      <c r="B10" s="6" t="s">
-        <v>9</v>
-      </c>
-      <c r="C10" s="7">
-        <v>-8.92</v>
-      </c>
-      <c r="D10" s="7">
-        <v>-6.61</v>
-      </c>
-      <c r="E10" s="8">
-        <v>2.31</v>
-      </c>
-    </row>
-    <row r="11" spans="1:6">
-      <c r="A11" s="6" t="s">
+      <c r="B16" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="C16" s="5">
+        <v>5.74</v>
+      </c>
+      <c r="D16" s="5">
+        <v>1.11</v>
+      </c>
+      <c r="E16" s="6">
+        <v>-4.63</v>
+      </c>
+    </row>
+    <row r="17" spans="1:5">
+      <c r="A17" s="3" t="s">
         <v>40</v>
       </c>
-      <c r="B11" s="6" t="s">
-        <v>9</v>
-      </c>
-      <c r="C11" s="7">
-        <v>-10.02</v>
-      </c>
-      <c r="D11" s="7">
-        <v>-6.66</v>
-      </c>
-      <c r="E11" s="8">
-        <v>3.36</v>
-      </c>
-    </row>
-    <row r="12" spans="1:6">
-      <c r="A12" s="6" t="s">
+      <c r="B17" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="C17" s="5">
+        <v>1.41</v>
+      </c>
+      <c r="D17" s="5">
+        <v>-0.33</v>
+      </c>
+      <c r="E17" s="6">
+        <v>-1.74</v>
+      </c>
+    </row>
+    <row r="18" spans="1:5">
+      <c r="A18" s="3" t="s">
         <v>41</v>
       </c>
-      <c r="B12" s="6" t="s">
-        <v>9</v>
-      </c>
-      <c r="C12" s="7">
-        <v>-3.23</v>
-      </c>
-      <c r="D12" s="7">
-        <v>1.13</v>
-      </c>
-      <c r="E12" s="8">
-        <v>4.36</v>
-      </c>
-    </row>
-    <row r="13" spans="1:6">
-      <c r="A13" s="6" t="s">
+      <c r="B18" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="C18" s="5">
+        <v>5.9</v>
+      </c>
+      <c r="D18" s="5">
+        <v>3.49</v>
+      </c>
+      <c r="E18" s="6">
+        <v>-2.41</v>
+      </c>
+    </row>
+    <row r="19" spans="1:5">
+      <c r="A19" s="3" t="s">
         <v>42</v>
       </c>
-      <c r="B13" s="6" t="s">
-        <v>9</v>
-      </c>
-      <c r="C13" s="7">
+      <c r="B19" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="C19" s="5">
+        <v>0.97</v>
+      </c>
+      <c r="D19" s="5">
+        <v>2.3</v>
+      </c>
+      <c r="E19" s="7">
+        <v>1.33</v>
+      </c>
+    </row>
+    <row r="20" spans="1:5">
+      <c r="A20" s="3" t="s">
+        <v>43</v>
+      </c>
+      <c r="B20" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="C20" s="5">
+        <v>-2.26</v>
+      </c>
+      <c r="D20" s="5">
+        <v>-2.27</v>
+      </c>
+      <c r="E20" s="6">
+        <v>-0.01</v>
+      </c>
+    </row>
+    <row r="21" spans="1:5">
+      <c r="A21" s="3" t="s">
+        <v>37</v>
+      </c>
+      <c r="B21" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="C21" s="5">
+        <v>17.71</v>
+      </c>
+      <c r="D21" s="5">
+        <v>16.38</v>
+      </c>
+      <c r="E21" s="6">
+        <v>-1.33</v>
+      </c>
+    </row>
+    <row r="22" spans="1:5">
+      <c r="A22" s="3" t="s">
+        <v>38</v>
+      </c>
+      <c r="B22" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="C22" s="5">
+        <v>77.38</v>
+      </c>
+      <c r="D22" s="5">
+        <v>77.61</v>
+      </c>
+      <c r="E22" s="7">
+        <v>0.23</v>
+      </c>
+    </row>
+    <row r="23" spans="1:5">
+      <c r="A23" s="3" t="s">
+        <v>39</v>
+      </c>
+      <c r="B23" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="C23" s="5">
+        <v>-43.53</v>
+      </c>
+      <c r="D23" s="5">
+        <v>-44.71</v>
+      </c>
+      <c r="E23" s="6">
+        <v>-1.18</v>
+      </c>
+    </row>
+    <row r="24" spans="1:5">
+      <c r="A24" s="3" t="s">
+        <v>40</v>
+      </c>
+      <c r="B24" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="C24" s="5">
+        <v>-13.59</v>
+      </c>
+      <c r="D24" s="5">
+        <v>-14.42</v>
+      </c>
+      <c r="E24" s="6">
+        <v>-0.83</v>
+      </c>
+    </row>
+    <row r="25" spans="1:5">
+      <c r="A25" s="3" t="s">
+        <v>41</v>
+      </c>
+      <c r="B25" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="C25" s="5">
+        <v>-7.03</v>
+      </c>
+      <c r="D25" s="5">
+        <v>-9.359999999999999</v>
+      </c>
+      <c r="E25" s="6">
+        <v>-2.33</v>
+      </c>
+    </row>
+    <row r="26" spans="1:5">
+      <c r="A26" s="3" t="s">
+        <v>42</v>
+      </c>
+      <c r="B26" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="C26" s="5">
+        <v>-5.72</v>
+      </c>
+      <c r="D26" s="5">
+        <v>-5.27</v>
+      </c>
+      <c r="E26" s="7">
+        <v>0.45</v>
+      </c>
+    </row>
+    <row r="27" spans="1:5">
+      <c r="A27" s="3" t="s">
+        <v>43</v>
+      </c>
+      <c r="B27" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="C27" s="5">
+        <v>28.89</v>
+      </c>
+      <c r="D27" s="5">
+        <v>32.62</v>
+      </c>
+      <c r="E27" s="7">
+        <v>3.73</v>
+      </c>
+    </row>
+    <row r="28" spans="1:5">
+      <c r="A28" s="3" t="s">
+        <v>37</v>
+      </c>
+      <c r="B28" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="C28" s="5">
+        <v>0.52</v>
+      </c>
+      <c r="D28" s="5">
+        <v>-0.36</v>
+      </c>
+      <c r="E28" s="6">
+        <v>-0.88</v>
+      </c>
+    </row>
+    <row r="29" spans="1:5">
+      <c r="A29" s="3" t="s">
+        <v>38</v>
+      </c>
+      <c r="B29" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="C29" s="5">
+        <v>-15.39</v>
+      </c>
+      <c r="D29" s="5">
+        <v>-10.21</v>
+      </c>
+      <c r="E29" s="7">
+        <v>5.18</v>
+      </c>
+    </row>
+    <row r="30" spans="1:5">
+      <c r="A30" s="3" t="s">
+        <v>39</v>
+      </c>
+      <c r="B30" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="C30" s="5">
+        <v>-8.69</v>
+      </c>
+      <c r="D30" s="5">
+        <v>-9.1</v>
+      </c>
+      <c r="E30" s="6">
+        <v>-0.41</v>
+      </c>
+    </row>
+    <row r="31" spans="1:5">
+      <c r="A31" s="3" t="s">
+        <v>40</v>
+      </c>
+      <c r="B31" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="C31" s="5">
+        <v>-5.8</v>
+      </c>
+      <c r="D31" s="5">
+        <v>-6.74</v>
+      </c>
+      <c r="E31" s="6">
+        <v>-0.9399999999999999</v>
+      </c>
+    </row>
+    <row r="32" spans="1:5">
+      <c r="A32" s="3" t="s">
+        <v>41</v>
+      </c>
+      <c r="B32" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="C32" s="5">
+        <v>7.76</v>
+      </c>
+      <c r="D32" s="5">
+        <v>7.69</v>
+      </c>
+      <c r="E32" s="6">
+        <v>-0.07000000000000001</v>
+      </c>
+    </row>
+    <row r="33" spans="1:5">
+      <c r="A33" s="3" t="s">
+        <v>42</v>
+      </c>
+      <c r="B33" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="C33" s="5">
+        <v>-6.97</v>
+      </c>
+      <c r="D33" s="5">
+        <v>-7.02</v>
+      </c>
+      <c r="E33" s="6">
+        <v>-0.05</v>
+      </c>
+    </row>
+    <row r="34" spans="1:5">
+      <c r="A34" s="3" t="s">
+        <v>43</v>
+      </c>
+      <c r="B34" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="C34" s="5">
+        <v>16.52</v>
+      </c>
+      <c r="D34" s="5">
+        <v>18.05</v>
+      </c>
+      <c r="E34" s="7">
+        <v>1.53</v>
+      </c>
+    </row>
+    <row r="35" spans="1:5">
+      <c r="A35" s="3" t="s">
+        <v>37</v>
+      </c>
+      <c r="B35" s="3" t="s">
+        <v>6</v>
+      </c>
+      <c r="C35" s="5">
+        <v>-15.99</v>
+      </c>
+      <c r="D35" s="5">
+        <v>-15.82</v>
+      </c>
+      <c r="E35" s="7">
+        <v>0.17</v>
+      </c>
+    </row>
+    <row r="36" spans="1:5">
+      <c r="A36" s="3" t="s">
+        <v>38</v>
+      </c>
+      <c r="B36" s="3" t="s">
+        <v>6</v>
+      </c>
+      <c r="C36" s="5">
+        <v>-30.1</v>
+      </c>
+      <c r="D36" s="5">
+        <v>-29.58</v>
+      </c>
+      <c r="E36" s="7">
+        <v>0.52</v>
+      </c>
+    </row>
+    <row r="37" spans="1:5">
+      <c r="A37" s="3" t="s">
+        <v>39</v>
+      </c>
+      <c r="B37" s="3" t="s">
+        <v>6</v>
+      </c>
+      <c r="C37" s="5">
+        <v>-44.03</v>
+      </c>
+      <c r="D37" s="5">
+        <v>-45.02</v>
+      </c>
+      <c r="E37" s="6">
+        <v>-0.99</v>
+      </c>
+    </row>
+    <row r="38" spans="1:5">
+      <c r="A38" s="3" t="s">
+        <v>40</v>
+      </c>
+      <c r="B38" s="3" t="s">
+        <v>6</v>
+      </c>
+      <c r="C38" s="5">
+        <v>-20.43</v>
+      </c>
+      <c r="D38" s="5">
+        <v>-20.56</v>
+      </c>
+      <c r="E38" s="6">
+        <v>-0.13</v>
+      </c>
+    </row>
+    <row r="39" spans="1:5">
+      <c r="A39" s="3" t="s">
+        <v>41</v>
+      </c>
+      <c r="B39" s="3" t="s">
+        <v>6</v>
+      </c>
+      <c r="C39" s="5">
+        <v>-14.6</v>
+      </c>
+      <c r="D39" s="5">
+        <v>-14.81</v>
+      </c>
+      <c r="E39" s="6">
+        <v>-0.21</v>
+      </c>
+    </row>
+    <row r="40" spans="1:5">
+      <c r="A40" s="3" t="s">
+        <v>42</v>
+      </c>
+      <c r="B40" s="3" t="s">
+        <v>6</v>
+      </c>
+      <c r="C40" s="5">
+        <v>-16.7</v>
+      </c>
+      <c r="D40" s="5">
+        <v>-15.25</v>
+      </c>
+      <c r="E40" s="7">
+        <v>1.45</v>
+      </c>
+    </row>
+    <row r="41" spans="1:5">
+      <c r="A41" s="3" t="s">
+        <v>43</v>
+      </c>
+      <c r="B41" s="3" t="s">
+        <v>6</v>
+      </c>
+      <c r="C41" s="5">
+        <v>-8.369999999999999</v>
+      </c>
+      <c r="D41" s="5">
         <v>-7.49</v>
       </c>
-      <c r="D13" s="7">
-        <v>-4.35</v>
-      </c>
-      <c r="E13" s="8">
-        <v>3.14</v>
-      </c>
-    </row>
-    <row r="14" spans="1:6">
-      <c r="A14" s="6" t="s">
+      <c r="E41" s="7">
+        <v>0.88</v>
+      </c>
+    </row>
+    <row r="42" spans="1:5">
+      <c r="A42" s="3" t="s">
+        <v>37</v>
+      </c>
+      <c r="B42" s="3" t="s">
+        <v>2</v>
+      </c>
+      <c r="C42" s="5">
+        <v>10385</v>
+      </c>
+      <c r="D42" s="5">
+        <v>10405</v>
+      </c>
+      <c r="E42" s="7">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="43" spans="1:5">
+      <c r="A43" s="3" t="s">
+        <v>38</v>
+      </c>
+      <c r="B43" s="3" t="s">
+        <v>2</v>
+      </c>
+      <c r="C43" s="5">
+        <v>468.5</v>
+      </c>
+      <c r="D43" s="5">
+        <v>472</v>
+      </c>
+      <c r="E43" s="7">
+        <v>3.5</v>
+      </c>
+    </row>
+    <row r="44" spans="1:5">
+      <c r="A44" s="3" t="s">
+        <v>39</v>
+      </c>
+      <c r="B44" s="3" t="s">
+        <v>2</v>
+      </c>
+      <c r="C44" s="5">
+        <v>306.7</v>
+      </c>
+      <c r="D44" s="5">
+        <v>301.3</v>
+      </c>
+      <c r="E44" s="6">
+        <v>-5.4</v>
+      </c>
+    </row>
+    <row r="45" spans="1:5">
+      <c r="A45" s="3" t="s">
+        <v>40</v>
+      </c>
+      <c r="B45" s="3" t="s">
+        <v>2</v>
+      </c>
+      <c r="C45" s="5">
+        <v>1732</v>
+      </c>
+      <c r="D45" s="5">
+        <v>1729</v>
+      </c>
+      <c r="E45" s="6">
+        <v>-3</v>
+      </c>
+    </row>
+    <row r="46" spans="1:5">
+      <c r="A46" s="3" t="s">
+        <v>41</v>
+      </c>
+      <c r="B46" s="3" t="s">
+        <v>2</v>
+      </c>
+      <c r="C46" s="5">
+        <v>11225</v>
+      </c>
+      <c r="D46" s="5">
+        <v>11198</v>
+      </c>
+      <c r="E46" s="6">
+        <v>-27</v>
+      </c>
+    </row>
+    <row r="47" spans="1:5">
+      <c r="A47" s="3" t="s">
+        <v>42</v>
+      </c>
+      <c r="B47" s="3" t="s">
+        <v>2</v>
+      </c>
+      <c r="C47" s="5">
+        <v>965.25</v>
+      </c>
+      <c r="D47" s="5">
+        <v>982.1</v>
+      </c>
+      <c r="E47" s="7">
+        <v>16.85</v>
+      </c>
+    </row>
+    <row r="48" spans="1:5">
+      <c r="A48" s="3" t="s">
         <v>43</v>
       </c>
-      <c r="B14" s="6" t="s">
-        <v>9</v>
-      </c>
-      <c r="C14" s="7">
-        <v>25.48</v>
-      </c>
-      <c r="D14" s="7">
-        <v>25.61</v>
-      </c>
-      <c r="E14" s="8">
-        <v>0.13</v>
-      </c>
-    </row>
-    <row r="15" spans="1:6">
-      <c r="A15" s="6" t="s">
+      <c r="B48" s="3" t="s">
+        <v>2</v>
+      </c>
+      <c r="C48" s="5">
+        <v>170.35</v>
+      </c>
+      <c r="D48" s="5">
+        <v>171.99</v>
+      </c>
+      <c r="E48" s="7">
+        <v>1.64</v>
+      </c>
+    </row>
+    <row r="49" spans="1:5">
+      <c r="A49" s="3" t="s">
         <v>37</v>
       </c>
-      <c r="B15" s="6" t="s">
-        <v>8</v>
-      </c>
-      <c r="C15" s="7">
-        <v>3.7</v>
-      </c>
-      <c r="D15" s="7">
-        <v>7.76</v>
-      </c>
-      <c r="E15" s="8">
-        <v>4.06</v>
-      </c>
-    </row>
-    <row r="16" spans="1:6">
-      <c r="A16" s="6" t="s">
+      <c r="B49" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="C49" s="5">
+        <v>42.27</v>
+      </c>
+      <c r="D49" s="5">
+        <v>42.81</v>
+      </c>
+      <c r="E49" s="7">
+        <v>0.54</v>
+      </c>
+    </row>
+    <row r="50" spans="1:5">
+      <c r="A50" s="3" t="s">
         <v>38</v>
       </c>
-      <c r="B16" s="6" t="s">
-        <v>8</v>
-      </c>
-      <c r="C16" s="7">
-        <v>7.67</v>
-      </c>
-      <c r="D16" s="7">
-        <v>-4.22</v>
-      </c>
-      <c r="E16" s="9">
-        <v>-11.89</v>
-      </c>
-    </row>
-    <row r="17" spans="1:5">
-      <c r="A17" s="6" t="s">
+      <c r="B50" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="C50" s="5">
+        <v>41.31</v>
+      </c>
+      <c r="D50" s="5">
+        <v>42.46</v>
+      </c>
+      <c r="E50" s="7">
+        <v>1.15</v>
+      </c>
+    </row>
+    <row r="51" spans="1:5">
+      <c r="A51" s="3" t="s">
         <v>39</v>
       </c>
-      <c r="B17" s="6" t="s">
-        <v>8</v>
-      </c>
-      <c r="C17" s="7">
-        <v>1.56</v>
-      </c>
-      <c r="D17" s="7">
-        <v>5.74</v>
-      </c>
-      <c r="E17" s="8">
-        <v>4.18</v>
-      </c>
-    </row>
-    <row r="18" spans="1:5">
-      <c r="A18" s="6" t="s">
+      <c r="B51" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="C51" s="5">
+        <v>43.44</v>
+      </c>
+      <c r="D51" s="5">
+        <v>39.3</v>
+      </c>
+      <c r="E51" s="6">
+        <v>-4.14</v>
+      </c>
+    </row>
+    <row r="52" spans="1:5">
+      <c r="A52" s="3" t="s">
         <v>40</v>
       </c>
-      <c r="B18" s="6" t="s">
-        <v>8</v>
-      </c>
-      <c r="C18" s="7">
-        <v>-1.24</v>
-      </c>
-      <c r="D18" s="7">
-        <v>1.41</v>
-      </c>
-      <c r="E18" s="8">
-        <v>2.65</v>
-      </c>
-    </row>
-    <row r="19" spans="1:5">
-      <c r="A19" s="6" t="s">
+      <c r="B52" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="C52" s="5">
+        <v>37.57</v>
+      </c>
+      <c r="D52" s="5">
+        <v>37.15</v>
+      </c>
+      <c r="E52" s="6">
+        <v>-0.42</v>
+      </c>
+    </row>
+    <row r="53" spans="1:5">
+      <c r="A53" s="3" t="s">
         <v>41</v>
       </c>
-      <c r="B19" s="6" t="s">
-        <v>8</v>
-      </c>
-      <c r="C19" s="7">
-        <v>1.05</v>
-      </c>
-      <c r="D19" s="7">
-        <v>5.9</v>
-      </c>
-      <c r="E19" s="8">
-        <v>4.85</v>
-      </c>
-    </row>
-    <row r="20" spans="1:5">
-      <c r="A20" s="6" t="s">
+      <c r="B53" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="C53" s="5">
+        <v>57.61</v>
+      </c>
+      <c r="D53" s="5">
+        <v>56.84</v>
+      </c>
+      <c r="E53" s="6">
+        <v>-0.77</v>
+      </c>
+    </row>
+    <row r="54" spans="1:5">
+      <c r="A54" s="3" t="s">
         <v>42</v>
       </c>
-      <c r="B20" s="6" t="s">
-        <v>8</v>
-      </c>
-      <c r="C20" s="7">
-        <v>-0.71</v>
-      </c>
-      <c r="D20" s="7">
-        <v>0.97</v>
-      </c>
-      <c r="E20" s="8">
-        <v>1.68</v>
-      </c>
-    </row>
-    <row r="21" spans="1:5">
-      <c r="A21" s="6" t="s">
+      <c r="B54" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="C54" s="5">
+        <v>42.31</v>
+      </c>
+      <c r="D54" s="5">
+        <v>47.29</v>
+      </c>
+      <c r="E54" s="7">
+        <v>4.98</v>
+      </c>
+    </row>
+    <row r="55" spans="1:5">
+      <c r="A55" s="3" t="s">
         <v>43</v>
       </c>
-      <c r="B21" s="6" t="s">
-        <v>8</v>
-      </c>
-      <c r="C21" s="7">
-        <v>-5.86</v>
-      </c>
-      <c r="D21" s="7">
-        <v>-2.26</v>
-      </c>
-      <c r="E21" s="8">
-        <v>3.6</v>
-      </c>
-    </row>
-    <row r="22" spans="1:5">
-      <c r="A22" s="6" t="s">
+      <c r="B55" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="C55" s="5">
+        <v>57.18</v>
+      </c>
+      <c r="D55" s="5">
+        <v>58.54</v>
+      </c>
+      <c r="E55" s="7">
+        <v>1.36</v>
+      </c>
+    </row>
+    <row r="56" spans="1:5">
+      <c r="A56" s="3" t="s">
         <v>37</v>
       </c>
-      <c r="B22" s="6" t="s">
-        <v>11</v>
-      </c>
-      <c r="C22" s="7">
-        <v>17.98</v>
-      </c>
-      <c r="D22" s="7">
-        <v>17.71</v>
-      </c>
-      <c r="E22" s="9">
-        <v>-0.27</v>
-      </c>
-    </row>
-    <row r="23" spans="1:5">
-      <c r="A23" s="6" t="s">
+      <c r="B56" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="C56" s="5">
+        <v>-31.77</v>
+      </c>
+      <c r="D56" s="5">
+        <v>-39.09</v>
+      </c>
+      <c r="E56" s="6">
+        <v>-7.32</v>
+      </c>
+    </row>
+    <row r="57" spans="1:5">
+      <c r="A57" s="3" t="s">
         <v>38</v>
       </c>
-      <c r="B23" s="6" t="s">
-        <v>11</v>
-      </c>
-      <c r="C23" s="7">
-        <v>109.99</v>
-      </c>
-      <c r="D23" s="7">
-        <v>77.38</v>
-      </c>
-      <c r="E23" s="9">
-        <v>-32.61</v>
-      </c>
-    </row>
-    <row r="24" spans="1:5">
-      <c r="A24" s="6" t="s">
+      <c r="B57" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="C57" s="5">
+        <v>1243.02</v>
+      </c>
+      <c r="D57" s="5">
+        <v>26.05</v>
+      </c>
+      <c r="E57" s="6">
+        <v>-1216.97</v>
+      </c>
+    </row>
+    <row r="58" spans="1:5">
+      <c r="A58" s="3" t="s">
         <v>39</v>
       </c>
-      <c r="B24" s="6" t="s">
-        <v>11</v>
-      </c>
-      <c r="C24" s="7">
-        <v>-43.26</v>
-      </c>
-      <c r="D24" s="7">
-        <v>-43.53</v>
-      </c>
-      <c r="E24" s="9">
-        <v>-0.27</v>
-      </c>
-    </row>
-    <row r="25" spans="1:5">
-      <c r="A25" s="6" t="s">
+      <c r="B58" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="C58" s="5">
+        <v>8636.33</v>
+      </c>
+      <c r="D58" s="5">
+        <v>-16.85</v>
+      </c>
+      <c r="E58" s="6">
+        <v>-8653.18</v>
+      </c>
+    </row>
+    <row r="59" spans="1:5">
+      <c r="A59" s="3" t="s">
         <v>40</v>
       </c>
-      <c r="B25" s="6" t="s">
-        <v>11</v>
-      </c>
-      <c r="C25" s="7">
-        <v>-14.54</v>
-      </c>
-      <c r="D25" s="7">
-        <v>-13.59</v>
-      </c>
-      <c r="E25" s="8">
-        <v>0.95</v>
-      </c>
-    </row>
-    <row r="26" spans="1:5">
-      <c r="A26" s="6" t="s">
+      <c r="B59" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="C59" s="5">
+        <v>7.06</v>
+      </c>
+      <c r="D59" s="5">
+        <v>26.53</v>
+      </c>
+      <c r="E59" s="7">
+        <v>19.47</v>
+      </c>
+    </row>
+    <row r="60" spans="1:5">
+      <c r="A60" s="3" t="s">
         <v>41</v>
       </c>
-      <c r="B26" s="6" t="s">
-        <v>11</v>
-      </c>
-      <c r="C26" s="7">
-        <v>-9.529999999999999</v>
-      </c>
-      <c r="D26" s="7">
-        <v>-7.03</v>
-      </c>
-      <c r="E26" s="8">
-        <v>2.5</v>
-      </c>
-    </row>
-    <row r="27" spans="1:5">
-      <c r="A27" s="6" t="s">
+      <c r="B60" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="C60" s="5">
+        <v>98.14</v>
+      </c>
+      <c r="D60" s="5">
+        <v>-37</v>
+      </c>
+      <c r="E60" s="6">
+        <v>-135.14</v>
+      </c>
+    </row>
+    <row r="61" spans="1:5">
+      <c r="A61" s="3" t="s">
         <v>42</v>
       </c>
-      <c r="B27" s="6" t="s">
-        <v>11</v>
-      </c>
-      <c r="C27" s="7">
-        <v>-6.55</v>
-      </c>
-      <c r="D27" s="7">
-        <v>-5.72</v>
-      </c>
-      <c r="E27" s="8">
-        <v>0.83</v>
-      </c>
-    </row>
-    <row r="28" spans="1:5">
-      <c r="A28" s="6" t="s">
+      <c r="B61" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="C61" s="5">
+        <v>48.19</v>
+      </c>
+      <c r="D61" s="5">
+        <v>3.74</v>
+      </c>
+      <c r="E61" s="6">
+        <v>-44.45</v>
+      </c>
+    </row>
+    <row r="62" spans="1:5">
+      <c r="A62" s="3" t="s">
         <v>43</v>
       </c>
-      <c r="B28" s="6" t="s">
-        <v>11</v>
-      </c>
-      <c r="C28" s="7">
-        <v>29.65</v>
-      </c>
-      <c r="D28" s="7">
-        <v>28.89</v>
-      </c>
-      <c r="E28" s="9">
-        <v>-0.76</v>
-      </c>
-    </row>
-    <row r="29" spans="1:5">
-      <c r="A29" s="6" t="s">
-        <v>37</v>
-      </c>
-      <c r="B29" s="6" t="s">
-        <v>10</v>
-      </c>
-      <c r="C29" s="7">
-        <v>-0.71</v>
-      </c>
-      <c r="D29" s="7">
-        <v>0.52</v>
-      </c>
-      <c r="E29" s="8">
-        <v>1.23</v>
-      </c>
-    </row>
-    <row r="30" spans="1:5">
-      <c r="A30" s="6" t="s">
-        <v>38</v>
-      </c>
-      <c r="B30" s="6" t="s">
-        <v>10</v>
-      </c>
-      <c r="C30" s="7">
-        <v>-8.51</v>
-      </c>
-      <c r="D30" s="7">
-        <v>-15.39</v>
-      </c>
-      <c r="E30" s="9">
-        <v>-6.88</v>
-      </c>
-    </row>
-    <row r="31" spans="1:5">
-      <c r="A31" s="6" t="s">
-        <v>39</v>
-      </c>
-      <c r="B31" s="6" t="s">
-        <v>10</v>
-      </c>
-      <c r="C31" s="7">
-        <v>-7.47</v>
-      </c>
-      <c r="D31" s="7">
-        <v>-8.69</v>
-      </c>
-      <c r="E31" s="9">
-        <v>-1.22</v>
-      </c>
-    </row>
-    <row r="32" spans="1:5">
-      <c r="A32" s="6" t="s">
-        <v>40</v>
-      </c>
-      <c r="B32" s="6" t="s">
-        <v>10</v>
-      </c>
-      <c r="C32" s="7">
-        <v>-6.92</v>
-      </c>
-      <c r="D32" s="7">
-        <v>-5.8</v>
-      </c>
-      <c r="E32" s="8">
-        <v>1.12</v>
-      </c>
-    </row>
-    <row r="33" spans="1:5">
-      <c r="A33" s="6" t="s">
-        <v>41</v>
-      </c>
-      <c r="B33" s="6" t="s">
-        <v>10</v>
-      </c>
-      <c r="C33" s="7">
-        <v>2.31</v>
-      </c>
-      <c r="D33" s="7">
-        <v>7.76</v>
-      </c>
-      <c r="E33" s="8">
-        <v>5.45</v>
-      </c>
-    </row>
-    <row r="34" spans="1:5">
-      <c r="A34" s="6" t="s">
-        <v>42</v>
-      </c>
-      <c r="B34" s="6" t="s">
-        <v>10</v>
-      </c>
-      <c r="C34" s="7">
-        <v>-6.3</v>
-      </c>
-      <c r="D34" s="7">
-        <v>-6.97</v>
-      </c>
-      <c r="E34" s="9">
-        <v>-0.67</v>
-      </c>
-    </row>
-    <row r="35" spans="1:5">
-      <c r="A35" s="6" t="s">
-        <v>43</v>
-      </c>
-      <c r="B35" s="6" t="s">
-        <v>10</v>
-      </c>
-      <c r="C35" s="7">
-        <v>23.56</v>
-      </c>
-      <c r="D35" s="7">
-        <v>16.52</v>
-      </c>
-      <c r="E35" s="9">
-        <v>-7.04</v>
-      </c>
-    </row>
-    <row r="36" spans="1:5">
-      <c r="A36" s="6" t="s">
-        <v>37</v>
-      </c>
-      <c r="B36" s="6" t="s">
-        <v>6</v>
-      </c>
-      <c r="C36" s="7">
-        <v>-17.08</v>
-      </c>
-      <c r="D36" s="7">
-        <v>-15.99</v>
-      </c>
-      <c r="E36" s="8">
-        <v>1.09</v>
-      </c>
-    </row>
-    <row r="37" spans="1:5">
-      <c r="A37" s="6" t="s">
-        <v>38</v>
-      </c>
-      <c r="B37" s="6" t="s">
-        <v>6</v>
-      </c>
-      <c r="C37" s="7">
-        <v>-22.41</v>
-      </c>
-      <c r="D37" s="7">
-        <v>-30.1</v>
-      </c>
-      <c r="E37" s="9">
-        <v>-7.69</v>
-      </c>
-    </row>
-    <row r="38" spans="1:5">
-      <c r="A38" s="6" t="s">
-        <v>39</v>
-      </c>
-      <c r="B38" s="6" t="s">
-        <v>6</v>
-      </c>
-      <c r="C38" s="7">
-        <v>-44.27</v>
-      </c>
-      <c r="D38" s="7">
-        <v>-44.03</v>
-      </c>
-      <c r="E38" s="8">
-        <v>0.24</v>
-      </c>
-    </row>
-    <row r="39" spans="1:5">
-      <c r="A39" s="6" t="s">
-        <v>40</v>
-      </c>
-      <c r="B39" s="6" t="s">
-        <v>6</v>
-      </c>
-      <c r="C39" s="7">
-        <v>-20.9</v>
-      </c>
-      <c r="D39" s="7">
-        <v>-20.43</v>
-      </c>
-      <c r="E39" s="8">
-        <v>0.47</v>
-      </c>
-    </row>
-    <row r="40" spans="1:5">
-      <c r="A40" s="6" t="s">
-        <v>41</v>
-      </c>
-      <c r="B40" s="6" t="s">
-        <v>6</v>
-      </c>
-      <c r="C40" s="7">
-        <v>-18.03</v>
-      </c>
-      <c r="D40" s="7">
-        <v>-14.6</v>
-      </c>
-      <c r="E40" s="8">
-        <v>3.43</v>
-      </c>
-    </row>
-    <row r="41" spans="1:5">
-      <c r="A41" s="6" t="s">
-        <v>42</v>
-      </c>
-      <c r="B41" s="6" t="s">
-        <v>6</v>
-      </c>
-      <c r="C41" s="7">
-        <v>-17.41</v>
-      </c>
-      <c r="D41" s="7">
-        <v>-16.7</v>
-      </c>
-      <c r="E41" s="8">
-        <v>0.71</v>
-      </c>
-    </row>
-    <row r="42" spans="1:5">
-      <c r="A42" s="6" t="s">
-        <v>43</v>
-      </c>
-      <c r="B42" s="6" t="s">
-        <v>6</v>
-      </c>
-      <c r="C42" s="7">
-        <v>-5.86</v>
-      </c>
-      <c r="D42" s="7">
-        <v>-8.369999999999999</v>
-      </c>
-      <c r="E42" s="9">
-        <v>-2.51</v>
-      </c>
-    </row>
-    <row r="43" spans="1:5">
-      <c r="A43" s="6" t="s">
-        <v>37</v>
-      </c>
-      <c r="B43" s="6" t="s">
-        <v>2</v>
-      </c>
-      <c r="C43" s="7">
-        <v>10250</v>
-      </c>
-      <c r="D43" s="7">
-        <v>10385</v>
-      </c>
-      <c r="E43" s="8">
-        <v>135</v>
-      </c>
-    </row>
-    <row r="44" spans="1:5">
-      <c r="A44" s="6" t="s">
-        <v>38</v>
-      </c>
-      <c r="B44" s="6" t="s">
-        <v>2</v>
-      </c>
-      <c r="C44" s="7">
-        <v>520.05</v>
-      </c>
-      <c r="D44" s="7">
-        <v>468.5</v>
-      </c>
-      <c r="E44" s="9">
-        <v>-51.55</v>
-      </c>
-    </row>
-    <row r="45" spans="1:5">
-      <c r="A45" s="6" t="s">
-        <v>39</v>
-      </c>
-      <c r="B45" s="6" t="s">
-        <v>2</v>
-      </c>
-      <c r="C45" s="7">
-        <v>305.4</v>
-      </c>
-      <c r="D45" s="7">
-        <v>306.7</v>
-      </c>
-      <c r="E45" s="8">
-        <v>1.3</v>
-      </c>
-    </row>
-    <row r="46" spans="1:5">
-      <c r="A46" s="6" t="s">
-        <v>40</v>
-      </c>
-      <c r="B46" s="6" t="s">
-        <v>2</v>
-      </c>
-      <c r="C46" s="7">
-        <v>1721.7</v>
-      </c>
-      <c r="D46" s="7">
-        <v>1732</v>
-      </c>
-      <c r="E46" s="8">
-        <v>10.3</v>
-      </c>
-    </row>
-    <row r="47" spans="1:5">
-      <c r="A47" s="6" t="s">
-        <v>41</v>
-      </c>
-      <c r="B47" s="6" t="s">
-        <v>2</v>
-      </c>
-      <c r="C47" s="7">
-        <v>10774</v>
-      </c>
-      <c r="D47" s="7">
-        <v>11225</v>
-      </c>
-      <c r="E47" s="8">
-        <v>451</v>
-      </c>
-    </row>
-    <row r="48" spans="1:5">
-      <c r="A48" s="6" t="s">
-        <v>42</v>
-      </c>
-      <c r="B48" s="6" t="s">
-        <v>2</v>
-      </c>
-      <c r="C48" s="7">
-        <v>957</v>
-      </c>
-      <c r="D48" s="7">
-        <v>965.25</v>
-      </c>
-      <c r="E48" s="8">
-        <v>8.25</v>
-      </c>
-    </row>
-    <row r="49" spans="1:5">
-      <c r="A49" s="6" t="s">
-        <v>43</v>
-      </c>
-      <c r="B49" s="6" t="s">
-        <v>2</v>
-      </c>
-      <c r="C49" s="7">
-        <v>175.02</v>
-      </c>
-      <c r="D49" s="7">
-        <v>170.35</v>
-      </c>
-      <c r="E49" s="9">
-        <v>-4.67</v>
-      </c>
-    </row>
-    <row r="50" spans="1:5">
-      <c r="A50" s="6" t="s">
-        <v>37</v>
-      </c>
-      <c r="B50" s="6" t="s">
-        <v>24</v>
-      </c>
-      <c r="C50" s="7">
-        <v>38.63</v>
-      </c>
-      <c r="D50" s="7">
-        <v>42.27</v>
-      </c>
-      <c r="E50" s="8">
-        <v>3.64</v>
-      </c>
-    </row>
-    <row r="51" spans="1:5">
-      <c r="A51" s="6" t="s">
-        <v>38</v>
-      </c>
-      <c r="B51" s="6" t="s">
-        <v>24</v>
-      </c>
-      <c r="C51" s="7">
-        <v>56.9</v>
-      </c>
-      <c r="D51" s="7">
-        <v>41.31</v>
-      </c>
-      <c r="E51" s="9">
-        <v>-15.59</v>
-      </c>
-    </row>
-    <row r="52" spans="1:5">
-      <c r="A52" s="6" t="s">
-        <v>39</v>
-      </c>
-      <c r="B52" s="6" t="s">
-        <v>24</v>
-      </c>
-      <c r="C52" s="7">
-        <v>42.08</v>
-      </c>
-      <c r="D52" s="7">
-        <v>43.44</v>
-      </c>
-      <c r="E52" s="8">
-        <v>1.36</v>
-      </c>
-    </row>
-    <row r="53" spans="1:5">
-      <c r="A53" s="6" t="s">
-        <v>40</v>
-      </c>
-      <c r="B53" s="6" t="s">
-        <v>24</v>
-      </c>
-      <c r="C53" s="7">
-        <v>35.23</v>
-      </c>
-      <c r="D53" s="7">
-        <v>37.57</v>
-      </c>
-      <c r="E53" s="8">
-        <v>2.34</v>
-      </c>
-    </row>
-    <row r="54" spans="1:5">
-      <c r="A54" s="6" t="s">
-        <v>41</v>
-      </c>
-      <c r="B54" s="6" t="s">
-        <v>24</v>
-      </c>
-      <c r="C54" s="7">
-        <v>46.18</v>
-      </c>
-      <c r="D54" s="7">
-        <v>57.61</v>
-      </c>
-      <c r="E54" s="8">
-        <v>11.43</v>
-      </c>
-    </row>
-    <row r="55" spans="1:5">
-      <c r="A55" s="6" t="s">
-        <v>42</v>
-      </c>
-      <c r="B55" s="6" t="s">
-        <v>24</v>
-      </c>
-      <c r="C55" s="7">
-        <v>39.73</v>
-      </c>
-      <c r="D55" s="7">
-        <v>42.31</v>
-      </c>
-      <c r="E55" s="8">
-        <v>2.58</v>
-      </c>
-    </row>
-    <row r="56" spans="1:5">
-      <c r="A56" s="6" t="s">
-        <v>43</v>
-      </c>
-      <c r="B56" s="6" t="s">
-        <v>24</v>
-      </c>
-      <c r="C56" s="7">
-        <v>62.62</v>
-      </c>
-      <c r="D56" s="7">
-        <v>57.18</v>
-      </c>
-      <c r="E56" s="9">
-        <v>-5.44</v>
-      </c>
-    </row>
-    <row r="57" spans="1:5">
-      <c r="A57" s="6" t="s">
-        <v>37</v>
-      </c>
-      <c r="B57" s="6" t="s">
+      <c r="B62" s="3" t="s">
         <v>31</v>
       </c>
-      <c r="C57" s="7">
-        <v>-22.12</v>
-      </c>
-      <c r="D57" s="7">
-        <v>-31.77</v>
-      </c>
-      <c r="E57" s="9">
-        <v>-9.65</v>
-      </c>
-    </row>
-    <row r="58" spans="1:5">
-      <c r="A58" s="6" t="s">
-        <v>38</v>
-      </c>
-      <c r="B58" s="6" t="s">
-        <v>31</v>
-      </c>
-      <c r="C58" s="7">
-        <v>87.65000000000001</v>
-      </c>
-      <c r="D58" s="7">
-        <v>1243.02</v>
-      </c>
-      <c r="E58" s="8">
-        <v>1155.37</v>
-      </c>
-    </row>
-    <row r="59" spans="1:5">
-      <c r="A59" s="6" t="s">
-        <v>39</v>
-      </c>
-      <c r="B59" s="6" t="s">
-        <v>31</v>
-      </c>
-      <c r="C59" s="7">
-        <v>-65.81999999999999</v>
-      </c>
-      <c r="D59" s="7">
-        <v>8636.33</v>
-      </c>
-      <c r="E59" s="8">
-        <v>8702.15</v>
-      </c>
-    </row>
-    <row r="60" spans="1:5">
-      <c r="A60" s="6" t="s">
-        <v>40</v>
-      </c>
-      <c r="B60" s="6" t="s">
-        <v>31</v>
-      </c>
-      <c r="C60" s="7">
-        <v>-1.12</v>
-      </c>
-      <c r="D60" s="7">
-        <v>7.06</v>
-      </c>
-      <c r="E60" s="8">
-        <v>8.18</v>
-      </c>
-    </row>
-    <row r="61" spans="1:5">
-      <c r="A61" s="6" t="s">
-        <v>41</v>
-      </c>
-      <c r="B61" s="6" t="s">
-        <v>31</v>
-      </c>
-      <c r="C61" s="7">
-        <v>-35.35</v>
-      </c>
-      <c r="D61" s="7">
-        <v>98.14</v>
-      </c>
-      <c r="E61" s="8">
-        <v>133.49</v>
-      </c>
-    </row>
-    <row r="62" spans="1:5">
-      <c r="A62" s="6" t="s">
-        <v>42</v>
-      </c>
-      <c r="B62" s="6" t="s">
-        <v>31</v>
-      </c>
-      <c r="C62" s="7">
-        <v>-0.9399999999999999</v>
-      </c>
-      <c r="D62" s="7">
-        <v>48.19</v>
-      </c>
-      <c r="E62" s="8">
-        <v>49.13</v>
-      </c>
-    </row>
-    <row r="63" spans="1:5">
-      <c r="A63" s="6" t="s">
-        <v>43</v>
-      </c>
-      <c r="B63" s="6" t="s">
-        <v>31</v>
-      </c>
-      <c r="C63" s="7">
-        <v>-84.72</v>
-      </c>
-      <c r="D63" s="7">
+      <c r="C62" s="5">
         <v>-69.31999999999999</v>
       </c>
-      <c r="E63" s="8">
-        <v>15.4</v>
+      <c r="D62" s="5">
+        <v>-80.87</v>
+      </c>
+      <c r="E62" s="6">
+        <v>-11.55</v>
       </c>
     </row>
   </sheetData>
   <mergeCells count="2">
     <mergeCell ref="A1:F1"/>
-    <mergeCell ref="A6:E6"/>
+    <mergeCell ref="A5:E5"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -2937,60 +2841,60 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:9" ht="28" customHeight="1">
-      <c r="A1" s="10" t="s">
+      <c r="A1" s="8" t="s">
         <v>1</v>
       </c>
-      <c r="B1" s="10" t="s">
-        <v>69</v>
-      </c>
-      <c r="C1" s="10" t="s">
+      <c r="B1" s="8" t="s">
+        <v>56</v>
+      </c>
+      <c r="C1" s="8" t="s">
+        <v>57</v>
+      </c>
+      <c r="D1" s="8" t="s">
+        <v>58</v>
+      </c>
+      <c r="E1" s="8" t="s">
+        <v>59</v>
+      </c>
+      <c r="F1" s="8" t="s">
+        <v>60</v>
+      </c>
+      <c r="G1" s="8" t="s">
+        <v>61</v>
+      </c>
+      <c r="H1" s="8" t="s">
+        <v>62</v>
+      </c>
+      <c r="I1" s="8" t="s">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="2" spans="1:9">
+      <c r="A2" s="9" t="s">
+        <v>44</v>
+      </c>
+      <c r="B2" s="10">
+        <v>60.8</v>
+      </c>
+      <c r="C2" s="11">
+        <v>7</v>
+      </c>
+      <c r="D2" s="10">
+        <v>46.3</v>
+      </c>
+      <c r="E2" s="10">
         <v>70</v>
       </c>
-      <c r="D1" s="10" t="s">
-        <v>71</v>
-      </c>
-      <c r="E1" s="10" t="s">
-        <v>72</v>
-      </c>
-      <c r="F1" s="10" t="s">
-        <v>73</v>
-      </c>
-      <c r="G1" s="10" t="s">
-        <v>74</v>
-      </c>
-      <c r="H1" s="10" t="s">
-        <v>75</v>
-      </c>
-      <c r="I1" s="10" t="s">
-        <v>76</v>
-      </c>
-    </row>
-    <row r="2" spans="1:9">
-      <c r="A2" s="11" t="s">
-        <v>44</v>
-      </c>
-      <c r="B2" s="12">
-        <v>56.8</v>
-      </c>
-      <c r="C2" s="13">
-        <v>7</v>
-      </c>
-      <c r="D2" s="12">
-        <v>46</v>
-      </c>
-      <c r="E2" s="12">
-        <v>60</v>
-      </c>
-      <c r="F2" s="12">
-        <v>-1</v>
-      </c>
-      <c r="G2" s="12">
-        <v>-1.7</v>
-      </c>
-      <c r="H2" s="12">
+      <c r="F2" s="10">
+        <v>-0.1</v>
+      </c>
+      <c r="G2" s="10">
+        <v>-1.1</v>
+      </c>
+      <c r="H2" s="10">
         <v>57</v>
       </c>
-      <c r="I2" s="12">
+      <c r="I2" s="10">
         <v>10</v>
       </c>
     </row>
@@ -3092,49 +2996,49 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:7">
-      <c r="A1" s="14" t="s">
+      <c r="A1" s="12" t="s">
         <v>37</v>
       </c>
-      <c r="B1" s="14" t="s">
+      <c r="B1" s="12" t="s">
         <v>41</v>
       </c>
-      <c r="C1" s="14" t="s">
+      <c r="C1" s="12" t="s">
         <v>38</v>
       </c>
-      <c r="D1" s="14" t="s">
+      <c r="D1" s="12" t="s">
         <v>43</v>
       </c>
-      <c r="E1" s="14" t="s">
+      <c r="E1" s="12" t="s">
         <v>42</v>
       </c>
-      <c r="F1" s="14" t="s">
+      <c r="F1" s="12" t="s">
         <v>40</v>
       </c>
-      <c r="G1" s="14" t="s">
+      <c r="G1" s="12" t="s">
         <v>39</v>
       </c>
     </row>
     <row r="2" spans="1:7">
-      <c r="A2" s="15">
-        <v>0.2439</v>
-      </c>
-      <c r="B2" s="15">
-        <v>0.1998</v>
-      </c>
-      <c r="C2" s="15">
-        <v>0.1487</v>
-      </c>
-      <c r="D2" s="15">
-        <v>0.0492</v>
-      </c>
-      <c r="E2" s="15">
-        <v>0.0459</v>
-      </c>
-      <c r="F2" s="15">
-        <v>-0.0146</v>
-      </c>
-      <c r="G2" s="15">
-        <v>-0.2391</v>
+      <c r="A2" s="13">
+        <v>0.2443</v>
+      </c>
+      <c r="B2" s="13">
+        <v>0.1991</v>
+      </c>
+      <c r="C2" s="13">
+        <v>0.1504</v>
+      </c>
+      <c r="D2" s="13">
+        <v>0.0512</v>
+      </c>
+      <c r="E2" s="13">
+        <v>0.0495</v>
+      </c>
+      <c r="F2" s="13">
+        <v>-0.0149</v>
+      </c>
+      <c r="G2" s="13">
+        <v>-0.2417</v>
       </c>
     </row>
   </sheetData>

--- a/BAJAJ_GROUP_Technical_Metrics.xlsx
+++ b/BAJAJ_GROUP_Technical_Metrics.xlsx
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="253" uniqueCount="64">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="257" uniqueCount="64">
   <si>
     <t>Symbol</t>
   </si>
@@ -896,10 +896,10 @@
         <v>44</v>
       </c>
       <c r="C2">
-        <v>10405</v>
+        <v>10287</v>
       </c>
       <c r="D2">
-        <v>0.19</v>
+        <v>-1.13</v>
       </c>
       <c r="E2">
         <v>12361</v>
@@ -908,46 +908,46 @@
         <v>8599.48</v>
       </c>
       <c r="G2">
-        <v>-15.82</v>
+        <v>-16.78</v>
       </c>
       <c r="H2">
-        <v>21</v>
+        <v>19.62</v>
       </c>
       <c r="I2">
-        <v>6.41</v>
+        <v>2.52</v>
       </c>
       <c r="J2">
-        <v>-10.25</v>
+        <v>-10.55</v>
       </c>
       <c r="K2">
-        <v>-0.36</v>
+        <v>-2.24</v>
       </c>
       <c r="L2">
-        <v>16.38</v>
+        <v>14.6</v>
       </c>
       <c r="M2">
-        <v>24.43</v>
+        <v>24.14</v>
       </c>
       <c r="N2">
         <v>71</v>
       </c>
       <c r="O2">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="P2">
-        <v>10278.4</v>
+        <v>10329</v>
       </c>
       <c r="Q2">
-        <v>10580.6</v>
+        <v>10524.25</v>
       </c>
       <c r="R2">
-        <v>11295.36</v>
+        <v>11268.7</v>
       </c>
       <c r="S2">
-        <v>10198.61</v>
+        <v>10204.28</v>
       </c>
       <c r="T2">
-        <v>2.02</v>
+        <v>0.8100000000000001</v>
       </c>
       <c r="U2" t="s">
         <v>45</v>
@@ -962,34 +962,34 @@
         <v>2</v>
       </c>
       <c r="Y2">
-        <v>42.81</v>
+        <v>40.4</v>
       </c>
       <c r="Z2">
-        <v>-339.51</v>
+        <v>-317.98</v>
       </c>
       <c r="AA2">
-        <v>-370.06</v>
+        <v>-359.64</v>
       </c>
       <c r="AB2">
-        <v>30.55</v>
+        <v>41.66</v>
       </c>
       <c r="AC2">
-        <v>97.04000000000001</v>
+        <v>96.78</v>
       </c>
       <c r="AD2">
-        <v>89.38</v>
+        <v>95.59999999999999</v>
       </c>
       <c r="AE2">
-        <v>257.29</v>
+        <v>254.06</v>
       </c>
       <c r="AF2">
-        <v>-39.09</v>
+        <v>-63.23</v>
       </c>
       <c r="AG2">
-        <v>11833.11</v>
+        <v>11718.96</v>
       </c>
       <c r="AH2">
-        <v>9328.09</v>
+        <v>9329.540000000001</v>
       </c>
       <c r="AI2">
         <v>10503.51</v>
@@ -998,7 +998,7 @@
         <v>47</v>
       </c>
       <c r="AK2">
-        <v>48.8</v>
+        <v>42.83</v>
       </c>
     </row>
     <row r="3" spans="1:37">
@@ -1009,10 +1009,10 @@
         <v>44</v>
       </c>
       <c r="C3">
-        <v>472</v>
+        <v>447.05</v>
       </c>
       <c r="D3">
-        <v>0.75</v>
+        <v>-5.29</v>
       </c>
       <c r="E3">
         <v>670.25</v>
@@ -1021,46 +1021,46 @@
         <v>247.45</v>
       </c>
       <c r="G3">
-        <v>-29.58</v>
+        <v>-33.3</v>
       </c>
       <c r="H3">
-        <v>90.75</v>
+        <v>80.66</v>
       </c>
       <c r="I3">
-        <v>-6.89</v>
+        <v>-9.210000000000001</v>
       </c>
       <c r="J3">
-        <v>-5.23</v>
+        <v>-11.03</v>
       </c>
       <c r="K3">
-        <v>-10.21</v>
+        <v>-17.05</v>
       </c>
       <c r="L3">
-        <v>77.61</v>
+        <v>72.45</v>
       </c>
       <c r="M3">
-        <v>15.04</v>
+        <v>14.24</v>
       </c>
       <c r="N3">
-        <v>99</v>
+        <v>85</v>
       </c>
       <c r="O3">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="P3">
-        <v>492.24</v>
+        <v>483.17</v>
       </c>
       <c r="Q3">
-        <v>496.4</v>
+        <v>493.15</v>
       </c>
       <c r="R3">
-        <v>499.23</v>
+        <v>497.52</v>
       </c>
       <c r="S3">
-        <v>463.78</v>
+        <v>464.74</v>
       </c>
       <c r="T3">
-        <v>1.77</v>
+        <v>-3.81</v>
       </c>
       <c r="U3" t="s">
         <v>45</v>
@@ -1072,46 +1072,46 @@
         <v>45</v>
       </c>
       <c r="X3">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="Y3">
-        <v>42.46</v>
+        <v>36.9</v>
       </c>
       <c r="Z3">
-        <v>-4.66</v>
+        <v>-7.89</v>
       </c>
       <c r="AA3">
-        <v>-3.39</v>
+        <v>-4.29</v>
       </c>
       <c r="AB3">
-        <v>-1.26</v>
+        <v>-3.6</v>
       </c>
       <c r="AC3">
-        <v>43.78</v>
+        <v>10.44</v>
       </c>
       <c r="AD3">
-        <v>67.09999999999999</v>
+        <v>41.68</v>
       </c>
       <c r="AE3">
-        <v>23.44</v>
+        <v>23.96</v>
       </c>
       <c r="AF3">
-        <v>26.05</v>
+        <v>28.57</v>
       </c>
       <c r="AG3">
-        <v>525.47</v>
+        <v>528.65</v>
       </c>
       <c r="AH3">
-        <v>467.34</v>
+        <v>457.64</v>
       </c>
       <c r="AI3">
-        <v>460.99</v>
+        <v>527.52</v>
       </c>
       <c r="AJ3" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="AK3">
-        <v>26.02</v>
+        <v>29.29</v>
       </c>
     </row>
     <row r="4" spans="1:37">
@@ -1122,10 +1122,10 @@
         <v>44</v>
       </c>
       <c r="C4">
-        <v>301.3</v>
+        <v>296.35</v>
       </c>
       <c r="D4">
-        <v>-1.76</v>
+        <v>-1.64</v>
       </c>
       <c r="E4">
         <v>548</v>
@@ -1134,46 +1134,46 @@
         <v>290.05</v>
       </c>
       <c r="G4">
-        <v>-45.02</v>
+        <v>-45.92</v>
       </c>
       <c r="H4">
-        <v>3.88</v>
+        <v>2.17</v>
       </c>
       <c r="I4">
-        <v>1.11</v>
+        <v>-0.84</v>
       </c>
       <c r="J4">
-        <v>-6.59</v>
+        <v>-8.9</v>
       </c>
       <c r="K4">
-        <v>-9.1</v>
+        <v>-11.34</v>
       </c>
       <c r="L4">
-        <v>-44.71</v>
+        <v>-45.92</v>
       </c>
       <c r="M4">
-        <v>-24.17</v>
+        <v>-24.18</v>
       </c>
       <c r="N4">
         <v>15</v>
       </c>
       <c r="O4">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="P4">
-        <v>303.06</v>
+        <v>302.56</v>
       </c>
       <c r="Q4">
-        <v>308.68</v>
+        <v>307.34</v>
       </c>
       <c r="R4">
-        <v>330.18</v>
+        <v>328.46</v>
       </c>
       <c r="S4">
-        <v>358.96</v>
+        <v>358.08</v>
       </c>
       <c r="T4">
-        <v>-16.06</v>
+        <v>-17.24</v>
       </c>
       <c r="U4" t="s">
         <v>45</v>
@@ -1188,34 +1188,34 @@
         <v>0</v>
       </c>
       <c r="Y4">
-        <v>39.3</v>
+        <v>35.93</v>
       </c>
       <c r="Z4">
-        <v>-7.76</v>
+        <v>-7.82</v>
       </c>
       <c r="AA4">
-        <v>-8.720000000000001</v>
+        <v>-8.539999999999999</v>
       </c>
       <c r="AB4">
-        <v>0.96</v>
+        <v>0.72</v>
       </c>
       <c r="AC4">
-        <v>92.59999999999999</v>
+        <v>79.17</v>
       </c>
       <c r="AD4">
-        <v>85.03</v>
+        <v>87.20999999999999</v>
       </c>
       <c r="AE4">
-        <v>11.58</v>
+        <v>11.25</v>
       </c>
       <c r="AF4">
-        <v>-16.85</v>
+        <v>-75</v>
       </c>
       <c r="AG4">
-        <v>331.38</v>
+        <v>329.62</v>
       </c>
       <c r="AH4">
-        <v>285.97</v>
+        <v>285.06</v>
       </c>
       <c r="AI4">
         <v>322.52</v>
@@ -1224,7 +1224,7 @@
         <v>47</v>
       </c>
       <c r="AK4">
-        <v>50.65</v>
+        <v>49.13</v>
       </c>
     </row>
     <row r="5" spans="1:37">
@@ -1235,10 +1235,10 @@
         <v>44</v>
       </c>
       <c r="C5">
-        <v>1729</v>
+        <v>1700</v>
       </c>
       <c r="D5">
-        <v>-0.17</v>
+        <v>-1.68</v>
       </c>
       <c r="E5">
         <v>2176.6</v>
@@ -1247,46 +1247,46 @@
         <v>1631.8</v>
       </c>
       <c r="G5">
-        <v>-20.56</v>
+        <v>-21.9</v>
       </c>
       <c r="H5">
-        <v>5.96</v>
+        <v>4.18</v>
       </c>
       <c r="I5">
-        <v>-0.33</v>
+        <v>-1.16</v>
       </c>
       <c r="J5">
-        <v>-5.88</v>
+        <v>-8.56</v>
       </c>
       <c r="K5">
-        <v>-6.74</v>
+        <v>-8.68</v>
       </c>
       <c r="L5">
-        <v>-14.42</v>
+        <v>-15.82</v>
       </c>
       <c r="M5">
-        <v>-1.49</v>
+        <v>-2.24</v>
       </c>
       <c r="N5">
         <v>29</v>
       </c>
       <c r="O5">
-        <v>42</v>
+        <v>39</v>
       </c>
       <c r="P5">
-        <v>1731.66</v>
+        <v>1727.68</v>
       </c>
       <c r="Q5">
-        <v>1760.58</v>
+        <v>1752.96</v>
       </c>
       <c r="R5">
-        <v>1893.47</v>
+        <v>1885.75</v>
       </c>
       <c r="S5">
-        <v>1869.62</v>
+        <v>1867.99</v>
       </c>
       <c r="T5">
-        <v>-7.52</v>
+        <v>-8.99</v>
       </c>
       <c r="U5" t="s">
         <v>45</v>
@@ -1301,34 +1301,34 @@
         <v>1</v>
       </c>
       <c r="Y5">
-        <v>37.15</v>
+        <v>33.26</v>
       </c>
       <c r="Z5">
-        <v>-45.56</v>
+        <v>-45.71</v>
       </c>
       <c r="AA5">
-        <v>-50.64</v>
+        <v>-49.66</v>
       </c>
       <c r="AB5">
-        <v>5.09</v>
+        <v>3.94</v>
       </c>
       <c r="AC5">
-        <v>79.12</v>
+        <v>74.79000000000001</v>
       </c>
       <c r="AD5">
-        <v>80.29000000000001</v>
+        <v>79.63</v>
       </c>
       <c r="AE5">
-        <v>38.22</v>
+        <v>38.36</v>
       </c>
       <c r="AF5">
-        <v>26.53</v>
+        <v>1.4</v>
       </c>
       <c r="AG5">
-        <v>1850.96</v>
+        <v>1836.13</v>
       </c>
       <c r="AH5">
-        <v>1670.2</v>
+        <v>1669.78</v>
       </c>
       <c r="AI5">
         <v>1825.61</v>
@@ -1337,7 +1337,7 @@
         <v>47</v>
       </c>
       <c r="AK5">
-        <v>53.7</v>
+        <v>53.25</v>
       </c>
     </row>
     <row r="6" spans="1:37">
@@ -1348,10 +1348,10 @@
         <v>44</v>
       </c>
       <c r="C6">
-        <v>11198</v>
+        <v>11265</v>
       </c>
       <c r="D6">
-        <v>-0.24</v>
+        <v>0.6</v>
       </c>
       <c r="E6">
         <v>13144</v>
@@ -1360,46 +1360,46 @@
         <v>8746</v>
       </c>
       <c r="G6">
-        <v>-14.81</v>
+        <v>-14.3</v>
       </c>
       <c r="H6">
-        <v>28.04</v>
+        <v>28.8</v>
       </c>
       <c r="I6">
-        <v>3.49</v>
+        <v>4.79</v>
       </c>
       <c r="J6">
-        <v>2.45</v>
+        <v>2.32</v>
       </c>
       <c r="K6">
-        <v>7.69</v>
+        <v>9.380000000000001</v>
       </c>
       <c r="L6">
-        <v>-9.359999999999999</v>
+        <v>-7.75</v>
       </c>
       <c r="M6">
-        <v>19.91</v>
+        <v>19.87</v>
       </c>
       <c r="N6">
         <v>57</v>
       </c>
       <c r="O6">
-        <v>62</v>
+        <v>67</v>
       </c>
       <c r="P6">
-        <v>10951</v>
+        <v>11054</v>
       </c>
       <c r="Q6">
-        <v>10910.25</v>
+        <v>10909.4</v>
       </c>
       <c r="R6">
-        <v>11130.86</v>
+        <v>11128.42</v>
       </c>
       <c r="S6">
-        <v>10659.48</v>
+        <v>10660.9</v>
       </c>
       <c r="T6">
-        <v>5.05</v>
+        <v>5.67</v>
       </c>
       <c r="U6" t="s">
         <v>45</v>
@@ -1414,34 +1414,34 @@
         <v>2</v>
       </c>
       <c r="Y6">
-        <v>56.84</v>
+        <v>58.34</v>
       </c>
       <c r="Z6">
-        <v>-33.64</v>
+        <v>-2.62</v>
       </c>
       <c r="AA6">
-        <v>-89.89</v>
+        <v>-72.44</v>
       </c>
       <c r="AB6">
-        <v>56.25</v>
+        <v>69.81999999999999</v>
       </c>
       <c r="AC6">
-        <v>95.2</v>
+        <v>98.64</v>
       </c>
       <c r="AD6">
-        <v>77.51000000000001</v>
+        <v>90.94</v>
       </c>
       <c r="AE6">
-        <v>268.76</v>
+        <v>264.35</v>
       </c>
       <c r="AF6">
-        <v>-37</v>
+        <v>-37.8</v>
       </c>
       <c r="AG6">
-        <v>11466.03</v>
+        <v>11462.84</v>
       </c>
       <c r="AH6">
-        <v>10354.47</v>
+        <v>10355.96</v>
       </c>
       <c r="AI6">
         <v>11368.55</v>
@@ -1450,7 +1450,7 @@
         <v>47</v>
       </c>
       <c r="AK6">
-        <v>26.86</v>
+        <v>28.26</v>
       </c>
     </row>
     <row r="7" spans="1:37">
@@ -1461,10 +1461,10 @@
         <v>44</v>
       </c>
       <c r="C7">
-        <v>982.1</v>
+        <v>957.35</v>
       </c>
       <c r="D7">
-        <v>1.75</v>
+        <v>-2.52</v>
       </c>
       <c r="E7">
         <v>1158.8</v>
@@ -1473,46 +1473,46 @@
         <v>801.55</v>
       </c>
       <c r="G7">
-        <v>-15.25</v>
+        <v>-17.38</v>
       </c>
       <c r="H7">
-        <v>22.53</v>
+        <v>19.44</v>
       </c>
       <c r="I7">
-        <v>2.3</v>
+        <v>0.01</v>
       </c>
       <c r="J7">
-        <v>-2.4</v>
+        <v>-5.68</v>
       </c>
       <c r="K7">
-        <v>-7.02</v>
+        <v>-10.02</v>
       </c>
       <c r="L7">
-        <v>-5.27</v>
+        <v>-6.06</v>
       </c>
       <c r="M7">
-        <v>4.95</v>
+        <v>4.74</v>
       </c>
       <c r="N7">
         <v>43</v>
       </c>
       <c r="O7">
-        <v>52</v>
+        <v>49</v>
       </c>
       <c r="P7">
-        <v>968.87</v>
+        <v>968.89</v>
       </c>
       <c r="Q7">
-        <v>980.8099999999999</v>
+        <v>976.66</v>
       </c>
       <c r="R7">
-        <v>1034.22</v>
+        <v>1030.47</v>
       </c>
       <c r="S7">
-        <v>974.36</v>
+        <v>974.2</v>
       </c>
       <c r="T7">
-        <v>0.79</v>
+        <v>-1.73</v>
       </c>
       <c r="U7" t="s">
         <v>45</v>
@@ -1524,37 +1524,37 @@
         <v>45</v>
       </c>
       <c r="X7">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="Y7">
-        <v>47.29</v>
+        <v>41.61</v>
       </c>
       <c r="Z7">
-        <v>-18.41</v>
+        <v>-18.24</v>
       </c>
       <c r="AA7">
-        <v>-21.86</v>
+        <v>-21.14</v>
       </c>
       <c r="AB7">
-        <v>3.45</v>
+        <v>2.89</v>
       </c>
       <c r="AC7">
-        <v>77.11</v>
+        <v>79.25</v>
       </c>
       <c r="AD7">
-        <v>67.55</v>
+        <v>75.62</v>
       </c>
       <c r="AE7">
-        <v>25.68</v>
+        <v>25.98</v>
       </c>
       <c r="AF7">
-        <v>3.74</v>
+        <v>7.89</v>
       </c>
       <c r="AG7">
-        <v>1036.7</v>
+        <v>1025.88</v>
       </c>
       <c r="AH7">
-        <v>924.9299999999999</v>
+        <v>927.45</v>
       </c>
       <c r="AI7">
         <v>1020.6</v>
@@ -1563,7 +1563,7 @@
         <v>47</v>
       </c>
       <c r="AK7">
-        <v>19.45</v>
+        <v>19.14</v>
       </c>
     </row>
     <row r="8" spans="1:37">
@@ -1574,10 +1574,10 @@
         <v>44</v>
       </c>
       <c r="C8">
-        <v>171.99</v>
+        <v>164.48</v>
       </c>
       <c r="D8">
-        <v>0.96</v>
+        <v>-4.37</v>
       </c>
       <c r="E8">
         <v>185.92</v>
@@ -1586,46 +1586,46 @@
         <v>115.96</v>
       </c>
       <c r="G8">
-        <v>-7.49</v>
+        <v>-11.53</v>
       </c>
       <c r="H8">
-        <v>48.32</v>
+        <v>41.84</v>
       </c>
       <c r="I8">
-        <v>-2.27</v>
+        <v>-7.38</v>
       </c>
       <c r="J8">
-        <v>27.5</v>
+        <v>22.56</v>
       </c>
       <c r="K8">
-        <v>18.05</v>
+        <v>14.33</v>
       </c>
       <c r="L8">
-        <v>32.62</v>
+        <v>29.03</v>
       </c>
       <c r="M8">
-        <v>5.12</v>
+        <v>4.55</v>
       </c>
       <c r="N8">
-        <v>85</v>
+        <v>99</v>
       </c>
       <c r="O8">
-        <v>88</v>
+        <v>86</v>
       </c>
       <c r="P8">
-        <v>174.29</v>
+        <v>171.67</v>
       </c>
       <c r="Q8">
-        <v>167.97</v>
+        <v>169.45</v>
       </c>
       <c r="R8">
-        <v>149.38</v>
+        <v>149.8</v>
       </c>
       <c r="S8">
-        <v>137.35</v>
+        <v>137.5</v>
       </c>
       <c r="T8">
-        <v>25.22</v>
+        <v>19.62</v>
       </c>
       <c r="U8" t="s">
         <v>46</v>
@@ -1640,34 +1640,34 @@
         <v>3</v>
       </c>
       <c r="Y8">
-        <v>58.54</v>
+        <v>50.61</v>
       </c>
       <c r="Z8">
-        <v>8.18</v>
+        <v>6.94</v>
       </c>
       <c r="AA8">
-        <v>9.359999999999999</v>
+        <v>8.880000000000001</v>
       </c>
       <c r="AB8">
-        <v>-1.18</v>
+        <v>-1.94</v>
       </c>
       <c r="AC8">
         <v>1.68</v>
       </c>
       <c r="AD8">
-        <v>4.26</v>
+        <v>1.51</v>
       </c>
       <c r="AE8">
-        <v>7.71</v>
+        <v>7.77</v>
       </c>
       <c r="AF8">
-        <v>-80.87</v>
+        <v>-71.05</v>
       </c>
       <c r="AG8">
-        <v>198.26</v>
+        <v>195.51</v>
       </c>
       <c r="AH8">
-        <v>137.68</v>
+        <v>143.4</v>
       </c>
       <c r="AI8">
         <v>159.98</v>
@@ -1676,12 +1676,72 @@
         <v>48</v>
       </c>
       <c r="AK8">
-        <v>33.87</v>
+        <v>31.54</v>
       </c>
     </row>
   </sheetData>
   <autoFilter ref="A1:AK8"/>
   <conditionalFormatting sqref="AF2:AF8">
+    <cfRule type="colorScale" priority="13">
+      <colorScale>
+        <cfvo type="min" val="0"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max" val="0"/>
+        <color rgb="FFF8696B"/>
+        <color rgb="FFFFFFFF"/>
+        <color rgb="FF63BE7B"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="D2:D8">
+    <cfRule type="colorScale" priority="7">
+      <colorScale>
+        <cfvo type="min" val="0"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max" val="0"/>
+        <color rgb="FFF8696B"/>
+        <color rgb="FFFFFFFF"/>
+        <color rgb="FF63BE7B"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="I2:I8">
+    <cfRule type="colorScale" priority="8">
+      <colorScale>
+        <cfvo type="min" val="0"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max" val="0"/>
+        <color rgb="FFF8696B"/>
+        <color rgb="FFFFFFFF"/>
+        <color rgb="FF63BE7B"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="J2:J8">
+    <cfRule type="colorScale" priority="9">
+      <colorScale>
+        <cfvo type="min" val="0"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max" val="0"/>
+        <color rgb="FFF8696B"/>
+        <color rgb="FFFFFFFF"/>
+        <color rgb="FF63BE7B"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="K2:K8">
+    <cfRule type="colorScale" priority="10">
+      <colorScale>
+        <cfvo type="min" val="0"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max" val="0"/>
+        <color rgb="FFF8696B"/>
+        <color rgb="FFFFFFFF"/>
+        <color rgb="FF63BE7B"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="L2:L8">
     <cfRule type="colorScale" priority="11">
       <colorScale>
         <cfvo type="min" val="0"/>
@@ -1693,8 +1753,14 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="D2:D8">
-    <cfRule type="colorScale" priority="5">
+  <conditionalFormatting sqref="N2:N8">
+    <cfRule type="cellIs" dxfId="2" priority="5" operator="greaterThanOrEqual">
+      <formula>80</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="3" priority="6" operator="lessThanOrEqual">
+      <formula>20</formula>
+    </cfRule>
+    <cfRule type="colorScale" priority="12">
       <colorScale>
         <cfvo type="min" val="0"/>
         <cfvo type="percentile" val="50"/>
@@ -1703,72 +1769,6 @@
         <color rgb="FFFFFFFF"/>
         <color rgb="FF63BE7B"/>
       </colorScale>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="I2:I8">
-    <cfRule type="colorScale" priority="6">
-      <colorScale>
-        <cfvo type="min" val="0"/>
-        <cfvo type="percentile" val="50"/>
-        <cfvo type="max" val="0"/>
-        <color rgb="FFF8696B"/>
-        <color rgb="FFFFFFFF"/>
-        <color rgb="FF63BE7B"/>
-      </colorScale>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="J2:J8">
-    <cfRule type="colorScale" priority="7">
-      <colorScale>
-        <cfvo type="min" val="0"/>
-        <cfvo type="percentile" val="50"/>
-        <cfvo type="max" val="0"/>
-        <color rgb="FFF8696B"/>
-        <color rgb="FFFFFFFF"/>
-        <color rgb="FF63BE7B"/>
-      </colorScale>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="K2:K8">
-    <cfRule type="colorScale" priority="8">
-      <colorScale>
-        <cfvo type="min" val="0"/>
-        <cfvo type="percentile" val="50"/>
-        <cfvo type="max" val="0"/>
-        <color rgb="FFF8696B"/>
-        <color rgb="FFFFFFFF"/>
-        <color rgb="FF63BE7B"/>
-      </colorScale>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="L2:L8">
-    <cfRule type="colorScale" priority="9">
-      <colorScale>
-        <cfvo type="min" val="0"/>
-        <cfvo type="percentile" val="50"/>
-        <cfvo type="max" val="0"/>
-        <color rgb="FFF8696B"/>
-        <color rgb="FFFFFFFF"/>
-        <color rgb="FF63BE7B"/>
-      </colorScale>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="N2:N8">
-    <cfRule type="colorScale" priority="10">
-      <colorScale>
-        <cfvo type="min" val="0"/>
-        <cfvo type="percentile" val="50"/>
-        <cfvo type="max" val="0"/>
-        <color rgb="FFF8696B"/>
-        <color rgb="FFFFFFFF"/>
-        <color rgb="FF63BE7B"/>
-      </colorScale>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="2" priority="18" operator="greaterThanOrEqual">
-      <formula>80</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="3" priority="19" operator="lessThanOrEqual">
-      <formula>20</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="T2:T8">
@@ -1780,26 +1780,26 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="U2:U8">
-    <cfRule type="containsText" dxfId="1" priority="12" operator="containsText" text="Yes">
+    <cfRule type="containsText" dxfId="1" priority="14" operator="containsText" text="Yes">
       <formula>NOT(ISERROR(SEARCH("Yes",U2)))</formula>
     </cfRule>
-    <cfRule type="containsText" dxfId="0" priority="13" operator="containsText" text="No">
+    <cfRule type="containsText" dxfId="0" priority="15" operator="containsText" text="No">
       <formula>NOT(ISERROR(SEARCH("No",U2)))</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="V2:V8">
-    <cfRule type="containsText" dxfId="1" priority="14" operator="containsText" text="Yes">
+    <cfRule type="containsText" dxfId="1" priority="16" operator="containsText" text="Yes">
       <formula>NOT(ISERROR(SEARCH("Yes",V2)))</formula>
     </cfRule>
-    <cfRule type="containsText" dxfId="0" priority="15" operator="containsText" text="No">
+    <cfRule type="containsText" dxfId="0" priority="17" operator="containsText" text="No">
       <formula>NOT(ISERROR(SEARCH("No",V2)))</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="W2:W8">
-    <cfRule type="containsText" dxfId="1" priority="16" operator="containsText" text="Yes">
+    <cfRule type="containsText" dxfId="1" priority="18" operator="containsText" text="Yes">
       <formula>NOT(ISERROR(SEARCH("Yes",W2)))</formula>
     </cfRule>
-    <cfRule type="containsText" dxfId="0" priority="17" operator="containsText" text="No">
+    <cfRule type="containsText" dxfId="0" priority="19" operator="containsText" text="No">
       <formula>NOT(ISERROR(SEARCH("No",W2)))</formula>
     </cfRule>
   </conditionalFormatting>
@@ -1817,7 +1817,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:F62"/>
+  <dimension ref="A1:F64"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="16.7109375" customWidth="1"/>
@@ -1874,13 +1874,13 @@
         <v>9</v>
       </c>
       <c r="C7" s="5">
-        <v>-9.09</v>
+        <v>-10.25</v>
       </c>
       <c r="D7" s="5">
-        <v>-10.25</v>
+        <v>-10.55</v>
       </c>
       <c r="E7" s="6">
-        <v>-1.16</v>
+        <v>-0.3</v>
       </c>
     </row>
     <row r="8" spans="1:6">
@@ -1891,13 +1891,13 @@
         <v>9</v>
       </c>
       <c r="C8" s="5">
-        <v>-7.01</v>
+        <v>-5.23</v>
       </c>
       <c r="D8" s="5">
-        <v>-5.23</v>
-      </c>
-      <c r="E8" s="7">
-        <v>1.78</v>
+        <v>-11.03</v>
+      </c>
+      <c r="E8" s="6">
+        <v>-5.8</v>
       </c>
     </row>
     <row r="9" spans="1:6">
@@ -1908,13 +1908,13 @@
         <v>9</v>
       </c>
       <c r="C9" s="5">
-        <v>-6.61</v>
+        <v>-6.59</v>
       </c>
       <c r="D9" s="5">
-        <v>-6.59</v>
-      </c>
-      <c r="E9" s="7">
-        <v>0.02</v>
+        <v>-8.9</v>
+      </c>
+      <c r="E9" s="6">
+        <v>-2.31</v>
       </c>
     </row>
     <row r="10" spans="1:6">
@@ -1925,13 +1925,13 @@
         <v>9</v>
       </c>
       <c r="C10" s="5">
-        <v>-6.66</v>
+        <v>-5.88</v>
       </c>
       <c r="D10" s="5">
-        <v>-5.88</v>
-      </c>
-      <c r="E10" s="7">
-        <v>0.78</v>
+        <v>-8.56</v>
+      </c>
+      <c r="E10" s="6">
+        <v>-2.68</v>
       </c>
     </row>
     <row r="11" spans="1:6">
@@ -1942,13 +1942,13 @@
         <v>9</v>
       </c>
       <c r="C11" s="5">
-        <v>1.13</v>
+        <v>2.45</v>
       </c>
       <c r="D11" s="5">
-        <v>2.45</v>
-      </c>
-      <c r="E11" s="7">
-        <v>1.32</v>
+        <v>2.32</v>
+      </c>
+      <c r="E11" s="6">
+        <v>-0.13</v>
       </c>
     </row>
     <row r="12" spans="1:6">
@@ -1959,13 +1959,13 @@
         <v>9</v>
       </c>
       <c r="C12" s="5">
-        <v>-4.35</v>
+        <v>-2.4</v>
       </c>
       <c r="D12" s="5">
-        <v>-2.4</v>
-      </c>
-      <c r="E12" s="7">
-        <v>1.95</v>
+        <v>-5.68</v>
+      </c>
+      <c r="E12" s="6">
+        <v>-3.28</v>
       </c>
     </row>
     <row r="13" spans="1:6">
@@ -1976,13 +1976,13 @@
         <v>9</v>
       </c>
       <c r="C13" s="5">
-        <v>25.61</v>
+        <v>27.5</v>
       </c>
       <c r="D13" s="5">
-        <v>27.5</v>
-      </c>
-      <c r="E13" s="7">
-        <v>1.89</v>
+        <v>22.56</v>
+      </c>
+      <c r="E13" s="6">
+        <v>-4.94</v>
       </c>
     </row>
     <row r="14" spans="1:6">
@@ -1993,13 +1993,13 @@
         <v>8</v>
       </c>
       <c r="C14" s="5">
-        <v>7.76</v>
+        <v>6.41</v>
       </c>
       <c r="D14" s="5">
-        <v>6.41</v>
+        <v>2.52</v>
       </c>
       <c r="E14" s="6">
-        <v>-1.35</v>
+        <v>-3.89</v>
       </c>
     </row>
     <row r="15" spans="1:6">
@@ -2010,13 +2010,13 @@
         <v>8</v>
       </c>
       <c r="C15" s="5">
-        <v>-4.22</v>
+        <v>-6.89</v>
       </c>
       <c r="D15" s="5">
-        <v>-6.89</v>
+        <v>-9.210000000000001</v>
       </c>
       <c r="E15" s="6">
-        <v>-2.67</v>
+        <v>-2.32</v>
       </c>
     </row>
     <row r="16" spans="1:6">
@@ -2027,13 +2027,13 @@
         <v>8</v>
       </c>
       <c r="C16" s="5">
-        <v>5.74</v>
+        <v>1.11</v>
       </c>
       <c r="D16" s="5">
-        <v>1.11</v>
+        <v>-0.84</v>
       </c>
       <c r="E16" s="6">
-        <v>-4.63</v>
+        <v>-1.95</v>
       </c>
     </row>
     <row r="17" spans="1:5">
@@ -2044,13 +2044,13 @@
         <v>8</v>
       </c>
       <c r="C17" s="5">
-        <v>1.41</v>
+        <v>-0.33</v>
       </c>
       <c r="D17" s="5">
-        <v>-0.33</v>
+        <v>-1.16</v>
       </c>
       <c r="E17" s="6">
-        <v>-1.74</v>
+        <v>-0.83</v>
       </c>
     </row>
     <row r="18" spans="1:5">
@@ -2061,13 +2061,13 @@
         <v>8</v>
       </c>
       <c r="C18" s="5">
-        <v>5.9</v>
+        <v>3.49</v>
       </c>
       <c r="D18" s="5">
-        <v>3.49</v>
-      </c>
-      <c r="E18" s="6">
-        <v>-2.41</v>
+        <v>4.79</v>
+      </c>
+      <c r="E18" s="7">
+        <v>1.3</v>
       </c>
     </row>
     <row r="19" spans="1:5">
@@ -2078,13 +2078,13 @@
         <v>8</v>
       </c>
       <c r="C19" s="5">
-        <v>0.97</v>
+        <v>2.3</v>
       </c>
       <c r="D19" s="5">
-        <v>2.3</v>
-      </c>
-      <c r="E19" s="7">
-        <v>1.33</v>
+        <v>0.01</v>
+      </c>
+      <c r="E19" s="6">
+        <v>-2.29</v>
       </c>
     </row>
     <row r="20" spans="1:5">
@@ -2095,13 +2095,13 @@
         <v>8</v>
       </c>
       <c r="C20" s="5">
-        <v>-2.26</v>
+        <v>-2.27</v>
       </c>
       <c r="D20" s="5">
-        <v>-2.27</v>
+        <v>-7.38</v>
       </c>
       <c r="E20" s="6">
-        <v>-0.01</v>
+        <v>-5.11</v>
       </c>
     </row>
     <row r="21" spans="1:5">
@@ -2112,13 +2112,13 @@
         <v>11</v>
       </c>
       <c r="C21" s="5">
-        <v>17.71</v>
+        <v>16.38</v>
       </c>
       <c r="D21" s="5">
-        <v>16.38</v>
+        <v>14.6</v>
       </c>
       <c r="E21" s="6">
-        <v>-1.33</v>
+        <v>-1.78</v>
       </c>
     </row>
     <row r="22" spans="1:5">
@@ -2129,13 +2129,13 @@
         <v>11</v>
       </c>
       <c r="C22" s="5">
-        <v>77.38</v>
+        <v>77.61</v>
       </c>
       <c r="D22" s="5">
-        <v>77.61</v>
-      </c>
-      <c r="E22" s="7">
-        <v>0.23</v>
+        <v>72.45</v>
+      </c>
+      <c r="E22" s="6">
+        <v>-5.16</v>
       </c>
     </row>
     <row r="23" spans="1:5">
@@ -2146,13 +2146,13 @@
         <v>11</v>
       </c>
       <c r="C23" s="5">
-        <v>-43.53</v>
+        <v>-44.71</v>
       </c>
       <c r="D23" s="5">
-        <v>-44.71</v>
+        <v>-45.92</v>
       </c>
       <c r="E23" s="6">
-        <v>-1.18</v>
+        <v>-1.21</v>
       </c>
     </row>
     <row r="24" spans="1:5">
@@ -2163,13 +2163,13 @@
         <v>11</v>
       </c>
       <c r="C24" s="5">
-        <v>-13.59</v>
+        <v>-14.42</v>
       </c>
       <c r="D24" s="5">
-        <v>-14.42</v>
+        <v>-15.82</v>
       </c>
       <c r="E24" s="6">
-        <v>-0.83</v>
+        <v>-1.4</v>
       </c>
     </row>
     <row r="25" spans="1:5">
@@ -2180,13 +2180,13 @@
         <v>11</v>
       </c>
       <c r="C25" s="5">
-        <v>-7.03</v>
+        <v>-9.359999999999999</v>
       </c>
       <c r="D25" s="5">
-        <v>-9.359999999999999</v>
-      </c>
-      <c r="E25" s="6">
-        <v>-2.33</v>
+        <v>-7.75</v>
+      </c>
+      <c r="E25" s="7">
+        <v>1.61</v>
       </c>
     </row>
     <row r="26" spans="1:5">
@@ -2197,13 +2197,13 @@
         <v>11</v>
       </c>
       <c r="C26" s="5">
-        <v>-5.72</v>
+        <v>-5.27</v>
       </c>
       <c r="D26" s="5">
-        <v>-5.27</v>
-      </c>
-      <c r="E26" s="7">
-        <v>0.45</v>
+        <v>-6.06</v>
+      </c>
+      <c r="E26" s="6">
+        <v>-0.79</v>
       </c>
     </row>
     <row r="27" spans="1:5">
@@ -2214,13 +2214,13 @@
         <v>11</v>
       </c>
       <c r="C27" s="5">
-        <v>28.89</v>
+        <v>32.62</v>
       </c>
       <c r="D27" s="5">
-        <v>32.62</v>
-      </c>
-      <c r="E27" s="7">
-        <v>3.73</v>
+        <v>29.03</v>
+      </c>
+      <c r="E27" s="6">
+        <v>-3.59</v>
       </c>
     </row>
     <row r="28" spans="1:5">
@@ -2231,13 +2231,13 @@
         <v>10</v>
       </c>
       <c r="C28" s="5">
-        <v>0.52</v>
+        <v>-0.36</v>
       </c>
       <c r="D28" s="5">
-        <v>-0.36</v>
+        <v>-2.24</v>
       </c>
       <c r="E28" s="6">
-        <v>-0.88</v>
+        <v>-1.88</v>
       </c>
     </row>
     <row r="29" spans="1:5">
@@ -2248,13 +2248,13 @@
         <v>10</v>
       </c>
       <c r="C29" s="5">
-        <v>-15.39</v>
+        <v>-10.21</v>
       </c>
       <c r="D29" s="5">
-        <v>-10.21</v>
-      </c>
-      <c r="E29" s="7">
-        <v>5.18</v>
+        <v>-17.05</v>
+      </c>
+      <c r="E29" s="6">
+        <v>-6.84</v>
       </c>
     </row>
     <row r="30" spans="1:5">
@@ -2265,13 +2265,13 @@
         <v>10</v>
       </c>
       <c r="C30" s="5">
-        <v>-8.69</v>
+        <v>-9.1</v>
       </c>
       <c r="D30" s="5">
-        <v>-9.1</v>
+        <v>-11.34</v>
       </c>
       <c r="E30" s="6">
-        <v>-0.41</v>
+        <v>-2.24</v>
       </c>
     </row>
     <row r="31" spans="1:5">
@@ -2282,13 +2282,13 @@
         <v>10</v>
       </c>
       <c r="C31" s="5">
-        <v>-5.8</v>
+        <v>-6.74</v>
       </c>
       <c r="D31" s="5">
-        <v>-6.74</v>
+        <v>-8.68</v>
       </c>
       <c r="E31" s="6">
-        <v>-0.9399999999999999</v>
+        <v>-1.94</v>
       </c>
     </row>
     <row r="32" spans="1:5">
@@ -2299,13 +2299,13 @@
         <v>10</v>
       </c>
       <c r="C32" s="5">
-        <v>7.76</v>
+        <v>7.69</v>
       </c>
       <c r="D32" s="5">
-        <v>7.69</v>
-      </c>
-      <c r="E32" s="6">
-        <v>-0.07000000000000001</v>
+        <v>9.380000000000001</v>
+      </c>
+      <c r="E32" s="7">
+        <v>1.69</v>
       </c>
     </row>
     <row r="33" spans="1:5">
@@ -2316,13 +2316,13 @@
         <v>10</v>
       </c>
       <c r="C33" s="5">
-        <v>-6.97</v>
+        <v>-7.02</v>
       </c>
       <c r="D33" s="5">
-        <v>-7.02</v>
+        <v>-10.02</v>
       </c>
       <c r="E33" s="6">
-        <v>-0.05</v>
+        <v>-3</v>
       </c>
     </row>
     <row r="34" spans="1:5">
@@ -2333,13 +2333,13 @@
         <v>10</v>
       </c>
       <c r="C34" s="5">
-        <v>16.52</v>
+        <v>18.05</v>
       </c>
       <c r="D34" s="5">
-        <v>18.05</v>
-      </c>
-      <c r="E34" s="7">
-        <v>1.53</v>
+        <v>14.33</v>
+      </c>
+      <c r="E34" s="6">
+        <v>-3.72</v>
       </c>
     </row>
     <row r="35" spans="1:5">
@@ -2350,13 +2350,13 @@
         <v>6</v>
       </c>
       <c r="C35" s="5">
-        <v>-15.99</v>
+        <v>-15.82</v>
       </c>
       <c r="D35" s="5">
-        <v>-15.82</v>
-      </c>
-      <c r="E35" s="7">
-        <v>0.17</v>
+        <v>-16.78</v>
+      </c>
+      <c r="E35" s="6">
+        <v>-0.96</v>
       </c>
     </row>
     <row r="36" spans="1:5">
@@ -2367,13 +2367,13 @@
         <v>6</v>
       </c>
       <c r="C36" s="5">
-        <v>-30.1</v>
+        <v>-29.58</v>
       </c>
       <c r="D36" s="5">
-        <v>-29.58</v>
-      </c>
-      <c r="E36" s="7">
-        <v>0.52</v>
+        <v>-33.3</v>
+      </c>
+      <c r="E36" s="6">
+        <v>-3.72</v>
       </c>
     </row>
     <row r="37" spans="1:5">
@@ -2384,13 +2384,13 @@
         <v>6</v>
       </c>
       <c r="C37" s="5">
-        <v>-44.03</v>
+        <v>-45.02</v>
       </c>
       <c r="D37" s="5">
-        <v>-45.02</v>
+        <v>-45.92</v>
       </c>
       <c r="E37" s="6">
-        <v>-0.99</v>
+        <v>-0.9</v>
       </c>
     </row>
     <row r="38" spans="1:5">
@@ -2401,13 +2401,13 @@
         <v>6</v>
       </c>
       <c r="C38" s="5">
-        <v>-20.43</v>
+        <v>-20.56</v>
       </c>
       <c r="D38" s="5">
-        <v>-20.56</v>
+        <v>-21.9</v>
       </c>
       <c r="E38" s="6">
-        <v>-0.13</v>
+        <v>-1.34</v>
       </c>
     </row>
     <row r="39" spans="1:5">
@@ -2418,13 +2418,13 @@
         <v>6</v>
       </c>
       <c r="C39" s="5">
-        <v>-14.6</v>
+        <v>-14.81</v>
       </c>
       <c r="D39" s="5">
-        <v>-14.81</v>
-      </c>
-      <c r="E39" s="6">
-        <v>-0.21</v>
+        <v>-14.3</v>
+      </c>
+      <c r="E39" s="7">
+        <v>0.51</v>
       </c>
     </row>
     <row r="40" spans="1:5">
@@ -2435,13 +2435,13 @@
         <v>6</v>
       </c>
       <c r="C40" s="5">
-        <v>-16.7</v>
+        <v>-15.25</v>
       </c>
       <c r="D40" s="5">
-        <v>-15.25</v>
-      </c>
-      <c r="E40" s="7">
-        <v>1.45</v>
+        <v>-17.38</v>
+      </c>
+      <c r="E40" s="6">
+        <v>-2.13</v>
       </c>
     </row>
     <row r="41" spans="1:5">
@@ -2452,13 +2452,13 @@
         <v>6</v>
       </c>
       <c r="C41" s="5">
-        <v>-8.369999999999999</v>
+        <v>-7.49</v>
       </c>
       <c r="D41" s="5">
-        <v>-7.49</v>
-      </c>
-      <c r="E41" s="7">
-        <v>0.88</v>
+        <v>-11.53</v>
+      </c>
+      <c r="E41" s="6">
+        <v>-4.04</v>
       </c>
     </row>
     <row r="42" spans="1:5">
@@ -2469,13 +2469,13 @@
         <v>2</v>
       </c>
       <c r="C42" s="5">
-        <v>10385</v>
+        <v>10405</v>
       </c>
       <c r="D42" s="5">
-        <v>10405</v>
-      </c>
-      <c r="E42" s="7">
-        <v>20</v>
+        <v>10287</v>
+      </c>
+      <c r="E42" s="6">
+        <v>-118</v>
       </c>
     </row>
     <row r="43" spans="1:5">
@@ -2486,13 +2486,13 @@
         <v>2</v>
       </c>
       <c r="C43" s="5">
-        <v>468.5</v>
+        <v>472</v>
       </c>
       <c r="D43" s="5">
-        <v>472</v>
-      </c>
-      <c r="E43" s="7">
-        <v>3.5</v>
+        <v>447.05</v>
+      </c>
+      <c r="E43" s="6">
+        <v>-24.95</v>
       </c>
     </row>
     <row r="44" spans="1:5">
@@ -2503,13 +2503,13 @@
         <v>2</v>
       </c>
       <c r="C44" s="5">
-        <v>306.7</v>
+        <v>301.3</v>
       </c>
       <c r="D44" s="5">
-        <v>301.3</v>
+        <v>296.35</v>
       </c>
       <c r="E44" s="6">
-        <v>-5.4</v>
+        <v>-4.95</v>
       </c>
     </row>
     <row r="45" spans="1:5">
@@ -2520,13 +2520,13 @@
         <v>2</v>
       </c>
       <c r="C45" s="5">
-        <v>1732</v>
+        <v>1729</v>
       </c>
       <c r="D45" s="5">
-        <v>1729</v>
+        <v>1700</v>
       </c>
       <c r="E45" s="6">
-        <v>-3</v>
+        <v>-29</v>
       </c>
     </row>
     <row r="46" spans="1:5">
@@ -2537,13 +2537,13 @@
         <v>2</v>
       </c>
       <c r="C46" s="5">
-        <v>11225</v>
+        <v>11198</v>
       </c>
       <c r="D46" s="5">
-        <v>11198</v>
-      </c>
-      <c r="E46" s="6">
-        <v>-27</v>
+        <v>11265</v>
+      </c>
+      <c r="E46" s="7">
+        <v>67</v>
       </c>
     </row>
     <row r="47" spans="1:5">
@@ -2554,13 +2554,13 @@
         <v>2</v>
       </c>
       <c r="C47" s="5">
-        <v>965.25</v>
+        <v>982.1</v>
       </c>
       <c r="D47" s="5">
-        <v>982.1</v>
-      </c>
-      <c r="E47" s="7">
-        <v>16.85</v>
+        <v>957.35</v>
+      </c>
+      <c r="E47" s="6">
+        <v>-24.75</v>
       </c>
     </row>
     <row r="48" spans="1:5">
@@ -2571,251 +2571,285 @@
         <v>2</v>
       </c>
       <c r="C48" s="5">
-        <v>170.35</v>
+        <v>171.99</v>
       </c>
       <c r="D48" s="5">
-        <v>171.99</v>
-      </c>
-      <c r="E48" s="7">
-        <v>1.64</v>
+        <v>164.48</v>
+      </c>
+      <c r="E48" s="6">
+        <v>-7.51</v>
       </c>
     </row>
     <row r="49" spans="1:5">
       <c r="A49" s="3" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="B49" s="3" t="s">
-        <v>24</v>
+        <v>13</v>
       </c>
       <c r="C49" s="5">
-        <v>42.27</v>
+        <v>99</v>
       </c>
       <c r="D49" s="5">
-        <v>42.81</v>
-      </c>
-      <c r="E49" s="7">
-        <v>0.54</v>
+        <v>85</v>
+      </c>
+      <c r="E49" s="6">
+        <v>-14</v>
       </c>
     </row>
     <row r="50" spans="1:5">
       <c r="A50" s="3" t="s">
-        <v>38</v>
+        <v>43</v>
       </c>
       <c r="B50" s="3" t="s">
-        <v>24</v>
+        <v>13</v>
       </c>
       <c r="C50" s="5">
-        <v>41.31</v>
+        <v>85</v>
       </c>
       <c r="D50" s="5">
-        <v>42.46</v>
+        <v>99</v>
       </c>
       <c r="E50" s="7">
-        <v>1.15</v>
+        <v>14</v>
       </c>
     </row>
     <row r="51" spans="1:5">
       <c r="A51" s="3" t="s">
-        <v>39</v>
+        <v>37</v>
       </c>
       <c r="B51" s="3" t="s">
         <v>24</v>
       </c>
       <c r="C51" s="5">
-        <v>43.44</v>
+        <v>42.81</v>
       </c>
       <c r="D51" s="5">
-        <v>39.3</v>
+        <v>40.4</v>
       </c>
       <c r="E51" s="6">
-        <v>-4.14</v>
+        <v>-2.41</v>
       </c>
     </row>
     <row r="52" spans="1:5">
       <c r="A52" s="3" t="s">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="B52" s="3" t="s">
         <v>24</v>
       </c>
       <c r="C52" s="5">
-        <v>37.57</v>
+        <v>42.46</v>
       </c>
       <c r="D52" s="5">
-        <v>37.15</v>
+        <v>36.9</v>
       </c>
       <c r="E52" s="6">
-        <v>-0.42</v>
+        <v>-5.56</v>
       </c>
     </row>
     <row r="53" spans="1:5">
       <c r="A53" s="3" t="s">
-        <v>41</v>
+        <v>39</v>
       </c>
       <c r="B53" s="3" t="s">
         <v>24</v>
       </c>
       <c r="C53" s="5">
-        <v>57.61</v>
+        <v>39.3</v>
       </c>
       <c r="D53" s="5">
-        <v>56.84</v>
+        <v>35.93</v>
       </c>
       <c r="E53" s="6">
-        <v>-0.77</v>
+        <v>-3.37</v>
       </c>
     </row>
     <row r="54" spans="1:5">
       <c r="A54" s="3" t="s">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="B54" s="3" t="s">
         <v>24</v>
       </c>
       <c r="C54" s="5">
-        <v>42.31</v>
+        <v>37.15</v>
       </c>
       <c r="D54" s="5">
-        <v>47.29</v>
-      </c>
-      <c r="E54" s="7">
-        <v>4.98</v>
+        <v>33.26</v>
+      </c>
+      <c r="E54" s="6">
+        <v>-3.89</v>
       </c>
     </row>
     <row r="55" spans="1:5">
       <c r="A55" s="3" t="s">
-        <v>43</v>
+        <v>41</v>
       </c>
       <c r="B55" s="3" t="s">
         <v>24</v>
       </c>
       <c r="C55" s="5">
-        <v>57.18</v>
+        <v>56.84</v>
       </c>
       <c r="D55" s="5">
-        <v>58.54</v>
+        <v>58.34</v>
       </c>
       <c r="E55" s="7">
-        <v>1.36</v>
+        <v>1.5</v>
       </c>
     </row>
     <row r="56" spans="1:5">
       <c r="A56" s="3" t="s">
-        <v>37</v>
+        <v>42</v>
       </c>
       <c r="B56" s="3" t="s">
-        <v>31</v>
+        <v>24</v>
       </c>
       <c r="C56" s="5">
-        <v>-31.77</v>
+        <v>47.29</v>
       </c>
       <c r="D56" s="5">
-        <v>-39.09</v>
+        <v>41.61</v>
       </c>
       <c r="E56" s="6">
-        <v>-7.32</v>
+        <v>-5.68</v>
       </c>
     </row>
     <row r="57" spans="1:5">
       <c r="A57" s="3" t="s">
-        <v>38</v>
+        <v>43</v>
       </c>
       <c r="B57" s="3" t="s">
-        <v>31</v>
+        <v>24</v>
       </c>
       <c r="C57" s="5">
-        <v>1243.02</v>
+        <v>58.54</v>
       </c>
       <c r="D57" s="5">
-        <v>26.05</v>
+        <v>50.61</v>
       </c>
       <c r="E57" s="6">
-        <v>-1216.97</v>
+        <v>-7.93</v>
       </c>
     </row>
     <row r="58" spans="1:5">
       <c r="A58" s="3" t="s">
-        <v>39</v>
+        <v>37</v>
       </c>
       <c r="B58" s="3" t="s">
         <v>31</v>
       </c>
       <c r="C58" s="5">
-        <v>8636.33</v>
+        <v>-39.09</v>
       </c>
       <c r="D58" s="5">
-        <v>-16.85</v>
+        <v>-63.23</v>
       </c>
       <c r="E58" s="6">
-        <v>-8653.18</v>
+        <v>-24.14</v>
       </c>
     </row>
     <row r="59" spans="1:5">
       <c r="A59" s="3" t="s">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="B59" s="3" t="s">
         <v>31</v>
       </c>
       <c r="C59" s="5">
-        <v>7.06</v>
+        <v>26.05</v>
       </c>
       <c r="D59" s="5">
-        <v>26.53</v>
+        <v>28.57</v>
       </c>
       <c r="E59" s="7">
-        <v>19.47</v>
+        <v>2.52</v>
       </c>
     </row>
     <row r="60" spans="1:5">
       <c r="A60" s="3" t="s">
-        <v>41</v>
+        <v>39</v>
       </c>
       <c r="B60" s="3" t="s">
         <v>31</v>
       </c>
       <c r="C60" s="5">
-        <v>98.14</v>
+        <v>-16.85</v>
       </c>
       <c r="D60" s="5">
-        <v>-37</v>
+        <v>-75</v>
       </c>
       <c r="E60" s="6">
-        <v>-135.14</v>
+        <v>-58.15</v>
       </c>
     </row>
     <row r="61" spans="1:5">
       <c r="A61" s="3" t="s">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="B61" s="3" t="s">
         <v>31</v>
       </c>
       <c r="C61" s="5">
-        <v>48.19</v>
+        <v>26.53</v>
       </c>
       <c r="D61" s="5">
-        <v>3.74</v>
+        <v>1.4</v>
       </c>
       <c r="E61" s="6">
-        <v>-44.45</v>
+        <v>-25.13</v>
       </c>
     </row>
     <row r="62" spans="1:5">
       <c r="A62" s="3" t="s">
-        <v>43</v>
+        <v>41</v>
       </c>
       <c r="B62" s="3" t="s">
         <v>31</v>
       </c>
       <c r="C62" s="5">
-        <v>-69.31999999999999</v>
+        <v>-37</v>
       </c>
       <c r="D62" s="5">
+        <v>-37.8</v>
+      </c>
+      <c r="E62" s="6">
+        <v>-0.8</v>
+      </c>
+    </row>
+    <row r="63" spans="1:5">
+      <c r="A63" s="3" t="s">
+        <v>42</v>
+      </c>
+      <c r="B63" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="C63" s="5">
+        <v>3.74</v>
+      </c>
+      <c r="D63" s="5">
+        <v>7.89</v>
+      </c>
+      <c r="E63" s="7">
+        <v>4.15</v>
+      </c>
+    </row>
+    <row r="64" spans="1:5">
+      <c r="A64" s="3" t="s">
+        <v>43</v>
+      </c>
+      <c r="B64" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="C64" s="5">
         <v>-80.87</v>
       </c>
-      <c r="E62" s="6">
-        <v>-11.55</v>
+      <c r="D64" s="5">
+        <v>-71.05</v>
+      </c>
+      <c r="E64" s="7">
+        <v>9.82</v>
       </c>
     </row>
   </sheetData>
@@ -2874,28 +2908,28 @@
         <v>44</v>
       </c>
       <c r="B2" s="10">
-        <v>60.8</v>
+        <v>49.96</v>
       </c>
       <c r="C2" s="11">
         <v>7</v>
       </c>
       <c r="D2" s="10">
-        <v>46.3</v>
+        <v>42.4</v>
       </c>
       <c r="E2" s="10">
-        <v>70</v>
+        <v>42.9</v>
       </c>
       <c r="F2" s="10">
-        <v>-0.1</v>
+        <v>-2.8</v>
       </c>
       <c r="G2" s="10">
-        <v>-1.1</v>
+        <v>-3.7</v>
       </c>
       <c r="H2" s="10">
         <v>57</v>
       </c>
       <c r="I2" s="10">
-        <v>10</v>
+        <v>14.3</v>
       </c>
     </row>
   </sheetData>
@@ -3006,10 +3040,10 @@
         <v>38</v>
       </c>
       <c r="D1" s="12" t="s">
+        <v>42</v>
+      </c>
+      <c r="E1" s="12" t="s">
         <v>43</v>
-      </c>
-      <c r="E1" s="12" t="s">
-        <v>42</v>
       </c>
       <c r="F1" s="12" t="s">
         <v>40</v>
@@ -3020,25 +3054,25 @@
     </row>
     <row r="2" spans="1:7">
       <c r="A2" s="13">
-        <v>0.2443</v>
+        <v>0.2414</v>
       </c>
       <c r="B2" s="13">
-        <v>0.1991</v>
+        <v>0.1987</v>
       </c>
       <c r="C2" s="13">
-        <v>0.1504</v>
+        <v>0.1424</v>
       </c>
       <c r="D2" s="13">
-        <v>0.0512</v>
+        <v>0.0474</v>
       </c>
       <c r="E2" s="13">
-        <v>0.0495</v>
+        <v>0.0455</v>
       </c>
       <c r="F2" s="13">
-        <v>-0.0149</v>
+        <v>-0.0224</v>
       </c>
       <c r="G2" s="13">
-        <v>-0.2417</v>
+        <v>-0.2418</v>
       </c>
     </row>
   </sheetData>

--- a/BAJAJ_GROUP_Technical_Metrics.xlsx
+++ b/BAJAJ_GROUP_Technical_Metrics.xlsx
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="257" uniqueCount="64">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="264" uniqueCount="72">
   <si>
     <t>Symbol</t>
   </si>
@@ -166,13 +166,37 @@
     <t>DOWN</t>
   </si>
   <si>
-    <t>UP</t>
-  </si>
-  <si>
     <t>▶  SIGNAL EVENTS (vs Previous Run)</t>
   </si>
   <si>
-    <t>No signal events detected since last run.</t>
+    <t>Signal</t>
+  </si>
+  <si>
+    <t>Change</t>
+  </si>
+  <si>
+    <t>Direction</t>
+  </si>
+  <si>
+    <t>Prev Value</t>
+  </si>
+  <si>
+    <t>Curr Value</t>
+  </si>
+  <si>
+    <t>RSI Momentum</t>
+  </si>
+  <si>
+    <t>50.6 → 44.0</t>
+  </si>
+  <si>
+    <t>🔴 BEARISH</t>
+  </si>
+  <si>
+    <t>50.6</t>
+  </si>
+  <si>
+    <t>44.0</t>
   </si>
   <si>
     <t>▶  NUMERIC METRIC CHANGES (vs Previous Run)</t>
@@ -374,14 +398,15 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="14">
+  <cellXfs count="15">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="2" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="3" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
+    <xf numFmtId="0" fontId="4" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1"/>
     <xf numFmtId="165" fontId="4" fillId="5" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="165" fontId="5" fillId="6" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
@@ -896,10 +921,10 @@
         <v>44</v>
       </c>
       <c r="C2">
-        <v>10287</v>
+        <v>10072</v>
       </c>
       <c r="D2">
-        <v>-1.13</v>
+        <v>-2.09</v>
       </c>
       <c r="E2">
         <v>12361</v>
@@ -908,46 +933,46 @@
         <v>8599.48</v>
       </c>
       <c r="G2">
-        <v>-16.78</v>
+        <v>-18.52</v>
       </c>
       <c r="H2">
-        <v>19.62</v>
+        <v>17.12</v>
       </c>
       <c r="I2">
-        <v>2.52</v>
+        <v>-2.38</v>
       </c>
       <c r="J2">
-        <v>-10.55</v>
+        <v>-11.76</v>
       </c>
       <c r="K2">
-        <v>-2.24</v>
+        <v>-3.19</v>
       </c>
       <c r="L2">
-        <v>14.6</v>
+        <v>13.51</v>
       </c>
       <c r="M2">
-        <v>24.14</v>
+        <v>24.31</v>
       </c>
       <c r="N2">
         <v>71</v>
       </c>
       <c r="O2">
-        <v>70</v>
+        <v>72</v>
       </c>
       <c r="P2">
-        <v>10329</v>
+        <v>10279.8</v>
       </c>
       <c r="Q2">
-        <v>10524.25</v>
+        <v>10454.85</v>
       </c>
       <c r="R2">
-        <v>11268.7</v>
+        <v>11236.9</v>
       </c>
       <c r="S2">
-        <v>10204.28</v>
+        <v>10208.57</v>
       </c>
       <c r="T2">
-        <v>0.8100000000000001</v>
+        <v>-1.34</v>
       </c>
       <c r="U2" t="s">
         <v>45</v>
@@ -959,37 +984,37 @@
         <v>45</v>
       </c>
       <c r="X2">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="Y2">
-        <v>40.4</v>
+        <v>36.39</v>
       </c>
       <c r="Z2">
-        <v>-317.98</v>
+        <v>-314.64</v>
       </c>
       <c r="AA2">
-        <v>-359.64</v>
+        <v>-350.64</v>
       </c>
       <c r="AB2">
-        <v>41.66</v>
+        <v>36</v>
       </c>
       <c r="AC2">
-        <v>96.78</v>
+        <v>88.19</v>
       </c>
       <c r="AD2">
-        <v>95.59999999999999</v>
+        <v>94</v>
       </c>
       <c r="AE2">
-        <v>254.06</v>
+        <v>263.91</v>
       </c>
       <c r="AF2">
-        <v>-63.23</v>
+        <v>-49.7</v>
       </c>
       <c r="AG2">
-        <v>11718.96</v>
+        <v>11579.91</v>
       </c>
       <c r="AH2">
-        <v>9329.540000000001</v>
+        <v>9329.790000000001</v>
       </c>
       <c r="AI2">
         <v>10503.51</v>
@@ -998,7 +1023,7 @@
         <v>47</v>
       </c>
       <c r="AK2">
-        <v>42.83</v>
+        <v>41.5</v>
       </c>
     </row>
     <row r="3" spans="1:37">
@@ -1009,10 +1034,10 @@
         <v>44</v>
       </c>
       <c r="C3">
-        <v>447.05</v>
+        <v>425.4</v>
       </c>
       <c r="D3">
-        <v>-5.29</v>
+        <v>-4.84</v>
       </c>
       <c r="E3">
         <v>670.25</v>
@@ -1021,46 +1046,46 @@
         <v>247.45</v>
       </c>
       <c r="G3">
-        <v>-33.3</v>
+        <v>-36.53</v>
       </c>
       <c r="H3">
-        <v>80.66</v>
+        <v>71.91</v>
       </c>
       <c r="I3">
-        <v>-9.210000000000001</v>
+        <v>-16.3</v>
       </c>
       <c r="J3">
-        <v>-11.03</v>
+        <v>-16.94</v>
       </c>
       <c r="K3">
-        <v>-17.05</v>
+        <v>-19.01</v>
       </c>
       <c r="L3">
-        <v>72.45</v>
+        <v>60.84</v>
       </c>
       <c r="M3">
-        <v>14.24</v>
+        <v>14.17</v>
       </c>
       <c r="N3">
         <v>85</v>
       </c>
       <c r="O3">
-        <v>86</v>
+        <v>84</v>
       </c>
       <c r="P3">
-        <v>483.17</v>
+        <v>466.6</v>
       </c>
       <c r="Q3">
-        <v>493.15</v>
+        <v>488.65</v>
       </c>
       <c r="R3">
-        <v>497.52</v>
+        <v>495.28</v>
       </c>
       <c r="S3">
-        <v>464.74</v>
+        <v>465.58</v>
       </c>
       <c r="T3">
-        <v>-3.81</v>
+        <v>-8.630000000000001</v>
       </c>
       <c r="U3" t="s">
         <v>45</v>
@@ -1075,43 +1100,43 @@
         <v>1</v>
       </c>
       <c r="Y3">
-        <v>36.9</v>
+        <v>32.87</v>
       </c>
       <c r="Z3">
-        <v>-7.89</v>
+        <v>-12.07</v>
       </c>
       <c r="AA3">
-        <v>-4.29</v>
+        <v>-5.85</v>
       </c>
       <c r="AB3">
-        <v>-3.6</v>
+        <v>-6.22</v>
       </c>
       <c r="AC3">
-        <v>10.44</v>
+        <v>6.3</v>
       </c>
       <c r="AD3">
-        <v>41.68</v>
+        <v>20.17</v>
       </c>
       <c r="AE3">
-        <v>23.96</v>
+        <v>24.08</v>
       </c>
       <c r="AF3">
-        <v>28.57</v>
+        <v>-35.33</v>
       </c>
       <c r="AG3">
-        <v>528.65</v>
+        <v>533.8</v>
       </c>
       <c r="AH3">
-        <v>457.64</v>
+        <v>443.5</v>
       </c>
       <c r="AI3">
-        <v>527.52</v>
+        <v>508.7</v>
       </c>
       <c r="AJ3" t="s">
         <v>47</v>
       </c>
       <c r="AK3">
-        <v>29.29</v>
+        <v>33.48</v>
       </c>
     </row>
     <row r="4" spans="1:37">
@@ -1122,58 +1147,58 @@
         <v>44</v>
       </c>
       <c r="C4">
-        <v>296.35</v>
+        <v>293.1</v>
       </c>
       <c r="D4">
-        <v>-1.64</v>
+        <v>-1.1</v>
       </c>
       <c r="E4">
-        <v>548</v>
+        <v>543.1</v>
       </c>
       <c r="F4">
         <v>290.05</v>
       </c>
       <c r="G4">
-        <v>-45.92</v>
+        <v>-46.03</v>
       </c>
       <c r="H4">
-        <v>2.17</v>
+        <v>1.05</v>
       </c>
       <c r="I4">
-        <v>-0.84</v>
+        <v>-3.28</v>
       </c>
       <c r="J4">
-        <v>-8.9</v>
+        <v>-9.27</v>
       </c>
       <c r="K4">
-        <v>-11.34</v>
+        <v>-12.02</v>
       </c>
       <c r="L4">
-        <v>-45.92</v>
+        <v>-46.51</v>
       </c>
       <c r="M4">
-        <v>-24.18</v>
+        <v>-22.98</v>
       </c>
       <c r="N4">
         <v>15</v>
       </c>
       <c r="O4">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="P4">
-        <v>302.56</v>
+        <v>300.57</v>
       </c>
       <c r="Q4">
-        <v>307.34</v>
+        <v>305.7</v>
       </c>
       <c r="R4">
-        <v>328.46</v>
+        <v>326.9</v>
       </c>
       <c r="S4">
-        <v>358.08</v>
+        <v>357.16</v>
       </c>
       <c r="T4">
-        <v>-17.24</v>
+        <v>-17.94</v>
       </c>
       <c r="U4" t="s">
         <v>45</v>
@@ -1188,34 +1213,34 @@
         <v>0</v>
       </c>
       <c r="Y4">
-        <v>35.93</v>
+        <v>33.87</v>
       </c>
       <c r="Z4">
-        <v>-7.82</v>
+        <v>-8.039999999999999</v>
       </c>
       <c r="AA4">
-        <v>-8.539999999999999</v>
+        <v>-8.44</v>
       </c>
       <c r="AB4">
-        <v>0.72</v>
+        <v>0.4</v>
       </c>
       <c r="AC4">
-        <v>79.17</v>
+        <v>62.05</v>
       </c>
       <c r="AD4">
-        <v>87.20999999999999</v>
+        <v>77.94</v>
       </c>
       <c r="AE4">
-        <v>11.25</v>
+        <v>10.97</v>
       </c>
       <c r="AF4">
-        <v>-75</v>
+        <v>-72.79000000000001</v>
       </c>
       <c r="AG4">
-        <v>329.62</v>
+        <v>327.02</v>
       </c>
       <c r="AH4">
-        <v>285.06</v>
+        <v>284.38</v>
       </c>
       <c r="AI4">
         <v>322.52</v>
@@ -1224,7 +1249,7 @@
         <v>47</v>
       </c>
       <c r="AK4">
-        <v>49.13</v>
+        <v>45.79</v>
       </c>
     </row>
     <row r="5" spans="1:37">
@@ -1235,10 +1260,10 @@
         <v>44</v>
       </c>
       <c r="C5">
-        <v>1700</v>
+        <v>1690</v>
       </c>
       <c r="D5">
-        <v>-1.68</v>
+        <v>-0.59</v>
       </c>
       <c r="E5">
         <v>2176.6</v>
@@ -1247,25 +1272,25 @@
         <v>1631.8</v>
       </c>
       <c r="G5">
-        <v>-21.9</v>
+        <v>-22.36</v>
       </c>
       <c r="H5">
-        <v>4.18</v>
+        <v>3.57</v>
       </c>
       <c r="I5">
-        <v>-1.16</v>
+        <v>-3.74</v>
       </c>
       <c r="J5">
-        <v>-8.56</v>
+        <v>-8.77</v>
       </c>
       <c r="K5">
-        <v>-8.68</v>
+        <v>-11.08</v>
       </c>
       <c r="L5">
-        <v>-15.82</v>
+        <v>-18.91</v>
       </c>
       <c r="M5">
-        <v>-2.24</v>
+        <v>-1.84</v>
       </c>
       <c r="N5">
         <v>29</v>
@@ -1274,19 +1299,19 @@
         <v>39</v>
       </c>
       <c r="P5">
-        <v>1727.68</v>
+        <v>1714.54</v>
       </c>
       <c r="Q5">
-        <v>1752.96</v>
+        <v>1744.97</v>
       </c>
       <c r="R5">
-        <v>1885.75</v>
+        <v>1879.37</v>
       </c>
       <c r="S5">
-        <v>1867.99</v>
+        <v>1866.24</v>
       </c>
       <c r="T5">
-        <v>-8.99</v>
+        <v>-9.44</v>
       </c>
       <c r="U5" t="s">
         <v>45</v>
@@ -1301,43 +1326,43 @@
         <v>1</v>
       </c>
       <c r="Y5">
-        <v>33.26</v>
+        <v>32.02</v>
       </c>
       <c r="Z5">
-        <v>-45.71</v>
+        <v>-46.11</v>
       </c>
       <c r="AA5">
-        <v>-49.66</v>
+        <v>-48.95</v>
       </c>
       <c r="AB5">
-        <v>3.94</v>
+        <v>2.84</v>
       </c>
       <c r="AC5">
-        <v>74.79000000000001</v>
+        <v>62.57</v>
       </c>
       <c r="AD5">
-        <v>79.63</v>
+        <v>72.16</v>
       </c>
       <c r="AE5">
-        <v>38.36</v>
+        <v>38.3</v>
       </c>
       <c r="AF5">
-        <v>1.4</v>
+        <v>35.35</v>
       </c>
       <c r="AG5">
-        <v>1836.13</v>
+        <v>1819.18</v>
       </c>
       <c r="AH5">
-        <v>1669.78</v>
+        <v>1670.75</v>
       </c>
       <c r="AI5">
-        <v>1825.61</v>
+        <v>1797.01</v>
       </c>
       <c r="AJ5" t="s">
         <v>47</v>
       </c>
       <c r="AK5">
-        <v>53.25</v>
+        <v>55.17</v>
       </c>
     </row>
     <row r="6" spans="1:37">
@@ -1348,10 +1373,10 @@
         <v>44</v>
       </c>
       <c r="C6">
-        <v>11265</v>
+        <v>10975</v>
       </c>
       <c r="D6">
-        <v>0.6</v>
+        <v>-2.57</v>
       </c>
       <c r="E6">
         <v>13144</v>
@@ -1360,46 +1385,46 @@
         <v>8746</v>
       </c>
       <c r="G6">
-        <v>-14.3</v>
+        <v>-16.5</v>
       </c>
       <c r="H6">
-        <v>28.8</v>
+        <v>25.49</v>
       </c>
       <c r="I6">
-        <v>4.79</v>
+        <v>1.55</v>
       </c>
       <c r="J6">
-        <v>2.32</v>
+        <v>-2.72</v>
       </c>
       <c r="K6">
-        <v>9.380000000000001</v>
+        <v>5.06</v>
       </c>
       <c r="L6">
-        <v>-7.75</v>
+        <v>-10.17</v>
       </c>
       <c r="M6">
-        <v>19.87</v>
+        <v>19.61</v>
       </c>
       <c r="N6">
         <v>57</v>
       </c>
       <c r="O6">
-        <v>67</v>
+        <v>64</v>
       </c>
       <c r="P6">
-        <v>11054</v>
+        <v>11087.4</v>
       </c>
       <c r="Q6">
-        <v>10909.4</v>
+        <v>10887.7</v>
       </c>
       <c r="R6">
-        <v>11128.42</v>
+        <v>11122.66</v>
       </c>
       <c r="S6">
-        <v>10660.9</v>
+        <v>10659.14</v>
       </c>
       <c r="T6">
-        <v>5.67</v>
+        <v>2.96</v>
       </c>
       <c r="U6" t="s">
         <v>45</v>
@@ -1414,34 +1439,34 @@
         <v>2</v>
       </c>
       <c r="Y6">
-        <v>58.34</v>
+        <v>50.19</v>
       </c>
       <c r="Z6">
-        <v>-2.62</v>
+        <v>-1.42</v>
       </c>
       <c r="AA6">
-        <v>-72.44</v>
+        <v>-58.24</v>
       </c>
       <c r="AB6">
-        <v>69.81999999999999</v>
+        <v>56.81</v>
       </c>
       <c r="AC6">
-        <v>98.64</v>
+        <v>83.59999999999999</v>
       </c>
       <c r="AD6">
-        <v>90.94</v>
+        <v>92.48</v>
       </c>
       <c r="AE6">
-        <v>264.35</v>
+        <v>269.82</v>
       </c>
       <c r="AF6">
-        <v>-37.8</v>
+        <v>-10.37</v>
       </c>
       <c r="AG6">
-        <v>11462.84</v>
+        <v>11390.36</v>
       </c>
       <c r="AH6">
-        <v>10355.96</v>
+        <v>10385.04</v>
       </c>
       <c r="AI6">
         <v>11368.55</v>
@@ -1450,7 +1475,7 @@
         <v>47</v>
       </c>
       <c r="AK6">
-        <v>28.26</v>
+        <v>25.68</v>
       </c>
     </row>
     <row r="7" spans="1:37">
@@ -1461,10 +1486,10 @@
         <v>44</v>
       </c>
       <c r="C7">
-        <v>957.35</v>
+        <v>926</v>
       </c>
       <c r="D7">
-        <v>-2.52</v>
+        <v>-3.27</v>
       </c>
       <c r="E7">
         <v>1158.8</v>
@@ -1473,46 +1498,46 @@
         <v>801.55</v>
       </c>
       <c r="G7">
-        <v>-17.38</v>
+        <v>-20.09</v>
       </c>
       <c r="H7">
-        <v>19.44</v>
+        <v>15.53</v>
       </c>
       <c r="I7">
-        <v>0.01</v>
+        <v>-5.77</v>
       </c>
       <c r="J7">
-        <v>-5.68</v>
+        <v>-10.99</v>
       </c>
       <c r="K7">
-        <v>-10.02</v>
+        <v>-13.39</v>
       </c>
       <c r="L7">
-        <v>-6.06</v>
+        <v>-12.63</v>
       </c>
       <c r="M7">
-        <v>4.74</v>
+        <v>4.05</v>
       </c>
       <c r="N7">
         <v>43</v>
       </c>
       <c r="O7">
-        <v>49</v>
+        <v>42</v>
       </c>
       <c r="P7">
-        <v>968.89</v>
+        <v>957.54</v>
       </c>
       <c r="Q7">
-        <v>976.66</v>
+        <v>971.9</v>
       </c>
       <c r="R7">
-        <v>1030.47</v>
+        <v>1027.43</v>
       </c>
       <c r="S7">
-        <v>974.2</v>
+        <v>973.9</v>
       </c>
       <c r="T7">
-        <v>-1.73</v>
+        <v>-4.92</v>
       </c>
       <c r="U7" t="s">
         <v>45</v>
@@ -1527,34 +1552,34 @@
         <v>1</v>
       </c>
       <c r="Y7">
-        <v>41.61</v>
+        <v>35.76</v>
       </c>
       <c r="Z7">
-        <v>-18.24</v>
+        <v>-20.4</v>
       </c>
       <c r="AA7">
-        <v>-21.14</v>
+        <v>-20.99</v>
       </c>
       <c r="AB7">
-        <v>2.89</v>
+        <v>0.59</v>
       </c>
       <c r="AC7">
-        <v>79.25</v>
+        <v>62.11</v>
       </c>
       <c r="AD7">
-        <v>75.62</v>
+        <v>72.83</v>
       </c>
       <c r="AE7">
-        <v>25.98</v>
+        <v>27.7</v>
       </c>
       <c r="AF7">
-        <v>7.89</v>
+        <v>135.86</v>
       </c>
       <c r="AG7">
-        <v>1025.88</v>
+        <v>1021.37</v>
       </c>
       <c r="AH7">
-        <v>927.45</v>
+        <v>922.4299999999999</v>
       </c>
       <c r="AI7">
         <v>1020.6</v>
@@ -1563,7 +1588,7 @@
         <v>47</v>
       </c>
       <c r="AK7">
-        <v>19.14</v>
+        <v>20.52</v>
       </c>
     </row>
     <row r="8" spans="1:37">
@@ -1574,10 +1599,10 @@
         <v>44</v>
       </c>
       <c r="C8">
-        <v>164.48</v>
+        <v>156.81</v>
       </c>
       <c r="D8">
-        <v>-4.37</v>
+        <v>-4.66</v>
       </c>
       <c r="E8">
         <v>185.92</v>
@@ -1586,46 +1611,46 @@
         <v>115.96</v>
       </c>
       <c r="G8">
-        <v>-11.53</v>
+        <v>-15.66</v>
       </c>
       <c r="H8">
-        <v>41.84</v>
+        <v>35.23</v>
       </c>
       <c r="I8">
-        <v>-7.38</v>
+        <v>-11.17</v>
       </c>
       <c r="J8">
-        <v>22.56</v>
+        <v>16.35</v>
       </c>
       <c r="K8">
-        <v>14.33</v>
+        <v>7.49</v>
       </c>
       <c r="L8">
-        <v>29.03</v>
+        <v>20.5</v>
       </c>
       <c r="M8">
-        <v>4.55</v>
+        <v>3.64</v>
       </c>
       <c r="N8">
         <v>99</v>
       </c>
       <c r="O8">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="P8">
-        <v>171.67</v>
+        <v>167.73</v>
       </c>
       <c r="Q8">
-        <v>169.45</v>
+        <v>170.49</v>
       </c>
       <c r="R8">
-        <v>149.8</v>
+        <v>150.07</v>
       </c>
       <c r="S8">
-        <v>137.5</v>
+        <v>137.61</v>
       </c>
       <c r="T8">
-        <v>19.62</v>
+        <v>13.96</v>
       </c>
       <c r="U8" t="s">
         <v>46</v>
@@ -1640,43 +1665,43 @@
         <v>3</v>
       </c>
       <c r="Y8">
-        <v>50.61</v>
+        <v>44.04</v>
       </c>
       <c r="Z8">
-        <v>6.94</v>
+        <v>5.27</v>
       </c>
       <c r="AA8">
-        <v>8.880000000000001</v>
+        <v>8.15</v>
       </c>
       <c r="AB8">
-        <v>-1.94</v>
+        <v>-2.88</v>
       </c>
       <c r="AC8">
         <v>1.68</v>
       </c>
       <c r="AD8">
-        <v>1.51</v>
+        <v>1.68</v>
       </c>
       <c r="AE8">
-        <v>7.77</v>
+        <v>8.050000000000001</v>
       </c>
       <c r="AF8">
-        <v>-71.05</v>
+        <v>-55.84</v>
       </c>
       <c r="AG8">
-        <v>195.51</v>
+        <v>192.23</v>
       </c>
       <c r="AH8">
-        <v>143.4</v>
+        <v>148.75</v>
       </c>
       <c r="AI8">
-        <v>159.98</v>
+        <v>183.38</v>
       </c>
       <c r="AJ8" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="AK8">
-        <v>31.54</v>
+        <v>32.9</v>
       </c>
     </row>
   </sheetData>
@@ -1817,7 +1842,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:F64"/>
+  <dimension ref="A1:F62"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="16.7109375" customWidth="1"/>
@@ -1827,7 +1852,7 @@
   <sheetData>
     <row r="1" spans="1:6">
       <c r="A1" s="2" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="B1" s="2"/>
       <c r="C1" s="2"/>
@@ -1837,12 +1862,47 @@
     </row>
     <row r="2" spans="1:6">
       <c r="A2" s="3" t="s">
+        <v>0</v>
+      </c>
+      <c r="B2" s="3" t="s">
+        <v>49</v>
+      </c>
+      <c r="C2" s="3" t="s">
         <v>50</v>
+      </c>
+      <c r="D2" s="3" t="s">
+        <v>51</v>
+      </c>
+      <c r="E2" s="3" t="s">
+        <v>52</v>
+      </c>
+      <c r="F2" s="3" t="s">
+        <v>53</v>
+      </c>
+    </row>
+    <row r="3" spans="1:6">
+      <c r="A3" s="4" t="s">
+        <v>43</v>
+      </c>
+      <c r="B3" s="4" t="s">
+        <v>54</v>
+      </c>
+      <c r="C3" s="4" t="s">
+        <v>55</v>
+      </c>
+      <c r="D3" s="4" t="s">
+        <v>56</v>
+      </c>
+      <c r="E3" s="4" t="s">
+        <v>57</v>
+      </c>
+      <c r="F3" s="4" t="s">
+        <v>58</v>
       </c>
     </row>
     <row r="5" spans="1:6">
       <c r="A5" s="2" t="s">
-        <v>51</v>
+        <v>59</v>
       </c>
       <c r="B5" s="2"/>
       <c r="C5" s="2"/>
@@ -1850,1006 +1910,972 @@
       <c r="E5" s="2"/>
     </row>
     <row r="6" spans="1:6">
-      <c r="A6" s="4" t="s">
+      <c r="A6" s="3" t="s">
         <v>0</v>
       </c>
-      <c r="B6" s="4" t="s">
-        <v>52</v>
-      </c>
-      <c r="C6" s="4" t="s">
-        <v>53</v>
-      </c>
-      <c r="D6" s="4" t="s">
-        <v>54</v>
-      </c>
-      <c r="E6" s="4" t="s">
-        <v>55</v>
+      <c r="B6" s="3" t="s">
+        <v>60</v>
+      </c>
+      <c r="C6" s="3" t="s">
+        <v>61</v>
+      </c>
+      <c r="D6" s="3" t="s">
+        <v>62</v>
+      </c>
+      <c r="E6" s="3" t="s">
+        <v>63</v>
       </c>
     </row>
     <row r="7" spans="1:6">
-      <c r="A7" s="3" t="s">
+      <c r="A7" s="5" t="s">
         <v>37</v>
       </c>
-      <c r="B7" s="3" t="s">
+      <c r="B7" s="5" t="s">
         <v>9</v>
       </c>
-      <c r="C7" s="5">
-        <v>-10.25</v>
-      </c>
-      <c r="D7" s="5">
+      <c r="C7" s="6">
         <v>-10.55</v>
       </c>
-      <c r="E7" s="6">
-        <v>-0.3</v>
+      <c r="D7" s="6">
+        <v>-11.76</v>
+      </c>
+      <c r="E7" s="7">
+        <v>-1.21</v>
       </c>
     </row>
     <row r="8" spans="1:6">
-      <c r="A8" s="3" t="s">
+      <c r="A8" s="5" t="s">
         <v>38</v>
       </c>
-      <c r="B8" s="3" t="s">
+      <c r="B8" s="5" t="s">
         <v>9</v>
       </c>
-      <c r="C8" s="5">
-        <v>-5.23</v>
-      </c>
-      <c r="D8" s="5">
+      <c r="C8" s="6">
         <v>-11.03</v>
       </c>
-      <c r="E8" s="6">
-        <v>-5.8</v>
+      <c r="D8" s="6">
+        <v>-16.94</v>
+      </c>
+      <c r="E8" s="7">
+        <v>-5.91</v>
       </c>
     </row>
     <row r="9" spans="1:6">
-      <c r="A9" s="3" t="s">
+      <c r="A9" s="5" t="s">
         <v>39</v>
       </c>
-      <c r="B9" s="3" t="s">
+      <c r="B9" s="5" t="s">
         <v>9</v>
       </c>
-      <c r="C9" s="5">
-        <v>-6.59</v>
-      </c>
-      <c r="D9" s="5">
+      <c r="C9" s="6">
         <v>-8.9</v>
       </c>
-      <c r="E9" s="6">
-        <v>-2.31</v>
+      <c r="D9" s="6">
+        <v>-9.27</v>
+      </c>
+      <c r="E9" s="7">
+        <v>-0.37</v>
       </c>
     </row>
     <row r="10" spans="1:6">
-      <c r="A10" s="3" t="s">
+      <c r="A10" s="5" t="s">
         <v>40</v>
       </c>
-      <c r="B10" s="3" t="s">
+      <c r="B10" s="5" t="s">
         <v>9</v>
       </c>
-      <c r="C10" s="5">
-        <v>-5.88</v>
-      </c>
-      <c r="D10" s="5">
+      <c r="C10" s="6">
         <v>-8.56</v>
       </c>
-      <c r="E10" s="6">
-        <v>-2.68</v>
+      <c r="D10" s="6">
+        <v>-8.77</v>
+      </c>
+      <c r="E10" s="7">
+        <v>-0.21</v>
       </c>
     </row>
     <row r="11" spans="1:6">
-      <c r="A11" s="3" t="s">
+      <c r="A11" s="5" t="s">
         <v>41</v>
       </c>
-      <c r="B11" s="3" t="s">
+      <c r="B11" s="5" t="s">
         <v>9</v>
       </c>
-      <c r="C11" s="5">
-        <v>2.45</v>
-      </c>
-      <c r="D11" s="5">
+      <c r="C11" s="6">
         <v>2.32</v>
       </c>
-      <c r="E11" s="6">
-        <v>-0.13</v>
+      <c r="D11" s="6">
+        <v>-2.72</v>
+      </c>
+      <c r="E11" s="7">
+        <v>-5.04</v>
       </c>
     </row>
     <row r="12" spans="1:6">
-      <c r="A12" s="3" t="s">
+      <c r="A12" s="5" t="s">
         <v>42</v>
       </c>
-      <c r="B12" s="3" t="s">
+      <c r="B12" s="5" t="s">
         <v>9</v>
       </c>
-      <c r="C12" s="5">
+      <c r="C12" s="6">
+        <v>-5.68</v>
+      </c>
+      <c r="D12" s="6">
+        <v>-10.99</v>
+      </c>
+      <c r="E12" s="7">
+        <v>-5.31</v>
+      </c>
+    </row>
+    <row r="13" spans="1:6">
+      <c r="A13" s="5" t="s">
+        <v>43</v>
+      </c>
+      <c r="B13" s="5" t="s">
+        <v>9</v>
+      </c>
+      <c r="C13" s="6">
+        <v>22.56</v>
+      </c>
+      <c r="D13" s="6">
+        <v>16.35</v>
+      </c>
+      <c r="E13" s="7">
+        <v>-6.21</v>
+      </c>
+    </row>
+    <row r="14" spans="1:6">
+      <c r="A14" s="5" t="s">
+        <v>37</v>
+      </c>
+      <c r="B14" s="5" t="s">
+        <v>8</v>
+      </c>
+      <c r="C14" s="6">
+        <v>2.52</v>
+      </c>
+      <c r="D14" s="6">
+        <v>-2.38</v>
+      </c>
+      <c r="E14" s="7">
+        <v>-4.9</v>
+      </c>
+    </row>
+    <row r="15" spans="1:6">
+      <c r="A15" s="5" t="s">
+        <v>38</v>
+      </c>
+      <c r="B15" s="5" t="s">
+        <v>8</v>
+      </c>
+      <c r="C15" s="6">
+        <v>-9.210000000000001</v>
+      </c>
+      <c r="D15" s="6">
+        <v>-16.3</v>
+      </c>
+      <c r="E15" s="7">
+        <v>-7.09</v>
+      </c>
+    </row>
+    <row r="16" spans="1:6">
+      <c r="A16" s="5" t="s">
+        <v>39</v>
+      </c>
+      <c r="B16" s="5" t="s">
+        <v>8</v>
+      </c>
+      <c r="C16" s="6">
+        <v>-0.84</v>
+      </c>
+      <c r="D16" s="6">
+        <v>-3.28</v>
+      </c>
+      <c r="E16" s="7">
+        <v>-2.44</v>
+      </c>
+    </row>
+    <row r="17" spans="1:5">
+      <c r="A17" s="5" t="s">
+        <v>40</v>
+      </c>
+      <c r="B17" s="5" t="s">
+        <v>8</v>
+      </c>
+      <c r="C17" s="6">
+        <v>-1.16</v>
+      </c>
+      <c r="D17" s="6">
+        <v>-3.74</v>
+      </c>
+      <c r="E17" s="7">
+        <v>-2.58</v>
+      </c>
+    </row>
+    <row r="18" spans="1:5">
+      <c r="A18" s="5" t="s">
+        <v>41</v>
+      </c>
+      <c r="B18" s="5" t="s">
+        <v>8</v>
+      </c>
+      <c r="C18" s="6">
+        <v>4.79</v>
+      </c>
+      <c r="D18" s="6">
+        <v>1.55</v>
+      </c>
+      <c r="E18" s="7">
+        <v>-3.24</v>
+      </c>
+    </row>
+    <row r="19" spans="1:5">
+      <c r="A19" s="5" t="s">
+        <v>42</v>
+      </c>
+      <c r="B19" s="5" t="s">
+        <v>8</v>
+      </c>
+      <c r="C19" s="6">
+        <v>0.01</v>
+      </c>
+      <c r="D19" s="6">
+        <v>-5.77</v>
+      </c>
+      <c r="E19" s="7">
+        <v>-5.78</v>
+      </c>
+    </row>
+    <row r="20" spans="1:5">
+      <c r="A20" s="5" t="s">
+        <v>43</v>
+      </c>
+      <c r="B20" s="5" t="s">
+        <v>8</v>
+      </c>
+      <c r="C20" s="6">
+        <v>-7.38</v>
+      </c>
+      <c r="D20" s="6">
+        <v>-11.17</v>
+      </c>
+      <c r="E20" s="7">
+        <v>-3.79</v>
+      </c>
+    </row>
+    <row r="21" spans="1:5">
+      <c r="A21" s="5" t="s">
+        <v>37</v>
+      </c>
+      <c r="B21" s="5" t="s">
+        <v>11</v>
+      </c>
+      <c r="C21" s="6">
+        <v>14.6</v>
+      </c>
+      <c r="D21" s="6">
+        <v>13.51</v>
+      </c>
+      <c r="E21" s="7">
+        <v>-1.09</v>
+      </c>
+    </row>
+    <row r="22" spans="1:5">
+      <c r="A22" s="5" t="s">
+        <v>38</v>
+      </c>
+      <c r="B22" s="5" t="s">
+        <v>11</v>
+      </c>
+      <c r="C22" s="6">
+        <v>72.45</v>
+      </c>
+      <c r="D22" s="6">
+        <v>60.84</v>
+      </c>
+      <c r="E22" s="7">
+        <v>-11.61</v>
+      </c>
+    </row>
+    <row r="23" spans="1:5">
+      <c r="A23" s="5" t="s">
+        <v>39</v>
+      </c>
+      <c r="B23" s="5" t="s">
+        <v>11</v>
+      </c>
+      <c r="C23" s="6">
+        <v>-45.92</v>
+      </c>
+      <c r="D23" s="6">
+        <v>-46.51</v>
+      </c>
+      <c r="E23" s="7">
+        <v>-0.59</v>
+      </c>
+    </row>
+    <row r="24" spans="1:5">
+      <c r="A24" s="5" t="s">
+        <v>40</v>
+      </c>
+      <c r="B24" s="5" t="s">
+        <v>11</v>
+      </c>
+      <c r="C24" s="6">
+        <v>-15.82</v>
+      </c>
+      <c r="D24" s="6">
+        <v>-18.91</v>
+      </c>
+      <c r="E24" s="7">
+        <v>-3.09</v>
+      </c>
+    </row>
+    <row r="25" spans="1:5">
+      <c r="A25" s="5" t="s">
+        <v>41</v>
+      </c>
+      <c r="B25" s="5" t="s">
+        <v>11</v>
+      </c>
+      <c r="C25" s="6">
+        <v>-7.75</v>
+      </c>
+      <c r="D25" s="6">
+        <v>-10.17</v>
+      </c>
+      <c r="E25" s="7">
+        <v>-2.42</v>
+      </c>
+    </row>
+    <row r="26" spans="1:5">
+      <c r="A26" s="5" t="s">
+        <v>42</v>
+      </c>
+      <c r="B26" s="5" t="s">
+        <v>11</v>
+      </c>
+      <c r="C26" s="6">
+        <v>-6.06</v>
+      </c>
+      <c r="D26" s="6">
+        <v>-12.63</v>
+      </c>
+      <c r="E26" s="7">
+        <v>-6.57</v>
+      </c>
+    </row>
+    <row r="27" spans="1:5">
+      <c r="A27" s="5" t="s">
+        <v>43</v>
+      </c>
+      <c r="B27" s="5" t="s">
+        <v>11</v>
+      </c>
+      <c r="C27" s="6">
+        <v>29.03</v>
+      </c>
+      <c r="D27" s="6">
+        <v>20.5</v>
+      </c>
+      <c r="E27" s="7">
+        <v>-8.529999999999999</v>
+      </c>
+    </row>
+    <row r="28" spans="1:5">
+      <c r="A28" s="5" t="s">
+        <v>37</v>
+      </c>
+      <c r="B28" s="5" t="s">
+        <v>10</v>
+      </c>
+      <c r="C28" s="6">
+        <v>-2.24</v>
+      </c>
+      <c r="D28" s="6">
+        <v>-3.19</v>
+      </c>
+      <c r="E28" s="7">
+        <v>-0.95</v>
+      </c>
+    </row>
+    <row r="29" spans="1:5">
+      <c r="A29" s="5" t="s">
+        <v>38</v>
+      </c>
+      <c r="B29" s="5" t="s">
+        <v>10</v>
+      </c>
+      <c r="C29" s="6">
+        <v>-17.05</v>
+      </c>
+      <c r="D29" s="6">
+        <v>-19.01</v>
+      </c>
+      <c r="E29" s="7">
+        <v>-1.96</v>
+      </c>
+    </row>
+    <row r="30" spans="1:5">
+      <c r="A30" s="5" t="s">
+        <v>39</v>
+      </c>
+      <c r="B30" s="5" t="s">
+        <v>10</v>
+      </c>
+      <c r="C30" s="6">
+        <v>-11.34</v>
+      </c>
+      <c r="D30" s="6">
+        <v>-12.02</v>
+      </c>
+      <c r="E30" s="7">
+        <v>-0.68</v>
+      </c>
+    </row>
+    <row r="31" spans="1:5">
+      <c r="A31" s="5" t="s">
+        <v>40</v>
+      </c>
+      <c r="B31" s="5" t="s">
+        <v>10</v>
+      </c>
+      <c r="C31" s="6">
+        <v>-8.68</v>
+      </c>
+      <c r="D31" s="6">
+        <v>-11.08</v>
+      </c>
+      <c r="E31" s="7">
         <v>-2.4</v>
       </c>
-      <c r="D12" s="5">
-        <v>-5.68</v>
-      </c>
-      <c r="E12" s="6">
-        <v>-3.28</v>
-      </c>
-    </row>
-    <row r="13" spans="1:6">
-      <c r="A13" s="3" t="s">
+    </row>
+    <row r="32" spans="1:5">
+      <c r="A32" s="5" t="s">
+        <v>41</v>
+      </c>
+      <c r="B32" s="5" t="s">
+        <v>10</v>
+      </c>
+      <c r="C32" s="6">
+        <v>9.380000000000001</v>
+      </c>
+      <c r="D32" s="6">
+        <v>5.06</v>
+      </c>
+      <c r="E32" s="7">
+        <v>-4.32</v>
+      </c>
+    </row>
+    <row r="33" spans="1:5">
+      <c r="A33" s="5" t="s">
+        <v>42</v>
+      </c>
+      <c r="B33" s="5" t="s">
+        <v>10</v>
+      </c>
+      <c r="C33" s="6">
+        <v>-10.02</v>
+      </c>
+      <c r="D33" s="6">
+        <v>-13.39</v>
+      </c>
+      <c r="E33" s="7">
+        <v>-3.37</v>
+      </c>
+    </row>
+    <row r="34" spans="1:5">
+      <c r="A34" s="5" t="s">
         <v>43</v>
       </c>
-      <c r="B13" s="3" t="s">
-        <v>9</v>
-      </c>
-      <c r="C13" s="5">
-        <v>27.5</v>
-      </c>
-      <c r="D13" s="5">
-        <v>22.56</v>
-      </c>
-      <c r="E13" s="6">
-        <v>-4.94</v>
-      </c>
-    </row>
-    <row r="14" spans="1:6">
-      <c r="A14" s="3" t="s">
+      <c r="B34" s="5" t="s">
+        <v>10</v>
+      </c>
+      <c r="C34" s="6">
+        <v>14.33</v>
+      </c>
+      <c r="D34" s="6">
+        <v>7.49</v>
+      </c>
+      <c r="E34" s="7">
+        <v>-6.84</v>
+      </c>
+    </row>
+    <row r="35" spans="1:5">
+      <c r="A35" s="5" t="s">
         <v>37</v>
       </c>
-      <c r="B14" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="C14" s="5">
-        <v>6.41</v>
-      </c>
-      <c r="D14" s="5">
-        <v>2.52</v>
-      </c>
-      <c r="E14" s="6">
-        <v>-3.89</v>
-      </c>
-    </row>
-    <row r="15" spans="1:6">
-      <c r="A15" s="3" t="s">
+      <c r="B35" s="5" t="s">
+        <v>6</v>
+      </c>
+      <c r="C35" s="6">
+        <v>-16.78</v>
+      </c>
+      <c r="D35" s="6">
+        <v>-18.52</v>
+      </c>
+      <c r="E35" s="7">
+        <v>-1.74</v>
+      </c>
+    </row>
+    <row r="36" spans="1:5">
+      <c r="A36" s="5" t="s">
         <v>38</v>
       </c>
-      <c r="B15" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="C15" s="5">
-        <v>-6.89</v>
-      </c>
-      <c r="D15" s="5">
-        <v>-9.210000000000001</v>
-      </c>
-      <c r="E15" s="6">
-        <v>-2.32</v>
-      </c>
-    </row>
-    <row r="16" spans="1:6">
-      <c r="A16" s="3" t="s">
+      <c r="B36" s="5" t="s">
+        <v>6</v>
+      </c>
+      <c r="C36" s="6">
+        <v>-33.3</v>
+      </c>
+      <c r="D36" s="6">
+        <v>-36.53</v>
+      </c>
+      <c r="E36" s="7">
+        <v>-3.23</v>
+      </c>
+    </row>
+    <row r="37" spans="1:5">
+      <c r="A37" s="5" t="s">
         <v>39</v>
       </c>
-      <c r="B16" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="C16" s="5">
-        <v>1.11</v>
-      </c>
-      <c r="D16" s="5">
-        <v>-0.84</v>
-      </c>
-      <c r="E16" s="6">
-        <v>-1.95</v>
-      </c>
-    </row>
-    <row r="17" spans="1:5">
-      <c r="A17" s="3" t="s">
+      <c r="B37" s="5" t="s">
+        <v>6</v>
+      </c>
+      <c r="C37" s="6">
+        <v>-45.92</v>
+      </c>
+      <c r="D37" s="6">
+        <v>-46.03</v>
+      </c>
+      <c r="E37" s="7">
+        <v>-0.11</v>
+      </c>
+    </row>
+    <row r="38" spans="1:5">
+      <c r="A38" s="5" t="s">
         <v>40</v>
       </c>
-      <c r="B17" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="C17" s="5">
-        <v>-0.33</v>
-      </c>
-      <c r="D17" s="5">
-        <v>-1.16</v>
-      </c>
-      <c r="E17" s="6">
-        <v>-0.83</v>
-      </c>
-    </row>
-    <row r="18" spans="1:5">
-      <c r="A18" s="3" t="s">
+      <c r="B38" s="5" t="s">
+        <v>6</v>
+      </c>
+      <c r="C38" s="6">
+        <v>-21.9</v>
+      </c>
+      <c r="D38" s="6">
+        <v>-22.36</v>
+      </c>
+      <c r="E38" s="7">
+        <v>-0.46</v>
+      </c>
+    </row>
+    <row r="39" spans="1:5">
+      <c r="A39" s="5" t="s">
         <v>41</v>
       </c>
-      <c r="B18" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="C18" s="5">
-        <v>3.49</v>
-      </c>
-      <c r="D18" s="5">
-        <v>4.79</v>
-      </c>
-      <c r="E18" s="7">
-        <v>1.3</v>
-      </c>
-    </row>
-    <row r="19" spans="1:5">
-      <c r="A19" s="3" t="s">
+      <c r="B39" s="5" t="s">
+        <v>6</v>
+      </c>
+      <c r="C39" s="6">
+        <v>-14.3</v>
+      </c>
+      <c r="D39" s="6">
+        <v>-16.5</v>
+      </c>
+      <c r="E39" s="7">
+        <v>-2.2</v>
+      </c>
+    </row>
+    <row r="40" spans="1:5">
+      <c r="A40" s="5" t="s">
         <v>42</v>
       </c>
-      <c r="B19" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="C19" s="5">
-        <v>2.3</v>
-      </c>
-      <c r="D19" s="5">
-        <v>0.01</v>
-      </c>
-      <c r="E19" s="6">
-        <v>-2.29</v>
-      </c>
-    </row>
-    <row r="20" spans="1:5">
-      <c r="A20" s="3" t="s">
+      <c r="B40" s="5" t="s">
+        <v>6</v>
+      </c>
+      <c r="C40" s="6">
+        <v>-17.38</v>
+      </c>
+      <c r="D40" s="6">
+        <v>-20.09</v>
+      </c>
+      <c r="E40" s="7">
+        <v>-2.71</v>
+      </c>
+    </row>
+    <row r="41" spans="1:5">
+      <c r="A41" s="5" t="s">
         <v>43</v>
       </c>
-      <c r="B20" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="C20" s="5">
-        <v>-2.27</v>
-      </c>
-      <c r="D20" s="5">
-        <v>-7.38</v>
-      </c>
-      <c r="E20" s="6">
-        <v>-5.11</v>
-      </c>
-    </row>
-    <row r="21" spans="1:5">
-      <c r="A21" s="3" t="s">
+      <c r="B41" s="5" t="s">
+        <v>6</v>
+      </c>
+      <c r="C41" s="6">
+        <v>-11.53</v>
+      </c>
+      <c r="D41" s="6">
+        <v>-15.66</v>
+      </c>
+      <c r="E41" s="7">
+        <v>-4.13</v>
+      </c>
+    </row>
+    <row r="42" spans="1:5">
+      <c r="A42" s="5" t="s">
         <v>37</v>
       </c>
-      <c r="B21" s="3" t="s">
-        <v>11</v>
-      </c>
-      <c r="C21" s="5">
-        <v>16.38</v>
-      </c>
-      <c r="D21" s="5">
-        <v>14.6</v>
-      </c>
-      <c r="E21" s="6">
-        <v>-1.78</v>
-      </c>
-    </row>
-    <row r="22" spans="1:5">
-      <c r="A22" s="3" t="s">
+      <c r="B42" s="5" t="s">
+        <v>2</v>
+      </c>
+      <c r="C42" s="6">
+        <v>10287</v>
+      </c>
+      <c r="D42" s="6">
+        <v>10072</v>
+      </c>
+      <c r="E42" s="7">
+        <v>-215</v>
+      </c>
+    </row>
+    <row r="43" spans="1:5">
+      <c r="A43" s="5" t="s">
         <v>38</v>
       </c>
-      <c r="B22" s="3" t="s">
-        <v>11</v>
-      </c>
-      <c r="C22" s="5">
-        <v>77.61</v>
-      </c>
-      <c r="D22" s="5">
-        <v>72.45</v>
-      </c>
-      <c r="E22" s="6">
-        <v>-5.16</v>
-      </c>
-    </row>
-    <row r="23" spans="1:5">
-      <c r="A23" s="3" t="s">
+      <c r="B43" s="5" t="s">
+        <v>2</v>
+      </c>
+      <c r="C43" s="6">
+        <v>447.05</v>
+      </c>
+      <c r="D43" s="6">
+        <v>425.4</v>
+      </c>
+      <c r="E43" s="7">
+        <v>-21.65</v>
+      </c>
+    </row>
+    <row r="44" spans="1:5">
+      <c r="A44" s="5" t="s">
         <v>39</v>
       </c>
-      <c r="B23" s="3" t="s">
-        <v>11</v>
-      </c>
-      <c r="C23" s="5">
-        <v>-44.71</v>
-      </c>
-      <c r="D23" s="5">
-        <v>-45.92</v>
-      </c>
-      <c r="E23" s="6">
-        <v>-1.21</v>
-      </c>
-    </row>
-    <row r="24" spans="1:5">
-      <c r="A24" s="3" t="s">
+      <c r="B44" s="5" t="s">
+        <v>2</v>
+      </c>
+      <c r="C44" s="6">
+        <v>296.35</v>
+      </c>
+      <c r="D44" s="6">
+        <v>293.1</v>
+      </c>
+      <c r="E44" s="7">
+        <v>-3.25</v>
+      </c>
+    </row>
+    <row r="45" spans="1:5">
+      <c r="A45" s="5" t="s">
         <v>40</v>
       </c>
-      <c r="B24" s="3" t="s">
-        <v>11</v>
-      </c>
-      <c r="C24" s="5">
-        <v>-14.42</v>
-      </c>
-      <c r="D24" s="5">
-        <v>-15.82</v>
-      </c>
-      <c r="E24" s="6">
-        <v>-1.4</v>
-      </c>
-    </row>
-    <row r="25" spans="1:5">
-      <c r="A25" s="3" t="s">
+      <c r="B45" s="5" t="s">
+        <v>2</v>
+      </c>
+      <c r="C45" s="6">
+        <v>1700</v>
+      </c>
+      <c r="D45" s="6">
+        <v>1690</v>
+      </c>
+      <c r="E45" s="7">
+        <v>-10</v>
+      </c>
+    </row>
+    <row r="46" spans="1:5">
+      <c r="A46" s="5" t="s">
         <v>41</v>
       </c>
-      <c r="B25" s="3" t="s">
-        <v>11</v>
-      </c>
-      <c r="C25" s="5">
-        <v>-9.359999999999999</v>
-      </c>
-      <c r="D25" s="5">
-        <v>-7.75</v>
-      </c>
-      <c r="E25" s="7">
-        <v>1.61</v>
-      </c>
-    </row>
-    <row r="26" spans="1:5">
-      <c r="A26" s="3" t="s">
+      <c r="B46" s="5" t="s">
+        <v>2</v>
+      </c>
+      <c r="C46" s="6">
+        <v>11265</v>
+      </c>
+      <c r="D46" s="6">
+        <v>10975</v>
+      </c>
+      <c r="E46" s="7">
+        <v>-290</v>
+      </c>
+    </row>
+    <row r="47" spans="1:5">
+      <c r="A47" s="5" t="s">
         <v>42</v>
       </c>
-      <c r="B26" s="3" t="s">
-        <v>11</v>
-      </c>
-      <c r="C26" s="5">
-        <v>-5.27</v>
-      </c>
-      <c r="D26" s="5">
-        <v>-6.06</v>
-      </c>
-      <c r="E26" s="6">
-        <v>-0.79</v>
-      </c>
-    </row>
-    <row r="27" spans="1:5">
-      <c r="A27" s="3" t="s">
+      <c r="B47" s="5" t="s">
+        <v>2</v>
+      </c>
+      <c r="C47" s="6">
+        <v>957.35</v>
+      </c>
+      <c r="D47" s="6">
+        <v>926</v>
+      </c>
+      <c r="E47" s="7">
+        <v>-31.35</v>
+      </c>
+    </row>
+    <row r="48" spans="1:5">
+      <c r="A48" s="5" t="s">
         <v>43</v>
       </c>
-      <c r="B27" s="3" t="s">
-        <v>11</v>
-      </c>
-      <c r="C27" s="5">
-        <v>32.62</v>
-      </c>
-      <c r="D27" s="5">
-        <v>29.03</v>
-      </c>
-      <c r="E27" s="6">
-        <v>-3.59</v>
-      </c>
-    </row>
-    <row r="28" spans="1:5">
-      <c r="A28" s="3" t="s">
+      <c r="B48" s="5" t="s">
+        <v>2</v>
+      </c>
+      <c r="C48" s="6">
+        <v>164.48</v>
+      </c>
+      <c r="D48" s="6">
+        <v>156.81</v>
+      </c>
+      <c r="E48" s="7">
+        <v>-7.67</v>
+      </c>
+    </row>
+    <row r="49" spans="1:5">
+      <c r="A49" s="5" t="s">
         <v>37</v>
       </c>
-      <c r="B28" s="3" t="s">
-        <v>10</v>
-      </c>
-      <c r="C28" s="5">
-        <v>-0.36</v>
-      </c>
-      <c r="D28" s="5">
-        <v>-2.24</v>
-      </c>
-      <c r="E28" s="6">
-        <v>-1.88</v>
-      </c>
-    </row>
-    <row r="29" spans="1:5">
-      <c r="A29" s="3" t="s">
+      <c r="B49" s="5" t="s">
+        <v>24</v>
+      </c>
+      <c r="C49" s="6">
+        <v>40.4</v>
+      </c>
+      <c r="D49" s="6">
+        <v>36.39</v>
+      </c>
+      <c r="E49" s="7">
+        <v>-4.01</v>
+      </c>
+    </row>
+    <row r="50" spans="1:5">
+      <c r="A50" s="5" t="s">
         <v>38</v>
       </c>
-      <c r="B29" s="3" t="s">
-        <v>10</v>
-      </c>
-      <c r="C29" s="5">
-        <v>-10.21</v>
-      </c>
-      <c r="D29" s="5">
-        <v>-17.05</v>
-      </c>
-      <c r="E29" s="6">
-        <v>-6.84</v>
-      </c>
-    </row>
-    <row r="30" spans="1:5">
-      <c r="A30" s="3" t="s">
+      <c r="B50" s="5" t="s">
+        <v>24</v>
+      </c>
+      <c r="C50" s="6">
+        <v>36.9</v>
+      </c>
+      <c r="D50" s="6">
+        <v>32.87</v>
+      </c>
+      <c r="E50" s="7">
+        <v>-4.03</v>
+      </c>
+    </row>
+    <row r="51" spans="1:5">
+      <c r="A51" s="5" t="s">
         <v>39</v>
       </c>
-      <c r="B30" s="3" t="s">
-        <v>10</v>
-      </c>
-      <c r="C30" s="5">
-        <v>-9.1</v>
-      </c>
-      <c r="D30" s="5">
-        <v>-11.34</v>
-      </c>
-      <c r="E30" s="6">
-        <v>-2.24</v>
-      </c>
-    </row>
-    <row r="31" spans="1:5">
-      <c r="A31" s="3" t="s">
+      <c r="B51" s="5" t="s">
+        <v>24</v>
+      </c>
+      <c r="C51" s="6">
+        <v>35.93</v>
+      </c>
+      <c r="D51" s="6">
+        <v>33.87</v>
+      </c>
+      <c r="E51" s="7">
+        <v>-2.06</v>
+      </c>
+    </row>
+    <row r="52" spans="1:5">
+      <c r="A52" s="5" t="s">
         <v>40</v>
       </c>
-      <c r="B31" s="3" t="s">
-        <v>10</v>
-      </c>
-      <c r="C31" s="5">
-        <v>-6.74</v>
-      </c>
-      <c r="D31" s="5">
-        <v>-8.68</v>
-      </c>
-      <c r="E31" s="6">
-        <v>-1.94</v>
-      </c>
-    </row>
-    <row r="32" spans="1:5">
-      <c r="A32" s="3" t="s">
+      <c r="B52" s="5" t="s">
+        <v>24</v>
+      </c>
+      <c r="C52" s="6">
+        <v>33.26</v>
+      </c>
+      <c r="D52" s="6">
+        <v>32.02</v>
+      </c>
+      <c r="E52" s="7">
+        <v>-1.24</v>
+      </c>
+    </row>
+    <row r="53" spans="1:5">
+      <c r="A53" s="5" t="s">
         <v>41</v>
       </c>
-      <c r="B32" s="3" t="s">
-        <v>10</v>
-      </c>
-      <c r="C32" s="5">
-        <v>7.69</v>
-      </c>
-      <c r="D32" s="5">
-        <v>9.380000000000001</v>
-      </c>
-      <c r="E32" s="7">
-        <v>1.69</v>
-      </c>
-    </row>
-    <row r="33" spans="1:5">
-      <c r="A33" s="3" t="s">
+      <c r="B53" s="5" t="s">
+        <v>24</v>
+      </c>
+      <c r="C53" s="6">
+        <v>58.34</v>
+      </c>
+      <c r="D53" s="6">
+        <v>50.19</v>
+      </c>
+      <c r="E53" s="7">
+        <v>-8.15</v>
+      </c>
+    </row>
+    <row r="54" spans="1:5">
+      <c r="A54" s="5" t="s">
         <v>42</v>
       </c>
-      <c r="B33" s="3" t="s">
-        <v>10</v>
-      </c>
-      <c r="C33" s="5">
-        <v>-7.02</v>
-      </c>
-      <c r="D33" s="5">
-        <v>-10.02</v>
-      </c>
-      <c r="E33" s="6">
-        <v>-3</v>
-      </c>
-    </row>
-    <row r="34" spans="1:5">
-      <c r="A34" s="3" t="s">
+      <c r="B54" s="5" t="s">
+        <v>24</v>
+      </c>
+      <c r="C54" s="6">
+        <v>41.61</v>
+      </c>
+      <c r="D54" s="6">
+        <v>35.76</v>
+      </c>
+      <c r="E54" s="7">
+        <v>-5.85</v>
+      </c>
+    </row>
+    <row r="55" spans="1:5">
+      <c r="A55" s="5" t="s">
         <v>43</v>
       </c>
-      <c r="B34" s="3" t="s">
-        <v>10</v>
-      </c>
-      <c r="C34" s="5">
-        <v>18.05</v>
-      </c>
-      <c r="D34" s="5">
-        <v>14.33</v>
-      </c>
-      <c r="E34" s="6">
-        <v>-3.72</v>
-      </c>
-    </row>
-    <row r="35" spans="1:5">
-      <c r="A35" s="3" t="s">
+      <c r="B55" s="5" t="s">
+        <v>24</v>
+      </c>
+      <c r="C55" s="6">
+        <v>50.61</v>
+      </c>
+      <c r="D55" s="6">
+        <v>44.04</v>
+      </c>
+      <c r="E55" s="7">
+        <v>-6.57</v>
+      </c>
+    </row>
+    <row r="56" spans="1:5">
+      <c r="A56" s="5" t="s">
         <v>37</v>
       </c>
-      <c r="B35" s="3" t="s">
-        <v>6</v>
-      </c>
-      <c r="C35" s="5">
-        <v>-15.82</v>
-      </c>
-      <c r="D35" s="5">
-        <v>-16.78</v>
-      </c>
-      <c r="E35" s="6">
-        <v>-0.96</v>
-      </c>
-    </row>
-    <row r="36" spans="1:5">
-      <c r="A36" s="3" t="s">
+      <c r="B56" s="5" t="s">
+        <v>31</v>
+      </c>
+      <c r="C56" s="6">
+        <v>-63.23</v>
+      </c>
+      <c r="D56" s="6">
+        <v>-49.7</v>
+      </c>
+      <c r="E56" s="8">
+        <v>13.53</v>
+      </c>
+    </row>
+    <row r="57" spans="1:5">
+      <c r="A57" s="5" t="s">
         <v>38</v>
       </c>
-      <c r="B36" s="3" t="s">
-        <v>6</v>
-      </c>
-      <c r="C36" s="5">
-        <v>-29.58</v>
-      </c>
-      <c r="D36" s="5">
-        <v>-33.3</v>
-      </c>
-      <c r="E36" s="6">
-        <v>-3.72</v>
-      </c>
-    </row>
-    <row r="37" spans="1:5">
-      <c r="A37" s="3" t="s">
+      <c r="B57" s="5" t="s">
+        <v>31</v>
+      </c>
+      <c r="C57" s="6">
+        <v>28.57</v>
+      </c>
+      <c r="D57" s="6">
+        <v>-35.33</v>
+      </c>
+      <c r="E57" s="7">
+        <v>-63.9</v>
+      </c>
+    </row>
+    <row r="58" spans="1:5">
+      <c r="A58" s="5" t="s">
         <v>39</v>
       </c>
-      <c r="B37" s="3" t="s">
-        <v>6</v>
-      </c>
-      <c r="C37" s="5">
-        <v>-45.02</v>
-      </c>
-      <c r="D37" s="5">
-        <v>-45.92</v>
-      </c>
-      <c r="E37" s="6">
-        <v>-0.9</v>
-      </c>
-    </row>
-    <row r="38" spans="1:5">
-      <c r="A38" s="3" t="s">
+      <c r="B58" s="5" t="s">
+        <v>31</v>
+      </c>
+      <c r="C58" s="6">
+        <v>-75</v>
+      </c>
+      <c r="D58" s="6">
+        <v>-72.79000000000001</v>
+      </c>
+      <c r="E58" s="8">
+        <v>2.21</v>
+      </c>
+    </row>
+    <row r="59" spans="1:5">
+      <c r="A59" s="5" t="s">
         <v>40</v>
       </c>
-      <c r="B38" s="3" t="s">
-        <v>6</v>
-      </c>
-      <c r="C38" s="5">
-        <v>-20.56</v>
-      </c>
-      <c r="D38" s="5">
-        <v>-21.9</v>
-      </c>
-      <c r="E38" s="6">
-        <v>-1.34</v>
-      </c>
-    </row>
-    <row r="39" spans="1:5">
-      <c r="A39" s="3" t="s">
+      <c r="B59" s="5" t="s">
+        <v>31</v>
+      </c>
+      <c r="C59" s="6">
+        <v>1.4</v>
+      </c>
+      <c r="D59" s="6">
+        <v>35.35</v>
+      </c>
+      <c r="E59" s="8">
+        <v>33.95</v>
+      </c>
+    </row>
+    <row r="60" spans="1:5">
+      <c r="A60" s="5" t="s">
         <v>41</v>
       </c>
-      <c r="B39" s="3" t="s">
-        <v>6</v>
-      </c>
-      <c r="C39" s="5">
-        <v>-14.81</v>
-      </c>
-      <c r="D39" s="5">
-        <v>-14.3</v>
-      </c>
-      <c r="E39" s="7">
-        <v>0.51</v>
-      </c>
-    </row>
-    <row r="40" spans="1:5">
-      <c r="A40" s="3" t="s">
+      <c r="B60" s="5" t="s">
+        <v>31</v>
+      </c>
+      <c r="C60" s="6">
+        <v>-37.8</v>
+      </c>
+      <c r="D60" s="6">
+        <v>-10.37</v>
+      </c>
+      <c r="E60" s="8">
+        <v>27.43</v>
+      </c>
+    </row>
+    <row r="61" spans="1:5">
+      <c r="A61" s="5" t="s">
         <v>42</v>
       </c>
-      <c r="B40" s="3" t="s">
-        <v>6</v>
-      </c>
-      <c r="C40" s="5">
-        <v>-15.25</v>
-      </c>
-      <c r="D40" s="5">
-        <v>-17.38</v>
-      </c>
-      <c r="E40" s="6">
-        <v>-2.13</v>
-      </c>
-    </row>
-    <row r="41" spans="1:5">
-      <c r="A41" s="3" t="s">
+      <c r="B61" s="5" t="s">
+        <v>31</v>
+      </c>
+      <c r="C61" s="6">
+        <v>7.89</v>
+      </c>
+      <c r="D61" s="6">
+        <v>135.86</v>
+      </c>
+      <c r="E61" s="8">
+        <v>127.97</v>
+      </c>
+    </row>
+    <row r="62" spans="1:5">
+      <c r="A62" s="5" t="s">
         <v>43</v>
       </c>
-      <c r="B41" s="3" t="s">
-        <v>6</v>
-      </c>
-      <c r="C41" s="5">
-        <v>-7.49</v>
-      </c>
-      <c r="D41" s="5">
-        <v>-11.53</v>
-      </c>
-      <c r="E41" s="6">
-        <v>-4.04</v>
-      </c>
-    </row>
-    <row r="42" spans="1:5">
-      <c r="A42" s="3" t="s">
-        <v>37</v>
-      </c>
-      <c r="B42" s="3" t="s">
-        <v>2</v>
-      </c>
-      <c r="C42" s="5">
-        <v>10405</v>
-      </c>
-      <c r="D42" s="5">
-        <v>10287</v>
-      </c>
-      <c r="E42" s="6">
-        <v>-118</v>
-      </c>
-    </row>
-    <row r="43" spans="1:5">
-      <c r="A43" s="3" t="s">
-        <v>38</v>
-      </c>
-      <c r="B43" s="3" t="s">
-        <v>2</v>
-      </c>
-      <c r="C43" s="5">
-        <v>472</v>
-      </c>
-      <c r="D43" s="5">
-        <v>447.05</v>
-      </c>
-      <c r="E43" s="6">
-        <v>-24.95</v>
-      </c>
-    </row>
-    <row r="44" spans="1:5">
-      <c r="A44" s="3" t="s">
-        <v>39</v>
-      </c>
-      <c r="B44" s="3" t="s">
-        <v>2</v>
-      </c>
-      <c r="C44" s="5">
-        <v>301.3</v>
-      </c>
-      <c r="D44" s="5">
-        <v>296.35</v>
-      </c>
-      <c r="E44" s="6">
-        <v>-4.95</v>
-      </c>
-    </row>
-    <row r="45" spans="1:5">
-      <c r="A45" s="3" t="s">
-        <v>40</v>
-      </c>
-      <c r="B45" s="3" t="s">
-        <v>2</v>
-      </c>
-      <c r="C45" s="5">
-        <v>1729</v>
-      </c>
-      <c r="D45" s="5">
-        <v>1700</v>
-      </c>
-      <c r="E45" s="6">
-        <v>-29</v>
-      </c>
-    </row>
-    <row r="46" spans="1:5">
-      <c r="A46" s="3" t="s">
-        <v>41</v>
-      </c>
-      <c r="B46" s="3" t="s">
-        <v>2</v>
-      </c>
-      <c r="C46" s="5">
-        <v>11198</v>
-      </c>
-      <c r="D46" s="5">
-        <v>11265</v>
-      </c>
-      <c r="E46" s="7">
-        <v>67</v>
-      </c>
-    </row>
-    <row r="47" spans="1:5">
-      <c r="A47" s="3" t="s">
-        <v>42</v>
-      </c>
-      <c r="B47" s="3" t="s">
-        <v>2</v>
-      </c>
-      <c r="C47" s="5">
-        <v>982.1</v>
-      </c>
-      <c r="D47" s="5">
-        <v>957.35</v>
-      </c>
-      <c r="E47" s="6">
-        <v>-24.75</v>
-      </c>
-    </row>
-    <row r="48" spans="1:5">
-      <c r="A48" s="3" t="s">
-        <v>43</v>
-      </c>
-      <c r="B48" s="3" t="s">
-        <v>2</v>
-      </c>
-      <c r="C48" s="5">
-        <v>171.99</v>
-      </c>
-      <c r="D48" s="5">
-        <v>164.48</v>
-      </c>
-      <c r="E48" s="6">
-        <v>-7.51</v>
-      </c>
-    </row>
-    <row r="49" spans="1:5">
-      <c r="A49" s="3" t="s">
-        <v>38</v>
-      </c>
-      <c r="B49" s="3" t="s">
-        <v>13</v>
-      </c>
-      <c r="C49" s="5">
-        <v>99</v>
-      </c>
-      <c r="D49" s="5">
-        <v>85</v>
-      </c>
-      <c r="E49" s="6">
-        <v>-14</v>
-      </c>
-    </row>
-    <row r="50" spans="1:5">
-      <c r="A50" s="3" t="s">
-        <v>43</v>
-      </c>
-      <c r="B50" s="3" t="s">
-        <v>13</v>
-      </c>
-      <c r="C50" s="5">
-        <v>85</v>
-      </c>
-      <c r="D50" s="5">
-        <v>99</v>
-      </c>
-      <c r="E50" s="7">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="51" spans="1:5">
-      <c r="A51" s="3" t="s">
-        <v>37</v>
-      </c>
-      <c r="B51" s="3" t="s">
-        <v>24</v>
-      </c>
-      <c r="C51" s="5">
-        <v>42.81</v>
-      </c>
-      <c r="D51" s="5">
-        <v>40.4</v>
-      </c>
-      <c r="E51" s="6">
-        <v>-2.41</v>
-      </c>
-    </row>
-    <row r="52" spans="1:5">
-      <c r="A52" s="3" t="s">
-        <v>38</v>
-      </c>
-      <c r="B52" s="3" t="s">
-        <v>24</v>
-      </c>
-      <c r="C52" s="5">
-        <v>42.46</v>
-      </c>
-      <c r="D52" s="5">
-        <v>36.9</v>
-      </c>
-      <c r="E52" s="6">
-        <v>-5.56</v>
-      </c>
-    </row>
-    <row r="53" spans="1:5">
-      <c r="A53" s="3" t="s">
-        <v>39</v>
-      </c>
-      <c r="B53" s="3" t="s">
-        <v>24</v>
-      </c>
-      <c r="C53" s="5">
-        <v>39.3</v>
-      </c>
-      <c r="D53" s="5">
-        <v>35.93</v>
-      </c>
-      <c r="E53" s="6">
-        <v>-3.37</v>
-      </c>
-    </row>
-    <row r="54" spans="1:5">
-      <c r="A54" s="3" t="s">
-        <v>40</v>
-      </c>
-      <c r="B54" s="3" t="s">
-        <v>24</v>
-      </c>
-      <c r="C54" s="5">
-        <v>37.15</v>
-      </c>
-      <c r="D54" s="5">
-        <v>33.26</v>
-      </c>
-      <c r="E54" s="6">
-        <v>-3.89</v>
-      </c>
-    </row>
-    <row r="55" spans="1:5">
-      <c r="A55" s="3" t="s">
-        <v>41</v>
-      </c>
-      <c r="B55" s="3" t="s">
-        <v>24</v>
-      </c>
-      <c r="C55" s="5">
-        <v>56.84</v>
-      </c>
-      <c r="D55" s="5">
-        <v>58.34</v>
-      </c>
-      <c r="E55" s="7">
-        <v>1.5</v>
-      </c>
-    </row>
-    <row r="56" spans="1:5">
-      <c r="A56" s="3" t="s">
-        <v>42</v>
-      </c>
-      <c r="B56" s="3" t="s">
-        <v>24</v>
-      </c>
-      <c r="C56" s="5">
-        <v>47.29</v>
-      </c>
-      <c r="D56" s="5">
-        <v>41.61</v>
-      </c>
-      <c r="E56" s="6">
-        <v>-5.68</v>
-      </c>
-    </row>
-    <row r="57" spans="1:5">
-      <c r="A57" s="3" t="s">
-        <v>43</v>
-      </c>
-      <c r="B57" s="3" t="s">
-        <v>24</v>
-      </c>
-      <c r="C57" s="5">
-        <v>58.54</v>
-      </c>
-      <c r="D57" s="5">
-        <v>50.61</v>
-      </c>
-      <c r="E57" s="6">
-        <v>-7.93</v>
-      </c>
-    </row>
-    <row r="58" spans="1:5">
-      <c r="A58" s="3" t="s">
-        <v>37</v>
-      </c>
-      <c r="B58" s="3" t="s">
+      <c r="B62" s="5" t="s">
         <v>31</v>
       </c>
-      <c r="C58" s="5">
-        <v>-39.09</v>
-      </c>
-      <c r="D58" s="5">
-        <v>-63.23</v>
-      </c>
-      <c r="E58" s="6">
-        <v>-24.14</v>
-      </c>
-    </row>
-    <row r="59" spans="1:5">
-      <c r="A59" s="3" t="s">
-        <v>38</v>
-      </c>
-      <c r="B59" s="3" t="s">
-        <v>31</v>
-      </c>
-      <c r="C59" s="5">
-        <v>26.05</v>
-      </c>
-      <c r="D59" s="5">
-        <v>28.57</v>
-      </c>
-      <c r="E59" s="7">
-        <v>2.52</v>
-      </c>
-    </row>
-    <row r="60" spans="1:5">
-      <c r="A60" s="3" t="s">
-        <v>39</v>
-      </c>
-      <c r="B60" s="3" t="s">
-        <v>31</v>
-      </c>
-      <c r="C60" s="5">
-        <v>-16.85</v>
-      </c>
-      <c r="D60" s="5">
-        <v>-75</v>
-      </c>
-      <c r="E60" s="6">
-        <v>-58.15</v>
-      </c>
-    </row>
-    <row r="61" spans="1:5">
-      <c r="A61" s="3" t="s">
-        <v>40</v>
-      </c>
-      <c r="B61" s="3" t="s">
-        <v>31</v>
-      </c>
-      <c r="C61" s="5">
-        <v>26.53</v>
-      </c>
-      <c r="D61" s="5">
-        <v>1.4</v>
-      </c>
-      <c r="E61" s="6">
-        <v>-25.13</v>
-      </c>
-    </row>
-    <row r="62" spans="1:5">
-      <c r="A62" s="3" t="s">
-        <v>41</v>
-      </c>
-      <c r="B62" s="3" t="s">
-        <v>31</v>
-      </c>
-      <c r="C62" s="5">
-        <v>-37</v>
-      </c>
-      <c r="D62" s="5">
-        <v>-37.8</v>
-      </c>
-      <c r="E62" s="6">
-        <v>-0.8</v>
-      </c>
-    </row>
-    <row r="63" spans="1:5">
-      <c r="A63" s="3" t="s">
-        <v>42</v>
-      </c>
-      <c r="B63" s="3" t="s">
-        <v>31</v>
-      </c>
-      <c r="C63" s="5">
-        <v>3.74</v>
-      </c>
-      <c r="D63" s="5">
-        <v>7.89</v>
-      </c>
-      <c r="E63" s="7">
-        <v>4.15</v>
-      </c>
-    </row>
-    <row r="64" spans="1:5">
-      <c r="A64" s="3" t="s">
-        <v>43</v>
-      </c>
-      <c r="B64" s="3" t="s">
-        <v>31</v>
-      </c>
-      <c r="C64" s="5">
-        <v>-80.87</v>
-      </c>
-      <c r="D64" s="5">
+      <c r="C62" s="6">
         <v>-71.05</v>
       </c>
-      <c r="E64" s="7">
-        <v>9.82</v>
+      <c r="D62" s="6">
+        <v>-55.84</v>
+      </c>
+      <c r="E62" s="8">
+        <v>15.21</v>
       </c>
     </row>
   </sheetData>
@@ -2875,60 +2901,60 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:9" ht="28" customHeight="1">
-      <c r="A1" s="8" t="s">
+      <c r="A1" s="9" t="s">
         <v>1</v>
       </c>
-      <c r="B1" s="8" t="s">
-        <v>56</v>
-      </c>
-      <c r="C1" s="8" t="s">
+      <c r="B1" s="9" t="s">
+        <v>64</v>
+      </c>
+      <c r="C1" s="9" t="s">
+        <v>65</v>
+      </c>
+      <c r="D1" s="9" t="s">
+        <v>66</v>
+      </c>
+      <c r="E1" s="9" t="s">
+        <v>67</v>
+      </c>
+      <c r="F1" s="9" t="s">
+        <v>68</v>
+      </c>
+      <c r="G1" s="9" t="s">
+        <v>69</v>
+      </c>
+      <c r="H1" s="9" t="s">
+        <v>70</v>
+      </c>
+      <c r="I1" s="9" t="s">
+        <v>71</v>
+      </c>
+    </row>
+    <row r="2" spans="1:9">
+      <c r="A2" s="10" t="s">
+        <v>44</v>
+      </c>
+      <c r="B2" s="11">
+        <v>44.24</v>
+      </c>
+      <c r="C2" s="12">
+        <v>7</v>
+      </c>
+      <c r="D2" s="11">
+        <v>37.9</v>
+      </c>
+      <c r="E2" s="11">
+        <v>28.6</v>
+      </c>
+      <c r="F2" s="11">
+        <v>-6.3</v>
+      </c>
+      <c r="G2" s="11">
+        <v>-6.6</v>
+      </c>
+      <c r="H2" s="11">
         <v>57</v>
       </c>
-      <c r="D1" s="8" t="s">
-        <v>58</v>
-      </c>
-      <c r="E1" s="8" t="s">
-        <v>59</v>
-      </c>
-      <c r="F1" s="8" t="s">
-        <v>60</v>
-      </c>
-      <c r="G1" s="8" t="s">
-        <v>61</v>
-      </c>
-      <c r="H1" s="8" t="s">
-        <v>62</v>
-      </c>
-      <c r="I1" s="8" t="s">
-        <v>63</v>
-      </c>
-    </row>
-    <row r="2" spans="1:9">
-      <c r="A2" s="9" t="s">
-        <v>44</v>
-      </c>
-      <c r="B2" s="10">
-        <v>49.96</v>
-      </c>
-      <c r="C2" s="11">
-        <v>7</v>
-      </c>
-      <c r="D2" s="10">
-        <v>42.4</v>
-      </c>
-      <c r="E2" s="10">
-        <v>42.9</v>
-      </c>
-      <c r="F2" s="10">
-        <v>-2.8</v>
-      </c>
-      <c r="G2" s="10">
-        <v>-3.7</v>
-      </c>
-      <c r="H2" s="10">
-        <v>57</v>
-      </c>
-      <c r="I2" s="10">
+      <c r="I2" s="11">
         <v>14.3</v>
       </c>
     </row>
@@ -3030,49 +3056,49 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:7">
-      <c r="A1" s="12" t="s">
+      <c r="A1" s="13" t="s">
         <v>37</v>
       </c>
-      <c r="B1" s="12" t="s">
+      <c r="B1" s="13" t="s">
         <v>41</v>
       </c>
-      <c r="C1" s="12" t="s">
+      <c r="C1" s="13" t="s">
         <v>38</v>
       </c>
-      <c r="D1" s="12" t="s">
+      <c r="D1" s="13" t="s">
         <v>42</v>
       </c>
-      <c r="E1" s="12" t="s">
+      <c r="E1" s="13" t="s">
         <v>43</v>
       </c>
-      <c r="F1" s="12" t="s">
+      <c r="F1" s="13" t="s">
         <v>40</v>
       </c>
-      <c r="G1" s="12" t="s">
+      <c r="G1" s="13" t="s">
         <v>39</v>
       </c>
     </row>
     <row r="2" spans="1:7">
-      <c r="A2" s="13">
-        <v>0.2414</v>
-      </c>
-      <c r="B2" s="13">
-        <v>0.1987</v>
-      </c>
-      <c r="C2" s="13">
-        <v>0.1424</v>
-      </c>
-      <c r="D2" s="13">
-        <v>0.0474</v>
-      </c>
-      <c r="E2" s="13">
-        <v>0.0455</v>
-      </c>
-      <c r="F2" s="13">
-        <v>-0.0224</v>
-      </c>
-      <c r="G2" s="13">
-        <v>-0.2418</v>
+      <c r="A2" s="14">
+        <v>0.2431</v>
+      </c>
+      <c r="B2" s="14">
+        <v>0.1961</v>
+      </c>
+      <c r="C2" s="14">
+        <v>0.1417</v>
+      </c>
+      <c r="D2" s="14">
+        <v>0.0405</v>
+      </c>
+      <c r="E2" s="14">
+        <v>0.0364</v>
+      </c>
+      <c r="F2" s="14">
+        <v>-0.0184</v>
+      </c>
+      <c r="G2" s="14">
+        <v>-0.2298</v>
       </c>
     </row>
   </sheetData>

--- a/BAJAJ_GROUP_Technical_Metrics.xlsx
+++ b/BAJAJ_GROUP_Technical_Metrics.xlsx
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="264" uniqueCount="72">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="253" uniqueCount="63">
   <si>
     <t>Symbol</t>
   </si>
@@ -169,34 +169,7 @@
     <t>▶  SIGNAL EVENTS (vs Previous Run)</t>
   </si>
   <si>
-    <t>Signal</t>
-  </si>
-  <si>
-    <t>Change</t>
-  </si>
-  <si>
-    <t>Direction</t>
-  </si>
-  <si>
-    <t>Prev Value</t>
-  </si>
-  <si>
-    <t>Curr Value</t>
-  </si>
-  <si>
-    <t>RSI Momentum</t>
-  </si>
-  <si>
-    <t>50.6 → 44.0</t>
-  </si>
-  <si>
-    <t>🔴 BEARISH</t>
-  </si>
-  <si>
-    <t>50.6</t>
-  </si>
-  <si>
-    <t>44.0</t>
+    <t>No signal events detected since last run.</t>
   </si>
   <si>
     <t>▶  NUMERIC METRIC CHANGES (vs Previous Run)</t>
@@ -282,14 +255,14 @@
     </font>
     <font>
       <sz val="11"/>
-      <color rgb="FF9C0006"/>
+      <color rgb="FF006100"/>
       <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
     </font>
     <font>
       <sz val="11"/>
-      <color rgb="FF006100"/>
+      <color rgb="FF9C0006"/>
       <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
@@ -322,13 +295,13 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFFFC7CE"/>
+        <fgColor rgb="FFC6EFCE"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFC6EFCE"/>
+        <fgColor rgb="FFFFC7CE"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -398,15 +371,14 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="15">
+  <cellXfs count="14">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="2" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="3" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1"/>
     <xf numFmtId="165" fontId="4" fillId="5" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="165" fontId="5" fillId="6" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
@@ -921,10 +893,10 @@
         <v>44</v>
       </c>
       <c r="C2">
-        <v>10072</v>
+        <v>10155</v>
       </c>
       <c r="D2">
-        <v>-2.09</v>
+        <v>0.82</v>
       </c>
       <c r="E2">
         <v>12361</v>
@@ -933,46 +905,46 @@
         <v>8599.48</v>
       </c>
       <c r="G2">
-        <v>-18.52</v>
+        <v>-17.85</v>
       </c>
       <c r="H2">
-        <v>17.12</v>
+        <v>18.09</v>
       </c>
       <c r="I2">
-        <v>-2.38</v>
+        <v>-0.93</v>
       </c>
       <c r="J2">
-        <v>-11.76</v>
+        <v>-11.39</v>
       </c>
       <c r="K2">
-        <v>-3.19</v>
+        <v>-7.67</v>
       </c>
       <c r="L2">
-        <v>13.51</v>
+        <v>12.53</v>
       </c>
       <c r="M2">
-        <v>24.31</v>
+        <v>24.11</v>
       </c>
       <c r="N2">
         <v>71</v>
       </c>
       <c r="O2">
-        <v>72</v>
+        <v>70</v>
       </c>
       <c r="P2">
-        <v>10279.8</v>
+        <v>10260.8</v>
       </c>
       <c r="Q2">
-        <v>10454.85</v>
+        <v>10394.45</v>
       </c>
       <c r="R2">
-        <v>11236.9</v>
+        <v>11206.46</v>
       </c>
       <c r="S2">
-        <v>10208.57</v>
+        <v>10212.22</v>
       </c>
       <c r="T2">
-        <v>-1.34</v>
+        <v>-0.5600000000000001</v>
       </c>
       <c r="U2" t="s">
         <v>45</v>
@@ -987,34 +959,34 @@
         <v>1</v>
       </c>
       <c r="Y2">
-        <v>36.39</v>
+        <v>38.91</v>
       </c>
       <c r="Z2">
-        <v>-314.64</v>
+        <v>-301.82</v>
       </c>
       <c r="AA2">
-        <v>-350.64</v>
+        <v>-340.88</v>
       </c>
       <c r="AB2">
-        <v>36</v>
+        <v>39.06</v>
       </c>
       <c r="AC2">
-        <v>88.19</v>
+        <v>82.97</v>
       </c>
       <c r="AD2">
-        <v>94</v>
+        <v>89.31</v>
       </c>
       <c r="AE2">
-        <v>263.91</v>
+        <v>271.13</v>
       </c>
       <c r="AF2">
-        <v>-49.7</v>
+        <v>-21.71</v>
       </c>
       <c r="AG2">
-        <v>11579.91</v>
+        <v>11441.21</v>
       </c>
       <c r="AH2">
-        <v>9329.790000000001</v>
+        <v>9347.690000000001</v>
       </c>
       <c r="AI2">
         <v>10503.51</v>
@@ -1023,7 +995,7 @@
         <v>47</v>
       </c>
       <c r="AK2">
-        <v>41.5</v>
+        <v>41.33</v>
       </c>
     </row>
     <row r="3" spans="1:37">
@@ -1034,10 +1006,10 @@
         <v>44</v>
       </c>
       <c r="C3">
-        <v>425.4</v>
+        <v>415.9</v>
       </c>
       <c r="D3">
-        <v>-4.84</v>
+        <v>-2.23</v>
       </c>
       <c r="E3">
         <v>670.25</v>
@@ -1046,46 +1018,46 @@
         <v>247.45</v>
       </c>
       <c r="G3">
-        <v>-36.53</v>
+        <v>-37.95</v>
       </c>
       <c r="H3">
-        <v>71.91</v>
+        <v>68.06999999999999</v>
       </c>
       <c r="I3">
-        <v>-16.3</v>
+        <v>-20.03</v>
       </c>
       <c r="J3">
-        <v>-16.94</v>
+        <v>-19.29</v>
       </c>
       <c r="K3">
-        <v>-19.01</v>
+        <v>-21.47</v>
       </c>
       <c r="L3">
-        <v>60.84</v>
+        <v>56.89</v>
       </c>
       <c r="M3">
-        <v>14.17</v>
+        <v>13.99</v>
       </c>
       <c r="N3">
         <v>85</v>
       </c>
       <c r="O3">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="P3">
-        <v>466.6</v>
+        <v>445.77</v>
       </c>
       <c r="Q3">
-        <v>488.65</v>
+        <v>483.76</v>
       </c>
       <c r="R3">
-        <v>495.28</v>
+        <v>492.66</v>
       </c>
       <c r="S3">
-        <v>465.58</v>
+        <v>466.34</v>
       </c>
       <c r="T3">
-        <v>-8.630000000000001</v>
+        <v>-10.82</v>
       </c>
       <c r="U3" t="s">
         <v>45</v>
@@ -1100,43 +1072,43 @@
         <v>1</v>
       </c>
       <c r="Y3">
-        <v>32.87</v>
+        <v>31.26</v>
       </c>
       <c r="Z3">
-        <v>-12.07</v>
+        <v>-15.96</v>
       </c>
       <c r="AA3">
-        <v>-5.85</v>
+        <v>-7.87</v>
       </c>
       <c r="AB3">
-        <v>-6.22</v>
+        <v>-8.09</v>
       </c>
       <c r="AC3">
-        <v>6.3</v>
+        <v>0</v>
       </c>
       <c r="AD3">
-        <v>20.17</v>
+        <v>5.58</v>
       </c>
       <c r="AE3">
-        <v>24.08</v>
+        <v>23.49</v>
       </c>
       <c r="AF3">
-        <v>-35.33</v>
+        <v>-22.93</v>
       </c>
       <c r="AG3">
-        <v>533.8</v>
+        <v>537.79</v>
       </c>
       <c r="AH3">
-        <v>443.5</v>
+        <v>429.73</v>
       </c>
       <c r="AI3">
-        <v>508.7</v>
+        <v>490.69</v>
       </c>
       <c r="AJ3" t="s">
         <v>47</v>
       </c>
       <c r="AK3">
-        <v>33.48</v>
+        <v>37.78</v>
       </c>
     </row>
     <row r="4" spans="1:37">
@@ -1147,58 +1119,58 @@
         <v>44</v>
       </c>
       <c r="C4">
-        <v>293.1</v>
+        <v>278.8</v>
       </c>
       <c r="D4">
-        <v>-1.1</v>
+        <v>-4.88</v>
       </c>
       <c r="E4">
-        <v>543.1</v>
+        <v>542.2</v>
       </c>
       <c r="F4">
-        <v>290.05</v>
+        <v>278.8</v>
       </c>
       <c r="G4">
-        <v>-46.03</v>
+        <v>-48.58</v>
       </c>
       <c r="H4">
-        <v>1.05</v>
+        <v>0</v>
       </c>
       <c r="I4">
-        <v>-3.28</v>
+        <v>-8.710000000000001</v>
       </c>
       <c r="J4">
-        <v>-9.27</v>
+        <v>-14.48</v>
       </c>
       <c r="K4">
-        <v>-12.02</v>
+        <v>-15.55</v>
       </c>
       <c r="L4">
-        <v>-46.51</v>
+        <v>-48.67</v>
       </c>
       <c r="M4">
-        <v>-22.98</v>
+        <v>-23.67</v>
       </c>
       <c r="N4">
         <v>15</v>
       </c>
       <c r="O4">
-        <v>13</v>
+        <v>9</v>
       </c>
       <c r="P4">
-        <v>300.57</v>
+        <v>295.25</v>
       </c>
       <c r="Q4">
-        <v>305.7</v>
+        <v>303.46</v>
       </c>
       <c r="R4">
-        <v>326.9</v>
+        <v>325.21</v>
       </c>
       <c r="S4">
-        <v>357.16</v>
+        <v>356.18</v>
       </c>
       <c r="T4">
-        <v>-17.94</v>
+        <v>-21.72</v>
       </c>
       <c r="U4" t="s">
         <v>45</v>
@@ -1213,43 +1185,43 @@
         <v>0</v>
       </c>
       <c r="Y4">
-        <v>33.87</v>
+        <v>26.64</v>
       </c>
       <c r="Z4">
-        <v>-8.039999999999999</v>
+        <v>-9.26</v>
       </c>
       <c r="AA4">
-        <v>-8.44</v>
+        <v>-8.6</v>
       </c>
       <c r="AB4">
-        <v>0.4</v>
+        <v>-0.65</v>
       </c>
       <c r="AC4">
-        <v>62.05</v>
+        <v>39.4</v>
       </c>
       <c r="AD4">
-        <v>77.94</v>
+        <v>60.21</v>
       </c>
       <c r="AE4">
-        <v>10.97</v>
+        <v>11.49</v>
       </c>
       <c r="AF4">
-        <v>-72.79000000000001</v>
+        <v>-38.35</v>
       </c>
       <c r="AG4">
-        <v>327.02</v>
+        <v>326.26</v>
       </c>
       <c r="AH4">
-        <v>284.38</v>
+        <v>280.67</v>
       </c>
       <c r="AI4">
-        <v>322.52</v>
+        <v>317.46</v>
       </c>
       <c r="AJ4" t="s">
         <v>47</v>
       </c>
       <c r="AK4">
-        <v>45.79</v>
+        <v>40.69</v>
       </c>
     </row>
     <row r="5" spans="1:37">
@@ -1260,10 +1232,10 @@
         <v>44</v>
       </c>
       <c r="C5">
-        <v>1690</v>
+        <v>1678</v>
       </c>
       <c r="D5">
-        <v>-0.59</v>
+        <v>-0.71</v>
       </c>
       <c r="E5">
         <v>2176.6</v>
@@ -1272,46 +1244,46 @@
         <v>1631.8</v>
       </c>
       <c r="G5">
-        <v>-22.36</v>
+        <v>-22.91</v>
       </c>
       <c r="H5">
-        <v>3.57</v>
+        <v>2.83</v>
       </c>
       <c r="I5">
-        <v>-3.74</v>
+        <v>-2.54</v>
       </c>
       <c r="J5">
-        <v>-8.77</v>
+        <v>-9.289999999999999</v>
       </c>
       <c r="K5">
-        <v>-11.08</v>
+        <v>-10.57</v>
       </c>
       <c r="L5">
-        <v>-18.91</v>
+        <v>-19.72</v>
       </c>
       <c r="M5">
-        <v>-1.84</v>
+        <v>-2.06</v>
       </c>
       <c r="N5">
         <v>29</v>
       </c>
       <c r="O5">
-        <v>39</v>
+        <v>41</v>
       </c>
       <c r="P5">
-        <v>1714.54</v>
+        <v>1705.8</v>
       </c>
       <c r="Q5">
-        <v>1744.97</v>
+        <v>1737.7</v>
       </c>
       <c r="R5">
-        <v>1879.37</v>
+        <v>1872.51</v>
       </c>
       <c r="S5">
-        <v>1866.24</v>
+        <v>1864.45</v>
       </c>
       <c r="T5">
-        <v>-9.44</v>
+        <v>-10</v>
       </c>
       <c r="U5" t="s">
         <v>45</v>
@@ -1326,43 +1298,43 @@
         <v>1</v>
       </c>
       <c r="Y5">
-        <v>32.02</v>
+        <v>30.54</v>
       </c>
       <c r="Z5">
-        <v>-46.11</v>
+        <v>-46.86</v>
       </c>
       <c r="AA5">
-        <v>-48.95</v>
+        <v>-48.53</v>
       </c>
       <c r="AB5">
-        <v>2.84</v>
+        <v>1.67</v>
       </c>
       <c r="AC5">
-        <v>62.57</v>
+        <v>47.4</v>
       </c>
       <c r="AD5">
-        <v>72.16</v>
+        <v>61.59</v>
       </c>
       <c r="AE5">
-        <v>38.3</v>
+        <v>38.5</v>
       </c>
       <c r="AF5">
-        <v>35.35</v>
+        <v>24.43</v>
       </c>
       <c r="AG5">
-        <v>1819.18</v>
+        <v>1807.94</v>
       </c>
       <c r="AH5">
-        <v>1670.75</v>
+        <v>1667.45</v>
       </c>
       <c r="AI5">
-        <v>1797.01</v>
+        <v>1787.89</v>
       </c>
       <c r="AJ5" t="s">
         <v>47</v>
       </c>
       <c r="AK5">
-        <v>55.17</v>
+        <v>57.4</v>
       </c>
     </row>
     <row r="6" spans="1:37">
@@ -1373,10 +1345,10 @@
         <v>44</v>
       </c>
       <c r="C6">
-        <v>10975</v>
+        <v>11293</v>
       </c>
       <c r="D6">
-        <v>-2.57</v>
+        <v>2.9</v>
       </c>
       <c r="E6">
         <v>13144</v>
@@ -1385,46 +1357,46 @@
         <v>8746</v>
       </c>
       <c r="G6">
-        <v>-16.5</v>
+        <v>-14.08</v>
       </c>
       <c r="H6">
-        <v>25.49</v>
+        <v>29.12</v>
       </c>
       <c r="I6">
-        <v>1.55</v>
+        <v>4.82</v>
       </c>
       <c r="J6">
-        <v>-2.72</v>
+        <v>-1.02</v>
       </c>
       <c r="K6">
-        <v>5.06</v>
+        <v>8.33</v>
       </c>
       <c r="L6">
-        <v>-10.17</v>
+        <v>-9.66</v>
       </c>
       <c r="M6">
-        <v>19.61</v>
+        <v>20.22</v>
       </c>
       <c r="N6">
         <v>57</v>
       </c>
       <c r="O6">
-        <v>64</v>
+        <v>69</v>
       </c>
       <c r="P6">
-        <v>11087.4</v>
+        <v>11191.2</v>
       </c>
       <c r="Q6">
-        <v>10887.7</v>
+        <v>10893.1</v>
       </c>
       <c r="R6">
-        <v>11122.66</v>
+        <v>11119.1</v>
       </c>
       <c r="S6">
-        <v>10659.14</v>
+        <v>10658.89</v>
       </c>
       <c r="T6">
-        <v>2.96</v>
+        <v>5.95</v>
       </c>
       <c r="U6" t="s">
         <v>45</v>
@@ -1439,34 +1411,34 @@
         <v>2</v>
       </c>
       <c r="Y6">
-        <v>50.19</v>
+        <v>57.24</v>
       </c>
       <c r="Z6">
-        <v>-1.42</v>
+        <v>24.9</v>
       </c>
       <c r="AA6">
-        <v>-58.24</v>
+        <v>-41.61</v>
       </c>
       <c r="AB6">
-        <v>56.81</v>
+        <v>66.51000000000001</v>
       </c>
       <c r="AC6">
-        <v>83.59999999999999</v>
+        <v>82.93000000000001</v>
       </c>
       <c r="AD6">
-        <v>92.48</v>
+        <v>88.39</v>
       </c>
       <c r="AE6">
-        <v>269.82</v>
+        <v>292.41</v>
       </c>
       <c r="AF6">
-        <v>-10.37</v>
+        <v>224.33</v>
       </c>
       <c r="AG6">
-        <v>11390.36</v>
+        <v>11411.29</v>
       </c>
       <c r="AH6">
-        <v>10385.04</v>
+        <v>10374.91</v>
       </c>
       <c r="AI6">
         <v>11368.55</v>
@@ -1475,7 +1447,7 @@
         <v>47</v>
       </c>
       <c r="AK6">
-        <v>25.68</v>
+        <v>25.64</v>
       </c>
     </row>
     <row r="7" spans="1:37">
@@ -1486,10 +1458,10 @@
         <v>44</v>
       </c>
       <c r="C7">
-        <v>926</v>
+        <v>942.1</v>
       </c>
       <c r="D7">
-        <v>-3.27</v>
+        <v>1.74</v>
       </c>
       <c r="E7">
         <v>1158.8</v>
@@ -1498,46 +1470,46 @@
         <v>801.55</v>
       </c>
       <c r="G7">
-        <v>-20.09</v>
+        <v>-18.7</v>
       </c>
       <c r="H7">
-        <v>15.53</v>
+        <v>17.53</v>
       </c>
       <c r="I7">
-        <v>-5.77</v>
+        <v>-1.56</v>
       </c>
       <c r="J7">
-        <v>-10.99</v>
+        <v>-7.75</v>
       </c>
       <c r="K7">
-        <v>-13.39</v>
+        <v>-11.15</v>
       </c>
       <c r="L7">
-        <v>-12.63</v>
+        <v>-11.6</v>
       </c>
       <c r="M7">
-        <v>4.05</v>
+        <v>4.49</v>
       </c>
       <c r="N7">
         <v>43</v>
       </c>
       <c r="O7">
-        <v>42</v>
+        <v>49</v>
       </c>
       <c r="P7">
-        <v>957.54</v>
+        <v>954.5599999999999</v>
       </c>
       <c r="Q7">
-        <v>971.9</v>
+        <v>968.5599999999999</v>
       </c>
       <c r="R7">
-        <v>1027.43</v>
+        <v>1024.22</v>
       </c>
       <c r="S7">
-        <v>973.9</v>
+        <v>973.75</v>
       </c>
       <c r="T7">
-        <v>-4.92</v>
+        <v>-3.25</v>
       </c>
       <c r="U7" t="s">
         <v>45</v>
@@ -1552,43 +1524,43 @@
         <v>1</v>
       </c>
       <c r="Y7">
-        <v>35.76</v>
+        <v>40.4</v>
       </c>
       <c r="Z7">
-        <v>-20.4</v>
+        <v>-20.58</v>
       </c>
       <c r="AA7">
-        <v>-20.99</v>
+        <v>-20.91</v>
       </c>
       <c r="AB7">
-        <v>0.59</v>
+        <v>0.33</v>
       </c>
       <c r="AC7">
-        <v>62.11</v>
+        <v>46.94</v>
       </c>
       <c r="AD7">
-        <v>72.83</v>
+        <v>62.77</v>
       </c>
       <c r="AE7">
-        <v>27.7</v>
+        <v>28.2</v>
       </c>
       <c r="AF7">
-        <v>135.86</v>
+        <v>27.05</v>
       </c>
       <c r="AG7">
-        <v>1021.37</v>
+        <v>1016.53</v>
       </c>
       <c r="AH7">
-        <v>922.4299999999999</v>
+        <v>920.6</v>
       </c>
       <c r="AI7">
-        <v>1020.6</v>
+        <v>1009.35</v>
       </c>
       <c r="AJ7" t="s">
         <v>47</v>
       </c>
       <c r="AK7">
-        <v>20.52</v>
+        <v>22.87</v>
       </c>
     </row>
     <row r="8" spans="1:37">
@@ -1599,10 +1571,10 @@
         <v>44</v>
       </c>
       <c r="C8">
-        <v>156.81</v>
+        <v>153.38</v>
       </c>
       <c r="D8">
-        <v>-4.66</v>
+        <v>-2.19</v>
       </c>
       <c r="E8">
         <v>185.92</v>
@@ -1611,25 +1583,25 @@
         <v>115.96</v>
       </c>
       <c r="G8">
-        <v>-15.66</v>
+        <v>-17.5</v>
       </c>
       <c r="H8">
-        <v>35.23</v>
+        <v>32.27</v>
       </c>
       <c r="I8">
-        <v>-11.17</v>
+        <v>-12.36</v>
       </c>
       <c r="J8">
-        <v>16.35</v>
+        <v>12.75</v>
       </c>
       <c r="K8">
-        <v>7.49</v>
+        <v>7.64</v>
       </c>
       <c r="L8">
-        <v>20.5</v>
+        <v>17.79</v>
       </c>
       <c r="M8">
-        <v>3.64</v>
+        <v>3.5</v>
       </c>
       <c r="N8">
         <v>99</v>
@@ -1638,19 +1610,19 @@
         <v>85</v>
       </c>
       <c r="P8">
-        <v>167.73</v>
+        <v>163.4</v>
       </c>
       <c r="Q8">
-        <v>170.49</v>
+        <v>171.09</v>
       </c>
       <c r="R8">
-        <v>150.07</v>
+        <v>150.32</v>
       </c>
       <c r="S8">
-        <v>137.61</v>
+        <v>137.69</v>
       </c>
       <c r="T8">
-        <v>13.96</v>
+        <v>11.39</v>
       </c>
       <c r="U8" t="s">
         <v>46</v>
@@ -1665,43 +1637,43 @@
         <v>3</v>
       </c>
       <c r="Y8">
-        <v>44.04</v>
+        <v>41.45</v>
       </c>
       <c r="Z8">
-        <v>5.27</v>
+        <v>3.63</v>
       </c>
       <c r="AA8">
-        <v>8.15</v>
+        <v>7.25</v>
       </c>
       <c r="AB8">
-        <v>-2.88</v>
+        <v>-3.62</v>
       </c>
       <c r="AC8">
-        <v>1.68</v>
+        <v>0</v>
       </c>
       <c r="AD8">
-        <v>1.68</v>
+        <v>1.12</v>
       </c>
       <c r="AE8">
-        <v>8.050000000000001</v>
+        <v>8.07</v>
       </c>
       <c r="AF8">
-        <v>-55.84</v>
+        <v>-61.31</v>
       </c>
       <c r="AG8">
-        <v>192.23</v>
+        <v>189.93</v>
       </c>
       <c r="AH8">
-        <v>148.75</v>
+        <v>152.25</v>
       </c>
       <c r="AI8">
-        <v>183.38</v>
+        <v>180.62</v>
       </c>
       <c r="AJ8" t="s">
         <v>47</v>
       </c>
       <c r="AK8">
-        <v>32.9</v>
+        <v>34.36</v>
       </c>
     </row>
   </sheetData>
@@ -1862,47 +1834,12 @@
     </row>
     <row r="2" spans="1:6">
       <c r="A2" s="3" t="s">
-        <v>0</v>
-      </c>
-      <c r="B2" s="3" t="s">
         <v>49</v>
-      </c>
-      <c r="C2" s="3" t="s">
-        <v>50</v>
-      </c>
-      <c r="D2" s="3" t="s">
-        <v>51</v>
-      </c>
-      <c r="E2" s="3" t="s">
-        <v>52</v>
-      </c>
-      <c r="F2" s="3" t="s">
-        <v>53</v>
-      </c>
-    </row>
-    <row r="3" spans="1:6">
-      <c r="A3" s="4" t="s">
-        <v>43</v>
-      </c>
-      <c r="B3" s="4" t="s">
-        <v>54</v>
-      </c>
-      <c r="C3" s="4" t="s">
-        <v>55</v>
-      </c>
-      <c r="D3" s="4" t="s">
-        <v>56</v>
-      </c>
-      <c r="E3" s="4" t="s">
-        <v>57</v>
-      </c>
-      <c r="F3" s="4" t="s">
-        <v>58</v>
       </c>
     </row>
     <row r="5" spans="1:6">
       <c r="A5" s="2" t="s">
-        <v>59</v>
+        <v>50</v>
       </c>
       <c r="B5" s="2"/>
       <c r="C5" s="2"/>
@@ -1910,972 +1847,972 @@
       <c r="E5" s="2"/>
     </row>
     <row r="6" spans="1:6">
-      <c r="A6" s="3" t="s">
+      <c r="A6" s="4" t="s">
         <v>0</v>
       </c>
-      <c r="B6" s="3" t="s">
-        <v>60</v>
-      </c>
-      <c r="C6" s="3" t="s">
-        <v>61</v>
-      </c>
-      <c r="D6" s="3" t="s">
-        <v>62</v>
-      </c>
-      <c r="E6" s="3" t="s">
-        <v>63</v>
+      <c r="B6" s="4" t="s">
+        <v>51</v>
+      </c>
+      <c r="C6" s="4" t="s">
+        <v>52</v>
+      </c>
+      <c r="D6" s="4" t="s">
+        <v>53</v>
+      </c>
+      <c r="E6" s="4" t="s">
+        <v>54</v>
       </c>
     </row>
     <row r="7" spans="1:6">
-      <c r="A7" s="5" t="s">
+      <c r="A7" s="3" t="s">
         <v>37</v>
       </c>
-      <c r="B7" s="5" t="s">
+      <c r="B7" s="3" t="s">
         <v>9</v>
       </c>
-      <c r="C7" s="6">
-        <v>-10.55</v>
-      </c>
-      <c r="D7" s="6">
+      <c r="C7" s="5">
         <v>-11.76</v>
       </c>
-      <c r="E7" s="7">
-        <v>-1.21</v>
+      <c r="D7" s="5">
+        <v>-11.39</v>
+      </c>
+      <c r="E7" s="6">
+        <v>0.37</v>
       </c>
     </row>
     <row r="8" spans="1:6">
-      <c r="A8" s="5" t="s">
+      <c r="A8" s="3" t="s">
         <v>38</v>
       </c>
-      <c r="B8" s="5" t="s">
+      <c r="B8" s="3" t="s">
         <v>9</v>
       </c>
-      <c r="C8" s="6">
-        <v>-11.03</v>
-      </c>
-      <c r="D8" s="6">
+      <c r="C8" s="5">
         <v>-16.94</v>
       </c>
+      <c r="D8" s="5">
+        <v>-19.29</v>
+      </c>
       <c r="E8" s="7">
-        <v>-5.91</v>
+        <v>-2.35</v>
       </c>
     </row>
     <row r="9" spans="1:6">
-      <c r="A9" s="5" t="s">
+      <c r="A9" s="3" t="s">
         <v>39</v>
       </c>
-      <c r="B9" s="5" t="s">
+      <c r="B9" s="3" t="s">
         <v>9</v>
       </c>
-      <c r="C9" s="6">
-        <v>-8.9</v>
-      </c>
-      <c r="D9" s="6">
+      <c r="C9" s="5">
         <v>-9.27</v>
       </c>
+      <c r="D9" s="5">
+        <v>-14.48</v>
+      </c>
       <c r="E9" s="7">
-        <v>-0.37</v>
+        <v>-5.21</v>
       </c>
     </row>
     <row r="10" spans="1:6">
-      <c r="A10" s="5" t="s">
+      <c r="A10" s="3" t="s">
         <v>40</v>
       </c>
-      <c r="B10" s="5" t="s">
+      <c r="B10" s="3" t="s">
         <v>9</v>
       </c>
-      <c r="C10" s="6">
-        <v>-8.56</v>
-      </c>
-      <c r="D10" s="6">
+      <c r="C10" s="5">
         <v>-8.77</v>
       </c>
+      <c r="D10" s="5">
+        <v>-9.289999999999999</v>
+      </c>
       <c r="E10" s="7">
-        <v>-0.21</v>
+        <v>-0.52</v>
       </c>
     </row>
     <row r="11" spans="1:6">
-      <c r="A11" s="5" t="s">
+      <c r="A11" s="3" t="s">
         <v>41</v>
       </c>
-      <c r="B11" s="5" t="s">
+      <c r="B11" s="3" t="s">
         <v>9</v>
       </c>
-      <c r="C11" s="6">
-        <v>2.32</v>
-      </c>
-      <c r="D11" s="6">
+      <c r="C11" s="5">
         <v>-2.72</v>
       </c>
-      <c r="E11" s="7">
-        <v>-5.04</v>
+      <c r="D11" s="5">
+        <v>-1.02</v>
+      </c>
+      <c r="E11" s="6">
+        <v>1.7</v>
       </c>
     </row>
     <row r="12" spans="1:6">
-      <c r="A12" s="5" t="s">
+      <c r="A12" s="3" t="s">
         <v>42</v>
       </c>
-      <c r="B12" s="5" t="s">
+      <c r="B12" s="3" t="s">
         <v>9</v>
       </c>
-      <c r="C12" s="6">
-        <v>-5.68</v>
-      </c>
-      <c r="D12" s="6">
+      <c r="C12" s="5">
         <v>-10.99</v>
       </c>
-      <c r="E12" s="7">
-        <v>-5.31</v>
+      <c r="D12" s="5">
+        <v>-7.75</v>
+      </c>
+      <c r="E12" s="6">
+        <v>3.24</v>
       </c>
     </row>
     <row r="13" spans="1:6">
-      <c r="A13" s="5" t="s">
+      <c r="A13" s="3" t="s">
         <v>43</v>
       </c>
-      <c r="B13" s="5" t="s">
+      <c r="B13" s="3" t="s">
         <v>9</v>
       </c>
-      <c r="C13" s="6">
-        <v>22.56</v>
-      </c>
-      <c r="D13" s="6">
+      <c r="C13" s="5">
         <v>16.35</v>
       </c>
+      <c r="D13" s="5">
+        <v>12.75</v>
+      </c>
       <c r="E13" s="7">
-        <v>-6.21</v>
+        <v>-3.6</v>
       </c>
     </row>
     <row r="14" spans="1:6">
-      <c r="A14" s="5" t="s">
+      <c r="A14" s="3" t="s">
         <v>37</v>
       </c>
-      <c r="B14" s="5" t="s">
+      <c r="B14" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="C14" s="6">
+      <c r="C14" s="5">
+        <v>-2.38</v>
+      </c>
+      <c r="D14" s="5">
+        <v>-0.93</v>
+      </c>
+      <c r="E14" s="6">
+        <v>1.45</v>
+      </c>
+    </row>
+    <row r="15" spans="1:6">
+      <c r="A15" s="3" t="s">
+        <v>38</v>
+      </c>
+      <c r="B15" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="C15" s="5">
+        <v>-16.3</v>
+      </c>
+      <c r="D15" s="5">
+        <v>-20.03</v>
+      </c>
+      <c r="E15" s="7">
+        <v>-3.73</v>
+      </c>
+    </row>
+    <row r="16" spans="1:6">
+      <c r="A16" s="3" t="s">
+        <v>39</v>
+      </c>
+      <c r="B16" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="C16" s="5">
+        <v>-3.28</v>
+      </c>
+      <c r="D16" s="5">
+        <v>-8.710000000000001</v>
+      </c>
+      <c r="E16" s="7">
+        <v>-5.43</v>
+      </c>
+    </row>
+    <row r="17" spans="1:5">
+      <c r="A17" s="3" t="s">
+        <v>40</v>
+      </c>
+      <c r="B17" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="C17" s="5">
+        <v>-3.74</v>
+      </c>
+      <c r="D17" s="5">
+        <v>-2.54</v>
+      </c>
+      <c r="E17" s="6">
+        <v>1.2</v>
+      </c>
+    </row>
+    <row r="18" spans="1:5">
+      <c r="A18" s="3" t="s">
+        <v>41</v>
+      </c>
+      <c r="B18" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="C18" s="5">
+        <v>1.55</v>
+      </c>
+      <c r="D18" s="5">
+        <v>4.82</v>
+      </c>
+      <c r="E18" s="6">
+        <v>3.27</v>
+      </c>
+    </row>
+    <row r="19" spans="1:5">
+      <c r="A19" s="3" t="s">
+        <v>42</v>
+      </c>
+      <c r="B19" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="C19" s="5">
+        <v>-5.77</v>
+      </c>
+      <c r="D19" s="5">
+        <v>-1.56</v>
+      </c>
+      <c r="E19" s="6">
+        <v>4.21</v>
+      </c>
+    </row>
+    <row r="20" spans="1:5">
+      <c r="A20" s="3" t="s">
+        <v>43</v>
+      </c>
+      <c r="B20" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="C20" s="5">
+        <v>-11.17</v>
+      </c>
+      <c r="D20" s="5">
+        <v>-12.36</v>
+      </c>
+      <c r="E20" s="7">
+        <v>-1.19</v>
+      </c>
+    </row>
+    <row r="21" spans="1:5">
+      <c r="A21" s="3" t="s">
+        <v>37</v>
+      </c>
+      <c r="B21" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="C21" s="5">
+        <v>13.51</v>
+      </c>
+      <c r="D21" s="5">
+        <v>12.53</v>
+      </c>
+      <c r="E21" s="7">
+        <v>-0.98</v>
+      </c>
+    </row>
+    <row r="22" spans="1:5">
+      <c r="A22" s="3" t="s">
+        <v>38</v>
+      </c>
+      <c r="B22" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="C22" s="5">
+        <v>60.84</v>
+      </c>
+      <c r="D22" s="5">
+        <v>56.89</v>
+      </c>
+      <c r="E22" s="7">
+        <v>-3.95</v>
+      </c>
+    </row>
+    <row r="23" spans="1:5">
+      <c r="A23" s="3" t="s">
+        <v>39</v>
+      </c>
+      <c r="B23" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="C23" s="5">
+        <v>-46.51</v>
+      </c>
+      <c r="D23" s="5">
+        <v>-48.67</v>
+      </c>
+      <c r="E23" s="7">
+        <v>-2.16</v>
+      </c>
+    </row>
+    <row r="24" spans="1:5">
+      <c r="A24" s="3" t="s">
+        <v>40</v>
+      </c>
+      <c r="B24" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="C24" s="5">
+        <v>-18.91</v>
+      </c>
+      <c r="D24" s="5">
+        <v>-19.72</v>
+      </c>
+      <c r="E24" s="7">
+        <v>-0.8100000000000001</v>
+      </c>
+    </row>
+    <row r="25" spans="1:5">
+      <c r="A25" s="3" t="s">
+        <v>41</v>
+      </c>
+      <c r="B25" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="C25" s="5">
+        <v>-10.17</v>
+      </c>
+      <c r="D25" s="5">
+        <v>-9.66</v>
+      </c>
+      <c r="E25" s="6">
+        <v>0.51</v>
+      </c>
+    </row>
+    <row r="26" spans="1:5">
+      <c r="A26" s="3" t="s">
+        <v>42</v>
+      </c>
+      <c r="B26" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="C26" s="5">
+        <v>-12.63</v>
+      </c>
+      <c r="D26" s="5">
+        <v>-11.6</v>
+      </c>
+      <c r="E26" s="6">
+        <v>1.03</v>
+      </c>
+    </row>
+    <row r="27" spans="1:5">
+      <c r="A27" s="3" t="s">
+        <v>43</v>
+      </c>
+      <c r="B27" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="C27" s="5">
+        <v>20.5</v>
+      </c>
+      <c r="D27" s="5">
+        <v>17.79</v>
+      </c>
+      <c r="E27" s="7">
+        <v>-2.71</v>
+      </c>
+    </row>
+    <row r="28" spans="1:5">
+      <c r="A28" s="3" t="s">
+        <v>37</v>
+      </c>
+      <c r="B28" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="C28" s="5">
+        <v>-3.19</v>
+      </c>
+      <c r="D28" s="5">
+        <v>-7.67</v>
+      </c>
+      <c r="E28" s="7">
+        <v>-4.48</v>
+      </c>
+    </row>
+    <row r="29" spans="1:5">
+      <c r="A29" s="3" t="s">
+        <v>38</v>
+      </c>
+      <c r="B29" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="C29" s="5">
+        <v>-19.01</v>
+      </c>
+      <c r="D29" s="5">
+        <v>-21.47</v>
+      </c>
+      <c r="E29" s="7">
+        <v>-2.46</v>
+      </c>
+    </row>
+    <row r="30" spans="1:5">
+      <c r="A30" s="3" t="s">
+        <v>39</v>
+      </c>
+      <c r="B30" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="C30" s="5">
+        <v>-12.02</v>
+      </c>
+      <c r="D30" s="5">
+        <v>-15.55</v>
+      </c>
+      <c r="E30" s="7">
+        <v>-3.53</v>
+      </c>
+    </row>
+    <row r="31" spans="1:5">
+      <c r="A31" s="3" t="s">
+        <v>40</v>
+      </c>
+      <c r="B31" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="C31" s="5">
+        <v>-11.08</v>
+      </c>
+      <c r="D31" s="5">
+        <v>-10.57</v>
+      </c>
+      <c r="E31" s="6">
+        <v>0.51</v>
+      </c>
+    </row>
+    <row r="32" spans="1:5">
+      <c r="A32" s="3" t="s">
+        <v>41</v>
+      </c>
+      <c r="B32" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="C32" s="5">
+        <v>5.06</v>
+      </c>
+      <c r="D32" s="5">
+        <v>8.33</v>
+      </c>
+      <c r="E32" s="6">
+        <v>3.27</v>
+      </c>
+    </row>
+    <row r="33" spans="1:5">
+      <c r="A33" s="3" t="s">
+        <v>42</v>
+      </c>
+      <c r="B33" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="C33" s="5">
+        <v>-13.39</v>
+      </c>
+      <c r="D33" s="5">
+        <v>-11.15</v>
+      </c>
+      <c r="E33" s="6">
+        <v>2.24</v>
+      </c>
+    </row>
+    <row r="34" spans="1:5">
+      <c r="A34" s="3" t="s">
+        <v>43</v>
+      </c>
+      <c r="B34" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="C34" s="5">
+        <v>7.49</v>
+      </c>
+      <c r="D34" s="5">
+        <v>7.64</v>
+      </c>
+      <c r="E34" s="6">
+        <v>0.15</v>
+      </c>
+    </row>
+    <row r="35" spans="1:5">
+      <c r="A35" s="3" t="s">
+        <v>37</v>
+      </c>
+      <c r="B35" s="3" t="s">
+        <v>6</v>
+      </c>
+      <c r="C35" s="5">
+        <v>-18.52</v>
+      </c>
+      <c r="D35" s="5">
+        <v>-17.85</v>
+      </c>
+      <c r="E35" s="6">
+        <v>0.67</v>
+      </c>
+    </row>
+    <row r="36" spans="1:5">
+      <c r="A36" s="3" t="s">
+        <v>38</v>
+      </c>
+      <c r="B36" s="3" t="s">
+        <v>6</v>
+      </c>
+      <c r="C36" s="5">
+        <v>-36.53</v>
+      </c>
+      <c r="D36" s="5">
+        <v>-37.95</v>
+      </c>
+      <c r="E36" s="7">
+        <v>-1.42</v>
+      </c>
+    </row>
+    <row r="37" spans="1:5">
+      <c r="A37" s="3" t="s">
+        <v>39</v>
+      </c>
+      <c r="B37" s="3" t="s">
+        <v>6</v>
+      </c>
+      <c r="C37" s="5">
+        <v>-46.03</v>
+      </c>
+      <c r="D37" s="5">
+        <v>-48.58</v>
+      </c>
+      <c r="E37" s="7">
+        <v>-2.55</v>
+      </c>
+    </row>
+    <row r="38" spans="1:5">
+      <c r="A38" s="3" t="s">
+        <v>40</v>
+      </c>
+      <c r="B38" s="3" t="s">
+        <v>6</v>
+      </c>
+      <c r="C38" s="5">
+        <v>-22.36</v>
+      </c>
+      <c r="D38" s="5">
+        <v>-22.91</v>
+      </c>
+      <c r="E38" s="7">
+        <v>-0.55</v>
+      </c>
+    </row>
+    <row r="39" spans="1:5">
+      <c r="A39" s="3" t="s">
+        <v>41</v>
+      </c>
+      <c r="B39" s="3" t="s">
+        <v>6</v>
+      </c>
+      <c r="C39" s="5">
+        <v>-16.5</v>
+      </c>
+      <c r="D39" s="5">
+        <v>-14.08</v>
+      </c>
+      <c r="E39" s="6">
+        <v>2.42</v>
+      </c>
+    </row>
+    <row r="40" spans="1:5">
+      <c r="A40" s="3" t="s">
+        <v>42</v>
+      </c>
+      <c r="B40" s="3" t="s">
+        <v>6</v>
+      </c>
+      <c r="C40" s="5">
+        <v>-20.09</v>
+      </c>
+      <c r="D40" s="5">
+        <v>-18.7</v>
+      </c>
+      <c r="E40" s="6">
+        <v>1.39</v>
+      </c>
+    </row>
+    <row r="41" spans="1:5">
+      <c r="A41" s="3" t="s">
+        <v>43</v>
+      </c>
+      <c r="B41" s="3" t="s">
+        <v>6</v>
+      </c>
+      <c r="C41" s="5">
+        <v>-15.66</v>
+      </c>
+      <c r="D41" s="5">
+        <v>-17.5</v>
+      </c>
+      <c r="E41" s="7">
+        <v>-1.84</v>
+      </c>
+    </row>
+    <row r="42" spans="1:5">
+      <c r="A42" s="3" t="s">
+        <v>37</v>
+      </c>
+      <c r="B42" s="3" t="s">
+        <v>2</v>
+      </c>
+      <c r="C42" s="5">
+        <v>10072</v>
+      </c>
+      <c r="D42" s="5">
+        <v>10155</v>
+      </c>
+      <c r="E42" s="6">
+        <v>83</v>
+      </c>
+    </row>
+    <row r="43" spans="1:5">
+      <c r="A43" s="3" t="s">
+        <v>38</v>
+      </c>
+      <c r="B43" s="3" t="s">
+        <v>2</v>
+      </c>
+      <c r="C43" s="5">
+        <v>425.4</v>
+      </c>
+      <c r="D43" s="5">
+        <v>415.9</v>
+      </c>
+      <c r="E43" s="7">
+        <v>-9.5</v>
+      </c>
+    </row>
+    <row r="44" spans="1:5">
+      <c r="A44" s="3" t="s">
+        <v>39</v>
+      </c>
+      <c r="B44" s="3" t="s">
+        <v>2</v>
+      </c>
+      <c r="C44" s="5">
+        <v>293.1</v>
+      </c>
+      <c r="D44" s="5">
+        <v>278.8</v>
+      </c>
+      <c r="E44" s="7">
+        <v>-14.3</v>
+      </c>
+    </row>
+    <row r="45" spans="1:5">
+      <c r="A45" s="3" t="s">
+        <v>40</v>
+      </c>
+      <c r="B45" s="3" t="s">
+        <v>2</v>
+      </c>
+      <c r="C45" s="5">
+        <v>1690</v>
+      </c>
+      <c r="D45" s="5">
+        <v>1678</v>
+      </c>
+      <c r="E45" s="7">
+        <v>-12</v>
+      </c>
+    </row>
+    <row r="46" spans="1:5">
+      <c r="A46" s="3" t="s">
+        <v>41</v>
+      </c>
+      <c r="B46" s="3" t="s">
+        <v>2</v>
+      </c>
+      <c r="C46" s="5">
+        <v>10975</v>
+      </c>
+      <c r="D46" s="5">
+        <v>11293</v>
+      </c>
+      <c r="E46" s="6">
+        <v>318</v>
+      </c>
+    </row>
+    <row r="47" spans="1:5">
+      <c r="A47" s="3" t="s">
+        <v>42</v>
+      </c>
+      <c r="B47" s="3" t="s">
+        <v>2</v>
+      </c>
+      <c r="C47" s="5">
+        <v>926</v>
+      </c>
+      <c r="D47" s="5">
+        <v>942.1</v>
+      </c>
+      <c r="E47" s="6">
+        <v>16.1</v>
+      </c>
+    </row>
+    <row r="48" spans="1:5">
+      <c r="A48" s="3" t="s">
+        <v>43</v>
+      </c>
+      <c r="B48" s="3" t="s">
+        <v>2</v>
+      </c>
+      <c r="C48" s="5">
+        <v>156.81</v>
+      </c>
+      <c r="D48" s="5">
+        <v>153.38</v>
+      </c>
+      <c r="E48" s="7">
+        <v>-3.43</v>
+      </c>
+    </row>
+    <row r="49" spans="1:5">
+      <c r="A49" s="3" t="s">
+        <v>37</v>
+      </c>
+      <c r="B49" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="C49" s="5">
+        <v>36.39</v>
+      </c>
+      <c r="D49" s="5">
+        <v>38.91</v>
+      </c>
+      <c r="E49" s="6">
         <v>2.52</v>
       </c>
-      <c r="D14" s="6">
-        <v>-2.38</v>
-      </c>
-      <c r="E14" s="7">
-        <v>-4.9</v>
-      </c>
-    </row>
-    <row r="15" spans="1:6">
-      <c r="A15" s="5" t="s">
+    </row>
+    <row r="50" spans="1:5">
+      <c r="A50" s="3" t="s">
         <v>38</v>
       </c>
-      <c r="B15" s="5" t="s">
-        <v>8</v>
-      </c>
-      <c r="C15" s="6">
-        <v>-9.210000000000001</v>
-      </c>
-      <c r="D15" s="6">
-        <v>-16.3</v>
-      </c>
-      <c r="E15" s="7">
-        <v>-7.09</v>
-      </c>
-    </row>
-    <row r="16" spans="1:6">
-      <c r="A16" s="5" t="s">
+      <c r="B50" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="C50" s="5">
+        <v>32.87</v>
+      </c>
+      <c r="D50" s="5">
+        <v>31.26</v>
+      </c>
+      <c r="E50" s="7">
+        <v>-1.61</v>
+      </c>
+    </row>
+    <row r="51" spans="1:5">
+      <c r="A51" s="3" t="s">
         <v>39</v>
       </c>
-      <c r="B16" s="5" t="s">
-        <v>8</v>
-      </c>
-      <c r="C16" s="6">
-        <v>-0.84</v>
-      </c>
-      <c r="D16" s="6">
-        <v>-3.28</v>
-      </c>
-      <c r="E16" s="7">
-        <v>-2.44</v>
-      </c>
-    </row>
-    <row r="17" spans="1:5">
-      <c r="A17" s="5" t="s">
+      <c r="B51" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="C51" s="5">
+        <v>33.87</v>
+      </c>
+      <c r="D51" s="5">
+        <v>26.64</v>
+      </c>
+      <c r="E51" s="7">
+        <v>-7.23</v>
+      </c>
+    </row>
+    <row r="52" spans="1:5">
+      <c r="A52" s="3" t="s">
         <v>40</v>
       </c>
-      <c r="B17" s="5" t="s">
-        <v>8</v>
-      </c>
-      <c r="C17" s="6">
-        <v>-1.16</v>
-      </c>
-      <c r="D17" s="6">
-        <v>-3.74</v>
-      </c>
-      <c r="E17" s="7">
-        <v>-2.58</v>
-      </c>
-    </row>
-    <row r="18" spans="1:5">
-      <c r="A18" s="5" t="s">
+      <c r="B52" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="C52" s="5">
+        <v>32.02</v>
+      </c>
+      <c r="D52" s="5">
+        <v>30.54</v>
+      </c>
+      <c r="E52" s="7">
+        <v>-1.48</v>
+      </c>
+    </row>
+    <row r="53" spans="1:5">
+      <c r="A53" s="3" t="s">
         <v>41</v>
       </c>
-      <c r="B18" s="5" t="s">
-        <v>8</v>
-      </c>
-      <c r="C18" s="6">
-        <v>4.79</v>
-      </c>
-      <c r="D18" s="6">
-        <v>1.55</v>
-      </c>
-      <c r="E18" s="7">
-        <v>-3.24</v>
-      </c>
-    </row>
-    <row r="19" spans="1:5">
-      <c r="A19" s="5" t="s">
+      <c r="B53" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="C53" s="5">
+        <v>50.19</v>
+      </c>
+      <c r="D53" s="5">
+        <v>57.24</v>
+      </c>
+      <c r="E53" s="6">
+        <v>7.05</v>
+      </c>
+    </row>
+    <row r="54" spans="1:5">
+      <c r="A54" s="3" t="s">
         <v>42</v>
       </c>
-      <c r="B19" s="5" t="s">
-        <v>8</v>
-      </c>
-      <c r="C19" s="6">
-        <v>0.01</v>
-      </c>
-      <c r="D19" s="6">
-        <v>-5.77</v>
-      </c>
-      <c r="E19" s="7">
-        <v>-5.78</v>
-      </c>
-    </row>
-    <row r="20" spans="1:5">
-      <c r="A20" s="5" t="s">
+      <c r="B54" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="C54" s="5">
+        <v>35.76</v>
+      </c>
+      <c r="D54" s="5">
+        <v>40.4</v>
+      </c>
+      <c r="E54" s="6">
+        <v>4.64</v>
+      </c>
+    </row>
+    <row r="55" spans="1:5">
+      <c r="A55" s="3" t="s">
         <v>43</v>
       </c>
-      <c r="B20" s="5" t="s">
-        <v>8</v>
-      </c>
-      <c r="C20" s="6">
-        <v>-7.38</v>
-      </c>
-      <c r="D20" s="6">
-        <v>-11.17</v>
-      </c>
-      <c r="E20" s="7">
-        <v>-3.79</v>
-      </c>
-    </row>
-    <row r="21" spans="1:5">
-      <c r="A21" s="5" t="s">
+      <c r="B55" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="C55" s="5">
+        <v>44.04</v>
+      </c>
+      <c r="D55" s="5">
+        <v>41.45</v>
+      </c>
+      <c r="E55" s="7">
+        <v>-2.59</v>
+      </c>
+    </row>
+    <row r="56" spans="1:5">
+      <c r="A56" s="3" t="s">
         <v>37</v>
       </c>
-      <c r="B21" s="5" t="s">
-        <v>11</v>
-      </c>
-      <c r="C21" s="6">
-        <v>14.6</v>
-      </c>
-      <c r="D21" s="6">
-        <v>13.51</v>
-      </c>
-      <c r="E21" s="7">
-        <v>-1.09</v>
-      </c>
-    </row>
-    <row r="22" spans="1:5">
-      <c r="A22" s="5" t="s">
+      <c r="B56" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="C56" s="5">
+        <v>-49.7</v>
+      </c>
+      <c r="D56" s="5">
+        <v>-21.71</v>
+      </c>
+      <c r="E56" s="6">
+        <v>27.99</v>
+      </c>
+    </row>
+    <row r="57" spans="1:5">
+      <c r="A57" s="3" t="s">
         <v>38</v>
       </c>
-      <c r="B22" s="5" t="s">
-        <v>11</v>
-      </c>
-      <c r="C22" s="6">
-        <v>72.45</v>
-      </c>
-      <c r="D22" s="6">
-        <v>60.84</v>
-      </c>
-      <c r="E22" s="7">
-        <v>-11.61</v>
-      </c>
-    </row>
-    <row r="23" spans="1:5">
-      <c r="A23" s="5" t="s">
+      <c r="B57" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="C57" s="5">
+        <v>-35.33</v>
+      </c>
+      <c r="D57" s="5">
+        <v>-22.93</v>
+      </c>
+      <c r="E57" s="6">
+        <v>12.4</v>
+      </c>
+    </row>
+    <row r="58" spans="1:5">
+      <c r="A58" s="3" t="s">
         <v>39</v>
       </c>
-      <c r="B23" s="5" t="s">
-        <v>11</v>
-      </c>
-      <c r="C23" s="6">
-        <v>-45.92</v>
-      </c>
-      <c r="D23" s="6">
-        <v>-46.51</v>
-      </c>
-      <c r="E23" s="7">
-        <v>-0.59</v>
-      </c>
-    </row>
-    <row r="24" spans="1:5">
-      <c r="A24" s="5" t="s">
+      <c r="B58" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="C58" s="5">
+        <v>-72.79000000000001</v>
+      </c>
+      <c r="D58" s="5">
+        <v>-38.35</v>
+      </c>
+      <c r="E58" s="6">
+        <v>34.44</v>
+      </c>
+    </row>
+    <row r="59" spans="1:5">
+      <c r="A59" s="3" t="s">
         <v>40</v>
       </c>
-      <c r="B24" s="5" t="s">
-        <v>11</v>
-      </c>
-      <c r="C24" s="6">
-        <v>-15.82</v>
-      </c>
-      <c r="D24" s="6">
-        <v>-18.91</v>
-      </c>
-      <c r="E24" s="7">
-        <v>-3.09</v>
-      </c>
-    </row>
-    <row r="25" spans="1:5">
-      <c r="A25" s="5" t="s">
+      <c r="B59" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="C59" s="5">
+        <v>35.35</v>
+      </c>
+      <c r="D59" s="5">
+        <v>24.43</v>
+      </c>
+      <c r="E59" s="7">
+        <v>-10.92</v>
+      </c>
+    </row>
+    <row r="60" spans="1:5">
+      <c r="A60" s="3" t="s">
         <v>41</v>
       </c>
-      <c r="B25" s="5" t="s">
-        <v>11</v>
-      </c>
-      <c r="C25" s="6">
-        <v>-7.75</v>
-      </c>
-      <c r="D25" s="6">
-        <v>-10.17</v>
-      </c>
-      <c r="E25" s="7">
-        <v>-2.42</v>
-      </c>
-    </row>
-    <row r="26" spans="1:5">
-      <c r="A26" s="5" t="s">
+      <c r="B60" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="C60" s="5">
+        <v>-10.37</v>
+      </c>
+      <c r="D60" s="5">
+        <v>224.33</v>
+      </c>
+      <c r="E60" s="6">
+        <v>234.7</v>
+      </c>
+    </row>
+    <row r="61" spans="1:5">
+      <c r="A61" s="3" t="s">
         <v>42</v>
       </c>
-      <c r="B26" s="5" t="s">
-        <v>11</v>
-      </c>
-      <c r="C26" s="6">
-        <v>-6.06</v>
-      </c>
-      <c r="D26" s="6">
-        <v>-12.63</v>
-      </c>
-      <c r="E26" s="7">
-        <v>-6.57</v>
-      </c>
-    </row>
-    <row r="27" spans="1:5">
-      <c r="A27" s="5" t="s">
+      <c r="B61" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="C61" s="5">
+        <v>135.86</v>
+      </c>
+      <c r="D61" s="5">
+        <v>27.05</v>
+      </c>
+      <c r="E61" s="7">
+        <v>-108.81</v>
+      </c>
+    </row>
+    <row r="62" spans="1:5">
+      <c r="A62" s="3" t="s">
         <v>43</v>
       </c>
-      <c r="B27" s="5" t="s">
-        <v>11</v>
-      </c>
-      <c r="C27" s="6">
-        <v>29.03</v>
-      </c>
-      <c r="D27" s="6">
-        <v>20.5</v>
-      </c>
-      <c r="E27" s="7">
-        <v>-8.529999999999999</v>
-      </c>
-    </row>
-    <row r="28" spans="1:5">
-      <c r="A28" s="5" t="s">
-        <v>37</v>
-      </c>
-      <c r="B28" s="5" t="s">
-        <v>10</v>
-      </c>
-      <c r="C28" s="6">
-        <v>-2.24</v>
-      </c>
-      <c r="D28" s="6">
-        <v>-3.19</v>
-      </c>
-      <c r="E28" s="7">
-        <v>-0.95</v>
-      </c>
-    </row>
-    <row r="29" spans="1:5">
-      <c r="A29" s="5" t="s">
-        <v>38</v>
-      </c>
-      <c r="B29" s="5" t="s">
-        <v>10</v>
-      </c>
-      <c r="C29" s="6">
-        <v>-17.05</v>
-      </c>
-      <c r="D29" s="6">
-        <v>-19.01</v>
-      </c>
-      <c r="E29" s="7">
-        <v>-1.96</v>
-      </c>
-    </row>
-    <row r="30" spans="1:5">
-      <c r="A30" s="5" t="s">
-        <v>39</v>
-      </c>
-      <c r="B30" s="5" t="s">
-        <v>10</v>
-      </c>
-      <c r="C30" s="6">
-        <v>-11.34</v>
-      </c>
-      <c r="D30" s="6">
-        <v>-12.02</v>
-      </c>
-      <c r="E30" s="7">
-        <v>-0.68</v>
-      </c>
-    </row>
-    <row r="31" spans="1:5">
-      <c r="A31" s="5" t="s">
-        <v>40</v>
-      </c>
-      <c r="B31" s="5" t="s">
-        <v>10</v>
-      </c>
-      <c r="C31" s="6">
-        <v>-8.68</v>
-      </c>
-      <c r="D31" s="6">
-        <v>-11.08</v>
-      </c>
-      <c r="E31" s="7">
-        <v>-2.4</v>
-      </c>
-    </row>
-    <row r="32" spans="1:5">
-      <c r="A32" s="5" t="s">
-        <v>41</v>
-      </c>
-      <c r="B32" s="5" t="s">
-        <v>10</v>
-      </c>
-      <c r="C32" s="6">
-        <v>9.380000000000001</v>
-      </c>
-      <c r="D32" s="6">
-        <v>5.06</v>
-      </c>
-      <c r="E32" s="7">
-        <v>-4.32</v>
-      </c>
-    </row>
-    <row r="33" spans="1:5">
-      <c r="A33" s="5" t="s">
-        <v>42</v>
-      </c>
-      <c r="B33" s="5" t="s">
-        <v>10</v>
-      </c>
-      <c r="C33" s="6">
-        <v>-10.02</v>
-      </c>
-      <c r="D33" s="6">
-        <v>-13.39</v>
-      </c>
-      <c r="E33" s="7">
-        <v>-3.37</v>
-      </c>
-    </row>
-    <row r="34" spans="1:5">
-      <c r="A34" s="5" t="s">
-        <v>43</v>
-      </c>
-      <c r="B34" s="5" t="s">
-        <v>10</v>
-      </c>
-      <c r="C34" s="6">
-        <v>14.33</v>
-      </c>
-      <c r="D34" s="6">
-        <v>7.49</v>
-      </c>
-      <c r="E34" s="7">
-        <v>-6.84</v>
-      </c>
-    </row>
-    <row r="35" spans="1:5">
-      <c r="A35" s="5" t="s">
-        <v>37</v>
-      </c>
-      <c r="B35" s="5" t="s">
-        <v>6</v>
-      </c>
-      <c r="C35" s="6">
-        <v>-16.78</v>
-      </c>
-      <c r="D35" s="6">
-        <v>-18.52</v>
-      </c>
-      <c r="E35" s="7">
-        <v>-1.74</v>
-      </c>
-    </row>
-    <row r="36" spans="1:5">
-      <c r="A36" s="5" t="s">
-        <v>38</v>
-      </c>
-      <c r="B36" s="5" t="s">
-        <v>6</v>
-      </c>
-      <c r="C36" s="6">
-        <v>-33.3</v>
-      </c>
-      <c r="D36" s="6">
-        <v>-36.53</v>
-      </c>
-      <c r="E36" s="7">
-        <v>-3.23</v>
-      </c>
-    </row>
-    <row r="37" spans="1:5">
-      <c r="A37" s="5" t="s">
-        <v>39</v>
-      </c>
-      <c r="B37" s="5" t="s">
-        <v>6</v>
-      </c>
-      <c r="C37" s="6">
-        <v>-45.92</v>
-      </c>
-      <c r="D37" s="6">
-        <v>-46.03</v>
-      </c>
-      <c r="E37" s="7">
-        <v>-0.11</v>
-      </c>
-    </row>
-    <row r="38" spans="1:5">
-      <c r="A38" s="5" t="s">
-        <v>40</v>
-      </c>
-      <c r="B38" s="5" t="s">
-        <v>6</v>
-      </c>
-      <c r="C38" s="6">
-        <v>-21.9</v>
-      </c>
-      <c r="D38" s="6">
-        <v>-22.36</v>
-      </c>
-      <c r="E38" s="7">
-        <v>-0.46</v>
-      </c>
-    </row>
-    <row r="39" spans="1:5">
-      <c r="A39" s="5" t="s">
-        <v>41</v>
-      </c>
-      <c r="B39" s="5" t="s">
-        <v>6</v>
-      </c>
-      <c r="C39" s="6">
-        <v>-14.3</v>
-      </c>
-      <c r="D39" s="6">
-        <v>-16.5</v>
-      </c>
-      <c r="E39" s="7">
-        <v>-2.2</v>
-      </c>
-    </row>
-    <row r="40" spans="1:5">
-      <c r="A40" s="5" t="s">
-        <v>42</v>
-      </c>
-      <c r="B40" s="5" t="s">
-        <v>6</v>
-      </c>
-      <c r="C40" s="6">
-        <v>-17.38</v>
-      </c>
-      <c r="D40" s="6">
-        <v>-20.09</v>
-      </c>
-      <c r="E40" s="7">
-        <v>-2.71</v>
-      </c>
-    </row>
-    <row r="41" spans="1:5">
-      <c r="A41" s="5" t="s">
-        <v>43</v>
-      </c>
-      <c r="B41" s="5" t="s">
-        <v>6</v>
-      </c>
-      <c r="C41" s="6">
-        <v>-11.53</v>
-      </c>
-      <c r="D41" s="6">
-        <v>-15.66</v>
-      </c>
-      <c r="E41" s="7">
-        <v>-4.13</v>
-      </c>
-    </row>
-    <row r="42" spans="1:5">
-      <c r="A42" s="5" t="s">
-        <v>37</v>
-      </c>
-      <c r="B42" s="5" t="s">
-        <v>2</v>
-      </c>
-      <c r="C42" s="6">
-        <v>10287</v>
-      </c>
-      <c r="D42" s="6">
-        <v>10072</v>
-      </c>
-      <c r="E42" s="7">
-        <v>-215</v>
-      </c>
-    </row>
-    <row r="43" spans="1:5">
-      <c r="A43" s="5" t="s">
-        <v>38</v>
-      </c>
-      <c r="B43" s="5" t="s">
-        <v>2</v>
-      </c>
-      <c r="C43" s="6">
-        <v>447.05</v>
-      </c>
-      <c r="D43" s="6">
-        <v>425.4</v>
-      </c>
-      <c r="E43" s="7">
-        <v>-21.65</v>
-      </c>
-    </row>
-    <row r="44" spans="1:5">
-      <c r="A44" s="5" t="s">
-        <v>39</v>
-      </c>
-      <c r="B44" s="5" t="s">
-        <v>2</v>
-      </c>
-      <c r="C44" s="6">
-        <v>296.35</v>
-      </c>
-      <c r="D44" s="6">
-        <v>293.1</v>
-      </c>
-      <c r="E44" s="7">
-        <v>-3.25</v>
-      </c>
-    </row>
-    <row r="45" spans="1:5">
-      <c r="A45" s="5" t="s">
-        <v>40</v>
-      </c>
-      <c r="B45" s="5" t="s">
-        <v>2</v>
-      </c>
-      <c r="C45" s="6">
-        <v>1700</v>
-      </c>
-      <c r="D45" s="6">
-        <v>1690</v>
-      </c>
-      <c r="E45" s="7">
-        <v>-10</v>
-      </c>
-    </row>
-    <row r="46" spans="1:5">
-      <c r="A46" s="5" t="s">
-        <v>41</v>
-      </c>
-      <c r="B46" s="5" t="s">
-        <v>2</v>
-      </c>
-      <c r="C46" s="6">
-        <v>11265</v>
-      </c>
-      <c r="D46" s="6">
-        <v>10975</v>
-      </c>
-      <c r="E46" s="7">
-        <v>-290</v>
-      </c>
-    </row>
-    <row r="47" spans="1:5">
-      <c r="A47" s="5" t="s">
-        <v>42</v>
-      </c>
-      <c r="B47" s="5" t="s">
-        <v>2</v>
-      </c>
-      <c r="C47" s="6">
-        <v>957.35</v>
-      </c>
-      <c r="D47" s="6">
-        <v>926</v>
-      </c>
-      <c r="E47" s="7">
-        <v>-31.35</v>
-      </c>
-    </row>
-    <row r="48" spans="1:5">
-      <c r="A48" s="5" t="s">
-        <v>43</v>
-      </c>
-      <c r="B48" s="5" t="s">
-        <v>2</v>
-      </c>
-      <c r="C48" s="6">
-        <v>164.48</v>
-      </c>
-      <c r="D48" s="6">
-        <v>156.81</v>
-      </c>
-      <c r="E48" s="7">
-        <v>-7.67</v>
-      </c>
-    </row>
-    <row r="49" spans="1:5">
-      <c r="A49" s="5" t="s">
-        <v>37</v>
-      </c>
-      <c r="B49" s="5" t="s">
-        <v>24</v>
-      </c>
-      <c r="C49" s="6">
-        <v>40.4</v>
-      </c>
-      <c r="D49" s="6">
-        <v>36.39</v>
-      </c>
-      <c r="E49" s="7">
-        <v>-4.01</v>
-      </c>
-    </row>
-    <row r="50" spans="1:5">
-      <c r="A50" s="5" t="s">
-        <v>38</v>
-      </c>
-      <c r="B50" s="5" t="s">
-        <v>24</v>
-      </c>
-      <c r="C50" s="6">
-        <v>36.9</v>
-      </c>
-      <c r="D50" s="6">
-        <v>32.87</v>
-      </c>
-      <c r="E50" s="7">
-        <v>-4.03</v>
-      </c>
-    </row>
-    <row r="51" spans="1:5">
-      <c r="A51" s="5" t="s">
-        <v>39</v>
-      </c>
-      <c r="B51" s="5" t="s">
-        <v>24</v>
-      </c>
-      <c r="C51" s="6">
-        <v>35.93</v>
-      </c>
-      <c r="D51" s="6">
-        <v>33.87</v>
-      </c>
-      <c r="E51" s="7">
-        <v>-2.06</v>
-      </c>
-    </row>
-    <row r="52" spans="1:5">
-      <c r="A52" s="5" t="s">
-        <v>40</v>
-      </c>
-      <c r="B52" s="5" t="s">
-        <v>24</v>
-      </c>
-      <c r="C52" s="6">
-        <v>33.26</v>
-      </c>
-      <c r="D52" s="6">
-        <v>32.02</v>
-      </c>
-      <c r="E52" s="7">
-        <v>-1.24</v>
-      </c>
-    </row>
-    <row r="53" spans="1:5">
-      <c r="A53" s="5" t="s">
-        <v>41</v>
-      </c>
-      <c r="B53" s="5" t="s">
-        <v>24</v>
-      </c>
-      <c r="C53" s="6">
-        <v>58.34</v>
-      </c>
-      <c r="D53" s="6">
-        <v>50.19</v>
-      </c>
-      <c r="E53" s="7">
-        <v>-8.15</v>
-      </c>
-    </row>
-    <row r="54" spans="1:5">
-      <c r="A54" s="5" t="s">
-        <v>42</v>
-      </c>
-      <c r="B54" s="5" t="s">
-        <v>24</v>
-      </c>
-      <c r="C54" s="6">
-        <v>41.61</v>
-      </c>
-      <c r="D54" s="6">
-        <v>35.76</v>
-      </c>
-      <c r="E54" s="7">
-        <v>-5.85</v>
-      </c>
-    </row>
-    <row r="55" spans="1:5">
-      <c r="A55" s="5" t="s">
-        <v>43</v>
-      </c>
-      <c r="B55" s="5" t="s">
-        <v>24</v>
-      </c>
-      <c r="C55" s="6">
-        <v>50.61</v>
-      </c>
-      <c r="D55" s="6">
-        <v>44.04</v>
-      </c>
-      <c r="E55" s="7">
-        <v>-6.57</v>
-      </c>
-    </row>
-    <row r="56" spans="1:5">
-      <c r="A56" s="5" t="s">
-        <v>37</v>
-      </c>
-      <c r="B56" s="5" t="s">
+      <c r="B62" s="3" t="s">
         <v>31</v>
       </c>
-      <c r="C56" s="6">
-        <v>-63.23</v>
-      </c>
-      <c r="D56" s="6">
-        <v>-49.7</v>
-      </c>
-      <c r="E56" s="8">
-        <v>13.53</v>
-      </c>
-    </row>
-    <row r="57" spans="1:5">
-      <c r="A57" s="5" t="s">
-        <v>38</v>
-      </c>
-      <c r="B57" s="5" t="s">
-        <v>31</v>
-      </c>
-      <c r="C57" s="6">
-        <v>28.57</v>
-      </c>
-      <c r="D57" s="6">
-        <v>-35.33</v>
-      </c>
-      <c r="E57" s="7">
-        <v>-63.9</v>
-      </c>
-    </row>
-    <row r="58" spans="1:5">
-      <c r="A58" s="5" t="s">
-        <v>39</v>
-      </c>
-      <c r="B58" s="5" t="s">
-        <v>31</v>
-      </c>
-      <c r="C58" s="6">
-        <v>-75</v>
-      </c>
-      <c r="D58" s="6">
-        <v>-72.79000000000001</v>
-      </c>
-      <c r="E58" s="8">
-        <v>2.21</v>
-      </c>
-    </row>
-    <row r="59" spans="1:5">
-      <c r="A59" s="5" t="s">
-        <v>40</v>
-      </c>
-      <c r="B59" s="5" t="s">
-        <v>31</v>
-      </c>
-      <c r="C59" s="6">
-        <v>1.4</v>
-      </c>
-      <c r="D59" s="6">
-        <v>35.35</v>
-      </c>
-      <c r="E59" s="8">
-        <v>33.95</v>
-      </c>
-    </row>
-    <row r="60" spans="1:5">
-      <c r="A60" s="5" t="s">
-        <v>41</v>
-      </c>
-      <c r="B60" s="5" t="s">
-        <v>31</v>
-      </c>
-      <c r="C60" s="6">
-        <v>-37.8</v>
-      </c>
-      <c r="D60" s="6">
-        <v>-10.37</v>
-      </c>
-      <c r="E60" s="8">
-        <v>27.43</v>
-      </c>
-    </row>
-    <row r="61" spans="1:5">
-      <c r="A61" s="5" t="s">
-        <v>42</v>
-      </c>
-      <c r="B61" s="5" t="s">
-        <v>31</v>
-      </c>
-      <c r="C61" s="6">
-        <v>7.89</v>
-      </c>
-      <c r="D61" s="6">
-        <v>135.86</v>
-      </c>
-      <c r="E61" s="8">
-        <v>127.97</v>
-      </c>
-    </row>
-    <row r="62" spans="1:5">
-      <c r="A62" s="5" t="s">
-        <v>43</v>
-      </c>
-      <c r="B62" s="5" t="s">
-        <v>31</v>
-      </c>
-      <c r="C62" s="6">
-        <v>-71.05</v>
-      </c>
-      <c r="D62" s="6">
+      <c r="C62" s="5">
         <v>-55.84</v>
       </c>
-      <c r="E62" s="8">
-        <v>15.21</v>
+      <c r="D62" s="5">
+        <v>-61.31</v>
+      </c>
+      <c r="E62" s="7">
+        <v>-5.47</v>
       </c>
     </row>
   </sheetData>
@@ -2901,60 +2838,60 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:9" ht="28" customHeight="1">
-      <c r="A1" s="9" t="s">
+      <c r="A1" s="8" t="s">
         <v>1</v>
       </c>
-      <c r="B1" s="9" t="s">
-        <v>64</v>
-      </c>
-      <c r="C1" s="9" t="s">
-        <v>65</v>
-      </c>
-      <c r="D1" s="9" t="s">
-        <v>66</v>
-      </c>
-      <c r="E1" s="9" t="s">
-        <v>67</v>
-      </c>
-      <c r="F1" s="9" t="s">
-        <v>68</v>
-      </c>
-      <c r="G1" s="9" t="s">
-        <v>69</v>
-      </c>
-      <c r="H1" s="9" t="s">
-        <v>70</v>
-      </c>
-      <c r="I1" s="9" t="s">
-        <v>71</v>
+      <c r="B1" s="8" t="s">
+        <v>55</v>
+      </c>
+      <c r="C1" s="8" t="s">
+        <v>56</v>
+      </c>
+      <c r="D1" s="8" t="s">
+        <v>57</v>
+      </c>
+      <c r="E1" s="8" t="s">
+        <v>58</v>
+      </c>
+      <c r="F1" s="8" t="s">
+        <v>59</v>
+      </c>
+      <c r="G1" s="8" t="s">
+        <v>60</v>
+      </c>
+      <c r="H1" s="8" t="s">
+        <v>61</v>
+      </c>
+      <c r="I1" s="8" t="s">
+        <v>62</v>
       </c>
     </row>
     <row r="2" spans="1:9">
-      <c r="A2" s="10" t="s">
+      <c r="A2" s="9" t="s">
         <v>44</v>
       </c>
-      <c r="B2" s="11">
+      <c r="B2" s="10">
         <v>44.24</v>
       </c>
-      <c r="C2" s="12">
+      <c r="C2" s="11">
         <v>7</v>
       </c>
-      <c r="D2" s="11">
-        <v>37.9</v>
-      </c>
-      <c r="E2" s="11">
+      <c r="D2" s="10">
+        <v>38.1</v>
+      </c>
+      <c r="E2" s="10">
         <v>28.6</v>
       </c>
-      <c r="F2" s="11">
-        <v>-6.3</v>
-      </c>
-      <c r="G2" s="11">
-        <v>-6.6</v>
-      </c>
-      <c r="H2" s="11">
+      <c r="F2" s="10">
+        <v>-7.2</v>
+      </c>
+      <c r="G2" s="10">
+        <v>-7.2</v>
+      </c>
+      <c r="H2" s="10">
         <v>57</v>
       </c>
-      <c r="I2" s="11">
+      <c r="I2" s="10">
         <v>14.3</v>
       </c>
     </row>
@@ -3056,49 +2993,49 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:7">
-      <c r="A1" s="13" t="s">
+      <c r="A1" s="12" t="s">
         <v>37</v>
       </c>
-      <c r="B1" s="13" t="s">
+      <c r="B1" s="12" t="s">
         <v>41</v>
       </c>
-      <c r="C1" s="13" t="s">
+      <c r="C1" s="12" t="s">
         <v>38</v>
       </c>
-      <c r="D1" s="13" t="s">
+      <c r="D1" s="12" t="s">
         <v>42</v>
       </c>
-      <c r="E1" s="13" t="s">
+      <c r="E1" s="12" t="s">
         <v>43</v>
       </c>
-      <c r="F1" s="13" t="s">
+      <c r="F1" s="12" t="s">
         <v>40</v>
       </c>
-      <c r="G1" s="13" t="s">
+      <c r="G1" s="12" t="s">
         <v>39</v>
       </c>
     </row>
     <row r="2" spans="1:7">
-      <c r="A2" s="14">
-        <v>0.2431</v>
-      </c>
-      <c r="B2" s="14">
-        <v>0.1961</v>
-      </c>
-      <c r="C2" s="14">
-        <v>0.1417</v>
-      </c>
-      <c r="D2" s="14">
-        <v>0.0405</v>
-      </c>
-      <c r="E2" s="14">
-        <v>0.0364</v>
-      </c>
-      <c r="F2" s="14">
-        <v>-0.0184</v>
-      </c>
-      <c r="G2" s="14">
-        <v>-0.2298</v>
+      <c r="A2" s="13">
+        <v>0.2411</v>
+      </c>
+      <c r="B2" s="13">
+        <v>0.2022</v>
+      </c>
+      <c r="C2" s="13">
+        <v>0.1399</v>
+      </c>
+      <c r="D2" s="13">
+        <v>0.0449</v>
+      </c>
+      <c r="E2" s="13">
+        <v>0.035</v>
+      </c>
+      <c r="F2" s="13">
+        <v>-0.0206</v>
+      </c>
+      <c r="G2" s="13">
+        <v>-0.2367</v>
       </c>
     </row>
   </sheetData>

--- a/BAJAJ_GROUP_Technical_Metrics.xlsx
+++ b/BAJAJ_GROUP_Technical_Metrics.xlsx
@@ -893,10 +893,10 @@
         <v>44</v>
       </c>
       <c r="C2">
-        <v>10155</v>
+        <v>10072</v>
       </c>
       <c r="D2">
-        <v>0.82</v>
+        <v>-0.82</v>
       </c>
       <c r="E2">
         <v>12361</v>
@@ -905,46 +905,46 @@
         <v>8599.48</v>
       </c>
       <c r="G2">
-        <v>-17.85</v>
+        <v>-18.52</v>
       </c>
       <c r="H2">
-        <v>18.09</v>
+        <v>17.12</v>
       </c>
       <c r="I2">
-        <v>-0.93</v>
+        <v>-3.01</v>
       </c>
       <c r="J2">
-        <v>-11.39</v>
+        <v>-11.36</v>
       </c>
       <c r="K2">
-        <v>-7.67</v>
+        <v>-10.74</v>
       </c>
       <c r="L2">
-        <v>12.53</v>
+        <v>11.62</v>
       </c>
       <c r="M2">
-        <v>24.11</v>
+        <v>24.6</v>
       </c>
       <c r="N2">
         <v>71</v>
       </c>
       <c r="O2">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="P2">
-        <v>10260.8</v>
+        <v>10198.2</v>
       </c>
       <c r="Q2">
-        <v>10394.45</v>
+        <v>10328.05</v>
       </c>
       <c r="R2">
-        <v>11206.46</v>
+        <v>11173.56</v>
       </c>
       <c r="S2">
-        <v>10212.22</v>
+        <v>10215.72</v>
       </c>
       <c r="T2">
-        <v>-0.5600000000000001</v>
+        <v>-1.41</v>
       </c>
       <c r="U2" t="s">
         <v>45</v>
@@ -959,34 +959,34 @@
         <v>1</v>
       </c>
       <c r="Y2">
-        <v>38.91</v>
+        <v>37.32</v>
       </c>
       <c r="Z2">
-        <v>-301.82</v>
+        <v>-294.95</v>
       </c>
       <c r="AA2">
-        <v>-340.88</v>
+        <v>-331.69</v>
       </c>
       <c r="AB2">
-        <v>39.06</v>
+        <v>36.74</v>
       </c>
       <c r="AC2">
-        <v>82.97</v>
+        <v>78.84999999999999</v>
       </c>
       <c r="AD2">
-        <v>89.31</v>
+        <v>83.34</v>
       </c>
       <c r="AE2">
-        <v>271.13</v>
+        <v>266.34</v>
       </c>
       <c r="AF2">
-        <v>-21.71</v>
+        <v>-16.35</v>
       </c>
       <c r="AG2">
-        <v>11441.21</v>
+        <v>11269.41</v>
       </c>
       <c r="AH2">
-        <v>9347.690000000001</v>
+        <v>9386.690000000001</v>
       </c>
       <c r="AI2">
         <v>10503.51</v>
@@ -995,7 +995,7 @@
         <v>47</v>
       </c>
       <c r="AK2">
-        <v>41.33</v>
+        <v>41.18</v>
       </c>
     </row>
     <row r="3" spans="1:37">
@@ -1006,10 +1006,10 @@
         <v>44</v>
       </c>
       <c r="C3">
-        <v>415.9</v>
+        <v>396.95</v>
       </c>
       <c r="D3">
-        <v>-2.23</v>
+        <v>-4.56</v>
       </c>
       <c r="E3">
         <v>670.25</v>
@@ -1018,46 +1018,46 @@
         <v>247.45</v>
       </c>
       <c r="G3">
-        <v>-37.95</v>
+        <v>-40.78</v>
       </c>
       <c r="H3">
-        <v>68.06999999999999</v>
+        <v>60.42</v>
       </c>
       <c r="I3">
-        <v>-20.03</v>
+        <v>-15.27</v>
       </c>
       <c r="J3">
-        <v>-19.29</v>
+        <v>-22.73</v>
       </c>
       <c r="K3">
-        <v>-21.47</v>
+        <v>-28.59</v>
       </c>
       <c r="L3">
-        <v>56.89</v>
+        <v>47.42</v>
       </c>
       <c r="M3">
-        <v>13.99</v>
+        <v>13.55</v>
       </c>
       <c r="N3">
         <v>85</v>
       </c>
       <c r="O3">
-        <v>83</v>
+        <v>79</v>
       </c>
       <c r="P3">
-        <v>445.77</v>
+        <v>431.46</v>
       </c>
       <c r="Q3">
-        <v>483.76</v>
+        <v>478.31</v>
       </c>
       <c r="R3">
-        <v>492.66</v>
+        <v>489.78</v>
       </c>
       <c r="S3">
-        <v>466.34</v>
+        <v>466.98</v>
       </c>
       <c r="T3">
-        <v>-10.82</v>
+        <v>-15</v>
       </c>
       <c r="U3" t="s">
         <v>45</v>
@@ -1072,43 +1072,43 @@
         <v>1</v>
       </c>
       <c r="Y3">
-        <v>31.26</v>
+        <v>28.28</v>
       </c>
       <c r="Z3">
-        <v>-15.96</v>
+        <v>-20.34</v>
       </c>
       <c r="AA3">
-        <v>-7.87</v>
+        <v>-10.36</v>
       </c>
       <c r="AB3">
-        <v>-8.09</v>
+        <v>-9.970000000000001</v>
       </c>
       <c r="AC3">
         <v>0</v>
       </c>
       <c r="AD3">
-        <v>5.58</v>
+        <v>2.1</v>
       </c>
       <c r="AE3">
-        <v>23.49</v>
+        <v>23.92</v>
       </c>
       <c r="AF3">
-        <v>-22.93</v>
+        <v>-35.24</v>
       </c>
       <c r="AG3">
-        <v>537.79</v>
+        <v>543.72</v>
       </c>
       <c r="AH3">
-        <v>429.73</v>
+        <v>412.91</v>
       </c>
       <c r="AI3">
-        <v>490.69</v>
+        <v>475.83</v>
       </c>
       <c r="AJ3" t="s">
         <v>47</v>
       </c>
       <c r="AK3">
-        <v>37.78</v>
+        <v>42.59</v>
       </c>
     </row>
     <row r="4" spans="1:37">
@@ -1119,58 +1119,58 @@
         <v>44</v>
       </c>
       <c r="C4">
-        <v>278.8</v>
+        <v>278.2</v>
       </c>
       <c r="D4">
-        <v>-4.88</v>
+        <v>-0.22</v>
       </c>
       <c r="E4">
         <v>542.2</v>
       </c>
       <c r="F4">
-        <v>278.8</v>
+        <v>278.2</v>
       </c>
       <c r="G4">
-        <v>-48.58</v>
+        <v>-48.69</v>
       </c>
       <c r="H4">
         <v>0</v>
       </c>
       <c r="I4">
-        <v>-8.710000000000001</v>
+        <v>-9.289999999999999</v>
       </c>
       <c r="J4">
-        <v>-14.48</v>
+        <v>-13.99</v>
       </c>
       <c r="K4">
-        <v>-15.55</v>
+        <v>-14.71</v>
       </c>
       <c r="L4">
-        <v>-48.67</v>
+        <v>-48.46</v>
       </c>
       <c r="M4">
-        <v>-23.67</v>
+        <v>-23.68</v>
       </c>
       <c r="N4">
         <v>15</v>
       </c>
       <c r="O4">
-        <v>9</v>
+        <v>13</v>
       </c>
       <c r="P4">
-        <v>295.25</v>
+        <v>289.55</v>
       </c>
       <c r="Q4">
-        <v>303.46</v>
+        <v>300.91</v>
       </c>
       <c r="R4">
-        <v>325.21</v>
+        <v>323.57</v>
       </c>
       <c r="S4">
-        <v>356.18</v>
+        <v>355.17</v>
       </c>
       <c r="T4">
-        <v>-21.72</v>
+        <v>-21.67</v>
       </c>
       <c r="U4" t="s">
         <v>45</v>
@@ -1185,43 +1185,43 @@
         <v>0</v>
       </c>
       <c r="Y4">
-        <v>26.64</v>
+        <v>26.38</v>
       </c>
       <c r="Z4">
-        <v>-9.26</v>
+        <v>-10.15</v>
       </c>
       <c r="AA4">
-        <v>-8.6</v>
+        <v>-8.91</v>
       </c>
       <c r="AB4">
-        <v>-0.65</v>
+        <v>-1.24</v>
       </c>
       <c r="AC4">
-        <v>39.4</v>
+        <v>22.34</v>
       </c>
       <c r="AD4">
-        <v>60.21</v>
+        <v>41.27</v>
       </c>
       <c r="AE4">
-        <v>11.49</v>
+        <v>11.16</v>
       </c>
       <c r="AF4">
-        <v>-38.35</v>
+        <v>-65.54000000000001</v>
       </c>
       <c r="AG4">
-        <v>326.26</v>
+        <v>322.92</v>
       </c>
       <c r="AH4">
-        <v>280.67</v>
+        <v>278.89</v>
       </c>
       <c r="AI4">
-        <v>317.46</v>
+        <v>310.01</v>
       </c>
       <c r="AJ4" t="s">
         <v>47</v>
       </c>
       <c r="AK4">
-        <v>40.69</v>
+        <v>36.72</v>
       </c>
     </row>
     <row r="5" spans="1:37">
@@ -1232,10 +1232,10 @@
         <v>44</v>
       </c>
       <c r="C5">
-        <v>1678</v>
+        <v>1655</v>
       </c>
       <c r="D5">
-        <v>-0.71</v>
+        <v>-1.37</v>
       </c>
       <c r="E5">
         <v>2176.6</v>
@@ -1244,46 +1244,46 @@
         <v>1631.8</v>
       </c>
       <c r="G5">
-        <v>-22.91</v>
+        <v>-23.96</v>
       </c>
       <c r="H5">
-        <v>2.83</v>
+        <v>1.42</v>
       </c>
       <c r="I5">
-        <v>-2.54</v>
+        <v>-4.45</v>
       </c>
       <c r="J5">
-        <v>-9.289999999999999</v>
+        <v>-9.24</v>
       </c>
       <c r="K5">
-        <v>-10.57</v>
+        <v>-12.41</v>
       </c>
       <c r="L5">
-        <v>-19.72</v>
+        <v>-20.57</v>
       </c>
       <c r="M5">
-        <v>-2.06</v>
+        <v>-1.72</v>
       </c>
       <c r="N5">
         <v>29</v>
       </c>
       <c r="O5">
-        <v>41</v>
+        <v>43</v>
       </c>
       <c r="P5">
-        <v>1705.8</v>
+        <v>1690.4</v>
       </c>
       <c r="Q5">
-        <v>1737.7</v>
+        <v>1728.12</v>
       </c>
       <c r="R5">
-        <v>1872.51</v>
+        <v>1864.97</v>
       </c>
       <c r="S5">
-        <v>1864.45</v>
+        <v>1862.53</v>
       </c>
       <c r="T5">
-        <v>-10</v>
+        <v>-11.14</v>
       </c>
       <c r="U5" t="s">
         <v>45</v>
@@ -1298,43 +1298,43 @@
         <v>1</v>
       </c>
       <c r="Y5">
-        <v>30.54</v>
+        <v>27.88</v>
       </c>
       <c r="Z5">
-        <v>-46.86</v>
+        <v>-48.74</v>
       </c>
       <c r="AA5">
-        <v>-48.53</v>
+        <v>-48.57</v>
       </c>
       <c r="AB5">
-        <v>1.67</v>
+        <v>-0.17</v>
       </c>
       <c r="AC5">
-        <v>47.4</v>
+        <v>34.09</v>
       </c>
       <c r="AD5">
-        <v>61.59</v>
+        <v>48.02</v>
       </c>
       <c r="AE5">
-        <v>38.5</v>
+        <v>39.25</v>
       </c>
       <c r="AF5">
-        <v>24.43</v>
+        <v>-1.99</v>
       </c>
       <c r="AG5">
-        <v>1807.94</v>
+        <v>1787.25</v>
       </c>
       <c r="AH5">
-        <v>1667.45</v>
+        <v>1668.99</v>
       </c>
       <c r="AI5">
-        <v>1787.89</v>
+        <v>1777.24</v>
       </c>
       <c r="AJ5" t="s">
         <v>47</v>
       </c>
       <c r="AK5">
-        <v>57.4</v>
+        <v>60.01</v>
       </c>
     </row>
     <row r="6" spans="1:37">
@@ -1345,10 +1345,10 @@
         <v>44</v>
       </c>
       <c r="C6">
-        <v>11293</v>
+        <v>11175</v>
       </c>
       <c r="D6">
-        <v>2.9</v>
+        <v>-1.04</v>
       </c>
       <c r="E6">
         <v>13144</v>
@@ -1357,46 +1357,46 @@
         <v>8746</v>
       </c>
       <c r="G6">
-        <v>-14.08</v>
+        <v>-14.98</v>
       </c>
       <c r="H6">
-        <v>29.12</v>
+        <v>27.77</v>
       </c>
       <c r="I6">
-        <v>4.82</v>
+        <v>-0.45</v>
       </c>
       <c r="J6">
-        <v>-1.02</v>
+        <v>-0.09</v>
       </c>
       <c r="K6">
-        <v>8.33</v>
+        <v>5.07</v>
       </c>
       <c r="L6">
-        <v>-9.66</v>
+        <v>-11.69</v>
       </c>
       <c r="M6">
-        <v>20.22</v>
+        <v>20.05</v>
       </c>
       <c r="N6">
         <v>57</v>
       </c>
       <c r="O6">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="P6">
-        <v>11191.2</v>
+        <v>11181.2</v>
       </c>
       <c r="Q6">
-        <v>10893.1</v>
+        <v>10879.4</v>
       </c>
       <c r="R6">
-        <v>11119.1</v>
+        <v>11111.6</v>
       </c>
       <c r="S6">
-        <v>10658.89</v>
+        <v>10658.86</v>
       </c>
       <c r="T6">
-        <v>5.95</v>
+        <v>4.84</v>
       </c>
       <c r="U6" t="s">
         <v>45</v>
@@ -1411,34 +1411,34 @@
         <v>2</v>
       </c>
       <c r="Y6">
-        <v>57.24</v>
+        <v>54.18</v>
       </c>
       <c r="Z6">
-        <v>24.9</v>
+        <v>35.83</v>
       </c>
       <c r="AA6">
-        <v>-41.61</v>
+        <v>-26.12</v>
       </c>
       <c r="AB6">
-        <v>66.51000000000001</v>
+        <v>61.95</v>
       </c>
       <c r="AC6">
-        <v>82.93000000000001</v>
+        <v>75.25</v>
       </c>
       <c r="AD6">
-        <v>88.39</v>
+        <v>80.59</v>
       </c>
       <c r="AE6">
-        <v>292.41</v>
+        <v>290.81</v>
       </c>
       <c r="AF6">
-        <v>224.33</v>
+        <v>-26.77</v>
       </c>
       <c r="AG6">
-        <v>11411.29</v>
+        <v>11347.8</v>
       </c>
       <c r="AH6">
-        <v>10374.91</v>
+        <v>10411</v>
       </c>
       <c r="AI6">
         <v>11368.55</v>
@@ -1447,7 +1447,7 @@
         <v>47</v>
       </c>
       <c r="AK6">
-        <v>25.64</v>
+        <v>25.6</v>
       </c>
     </row>
     <row r="7" spans="1:37">
@@ -1458,10 +1458,10 @@
         <v>44</v>
       </c>
       <c r="C7">
-        <v>942.1</v>
+        <v>928.95</v>
       </c>
       <c r="D7">
-        <v>1.74</v>
+        <v>-1.4</v>
       </c>
       <c r="E7">
         <v>1158.8</v>
@@ -1470,46 +1470,46 @@
         <v>801.55</v>
       </c>
       <c r="G7">
-        <v>-18.7</v>
+        <v>-19.84</v>
       </c>
       <c r="H7">
-        <v>17.53</v>
+        <v>15.89</v>
       </c>
       <c r="I7">
-        <v>-1.56</v>
+        <v>-3.76</v>
       </c>
       <c r="J7">
-        <v>-7.75</v>
+        <v>-7.92</v>
       </c>
       <c r="K7">
-        <v>-11.15</v>
+        <v>-10.66</v>
       </c>
       <c r="L7">
-        <v>-11.6</v>
+        <v>-13.19</v>
       </c>
       <c r="M7">
-        <v>4.49</v>
+        <v>4.37</v>
       </c>
       <c r="N7">
         <v>43</v>
       </c>
       <c r="O7">
-        <v>49</v>
+        <v>53</v>
       </c>
       <c r="P7">
-        <v>954.5599999999999</v>
+        <v>947.3</v>
       </c>
       <c r="Q7">
-        <v>968.5599999999999</v>
+        <v>962.85</v>
       </c>
       <c r="R7">
-        <v>1024.22</v>
+        <v>1020.94</v>
       </c>
       <c r="S7">
-        <v>973.75</v>
+        <v>973.4400000000001</v>
       </c>
       <c r="T7">
-        <v>-3.25</v>
+        <v>-4.57</v>
       </c>
       <c r="U7" t="s">
         <v>45</v>
@@ -1524,34 +1524,34 @@
         <v>1</v>
       </c>
       <c r="Y7">
-        <v>40.4</v>
+        <v>37.99</v>
       </c>
       <c r="Z7">
-        <v>-20.58</v>
+        <v>-21.53</v>
       </c>
       <c r="AA7">
-        <v>-20.91</v>
+        <v>-21.03</v>
       </c>
       <c r="AB7">
-        <v>0.33</v>
+        <v>-0.5</v>
       </c>
       <c r="AC7">
-        <v>46.94</v>
+        <v>32.53</v>
       </c>
       <c r="AD7">
-        <v>62.77</v>
+        <v>47.19</v>
       </c>
       <c r="AE7">
-        <v>28.2</v>
+        <v>28.64</v>
       </c>
       <c r="AF7">
-        <v>27.05</v>
+        <v>-27.66</v>
       </c>
       <c r="AG7">
-        <v>1016.53</v>
+        <v>999.2</v>
       </c>
       <c r="AH7">
-        <v>920.6</v>
+        <v>926.51</v>
       </c>
       <c r="AI7">
         <v>1009.35</v>
@@ -1560,7 +1560,7 @@
         <v>47</v>
       </c>
       <c r="AK7">
-        <v>22.87</v>
+        <v>23.31</v>
       </c>
     </row>
     <row r="8" spans="1:37">
@@ -1571,10 +1571,10 @@
         <v>44</v>
       </c>
       <c r="C8">
-        <v>153.38</v>
+        <v>143.06</v>
       </c>
       <c r="D8">
-        <v>-2.19</v>
+        <v>-6.73</v>
       </c>
       <c r="E8">
         <v>185.92</v>
@@ -1583,46 +1583,46 @@
         <v>115.96</v>
       </c>
       <c r="G8">
-        <v>-17.5</v>
+        <v>-23.05</v>
       </c>
       <c r="H8">
-        <v>32.27</v>
+        <v>23.37</v>
       </c>
       <c r="I8">
-        <v>-12.36</v>
+        <v>-16.02</v>
       </c>
       <c r="J8">
-        <v>12.75</v>
+        <v>1.17</v>
       </c>
       <c r="K8">
-        <v>7.64</v>
+        <v>3.26</v>
       </c>
       <c r="L8">
-        <v>17.79</v>
+        <v>11</v>
       </c>
       <c r="M8">
-        <v>3.5</v>
+        <v>2.46</v>
       </c>
       <c r="N8">
         <v>99</v>
       </c>
       <c r="O8">
-        <v>85</v>
+        <v>82</v>
       </c>
       <c r="P8">
-        <v>163.4</v>
+        <v>157.94</v>
       </c>
       <c r="Q8">
-        <v>171.09</v>
+        <v>170.39</v>
       </c>
       <c r="R8">
-        <v>150.32</v>
+        <v>150.37</v>
       </c>
       <c r="S8">
-        <v>137.69</v>
+        <v>137.71</v>
       </c>
       <c r="T8">
-        <v>11.39</v>
+        <v>3.88</v>
       </c>
       <c r="U8" t="s">
         <v>46</v>
@@ -1637,43 +1637,43 @@
         <v>3</v>
       </c>
       <c r="Y8">
-        <v>41.45</v>
+        <v>34.82</v>
       </c>
       <c r="Z8">
-        <v>3.63</v>
+        <v>1.48</v>
       </c>
       <c r="AA8">
-        <v>7.25</v>
+        <v>6.1</v>
       </c>
       <c r="AB8">
-        <v>-3.62</v>
+        <v>-4.62</v>
       </c>
       <c r="AC8">
         <v>0</v>
       </c>
       <c r="AD8">
-        <v>1.12</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="AE8">
-        <v>8.07</v>
+        <v>8.48</v>
       </c>
       <c r="AF8">
-        <v>-61.31</v>
+        <v>3.62</v>
       </c>
       <c r="AG8">
-        <v>189.93</v>
+        <v>192.23</v>
       </c>
       <c r="AH8">
-        <v>152.25</v>
+        <v>148.55</v>
       </c>
       <c r="AI8">
-        <v>180.62</v>
+        <v>172.56</v>
       </c>
       <c r="AJ8" t="s">
         <v>47</v>
       </c>
       <c r="AK8">
-        <v>34.36</v>
+        <v>37.93</v>
       </c>
     </row>
   </sheetData>
@@ -1871,13 +1871,13 @@
         <v>9</v>
       </c>
       <c r="C7" s="5">
-        <v>-11.76</v>
+        <v>-11.39</v>
       </c>
       <c r="D7" s="5">
-        <v>-11.39</v>
+        <v>-11.36</v>
       </c>
       <c r="E7" s="6">
-        <v>0.37</v>
+        <v>0.03</v>
       </c>
     </row>
     <row r="8" spans="1:6">
@@ -1888,13 +1888,13 @@
         <v>9</v>
       </c>
       <c r="C8" s="5">
-        <v>-16.94</v>
+        <v>-19.29</v>
       </c>
       <c r="D8" s="5">
-        <v>-19.29</v>
+        <v>-22.73</v>
       </c>
       <c r="E8" s="7">
-        <v>-2.35</v>
+        <v>-3.44</v>
       </c>
     </row>
     <row r="9" spans="1:6">
@@ -1905,13 +1905,13 @@
         <v>9</v>
       </c>
       <c r="C9" s="5">
-        <v>-9.27</v>
+        <v>-14.48</v>
       </c>
       <c r="D9" s="5">
-        <v>-14.48</v>
-      </c>
-      <c r="E9" s="7">
-        <v>-5.21</v>
+        <v>-13.99</v>
+      </c>
+      <c r="E9" s="6">
+        <v>0.49</v>
       </c>
     </row>
     <row r="10" spans="1:6">
@@ -1922,13 +1922,13 @@
         <v>9</v>
       </c>
       <c r="C10" s="5">
-        <v>-8.77</v>
+        <v>-9.289999999999999</v>
       </c>
       <c r="D10" s="5">
-        <v>-9.289999999999999</v>
-      </c>
-      <c r="E10" s="7">
-        <v>-0.52</v>
+        <v>-9.24</v>
+      </c>
+      <c r="E10" s="6">
+        <v>0.05</v>
       </c>
     </row>
     <row r="11" spans="1:6">
@@ -1939,13 +1939,13 @@
         <v>9</v>
       </c>
       <c r="C11" s="5">
-        <v>-2.72</v>
+        <v>-1.02</v>
       </c>
       <c r="D11" s="5">
-        <v>-1.02</v>
+        <v>-0.09</v>
       </c>
       <c r="E11" s="6">
-        <v>1.7</v>
+        <v>0.93</v>
       </c>
     </row>
     <row r="12" spans="1:6">
@@ -1956,13 +1956,13 @@
         <v>9</v>
       </c>
       <c r="C12" s="5">
-        <v>-10.99</v>
+        <v>-7.75</v>
       </c>
       <c r="D12" s="5">
-        <v>-7.75</v>
-      </c>
-      <c r="E12" s="6">
-        <v>3.24</v>
+        <v>-7.92</v>
+      </c>
+      <c r="E12" s="7">
+        <v>-0.17</v>
       </c>
     </row>
     <row r="13" spans="1:6">
@@ -1973,13 +1973,13 @@
         <v>9</v>
       </c>
       <c r="C13" s="5">
-        <v>16.35</v>
+        <v>12.75</v>
       </c>
       <c r="D13" s="5">
-        <v>12.75</v>
+        <v>1.17</v>
       </c>
       <c r="E13" s="7">
-        <v>-3.6</v>
+        <v>-11.58</v>
       </c>
     </row>
     <row r="14" spans="1:6">
@@ -1990,13 +1990,13 @@
         <v>8</v>
       </c>
       <c r="C14" s="5">
-        <v>-2.38</v>
+        <v>-0.93</v>
       </c>
       <c r="D14" s="5">
-        <v>-0.93</v>
-      </c>
-      <c r="E14" s="6">
-        <v>1.45</v>
+        <v>-3.01</v>
+      </c>
+      <c r="E14" s="7">
+        <v>-2.08</v>
       </c>
     </row>
     <row r="15" spans="1:6">
@@ -2007,13 +2007,13 @@
         <v>8</v>
       </c>
       <c r="C15" s="5">
-        <v>-16.3</v>
+        <v>-20.03</v>
       </c>
       <c r="D15" s="5">
-        <v>-20.03</v>
-      </c>
-      <c r="E15" s="7">
-        <v>-3.73</v>
+        <v>-15.27</v>
+      </c>
+      <c r="E15" s="6">
+        <v>4.76</v>
       </c>
     </row>
     <row r="16" spans="1:6">
@@ -2024,13 +2024,13 @@
         <v>8</v>
       </c>
       <c r="C16" s="5">
-        <v>-3.28</v>
+        <v>-8.710000000000001</v>
       </c>
       <c r="D16" s="5">
-        <v>-8.710000000000001</v>
+        <v>-9.289999999999999</v>
       </c>
       <c r="E16" s="7">
-        <v>-5.43</v>
+        <v>-0.58</v>
       </c>
     </row>
     <row r="17" spans="1:5">
@@ -2041,13 +2041,13 @@
         <v>8</v>
       </c>
       <c r="C17" s="5">
-        <v>-3.74</v>
+        <v>-2.54</v>
       </c>
       <c r="D17" s="5">
-        <v>-2.54</v>
-      </c>
-      <c r="E17" s="6">
-        <v>1.2</v>
+        <v>-4.45</v>
+      </c>
+      <c r="E17" s="7">
+        <v>-1.91</v>
       </c>
     </row>
     <row r="18" spans="1:5">
@@ -2058,13 +2058,13 @@
         <v>8</v>
       </c>
       <c r="C18" s="5">
-        <v>1.55</v>
+        <v>4.82</v>
       </c>
       <c r="D18" s="5">
-        <v>4.82</v>
-      </c>
-      <c r="E18" s="6">
-        <v>3.27</v>
+        <v>-0.45</v>
+      </c>
+      <c r="E18" s="7">
+        <v>-5.27</v>
       </c>
     </row>
     <row r="19" spans="1:5">
@@ -2075,13 +2075,13 @@
         <v>8</v>
       </c>
       <c r="C19" s="5">
-        <v>-5.77</v>
+        <v>-1.56</v>
       </c>
       <c r="D19" s="5">
-        <v>-1.56</v>
-      </c>
-      <c r="E19" s="6">
-        <v>4.21</v>
+        <v>-3.76</v>
+      </c>
+      <c r="E19" s="7">
+        <v>-2.2</v>
       </c>
     </row>
     <row r="20" spans="1:5">
@@ -2092,13 +2092,13 @@
         <v>8</v>
       </c>
       <c r="C20" s="5">
-        <v>-11.17</v>
+        <v>-12.36</v>
       </c>
       <c r="D20" s="5">
-        <v>-12.36</v>
+        <v>-16.02</v>
       </c>
       <c r="E20" s="7">
-        <v>-1.19</v>
+        <v>-3.66</v>
       </c>
     </row>
     <row r="21" spans="1:5">
@@ -2109,13 +2109,13 @@
         <v>11</v>
       </c>
       <c r="C21" s="5">
-        <v>13.51</v>
+        <v>12.53</v>
       </c>
       <c r="D21" s="5">
-        <v>12.53</v>
+        <v>11.62</v>
       </c>
       <c r="E21" s="7">
-        <v>-0.98</v>
+        <v>-0.91</v>
       </c>
     </row>
     <row r="22" spans="1:5">
@@ -2126,13 +2126,13 @@
         <v>11</v>
       </c>
       <c r="C22" s="5">
-        <v>60.84</v>
+        <v>56.89</v>
       </c>
       <c r="D22" s="5">
-        <v>56.89</v>
+        <v>47.42</v>
       </c>
       <c r="E22" s="7">
-        <v>-3.95</v>
+        <v>-9.470000000000001</v>
       </c>
     </row>
     <row r="23" spans="1:5">
@@ -2143,13 +2143,13 @@
         <v>11</v>
       </c>
       <c r="C23" s="5">
-        <v>-46.51</v>
+        <v>-48.67</v>
       </c>
       <c r="D23" s="5">
-        <v>-48.67</v>
-      </c>
-      <c r="E23" s="7">
-        <v>-2.16</v>
+        <v>-48.46</v>
+      </c>
+      <c r="E23" s="6">
+        <v>0.21</v>
       </c>
     </row>
     <row r="24" spans="1:5">
@@ -2160,13 +2160,13 @@
         <v>11</v>
       </c>
       <c r="C24" s="5">
-        <v>-18.91</v>
+        <v>-19.72</v>
       </c>
       <c r="D24" s="5">
-        <v>-19.72</v>
+        <v>-20.57</v>
       </c>
       <c r="E24" s="7">
-        <v>-0.8100000000000001</v>
+        <v>-0.85</v>
       </c>
     </row>
     <row r="25" spans="1:5">
@@ -2177,13 +2177,13 @@
         <v>11</v>
       </c>
       <c r="C25" s="5">
-        <v>-10.17</v>
+        <v>-9.66</v>
       </c>
       <c r="D25" s="5">
-        <v>-9.66</v>
-      </c>
-      <c r="E25" s="6">
-        <v>0.51</v>
+        <v>-11.69</v>
+      </c>
+      <c r="E25" s="7">
+        <v>-2.03</v>
       </c>
     </row>
     <row r="26" spans="1:5">
@@ -2194,13 +2194,13 @@
         <v>11</v>
       </c>
       <c r="C26" s="5">
-        <v>-12.63</v>
+        <v>-11.6</v>
       </c>
       <c r="D26" s="5">
-        <v>-11.6</v>
-      </c>
-      <c r="E26" s="6">
-        <v>1.03</v>
+        <v>-13.19</v>
+      </c>
+      <c r="E26" s="7">
+        <v>-1.59</v>
       </c>
     </row>
     <row r="27" spans="1:5">
@@ -2211,13 +2211,13 @@
         <v>11</v>
       </c>
       <c r="C27" s="5">
-        <v>20.5</v>
+        <v>17.79</v>
       </c>
       <c r="D27" s="5">
-        <v>17.79</v>
+        <v>11</v>
       </c>
       <c r="E27" s="7">
-        <v>-2.71</v>
+        <v>-6.79</v>
       </c>
     </row>
     <row r="28" spans="1:5">
@@ -2228,13 +2228,13 @@
         <v>10</v>
       </c>
       <c r="C28" s="5">
-        <v>-3.19</v>
+        <v>-7.67</v>
       </c>
       <c r="D28" s="5">
-        <v>-7.67</v>
+        <v>-10.74</v>
       </c>
       <c r="E28" s="7">
-        <v>-4.48</v>
+        <v>-3.07</v>
       </c>
     </row>
     <row r="29" spans="1:5">
@@ -2245,13 +2245,13 @@
         <v>10</v>
       </c>
       <c r="C29" s="5">
-        <v>-19.01</v>
+        <v>-21.47</v>
       </c>
       <c r="D29" s="5">
-        <v>-21.47</v>
+        <v>-28.59</v>
       </c>
       <c r="E29" s="7">
-        <v>-2.46</v>
+        <v>-7.12</v>
       </c>
     </row>
     <row r="30" spans="1:5">
@@ -2262,13 +2262,13 @@
         <v>10</v>
       </c>
       <c r="C30" s="5">
-        <v>-12.02</v>
+        <v>-15.55</v>
       </c>
       <c r="D30" s="5">
-        <v>-15.55</v>
-      </c>
-      <c r="E30" s="7">
-        <v>-3.53</v>
+        <v>-14.71</v>
+      </c>
+      <c r="E30" s="6">
+        <v>0.84</v>
       </c>
     </row>
     <row r="31" spans="1:5">
@@ -2279,13 +2279,13 @@
         <v>10</v>
       </c>
       <c r="C31" s="5">
-        <v>-11.08</v>
+        <v>-10.57</v>
       </c>
       <c r="D31" s="5">
-        <v>-10.57</v>
-      </c>
-      <c r="E31" s="6">
-        <v>0.51</v>
+        <v>-12.41</v>
+      </c>
+      <c r="E31" s="7">
+        <v>-1.84</v>
       </c>
     </row>
     <row r="32" spans="1:5">
@@ -2296,13 +2296,13 @@
         <v>10</v>
       </c>
       <c r="C32" s="5">
-        <v>5.06</v>
+        <v>8.33</v>
       </c>
       <c r="D32" s="5">
-        <v>8.33</v>
-      </c>
-      <c r="E32" s="6">
-        <v>3.27</v>
+        <v>5.07</v>
+      </c>
+      <c r="E32" s="7">
+        <v>-3.26</v>
       </c>
     </row>
     <row r="33" spans="1:5">
@@ -2313,13 +2313,13 @@
         <v>10</v>
       </c>
       <c r="C33" s="5">
-        <v>-13.39</v>
+        <v>-11.15</v>
       </c>
       <c r="D33" s="5">
-        <v>-11.15</v>
+        <v>-10.66</v>
       </c>
       <c r="E33" s="6">
-        <v>2.24</v>
+        <v>0.49</v>
       </c>
     </row>
     <row r="34" spans="1:5">
@@ -2330,13 +2330,13 @@
         <v>10</v>
       </c>
       <c r="C34" s="5">
-        <v>7.49</v>
+        <v>7.64</v>
       </c>
       <c r="D34" s="5">
-        <v>7.64</v>
-      </c>
-      <c r="E34" s="6">
-        <v>0.15</v>
+        <v>3.26</v>
+      </c>
+      <c r="E34" s="7">
+        <v>-4.38</v>
       </c>
     </row>
     <row r="35" spans="1:5">
@@ -2347,13 +2347,13 @@
         <v>6</v>
       </c>
       <c r="C35" s="5">
+        <v>-17.85</v>
+      </c>
+      <c r="D35" s="5">
         <v>-18.52</v>
       </c>
-      <c r="D35" s="5">
-        <v>-17.85</v>
-      </c>
-      <c r="E35" s="6">
-        <v>0.67</v>
+      <c r="E35" s="7">
+        <v>-0.67</v>
       </c>
     </row>
     <row r="36" spans="1:5">
@@ -2364,13 +2364,13 @@
         <v>6</v>
       </c>
       <c r="C36" s="5">
-        <v>-36.53</v>
+        <v>-37.95</v>
       </c>
       <c r="D36" s="5">
-        <v>-37.95</v>
+        <v>-40.78</v>
       </c>
       <c r="E36" s="7">
-        <v>-1.42</v>
+        <v>-2.83</v>
       </c>
     </row>
     <row r="37" spans="1:5">
@@ -2381,13 +2381,13 @@
         <v>6</v>
       </c>
       <c r="C37" s="5">
-        <v>-46.03</v>
+        <v>-48.58</v>
       </c>
       <c r="D37" s="5">
-        <v>-48.58</v>
+        <v>-48.69</v>
       </c>
       <c r="E37" s="7">
-        <v>-2.55</v>
+        <v>-0.11</v>
       </c>
     </row>
     <row r="38" spans="1:5">
@@ -2398,13 +2398,13 @@
         <v>6</v>
       </c>
       <c r="C38" s="5">
-        <v>-22.36</v>
+        <v>-22.91</v>
       </c>
       <c r="D38" s="5">
-        <v>-22.91</v>
+        <v>-23.96</v>
       </c>
       <c r="E38" s="7">
-        <v>-0.55</v>
+        <v>-1.05</v>
       </c>
     </row>
     <row r="39" spans="1:5">
@@ -2415,13 +2415,13 @@
         <v>6</v>
       </c>
       <c r="C39" s="5">
-        <v>-16.5</v>
+        <v>-14.08</v>
       </c>
       <c r="D39" s="5">
-        <v>-14.08</v>
-      </c>
-      <c r="E39" s="6">
-        <v>2.42</v>
+        <v>-14.98</v>
+      </c>
+      <c r="E39" s="7">
+        <v>-0.9</v>
       </c>
     </row>
     <row r="40" spans="1:5">
@@ -2432,13 +2432,13 @@
         <v>6</v>
       </c>
       <c r="C40" s="5">
-        <v>-20.09</v>
+        <v>-18.7</v>
       </c>
       <c r="D40" s="5">
-        <v>-18.7</v>
-      </c>
-      <c r="E40" s="6">
-        <v>1.39</v>
+        <v>-19.84</v>
+      </c>
+      <c r="E40" s="7">
+        <v>-1.14</v>
       </c>
     </row>
     <row r="41" spans="1:5">
@@ -2449,13 +2449,13 @@
         <v>6</v>
       </c>
       <c r="C41" s="5">
-        <v>-15.66</v>
+        <v>-17.5</v>
       </c>
       <c r="D41" s="5">
-        <v>-17.5</v>
+        <v>-23.05</v>
       </c>
       <c r="E41" s="7">
-        <v>-1.84</v>
+        <v>-5.55</v>
       </c>
     </row>
     <row r="42" spans="1:5">
@@ -2466,13 +2466,13 @@
         <v>2</v>
       </c>
       <c r="C42" s="5">
+        <v>10155</v>
+      </c>
+      <c r="D42" s="5">
         <v>10072</v>
       </c>
-      <c r="D42" s="5">
-        <v>10155</v>
-      </c>
-      <c r="E42" s="6">
-        <v>83</v>
+      <c r="E42" s="7">
+        <v>-83</v>
       </c>
     </row>
     <row r="43" spans="1:5">
@@ -2483,13 +2483,13 @@
         <v>2</v>
       </c>
       <c r="C43" s="5">
-        <v>425.4</v>
+        <v>415.9</v>
       </c>
       <c r="D43" s="5">
-        <v>415.9</v>
+        <v>396.95</v>
       </c>
       <c r="E43" s="7">
-        <v>-9.5</v>
+        <v>-18.95</v>
       </c>
     </row>
     <row r="44" spans="1:5">
@@ -2500,13 +2500,13 @@
         <v>2</v>
       </c>
       <c r="C44" s="5">
-        <v>293.1</v>
+        <v>278.8</v>
       </c>
       <c r="D44" s="5">
-        <v>278.8</v>
+        <v>278.2</v>
       </c>
       <c r="E44" s="7">
-        <v>-14.3</v>
+        <v>-0.6</v>
       </c>
     </row>
     <row r="45" spans="1:5">
@@ -2517,13 +2517,13 @@
         <v>2</v>
       </c>
       <c r="C45" s="5">
-        <v>1690</v>
+        <v>1678</v>
       </c>
       <c r="D45" s="5">
-        <v>1678</v>
+        <v>1655</v>
       </c>
       <c r="E45" s="7">
-        <v>-12</v>
+        <v>-23</v>
       </c>
     </row>
     <row r="46" spans="1:5">
@@ -2534,13 +2534,13 @@
         <v>2</v>
       </c>
       <c r="C46" s="5">
-        <v>10975</v>
+        <v>11293</v>
       </c>
       <c r="D46" s="5">
-        <v>11293</v>
-      </c>
-      <c r="E46" s="6">
-        <v>318</v>
+        <v>11175</v>
+      </c>
+      <c r="E46" s="7">
+        <v>-118</v>
       </c>
     </row>
     <row r="47" spans="1:5">
@@ -2551,13 +2551,13 @@
         <v>2</v>
       </c>
       <c r="C47" s="5">
-        <v>926</v>
+        <v>942.1</v>
       </c>
       <c r="D47" s="5">
-        <v>942.1</v>
-      </c>
-      <c r="E47" s="6">
-        <v>16.1</v>
+        <v>928.95</v>
+      </c>
+      <c r="E47" s="7">
+        <v>-13.15</v>
       </c>
     </row>
     <row r="48" spans="1:5">
@@ -2568,13 +2568,13 @@
         <v>2</v>
       </c>
       <c r="C48" s="5">
-        <v>156.81</v>
+        <v>153.38</v>
       </c>
       <c r="D48" s="5">
-        <v>153.38</v>
+        <v>143.06</v>
       </c>
       <c r="E48" s="7">
-        <v>-3.43</v>
+        <v>-10.32</v>
       </c>
     </row>
     <row r="49" spans="1:5">
@@ -2585,13 +2585,13 @@
         <v>24</v>
       </c>
       <c r="C49" s="5">
-        <v>36.39</v>
+        <v>38.91</v>
       </c>
       <c r="D49" s="5">
-        <v>38.91</v>
-      </c>
-      <c r="E49" s="6">
-        <v>2.52</v>
+        <v>37.32</v>
+      </c>
+      <c r="E49" s="7">
+        <v>-1.59</v>
       </c>
     </row>
     <row r="50" spans="1:5">
@@ -2602,13 +2602,13 @@
         <v>24</v>
       </c>
       <c r="C50" s="5">
-        <v>32.87</v>
+        <v>31.26</v>
       </c>
       <c r="D50" s="5">
-        <v>31.26</v>
+        <v>28.28</v>
       </c>
       <c r="E50" s="7">
-        <v>-1.61</v>
+        <v>-2.98</v>
       </c>
     </row>
     <row r="51" spans="1:5">
@@ -2619,13 +2619,13 @@
         <v>24</v>
       </c>
       <c r="C51" s="5">
-        <v>33.87</v>
+        <v>26.64</v>
       </c>
       <c r="D51" s="5">
-        <v>26.64</v>
+        <v>26.38</v>
       </c>
       <c r="E51" s="7">
-        <v>-7.23</v>
+        <v>-0.26</v>
       </c>
     </row>
     <row r="52" spans="1:5">
@@ -2636,13 +2636,13 @@
         <v>24</v>
       </c>
       <c r="C52" s="5">
-        <v>32.02</v>
+        <v>30.54</v>
       </c>
       <c r="D52" s="5">
-        <v>30.54</v>
+        <v>27.88</v>
       </c>
       <c r="E52" s="7">
-        <v>-1.48</v>
+        <v>-2.66</v>
       </c>
     </row>
     <row r="53" spans="1:5">
@@ -2653,13 +2653,13 @@
         <v>24</v>
       </c>
       <c r="C53" s="5">
-        <v>50.19</v>
+        <v>57.24</v>
       </c>
       <c r="D53" s="5">
-        <v>57.24</v>
-      </c>
-      <c r="E53" s="6">
-        <v>7.05</v>
+        <v>54.18</v>
+      </c>
+      <c r="E53" s="7">
+        <v>-3.06</v>
       </c>
     </row>
     <row r="54" spans="1:5">
@@ -2670,13 +2670,13 @@
         <v>24</v>
       </c>
       <c r="C54" s="5">
-        <v>35.76</v>
+        <v>40.4</v>
       </c>
       <c r="D54" s="5">
-        <v>40.4</v>
-      </c>
-      <c r="E54" s="6">
-        <v>4.64</v>
+        <v>37.99</v>
+      </c>
+      <c r="E54" s="7">
+        <v>-2.41</v>
       </c>
     </row>
     <row r="55" spans="1:5">
@@ -2687,13 +2687,13 @@
         <v>24</v>
       </c>
       <c r="C55" s="5">
-        <v>44.04</v>
+        <v>41.45</v>
       </c>
       <c r="D55" s="5">
-        <v>41.45</v>
+        <v>34.82</v>
       </c>
       <c r="E55" s="7">
-        <v>-2.59</v>
+        <v>-6.63</v>
       </c>
     </row>
     <row r="56" spans="1:5">
@@ -2704,13 +2704,13 @@
         <v>31</v>
       </c>
       <c r="C56" s="5">
-        <v>-49.7</v>
+        <v>-21.71</v>
       </c>
       <c r="D56" s="5">
-        <v>-21.71</v>
+        <v>-16.35</v>
       </c>
       <c r="E56" s="6">
-        <v>27.99</v>
+        <v>5.36</v>
       </c>
     </row>
     <row r="57" spans="1:5">
@@ -2721,13 +2721,13 @@
         <v>31</v>
       </c>
       <c r="C57" s="5">
-        <v>-35.33</v>
+        <v>-22.93</v>
       </c>
       <c r="D57" s="5">
-        <v>-22.93</v>
-      </c>
-      <c r="E57" s="6">
-        <v>12.4</v>
+        <v>-35.24</v>
+      </c>
+      <c r="E57" s="7">
+        <v>-12.31</v>
       </c>
     </row>
     <row r="58" spans="1:5">
@@ -2738,13 +2738,13 @@
         <v>31</v>
       </c>
       <c r="C58" s="5">
-        <v>-72.79000000000001</v>
+        <v>-38.35</v>
       </c>
       <c r="D58" s="5">
-        <v>-38.35</v>
-      </c>
-      <c r="E58" s="6">
-        <v>34.44</v>
+        <v>-65.54000000000001</v>
+      </c>
+      <c r="E58" s="7">
+        <v>-27.19</v>
       </c>
     </row>
     <row r="59" spans="1:5">
@@ -2755,13 +2755,13 @@
         <v>31</v>
       </c>
       <c r="C59" s="5">
-        <v>35.35</v>
+        <v>24.43</v>
       </c>
       <c r="D59" s="5">
-        <v>24.43</v>
+        <v>-1.99</v>
       </c>
       <c r="E59" s="7">
-        <v>-10.92</v>
+        <v>-26.42</v>
       </c>
     </row>
     <row r="60" spans="1:5">
@@ -2772,13 +2772,13 @@
         <v>31</v>
       </c>
       <c r="C60" s="5">
-        <v>-10.37</v>
+        <v>224.33</v>
       </c>
       <c r="D60" s="5">
-        <v>224.33</v>
-      </c>
-      <c r="E60" s="6">
-        <v>234.7</v>
+        <v>-26.77</v>
+      </c>
+      <c r="E60" s="7">
+        <v>-251.1</v>
       </c>
     </row>
     <row r="61" spans="1:5">
@@ -2789,13 +2789,13 @@
         <v>31</v>
       </c>
       <c r="C61" s="5">
-        <v>135.86</v>
+        <v>27.05</v>
       </c>
       <c r="D61" s="5">
-        <v>27.05</v>
+        <v>-27.66</v>
       </c>
       <c r="E61" s="7">
-        <v>-108.81</v>
+        <v>-54.71</v>
       </c>
     </row>
     <row r="62" spans="1:5">
@@ -2806,13 +2806,13 @@
         <v>31</v>
       </c>
       <c r="C62" s="5">
-        <v>-55.84</v>
+        <v>-61.31</v>
       </c>
       <c r="D62" s="5">
-        <v>-61.31</v>
-      </c>
-      <c r="E62" s="7">
-        <v>-5.47</v>
+        <v>3.62</v>
+      </c>
+      <c r="E62" s="6">
+        <v>64.93000000000001</v>
       </c>
     </row>
   </sheetData>
@@ -2877,16 +2877,16 @@
         <v>7</v>
       </c>
       <c r="D2" s="10">
-        <v>38.1</v>
+        <v>35.3</v>
       </c>
       <c r="E2" s="10">
         <v>28.6</v>
       </c>
       <c r="F2" s="10">
-        <v>-7.2</v>
+        <v>-9.199999999999999</v>
       </c>
       <c r="G2" s="10">
-        <v>-7.2</v>
+        <v>-9.800000000000001</v>
       </c>
       <c r="H2" s="10">
         <v>57</v>
@@ -3017,25 +3017,25 @@
     </row>
     <row r="2" spans="1:7">
       <c r="A2" s="13">
-        <v>0.2411</v>
+        <v>0.246</v>
       </c>
       <c r="B2" s="13">
-        <v>0.2022</v>
+        <v>0.2005</v>
       </c>
       <c r="C2" s="13">
-        <v>0.1399</v>
+        <v>0.1355</v>
       </c>
       <c r="D2" s="13">
-        <v>0.0449</v>
+        <v>0.0437</v>
       </c>
       <c r="E2" s="13">
-        <v>0.035</v>
+        <v>0.0246</v>
       </c>
       <c r="F2" s="13">
-        <v>-0.0206</v>
+        <v>-0.0172</v>
       </c>
       <c r="G2" s="13">
-        <v>-0.2367</v>
+        <v>-0.2368</v>
       </c>
     </row>
   </sheetData>

--- a/BAJAJ_GROUP_Technical_Metrics.xlsx
+++ b/BAJAJ_GROUP_Technical_Metrics.xlsx
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="253" uniqueCount="63">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="270" uniqueCount="75">
   <si>
     <t>Symbol</t>
   </si>
@@ -169,7 +169,43 @@
     <t>▶  SIGNAL EVENTS (vs Previous Run)</t>
   </si>
   <si>
-    <t>No signal events detected since last run.</t>
+    <t>Signal</t>
+  </si>
+  <si>
+    <t>Change</t>
+  </si>
+  <si>
+    <t>Direction</t>
+  </si>
+  <si>
+    <t>Prev Value</t>
+  </si>
+  <si>
+    <t>Curr Value</t>
+  </si>
+  <si>
+    <t>RSI Oversold Recovery</t>
+  </si>
+  <si>
+    <t>27.9 → 32.3</t>
+  </si>
+  <si>
+    <t>🟢 BULLISH</t>
+  </si>
+  <si>
+    <t>27.9</t>
+  </si>
+  <si>
+    <t>32.3</t>
+  </si>
+  <si>
+    <t>50 DMA &gt; 200 DMA</t>
+  </si>
+  <si>
+    <t>Yes → No</t>
+  </si>
+  <si>
+    <t>🔴 DEATH CROSS</t>
   </si>
   <si>
     <t>▶  NUMERIC METRIC CHANGES (vs Previous Run)</t>
@@ -371,17 +407,19 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="14">
+  <cellXfs count="16">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="2" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="3" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
+    <xf numFmtId="0" fontId="4" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="5" fillId="6" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1"/>
+    <xf numFmtId="165" fontId="5" fillId="6" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="165" fontId="4" fillId="5" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="165" fontId="5" fillId="6" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="3" fillId="7" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
@@ -893,10 +931,10 @@
         <v>44</v>
       </c>
       <c r="C2">
-        <v>10072</v>
+        <v>10071</v>
       </c>
       <c r="D2">
-        <v>-0.82</v>
+        <v>-0.01</v>
       </c>
       <c r="E2">
         <v>12361</v>
@@ -905,46 +943,46 @@
         <v>8599.48</v>
       </c>
       <c r="G2">
-        <v>-18.52</v>
+        <v>-18.53</v>
       </c>
       <c r="H2">
-        <v>17.12</v>
+        <v>17.11</v>
       </c>
       <c r="I2">
-        <v>-3.01</v>
+        <v>-3.21</v>
       </c>
       <c r="J2">
-        <v>-11.36</v>
+        <v>-11.66</v>
       </c>
       <c r="K2">
-        <v>-10.74</v>
+        <v>-9.51</v>
       </c>
       <c r="L2">
-        <v>11.62</v>
+        <v>11.93</v>
       </c>
       <c r="M2">
-        <v>24.6</v>
+        <v>24.39</v>
       </c>
       <c r="N2">
         <v>71</v>
       </c>
       <c r="O2">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="P2">
-        <v>10198.2</v>
+        <v>10131.4</v>
       </c>
       <c r="Q2">
-        <v>10328.05</v>
+        <v>10271.2</v>
       </c>
       <c r="R2">
-        <v>11173.56</v>
+        <v>11140.98</v>
       </c>
       <c r="S2">
-        <v>10215.72</v>
+        <v>10219.25</v>
       </c>
       <c r="T2">
-        <v>-1.41</v>
+        <v>-1.45</v>
       </c>
       <c r="U2" t="s">
         <v>45</v>
@@ -959,34 +997,34 @@
         <v>1</v>
       </c>
       <c r="Y2">
-        <v>37.32</v>
+        <v>37.3</v>
       </c>
       <c r="Z2">
-        <v>-294.95</v>
+        <v>-286.29</v>
       </c>
       <c r="AA2">
-        <v>-331.69</v>
+        <v>-322.61</v>
       </c>
       <c r="AB2">
-        <v>36.74</v>
+        <v>36.32</v>
       </c>
       <c r="AC2">
-        <v>78.84999999999999</v>
+        <v>80.06</v>
       </c>
       <c r="AD2">
-        <v>83.34</v>
+        <v>80.63</v>
       </c>
       <c r="AE2">
-        <v>266.34</v>
+        <v>264.24</v>
       </c>
       <c r="AF2">
-        <v>-16.35</v>
+        <v>-40.81</v>
       </c>
       <c r="AG2">
-        <v>11269.41</v>
+        <v>11121.76</v>
       </c>
       <c r="AH2">
-        <v>9386.690000000001</v>
+        <v>9420.639999999999</v>
       </c>
       <c r="AI2">
         <v>10503.51</v>
@@ -995,7 +1033,7 @@
         <v>47</v>
       </c>
       <c r="AK2">
-        <v>41.18</v>
+        <v>41.53</v>
       </c>
     </row>
     <row r="3" spans="1:37">
@@ -1006,10 +1044,10 @@
         <v>44</v>
       </c>
       <c r="C3">
-        <v>396.95</v>
+        <v>387.35</v>
       </c>
       <c r="D3">
-        <v>-4.56</v>
+        <v>-2.42</v>
       </c>
       <c r="E3">
         <v>670.25</v>
@@ -1018,46 +1056,46 @@
         <v>247.45</v>
       </c>
       <c r="G3">
-        <v>-40.78</v>
+        <v>-42.21</v>
       </c>
       <c r="H3">
-        <v>60.42</v>
+        <v>56.54</v>
       </c>
       <c r="I3">
-        <v>-15.27</v>
+        <v>-17.93</v>
       </c>
       <c r="J3">
-        <v>-22.73</v>
+        <v>-23.43</v>
       </c>
       <c r="K3">
-        <v>-28.59</v>
+        <v>-29.55</v>
       </c>
       <c r="L3">
-        <v>47.42</v>
+        <v>44.16</v>
       </c>
       <c r="M3">
-        <v>13.55</v>
+        <v>12.36</v>
       </c>
       <c r="N3">
         <v>85</v>
       </c>
       <c r="O3">
-        <v>79</v>
+        <v>76</v>
       </c>
       <c r="P3">
-        <v>431.46</v>
+        <v>414.53</v>
       </c>
       <c r="Q3">
-        <v>478.31</v>
+        <v>472.6</v>
       </c>
       <c r="R3">
-        <v>489.78</v>
+        <v>486.76</v>
       </c>
       <c r="S3">
-        <v>466.98</v>
+        <v>467.52</v>
       </c>
       <c r="T3">
-        <v>-15</v>
+        <v>-17.15</v>
       </c>
       <c r="U3" t="s">
         <v>45</v>
@@ -1072,43 +1110,43 @@
         <v>1</v>
       </c>
       <c r="Y3">
-        <v>28.28</v>
+        <v>26.88</v>
       </c>
       <c r="Z3">
-        <v>-20.34</v>
+        <v>-24.3</v>
       </c>
       <c r="AA3">
-        <v>-10.36</v>
+        <v>-13.15</v>
       </c>
       <c r="AB3">
-        <v>-9.970000000000001</v>
+        <v>-11.15</v>
       </c>
       <c r="AC3">
         <v>0</v>
       </c>
       <c r="AD3">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="AE3">
-        <v>23.92</v>
+        <v>23.88</v>
       </c>
       <c r="AF3">
-        <v>-35.24</v>
+        <v>-3.76</v>
       </c>
       <c r="AG3">
-        <v>543.72</v>
+        <v>548.54</v>
       </c>
       <c r="AH3">
-        <v>412.91</v>
+        <v>396.65</v>
       </c>
       <c r="AI3">
-        <v>475.83</v>
+        <v>455.35</v>
       </c>
       <c r="AJ3" t="s">
         <v>47</v>
       </c>
       <c r="AK3">
-        <v>42.59</v>
+        <v>47.3</v>
       </c>
     </row>
     <row r="4" spans="1:37">
@@ -1119,58 +1157,58 @@
         <v>44</v>
       </c>
       <c r="C4">
-        <v>278.2</v>
+        <v>275.65</v>
       </c>
       <c r="D4">
-        <v>-0.22</v>
+        <v>-0.92</v>
       </c>
       <c r="E4">
         <v>542.2</v>
       </c>
       <c r="F4">
-        <v>278.2</v>
+        <v>275.65</v>
       </c>
       <c r="G4">
-        <v>-48.69</v>
+        <v>-49.16</v>
       </c>
       <c r="H4">
         <v>0</v>
       </c>
       <c r="I4">
-        <v>-9.289999999999999</v>
+        <v>-8.51</v>
       </c>
       <c r="J4">
-        <v>-13.99</v>
+        <v>-16.32</v>
       </c>
       <c r="K4">
-        <v>-14.71</v>
+        <v>-16.19</v>
       </c>
       <c r="L4">
-        <v>-48.46</v>
+        <v>-48.8</v>
       </c>
       <c r="M4">
-        <v>-23.68</v>
+        <v>-23.7</v>
       </c>
       <c r="N4">
         <v>15</v>
       </c>
       <c r="O4">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="P4">
-        <v>289.55</v>
+        <v>284.42</v>
       </c>
       <c r="Q4">
-        <v>300.91</v>
+        <v>298.61</v>
       </c>
       <c r="R4">
-        <v>323.57</v>
+        <v>321.8</v>
       </c>
       <c r="S4">
-        <v>355.17</v>
+        <v>354.16</v>
       </c>
       <c r="T4">
-        <v>-21.67</v>
+        <v>-22.17</v>
       </c>
       <c r="U4" t="s">
         <v>45</v>
@@ -1185,43 +1223,43 @@
         <v>0</v>
       </c>
       <c r="Y4">
-        <v>26.38</v>
+        <v>25.28</v>
       </c>
       <c r="Z4">
-        <v>-10.15</v>
+        <v>-10.94</v>
       </c>
       <c r="AA4">
-        <v>-8.91</v>
+        <v>-9.32</v>
       </c>
       <c r="AB4">
-        <v>-1.24</v>
+        <v>-1.62</v>
       </c>
       <c r="AC4">
-        <v>22.34</v>
+        <v>6.99</v>
       </c>
       <c r="AD4">
-        <v>41.27</v>
+        <v>22.91</v>
       </c>
       <c r="AE4">
-        <v>11.16</v>
+        <v>10.79</v>
       </c>
       <c r="AF4">
-        <v>-65.54000000000001</v>
+        <v>-78.95999999999999</v>
       </c>
       <c r="AG4">
-        <v>322.92</v>
+        <v>321.15</v>
       </c>
       <c r="AH4">
-        <v>278.89</v>
+        <v>276.08</v>
       </c>
       <c r="AI4">
-        <v>310.01</v>
+        <v>308.71</v>
       </c>
       <c r="AJ4" t="s">
         <v>47</v>
       </c>
       <c r="AK4">
-        <v>36.72</v>
+        <v>33.27</v>
       </c>
     </row>
     <row r="5" spans="1:37">
@@ -1232,10 +1270,10 @@
         <v>44</v>
       </c>
       <c r="C5">
-        <v>1655</v>
+        <v>1670.9</v>
       </c>
       <c r="D5">
-        <v>-1.37</v>
+        <v>0.96</v>
       </c>
       <c r="E5">
         <v>2176.6</v>
@@ -1244,25 +1282,25 @@
         <v>1631.8</v>
       </c>
       <c r="G5">
-        <v>-23.96</v>
+        <v>-23.23</v>
       </c>
       <c r="H5">
-        <v>1.42</v>
+        <v>2.4</v>
       </c>
       <c r="I5">
-        <v>-4.45</v>
+        <v>-3.36</v>
       </c>
       <c r="J5">
-        <v>-9.24</v>
+        <v>-9.51</v>
       </c>
       <c r="K5">
-        <v>-12.41</v>
+        <v>-10.97</v>
       </c>
       <c r="L5">
-        <v>-20.57</v>
+        <v>-21.91</v>
       </c>
       <c r="M5">
-        <v>-1.72</v>
+        <v>-1.82</v>
       </c>
       <c r="N5">
         <v>29</v>
@@ -1271,70 +1309,70 @@
         <v>43</v>
       </c>
       <c r="P5">
-        <v>1690.4</v>
+        <v>1678.78</v>
       </c>
       <c r="Q5">
-        <v>1728.12</v>
+        <v>1723.55</v>
       </c>
       <c r="R5">
-        <v>1864.97</v>
+        <v>1857.97</v>
       </c>
       <c r="S5">
-        <v>1862.53</v>
+        <v>1860.69</v>
       </c>
       <c r="T5">
-        <v>-11.14</v>
+        <v>-10.2</v>
       </c>
       <c r="U5" t="s">
         <v>45</v>
       </c>
       <c r="V5" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="W5" t="s">
         <v>45</v>
       </c>
       <c r="X5">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Y5">
-        <v>27.88</v>
+        <v>32.27</v>
       </c>
       <c r="Z5">
-        <v>-48.74</v>
+        <v>-48.39</v>
       </c>
       <c r="AA5">
-        <v>-48.57</v>
+        <v>-48.54</v>
       </c>
       <c r="AB5">
-        <v>-0.17</v>
+        <v>0.14</v>
       </c>
       <c r="AC5">
-        <v>34.09</v>
+        <v>33.72</v>
       </c>
       <c r="AD5">
-        <v>48.02</v>
+        <v>38.4</v>
       </c>
       <c r="AE5">
-        <v>39.25</v>
+        <v>38.97</v>
       </c>
       <c r="AF5">
-        <v>-1.99</v>
+        <v>-46.54</v>
       </c>
       <c r="AG5">
-        <v>1787.25</v>
+        <v>1785.61</v>
       </c>
       <c r="AH5">
-        <v>1668.99</v>
+        <v>1661.49</v>
       </c>
       <c r="AI5">
-        <v>1777.24</v>
+        <v>1770.15</v>
       </c>
       <c r="AJ5" t="s">
         <v>47</v>
       </c>
       <c r="AK5">
-        <v>60.01</v>
+        <v>62.27</v>
       </c>
     </row>
     <row r="6" spans="1:37">
@@ -1345,10 +1383,10 @@
         <v>44</v>
       </c>
       <c r="C6">
-        <v>11175</v>
+        <v>11050</v>
       </c>
       <c r="D6">
-        <v>-1.04</v>
+        <v>-1.12</v>
       </c>
       <c r="E6">
         <v>13144</v>
@@ -1357,46 +1395,46 @@
         <v>8746</v>
       </c>
       <c r="G6">
-        <v>-14.98</v>
+        <v>-15.93</v>
       </c>
       <c r="H6">
-        <v>27.77</v>
+        <v>26.34</v>
       </c>
       <c r="I6">
-        <v>-0.45</v>
+        <v>-1.32</v>
       </c>
       <c r="J6">
-        <v>-0.09</v>
+        <v>-3.49</v>
       </c>
       <c r="K6">
-        <v>5.07</v>
+        <v>3.47</v>
       </c>
       <c r="L6">
-        <v>-11.69</v>
+        <v>-12.34</v>
       </c>
       <c r="M6">
-        <v>20.05</v>
+        <v>19.81</v>
       </c>
       <c r="N6">
         <v>57</v>
       </c>
       <c r="O6">
-        <v>70</v>
+        <v>67</v>
       </c>
       <c r="P6">
-        <v>11181.2</v>
+        <v>11151.6</v>
       </c>
       <c r="Q6">
-        <v>10879.4</v>
+        <v>10886.05</v>
       </c>
       <c r="R6">
-        <v>11111.6</v>
+        <v>11101.02</v>
       </c>
       <c r="S6">
-        <v>10658.86</v>
+        <v>10657.75</v>
       </c>
       <c r="T6">
-        <v>4.84</v>
+        <v>3.68</v>
       </c>
       <c r="U6" t="s">
         <v>45</v>
@@ -1411,34 +1449,34 @@
         <v>2</v>
       </c>
       <c r="Y6">
-        <v>54.18</v>
+        <v>51.06</v>
       </c>
       <c r="Z6">
-        <v>35.83</v>
+        <v>34.01</v>
       </c>
       <c r="AA6">
-        <v>-26.12</v>
+        <v>-14.1</v>
       </c>
       <c r="AB6">
-        <v>61.95</v>
+        <v>48.1</v>
       </c>
       <c r="AC6">
-        <v>75.25</v>
+        <v>76.84999999999999</v>
       </c>
       <c r="AD6">
-        <v>80.59</v>
+        <v>78.34</v>
       </c>
       <c r="AE6">
-        <v>290.81</v>
+        <v>295.25</v>
       </c>
       <c r="AF6">
-        <v>-26.77</v>
+        <v>-18.19</v>
       </c>
       <c r="AG6">
-        <v>11347.8</v>
+        <v>11360.44</v>
       </c>
       <c r="AH6">
-        <v>10411</v>
+        <v>10411.66</v>
       </c>
       <c r="AI6">
         <v>11368.55</v>
@@ -1447,7 +1485,7 @@
         <v>47</v>
       </c>
       <c r="AK6">
-        <v>25.6</v>
+        <v>23.75</v>
       </c>
     </row>
     <row r="7" spans="1:37">
@@ -1458,10 +1496,10 @@
         <v>44</v>
       </c>
       <c r="C7">
-        <v>928.95</v>
+        <v>918.7</v>
       </c>
       <c r="D7">
-        <v>-1.4</v>
+        <v>-1.1</v>
       </c>
       <c r="E7">
         <v>1158.8</v>
@@ -1470,46 +1508,46 @@
         <v>801.55</v>
       </c>
       <c r="G7">
-        <v>-19.84</v>
+        <v>-20.72</v>
       </c>
       <c r="H7">
-        <v>15.89</v>
+        <v>14.62</v>
       </c>
       <c r="I7">
-        <v>-3.76</v>
+        <v>-6.46</v>
       </c>
       <c r="J7">
-        <v>-7.92</v>
+        <v>-11.93</v>
       </c>
       <c r="K7">
-        <v>-10.66</v>
+        <v>-9.289999999999999</v>
       </c>
       <c r="L7">
-        <v>-13.19</v>
+        <v>-15.01</v>
       </c>
       <c r="M7">
-        <v>4.37</v>
+        <v>3.57</v>
       </c>
       <c r="N7">
         <v>43</v>
       </c>
       <c r="O7">
-        <v>53</v>
+        <v>50</v>
       </c>
       <c r="P7">
-        <v>947.3</v>
+        <v>934.62</v>
       </c>
       <c r="Q7">
-        <v>962.85</v>
+        <v>959.6900000000001</v>
       </c>
       <c r="R7">
-        <v>1020.94</v>
+        <v>1017.43</v>
       </c>
       <c r="S7">
-        <v>973.4400000000001</v>
+        <v>973.14</v>
       </c>
       <c r="T7">
-        <v>-4.57</v>
+        <v>-5.59</v>
       </c>
       <c r="U7" t="s">
         <v>45</v>
@@ -1524,43 +1562,43 @@
         <v>1</v>
       </c>
       <c r="Y7">
-        <v>37.99</v>
+        <v>36.17</v>
       </c>
       <c r="Z7">
-        <v>-21.53</v>
+        <v>-22.85</v>
       </c>
       <c r="AA7">
-        <v>-21.03</v>
+        <v>-21.4</v>
       </c>
       <c r="AB7">
-        <v>-0.5</v>
+        <v>-1.45</v>
       </c>
       <c r="AC7">
-        <v>32.53</v>
+        <v>25.78</v>
       </c>
       <c r="AD7">
-        <v>47.19</v>
+        <v>35.08</v>
       </c>
       <c r="AE7">
-        <v>28.64</v>
+        <v>28.22</v>
       </c>
       <c r="AF7">
-        <v>-27.66</v>
+        <v>-54.54</v>
       </c>
       <c r="AG7">
-        <v>999.2</v>
+        <v>999.84</v>
       </c>
       <c r="AH7">
-        <v>926.51</v>
+        <v>919.54</v>
       </c>
       <c r="AI7">
-        <v>1009.35</v>
+        <v>1001.1</v>
       </c>
       <c r="AJ7" t="s">
         <v>47</v>
       </c>
       <c r="AK7">
-        <v>23.31</v>
+        <v>24.75</v>
       </c>
     </row>
     <row r="8" spans="1:37">
@@ -1571,10 +1609,10 @@
         <v>44</v>
       </c>
       <c r="C8">
-        <v>143.06</v>
+        <v>146.07</v>
       </c>
       <c r="D8">
-        <v>-6.73</v>
+        <v>2.1</v>
       </c>
       <c r="E8">
         <v>185.92</v>
@@ -1583,46 +1621,46 @@
         <v>115.96</v>
       </c>
       <c r="G8">
-        <v>-23.05</v>
+        <v>-21.43</v>
       </c>
       <c r="H8">
-        <v>23.37</v>
+        <v>25.97</v>
       </c>
       <c r="I8">
-        <v>-16.02</v>
+        <v>-15.07</v>
       </c>
       <c r="J8">
-        <v>1.17</v>
+        <v>-7.03</v>
       </c>
       <c r="K8">
-        <v>3.26</v>
+        <v>5.54</v>
       </c>
       <c r="L8">
-        <v>11</v>
+        <v>14.44</v>
       </c>
       <c r="M8">
-        <v>2.46</v>
+        <v>3.01</v>
       </c>
       <c r="N8">
         <v>99</v>
       </c>
       <c r="O8">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="P8">
-        <v>157.94</v>
+        <v>152.76</v>
       </c>
       <c r="Q8">
-        <v>170.39</v>
+        <v>169.93</v>
       </c>
       <c r="R8">
-        <v>150.37</v>
+        <v>150.58</v>
       </c>
       <c r="S8">
-        <v>137.71</v>
+        <v>137.76</v>
       </c>
       <c r="T8">
-        <v>3.88</v>
+        <v>6.04</v>
       </c>
       <c r="U8" t="s">
         <v>46</v>
@@ -1637,43 +1675,43 @@
         <v>3</v>
       </c>
       <c r="Y8">
-        <v>34.82</v>
+        <v>37.94</v>
       </c>
       <c r="Z8">
-        <v>1.48</v>
+        <v>0.02</v>
       </c>
       <c r="AA8">
-        <v>6.1</v>
+        <v>4.88</v>
       </c>
       <c r="AB8">
-        <v>-4.62</v>
+        <v>-4.86</v>
       </c>
       <c r="AC8">
-        <v>0</v>
+        <v>2.42</v>
       </c>
       <c r="AD8">
-        <v>0.5600000000000001</v>
+        <v>0.8100000000000001</v>
       </c>
       <c r="AE8">
-        <v>8.48</v>
+        <v>8.52</v>
       </c>
       <c r="AF8">
-        <v>3.62</v>
+        <v>-74.67</v>
       </c>
       <c r="AG8">
-        <v>192.23</v>
+        <v>193.43</v>
       </c>
       <c r="AH8">
-        <v>148.55</v>
+        <v>146.43</v>
       </c>
       <c r="AI8">
-        <v>172.56</v>
+        <v>170.73</v>
       </c>
       <c r="AJ8" t="s">
         <v>47</v>
       </c>
       <c r="AK8">
-        <v>37.93</v>
+        <v>41.02</v>
       </c>
     </row>
   </sheetData>
@@ -1814,7 +1852,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:F62"/>
+  <dimension ref="A1:F63"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="16.7109375" customWidth="1"/>
@@ -1834,991 +1872,1046 @@
     </row>
     <row r="2" spans="1:6">
       <c r="A2" s="3" t="s">
+        <v>0</v>
+      </c>
+      <c r="B2" s="3" t="s">
         <v>49</v>
       </c>
-    </row>
-    <row r="5" spans="1:6">
-      <c r="A5" s="2" t="s">
+      <c r="C2" s="3" t="s">
         <v>50</v>
       </c>
-      <c r="B5" s="2"/>
-      <c r="C5" s="2"/>
-      <c r="D5" s="2"/>
-      <c r="E5" s="2"/>
+      <c r="D2" s="3" t="s">
+        <v>51</v>
+      </c>
+      <c r="E2" s="3" t="s">
+        <v>52</v>
+      </c>
+      <c r="F2" s="3" t="s">
+        <v>53</v>
+      </c>
+    </row>
+    <row r="3" spans="1:6">
+      <c r="A3" s="4" t="s">
+        <v>40</v>
+      </c>
+      <c r="B3" s="4" t="s">
+        <v>54</v>
+      </c>
+      <c r="C3" s="4" t="s">
+        <v>55</v>
+      </c>
+      <c r="D3" s="4" t="s">
+        <v>56</v>
+      </c>
+      <c r="E3" s="4" t="s">
+        <v>57</v>
+      </c>
+      <c r="F3" s="4" t="s">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="4" spans="1:6">
+      <c r="A4" s="5" t="s">
+        <v>40</v>
+      </c>
+      <c r="B4" s="5" t="s">
+        <v>59</v>
+      </c>
+      <c r="C4" s="5" t="s">
+        <v>60</v>
+      </c>
+      <c r="D4" s="5" t="s">
+        <v>61</v>
+      </c>
+      <c r="E4" s="5" t="s">
+        <v>46</v>
+      </c>
+      <c r="F4" s="5" t="s">
+        <v>45</v>
+      </c>
     </row>
     <row r="6" spans="1:6">
-      <c r="A6" s="4" t="s">
-        <v>0</v>
-      </c>
-      <c r="B6" s="4" t="s">
-        <v>51</v>
-      </c>
-      <c r="C6" s="4" t="s">
-        <v>52</v>
-      </c>
-      <c r="D6" s="4" t="s">
-        <v>53</v>
-      </c>
-      <c r="E6" s="4" t="s">
-        <v>54</v>
-      </c>
+      <c r="A6" s="2" t="s">
+        <v>62</v>
+      </c>
+      <c r="B6" s="2"/>
+      <c r="C6" s="2"/>
+      <c r="D6" s="2"/>
+      <c r="E6" s="2"/>
     </row>
     <row r="7" spans="1:6">
       <c r="A7" s="3" t="s">
+        <v>0</v>
+      </c>
+      <c r="B7" s="3" t="s">
+        <v>63</v>
+      </c>
+      <c r="C7" s="3" t="s">
+        <v>64</v>
+      </c>
+      <c r="D7" s="3" t="s">
+        <v>65</v>
+      </c>
+      <c r="E7" s="3" t="s">
+        <v>66</v>
+      </c>
+    </row>
+    <row r="8" spans="1:6">
+      <c r="A8" s="6" t="s">
         <v>37</v>
       </c>
-      <c r="B7" s="3" t="s">
+      <c r="B8" s="6" t="s">
         <v>9</v>
       </c>
-      <c r="C7" s="5">
-        <v>-11.39</v>
-      </c>
-      <c r="D7" s="5">
+      <c r="C8" s="7">
         <v>-11.36</v>
       </c>
-      <c r="E7" s="6">
-        <v>0.03</v>
-      </c>
-    </row>
-    <row r="8" spans="1:6">
-      <c r="A8" s="3" t="s">
+      <c r="D8" s="7">
+        <v>-11.66</v>
+      </c>
+      <c r="E8" s="8">
+        <v>-0.3</v>
+      </c>
+    </row>
+    <row r="9" spans="1:6">
+      <c r="A9" s="6" t="s">
         <v>38</v>
       </c>
-      <c r="B8" s="3" t="s">
+      <c r="B9" s="6" t="s">
         <v>9</v>
       </c>
-      <c r="C8" s="5">
-        <v>-19.29</v>
-      </c>
-      <c r="D8" s="5">
+      <c r="C9" s="7">
         <v>-22.73</v>
       </c>
-      <c r="E8" s="7">
-        <v>-3.44</v>
-      </c>
-    </row>
-    <row r="9" spans="1:6">
-      <c r="A9" s="3" t="s">
+      <c r="D9" s="7">
+        <v>-23.43</v>
+      </c>
+      <c r="E9" s="8">
+        <v>-0.7</v>
+      </c>
+    </row>
+    <row r="10" spans="1:6">
+      <c r="A10" s="6" t="s">
         <v>39</v>
       </c>
-      <c r="B9" s="3" t="s">
+      <c r="B10" s="6" t="s">
         <v>9</v>
       </c>
-      <c r="C9" s="5">
-        <v>-14.48</v>
-      </c>
-      <c r="D9" s="5">
+      <c r="C10" s="7">
         <v>-13.99</v>
       </c>
-      <c r="E9" s="6">
-        <v>0.49</v>
-      </c>
-    </row>
-    <row r="10" spans="1:6">
-      <c r="A10" s="3" t="s">
+      <c r="D10" s="7">
+        <v>-16.32</v>
+      </c>
+      <c r="E10" s="8">
+        <v>-2.33</v>
+      </c>
+    </row>
+    <row r="11" spans="1:6">
+      <c r="A11" s="6" t="s">
         <v>40</v>
       </c>
-      <c r="B10" s="3" t="s">
+      <c r="B11" s="6" t="s">
         <v>9</v>
       </c>
-      <c r="C10" s="5">
+      <c r="C11" s="7">
+        <v>-9.24</v>
+      </c>
+      <c r="D11" s="7">
+        <v>-9.51</v>
+      </c>
+      <c r="E11" s="8">
+        <v>-0.27</v>
+      </c>
+    </row>
+    <row r="12" spans="1:6">
+      <c r="A12" s="6" t="s">
+        <v>41</v>
+      </c>
+      <c r="B12" s="6" t="s">
+        <v>9</v>
+      </c>
+      <c r="C12" s="7">
+        <v>-0.09</v>
+      </c>
+      <c r="D12" s="7">
+        <v>-3.49</v>
+      </c>
+      <c r="E12" s="8">
+        <v>-3.4</v>
+      </c>
+    </row>
+    <row r="13" spans="1:6">
+      <c r="A13" s="6" t="s">
+        <v>42</v>
+      </c>
+      <c r="B13" s="6" t="s">
+        <v>9</v>
+      </c>
+      <c r="C13" s="7">
+        <v>-7.92</v>
+      </c>
+      <c r="D13" s="7">
+        <v>-11.93</v>
+      </c>
+      <c r="E13" s="8">
+        <v>-4.01</v>
+      </c>
+    </row>
+    <row r="14" spans="1:6">
+      <c r="A14" s="6" t="s">
+        <v>43</v>
+      </c>
+      <c r="B14" s="6" t="s">
+        <v>9</v>
+      </c>
+      <c r="C14" s="7">
+        <v>1.17</v>
+      </c>
+      <c r="D14" s="7">
+        <v>-7.03</v>
+      </c>
+      <c r="E14" s="8">
+        <v>-8.199999999999999</v>
+      </c>
+    </row>
+    <row r="15" spans="1:6">
+      <c r="A15" s="6" t="s">
+        <v>37</v>
+      </c>
+      <c r="B15" s="6" t="s">
+        <v>8</v>
+      </c>
+      <c r="C15" s="7">
+        <v>-3.01</v>
+      </c>
+      <c r="D15" s="7">
+        <v>-3.21</v>
+      </c>
+      <c r="E15" s="8">
+        <v>-0.2</v>
+      </c>
+    </row>
+    <row r="16" spans="1:6">
+      <c r="A16" s="6" t="s">
+        <v>38</v>
+      </c>
+      <c r="B16" s="6" t="s">
+        <v>8</v>
+      </c>
+      <c r="C16" s="7">
+        <v>-15.27</v>
+      </c>
+      <c r="D16" s="7">
+        <v>-17.93</v>
+      </c>
+      <c r="E16" s="8">
+        <v>-2.66</v>
+      </c>
+    </row>
+    <row r="17" spans="1:5">
+      <c r="A17" s="6" t="s">
+        <v>39</v>
+      </c>
+      <c r="B17" s="6" t="s">
+        <v>8</v>
+      </c>
+      <c r="C17" s="7">
         <v>-9.289999999999999</v>
       </c>
-      <c r="D10" s="5">
-        <v>-9.24</v>
-      </c>
-      <c r="E10" s="6">
-        <v>0.05</v>
-      </c>
-    </row>
-    <row r="11" spans="1:6">
-      <c r="A11" s="3" t="s">
+      <c r="D17" s="7">
+        <v>-8.51</v>
+      </c>
+      <c r="E17" s="9">
+        <v>0.78</v>
+      </c>
+    </row>
+    <row r="18" spans="1:5">
+      <c r="A18" s="6" t="s">
+        <v>40</v>
+      </c>
+      <c r="B18" s="6" t="s">
+        <v>8</v>
+      </c>
+      <c r="C18" s="7">
+        <v>-4.45</v>
+      </c>
+      <c r="D18" s="7">
+        <v>-3.36</v>
+      </c>
+      <c r="E18" s="9">
+        <v>1.09</v>
+      </c>
+    </row>
+    <row r="19" spans="1:5">
+      <c r="A19" s="6" t="s">
         <v>41</v>
       </c>
-      <c r="B11" s="3" t="s">
-        <v>9</v>
-      </c>
-      <c r="C11" s="5">
-        <v>-1.02</v>
-      </c>
-      <c r="D11" s="5">
-        <v>-0.09</v>
-      </c>
-      <c r="E11" s="6">
-        <v>0.93</v>
-      </c>
-    </row>
-    <row r="12" spans="1:6">
-      <c r="A12" s="3" t="s">
+      <c r="B19" s="6" t="s">
+        <v>8</v>
+      </c>
+      <c r="C19" s="7">
+        <v>-0.45</v>
+      </c>
+      <c r="D19" s="7">
+        <v>-1.32</v>
+      </c>
+      <c r="E19" s="8">
+        <v>-0.87</v>
+      </c>
+    </row>
+    <row r="20" spans="1:5">
+      <c r="A20" s="6" t="s">
         <v>42</v>
       </c>
-      <c r="B12" s="3" t="s">
-        <v>9</v>
-      </c>
-      <c r="C12" s="5">
-        <v>-7.75</v>
-      </c>
-      <c r="D12" s="5">
-        <v>-7.92</v>
-      </c>
-      <c r="E12" s="7">
-        <v>-0.17</v>
-      </c>
-    </row>
-    <row r="13" spans="1:6">
-      <c r="A13" s="3" t="s">
+      <c r="B20" s="6" t="s">
+        <v>8</v>
+      </c>
+      <c r="C20" s="7">
+        <v>-3.76</v>
+      </c>
+      <c r="D20" s="7">
+        <v>-6.46</v>
+      </c>
+      <c r="E20" s="8">
+        <v>-2.7</v>
+      </c>
+    </row>
+    <row r="21" spans="1:5">
+      <c r="A21" s="6" t="s">
         <v>43</v>
       </c>
-      <c r="B13" s="3" t="s">
-        <v>9</v>
-      </c>
-      <c r="C13" s="5">
-        <v>12.75</v>
-      </c>
-      <c r="D13" s="5">
-        <v>1.17</v>
-      </c>
-      <c r="E13" s="7">
-        <v>-11.58</v>
-      </c>
-    </row>
-    <row r="14" spans="1:6">
-      <c r="A14" s="3" t="s">
+      <c r="B21" s="6" t="s">
+        <v>8</v>
+      </c>
+      <c r="C21" s="7">
+        <v>-16.02</v>
+      </c>
+      <c r="D21" s="7">
+        <v>-15.07</v>
+      </c>
+      <c r="E21" s="9">
+        <v>0.95</v>
+      </c>
+    </row>
+    <row r="22" spans="1:5">
+      <c r="A22" s="6" t="s">
         <v>37</v>
       </c>
-      <c r="B14" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="C14" s="5">
-        <v>-0.93</v>
-      </c>
-      <c r="D14" s="5">
-        <v>-3.01</v>
-      </c>
-      <c r="E14" s="7">
-        <v>-2.08</v>
-      </c>
-    </row>
-    <row r="15" spans="1:6">
-      <c r="A15" s="3" t="s">
+      <c r="B22" s="6" t="s">
+        <v>11</v>
+      </c>
+      <c r="C22" s="7">
+        <v>11.62</v>
+      </c>
+      <c r="D22" s="7">
+        <v>11.93</v>
+      </c>
+      <c r="E22" s="9">
+        <v>0.31</v>
+      </c>
+    </row>
+    <row r="23" spans="1:5">
+      <c r="A23" s="6" t="s">
         <v>38</v>
       </c>
-      <c r="B15" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="C15" s="5">
-        <v>-20.03</v>
-      </c>
-      <c r="D15" s="5">
-        <v>-15.27</v>
-      </c>
-      <c r="E15" s="6">
-        <v>4.76</v>
-      </c>
-    </row>
-    <row r="16" spans="1:6">
-      <c r="A16" s="3" t="s">
+      <c r="B23" s="6" t="s">
+        <v>11</v>
+      </c>
+      <c r="C23" s="7">
+        <v>47.42</v>
+      </c>
+      <c r="D23" s="7">
+        <v>44.16</v>
+      </c>
+      <c r="E23" s="8">
+        <v>-3.26</v>
+      </c>
+    </row>
+    <row r="24" spans="1:5">
+      <c r="A24" s="6" t="s">
         <v>39</v>
       </c>
-      <c r="B16" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="C16" s="5">
-        <v>-8.710000000000001</v>
-      </c>
-      <c r="D16" s="5">
+      <c r="B24" s="6" t="s">
+        <v>11</v>
+      </c>
+      <c r="C24" s="7">
+        <v>-48.46</v>
+      </c>
+      <c r="D24" s="7">
+        <v>-48.8</v>
+      </c>
+      <c r="E24" s="8">
+        <v>-0.34</v>
+      </c>
+    </row>
+    <row r="25" spans="1:5">
+      <c r="A25" s="6" t="s">
+        <v>40</v>
+      </c>
+      <c r="B25" s="6" t="s">
+        <v>11</v>
+      </c>
+      <c r="C25" s="7">
+        <v>-20.57</v>
+      </c>
+      <c r="D25" s="7">
+        <v>-21.91</v>
+      </c>
+      <c r="E25" s="8">
+        <v>-1.34</v>
+      </c>
+    </row>
+    <row r="26" spans="1:5">
+      <c r="A26" s="6" t="s">
+        <v>41</v>
+      </c>
+      <c r="B26" s="6" t="s">
+        <v>11</v>
+      </c>
+      <c r="C26" s="7">
+        <v>-11.69</v>
+      </c>
+      <c r="D26" s="7">
+        <v>-12.34</v>
+      </c>
+      <c r="E26" s="8">
+        <v>-0.65</v>
+      </c>
+    </row>
+    <row r="27" spans="1:5">
+      <c r="A27" s="6" t="s">
+        <v>42</v>
+      </c>
+      <c r="B27" s="6" t="s">
+        <v>11</v>
+      </c>
+      <c r="C27" s="7">
+        <v>-13.19</v>
+      </c>
+      <c r="D27" s="7">
+        <v>-15.01</v>
+      </c>
+      <c r="E27" s="8">
+        <v>-1.82</v>
+      </c>
+    </row>
+    <row r="28" spans="1:5">
+      <c r="A28" s="6" t="s">
+        <v>43</v>
+      </c>
+      <c r="B28" s="6" t="s">
+        <v>11</v>
+      </c>
+      <c r="C28" s="7">
+        <v>11</v>
+      </c>
+      <c r="D28" s="7">
+        <v>14.44</v>
+      </c>
+      <c r="E28" s="9">
+        <v>3.44</v>
+      </c>
+    </row>
+    <row r="29" spans="1:5">
+      <c r="A29" s="6" t="s">
+        <v>37</v>
+      </c>
+      <c r="B29" s="6" t="s">
+        <v>10</v>
+      </c>
+      <c r="C29" s="7">
+        <v>-10.74</v>
+      </c>
+      <c r="D29" s="7">
+        <v>-9.51</v>
+      </c>
+      <c r="E29" s="9">
+        <v>1.23</v>
+      </c>
+    </row>
+    <row r="30" spans="1:5">
+      <c r="A30" s="6" t="s">
+        <v>38</v>
+      </c>
+      <c r="B30" s="6" t="s">
+        <v>10</v>
+      </c>
+      <c r="C30" s="7">
+        <v>-28.59</v>
+      </c>
+      <c r="D30" s="7">
+        <v>-29.55</v>
+      </c>
+      <c r="E30" s="8">
+        <v>-0.96</v>
+      </c>
+    </row>
+    <row r="31" spans="1:5">
+      <c r="A31" s="6" t="s">
+        <v>39</v>
+      </c>
+      <c r="B31" s="6" t="s">
+        <v>10</v>
+      </c>
+      <c r="C31" s="7">
+        <v>-14.71</v>
+      </c>
+      <c r="D31" s="7">
+        <v>-16.19</v>
+      </c>
+      <c r="E31" s="8">
+        <v>-1.48</v>
+      </c>
+    </row>
+    <row r="32" spans="1:5">
+      <c r="A32" s="6" t="s">
+        <v>40</v>
+      </c>
+      <c r="B32" s="6" t="s">
+        <v>10</v>
+      </c>
+      <c r="C32" s="7">
+        <v>-12.41</v>
+      </c>
+      <c r="D32" s="7">
+        <v>-10.97</v>
+      </c>
+      <c r="E32" s="9">
+        <v>1.44</v>
+      </c>
+    </row>
+    <row r="33" spans="1:5">
+      <c r="A33" s="6" t="s">
+        <v>41</v>
+      </c>
+      <c r="B33" s="6" t="s">
+        <v>10</v>
+      </c>
+      <c r="C33" s="7">
+        <v>5.07</v>
+      </c>
+      <c r="D33" s="7">
+        <v>3.47</v>
+      </c>
+      <c r="E33" s="8">
+        <v>-1.6</v>
+      </c>
+    </row>
+    <row r="34" spans="1:5">
+      <c r="A34" s="6" t="s">
+        <v>42</v>
+      </c>
+      <c r="B34" s="6" t="s">
+        <v>10</v>
+      </c>
+      <c r="C34" s="7">
+        <v>-10.66</v>
+      </c>
+      <c r="D34" s="7">
         <v>-9.289999999999999</v>
       </c>
-      <c r="E16" s="7">
-        <v>-0.58</v>
-      </c>
-    </row>
-    <row r="17" spans="1:5">
-      <c r="A17" s="3" t="s">
+      <c r="E34" s="9">
+        <v>1.37</v>
+      </c>
+    </row>
+    <row r="35" spans="1:5">
+      <c r="A35" s="6" t="s">
+        <v>43</v>
+      </c>
+      <c r="B35" s="6" t="s">
+        <v>10</v>
+      </c>
+      <c r="C35" s="7">
+        <v>3.26</v>
+      </c>
+      <c r="D35" s="7">
+        <v>5.54</v>
+      </c>
+      <c r="E35" s="9">
+        <v>2.28</v>
+      </c>
+    </row>
+    <row r="36" spans="1:5">
+      <c r="A36" s="6" t="s">
+        <v>37</v>
+      </c>
+      <c r="B36" s="6" t="s">
+        <v>6</v>
+      </c>
+      <c r="C36" s="7">
+        <v>-18.52</v>
+      </c>
+      <c r="D36" s="7">
+        <v>-18.53</v>
+      </c>
+      <c r="E36" s="8">
+        <v>-0.01</v>
+      </c>
+    </row>
+    <row r="37" spans="1:5">
+      <c r="A37" s="6" t="s">
+        <v>38</v>
+      </c>
+      <c r="B37" s="6" t="s">
+        <v>6</v>
+      </c>
+      <c r="C37" s="7">
+        <v>-40.78</v>
+      </c>
+      <c r="D37" s="7">
+        <v>-42.21</v>
+      </c>
+      <c r="E37" s="8">
+        <v>-1.43</v>
+      </c>
+    </row>
+    <row r="38" spans="1:5">
+      <c r="A38" s="6" t="s">
+        <v>39</v>
+      </c>
+      <c r="B38" s="6" t="s">
+        <v>6</v>
+      </c>
+      <c r="C38" s="7">
+        <v>-48.69</v>
+      </c>
+      <c r="D38" s="7">
+        <v>-49.16</v>
+      </c>
+      <c r="E38" s="8">
+        <v>-0.47</v>
+      </c>
+    </row>
+    <row r="39" spans="1:5">
+      <c r="A39" s="6" t="s">
         <v>40</v>
       </c>
-      <c r="B17" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="C17" s="5">
-        <v>-2.54</v>
-      </c>
-      <c r="D17" s="5">
-        <v>-4.45</v>
-      </c>
-      <c r="E17" s="7">
-        <v>-1.91</v>
-      </c>
-    </row>
-    <row r="18" spans="1:5">
-      <c r="A18" s="3" t="s">
+      <c r="B39" s="6" t="s">
+        <v>6</v>
+      </c>
+      <c r="C39" s="7">
+        <v>-23.96</v>
+      </c>
+      <c r="D39" s="7">
+        <v>-23.23</v>
+      </c>
+      <c r="E39" s="9">
+        <v>0.73</v>
+      </c>
+    </row>
+    <row r="40" spans="1:5">
+      <c r="A40" s="6" t="s">
         <v>41</v>
       </c>
-      <c r="B18" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="C18" s="5">
-        <v>4.82</v>
-      </c>
-      <c r="D18" s="5">
-        <v>-0.45</v>
-      </c>
-      <c r="E18" s="7">
-        <v>-5.27</v>
-      </c>
-    </row>
-    <row r="19" spans="1:5">
-      <c r="A19" s="3" t="s">
+      <c r="B40" s="6" t="s">
+        <v>6</v>
+      </c>
+      <c r="C40" s="7">
+        <v>-14.98</v>
+      </c>
+      <c r="D40" s="7">
+        <v>-15.93</v>
+      </c>
+      <c r="E40" s="8">
+        <v>-0.95</v>
+      </c>
+    </row>
+    <row r="41" spans="1:5">
+      <c r="A41" s="6" t="s">
         <v>42</v>
       </c>
-      <c r="B19" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="C19" s="5">
-        <v>-1.56</v>
-      </c>
-      <c r="D19" s="5">
+      <c r="B41" s="6" t="s">
+        <v>6</v>
+      </c>
+      <c r="C41" s="7">
+        <v>-19.84</v>
+      </c>
+      <c r="D41" s="7">
+        <v>-20.72</v>
+      </c>
+      <c r="E41" s="8">
+        <v>-0.88</v>
+      </c>
+    </row>
+    <row r="42" spans="1:5">
+      <c r="A42" s="6" t="s">
+        <v>43</v>
+      </c>
+      <c r="B42" s="6" t="s">
+        <v>6</v>
+      </c>
+      <c r="C42" s="7">
+        <v>-23.05</v>
+      </c>
+      <c r="D42" s="7">
+        <v>-21.43</v>
+      </c>
+      <c r="E42" s="9">
+        <v>1.62</v>
+      </c>
+    </row>
+    <row r="43" spans="1:5">
+      <c r="A43" s="6" t="s">
+        <v>37</v>
+      </c>
+      <c r="B43" s="6" t="s">
+        <v>2</v>
+      </c>
+      <c r="C43" s="7">
+        <v>10072</v>
+      </c>
+      <c r="D43" s="7">
+        <v>10071</v>
+      </c>
+      <c r="E43" s="8">
+        <v>-1</v>
+      </c>
+    </row>
+    <row r="44" spans="1:5">
+      <c r="A44" s="6" t="s">
+        <v>38</v>
+      </c>
+      <c r="B44" s="6" t="s">
+        <v>2</v>
+      </c>
+      <c r="C44" s="7">
+        <v>396.95</v>
+      </c>
+      <c r="D44" s="7">
+        <v>387.35</v>
+      </c>
+      <c r="E44" s="8">
+        <v>-9.6</v>
+      </c>
+    </row>
+    <row r="45" spans="1:5">
+      <c r="A45" s="6" t="s">
+        <v>39</v>
+      </c>
+      <c r="B45" s="6" t="s">
+        <v>2</v>
+      </c>
+      <c r="C45" s="7">
+        <v>278.2</v>
+      </c>
+      <c r="D45" s="7">
+        <v>275.65</v>
+      </c>
+      <c r="E45" s="8">
+        <v>-2.55</v>
+      </c>
+    </row>
+    <row r="46" spans="1:5">
+      <c r="A46" s="6" t="s">
+        <v>40</v>
+      </c>
+      <c r="B46" s="6" t="s">
+        <v>2</v>
+      </c>
+      <c r="C46" s="7">
+        <v>1655</v>
+      </c>
+      <c r="D46" s="7">
+        <v>1670.9</v>
+      </c>
+      <c r="E46" s="9">
+        <v>15.9</v>
+      </c>
+    </row>
+    <row r="47" spans="1:5">
+      <c r="A47" s="6" t="s">
+        <v>41</v>
+      </c>
+      <c r="B47" s="6" t="s">
+        <v>2</v>
+      </c>
+      <c r="C47" s="7">
+        <v>11175</v>
+      </c>
+      <c r="D47" s="7">
+        <v>11050</v>
+      </c>
+      <c r="E47" s="8">
+        <v>-125</v>
+      </c>
+    </row>
+    <row r="48" spans="1:5">
+      <c r="A48" s="6" t="s">
+        <v>42</v>
+      </c>
+      <c r="B48" s="6" t="s">
+        <v>2</v>
+      </c>
+      <c r="C48" s="7">
+        <v>928.95</v>
+      </c>
+      <c r="D48" s="7">
+        <v>918.7</v>
+      </c>
+      <c r="E48" s="8">
+        <v>-10.25</v>
+      </c>
+    </row>
+    <row r="49" spans="1:5">
+      <c r="A49" s="6" t="s">
+        <v>43</v>
+      </c>
+      <c r="B49" s="6" t="s">
+        <v>2</v>
+      </c>
+      <c r="C49" s="7">
+        <v>143.06</v>
+      </c>
+      <c r="D49" s="7">
+        <v>146.07</v>
+      </c>
+      <c r="E49" s="9">
+        <v>3.01</v>
+      </c>
+    </row>
+    <row r="50" spans="1:5">
+      <c r="A50" s="6" t="s">
+        <v>37</v>
+      </c>
+      <c r="B50" s="6" t="s">
+        <v>24</v>
+      </c>
+      <c r="C50" s="7">
+        <v>37.32</v>
+      </c>
+      <c r="D50" s="7">
+        <v>37.3</v>
+      </c>
+      <c r="E50" s="8">
+        <v>-0.02</v>
+      </c>
+    </row>
+    <row r="51" spans="1:5">
+      <c r="A51" s="6" t="s">
+        <v>38</v>
+      </c>
+      <c r="B51" s="6" t="s">
+        <v>24</v>
+      </c>
+      <c r="C51" s="7">
+        <v>28.28</v>
+      </c>
+      <c r="D51" s="7">
+        <v>26.88</v>
+      </c>
+      <c r="E51" s="8">
+        <v>-1.4</v>
+      </c>
+    </row>
+    <row r="52" spans="1:5">
+      <c r="A52" s="6" t="s">
+        <v>39</v>
+      </c>
+      <c r="B52" s="6" t="s">
+        <v>24</v>
+      </c>
+      <c r="C52" s="7">
+        <v>26.38</v>
+      </c>
+      <c r="D52" s="7">
+        <v>25.28</v>
+      </c>
+      <c r="E52" s="8">
+        <v>-1.1</v>
+      </c>
+    </row>
+    <row r="53" spans="1:5">
+      <c r="A53" s="6" t="s">
+        <v>40</v>
+      </c>
+      <c r="B53" s="6" t="s">
+        <v>24</v>
+      </c>
+      <c r="C53" s="7">
+        <v>27.88</v>
+      </c>
+      <c r="D53" s="7">
+        <v>32.27</v>
+      </c>
+      <c r="E53" s="9">
+        <v>4.39</v>
+      </c>
+    </row>
+    <row r="54" spans="1:5">
+      <c r="A54" s="6" t="s">
+        <v>41</v>
+      </c>
+      <c r="B54" s="6" t="s">
+        <v>24</v>
+      </c>
+      <c r="C54" s="7">
+        <v>54.18</v>
+      </c>
+      <c r="D54" s="7">
+        <v>51.06</v>
+      </c>
+      <c r="E54" s="8">
+        <v>-3.12</v>
+      </c>
+    </row>
+    <row r="55" spans="1:5">
+      <c r="A55" s="6" t="s">
+        <v>42</v>
+      </c>
+      <c r="B55" s="6" t="s">
+        <v>24</v>
+      </c>
+      <c r="C55" s="7">
+        <v>37.99</v>
+      </c>
+      <c r="D55" s="7">
+        <v>36.17</v>
+      </c>
+      <c r="E55" s="8">
+        <v>-1.82</v>
+      </c>
+    </row>
+    <row r="56" spans="1:5">
+      <c r="A56" s="6" t="s">
+        <v>43</v>
+      </c>
+      <c r="B56" s="6" t="s">
+        <v>24</v>
+      </c>
+      <c r="C56" s="7">
+        <v>34.82</v>
+      </c>
+      <c r="D56" s="7">
+        <v>37.94</v>
+      </c>
+      <c r="E56" s="9">
+        <v>3.12</v>
+      </c>
+    </row>
+    <row r="57" spans="1:5">
+      <c r="A57" s="6" t="s">
+        <v>37</v>
+      </c>
+      <c r="B57" s="6" t="s">
+        <v>31</v>
+      </c>
+      <c r="C57" s="7">
+        <v>-16.35</v>
+      </c>
+      <c r="D57" s="7">
+        <v>-40.81</v>
+      </c>
+      <c r="E57" s="8">
+        <v>-24.46</v>
+      </c>
+    </row>
+    <row r="58" spans="1:5">
+      <c r="A58" s="6" t="s">
+        <v>38</v>
+      </c>
+      <c r="B58" s="6" t="s">
+        <v>31</v>
+      </c>
+      <c r="C58" s="7">
+        <v>-35.24</v>
+      </c>
+      <c r="D58" s="7">
         <v>-3.76</v>
       </c>
-      <c r="E19" s="7">
-        <v>-2.2</v>
-      </c>
-    </row>
-    <row r="20" spans="1:5">
-      <c r="A20" s="3" t="s">
+      <c r="E58" s="9">
+        <v>31.48</v>
+      </c>
+    </row>
+    <row r="59" spans="1:5">
+      <c r="A59" s="6" t="s">
+        <v>39</v>
+      </c>
+      <c r="B59" s="6" t="s">
+        <v>31</v>
+      </c>
+      <c r="C59" s="7">
+        <v>-65.54000000000001</v>
+      </c>
+      <c r="D59" s="7">
+        <v>-78.95999999999999</v>
+      </c>
+      <c r="E59" s="8">
+        <v>-13.42</v>
+      </c>
+    </row>
+    <row r="60" spans="1:5">
+      <c r="A60" s="6" t="s">
+        <v>40</v>
+      </c>
+      <c r="B60" s="6" t="s">
+        <v>31</v>
+      </c>
+      <c r="C60" s="7">
+        <v>-1.99</v>
+      </c>
+      <c r="D60" s="7">
+        <v>-46.54</v>
+      </c>
+      <c r="E60" s="8">
+        <v>-44.55</v>
+      </c>
+    </row>
+    <row r="61" spans="1:5">
+      <c r="A61" s="6" t="s">
+        <v>41</v>
+      </c>
+      <c r="B61" s="6" t="s">
+        <v>31</v>
+      </c>
+      <c r="C61" s="7">
+        <v>-26.77</v>
+      </c>
+      <c r="D61" s="7">
+        <v>-18.19</v>
+      </c>
+      <c r="E61" s="9">
+        <v>8.58</v>
+      </c>
+    </row>
+    <row r="62" spans="1:5">
+      <c r="A62" s="6" t="s">
+        <v>42</v>
+      </c>
+      <c r="B62" s="6" t="s">
+        <v>31</v>
+      </c>
+      <c r="C62" s="7">
+        <v>-27.66</v>
+      </c>
+      <c r="D62" s="7">
+        <v>-54.54</v>
+      </c>
+      <c r="E62" s="8">
+        <v>-26.88</v>
+      </c>
+    </row>
+    <row r="63" spans="1:5">
+      <c r="A63" s="6" t="s">
         <v>43</v>
       </c>
-      <c r="B20" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="C20" s="5">
-        <v>-12.36</v>
-      </c>
-      <c r="D20" s="5">
-        <v>-16.02</v>
-      </c>
-      <c r="E20" s="7">
-        <v>-3.66</v>
-      </c>
-    </row>
-    <row r="21" spans="1:5">
-      <c r="A21" s="3" t="s">
-        <v>37</v>
-      </c>
-      <c r="B21" s="3" t="s">
-        <v>11</v>
-      </c>
-      <c r="C21" s="5">
-        <v>12.53</v>
-      </c>
-      <c r="D21" s="5">
-        <v>11.62</v>
-      </c>
-      <c r="E21" s="7">
-        <v>-0.91</v>
-      </c>
-    </row>
-    <row r="22" spans="1:5">
-      <c r="A22" s="3" t="s">
-        <v>38</v>
-      </c>
-      <c r="B22" s="3" t="s">
-        <v>11</v>
-      </c>
-      <c r="C22" s="5">
-        <v>56.89</v>
-      </c>
-      <c r="D22" s="5">
-        <v>47.42</v>
-      </c>
-      <c r="E22" s="7">
-        <v>-9.470000000000001</v>
-      </c>
-    </row>
-    <row r="23" spans="1:5">
-      <c r="A23" s="3" t="s">
-        <v>39</v>
-      </c>
-      <c r="B23" s="3" t="s">
-        <v>11</v>
-      </c>
-      <c r="C23" s="5">
-        <v>-48.67</v>
-      </c>
-      <c r="D23" s="5">
-        <v>-48.46</v>
-      </c>
-      <c r="E23" s="6">
-        <v>0.21</v>
-      </c>
-    </row>
-    <row r="24" spans="1:5">
-      <c r="A24" s="3" t="s">
-        <v>40</v>
-      </c>
-      <c r="B24" s="3" t="s">
-        <v>11</v>
-      </c>
-      <c r="C24" s="5">
-        <v>-19.72</v>
-      </c>
-      <c r="D24" s="5">
-        <v>-20.57</v>
-      </c>
-      <c r="E24" s="7">
-        <v>-0.85</v>
-      </c>
-    </row>
-    <row r="25" spans="1:5">
-      <c r="A25" s="3" t="s">
-        <v>41</v>
-      </c>
-      <c r="B25" s="3" t="s">
-        <v>11</v>
-      </c>
-      <c r="C25" s="5">
-        <v>-9.66</v>
-      </c>
-      <c r="D25" s="5">
-        <v>-11.69</v>
-      </c>
-      <c r="E25" s="7">
-        <v>-2.03</v>
-      </c>
-    </row>
-    <row r="26" spans="1:5">
-      <c r="A26" s="3" t="s">
-        <v>42</v>
-      </c>
-      <c r="B26" s="3" t="s">
-        <v>11</v>
-      </c>
-      <c r="C26" s="5">
-        <v>-11.6</v>
-      </c>
-      <c r="D26" s="5">
-        <v>-13.19</v>
-      </c>
-      <c r="E26" s="7">
-        <v>-1.59</v>
-      </c>
-    </row>
-    <row r="27" spans="1:5">
-      <c r="A27" s="3" t="s">
-        <v>43</v>
-      </c>
-      <c r="B27" s="3" t="s">
-        <v>11</v>
-      </c>
-      <c r="C27" s="5">
-        <v>17.79</v>
-      </c>
-      <c r="D27" s="5">
-        <v>11</v>
-      </c>
-      <c r="E27" s="7">
-        <v>-6.79</v>
-      </c>
-    </row>
-    <row r="28" spans="1:5">
-      <c r="A28" s="3" t="s">
-        <v>37</v>
-      </c>
-      <c r="B28" s="3" t="s">
-        <v>10</v>
-      </c>
-      <c r="C28" s="5">
-        <v>-7.67</v>
-      </c>
-      <c r="D28" s="5">
-        <v>-10.74</v>
-      </c>
-      <c r="E28" s="7">
-        <v>-3.07</v>
-      </c>
-    </row>
-    <row r="29" spans="1:5">
-      <c r="A29" s="3" t="s">
-        <v>38</v>
-      </c>
-      <c r="B29" s="3" t="s">
-        <v>10</v>
-      </c>
-      <c r="C29" s="5">
-        <v>-21.47</v>
-      </c>
-      <c r="D29" s="5">
-        <v>-28.59</v>
-      </c>
-      <c r="E29" s="7">
-        <v>-7.12</v>
-      </c>
-    </row>
-    <row r="30" spans="1:5">
-      <c r="A30" s="3" t="s">
-        <v>39</v>
-      </c>
-      <c r="B30" s="3" t="s">
-        <v>10</v>
-      </c>
-      <c r="C30" s="5">
-        <v>-15.55</v>
-      </c>
-      <c r="D30" s="5">
-        <v>-14.71</v>
-      </c>
-      <c r="E30" s="6">
-        <v>0.84</v>
-      </c>
-    </row>
-    <row r="31" spans="1:5">
-      <c r="A31" s="3" t="s">
-        <v>40</v>
-      </c>
-      <c r="B31" s="3" t="s">
-        <v>10</v>
-      </c>
-      <c r="C31" s="5">
-        <v>-10.57</v>
-      </c>
-      <c r="D31" s="5">
-        <v>-12.41</v>
-      </c>
-      <c r="E31" s="7">
-        <v>-1.84</v>
-      </c>
-    </row>
-    <row r="32" spans="1:5">
-      <c r="A32" s="3" t="s">
-        <v>41</v>
-      </c>
-      <c r="B32" s="3" t="s">
-        <v>10</v>
-      </c>
-      <c r="C32" s="5">
-        <v>8.33</v>
-      </c>
-      <c r="D32" s="5">
-        <v>5.07</v>
-      </c>
-      <c r="E32" s="7">
-        <v>-3.26</v>
-      </c>
-    </row>
-    <row r="33" spans="1:5">
-      <c r="A33" s="3" t="s">
-        <v>42</v>
-      </c>
-      <c r="B33" s="3" t="s">
-        <v>10</v>
-      </c>
-      <c r="C33" s="5">
-        <v>-11.15</v>
-      </c>
-      <c r="D33" s="5">
-        <v>-10.66</v>
-      </c>
-      <c r="E33" s="6">
-        <v>0.49</v>
-      </c>
-    </row>
-    <row r="34" spans="1:5">
-      <c r="A34" s="3" t="s">
-        <v>43</v>
-      </c>
-      <c r="B34" s="3" t="s">
-        <v>10</v>
-      </c>
-      <c r="C34" s="5">
-        <v>7.64</v>
-      </c>
-      <c r="D34" s="5">
-        <v>3.26</v>
-      </c>
-      <c r="E34" s="7">
-        <v>-4.38</v>
-      </c>
-    </row>
-    <row r="35" spans="1:5">
-      <c r="A35" s="3" t="s">
-        <v>37</v>
-      </c>
-      <c r="B35" s="3" t="s">
-        <v>6</v>
-      </c>
-      <c r="C35" s="5">
-        <v>-17.85</v>
-      </c>
-      <c r="D35" s="5">
-        <v>-18.52</v>
-      </c>
-      <c r="E35" s="7">
-        <v>-0.67</v>
-      </c>
-    </row>
-    <row r="36" spans="1:5">
-      <c r="A36" s="3" t="s">
-        <v>38</v>
-      </c>
-      <c r="B36" s="3" t="s">
-        <v>6</v>
-      </c>
-      <c r="C36" s="5">
-        <v>-37.95</v>
-      </c>
-      <c r="D36" s="5">
-        <v>-40.78</v>
-      </c>
-      <c r="E36" s="7">
-        <v>-2.83</v>
-      </c>
-    </row>
-    <row r="37" spans="1:5">
-      <c r="A37" s="3" t="s">
-        <v>39</v>
-      </c>
-      <c r="B37" s="3" t="s">
-        <v>6</v>
-      </c>
-      <c r="C37" s="5">
-        <v>-48.58</v>
-      </c>
-      <c r="D37" s="5">
-        <v>-48.69</v>
-      </c>
-      <c r="E37" s="7">
-        <v>-0.11</v>
-      </c>
-    </row>
-    <row r="38" spans="1:5">
-      <c r="A38" s="3" t="s">
-        <v>40</v>
-      </c>
-      <c r="B38" s="3" t="s">
-        <v>6</v>
-      </c>
-      <c r="C38" s="5">
-        <v>-22.91</v>
-      </c>
-      <c r="D38" s="5">
-        <v>-23.96</v>
-      </c>
-      <c r="E38" s="7">
-        <v>-1.05</v>
-      </c>
-    </row>
-    <row r="39" spans="1:5">
-      <c r="A39" s="3" t="s">
-        <v>41</v>
-      </c>
-      <c r="B39" s="3" t="s">
-        <v>6</v>
-      </c>
-      <c r="C39" s="5">
-        <v>-14.08</v>
-      </c>
-      <c r="D39" s="5">
-        <v>-14.98</v>
-      </c>
-      <c r="E39" s="7">
-        <v>-0.9</v>
-      </c>
-    </row>
-    <row r="40" spans="1:5">
-      <c r="A40" s="3" t="s">
-        <v>42</v>
-      </c>
-      <c r="B40" s="3" t="s">
-        <v>6</v>
-      </c>
-      <c r="C40" s="5">
-        <v>-18.7</v>
-      </c>
-      <c r="D40" s="5">
-        <v>-19.84</v>
-      </c>
-      <c r="E40" s="7">
-        <v>-1.14</v>
-      </c>
-    </row>
-    <row r="41" spans="1:5">
-      <c r="A41" s="3" t="s">
-        <v>43</v>
-      </c>
-      <c r="B41" s="3" t="s">
-        <v>6</v>
-      </c>
-      <c r="C41" s="5">
-        <v>-17.5</v>
-      </c>
-      <c r="D41" s="5">
-        <v>-23.05</v>
-      </c>
-      <c r="E41" s="7">
-        <v>-5.55</v>
-      </c>
-    </row>
-    <row r="42" spans="1:5">
-      <c r="A42" s="3" t="s">
-        <v>37</v>
-      </c>
-      <c r="B42" s="3" t="s">
-        <v>2</v>
-      </c>
-      <c r="C42" s="5">
-        <v>10155</v>
-      </c>
-      <c r="D42" s="5">
-        <v>10072</v>
-      </c>
-      <c r="E42" s="7">
-        <v>-83</v>
-      </c>
-    </row>
-    <row r="43" spans="1:5">
-      <c r="A43" s="3" t="s">
-        <v>38</v>
-      </c>
-      <c r="B43" s="3" t="s">
-        <v>2</v>
-      </c>
-      <c r="C43" s="5">
-        <v>415.9</v>
-      </c>
-      <c r="D43" s="5">
-        <v>396.95</v>
-      </c>
-      <c r="E43" s="7">
-        <v>-18.95</v>
-      </c>
-    </row>
-    <row r="44" spans="1:5">
-      <c r="A44" s="3" t="s">
-        <v>39</v>
-      </c>
-      <c r="B44" s="3" t="s">
-        <v>2</v>
-      </c>
-      <c r="C44" s="5">
-        <v>278.8</v>
-      </c>
-      <c r="D44" s="5">
-        <v>278.2</v>
-      </c>
-      <c r="E44" s="7">
-        <v>-0.6</v>
-      </c>
-    </row>
-    <row r="45" spans="1:5">
-      <c r="A45" s="3" t="s">
-        <v>40</v>
-      </c>
-      <c r="B45" s="3" t="s">
-        <v>2</v>
-      </c>
-      <c r="C45" s="5">
-        <v>1678</v>
-      </c>
-      <c r="D45" s="5">
-        <v>1655</v>
-      </c>
-      <c r="E45" s="7">
-        <v>-23</v>
-      </c>
-    </row>
-    <row r="46" spans="1:5">
-      <c r="A46" s="3" t="s">
-        <v>41</v>
-      </c>
-      <c r="B46" s="3" t="s">
-        <v>2</v>
-      </c>
-      <c r="C46" s="5">
-        <v>11293</v>
-      </c>
-      <c r="D46" s="5">
-        <v>11175</v>
-      </c>
-      <c r="E46" s="7">
-        <v>-118</v>
-      </c>
-    </row>
-    <row r="47" spans="1:5">
-      <c r="A47" s="3" t="s">
-        <v>42</v>
-      </c>
-      <c r="B47" s="3" t="s">
-        <v>2</v>
-      </c>
-      <c r="C47" s="5">
-        <v>942.1</v>
-      </c>
-      <c r="D47" s="5">
-        <v>928.95</v>
-      </c>
-      <c r="E47" s="7">
-        <v>-13.15</v>
-      </c>
-    </row>
-    <row r="48" spans="1:5">
-      <c r="A48" s="3" t="s">
-        <v>43</v>
-      </c>
-      <c r="B48" s="3" t="s">
-        <v>2</v>
-      </c>
-      <c r="C48" s="5">
-        <v>153.38</v>
-      </c>
-      <c r="D48" s="5">
-        <v>143.06</v>
-      </c>
-      <c r="E48" s="7">
-        <v>-10.32</v>
-      </c>
-    </row>
-    <row r="49" spans="1:5">
-      <c r="A49" s="3" t="s">
-        <v>37</v>
-      </c>
-      <c r="B49" s="3" t="s">
-        <v>24</v>
-      </c>
-      <c r="C49" s="5">
-        <v>38.91</v>
-      </c>
-      <c r="D49" s="5">
-        <v>37.32</v>
-      </c>
-      <c r="E49" s="7">
-        <v>-1.59</v>
-      </c>
-    </row>
-    <row r="50" spans="1:5">
-      <c r="A50" s="3" t="s">
-        <v>38</v>
-      </c>
-      <c r="B50" s="3" t="s">
-        <v>24</v>
-      </c>
-      <c r="C50" s="5">
-        <v>31.26</v>
-      </c>
-      <c r="D50" s="5">
-        <v>28.28</v>
-      </c>
-      <c r="E50" s="7">
-        <v>-2.98</v>
-      </c>
-    </row>
-    <row r="51" spans="1:5">
-      <c r="A51" s="3" t="s">
-        <v>39</v>
-      </c>
-      <c r="B51" s="3" t="s">
-        <v>24</v>
-      </c>
-      <c r="C51" s="5">
-        <v>26.64</v>
-      </c>
-      <c r="D51" s="5">
-        <v>26.38</v>
-      </c>
-      <c r="E51" s="7">
-        <v>-0.26</v>
-      </c>
-    </row>
-    <row r="52" spans="1:5">
-      <c r="A52" s="3" t="s">
-        <v>40</v>
-      </c>
-      <c r="B52" s="3" t="s">
-        <v>24</v>
-      </c>
-      <c r="C52" s="5">
-        <v>30.54</v>
-      </c>
-      <c r="D52" s="5">
-        <v>27.88</v>
-      </c>
-      <c r="E52" s="7">
-        <v>-2.66</v>
-      </c>
-    </row>
-    <row r="53" spans="1:5">
-      <c r="A53" s="3" t="s">
-        <v>41</v>
-      </c>
-      <c r="B53" s="3" t="s">
-        <v>24</v>
-      </c>
-      <c r="C53" s="5">
-        <v>57.24</v>
-      </c>
-      <c r="D53" s="5">
-        <v>54.18</v>
-      </c>
-      <c r="E53" s="7">
-        <v>-3.06</v>
-      </c>
-    </row>
-    <row r="54" spans="1:5">
-      <c r="A54" s="3" t="s">
-        <v>42</v>
-      </c>
-      <c r="B54" s="3" t="s">
-        <v>24</v>
-      </c>
-      <c r="C54" s="5">
-        <v>40.4</v>
-      </c>
-      <c r="D54" s="5">
-        <v>37.99</v>
-      </c>
-      <c r="E54" s="7">
-        <v>-2.41</v>
-      </c>
-    </row>
-    <row r="55" spans="1:5">
-      <c r="A55" s="3" t="s">
-        <v>43</v>
-      </c>
-      <c r="B55" s="3" t="s">
-        <v>24</v>
-      </c>
-      <c r="C55" s="5">
-        <v>41.45</v>
-      </c>
-      <c r="D55" s="5">
-        <v>34.82</v>
-      </c>
-      <c r="E55" s="7">
-        <v>-6.63</v>
-      </c>
-    </row>
-    <row r="56" spans="1:5">
-      <c r="A56" s="3" t="s">
-        <v>37</v>
-      </c>
-      <c r="B56" s="3" t="s">
+      <c r="B63" s="6" t="s">
         <v>31</v>
       </c>
-      <c r="C56" s="5">
-        <v>-21.71</v>
-      </c>
-      <c r="D56" s="5">
-        <v>-16.35</v>
-      </c>
-      <c r="E56" s="6">
-        <v>5.36</v>
-      </c>
-    </row>
-    <row r="57" spans="1:5">
-      <c r="A57" s="3" t="s">
-        <v>38</v>
-      </c>
-      <c r="B57" s="3" t="s">
-        <v>31</v>
-      </c>
-      <c r="C57" s="5">
-        <v>-22.93</v>
-      </c>
-      <c r="D57" s="5">
-        <v>-35.24</v>
-      </c>
-      <c r="E57" s="7">
-        <v>-12.31</v>
-      </c>
-    </row>
-    <row r="58" spans="1:5">
-      <c r="A58" s="3" t="s">
-        <v>39</v>
-      </c>
-      <c r="B58" s="3" t="s">
-        <v>31</v>
-      </c>
-      <c r="C58" s="5">
-        <v>-38.35</v>
-      </c>
-      <c r="D58" s="5">
-        <v>-65.54000000000001</v>
-      </c>
-      <c r="E58" s="7">
-        <v>-27.19</v>
-      </c>
-    </row>
-    <row r="59" spans="1:5">
-      <c r="A59" s="3" t="s">
-        <v>40</v>
-      </c>
-      <c r="B59" s="3" t="s">
-        <v>31</v>
-      </c>
-      <c r="C59" s="5">
-        <v>24.43</v>
-      </c>
-      <c r="D59" s="5">
-        <v>-1.99</v>
-      </c>
-      <c r="E59" s="7">
-        <v>-26.42</v>
-      </c>
-    </row>
-    <row r="60" spans="1:5">
-      <c r="A60" s="3" t="s">
-        <v>41</v>
-      </c>
-      <c r="B60" s="3" t="s">
-        <v>31</v>
-      </c>
-      <c r="C60" s="5">
-        <v>224.33</v>
-      </c>
-      <c r="D60" s="5">
-        <v>-26.77</v>
-      </c>
-      <c r="E60" s="7">
-        <v>-251.1</v>
-      </c>
-    </row>
-    <row r="61" spans="1:5">
-      <c r="A61" s="3" t="s">
-        <v>42</v>
-      </c>
-      <c r="B61" s="3" t="s">
-        <v>31</v>
-      </c>
-      <c r="C61" s="5">
-        <v>27.05</v>
-      </c>
-      <c r="D61" s="5">
-        <v>-27.66</v>
-      </c>
-      <c r="E61" s="7">
-        <v>-54.71</v>
-      </c>
-    </row>
-    <row r="62" spans="1:5">
-      <c r="A62" s="3" t="s">
-        <v>43</v>
-      </c>
-      <c r="B62" s="3" t="s">
-        <v>31</v>
-      </c>
-      <c r="C62" s="5">
-        <v>-61.31</v>
-      </c>
-      <c r="D62" s="5">
+      <c r="C63" s="7">
         <v>3.62</v>
       </c>
-      <c r="E62" s="6">
-        <v>64.93000000000001</v>
+      <c r="D63" s="7">
+        <v>-74.67</v>
+      </c>
+      <c r="E63" s="8">
+        <v>-78.29000000000001</v>
       </c>
     </row>
   </sheetData>
   <mergeCells count="2">
     <mergeCell ref="A1:F1"/>
-    <mergeCell ref="A5:E5"/>
+    <mergeCell ref="A6:E6"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -2838,60 +2931,60 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:9" ht="28" customHeight="1">
-      <c r="A1" s="8" t="s">
+      <c r="A1" s="10" t="s">
         <v>1</v>
       </c>
-      <c r="B1" s="8" t="s">
-        <v>55</v>
-      </c>
-      <c r="C1" s="8" t="s">
-        <v>56</v>
-      </c>
-      <c r="D1" s="8" t="s">
+      <c r="B1" s="10" t="s">
+        <v>67</v>
+      </c>
+      <c r="C1" s="10" t="s">
+        <v>68</v>
+      </c>
+      <c r="D1" s="10" t="s">
+        <v>69</v>
+      </c>
+      <c r="E1" s="10" t="s">
+        <v>70</v>
+      </c>
+      <c r="F1" s="10" t="s">
+        <v>71</v>
+      </c>
+      <c r="G1" s="10" t="s">
+        <v>72</v>
+      </c>
+      <c r="H1" s="10" t="s">
+        <v>73</v>
+      </c>
+      <c r="I1" s="10" t="s">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="2" spans="1:9">
+      <c r="A2" s="11" t="s">
+        <v>44</v>
+      </c>
+      <c r="B2" s="12">
+        <v>44.24</v>
+      </c>
+      <c r="C2" s="13">
+        <v>7</v>
+      </c>
+      <c r="D2" s="12">
+        <v>35.3</v>
+      </c>
+      <c r="E2" s="12">
+        <v>28.6</v>
+      </c>
+      <c r="F2" s="12">
+        <v>-11.9</v>
+      </c>
+      <c r="G2" s="12">
+        <v>-9.5</v>
+      </c>
+      <c r="H2" s="12">
         <v>57</v>
       </c>
-      <c r="E1" s="8" t="s">
-        <v>58</v>
-      </c>
-      <c r="F1" s="8" t="s">
-        <v>59</v>
-      </c>
-      <c r="G1" s="8" t="s">
-        <v>60</v>
-      </c>
-      <c r="H1" s="8" t="s">
-        <v>61</v>
-      </c>
-      <c r="I1" s="8" t="s">
-        <v>62</v>
-      </c>
-    </row>
-    <row r="2" spans="1:9">
-      <c r="A2" s="9" t="s">
-        <v>44</v>
-      </c>
-      <c r="B2" s="10">
-        <v>44.24</v>
-      </c>
-      <c r="C2" s="11">
-        <v>7</v>
-      </c>
-      <c r="D2" s="10">
-        <v>35.3</v>
-      </c>
-      <c r="E2" s="10">
-        <v>28.6</v>
-      </c>
-      <c r="F2" s="10">
-        <v>-9.199999999999999</v>
-      </c>
-      <c r="G2" s="10">
-        <v>-9.800000000000001</v>
-      </c>
-      <c r="H2" s="10">
-        <v>57</v>
-      </c>
-      <c r="I2" s="10">
+      <c r="I2" s="12">
         <v>14.3</v>
       </c>
     </row>
@@ -2993,49 +3086,49 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:7">
-      <c r="A1" s="12" t="s">
+      <c r="A1" s="14" t="s">
         <v>37</v>
       </c>
-      <c r="B1" s="12" t="s">
+      <c r="B1" s="14" t="s">
         <v>41</v>
       </c>
-      <c r="C1" s="12" t="s">
+      <c r="C1" s="14" t="s">
         <v>38</v>
       </c>
-      <c r="D1" s="12" t="s">
+      <c r="D1" s="14" t="s">
         <v>42</v>
       </c>
-      <c r="E1" s="12" t="s">
+      <c r="E1" s="14" t="s">
         <v>43</v>
       </c>
-      <c r="F1" s="12" t="s">
+      <c r="F1" s="14" t="s">
         <v>40</v>
       </c>
-      <c r="G1" s="12" t="s">
+      <c r="G1" s="14" t="s">
         <v>39</v>
       </c>
     </row>
     <row r="2" spans="1:7">
-      <c r="A2" s="13">
-        <v>0.246</v>
-      </c>
-      <c r="B2" s="13">
-        <v>0.2005</v>
-      </c>
-      <c r="C2" s="13">
-        <v>0.1355</v>
-      </c>
-      <c r="D2" s="13">
-        <v>0.0437</v>
-      </c>
-      <c r="E2" s="13">
-        <v>0.0246</v>
-      </c>
-      <c r="F2" s="13">
-        <v>-0.0172</v>
-      </c>
-      <c r="G2" s="13">
-        <v>-0.2368</v>
+      <c r="A2" s="15">
+        <v>0.2439</v>
+      </c>
+      <c r="B2" s="15">
+        <v>0.1981</v>
+      </c>
+      <c r="C2" s="15">
+        <v>0.1236</v>
+      </c>
+      <c r="D2" s="15">
+        <v>0.0357</v>
+      </c>
+      <c r="E2" s="15">
+        <v>0.0301</v>
+      </c>
+      <c r="F2" s="15">
+        <v>-0.0182</v>
+      </c>
+      <c r="G2" s="15">
+        <v>-0.237</v>
       </c>
     </row>
   </sheetData>

--- a/BAJAJ_GROUP_Technical_Metrics.xlsx
+++ b/BAJAJ_GROUP_Technical_Metrics.xlsx
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="270" uniqueCount="75">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="274" uniqueCount="77">
   <si>
     <t>Symbol</t>
   </si>
@@ -187,25 +187,31 @@
     <t>RSI Oversold Recovery</t>
   </si>
   <si>
-    <t>27.9 → 32.3</t>
+    <t>25.3 → 32.6</t>
   </si>
   <si>
     <t>🟢 BULLISH</t>
   </si>
   <si>
-    <t>27.9</t>
-  </si>
-  <si>
-    <t>32.3</t>
-  </si>
-  <si>
-    <t>50 DMA &gt; 200 DMA</t>
-  </si>
-  <si>
-    <t>Yes → No</t>
-  </si>
-  <si>
-    <t>🔴 DEATH CROSS</t>
+    <t>25.3</t>
+  </si>
+  <si>
+    <t>32.6</t>
+  </si>
+  <si>
+    <t>RSI Momentum</t>
+  </si>
+  <si>
+    <t>51.1 → 47.5</t>
+  </si>
+  <si>
+    <t>🔴 BEARISH</t>
+  </si>
+  <si>
+    <t>51.1</t>
+  </si>
+  <si>
+    <t>47.5</t>
   </si>
   <si>
     <t>▶  NUMERIC METRIC CHANGES (vs Previous Run)</t>
@@ -418,8 +424,8 @@
     <xf numFmtId="0" fontId="5" fillId="6" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1"/>
+    <xf numFmtId="165" fontId="4" fillId="5" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="165" fontId="5" fillId="6" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="165" fontId="4" fillId="5" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="3" fillId="7" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
@@ -931,10 +937,10 @@
         <v>44</v>
       </c>
       <c r="C2">
-        <v>10071</v>
+        <v>10390</v>
       </c>
       <c r="D2">
-        <v>-0.01</v>
+        <v>3.17</v>
       </c>
       <c r="E2">
         <v>12361</v>
@@ -943,46 +949,46 @@
         <v>8599.48</v>
       </c>
       <c r="G2">
-        <v>-18.53</v>
+        <v>-15.95</v>
       </c>
       <c r="H2">
-        <v>17.11</v>
+        <v>20.82</v>
       </c>
       <c r="I2">
-        <v>-3.21</v>
+        <v>1</v>
       </c>
       <c r="J2">
-        <v>-11.66</v>
+        <v>-7.3</v>
       </c>
       <c r="K2">
-        <v>-9.51</v>
+        <v>-7.1</v>
       </c>
       <c r="L2">
-        <v>11.93</v>
+        <v>15.55</v>
       </c>
       <c r="M2">
-        <v>24.39</v>
+        <v>25.26</v>
       </c>
       <c r="N2">
-        <v>71</v>
+        <v>85</v>
       </c>
       <c r="O2">
-        <v>72</v>
+        <v>75</v>
       </c>
       <c r="P2">
-        <v>10131.4</v>
+        <v>10152</v>
       </c>
       <c r="Q2">
-        <v>10271.2</v>
+        <v>10226.65</v>
       </c>
       <c r="R2">
-        <v>11140.98</v>
+        <v>11115.56</v>
       </c>
       <c r="S2">
-        <v>10219.25</v>
+        <v>10223.57</v>
       </c>
       <c r="T2">
-        <v>-1.45</v>
+        <v>1.63</v>
       </c>
       <c r="U2" t="s">
         <v>45</v>
@@ -994,37 +1000,37 @@
         <v>45</v>
       </c>
       <c r="X2">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="Y2">
-        <v>37.3</v>
+        <v>46.97</v>
       </c>
       <c r="Z2">
-        <v>-286.29</v>
+        <v>-250.79</v>
       </c>
       <c r="AA2">
-        <v>-322.61</v>
+        <v>-308.25</v>
       </c>
       <c r="AB2">
-        <v>36.32</v>
+        <v>57.45</v>
       </c>
       <c r="AC2">
-        <v>80.06</v>
+        <v>85.28</v>
       </c>
       <c r="AD2">
-        <v>80.63</v>
+        <v>81.39</v>
       </c>
       <c r="AE2">
-        <v>264.24</v>
+        <v>268.15</v>
       </c>
       <c r="AF2">
-        <v>-40.81</v>
+        <v>11.3</v>
       </c>
       <c r="AG2">
-        <v>11121.76</v>
+        <v>10936.15</v>
       </c>
       <c r="AH2">
-        <v>9420.639999999999</v>
+        <v>9517.15</v>
       </c>
       <c r="AI2">
         <v>10503.51</v>
@@ -1033,7 +1039,7 @@
         <v>47</v>
       </c>
       <c r="AK2">
-        <v>41.53</v>
+        <v>36.95</v>
       </c>
     </row>
     <row r="3" spans="1:37">
@@ -1044,10 +1050,10 @@
         <v>44</v>
       </c>
       <c r="C3">
-        <v>387.35</v>
+        <v>386.5</v>
       </c>
       <c r="D3">
-        <v>-2.42</v>
+        <v>-0.22</v>
       </c>
       <c r="E3">
         <v>670.25</v>
@@ -1056,46 +1062,46 @@
         <v>247.45</v>
       </c>
       <c r="G3">
-        <v>-42.21</v>
+        <v>-42.33</v>
       </c>
       <c r="H3">
-        <v>56.54</v>
+        <v>56.19</v>
       </c>
       <c r="I3">
-        <v>-17.93</v>
+        <v>-13.54</v>
       </c>
       <c r="J3">
-        <v>-23.43</v>
+        <v>-22.96</v>
       </c>
       <c r="K3">
-        <v>-29.55</v>
+        <v>-28.54</v>
       </c>
       <c r="L3">
-        <v>44.16</v>
+        <v>41.66</v>
       </c>
       <c r="M3">
-        <v>12.36</v>
+        <v>12.32</v>
       </c>
       <c r="N3">
-        <v>85</v>
+        <v>71</v>
       </c>
       <c r="O3">
-        <v>76</v>
+        <v>73</v>
       </c>
       <c r="P3">
-        <v>414.53</v>
+        <v>402.42</v>
       </c>
       <c r="Q3">
-        <v>472.6</v>
+        <v>466.95</v>
       </c>
       <c r="R3">
-        <v>486.76</v>
+        <v>483.94</v>
       </c>
       <c r="S3">
-        <v>467.52</v>
+        <v>468.07</v>
       </c>
       <c r="T3">
-        <v>-17.15</v>
+        <v>-17.43</v>
       </c>
       <c r="U3" t="s">
         <v>45</v>
@@ -1110,16 +1116,16 @@
         <v>1</v>
       </c>
       <c r="Y3">
-        <v>26.88</v>
+        <v>26.76</v>
       </c>
       <c r="Z3">
-        <v>-24.3</v>
+        <v>-27.2</v>
       </c>
       <c r="AA3">
-        <v>-13.15</v>
+        <v>-15.96</v>
       </c>
       <c r="AB3">
-        <v>-11.15</v>
+        <v>-11.24</v>
       </c>
       <c r="AC3">
         <v>0</v>
@@ -1128,16 +1134,16 @@
         <v>0</v>
       </c>
       <c r="AE3">
-        <v>23.88</v>
+        <v>22.88</v>
       </c>
       <c r="AF3">
-        <v>-3.76</v>
+        <v>-72.42</v>
       </c>
       <c r="AG3">
-        <v>548.54</v>
+        <v>550.86</v>
       </c>
       <c r="AH3">
-        <v>396.65</v>
+        <v>383.03</v>
       </c>
       <c r="AI3">
         <v>455.35</v>
@@ -1146,7 +1152,7 @@
         <v>47</v>
       </c>
       <c r="AK3">
-        <v>47.3</v>
+        <v>51.09</v>
       </c>
     </row>
     <row r="4" spans="1:37">
@@ -1157,58 +1163,58 @@
         <v>44</v>
       </c>
       <c r="C4">
-        <v>275.65</v>
+        <v>281.8</v>
       </c>
       <c r="D4">
-        <v>-0.92</v>
+        <v>2.23</v>
       </c>
       <c r="E4">
-        <v>542.2</v>
+        <v>533.05</v>
       </c>
       <c r="F4">
         <v>275.65</v>
       </c>
       <c r="G4">
-        <v>-49.16</v>
+        <v>-47.13</v>
       </c>
       <c r="H4">
-        <v>0</v>
+        <v>2.23</v>
       </c>
       <c r="I4">
-        <v>-8.51</v>
+        <v>-4.91</v>
       </c>
       <c r="J4">
-        <v>-16.32</v>
+        <v>-12.33</v>
       </c>
       <c r="K4">
-        <v>-16.19</v>
+        <v>-14.45</v>
       </c>
       <c r="L4">
-        <v>-48.8</v>
+        <v>-48.03</v>
       </c>
       <c r="M4">
-        <v>-23.7</v>
+        <v>-23.11</v>
       </c>
       <c r="N4">
         <v>15</v>
       </c>
       <c r="O4">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="P4">
-        <v>284.42</v>
+        <v>281.51</v>
       </c>
       <c r="Q4">
-        <v>298.61</v>
+        <v>296.76</v>
       </c>
       <c r="R4">
-        <v>321.8</v>
+        <v>320.3</v>
       </c>
       <c r="S4">
-        <v>354.16</v>
+        <v>353.21</v>
       </c>
       <c r="T4">
-        <v>-22.17</v>
+        <v>-20.22</v>
       </c>
       <c r="U4" t="s">
         <v>45</v>
@@ -1223,34 +1229,34 @@
         <v>0</v>
       </c>
       <c r="Y4">
-        <v>25.28</v>
+        <v>32.61</v>
       </c>
       <c r="Z4">
-        <v>-10.94</v>
+        <v>-10.95</v>
       </c>
       <c r="AA4">
-        <v>-9.32</v>
+        <v>-9.65</v>
       </c>
       <c r="AB4">
-        <v>-1.62</v>
+        <v>-1.3</v>
       </c>
       <c r="AC4">
-        <v>6.99</v>
+        <v>17.67</v>
       </c>
       <c r="AD4">
-        <v>22.91</v>
+        <v>15.67</v>
       </c>
       <c r="AE4">
-        <v>10.79</v>
+        <v>10.72</v>
       </c>
       <c r="AF4">
-        <v>-78.95999999999999</v>
+        <v>-83.40000000000001</v>
       </c>
       <c r="AG4">
-        <v>321.15</v>
+        <v>318.34</v>
       </c>
       <c r="AH4">
-        <v>276.08</v>
+        <v>275.17</v>
       </c>
       <c r="AI4">
         <v>308.71</v>
@@ -1259,7 +1265,7 @@
         <v>47</v>
       </c>
       <c r="AK4">
-        <v>33.27</v>
+        <v>28.97</v>
       </c>
     </row>
     <row r="5" spans="1:37">
@@ -1270,10 +1276,10 @@
         <v>44</v>
       </c>
       <c r="C5">
-        <v>1670.9</v>
+        <v>1677</v>
       </c>
       <c r="D5">
-        <v>0.96</v>
+        <v>0.37</v>
       </c>
       <c r="E5">
         <v>2176.6</v>
@@ -1282,46 +1288,46 @@
         <v>1631.8</v>
       </c>
       <c r="G5">
-        <v>-23.23</v>
+        <v>-22.95</v>
       </c>
       <c r="H5">
-        <v>2.4</v>
+        <v>2.77</v>
       </c>
       <c r="I5">
-        <v>-3.36</v>
+        <v>-1.35</v>
       </c>
       <c r="J5">
-        <v>-9.51</v>
+        <v>-4.84</v>
       </c>
       <c r="K5">
-        <v>-10.97</v>
+        <v>-12.34</v>
       </c>
       <c r="L5">
-        <v>-21.91</v>
+        <v>-22.69</v>
       </c>
       <c r="M5">
-        <v>-1.82</v>
+        <v>-1.38</v>
       </c>
       <c r="N5">
         <v>29</v>
       </c>
       <c r="O5">
-        <v>43</v>
+        <v>41</v>
       </c>
       <c r="P5">
-        <v>1678.78</v>
+        <v>1674.18</v>
       </c>
       <c r="Q5">
-        <v>1723.55</v>
+        <v>1718.85</v>
       </c>
       <c r="R5">
-        <v>1857.97</v>
+        <v>1851.01</v>
       </c>
       <c r="S5">
-        <v>1860.69</v>
+        <v>1858.85</v>
       </c>
       <c r="T5">
-        <v>-10.2</v>
+        <v>-9.779999999999999</v>
       </c>
       <c r="U5" t="s">
         <v>45</v>
@@ -1336,34 +1342,34 @@
         <v>0</v>
       </c>
       <c r="Y5">
-        <v>32.27</v>
+        <v>33.93</v>
       </c>
       <c r="Z5">
-        <v>-48.39</v>
+        <v>-47.08</v>
       </c>
       <c r="AA5">
-        <v>-48.54</v>
+        <v>-48.25</v>
       </c>
       <c r="AB5">
-        <v>0.14</v>
+        <v>1.16</v>
       </c>
       <c r="AC5">
-        <v>33.72</v>
+        <v>41.07</v>
       </c>
       <c r="AD5">
-        <v>38.4</v>
+        <v>36.29</v>
       </c>
       <c r="AE5">
-        <v>38.97</v>
+        <v>38.25</v>
       </c>
       <c r="AF5">
-        <v>-46.54</v>
+        <v>130.11</v>
       </c>
       <c r="AG5">
-        <v>1785.61</v>
+        <v>1780.01</v>
       </c>
       <c r="AH5">
-        <v>1661.49</v>
+        <v>1657.69</v>
       </c>
       <c r="AI5">
         <v>1770.15</v>
@@ -1372,7 +1378,7 @@
         <v>47</v>
       </c>
       <c r="AK5">
-        <v>62.27</v>
+        <v>61.38</v>
       </c>
     </row>
     <row r="6" spans="1:37">
@@ -1383,10 +1389,10 @@
         <v>44</v>
       </c>
       <c r="C6">
-        <v>11050</v>
+        <v>10901</v>
       </c>
       <c r="D6">
-        <v>-1.12</v>
+        <v>-1.35</v>
       </c>
       <c r="E6">
         <v>13144</v>
@@ -1395,46 +1401,46 @@
         <v>8746</v>
       </c>
       <c r="G6">
-        <v>-15.93</v>
+        <v>-17.06</v>
       </c>
       <c r="H6">
-        <v>26.34</v>
+        <v>24.64</v>
       </c>
       <c r="I6">
-        <v>-1.32</v>
+        <v>-3.23</v>
       </c>
       <c r="J6">
-        <v>-3.49</v>
+        <v>-0.15</v>
       </c>
       <c r="K6">
-        <v>3.47</v>
+        <v>0.84</v>
       </c>
       <c r="L6">
-        <v>-12.34</v>
+        <v>-14.38</v>
       </c>
       <c r="M6">
-        <v>19.81</v>
+        <v>19.19</v>
       </c>
       <c r="N6">
         <v>57</v>
       </c>
       <c r="O6">
-        <v>67</v>
+        <v>63</v>
       </c>
       <c r="P6">
-        <v>11151.6</v>
+        <v>11078.8</v>
       </c>
       <c r="Q6">
-        <v>10886.05</v>
+        <v>10884.1</v>
       </c>
       <c r="R6">
-        <v>11101.02</v>
+        <v>11089.04</v>
       </c>
       <c r="S6">
-        <v>10657.75</v>
+        <v>10656.24</v>
       </c>
       <c r="T6">
-        <v>3.68</v>
+        <v>2.3</v>
       </c>
       <c r="U6" t="s">
         <v>45</v>
@@ -1449,34 +1455,34 @@
         <v>2</v>
       </c>
       <c r="Y6">
-        <v>51.06</v>
+        <v>47.54</v>
       </c>
       <c r="Z6">
-        <v>34.01</v>
+        <v>20.31</v>
       </c>
       <c r="AA6">
-        <v>-14.1</v>
+        <v>-7.21</v>
       </c>
       <c r="AB6">
-        <v>48.1</v>
+        <v>27.52</v>
       </c>
       <c r="AC6">
-        <v>76.84999999999999</v>
+        <v>58.41</v>
       </c>
       <c r="AD6">
-        <v>78.34</v>
+        <v>70.17</v>
       </c>
       <c r="AE6">
-        <v>295.25</v>
+        <v>299.37</v>
       </c>
       <c r="AF6">
-        <v>-18.19</v>
+        <v>95.76000000000001</v>
       </c>
       <c r="AG6">
-        <v>11360.44</v>
+        <v>11357.88</v>
       </c>
       <c r="AH6">
-        <v>10411.66</v>
+        <v>10410.32</v>
       </c>
       <c r="AI6">
         <v>11368.55</v>
@@ -1485,7 +1491,7 @@
         <v>47</v>
       </c>
       <c r="AK6">
-        <v>23.75</v>
+        <v>22.65</v>
       </c>
     </row>
     <row r="7" spans="1:37">
@@ -1496,10 +1502,10 @@
         <v>44</v>
       </c>
       <c r="C7">
-        <v>918.7</v>
+        <v>912</v>
       </c>
       <c r="D7">
-        <v>-1.1</v>
+        <v>-0.73</v>
       </c>
       <c r="E7">
         <v>1158.8</v>
@@ -1508,46 +1514,46 @@
         <v>801.55</v>
       </c>
       <c r="G7">
-        <v>-20.72</v>
+        <v>-21.3</v>
       </c>
       <c r="H7">
-        <v>14.62</v>
+        <v>13.78</v>
       </c>
       <c r="I7">
-        <v>-6.46</v>
+        <v>-4.74</v>
       </c>
       <c r="J7">
-        <v>-11.93</v>
+        <v>-7.13</v>
       </c>
       <c r="K7">
-        <v>-9.289999999999999</v>
+        <v>-13</v>
       </c>
       <c r="L7">
-        <v>-15.01</v>
+        <v>-16.06</v>
       </c>
       <c r="M7">
-        <v>3.57</v>
+        <v>4.44</v>
       </c>
       <c r="N7">
         <v>43</v>
       </c>
       <c r="O7">
-        <v>50</v>
+        <v>45</v>
       </c>
       <c r="P7">
-        <v>934.62</v>
+        <v>925.55</v>
       </c>
       <c r="Q7">
-        <v>959.6900000000001</v>
+        <v>955.4400000000001</v>
       </c>
       <c r="R7">
-        <v>1017.43</v>
+        <v>1013.85</v>
       </c>
       <c r="S7">
-        <v>973.14</v>
+        <v>972.8099999999999</v>
       </c>
       <c r="T7">
-        <v>-5.59</v>
+        <v>-6.25</v>
       </c>
       <c r="U7" t="s">
         <v>45</v>
@@ -1562,43 +1568,43 @@
         <v>1</v>
       </c>
       <c r="Y7">
-        <v>36.17</v>
+        <v>35</v>
       </c>
       <c r="Z7">
-        <v>-22.85</v>
+        <v>-24.16</v>
       </c>
       <c r="AA7">
-        <v>-21.4</v>
+        <v>-21.95</v>
       </c>
       <c r="AB7">
-        <v>-1.45</v>
+        <v>-2.21</v>
       </c>
       <c r="AC7">
-        <v>25.78</v>
+        <v>7.63</v>
       </c>
       <c r="AD7">
-        <v>35.08</v>
+        <v>21.98</v>
       </c>
       <c r="AE7">
-        <v>28.22</v>
+        <v>27.38</v>
       </c>
       <c r="AF7">
-        <v>-54.54</v>
+        <v>-26.91</v>
       </c>
       <c r="AG7">
-        <v>999.84</v>
+        <v>996.95</v>
       </c>
       <c r="AH7">
-        <v>919.54</v>
+        <v>913.9299999999999</v>
       </c>
       <c r="AI7">
-        <v>1001.1</v>
+        <v>997.89</v>
       </c>
       <c r="AJ7" t="s">
         <v>47</v>
       </c>
       <c r="AK7">
-        <v>24.75</v>
+        <v>26.01</v>
       </c>
     </row>
     <row r="8" spans="1:37">
@@ -1609,10 +1615,10 @@
         <v>44</v>
       </c>
       <c r="C8">
-        <v>146.07</v>
+        <v>148.69</v>
       </c>
       <c r="D8">
-        <v>2.1</v>
+        <v>1.79</v>
       </c>
       <c r="E8">
         <v>185.92</v>
@@ -1621,25 +1627,25 @@
         <v>115.96</v>
       </c>
       <c r="G8">
-        <v>-21.43</v>
+        <v>-20.02</v>
       </c>
       <c r="H8">
-        <v>25.97</v>
+        <v>28.23</v>
       </c>
       <c r="I8">
-        <v>-15.07</v>
+        <v>-9.6</v>
       </c>
       <c r="J8">
-        <v>-7.03</v>
+        <v>-4.23</v>
       </c>
       <c r="K8">
-        <v>5.54</v>
+        <v>5.78</v>
       </c>
       <c r="L8">
-        <v>14.44</v>
+        <v>14.92</v>
       </c>
       <c r="M8">
-        <v>3.01</v>
+        <v>2.72</v>
       </c>
       <c r="N8">
         <v>99</v>
@@ -1648,19 +1654,19 @@
         <v>81</v>
       </c>
       <c r="P8">
-        <v>152.76</v>
+        <v>149.6</v>
       </c>
       <c r="Q8">
-        <v>169.93</v>
+        <v>169.01</v>
       </c>
       <c r="R8">
-        <v>150.58</v>
+        <v>150.84</v>
       </c>
       <c r="S8">
-        <v>137.76</v>
+        <v>137.8</v>
       </c>
       <c r="T8">
-        <v>6.04</v>
+        <v>7.9</v>
       </c>
       <c r="U8" t="s">
         <v>46</v>
@@ -1675,34 +1681,34 @@
         <v>3</v>
       </c>
       <c r="Y8">
-        <v>37.94</v>
+        <v>40.6</v>
       </c>
       <c r="Z8">
-        <v>0.02</v>
+        <v>-0.92</v>
       </c>
       <c r="AA8">
-        <v>4.88</v>
+        <v>3.72</v>
       </c>
       <c r="AB8">
-        <v>-4.86</v>
+        <v>-4.64</v>
       </c>
       <c r="AC8">
-        <v>2.42</v>
+        <v>6.9</v>
       </c>
       <c r="AD8">
-        <v>0.8100000000000001</v>
+        <v>3.1</v>
       </c>
       <c r="AE8">
-        <v>8.52</v>
+        <v>8.31</v>
       </c>
       <c r="AF8">
-        <v>-74.67</v>
+        <v>-86.34999999999999</v>
       </c>
       <c r="AG8">
-        <v>193.43</v>
+        <v>194.35</v>
       </c>
       <c r="AH8">
-        <v>146.43</v>
+        <v>143.67</v>
       </c>
       <c r="AI8">
         <v>170.73</v>
@@ -1711,7 +1717,7 @@
         <v>47</v>
       </c>
       <c r="AK8">
-        <v>41.02</v>
+        <v>43.64</v>
       </c>
     </row>
   </sheetData>
@@ -1852,7 +1858,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:F63"/>
+  <dimension ref="A1:F65"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="16.7109375" customWidth="1"/>
@@ -1892,7 +1898,7 @@
     </row>
     <row r="3" spans="1:6">
       <c r="A3" s="4" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="B3" s="4" t="s">
         <v>54</v>
@@ -1912,7 +1918,7 @@
     </row>
     <row r="4" spans="1:6">
       <c r="A4" s="5" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="B4" s="5" t="s">
         <v>59</v>
@@ -1924,15 +1930,15 @@
         <v>61</v>
       </c>
       <c r="E4" s="5" t="s">
-        <v>46</v>
+        <v>62</v>
       </c>
       <c r="F4" s="5" t="s">
-        <v>45</v>
+        <v>63</v>
       </c>
     </row>
     <row r="6" spans="1:6">
       <c r="A6" s="2" t="s">
-        <v>62</v>
+        <v>64</v>
       </c>
       <c r="B6" s="2"/>
       <c r="C6" s="2"/>
@@ -1944,16 +1950,16 @@
         <v>0</v>
       </c>
       <c r="B7" s="3" t="s">
-        <v>63</v>
+        <v>65</v>
       </c>
       <c r="C7" s="3" t="s">
-        <v>64</v>
+        <v>66</v>
       </c>
       <c r="D7" s="3" t="s">
-        <v>65</v>
+        <v>67</v>
       </c>
       <c r="E7" s="3" t="s">
-        <v>66</v>
+        <v>68</v>
       </c>
     </row>
     <row r="8" spans="1:6">
@@ -1964,13 +1970,13 @@
         <v>9</v>
       </c>
       <c r="C8" s="7">
-        <v>-11.36</v>
+        <v>-11.66</v>
       </c>
       <c r="D8" s="7">
-        <v>-11.66</v>
+        <v>-7.3</v>
       </c>
       <c r="E8" s="8">
-        <v>-0.3</v>
+        <v>4.36</v>
       </c>
     </row>
     <row r="9" spans="1:6">
@@ -1981,13 +1987,13 @@
         <v>9</v>
       </c>
       <c r="C9" s="7">
-        <v>-22.73</v>
+        <v>-23.43</v>
       </c>
       <c r="D9" s="7">
-        <v>-23.43</v>
+        <v>-22.96</v>
       </c>
       <c r="E9" s="8">
-        <v>-0.7</v>
+        <v>0.47</v>
       </c>
     </row>
     <row r="10" spans="1:6">
@@ -1998,13 +2004,13 @@
         <v>9</v>
       </c>
       <c r="C10" s="7">
-        <v>-13.99</v>
+        <v>-16.32</v>
       </c>
       <c r="D10" s="7">
-        <v>-16.32</v>
+        <v>-12.33</v>
       </c>
       <c r="E10" s="8">
-        <v>-2.33</v>
+        <v>3.99</v>
       </c>
     </row>
     <row r="11" spans="1:6">
@@ -2015,13 +2021,13 @@
         <v>9</v>
       </c>
       <c r="C11" s="7">
-        <v>-9.24</v>
+        <v>-9.51</v>
       </c>
       <c r="D11" s="7">
-        <v>-9.51</v>
+        <v>-4.84</v>
       </c>
       <c r="E11" s="8">
-        <v>-0.27</v>
+        <v>4.67</v>
       </c>
     </row>
     <row r="12" spans="1:6">
@@ -2032,13 +2038,13 @@
         <v>9</v>
       </c>
       <c r="C12" s="7">
-        <v>-0.09</v>
+        <v>-3.49</v>
       </c>
       <c r="D12" s="7">
-        <v>-3.49</v>
+        <v>-0.15</v>
       </c>
       <c r="E12" s="8">
-        <v>-3.4</v>
+        <v>3.34</v>
       </c>
     </row>
     <row r="13" spans="1:6">
@@ -2049,13 +2055,13 @@
         <v>9</v>
       </c>
       <c r="C13" s="7">
-        <v>-7.92</v>
+        <v>-11.93</v>
       </c>
       <c r="D13" s="7">
-        <v>-11.93</v>
+        <v>-7.13</v>
       </c>
       <c r="E13" s="8">
-        <v>-4.01</v>
+        <v>4.8</v>
       </c>
     </row>
     <row r="14" spans="1:6">
@@ -2066,13 +2072,13 @@
         <v>9</v>
       </c>
       <c r="C14" s="7">
-        <v>1.17</v>
+        <v>-7.03</v>
       </c>
       <c r="D14" s="7">
-        <v>-7.03</v>
+        <v>-4.23</v>
       </c>
       <c r="E14" s="8">
-        <v>-8.199999999999999</v>
+        <v>2.8</v>
       </c>
     </row>
     <row r="15" spans="1:6">
@@ -2083,13 +2089,13 @@
         <v>8</v>
       </c>
       <c r="C15" s="7">
-        <v>-3.01</v>
+        <v>-3.21</v>
       </c>
       <c r="D15" s="7">
-        <v>-3.21</v>
+        <v>1</v>
       </c>
       <c r="E15" s="8">
-        <v>-0.2</v>
+        <v>4.21</v>
       </c>
     </row>
     <row r="16" spans="1:6">
@@ -2100,13 +2106,13 @@
         <v>8</v>
       </c>
       <c r="C16" s="7">
-        <v>-15.27</v>
+        <v>-17.93</v>
       </c>
       <c r="D16" s="7">
-        <v>-17.93</v>
+        <v>-13.54</v>
       </c>
       <c r="E16" s="8">
-        <v>-2.66</v>
+        <v>4.39</v>
       </c>
     </row>
     <row r="17" spans="1:5">
@@ -2117,13 +2123,13 @@
         <v>8</v>
       </c>
       <c r="C17" s="7">
-        <v>-9.289999999999999</v>
+        <v>-8.51</v>
       </c>
       <c r="D17" s="7">
-        <v>-8.51</v>
-      </c>
-      <c r="E17" s="9">
-        <v>0.78</v>
+        <v>-4.91</v>
+      </c>
+      <c r="E17" s="8">
+        <v>3.6</v>
       </c>
     </row>
     <row r="18" spans="1:5">
@@ -2134,13 +2140,13 @@
         <v>8</v>
       </c>
       <c r="C18" s="7">
-        <v>-4.45</v>
+        <v>-3.36</v>
       </c>
       <c r="D18" s="7">
-        <v>-3.36</v>
-      </c>
-      <c r="E18" s="9">
-        <v>1.09</v>
+        <v>-1.35</v>
+      </c>
+      <c r="E18" s="8">
+        <v>2.01</v>
       </c>
     </row>
     <row r="19" spans="1:5">
@@ -2151,13 +2157,13 @@
         <v>8</v>
       </c>
       <c r="C19" s="7">
-        <v>-0.45</v>
+        <v>-1.32</v>
       </c>
       <c r="D19" s="7">
-        <v>-1.32</v>
-      </c>
-      <c r="E19" s="8">
-        <v>-0.87</v>
+        <v>-3.23</v>
+      </c>
+      <c r="E19" s="9">
+        <v>-1.91</v>
       </c>
     </row>
     <row r="20" spans="1:5">
@@ -2168,13 +2174,13 @@
         <v>8</v>
       </c>
       <c r="C20" s="7">
-        <v>-3.76</v>
+        <v>-6.46</v>
       </c>
       <c r="D20" s="7">
-        <v>-6.46</v>
+        <v>-4.74</v>
       </c>
       <c r="E20" s="8">
-        <v>-2.7</v>
+        <v>1.72</v>
       </c>
     </row>
     <row r="21" spans="1:5">
@@ -2185,13 +2191,13 @@
         <v>8</v>
       </c>
       <c r="C21" s="7">
-        <v>-16.02</v>
+        <v>-15.07</v>
       </c>
       <c r="D21" s="7">
-        <v>-15.07</v>
-      </c>
-      <c r="E21" s="9">
-        <v>0.95</v>
+        <v>-9.6</v>
+      </c>
+      <c r="E21" s="8">
+        <v>5.47</v>
       </c>
     </row>
     <row r="22" spans="1:5">
@@ -2202,13 +2208,13 @@
         <v>11</v>
       </c>
       <c r="C22" s="7">
-        <v>11.62</v>
+        <v>11.93</v>
       </c>
       <c r="D22" s="7">
-        <v>11.93</v>
-      </c>
-      <c r="E22" s="9">
-        <v>0.31</v>
+        <v>15.55</v>
+      </c>
+      <c r="E22" s="8">
+        <v>3.62</v>
       </c>
     </row>
     <row r="23" spans="1:5">
@@ -2219,13 +2225,13 @@
         <v>11</v>
       </c>
       <c r="C23" s="7">
-        <v>47.42</v>
+        <v>44.16</v>
       </c>
       <c r="D23" s="7">
-        <v>44.16</v>
-      </c>
-      <c r="E23" s="8">
-        <v>-3.26</v>
+        <v>41.66</v>
+      </c>
+      <c r="E23" s="9">
+        <v>-2.5</v>
       </c>
     </row>
     <row r="24" spans="1:5">
@@ -2236,13 +2242,13 @@
         <v>11</v>
       </c>
       <c r="C24" s="7">
-        <v>-48.46</v>
+        <v>-48.8</v>
       </c>
       <c r="D24" s="7">
-        <v>-48.8</v>
+        <v>-48.03</v>
       </c>
       <c r="E24" s="8">
-        <v>-0.34</v>
+        <v>0.77</v>
       </c>
     </row>
     <row r="25" spans="1:5">
@@ -2253,13 +2259,13 @@
         <v>11</v>
       </c>
       <c r="C25" s="7">
-        <v>-20.57</v>
+        <v>-21.91</v>
       </c>
       <c r="D25" s="7">
-        <v>-21.91</v>
-      </c>
-      <c r="E25" s="8">
-        <v>-1.34</v>
+        <v>-22.69</v>
+      </c>
+      <c r="E25" s="9">
+        <v>-0.78</v>
       </c>
     </row>
     <row r="26" spans="1:5">
@@ -2270,13 +2276,13 @@
         <v>11</v>
       </c>
       <c r="C26" s="7">
-        <v>-11.69</v>
+        <v>-12.34</v>
       </c>
       <c r="D26" s="7">
-        <v>-12.34</v>
-      </c>
-      <c r="E26" s="8">
-        <v>-0.65</v>
+        <v>-14.38</v>
+      </c>
+      <c r="E26" s="9">
+        <v>-2.04</v>
       </c>
     </row>
     <row r="27" spans="1:5">
@@ -2287,13 +2293,13 @@
         <v>11</v>
       </c>
       <c r="C27" s="7">
-        <v>-13.19</v>
+        <v>-15.01</v>
       </c>
       <c r="D27" s="7">
-        <v>-15.01</v>
-      </c>
-      <c r="E27" s="8">
-        <v>-1.82</v>
+        <v>-16.06</v>
+      </c>
+      <c r="E27" s="9">
+        <v>-1.05</v>
       </c>
     </row>
     <row r="28" spans="1:5">
@@ -2304,13 +2310,13 @@
         <v>11</v>
       </c>
       <c r="C28" s="7">
-        <v>11</v>
+        <v>14.44</v>
       </c>
       <c r="D28" s="7">
-        <v>14.44</v>
-      </c>
-      <c r="E28" s="9">
-        <v>3.44</v>
+        <v>14.92</v>
+      </c>
+      <c r="E28" s="8">
+        <v>0.48</v>
       </c>
     </row>
     <row r="29" spans="1:5">
@@ -2321,13 +2327,13 @@
         <v>10</v>
       </c>
       <c r="C29" s="7">
-        <v>-10.74</v>
+        <v>-9.51</v>
       </c>
       <c r="D29" s="7">
-        <v>-9.51</v>
-      </c>
-      <c r="E29" s="9">
-        <v>1.23</v>
+        <v>-7.1</v>
+      </c>
+      <c r="E29" s="8">
+        <v>2.41</v>
       </c>
     </row>
     <row r="30" spans="1:5">
@@ -2338,13 +2344,13 @@
         <v>10</v>
       </c>
       <c r="C30" s="7">
-        <v>-28.59</v>
+        <v>-29.55</v>
       </c>
       <c r="D30" s="7">
-        <v>-29.55</v>
+        <v>-28.54</v>
       </c>
       <c r="E30" s="8">
-        <v>-0.96</v>
+        <v>1.01</v>
       </c>
     </row>
     <row r="31" spans="1:5">
@@ -2355,13 +2361,13 @@
         <v>10</v>
       </c>
       <c r="C31" s="7">
-        <v>-14.71</v>
+        <v>-16.19</v>
       </c>
       <c r="D31" s="7">
-        <v>-16.19</v>
+        <v>-14.45</v>
       </c>
       <c r="E31" s="8">
-        <v>-1.48</v>
+        <v>1.74</v>
       </c>
     </row>
     <row r="32" spans="1:5">
@@ -2372,13 +2378,13 @@
         <v>10</v>
       </c>
       <c r="C32" s="7">
-        <v>-12.41</v>
+        <v>-10.97</v>
       </c>
       <c r="D32" s="7">
-        <v>-10.97</v>
+        <v>-12.34</v>
       </c>
       <c r="E32" s="9">
-        <v>1.44</v>
+        <v>-1.37</v>
       </c>
     </row>
     <row r="33" spans="1:5">
@@ -2389,13 +2395,13 @@
         <v>10</v>
       </c>
       <c r="C33" s="7">
-        <v>5.07</v>
+        <v>3.47</v>
       </c>
       <c r="D33" s="7">
-        <v>3.47</v>
-      </c>
-      <c r="E33" s="8">
-        <v>-1.6</v>
+        <v>0.84</v>
+      </c>
+      <c r="E33" s="9">
+        <v>-2.63</v>
       </c>
     </row>
     <row r="34" spans="1:5">
@@ -2406,13 +2412,13 @@
         <v>10</v>
       </c>
       <c r="C34" s="7">
-        <v>-10.66</v>
+        <v>-9.289999999999999</v>
       </c>
       <c r="D34" s="7">
-        <v>-9.289999999999999</v>
+        <v>-13</v>
       </c>
       <c r="E34" s="9">
-        <v>1.37</v>
+        <v>-3.71</v>
       </c>
     </row>
     <row r="35" spans="1:5">
@@ -2423,13 +2429,13 @@
         <v>10</v>
       </c>
       <c r="C35" s="7">
-        <v>3.26</v>
+        <v>5.54</v>
       </c>
       <c r="D35" s="7">
-        <v>5.54</v>
-      </c>
-      <c r="E35" s="9">
-        <v>2.28</v>
+        <v>5.78</v>
+      </c>
+      <c r="E35" s="8">
+        <v>0.24</v>
       </c>
     </row>
     <row r="36" spans="1:5">
@@ -2440,13 +2446,13 @@
         <v>6</v>
       </c>
       <c r="C36" s="7">
-        <v>-18.52</v>
+        <v>-18.53</v>
       </c>
       <c r="D36" s="7">
-        <v>-18.53</v>
+        <v>-15.95</v>
       </c>
       <c r="E36" s="8">
-        <v>-0.01</v>
+        <v>2.58</v>
       </c>
     </row>
     <row r="37" spans="1:5">
@@ -2457,13 +2463,13 @@
         <v>6</v>
       </c>
       <c r="C37" s="7">
-        <v>-40.78</v>
+        <v>-42.21</v>
       </c>
       <c r="D37" s="7">
-        <v>-42.21</v>
-      </c>
-      <c r="E37" s="8">
-        <v>-1.43</v>
+        <v>-42.33</v>
+      </c>
+      <c r="E37" s="9">
+        <v>-0.12</v>
       </c>
     </row>
     <row r="38" spans="1:5">
@@ -2474,13 +2480,13 @@
         <v>6</v>
       </c>
       <c r="C38" s="7">
-        <v>-48.69</v>
+        <v>-49.16</v>
       </c>
       <c r="D38" s="7">
-        <v>-49.16</v>
+        <v>-47.13</v>
       </c>
       <c r="E38" s="8">
-        <v>-0.47</v>
+        <v>2.03</v>
       </c>
     </row>
     <row r="39" spans="1:5">
@@ -2491,13 +2497,13 @@
         <v>6</v>
       </c>
       <c r="C39" s="7">
-        <v>-23.96</v>
+        <v>-23.23</v>
       </c>
       <c r="D39" s="7">
-        <v>-23.23</v>
-      </c>
-      <c r="E39" s="9">
-        <v>0.73</v>
+        <v>-22.95</v>
+      </c>
+      <c r="E39" s="8">
+        <v>0.28</v>
       </c>
     </row>
     <row r="40" spans="1:5">
@@ -2508,13 +2514,13 @@
         <v>6</v>
       </c>
       <c r="C40" s="7">
-        <v>-14.98</v>
+        <v>-15.93</v>
       </c>
       <c r="D40" s="7">
-        <v>-15.93</v>
-      </c>
-      <c r="E40" s="8">
-        <v>-0.95</v>
+        <v>-17.06</v>
+      </c>
+      <c r="E40" s="9">
+        <v>-1.13</v>
       </c>
     </row>
     <row r="41" spans="1:5">
@@ -2525,13 +2531,13 @@
         <v>6</v>
       </c>
       <c r="C41" s="7">
-        <v>-19.84</v>
+        <v>-20.72</v>
       </c>
       <c r="D41" s="7">
-        <v>-20.72</v>
-      </c>
-      <c r="E41" s="8">
-        <v>-0.88</v>
+        <v>-21.3</v>
+      </c>
+      <c r="E41" s="9">
+        <v>-0.58</v>
       </c>
     </row>
     <row r="42" spans="1:5">
@@ -2542,13 +2548,13 @@
         <v>6</v>
       </c>
       <c r="C42" s="7">
-        <v>-23.05</v>
+        <v>-21.43</v>
       </c>
       <c r="D42" s="7">
-        <v>-21.43</v>
-      </c>
-      <c r="E42" s="9">
-        <v>1.62</v>
+        <v>-20.02</v>
+      </c>
+      <c r="E42" s="8">
+        <v>1.41</v>
       </c>
     </row>
     <row r="43" spans="1:5">
@@ -2559,13 +2565,13 @@
         <v>2</v>
       </c>
       <c r="C43" s="7">
-        <v>10072</v>
+        <v>10071</v>
       </c>
       <c r="D43" s="7">
-        <v>10071</v>
+        <v>10390</v>
       </c>
       <c r="E43" s="8">
-        <v>-1</v>
+        <v>319</v>
       </c>
     </row>
     <row r="44" spans="1:5">
@@ -2576,13 +2582,13 @@
         <v>2</v>
       </c>
       <c r="C44" s="7">
-        <v>396.95</v>
+        <v>387.35</v>
       </c>
       <c r="D44" s="7">
-        <v>387.35</v>
-      </c>
-      <c r="E44" s="8">
-        <v>-9.6</v>
+        <v>386.5</v>
+      </c>
+      <c r="E44" s="9">
+        <v>-0.85</v>
       </c>
     </row>
     <row r="45" spans="1:5">
@@ -2593,13 +2599,13 @@
         <v>2</v>
       </c>
       <c r="C45" s="7">
-        <v>278.2</v>
+        <v>275.65</v>
       </c>
       <c r="D45" s="7">
-        <v>275.65</v>
+        <v>281.8</v>
       </c>
       <c r="E45" s="8">
-        <v>-2.55</v>
+        <v>6.15</v>
       </c>
     </row>
     <row r="46" spans="1:5">
@@ -2610,13 +2616,13 @@
         <v>2</v>
       </c>
       <c r="C46" s="7">
-        <v>1655</v>
+        <v>1670.9</v>
       </c>
       <c r="D46" s="7">
-        <v>1670.9</v>
-      </c>
-      <c r="E46" s="9">
-        <v>15.9</v>
+        <v>1677</v>
+      </c>
+      <c r="E46" s="8">
+        <v>6.1</v>
       </c>
     </row>
     <row r="47" spans="1:5">
@@ -2627,13 +2633,13 @@
         <v>2</v>
       </c>
       <c r="C47" s="7">
-        <v>11175</v>
+        <v>11050</v>
       </c>
       <c r="D47" s="7">
-        <v>11050</v>
-      </c>
-      <c r="E47" s="8">
-        <v>-125</v>
+        <v>10901</v>
+      </c>
+      <c r="E47" s="9">
+        <v>-149</v>
       </c>
     </row>
     <row r="48" spans="1:5">
@@ -2644,13 +2650,13 @@
         <v>2</v>
       </c>
       <c r="C48" s="7">
-        <v>928.95</v>
+        <v>918.7</v>
       </c>
       <c r="D48" s="7">
-        <v>918.7</v>
-      </c>
-      <c r="E48" s="8">
-        <v>-10.25</v>
+        <v>912</v>
+      </c>
+      <c r="E48" s="9">
+        <v>-6.7</v>
       </c>
     </row>
     <row r="49" spans="1:5">
@@ -2661,13 +2667,13 @@
         <v>2</v>
       </c>
       <c r="C49" s="7">
-        <v>143.06</v>
+        <v>146.07</v>
       </c>
       <c r="D49" s="7">
-        <v>146.07</v>
-      </c>
-      <c r="E49" s="9">
-        <v>3.01</v>
+        <v>148.69</v>
+      </c>
+      <c r="E49" s="8">
+        <v>2.62</v>
       </c>
     </row>
     <row r="50" spans="1:5">
@@ -2675,16 +2681,16 @@
         <v>37</v>
       </c>
       <c r="B50" s="6" t="s">
-        <v>24</v>
+        <v>13</v>
       </c>
       <c r="C50" s="7">
-        <v>37.32</v>
+        <v>71</v>
       </c>
       <c r="D50" s="7">
-        <v>37.3</v>
+        <v>85</v>
       </c>
       <c r="E50" s="8">
-        <v>-0.02</v>
+        <v>14</v>
       </c>
     </row>
     <row r="51" spans="1:5">
@@ -2692,220 +2698,254 @@
         <v>38</v>
       </c>
       <c r="B51" s="6" t="s">
-        <v>24</v>
+        <v>13</v>
       </c>
       <c r="C51" s="7">
-        <v>28.28</v>
+        <v>85</v>
       </c>
       <c r="D51" s="7">
-        <v>26.88</v>
-      </c>
-      <c r="E51" s="8">
-        <v>-1.4</v>
+        <v>71</v>
+      </c>
+      <c r="E51" s="9">
+        <v>-14</v>
       </c>
     </row>
     <row r="52" spans="1:5">
       <c r="A52" s="6" t="s">
-        <v>39</v>
+        <v>37</v>
       </c>
       <c r="B52" s="6" t="s">
         <v>24</v>
       </c>
       <c r="C52" s="7">
-        <v>26.38</v>
+        <v>37.3</v>
       </c>
       <c r="D52" s="7">
-        <v>25.28</v>
+        <v>46.97</v>
       </c>
       <c r="E52" s="8">
-        <v>-1.1</v>
+        <v>9.67</v>
       </c>
     </row>
     <row r="53" spans="1:5">
       <c r="A53" s="6" t="s">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="B53" s="6" t="s">
         <v>24</v>
       </c>
       <c r="C53" s="7">
-        <v>27.88</v>
+        <v>26.88</v>
       </c>
       <c r="D53" s="7">
-        <v>32.27</v>
+        <v>26.76</v>
       </c>
       <c r="E53" s="9">
-        <v>4.39</v>
+        <v>-0.12</v>
       </c>
     </row>
     <row r="54" spans="1:5">
       <c r="A54" s="6" t="s">
-        <v>41</v>
+        <v>39</v>
       </c>
       <c r="B54" s="6" t="s">
         <v>24</v>
       </c>
       <c r="C54" s="7">
-        <v>54.18</v>
+        <v>25.28</v>
       </c>
       <c r="D54" s="7">
-        <v>51.06</v>
+        <v>32.61</v>
       </c>
       <c r="E54" s="8">
-        <v>-3.12</v>
+        <v>7.33</v>
       </c>
     </row>
     <row r="55" spans="1:5">
       <c r="A55" s="6" t="s">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="B55" s="6" t="s">
         <v>24</v>
       </c>
       <c r="C55" s="7">
-        <v>37.99</v>
+        <v>32.27</v>
       </c>
       <c r="D55" s="7">
-        <v>36.17</v>
+        <v>33.93</v>
       </c>
       <c r="E55" s="8">
-        <v>-1.82</v>
+        <v>1.66</v>
       </c>
     </row>
     <row r="56" spans="1:5">
       <c r="A56" s="6" t="s">
-        <v>43</v>
+        <v>41</v>
       </c>
       <c r="B56" s="6" t="s">
         <v>24</v>
       </c>
       <c r="C56" s="7">
-        <v>34.82</v>
+        <v>51.06</v>
       </c>
       <c r="D56" s="7">
-        <v>37.94</v>
+        <v>47.54</v>
       </c>
       <c r="E56" s="9">
-        <v>3.12</v>
+        <v>-3.52</v>
       </c>
     </row>
     <row r="57" spans="1:5">
       <c r="A57" s="6" t="s">
-        <v>37</v>
+        <v>42</v>
       </c>
       <c r="B57" s="6" t="s">
-        <v>31</v>
+        <v>24</v>
       </c>
       <c r="C57" s="7">
-        <v>-16.35</v>
+        <v>36.17</v>
       </c>
       <c r="D57" s="7">
-        <v>-40.81</v>
-      </c>
-      <c r="E57" s="8">
-        <v>-24.46</v>
+        <v>35</v>
+      </c>
+      <c r="E57" s="9">
+        <v>-1.17</v>
       </c>
     </row>
     <row r="58" spans="1:5">
       <c r="A58" s="6" t="s">
-        <v>38</v>
+        <v>43</v>
       </c>
       <c r="B58" s="6" t="s">
-        <v>31</v>
+        <v>24</v>
       </c>
       <c r="C58" s="7">
-        <v>-35.24</v>
+        <v>37.94</v>
       </c>
       <c r="D58" s="7">
-        <v>-3.76</v>
-      </c>
-      <c r="E58" s="9">
-        <v>31.48</v>
+        <v>40.6</v>
+      </c>
+      <c r="E58" s="8">
+        <v>2.66</v>
       </c>
     </row>
     <row r="59" spans="1:5">
       <c r="A59" s="6" t="s">
-        <v>39</v>
+        <v>37</v>
       </c>
       <c r="B59" s="6" t="s">
         <v>31</v>
       </c>
       <c r="C59" s="7">
-        <v>-65.54000000000001</v>
+        <v>-40.81</v>
       </c>
       <c r="D59" s="7">
-        <v>-78.95999999999999</v>
+        <v>11.3</v>
       </c>
       <c r="E59" s="8">
-        <v>-13.42</v>
+        <v>52.11</v>
       </c>
     </row>
     <row r="60" spans="1:5">
       <c r="A60" s="6" t="s">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="B60" s="6" t="s">
         <v>31</v>
       </c>
       <c r="C60" s="7">
-        <v>-1.99</v>
+        <v>-3.76</v>
       </c>
       <c r="D60" s="7">
-        <v>-46.54</v>
-      </c>
-      <c r="E60" s="8">
-        <v>-44.55</v>
+        <v>-72.42</v>
+      </c>
+      <c r="E60" s="9">
+        <v>-68.66</v>
       </c>
     </row>
     <row r="61" spans="1:5">
       <c r="A61" s="6" t="s">
-        <v>41</v>
+        <v>39</v>
       </c>
       <c r="B61" s="6" t="s">
         <v>31</v>
       </c>
       <c r="C61" s="7">
-        <v>-26.77</v>
+        <v>-78.95999999999999</v>
       </c>
       <c r="D61" s="7">
-        <v>-18.19</v>
+        <v>-83.40000000000001</v>
       </c>
       <c r="E61" s="9">
-        <v>8.58</v>
+        <v>-4.44</v>
       </c>
     </row>
     <row r="62" spans="1:5">
       <c r="A62" s="6" t="s">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="B62" s="6" t="s">
         <v>31</v>
       </c>
       <c r="C62" s="7">
-        <v>-27.66</v>
+        <v>-46.54</v>
       </c>
       <c r="D62" s="7">
-        <v>-54.54</v>
+        <v>130.11</v>
       </c>
       <c r="E62" s="8">
-        <v>-26.88</v>
+        <v>176.65</v>
       </c>
     </row>
     <row r="63" spans="1:5">
       <c r="A63" s="6" t="s">
-        <v>43</v>
+        <v>41</v>
       </c>
       <c r="B63" s="6" t="s">
         <v>31</v>
       </c>
       <c r="C63" s="7">
-        <v>3.62</v>
+        <v>-18.19</v>
       </c>
       <c r="D63" s="7">
+        <v>95.76000000000001</v>
+      </c>
+      <c r="E63" s="8">
+        <v>113.95</v>
+      </c>
+    </row>
+    <row r="64" spans="1:5">
+      <c r="A64" s="6" t="s">
+        <v>42</v>
+      </c>
+      <c r="B64" s="6" t="s">
+        <v>31</v>
+      </c>
+      <c r="C64" s="7">
+        <v>-54.54</v>
+      </c>
+      <c r="D64" s="7">
+        <v>-26.91</v>
+      </c>
+      <c r="E64" s="8">
+        <v>27.63</v>
+      </c>
+    </row>
+    <row r="65" spans="1:5">
+      <c r="A65" s="6" t="s">
+        <v>43</v>
+      </c>
+      <c r="B65" s="6" t="s">
+        <v>31</v>
+      </c>
+      <c r="C65" s="7">
         <v>-74.67</v>
       </c>
-      <c r="E63" s="8">
-        <v>-78.29000000000001</v>
+      <c r="D65" s="7">
+        <v>-86.34999999999999</v>
+      </c>
+      <c r="E65" s="9">
+        <v>-11.68</v>
       </c>
     </row>
   </sheetData>
@@ -2935,28 +2975,28 @@
         <v>1</v>
       </c>
       <c r="B1" s="10" t="s">
-        <v>67</v>
+        <v>69</v>
       </c>
       <c r="C1" s="10" t="s">
-        <v>68</v>
+        <v>70</v>
       </c>
       <c r="D1" s="10" t="s">
-        <v>69</v>
+        <v>71</v>
       </c>
       <c r="E1" s="10" t="s">
-        <v>70</v>
+        <v>72</v>
       </c>
       <c r="F1" s="10" t="s">
-        <v>71</v>
+        <v>73</v>
       </c>
       <c r="G1" s="10" t="s">
-        <v>72</v>
+        <v>74</v>
       </c>
       <c r="H1" s="10" t="s">
-        <v>73</v>
+        <v>75</v>
       </c>
       <c r="I1" s="10" t="s">
-        <v>74</v>
+        <v>76</v>
       </c>
     </row>
     <row r="2" spans="1:9">
@@ -2964,22 +3004,22 @@
         <v>44</v>
       </c>
       <c r="B2" s="12">
-        <v>44.24</v>
+        <v>49.96</v>
       </c>
       <c r="C2" s="13">
         <v>7</v>
       </c>
       <c r="D2" s="12">
-        <v>35.3</v>
+        <v>37.6</v>
       </c>
       <c r="E2" s="12">
-        <v>28.6</v>
+        <v>42.9</v>
       </c>
       <c r="F2" s="12">
-        <v>-11.9</v>
+        <v>-8.4</v>
       </c>
       <c r="G2" s="12">
-        <v>-9.5</v>
+        <v>-9.800000000000001</v>
       </c>
       <c r="H2" s="12">
         <v>57</v>
@@ -3110,25 +3150,25 @@
     </row>
     <row r="2" spans="1:7">
       <c r="A2" s="15">
-        <v>0.2439</v>
+        <v>0.2526</v>
       </c>
       <c r="B2" s="15">
-        <v>0.1981</v>
+        <v>0.1919</v>
       </c>
       <c r="C2" s="15">
-        <v>0.1236</v>
+        <v>0.1232</v>
       </c>
       <c r="D2" s="15">
-        <v>0.0357</v>
+        <v>0.0444</v>
       </c>
       <c r="E2" s="15">
-        <v>0.0301</v>
+        <v>0.0272</v>
       </c>
       <c r="F2" s="15">
-        <v>-0.0182</v>
+        <v>-0.0138</v>
       </c>
       <c r="G2" s="15">
-        <v>-0.237</v>
+        <v>-0.2311</v>
       </c>
     </row>
   </sheetData>

--- a/BAJAJ_GROUP_Technical_Metrics.xlsx
+++ b/BAJAJ_GROUP_Technical_Metrics.xlsx
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="274" uniqueCount="77">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="253" uniqueCount="63">
   <si>
     <t>Symbol</t>
   </si>
@@ -169,49 +169,7 @@
     <t>▶  SIGNAL EVENTS (vs Previous Run)</t>
   </si>
   <si>
-    <t>Signal</t>
-  </si>
-  <si>
-    <t>Change</t>
-  </si>
-  <si>
-    <t>Direction</t>
-  </si>
-  <si>
-    <t>Prev Value</t>
-  </si>
-  <si>
-    <t>Curr Value</t>
-  </si>
-  <si>
-    <t>RSI Oversold Recovery</t>
-  </si>
-  <si>
-    <t>25.3 → 32.6</t>
-  </si>
-  <si>
-    <t>🟢 BULLISH</t>
-  </si>
-  <si>
-    <t>25.3</t>
-  </si>
-  <si>
-    <t>32.6</t>
-  </si>
-  <si>
-    <t>RSI Momentum</t>
-  </si>
-  <si>
-    <t>51.1 → 47.5</t>
-  </si>
-  <si>
-    <t>🔴 BEARISH</t>
-  </si>
-  <si>
-    <t>51.1</t>
-  </si>
-  <si>
-    <t>47.5</t>
+    <t>No signal events detected since last run.</t>
   </si>
   <si>
     <t>▶  NUMERIC METRIC CHANGES (vs Previous Run)</t>
@@ -413,16 +371,14 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="16">
+  <cellXfs count="14">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="2" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="3" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="5" fillId="6" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1"/>
     <xf numFmtId="165" fontId="4" fillId="5" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="165" fontId="5" fillId="6" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
@@ -937,10 +893,10 @@
         <v>44</v>
       </c>
       <c r="C2">
-        <v>10390</v>
+        <v>10485</v>
       </c>
       <c r="D2">
-        <v>3.17</v>
+        <v>0.91</v>
       </c>
       <c r="E2">
         <v>12361</v>
@@ -949,25 +905,25 @@
         <v>8599.48</v>
       </c>
       <c r="G2">
-        <v>-15.95</v>
+        <v>-15.18</v>
       </c>
       <c r="H2">
-        <v>20.82</v>
+        <v>21.93</v>
       </c>
       <c r="I2">
-        <v>1</v>
+        <v>4.1</v>
       </c>
       <c r="J2">
-        <v>-7.3</v>
+        <v>-7.06</v>
       </c>
       <c r="K2">
-        <v>-7.1</v>
+        <v>-7.82</v>
       </c>
       <c r="L2">
-        <v>15.55</v>
+        <v>17.53</v>
       </c>
       <c r="M2">
-        <v>25.26</v>
+        <v>26</v>
       </c>
       <c r="N2">
         <v>85</v>
@@ -976,19 +932,19 @@
         <v>75</v>
       </c>
       <c r="P2">
-        <v>10152</v>
+        <v>10234.6</v>
       </c>
       <c r="Q2">
-        <v>10226.65</v>
+        <v>10199.7</v>
       </c>
       <c r="R2">
-        <v>11115.56</v>
+        <v>11091.26</v>
       </c>
       <c r="S2">
-        <v>10223.57</v>
+        <v>10227.72</v>
       </c>
       <c r="T2">
-        <v>1.63</v>
+        <v>2.52</v>
       </c>
       <c r="U2" t="s">
         <v>45</v>
@@ -1003,34 +959,34 @@
         <v>2</v>
       </c>
       <c r="Y2">
-        <v>46.97</v>
+        <v>49.47</v>
       </c>
       <c r="Z2">
-        <v>-250.79</v>
+        <v>-212.55</v>
       </c>
       <c r="AA2">
-        <v>-308.25</v>
+        <v>-289.11</v>
       </c>
       <c r="AB2">
-        <v>57.45</v>
+        <v>76.56</v>
       </c>
       <c r="AC2">
-        <v>85.28</v>
+        <v>92.63</v>
       </c>
       <c r="AD2">
-        <v>81.39</v>
+        <v>85.98999999999999</v>
       </c>
       <c r="AE2">
-        <v>268.15</v>
+        <v>276.5</v>
       </c>
       <c r="AF2">
-        <v>11.3</v>
+        <v>205.37</v>
       </c>
       <c r="AG2">
-        <v>10936.15</v>
+        <v>10816.58</v>
       </c>
       <c r="AH2">
-        <v>9517.15</v>
+        <v>9582.82</v>
       </c>
       <c r="AI2">
         <v>10503.51</v>
@@ -1039,7 +995,7 @@
         <v>47</v>
       </c>
       <c r="AK2">
-        <v>36.95</v>
+        <v>35.98</v>
       </c>
     </row>
     <row r="3" spans="1:37">
@@ -1050,10 +1006,10 @@
         <v>44</v>
       </c>
       <c r="C3">
-        <v>386.5</v>
+        <v>381.3</v>
       </c>
       <c r="D3">
-        <v>-0.22</v>
+        <v>-1.35</v>
       </c>
       <c r="E3">
         <v>670.25</v>
@@ -1062,46 +1018,46 @@
         <v>247.45</v>
       </c>
       <c r="G3">
-        <v>-42.33</v>
+        <v>-43.11</v>
       </c>
       <c r="H3">
-        <v>56.19</v>
+        <v>54.09</v>
       </c>
       <c r="I3">
-        <v>-13.54</v>
+        <v>-10.37</v>
       </c>
       <c r="J3">
-        <v>-22.96</v>
+        <v>-23.66</v>
       </c>
       <c r="K3">
-        <v>-28.54</v>
+        <v>-28.19</v>
       </c>
       <c r="L3">
-        <v>41.66</v>
+        <v>39.59</v>
       </c>
       <c r="M3">
-        <v>12.32</v>
+        <v>12.39</v>
       </c>
       <c r="N3">
         <v>71</v>
       </c>
       <c r="O3">
-        <v>73</v>
+        <v>71</v>
       </c>
       <c r="P3">
-        <v>402.42</v>
+        <v>393.6</v>
       </c>
       <c r="Q3">
-        <v>466.95</v>
+        <v>462.01</v>
       </c>
       <c r="R3">
-        <v>483.94</v>
+        <v>481.55</v>
       </c>
       <c r="S3">
-        <v>468.07</v>
+        <v>468.57</v>
       </c>
       <c r="T3">
-        <v>-17.43</v>
+        <v>-18.63</v>
       </c>
       <c r="U3" t="s">
         <v>45</v>
@@ -1116,16 +1072,16 @@
         <v>1</v>
       </c>
       <c r="Y3">
-        <v>26.76</v>
+        <v>25.96</v>
       </c>
       <c r="Z3">
-        <v>-27.2</v>
+        <v>-29.57</v>
       </c>
       <c r="AA3">
-        <v>-15.96</v>
+        <v>-18.68</v>
       </c>
       <c r="AB3">
-        <v>-11.24</v>
+        <v>-10.89</v>
       </c>
       <c r="AC3">
         <v>0</v>
@@ -1134,25 +1090,25 @@
         <v>0</v>
       </c>
       <c r="AE3">
-        <v>22.88</v>
+        <v>21.9</v>
       </c>
       <c r="AF3">
-        <v>-72.42</v>
+        <v>-69.27</v>
       </c>
       <c r="AG3">
-        <v>550.86</v>
+        <v>553.92</v>
       </c>
       <c r="AH3">
-        <v>383.03</v>
+        <v>370.1</v>
       </c>
       <c r="AI3">
-        <v>455.35</v>
+        <v>446.85</v>
       </c>
       <c r="AJ3" t="s">
         <v>47</v>
       </c>
       <c r="AK3">
-        <v>51.09</v>
+        <v>54.67</v>
       </c>
     </row>
     <row r="4" spans="1:37">
@@ -1163,58 +1119,58 @@
         <v>44</v>
       </c>
       <c r="C4">
-        <v>281.8</v>
+        <v>292.65</v>
       </c>
       <c r="D4">
-        <v>2.23</v>
+        <v>3.85</v>
       </c>
       <c r="E4">
-        <v>533.05</v>
+        <v>529.85</v>
       </c>
       <c r="F4">
         <v>275.65</v>
       </c>
       <c r="G4">
-        <v>-47.13</v>
+        <v>-44.77</v>
       </c>
       <c r="H4">
-        <v>2.23</v>
+        <v>6.17</v>
       </c>
       <c r="I4">
-        <v>-4.91</v>
+        <v>-0.15</v>
       </c>
       <c r="J4">
-        <v>-12.33</v>
+        <v>-8.25</v>
       </c>
       <c r="K4">
-        <v>-14.45</v>
+        <v>-10.52</v>
       </c>
       <c r="L4">
-        <v>-48.03</v>
+        <v>-45.1</v>
       </c>
       <c r="M4">
-        <v>-23.11</v>
+        <v>-22.46</v>
       </c>
       <c r="N4">
         <v>15</v>
       </c>
       <c r="O4">
-        <v>12</v>
+        <v>18</v>
       </c>
       <c r="P4">
-        <v>281.51</v>
+        <v>281.42</v>
       </c>
       <c r="Q4">
-        <v>296.76</v>
+        <v>295.66</v>
       </c>
       <c r="R4">
-        <v>320.3</v>
+        <v>318.91</v>
       </c>
       <c r="S4">
-        <v>353.21</v>
+        <v>352.3</v>
       </c>
       <c r="T4">
-        <v>-20.22</v>
+        <v>-16.93</v>
       </c>
       <c r="U4" t="s">
         <v>45</v>
@@ -1229,34 +1185,34 @@
         <v>0</v>
       </c>
       <c r="Y4">
-        <v>32.61</v>
+        <v>43.2</v>
       </c>
       <c r="Z4">
-        <v>-10.95</v>
+        <v>-9.960000000000001</v>
       </c>
       <c r="AA4">
-        <v>-9.65</v>
+        <v>-9.710000000000001</v>
       </c>
       <c r="AB4">
-        <v>-1.3</v>
+        <v>-0.25</v>
       </c>
       <c r="AC4">
-        <v>17.67</v>
+        <v>47.73</v>
       </c>
       <c r="AD4">
-        <v>15.67</v>
+        <v>24.13</v>
       </c>
       <c r="AE4">
-        <v>10.72</v>
+        <v>12.34</v>
       </c>
       <c r="AF4">
-        <v>-83.40000000000001</v>
+        <v>1223.89</v>
       </c>
       <c r="AG4">
-        <v>318.34</v>
+        <v>315.58</v>
       </c>
       <c r="AH4">
-        <v>275.17</v>
+        <v>275.73</v>
       </c>
       <c r="AI4">
         <v>308.71</v>
@@ -1265,7 +1221,7 @@
         <v>47</v>
       </c>
       <c r="AK4">
-        <v>28.97</v>
+        <v>31.17</v>
       </c>
     </row>
     <row r="5" spans="1:37">
@@ -1276,58 +1232,58 @@
         <v>44</v>
       </c>
       <c r="C5">
-        <v>1677</v>
+        <v>1652.4</v>
       </c>
       <c r="D5">
-        <v>0.37</v>
+        <v>-1.47</v>
       </c>
       <c r="E5">
-        <v>2176.6</v>
+        <v>2170.2</v>
       </c>
       <c r="F5">
         <v>1631.8</v>
       </c>
       <c r="G5">
-        <v>-22.95</v>
+        <v>-23.86</v>
       </c>
       <c r="H5">
-        <v>2.77</v>
+        <v>1.26</v>
       </c>
       <c r="I5">
-        <v>-1.35</v>
+        <v>-2.22</v>
       </c>
       <c r="J5">
-        <v>-4.84</v>
+        <v>-6.7</v>
       </c>
       <c r="K5">
-        <v>-12.34</v>
+        <v>-14.29</v>
       </c>
       <c r="L5">
-        <v>-22.69</v>
+        <v>-24.08</v>
       </c>
       <c r="M5">
-        <v>-1.38</v>
+        <v>-1.64</v>
       </c>
       <c r="N5">
         <v>29</v>
       </c>
       <c r="O5">
-        <v>41</v>
+        <v>35</v>
       </c>
       <c r="P5">
-        <v>1674.18</v>
+        <v>1666.66</v>
       </c>
       <c r="Q5">
-        <v>1718.85</v>
+        <v>1713.87</v>
       </c>
       <c r="R5">
-        <v>1851.01</v>
+        <v>1843.9</v>
       </c>
       <c r="S5">
-        <v>1858.85</v>
+        <v>1856.95</v>
       </c>
       <c r="T5">
-        <v>-9.779999999999999</v>
+        <v>-11.02</v>
       </c>
       <c r="U5" t="s">
         <v>45</v>
@@ -1342,43 +1298,43 @@
         <v>0</v>
       </c>
       <c r="Y5">
-        <v>33.93</v>
+        <v>30.66</v>
       </c>
       <c r="Z5">
-        <v>-47.08</v>
+        <v>-47.48</v>
       </c>
       <c r="AA5">
-        <v>-48.25</v>
+        <v>-48.09</v>
       </c>
       <c r="AB5">
-        <v>1.16</v>
+        <v>0.61</v>
       </c>
       <c r="AC5">
-        <v>41.07</v>
+        <v>47.53</v>
       </c>
       <c r="AD5">
-        <v>36.29</v>
+        <v>40.77</v>
       </c>
       <c r="AE5">
-        <v>38.25</v>
+        <v>39.24</v>
       </c>
       <c r="AF5">
-        <v>130.11</v>
+        <v>36.35</v>
       </c>
       <c r="AG5">
-        <v>1780.01</v>
+        <v>1779.71</v>
       </c>
       <c r="AH5">
-        <v>1657.69</v>
+        <v>1648.03</v>
       </c>
       <c r="AI5">
-        <v>1770.15</v>
+        <v>1762.43</v>
       </c>
       <c r="AJ5" t="s">
         <v>47</v>
       </c>
       <c r="AK5">
-        <v>61.38</v>
+        <v>62.27</v>
       </c>
     </row>
     <row r="6" spans="1:37">
@@ -1389,10 +1345,10 @@
         <v>44</v>
       </c>
       <c r="C6">
-        <v>10901</v>
+        <v>10461</v>
       </c>
       <c r="D6">
-        <v>-1.35</v>
+        <v>-4.04</v>
       </c>
       <c r="E6">
         <v>13144</v>
@@ -1401,46 +1357,46 @@
         <v>8746</v>
       </c>
       <c r="G6">
-        <v>-17.06</v>
+        <v>-20.41</v>
       </c>
       <c r="H6">
-        <v>24.64</v>
+        <v>19.61</v>
       </c>
       <c r="I6">
-        <v>-3.23</v>
+        <v>-4.68</v>
       </c>
       <c r="J6">
-        <v>-0.15</v>
+        <v>-4.38</v>
       </c>
       <c r="K6">
-        <v>0.84</v>
+        <v>-3.42</v>
       </c>
       <c r="L6">
-        <v>-14.38</v>
+        <v>-20.41</v>
       </c>
       <c r="M6">
-        <v>19.19</v>
+        <v>18.27</v>
       </c>
       <c r="N6">
         <v>57</v>
       </c>
       <c r="O6">
-        <v>63</v>
+        <v>51</v>
       </c>
       <c r="P6">
-        <v>11078.8</v>
+        <v>10976</v>
       </c>
       <c r="Q6">
-        <v>10884.1</v>
+        <v>10867.15</v>
       </c>
       <c r="R6">
-        <v>11089.04</v>
+        <v>11068.76</v>
       </c>
       <c r="S6">
-        <v>10656.24</v>
+        <v>10652.56</v>
       </c>
       <c r="T6">
-        <v>2.3</v>
+        <v>-1.8</v>
       </c>
       <c r="U6" t="s">
         <v>45</v>
@@ -1452,37 +1408,37 @@
         <v>45</v>
       </c>
       <c r="X6">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="Y6">
-        <v>47.54</v>
+        <v>39</v>
       </c>
       <c r="Z6">
-        <v>20.31</v>
+        <v>-25.75</v>
       </c>
       <c r="AA6">
-        <v>-7.21</v>
+        <v>-10.92</v>
       </c>
       <c r="AB6">
-        <v>27.52</v>
+        <v>-14.83</v>
       </c>
       <c r="AC6">
-        <v>58.41</v>
+        <v>32.76</v>
       </c>
       <c r="AD6">
-        <v>70.17</v>
+        <v>56.01</v>
       </c>
       <c r="AE6">
-        <v>299.37</v>
+        <v>309.42</v>
       </c>
       <c r="AF6">
-        <v>95.76000000000001</v>
+        <v>-39.29</v>
       </c>
       <c r="AG6">
-        <v>11357.88</v>
+        <v>11376.52</v>
       </c>
       <c r="AH6">
-        <v>10410.32</v>
+        <v>10357.78</v>
       </c>
       <c r="AI6">
         <v>11368.55</v>
@@ -1491,7 +1447,7 @@
         <v>47</v>
       </c>
       <c r="AK6">
-        <v>22.65</v>
+        <v>24.63</v>
       </c>
     </row>
     <row r="7" spans="1:37">
@@ -1502,10 +1458,10 @@
         <v>44</v>
       </c>
       <c r="C7">
-        <v>912</v>
+        <v>917.25</v>
       </c>
       <c r="D7">
-        <v>-0.73</v>
+        <v>0.58</v>
       </c>
       <c r="E7">
         <v>1158.8</v>
@@ -1514,25 +1470,25 @@
         <v>801.55</v>
       </c>
       <c r="G7">
-        <v>-21.3</v>
+        <v>-20.84</v>
       </c>
       <c r="H7">
-        <v>13.78</v>
+        <v>14.43</v>
       </c>
       <c r="I7">
-        <v>-4.74</v>
+        <v>-0.9399999999999999</v>
       </c>
       <c r="J7">
-        <v>-7.13</v>
+        <v>-7.99</v>
       </c>
       <c r="K7">
-        <v>-13</v>
+        <v>-12.51</v>
       </c>
       <c r="L7">
-        <v>-16.06</v>
+        <v>-16.17</v>
       </c>
       <c r="M7">
-        <v>4.44</v>
+        <v>4.55</v>
       </c>
       <c r="N7">
         <v>43</v>
@@ -1541,19 +1497,19 @@
         <v>45</v>
       </c>
       <c r="P7">
-        <v>925.55</v>
+        <v>923.8</v>
       </c>
       <c r="Q7">
-        <v>955.4400000000001</v>
+        <v>952.05</v>
       </c>
       <c r="R7">
-        <v>1013.85</v>
+        <v>1010.46</v>
       </c>
       <c r="S7">
-        <v>972.8099999999999</v>
+        <v>972.55</v>
       </c>
       <c r="T7">
-        <v>-6.25</v>
+        <v>-5.69</v>
       </c>
       <c r="U7" t="s">
         <v>45</v>
@@ -1568,43 +1524,43 @@
         <v>1</v>
       </c>
       <c r="Y7">
-        <v>35</v>
+        <v>36.73</v>
       </c>
       <c r="Z7">
-        <v>-24.16</v>
+        <v>-24.49</v>
       </c>
       <c r="AA7">
-        <v>-21.95</v>
+        <v>-22.46</v>
       </c>
       <c r="AB7">
-        <v>-2.21</v>
+        <v>-2.03</v>
       </c>
       <c r="AC7">
-        <v>7.63</v>
+        <v>5.9</v>
       </c>
       <c r="AD7">
-        <v>21.98</v>
+        <v>13.1</v>
       </c>
       <c r="AE7">
-        <v>27.38</v>
+        <v>26.84</v>
       </c>
       <c r="AF7">
-        <v>-26.91</v>
+        <v>-33.3</v>
       </c>
       <c r="AG7">
-        <v>996.95</v>
+        <v>994.46</v>
       </c>
       <c r="AH7">
-        <v>913.9299999999999</v>
+        <v>909.65</v>
       </c>
       <c r="AI7">
-        <v>997.89</v>
+        <v>989.6</v>
       </c>
       <c r="AJ7" t="s">
         <v>47</v>
       </c>
       <c r="AK7">
-        <v>26.01</v>
+        <v>28.11</v>
       </c>
     </row>
     <row r="8" spans="1:37">
@@ -1615,10 +1571,10 @@
         <v>44</v>
       </c>
       <c r="C8">
-        <v>148.69</v>
+        <v>148.42</v>
       </c>
       <c r="D8">
-        <v>1.79</v>
+        <v>-0.18</v>
       </c>
       <c r="E8">
         <v>185.92</v>
@@ -1627,46 +1583,46 @@
         <v>115.96</v>
       </c>
       <c r="G8">
-        <v>-20.02</v>
+        <v>-20.17</v>
       </c>
       <c r="H8">
-        <v>28.23</v>
+        <v>27.99</v>
       </c>
       <c r="I8">
-        <v>-9.6</v>
+        <v>-5.35</v>
       </c>
       <c r="J8">
-        <v>-4.23</v>
+        <v>-11.15</v>
       </c>
       <c r="K8">
-        <v>5.78</v>
+        <v>6.7</v>
       </c>
       <c r="L8">
-        <v>14.92</v>
+        <v>14.81</v>
       </c>
       <c r="M8">
-        <v>2.72</v>
+        <v>2.96</v>
       </c>
       <c r="N8">
         <v>99</v>
       </c>
       <c r="O8">
-        <v>81</v>
+        <v>79</v>
       </c>
       <c r="P8">
-        <v>149.6</v>
+        <v>147.92</v>
       </c>
       <c r="Q8">
-        <v>169.01</v>
+        <v>167.88</v>
       </c>
       <c r="R8">
-        <v>150.84</v>
+        <v>151.12</v>
       </c>
       <c r="S8">
-        <v>137.8</v>
+        <v>137.85</v>
       </c>
       <c r="T8">
-        <v>7.9</v>
+        <v>7.67</v>
       </c>
       <c r="U8" t="s">
         <v>46</v>
@@ -1681,34 +1637,34 @@
         <v>3</v>
       </c>
       <c r="Y8">
-        <v>40.6</v>
+        <v>40.41</v>
       </c>
       <c r="Z8">
-        <v>-0.92</v>
+        <v>-1.66</v>
       </c>
       <c r="AA8">
-        <v>3.72</v>
+        <v>2.64</v>
       </c>
       <c r="AB8">
-        <v>-4.64</v>
+        <v>-4.31</v>
       </c>
       <c r="AC8">
-        <v>6.9</v>
+        <v>12.93</v>
       </c>
       <c r="AD8">
-        <v>3.1</v>
+        <v>7.41</v>
       </c>
       <c r="AE8">
-        <v>8.31</v>
+        <v>8.050000000000001</v>
       </c>
       <c r="AF8">
-        <v>-86.34999999999999</v>
+        <v>-80.23999999999999</v>
       </c>
       <c r="AG8">
-        <v>194.35</v>
+        <v>194.81</v>
       </c>
       <c r="AH8">
-        <v>143.67</v>
+        <v>140.95</v>
       </c>
       <c r="AI8">
         <v>170.73</v>
@@ -1717,7 +1673,7 @@
         <v>47</v>
       </c>
       <c r="AK8">
-        <v>43.64</v>
+        <v>45.02</v>
       </c>
     </row>
   </sheetData>
@@ -1858,7 +1814,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:F65"/>
+  <dimension ref="A1:F62"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="16.7109375" customWidth="1"/>
@@ -1878,1080 +1834,991 @@
     </row>
     <row r="2" spans="1:6">
       <c r="A2" s="3" t="s">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="5" spans="1:6">
+      <c r="A5" s="2" t="s">
+        <v>50</v>
+      </c>
+      <c r="B5" s="2"/>
+      <c r="C5" s="2"/>
+      <c r="D5" s="2"/>
+      <c r="E5" s="2"/>
+    </row>
+    <row r="6" spans="1:6">
+      <c r="A6" s="4" t="s">
         <v>0</v>
       </c>
-      <c r="B2" s="3" t="s">
-        <v>49</v>
-      </c>
-      <c r="C2" s="3" t="s">
-        <v>50</v>
-      </c>
-      <c r="D2" s="3" t="s">
+      <c r="B6" s="4" t="s">
         <v>51</v>
       </c>
-      <c r="E2" s="3" t="s">
+      <c r="C6" s="4" t="s">
         <v>52</v>
       </c>
-      <c r="F2" s="3" t="s">
+      <c r="D6" s="4" t="s">
         <v>53</v>
       </c>
-    </row>
-    <row r="3" spans="1:6">
-      <c r="A3" s="4" t="s">
-        <v>39</v>
-      </c>
-      <c r="B3" s="4" t="s">
+      <c r="E6" s="4" t="s">
         <v>54</v>
       </c>
-      <c r="C3" s="4" t="s">
-        <v>55</v>
-      </c>
-      <c r="D3" s="4" t="s">
-        <v>56</v>
-      </c>
-      <c r="E3" s="4" t="s">
-        <v>57</v>
-      </c>
-      <c r="F3" s="4" t="s">
-        <v>58</v>
-      </c>
-    </row>
-    <row r="4" spans="1:6">
-      <c r="A4" s="5" t="s">
-        <v>41</v>
-      </c>
-      <c r="B4" s="5" t="s">
-        <v>59</v>
-      </c>
-      <c r="C4" s="5" t="s">
-        <v>60</v>
-      </c>
-      <c r="D4" s="5" t="s">
-        <v>61</v>
-      </c>
-      <c r="E4" s="5" t="s">
-        <v>62</v>
-      </c>
-      <c r="F4" s="5" t="s">
-        <v>63</v>
-      </c>
-    </row>
-    <row r="6" spans="1:6">
-      <c r="A6" s="2" t="s">
-        <v>64</v>
-      </c>
-      <c r="B6" s="2"/>
-      <c r="C6" s="2"/>
-      <c r="D6" s="2"/>
-      <c r="E6" s="2"/>
     </row>
     <row r="7" spans="1:6">
       <c r="A7" s="3" t="s">
-        <v>0</v>
+        <v>37</v>
       </c>
       <c r="B7" s="3" t="s">
-        <v>65</v>
-      </c>
-      <c r="C7" s="3" t="s">
-        <v>66</v>
-      </c>
-      <c r="D7" s="3" t="s">
-        <v>67</v>
-      </c>
-      <c r="E7" s="3" t="s">
-        <v>68</v>
+        <v>9</v>
+      </c>
+      <c r="C7" s="5">
+        <v>-7.3</v>
+      </c>
+      <c r="D7" s="5">
+        <v>-7.06</v>
+      </c>
+      <c r="E7" s="6">
+        <v>0.24</v>
       </c>
     </row>
     <row r="8" spans="1:6">
-      <c r="A8" s="6" t="s">
+      <c r="A8" s="3" t="s">
+        <v>38</v>
+      </c>
+      <c r="B8" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="C8" s="5">
+        <v>-22.96</v>
+      </c>
+      <c r="D8" s="5">
+        <v>-23.66</v>
+      </c>
+      <c r="E8" s="7">
+        <v>-0.7</v>
+      </c>
+    </row>
+    <row r="9" spans="1:6">
+      <c r="A9" s="3" t="s">
+        <v>39</v>
+      </c>
+      <c r="B9" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="C9" s="5">
+        <v>-12.33</v>
+      </c>
+      <c r="D9" s="5">
+        <v>-8.25</v>
+      </c>
+      <c r="E9" s="6">
+        <v>4.08</v>
+      </c>
+    </row>
+    <row r="10" spans="1:6">
+      <c r="A10" s="3" t="s">
+        <v>40</v>
+      </c>
+      <c r="B10" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="C10" s="5">
+        <v>-4.84</v>
+      </c>
+      <c r="D10" s="5">
+        <v>-6.7</v>
+      </c>
+      <c r="E10" s="7">
+        <v>-1.86</v>
+      </c>
+    </row>
+    <row r="11" spans="1:6">
+      <c r="A11" s="3" t="s">
+        <v>41</v>
+      </c>
+      <c r="B11" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="C11" s="5">
+        <v>-0.15</v>
+      </c>
+      <c r="D11" s="5">
+        <v>-4.38</v>
+      </c>
+      <c r="E11" s="7">
+        <v>-4.23</v>
+      </c>
+    </row>
+    <row r="12" spans="1:6">
+      <c r="A12" s="3" t="s">
+        <v>42</v>
+      </c>
+      <c r="B12" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="C12" s="5">
+        <v>-7.13</v>
+      </c>
+      <c r="D12" s="5">
+        <v>-7.99</v>
+      </c>
+      <c r="E12" s="7">
+        <v>-0.86</v>
+      </c>
+    </row>
+    <row r="13" spans="1:6">
+      <c r="A13" s="3" t="s">
+        <v>43</v>
+      </c>
+      <c r="B13" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="C13" s="5">
+        <v>-4.23</v>
+      </c>
+      <c r="D13" s="5">
+        <v>-11.15</v>
+      </c>
+      <c r="E13" s="7">
+        <v>-6.92</v>
+      </c>
+    </row>
+    <row r="14" spans="1:6">
+      <c r="A14" s="3" t="s">
         <v>37</v>
       </c>
-      <c r="B8" s="6" t="s">
-        <v>9</v>
-      </c>
-      <c r="C8" s="7">
-        <v>-11.66</v>
-      </c>
-      <c r="D8" s="7">
-        <v>-7.3</v>
-      </c>
-      <c r="E8" s="8">
-        <v>4.36</v>
-      </c>
-    </row>
-    <row r="9" spans="1:6">
-      <c r="A9" s="6" t="s">
+      <c r="B14" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="C14" s="5">
+        <v>1</v>
+      </c>
+      <c r="D14" s="5">
+        <v>4.1</v>
+      </c>
+      <c r="E14" s="6">
+        <v>3.1</v>
+      </c>
+    </row>
+    <row r="15" spans="1:6">
+      <c r="A15" s="3" t="s">
         <v>38</v>
       </c>
-      <c r="B9" s="6" t="s">
-        <v>9</v>
-      </c>
-      <c r="C9" s="7">
-        <v>-23.43</v>
-      </c>
-      <c r="D9" s="7">
-        <v>-22.96</v>
-      </c>
-      <c r="E9" s="8">
-        <v>0.47</v>
-      </c>
-    </row>
-    <row r="10" spans="1:6">
-      <c r="A10" s="6" t="s">
+      <c r="B15" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="C15" s="5">
+        <v>-13.54</v>
+      </c>
+      <c r="D15" s="5">
+        <v>-10.37</v>
+      </c>
+      <c r="E15" s="6">
+        <v>3.17</v>
+      </c>
+    </row>
+    <row r="16" spans="1:6">
+      <c r="A16" s="3" t="s">
         <v>39</v>
       </c>
-      <c r="B10" s="6" t="s">
-        <v>9</v>
-      </c>
-      <c r="C10" s="7">
-        <v>-16.32</v>
-      </c>
-      <c r="D10" s="7">
-        <v>-12.33</v>
-      </c>
-      <c r="E10" s="8">
-        <v>3.99</v>
-      </c>
-    </row>
-    <row r="11" spans="1:6">
-      <c r="A11" s="6" t="s">
+      <c r="B16" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="C16" s="5">
+        <v>-4.91</v>
+      </c>
+      <c r="D16" s="5">
+        <v>-0.15</v>
+      </c>
+      <c r="E16" s="6">
+        <v>4.76</v>
+      </c>
+    </row>
+    <row r="17" spans="1:5">
+      <c r="A17" s="3" t="s">
         <v>40</v>
       </c>
-      <c r="B11" s="6" t="s">
-        <v>9</v>
-      </c>
-      <c r="C11" s="7">
-        <v>-9.51</v>
-      </c>
-      <c r="D11" s="7">
-        <v>-4.84</v>
-      </c>
-      <c r="E11" s="8">
-        <v>4.67</v>
-      </c>
-    </row>
-    <row r="12" spans="1:6">
-      <c r="A12" s="6" t="s">
+      <c r="B17" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="C17" s="5">
+        <v>-1.35</v>
+      </c>
+      <c r="D17" s="5">
+        <v>-2.22</v>
+      </c>
+      <c r="E17" s="7">
+        <v>-0.87</v>
+      </c>
+    </row>
+    <row r="18" spans="1:5">
+      <c r="A18" s="3" t="s">
         <v>41</v>
       </c>
-      <c r="B12" s="6" t="s">
-        <v>9</v>
-      </c>
-      <c r="C12" s="7">
-        <v>-3.49</v>
-      </c>
-      <c r="D12" s="7">
+      <c r="B18" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="C18" s="5">
+        <v>-3.23</v>
+      </c>
+      <c r="D18" s="5">
+        <v>-4.68</v>
+      </c>
+      <c r="E18" s="7">
+        <v>-1.45</v>
+      </c>
+    </row>
+    <row r="19" spans="1:5">
+      <c r="A19" s="3" t="s">
+        <v>42</v>
+      </c>
+      <c r="B19" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="C19" s="5">
+        <v>-4.74</v>
+      </c>
+      <c r="D19" s="5">
+        <v>-0.9399999999999999</v>
+      </c>
+      <c r="E19" s="6">
+        <v>3.8</v>
+      </c>
+    </row>
+    <row r="20" spans="1:5">
+      <c r="A20" s="3" t="s">
+        <v>43</v>
+      </c>
+      <c r="B20" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="C20" s="5">
+        <v>-9.6</v>
+      </c>
+      <c r="D20" s="5">
+        <v>-5.35</v>
+      </c>
+      <c r="E20" s="6">
+        <v>4.25</v>
+      </c>
+    </row>
+    <row r="21" spans="1:5">
+      <c r="A21" s="3" t="s">
+        <v>37</v>
+      </c>
+      <c r="B21" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="C21" s="5">
+        <v>15.55</v>
+      </c>
+      <c r="D21" s="5">
+        <v>17.53</v>
+      </c>
+      <c r="E21" s="6">
+        <v>1.98</v>
+      </c>
+    </row>
+    <row r="22" spans="1:5">
+      <c r="A22" s="3" t="s">
+        <v>38</v>
+      </c>
+      <c r="B22" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="C22" s="5">
+        <v>41.66</v>
+      </c>
+      <c r="D22" s="5">
+        <v>39.59</v>
+      </c>
+      <c r="E22" s="7">
+        <v>-2.07</v>
+      </c>
+    </row>
+    <row r="23" spans="1:5">
+      <c r="A23" s="3" t="s">
+        <v>39</v>
+      </c>
+      <c r="B23" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="C23" s="5">
+        <v>-48.03</v>
+      </c>
+      <c r="D23" s="5">
+        <v>-45.1</v>
+      </c>
+      <c r="E23" s="6">
+        <v>2.93</v>
+      </c>
+    </row>
+    <row r="24" spans="1:5">
+      <c r="A24" s="3" t="s">
+        <v>40</v>
+      </c>
+      <c r="B24" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="C24" s="5">
+        <v>-22.69</v>
+      </c>
+      <c r="D24" s="5">
+        <v>-24.08</v>
+      </c>
+      <c r="E24" s="7">
+        <v>-1.39</v>
+      </c>
+    </row>
+    <row r="25" spans="1:5">
+      <c r="A25" s="3" t="s">
+        <v>41</v>
+      </c>
+      <c r="B25" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="C25" s="5">
+        <v>-14.38</v>
+      </c>
+      <c r="D25" s="5">
+        <v>-20.41</v>
+      </c>
+      <c r="E25" s="7">
+        <v>-6.03</v>
+      </c>
+    </row>
+    <row r="26" spans="1:5">
+      <c r="A26" s="3" t="s">
+        <v>42</v>
+      </c>
+      <c r="B26" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="C26" s="5">
+        <v>-16.06</v>
+      </c>
+      <c r="D26" s="5">
+        <v>-16.17</v>
+      </c>
+      <c r="E26" s="7">
+        <v>-0.11</v>
+      </c>
+    </row>
+    <row r="27" spans="1:5">
+      <c r="A27" s="3" t="s">
+        <v>43</v>
+      </c>
+      <c r="B27" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="C27" s="5">
+        <v>14.92</v>
+      </c>
+      <c r="D27" s="5">
+        <v>14.81</v>
+      </c>
+      <c r="E27" s="7">
+        <v>-0.11</v>
+      </c>
+    </row>
+    <row r="28" spans="1:5">
+      <c r="A28" s="3" t="s">
+        <v>37</v>
+      </c>
+      <c r="B28" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="C28" s="5">
+        <v>-7.1</v>
+      </c>
+      <c r="D28" s="5">
+        <v>-7.82</v>
+      </c>
+      <c r="E28" s="7">
+        <v>-0.72</v>
+      </c>
+    </row>
+    <row r="29" spans="1:5">
+      <c r="A29" s="3" t="s">
+        <v>38</v>
+      </c>
+      <c r="B29" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="C29" s="5">
+        <v>-28.54</v>
+      </c>
+      <c r="D29" s="5">
+        <v>-28.19</v>
+      </c>
+      <c r="E29" s="6">
+        <v>0.35</v>
+      </c>
+    </row>
+    <row r="30" spans="1:5">
+      <c r="A30" s="3" t="s">
+        <v>39</v>
+      </c>
+      <c r="B30" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="C30" s="5">
+        <v>-14.45</v>
+      </c>
+      <c r="D30" s="5">
+        <v>-10.52</v>
+      </c>
+      <c r="E30" s="6">
+        <v>3.93</v>
+      </c>
+    </row>
+    <row r="31" spans="1:5">
+      <c r="A31" s="3" t="s">
+        <v>40</v>
+      </c>
+      <c r="B31" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="C31" s="5">
+        <v>-12.34</v>
+      </c>
+      <c r="D31" s="5">
+        <v>-14.29</v>
+      </c>
+      <c r="E31" s="7">
+        <v>-1.95</v>
+      </c>
+    </row>
+    <row r="32" spans="1:5">
+      <c r="A32" s="3" t="s">
+        <v>41</v>
+      </c>
+      <c r="B32" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="C32" s="5">
+        <v>0.84</v>
+      </c>
+      <c r="D32" s="5">
+        <v>-3.42</v>
+      </c>
+      <c r="E32" s="7">
+        <v>-4.26</v>
+      </c>
+    </row>
+    <row r="33" spans="1:5">
+      <c r="A33" s="3" t="s">
+        <v>42</v>
+      </c>
+      <c r="B33" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="C33" s="5">
+        <v>-13</v>
+      </c>
+      <c r="D33" s="5">
+        <v>-12.51</v>
+      </c>
+      <c r="E33" s="6">
+        <v>0.49</v>
+      </c>
+    </row>
+    <row r="34" spans="1:5">
+      <c r="A34" s="3" t="s">
+        <v>43</v>
+      </c>
+      <c r="B34" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="C34" s="5">
+        <v>5.78</v>
+      </c>
+      <c r="D34" s="5">
+        <v>6.7</v>
+      </c>
+      <c r="E34" s="6">
+        <v>0.92</v>
+      </c>
+    </row>
+    <row r="35" spans="1:5">
+      <c r="A35" s="3" t="s">
+        <v>37</v>
+      </c>
+      <c r="B35" s="3" t="s">
+        <v>6</v>
+      </c>
+      <c r="C35" s="5">
+        <v>-15.95</v>
+      </c>
+      <c r="D35" s="5">
+        <v>-15.18</v>
+      </c>
+      <c r="E35" s="6">
+        <v>0.77</v>
+      </c>
+    </row>
+    <row r="36" spans="1:5">
+      <c r="A36" s="3" t="s">
+        <v>38</v>
+      </c>
+      <c r="B36" s="3" t="s">
+        <v>6</v>
+      </c>
+      <c r="C36" s="5">
+        <v>-42.33</v>
+      </c>
+      <c r="D36" s="5">
+        <v>-43.11</v>
+      </c>
+      <c r="E36" s="7">
+        <v>-0.78</v>
+      </c>
+    </row>
+    <row r="37" spans="1:5">
+      <c r="A37" s="3" t="s">
+        <v>39</v>
+      </c>
+      <c r="B37" s="3" t="s">
+        <v>6</v>
+      </c>
+      <c r="C37" s="5">
+        <v>-47.13</v>
+      </c>
+      <c r="D37" s="5">
+        <v>-44.77</v>
+      </c>
+      <c r="E37" s="6">
+        <v>2.36</v>
+      </c>
+    </row>
+    <row r="38" spans="1:5">
+      <c r="A38" s="3" t="s">
+        <v>40</v>
+      </c>
+      <c r="B38" s="3" t="s">
+        <v>6</v>
+      </c>
+      <c r="C38" s="5">
+        <v>-22.95</v>
+      </c>
+      <c r="D38" s="5">
+        <v>-23.86</v>
+      </c>
+      <c r="E38" s="7">
+        <v>-0.91</v>
+      </c>
+    </row>
+    <row r="39" spans="1:5">
+      <c r="A39" s="3" t="s">
+        <v>41</v>
+      </c>
+      <c r="B39" s="3" t="s">
+        <v>6</v>
+      </c>
+      <c r="C39" s="5">
+        <v>-17.06</v>
+      </c>
+      <c r="D39" s="5">
+        <v>-20.41</v>
+      </c>
+      <c r="E39" s="7">
+        <v>-3.35</v>
+      </c>
+    </row>
+    <row r="40" spans="1:5">
+      <c r="A40" s="3" t="s">
+        <v>42</v>
+      </c>
+      <c r="B40" s="3" t="s">
+        <v>6</v>
+      </c>
+      <c r="C40" s="5">
+        <v>-21.3</v>
+      </c>
+      <c r="D40" s="5">
+        <v>-20.84</v>
+      </c>
+      <c r="E40" s="6">
+        <v>0.46</v>
+      </c>
+    </row>
+    <row r="41" spans="1:5">
+      <c r="A41" s="3" t="s">
+        <v>43</v>
+      </c>
+      <c r="B41" s="3" t="s">
+        <v>6</v>
+      </c>
+      <c r="C41" s="5">
+        <v>-20.02</v>
+      </c>
+      <c r="D41" s="5">
+        <v>-20.17</v>
+      </c>
+      <c r="E41" s="7">
         <v>-0.15</v>
       </c>
-      <c r="E12" s="8">
-        <v>3.34</v>
-      </c>
-    </row>
-    <row r="13" spans="1:6">
-      <c r="A13" s="6" t="s">
+    </row>
+    <row r="42" spans="1:5">
+      <c r="A42" s="3" t="s">
+        <v>37</v>
+      </c>
+      <c r="B42" s="3" t="s">
+        <v>2</v>
+      </c>
+      <c r="C42" s="5">
+        <v>10390</v>
+      </c>
+      <c r="D42" s="5">
+        <v>10485</v>
+      </c>
+      <c r="E42" s="6">
+        <v>95</v>
+      </c>
+    </row>
+    <row r="43" spans="1:5">
+      <c r="A43" s="3" t="s">
+        <v>38</v>
+      </c>
+      <c r="B43" s="3" t="s">
+        <v>2</v>
+      </c>
+      <c r="C43" s="5">
+        <v>386.5</v>
+      </c>
+      <c r="D43" s="5">
+        <v>381.3</v>
+      </c>
+      <c r="E43" s="7">
+        <v>-5.2</v>
+      </c>
+    </row>
+    <row r="44" spans="1:5">
+      <c r="A44" s="3" t="s">
+        <v>39</v>
+      </c>
+      <c r="B44" s="3" t="s">
+        <v>2</v>
+      </c>
+      <c r="C44" s="5">
+        <v>281.8</v>
+      </c>
+      <c r="D44" s="5">
+        <v>292.65</v>
+      </c>
+      <c r="E44" s="6">
+        <v>10.85</v>
+      </c>
+    </row>
+    <row r="45" spans="1:5">
+      <c r="A45" s="3" t="s">
+        <v>40</v>
+      </c>
+      <c r="B45" s="3" t="s">
+        <v>2</v>
+      </c>
+      <c r="C45" s="5">
+        <v>1677</v>
+      </c>
+      <c r="D45" s="5">
+        <v>1652.4</v>
+      </c>
+      <c r="E45" s="7">
+        <v>-24.6</v>
+      </c>
+    </row>
+    <row r="46" spans="1:5">
+      <c r="A46" s="3" t="s">
+        <v>41</v>
+      </c>
+      <c r="B46" s="3" t="s">
+        <v>2</v>
+      </c>
+      <c r="C46" s="5">
+        <v>10901</v>
+      </c>
+      <c r="D46" s="5">
+        <v>10461</v>
+      </c>
+      <c r="E46" s="7">
+        <v>-440</v>
+      </c>
+    </row>
+    <row r="47" spans="1:5">
+      <c r="A47" s="3" t="s">
         <v>42</v>
       </c>
-      <c r="B13" s="6" t="s">
-        <v>9</v>
-      </c>
-      <c r="C13" s="7">
-        <v>-11.93</v>
-      </c>
-      <c r="D13" s="7">
-        <v>-7.13</v>
-      </c>
-      <c r="E13" s="8">
-        <v>4.8</v>
-      </c>
-    </row>
-    <row r="14" spans="1:6">
-      <c r="A14" s="6" t="s">
+      <c r="B47" s="3" t="s">
+        <v>2</v>
+      </c>
+      <c r="C47" s="5">
+        <v>912</v>
+      </c>
+      <c r="D47" s="5">
+        <v>917.25</v>
+      </c>
+      <c r="E47" s="6">
+        <v>5.25</v>
+      </c>
+    </row>
+    <row r="48" spans="1:5">
+      <c r="A48" s="3" t="s">
         <v>43</v>
       </c>
-      <c r="B14" s="6" t="s">
-        <v>9</v>
-      </c>
-      <c r="C14" s="7">
-        <v>-7.03</v>
-      </c>
-      <c r="D14" s="7">
-        <v>-4.23</v>
-      </c>
-      <c r="E14" s="8">
-        <v>2.8</v>
-      </c>
-    </row>
-    <row r="15" spans="1:6">
-      <c r="A15" s="6" t="s">
+      <c r="B48" s="3" t="s">
+        <v>2</v>
+      </c>
+      <c r="C48" s="5">
+        <v>148.69</v>
+      </c>
+      <c r="D48" s="5">
+        <v>148.42</v>
+      </c>
+      <c r="E48" s="7">
+        <v>-0.27</v>
+      </c>
+    </row>
+    <row r="49" spans="1:5">
+      <c r="A49" s="3" t="s">
         <v>37</v>
       </c>
-      <c r="B15" s="6" t="s">
-        <v>8</v>
-      </c>
-      <c r="C15" s="7">
-        <v>-3.21</v>
-      </c>
-      <c r="D15" s="7">
-        <v>1</v>
-      </c>
-      <c r="E15" s="8">
-        <v>4.21</v>
-      </c>
-    </row>
-    <row r="16" spans="1:6">
-      <c r="A16" s="6" t="s">
+      <c r="B49" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="C49" s="5">
+        <v>46.97</v>
+      </c>
+      <c r="D49" s="5">
+        <v>49.47</v>
+      </c>
+      <c r="E49" s="6">
+        <v>2.5</v>
+      </c>
+    </row>
+    <row r="50" spans="1:5">
+      <c r="A50" s="3" t="s">
         <v>38</v>
       </c>
-      <c r="B16" s="6" t="s">
-        <v>8</v>
-      </c>
-      <c r="C16" s="7">
-        <v>-17.93</v>
-      </c>
-      <c r="D16" s="7">
-        <v>-13.54</v>
-      </c>
-      <c r="E16" s="8">
-        <v>4.39</v>
-      </c>
-    </row>
-    <row r="17" spans="1:5">
-      <c r="A17" s="6" t="s">
+      <c r="B50" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="C50" s="5">
+        <v>26.76</v>
+      </c>
+      <c r="D50" s="5">
+        <v>25.96</v>
+      </c>
+      <c r="E50" s="7">
+        <v>-0.8</v>
+      </c>
+    </row>
+    <row r="51" spans="1:5">
+      <c r="A51" s="3" t="s">
         <v>39</v>
       </c>
-      <c r="B17" s="6" t="s">
-        <v>8</v>
-      </c>
-      <c r="C17" s="7">
-        <v>-8.51</v>
-      </c>
-      <c r="D17" s="7">
-        <v>-4.91</v>
-      </c>
-      <c r="E17" s="8">
-        <v>3.6</v>
-      </c>
-    </row>
-    <row r="18" spans="1:5">
-      <c r="A18" s="6" t="s">
+      <c r="B51" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="C51" s="5">
+        <v>32.61</v>
+      </c>
+      <c r="D51" s="5">
+        <v>43.2</v>
+      </c>
+      <c r="E51" s="6">
+        <v>10.59</v>
+      </c>
+    </row>
+    <row r="52" spans="1:5">
+      <c r="A52" s="3" t="s">
         <v>40</v>
       </c>
-      <c r="B18" s="6" t="s">
-        <v>8</v>
-      </c>
-      <c r="C18" s="7">
-        <v>-3.36</v>
-      </c>
-      <c r="D18" s="7">
-        <v>-1.35</v>
-      </c>
-      <c r="E18" s="8">
-        <v>2.01</v>
-      </c>
-    </row>
-    <row r="19" spans="1:5">
-      <c r="A19" s="6" t="s">
+      <c r="B52" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="C52" s="5">
+        <v>33.93</v>
+      </c>
+      <c r="D52" s="5">
+        <v>30.66</v>
+      </c>
+      <c r="E52" s="7">
+        <v>-3.27</v>
+      </c>
+    </row>
+    <row r="53" spans="1:5">
+      <c r="A53" s="3" t="s">
         <v>41</v>
       </c>
-      <c r="B19" s="6" t="s">
-        <v>8</v>
-      </c>
-      <c r="C19" s="7">
-        <v>-1.32</v>
-      </c>
-      <c r="D19" s="7">
-        <v>-3.23</v>
-      </c>
-      <c r="E19" s="9">
-        <v>-1.91</v>
-      </c>
-    </row>
-    <row r="20" spans="1:5">
-      <c r="A20" s="6" t="s">
+      <c r="B53" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="C53" s="5">
+        <v>47.54</v>
+      </c>
+      <c r="D53" s="5">
+        <v>39</v>
+      </c>
+      <c r="E53" s="7">
+        <v>-8.539999999999999</v>
+      </c>
+    </row>
+    <row r="54" spans="1:5">
+      <c r="A54" s="3" t="s">
         <v>42</v>
       </c>
-      <c r="B20" s="6" t="s">
-        <v>8</v>
-      </c>
-      <c r="C20" s="7">
-        <v>-6.46</v>
-      </c>
-      <c r="D20" s="7">
-        <v>-4.74</v>
-      </c>
-      <c r="E20" s="8">
-        <v>1.72</v>
-      </c>
-    </row>
-    <row r="21" spans="1:5">
-      <c r="A21" s="6" t="s">
+      <c r="B54" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="C54" s="5">
+        <v>35</v>
+      </c>
+      <c r="D54" s="5">
+        <v>36.73</v>
+      </c>
+      <c r="E54" s="6">
+        <v>1.73</v>
+      </c>
+    </row>
+    <row r="55" spans="1:5">
+      <c r="A55" s="3" t="s">
         <v>43</v>
       </c>
-      <c r="B21" s="6" t="s">
-        <v>8</v>
-      </c>
-      <c r="C21" s="7">
-        <v>-15.07</v>
-      </c>
-      <c r="D21" s="7">
-        <v>-9.6</v>
-      </c>
-      <c r="E21" s="8">
-        <v>5.47</v>
-      </c>
-    </row>
-    <row r="22" spans="1:5">
-      <c r="A22" s="6" t="s">
+      <c r="B55" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="C55" s="5">
+        <v>40.6</v>
+      </c>
+      <c r="D55" s="5">
+        <v>40.41</v>
+      </c>
+      <c r="E55" s="7">
+        <v>-0.19</v>
+      </c>
+    </row>
+    <row r="56" spans="1:5">
+      <c r="A56" s="3" t="s">
         <v>37</v>
       </c>
-      <c r="B22" s="6" t="s">
-        <v>11</v>
-      </c>
-      <c r="C22" s="7">
-        <v>11.93</v>
-      </c>
-      <c r="D22" s="7">
-        <v>15.55</v>
-      </c>
-      <c r="E22" s="8">
-        <v>3.62</v>
-      </c>
-    </row>
-    <row r="23" spans="1:5">
-      <c r="A23" s="6" t="s">
+      <c r="B56" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="C56" s="5">
+        <v>11.3</v>
+      </c>
+      <c r="D56" s="5">
+        <v>205.37</v>
+      </c>
+      <c r="E56" s="6">
+        <v>194.07</v>
+      </c>
+    </row>
+    <row r="57" spans="1:5">
+      <c r="A57" s="3" t="s">
         <v>38</v>
       </c>
-      <c r="B23" s="6" t="s">
-        <v>11</v>
-      </c>
-      <c r="C23" s="7">
-        <v>44.16</v>
-      </c>
-      <c r="D23" s="7">
-        <v>41.66</v>
-      </c>
-      <c r="E23" s="9">
-        <v>-2.5</v>
-      </c>
-    </row>
-    <row r="24" spans="1:5">
-      <c r="A24" s="6" t="s">
+      <c r="B57" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="C57" s="5">
+        <v>-72.42</v>
+      </c>
+      <c r="D57" s="5">
+        <v>-69.27</v>
+      </c>
+      <c r="E57" s="6">
+        <v>3.15</v>
+      </c>
+    </row>
+    <row r="58" spans="1:5">
+      <c r="A58" s="3" t="s">
         <v>39</v>
       </c>
-      <c r="B24" s="6" t="s">
-        <v>11</v>
-      </c>
-      <c r="C24" s="7">
-        <v>-48.8</v>
-      </c>
-      <c r="D24" s="7">
-        <v>-48.03</v>
-      </c>
-      <c r="E24" s="8">
-        <v>0.77</v>
-      </c>
-    </row>
-    <row r="25" spans="1:5">
-      <c r="A25" s="6" t="s">
+      <c r="B58" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="C58" s="5">
+        <v>-83.40000000000001</v>
+      </c>
+      <c r="D58" s="5">
+        <v>1223.89</v>
+      </c>
+      <c r="E58" s="6">
+        <v>1307.29</v>
+      </c>
+    </row>
+    <row r="59" spans="1:5">
+      <c r="A59" s="3" t="s">
         <v>40</v>
       </c>
-      <c r="B25" s="6" t="s">
-        <v>11</v>
-      </c>
-      <c r="C25" s="7">
-        <v>-21.91</v>
-      </c>
-      <c r="D25" s="7">
-        <v>-22.69</v>
-      </c>
-      <c r="E25" s="9">
-        <v>-0.78</v>
-      </c>
-    </row>
-    <row r="26" spans="1:5">
-      <c r="A26" s="6" t="s">
+      <c r="B59" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="C59" s="5">
+        <v>130.11</v>
+      </c>
+      <c r="D59" s="5">
+        <v>36.35</v>
+      </c>
+      <c r="E59" s="7">
+        <v>-93.76000000000001</v>
+      </c>
+    </row>
+    <row r="60" spans="1:5">
+      <c r="A60" s="3" t="s">
         <v>41</v>
       </c>
-      <c r="B26" s="6" t="s">
-        <v>11</v>
-      </c>
-      <c r="C26" s="7">
-        <v>-12.34</v>
-      </c>
-      <c r="D26" s="7">
-        <v>-14.38</v>
-      </c>
-      <c r="E26" s="9">
-        <v>-2.04</v>
-      </c>
-    </row>
-    <row r="27" spans="1:5">
-      <c r="A27" s="6" t="s">
+      <c r="B60" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="C60" s="5">
+        <v>95.76000000000001</v>
+      </c>
+      <c r="D60" s="5">
+        <v>-39.29</v>
+      </c>
+      <c r="E60" s="7">
+        <v>-135.05</v>
+      </c>
+    </row>
+    <row r="61" spans="1:5">
+      <c r="A61" s="3" t="s">
         <v>42</v>
       </c>
-      <c r="B27" s="6" t="s">
-        <v>11</v>
-      </c>
-      <c r="C27" s="7">
-        <v>-15.01</v>
-      </c>
-      <c r="D27" s="7">
-        <v>-16.06</v>
-      </c>
-      <c r="E27" s="9">
-        <v>-1.05</v>
-      </c>
-    </row>
-    <row r="28" spans="1:5">
-      <c r="A28" s="6" t="s">
+      <c r="B61" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="C61" s="5">
+        <v>-26.91</v>
+      </c>
+      <c r="D61" s="5">
+        <v>-33.3</v>
+      </c>
+      <c r="E61" s="7">
+        <v>-6.39</v>
+      </c>
+    </row>
+    <row r="62" spans="1:5">
+      <c r="A62" s="3" t="s">
         <v>43</v>
       </c>
-      <c r="B28" s="6" t="s">
-        <v>11</v>
-      </c>
-      <c r="C28" s="7">
-        <v>14.44</v>
-      </c>
-      <c r="D28" s="7">
-        <v>14.92</v>
-      </c>
-      <c r="E28" s="8">
-        <v>0.48</v>
-      </c>
-    </row>
-    <row r="29" spans="1:5">
-      <c r="A29" s="6" t="s">
-        <v>37</v>
-      </c>
-      <c r="B29" s="6" t="s">
-        <v>10</v>
-      </c>
-      <c r="C29" s="7">
-        <v>-9.51</v>
-      </c>
-      <c r="D29" s="7">
-        <v>-7.1</v>
-      </c>
-      <c r="E29" s="8">
-        <v>2.41</v>
-      </c>
-    </row>
-    <row r="30" spans="1:5">
-      <c r="A30" s="6" t="s">
-        <v>38</v>
-      </c>
-      <c r="B30" s="6" t="s">
-        <v>10</v>
-      </c>
-      <c r="C30" s="7">
-        <v>-29.55</v>
-      </c>
-      <c r="D30" s="7">
-        <v>-28.54</v>
-      </c>
-      <c r="E30" s="8">
-        <v>1.01</v>
-      </c>
-    </row>
-    <row r="31" spans="1:5">
-      <c r="A31" s="6" t="s">
-        <v>39</v>
-      </c>
-      <c r="B31" s="6" t="s">
-        <v>10</v>
-      </c>
-      <c r="C31" s="7">
-        <v>-16.19</v>
-      </c>
-      <c r="D31" s="7">
-        <v>-14.45</v>
-      </c>
-      <c r="E31" s="8">
-        <v>1.74</v>
-      </c>
-    </row>
-    <row r="32" spans="1:5">
-      <c r="A32" s="6" t="s">
-        <v>40</v>
-      </c>
-      <c r="B32" s="6" t="s">
-        <v>10</v>
-      </c>
-      <c r="C32" s="7">
-        <v>-10.97</v>
-      </c>
-      <c r="D32" s="7">
-        <v>-12.34</v>
-      </c>
-      <c r="E32" s="9">
-        <v>-1.37</v>
-      </c>
-    </row>
-    <row r="33" spans="1:5">
-      <c r="A33" s="6" t="s">
-        <v>41</v>
-      </c>
-      <c r="B33" s="6" t="s">
-        <v>10</v>
-      </c>
-      <c r="C33" s="7">
-        <v>3.47</v>
-      </c>
-      <c r="D33" s="7">
-        <v>0.84</v>
-      </c>
-      <c r="E33" s="9">
-        <v>-2.63</v>
-      </c>
-    </row>
-    <row r="34" spans="1:5">
-      <c r="A34" s="6" t="s">
-        <v>42</v>
-      </c>
-      <c r="B34" s="6" t="s">
-        <v>10</v>
-      </c>
-      <c r="C34" s="7">
-        <v>-9.289999999999999</v>
-      </c>
-      <c r="D34" s="7">
-        <v>-13</v>
-      </c>
-      <c r="E34" s="9">
-        <v>-3.71</v>
-      </c>
-    </row>
-    <row r="35" spans="1:5">
-      <c r="A35" s="6" t="s">
-        <v>43</v>
-      </c>
-      <c r="B35" s="6" t="s">
-        <v>10</v>
-      </c>
-      <c r="C35" s="7">
-        <v>5.54</v>
-      </c>
-      <c r="D35" s="7">
-        <v>5.78</v>
-      </c>
-      <c r="E35" s="8">
-        <v>0.24</v>
-      </c>
-    </row>
-    <row r="36" spans="1:5">
-      <c r="A36" s="6" t="s">
-        <v>37</v>
-      </c>
-      <c r="B36" s="6" t="s">
-        <v>6</v>
-      </c>
-      <c r="C36" s="7">
-        <v>-18.53</v>
-      </c>
-      <c r="D36" s="7">
-        <v>-15.95</v>
-      </c>
-      <c r="E36" s="8">
-        <v>2.58</v>
-      </c>
-    </row>
-    <row r="37" spans="1:5">
-      <c r="A37" s="6" t="s">
-        <v>38</v>
-      </c>
-      <c r="B37" s="6" t="s">
-        <v>6</v>
-      </c>
-      <c r="C37" s="7">
-        <v>-42.21</v>
-      </c>
-      <c r="D37" s="7">
-        <v>-42.33</v>
-      </c>
-      <c r="E37" s="9">
-        <v>-0.12</v>
-      </c>
-    </row>
-    <row r="38" spans="1:5">
-      <c r="A38" s="6" t="s">
-        <v>39</v>
-      </c>
-      <c r="B38" s="6" t="s">
-        <v>6</v>
-      </c>
-      <c r="C38" s="7">
-        <v>-49.16</v>
-      </c>
-      <c r="D38" s="7">
-        <v>-47.13</v>
-      </c>
-      <c r="E38" s="8">
-        <v>2.03</v>
-      </c>
-    </row>
-    <row r="39" spans="1:5">
-      <c r="A39" s="6" t="s">
-        <v>40</v>
-      </c>
-      <c r="B39" s="6" t="s">
-        <v>6</v>
-      </c>
-      <c r="C39" s="7">
-        <v>-23.23</v>
-      </c>
-      <c r="D39" s="7">
-        <v>-22.95</v>
-      </c>
-      <c r="E39" s="8">
-        <v>0.28</v>
-      </c>
-    </row>
-    <row r="40" spans="1:5">
-      <c r="A40" s="6" t="s">
-        <v>41</v>
-      </c>
-      <c r="B40" s="6" t="s">
-        <v>6</v>
-      </c>
-      <c r="C40" s="7">
-        <v>-15.93</v>
-      </c>
-      <c r="D40" s="7">
-        <v>-17.06</v>
-      </c>
-      <c r="E40" s="9">
-        <v>-1.13</v>
-      </c>
-    </row>
-    <row r="41" spans="1:5">
-      <c r="A41" s="6" t="s">
-        <v>42</v>
-      </c>
-      <c r="B41" s="6" t="s">
-        <v>6</v>
-      </c>
-      <c r="C41" s="7">
-        <v>-20.72</v>
-      </c>
-      <c r="D41" s="7">
-        <v>-21.3</v>
-      </c>
-      <c r="E41" s="9">
-        <v>-0.58</v>
-      </c>
-    </row>
-    <row r="42" spans="1:5">
-      <c r="A42" s="6" t="s">
-        <v>43</v>
-      </c>
-      <c r="B42" s="6" t="s">
-        <v>6</v>
-      </c>
-      <c r="C42" s="7">
-        <v>-21.43</v>
-      </c>
-      <c r="D42" s="7">
-        <v>-20.02</v>
-      </c>
-      <c r="E42" s="8">
-        <v>1.41</v>
-      </c>
-    </row>
-    <row r="43" spans="1:5">
-      <c r="A43" s="6" t="s">
-        <v>37</v>
-      </c>
-      <c r="B43" s="6" t="s">
-        <v>2</v>
-      </c>
-      <c r="C43" s="7">
-        <v>10071</v>
-      </c>
-      <c r="D43" s="7">
-        <v>10390</v>
-      </c>
-      <c r="E43" s="8">
-        <v>319</v>
-      </c>
-    </row>
-    <row r="44" spans="1:5">
-      <c r="A44" s="6" t="s">
-        <v>38</v>
-      </c>
-      <c r="B44" s="6" t="s">
-        <v>2</v>
-      </c>
-      <c r="C44" s="7">
-        <v>387.35</v>
-      </c>
-      <c r="D44" s="7">
-        <v>386.5</v>
-      </c>
-      <c r="E44" s="9">
-        <v>-0.85</v>
-      </c>
-    </row>
-    <row r="45" spans="1:5">
-      <c r="A45" s="6" t="s">
-        <v>39</v>
-      </c>
-      <c r="B45" s="6" t="s">
-        <v>2</v>
-      </c>
-      <c r="C45" s="7">
-        <v>275.65</v>
-      </c>
-      <c r="D45" s="7">
-        <v>281.8</v>
-      </c>
-      <c r="E45" s="8">
-        <v>6.15</v>
-      </c>
-    </row>
-    <row r="46" spans="1:5">
-      <c r="A46" s="6" t="s">
-        <v>40</v>
-      </c>
-      <c r="B46" s="6" t="s">
-        <v>2</v>
-      </c>
-      <c r="C46" s="7">
-        <v>1670.9</v>
-      </c>
-      <c r="D46" s="7">
-        <v>1677</v>
-      </c>
-      <c r="E46" s="8">
-        <v>6.1</v>
-      </c>
-    </row>
-    <row r="47" spans="1:5">
-      <c r="A47" s="6" t="s">
-        <v>41</v>
-      </c>
-      <c r="B47" s="6" t="s">
-        <v>2</v>
-      </c>
-      <c r="C47" s="7">
-        <v>11050</v>
-      </c>
-      <c r="D47" s="7">
-        <v>10901</v>
-      </c>
-      <c r="E47" s="9">
-        <v>-149</v>
-      </c>
-    </row>
-    <row r="48" spans="1:5">
-      <c r="A48" s="6" t="s">
-        <v>42</v>
-      </c>
-      <c r="B48" s="6" t="s">
-        <v>2</v>
-      </c>
-      <c r="C48" s="7">
-        <v>918.7</v>
-      </c>
-      <c r="D48" s="7">
-        <v>912</v>
-      </c>
-      <c r="E48" s="9">
-        <v>-6.7</v>
-      </c>
-    </row>
-    <row r="49" spans="1:5">
-      <c r="A49" s="6" t="s">
-        <v>43</v>
-      </c>
-      <c r="B49" s="6" t="s">
-        <v>2</v>
-      </c>
-      <c r="C49" s="7">
-        <v>146.07</v>
-      </c>
-      <c r="D49" s="7">
-        <v>148.69</v>
-      </c>
-      <c r="E49" s="8">
-        <v>2.62</v>
-      </c>
-    </row>
-    <row r="50" spans="1:5">
-      <c r="A50" s="6" t="s">
-        <v>37</v>
-      </c>
-      <c r="B50" s="6" t="s">
-        <v>13</v>
-      </c>
-      <c r="C50" s="7">
-        <v>71</v>
-      </c>
-      <c r="D50" s="7">
-        <v>85</v>
-      </c>
-      <c r="E50" s="8">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="51" spans="1:5">
-      <c r="A51" s="6" t="s">
-        <v>38</v>
-      </c>
-      <c r="B51" s="6" t="s">
-        <v>13</v>
-      </c>
-      <c r="C51" s="7">
-        <v>85</v>
-      </c>
-      <c r="D51" s="7">
-        <v>71</v>
-      </c>
-      <c r="E51" s="9">
-        <v>-14</v>
-      </c>
-    </row>
-    <row r="52" spans="1:5">
-      <c r="A52" s="6" t="s">
-        <v>37</v>
-      </c>
-      <c r="B52" s="6" t="s">
-        <v>24</v>
-      </c>
-      <c r="C52" s="7">
-        <v>37.3</v>
-      </c>
-      <c r="D52" s="7">
-        <v>46.97</v>
-      </c>
-      <c r="E52" s="8">
-        <v>9.67</v>
-      </c>
-    </row>
-    <row r="53" spans="1:5">
-      <c r="A53" s="6" t="s">
-        <v>38</v>
-      </c>
-      <c r="B53" s="6" t="s">
-        <v>24</v>
-      </c>
-      <c r="C53" s="7">
-        <v>26.88</v>
-      </c>
-      <c r="D53" s="7">
-        <v>26.76</v>
-      </c>
-      <c r="E53" s="9">
-        <v>-0.12</v>
-      </c>
-    </row>
-    <row r="54" spans="1:5">
-      <c r="A54" s="6" t="s">
-        <v>39</v>
-      </c>
-      <c r="B54" s="6" t="s">
-        <v>24</v>
-      </c>
-      <c r="C54" s="7">
-        <v>25.28</v>
-      </c>
-      <c r="D54" s="7">
-        <v>32.61</v>
-      </c>
-      <c r="E54" s="8">
-        <v>7.33</v>
-      </c>
-    </row>
-    <row r="55" spans="1:5">
-      <c r="A55" s="6" t="s">
-        <v>40</v>
-      </c>
-      <c r="B55" s="6" t="s">
-        <v>24</v>
-      </c>
-      <c r="C55" s="7">
-        <v>32.27</v>
-      </c>
-      <c r="D55" s="7">
-        <v>33.93</v>
-      </c>
-      <c r="E55" s="8">
-        <v>1.66</v>
-      </c>
-    </row>
-    <row r="56" spans="1:5">
-      <c r="A56" s="6" t="s">
-        <v>41</v>
-      </c>
-      <c r="B56" s="6" t="s">
-        <v>24</v>
-      </c>
-      <c r="C56" s="7">
-        <v>51.06</v>
-      </c>
-      <c r="D56" s="7">
-        <v>47.54</v>
-      </c>
-      <c r="E56" s="9">
-        <v>-3.52</v>
-      </c>
-    </row>
-    <row r="57" spans="1:5">
-      <c r="A57" s="6" t="s">
-        <v>42</v>
-      </c>
-      <c r="B57" s="6" t="s">
-        <v>24</v>
-      </c>
-      <c r="C57" s="7">
-        <v>36.17</v>
-      </c>
-      <c r="D57" s="7">
-        <v>35</v>
-      </c>
-      <c r="E57" s="9">
-        <v>-1.17</v>
-      </c>
-    </row>
-    <row r="58" spans="1:5">
-      <c r="A58" s="6" t="s">
-        <v>43</v>
-      </c>
-      <c r="B58" s="6" t="s">
-        <v>24</v>
-      </c>
-      <c r="C58" s="7">
-        <v>37.94</v>
-      </c>
-      <c r="D58" s="7">
-        <v>40.6</v>
-      </c>
-      <c r="E58" s="8">
-        <v>2.66</v>
-      </c>
-    </row>
-    <row r="59" spans="1:5">
-      <c r="A59" s="6" t="s">
-        <v>37</v>
-      </c>
-      <c r="B59" s="6" t="s">
+      <c r="B62" s="3" t="s">
         <v>31</v>
       </c>
-      <c r="C59" s="7">
-        <v>-40.81</v>
-      </c>
-      <c r="D59" s="7">
-        <v>11.3</v>
-      </c>
-      <c r="E59" s="8">
-        <v>52.11</v>
-      </c>
-    </row>
-    <row r="60" spans="1:5">
-      <c r="A60" s="6" t="s">
-        <v>38</v>
-      </c>
-      <c r="B60" s="6" t="s">
-        <v>31</v>
-      </c>
-      <c r="C60" s="7">
-        <v>-3.76</v>
-      </c>
-      <c r="D60" s="7">
-        <v>-72.42</v>
-      </c>
-      <c r="E60" s="9">
-        <v>-68.66</v>
-      </c>
-    </row>
-    <row r="61" spans="1:5">
-      <c r="A61" s="6" t="s">
-        <v>39</v>
-      </c>
-      <c r="B61" s="6" t="s">
-        <v>31</v>
-      </c>
-      <c r="C61" s="7">
-        <v>-78.95999999999999</v>
-      </c>
-      <c r="D61" s="7">
-        <v>-83.40000000000001</v>
-      </c>
-      <c r="E61" s="9">
-        <v>-4.44</v>
-      </c>
-    </row>
-    <row r="62" spans="1:5">
-      <c r="A62" s="6" t="s">
-        <v>40</v>
-      </c>
-      <c r="B62" s="6" t="s">
-        <v>31</v>
-      </c>
-      <c r="C62" s="7">
-        <v>-46.54</v>
-      </c>
-      <c r="D62" s="7">
-        <v>130.11</v>
-      </c>
-      <c r="E62" s="8">
-        <v>176.65</v>
-      </c>
-    </row>
-    <row r="63" spans="1:5">
-      <c r="A63" s="6" t="s">
-        <v>41</v>
-      </c>
-      <c r="B63" s="6" t="s">
-        <v>31</v>
-      </c>
-      <c r="C63" s="7">
-        <v>-18.19</v>
-      </c>
-      <c r="D63" s="7">
-        <v>95.76000000000001</v>
-      </c>
-      <c r="E63" s="8">
-        <v>113.95</v>
-      </c>
-    </row>
-    <row r="64" spans="1:5">
-      <c r="A64" s="6" t="s">
-        <v>42</v>
-      </c>
-      <c r="B64" s="6" t="s">
-        <v>31</v>
-      </c>
-      <c r="C64" s="7">
-        <v>-54.54</v>
-      </c>
-      <c r="D64" s="7">
-        <v>-26.91</v>
-      </c>
-      <c r="E64" s="8">
-        <v>27.63</v>
-      </c>
-    </row>
-    <row r="65" spans="1:5">
-      <c r="A65" s="6" t="s">
-        <v>43</v>
-      </c>
-      <c r="B65" s="6" t="s">
-        <v>31</v>
-      </c>
-      <c r="C65" s="7">
-        <v>-74.67</v>
-      </c>
-      <c r="D65" s="7">
+      <c r="C62" s="5">
         <v>-86.34999999999999</v>
       </c>
-      <c r="E65" s="9">
-        <v>-11.68</v>
+      <c r="D62" s="5">
+        <v>-80.23999999999999</v>
+      </c>
+      <c r="E62" s="6">
+        <v>6.11</v>
       </c>
     </row>
   </sheetData>
   <mergeCells count="2">
     <mergeCell ref="A1:F1"/>
-    <mergeCell ref="A6:E6"/>
+    <mergeCell ref="A5:E5"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -2971,60 +2838,60 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:9" ht="28" customHeight="1">
-      <c r="A1" s="10" t="s">
+      <c r="A1" s="8" t="s">
         <v>1</v>
       </c>
-      <c r="B1" s="10" t="s">
-        <v>69</v>
-      </c>
-      <c r="C1" s="10" t="s">
-        <v>70</v>
-      </c>
-      <c r="D1" s="10" t="s">
-        <v>71</v>
-      </c>
-      <c r="E1" s="10" t="s">
-        <v>72</v>
-      </c>
-      <c r="F1" s="10" t="s">
-        <v>73</v>
-      </c>
-      <c r="G1" s="10" t="s">
-        <v>74</v>
-      </c>
-      <c r="H1" s="10" t="s">
-        <v>75</v>
-      </c>
-      <c r="I1" s="10" t="s">
-        <v>76</v>
+      <c r="B1" s="8" t="s">
+        <v>55</v>
+      </c>
+      <c r="C1" s="8" t="s">
+        <v>56</v>
+      </c>
+      <c r="D1" s="8" t="s">
+        <v>57</v>
+      </c>
+      <c r="E1" s="8" t="s">
+        <v>58</v>
+      </c>
+      <c r="F1" s="8" t="s">
+        <v>59</v>
+      </c>
+      <c r="G1" s="8" t="s">
+        <v>60</v>
+      </c>
+      <c r="H1" s="8" t="s">
+        <v>61</v>
+      </c>
+      <c r="I1" s="8" t="s">
+        <v>62</v>
       </c>
     </row>
     <row r="2" spans="1:9">
-      <c r="A2" s="11" t="s">
+      <c r="A2" s="9" t="s">
         <v>44</v>
       </c>
-      <c r="B2" s="12">
-        <v>49.96</v>
-      </c>
-      <c r="C2" s="13">
+      <c r="B2" s="10">
+        <v>44.24</v>
+      </c>
+      <c r="C2" s="11">
         <v>7</v>
       </c>
-      <c r="D2" s="12">
-        <v>37.6</v>
-      </c>
-      <c r="E2" s="12">
-        <v>42.9</v>
-      </c>
-      <c r="F2" s="12">
-        <v>-8.4</v>
-      </c>
-      <c r="G2" s="12">
-        <v>-9.800000000000001</v>
-      </c>
-      <c r="H2" s="12">
+      <c r="D2" s="10">
+        <v>37.9</v>
+      </c>
+      <c r="E2" s="10">
+        <v>28.6</v>
+      </c>
+      <c r="F2" s="10">
+        <v>-9.9</v>
+      </c>
+      <c r="G2" s="10">
+        <v>-10</v>
+      </c>
+      <c r="H2" s="10">
         <v>57</v>
       </c>
-      <c r="I2" s="12">
+      <c r="I2" s="10">
         <v>14.3</v>
       </c>
     </row>
@@ -3126,49 +2993,49 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:7">
-      <c r="A1" s="14" t="s">
+      <c r="A1" s="12" t="s">
         <v>37</v>
       </c>
-      <c r="B1" s="14" t="s">
+      <c r="B1" s="12" t="s">
         <v>41</v>
       </c>
-      <c r="C1" s="14" t="s">
+      <c r="C1" s="12" t="s">
         <v>38</v>
       </c>
-      <c r="D1" s="14" t="s">
+      <c r="D1" s="12" t="s">
         <v>42</v>
       </c>
-      <c r="E1" s="14" t="s">
+      <c r="E1" s="12" t="s">
         <v>43</v>
       </c>
-      <c r="F1" s="14" t="s">
+      <c r="F1" s="12" t="s">
         <v>40</v>
       </c>
-      <c r="G1" s="14" t="s">
+      <c r="G1" s="12" t="s">
         <v>39</v>
       </c>
     </row>
     <row r="2" spans="1:7">
-      <c r="A2" s="15">
-        <v>0.2526</v>
-      </c>
-      <c r="B2" s="15">
-        <v>0.1919</v>
-      </c>
-      <c r="C2" s="15">
-        <v>0.1232</v>
-      </c>
-      <c r="D2" s="15">
-        <v>0.0444</v>
-      </c>
-      <c r="E2" s="15">
-        <v>0.0272</v>
-      </c>
-      <c r="F2" s="15">
-        <v>-0.0138</v>
-      </c>
-      <c r="G2" s="15">
-        <v>-0.2311</v>
+      <c r="A2" s="13">
+        <v>0.26</v>
+      </c>
+      <c r="B2" s="13">
+        <v>0.1827</v>
+      </c>
+      <c r="C2" s="13">
+        <v>0.1239</v>
+      </c>
+      <c r="D2" s="13">
+        <v>0.0455</v>
+      </c>
+      <c r="E2" s="13">
+        <v>0.0296</v>
+      </c>
+      <c r="F2" s="13">
+        <v>-0.0164</v>
+      </c>
+      <c r="G2" s="13">
+        <v>-0.2246</v>
       </c>
     </row>
   </sheetData>

--- a/BAJAJ_GROUP_Technical_Metrics.xlsx
+++ b/BAJAJ_GROUP_Technical_Metrics.xlsx
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="253" uniqueCount="63">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="272" uniqueCount="72">
   <si>
     <t>Symbol</t>
   </si>
@@ -169,7 +169,34 @@
     <t>▶  SIGNAL EVENTS (vs Previous Run)</t>
   </si>
   <si>
-    <t>No signal events detected since last run.</t>
+    <t>Signal</t>
+  </si>
+  <si>
+    <t>Change</t>
+  </si>
+  <si>
+    <t>Direction</t>
+  </si>
+  <si>
+    <t>Prev Value</t>
+  </si>
+  <si>
+    <t>Curr Value</t>
+  </si>
+  <si>
+    <t>RSI Oversold Recovery</t>
+  </si>
+  <si>
+    <t>26.0 → 30.0</t>
+  </si>
+  <si>
+    <t>🟢 BULLISH</t>
+  </si>
+  <si>
+    <t>26.0</t>
+  </si>
+  <si>
+    <t>30.0</t>
   </si>
   <si>
     <t>▶  NUMERIC METRIC CHANGES (vs Previous Run)</t>
@@ -371,14 +398,15 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="14">
+  <cellXfs count="15">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="2" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="3" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
+    <xf numFmtId="0" fontId="4" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1"/>
     <xf numFmtId="165" fontId="4" fillId="5" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="165" fontId="5" fillId="6" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
@@ -760,7 +788,7 @@
     <col min="23" max="23" width="16.7109375" customWidth="1"/>
     <col min="24" max="24" width="13.7109375" customWidth="1"/>
     <col min="25" max="25" width="7.7109375" customWidth="1"/>
-    <col min="26" max="26" width="9.7109375" customWidth="1"/>
+    <col min="26" max="26" width="8.7109375" customWidth="1"/>
     <col min="27" max="27" width="13.7109375" customWidth="1"/>
     <col min="28" max="28" width="11.7109375" customWidth="1"/>
     <col min="29" max="30" width="13.7109375" customWidth="1"/>
@@ -893,10 +921,10 @@
         <v>44</v>
       </c>
       <c r="C2">
-        <v>10485</v>
+        <v>10383</v>
       </c>
       <c r="D2">
-        <v>0.91</v>
+        <v>-0.97</v>
       </c>
       <c r="E2">
         <v>12361</v>
@@ -905,46 +933,46 @@
         <v>8599.48</v>
       </c>
       <c r="G2">
-        <v>-15.18</v>
+        <v>-16</v>
       </c>
       <c r="H2">
-        <v>21.93</v>
+        <v>20.74</v>
       </c>
       <c r="I2">
-        <v>4.1</v>
+        <v>2.25</v>
       </c>
       <c r="J2">
-        <v>-7.06</v>
+        <v>-5.81</v>
       </c>
       <c r="K2">
-        <v>-7.82</v>
+        <v>-8.42</v>
       </c>
       <c r="L2">
-        <v>17.53</v>
+        <v>16</v>
       </c>
       <c r="M2">
-        <v>26</v>
+        <v>25.71</v>
       </c>
       <c r="N2">
-        <v>85</v>
+        <v>71</v>
       </c>
       <c r="O2">
-        <v>75</v>
+        <v>73</v>
       </c>
       <c r="P2">
-        <v>10234.6</v>
+        <v>10280.2</v>
       </c>
       <c r="Q2">
-        <v>10199.7</v>
+        <v>10178.3</v>
       </c>
       <c r="R2">
-        <v>11091.26</v>
+        <v>11064.92</v>
       </c>
       <c r="S2">
-        <v>10227.72</v>
+        <v>10231.51</v>
       </c>
       <c r="T2">
-        <v>2.52</v>
+        <v>1.48</v>
       </c>
       <c r="U2" t="s">
         <v>45</v>
@@ -959,34 +987,34 @@
         <v>2</v>
       </c>
       <c r="Y2">
-        <v>49.47</v>
+        <v>46.91</v>
       </c>
       <c r="Z2">
-        <v>-212.55</v>
+        <v>-188.3</v>
       </c>
       <c r="AA2">
-        <v>-289.11</v>
+        <v>-268.95</v>
       </c>
       <c r="AB2">
-        <v>76.56</v>
+        <v>80.65000000000001</v>
       </c>
       <c r="AC2">
-        <v>92.63</v>
+        <v>96.76000000000001</v>
       </c>
       <c r="AD2">
-        <v>85.98999999999999</v>
+        <v>91.55</v>
       </c>
       <c r="AE2">
-        <v>276.5</v>
+        <v>277.25</v>
       </c>
       <c r="AF2">
-        <v>205.37</v>
+        <v>-22.88</v>
       </c>
       <c r="AG2">
-        <v>10816.58</v>
+        <v>10732.39</v>
       </c>
       <c r="AH2">
-        <v>9582.82</v>
+        <v>9624.209999999999</v>
       </c>
       <c r="AI2">
         <v>10503.51</v>
@@ -995,7 +1023,7 @@
         <v>47</v>
       </c>
       <c r="AK2">
-        <v>35.98</v>
+        <v>32.63</v>
       </c>
     </row>
     <row r="3" spans="1:37">
@@ -1006,10 +1034,10 @@
         <v>44</v>
       </c>
       <c r="C3">
-        <v>381.3</v>
+        <v>390.6</v>
       </c>
       <c r="D3">
-        <v>-1.35</v>
+        <v>2.44</v>
       </c>
       <c r="E3">
         <v>670.25</v>
@@ -1018,46 +1046,46 @@
         <v>247.45</v>
       </c>
       <c r="G3">
-        <v>-43.11</v>
+        <v>-41.72</v>
       </c>
       <c r="H3">
-        <v>54.09</v>
+        <v>57.85</v>
       </c>
       <c r="I3">
-        <v>-10.37</v>
+        <v>-6.08</v>
       </c>
       <c r="J3">
-        <v>-23.66</v>
+        <v>-18.63</v>
       </c>
       <c r="K3">
-        <v>-28.19</v>
+        <v>-27.19</v>
       </c>
       <c r="L3">
-        <v>39.59</v>
+        <v>44.45</v>
       </c>
       <c r="M3">
-        <v>12.39</v>
+        <v>12.95</v>
       </c>
       <c r="N3">
-        <v>71</v>
+        <v>85</v>
       </c>
       <c r="O3">
-        <v>71</v>
+        <v>75</v>
       </c>
       <c r="P3">
-        <v>393.6</v>
+        <v>388.54</v>
       </c>
       <c r="Q3">
-        <v>462.01</v>
+        <v>456.89</v>
       </c>
       <c r="R3">
-        <v>481.55</v>
+        <v>479.74</v>
       </c>
       <c r="S3">
-        <v>468.57</v>
+        <v>469.12</v>
       </c>
       <c r="T3">
-        <v>-18.63</v>
+        <v>-16.74</v>
       </c>
       <c r="U3" t="s">
         <v>45</v>
@@ -1072,34 +1100,34 @@
         <v>1</v>
       </c>
       <c r="Y3">
-        <v>25.96</v>
+        <v>30</v>
       </c>
       <c r="Z3">
-        <v>-29.57</v>
+        <v>-30.35</v>
       </c>
       <c r="AA3">
-        <v>-18.68</v>
+        <v>-21.02</v>
       </c>
       <c r="AB3">
-        <v>-10.89</v>
+        <v>-9.34</v>
       </c>
       <c r="AC3">
-        <v>0</v>
+        <v>4.35</v>
       </c>
       <c r="AD3">
-        <v>0</v>
+        <v>1.45</v>
       </c>
       <c r="AE3">
-        <v>21.9</v>
+        <v>21.52</v>
       </c>
       <c r="AF3">
-        <v>-69.27</v>
+        <v>-44.22</v>
       </c>
       <c r="AG3">
-        <v>553.92</v>
+        <v>552.85</v>
       </c>
       <c r="AH3">
-        <v>370.1</v>
+        <v>360.93</v>
       </c>
       <c r="AI3">
         <v>446.85</v>
@@ -1108,7 +1136,7 @@
         <v>47</v>
       </c>
       <c r="AK3">
-        <v>54.67</v>
+        <v>55.5</v>
       </c>
     </row>
     <row r="4" spans="1:37">
@@ -1119,10 +1147,10 @@
         <v>44</v>
       </c>
       <c r="C4">
-        <v>292.65</v>
+        <v>283.8</v>
       </c>
       <c r="D4">
-        <v>3.85</v>
+        <v>-3.02</v>
       </c>
       <c r="E4">
         <v>529.85</v>
@@ -1131,46 +1159,46 @@
         <v>275.65</v>
       </c>
       <c r="G4">
-        <v>-44.77</v>
+        <v>-46.44</v>
       </c>
       <c r="H4">
-        <v>6.17</v>
+        <v>2.96</v>
       </c>
       <c r="I4">
-        <v>-0.15</v>
+        <v>1.79</v>
       </c>
       <c r="J4">
-        <v>-8.25</v>
+        <v>-9.800000000000001</v>
       </c>
       <c r="K4">
-        <v>-10.52</v>
+        <v>-14.14</v>
       </c>
       <c r="L4">
-        <v>-45.1</v>
+        <v>-46</v>
       </c>
       <c r="M4">
-        <v>-22.46</v>
+        <v>-22.67</v>
       </c>
       <c r="N4">
         <v>15</v>
       </c>
       <c r="O4">
-        <v>18</v>
+        <v>14</v>
       </c>
       <c r="P4">
-        <v>281.42</v>
+        <v>282.42</v>
       </c>
       <c r="Q4">
-        <v>295.66</v>
+        <v>294.35</v>
       </c>
       <c r="R4">
-        <v>318.91</v>
+        <v>317.34</v>
       </c>
       <c r="S4">
-        <v>352.3</v>
+        <v>351.37</v>
       </c>
       <c r="T4">
-        <v>-16.93</v>
+        <v>-19.23</v>
       </c>
       <c r="U4" t="s">
         <v>45</v>
@@ -1185,34 +1213,34 @@
         <v>0</v>
       </c>
       <c r="Y4">
-        <v>43.2</v>
+        <v>37.96</v>
       </c>
       <c r="Z4">
-        <v>-9.960000000000001</v>
+        <v>-9.779999999999999</v>
       </c>
       <c r="AA4">
-        <v>-9.710000000000001</v>
+        <v>-9.720000000000001</v>
       </c>
       <c r="AB4">
-        <v>-0.25</v>
+        <v>-0.06</v>
       </c>
       <c r="AC4">
-        <v>47.73</v>
+        <v>70.15000000000001</v>
       </c>
       <c r="AD4">
-        <v>24.13</v>
+        <v>45.18</v>
       </c>
       <c r="AE4">
-        <v>12.34</v>
+        <v>12.36</v>
       </c>
       <c r="AF4">
-        <v>1223.89</v>
+        <v>-37.31</v>
       </c>
       <c r="AG4">
-        <v>315.58</v>
+        <v>313.77</v>
       </c>
       <c r="AH4">
-        <v>275.73</v>
+        <v>274.94</v>
       </c>
       <c r="AI4">
         <v>308.71</v>
@@ -1221,7 +1249,7 @@
         <v>47</v>
       </c>
       <c r="AK4">
-        <v>31.17</v>
+        <v>33.07</v>
       </c>
     </row>
     <row r="5" spans="1:37">
@@ -1232,10 +1260,10 @@
         <v>44</v>
       </c>
       <c r="C5">
-        <v>1652.4</v>
+        <v>1668</v>
       </c>
       <c r="D5">
-        <v>-1.47</v>
+        <v>0.9399999999999999</v>
       </c>
       <c r="E5">
         <v>2170.2</v>
@@ -1244,46 +1272,46 @@
         <v>1631.8</v>
       </c>
       <c r="G5">
-        <v>-23.86</v>
+        <v>-23.14</v>
       </c>
       <c r="H5">
-        <v>1.26</v>
+        <v>2.22</v>
       </c>
       <c r="I5">
-        <v>-2.22</v>
+        <v>-0.6</v>
       </c>
       <c r="J5">
-        <v>-6.7</v>
+        <v>-4.79</v>
       </c>
       <c r="K5">
-        <v>-14.29</v>
+        <v>-13.32</v>
       </c>
       <c r="L5">
-        <v>-24.08</v>
+        <v>-22.76</v>
       </c>
       <c r="M5">
-        <v>-1.64</v>
+        <v>-1.28</v>
       </c>
       <c r="N5">
         <v>29</v>
       </c>
       <c r="O5">
-        <v>35</v>
+        <v>37</v>
       </c>
       <c r="P5">
-        <v>1666.66</v>
+        <v>1664.66</v>
       </c>
       <c r="Q5">
-        <v>1713.87</v>
+        <v>1710.15</v>
       </c>
       <c r="R5">
-        <v>1843.9</v>
+        <v>1837.16</v>
       </c>
       <c r="S5">
-        <v>1856.95</v>
+        <v>1855.25</v>
       </c>
       <c r="T5">
-        <v>-11.02</v>
+        <v>-10.09</v>
       </c>
       <c r="U5" t="s">
         <v>45</v>
@@ -1298,34 +1326,34 @@
         <v>0</v>
       </c>
       <c r="Y5">
-        <v>30.66</v>
+        <v>34.94</v>
       </c>
       <c r="Z5">
-        <v>-47.48</v>
+        <v>-46.01</v>
       </c>
       <c r="AA5">
-        <v>-48.09</v>
+        <v>-47.68</v>
       </c>
       <c r="AB5">
-        <v>0.61</v>
+        <v>1.67</v>
       </c>
       <c r="AC5">
-        <v>47.53</v>
+        <v>51.45</v>
       </c>
       <c r="AD5">
-        <v>40.77</v>
+        <v>46.68</v>
       </c>
       <c r="AE5">
-        <v>39.24</v>
+        <v>38.72</v>
       </c>
       <c r="AF5">
-        <v>36.35</v>
+        <v>14.81</v>
       </c>
       <c r="AG5">
-        <v>1779.71</v>
+        <v>1777.59</v>
       </c>
       <c r="AH5">
-        <v>1648.03</v>
+        <v>1642.71</v>
       </c>
       <c r="AI5">
         <v>1762.43</v>
@@ -1334,7 +1362,7 @@
         <v>47</v>
       </c>
       <c r="AK5">
-        <v>62.27</v>
+        <v>60.97</v>
       </c>
     </row>
     <row r="6" spans="1:37">
@@ -1345,58 +1373,58 @@
         <v>44</v>
       </c>
       <c r="C6">
-        <v>10461</v>
+        <v>10160</v>
       </c>
       <c r="D6">
-        <v>-4.04</v>
+        <v>-2.88</v>
       </c>
       <c r="E6">
-        <v>13144</v>
+        <v>13139</v>
       </c>
       <c r="F6">
         <v>8746</v>
       </c>
       <c r="G6">
-        <v>-20.41</v>
+        <v>-22.67</v>
       </c>
       <c r="H6">
-        <v>19.61</v>
+        <v>16.17</v>
       </c>
       <c r="I6">
-        <v>-4.68</v>
+        <v>-10.03</v>
       </c>
       <c r="J6">
-        <v>-4.38</v>
+        <v>-5.93</v>
       </c>
       <c r="K6">
-        <v>-3.42</v>
+        <v>-7.21</v>
       </c>
       <c r="L6">
-        <v>-20.41</v>
+        <v>-22.7</v>
       </c>
       <c r="M6">
-        <v>18.27</v>
+        <v>17.3</v>
       </c>
       <c r="N6">
-        <v>57</v>
+        <v>43</v>
       </c>
       <c r="O6">
-        <v>51</v>
+        <v>43</v>
       </c>
       <c r="P6">
-        <v>10976</v>
+        <v>10749.4</v>
       </c>
       <c r="Q6">
-        <v>10867.15</v>
+        <v>10845.15</v>
       </c>
       <c r="R6">
-        <v>11068.76</v>
+        <v>11042.46</v>
       </c>
       <c r="S6">
-        <v>10652.56</v>
+        <v>10647.32</v>
       </c>
       <c r="T6">
-        <v>-1.8</v>
+        <v>-4.58</v>
       </c>
       <c r="U6" t="s">
         <v>45</v>
@@ -1411,43 +1439,43 @@
         <v>1</v>
       </c>
       <c r="Y6">
-        <v>39</v>
+        <v>34.45</v>
       </c>
       <c r="Z6">
-        <v>-25.75</v>
+        <v>-85.56</v>
       </c>
       <c r="AA6">
-        <v>-10.92</v>
+        <v>-25.85</v>
       </c>
       <c r="AB6">
-        <v>-14.83</v>
+        <v>-59.71</v>
       </c>
       <c r="AC6">
-        <v>32.76</v>
+        <v>12.87</v>
       </c>
       <c r="AD6">
-        <v>56.01</v>
+        <v>34.68</v>
       </c>
       <c r="AE6">
-        <v>309.42</v>
+        <v>314.75</v>
       </c>
       <c r="AF6">
-        <v>-39.29</v>
+        <v>36.92</v>
       </c>
       <c r="AG6">
-        <v>11376.52</v>
+        <v>11434.78</v>
       </c>
       <c r="AH6">
-        <v>10357.78</v>
+        <v>10255.52</v>
       </c>
       <c r="AI6">
-        <v>11368.55</v>
+        <v>11286.24</v>
       </c>
       <c r="AJ6" t="s">
         <v>47</v>
       </c>
       <c r="AK6">
-        <v>24.63</v>
+        <v>28.49</v>
       </c>
     </row>
     <row r="7" spans="1:37">
@@ -1458,10 +1486,10 @@
         <v>44</v>
       </c>
       <c r="C7">
-        <v>917.25</v>
+        <v>938.9</v>
       </c>
       <c r="D7">
-        <v>0.58</v>
+        <v>2.36</v>
       </c>
       <c r="E7">
         <v>1158.8</v>
@@ -1470,46 +1498,46 @@
         <v>801.55</v>
       </c>
       <c r="G7">
-        <v>-20.84</v>
+        <v>-18.98</v>
       </c>
       <c r="H7">
-        <v>14.43</v>
+        <v>17.14</v>
       </c>
       <c r="I7">
-        <v>-0.9399999999999999</v>
+        <v>-0.34</v>
       </c>
       <c r="J7">
-        <v>-7.99</v>
+        <v>-4.68</v>
       </c>
       <c r="K7">
-        <v>-12.51</v>
+        <v>-10.95</v>
       </c>
       <c r="L7">
-        <v>-16.17</v>
+        <v>-13.84</v>
       </c>
       <c r="M7">
-        <v>4.55</v>
+        <v>5.28</v>
       </c>
       <c r="N7">
-        <v>43</v>
+        <v>57</v>
       </c>
       <c r="O7">
-        <v>45</v>
+        <v>48</v>
       </c>
       <c r="P7">
-        <v>923.8</v>
+        <v>923.16</v>
       </c>
       <c r="Q7">
-        <v>952.05</v>
+        <v>950.3099999999999</v>
       </c>
       <c r="R7">
-        <v>1010.46</v>
+        <v>1007.45</v>
       </c>
       <c r="S7">
-        <v>972.55</v>
+        <v>972.39</v>
       </c>
       <c r="T7">
-        <v>-5.69</v>
+        <v>-3.44</v>
       </c>
       <c r="U7" t="s">
         <v>45</v>
@@ -1524,34 +1552,34 @@
         <v>1</v>
       </c>
       <c r="Y7">
-        <v>36.73</v>
+        <v>43.44</v>
       </c>
       <c r="Z7">
-        <v>-24.49</v>
+        <v>-22.74</v>
       </c>
       <c r="AA7">
-        <v>-22.46</v>
+        <v>-22.51</v>
       </c>
       <c r="AB7">
-        <v>-2.03</v>
+        <v>-0.23</v>
       </c>
       <c r="AC7">
-        <v>5.9</v>
+        <v>27.6</v>
       </c>
       <c r="AD7">
-        <v>13.1</v>
+        <v>13.71</v>
       </c>
       <c r="AE7">
-        <v>26.84</v>
+        <v>27.39</v>
       </c>
       <c r="AF7">
-        <v>-33.3</v>
+        <v>5.48</v>
       </c>
       <c r="AG7">
-        <v>994.46</v>
+        <v>991.8099999999999</v>
       </c>
       <c r="AH7">
-        <v>909.65</v>
+        <v>908.8099999999999</v>
       </c>
       <c r="AI7">
         <v>989.6</v>
@@ -1560,7 +1588,7 @@
         <v>47</v>
       </c>
       <c r="AK7">
-        <v>28.11</v>
+        <v>24.63</v>
       </c>
     </row>
     <row r="8" spans="1:37">
@@ -1571,10 +1599,10 @@
         <v>44</v>
       </c>
       <c r="C8">
-        <v>148.42</v>
+        <v>149.63</v>
       </c>
       <c r="D8">
-        <v>-0.18</v>
+        <v>0.82</v>
       </c>
       <c r="E8">
         <v>185.92</v>
@@ -1583,46 +1611,46 @@
         <v>115.96</v>
       </c>
       <c r="G8">
-        <v>-20.17</v>
+        <v>-19.52</v>
       </c>
       <c r="H8">
-        <v>27.99</v>
+        <v>29.04</v>
       </c>
       <c r="I8">
-        <v>-5.35</v>
+        <v>-2.44</v>
       </c>
       <c r="J8">
-        <v>-11.15</v>
+        <v>-12.51</v>
       </c>
       <c r="K8">
-        <v>6.7</v>
+        <v>7.32</v>
       </c>
       <c r="L8">
-        <v>14.81</v>
+        <v>15.46</v>
       </c>
       <c r="M8">
-        <v>2.96</v>
+        <v>3.67</v>
       </c>
       <c r="N8">
         <v>99</v>
       </c>
       <c r="O8">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="P8">
-        <v>147.92</v>
+        <v>147.17</v>
       </c>
       <c r="Q8">
-        <v>167.88</v>
+        <v>166.74</v>
       </c>
       <c r="R8">
-        <v>151.12</v>
+        <v>151.43</v>
       </c>
       <c r="S8">
-        <v>137.85</v>
+        <v>137.94</v>
       </c>
       <c r="T8">
-        <v>7.67</v>
+        <v>8.470000000000001</v>
       </c>
       <c r="U8" t="s">
         <v>46</v>
@@ -1637,34 +1665,34 @@
         <v>3</v>
       </c>
       <c r="Y8">
-        <v>40.41</v>
+        <v>41.74</v>
       </c>
       <c r="Z8">
-        <v>-1.66</v>
+        <v>-2.13</v>
       </c>
       <c r="AA8">
-        <v>2.64</v>
+        <v>1.69</v>
       </c>
       <c r="AB8">
-        <v>-4.31</v>
+        <v>-3.82</v>
       </c>
       <c r="AC8">
-        <v>12.93</v>
+        <v>17.99</v>
       </c>
       <c r="AD8">
-        <v>7.41</v>
+        <v>12.61</v>
       </c>
       <c r="AE8">
-        <v>8.050000000000001</v>
+        <v>8.039999999999999</v>
       </c>
       <c r="AF8">
-        <v>-80.23999999999999</v>
+        <v>-69.48999999999999</v>
       </c>
       <c r="AG8">
-        <v>194.81</v>
+        <v>194.76</v>
       </c>
       <c r="AH8">
-        <v>140.95</v>
+        <v>138.71</v>
       </c>
       <c r="AI8">
         <v>170.73</v>
@@ -1673,7 +1701,7 @@
         <v>47</v>
       </c>
       <c r="AK8">
-        <v>45.02</v>
+        <v>43.82</v>
       </c>
     </row>
   </sheetData>
@@ -1814,7 +1842,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:F62"/>
+  <dimension ref="A1:F66"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="16.7109375" customWidth="1"/>
@@ -1834,12 +1862,47 @@
     </row>
     <row r="2" spans="1:6">
       <c r="A2" s="3" t="s">
+        <v>0</v>
+      </c>
+      <c r="B2" s="3" t="s">
         <v>49</v>
+      </c>
+      <c r="C2" s="3" t="s">
+        <v>50</v>
+      </c>
+      <c r="D2" s="3" t="s">
+        <v>51</v>
+      </c>
+      <c r="E2" s="3" t="s">
+        <v>52</v>
+      </c>
+      <c r="F2" s="3" t="s">
+        <v>53</v>
+      </c>
+    </row>
+    <row r="3" spans="1:6">
+      <c r="A3" s="4" t="s">
+        <v>38</v>
+      </c>
+      <c r="B3" s="4" t="s">
+        <v>54</v>
+      </c>
+      <c r="C3" s="4" t="s">
+        <v>55</v>
+      </c>
+      <c r="D3" s="4" t="s">
+        <v>56</v>
+      </c>
+      <c r="E3" s="4" t="s">
+        <v>57</v>
+      </c>
+      <c r="F3" s="4" t="s">
+        <v>58</v>
       </c>
     </row>
     <row r="5" spans="1:6">
       <c r="A5" s="2" t="s">
-        <v>50</v>
+        <v>59</v>
       </c>
       <c r="B5" s="2"/>
       <c r="C5" s="2"/>
@@ -1847,972 +1910,1040 @@
       <c r="E5" s="2"/>
     </row>
     <row r="6" spans="1:6">
-      <c r="A6" s="4" t="s">
+      <c r="A6" s="3" t="s">
         <v>0</v>
       </c>
-      <c r="B6" s="4" t="s">
-        <v>51</v>
-      </c>
-      <c r="C6" s="4" t="s">
-        <v>52</v>
-      </c>
-      <c r="D6" s="4" t="s">
-        <v>53</v>
-      </c>
-      <c r="E6" s="4" t="s">
-        <v>54</v>
+      <c r="B6" s="3" t="s">
+        <v>60</v>
+      </c>
+      <c r="C6" s="3" t="s">
+        <v>61</v>
+      </c>
+      <c r="D6" s="3" t="s">
+        <v>62</v>
+      </c>
+      <c r="E6" s="3" t="s">
+        <v>63</v>
       </c>
     </row>
     <row r="7" spans="1:6">
-      <c r="A7" s="3" t="s">
+      <c r="A7" s="5" t="s">
         <v>37</v>
       </c>
-      <c r="B7" s="3" t="s">
+      <c r="B7" s="5" t="s">
         <v>9</v>
       </c>
-      <c r="C7" s="5">
-        <v>-7.3</v>
-      </c>
-      <c r="D7" s="5">
+      <c r="C7" s="6">
         <v>-7.06</v>
       </c>
-      <c r="E7" s="6">
-        <v>0.24</v>
+      <c r="D7" s="6">
+        <v>-5.81</v>
+      </c>
+      <c r="E7" s="7">
+        <v>1.25</v>
       </c>
     </row>
     <row r="8" spans="1:6">
-      <c r="A8" s="3" t="s">
+      <c r="A8" s="5" t="s">
         <v>38</v>
       </c>
-      <c r="B8" s="3" t="s">
+      <c r="B8" s="5" t="s">
         <v>9</v>
       </c>
-      <c r="C8" s="5">
-        <v>-22.96</v>
-      </c>
-      <c r="D8" s="5">
+      <c r="C8" s="6">
         <v>-23.66</v>
       </c>
+      <c r="D8" s="6">
+        <v>-18.63</v>
+      </c>
       <c r="E8" s="7">
-        <v>-0.7</v>
+        <v>5.03</v>
       </c>
     </row>
     <row r="9" spans="1:6">
-      <c r="A9" s="3" t="s">
+      <c r="A9" s="5" t="s">
         <v>39</v>
       </c>
-      <c r="B9" s="3" t="s">
+      <c r="B9" s="5" t="s">
         <v>9</v>
       </c>
-      <c r="C9" s="5">
-        <v>-12.33</v>
-      </c>
-      <c r="D9" s="5">
+      <c r="C9" s="6">
         <v>-8.25</v>
       </c>
-      <c r="E9" s="6">
-        <v>4.08</v>
+      <c r="D9" s="6">
+        <v>-9.800000000000001</v>
+      </c>
+      <c r="E9" s="8">
+        <v>-1.55</v>
       </c>
     </row>
     <row r="10" spans="1:6">
-      <c r="A10" s="3" t="s">
+      <c r="A10" s="5" t="s">
         <v>40</v>
       </c>
-      <c r="B10" s="3" t="s">
+      <c r="B10" s="5" t="s">
         <v>9</v>
       </c>
-      <c r="C10" s="5">
-        <v>-4.84</v>
-      </c>
-      <c r="D10" s="5">
+      <c r="C10" s="6">
         <v>-6.7</v>
       </c>
+      <c r="D10" s="6">
+        <v>-4.79</v>
+      </c>
       <c r="E10" s="7">
-        <v>-1.86</v>
+        <v>1.91</v>
       </c>
     </row>
     <row r="11" spans="1:6">
-      <c r="A11" s="3" t="s">
+      <c r="A11" s="5" t="s">
         <v>41</v>
       </c>
-      <c r="B11" s="3" t="s">
+      <c r="B11" s="5" t="s">
         <v>9</v>
       </c>
-      <c r="C11" s="5">
+      <c r="C11" s="6">
+        <v>-4.38</v>
+      </c>
+      <c r="D11" s="6">
+        <v>-5.93</v>
+      </c>
+      <c r="E11" s="8">
+        <v>-1.55</v>
+      </c>
+    </row>
+    <row r="12" spans="1:6">
+      <c r="A12" s="5" t="s">
+        <v>42</v>
+      </c>
+      <c r="B12" s="5" t="s">
+        <v>9</v>
+      </c>
+      <c r="C12" s="6">
+        <v>-7.99</v>
+      </c>
+      <c r="D12" s="6">
+        <v>-4.68</v>
+      </c>
+      <c r="E12" s="7">
+        <v>3.31</v>
+      </c>
+    </row>
+    <row r="13" spans="1:6">
+      <c r="A13" s="5" t="s">
+        <v>43</v>
+      </c>
+      <c r="B13" s="5" t="s">
+        <v>9</v>
+      </c>
+      <c r="C13" s="6">
+        <v>-11.15</v>
+      </c>
+      <c r="D13" s="6">
+        <v>-12.51</v>
+      </c>
+      <c r="E13" s="8">
+        <v>-1.36</v>
+      </c>
+    </row>
+    <row r="14" spans="1:6">
+      <c r="A14" s="5" t="s">
+        <v>37</v>
+      </c>
+      <c r="B14" s="5" t="s">
+        <v>8</v>
+      </c>
+      <c r="C14" s="6">
+        <v>4.1</v>
+      </c>
+      <c r="D14" s="6">
+        <v>2.25</v>
+      </c>
+      <c r="E14" s="8">
+        <v>-1.85</v>
+      </c>
+    </row>
+    <row r="15" spans="1:6">
+      <c r="A15" s="5" t="s">
+        <v>38</v>
+      </c>
+      <c r="B15" s="5" t="s">
+        <v>8</v>
+      </c>
+      <c r="C15" s="6">
+        <v>-10.37</v>
+      </c>
+      <c r="D15" s="6">
+        <v>-6.08</v>
+      </c>
+      <c r="E15" s="7">
+        <v>4.29</v>
+      </c>
+    </row>
+    <row r="16" spans="1:6">
+      <c r="A16" s="5" t="s">
+        <v>39</v>
+      </c>
+      <c r="B16" s="5" t="s">
+        <v>8</v>
+      </c>
+      <c r="C16" s="6">
         <v>-0.15</v>
       </c>
-      <c r="D11" s="5">
-        <v>-4.38</v>
-      </c>
-      <c r="E11" s="7">
-        <v>-4.23</v>
-      </c>
-    </row>
-    <row r="12" spans="1:6">
-      <c r="A12" s="3" t="s">
+      <c r="D16" s="6">
+        <v>1.79</v>
+      </c>
+      <c r="E16" s="7">
+        <v>1.94</v>
+      </c>
+    </row>
+    <row r="17" spans="1:5">
+      <c r="A17" s="5" t="s">
+        <v>40</v>
+      </c>
+      <c r="B17" s="5" t="s">
+        <v>8</v>
+      </c>
+      <c r="C17" s="6">
+        <v>-2.22</v>
+      </c>
+      <c r="D17" s="6">
+        <v>-0.6</v>
+      </c>
+      <c r="E17" s="7">
+        <v>1.62</v>
+      </c>
+    </row>
+    <row r="18" spans="1:5">
+      <c r="A18" s="5" t="s">
+        <v>41</v>
+      </c>
+      <c r="B18" s="5" t="s">
+        <v>8</v>
+      </c>
+      <c r="C18" s="6">
+        <v>-4.68</v>
+      </c>
+      <c r="D18" s="6">
+        <v>-10.03</v>
+      </c>
+      <c r="E18" s="8">
+        <v>-5.35</v>
+      </c>
+    </row>
+    <row r="19" spans="1:5">
+      <c r="A19" s="5" t="s">
         <v>42</v>
       </c>
-      <c r="B12" s="3" t="s">
-        <v>9</v>
-      </c>
-      <c r="C12" s="5">
-        <v>-7.13</v>
-      </c>
-      <c r="D12" s="5">
-        <v>-7.99</v>
-      </c>
-      <c r="E12" s="7">
-        <v>-0.86</v>
-      </c>
-    </row>
-    <row r="13" spans="1:6">
-      <c r="A13" s="3" t="s">
+      <c r="B19" s="5" t="s">
+        <v>8</v>
+      </c>
+      <c r="C19" s="6">
+        <v>-0.9399999999999999</v>
+      </c>
+      <c r="D19" s="6">
+        <v>-0.34</v>
+      </c>
+      <c r="E19" s="7">
+        <v>0.6</v>
+      </c>
+    </row>
+    <row r="20" spans="1:5">
+      <c r="A20" s="5" t="s">
         <v>43</v>
       </c>
-      <c r="B13" s="3" t="s">
-        <v>9</v>
-      </c>
-      <c r="C13" s="5">
-        <v>-4.23</v>
-      </c>
-      <c r="D13" s="5">
-        <v>-11.15</v>
-      </c>
-      <c r="E13" s="7">
-        <v>-6.92</v>
-      </c>
-    </row>
-    <row r="14" spans="1:6">
-      <c r="A14" s="3" t="s">
+      <c r="B20" s="5" t="s">
+        <v>8</v>
+      </c>
+      <c r="C20" s="6">
+        <v>-5.35</v>
+      </c>
+      <c r="D20" s="6">
+        <v>-2.44</v>
+      </c>
+      <c r="E20" s="7">
+        <v>2.91</v>
+      </c>
+    </row>
+    <row r="21" spans="1:5">
+      <c r="A21" s="5" t="s">
         <v>37</v>
       </c>
-      <c r="B14" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="C14" s="5">
+      <c r="B21" s="5" t="s">
+        <v>11</v>
+      </c>
+      <c r="C21" s="6">
+        <v>17.53</v>
+      </c>
+      <c r="D21" s="6">
+        <v>16</v>
+      </c>
+      <c r="E21" s="8">
+        <v>-1.53</v>
+      </c>
+    </row>
+    <row r="22" spans="1:5">
+      <c r="A22" s="5" t="s">
+        <v>38</v>
+      </c>
+      <c r="B22" s="5" t="s">
+        <v>11</v>
+      </c>
+      <c r="C22" s="6">
+        <v>39.59</v>
+      </c>
+      <c r="D22" s="6">
+        <v>44.45</v>
+      </c>
+      <c r="E22" s="7">
+        <v>4.86</v>
+      </c>
+    </row>
+    <row r="23" spans="1:5">
+      <c r="A23" s="5" t="s">
+        <v>39</v>
+      </c>
+      <c r="B23" s="5" t="s">
+        <v>11</v>
+      </c>
+      <c r="C23" s="6">
+        <v>-45.1</v>
+      </c>
+      <c r="D23" s="6">
+        <v>-46</v>
+      </c>
+      <c r="E23" s="8">
+        <v>-0.9</v>
+      </c>
+    </row>
+    <row r="24" spans="1:5">
+      <c r="A24" s="5" t="s">
+        <v>40</v>
+      </c>
+      <c r="B24" s="5" t="s">
+        <v>11</v>
+      </c>
+      <c r="C24" s="6">
+        <v>-24.08</v>
+      </c>
+      <c r="D24" s="6">
+        <v>-22.76</v>
+      </c>
+      <c r="E24" s="7">
+        <v>1.32</v>
+      </c>
+    </row>
+    <row r="25" spans="1:5">
+      <c r="A25" s="5" t="s">
+        <v>41</v>
+      </c>
+      <c r="B25" s="5" t="s">
+        <v>11</v>
+      </c>
+      <c r="C25" s="6">
+        <v>-20.41</v>
+      </c>
+      <c r="D25" s="6">
+        <v>-22.7</v>
+      </c>
+      <c r="E25" s="8">
+        <v>-2.29</v>
+      </c>
+    </row>
+    <row r="26" spans="1:5">
+      <c r="A26" s="5" t="s">
+        <v>42</v>
+      </c>
+      <c r="B26" s="5" t="s">
+        <v>11</v>
+      </c>
+      <c r="C26" s="6">
+        <v>-16.17</v>
+      </c>
+      <c r="D26" s="6">
+        <v>-13.84</v>
+      </c>
+      <c r="E26" s="7">
+        <v>2.33</v>
+      </c>
+    </row>
+    <row r="27" spans="1:5">
+      <c r="A27" s="5" t="s">
+        <v>43</v>
+      </c>
+      <c r="B27" s="5" t="s">
+        <v>11</v>
+      </c>
+      <c r="C27" s="6">
+        <v>14.81</v>
+      </c>
+      <c r="D27" s="6">
+        <v>15.46</v>
+      </c>
+      <c r="E27" s="7">
+        <v>0.65</v>
+      </c>
+    </row>
+    <row r="28" spans="1:5">
+      <c r="A28" s="5" t="s">
+        <v>37</v>
+      </c>
+      <c r="B28" s="5" t="s">
+        <v>10</v>
+      </c>
+      <c r="C28" s="6">
+        <v>-7.82</v>
+      </c>
+      <c r="D28" s="6">
+        <v>-8.42</v>
+      </c>
+      <c r="E28" s="8">
+        <v>-0.6</v>
+      </c>
+    </row>
+    <row r="29" spans="1:5">
+      <c r="A29" s="5" t="s">
+        <v>38</v>
+      </c>
+      <c r="B29" s="5" t="s">
+        <v>10</v>
+      </c>
+      <c r="C29" s="6">
+        <v>-28.19</v>
+      </c>
+      <c r="D29" s="6">
+        <v>-27.19</v>
+      </c>
+      <c r="E29" s="7">
         <v>1</v>
       </c>
-      <c r="D14" s="5">
-        <v>4.1</v>
-      </c>
-      <c r="E14" s="6">
-        <v>3.1</v>
-      </c>
-    </row>
-    <row r="15" spans="1:6">
-      <c r="A15" s="3" t="s">
+    </row>
+    <row r="30" spans="1:5">
+      <c r="A30" s="5" t="s">
+        <v>39</v>
+      </c>
+      <c r="B30" s="5" t="s">
+        <v>10</v>
+      </c>
+      <c r="C30" s="6">
+        <v>-10.52</v>
+      </c>
+      <c r="D30" s="6">
+        <v>-14.14</v>
+      </c>
+      <c r="E30" s="8">
+        <v>-3.62</v>
+      </c>
+    </row>
+    <row r="31" spans="1:5">
+      <c r="A31" s="5" t="s">
+        <v>40</v>
+      </c>
+      <c r="B31" s="5" t="s">
+        <v>10</v>
+      </c>
+      <c r="C31" s="6">
+        <v>-14.29</v>
+      </c>
+      <c r="D31" s="6">
+        <v>-13.32</v>
+      </c>
+      <c r="E31" s="7">
+        <v>0.97</v>
+      </c>
+    </row>
+    <row r="32" spans="1:5">
+      <c r="A32" s="5" t="s">
+        <v>41</v>
+      </c>
+      <c r="B32" s="5" t="s">
+        <v>10</v>
+      </c>
+      <c r="C32" s="6">
+        <v>-3.42</v>
+      </c>
+      <c r="D32" s="6">
+        <v>-7.21</v>
+      </c>
+      <c r="E32" s="8">
+        <v>-3.79</v>
+      </c>
+    </row>
+    <row r="33" spans="1:5">
+      <c r="A33" s="5" t="s">
+        <v>42</v>
+      </c>
+      <c r="B33" s="5" t="s">
+        <v>10</v>
+      </c>
+      <c r="C33" s="6">
+        <v>-12.51</v>
+      </c>
+      <c r="D33" s="6">
+        <v>-10.95</v>
+      </c>
+      <c r="E33" s="7">
+        <v>1.56</v>
+      </c>
+    </row>
+    <row r="34" spans="1:5">
+      <c r="A34" s="5" t="s">
+        <v>43</v>
+      </c>
+      <c r="B34" s="5" t="s">
+        <v>10</v>
+      </c>
+      <c r="C34" s="6">
+        <v>6.7</v>
+      </c>
+      <c r="D34" s="6">
+        <v>7.32</v>
+      </c>
+      <c r="E34" s="7">
+        <v>0.62</v>
+      </c>
+    </row>
+    <row r="35" spans="1:5">
+      <c r="A35" s="5" t="s">
+        <v>37</v>
+      </c>
+      <c r="B35" s="5" t="s">
+        <v>6</v>
+      </c>
+      <c r="C35" s="6">
+        <v>-15.18</v>
+      </c>
+      <c r="D35" s="6">
+        <v>-16</v>
+      </c>
+      <c r="E35" s="8">
+        <v>-0.82</v>
+      </c>
+    </row>
+    <row r="36" spans="1:5">
+      <c r="A36" s="5" t="s">
         <v>38</v>
       </c>
-      <c r="B15" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="C15" s="5">
-        <v>-13.54</v>
-      </c>
-      <c r="D15" s="5">
-        <v>-10.37</v>
-      </c>
-      <c r="E15" s="6">
-        <v>3.17</v>
-      </c>
-    </row>
-    <row r="16" spans="1:6">
-      <c r="A16" s="3" t="s">
+      <c r="B36" s="5" t="s">
+        <v>6</v>
+      </c>
+      <c r="C36" s="6">
+        <v>-43.11</v>
+      </c>
+      <c r="D36" s="6">
+        <v>-41.72</v>
+      </c>
+      <c r="E36" s="7">
+        <v>1.39</v>
+      </c>
+    </row>
+    <row r="37" spans="1:5">
+      <c r="A37" s="5" t="s">
         <v>39</v>
       </c>
-      <c r="B16" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="C16" s="5">
-        <v>-4.91</v>
-      </c>
-      <c r="D16" s="5">
-        <v>-0.15</v>
-      </c>
-      <c r="E16" s="6">
-        <v>4.76</v>
-      </c>
-    </row>
-    <row r="17" spans="1:5">
-      <c r="A17" s="3" t="s">
+      <c r="B37" s="5" t="s">
+        <v>6</v>
+      </c>
+      <c r="C37" s="6">
+        <v>-44.77</v>
+      </c>
+      <c r="D37" s="6">
+        <v>-46.44</v>
+      </c>
+      <c r="E37" s="8">
+        <v>-1.67</v>
+      </c>
+    </row>
+    <row r="38" spans="1:5">
+      <c r="A38" s="5" t="s">
         <v>40</v>
       </c>
-      <c r="B17" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="C17" s="5">
-        <v>-1.35</v>
-      </c>
-      <c r="D17" s="5">
-        <v>-2.22</v>
-      </c>
-      <c r="E17" s="7">
-        <v>-0.87</v>
-      </c>
-    </row>
-    <row r="18" spans="1:5">
-      <c r="A18" s="3" t="s">
+      <c r="B38" s="5" t="s">
+        <v>6</v>
+      </c>
+      <c r="C38" s="6">
+        <v>-23.86</v>
+      </c>
+      <c r="D38" s="6">
+        <v>-23.14</v>
+      </c>
+      <c r="E38" s="7">
+        <v>0.72</v>
+      </c>
+    </row>
+    <row r="39" spans="1:5">
+      <c r="A39" s="5" t="s">
         <v>41</v>
       </c>
-      <c r="B18" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="C18" s="5">
-        <v>-3.23</v>
-      </c>
-      <c r="D18" s="5">
-        <v>-4.68</v>
-      </c>
-      <c r="E18" s="7">
-        <v>-1.45</v>
-      </c>
-    </row>
-    <row r="19" spans="1:5">
-      <c r="A19" s="3" t="s">
+      <c r="B39" s="5" t="s">
+        <v>6</v>
+      </c>
+      <c r="C39" s="6">
+        <v>-20.41</v>
+      </c>
+      <c r="D39" s="6">
+        <v>-22.67</v>
+      </c>
+      <c r="E39" s="8">
+        <v>-2.26</v>
+      </c>
+    </row>
+    <row r="40" spans="1:5">
+      <c r="A40" s="5" t="s">
         <v>42</v>
       </c>
-      <c r="B19" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="C19" s="5">
-        <v>-4.74</v>
-      </c>
-      <c r="D19" s="5">
-        <v>-0.9399999999999999</v>
-      </c>
-      <c r="E19" s="6">
-        <v>3.8</v>
-      </c>
-    </row>
-    <row r="20" spans="1:5">
-      <c r="A20" s="3" t="s">
+      <c r="B40" s="5" t="s">
+        <v>6</v>
+      </c>
+      <c r="C40" s="6">
+        <v>-20.84</v>
+      </c>
+      <c r="D40" s="6">
+        <v>-18.98</v>
+      </c>
+      <c r="E40" s="7">
+        <v>1.86</v>
+      </c>
+    </row>
+    <row r="41" spans="1:5">
+      <c r="A41" s="5" t="s">
         <v>43</v>
       </c>
-      <c r="B20" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="C20" s="5">
-        <v>-9.6</v>
-      </c>
-      <c r="D20" s="5">
-        <v>-5.35</v>
-      </c>
-      <c r="E20" s="6">
-        <v>4.25</v>
-      </c>
-    </row>
-    <row r="21" spans="1:5">
-      <c r="A21" s="3" t="s">
+      <c r="B41" s="5" t="s">
+        <v>6</v>
+      </c>
+      <c r="C41" s="6">
+        <v>-20.17</v>
+      </c>
+      <c r="D41" s="6">
+        <v>-19.52</v>
+      </c>
+      <c r="E41" s="7">
+        <v>0.65</v>
+      </c>
+    </row>
+    <row r="42" spans="1:5">
+      <c r="A42" s="5" t="s">
         <v>37</v>
       </c>
-      <c r="B21" s="3" t="s">
-        <v>11</v>
-      </c>
-      <c r="C21" s="5">
-        <v>15.55</v>
-      </c>
-      <c r="D21" s="5">
-        <v>17.53</v>
-      </c>
-      <c r="E21" s="6">
-        <v>1.98</v>
-      </c>
-    </row>
-    <row r="22" spans="1:5">
-      <c r="A22" s="3" t="s">
+      <c r="B42" s="5" t="s">
+        <v>2</v>
+      </c>
+      <c r="C42" s="6">
+        <v>10485</v>
+      </c>
+      <c r="D42" s="6">
+        <v>10383</v>
+      </c>
+      <c r="E42" s="8">
+        <v>-102</v>
+      </c>
+    </row>
+    <row r="43" spans="1:5">
+      <c r="A43" s="5" t="s">
         <v>38</v>
       </c>
-      <c r="B22" s="3" t="s">
-        <v>11</v>
-      </c>
-      <c r="C22" s="5">
-        <v>41.66</v>
-      </c>
-      <c r="D22" s="5">
-        <v>39.59</v>
-      </c>
-      <c r="E22" s="7">
-        <v>-2.07</v>
-      </c>
-    </row>
-    <row r="23" spans="1:5">
-      <c r="A23" s="3" t="s">
+      <c r="B43" s="5" t="s">
+        <v>2</v>
+      </c>
+      <c r="C43" s="6">
+        <v>381.3</v>
+      </c>
+      <c r="D43" s="6">
+        <v>390.6</v>
+      </c>
+      <c r="E43" s="7">
+        <v>9.300000000000001</v>
+      </c>
+    </row>
+    <row r="44" spans="1:5">
+      <c r="A44" s="5" t="s">
         <v>39</v>
       </c>
-      <c r="B23" s="3" t="s">
-        <v>11</v>
-      </c>
-      <c r="C23" s="5">
-        <v>-48.03</v>
-      </c>
-      <c r="D23" s="5">
-        <v>-45.1</v>
-      </c>
-      <c r="E23" s="6">
-        <v>2.93</v>
-      </c>
-    </row>
-    <row r="24" spans="1:5">
-      <c r="A24" s="3" t="s">
+      <c r="B44" s="5" t="s">
+        <v>2</v>
+      </c>
+      <c r="C44" s="6">
+        <v>292.65</v>
+      </c>
+      <c r="D44" s="6">
+        <v>283.8</v>
+      </c>
+      <c r="E44" s="8">
+        <v>-8.85</v>
+      </c>
+    </row>
+    <row r="45" spans="1:5">
+      <c r="A45" s="5" t="s">
         <v>40</v>
       </c>
-      <c r="B24" s="3" t="s">
-        <v>11</v>
-      </c>
-      <c r="C24" s="5">
-        <v>-22.69</v>
-      </c>
-      <c r="D24" s="5">
-        <v>-24.08</v>
-      </c>
-      <c r="E24" s="7">
-        <v>-1.39</v>
-      </c>
-    </row>
-    <row r="25" spans="1:5">
-      <c r="A25" s="3" t="s">
+      <c r="B45" s="5" t="s">
+        <v>2</v>
+      </c>
+      <c r="C45" s="6">
+        <v>1652.4</v>
+      </c>
+      <c r="D45" s="6">
+        <v>1668</v>
+      </c>
+      <c r="E45" s="7">
+        <v>15.6</v>
+      </c>
+    </row>
+    <row r="46" spans="1:5">
+      <c r="A46" s="5" t="s">
         <v>41</v>
       </c>
-      <c r="B25" s="3" t="s">
-        <v>11</v>
-      </c>
-      <c r="C25" s="5">
-        <v>-14.38</v>
-      </c>
-      <c r="D25" s="5">
-        <v>-20.41</v>
-      </c>
-      <c r="E25" s="7">
-        <v>-6.03</v>
-      </c>
-    </row>
-    <row r="26" spans="1:5">
-      <c r="A26" s="3" t="s">
+      <c r="B46" s="5" t="s">
+        <v>2</v>
+      </c>
+      <c r="C46" s="6">
+        <v>10461</v>
+      </c>
+      <c r="D46" s="6">
+        <v>10160</v>
+      </c>
+      <c r="E46" s="8">
+        <v>-301</v>
+      </c>
+    </row>
+    <row r="47" spans="1:5">
+      <c r="A47" s="5" t="s">
         <v>42</v>
       </c>
-      <c r="B26" s="3" t="s">
-        <v>11</v>
-      </c>
-      <c r="C26" s="5">
-        <v>-16.06</v>
-      </c>
-      <c r="D26" s="5">
-        <v>-16.17</v>
-      </c>
-      <c r="E26" s="7">
-        <v>-0.11</v>
-      </c>
-    </row>
-    <row r="27" spans="1:5">
-      <c r="A27" s="3" t="s">
+      <c r="B47" s="5" t="s">
+        <v>2</v>
+      </c>
+      <c r="C47" s="6">
+        <v>917.25</v>
+      </c>
+      <c r="D47" s="6">
+        <v>938.9</v>
+      </c>
+      <c r="E47" s="7">
+        <v>21.65</v>
+      </c>
+    </row>
+    <row r="48" spans="1:5">
+      <c r="A48" s="5" t="s">
         <v>43</v>
       </c>
-      <c r="B27" s="3" t="s">
-        <v>11</v>
-      </c>
-      <c r="C27" s="5">
-        <v>14.92</v>
-      </c>
-      <c r="D27" s="5">
+      <c r="B48" s="5" t="s">
+        <v>2</v>
+      </c>
+      <c r="C48" s="6">
+        <v>148.42</v>
+      </c>
+      <c r="D48" s="6">
+        <v>149.63</v>
+      </c>
+      <c r="E48" s="7">
+        <v>1.21</v>
+      </c>
+    </row>
+    <row r="49" spans="1:5">
+      <c r="A49" s="5" t="s">
+        <v>37</v>
+      </c>
+      <c r="B49" s="5" t="s">
+        <v>13</v>
+      </c>
+      <c r="C49" s="6">
+        <v>85</v>
+      </c>
+      <c r="D49" s="6">
+        <v>71</v>
+      </c>
+      <c r="E49" s="8">
+        <v>-14</v>
+      </c>
+    </row>
+    <row r="50" spans="1:5">
+      <c r="A50" s="5" t="s">
+        <v>38</v>
+      </c>
+      <c r="B50" s="5" t="s">
+        <v>13</v>
+      </c>
+      <c r="C50" s="6">
+        <v>71</v>
+      </c>
+      <c r="D50" s="6">
+        <v>85</v>
+      </c>
+      <c r="E50" s="7">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="51" spans="1:5">
+      <c r="A51" s="5" t="s">
+        <v>41</v>
+      </c>
+      <c r="B51" s="5" t="s">
+        <v>13</v>
+      </c>
+      <c r="C51" s="6">
+        <v>57</v>
+      </c>
+      <c r="D51" s="6">
+        <v>43</v>
+      </c>
+      <c r="E51" s="8">
+        <v>-14</v>
+      </c>
+    </row>
+    <row r="52" spans="1:5">
+      <c r="A52" s="5" t="s">
+        <v>42</v>
+      </c>
+      <c r="B52" s="5" t="s">
+        <v>13</v>
+      </c>
+      <c r="C52" s="6">
+        <v>43</v>
+      </c>
+      <c r="D52" s="6">
+        <v>57</v>
+      </c>
+      <c r="E52" s="7">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="53" spans="1:5">
+      <c r="A53" s="5" t="s">
+        <v>37</v>
+      </c>
+      <c r="B53" s="5" t="s">
+        <v>24</v>
+      </c>
+      <c r="C53" s="6">
+        <v>49.47</v>
+      </c>
+      <c r="D53" s="6">
+        <v>46.91</v>
+      </c>
+      <c r="E53" s="8">
+        <v>-2.56</v>
+      </c>
+    </row>
+    <row r="54" spans="1:5">
+      <c r="A54" s="5" t="s">
+        <v>38</v>
+      </c>
+      <c r="B54" s="5" t="s">
+        <v>24</v>
+      </c>
+      <c r="C54" s="6">
+        <v>25.96</v>
+      </c>
+      <c r="D54" s="6">
+        <v>30</v>
+      </c>
+      <c r="E54" s="7">
+        <v>4.04</v>
+      </c>
+    </row>
+    <row r="55" spans="1:5">
+      <c r="A55" s="5" t="s">
+        <v>39</v>
+      </c>
+      <c r="B55" s="5" t="s">
+        <v>24</v>
+      </c>
+      <c r="C55" s="6">
+        <v>43.2</v>
+      </c>
+      <c r="D55" s="6">
+        <v>37.96</v>
+      </c>
+      <c r="E55" s="8">
+        <v>-5.24</v>
+      </c>
+    </row>
+    <row r="56" spans="1:5">
+      <c r="A56" s="5" t="s">
+        <v>40</v>
+      </c>
+      <c r="B56" s="5" t="s">
+        <v>24</v>
+      </c>
+      <c r="C56" s="6">
+        <v>30.66</v>
+      </c>
+      <c r="D56" s="6">
+        <v>34.94</v>
+      </c>
+      <c r="E56" s="7">
+        <v>4.28</v>
+      </c>
+    </row>
+    <row r="57" spans="1:5">
+      <c r="A57" s="5" t="s">
+        <v>41</v>
+      </c>
+      <c r="B57" s="5" t="s">
+        <v>24</v>
+      </c>
+      <c r="C57" s="6">
+        <v>39</v>
+      </c>
+      <c r="D57" s="6">
+        <v>34.45</v>
+      </c>
+      <c r="E57" s="8">
+        <v>-4.55</v>
+      </c>
+    </row>
+    <row r="58" spans="1:5">
+      <c r="A58" s="5" t="s">
+        <v>42</v>
+      </c>
+      <c r="B58" s="5" t="s">
+        <v>24</v>
+      </c>
+      <c r="C58" s="6">
+        <v>36.73</v>
+      </c>
+      <c r="D58" s="6">
+        <v>43.44</v>
+      </c>
+      <c r="E58" s="7">
+        <v>6.71</v>
+      </c>
+    </row>
+    <row r="59" spans="1:5">
+      <c r="A59" s="5" t="s">
+        <v>43</v>
+      </c>
+      <c r="B59" s="5" t="s">
+        <v>24</v>
+      </c>
+      <c r="C59" s="6">
+        <v>40.41</v>
+      </c>
+      <c r="D59" s="6">
+        <v>41.74</v>
+      </c>
+      <c r="E59" s="7">
+        <v>1.33</v>
+      </c>
+    </row>
+    <row r="60" spans="1:5">
+      <c r="A60" s="5" t="s">
+        <v>37</v>
+      </c>
+      <c r="B60" s="5" t="s">
+        <v>31</v>
+      </c>
+      <c r="C60" s="6">
+        <v>205.37</v>
+      </c>
+      <c r="D60" s="6">
+        <v>-22.88</v>
+      </c>
+      <c r="E60" s="8">
+        <v>-228.25</v>
+      </c>
+    </row>
+    <row r="61" spans="1:5">
+      <c r="A61" s="5" t="s">
+        <v>38</v>
+      </c>
+      <c r="B61" s="5" t="s">
+        <v>31</v>
+      </c>
+      <c r="C61" s="6">
+        <v>-69.27</v>
+      </c>
+      <c r="D61" s="6">
+        <v>-44.22</v>
+      </c>
+      <c r="E61" s="7">
+        <v>25.05</v>
+      </c>
+    </row>
+    <row r="62" spans="1:5">
+      <c r="A62" s="5" t="s">
+        <v>39</v>
+      </c>
+      <c r="B62" s="5" t="s">
+        <v>31</v>
+      </c>
+      <c r="C62" s="6">
+        <v>1223.89</v>
+      </c>
+      <c r="D62" s="6">
+        <v>-37.31</v>
+      </c>
+      <c r="E62" s="8">
+        <v>-1261.2</v>
+      </c>
+    </row>
+    <row r="63" spans="1:5">
+      <c r="A63" s="5" t="s">
+        <v>40</v>
+      </c>
+      <c r="B63" s="5" t="s">
+        <v>31</v>
+      </c>
+      <c r="C63" s="6">
+        <v>36.35</v>
+      </c>
+      <c r="D63" s="6">
         <v>14.81</v>
       </c>
-      <c r="E27" s="7">
-        <v>-0.11</v>
-      </c>
-    </row>
-    <row r="28" spans="1:5">
-      <c r="A28" s="3" t="s">
-        <v>37</v>
-      </c>
-      <c r="B28" s="3" t="s">
-        <v>10</v>
-      </c>
-      <c r="C28" s="5">
-        <v>-7.1</v>
-      </c>
-      <c r="D28" s="5">
-        <v>-7.82</v>
-      </c>
-      <c r="E28" s="7">
-        <v>-0.72</v>
-      </c>
-    </row>
-    <row r="29" spans="1:5">
-      <c r="A29" s="3" t="s">
-        <v>38</v>
-      </c>
-      <c r="B29" s="3" t="s">
-        <v>10</v>
-      </c>
-      <c r="C29" s="5">
-        <v>-28.54</v>
-      </c>
-      <c r="D29" s="5">
-        <v>-28.19</v>
-      </c>
-      <c r="E29" s="6">
-        <v>0.35</v>
-      </c>
-    </row>
-    <row r="30" spans="1:5">
-      <c r="A30" s="3" t="s">
-        <v>39</v>
-      </c>
-      <c r="B30" s="3" t="s">
-        <v>10</v>
-      </c>
-      <c r="C30" s="5">
-        <v>-14.45</v>
-      </c>
-      <c r="D30" s="5">
-        <v>-10.52</v>
-      </c>
-      <c r="E30" s="6">
-        <v>3.93</v>
-      </c>
-    </row>
-    <row r="31" spans="1:5">
-      <c r="A31" s="3" t="s">
-        <v>40</v>
-      </c>
-      <c r="B31" s="3" t="s">
-        <v>10</v>
-      </c>
-      <c r="C31" s="5">
-        <v>-12.34</v>
-      </c>
-      <c r="D31" s="5">
-        <v>-14.29</v>
-      </c>
-      <c r="E31" s="7">
-        <v>-1.95</v>
-      </c>
-    </row>
-    <row r="32" spans="1:5">
-      <c r="A32" s="3" t="s">
+      <c r="E63" s="8">
+        <v>-21.54</v>
+      </c>
+    </row>
+    <row r="64" spans="1:5">
+      <c r="A64" s="5" t="s">
         <v>41</v>
       </c>
-      <c r="B32" s="3" t="s">
-        <v>10</v>
-      </c>
-      <c r="C32" s="5">
-        <v>0.84</v>
-      </c>
-      <c r="D32" s="5">
-        <v>-3.42</v>
-      </c>
-      <c r="E32" s="7">
-        <v>-4.26</v>
-      </c>
-    </row>
-    <row r="33" spans="1:5">
-      <c r="A33" s="3" t="s">
+      <c r="B64" s="5" t="s">
+        <v>31</v>
+      </c>
+      <c r="C64" s="6">
+        <v>-39.29</v>
+      </c>
+      <c r="D64" s="6">
+        <v>36.92</v>
+      </c>
+      <c r="E64" s="7">
+        <v>76.20999999999999</v>
+      </c>
+    </row>
+    <row r="65" spans="1:5">
+      <c r="A65" s="5" t="s">
         <v>42</v>
       </c>
-      <c r="B33" s="3" t="s">
-        <v>10</v>
-      </c>
-      <c r="C33" s="5">
-        <v>-13</v>
-      </c>
-      <c r="D33" s="5">
-        <v>-12.51</v>
-      </c>
-      <c r="E33" s="6">
-        <v>0.49</v>
-      </c>
-    </row>
-    <row r="34" spans="1:5">
-      <c r="A34" s="3" t="s">
+      <c r="B65" s="5" t="s">
+        <v>31</v>
+      </c>
+      <c r="C65" s="6">
+        <v>-33.3</v>
+      </c>
+      <c r="D65" s="6">
+        <v>5.48</v>
+      </c>
+      <c r="E65" s="7">
+        <v>38.78</v>
+      </c>
+    </row>
+    <row r="66" spans="1:5">
+      <c r="A66" s="5" t="s">
         <v>43</v>
       </c>
-      <c r="B34" s="3" t="s">
-        <v>10</v>
-      </c>
-      <c r="C34" s="5">
-        <v>5.78</v>
-      </c>
-      <c r="D34" s="5">
-        <v>6.7</v>
-      </c>
-      <c r="E34" s="6">
-        <v>0.92</v>
-      </c>
-    </row>
-    <row r="35" spans="1:5">
-      <c r="A35" s="3" t="s">
-        <v>37</v>
-      </c>
-      <c r="B35" s="3" t="s">
-        <v>6</v>
-      </c>
-      <c r="C35" s="5">
-        <v>-15.95</v>
-      </c>
-      <c r="D35" s="5">
-        <v>-15.18</v>
-      </c>
-      <c r="E35" s="6">
-        <v>0.77</v>
-      </c>
-    </row>
-    <row r="36" spans="1:5">
-      <c r="A36" s="3" t="s">
-        <v>38</v>
-      </c>
-      <c r="B36" s="3" t="s">
-        <v>6</v>
-      </c>
-      <c r="C36" s="5">
-        <v>-42.33</v>
-      </c>
-      <c r="D36" s="5">
-        <v>-43.11</v>
-      </c>
-      <c r="E36" s="7">
-        <v>-0.78</v>
-      </c>
-    </row>
-    <row r="37" spans="1:5">
-      <c r="A37" s="3" t="s">
-        <v>39</v>
-      </c>
-      <c r="B37" s="3" t="s">
-        <v>6</v>
-      </c>
-      <c r="C37" s="5">
-        <v>-47.13</v>
-      </c>
-      <c r="D37" s="5">
-        <v>-44.77</v>
-      </c>
-      <c r="E37" s="6">
-        <v>2.36</v>
-      </c>
-    </row>
-    <row r="38" spans="1:5">
-      <c r="A38" s="3" t="s">
-        <v>40</v>
-      </c>
-      <c r="B38" s="3" t="s">
-        <v>6</v>
-      </c>
-      <c r="C38" s="5">
-        <v>-22.95</v>
-      </c>
-      <c r="D38" s="5">
-        <v>-23.86</v>
-      </c>
-      <c r="E38" s="7">
-        <v>-0.91</v>
-      </c>
-    </row>
-    <row r="39" spans="1:5">
-      <c r="A39" s="3" t="s">
-        <v>41</v>
-      </c>
-      <c r="B39" s="3" t="s">
-        <v>6</v>
-      </c>
-      <c r="C39" s="5">
-        <v>-17.06</v>
-      </c>
-      <c r="D39" s="5">
-        <v>-20.41</v>
-      </c>
-      <c r="E39" s="7">
-        <v>-3.35</v>
-      </c>
-    </row>
-    <row r="40" spans="1:5">
-      <c r="A40" s="3" t="s">
-        <v>42</v>
-      </c>
-      <c r="B40" s="3" t="s">
-        <v>6</v>
-      </c>
-      <c r="C40" s="5">
-        <v>-21.3</v>
-      </c>
-      <c r="D40" s="5">
-        <v>-20.84</v>
-      </c>
-      <c r="E40" s="6">
-        <v>0.46</v>
-      </c>
-    </row>
-    <row r="41" spans="1:5">
-      <c r="A41" s="3" t="s">
-        <v>43</v>
-      </c>
-      <c r="B41" s="3" t="s">
-        <v>6</v>
-      </c>
-      <c r="C41" s="5">
-        <v>-20.02</v>
-      </c>
-      <c r="D41" s="5">
-        <v>-20.17</v>
-      </c>
-      <c r="E41" s="7">
-        <v>-0.15</v>
-      </c>
-    </row>
-    <row r="42" spans="1:5">
-      <c r="A42" s="3" t="s">
-        <v>37</v>
-      </c>
-      <c r="B42" s="3" t="s">
-        <v>2</v>
-      </c>
-      <c r="C42" s="5">
-        <v>10390</v>
-      </c>
-      <c r="D42" s="5">
-        <v>10485</v>
-      </c>
-      <c r="E42" s="6">
-        <v>95</v>
-      </c>
-    </row>
-    <row r="43" spans="1:5">
-      <c r="A43" s="3" t="s">
-        <v>38</v>
-      </c>
-      <c r="B43" s="3" t="s">
-        <v>2</v>
-      </c>
-      <c r="C43" s="5">
-        <v>386.5</v>
-      </c>
-      <c r="D43" s="5">
-        <v>381.3</v>
-      </c>
-      <c r="E43" s="7">
-        <v>-5.2</v>
-      </c>
-    </row>
-    <row r="44" spans="1:5">
-      <c r="A44" s="3" t="s">
-        <v>39</v>
-      </c>
-      <c r="B44" s="3" t="s">
-        <v>2</v>
-      </c>
-      <c r="C44" s="5">
-        <v>281.8</v>
-      </c>
-      <c r="D44" s="5">
-        <v>292.65</v>
-      </c>
-      <c r="E44" s="6">
-        <v>10.85</v>
-      </c>
-    </row>
-    <row r="45" spans="1:5">
-      <c r="A45" s="3" t="s">
-        <v>40</v>
-      </c>
-      <c r="B45" s="3" t="s">
-        <v>2</v>
-      </c>
-      <c r="C45" s="5">
-        <v>1677</v>
-      </c>
-      <c r="D45" s="5">
-        <v>1652.4</v>
-      </c>
-      <c r="E45" s="7">
-        <v>-24.6</v>
-      </c>
-    </row>
-    <row r="46" spans="1:5">
-      <c r="A46" s="3" t="s">
-        <v>41</v>
-      </c>
-      <c r="B46" s="3" t="s">
-        <v>2</v>
-      </c>
-      <c r="C46" s="5">
-        <v>10901</v>
-      </c>
-      <c r="D46" s="5">
-        <v>10461</v>
-      </c>
-      <c r="E46" s="7">
-        <v>-440</v>
-      </c>
-    </row>
-    <row r="47" spans="1:5">
-      <c r="A47" s="3" t="s">
-        <v>42</v>
-      </c>
-      <c r="B47" s="3" t="s">
-        <v>2</v>
-      </c>
-      <c r="C47" s="5">
-        <v>912</v>
-      </c>
-      <c r="D47" s="5">
-        <v>917.25</v>
-      </c>
-      <c r="E47" s="6">
-        <v>5.25</v>
-      </c>
-    </row>
-    <row r="48" spans="1:5">
-      <c r="A48" s="3" t="s">
-        <v>43</v>
-      </c>
-      <c r="B48" s="3" t="s">
-        <v>2</v>
-      </c>
-      <c r="C48" s="5">
-        <v>148.69</v>
-      </c>
-      <c r="D48" s="5">
-        <v>148.42</v>
-      </c>
-      <c r="E48" s="7">
-        <v>-0.27</v>
-      </c>
-    </row>
-    <row r="49" spans="1:5">
-      <c r="A49" s="3" t="s">
-        <v>37</v>
-      </c>
-      <c r="B49" s="3" t="s">
-        <v>24</v>
-      </c>
-      <c r="C49" s="5">
-        <v>46.97</v>
-      </c>
-      <c r="D49" s="5">
-        <v>49.47</v>
-      </c>
-      <c r="E49" s="6">
-        <v>2.5</v>
-      </c>
-    </row>
-    <row r="50" spans="1:5">
-      <c r="A50" s="3" t="s">
-        <v>38</v>
-      </c>
-      <c r="B50" s="3" t="s">
-        <v>24</v>
-      </c>
-      <c r="C50" s="5">
-        <v>26.76</v>
-      </c>
-      <c r="D50" s="5">
-        <v>25.96</v>
-      </c>
-      <c r="E50" s="7">
-        <v>-0.8</v>
-      </c>
-    </row>
-    <row r="51" spans="1:5">
-      <c r="A51" s="3" t="s">
-        <v>39</v>
-      </c>
-      <c r="B51" s="3" t="s">
-        <v>24</v>
-      </c>
-      <c r="C51" s="5">
-        <v>32.61</v>
-      </c>
-      <c r="D51" s="5">
-        <v>43.2</v>
-      </c>
-      <c r="E51" s="6">
-        <v>10.59</v>
-      </c>
-    </row>
-    <row r="52" spans="1:5">
-      <c r="A52" s="3" t="s">
-        <v>40</v>
-      </c>
-      <c r="B52" s="3" t="s">
-        <v>24</v>
-      </c>
-      <c r="C52" s="5">
-        <v>33.93</v>
-      </c>
-      <c r="D52" s="5">
-        <v>30.66</v>
-      </c>
-      <c r="E52" s="7">
-        <v>-3.27</v>
-      </c>
-    </row>
-    <row r="53" spans="1:5">
-      <c r="A53" s="3" t="s">
-        <v>41</v>
-      </c>
-      <c r="B53" s="3" t="s">
-        <v>24</v>
-      </c>
-      <c r="C53" s="5">
-        <v>47.54</v>
-      </c>
-      <c r="D53" s="5">
-        <v>39</v>
-      </c>
-      <c r="E53" s="7">
-        <v>-8.539999999999999</v>
-      </c>
-    </row>
-    <row r="54" spans="1:5">
-      <c r="A54" s="3" t="s">
-        <v>42</v>
-      </c>
-      <c r="B54" s="3" t="s">
-        <v>24</v>
-      </c>
-      <c r="C54" s="5">
-        <v>35</v>
-      </c>
-      <c r="D54" s="5">
-        <v>36.73</v>
-      </c>
-      <c r="E54" s="6">
-        <v>1.73</v>
-      </c>
-    </row>
-    <row r="55" spans="1:5">
-      <c r="A55" s="3" t="s">
-        <v>43</v>
-      </c>
-      <c r="B55" s="3" t="s">
-        <v>24</v>
-      </c>
-      <c r="C55" s="5">
-        <v>40.6</v>
-      </c>
-      <c r="D55" s="5">
-        <v>40.41</v>
-      </c>
-      <c r="E55" s="7">
-        <v>-0.19</v>
-      </c>
-    </row>
-    <row r="56" spans="1:5">
-      <c r="A56" s="3" t="s">
-        <v>37</v>
-      </c>
-      <c r="B56" s="3" t="s">
+      <c r="B66" s="5" t="s">
         <v>31</v>
       </c>
-      <c r="C56" s="5">
-        <v>11.3</v>
-      </c>
-      <c r="D56" s="5">
-        <v>205.37</v>
-      </c>
-      <c r="E56" s="6">
-        <v>194.07</v>
-      </c>
-    </row>
-    <row r="57" spans="1:5">
-      <c r="A57" s="3" t="s">
-        <v>38</v>
-      </c>
-      <c r="B57" s="3" t="s">
-        <v>31</v>
-      </c>
-      <c r="C57" s="5">
-        <v>-72.42</v>
-      </c>
-      <c r="D57" s="5">
-        <v>-69.27</v>
-      </c>
-      <c r="E57" s="6">
-        <v>3.15</v>
-      </c>
-    </row>
-    <row r="58" spans="1:5">
-      <c r="A58" s="3" t="s">
-        <v>39</v>
-      </c>
-      <c r="B58" s="3" t="s">
-        <v>31</v>
-      </c>
-      <c r="C58" s="5">
-        <v>-83.40000000000001</v>
-      </c>
-      <c r="D58" s="5">
-        <v>1223.89</v>
-      </c>
-      <c r="E58" s="6">
-        <v>1307.29</v>
-      </c>
-    </row>
-    <row r="59" spans="1:5">
-      <c r="A59" s="3" t="s">
-        <v>40</v>
-      </c>
-      <c r="B59" s="3" t="s">
-        <v>31</v>
-      </c>
-      <c r="C59" s="5">
-        <v>130.11</v>
-      </c>
-      <c r="D59" s="5">
-        <v>36.35</v>
-      </c>
-      <c r="E59" s="7">
-        <v>-93.76000000000001</v>
-      </c>
-    </row>
-    <row r="60" spans="1:5">
-      <c r="A60" s="3" t="s">
-        <v>41</v>
-      </c>
-      <c r="B60" s="3" t="s">
-        <v>31</v>
-      </c>
-      <c r="C60" s="5">
-        <v>95.76000000000001</v>
-      </c>
-      <c r="D60" s="5">
-        <v>-39.29</v>
-      </c>
-      <c r="E60" s="7">
-        <v>-135.05</v>
-      </c>
-    </row>
-    <row r="61" spans="1:5">
-      <c r="A61" s="3" t="s">
-        <v>42</v>
-      </c>
-      <c r="B61" s="3" t="s">
-        <v>31</v>
-      </c>
-      <c r="C61" s="5">
-        <v>-26.91</v>
-      </c>
-      <c r="D61" s="5">
-        <v>-33.3</v>
-      </c>
-      <c r="E61" s="7">
-        <v>-6.39</v>
-      </c>
-    </row>
-    <row r="62" spans="1:5">
-      <c r="A62" s="3" t="s">
-        <v>43</v>
-      </c>
-      <c r="B62" s="3" t="s">
-        <v>31</v>
-      </c>
-      <c r="C62" s="5">
-        <v>-86.34999999999999</v>
-      </c>
-      <c r="D62" s="5">
+      <c r="C66" s="6">
         <v>-80.23999999999999</v>
       </c>
-      <c r="E62" s="6">
-        <v>6.11</v>
+      <c r="D66" s="6">
+        <v>-69.48999999999999</v>
+      </c>
+      <c r="E66" s="7">
+        <v>10.75</v>
       </c>
     </row>
   </sheetData>
@@ -2838,60 +2969,60 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:9" ht="28" customHeight="1">
-      <c r="A1" s="8" t="s">
+      <c r="A1" s="9" t="s">
         <v>1</v>
       </c>
-      <c r="B1" s="8" t="s">
-        <v>55</v>
-      </c>
-      <c r="C1" s="8" t="s">
-        <v>56</v>
-      </c>
-      <c r="D1" s="8" t="s">
+      <c r="B1" s="9" t="s">
+        <v>64</v>
+      </c>
+      <c r="C1" s="9" t="s">
+        <v>65</v>
+      </c>
+      <c r="D1" s="9" t="s">
+        <v>66</v>
+      </c>
+      <c r="E1" s="9" t="s">
+        <v>67</v>
+      </c>
+      <c r="F1" s="9" t="s">
+        <v>68</v>
+      </c>
+      <c r="G1" s="9" t="s">
+        <v>69</v>
+      </c>
+      <c r="H1" s="9" t="s">
+        <v>70</v>
+      </c>
+      <c r="I1" s="9" t="s">
+        <v>71</v>
+      </c>
+    </row>
+    <row r="2" spans="1:9">
+      <c r="A2" s="10" t="s">
+        <v>44</v>
+      </c>
+      <c r="B2" s="11">
+        <v>44.24</v>
+      </c>
+      <c r="C2" s="12">
+        <v>7</v>
+      </c>
+      <c r="D2" s="11">
+        <v>38.5</v>
+      </c>
+      <c r="E2" s="11">
+        <v>28.6</v>
+      </c>
+      <c r="F2" s="11">
+        <v>-8.9</v>
+      </c>
+      <c r="G2" s="11">
+        <v>-10.6</v>
+      </c>
+      <c r="H2" s="11">
         <v>57</v>
       </c>
-      <c r="E1" s="8" t="s">
-        <v>58</v>
-      </c>
-      <c r="F1" s="8" t="s">
-        <v>59</v>
-      </c>
-      <c r="G1" s="8" t="s">
-        <v>60</v>
-      </c>
-      <c r="H1" s="8" t="s">
-        <v>61</v>
-      </c>
-      <c r="I1" s="8" t="s">
-        <v>62</v>
-      </c>
-    </row>
-    <row r="2" spans="1:9">
-      <c r="A2" s="9" t="s">
-        <v>44</v>
-      </c>
-      <c r="B2" s="10">
-        <v>44.24</v>
-      </c>
-      <c r="C2" s="11">
-        <v>7</v>
-      </c>
-      <c r="D2" s="10">
-        <v>37.9</v>
-      </c>
-      <c r="E2" s="10">
-        <v>28.6</v>
-      </c>
-      <c r="F2" s="10">
-        <v>-9.9</v>
-      </c>
-      <c r="G2" s="10">
-        <v>-10</v>
-      </c>
-      <c r="H2" s="10">
-        <v>57</v>
-      </c>
-      <c r="I2" s="10">
+      <c r="I2" s="11">
         <v>14.3</v>
       </c>
     </row>
@@ -2993,49 +3124,49 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:7">
-      <c r="A1" s="12" t="s">
+      <c r="A1" s="13" t="s">
         <v>37</v>
       </c>
-      <c r="B1" s="12" t="s">
+      <c r="B1" s="13" t="s">
         <v>41</v>
       </c>
-      <c r="C1" s="12" t="s">
+      <c r="C1" s="13" t="s">
         <v>38</v>
       </c>
-      <c r="D1" s="12" t="s">
+      <c r="D1" s="13" t="s">
         <v>42</v>
       </c>
-      <c r="E1" s="12" t="s">
+      <c r="E1" s="13" t="s">
         <v>43</v>
       </c>
-      <c r="F1" s="12" t="s">
+      <c r="F1" s="13" t="s">
         <v>40</v>
       </c>
-      <c r="G1" s="12" t="s">
+      <c r="G1" s="13" t="s">
         <v>39</v>
       </c>
     </row>
     <row r="2" spans="1:7">
-      <c r="A2" s="13">
-        <v>0.26</v>
-      </c>
-      <c r="B2" s="13">
-        <v>0.1827</v>
-      </c>
-      <c r="C2" s="13">
-        <v>0.1239</v>
-      </c>
-      <c r="D2" s="13">
-        <v>0.0455</v>
-      </c>
-      <c r="E2" s="13">
-        <v>0.0296</v>
-      </c>
-      <c r="F2" s="13">
-        <v>-0.0164</v>
-      </c>
-      <c r="G2" s="13">
-        <v>-0.2246</v>
+      <c r="A2" s="14">
+        <v>0.2571</v>
+      </c>
+      <c r="B2" s="14">
+        <v>0.173</v>
+      </c>
+      <c r="C2" s="14">
+        <v>0.1295</v>
+      </c>
+      <c r="D2" s="14">
+        <v>0.0528</v>
+      </c>
+      <c r="E2" s="14">
+        <v>0.0367</v>
+      </c>
+      <c r="F2" s="14">
+        <v>-0.0128</v>
+      </c>
+      <c r="G2" s="14">
+        <v>-0.2267</v>
       </c>
     </row>
   </sheetData>

--- a/BAJAJ_GROUP_Technical_Metrics.xlsx
+++ b/BAJAJ_GROUP_Technical_Metrics.xlsx
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="272" uniqueCount="72">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="259" uniqueCount="63">
   <si>
     <t>Symbol</t>
   </si>
@@ -169,34 +169,7 @@
     <t>▶  SIGNAL EVENTS (vs Previous Run)</t>
   </si>
   <si>
-    <t>Signal</t>
-  </si>
-  <si>
-    <t>Change</t>
-  </si>
-  <si>
-    <t>Direction</t>
-  </si>
-  <si>
-    <t>Prev Value</t>
-  </si>
-  <si>
-    <t>Curr Value</t>
-  </si>
-  <si>
-    <t>RSI Oversold Recovery</t>
-  </si>
-  <si>
-    <t>26.0 → 30.0</t>
-  </si>
-  <si>
-    <t>🟢 BULLISH</t>
-  </si>
-  <si>
-    <t>26.0</t>
-  </si>
-  <si>
-    <t>30.0</t>
+    <t>No signal events detected since last run.</t>
   </si>
   <si>
     <t>▶  NUMERIC METRIC CHANGES (vs Previous Run)</t>
@@ -398,15 +371,14 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="15">
+  <cellXfs count="14">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="2" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="3" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1"/>
     <xf numFmtId="165" fontId="4" fillId="5" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="165" fontId="5" fillId="6" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
@@ -780,15 +752,15 @@
     <col min="13" max="13" width="10.7109375" customWidth="1"/>
     <col min="14" max="14" width="11.7109375" customWidth="1"/>
     <col min="15" max="15" width="10.7109375" customWidth="1"/>
-    <col min="16" max="16" width="9.7109375" customWidth="1"/>
-    <col min="17" max="19" width="10.7109375" customWidth="1"/>
+    <col min="16" max="17" width="9.7109375" customWidth="1"/>
+    <col min="18" max="19" width="10.7109375" customWidth="1"/>
     <col min="20" max="20" width="22.7109375" customWidth="1"/>
     <col min="21" max="21" width="9.7109375" customWidth="1"/>
     <col min="22" max="22" width="10.7109375" customWidth="1"/>
     <col min="23" max="23" width="16.7109375" customWidth="1"/>
     <col min="24" max="24" width="13.7109375" customWidth="1"/>
     <col min="25" max="25" width="7.7109375" customWidth="1"/>
-    <col min="26" max="26" width="8.7109375" customWidth="1"/>
+    <col min="26" max="26" width="9.7109375" customWidth="1"/>
     <col min="27" max="27" width="13.7109375" customWidth="1"/>
     <col min="28" max="28" width="11.7109375" customWidth="1"/>
     <col min="29" max="30" width="13.7109375" customWidth="1"/>
@@ -921,10 +893,10 @@
         <v>44</v>
       </c>
       <c r="C2">
-        <v>10383</v>
+        <v>10350</v>
       </c>
       <c r="D2">
-        <v>-0.97</v>
+        <v>-0.32</v>
       </c>
       <c r="E2">
         <v>12361</v>
@@ -933,46 +905,46 @@
         <v>8599.48</v>
       </c>
       <c r="G2">
-        <v>-16</v>
+        <v>-16.27</v>
       </c>
       <c r="H2">
-        <v>20.74</v>
+        <v>20.36</v>
       </c>
       <c r="I2">
-        <v>2.25</v>
+        <v>2.76</v>
       </c>
       <c r="J2">
-        <v>-5.81</v>
+        <v>-4.26</v>
       </c>
       <c r="K2">
-        <v>-8.42</v>
+        <v>-9.460000000000001</v>
       </c>
       <c r="L2">
-        <v>16</v>
+        <v>15.39</v>
       </c>
       <c r="M2">
-        <v>25.71</v>
+        <v>25.54</v>
       </c>
       <c r="N2">
-        <v>71</v>
+        <v>99</v>
       </c>
       <c r="O2">
-        <v>73</v>
+        <v>75</v>
       </c>
       <c r="P2">
-        <v>10280.2</v>
+        <v>10335.8</v>
       </c>
       <c r="Q2">
-        <v>10178.3</v>
+        <v>10152.1</v>
       </c>
       <c r="R2">
-        <v>11064.92</v>
+        <v>11039.78</v>
       </c>
       <c r="S2">
-        <v>10231.51</v>
+        <v>10236.11</v>
       </c>
       <c r="T2">
-        <v>1.48</v>
+        <v>1.11</v>
       </c>
       <c r="U2" t="s">
         <v>45</v>
@@ -987,34 +959,34 @@
         <v>2</v>
       </c>
       <c r="Y2">
-        <v>46.91</v>
+        <v>46.08</v>
       </c>
       <c r="Z2">
-        <v>-188.3</v>
+        <v>-169.79</v>
       </c>
       <c r="AA2">
-        <v>-268.95</v>
+        <v>-249.11</v>
       </c>
       <c r="AB2">
-        <v>80.65000000000001</v>
+        <v>79.33</v>
       </c>
       <c r="AC2">
-        <v>96.76000000000001</v>
+        <v>90.38</v>
       </c>
       <c r="AD2">
-        <v>91.55</v>
+        <v>93.25</v>
       </c>
       <c r="AE2">
-        <v>277.25</v>
+        <v>273.23</v>
       </c>
       <c r="AF2">
-        <v>-22.88</v>
+        <v>6.17</v>
       </c>
       <c r="AG2">
-        <v>10732.39</v>
+        <v>10608.64</v>
       </c>
       <c r="AH2">
-        <v>9624.209999999999</v>
+        <v>9695.559999999999</v>
       </c>
       <c r="AI2">
         <v>10503.51</v>
@@ -1023,7 +995,7 @@
         <v>47</v>
       </c>
       <c r="AK2">
-        <v>32.63</v>
+        <v>29.73</v>
       </c>
     </row>
     <row r="3" spans="1:37">
@@ -1034,10 +1006,10 @@
         <v>44</v>
       </c>
       <c r="C3">
-        <v>390.6</v>
+        <v>370.15</v>
       </c>
       <c r="D3">
-        <v>2.44</v>
+        <v>-5.24</v>
       </c>
       <c r="E3">
         <v>670.25</v>
@@ -1046,46 +1018,46 @@
         <v>247.45</v>
       </c>
       <c r="G3">
-        <v>-41.72</v>
+        <v>-44.77</v>
       </c>
       <c r="H3">
-        <v>57.85</v>
+        <v>49.59</v>
       </c>
       <c r="I3">
-        <v>-6.08</v>
+        <v>-6.75</v>
       </c>
       <c r="J3">
-        <v>-18.63</v>
+        <v>-24.92</v>
       </c>
       <c r="K3">
-        <v>-27.19</v>
+        <v>-31.21</v>
       </c>
       <c r="L3">
-        <v>44.45</v>
+        <v>38.1</v>
       </c>
       <c r="M3">
-        <v>12.95</v>
+        <v>11.37</v>
       </c>
       <c r="N3">
-        <v>85</v>
+        <v>71</v>
       </c>
       <c r="O3">
-        <v>75</v>
+        <v>69</v>
       </c>
       <c r="P3">
-        <v>388.54</v>
+        <v>383.18</v>
       </c>
       <c r="Q3">
-        <v>456.89</v>
+        <v>450.62</v>
       </c>
       <c r="R3">
-        <v>479.74</v>
+        <v>477.46</v>
       </c>
       <c r="S3">
-        <v>469.12</v>
+        <v>469.57</v>
       </c>
       <c r="T3">
-        <v>-16.74</v>
+        <v>-21.17</v>
       </c>
       <c r="U3" t="s">
         <v>45</v>
@@ -1100,43 +1072,43 @@
         <v>1</v>
       </c>
       <c r="Y3">
-        <v>30</v>
+        <v>26.56</v>
       </c>
       <c r="Z3">
-        <v>-30.35</v>
+        <v>-32.25</v>
       </c>
       <c r="AA3">
-        <v>-21.02</v>
+        <v>-23.26</v>
       </c>
       <c r="AB3">
-        <v>-9.34</v>
+        <v>-8.99</v>
       </c>
       <c r="AC3">
-        <v>4.35</v>
+        <v>5.01</v>
       </c>
       <c r="AD3">
-        <v>1.45</v>
+        <v>3.12</v>
       </c>
       <c r="AE3">
-        <v>21.52</v>
+        <v>21.56</v>
       </c>
       <c r="AF3">
-        <v>-44.22</v>
+        <v>-54.64</v>
       </c>
       <c r="AG3">
-        <v>552.85</v>
+        <v>552.17</v>
       </c>
       <c r="AH3">
-        <v>360.93</v>
+        <v>349.07</v>
       </c>
       <c r="AI3">
-        <v>446.85</v>
+        <v>444.67</v>
       </c>
       <c r="AJ3" t="s">
         <v>47</v>
       </c>
       <c r="AK3">
-        <v>55.5</v>
+        <v>56.7</v>
       </c>
     </row>
     <row r="4" spans="1:37">
@@ -1147,58 +1119,58 @@
         <v>44</v>
       </c>
       <c r="C4">
-        <v>283.8</v>
+        <v>267.3</v>
       </c>
       <c r="D4">
-        <v>-3.02</v>
+        <v>-5.81</v>
       </c>
       <c r="E4">
         <v>529.85</v>
       </c>
       <c r="F4">
-        <v>275.65</v>
+        <v>267.3</v>
       </c>
       <c r="G4">
-        <v>-46.44</v>
+        <v>-49.55</v>
       </c>
       <c r="H4">
-        <v>2.96</v>
+        <v>0</v>
       </c>
       <c r="I4">
-        <v>1.79</v>
+        <v>-3.92</v>
       </c>
       <c r="J4">
-        <v>-9.800000000000001</v>
+        <v>-13.73</v>
       </c>
       <c r="K4">
-        <v>-14.14</v>
+        <v>-18.82</v>
       </c>
       <c r="L4">
-        <v>-46</v>
+        <v>-49.52</v>
       </c>
       <c r="M4">
-        <v>-22.67</v>
+        <v>-23.46</v>
       </c>
       <c r="N4">
         <v>15</v>
       </c>
       <c r="O4">
-        <v>14</v>
+        <v>10</v>
       </c>
       <c r="P4">
-        <v>282.42</v>
+        <v>280.24</v>
       </c>
       <c r="Q4">
-        <v>294.35</v>
+        <v>292.55</v>
       </c>
       <c r="R4">
-        <v>317.34</v>
+        <v>315.57</v>
       </c>
       <c r="S4">
-        <v>351.37</v>
+        <v>350.4</v>
       </c>
       <c r="T4">
-        <v>-19.23</v>
+        <v>-23.72</v>
       </c>
       <c r="U4" t="s">
         <v>45</v>
@@ -1213,34 +1185,34 @@
         <v>0</v>
       </c>
       <c r="Y4">
-        <v>37.96</v>
+        <v>30.53</v>
       </c>
       <c r="Z4">
-        <v>-9.779999999999999</v>
+        <v>-10.84</v>
       </c>
       <c r="AA4">
-        <v>-9.720000000000001</v>
+        <v>-9.949999999999999</v>
       </c>
       <c r="AB4">
-        <v>-0.06</v>
+        <v>-0.9</v>
       </c>
       <c r="AC4">
-        <v>70.15000000000001</v>
+        <v>65.81</v>
       </c>
       <c r="AD4">
-        <v>45.18</v>
+        <v>61.23</v>
       </c>
       <c r="AE4">
-        <v>12.36</v>
+        <v>12.95</v>
       </c>
       <c r="AF4">
-        <v>-37.31</v>
+        <v>-51.79</v>
       </c>
       <c r="AG4">
-        <v>313.77</v>
+        <v>314.92</v>
       </c>
       <c r="AH4">
-        <v>274.94</v>
+        <v>270.18</v>
       </c>
       <c r="AI4">
         <v>308.71</v>
@@ -1249,7 +1221,7 @@
         <v>47</v>
       </c>
       <c r="AK4">
-        <v>33.07</v>
+        <v>29.35</v>
       </c>
     </row>
     <row r="5" spans="1:37">
@@ -1260,58 +1232,58 @@
         <v>44</v>
       </c>
       <c r="C5">
-        <v>1668</v>
+        <v>1667.6</v>
       </c>
       <c r="D5">
-        <v>0.9399999999999999</v>
+        <v>-0.02</v>
       </c>
       <c r="E5">
-        <v>2170.2</v>
+        <v>2140.2</v>
       </c>
       <c r="F5">
         <v>1631.8</v>
       </c>
       <c r="G5">
-        <v>-23.14</v>
+        <v>-22.08</v>
       </c>
       <c r="H5">
-        <v>2.22</v>
+        <v>2.19</v>
       </c>
       <c r="I5">
-        <v>-0.6</v>
+        <v>0.76</v>
       </c>
       <c r="J5">
-        <v>-4.79</v>
+        <v>-4.29</v>
       </c>
       <c r="K5">
-        <v>-13.32</v>
+        <v>-12.66</v>
       </c>
       <c r="L5">
-        <v>-22.76</v>
+        <v>-23.16</v>
       </c>
       <c r="M5">
-        <v>-1.28</v>
+        <v>-1</v>
       </c>
       <c r="N5">
         <v>29</v>
       </c>
       <c r="O5">
-        <v>37</v>
+        <v>41</v>
       </c>
       <c r="P5">
-        <v>1664.66</v>
+        <v>1667.18</v>
       </c>
       <c r="Q5">
-        <v>1710.15</v>
+        <v>1706.98</v>
       </c>
       <c r="R5">
-        <v>1837.16</v>
+        <v>1830.28</v>
       </c>
       <c r="S5">
-        <v>1855.25</v>
+        <v>1853.62</v>
       </c>
       <c r="T5">
-        <v>-10.09</v>
+        <v>-10.04</v>
       </c>
       <c r="U5" t="s">
         <v>45</v>
@@ -1326,34 +1298,34 @@
         <v>0</v>
       </c>
       <c r="Y5">
-        <v>34.94</v>
+        <v>34.88</v>
       </c>
       <c r="Z5">
-        <v>-46.01</v>
+        <v>-44.36</v>
       </c>
       <c r="AA5">
-        <v>-47.68</v>
+        <v>-47.01</v>
       </c>
       <c r="AB5">
-        <v>1.67</v>
+        <v>2.65</v>
       </c>
       <c r="AC5">
-        <v>51.45</v>
+        <v>51.34</v>
       </c>
       <c r="AD5">
-        <v>46.68</v>
+        <v>50.1</v>
       </c>
       <c r="AE5">
-        <v>38.72</v>
+        <v>37.52</v>
       </c>
       <c r="AF5">
-        <v>14.81</v>
+        <v>-27.67</v>
       </c>
       <c r="AG5">
-        <v>1777.59</v>
+        <v>1776.23</v>
       </c>
       <c r="AH5">
-        <v>1642.71</v>
+        <v>1637.73</v>
       </c>
       <c r="AI5">
         <v>1762.43</v>
@@ -1362,7 +1334,7 @@
         <v>47</v>
       </c>
       <c r="AK5">
-        <v>60.97</v>
+        <v>58.19</v>
       </c>
     </row>
     <row r="6" spans="1:37">
@@ -1373,10 +1345,10 @@
         <v>44</v>
       </c>
       <c r="C6">
-        <v>10160</v>
+        <v>10217</v>
       </c>
       <c r="D6">
-        <v>-2.88</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="E6">
         <v>13139</v>
@@ -1385,46 +1357,46 @@
         <v>8746</v>
       </c>
       <c r="G6">
-        <v>-22.67</v>
+        <v>-22.24</v>
       </c>
       <c r="H6">
-        <v>16.17</v>
+        <v>16.82</v>
       </c>
       <c r="I6">
-        <v>-10.03</v>
+        <v>-8.57</v>
       </c>
       <c r="J6">
-        <v>-5.93</v>
+        <v>-3.61</v>
       </c>
       <c r="K6">
-        <v>-7.21</v>
+        <v>-6.86</v>
       </c>
       <c r="L6">
-        <v>-22.7</v>
+        <v>-21.12</v>
       </c>
       <c r="M6">
-        <v>17.3</v>
+        <v>17.77</v>
       </c>
       <c r="N6">
         <v>43</v>
       </c>
       <c r="O6">
-        <v>43</v>
+        <v>49</v>
       </c>
       <c r="P6">
-        <v>10749.4</v>
+        <v>10557.8</v>
       </c>
       <c r="Q6">
-        <v>10845.15</v>
+        <v>10816.6</v>
       </c>
       <c r="R6">
-        <v>11042.46</v>
+        <v>11021.72</v>
       </c>
       <c r="S6">
-        <v>10647.32</v>
+        <v>10643.18</v>
       </c>
       <c r="T6">
-        <v>-4.58</v>
+        <v>-4</v>
       </c>
       <c r="U6" t="s">
         <v>45</v>
@@ -1439,43 +1411,43 @@
         <v>1</v>
       </c>
       <c r="Y6">
-        <v>34.45</v>
+        <v>35.97</v>
       </c>
       <c r="Z6">
-        <v>-85.56</v>
+        <v>-126.9</v>
       </c>
       <c r="AA6">
-        <v>-25.85</v>
+        <v>-46.06</v>
       </c>
       <c r="AB6">
-        <v>-59.71</v>
+        <v>-80.84</v>
       </c>
       <c r="AC6">
-        <v>12.87</v>
+        <v>2.13</v>
       </c>
       <c r="AD6">
-        <v>34.68</v>
+        <v>15.92</v>
       </c>
       <c r="AE6">
-        <v>314.75</v>
+        <v>314.98</v>
       </c>
       <c r="AF6">
-        <v>36.92</v>
+        <v>-52.94</v>
       </c>
       <c r="AG6">
-        <v>11434.78</v>
+        <v>11469.76</v>
       </c>
       <c r="AH6">
-        <v>10255.52</v>
+        <v>10163.44</v>
       </c>
       <c r="AI6">
-        <v>11286.24</v>
+        <v>11134.94</v>
       </c>
       <c r="AJ6" t="s">
         <v>47</v>
       </c>
       <c r="AK6">
-        <v>28.49</v>
+        <v>32.47</v>
       </c>
     </row>
     <row r="7" spans="1:37">
@@ -1486,10 +1458,10 @@
         <v>44</v>
       </c>
       <c r="C7">
-        <v>938.9</v>
+        <v>939.1</v>
       </c>
       <c r="D7">
-        <v>2.36</v>
+        <v>0.02</v>
       </c>
       <c r="E7">
         <v>1158.8</v>
@@ -1498,46 +1470,46 @@
         <v>801.55</v>
       </c>
       <c r="G7">
-        <v>-18.98</v>
+        <v>-18.96</v>
       </c>
       <c r="H7">
-        <v>17.14</v>
+        <v>17.16</v>
       </c>
       <c r="I7">
-        <v>-0.34</v>
+        <v>1.09</v>
       </c>
       <c r="J7">
-        <v>-4.68</v>
+        <v>-3.56</v>
       </c>
       <c r="K7">
-        <v>-10.95</v>
+        <v>-10.86</v>
       </c>
       <c r="L7">
-        <v>-13.84</v>
+        <v>-13.4</v>
       </c>
       <c r="M7">
-        <v>5.28</v>
+        <v>5.25</v>
       </c>
       <c r="N7">
         <v>57</v>
       </c>
       <c r="O7">
-        <v>48</v>
+        <v>52</v>
       </c>
       <c r="P7">
-        <v>923.16</v>
+        <v>925.1900000000001</v>
       </c>
       <c r="Q7">
-        <v>950.3099999999999</v>
+        <v>949.29</v>
       </c>
       <c r="R7">
-        <v>1007.45</v>
+        <v>1004.34</v>
       </c>
       <c r="S7">
-        <v>972.39</v>
+        <v>972.29</v>
       </c>
       <c r="T7">
-        <v>-3.44</v>
+        <v>-3.41</v>
       </c>
       <c r="U7" t="s">
         <v>45</v>
@@ -1552,34 +1524,34 @@
         <v>1</v>
       </c>
       <c r="Y7">
-        <v>43.44</v>
+        <v>43.5</v>
       </c>
       <c r="Z7">
-        <v>-22.74</v>
+        <v>-21.09</v>
       </c>
       <c r="AA7">
-        <v>-22.51</v>
+        <v>-22.23</v>
       </c>
       <c r="AB7">
-        <v>-0.23</v>
+        <v>1.13</v>
       </c>
       <c r="AC7">
-        <v>27.6</v>
+        <v>50.65</v>
       </c>
       <c r="AD7">
-        <v>13.71</v>
+        <v>28.05</v>
       </c>
       <c r="AE7">
-        <v>27.39</v>
+        <v>26.95</v>
       </c>
       <c r="AF7">
-        <v>5.48</v>
+        <v>13.43</v>
       </c>
       <c r="AG7">
-        <v>991.8099999999999</v>
+        <v>990.85</v>
       </c>
       <c r="AH7">
-        <v>908.8099999999999</v>
+        <v>907.74</v>
       </c>
       <c r="AI7">
         <v>989.6</v>
@@ -1588,7 +1560,7 @@
         <v>47</v>
       </c>
       <c r="AK7">
-        <v>24.63</v>
+        <v>22.56</v>
       </c>
     </row>
     <row r="8" spans="1:37">
@@ -1599,10 +1571,10 @@
         <v>44</v>
       </c>
       <c r="C8">
-        <v>149.63</v>
+        <v>141.45</v>
       </c>
       <c r="D8">
-        <v>0.82</v>
+        <v>-5.47</v>
       </c>
       <c r="E8">
         <v>185.92</v>
@@ -1611,46 +1583,46 @@
         <v>115.96</v>
       </c>
       <c r="G8">
-        <v>-19.52</v>
+        <v>-23.92</v>
       </c>
       <c r="H8">
-        <v>29.04</v>
+        <v>21.98</v>
       </c>
       <c r="I8">
-        <v>-2.44</v>
+        <v>-1.13</v>
       </c>
       <c r="J8">
-        <v>-12.51</v>
+        <v>-18</v>
       </c>
       <c r="K8">
-        <v>7.32</v>
+        <v>1.1</v>
       </c>
       <c r="L8">
-        <v>15.46</v>
+        <v>6.77</v>
       </c>
       <c r="M8">
-        <v>3.67</v>
+        <v>2.88</v>
       </c>
       <c r="N8">
-        <v>99</v>
+        <v>85</v>
       </c>
       <c r="O8">
-        <v>78</v>
+        <v>68</v>
       </c>
       <c r="P8">
-        <v>147.17</v>
+        <v>146.85</v>
       </c>
       <c r="Q8">
-        <v>166.74</v>
+        <v>164.8</v>
       </c>
       <c r="R8">
-        <v>151.43</v>
+        <v>151.55</v>
       </c>
       <c r="S8">
-        <v>137.94</v>
+        <v>138.01</v>
       </c>
       <c r="T8">
-        <v>8.470000000000001</v>
+        <v>2.5</v>
       </c>
       <c r="U8" t="s">
         <v>46</v>
@@ -1665,43 +1637,43 @@
         <v>3</v>
       </c>
       <c r="Y8">
-        <v>41.74</v>
+        <v>35.9</v>
       </c>
       <c r="Z8">
-        <v>-2.13</v>
+        <v>-3.12</v>
       </c>
       <c r="AA8">
-        <v>1.69</v>
+        <v>0.73</v>
       </c>
       <c r="AB8">
-        <v>-3.82</v>
+        <v>-3.85</v>
       </c>
       <c r="AC8">
-        <v>17.99</v>
+        <v>14.67</v>
       </c>
       <c r="AD8">
-        <v>12.61</v>
+        <v>15.2</v>
       </c>
       <c r="AE8">
-        <v>8.039999999999999</v>
+        <v>8.18</v>
       </c>
       <c r="AF8">
-        <v>-69.48999999999999</v>
+        <v>-73.93000000000001</v>
       </c>
       <c r="AG8">
-        <v>194.76</v>
+        <v>194.24</v>
       </c>
       <c r="AH8">
-        <v>138.71</v>
+        <v>135.37</v>
       </c>
       <c r="AI8">
-        <v>170.73</v>
+        <v>169.71</v>
       </c>
       <c r="AJ8" t="s">
         <v>47</v>
       </c>
       <c r="AK8">
-        <v>43.82</v>
+        <v>44.55</v>
       </c>
     </row>
   </sheetData>
@@ -1805,27 +1777,27 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="U2:U8">
-    <cfRule type="containsText" dxfId="1" priority="14" operator="containsText" text="Yes">
-      <formula>NOT(ISERROR(SEARCH("Yes",U2)))</formula>
+    <cfRule type="cellIs" dxfId="1" priority="16" operator="equal">
+      <formula>"Yes"</formula>
     </cfRule>
-    <cfRule type="containsText" dxfId="0" priority="15" operator="containsText" text="No">
-      <formula>NOT(ISERROR(SEARCH("No",U2)))</formula>
+    <cfRule type="cellIs" dxfId="0" priority="17" operator="equal">
+      <formula>"No"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="V2:V8">
-    <cfRule type="containsText" dxfId="1" priority="16" operator="containsText" text="Yes">
-      <formula>NOT(ISERROR(SEARCH("Yes",V2)))</formula>
+    <cfRule type="cellIs" dxfId="1" priority="18" operator="equal">
+      <formula>"Yes"</formula>
     </cfRule>
-    <cfRule type="containsText" dxfId="0" priority="17" operator="containsText" text="No">
-      <formula>NOT(ISERROR(SEARCH("No",V2)))</formula>
+    <cfRule type="cellIs" dxfId="0" priority="19" operator="equal">
+      <formula>"No"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="W2:W8">
-    <cfRule type="containsText" dxfId="1" priority="18" operator="containsText" text="Yes">
-      <formula>NOT(ISERROR(SEARCH("Yes",W2)))</formula>
+    <cfRule type="cellIs" dxfId="1" priority="14" operator="equal">
+      <formula>"Yes"</formula>
     </cfRule>
-    <cfRule type="containsText" dxfId="0" priority="19" operator="containsText" text="No">
-      <formula>NOT(ISERROR(SEARCH("No",W2)))</formula>
+    <cfRule type="cellIs" dxfId="0" priority="15" operator="equal">
+      <formula>"No"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="Y2:Y8">
@@ -1842,7 +1814,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:F66"/>
+  <dimension ref="A1:F65"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="16.7109375" customWidth="1"/>
@@ -1862,47 +1834,12 @@
     </row>
     <row r="2" spans="1:6">
       <c r="A2" s="3" t="s">
-        <v>0</v>
-      </c>
-      <c r="B2" s="3" t="s">
         <v>49</v>
-      </c>
-      <c r="C2" s="3" t="s">
-        <v>50</v>
-      </c>
-      <c r="D2" s="3" t="s">
-        <v>51</v>
-      </c>
-      <c r="E2" s="3" t="s">
-        <v>52</v>
-      </c>
-      <c r="F2" s="3" t="s">
-        <v>53</v>
-      </c>
-    </row>
-    <row r="3" spans="1:6">
-      <c r="A3" s="4" t="s">
-        <v>38</v>
-      </c>
-      <c r="B3" s="4" t="s">
-        <v>54</v>
-      </c>
-      <c r="C3" s="4" t="s">
-        <v>55</v>
-      </c>
-      <c r="D3" s="4" t="s">
-        <v>56</v>
-      </c>
-      <c r="E3" s="4" t="s">
-        <v>57</v>
-      </c>
-      <c r="F3" s="4" t="s">
-        <v>58</v>
       </c>
     </row>
     <row r="5" spans="1:6">
       <c r="A5" s="2" t="s">
-        <v>59</v>
+        <v>50</v>
       </c>
       <c r="B5" s="2"/>
       <c r="C5" s="2"/>
@@ -1910,1040 +1847,1023 @@
       <c r="E5" s="2"/>
     </row>
     <row r="6" spans="1:6">
-      <c r="A6" s="3" t="s">
+      <c r="A6" s="4" t="s">
         <v>0</v>
       </c>
-      <c r="B6" s="3" t="s">
-        <v>60</v>
-      </c>
-      <c r="C6" s="3" t="s">
-        <v>61</v>
-      </c>
-      <c r="D6" s="3" t="s">
-        <v>62</v>
-      </c>
-      <c r="E6" s="3" t="s">
-        <v>63</v>
+      <c r="B6" s="4" t="s">
+        <v>51</v>
+      </c>
+      <c r="C6" s="4" t="s">
+        <v>52</v>
+      </c>
+      <c r="D6" s="4" t="s">
+        <v>53</v>
+      </c>
+      <c r="E6" s="4" t="s">
+        <v>54</v>
       </c>
     </row>
     <row r="7" spans="1:6">
-      <c r="A7" s="5" t="s">
+      <c r="A7" s="3" t="s">
         <v>37</v>
       </c>
-      <c r="B7" s="5" t="s">
+      <c r="B7" s="3" t="s">
         <v>9</v>
       </c>
-      <c r="C7" s="6">
-        <v>-7.06</v>
-      </c>
-      <c r="D7" s="6">
+      <c r="C7" s="5">
         <v>-5.81</v>
       </c>
-      <c r="E7" s="7">
-        <v>1.25</v>
+      <c r="D7" s="5">
+        <v>-4.26</v>
+      </c>
+      <c r="E7" s="6">
+        <v>1.55</v>
       </c>
     </row>
     <row r="8" spans="1:6">
-      <c r="A8" s="5" t="s">
+      <c r="A8" s="3" t="s">
         <v>38</v>
       </c>
-      <c r="B8" s="5" t="s">
+      <c r="B8" s="3" t="s">
         <v>9</v>
       </c>
-      <c r="C8" s="6">
-        <v>-23.66</v>
-      </c>
-      <c r="D8" s="6">
+      <c r="C8" s="5">
         <v>-18.63</v>
       </c>
+      <c r="D8" s="5">
+        <v>-24.92</v>
+      </c>
       <c r="E8" s="7">
-        <v>5.03</v>
+        <v>-6.29</v>
       </c>
     </row>
     <row r="9" spans="1:6">
-      <c r="A9" s="5" t="s">
+      <c r="A9" s="3" t="s">
         <v>39</v>
       </c>
-      <c r="B9" s="5" t="s">
+      <c r="B9" s="3" t="s">
         <v>9</v>
       </c>
-      <c r="C9" s="6">
-        <v>-8.25</v>
-      </c>
-      <c r="D9" s="6">
+      <c r="C9" s="5">
         <v>-9.800000000000001</v>
       </c>
-      <c r="E9" s="8">
-        <v>-1.55</v>
+      <c r="D9" s="5">
+        <v>-13.73</v>
+      </c>
+      <c r="E9" s="7">
+        <v>-3.93</v>
       </c>
     </row>
     <row r="10" spans="1:6">
-      <c r="A10" s="5" t="s">
+      <c r="A10" s="3" t="s">
         <v>40</v>
       </c>
-      <c r="B10" s="5" t="s">
+      <c r="B10" s="3" t="s">
         <v>9</v>
       </c>
-      <c r="C10" s="6">
-        <v>-6.7</v>
-      </c>
-      <c r="D10" s="6">
+      <c r="C10" s="5">
         <v>-4.79</v>
       </c>
-      <c r="E10" s="7">
-        <v>1.91</v>
+      <c r="D10" s="5">
+        <v>-4.29</v>
+      </c>
+      <c r="E10" s="6">
+        <v>0.5</v>
       </c>
     </row>
     <row r="11" spans="1:6">
-      <c r="A11" s="5" t="s">
+      <c r="A11" s="3" t="s">
         <v>41</v>
       </c>
-      <c r="B11" s="5" t="s">
+      <c r="B11" s="3" t="s">
         <v>9</v>
       </c>
-      <c r="C11" s="6">
-        <v>-4.38</v>
-      </c>
-      <c r="D11" s="6">
+      <c r="C11" s="5">
         <v>-5.93</v>
       </c>
-      <c r="E11" s="8">
-        <v>-1.55</v>
+      <c r="D11" s="5">
+        <v>-3.61</v>
+      </c>
+      <c r="E11" s="6">
+        <v>2.32</v>
       </c>
     </row>
     <row r="12" spans="1:6">
-      <c r="A12" s="5" t="s">
+      <c r="A12" s="3" t="s">
         <v>42</v>
       </c>
-      <c r="B12" s="5" t="s">
+      <c r="B12" s="3" t="s">
         <v>9</v>
       </c>
-      <c r="C12" s="6">
-        <v>-7.99</v>
-      </c>
-      <c r="D12" s="6">
+      <c r="C12" s="5">
         <v>-4.68</v>
       </c>
-      <c r="E12" s="7">
-        <v>3.31</v>
+      <c r="D12" s="5">
+        <v>-3.56</v>
+      </c>
+      <c r="E12" s="6">
+        <v>1.12</v>
       </c>
     </row>
     <row r="13" spans="1:6">
-      <c r="A13" s="5" t="s">
+      <c r="A13" s="3" t="s">
         <v>43</v>
       </c>
-      <c r="B13" s="5" t="s">
+      <c r="B13" s="3" t="s">
         <v>9</v>
       </c>
-      <c r="C13" s="6">
-        <v>-11.15</v>
-      </c>
-      <c r="D13" s="6">
+      <c r="C13" s="5">
         <v>-12.51</v>
       </c>
-      <c r="E13" s="8">
-        <v>-1.36</v>
+      <c r="D13" s="5">
+        <v>-18</v>
+      </c>
+      <c r="E13" s="7">
+        <v>-5.49</v>
       </c>
     </row>
     <row r="14" spans="1:6">
-      <c r="A14" s="5" t="s">
+      <c r="A14" s="3" t="s">
         <v>37</v>
       </c>
-      <c r="B14" s="5" t="s">
+      <c r="B14" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="C14" s="6">
-        <v>4.1</v>
-      </c>
-      <c r="D14" s="6">
+      <c r="C14" s="5">
         <v>2.25</v>
       </c>
-      <c r="E14" s="8">
-        <v>-1.85</v>
+      <c r="D14" s="5">
+        <v>2.76</v>
+      </c>
+      <c r="E14" s="6">
+        <v>0.51</v>
       </c>
     </row>
     <row r="15" spans="1:6">
-      <c r="A15" s="5" t="s">
+      <c r="A15" s="3" t="s">
         <v>38</v>
       </c>
-      <c r="B15" s="5" t="s">
+      <c r="B15" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="C15" s="6">
-        <v>-10.37</v>
-      </c>
-      <c r="D15" s="6">
+      <c r="C15" s="5">
         <v>-6.08</v>
       </c>
+      <c r="D15" s="5">
+        <v>-6.75</v>
+      </c>
       <c r="E15" s="7">
-        <v>4.29</v>
+        <v>-0.67</v>
       </c>
     </row>
     <row r="16" spans="1:6">
-      <c r="A16" s="5" t="s">
+      <c r="A16" s="3" t="s">
         <v>39</v>
       </c>
-      <c r="B16" s="5" t="s">
+      <c r="B16" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="C16" s="6">
-        <v>-0.15</v>
-      </c>
-      <c r="D16" s="6">
+      <c r="C16" s="5">
         <v>1.79</v>
       </c>
+      <c r="D16" s="5">
+        <v>-3.92</v>
+      </c>
       <c r="E16" s="7">
-        <v>1.94</v>
+        <v>-5.71</v>
       </c>
     </row>
     <row r="17" spans="1:5">
-      <c r="A17" s="5" t="s">
+      <c r="A17" s="3" t="s">
         <v>40</v>
       </c>
-      <c r="B17" s="5" t="s">
+      <c r="B17" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="C17" s="6">
-        <v>-2.22</v>
-      </c>
-      <c r="D17" s="6">
+      <c r="C17" s="5">
         <v>-0.6</v>
       </c>
-      <c r="E17" s="7">
-        <v>1.62</v>
+      <c r="D17" s="5">
+        <v>0.76</v>
+      </c>
+      <c r="E17" s="6">
+        <v>1.36</v>
       </c>
     </row>
     <row r="18" spans="1:5">
-      <c r="A18" s="5" t="s">
+      <c r="A18" s="3" t="s">
         <v>41</v>
       </c>
-      <c r="B18" s="5" t="s">
+      <c r="B18" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="C18" s="6">
+      <c r="C18" s="5">
+        <v>-10.03</v>
+      </c>
+      <c r="D18" s="5">
+        <v>-8.57</v>
+      </c>
+      <c r="E18" s="6">
+        <v>1.46</v>
+      </c>
+    </row>
+    <row r="19" spans="1:5">
+      <c r="A19" s="3" t="s">
+        <v>42</v>
+      </c>
+      <c r="B19" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="C19" s="5">
+        <v>-0.34</v>
+      </c>
+      <c r="D19" s="5">
+        <v>1.09</v>
+      </c>
+      <c r="E19" s="6">
+        <v>1.43</v>
+      </c>
+    </row>
+    <row r="20" spans="1:5">
+      <c r="A20" s="3" t="s">
+        <v>43</v>
+      </c>
+      <c r="B20" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="C20" s="5">
+        <v>-2.44</v>
+      </c>
+      <c r="D20" s="5">
+        <v>-1.13</v>
+      </c>
+      <c r="E20" s="6">
+        <v>1.31</v>
+      </c>
+    </row>
+    <row r="21" spans="1:5">
+      <c r="A21" s="3" t="s">
+        <v>37</v>
+      </c>
+      <c r="B21" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="C21" s="5">
+        <v>16</v>
+      </c>
+      <c r="D21" s="5">
+        <v>15.39</v>
+      </c>
+      <c r="E21" s="7">
+        <v>-0.61</v>
+      </c>
+    </row>
+    <row r="22" spans="1:5">
+      <c r="A22" s="3" t="s">
+        <v>38</v>
+      </c>
+      <c r="B22" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="C22" s="5">
+        <v>44.45</v>
+      </c>
+      <c r="D22" s="5">
+        <v>38.1</v>
+      </c>
+      <c r="E22" s="7">
+        <v>-6.35</v>
+      </c>
+    </row>
+    <row r="23" spans="1:5">
+      <c r="A23" s="3" t="s">
+        <v>39</v>
+      </c>
+      <c r="B23" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="C23" s="5">
+        <v>-46</v>
+      </c>
+      <c r="D23" s="5">
+        <v>-49.52</v>
+      </c>
+      <c r="E23" s="7">
+        <v>-3.52</v>
+      </c>
+    </row>
+    <row r="24" spans="1:5">
+      <c r="A24" s="3" t="s">
+        <v>40</v>
+      </c>
+      <c r="B24" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="C24" s="5">
+        <v>-22.76</v>
+      </c>
+      <c r="D24" s="5">
+        <v>-23.16</v>
+      </c>
+      <c r="E24" s="7">
+        <v>-0.4</v>
+      </c>
+    </row>
+    <row r="25" spans="1:5">
+      <c r="A25" s="3" t="s">
+        <v>41</v>
+      </c>
+      <c r="B25" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="C25" s="5">
+        <v>-22.7</v>
+      </c>
+      <c r="D25" s="5">
+        <v>-21.12</v>
+      </c>
+      <c r="E25" s="6">
+        <v>1.58</v>
+      </c>
+    </row>
+    <row r="26" spans="1:5">
+      <c r="A26" s="3" t="s">
+        <v>42</v>
+      </c>
+      <c r="B26" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="C26" s="5">
+        <v>-13.84</v>
+      </c>
+      <c r="D26" s="5">
+        <v>-13.4</v>
+      </c>
+      <c r="E26" s="6">
+        <v>0.44</v>
+      </c>
+    </row>
+    <row r="27" spans="1:5">
+      <c r="A27" s="3" t="s">
+        <v>43</v>
+      </c>
+      <c r="B27" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="C27" s="5">
+        <v>15.46</v>
+      </c>
+      <c r="D27" s="5">
+        <v>6.77</v>
+      </c>
+      <c r="E27" s="7">
+        <v>-8.69</v>
+      </c>
+    </row>
+    <row r="28" spans="1:5">
+      <c r="A28" s="3" t="s">
+        <v>37</v>
+      </c>
+      <c r="B28" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="C28" s="5">
+        <v>-8.42</v>
+      </c>
+      <c r="D28" s="5">
+        <v>-9.460000000000001</v>
+      </c>
+      <c r="E28" s="7">
+        <v>-1.04</v>
+      </c>
+    </row>
+    <row r="29" spans="1:5">
+      <c r="A29" s="3" t="s">
+        <v>38</v>
+      </c>
+      <c r="B29" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="C29" s="5">
+        <v>-27.19</v>
+      </c>
+      <c r="D29" s="5">
+        <v>-31.21</v>
+      </c>
+      <c r="E29" s="7">
+        <v>-4.02</v>
+      </c>
+    </row>
+    <row r="30" spans="1:5">
+      <c r="A30" s="3" t="s">
+        <v>39</v>
+      </c>
+      <c r="B30" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="C30" s="5">
+        <v>-14.14</v>
+      </c>
+      <c r="D30" s="5">
+        <v>-18.82</v>
+      </c>
+      <c r="E30" s="7">
         <v>-4.68</v>
       </c>
-      <c r="D18" s="6">
-        <v>-10.03</v>
-      </c>
-      <c r="E18" s="8">
-        <v>-5.35</v>
-      </c>
-    </row>
-    <row r="19" spans="1:5">
-      <c r="A19" s="5" t="s">
+    </row>
+    <row r="31" spans="1:5">
+      <c r="A31" s="3" t="s">
+        <v>40</v>
+      </c>
+      <c r="B31" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="C31" s="5">
+        <v>-13.32</v>
+      </c>
+      <c r="D31" s="5">
+        <v>-12.66</v>
+      </c>
+      <c r="E31" s="6">
+        <v>0.66</v>
+      </c>
+    </row>
+    <row r="32" spans="1:5">
+      <c r="A32" s="3" t="s">
+        <v>41</v>
+      </c>
+      <c r="B32" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="C32" s="5">
+        <v>-7.21</v>
+      </c>
+      <c r="D32" s="5">
+        <v>-6.86</v>
+      </c>
+      <c r="E32" s="6">
+        <v>0.35</v>
+      </c>
+    </row>
+    <row r="33" spans="1:5">
+      <c r="A33" s="3" t="s">
         <v>42</v>
       </c>
-      <c r="B19" s="5" t="s">
-        <v>8</v>
-      </c>
-      <c r="C19" s="6">
-        <v>-0.9399999999999999</v>
-      </c>
-      <c r="D19" s="6">
-        <v>-0.34</v>
-      </c>
-      <c r="E19" s="7">
-        <v>0.6</v>
-      </c>
-    </row>
-    <row r="20" spans="1:5">
-      <c r="A20" s="5" t="s">
+      <c r="B33" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="C33" s="5">
+        <v>-10.95</v>
+      </c>
+      <c r="D33" s="5">
+        <v>-10.86</v>
+      </c>
+      <c r="E33" s="6">
+        <v>0.09</v>
+      </c>
+    </row>
+    <row r="34" spans="1:5">
+      <c r="A34" s="3" t="s">
         <v>43</v>
       </c>
-      <c r="B20" s="5" t="s">
-        <v>8</v>
-      </c>
-      <c r="C20" s="6">
-        <v>-5.35</v>
-      </c>
-      <c r="D20" s="6">
-        <v>-2.44</v>
-      </c>
-      <c r="E20" s="7">
-        <v>2.91</v>
-      </c>
-    </row>
-    <row r="21" spans="1:5">
-      <c r="A21" s="5" t="s">
+      <c r="B34" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="C34" s="5">
+        <v>7.32</v>
+      </c>
+      <c r="D34" s="5">
+        <v>1.1</v>
+      </c>
+      <c r="E34" s="7">
+        <v>-6.22</v>
+      </c>
+    </row>
+    <row r="35" spans="1:5">
+      <c r="A35" s="3" t="s">
         <v>37</v>
       </c>
-      <c r="B21" s="5" t="s">
-        <v>11</v>
-      </c>
-      <c r="C21" s="6">
-        <v>17.53</v>
-      </c>
-      <c r="D21" s="6">
-        <v>16</v>
-      </c>
-      <c r="E21" s="8">
-        <v>-1.53</v>
-      </c>
-    </row>
-    <row r="22" spans="1:5">
-      <c r="A22" s="5" t="s">
+      <c r="B35" s="3" t="s">
+        <v>6</v>
+      </c>
+      <c r="C35" s="5">
+        <v>-16</v>
+      </c>
+      <c r="D35" s="5">
+        <v>-16.27</v>
+      </c>
+      <c r="E35" s="7">
+        <v>-0.27</v>
+      </c>
+    </row>
+    <row r="36" spans="1:5">
+      <c r="A36" s="3" t="s">
         <v>38</v>
       </c>
-      <c r="B22" s="5" t="s">
-        <v>11</v>
-      </c>
-      <c r="C22" s="6">
-        <v>39.59</v>
-      </c>
-      <c r="D22" s="6">
-        <v>44.45</v>
-      </c>
-      <c r="E22" s="7">
-        <v>4.86</v>
-      </c>
-    </row>
-    <row r="23" spans="1:5">
-      <c r="A23" s="5" t="s">
+      <c r="B36" s="3" t="s">
+        <v>6</v>
+      </c>
+      <c r="C36" s="5">
+        <v>-41.72</v>
+      </c>
+      <c r="D36" s="5">
+        <v>-44.77</v>
+      </c>
+      <c r="E36" s="7">
+        <v>-3.05</v>
+      </c>
+    </row>
+    <row r="37" spans="1:5">
+      <c r="A37" s="3" t="s">
         <v>39</v>
       </c>
-      <c r="B23" s="5" t="s">
-        <v>11</v>
-      </c>
-      <c r="C23" s="6">
-        <v>-45.1</v>
-      </c>
-      <c r="D23" s="6">
-        <v>-46</v>
-      </c>
-      <c r="E23" s="8">
-        <v>-0.9</v>
-      </c>
-    </row>
-    <row r="24" spans="1:5">
-      <c r="A24" s="5" t="s">
+      <c r="B37" s="3" t="s">
+        <v>6</v>
+      </c>
+      <c r="C37" s="5">
+        <v>-46.44</v>
+      </c>
+      <c r="D37" s="5">
+        <v>-49.55</v>
+      </c>
+      <c r="E37" s="7">
+        <v>-3.11</v>
+      </c>
+    </row>
+    <row r="38" spans="1:5">
+      <c r="A38" s="3" t="s">
         <v>40</v>
       </c>
-      <c r="B24" s="5" t="s">
-        <v>11</v>
-      </c>
-      <c r="C24" s="6">
-        <v>-24.08</v>
-      </c>
-      <c r="D24" s="6">
-        <v>-22.76</v>
-      </c>
-      <c r="E24" s="7">
-        <v>1.32</v>
-      </c>
-    </row>
-    <row r="25" spans="1:5">
-      <c r="A25" s="5" t="s">
+      <c r="B38" s="3" t="s">
+        <v>6</v>
+      </c>
+      <c r="C38" s="5">
+        <v>-23.14</v>
+      </c>
+      <c r="D38" s="5">
+        <v>-22.08</v>
+      </c>
+      <c r="E38" s="6">
+        <v>1.06</v>
+      </c>
+    </row>
+    <row r="39" spans="1:5">
+      <c r="A39" s="3" t="s">
         <v>41</v>
       </c>
-      <c r="B25" s="5" t="s">
-        <v>11</v>
-      </c>
-      <c r="C25" s="6">
-        <v>-20.41</v>
-      </c>
-      <c r="D25" s="6">
-        <v>-22.7</v>
-      </c>
-      <c r="E25" s="8">
-        <v>-2.29</v>
-      </c>
-    </row>
-    <row r="26" spans="1:5">
-      <c r="A26" s="5" t="s">
+      <c r="B39" s="3" t="s">
+        <v>6</v>
+      </c>
+      <c r="C39" s="5">
+        <v>-22.67</v>
+      </c>
+      <c r="D39" s="5">
+        <v>-22.24</v>
+      </c>
+      <c r="E39" s="6">
+        <v>0.43</v>
+      </c>
+    </row>
+    <row r="40" spans="1:5">
+      <c r="A40" s="3" t="s">
         <v>42</v>
       </c>
-      <c r="B26" s="5" t="s">
-        <v>11</v>
-      </c>
-      <c r="C26" s="6">
-        <v>-16.17</v>
-      </c>
-      <c r="D26" s="6">
-        <v>-13.84</v>
-      </c>
-      <c r="E26" s="7">
-        <v>2.33</v>
-      </c>
-    </row>
-    <row r="27" spans="1:5">
-      <c r="A27" s="5" t="s">
+      <c r="B40" s="3" t="s">
+        <v>6</v>
+      </c>
+      <c r="C40" s="5">
+        <v>-18.98</v>
+      </c>
+      <c r="D40" s="5">
+        <v>-18.96</v>
+      </c>
+      <c r="E40" s="6">
+        <v>0.02</v>
+      </c>
+    </row>
+    <row r="41" spans="1:5">
+      <c r="A41" s="3" t="s">
         <v>43</v>
       </c>
-      <c r="B27" s="5" t="s">
-        <v>11</v>
-      </c>
-      <c r="C27" s="6">
+      <c r="B41" s="3" t="s">
+        <v>6</v>
+      </c>
+      <c r="C41" s="5">
+        <v>-19.52</v>
+      </c>
+      <c r="D41" s="5">
+        <v>-23.92</v>
+      </c>
+      <c r="E41" s="7">
+        <v>-4.4</v>
+      </c>
+    </row>
+    <row r="42" spans="1:5">
+      <c r="A42" s="3" t="s">
+        <v>37</v>
+      </c>
+      <c r="B42" s="3" t="s">
+        <v>2</v>
+      </c>
+      <c r="C42" s="5">
+        <v>10383</v>
+      </c>
+      <c r="D42" s="5">
+        <v>10350</v>
+      </c>
+      <c r="E42" s="7">
+        <v>-33</v>
+      </c>
+    </row>
+    <row r="43" spans="1:5">
+      <c r="A43" s="3" t="s">
+        <v>38</v>
+      </c>
+      <c r="B43" s="3" t="s">
+        <v>2</v>
+      </c>
+      <c r="C43" s="5">
+        <v>390.6</v>
+      </c>
+      <c r="D43" s="5">
+        <v>370.15</v>
+      </c>
+      <c r="E43" s="7">
+        <v>-20.45</v>
+      </c>
+    </row>
+    <row r="44" spans="1:5">
+      <c r="A44" s="3" t="s">
+        <v>39</v>
+      </c>
+      <c r="B44" s="3" t="s">
+        <v>2</v>
+      </c>
+      <c r="C44" s="5">
+        <v>283.8</v>
+      </c>
+      <c r="D44" s="5">
+        <v>267.3</v>
+      </c>
+      <c r="E44" s="7">
+        <v>-16.5</v>
+      </c>
+    </row>
+    <row r="45" spans="1:5">
+      <c r="A45" s="3" t="s">
+        <v>40</v>
+      </c>
+      <c r="B45" s="3" t="s">
+        <v>2</v>
+      </c>
+      <c r="C45" s="5">
+        <v>1668</v>
+      </c>
+      <c r="D45" s="5">
+        <v>1667.6</v>
+      </c>
+      <c r="E45" s="7">
+        <v>-0.4</v>
+      </c>
+    </row>
+    <row r="46" spans="1:5">
+      <c r="A46" s="3" t="s">
+        <v>41</v>
+      </c>
+      <c r="B46" s="3" t="s">
+        <v>2</v>
+      </c>
+      <c r="C46" s="5">
+        <v>10160</v>
+      </c>
+      <c r="D46" s="5">
+        <v>10217</v>
+      </c>
+      <c r="E46" s="6">
+        <v>57</v>
+      </c>
+    </row>
+    <row r="47" spans="1:5">
+      <c r="A47" s="3" t="s">
+        <v>42</v>
+      </c>
+      <c r="B47" s="3" t="s">
+        <v>2</v>
+      </c>
+      <c r="C47" s="5">
+        <v>938.9</v>
+      </c>
+      <c r="D47" s="5">
+        <v>939.1</v>
+      </c>
+      <c r="E47" s="6">
+        <v>0.2</v>
+      </c>
+    </row>
+    <row r="48" spans="1:5">
+      <c r="A48" s="3" t="s">
+        <v>43</v>
+      </c>
+      <c r="B48" s="3" t="s">
+        <v>2</v>
+      </c>
+      <c r="C48" s="5">
+        <v>149.63</v>
+      </c>
+      <c r="D48" s="5">
+        <v>141.45</v>
+      </c>
+      <c r="E48" s="7">
+        <v>-8.18</v>
+      </c>
+    </row>
+    <row r="49" spans="1:5">
+      <c r="A49" s="3" t="s">
+        <v>37</v>
+      </c>
+      <c r="B49" s="3" t="s">
+        <v>13</v>
+      </c>
+      <c r="C49" s="5">
+        <v>71</v>
+      </c>
+      <c r="D49" s="5">
+        <v>99</v>
+      </c>
+      <c r="E49" s="6">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="50" spans="1:5">
+      <c r="A50" s="3" t="s">
+        <v>38</v>
+      </c>
+      <c r="B50" s="3" t="s">
+        <v>13</v>
+      </c>
+      <c r="C50" s="5">
+        <v>85</v>
+      </c>
+      <c r="D50" s="5">
+        <v>71</v>
+      </c>
+      <c r="E50" s="7">
+        <v>-14</v>
+      </c>
+    </row>
+    <row r="51" spans="1:5">
+      <c r="A51" s="3" t="s">
+        <v>43</v>
+      </c>
+      <c r="B51" s="3" t="s">
+        <v>13</v>
+      </c>
+      <c r="C51" s="5">
+        <v>99</v>
+      </c>
+      <c r="D51" s="5">
+        <v>85</v>
+      </c>
+      <c r="E51" s="7">
+        <v>-14</v>
+      </c>
+    </row>
+    <row r="52" spans="1:5">
+      <c r="A52" s="3" t="s">
+        <v>37</v>
+      </c>
+      <c r="B52" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="C52" s="5">
+        <v>46.91</v>
+      </c>
+      <c r="D52" s="5">
+        <v>46.08</v>
+      </c>
+      <c r="E52" s="7">
+        <v>-0.83</v>
+      </c>
+    </row>
+    <row r="53" spans="1:5">
+      <c r="A53" s="3" t="s">
+        <v>38</v>
+      </c>
+      <c r="B53" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="C53" s="5">
+        <v>30</v>
+      </c>
+      <c r="D53" s="5">
+        <v>26.56</v>
+      </c>
+      <c r="E53" s="7">
+        <v>-3.44</v>
+      </c>
+    </row>
+    <row r="54" spans="1:5">
+      <c r="A54" s="3" t="s">
+        <v>39</v>
+      </c>
+      <c r="B54" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="C54" s="5">
+        <v>37.96</v>
+      </c>
+      <c r="D54" s="5">
+        <v>30.53</v>
+      </c>
+      <c r="E54" s="7">
+        <v>-7.43</v>
+      </c>
+    </row>
+    <row r="55" spans="1:5">
+      <c r="A55" s="3" t="s">
+        <v>40</v>
+      </c>
+      <c r="B55" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="C55" s="5">
+        <v>34.94</v>
+      </c>
+      <c r="D55" s="5">
+        <v>34.88</v>
+      </c>
+      <c r="E55" s="7">
+        <v>-0.06</v>
+      </c>
+    </row>
+    <row r="56" spans="1:5">
+      <c r="A56" s="3" t="s">
+        <v>41</v>
+      </c>
+      <c r="B56" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="C56" s="5">
+        <v>34.45</v>
+      </c>
+      <c r="D56" s="5">
+        <v>35.97</v>
+      </c>
+      <c r="E56" s="6">
+        <v>1.52</v>
+      </c>
+    </row>
+    <row r="57" spans="1:5">
+      <c r="A57" s="3" t="s">
+        <v>42</v>
+      </c>
+      <c r="B57" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="C57" s="5">
+        <v>43.44</v>
+      </c>
+      <c r="D57" s="5">
+        <v>43.5</v>
+      </c>
+      <c r="E57" s="6">
+        <v>0.06</v>
+      </c>
+    </row>
+    <row r="58" spans="1:5">
+      <c r="A58" s="3" t="s">
+        <v>43</v>
+      </c>
+      <c r="B58" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="C58" s="5">
+        <v>41.74</v>
+      </c>
+      <c r="D58" s="5">
+        <v>35.9</v>
+      </c>
+      <c r="E58" s="7">
+        <v>-5.84</v>
+      </c>
+    </row>
+    <row r="59" spans="1:5">
+      <c r="A59" s="3" t="s">
+        <v>37</v>
+      </c>
+      <c r="B59" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="C59" s="5">
+        <v>-22.88</v>
+      </c>
+      <c r="D59" s="5">
+        <v>6.17</v>
+      </c>
+      <c r="E59" s="6">
+        <v>29.05</v>
+      </c>
+    </row>
+    <row r="60" spans="1:5">
+      <c r="A60" s="3" t="s">
+        <v>38</v>
+      </c>
+      <c r="B60" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="C60" s="5">
+        <v>-44.22</v>
+      </c>
+      <c r="D60" s="5">
+        <v>-54.64</v>
+      </c>
+      <c r="E60" s="7">
+        <v>-10.42</v>
+      </c>
+    </row>
+    <row r="61" spans="1:5">
+      <c r="A61" s="3" t="s">
+        <v>39</v>
+      </c>
+      <c r="B61" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="C61" s="5">
+        <v>-37.31</v>
+      </c>
+      <c r="D61" s="5">
+        <v>-51.79</v>
+      </c>
+      <c r="E61" s="7">
+        <v>-14.48</v>
+      </c>
+    </row>
+    <row r="62" spans="1:5">
+      <c r="A62" s="3" t="s">
+        <v>40</v>
+      </c>
+      <c r="B62" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="C62" s="5">
         <v>14.81</v>
       </c>
-      <c r="D27" s="6">
-        <v>15.46</v>
-      </c>
-      <c r="E27" s="7">
-        <v>0.65</v>
-      </c>
-    </row>
-    <row r="28" spans="1:5">
-      <c r="A28" s="5" t="s">
-        <v>37</v>
-      </c>
-      <c r="B28" s="5" t="s">
-        <v>10</v>
-      </c>
-      <c r="C28" s="6">
-        <v>-7.82</v>
-      </c>
-      <c r="D28" s="6">
-        <v>-8.42</v>
-      </c>
-      <c r="E28" s="8">
-        <v>-0.6</v>
-      </c>
-    </row>
-    <row r="29" spans="1:5">
-      <c r="A29" s="5" t="s">
-        <v>38</v>
-      </c>
-      <c r="B29" s="5" t="s">
-        <v>10</v>
-      </c>
-      <c r="C29" s="6">
-        <v>-28.19</v>
-      </c>
-      <c r="D29" s="6">
-        <v>-27.19</v>
-      </c>
-      <c r="E29" s="7">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="30" spans="1:5">
-      <c r="A30" s="5" t="s">
-        <v>39</v>
-      </c>
-      <c r="B30" s="5" t="s">
-        <v>10</v>
-      </c>
-      <c r="C30" s="6">
-        <v>-10.52</v>
-      </c>
-      <c r="D30" s="6">
-        <v>-14.14</v>
-      </c>
-      <c r="E30" s="8">
-        <v>-3.62</v>
-      </c>
-    </row>
-    <row r="31" spans="1:5">
-      <c r="A31" s="5" t="s">
-        <v>40</v>
-      </c>
-      <c r="B31" s="5" t="s">
-        <v>10</v>
-      </c>
-      <c r="C31" s="6">
-        <v>-14.29</v>
-      </c>
-      <c r="D31" s="6">
-        <v>-13.32</v>
-      </c>
-      <c r="E31" s="7">
-        <v>0.97</v>
-      </c>
-    </row>
-    <row r="32" spans="1:5">
-      <c r="A32" s="5" t="s">
+      <c r="D62" s="5">
+        <v>-27.67</v>
+      </c>
+      <c r="E62" s="7">
+        <v>-42.48</v>
+      </c>
+    </row>
+    <row r="63" spans="1:5">
+      <c r="A63" s="3" t="s">
         <v>41</v>
       </c>
-      <c r="B32" s="5" t="s">
-        <v>10</v>
-      </c>
-      <c r="C32" s="6">
-        <v>-3.42</v>
-      </c>
-      <c r="D32" s="6">
-        <v>-7.21</v>
-      </c>
-      <c r="E32" s="8">
-        <v>-3.79</v>
-      </c>
-    </row>
-    <row r="33" spans="1:5">
-      <c r="A33" s="5" t="s">
+      <c r="B63" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="C63" s="5">
+        <v>36.92</v>
+      </c>
+      <c r="D63" s="5">
+        <v>-52.94</v>
+      </c>
+      <c r="E63" s="7">
+        <v>-89.86</v>
+      </c>
+    </row>
+    <row r="64" spans="1:5">
+      <c r="A64" s="3" t="s">
         <v>42</v>
       </c>
-      <c r="B33" s="5" t="s">
-        <v>10</v>
-      </c>
-      <c r="C33" s="6">
-        <v>-12.51</v>
-      </c>
-      <c r="D33" s="6">
-        <v>-10.95</v>
-      </c>
-      <c r="E33" s="7">
-        <v>1.56</v>
-      </c>
-    </row>
-    <row r="34" spans="1:5">
-      <c r="A34" s="5" t="s">
+      <c r="B64" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="C64" s="5">
+        <v>5.48</v>
+      </c>
+      <c r="D64" s="5">
+        <v>13.43</v>
+      </c>
+      <c r="E64" s="6">
+        <v>7.95</v>
+      </c>
+    </row>
+    <row r="65" spans="1:5">
+      <c r="A65" s="3" t="s">
         <v>43</v>
       </c>
-      <c r="B34" s="5" t="s">
-        <v>10</v>
-      </c>
-      <c r="C34" s="6">
-        <v>6.7</v>
-      </c>
-      <c r="D34" s="6">
-        <v>7.32</v>
-      </c>
-      <c r="E34" s="7">
-        <v>0.62</v>
-      </c>
-    </row>
-    <row r="35" spans="1:5">
-      <c r="A35" s="5" t="s">
-        <v>37</v>
-      </c>
-      <c r="B35" s="5" t="s">
-        <v>6</v>
-      </c>
-      <c r="C35" s="6">
-        <v>-15.18</v>
-      </c>
-      <c r="D35" s="6">
-        <v>-16</v>
-      </c>
-      <c r="E35" s="8">
-        <v>-0.82</v>
-      </c>
-    </row>
-    <row r="36" spans="1:5">
-      <c r="A36" s="5" t="s">
-        <v>38</v>
-      </c>
-      <c r="B36" s="5" t="s">
-        <v>6</v>
-      </c>
-      <c r="C36" s="6">
-        <v>-43.11</v>
-      </c>
-      <c r="D36" s="6">
-        <v>-41.72</v>
-      </c>
-      <c r="E36" s="7">
-        <v>1.39</v>
-      </c>
-    </row>
-    <row r="37" spans="1:5">
-      <c r="A37" s="5" t="s">
-        <v>39</v>
-      </c>
-      <c r="B37" s="5" t="s">
-        <v>6</v>
-      </c>
-      <c r="C37" s="6">
-        <v>-44.77</v>
-      </c>
-      <c r="D37" s="6">
-        <v>-46.44</v>
-      </c>
-      <c r="E37" s="8">
-        <v>-1.67</v>
-      </c>
-    </row>
-    <row r="38" spans="1:5">
-      <c r="A38" s="5" t="s">
-        <v>40</v>
-      </c>
-      <c r="B38" s="5" t="s">
-        <v>6</v>
-      </c>
-      <c r="C38" s="6">
-        <v>-23.86</v>
-      </c>
-      <c r="D38" s="6">
-        <v>-23.14</v>
-      </c>
-      <c r="E38" s="7">
-        <v>0.72</v>
-      </c>
-    </row>
-    <row r="39" spans="1:5">
-      <c r="A39" s="5" t="s">
-        <v>41</v>
-      </c>
-      <c r="B39" s="5" t="s">
-        <v>6</v>
-      </c>
-      <c r="C39" s="6">
-        <v>-20.41</v>
-      </c>
-      <c r="D39" s="6">
-        <v>-22.67</v>
-      </c>
-      <c r="E39" s="8">
-        <v>-2.26</v>
-      </c>
-    </row>
-    <row r="40" spans="1:5">
-      <c r="A40" s="5" t="s">
-        <v>42</v>
-      </c>
-      <c r="B40" s="5" t="s">
-        <v>6</v>
-      </c>
-      <c r="C40" s="6">
-        <v>-20.84</v>
-      </c>
-      <c r="D40" s="6">
-        <v>-18.98</v>
-      </c>
-      <c r="E40" s="7">
-        <v>1.86</v>
-      </c>
-    </row>
-    <row r="41" spans="1:5">
-      <c r="A41" s="5" t="s">
-        <v>43</v>
-      </c>
-      <c r="B41" s="5" t="s">
-        <v>6</v>
-      </c>
-      <c r="C41" s="6">
-        <v>-20.17</v>
-      </c>
-      <c r="D41" s="6">
-        <v>-19.52</v>
-      </c>
-      <c r="E41" s="7">
-        <v>0.65</v>
-      </c>
-    </row>
-    <row r="42" spans="1:5">
-      <c r="A42" s="5" t="s">
-        <v>37</v>
-      </c>
-      <c r="B42" s="5" t="s">
-        <v>2</v>
-      </c>
-      <c r="C42" s="6">
-        <v>10485</v>
-      </c>
-      <c r="D42" s="6">
-        <v>10383</v>
-      </c>
-      <c r="E42" s="8">
-        <v>-102</v>
-      </c>
-    </row>
-    <row r="43" spans="1:5">
-      <c r="A43" s="5" t="s">
-        <v>38</v>
-      </c>
-      <c r="B43" s="5" t="s">
-        <v>2</v>
-      </c>
-      <c r="C43" s="6">
-        <v>381.3</v>
-      </c>
-      <c r="D43" s="6">
-        <v>390.6</v>
-      </c>
-      <c r="E43" s="7">
-        <v>9.300000000000001</v>
-      </c>
-    </row>
-    <row r="44" spans="1:5">
-      <c r="A44" s="5" t="s">
-        <v>39</v>
-      </c>
-      <c r="B44" s="5" t="s">
-        <v>2</v>
-      </c>
-      <c r="C44" s="6">
-        <v>292.65</v>
-      </c>
-      <c r="D44" s="6">
-        <v>283.8</v>
-      </c>
-      <c r="E44" s="8">
-        <v>-8.85</v>
-      </c>
-    </row>
-    <row r="45" spans="1:5">
-      <c r="A45" s="5" t="s">
-        <v>40</v>
-      </c>
-      <c r="B45" s="5" t="s">
-        <v>2</v>
-      </c>
-      <c r="C45" s="6">
-        <v>1652.4</v>
-      </c>
-      <c r="D45" s="6">
-        <v>1668</v>
-      </c>
-      <c r="E45" s="7">
-        <v>15.6</v>
-      </c>
-    </row>
-    <row r="46" spans="1:5">
-      <c r="A46" s="5" t="s">
-        <v>41</v>
-      </c>
-      <c r="B46" s="5" t="s">
-        <v>2</v>
-      </c>
-      <c r="C46" s="6">
-        <v>10461</v>
-      </c>
-      <c r="D46" s="6">
-        <v>10160</v>
-      </c>
-      <c r="E46" s="8">
-        <v>-301</v>
-      </c>
-    </row>
-    <row r="47" spans="1:5">
-      <c r="A47" s="5" t="s">
-        <v>42</v>
-      </c>
-      <c r="B47" s="5" t="s">
-        <v>2</v>
-      </c>
-      <c r="C47" s="6">
-        <v>917.25</v>
-      </c>
-      <c r="D47" s="6">
-        <v>938.9</v>
-      </c>
-      <c r="E47" s="7">
-        <v>21.65</v>
-      </c>
-    </row>
-    <row r="48" spans="1:5">
-      <c r="A48" s="5" t="s">
-        <v>43</v>
-      </c>
-      <c r="B48" s="5" t="s">
-        <v>2</v>
-      </c>
-      <c r="C48" s="6">
-        <v>148.42</v>
-      </c>
-      <c r="D48" s="6">
-        <v>149.63</v>
-      </c>
-      <c r="E48" s="7">
-        <v>1.21</v>
-      </c>
-    </row>
-    <row r="49" spans="1:5">
-      <c r="A49" s="5" t="s">
-        <v>37</v>
-      </c>
-      <c r="B49" s="5" t="s">
-        <v>13</v>
-      </c>
-      <c r="C49" s="6">
-        <v>85</v>
-      </c>
-      <c r="D49" s="6">
-        <v>71</v>
-      </c>
-      <c r="E49" s="8">
-        <v>-14</v>
-      </c>
-    </row>
-    <row r="50" spans="1:5">
-      <c r="A50" s="5" t="s">
-        <v>38</v>
-      </c>
-      <c r="B50" s="5" t="s">
-        <v>13</v>
-      </c>
-      <c r="C50" s="6">
-        <v>71</v>
-      </c>
-      <c r="D50" s="6">
-        <v>85</v>
-      </c>
-      <c r="E50" s="7">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="51" spans="1:5">
-      <c r="A51" s="5" t="s">
-        <v>41</v>
-      </c>
-      <c r="B51" s="5" t="s">
-        <v>13</v>
-      </c>
-      <c r="C51" s="6">
-        <v>57</v>
-      </c>
-      <c r="D51" s="6">
-        <v>43</v>
-      </c>
-      <c r="E51" s="8">
-        <v>-14</v>
-      </c>
-    </row>
-    <row r="52" spans="1:5">
-      <c r="A52" s="5" t="s">
-        <v>42</v>
-      </c>
-      <c r="B52" s="5" t="s">
-        <v>13</v>
-      </c>
-      <c r="C52" s="6">
-        <v>43</v>
-      </c>
-      <c r="D52" s="6">
-        <v>57</v>
-      </c>
-      <c r="E52" s="7">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="53" spans="1:5">
-      <c r="A53" s="5" t="s">
-        <v>37</v>
-      </c>
-      <c r="B53" s="5" t="s">
-        <v>24</v>
-      </c>
-      <c r="C53" s="6">
-        <v>49.47</v>
-      </c>
-      <c r="D53" s="6">
-        <v>46.91</v>
-      </c>
-      <c r="E53" s="8">
-        <v>-2.56</v>
-      </c>
-    </row>
-    <row r="54" spans="1:5">
-      <c r="A54" s="5" t="s">
-        <v>38</v>
-      </c>
-      <c r="B54" s="5" t="s">
-        <v>24</v>
-      </c>
-      <c r="C54" s="6">
-        <v>25.96</v>
-      </c>
-      <c r="D54" s="6">
-        <v>30</v>
-      </c>
-      <c r="E54" s="7">
-        <v>4.04</v>
-      </c>
-    </row>
-    <row r="55" spans="1:5">
-      <c r="A55" s="5" t="s">
-        <v>39</v>
-      </c>
-      <c r="B55" s="5" t="s">
-        <v>24</v>
-      </c>
-      <c r="C55" s="6">
-        <v>43.2</v>
-      </c>
-      <c r="D55" s="6">
-        <v>37.96</v>
-      </c>
-      <c r="E55" s="8">
-        <v>-5.24</v>
-      </c>
-    </row>
-    <row r="56" spans="1:5">
-      <c r="A56" s="5" t="s">
-        <v>40</v>
-      </c>
-      <c r="B56" s="5" t="s">
-        <v>24</v>
-      </c>
-      <c r="C56" s="6">
-        <v>30.66</v>
-      </c>
-      <c r="D56" s="6">
-        <v>34.94</v>
-      </c>
-      <c r="E56" s="7">
-        <v>4.28</v>
-      </c>
-    </row>
-    <row r="57" spans="1:5">
-      <c r="A57" s="5" t="s">
-        <v>41</v>
-      </c>
-      <c r="B57" s="5" t="s">
-        <v>24</v>
-      </c>
-      <c r="C57" s="6">
-        <v>39</v>
-      </c>
-      <c r="D57" s="6">
-        <v>34.45</v>
-      </c>
-      <c r="E57" s="8">
-        <v>-4.55</v>
-      </c>
-    </row>
-    <row r="58" spans="1:5">
-      <c r="A58" s="5" t="s">
-        <v>42</v>
-      </c>
-      <c r="B58" s="5" t="s">
-        <v>24</v>
-      </c>
-      <c r="C58" s="6">
-        <v>36.73</v>
-      </c>
-      <c r="D58" s="6">
-        <v>43.44</v>
-      </c>
-      <c r="E58" s="7">
-        <v>6.71</v>
-      </c>
-    </row>
-    <row r="59" spans="1:5">
-      <c r="A59" s="5" t="s">
-        <v>43</v>
-      </c>
-      <c r="B59" s="5" t="s">
-        <v>24</v>
-      </c>
-      <c r="C59" s="6">
-        <v>40.41</v>
-      </c>
-      <c r="D59" s="6">
-        <v>41.74</v>
-      </c>
-      <c r="E59" s="7">
-        <v>1.33</v>
-      </c>
-    </row>
-    <row r="60" spans="1:5">
-      <c r="A60" s="5" t="s">
-        <v>37</v>
-      </c>
-      <c r="B60" s="5" t="s">
+      <c r="B65" s="3" t="s">
         <v>31</v>
       </c>
-      <c r="C60" s="6">
-        <v>205.37</v>
-      </c>
-      <c r="D60" s="6">
-        <v>-22.88</v>
-      </c>
-      <c r="E60" s="8">
-        <v>-228.25</v>
-      </c>
-    </row>
-    <row r="61" spans="1:5">
-      <c r="A61" s="5" t="s">
-        <v>38</v>
-      </c>
-      <c r="B61" s="5" t="s">
-        <v>31</v>
-      </c>
-      <c r="C61" s="6">
-        <v>-69.27</v>
-      </c>
-      <c r="D61" s="6">
-        <v>-44.22</v>
-      </c>
-      <c r="E61" s="7">
-        <v>25.05</v>
-      </c>
-    </row>
-    <row r="62" spans="1:5">
-      <c r="A62" s="5" t="s">
-        <v>39</v>
-      </c>
-      <c r="B62" s="5" t="s">
-        <v>31</v>
-      </c>
-      <c r="C62" s="6">
-        <v>1223.89</v>
-      </c>
-      <c r="D62" s="6">
-        <v>-37.31</v>
-      </c>
-      <c r="E62" s="8">
-        <v>-1261.2</v>
-      </c>
-    </row>
-    <row r="63" spans="1:5">
-      <c r="A63" s="5" t="s">
-        <v>40</v>
-      </c>
-      <c r="B63" s="5" t="s">
-        <v>31</v>
-      </c>
-      <c r="C63" s="6">
-        <v>36.35</v>
-      </c>
-      <c r="D63" s="6">
-        <v>14.81</v>
-      </c>
-      <c r="E63" s="8">
-        <v>-21.54</v>
-      </c>
-    </row>
-    <row r="64" spans="1:5">
-      <c r="A64" s="5" t="s">
-        <v>41</v>
-      </c>
-      <c r="B64" s="5" t="s">
-        <v>31</v>
-      </c>
-      <c r="C64" s="6">
-        <v>-39.29</v>
-      </c>
-      <c r="D64" s="6">
-        <v>36.92</v>
-      </c>
-      <c r="E64" s="7">
-        <v>76.20999999999999</v>
-      </c>
-    </row>
-    <row r="65" spans="1:5">
-      <c r="A65" s="5" t="s">
-        <v>42</v>
-      </c>
-      <c r="B65" s="5" t="s">
-        <v>31</v>
-      </c>
-      <c r="C65" s="6">
-        <v>-33.3</v>
-      </c>
-      <c r="D65" s="6">
-        <v>5.48</v>
+      <c r="C65" s="5">
+        <v>-69.48999999999999</v>
+      </c>
+      <c r="D65" s="5">
+        <v>-73.93000000000001</v>
       </c>
       <c r="E65" s="7">
-        <v>38.78</v>
-      </c>
-    </row>
-    <row r="66" spans="1:5">
-      <c r="A66" s="5" t="s">
-        <v>43</v>
-      </c>
-      <c r="B66" s="5" t="s">
-        <v>31</v>
-      </c>
-      <c r="C66" s="6">
-        <v>-80.23999999999999</v>
-      </c>
-      <c r="D66" s="6">
-        <v>-69.48999999999999</v>
-      </c>
-      <c r="E66" s="7">
-        <v>10.75</v>
+        <v>-4.44</v>
       </c>
     </row>
   </sheetData>
@@ -2969,60 +2889,60 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:9" ht="28" customHeight="1">
-      <c r="A1" s="9" t="s">
+      <c r="A1" s="8" t="s">
         <v>1</v>
       </c>
-      <c r="B1" s="9" t="s">
-        <v>64</v>
-      </c>
-      <c r="C1" s="9" t="s">
-        <v>65</v>
-      </c>
-      <c r="D1" s="9" t="s">
-        <v>66</v>
-      </c>
-      <c r="E1" s="9" t="s">
-        <v>67</v>
-      </c>
-      <c r="F1" s="9" t="s">
-        <v>68</v>
-      </c>
-      <c r="G1" s="9" t="s">
-        <v>69</v>
-      </c>
-      <c r="H1" s="9" t="s">
-        <v>70</v>
-      </c>
-      <c r="I1" s="9" t="s">
-        <v>71</v>
+      <c r="B1" s="8" t="s">
+        <v>55</v>
+      </c>
+      <c r="C1" s="8" t="s">
+        <v>56</v>
+      </c>
+      <c r="D1" s="8" t="s">
+        <v>57</v>
+      </c>
+      <c r="E1" s="8" t="s">
+        <v>58</v>
+      </c>
+      <c r="F1" s="8" t="s">
+        <v>59</v>
+      </c>
+      <c r="G1" s="8" t="s">
+        <v>60</v>
+      </c>
+      <c r="H1" s="8" t="s">
+        <v>61</v>
+      </c>
+      <c r="I1" s="8" t="s">
+        <v>62</v>
       </c>
     </row>
     <row r="2" spans="1:9">
-      <c r="A2" s="10" t="s">
+      <c r="A2" s="9" t="s">
         <v>44</v>
       </c>
-      <c r="B2" s="11">
-        <v>44.24</v>
-      </c>
-      <c r="C2" s="12">
+      <c r="B2" s="10">
+        <v>44.2</v>
+      </c>
+      <c r="C2" s="11">
         <v>7</v>
       </c>
-      <c r="D2" s="11">
-        <v>38.5</v>
-      </c>
-      <c r="E2" s="11">
+      <c r="D2" s="10">
+        <v>36.2</v>
+      </c>
+      <c r="E2" s="10">
         <v>28.6</v>
       </c>
-      <c r="F2" s="11">
-        <v>-8.9</v>
-      </c>
-      <c r="G2" s="11">
-        <v>-10.6</v>
-      </c>
-      <c r="H2" s="11">
+      <c r="F2" s="10">
+        <v>-10.3</v>
+      </c>
+      <c r="G2" s="10">
+        <v>-12.7</v>
+      </c>
+      <c r="H2" s="10">
         <v>57</v>
       </c>
-      <c r="I2" s="11">
+      <c r="I2" s="10">
         <v>14.3</v>
       </c>
     </row>
@@ -3124,49 +3044,49 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:7">
-      <c r="A1" s="13" t="s">
+      <c r="A1" s="12" t="s">
         <v>37</v>
       </c>
-      <c r="B1" s="13" t="s">
+      <c r="B1" s="12" t="s">
         <v>41</v>
       </c>
-      <c r="C1" s="13" t="s">
+      <c r="C1" s="12" t="s">
         <v>38</v>
       </c>
-      <c r="D1" s="13" t="s">
+      <c r="D1" s="12" t="s">
         <v>42</v>
       </c>
-      <c r="E1" s="13" t="s">
+      <c r="E1" s="12" t="s">
         <v>43</v>
       </c>
-      <c r="F1" s="13" t="s">
+      <c r="F1" s="12" t="s">
         <v>40</v>
       </c>
-      <c r="G1" s="13" t="s">
+      <c r="G1" s="12" t="s">
         <v>39</v>
       </c>
     </row>
     <row r="2" spans="1:7">
-      <c r="A2" s="14">
-        <v>0.2571</v>
-      </c>
-      <c r="B2" s="14">
-        <v>0.173</v>
-      </c>
-      <c r="C2" s="14">
-        <v>0.1295</v>
-      </c>
-      <c r="D2" s="14">
-        <v>0.0528</v>
-      </c>
-      <c r="E2" s="14">
-        <v>0.0367</v>
-      </c>
-      <c r="F2" s="14">
-        <v>-0.0128</v>
-      </c>
-      <c r="G2" s="14">
-        <v>-0.2267</v>
+      <c r="A2" s="13">
+        <v>0.2554</v>
+      </c>
+      <c r="B2" s="13">
+        <v>0.1777</v>
+      </c>
+      <c r="C2" s="13">
+        <v>0.1137</v>
+      </c>
+      <c r="D2" s="13">
+        <v>0.0525</v>
+      </c>
+      <c r="E2" s="13">
+        <v>0.0288</v>
+      </c>
+      <c r="F2" s="13">
+        <v>-0.01</v>
+      </c>
+      <c r="G2" s="13">
+        <v>-0.2346</v>
       </c>
     </row>
   </sheetData>
